--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -713,12 +713,12 @@
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
+          <t>sf90</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
           <t>sgt</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>sf90</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
@@ -913,10 +913,10 @@
       <c r="Z2" s="4" t="n"/>
       <c r="AA2" s="4" t="n"/>
       <c r="AB2" s="4" t="n"/>
-      <c r="AC2" s="4" t="n"/>
-      <c r="AD2" s="4" t="n">
+      <c r="AC2" s="4" t="n">
         <v>19.2</v>
       </c>
+      <c r="AD2" s="4" t="n"/>
       <c r="AE2" s="4" t="n"/>
       <c r="AF2" s="4" t="n">
         <v>18.97</v>
@@ -978,7 +978,9 @@
       </c>
       <c r="J3" s="4" t="n"/>
       <c r="K3" s="4" t="n"/>
-      <c r="L3" s="4" t="n"/>
+      <c r="L3" s="4" t="n">
+        <v>27.59</v>
+      </c>
       <c r="M3" s="4" t="n"/>
       <c r="N3" s="4" t="n"/>
       <c r="O3" s="4" t="n">
@@ -1177,10 +1179,10 @@
         <v>17.5</v>
       </c>
       <c r="AB5" s="4" t="n"/>
-      <c r="AC5" s="4" t="n">
+      <c r="AC5" s="4" t="n"/>
+      <c r="AD5" s="4" t="n">
         <v>18.39</v>
       </c>
-      <c r="AD5" s="4" t="n"/>
       <c r="AE5" s="4" t="n">
         <v>18.46</v>
       </c>
@@ -1271,10 +1273,10 @@
       <c r="Z6" s="4" t="n"/>
       <c r="AA6" s="4" t="n"/>
       <c r="AB6" s="4" t="n"/>
-      <c r="AC6" s="4" t="n"/>
-      <c r="AD6" s="4" t="n">
+      <c r="AC6" s="4" t="n">
         <v>18.16</v>
       </c>
+      <c r="AD6" s="4" t="n"/>
       <c r="AE6" s="4" t="n"/>
       <c r="AF6" s="4" t="n"/>
       <c r="AG6" s="4" t="n">
@@ -1406,7 +1408,7 @@
         <v>26.6</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>26.2</v>
+        <v>26.09</v>
       </c>
       <c r="H8" s="4" t="n">
         <v>26.73</v>
@@ -1428,7 +1430,9 @@
       <c r="Q8" s="4" t="n">
         <v>27.3</v>
       </c>
-      <c r="R8" s="4" t="n"/>
+      <c r="R8" s="4" t="n">
+        <v>26.79</v>
+      </c>
       <c r="S8" s="4" t="n"/>
       <c r="T8" s="4" t="n"/>
       <c r="U8" s="4" t="n"/>
@@ -1527,10 +1531,10 @@
       <c r="Z9" s="4" t="n"/>
       <c r="AA9" s="4" t="n"/>
       <c r="AB9" s="4" t="n"/>
-      <c r="AC9" s="4" t="n">
+      <c r="AC9" s="4" t="n"/>
+      <c r="AD9" s="4" t="n">
         <v>20.19</v>
       </c>
-      <c r="AD9" s="4" t="n"/>
       <c r="AE9" s="4" t="n">
         <v>20.39</v>
       </c>
@@ -1942,7 +1946,7 @@
         <v>25.1</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>24.9</v>
+        <v>24.92</v>
       </c>
       <c r="L14" s="4" t="n"/>
       <c r="M14" s="4" t="n">
@@ -1952,7 +1956,7 @@
         <v>26.19</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>24.9</v>
+        <v>24.87</v>
       </c>
       <c r="P14" s="4" t="n"/>
       <c r="Q14" s="4" t="n">
@@ -2014,40 +2018,44 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>27.7</v>
+        <v>27.59</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>27.4</v>
+        <v>27.35</v>
       </c>
       <c r="E15" s="4" t="n">
+        <v>26.79</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>27.19</v>
+      </c>
+      <c r="G15" s="4" t="n">
         <v>26.9</v>
       </c>
-      <c r="F15" s="4" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>27.45</v>
-      </c>
       <c r="H15" s="4" t="n">
-        <v>28</v>
+        <v>27.65</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>28.84</v>
+        <v>27.99</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>28.2</v>
       </c>
       <c r="K15" s="4" t="n"/>
       <c r="L15" s="4" t="n">
-        <v>27.69</v>
+        <v>27.42</v>
       </c>
       <c r="M15" s="4" t="n"/>
-      <c r="N15" s="4" t="n"/>
+      <c r="N15" s="4" t="n">
+        <v>29.19</v>
+      </c>
       <c r="O15" s="4" t="n">
         <v>28.2</v>
       </c>
       <c r="P15" s="4" t="n"/>
-      <c r="Q15" s="4" t="n"/>
+      <c r="Q15" s="4" t="n">
+        <v>27.79</v>
+      </c>
       <c r="R15" s="4" t="n">
         <v>27.19</v>
       </c>
@@ -2106,7 +2114,7 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>37.15</v>
+        <v>37.12</v>
       </c>
       <c r="D16" s="4" t="n">
         <v>35.9</v>
@@ -2224,13 +2232,13 @@
         <v>29.6</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>29.5</v>
+        <v>29.39</v>
       </c>
       <c r="R17" s="4" t="n">
         <v>28.6</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>29.5</v>
+        <v>29.45</v>
       </c>
       <c r="T17" s="4" t="n"/>
       <c r="U17" s="4" t="n"/>
@@ -2290,7 +2298,9 @@
         <v>22.5</v>
       </c>
       <c r="G18" s="4" t="n"/>
-      <c r="H18" s="4" t="n"/>
+      <c r="H18" s="4" t="n">
+        <v>23.39</v>
+      </c>
       <c r="I18" s="4" t="n"/>
       <c r="J18" s="4" t="n">
         <v>23</v>
@@ -2311,7 +2321,9 @@
       <c r="R18" s="4" t="n">
         <v>22.99</v>
       </c>
-      <c r="S18" s="4" t="n"/>
+      <c r="S18" s="4" t="n">
+        <v>23.55</v>
+      </c>
       <c r="T18" s="4" t="n"/>
       <c r="U18" s="4" t="n"/>
       <c r="V18" s="4" t="n"/>
@@ -2503,10 +2515,10 @@
       <c r="AB20" s="4" t="n">
         <v>22.35</v>
       </c>
-      <c r="AC20" s="4" t="n"/>
-      <c r="AD20" s="4" t="n">
+      <c r="AC20" s="4" t="n">
         <v>22.5</v>
       </c>
+      <c r="AD20" s="4" t="n"/>
       <c r="AE20" s="4" t="n"/>
       <c r="AF20" s="4" t="n"/>
       <c r="AG20" s="4" t="n"/>
@@ -2568,7 +2580,7 @@
         <v>29.9</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>29.9</v>
+        <v>29.92</v>
       </c>
       <c r="J21" s="4" t="n"/>
       <c r="K21" s="4" t="n"/>
@@ -2590,7 +2602,7 @@
       <c r="U21" s="4" t="n"/>
       <c r="V21" s="4" t="n"/>
       <c r="W21" s="4" t="n">
-        <v>29.95</v>
+        <v>29.89</v>
       </c>
       <c r="X21" s="4" t="n"/>
       <c r="Y21" s="4" t="n"/>
@@ -2834,7 +2846,7 @@
       <c r="Q24" s="4" t="n"/>
       <c r="R24" s="4" t="n"/>
       <c r="S24" s="4" t="n">
-        <v>22.43</v>
+        <v>22.31</v>
       </c>
       <c r="T24" s="4" t="n"/>
       <c r="U24" s="4" t="n"/>
@@ -3075,7 +3087,7 @@
         <v>30.89</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>31.79</v>
+        <v>31.59</v>
       </c>
       <c r="I27" s="4" t="n">
         <v>31.89</v>
@@ -3358,10 +3370,10 @@
       <c r="AA30" s="4" t="n"/>
       <c r="AB30" s="4" t="n"/>
       <c r="AC30" s="4" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="AD30" s="4" t="n">
         <v>23.39</v>
-      </c>
-      <c r="AD30" s="4" t="n">
-        <v>23.1</v>
       </c>
       <c r="AE30" s="4" t="n"/>
       <c r="AF30" s="4" t="n"/>
@@ -3450,10 +3462,10 @@
       <c r="AA31" s="4" t="n"/>
       <c r="AB31" s="4" t="n"/>
       <c r="AC31" s="4" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="AD31" s="4" t="n">
         <v>19.3</v>
-      </c>
-      <c r="AD31" s="4" t="n">
-        <v>19.2</v>
       </c>
       <c r="AE31" s="4" t="n"/>
       <c r="AF31" s="4" t="n"/>
@@ -3640,10 +3652,10 @@
       <c r="AA33" s="4" t="n"/>
       <c r="AB33" s="4" t="n"/>
       <c r="AC33" s="4" t="n">
+        <v>19.83</v>
+      </c>
+      <c r="AD33" s="4" t="n">
         <v>20.49</v>
-      </c>
-      <c r="AD33" s="4" t="n">
-        <v>19.83</v>
       </c>
       <c r="AE33" s="4" t="n"/>
       <c r="AF33" s="4" t="n"/>
@@ -3811,10 +3823,10 @@
       <c r="Z35" s="4" t="n"/>
       <c r="AA35" s="4" t="n"/>
       <c r="AB35" s="4" t="n"/>
-      <c r="AC35" s="4" t="n"/>
-      <c r="AD35" s="4" t="n">
+      <c r="AC35" s="4" t="n">
         <v>23.1</v>
       </c>
+      <c r="AD35" s="4" t="n"/>
       <c r="AE35" s="4" t="n"/>
       <c r="AF35" s="4" t="n"/>
       <c r="AG35" s="4" t="n"/>
@@ -3985,10 +3997,10 @@
       <c r="Z37" s="4" t="n"/>
       <c r="AA37" s="4" t="n"/>
       <c r="AB37" s="4" t="n"/>
-      <c r="AC37" s="4" t="n">
+      <c r="AC37" s="4" t="n"/>
+      <c r="AD37" s="4" t="n">
         <v>23.59</v>
       </c>
-      <c r="AD37" s="4" t="n"/>
       <c r="AE37" s="4" t="n"/>
       <c r="AF37" s="4" t="n"/>
       <c r="AG37" s="4" t="n"/>
@@ -4051,7 +4063,9 @@
       <c r="R38" s="4" t="n">
         <v>19.59</v>
       </c>
-      <c r="S38" s="4" t="n"/>
+      <c r="S38" s="4" t="n">
+        <v>20.59</v>
+      </c>
       <c r="T38" s="4" t="n"/>
       <c r="U38" s="4" t="n">
         <v>20.24</v>
@@ -4172,22 +4186,22 @@
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>32.6</v>
+        <v>32.5</v>
       </c>
       <c r="D40" s="4" t="n">
         <v>32.6</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>31.4</v>
+        <v>31.19</v>
       </c>
       <c r="F40" s="4" t="n">
         <v>33.4</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>32.3</v>
+        <v>31.8</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>32.7</v>
+        <v>32.59</v>
       </c>
       <c r="I40" s="4" t="n">
         <v>33.8</v>
@@ -4205,7 +4219,7 @@
       <c r="R40" s="4" t="n"/>
       <c r="S40" s="4" t="n"/>
       <c r="T40" s="4" t="n">
-        <v>34.9</v>
+        <v>34.6</v>
       </c>
       <c r="U40" s="4" t="n">
         <v>32.55</v>
@@ -4217,7 +4231,9 @@
       <c r="Z40" s="4" t="n"/>
       <c r="AA40" s="4" t="n"/>
       <c r="AB40" s="4" t="n"/>
-      <c r="AC40" s="4" t="n"/>
+      <c r="AC40" s="4" t="n">
+        <v>34.72</v>
+      </c>
       <c r="AD40" s="4" t="n"/>
       <c r="AE40" s="4" t="n"/>
       <c r="AF40" s="4" t="n"/>
@@ -4260,7 +4276,7 @@
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>28.8</v>
+        <v>28.79</v>
       </c>
       <c r="D41" s="4" t="n">
         <v>29.1</v>
@@ -4272,7 +4288,7 @@
         <v>29.7</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>28.8</v>
+        <v>28.82</v>
       </c>
       <c r="H41" s="4" t="n">
         <v>29.4</v>
@@ -4555,10 +4571,10 @@
       <c r="Z44" s="4" t="n"/>
       <c r="AA44" s="4" t="n"/>
       <c r="AB44" s="4" t="n"/>
-      <c r="AC44" s="4" t="n">
+      <c r="AC44" s="4" t="n"/>
+      <c r="AD44" s="4" t="n">
         <v>22.4</v>
       </c>
-      <c r="AD44" s="4" t="n"/>
       <c r="AE44" s="4" t="n"/>
       <c r="AF44" s="4" t="n"/>
       <c r="AG44" s="4" t="n">
@@ -4711,7 +4727,9 @@
         <v>31.8</v>
       </c>
       <c r="R46" s="4" t="n"/>
-      <c r="S46" s="4" t="n"/>
+      <c r="S46" s="4" t="n">
+        <v>32.59</v>
+      </c>
       <c r="T46" s="4" t="n"/>
       <c r="U46" s="4" t="n"/>
       <c r="V46" s="4" t="n"/>
@@ -4842,7 +4860,7 @@
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>23.6</v>
+        <v>23.55</v>
       </c>
       <c r="D48" s="4" t="n">
         <v>23.6</v>
@@ -4854,19 +4872,19 @@
         <v>23.5</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>23.7</v>
+        <v>23.57</v>
       </c>
       <c r="H48" s="4" t="n">
         <v>24.6</v>
       </c>
       <c r="I48" s="4" t="n">
-        <v>24.3</v>
+        <v>24.33</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>24.2</v>
+        <v>24.12</v>
       </c>
       <c r="L48" s="4" t="n"/>
       <c r="M48" s="4" t="n">
@@ -4874,14 +4892,16 @@
       </c>
       <c r="N48" s="4" t="n"/>
       <c r="O48" s="4" t="n">
-        <v>24.3</v>
+        <v>24.25</v>
       </c>
       <c r="P48" s="4" t="n"/>
       <c r="Q48" s="4" t="n">
         <v>24.4</v>
       </c>
       <c r="R48" s="4" t="n"/>
-      <c r="S48" s="4" t="n"/>
+      <c r="S48" s="4" t="n">
+        <v>24.6</v>
+      </c>
       <c r="T48" s="4" t="n"/>
       <c r="U48" s="4" t="n">
         <v>23.87</v>
@@ -5085,10 +5105,10 @@
       <c r="AB50" s="4" t="n">
         <v>26.6</v>
       </c>
-      <c r="AC50" s="4" t="n"/>
-      <c r="AD50" s="4" t="n">
+      <c r="AC50" s="4" t="n">
         <v>26.6</v>
       </c>
+      <c r="AD50" s="4" t="n"/>
       <c r="AE50" s="4" t="n"/>
       <c r="AF50" s="4" t="n"/>
       <c r="AG50" s="4" t="n"/>
@@ -6013,10 +6033,10 @@
       <c r="Z61" s="4" t="n"/>
       <c r="AA61" s="4" t="n"/>
       <c r="AB61" s="4" t="n"/>
-      <c r="AC61" s="4" t="n"/>
-      <c r="AD61" s="4" t="n">
+      <c r="AC61" s="4" t="n">
         <v>21.69</v>
       </c>
+      <c r="AD61" s="4" t="n"/>
       <c r="AE61" s="4" t="n">
         <v>22.5</v>
       </c>
@@ -6205,10 +6225,10 @@
       <c r="Z63" s="4" t="n"/>
       <c r="AA63" s="4" t="n"/>
       <c r="AB63" s="4" t="n"/>
-      <c r="AC63" s="4" t="n">
+      <c r="AC63" s="4" t="n"/>
+      <c r="AD63" s="4" t="n">
         <v>24.89</v>
       </c>
-      <c r="AD63" s="4" t="n"/>
       <c r="AE63" s="4" t="n"/>
       <c r="AF63" s="4" t="n"/>
       <c r="AG63" s="4" t="n"/>
@@ -6588,12 +6608,14 @@
         <v>25.6</v>
       </c>
       <c r="E68" s="4" t="n"/>
-      <c r="F68" s="4" t="n"/>
+      <c r="F68" s="4" t="n">
+        <v>26.05</v>
+      </c>
       <c r="G68" s="4" t="n">
         <v>25.09</v>
       </c>
       <c r="H68" s="4" t="n">
-        <v>25.9</v>
+        <v>25.84</v>
       </c>
       <c r="I68" s="4" t="n">
         <v>25.99</v>
@@ -6621,7 +6643,7 @@
       <c r="V68" s="4" t="n"/>
       <c r="W68" s="4" t="n"/>
       <c r="X68" s="4" t="n">
-        <v>27.34</v>
+        <v>27.29</v>
       </c>
       <c r="Y68" s="4" t="n">
         <v>28.06</v>
@@ -7050,10 +7072,10 @@
       <c r="AA73" s="4" t="n"/>
       <c r="AB73" s="4" t="n"/>
       <c r="AC73" s="4" t="n">
+        <v>19.41</v>
+      </c>
+      <c r="AD73" s="4" t="n">
         <v>19.39</v>
-      </c>
-      <c r="AD73" s="4" t="n">
-        <v>19.41</v>
       </c>
       <c r="AE73" s="4" t="n"/>
       <c r="AF73" s="4" t="n"/>
@@ -7304,10 +7326,10 @@
       <c r="AA76" s="4" t="n"/>
       <c r="AB76" s="4" t="n"/>
       <c r="AC76" s="4" t="n">
+        <v>16.92</v>
+      </c>
+      <c r="AD76" s="4" t="n">
         <v>17.09</v>
-      </c>
-      <c r="AD76" s="4" t="n">
-        <v>16.92</v>
       </c>
       <c r="AE76" s="4" t="n"/>
       <c r="AF76" s="4" t="n"/>
@@ -8363,12 +8385,12 @@
       </c>
       <c r="BE1" s="1" t="inlineStr">
         <is>
+          <t>sf90★6</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
           <t>sgt★6</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>sf90★6</t>
         </is>
       </c>
       <c r="BG1" s="1" t="inlineStr">
@@ -8598,10 +8620,10 @@
       <c r="BC2" s="4" t="n"/>
       <c r="BD2" s="4" t="n"/>
       <c r="BE2" s="4" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="BF2" s="4" t="n">
         <v>19.3</v>
-      </c>
-      <c r="BF2" s="4" t="n">
-        <v>19.25</v>
       </c>
       <c r="BG2" s="4" t="n"/>
       <c r="BH2" s="4" t="n"/>
@@ -8667,10 +8689,14 @@
       <c r="T3" s="4" t="n"/>
       <c r="U3" s="4" t="n"/>
       <c r="V3" s="4" t="n"/>
-      <c r="W3" s="4" t="n"/>
+      <c r="W3" s="4" t="n">
+        <v>27.8</v>
+      </c>
       <c r="X3" s="4" t="n"/>
       <c r="Y3" s="4" t="n"/>
-      <c r="Z3" s="4" t="n"/>
+      <c r="Z3" s="4" t="n">
+        <v>28.2</v>
+      </c>
       <c r="AA3" s="4" t="n"/>
       <c r="AB3" s="4" t="n"/>
       <c r="AC3" s="4" t="n"/>
@@ -8683,7 +8709,9 @@
       <c r="AH3" s="4" t="n"/>
       <c r="AI3" s="4" t="n"/>
       <c r="AJ3" s="4" t="n"/>
-      <c r="AK3" s="4" t="n"/>
+      <c r="AK3" s="4" t="n">
+        <v>27.9</v>
+      </c>
       <c r="AL3" s="4" t="n"/>
       <c r="AM3" s="4" t="n"/>
       <c r="AN3" s="4" t="n"/>
@@ -9089,7 +9117,9 @@
       <c r="T7" s="4" t="n"/>
       <c r="U7" s="4" t="n"/>
       <c r="V7" s="4" t="n"/>
-      <c r="W7" s="4" t="n"/>
+      <c r="W7" s="4" t="n">
+        <v>24.6</v>
+      </c>
       <c r="X7" s="4" t="n"/>
       <c r="Y7" s="4" t="n"/>
       <c r="Z7" s="4" t="n"/>
@@ -9844,7 +9874,9 @@
       <c r="K14" s="4" t="n"/>
       <c r="L14" s="4" t="n"/>
       <c r="M14" s="4" t="n"/>
-      <c r="N14" s="4" t="n"/>
+      <c r="N14" s="4" t="n">
+        <v>24.6</v>
+      </c>
       <c r="O14" s="4" t="n"/>
       <c r="P14" s="4" t="n"/>
       <c r="Q14" s="4" t="n"/>
@@ -10545,10 +10577,10 @@
       <c r="BB20" s="4" t="n"/>
       <c r="BC20" s="4" t="n"/>
       <c r="BD20" s="4" t="n"/>
-      <c r="BE20" s="4" t="n"/>
-      <c r="BF20" s="4" t="n">
+      <c r="BE20" s="4" t="n">
         <v>22.6</v>
       </c>
+      <c r="BF20" s="4" t="n"/>
       <c r="BG20" s="4" t="n"/>
       <c r="BH20" s="4" t="n"/>
       <c r="BI20" s="4" t="n"/>
@@ -11715,10 +11747,10 @@
       <c r="BB31" s="4" t="n"/>
       <c r="BC31" s="4" t="n"/>
       <c r="BD31" s="4" t="n"/>
-      <c r="BE31" s="4" t="n"/>
-      <c r="BF31" s="4" t="n">
+      <c r="BE31" s="4" t="n">
         <v>19.23</v>
       </c>
+      <c r="BF31" s="4" t="n"/>
       <c r="BG31" s="4" t="n"/>
       <c r="BH31" s="4" t="n"/>
       <c r="BI31" s="4" t="n"/>
@@ -11962,10 +11994,10 @@
       <c r="BC33" s="4" t="n"/>
       <c r="BD33" s="4" t="n"/>
       <c r="BE33" s="4" t="n">
+        <v>19.95</v>
+      </c>
+      <c r="BF33" s="4" t="n">
         <v>20.5</v>
-      </c>
-      <c r="BF33" s="4" t="n">
-        <v>19.95</v>
       </c>
       <c r="BG33" s="4" t="n"/>
       <c r="BH33" s="4" t="n"/>
@@ -12172,10 +12204,10 @@
       <c r="BC35" s="4" t="n"/>
       <c r="BD35" s="4" t="n"/>
       <c r="BE35" s="4" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="BF35" s="4" t="n">
         <v>24.09</v>
-      </c>
-      <c r="BF35" s="4" t="n">
-        <v>23.4</v>
       </c>
       <c r="BG35" s="4" t="n"/>
       <c r="BH35" s="4" t="n"/>
@@ -12686,7 +12718,9 @@
       <c r="AI40" s="4" t="n"/>
       <c r="AJ40" s="4" t="n"/>
       <c r="AK40" s="4" t="n"/>
-      <c r="AL40" s="4" t="n"/>
+      <c r="AL40" s="4" t="n">
+        <v>34.5</v>
+      </c>
       <c r="AM40" s="4" t="n"/>
       <c r="AN40" s="4" t="n"/>
       <c r="AO40" s="4" t="n"/>
@@ -13635,7 +13669,9 @@
         <v>29.99</v>
       </c>
       <c r="L49" s="4" t="n"/>
-      <c r="M49" s="4" t="n"/>
+      <c r="M49" s="4" t="n">
+        <v>29.3</v>
+      </c>
       <c r="N49" s="4" t="n"/>
       <c r="O49" s="4" t="n"/>
       <c r="P49" s="4" t="n"/>
@@ -14987,10 +15023,10 @@
       <c r="BB61" s="4" t="n"/>
       <c r="BC61" s="4" t="n"/>
       <c r="BD61" s="4" t="n"/>
-      <c r="BE61" s="4" t="n"/>
-      <c r="BF61" s="4" t="n">
+      <c r="BE61" s="4" t="n">
         <v>21.85</v>
       </c>
+      <c r="BF61" s="4" t="n"/>
       <c r="BG61" s="4" t="n"/>
       <c r="BH61" s="4" t="n"/>
       <c r="BI61" s="4" t="n"/>
@@ -15191,10 +15227,10 @@
       <c r="BB63" s="4" t="n"/>
       <c r="BC63" s="4" t="n"/>
       <c r="BD63" s="4" t="n"/>
-      <c r="BE63" s="4" t="n">
+      <c r="BE63" s="4" t="n"/>
+      <c r="BF63" s="4" t="n">
         <v>25.1</v>
       </c>
-      <c r="BF63" s="4" t="n"/>
       <c r="BG63" s="4" t="n"/>
       <c r="BH63" s="4" t="n"/>
       <c r="BI63" s="4" t="n"/>
@@ -16266,10 +16302,10 @@
       <c r="BC73" s="4" t="n"/>
       <c r="BD73" s="4" t="n"/>
       <c r="BE73" s="4" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="BF73" s="4" t="n">
         <v>19.59</v>
-      </c>
-      <c r="BF73" s="4" t="n">
-        <v>18.9</v>
       </c>
       <c r="BG73" s="4" t="n"/>
       <c r="BH73" s="4" t="n"/>
@@ -16584,10 +16620,10 @@
       <c r="BC76" s="4" t="n"/>
       <c r="BD76" s="4" t="n"/>
       <c r="BE76" s="4" t="n">
+        <v>17.29</v>
+      </c>
+      <c r="BF76" s="4" t="n">
         <v>17.45</v>
-      </c>
-      <c r="BF76" s="4" t="n">
-        <v>17.29</v>
       </c>
       <c r="BG76" s="4" t="n"/>
       <c r="BH76" s="4" t="n"/>
@@ -17885,12 +17921,12 @@
       </c>
       <c r="BE1" s="1" t="inlineStr">
         <is>
+          <t>sf90★6</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
           <t>sgt★6</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>sf90★6</t>
         </is>
       </c>
       <c r="BG1" s="1" t="inlineStr">
@@ -18233,10 +18269,18 @@
       <c r="T3" s="4" t="n"/>
       <c r="U3" s="4" t="n"/>
       <c r="V3" s="4" t="n"/>
-      <c r="W3" s="4" t="n"/>
+      <c r="W3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="X3" s="4" t="n"/>
       <c r="Y3" s="4" t="n"/>
-      <c r="Z3" s="4" t="n"/>
+      <c r="Z3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AA3" s="4" t="n"/>
       <c r="AB3" s="4" t="n"/>
       <c r="AC3" s="4" t="n"/>
@@ -18251,7 +18295,11 @@
       <c r="AH3" s="4" t="n"/>
       <c r="AI3" s="4" t="n"/>
       <c r="AJ3" s="4" t="n"/>
-      <c r="AK3" s="4" t="n"/>
+      <c r="AK3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL3" s="4" t="n"/>
       <c r="AM3" s="4" t="n"/>
       <c r="AN3" s="4" t="n"/>
@@ -18583,12 +18631,12 @@
       <c r="BB5" s="4" t="n"/>
       <c r="BC5" s="4" t="n"/>
       <c r="BD5" s="4" t="n"/>
-      <c r="BE5" s="4" t="n"/>
-      <c r="BF5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BE5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BF5" s="4" t="n"/>
       <c r="BG5" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -18721,12 +18769,12 @@
       <c r="BB6" s="4" t="n"/>
       <c r="BC6" s="4" t="n"/>
       <c r="BD6" s="4" t="n"/>
-      <c r="BE6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BF6" s="4" t="n"/>
+      <c r="BE6" s="4" t="n"/>
+      <c r="BF6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BG6" s="4" t="n"/>
       <c r="BH6" s="4" t="n"/>
       <c r="BI6" s="4" t="inlineStr">
@@ -18891,12 +18939,12 @@
       <c r="BB7" s="4" t="n"/>
       <c r="BC7" s="4" t="n"/>
       <c r="BD7" s="4" t="n"/>
-      <c r="BE7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BF7" s="4" t="n"/>
+      <c r="BE7" s="4" t="n"/>
+      <c r="BF7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BG7" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -19231,12 +19279,12 @@
       <c r="BB9" s="4" t="n"/>
       <c r="BC9" s="4" t="n"/>
       <c r="BD9" s="4" t="n"/>
-      <c r="BE9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BF9" s="4" t="n"/>
+      <c r="BE9" s="4" t="n"/>
+      <c r="BF9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BG9" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -19405,12 +19453,12 @@
       <c r="BB10" s="4" t="n"/>
       <c r="BC10" s="4" t="n"/>
       <c r="BD10" s="4" t="n"/>
-      <c r="BE10" s="4" t="n"/>
-      <c r="BF10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BE10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BF10" s="4" t="n"/>
       <c r="BG10" s="4" t="n"/>
       <c r="BH10" s="4" t="n"/>
       <c r="BI10" s="4" t="inlineStr">
@@ -20223,12 +20271,12 @@
       <c r="BB15" s="4" t="n"/>
       <c r="BC15" s="4" t="n"/>
       <c r="BD15" s="4" t="n"/>
-      <c r="BE15" s="4" t="n"/>
-      <c r="BF15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BE15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BF15" s="4" t="n"/>
       <c r="BG15" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -20867,12 +20915,12 @@
       <c r="BB19" s="4" t="n"/>
       <c r="BC19" s="4" t="n"/>
       <c r="BD19" s="4" t="n"/>
-      <c r="BE19" s="4" t="n"/>
-      <c r="BF19" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BE19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BF19" s="4" t="n"/>
       <c r="BG19" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -21025,12 +21073,12 @@
       <c r="BB20" s="4" t="n"/>
       <c r="BC20" s="4" t="n"/>
       <c r="BD20" s="4" t="n"/>
-      <c r="BE20" s="4" t="n"/>
-      <c r="BF20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BE20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BF20" s="4" t="n"/>
       <c r="BG20" s="4" t="n"/>
       <c r="BH20" s="4" t="n"/>
       <c r="BI20" s="4" t="n"/>
@@ -22565,12 +22613,12 @@
       <c r="BB30" s="4" t="n"/>
       <c r="BC30" s="4" t="n"/>
       <c r="BD30" s="4" t="n"/>
-      <c r="BE30" s="4" t="n"/>
-      <c r="BF30" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BE30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BF30" s="4" t="n"/>
       <c r="BG30" s="4" t="n"/>
       <c r="BH30" s="4" t="n"/>
       <c r="BI30" s="4" t="inlineStr">
@@ -24137,12 +24185,12 @@
       <c r="BB40" s="4" t="n"/>
       <c r="BC40" s="4" t="n"/>
       <c r="BD40" s="4" t="n"/>
-      <c r="BE40" s="4" t="n"/>
-      <c r="BF40" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BE40" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BF40" s="4" t="n"/>
       <c r="BG40" s="4" t="n"/>
       <c r="BH40" s="4" t="n"/>
       <c r="BI40" s="4" t="n"/>
@@ -24761,12 +24809,12 @@
       <c r="BB44" s="4" t="n"/>
       <c r="BC44" s="4" t="n"/>
       <c r="BD44" s="4" t="n"/>
-      <c r="BE44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BF44" s="4" t="n"/>
+      <c r="BE44" s="4" t="n"/>
+      <c r="BF44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BG44" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -25089,12 +25137,12 @@
       <c r="BB46" s="4" t="n"/>
       <c r="BC46" s="4" t="n"/>
       <c r="BD46" s="4" t="n"/>
-      <c r="BE46" s="4" t="n"/>
-      <c r="BF46" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BE46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BF46" s="4" t="n"/>
       <c r="BG46" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -25409,12 +25457,12 @@
       <c r="BB48" s="4" t="n"/>
       <c r="BC48" s="4" t="n"/>
       <c r="BD48" s="4" t="n"/>
-      <c r="BE48" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BF48" s="4" t="n"/>
+      <c r="BE48" s="4" t="n"/>
+      <c r="BF48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BG48" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -25567,12 +25615,12 @@
       <c r="BB49" s="4" t="n"/>
       <c r="BC49" s="4" t="n"/>
       <c r="BD49" s="4" t="n"/>
-      <c r="BE49" s="4" t="n"/>
-      <c r="BF49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BE49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BF49" s="4" t="n"/>
       <c r="BG49" s="4" t="n"/>
       <c r="BH49" s="4" t="n"/>
       <c r="BI49" s="4" t="n"/>
@@ -25721,12 +25769,12 @@
       <c r="BB50" s="4" t="n"/>
       <c r="BC50" s="4" t="n"/>
       <c r="BD50" s="4" t="n"/>
-      <c r="BE50" s="4" t="n"/>
-      <c r="BF50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BE50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BF50" s="4" t="n"/>
       <c r="BG50" s="4" t="n"/>
       <c r="BH50" s="4" t="n"/>
       <c r="BI50" s="4" t="n"/>
@@ -25879,12 +25927,12 @@
       <c r="BB51" s="4" t="n"/>
       <c r="BC51" s="4" t="n"/>
       <c r="BD51" s="4" t="n"/>
-      <c r="BE51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BF51" s="4" t="n"/>
+      <c r="BE51" s="4" t="n"/>
+      <c r="BF51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BG51" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -26503,12 +26551,12 @@
       <c r="BB55" s="4" t="n"/>
       <c r="BC55" s="4" t="n"/>
       <c r="BD55" s="4" t="n"/>
-      <c r="BE55" s="4" t="n"/>
-      <c r="BF55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BE55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BF55" s="4" t="n"/>
       <c r="BG55" s="4" t="n"/>
       <c r="BH55" s="4" t="n"/>
       <c r="BI55" s="4" t="n"/>
@@ -27423,12 +27471,12 @@
       <c r="BB61" s="4" t="n"/>
       <c r="BC61" s="4" t="n"/>
       <c r="BD61" s="4" t="n"/>
-      <c r="BE61" s="4" t="n"/>
-      <c r="BF61" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BE61" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BF61" s="4" t="n"/>
       <c r="BG61" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -27585,12 +27633,12 @@
       <c r="BB62" s="4" t="n"/>
       <c r="BC62" s="4" t="n"/>
       <c r="BD62" s="4" t="n"/>
-      <c r="BE62" s="4" t="n"/>
-      <c r="BF62" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BE62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BF62" s="4" t="n"/>
       <c r="BG62" s="4" t="n"/>
       <c r="BH62" s="4" t="n"/>
       <c r="BI62" s="4" t="n"/>
@@ -27743,12 +27791,12 @@
       <c r="BB63" s="4" t="n"/>
       <c r="BC63" s="4" t="n"/>
       <c r="BD63" s="4" t="n"/>
-      <c r="BE63" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BF63" s="4" t="n"/>
+      <c r="BE63" s="4" t="n"/>
+      <c r="BF63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BG63" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -28359,12 +28407,12 @@
       <c r="BB67" s="4" t="n"/>
       <c r="BC67" s="4" t="n"/>
       <c r="BD67" s="4" t="n"/>
-      <c r="BE67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BF67" s="4" t="n"/>
+      <c r="BE67" s="4" t="n"/>
+      <c r="BF67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BG67" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -35178,22 +35226,22 @@
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
+          <t>白龙</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
           <t>sf90</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>urs</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>无敌牛</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>白龙</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
@@ -35415,7 +35463,9 @@
         <v>30.39</v>
       </c>
       <c r="E4" s="4" t="n"/>
-      <c r="F4" s="4" t="n"/>
+      <c r="F4" s="4" t="n">
+        <v>30.95</v>
+      </c>
       <c r="G4" s="4" t="n"/>
       <c r="H4" s="4" t="n">
         <v>31.69</v>
@@ -35574,12 +35624,12 @@
       <c r="V6" s="4" t="n"/>
       <c r="W6" s="4" t="n"/>
       <c r="X6" s="4" t="n"/>
-      <c r="Y6" s="4" t="n"/>
+      <c r="Y6" s="4" t="n">
+        <v>18.2</v>
+      </c>
       <c r="Z6" s="4" t="n"/>
       <c r="AA6" s="4" t="n"/>
-      <c r="AB6" s="4" t="n">
-        <v>18.2</v>
-      </c>
+      <c r="AB6" s="4" t="n"/>
       <c r="AC6" s="4" t="n"/>
       <c r="AD6" s="4" t="n"/>
       <c r="AE6" s="4" t="n"/>
@@ -35737,7 +35787,9 @@
       <c r="C9" s="4" t="n">
         <v>19.79</v>
       </c>
-      <c r="D9" s="4" t="n"/>
+      <c r="D9" s="4" t="n">
+        <v>19.5</v>
+      </c>
       <c r="E9" s="4" t="n"/>
       <c r="F9" s="4" t="n"/>
       <c r="G9" s="4" t="n"/>
@@ -35954,7 +36006,9 @@
       <c r="V12" s="4" t="n"/>
       <c r="W12" s="4" t="n"/>
       <c r="X12" s="4" t="n"/>
-      <c r="Y12" s="4" t="n"/>
+      <c r="Y12" s="4" t="n">
+        <v>21.87</v>
+      </c>
       <c r="Z12" s="4" t="n"/>
       <c r="AA12" s="4" t="n"/>
       <c r="AB12" s="4" t="n"/>
@@ -35962,7 +36016,9 @@
       <c r="AD12" s="4" t="n"/>
       <c r="AE12" s="4" t="n"/>
       <c r="AF12" s="4" t="n"/>
-      <c r="AG12" s="4" t="n"/>
+      <c r="AG12" s="4" t="n">
+        <v>21.85</v>
+      </c>
       <c r="AH12" s="4" t="n"/>
       <c r="AI12" s="4" t="n"/>
       <c r="AJ12" s="4" t="n"/>
@@ -36458,10 +36514,10 @@
       <c r="X20" s="4" t="n"/>
       <c r="Y20" s="4" t="n"/>
       <c r="Z20" s="4" t="n"/>
-      <c r="AA20" s="4" t="n">
+      <c r="AA20" s="4" t="n"/>
+      <c r="AB20" s="4" t="n">
         <v>23.3</v>
       </c>
-      <c r="AB20" s="4" t="n"/>
       <c r="AC20" s="4" t="n"/>
       <c r="AD20" s="4" t="n"/>
       <c r="AE20" s="4" t="n"/>
@@ -37072,10 +37128,10 @@
       <c r="X30" s="4" t="n"/>
       <c r="Y30" s="4" t="n"/>
       <c r="Z30" s="4" t="n"/>
-      <c r="AA30" s="4" t="n">
+      <c r="AA30" s="4" t="n"/>
+      <c r="AB30" s="4" t="n">
         <v>23.95</v>
       </c>
-      <c r="AB30" s="4" t="n"/>
       <c r="AC30" s="4" t="n"/>
       <c r="AD30" s="4" t="n"/>
       <c r="AE30" s="4" t="n"/>
@@ -37132,12 +37188,12 @@
         <v>19.29</v>
       </c>
       <c r="X31" s="4" t="n"/>
-      <c r="Y31" s="4" t="n"/>
+      <c r="Y31" s="4" t="n">
+        <v>19.15</v>
+      </c>
       <c r="Z31" s="4" t="n"/>
       <c r="AA31" s="4" t="n"/>
-      <c r="AB31" s="4" t="n">
-        <v>19.15</v>
-      </c>
+      <c r="AB31" s="4" t="n"/>
       <c r="AC31" s="4" t="n">
         <v>19.25</v>
       </c>
@@ -37201,10 +37257,10 @@
       </c>
       <c r="X32" s="4" t="n"/>
       <c r="Y32" s="4" t="n"/>
-      <c r="Z32" s="4" t="n">
+      <c r="Z32" s="4" t="n"/>
+      <c r="AA32" s="4" t="n">
         <v>28.79</v>
       </c>
-      <c r="AA32" s="4" t="n"/>
       <c r="AB32" s="4" t="n"/>
       <c r="AC32" s="4" t="n"/>
       <c r="AD32" s="4" t="n"/>
@@ -37266,10 +37322,10 @@
         <v>20.15</v>
       </c>
       <c r="X33" s="4" t="n"/>
-      <c r="Y33" s="4" t="n">
+      <c r="Y33" s="4" t="n"/>
+      <c r="Z33" s="4" t="n">
         <v>20.23</v>
       </c>
-      <c r="Z33" s="4" t="n"/>
       <c r="AA33" s="4" t="n"/>
       <c r="AB33" s="4" t="n"/>
       <c r="AC33" s="4" t="n"/>
@@ -37388,10 +37444,10 @@
       <c r="X35" s="4" t="n">
         <v>23.99</v>
       </c>
-      <c r="Y35" s="4" t="n">
+      <c r="Y35" s="4" t="n"/>
+      <c r="Z35" s="4" t="n">
         <v>23.45</v>
       </c>
-      <c r="Z35" s="4" t="n"/>
       <c r="AA35" s="4" t="n"/>
       <c r="AB35" s="4" t="n"/>
       <c r="AC35" s="4" t="n"/>
@@ -37511,10 +37567,10 @@
       <c r="W37" s="4" t="n"/>
       <c r="X37" s="4" t="n"/>
       <c r="Y37" s="4" t="n"/>
-      <c r="Z37" s="4" t="n">
+      <c r="Z37" s="4" t="n"/>
+      <c r="AA37" s="4" t="n">
         <v>23.11</v>
       </c>
-      <c r="AA37" s="4" t="n"/>
       <c r="AB37" s="4" t="n"/>
       <c r="AC37" s="4" t="n"/>
       <c r="AD37" s="4" t="n"/>
@@ -37945,13 +38001,13 @@
       <c r="W44" s="4" t="n"/>
       <c r="X44" s="4" t="n"/>
       <c r="Y44" s="4" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="Z44" s="4" t="n">
         <v>22.7</v>
       </c>
-      <c r="Z44" s="4" t="n"/>
       <c r="AA44" s="4" t="n"/>
-      <c r="AB44" s="4" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="AB44" s="4" t="n"/>
       <c r="AC44" s="4" t="n">
         <v>22.59</v>
       </c>
@@ -38127,10 +38183,10 @@
       <c r="W47" s="4" t="n"/>
       <c r="X47" s="4" t="n"/>
       <c r="Y47" s="4" t="n"/>
-      <c r="Z47" s="4" t="n">
+      <c r="Z47" s="4" t="n"/>
+      <c r="AA47" s="4" t="n">
         <v>42.29</v>
       </c>
-      <c r="AA47" s="4" t="n"/>
       <c r="AB47" s="4" t="n"/>
       <c r="AC47" s="4" t="n"/>
       <c r="AD47" s="4" t="n"/>
@@ -38304,10 +38360,10 @@
       <c r="X50" s="4" t="n"/>
       <c r="Y50" s="4" t="n"/>
       <c r="Z50" s="4" t="n"/>
-      <c r="AA50" s="4" t="n">
+      <c r="AA50" s="4" t="n"/>
+      <c r="AB50" s="4" t="n">
         <v>27.69</v>
       </c>
-      <c r="AB50" s="4" t="n"/>
       <c r="AC50" s="4" t="n"/>
       <c r="AD50" s="4" t="n"/>
       <c r="AE50" s="4" t="n"/>
@@ -38608,10 +38664,10 @@
       </c>
       <c r="Y55" s="4" t="n"/>
       <c r="Z55" s="4" t="n"/>
-      <c r="AA55" s="4" t="n">
+      <c r="AA55" s="4" t="n"/>
+      <c r="AB55" s="4" t="n">
         <v>34.65</v>
       </c>
-      <c r="AB55" s="4" t="n"/>
       <c r="AC55" s="4" t="n"/>
       <c r="AD55" s="4" t="n"/>
       <c r="AE55" s="4" t="n"/>
@@ -38974,14 +39030,14 @@
       <c r="V61" s="4" t="n"/>
       <c r="W61" s="4" t="n"/>
       <c r="X61" s="4" t="n"/>
-      <c r="Y61" s="4" t="n">
+      <c r="Y61" s="4" t="n"/>
+      <c r="Z61" s="4" t="n">
         <v>22.15</v>
       </c>
-      <c r="Z61" s="4" t="n"/>
-      <c r="AA61" s="4" t="n">
+      <c r="AA61" s="4" t="n"/>
+      <c r="AB61" s="4" t="n">
         <v>22.4</v>
       </c>
-      <c r="AB61" s="4" t="n"/>
       <c r="AC61" s="4" t="n"/>
       <c r="AD61" s="4" t="n">
         <v>21.8</v>
@@ -39338,12 +39394,12 @@
       <c r="V67" s="4" t="n"/>
       <c r="W67" s="4" t="n"/>
       <c r="X67" s="4" t="n"/>
-      <c r="Y67" s="4" t="n"/>
+      <c r="Y67" s="4" t="n">
+        <v>18.2</v>
+      </c>
       <c r="Z67" s="4" t="n"/>
       <c r="AA67" s="4" t="n"/>
-      <c r="AB67" s="4" t="n">
-        <v>18.2</v>
-      </c>
+      <c r="AB67" s="4" t="n"/>
       <c r="AC67" s="4" t="n">
         <v>18.23</v>
       </c>
@@ -39463,10 +39519,10 @@
       <c r="W69" s="4" t="n"/>
       <c r="X69" s="4" t="n"/>
       <c r="Y69" s="4" t="n"/>
-      <c r="Z69" s="4" t="n">
+      <c r="Z69" s="4" t="n"/>
+      <c r="AA69" s="4" t="n">
         <v>34.49</v>
       </c>
-      <c r="AA69" s="4" t="n"/>
       <c r="AB69" s="4" t="n"/>
       <c r="AC69" s="4" t="n"/>
       <c r="AD69" s="4" t="n"/>
@@ -39646,13 +39702,13 @@
       <c r="V72" s="4" t="n"/>
       <c r="W72" s="4" t="n"/>
       <c r="X72" s="4" t="n"/>
-      <c r="Y72" s="4" t="n">
+      <c r="Y72" s="4" t="n"/>
+      <c r="Z72" s="4" t="n">
         <v>26.25</v>
       </c>
-      <c r="Z72" s="4" t="n">
+      <c r="AA72" s="4" t="n">
         <v>25.81</v>
       </c>
-      <c r="AA72" s="4" t="n"/>
       <c r="AB72" s="4" t="n"/>
       <c r="AC72" s="4" t="n"/>
       <c r="AD72" s="4" t="n">
@@ -40694,22 +40750,22 @@
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
+          <t>白龙★6</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
           <t>sf90★6</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>urs★6</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>无敌牛★5</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>白龙★6</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
@@ -43014,12 +43070,12 @@
       <c r="AO31" s="4" t="n"/>
       <c r="AP31" s="4" t="n"/>
       <c r="AQ31" s="4" t="n"/>
-      <c r="AR31" s="4" t="n"/>
+      <c r="AR31" s="4" t="n">
+        <v>19.2</v>
+      </c>
       <c r="AS31" s="4" t="n"/>
       <c r="AT31" s="4" t="n"/>
-      <c r="AU31" s="4" t="n">
-        <v>19.2</v>
-      </c>
+      <c r="AU31" s="4" t="n"/>
       <c r="AV31" s="4" t="n"/>
       <c r="AW31" s="4" t="n"/>
       <c r="AX31" s="4" t="n"/>
@@ -43316,10 +43372,10 @@
       <c r="AO35" s="4" t="n"/>
       <c r="AP35" s="4" t="n"/>
       <c r="AQ35" s="4" t="n"/>
-      <c r="AR35" s="4" t="n">
+      <c r="AR35" s="4" t="n"/>
+      <c r="AS35" s="4" t="n">
         <v>23.74</v>
       </c>
-      <c r="AS35" s="4" t="n"/>
       <c r="AT35" s="4" t="n"/>
       <c r="AU35" s="4" t="n"/>
       <c r="AV35" s="4" t="n"/>
@@ -45774,7 +45830,9 @@
         <v>27.09</v>
       </c>
       <c r="F68" s="4" t="n"/>
-      <c r="G68" s="4" t="n"/>
+      <c r="G68" s="4" t="n">
+        <v>26.8</v>
+      </c>
       <c r="H68" s="4" t="n"/>
       <c r="I68" s="4" t="n"/>
       <c r="J68" s="4" t="n"/>
@@ -45784,7 +45842,9 @@
       <c r="N68" s="4" t="n"/>
       <c r="O68" s="4" t="n"/>
       <c r="P68" s="4" t="n"/>
-      <c r="Q68" s="4" t="n"/>
+      <c r="Q68" s="4" t="n">
+        <v>28.1</v>
+      </c>
       <c r="R68" s="4" t="n"/>
       <c r="S68" s="4" t="n"/>
       <c r="T68" s="4" t="n"/>
@@ -45794,7 +45854,9 @@
       <c r="X68" s="4" t="n"/>
       <c r="Y68" s="4" t="n"/>
       <c r="Z68" s="4" t="n"/>
-      <c r="AA68" s="4" t="n"/>
+      <c r="AA68" s="4" t="n">
+        <v>27.8</v>
+      </c>
       <c r="AB68" s="4" t="n"/>
       <c r="AC68" s="4" t="n"/>
       <c r="AD68" s="4" t="n"/>
@@ -47343,22 +47405,22 @@
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
+          <t>白龙★6</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
           <t>sf90★6</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>urs★6</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>无敌牛★5</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>白龙★6</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
@@ -47504,18 +47566,18 @@
       <c r="AO2" s="4" t="n"/>
       <c r="AP2" s="4" t="n"/>
       <c r="AQ2" s="4" t="n"/>
-      <c r="AR2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS2" s="4" t="n"/>
-      <c r="AT2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU2" s="4" t="n"/>
+      <c r="AR2" s="4" t="n"/>
+      <c r="AS2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AT2" s="4" t="n"/>
+      <c r="AU2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV2" s="4" t="n"/>
       <c r="AW2" s="4" t="n"/>
       <c r="AX2" s="4" t="n"/>
@@ -47621,12 +47683,12 @@
       <c r="AQ3" s="4" t="n"/>
       <c r="AR3" s="4" t="n"/>
       <c r="AS3" s="4" t="n"/>
-      <c r="AT3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU3" s="4" t="n"/>
+      <c r="AT3" s="4" t="n"/>
+      <c r="AU3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV3" s="4" t="n"/>
       <c r="AW3" s="4" t="n"/>
       <c r="AX3" s="4" t="n"/>
@@ -47724,12 +47786,12 @@
       <c r="AQ4" s="4" t="n"/>
       <c r="AR4" s="4" t="n"/>
       <c r="AS4" s="4" t="n"/>
-      <c r="AT4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU4" s="4" t="n"/>
+      <c r="AT4" s="4" t="n"/>
+      <c r="AU4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV4" s="4" t="n"/>
       <c r="AW4" s="4" t="n"/>
       <c r="AX4" s="4" t="n"/>
@@ -47825,18 +47887,18 @@
       <c r="AO5" s="4" t="n"/>
       <c r="AP5" s="4" t="n"/>
       <c r="AQ5" s="4" t="n"/>
-      <c r="AR5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS5" s="4" t="n"/>
-      <c r="AT5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU5" s="4" t="n"/>
+      <c r="AR5" s="4" t="n"/>
+      <c r="AS5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AT5" s="4" t="n"/>
+      <c r="AU5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV5" s="4" t="n"/>
       <c r="AW5" s="4" t="n"/>
       <c r="AX5" s="4" t="n"/>
@@ -47922,12 +47984,12 @@
       <c r="AQ6" s="4" t="n"/>
       <c r="AR6" s="4" t="n"/>
       <c r="AS6" s="4" t="n"/>
-      <c r="AT6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU6" s="4" t="n"/>
+      <c r="AT6" s="4" t="n"/>
+      <c r="AU6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV6" s="4" t="n"/>
       <c r="AW6" s="4" t="n"/>
       <c r="AX6" s="4" t="inlineStr">
@@ -48041,12 +48103,12 @@
       <c r="AQ7" s="4" t="n"/>
       <c r="AR7" s="4" t="n"/>
       <c r="AS7" s="4" t="n"/>
-      <c r="AT7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU7" s="4" t="n"/>
+      <c r="AT7" s="4" t="n"/>
+      <c r="AU7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV7" s="4" t="n"/>
       <c r="AW7" s="4" t="n"/>
       <c r="AX7" s="4" t="n"/>
@@ -48172,12 +48234,12 @@
       <c r="AQ8" s="4" t="n"/>
       <c r="AR8" s="4" t="n"/>
       <c r="AS8" s="4" t="n"/>
-      <c r="AT8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU8" s="4" t="n"/>
+      <c r="AT8" s="4" t="n"/>
+      <c r="AU8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV8" s="4" t="n"/>
       <c r="AW8" s="4" t="n"/>
       <c r="AX8" s="4" t="n"/>
@@ -48279,12 +48341,12 @@
       <c r="AQ9" s="4" t="n"/>
       <c r="AR9" s="4" t="n"/>
       <c r="AS9" s="4" t="n"/>
-      <c r="AT9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU9" s="4" t="n"/>
+      <c r="AT9" s="4" t="n"/>
+      <c r="AU9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV9" s="4" t="n"/>
       <c r="AW9" s="4" t="n"/>
       <c r="AX9" s="4" t="n"/>
@@ -48388,18 +48450,18 @@
       <c r="AO10" s="4" t="n"/>
       <c r="AP10" s="4" t="n"/>
       <c r="AQ10" s="4" t="n"/>
-      <c r="AR10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS10" s="4" t="n"/>
-      <c r="AT10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU10" s="4" t="n"/>
+      <c r="AR10" s="4" t="n"/>
+      <c r="AS10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AT10" s="4" t="n"/>
+      <c r="AU10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV10" s="4" t="n"/>
       <c r="AW10" s="4" t="n"/>
       <c r="AX10" s="4" t="n"/>
@@ -48497,12 +48559,12 @@
       <c r="AQ11" s="4" t="n"/>
       <c r="AR11" s="4" t="n"/>
       <c r="AS11" s="4" t="n"/>
-      <c r="AT11" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU11" s="4" t="n"/>
+      <c r="AT11" s="4" t="n"/>
+      <c r="AU11" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV11" s="4" t="n"/>
       <c r="AW11" s="4" t="n"/>
       <c r="AX11" s="4" t="n"/>
@@ -48608,12 +48670,12 @@
       <c r="AQ12" s="4" t="n"/>
       <c r="AR12" s="4" t="n"/>
       <c r="AS12" s="4" t="n"/>
-      <c r="AT12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU12" s="4" t="n"/>
+      <c r="AT12" s="4" t="n"/>
+      <c r="AU12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV12" s="4" t="n"/>
       <c r="AW12" s="4" t="n"/>
       <c r="AX12" s="4" t="n"/>
@@ -48715,12 +48777,12 @@
       <c r="AQ13" s="4" t="n"/>
       <c r="AR13" s="4" t="n"/>
       <c r="AS13" s="4" t="n"/>
-      <c r="AT13" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU13" s="4" t="n"/>
+      <c r="AT13" s="4" t="n"/>
+      <c r="AU13" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV13" s="4" t="n"/>
       <c r="AW13" s="4" t="n"/>
       <c r="AX13" s="4" t="n"/>
@@ -48834,12 +48896,12 @@
       <c r="AQ14" s="4" t="n"/>
       <c r="AR14" s="4" t="n"/>
       <c r="AS14" s="4" t="n"/>
-      <c r="AT14" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU14" s="4" t="n"/>
+      <c r="AT14" s="4" t="n"/>
+      <c r="AU14" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV14" s="4" t="n"/>
       <c r="AW14" s="4" t="n"/>
       <c r="AX14" s="4" t="n"/>
@@ -48955,18 +49017,18 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AR15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS15" s="4" t="n"/>
-      <c r="AT15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU15" s="4" t="n"/>
+      <c r="AR15" s="4" t="n"/>
+      <c r="AS15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AT15" s="4" t="n"/>
+      <c r="AU15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV15" s="4" t="n"/>
       <c r="AW15" s="4" t="n"/>
       <c r="AX15" s="4" t="n"/>
@@ -49072,12 +49134,12 @@
       <c r="AQ16" s="4" t="n"/>
       <c r="AR16" s="4" t="n"/>
       <c r="AS16" s="4" t="n"/>
-      <c r="AT16" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU16" s="4" t="n"/>
+      <c r="AT16" s="4" t="n"/>
+      <c r="AU16" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV16" s="4" t="n"/>
       <c r="AW16" s="4" t="n"/>
       <c r="AX16" s="4" t="n"/>
@@ -49177,18 +49239,18 @@
       <c r="AO17" s="4" t="n"/>
       <c r="AP17" s="4" t="n"/>
       <c r="AQ17" s="4" t="n"/>
-      <c r="AR17" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS17" s="4" t="n"/>
-      <c r="AT17" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU17" s="4" t="n"/>
+      <c r="AR17" s="4" t="n"/>
+      <c r="AS17" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AT17" s="4" t="n"/>
+      <c r="AU17" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV17" s="4" t="n"/>
       <c r="AW17" s="4" t="n"/>
       <c r="AX17" s="4" t="n"/>
@@ -49294,12 +49356,12 @@
       <c r="AQ18" s="4" t="n"/>
       <c r="AR18" s="4" t="n"/>
       <c r="AS18" s="4" t="n"/>
-      <c r="AT18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU18" s="4" t="n"/>
+      <c r="AT18" s="4" t="n"/>
+      <c r="AU18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV18" s="4" t="n"/>
       <c r="AW18" s="4" t="n"/>
       <c r="AX18" s="4" t="n"/>
@@ -49399,18 +49461,18 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AR19" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS19" s="4" t="n"/>
-      <c r="AT19" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU19" s="4" t="n"/>
+      <c r="AR19" s="4" t="n"/>
+      <c r="AS19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AT19" s="4" t="n"/>
+      <c r="AU19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV19" s="4" t="n"/>
       <c r="AW19" s="4" t="n"/>
       <c r="AX19" s="4" t="n"/>
@@ -49502,18 +49564,18 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AR20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS20" s="4" t="n"/>
-      <c r="AT20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU20" s="4" t="n"/>
+      <c r="AR20" s="4" t="n"/>
+      <c r="AS20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AT20" s="4" t="n"/>
+      <c r="AU20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV20" s="4" t="n"/>
       <c r="AW20" s="4" t="n"/>
       <c r="AX20" s="4" t="n"/>
@@ -49611,12 +49673,12 @@
       <c r="AQ21" s="4" t="n"/>
       <c r="AR21" s="4" t="n"/>
       <c r="AS21" s="4" t="n"/>
-      <c r="AT21" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU21" s="4" t="n"/>
+      <c r="AT21" s="4" t="n"/>
+      <c r="AU21" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV21" s="4" t="n"/>
       <c r="AW21" s="4" t="n"/>
       <c r="AX21" s="4" t="n"/>
@@ -49718,12 +49780,12 @@
       <c r="AQ22" s="4" t="n"/>
       <c r="AR22" s="4" t="n"/>
       <c r="AS22" s="4" t="n"/>
-      <c r="AT22" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU22" s="4" t="n"/>
+      <c r="AT22" s="4" t="n"/>
+      <c r="AU22" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV22" s="4" t="n"/>
       <c r="AW22" s="4" t="n"/>
       <c r="AX22" s="4" t="n"/>
@@ -49821,12 +49883,12 @@
       <c r="AQ23" s="4" t="n"/>
       <c r="AR23" s="4" t="n"/>
       <c r="AS23" s="4" t="n"/>
-      <c r="AT23" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU23" s="4" t="n"/>
+      <c r="AT23" s="4" t="n"/>
+      <c r="AU23" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV23" s="4" t="n"/>
       <c r="AW23" s="4" t="n"/>
       <c r="AX23" s="4" t="n"/>
@@ -49932,12 +49994,12 @@
       <c r="AQ24" s="4" t="n"/>
       <c r="AR24" s="4" t="n"/>
       <c r="AS24" s="4" t="n"/>
-      <c r="AT24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU24" s="4" t="n"/>
+      <c r="AT24" s="4" t="n"/>
+      <c r="AU24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV24" s="4" t="n"/>
       <c r="AW24" s="4" t="n"/>
       <c r="AX24" s="4" t="n"/>
@@ -50027,12 +50089,12 @@
       <c r="AQ25" s="4" t="n"/>
       <c r="AR25" s="4" t="n"/>
       <c r="AS25" s="4" t="n"/>
-      <c r="AT25" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU25" s="4" t="n"/>
+      <c r="AT25" s="4" t="n"/>
+      <c r="AU25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV25" s="4" t="n"/>
       <c r="AW25" s="4" t="n"/>
       <c r="AX25" s="4" t="n"/>
@@ -50150,12 +50212,12 @@
       <c r="AQ26" s="4" t="n"/>
       <c r="AR26" s="4" t="n"/>
       <c r="AS26" s="4" t="n"/>
-      <c r="AT26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU26" s="4" t="n"/>
+      <c r="AT26" s="4" t="n"/>
+      <c r="AU26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV26" s="4" t="n"/>
       <c r="AW26" s="4" t="inlineStr">
         <is>
@@ -50261,12 +50323,12 @@
       <c r="AQ27" s="4" t="n"/>
       <c r="AR27" s="4" t="n"/>
       <c r="AS27" s="4" t="n"/>
-      <c r="AT27" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU27" s="4" t="n"/>
+      <c r="AT27" s="4" t="n"/>
+      <c r="AU27" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV27" s="4" t="n"/>
       <c r="AW27" s="4" t="n"/>
       <c r="AX27" s="4" t="n"/>
@@ -50368,12 +50430,12 @@
       <c r="AQ28" s="4" t="n"/>
       <c r="AR28" s="4" t="n"/>
       <c r="AS28" s="4" t="n"/>
-      <c r="AT28" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU28" s="4" t="n"/>
+      <c r="AT28" s="4" t="n"/>
+      <c r="AU28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV28" s="4" t="n"/>
       <c r="AW28" s="4" t="n"/>
       <c r="AX28" s="4" t="n"/>
@@ -50463,12 +50525,12 @@
       <c r="AQ29" s="4" t="n"/>
       <c r="AR29" s="4" t="n"/>
       <c r="AS29" s="4" t="n"/>
-      <c r="AT29" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU29" s="4" t="n"/>
+      <c r="AT29" s="4" t="n"/>
+      <c r="AU29" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV29" s="4" t="n"/>
       <c r="AW29" s="4" t="n"/>
       <c r="AX29" s="4" t="n"/>
@@ -50564,18 +50626,18 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AR30" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS30" s="4" t="n"/>
-      <c r="AT30" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU30" s="4" t="n"/>
+      <c r="AR30" s="4" t="n"/>
+      <c r="AS30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AT30" s="4" t="n"/>
+      <c r="AU30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV30" s="4" t="n"/>
       <c r="AW30" s="4" t="n"/>
       <c r="AX30" s="4" t="n"/>
@@ -50668,12 +50730,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AS31" s="4" t="n"/>
-      <c r="AT31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AS31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AT31" s="4" t="n"/>
       <c r="AU31" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -50784,12 +50846,12 @@
       <c r="AQ32" s="4" t="n"/>
       <c r="AR32" s="4" t="n"/>
       <c r="AS32" s="4" t="n"/>
-      <c r="AT32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU32" s="4" t="n"/>
+      <c r="AT32" s="4" t="n"/>
+      <c r="AU32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV32" s="4" t="n"/>
       <c r="AW32" s="4" t="n"/>
       <c r="AX32" s="4" t="inlineStr">
@@ -50893,18 +50955,18 @@
       <c r="AO33" s="4" t="n"/>
       <c r="AP33" s="4" t="n"/>
       <c r="AQ33" s="4" t="n"/>
-      <c r="AR33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS33" s="4" t="n"/>
-      <c r="AT33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU33" s="4" t="n"/>
+      <c r="AR33" s="4" t="n"/>
+      <c r="AS33" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AT33" s="4" t="n"/>
+      <c r="AU33" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV33" s="4" t="n"/>
       <c r="AW33" s="4" t="n"/>
       <c r="AX33" s="4" t="n"/>
@@ -51010,12 +51072,12 @@
       <c r="AQ34" s="4" t="n"/>
       <c r="AR34" s="4" t="n"/>
       <c r="AS34" s="4" t="n"/>
-      <c r="AT34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU34" s="4" t="n"/>
+      <c r="AT34" s="4" t="n"/>
+      <c r="AU34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV34" s="4" t="n"/>
       <c r="AW34" s="4" t="n"/>
       <c r="AX34" s="4" t="n"/>
@@ -51107,18 +51169,18 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AR35" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS35" s="4" t="n"/>
-      <c r="AT35" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU35" s="4" t="n"/>
+      <c r="AR35" s="4" t="n"/>
+      <c r="AS35" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AT35" s="4" t="n"/>
+      <c r="AU35" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV35" s="4" t="n"/>
       <c r="AW35" s="4" t="n"/>
       <c r="AX35" s="4" t="n"/>
@@ -51228,12 +51290,12 @@
       <c r="AQ36" s="4" t="n"/>
       <c r="AR36" s="4" t="n"/>
       <c r="AS36" s="4" t="n"/>
-      <c r="AT36" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU36" s="4" t="n"/>
+      <c r="AT36" s="4" t="n"/>
+      <c r="AU36" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV36" s="4" t="n"/>
       <c r="AW36" s="4" t="n"/>
       <c r="AX36" s="4" t="n"/>
@@ -51337,18 +51399,18 @@
       <c r="AO37" s="4" t="n"/>
       <c r="AP37" s="4" t="n"/>
       <c r="AQ37" s="4" t="n"/>
-      <c r="AR37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS37" s="4" t="n"/>
-      <c r="AT37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU37" s="4" t="n"/>
+      <c r="AR37" s="4" t="n"/>
+      <c r="AS37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AT37" s="4" t="n"/>
+      <c r="AU37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV37" s="4" t="n"/>
       <c r="AW37" s="4" t="n"/>
       <c r="AX37" s="4" t="n"/>
@@ -51462,12 +51524,12 @@
       <c r="AQ38" s="4" t="n"/>
       <c r="AR38" s="4" t="n"/>
       <c r="AS38" s="4" t="n"/>
-      <c r="AT38" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU38" s="4" t="n"/>
+      <c r="AT38" s="4" t="n"/>
+      <c r="AU38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV38" s="4" t="n"/>
       <c r="AW38" s="4" t="n"/>
       <c r="AX38" s="4" t="n"/>
@@ -51573,12 +51635,12 @@
       <c r="AQ39" s="4" t="n"/>
       <c r="AR39" s="4" t="n"/>
       <c r="AS39" s="4" t="n"/>
-      <c r="AT39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU39" s="4" t="n"/>
+      <c r="AT39" s="4" t="n"/>
+      <c r="AU39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV39" s="4" t="n"/>
       <c r="AW39" s="4" t="n"/>
       <c r="AX39" s="4" t="n"/>
@@ -51690,18 +51752,18 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AR40" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS40" s="4" t="n"/>
-      <c r="AT40" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU40" s="4" t="n"/>
+      <c r="AR40" s="4" t="n"/>
+      <c r="AS40" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AT40" s="4" t="n"/>
+      <c r="AU40" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV40" s="4" t="n"/>
       <c r="AW40" s="4" t="n"/>
       <c r="AX40" s="4" t="n"/>
@@ -51799,12 +51861,12 @@
       <c r="AQ41" s="4" t="n"/>
       <c r="AR41" s="4" t="n"/>
       <c r="AS41" s="4" t="n"/>
-      <c r="AT41" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU41" s="4" t="n"/>
+      <c r="AT41" s="4" t="n"/>
+      <c r="AU41" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV41" s="4" t="n"/>
       <c r="AW41" s="4" t="n"/>
       <c r="AX41" s="4" t="n"/>
@@ -51906,12 +51968,12 @@
       <c r="AQ42" s="4" t="n"/>
       <c r="AR42" s="4" t="n"/>
       <c r="AS42" s="4" t="n"/>
-      <c r="AT42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU42" s="4" t="n"/>
+      <c r="AT42" s="4" t="n"/>
+      <c r="AU42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV42" s="4" t="n"/>
       <c r="AW42" s="4" t="n"/>
       <c r="AX42" s="4" t="n"/>
@@ -52009,12 +52071,12 @@
       <c r="AQ43" s="4" t="n"/>
       <c r="AR43" s="4" t="n"/>
       <c r="AS43" s="4" t="n"/>
-      <c r="AT43" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU43" s="4" t="n"/>
+      <c r="AT43" s="4" t="n"/>
+      <c r="AU43" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV43" s="4" t="n"/>
       <c r="AW43" s="4" t="n"/>
       <c r="AX43" s="4" t="n"/>
@@ -52104,12 +52166,12 @@
       </c>
       <c r="AR44" s="4" t="n"/>
       <c r="AS44" s="4" t="n"/>
-      <c r="AT44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU44" s="4" t="n"/>
+      <c r="AT44" s="4" t="n"/>
+      <c r="AU44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV44" s="4" t="n"/>
       <c r="AW44" s="4" t="n"/>
       <c r="AX44" s="4" t="n"/>
@@ -52227,12 +52289,12 @@
       <c r="AQ45" s="4" t="n"/>
       <c r="AR45" s="4" t="n"/>
       <c r="AS45" s="4" t="n"/>
-      <c r="AT45" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU45" s="4" t="n"/>
+      <c r="AT45" s="4" t="n"/>
+      <c r="AU45" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV45" s="4" t="n"/>
       <c r="AW45" s="4" t="n"/>
       <c r="AX45" s="4" t="n"/>
@@ -52344,18 +52406,18 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AR46" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS46" s="4" t="n"/>
-      <c r="AT46" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU46" s="4" t="n"/>
+      <c r="AR46" s="4" t="n"/>
+      <c r="AS46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AT46" s="4" t="n"/>
+      <c r="AU46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV46" s="4" t="n"/>
       <c r="AW46" s="4" t="n"/>
       <c r="AX46" s="4" t="n"/>
@@ -52461,12 +52523,12 @@
       <c r="AQ47" s="4" t="n"/>
       <c r="AR47" s="4" t="n"/>
       <c r="AS47" s="4" t="n"/>
-      <c r="AT47" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU47" s="4" t="n"/>
+      <c r="AT47" s="4" t="n"/>
+      <c r="AU47" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV47" s="4" t="n"/>
       <c r="AW47" s="4" t="n"/>
       <c r="AX47" s="4" t="n"/>
@@ -52583,17 +52645,17 @@
       <c r="AP48" s="4" t="n"/>
       <c r="AQ48" s="4" t="n"/>
       <c r="AR48" s="4" t="n"/>
-      <c r="AS48" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AS48" s="4" t="n"/>
       <c r="AT48" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AU48" s="4" t="n"/>
+      <c r="AU48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV48" s="4" t="n"/>
       <c r="AW48" s="4" t="n"/>
       <c r="AX48" s="4" t="n"/>
@@ -52681,18 +52743,18 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AR49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS49" s="4" t="n"/>
-      <c r="AT49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU49" s="4" t="n"/>
+      <c r="AR49" s="4" t="n"/>
+      <c r="AS49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AT49" s="4" t="n"/>
+      <c r="AU49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV49" s="4" t="n"/>
       <c r="AW49" s="4" t="n"/>
       <c r="AX49" s="4" t="n"/>
@@ -52776,18 +52838,18 @@
       <c r="AO50" s="4" t="n"/>
       <c r="AP50" s="4" t="n"/>
       <c r="AQ50" s="4" t="n"/>
-      <c r="AR50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS50" s="4" t="n"/>
-      <c r="AT50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU50" s="4" t="n"/>
+      <c r="AR50" s="4" t="n"/>
+      <c r="AS50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AT50" s="4" t="n"/>
+      <c r="AU50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV50" s="4" t="n"/>
       <c r="AW50" s="4" t="n"/>
       <c r="AX50" s="4" t="n"/>
@@ -52901,12 +52963,12 @@
       <c r="AQ51" s="4" t="n"/>
       <c r="AR51" s="4" t="n"/>
       <c r="AS51" s="4" t="n"/>
-      <c r="AT51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU51" s="4" t="n"/>
+      <c r="AT51" s="4" t="n"/>
+      <c r="AU51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV51" s="4" t="n"/>
       <c r="AW51" s="4" t="n"/>
       <c r="AX51" s="4" t="n"/>
@@ -53012,12 +53074,12 @@
       </c>
       <c r="AR52" s="4" t="n"/>
       <c r="AS52" s="4" t="n"/>
-      <c r="AT52" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU52" s="4" t="n"/>
+      <c r="AT52" s="4" t="n"/>
+      <c r="AU52" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV52" s="4" t="n"/>
       <c r="AW52" s="4" t="n"/>
       <c r="AX52" s="4" t="n"/>
@@ -53119,12 +53181,12 @@
       <c r="AQ53" s="4" t="n"/>
       <c r="AR53" s="4" t="n"/>
       <c r="AS53" s="4" t="n"/>
-      <c r="AT53" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU53" s="4" t="n"/>
+      <c r="AT53" s="4" t="n"/>
+      <c r="AU53" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV53" s="4" t="n"/>
       <c r="AW53" s="4" t="n"/>
       <c r="AX53" s="4" t="n"/>
@@ -53222,12 +53284,12 @@
       <c r="AQ54" s="4" t="n"/>
       <c r="AR54" s="4" t="n"/>
       <c r="AS54" s="4" t="n"/>
-      <c r="AT54" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU54" s="4" t="n"/>
+      <c r="AT54" s="4" t="n"/>
+      <c r="AU54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV54" s="4" t="n"/>
       <c r="AW54" s="4" t="n"/>
       <c r="AX54" s="4" t="n"/>
@@ -53311,18 +53373,18 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AR55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS55" s="4" t="n"/>
-      <c r="AT55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU55" s="4" t="n"/>
+      <c r="AR55" s="4" t="n"/>
+      <c r="AS55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AT55" s="4" t="n"/>
+      <c r="AU55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV55" s="4" t="n"/>
       <c r="AW55" s="4" t="n"/>
       <c r="AX55" s="4" t="n"/>
@@ -53424,12 +53486,12 @@
       <c r="AQ56" s="4" t="n"/>
       <c r="AR56" s="4" t="n"/>
       <c r="AS56" s="4" t="n"/>
-      <c r="AT56" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU56" s="4" t="n"/>
+      <c r="AT56" s="4" t="n"/>
+      <c r="AU56" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV56" s="4" t="n"/>
       <c r="AW56" s="4" t="n"/>
       <c r="AX56" s="4" t="n"/>
@@ -53539,12 +53601,12 @@
       <c r="AQ57" s="4" t="n"/>
       <c r="AR57" s="4" t="n"/>
       <c r="AS57" s="4" t="n"/>
-      <c r="AT57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU57" s="4" t="n"/>
+      <c r="AT57" s="4" t="n"/>
+      <c r="AU57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV57" s="4" t="n"/>
       <c r="AW57" s="4" t="n"/>
       <c r="AX57" s="4" t="n"/>
@@ -53642,12 +53704,12 @@
       <c r="AQ58" s="4" t="n"/>
       <c r="AR58" s="4" t="n"/>
       <c r="AS58" s="4" t="n"/>
-      <c r="AT58" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU58" s="4" t="n"/>
+      <c r="AT58" s="4" t="n"/>
+      <c r="AU58" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV58" s="4" t="n"/>
       <c r="AW58" s="4" t="n"/>
       <c r="AX58" s="4" t="n"/>
@@ -53739,18 +53801,18 @@
       <c r="AO59" s="4" t="n"/>
       <c r="AP59" s="4" t="n"/>
       <c r="AQ59" s="4" t="n"/>
-      <c r="AR59" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS59" s="4" t="n"/>
-      <c r="AT59" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU59" s="4" t="n"/>
+      <c r="AR59" s="4" t="n"/>
+      <c r="AS59" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AT59" s="4" t="n"/>
+      <c r="AU59" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV59" s="4" t="n"/>
       <c r="AW59" s="4" t="n"/>
       <c r="AX59" s="4" t="n"/>
@@ -53860,12 +53922,12 @@
       <c r="AQ60" s="4" t="n"/>
       <c r="AR60" s="4" t="n"/>
       <c r="AS60" s="4" t="n"/>
-      <c r="AT60" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU60" s="4" t="n"/>
+      <c r="AT60" s="4" t="n"/>
+      <c r="AU60" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV60" s="4" t="n"/>
       <c r="AW60" s="4" t="n"/>
       <c r="AX60" s="4" t="n"/>
@@ -53969,18 +54031,18 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AR61" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS61" s="4" t="n"/>
-      <c r="AT61" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU61" s="4" t="n"/>
+      <c r="AR61" s="4" t="n"/>
+      <c r="AS61" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AT61" s="4" t="n"/>
+      <c r="AU61" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV61" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -54080,18 +54142,18 @@
       <c r="AO62" s="4" t="n"/>
       <c r="AP62" s="4" t="n"/>
       <c r="AQ62" s="4" t="n"/>
-      <c r="AR62" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS62" s="4" t="n"/>
-      <c r="AT62" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU62" s="4" t="n"/>
+      <c r="AR62" s="4" t="n"/>
+      <c r="AS62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AT62" s="4" t="n"/>
+      <c r="AU62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV62" s="4" t="n"/>
       <c r="AW62" s="4" t="n"/>
       <c r="AX62" s="4" t="n"/>
@@ -54217,12 +54279,12 @@
       <c r="AQ63" s="4" t="n"/>
       <c r="AR63" s="4" t="n"/>
       <c r="AS63" s="4" t="n"/>
-      <c r="AT63" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU63" s="4" t="n"/>
+      <c r="AT63" s="4" t="n"/>
+      <c r="AU63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV63" s="4" t="n"/>
       <c r="AW63" s="4" t="n"/>
       <c r="AX63" s="4" t="n"/>
@@ -54328,12 +54390,12 @@
       <c r="AQ64" s="4" t="n"/>
       <c r="AR64" s="4" t="n"/>
       <c r="AS64" s="4" t="n"/>
-      <c r="AT64" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU64" s="4" t="n"/>
+      <c r="AT64" s="4" t="n"/>
+      <c r="AU64" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV64" s="4" t="n"/>
       <c r="AW64" s="4" t="n"/>
       <c r="AX64" s="4" t="n"/>
@@ -54427,12 +54489,12 @@
       <c r="AQ65" s="4" t="n"/>
       <c r="AR65" s="4" t="n"/>
       <c r="AS65" s="4" t="n"/>
-      <c r="AT65" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU65" s="4" t="n"/>
+      <c r="AT65" s="4" t="n"/>
+      <c r="AU65" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV65" s="4" t="n"/>
       <c r="AW65" s="4" t="n"/>
       <c r="AX65" s="4" t="n"/>
@@ -54534,12 +54596,12 @@
       <c r="AQ66" s="4" t="n"/>
       <c r="AR66" s="4" t="n"/>
       <c r="AS66" s="4" t="n"/>
-      <c r="AT66" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU66" s="4" t="n"/>
+      <c r="AT66" s="4" t="n"/>
+      <c r="AU66" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV66" s="4" t="n"/>
       <c r="AW66" s="4" t="n"/>
       <c r="AX66" s="4" t="n"/>
@@ -54645,12 +54707,12 @@
       <c r="AQ67" s="4" t="n"/>
       <c r="AR67" s="4" t="n"/>
       <c r="AS67" s="4" t="n"/>
-      <c r="AT67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU67" s="4" t="n"/>
+      <c r="AT67" s="4" t="n"/>
+      <c r="AU67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV67" s="4" t="n"/>
       <c r="AW67" s="4" t="n"/>
       <c r="AX67" s="4" t="inlineStr">
@@ -54752,12 +54814,12 @@
       <c r="AQ68" s="4" t="n"/>
       <c r="AR68" s="4" t="n"/>
       <c r="AS68" s="4" t="n"/>
-      <c r="AT68" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU68" s="4" t="n"/>
+      <c r="AT68" s="4" t="n"/>
+      <c r="AU68" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV68" s="4" t="n"/>
       <c r="AW68" s="4" t="n"/>
       <c r="AX68" s="4" t="n"/>
@@ -54854,17 +54916,17 @@
         </is>
       </c>
       <c r="AR69" s="4" t="n"/>
-      <c r="AS69" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AS69" s="4" t="n"/>
       <c r="AT69" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AU69" s="4" t="n"/>
+      <c r="AU69" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV69" s="4" t="n"/>
       <c r="AW69" s="4" t="n"/>
       <c r="AX69" s="4" t="n"/>
@@ -54958,12 +55020,12 @@
       <c r="AQ70" s="4" t="n"/>
       <c r="AR70" s="4" t="n"/>
       <c r="AS70" s="4" t="n"/>
-      <c r="AT70" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU70" s="4" t="n"/>
+      <c r="AT70" s="4" t="n"/>
+      <c r="AU70" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV70" s="4" t="n"/>
       <c r="AW70" s="4" t="n"/>
       <c r="AX70" s="4" t="n"/>
@@ -55057,12 +55119,12 @@
       <c r="AQ71" s="4" t="n"/>
       <c r="AR71" s="4" t="n"/>
       <c r="AS71" s="4" t="n"/>
-      <c r="AT71" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU71" s="4" t="n"/>
+      <c r="AT71" s="4" t="n"/>
+      <c r="AU71" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV71" s="4" t="n"/>
       <c r="AW71" s="4" t="n"/>
       <c r="AX71" s="4" t="n"/>
@@ -55151,17 +55213,17 @@
       <c r="AP72" s="4" t="n"/>
       <c r="AQ72" s="4" t="n"/>
       <c r="AR72" s="4" t="n"/>
-      <c r="AS72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AS72" s="4" t="n"/>
       <c r="AT72" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AU72" s="4" t="n"/>
+      <c r="AU72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV72" s="4" t="n"/>
       <c r="AW72" s="4" t="n"/>
       <c r="AX72" s="4" t="n"/>
@@ -55257,18 +55319,18 @@
       <c r="AO73" s="4" t="n"/>
       <c r="AP73" s="4" t="n"/>
       <c r="AQ73" s="4" t="n"/>
-      <c r="AR73" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS73" s="4" t="n"/>
-      <c r="AT73" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU73" s="4" t="n"/>
+      <c r="AR73" s="4" t="n"/>
+      <c r="AS73" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AT73" s="4" t="n"/>
+      <c r="AU73" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV73" s="4" t="n"/>
       <c r="AW73" s="4" t="n"/>
       <c r="AX73" s="4" t="n"/>
@@ -55382,12 +55444,12 @@
       <c r="AQ74" s="4" t="n"/>
       <c r="AR74" s="4" t="n"/>
       <c r="AS74" s="4" t="n"/>
-      <c r="AT74" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU74" s="4" t="n"/>
+      <c r="AT74" s="4" t="n"/>
+      <c r="AU74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV74" s="4" t="n"/>
       <c r="AW74" s="4" t="n"/>
       <c r="AX74" s="4" t="n"/>
@@ -55481,12 +55543,12 @@
       <c r="AQ75" s="4" t="n"/>
       <c r="AR75" s="4" t="n"/>
       <c r="AS75" s="4" t="n"/>
-      <c r="AT75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU75" s="4" t="n"/>
+      <c r="AT75" s="4" t="n"/>
+      <c r="AU75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV75" s="4" t="n"/>
       <c r="AW75" s="4" t="n"/>
       <c r="AX75" s="4" t="inlineStr">
@@ -55566,18 +55628,18 @@
       <c r="AO76" s="4" t="n"/>
       <c r="AP76" s="4" t="n"/>
       <c r="AQ76" s="4" t="n"/>
-      <c r="AR76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS76" s="4" t="n"/>
-      <c r="AT76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU76" s="4" t="n"/>
+      <c r="AR76" s="4" t="n"/>
+      <c r="AS76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AT76" s="4" t="n"/>
+      <c r="AU76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV76" s="4" t="n"/>
       <c r="AW76" s="4" t="n"/>
       <c r="AX76" s="4" t="n"/>
@@ -55699,12 +55761,12 @@
       <c r="AQ77" s="4" t="n"/>
       <c r="AR77" s="4" t="n"/>
       <c r="AS77" s="4" t="n"/>
-      <c r="AT77" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU77" s="4" t="n"/>
+      <c r="AT77" s="4" t="n"/>
+      <c r="AU77" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV77" s="4" t="n"/>
       <c r="AW77" s="4" t="n"/>
       <c r="AX77" s="4" t="n"/>
@@ -55806,12 +55868,12 @@
       <c r="AQ78" s="4" t="n"/>
       <c r="AR78" s="4" t="n"/>
       <c r="AS78" s="4" t="n"/>
-      <c r="AT78" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU78" s="4" t="n"/>
+      <c r="AT78" s="4" t="n"/>
+      <c r="AU78" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV78" s="4" t="n"/>
       <c r="AW78" s="4" t="n"/>
       <c r="AX78" s="4" t="n"/>
@@ -55913,12 +55975,12 @@
       <c r="AQ79" s="4" t="n"/>
       <c r="AR79" s="4" t="n"/>
       <c r="AS79" s="4" t="n"/>
-      <c r="AT79" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU79" s="4" t="n"/>
+      <c r="AT79" s="4" t="n"/>
+      <c r="AU79" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV79" s="4" t="n"/>
       <c r="AW79" s="4" t="n"/>
       <c r="AX79" s="4" t="n"/>
@@ -56012,12 +56074,12 @@
       <c r="AQ80" s="4" t="n"/>
       <c r="AR80" s="4" t="n"/>
       <c r="AS80" s="4" t="n"/>
-      <c r="AT80" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU80" s="4" t="n"/>
+      <c r="AT80" s="4" t="n"/>
+      <c r="AU80" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV80" s="4" t="n"/>
       <c r="AW80" s="4" t="n"/>
       <c r="AX80" s="4" t="n"/>
@@ -56103,12 +56165,12 @@
       <c r="AQ81" s="4" t="n"/>
       <c r="AR81" s="4" t="n"/>
       <c r="AS81" s="4" t="n"/>
-      <c r="AT81" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU81" s="4" t="n"/>
+      <c r="AT81" s="4" t="n"/>
+      <c r="AU81" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV81" s="4" t="n"/>
       <c r="AW81" s="4" t="n"/>
       <c r="AX81" s="4" t="n"/>
@@ -56178,12 +56240,12 @@
       <c r="AQ82" s="4" t="n"/>
       <c r="AR82" s="4" t="n"/>
       <c r="AS82" s="4" t="n"/>
-      <c r="AT82" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU82" s="4" t="n"/>
+      <c r="AT82" s="4" t="n"/>
+      <c r="AU82" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV82" s="4" t="n"/>
       <c r="AW82" s="4" t="n"/>
       <c r="AX82" s="4" t="n"/>
@@ -56261,12 +56323,12 @@
       <c r="AQ83" s="4" t="n"/>
       <c r="AR83" s="4" t="n"/>
       <c r="AS83" s="4" t="n"/>
-      <c r="AT83" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU83" s="4" t="n"/>
+      <c r="AT83" s="4" t="n"/>
+      <c r="AU83" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV83" s="4" t="n"/>
       <c r="AW83" s="4" t="n"/>
       <c r="AX83" s="4" t="n"/>
@@ -56360,12 +56422,12 @@
       <c r="AQ84" s="4" t="n"/>
       <c r="AR84" s="4" t="n"/>
       <c r="AS84" s="4" t="n"/>
-      <c r="AT84" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AU84" s="4" t="n"/>
+      <c r="AT84" s="4" t="n"/>
+      <c r="AU84" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV84" s="4" t="n"/>
       <c r="AW84" s="4" t="n"/>
       <c r="AX84" s="4" t="n"/>
@@ -56495,12 +56557,12 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>白龙</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>sf90</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>白龙</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
@@ -56555,12 +56617,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M2" s="4" t="n"/>
+      <c r="L2" s="4" t="n"/>
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N2" s="4" t="n"/>
       <c r="O2" s="4" t="n"/>
       <c r="P2" s="4" t="n"/>
@@ -56653,12 +56715,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M5" s="4" t="n"/>
+      <c r="L5" s="4" t="n"/>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N5" s="4" t="n"/>
       <c r="O5" s="4" t="n"/>
       <c r="P5" s="4" t="n"/>
@@ -56855,12 +56917,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M10" s="4" t="n"/>
+      <c r="L10" s="4" t="n"/>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N10" s="4" t="n"/>
       <c r="O10" s="4" t="inlineStr">
         <is>
@@ -57033,12 +57095,12 @@
       </c>
       <c r="J15" s="4" t="n"/>
       <c r="K15" s="4" t="n"/>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M15" s="4" t="n"/>
+      <c r="L15" s="4" t="n"/>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N15" s="4" t="n"/>
       <c r="O15" s="4" t="n"/>
       <c r="P15" s="4" t="n"/>
@@ -57105,12 +57167,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L17" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M17" s="4" t="n"/>
+      <c r="L17" s="4" t="n"/>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N17" s="4" t="n"/>
       <c r="O17" s="4" t="n"/>
       <c r="P17" s="4" t="n"/>
@@ -57185,12 +57247,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M19" s="4" t="n"/>
+      <c r="L19" s="4" t="n"/>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N19" s="4" t="n"/>
       <c r="O19" s="4" t="n"/>
       <c r="P19" s="4" t="n"/>
@@ -57227,12 +57289,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M20" s="4" t="n"/>
+      <c r="L20" s="4" t="n"/>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N20" s="4" t="n"/>
       <c r="O20" s="4" t="n"/>
       <c r="P20" s="4" t="n"/>
@@ -57575,12 +57637,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L30" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M30" s="4" t="n"/>
+      <c r="L30" s="4" t="n"/>
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N30" s="4" t="n"/>
       <c r="O30" s="4" t="n"/>
       <c r="P30" s="4" t="n"/>
@@ -57689,12 +57751,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M33" s="4" t="n"/>
+      <c r="L33" s="4" t="n"/>
+      <c r="M33" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N33" s="4" t="n"/>
       <c r="O33" s="4" t="n"/>
       <c r="P33" s="4" t="n"/>
@@ -57753,12 +57815,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L35" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M35" s="4" t="n"/>
+      <c r="L35" s="4" t="n"/>
+      <c r="M35" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N35" s="4" t="n"/>
       <c r="O35" s="4" t="n"/>
       <c r="P35" s="4" t="n"/>
@@ -57825,12 +57887,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M37" s="4" t="n"/>
+      <c r="L37" s="4" t="n"/>
+      <c r="M37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N37" s="4" t="n"/>
       <c r="O37" s="4" t="n"/>
       <c r="P37" s="4" t="n"/>
@@ -57943,12 +58005,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L40" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M40" s="4" t="n"/>
+      <c r="L40" s="4" t="n"/>
+      <c r="M40" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N40" s="4" t="n"/>
       <c r="O40" s="4" t="n"/>
       <c r="P40" s="4" t="n"/>
@@ -58147,12 +58209,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L46" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M46" s="4" t="n"/>
+      <c r="L46" s="4" t="n"/>
+      <c r="M46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N46" s="4" t="n"/>
       <c r="O46" s="4" t="n"/>
       <c r="P46" s="4" t="n"/>
@@ -58253,12 +58315,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M49" s="4" t="n"/>
+      <c r="L49" s="4" t="n"/>
+      <c r="M49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N49" s="4" t="n"/>
       <c r="O49" s="4" t="n"/>
       <c r="P49" s="4" t="n"/>
@@ -58291,12 +58353,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M50" s="4" t="n"/>
+      <c r="L50" s="4" t="n"/>
+      <c r="M50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N50" s="4" t="n"/>
       <c r="O50" s="4" t="n"/>
       <c r="P50" s="4" t="n"/>
@@ -58453,12 +58515,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M55" s="4" t="n"/>
+      <c r="L55" s="4" t="n"/>
+      <c r="M55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N55" s="4" t="n"/>
       <c r="O55" s="4" t="n"/>
       <c r="P55" s="4" t="n"/>
@@ -58577,12 +58639,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L59" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M59" s="4" t="n"/>
+      <c r="L59" s="4" t="n"/>
+      <c r="M59" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N59" s="4" t="n"/>
       <c r="O59" s="4" t="n"/>
       <c r="P59" s="4" t="n"/>
@@ -58657,12 +58719,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L61" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M61" s="4" t="n"/>
+      <c r="L61" s="4" t="n"/>
+      <c r="M61" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N61" s="4" t="n"/>
       <c r="O61" s="4" t="n"/>
       <c r="P61" s="4" t="n"/>
@@ -58699,12 +58761,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L62" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M62" s="4" t="n"/>
+      <c r="L62" s="4" t="n"/>
+      <c r="M62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N62" s="4" t="n"/>
       <c r="O62" s="4" t="n"/>
       <c r="P62" s="4" t="n"/>
@@ -59047,12 +59109,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M72" s="4" t="n"/>
+      <c r="L72" s="4" t="n"/>
+      <c r="M72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N72" s="4" t="n"/>
       <c r="O72" s="4" t="n"/>
       <c r="P72" s="4" t="n"/>
@@ -59089,12 +59151,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="L73" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M73" s="4" t="n"/>
+      <c r="L73" s="4" t="n"/>
+      <c r="M73" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N73" s="4" t="n"/>
       <c r="O73" s="4" t="n"/>
       <c r="P73" s="4" t="n"/>
@@ -59199,12 +59261,12 @@
       </c>
       <c r="J76" s="4" t="n"/>
       <c r="K76" s="4" t="n"/>
-      <c r="L76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="M76" s="4" t="n"/>
+      <c r="L76" s="4" t="n"/>
+      <c r="M76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N76" s="4" t="n"/>
       <c r="O76" s="4" t="n"/>
       <c r="P76" s="4" t="n"/>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -18199,11 +18199,7 @@
         </is>
       </c>
       <c r="BJ2" s="4" t="n"/>
-      <c r="BK2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK2" s="4" t="n"/>
       <c r="BL2" s="4" t="n"/>
       <c r="BM2" s="4" t="n"/>
       <c r="BN2" s="4" t="n"/>
@@ -18349,11 +18345,7 @@
       <c r="BH3" s="4" t="n"/>
       <c r="BI3" s="4" t="n"/>
       <c r="BJ3" s="4" t="n"/>
-      <c r="BK3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK3" s="4" t="n"/>
       <c r="BL3" s="4" t="n"/>
       <c r="BM3" s="4" t="n"/>
       <c r="BN3" s="4" t="n"/>
@@ -18483,11 +18475,7 @@
       <c r="BH4" s="4" t="n"/>
       <c r="BI4" s="4" t="n"/>
       <c r="BJ4" s="4" t="n"/>
-      <c r="BK4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK4" s="4" t="n"/>
       <c r="BL4" s="4" t="n"/>
       <c r="BM4" s="4" t="n"/>
       <c r="BN4" s="4" t="n"/>
@@ -18645,11 +18633,7 @@
       <c r="BH5" s="4" t="n"/>
       <c r="BI5" s="4" t="n"/>
       <c r="BJ5" s="4" t="n"/>
-      <c r="BK5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK5" s="4" t="n"/>
       <c r="BL5" s="4" t="n"/>
       <c r="BM5" s="4" t="n"/>
       <c r="BN5" s="4" t="n"/>
@@ -18783,11 +18767,7 @@
         </is>
       </c>
       <c r="BJ6" s="4" t="n"/>
-      <c r="BK6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK6" s="4" t="n"/>
       <c r="BL6" s="4" t="n"/>
       <c r="BM6" s="4" t="n"/>
       <c r="BN6" s="4" t="inlineStr">
@@ -18953,11 +18933,7 @@
       <c r="BH7" s="4" t="n"/>
       <c r="BI7" s="4" t="n"/>
       <c r="BJ7" s="4" t="n"/>
-      <c r="BK7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK7" s="4" t="n"/>
       <c r="BL7" s="4" t="n"/>
       <c r="BM7" s="4" t="n"/>
       <c r="BN7" s="4" t="n"/>
@@ -19139,11 +19115,7 @@
       <c r="BH8" s="4" t="n"/>
       <c r="BI8" s="4" t="n"/>
       <c r="BJ8" s="4" t="n"/>
-      <c r="BK8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK8" s="4" t="n"/>
       <c r="BL8" s="4" t="n"/>
       <c r="BM8" s="4" t="n"/>
       <c r="BN8" s="4" t="n"/>
@@ -19293,11 +19265,7 @@
       <c r="BH9" s="4" t="n"/>
       <c r="BI9" s="4" t="n"/>
       <c r="BJ9" s="4" t="n"/>
-      <c r="BK9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK9" s="4" t="n"/>
       <c r="BL9" s="4" t="n"/>
       <c r="BM9" s="4" t="n"/>
       <c r="BN9" s="4" t="n"/>
@@ -19467,11 +19435,7 @@
         </is>
       </c>
       <c r="BJ10" s="4" t="n"/>
-      <c r="BK10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK10" s="4" t="n"/>
       <c r="BL10" s="4" t="n"/>
       <c r="BM10" s="4" t="n"/>
       <c r="BN10" s="4" t="n"/>
@@ -19637,11 +19601,7 @@
       <c r="BH11" s="4" t="n"/>
       <c r="BI11" s="4" t="n"/>
       <c r="BJ11" s="4" t="n"/>
-      <c r="BK11" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK11" s="4" t="n"/>
       <c r="BL11" s="4" t="n"/>
       <c r="BM11" s="4" t="n"/>
       <c r="BN11" s="4" t="n"/>
@@ -19791,11 +19751,7 @@
       <c r="BH12" s="4" t="n"/>
       <c r="BI12" s="4" t="n"/>
       <c r="BJ12" s="4" t="n"/>
-      <c r="BK12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK12" s="4" t="n"/>
       <c r="BL12" s="4" t="n"/>
       <c r="BM12" s="4" t="n"/>
       <c r="BN12" s="4" t="n"/>
@@ -19949,11 +19905,7 @@
       <c r="BH13" s="4" t="n"/>
       <c r="BI13" s="4" t="n"/>
       <c r="BJ13" s="4" t="n"/>
-      <c r="BK13" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK13" s="4" t="n"/>
       <c r="BL13" s="4" t="n"/>
       <c r="BM13" s="4" t="n"/>
       <c r="BN13" s="4" t="n"/>
@@ -20115,11 +20067,7 @@
       <c r="BH14" s="4" t="n"/>
       <c r="BI14" s="4" t="n"/>
       <c r="BJ14" s="4" t="n"/>
-      <c r="BK14" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK14" s="4" t="n"/>
       <c r="BL14" s="4" t="n"/>
       <c r="BM14" s="4" t="n"/>
       <c r="BN14" s="4" t="n"/>
@@ -20289,11 +20237,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="BK15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK15" s="4" t="n"/>
       <c r="BL15" s="4" t="n"/>
       <c r="BM15" s="4" t="n"/>
       <c r="BN15" s="4" t="n"/>
@@ -20447,11 +20391,7 @@
       <c r="BH16" s="4" t="n"/>
       <c r="BI16" s="4" t="n"/>
       <c r="BJ16" s="4" t="n"/>
-      <c r="BK16" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK16" s="4" t="n"/>
       <c r="BL16" s="4" t="n"/>
       <c r="BM16" s="4" t="n"/>
       <c r="BN16" s="4" t="n"/>
@@ -20601,11 +20541,7 @@
       <c r="BH17" s="4" t="n"/>
       <c r="BI17" s="4" t="n"/>
       <c r="BJ17" s="4" t="n"/>
-      <c r="BK17" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK17" s="4" t="n"/>
       <c r="BL17" s="4" t="n"/>
       <c r="BM17" s="4" t="n"/>
       <c r="BN17" s="4" t="n"/>
@@ -20763,11 +20699,7 @@
       <c r="BH18" s="4" t="n"/>
       <c r="BI18" s="4" t="n"/>
       <c r="BJ18" s="4" t="n"/>
-      <c r="BK18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK18" s="4" t="n"/>
       <c r="BL18" s="4" t="n"/>
       <c r="BM18" s="4" t="n"/>
       <c r="BN18" s="4" t="n"/>
@@ -20933,11 +20865,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="BK19" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK19" s="4" t="n"/>
       <c r="BL19" s="4" t="n"/>
       <c r="BM19" s="4" t="n"/>
       <c r="BN19" s="4" t="n"/>
@@ -21229,11 +21157,7 @@
       <c r="BH21" s="4" t="n"/>
       <c r="BI21" s="4" t="n"/>
       <c r="BJ21" s="4" t="n"/>
-      <c r="BK21" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK21" s="4" t="n"/>
       <c r="BL21" s="4" t="n"/>
       <c r="BM21" s="4" t="n"/>
       <c r="BN21" s="4" t="n"/>
@@ -21395,11 +21319,7 @@
       <c r="BH22" s="4" t="n"/>
       <c r="BI22" s="4" t="n"/>
       <c r="BJ22" s="4" t="n"/>
-      <c r="BK22" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK22" s="4" t="n"/>
       <c r="BL22" s="4" t="n"/>
       <c r="BM22" s="4" t="n"/>
       <c r="BN22" s="4" t="n"/>
@@ -21549,11 +21469,7 @@
       <c r="BH23" s="4" t="n"/>
       <c r="BI23" s="4" t="n"/>
       <c r="BJ23" s="4" t="n"/>
-      <c r="BK23" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK23" s="4" t="n"/>
       <c r="BL23" s="4" t="n"/>
       <c r="BM23" s="4" t="n"/>
       <c r="BN23" s="4" t="n"/>
@@ -21695,11 +21611,7 @@
       <c r="BH24" s="4" t="n"/>
       <c r="BI24" s="4" t="n"/>
       <c r="BJ24" s="4" t="n"/>
-      <c r="BK24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK24" s="4" t="n"/>
       <c r="BL24" s="4" t="n"/>
       <c r="BM24" s="4" t="n"/>
       <c r="BN24" s="4" t="n"/>
@@ -21841,11 +21753,7 @@
       <c r="BH25" s="4" t="n"/>
       <c r="BI25" s="4" t="n"/>
       <c r="BJ25" s="4" t="n"/>
-      <c r="BK25" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK25" s="4" t="n"/>
       <c r="BL25" s="4" t="n"/>
       <c r="BM25" s="4" t="n"/>
       <c r="BN25" s="4" t="n"/>
@@ -22003,11 +21911,7 @@
         </is>
       </c>
       <c r="BJ26" s="4" t="n"/>
-      <c r="BK26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK26" s="4" t="n"/>
       <c r="BL26" s="4" t="n"/>
       <c r="BM26" s="4" t="n"/>
       <c r="BN26" s="4" t="n"/>
@@ -22181,11 +22085,7 @@
       <c r="BH27" s="4" t="n"/>
       <c r="BI27" s="4" t="n"/>
       <c r="BJ27" s="4" t="n"/>
-      <c r="BK27" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK27" s="4" t="n"/>
       <c r="BL27" s="4" t="n"/>
       <c r="BM27" s="4" t="n"/>
       <c r="BN27" s="4" t="n"/>
@@ -22331,11 +22231,7 @@
       <c r="BH28" s="4" t="n"/>
       <c r="BI28" s="4" t="n"/>
       <c r="BJ28" s="4" t="n"/>
-      <c r="BK28" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK28" s="4" t="n"/>
       <c r="BL28" s="4" t="n"/>
       <c r="BM28" s="4" t="n"/>
       <c r="BN28" s="4" t="n"/>
@@ -22489,11 +22385,7 @@
       <c r="BH29" s="4" t="n"/>
       <c r="BI29" s="4" t="n"/>
       <c r="BJ29" s="4" t="n"/>
-      <c r="BK29" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK29" s="4" t="n"/>
       <c r="BL29" s="4" t="n"/>
       <c r="BM29" s="4" t="n"/>
       <c r="BN29" s="4" t="n"/>
@@ -22757,11 +22649,7 @@
         </is>
       </c>
       <c r="BJ31" s="4" t="n"/>
-      <c r="BK31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK31" s="4" t="n"/>
       <c r="BL31" s="4" t="n"/>
       <c r="BM31" s="4" t="n"/>
       <c r="BN31" s="4" t="n"/>
@@ -22939,11 +22827,7 @@
       <c r="BH32" s="4" t="n"/>
       <c r="BI32" s="4" t="n"/>
       <c r="BJ32" s="4" t="n"/>
-      <c r="BK32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK32" s="4" t="n"/>
       <c r="BL32" s="4" t="n"/>
       <c r="BM32" s="4" t="n"/>
       <c r="BN32" s="4" t="inlineStr">
@@ -23113,11 +22997,7 @@
         </is>
       </c>
       <c r="BJ33" s="4" t="n"/>
-      <c r="BK33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK33" s="4" t="n"/>
       <c r="BL33" s="4" t="n"/>
       <c r="BM33" s="4" t="n"/>
       <c r="BN33" s="4" t="n"/>
@@ -23275,11 +23155,7 @@
       <c r="BH34" s="4" t="n"/>
       <c r="BI34" s="4" t="n"/>
       <c r="BJ34" s="4" t="n"/>
-      <c r="BK34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK34" s="4" t="n"/>
       <c r="BL34" s="4" t="n"/>
       <c r="BM34" s="4" t="n"/>
       <c r="BN34" s="4" t="n"/>
@@ -23409,11 +23285,7 @@
       <c r="BH35" s="4" t="n"/>
       <c r="BI35" s="4" t="n"/>
       <c r="BJ35" s="4" t="n"/>
-      <c r="BK35" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK35" s="4" t="n"/>
       <c r="BL35" s="4" t="n"/>
       <c r="BM35" s="4" t="n"/>
       <c r="BN35" s="4" t="n"/>
@@ -23555,11 +23427,7 @@
       <c r="BH36" s="4" t="n"/>
       <c r="BI36" s="4" t="n"/>
       <c r="BJ36" s="4" t="n"/>
-      <c r="BK36" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK36" s="4" t="n"/>
       <c r="BL36" s="4" t="n"/>
       <c r="BM36" s="4" t="n"/>
       <c r="BN36" s="4" t="n"/>
@@ -23713,11 +23581,7 @@
       <c r="BH37" s="4" t="n"/>
       <c r="BI37" s="4" t="n"/>
       <c r="BJ37" s="4" t="n"/>
-      <c r="BK37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK37" s="4" t="n"/>
       <c r="BL37" s="4" t="n"/>
       <c r="BM37" s="4" t="n"/>
       <c r="BN37" s="4" t="n"/>
@@ -23863,11 +23727,7 @@
       <c r="BH38" s="4" t="n"/>
       <c r="BI38" s="4" t="n"/>
       <c r="BJ38" s="4" t="n"/>
-      <c r="BK38" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK38" s="4" t="n"/>
       <c r="BL38" s="4" t="n"/>
       <c r="BM38" s="4" t="n"/>
       <c r="BN38" s="4" t="n"/>
@@ -24029,11 +23889,7 @@
         </is>
       </c>
       <c r="BJ39" s="4" t="n"/>
-      <c r="BK39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK39" s="4" t="n"/>
       <c r="BL39" s="4" t="n"/>
       <c r="BM39" s="4" t="n"/>
       <c r="BN39" s="4" t="n"/>
@@ -24199,11 +24055,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="BK40" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK40" s="4" t="n"/>
       <c r="BL40" s="4" t="n"/>
       <c r="BM40" s="4" t="n"/>
       <c r="BN40" s="4" t="n"/>
@@ -24361,11 +24213,7 @@
         </is>
       </c>
       <c r="BJ41" s="4" t="n"/>
-      <c r="BK41" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK41" s="4" t="n"/>
       <c r="BL41" s="4" t="n"/>
       <c r="BM41" s="4" t="n"/>
       <c r="BN41" s="4" t="n"/>
@@ -24519,11 +24367,7 @@
       <c r="BH42" s="4" t="n"/>
       <c r="BI42" s="4" t="n"/>
       <c r="BJ42" s="4" t="n"/>
-      <c r="BK42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK42" s="4" t="n"/>
       <c r="BL42" s="4" t="n"/>
       <c r="BM42" s="4" t="inlineStr">
         <is>
@@ -24681,11 +24525,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="BK43" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK43" s="4" t="n"/>
       <c r="BL43" s="4" t="n"/>
       <c r="BM43" s="4" t="n"/>
       <c r="BN43" s="4" t="n"/>
@@ -24827,11 +24667,7 @@
         </is>
       </c>
       <c r="BJ44" s="4" t="n"/>
-      <c r="BK44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK44" s="4" t="n"/>
       <c r="BL44" s="4" t="n"/>
       <c r="BM44" s="4" t="n"/>
       <c r="BN44" s="4" t="n"/>
@@ -24989,11 +24825,7 @@
       <c r="BH45" s="4" t="n"/>
       <c r="BI45" s="4" t="n"/>
       <c r="BJ45" s="4" t="n"/>
-      <c r="BK45" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK45" s="4" t="n"/>
       <c r="BL45" s="4" t="n"/>
       <c r="BM45" s="4" t="n"/>
       <c r="BN45" s="4" t="n"/>
@@ -25155,11 +24987,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="BK46" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK46" s="4" t="n"/>
       <c r="BL46" s="4" t="n"/>
       <c r="BM46" s="4" t="n"/>
       <c r="BN46" s="4" t="n"/>
@@ -25309,11 +25137,7 @@
       <c r="BH47" s="4" t="n"/>
       <c r="BI47" s="4" t="n"/>
       <c r="BJ47" s="4" t="n"/>
-      <c r="BK47" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK47" s="4" t="n"/>
       <c r="BL47" s="4" t="n"/>
       <c r="BM47" s="4" t="n"/>
       <c r="BN47" s="4" t="n"/>
@@ -25471,11 +25295,7 @@
       <c r="BH48" s="4" t="n"/>
       <c r="BI48" s="4" t="n"/>
       <c r="BJ48" s="4" t="n"/>
-      <c r="BK48" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK48" s="4" t="n"/>
       <c r="BL48" s="4" t="n"/>
       <c r="BM48" s="4" t="n"/>
       <c r="BN48" s="4" t="n"/>
@@ -25629,11 +25449,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="BK49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK49" s="4" t="n"/>
       <c r="BL49" s="4" t="n"/>
       <c r="BM49" s="4" t="n"/>
       <c r="BN49" s="4" t="n"/>
@@ -25945,11 +25761,7 @@
         </is>
       </c>
       <c r="BJ51" s="4" t="n"/>
-      <c r="BK51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK51" s="4" t="n"/>
       <c r="BL51" s="4" t="n"/>
       <c r="BM51" s="4" t="n"/>
       <c r="BN51" s="4" t="n"/>
@@ -26091,11 +25903,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="BK52" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK52" s="4" t="n"/>
       <c r="BL52" s="4" t="n"/>
       <c r="BM52" s="4" t="n"/>
       <c r="BN52" s="4" t="n"/>
@@ -26249,11 +26057,7 @@
       <c r="BH53" s="4" t="n"/>
       <c r="BI53" s="4" t="n"/>
       <c r="BJ53" s="4" t="n"/>
-      <c r="BK53" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK53" s="4" t="n"/>
       <c r="BL53" s="4" t="n"/>
       <c r="BM53" s="4" t="n"/>
       <c r="BN53" s="4" t="n"/>
@@ -26415,11 +26219,7 @@
       <c r="BH54" s="4" t="n"/>
       <c r="BI54" s="4" t="n"/>
       <c r="BJ54" s="4" t="n"/>
-      <c r="BK54" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK54" s="4" t="n"/>
       <c r="BL54" s="4" t="n"/>
       <c r="BM54" s="4" t="n"/>
       <c r="BN54" s="4" t="inlineStr">
@@ -26703,11 +26503,7 @@
       <c r="BH56" s="4" t="n"/>
       <c r="BI56" s="4" t="n"/>
       <c r="BJ56" s="4" t="n"/>
-      <c r="BK56" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK56" s="4" t="n"/>
       <c r="BL56" s="4" t="n"/>
       <c r="BM56" s="4" t="n"/>
       <c r="BN56" s="4" t="n"/>
@@ -26873,11 +26669,7 @@
       <c r="BH57" s="4" t="n"/>
       <c r="BI57" s="4" t="n"/>
       <c r="BJ57" s="4" t="n"/>
-      <c r="BK57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK57" s="4" t="n"/>
       <c r="BL57" s="4" t="n"/>
       <c r="BM57" s="4" t="n"/>
       <c r="BN57" s="4" t="n"/>
@@ -27051,11 +26843,7 @@
       <c r="BH58" s="4" t="n"/>
       <c r="BI58" s="4" t="n"/>
       <c r="BJ58" s="4" t="n"/>
-      <c r="BK58" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK58" s="4" t="n"/>
       <c r="BL58" s="4" t="n"/>
       <c r="BM58" s="4" t="n"/>
       <c r="BN58" s="4" t="n"/>
@@ -27193,11 +26981,7 @@
         </is>
       </c>
       <c r="BJ59" s="4" t="n"/>
-      <c r="BK59" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK59" s="4" t="n"/>
       <c r="BL59" s="4" t="n"/>
       <c r="BM59" s="4" t="n"/>
       <c r="BN59" s="4" t="n"/>
@@ -27335,11 +27119,7 @@
       <c r="BH60" s="4" t="n"/>
       <c r="BI60" s="4" t="n"/>
       <c r="BJ60" s="4" t="n"/>
-      <c r="BK60" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK60" s="4" t="n"/>
       <c r="BL60" s="4" t="n"/>
       <c r="BM60" s="4" t="n"/>
       <c r="BN60" s="4" t="n"/>
@@ -27643,11 +27423,7 @@
       <c r="BH62" s="4" t="n"/>
       <c r="BI62" s="4" t="n"/>
       <c r="BJ62" s="4" t="n"/>
-      <c r="BK62" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK62" s="4" t="n"/>
       <c r="BL62" s="4" t="n"/>
       <c r="BM62" s="4" t="n"/>
       <c r="BN62" s="4" t="n"/>
@@ -27805,11 +27581,7 @@
       <c r="BH63" s="4" t="n"/>
       <c r="BI63" s="4" t="n"/>
       <c r="BJ63" s="4" t="n"/>
-      <c r="BK63" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK63" s="4" t="n"/>
       <c r="BL63" s="4" t="n"/>
       <c r="BM63" s="4" t="n"/>
       <c r="BN63" s="4" t="n"/>
@@ -27967,11 +27739,7 @@
       <c r="BH64" s="4" t="n"/>
       <c r="BI64" s="4" t="n"/>
       <c r="BJ64" s="4" t="n"/>
-      <c r="BK64" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK64" s="4" t="n"/>
       <c r="BL64" s="4" t="n"/>
       <c r="BM64" s="4" t="n"/>
       <c r="BN64" s="4" t="n"/>
@@ -28121,11 +27889,7 @@
       <c r="BH65" s="4" t="n"/>
       <c r="BI65" s="4" t="n"/>
       <c r="BJ65" s="4" t="n"/>
-      <c r="BK65" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK65" s="4" t="n"/>
       <c r="BL65" s="4" t="n"/>
       <c r="BM65" s="4" t="n"/>
       <c r="BN65" s="4" t="n"/>
@@ -28275,11 +28039,7 @@
       <c r="BH66" s="4" t="n"/>
       <c r="BI66" s="4" t="n"/>
       <c r="BJ66" s="4" t="n"/>
-      <c r="BK66" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK66" s="4" t="n"/>
       <c r="BL66" s="4" t="n"/>
       <c r="BM66" s="4" t="n"/>
       <c r="BN66" s="4" t="n"/>
@@ -28429,11 +28189,7 @@
         </is>
       </c>
       <c r="BJ67" s="4" t="n"/>
-      <c r="BK67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK67" s="4" t="n"/>
       <c r="BL67" s="4" t="n"/>
       <c r="BM67" s="4" t="n"/>
       <c r="BN67" s="4" t="inlineStr">
@@ -28595,11 +28351,7 @@
       <c r="BH68" s="4" t="n"/>
       <c r="BI68" s="4" t="n"/>
       <c r="BJ68" s="4" t="n"/>
-      <c r="BK68" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK68" s="4" t="n"/>
       <c r="BL68" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -28765,11 +28517,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="BK69" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK69" s="4" t="n"/>
       <c r="BL69" s="4" t="n"/>
       <c r="BM69" s="4" t="n"/>
       <c r="BN69" s="4" t="n"/>
@@ -28915,11 +28663,7 @@
         </is>
       </c>
       <c r="BJ70" s="4" t="n"/>
-      <c r="BK70" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK70" s="4" t="n"/>
       <c r="BL70" s="4" t="n"/>
       <c r="BM70" s="4" t="n"/>
       <c r="BN70" s="4" t="n"/>
@@ -29073,11 +28817,7 @@
       <c r="BH71" s="4" t="n"/>
       <c r="BI71" s="4" t="n"/>
       <c r="BJ71" s="4" t="n"/>
-      <c r="BK71" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK71" s="4" t="n"/>
       <c r="BL71" s="4" t="n"/>
       <c r="BM71" s="4" t="n"/>
       <c r="BN71" s="4" t="n"/>
@@ -29235,11 +28975,7 @@
         </is>
       </c>
       <c r="BJ72" s="4" t="n"/>
-      <c r="BK72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK72" s="4" t="n"/>
       <c r="BL72" s="4" t="n"/>
       <c r="BM72" s="4" t="n"/>
       <c r="BN72" s="4" t="n"/>
@@ -29381,11 +29117,7 @@
         </is>
       </c>
       <c r="BJ73" s="4" t="n"/>
-      <c r="BK73" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK73" s="4" t="n"/>
       <c r="BL73" s="4" t="n"/>
       <c r="BM73" s="4" t="n"/>
       <c r="BN73" s="4" t="n"/>
@@ -29539,11 +29271,7 @@
       <c r="BH74" s="4" t="n"/>
       <c r="BI74" s="4" t="n"/>
       <c r="BJ74" s="4" t="n"/>
-      <c r="BK74" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK74" s="4" t="n"/>
       <c r="BL74" s="4" t="n"/>
       <c r="BM74" s="4" t="n"/>
       <c r="BN74" s="4" t="n"/>
@@ -29705,11 +29433,7 @@
         </is>
       </c>
       <c r="BJ75" s="4" t="n"/>
-      <c r="BK75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK75" s="4" t="n"/>
       <c r="BL75" s="4" t="n"/>
       <c r="BM75" s="4" t="n"/>
       <c r="BN75" s="4" t="inlineStr">
@@ -29831,11 +29555,7 @@
       <c r="BH76" s="4" t="n"/>
       <c r="BI76" s="4" t="n"/>
       <c r="BJ76" s="4" t="n"/>
-      <c r="BK76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK76" s="4" t="n"/>
       <c r="BL76" s="4" t="n"/>
       <c r="BM76" s="4" t="n"/>
       <c r="BN76" s="4" t="n"/>
@@ -30013,11 +29733,7 @@
       <c r="BH77" s="4" t="n"/>
       <c r="BI77" s="4" t="n"/>
       <c r="BJ77" s="4" t="n"/>
-      <c r="BK77" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK77" s="4" t="n"/>
       <c r="BL77" s="4" t="n"/>
       <c r="BM77" s="4" t="n"/>
       <c r="BN77" s="4" t="n"/>
@@ -30167,11 +29883,7 @@
       <c r="BH78" s="4" t="n"/>
       <c r="BI78" s="4" t="n"/>
       <c r="BJ78" s="4" t="n"/>
-      <c r="BK78" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK78" s="4" t="n"/>
       <c r="BL78" s="4" t="n"/>
       <c r="BM78" s="4" t="n"/>
       <c r="BN78" s="4" t="n"/>
@@ -30321,11 +30033,7 @@
       <c r="BH79" s="4" t="n"/>
       <c r="BI79" s="4" t="n"/>
       <c r="BJ79" s="4" t="n"/>
-      <c r="BK79" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK79" s="4" t="n"/>
       <c r="BL79" s="4" t="n"/>
       <c r="BM79" s="4" t="n"/>
       <c r="BN79" s="4" t="n"/>
@@ -30471,11 +30179,7 @@
       <c r="BH80" s="4" t="n"/>
       <c r="BI80" s="4" t="n"/>
       <c r="BJ80" s="4" t="n"/>
-      <c r="BK80" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK80" s="4" t="n"/>
       <c r="BL80" s="4" t="n"/>
       <c r="BM80" s="4" t="n"/>
       <c r="BN80" s="4" t="n"/>
@@ -30605,11 +30309,7 @@
       <c r="BH81" s="4" t="n"/>
       <c r="BI81" s="4" t="n"/>
       <c r="BJ81" s="4" t="n"/>
-      <c r="BK81" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK81" s="4" t="n"/>
       <c r="BL81" s="4" t="n"/>
       <c r="BM81" s="4" t="n"/>
       <c r="BN81" s="4" t="n"/>
@@ -30711,11 +30411,7 @@
       <c r="BH82" s="4" t="n"/>
       <c r="BI82" s="4" t="n"/>
       <c r="BJ82" s="4" t="n"/>
-      <c r="BK82" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK82" s="4" t="n"/>
       <c r="BL82" s="4" t="n"/>
       <c r="BM82" s="4" t="n"/>
       <c r="BN82" s="4" t="n"/>
@@ -30829,11 +30525,7 @@
       <c r="BH83" s="4" t="n"/>
       <c r="BI83" s="4" t="n"/>
       <c r="BJ83" s="4" t="n"/>
-      <c r="BK83" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK83" s="4" t="n"/>
       <c r="BL83" s="4" t="n"/>
       <c r="BM83" s="4" t="n"/>
       <c r="BN83" s="4" t="n"/>
@@ -30979,11 +30671,7 @@
       <c r="BH84" s="4" t="n"/>
       <c r="BI84" s="4" t="n"/>
       <c r="BJ84" s="4" t="n"/>
-      <c r="BK84" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BK84" s="4" t="n"/>
       <c r="BL84" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -47573,11 +47261,7 @@
         </is>
       </c>
       <c r="AT2" s="4" t="n"/>
-      <c r="AU2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU2" s="4" t="n"/>
       <c r="AV2" s="4" t="n"/>
       <c r="AW2" s="4" t="n"/>
       <c r="AX2" s="4" t="n"/>
@@ -47684,11 +47368,7 @@
       <c r="AR3" s="4" t="n"/>
       <c r="AS3" s="4" t="n"/>
       <c r="AT3" s="4" t="n"/>
-      <c r="AU3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU3" s="4" t="n"/>
       <c r="AV3" s="4" t="n"/>
       <c r="AW3" s="4" t="n"/>
       <c r="AX3" s="4" t="n"/>
@@ -47787,11 +47467,7 @@
       <c r="AR4" s="4" t="n"/>
       <c r="AS4" s="4" t="n"/>
       <c r="AT4" s="4" t="n"/>
-      <c r="AU4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU4" s="4" t="n"/>
       <c r="AV4" s="4" t="n"/>
       <c r="AW4" s="4" t="n"/>
       <c r="AX4" s="4" t="n"/>
@@ -47894,11 +47570,7 @@
         </is>
       </c>
       <c r="AT5" s="4" t="n"/>
-      <c r="AU5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU5" s="4" t="n"/>
       <c r="AV5" s="4" t="n"/>
       <c r="AW5" s="4" t="n"/>
       <c r="AX5" s="4" t="n"/>
@@ -47985,11 +47657,7 @@
       <c r="AR6" s="4" t="n"/>
       <c r="AS6" s="4" t="n"/>
       <c r="AT6" s="4" t="n"/>
-      <c r="AU6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU6" s="4" t="n"/>
       <c r="AV6" s="4" t="n"/>
       <c r="AW6" s="4" t="n"/>
       <c r="AX6" s="4" t="inlineStr">
@@ -48104,11 +47772,7 @@
       <c r="AR7" s="4" t="n"/>
       <c r="AS7" s="4" t="n"/>
       <c r="AT7" s="4" t="n"/>
-      <c r="AU7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU7" s="4" t="n"/>
       <c r="AV7" s="4" t="n"/>
       <c r="AW7" s="4" t="n"/>
       <c r="AX7" s="4" t="n"/>
@@ -48235,11 +47899,7 @@
       <c r="AR8" s="4" t="n"/>
       <c r="AS8" s="4" t="n"/>
       <c r="AT8" s="4" t="n"/>
-      <c r="AU8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU8" s="4" t="n"/>
       <c r="AV8" s="4" t="n"/>
       <c r="AW8" s="4" t="n"/>
       <c r="AX8" s="4" t="n"/>
@@ -48342,11 +48002,7 @@
       <c r="AR9" s="4" t="n"/>
       <c r="AS9" s="4" t="n"/>
       <c r="AT9" s="4" t="n"/>
-      <c r="AU9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU9" s="4" t="n"/>
       <c r="AV9" s="4" t="n"/>
       <c r="AW9" s="4" t="n"/>
       <c r="AX9" s="4" t="n"/>
@@ -48457,11 +48113,7 @@
         </is>
       </c>
       <c r="AT10" s="4" t="n"/>
-      <c r="AU10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU10" s="4" t="n"/>
       <c r="AV10" s="4" t="n"/>
       <c r="AW10" s="4" t="n"/>
       <c r="AX10" s="4" t="n"/>
@@ -48560,11 +48212,7 @@
       <c r="AR11" s="4" t="n"/>
       <c r="AS11" s="4" t="n"/>
       <c r="AT11" s="4" t="n"/>
-      <c r="AU11" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU11" s="4" t="n"/>
       <c r="AV11" s="4" t="n"/>
       <c r="AW11" s="4" t="n"/>
       <c r="AX11" s="4" t="n"/>
@@ -48671,11 +48319,7 @@
       <c r="AR12" s="4" t="n"/>
       <c r="AS12" s="4" t="n"/>
       <c r="AT12" s="4" t="n"/>
-      <c r="AU12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU12" s="4" t="n"/>
       <c r="AV12" s="4" t="n"/>
       <c r="AW12" s="4" t="n"/>
       <c r="AX12" s="4" t="n"/>
@@ -48778,11 +48422,7 @@
       <c r="AR13" s="4" t="n"/>
       <c r="AS13" s="4" t="n"/>
       <c r="AT13" s="4" t="n"/>
-      <c r="AU13" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU13" s="4" t="n"/>
       <c r="AV13" s="4" t="n"/>
       <c r="AW13" s="4" t="n"/>
       <c r="AX13" s="4" t="n"/>
@@ -48897,11 +48537,7 @@
       <c r="AR14" s="4" t="n"/>
       <c r="AS14" s="4" t="n"/>
       <c r="AT14" s="4" t="n"/>
-      <c r="AU14" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU14" s="4" t="n"/>
       <c r="AV14" s="4" t="n"/>
       <c r="AW14" s="4" t="n"/>
       <c r="AX14" s="4" t="n"/>
@@ -49024,11 +48660,7 @@
         </is>
       </c>
       <c r="AT15" s="4" t="n"/>
-      <c r="AU15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU15" s="4" t="n"/>
       <c r="AV15" s="4" t="n"/>
       <c r="AW15" s="4" t="n"/>
       <c r="AX15" s="4" t="n"/>
@@ -49135,11 +48767,7 @@
       <c r="AR16" s="4" t="n"/>
       <c r="AS16" s="4" t="n"/>
       <c r="AT16" s="4" t="n"/>
-      <c r="AU16" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU16" s="4" t="n"/>
       <c r="AV16" s="4" t="n"/>
       <c r="AW16" s="4" t="n"/>
       <c r="AX16" s="4" t="n"/>
@@ -49246,11 +48874,7 @@
         </is>
       </c>
       <c r="AT17" s="4" t="n"/>
-      <c r="AU17" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU17" s="4" t="n"/>
       <c r="AV17" s="4" t="n"/>
       <c r="AW17" s="4" t="n"/>
       <c r="AX17" s="4" t="n"/>
@@ -49357,11 +48981,7 @@
       <c r="AR18" s="4" t="n"/>
       <c r="AS18" s="4" t="n"/>
       <c r="AT18" s="4" t="n"/>
-      <c r="AU18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU18" s="4" t="n"/>
       <c r="AV18" s="4" t="n"/>
       <c r="AW18" s="4" t="n"/>
       <c r="AX18" s="4" t="n"/>
@@ -49468,11 +49088,7 @@
         </is>
       </c>
       <c r="AT19" s="4" t="n"/>
-      <c r="AU19" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU19" s="4" t="n"/>
       <c r="AV19" s="4" t="n"/>
       <c r="AW19" s="4" t="n"/>
       <c r="AX19" s="4" t="n"/>
@@ -49674,11 +49290,7 @@
       <c r="AR21" s="4" t="n"/>
       <c r="AS21" s="4" t="n"/>
       <c r="AT21" s="4" t="n"/>
-      <c r="AU21" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU21" s="4" t="n"/>
       <c r="AV21" s="4" t="n"/>
       <c r="AW21" s="4" t="n"/>
       <c r="AX21" s="4" t="n"/>
@@ -49781,11 +49393,7 @@
       <c r="AR22" s="4" t="n"/>
       <c r="AS22" s="4" t="n"/>
       <c r="AT22" s="4" t="n"/>
-      <c r="AU22" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU22" s="4" t="n"/>
       <c r="AV22" s="4" t="n"/>
       <c r="AW22" s="4" t="n"/>
       <c r="AX22" s="4" t="n"/>
@@ -49884,11 +49492,7 @@
       <c r="AR23" s="4" t="n"/>
       <c r="AS23" s="4" t="n"/>
       <c r="AT23" s="4" t="n"/>
-      <c r="AU23" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU23" s="4" t="n"/>
       <c r="AV23" s="4" t="n"/>
       <c r="AW23" s="4" t="n"/>
       <c r="AX23" s="4" t="n"/>
@@ -49995,11 +49599,7 @@
       <c r="AR24" s="4" t="n"/>
       <c r="AS24" s="4" t="n"/>
       <c r="AT24" s="4" t="n"/>
-      <c r="AU24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU24" s="4" t="n"/>
       <c r="AV24" s="4" t="n"/>
       <c r="AW24" s="4" t="n"/>
       <c r="AX24" s="4" t="n"/>
@@ -50090,11 +49690,7 @@
       <c r="AR25" s="4" t="n"/>
       <c r="AS25" s="4" t="n"/>
       <c r="AT25" s="4" t="n"/>
-      <c r="AU25" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU25" s="4" t="n"/>
       <c r="AV25" s="4" t="n"/>
       <c r="AW25" s="4" t="n"/>
       <c r="AX25" s="4" t="n"/>
@@ -50213,11 +49809,7 @@
       <c r="AR26" s="4" t="n"/>
       <c r="AS26" s="4" t="n"/>
       <c r="AT26" s="4" t="n"/>
-      <c r="AU26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU26" s="4" t="n"/>
       <c r="AV26" s="4" t="n"/>
       <c r="AW26" s="4" t="inlineStr">
         <is>
@@ -50324,11 +49916,7 @@
       <c r="AR27" s="4" t="n"/>
       <c r="AS27" s="4" t="n"/>
       <c r="AT27" s="4" t="n"/>
-      <c r="AU27" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU27" s="4" t="n"/>
       <c r="AV27" s="4" t="n"/>
       <c r="AW27" s="4" t="n"/>
       <c r="AX27" s="4" t="n"/>
@@ -50431,11 +50019,7 @@
       <c r="AR28" s="4" t="n"/>
       <c r="AS28" s="4" t="n"/>
       <c r="AT28" s="4" t="n"/>
-      <c r="AU28" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU28" s="4" t="n"/>
       <c r="AV28" s="4" t="n"/>
       <c r="AW28" s="4" t="n"/>
       <c r="AX28" s="4" t="n"/>
@@ -50526,11 +50110,7 @@
       <c r="AR29" s="4" t="n"/>
       <c r="AS29" s="4" t="n"/>
       <c r="AT29" s="4" t="n"/>
-      <c r="AU29" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU29" s="4" t="n"/>
       <c r="AV29" s="4" t="n"/>
       <c r="AW29" s="4" t="n"/>
       <c r="AX29" s="4" t="n"/>
@@ -50736,11 +50316,7 @@
         </is>
       </c>
       <c r="AT31" s="4" t="n"/>
-      <c r="AU31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU31" s="4" t="n"/>
       <c r="AV31" s="4" t="n"/>
       <c r="AW31" s="4" t="n"/>
       <c r="AX31" s="4" t="n"/>
@@ -50847,11 +50423,7 @@
       <c r="AR32" s="4" t="n"/>
       <c r="AS32" s="4" t="n"/>
       <c r="AT32" s="4" t="n"/>
-      <c r="AU32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU32" s="4" t="n"/>
       <c r="AV32" s="4" t="n"/>
       <c r="AW32" s="4" t="n"/>
       <c r="AX32" s="4" t="inlineStr">
@@ -50962,11 +50534,7 @@
         </is>
       </c>
       <c r="AT33" s="4" t="n"/>
-      <c r="AU33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU33" s="4" t="n"/>
       <c r="AV33" s="4" t="n"/>
       <c r="AW33" s="4" t="n"/>
       <c r="AX33" s="4" t="n"/>
@@ -51073,11 +50641,7 @@
       <c r="AR34" s="4" t="n"/>
       <c r="AS34" s="4" t="n"/>
       <c r="AT34" s="4" t="n"/>
-      <c r="AU34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU34" s="4" t="n"/>
       <c r="AV34" s="4" t="n"/>
       <c r="AW34" s="4" t="n"/>
       <c r="AX34" s="4" t="n"/>
@@ -51176,11 +50740,7 @@
         </is>
       </c>
       <c r="AT35" s="4" t="n"/>
-      <c r="AU35" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU35" s="4" t="n"/>
       <c r="AV35" s="4" t="n"/>
       <c r="AW35" s="4" t="n"/>
       <c r="AX35" s="4" t="n"/>
@@ -51291,11 +50851,7 @@
       <c r="AR36" s="4" t="n"/>
       <c r="AS36" s="4" t="n"/>
       <c r="AT36" s="4" t="n"/>
-      <c r="AU36" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU36" s="4" t="n"/>
       <c r="AV36" s="4" t="n"/>
       <c r="AW36" s="4" t="n"/>
       <c r="AX36" s="4" t="n"/>
@@ -51406,11 +50962,7 @@
         </is>
       </c>
       <c r="AT37" s="4" t="n"/>
-      <c r="AU37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU37" s="4" t="n"/>
       <c r="AV37" s="4" t="n"/>
       <c r="AW37" s="4" t="n"/>
       <c r="AX37" s="4" t="n"/>
@@ -51525,11 +51077,7 @@
       <c r="AR38" s="4" t="n"/>
       <c r="AS38" s="4" t="n"/>
       <c r="AT38" s="4" t="n"/>
-      <c r="AU38" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU38" s="4" t="n"/>
       <c r="AV38" s="4" t="n"/>
       <c r="AW38" s="4" t="n"/>
       <c r="AX38" s="4" t="n"/>
@@ -51636,11 +51184,7 @@
       <c r="AR39" s="4" t="n"/>
       <c r="AS39" s="4" t="n"/>
       <c r="AT39" s="4" t="n"/>
-      <c r="AU39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU39" s="4" t="n"/>
       <c r="AV39" s="4" t="n"/>
       <c r="AW39" s="4" t="n"/>
       <c r="AX39" s="4" t="n"/>
@@ -51759,11 +51303,7 @@
         </is>
       </c>
       <c r="AT40" s="4" t="n"/>
-      <c r="AU40" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU40" s="4" t="n"/>
       <c r="AV40" s="4" t="n"/>
       <c r="AW40" s="4" t="n"/>
       <c r="AX40" s="4" t="n"/>
@@ -51862,11 +51402,7 @@
       <c r="AR41" s="4" t="n"/>
       <c r="AS41" s="4" t="n"/>
       <c r="AT41" s="4" t="n"/>
-      <c r="AU41" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU41" s="4" t="n"/>
       <c r="AV41" s="4" t="n"/>
       <c r="AW41" s="4" t="n"/>
       <c r="AX41" s="4" t="n"/>
@@ -51969,11 +51505,7 @@
       <c r="AR42" s="4" t="n"/>
       <c r="AS42" s="4" t="n"/>
       <c r="AT42" s="4" t="n"/>
-      <c r="AU42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU42" s="4" t="n"/>
       <c r="AV42" s="4" t="n"/>
       <c r="AW42" s="4" t="n"/>
       <c r="AX42" s="4" t="n"/>
@@ -52072,11 +51604,7 @@
       <c r="AR43" s="4" t="n"/>
       <c r="AS43" s="4" t="n"/>
       <c r="AT43" s="4" t="n"/>
-      <c r="AU43" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU43" s="4" t="n"/>
       <c r="AV43" s="4" t="n"/>
       <c r="AW43" s="4" t="n"/>
       <c r="AX43" s="4" t="n"/>
@@ -52167,11 +51695,7 @@
       <c r="AR44" s="4" t="n"/>
       <c r="AS44" s="4" t="n"/>
       <c r="AT44" s="4" t="n"/>
-      <c r="AU44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU44" s="4" t="n"/>
       <c r="AV44" s="4" t="n"/>
       <c r="AW44" s="4" t="n"/>
       <c r="AX44" s="4" t="n"/>
@@ -52290,11 +51814,7 @@
       <c r="AR45" s="4" t="n"/>
       <c r="AS45" s="4" t="n"/>
       <c r="AT45" s="4" t="n"/>
-      <c r="AU45" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU45" s="4" t="n"/>
       <c r="AV45" s="4" t="n"/>
       <c r="AW45" s="4" t="n"/>
       <c r="AX45" s="4" t="n"/>
@@ -52413,11 +51933,7 @@
         </is>
       </c>
       <c r="AT46" s="4" t="n"/>
-      <c r="AU46" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU46" s="4" t="n"/>
       <c r="AV46" s="4" t="n"/>
       <c r="AW46" s="4" t="n"/>
       <c r="AX46" s="4" t="n"/>
@@ -52524,11 +52040,7 @@
       <c r="AR47" s="4" t="n"/>
       <c r="AS47" s="4" t="n"/>
       <c r="AT47" s="4" t="n"/>
-      <c r="AU47" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU47" s="4" t="n"/>
       <c r="AV47" s="4" t="n"/>
       <c r="AW47" s="4" t="n"/>
       <c r="AX47" s="4" t="n"/>
@@ -52651,11 +52163,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AU48" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU48" s="4" t="n"/>
       <c r="AV48" s="4" t="n"/>
       <c r="AW48" s="4" t="n"/>
       <c r="AX48" s="4" t="n"/>
@@ -52750,11 +52258,7 @@
         </is>
       </c>
       <c r="AT49" s="4" t="n"/>
-      <c r="AU49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU49" s="4" t="n"/>
       <c r="AV49" s="4" t="n"/>
       <c r="AW49" s="4" t="n"/>
       <c r="AX49" s="4" t="n"/>
@@ -52964,11 +52468,7 @@
       <c r="AR51" s="4" t="n"/>
       <c r="AS51" s="4" t="n"/>
       <c r="AT51" s="4" t="n"/>
-      <c r="AU51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU51" s="4" t="n"/>
       <c r="AV51" s="4" t="n"/>
       <c r="AW51" s="4" t="n"/>
       <c r="AX51" s="4" t="n"/>
@@ -53075,11 +52575,7 @@
       <c r="AR52" s="4" t="n"/>
       <c r="AS52" s="4" t="n"/>
       <c r="AT52" s="4" t="n"/>
-      <c r="AU52" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU52" s="4" t="n"/>
       <c r="AV52" s="4" t="n"/>
       <c r="AW52" s="4" t="n"/>
       <c r="AX52" s="4" t="n"/>
@@ -53182,11 +52678,7 @@
       <c r="AR53" s="4" t="n"/>
       <c r="AS53" s="4" t="n"/>
       <c r="AT53" s="4" t="n"/>
-      <c r="AU53" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU53" s="4" t="n"/>
       <c r="AV53" s="4" t="n"/>
       <c r="AW53" s="4" t="n"/>
       <c r="AX53" s="4" t="n"/>
@@ -53285,11 +52777,7 @@
       <c r="AR54" s="4" t="n"/>
       <c r="AS54" s="4" t="n"/>
       <c r="AT54" s="4" t="n"/>
-      <c r="AU54" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU54" s="4" t="n"/>
       <c r="AV54" s="4" t="n"/>
       <c r="AW54" s="4" t="n"/>
       <c r="AX54" s="4" t="n"/>
@@ -53487,11 +52975,7 @@
       <c r="AR56" s="4" t="n"/>
       <c r="AS56" s="4" t="n"/>
       <c r="AT56" s="4" t="n"/>
-      <c r="AU56" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU56" s="4" t="n"/>
       <c r="AV56" s="4" t="n"/>
       <c r="AW56" s="4" t="n"/>
       <c r="AX56" s="4" t="n"/>
@@ -53602,11 +53086,7 @@
       <c r="AR57" s="4" t="n"/>
       <c r="AS57" s="4" t="n"/>
       <c r="AT57" s="4" t="n"/>
-      <c r="AU57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU57" s="4" t="n"/>
       <c r="AV57" s="4" t="n"/>
       <c r="AW57" s="4" t="n"/>
       <c r="AX57" s="4" t="n"/>
@@ -53705,11 +53185,7 @@
       <c r="AR58" s="4" t="n"/>
       <c r="AS58" s="4" t="n"/>
       <c r="AT58" s="4" t="n"/>
-      <c r="AU58" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU58" s="4" t="n"/>
       <c r="AV58" s="4" t="n"/>
       <c r="AW58" s="4" t="n"/>
       <c r="AX58" s="4" t="n"/>
@@ -53808,11 +53284,7 @@
         </is>
       </c>
       <c r="AT59" s="4" t="n"/>
-      <c r="AU59" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU59" s="4" t="n"/>
       <c r="AV59" s="4" t="n"/>
       <c r="AW59" s="4" t="n"/>
       <c r="AX59" s="4" t="n"/>
@@ -53923,11 +53395,7 @@
       <c r="AR60" s="4" t="n"/>
       <c r="AS60" s="4" t="n"/>
       <c r="AT60" s="4" t="n"/>
-      <c r="AU60" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU60" s="4" t="n"/>
       <c r="AV60" s="4" t="n"/>
       <c r="AW60" s="4" t="n"/>
       <c r="AX60" s="4" t="n"/>
@@ -54149,11 +53617,7 @@
         </is>
       </c>
       <c r="AT62" s="4" t="n"/>
-      <c r="AU62" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU62" s="4" t="n"/>
       <c r="AV62" s="4" t="n"/>
       <c r="AW62" s="4" t="n"/>
       <c r="AX62" s="4" t="n"/>
@@ -54280,11 +53744,7 @@
       <c r="AR63" s="4" t="n"/>
       <c r="AS63" s="4" t="n"/>
       <c r="AT63" s="4" t="n"/>
-      <c r="AU63" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU63" s="4" t="n"/>
       <c r="AV63" s="4" t="n"/>
       <c r="AW63" s="4" t="n"/>
       <c r="AX63" s="4" t="n"/>
@@ -54391,11 +53851,7 @@
       <c r="AR64" s="4" t="n"/>
       <c r="AS64" s="4" t="n"/>
       <c r="AT64" s="4" t="n"/>
-      <c r="AU64" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU64" s="4" t="n"/>
       <c r="AV64" s="4" t="n"/>
       <c r="AW64" s="4" t="n"/>
       <c r="AX64" s="4" t="n"/>
@@ -54490,11 +53946,7 @@
       <c r="AR65" s="4" t="n"/>
       <c r="AS65" s="4" t="n"/>
       <c r="AT65" s="4" t="n"/>
-      <c r="AU65" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU65" s="4" t="n"/>
       <c r="AV65" s="4" t="n"/>
       <c r="AW65" s="4" t="n"/>
       <c r="AX65" s="4" t="n"/>
@@ -54597,11 +54049,7 @@
       <c r="AR66" s="4" t="n"/>
       <c r="AS66" s="4" t="n"/>
       <c r="AT66" s="4" t="n"/>
-      <c r="AU66" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU66" s="4" t="n"/>
       <c r="AV66" s="4" t="n"/>
       <c r="AW66" s="4" t="n"/>
       <c r="AX66" s="4" t="n"/>
@@ -54708,11 +54156,7 @@
       <c r="AR67" s="4" t="n"/>
       <c r="AS67" s="4" t="n"/>
       <c r="AT67" s="4" t="n"/>
-      <c r="AU67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU67" s="4" t="n"/>
       <c r="AV67" s="4" t="n"/>
       <c r="AW67" s="4" t="n"/>
       <c r="AX67" s="4" t="inlineStr">
@@ -54815,11 +54259,7 @@
       <c r="AR68" s="4" t="n"/>
       <c r="AS68" s="4" t="n"/>
       <c r="AT68" s="4" t="n"/>
-      <c r="AU68" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU68" s="4" t="n"/>
       <c r="AV68" s="4" t="n"/>
       <c r="AW68" s="4" t="n"/>
       <c r="AX68" s="4" t="n"/>
@@ -54922,11 +54362,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AU69" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU69" s="4" t="n"/>
       <c r="AV69" s="4" t="n"/>
       <c r="AW69" s="4" t="n"/>
       <c r="AX69" s="4" t="n"/>
@@ -55021,11 +54457,7 @@
       <c r="AR70" s="4" t="n"/>
       <c r="AS70" s="4" t="n"/>
       <c r="AT70" s="4" t="n"/>
-      <c r="AU70" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU70" s="4" t="n"/>
       <c r="AV70" s="4" t="n"/>
       <c r="AW70" s="4" t="n"/>
       <c r="AX70" s="4" t="n"/>
@@ -55120,11 +54552,7 @@
       <c r="AR71" s="4" t="n"/>
       <c r="AS71" s="4" t="n"/>
       <c r="AT71" s="4" t="n"/>
-      <c r="AU71" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU71" s="4" t="n"/>
       <c r="AV71" s="4" t="n"/>
       <c r="AW71" s="4" t="n"/>
       <c r="AX71" s="4" t="n"/>
@@ -55219,11 +54647,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AU72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU72" s="4" t="n"/>
       <c r="AV72" s="4" t="n"/>
       <c r="AW72" s="4" t="n"/>
       <c r="AX72" s="4" t="n"/>
@@ -55326,11 +54750,7 @@
         </is>
       </c>
       <c r="AT73" s="4" t="n"/>
-      <c r="AU73" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU73" s="4" t="n"/>
       <c r="AV73" s="4" t="n"/>
       <c r="AW73" s="4" t="n"/>
       <c r="AX73" s="4" t="n"/>
@@ -55445,11 +54865,7 @@
       <c r="AR74" s="4" t="n"/>
       <c r="AS74" s="4" t="n"/>
       <c r="AT74" s="4" t="n"/>
-      <c r="AU74" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU74" s="4" t="n"/>
       <c r="AV74" s="4" t="n"/>
       <c r="AW74" s="4" t="n"/>
       <c r="AX74" s="4" t="n"/>
@@ -55544,11 +54960,7 @@
       <c r="AR75" s="4" t="n"/>
       <c r="AS75" s="4" t="n"/>
       <c r="AT75" s="4" t="n"/>
-      <c r="AU75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU75" s="4" t="n"/>
       <c r="AV75" s="4" t="n"/>
       <c r="AW75" s="4" t="n"/>
       <c r="AX75" s="4" t="inlineStr">
@@ -55635,11 +55047,7 @@
         </is>
       </c>
       <c r="AT76" s="4" t="n"/>
-      <c r="AU76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU76" s="4" t="n"/>
       <c r="AV76" s="4" t="n"/>
       <c r="AW76" s="4" t="n"/>
       <c r="AX76" s="4" t="n"/>
@@ -55762,11 +55170,7 @@
       <c r="AR77" s="4" t="n"/>
       <c r="AS77" s="4" t="n"/>
       <c r="AT77" s="4" t="n"/>
-      <c r="AU77" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU77" s="4" t="n"/>
       <c r="AV77" s="4" t="n"/>
       <c r="AW77" s="4" t="n"/>
       <c r="AX77" s="4" t="n"/>
@@ -55869,11 +55273,7 @@
       <c r="AR78" s="4" t="n"/>
       <c r="AS78" s="4" t="n"/>
       <c r="AT78" s="4" t="n"/>
-      <c r="AU78" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU78" s="4" t="n"/>
       <c r="AV78" s="4" t="n"/>
       <c r="AW78" s="4" t="n"/>
       <c r="AX78" s="4" t="n"/>
@@ -55976,11 +55376,7 @@
       <c r="AR79" s="4" t="n"/>
       <c r="AS79" s="4" t="n"/>
       <c r="AT79" s="4" t="n"/>
-      <c r="AU79" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU79" s="4" t="n"/>
       <c r="AV79" s="4" t="n"/>
       <c r="AW79" s="4" t="n"/>
       <c r="AX79" s="4" t="n"/>
@@ -56075,11 +55471,7 @@
       <c r="AR80" s="4" t="n"/>
       <c r="AS80" s="4" t="n"/>
       <c r="AT80" s="4" t="n"/>
-      <c r="AU80" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU80" s="4" t="n"/>
       <c r="AV80" s="4" t="n"/>
       <c r="AW80" s="4" t="n"/>
       <c r="AX80" s="4" t="n"/>
@@ -56166,11 +55558,7 @@
       <c r="AR81" s="4" t="n"/>
       <c r="AS81" s="4" t="n"/>
       <c r="AT81" s="4" t="n"/>
-      <c r="AU81" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU81" s="4" t="n"/>
       <c r="AV81" s="4" t="n"/>
       <c r="AW81" s="4" t="n"/>
       <c r="AX81" s="4" t="n"/>
@@ -56241,11 +55629,7 @@
       <c r="AR82" s="4" t="n"/>
       <c r="AS82" s="4" t="n"/>
       <c r="AT82" s="4" t="n"/>
-      <c r="AU82" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU82" s="4" t="n"/>
       <c r="AV82" s="4" t="n"/>
       <c r="AW82" s="4" t="n"/>
       <c r="AX82" s="4" t="n"/>
@@ -56324,11 +55708,7 @@
       <c r="AR83" s="4" t="n"/>
       <c r="AS83" s="4" t="n"/>
       <c r="AT83" s="4" t="n"/>
-      <c r="AU83" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU83" s="4" t="n"/>
       <c r="AV83" s="4" t="n"/>
       <c r="AW83" s="4" t="n"/>
       <c r="AX83" s="4" t="n"/>
@@ -56423,11 +55803,7 @@
       <c r="AR84" s="4" t="n"/>
       <c r="AS84" s="4" t="n"/>
       <c r="AT84" s="4" t="n"/>
-      <c r="AU84" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU84" s="4" t="n"/>
       <c r="AV84" s="4" t="n"/>
       <c r="AW84" s="4" t="n"/>
       <c r="AX84" s="4" t="n"/>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -16271,7 +16271,7 @@
       <c r="AB73" s="4" t="n"/>
       <c r="AC73" s="4" t="n"/>
       <c r="AD73" s="4" t="n">
-        <v>19.45</v>
+        <v>19.4</v>
       </c>
       <c r="AE73" s="4" t="n"/>
       <c r="AF73" s="4" t="n"/>
@@ -16288,7 +16288,9 @@
       <c r="AO73" s="4" t="n"/>
       <c r="AP73" s="4" t="n"/>
       <c r="AQ73" s="4" t="n"/>
-      <c r="AR73" s="4" t="n"/>
+      <c r="AR73" s="4" t="n">
+        <v>19.5</v>
+      </c>
       <c r="AS73" s="4" t="n"/>
       <c r="AT73" s="4" t="n"/>
       <c r="AU73" s="4" t="n"/>
@@ -16301,11 +16303,9 @@
       <c r="BB73" s="4" t="n"/>
       <c r="BC73" s="4" t="n"/>
       <c r="BD73" s="4" t="n"/>
-      <c r="BE73" s="4" t="n">
-        <v>18.9</v>
-      </c>
+      <c r="BE73" s="4" t="n"/>
       <c r="BF73" s="4" t="n">
-        <v>19.59</v>
+        <v>19.6</v>
       </c>
       <c r="BG73" s="4" t="n"/>
       <c r="BH73" s="4" t="n"/>
@@ -29095,11 +29095,7 @@
       <c r="BB73" s="4" t="n"/>
       <c r="BC73" s="4" t="n"/>
       <c r="BD73" s="4" t="n"/>
-      <c r="BE73" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BE73" s="4" t="n"/>
       <c r="BF73" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -41154,7 +41150,9 @@
       </c>
       <c r="O10" s="4" t="n"/>
       <c r="P10" s="4" t="n"/>
-      <c r="Q10" s="4" t="n"/>
+      <c r="Q10" s="4" t="n">
+        <v>23.4</v>
+      </c>
       <c r="R10" s="4" t="n"/>
       <c r="S10" s="4" t="n"/>
       <c r="T10" s="4" t="n"/>
@@ -41164,8 +41162,12 @@
       <c r="X10" s="4" t="n"/>
       <c r="Y10" s="4" t="n"/>
       <c r="Z10" s="4" t="n"/>
-      <c r="AA10" s="4" t="n"/>
-      <c r="AB10" s="4" t="n"/>
+      <c r="AA10" s="4" t="n">
+        <v>23.42</v>
+      </c>
+      <c r="AB10" s="4" t="n">
+        <v>23.45</v>
+      </c>
       <c r="AC10" s="4" t="n"/>
       <c r="AD10" s="4" t="n"/>
       <c r="AE10" s="4" t="n"/>
@@ -41829,13 +41831,21 @@
       <c r="D19" s="4" t="n"/>
       <c r="E19" s="4" t="n"/>
       <c r="F19" s="4" t="n"/>
-      <c r="G19" s="4" t="n"/>
+      <c r="G19" s="4" t="n">
+        <v>33.5</v>
+      </c>
       <c r="H19" s="4" t="n"/>
-      <c r="I19" s="4" t="n"/>
-      <c r="J19" s="4" t="n"/>
+      <c r="I19" s="4" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>32.7</v>
+      </c>
       <c r="K19" s="4" t="n"/>
       <c r="L19" s="4" t="n"/>
-      <c r="M19" s="4" t="n"/>
+      <c r="M19" s="4" t="n">
+        <v>32.5</v>
+      </c>
       <c r="N19" s="4" t="n">
         <v>33.4</v>
       </c>
@@ -42208,7 +42218,9 @@
         <v>23.69</v>
       </c>
       <c r="P24" s="4" t="n"/>
-      <c r="Q24" s="4" t="n"/>
+      <c r="Q24" s="4" t="n">
+        <v>23.3</v>
+      </c>
       <c r="R24" s="4" t="n"/>
       <c r="S24" s="4" t="n"/>
       <c r="T24" s="4" t="n"/>
@@ -42218,8 +42230,12 @@
       <c r="X24" s="4" t="n"/>
       <c r="Y24" s="4" t="n"/>
       <c r="Z24" s="4" t="n"/>
-      <c r="AA24" s="4" t="n"/>
-      <c r="AB24" s="4" t="n"/>
+      <c r="AA24" s="4" t="n">
+        <v>22.97</v>
+      </c>
+      <c r="AB24" s="4" t="n">
+        <v>22.85</v>
+      </c>
       <c r="AC24" s="4" t="n"/>
       <c r="AD24" s="4" t="n"/>
       <c r="AE24" s="4" t="n"/>
@@ -42227,7 +42243,9 @@
       <c r="AG24" s="4" t="n"/>
       <c r="AH24" s="4" t="n"/>
       <c r="AI24" s="4" t="n"/>
-      <c r="AJ24" s="4" t="n"/>
+      <c r="AJ24" s="4" t="n">
+        <v>23.03</v>
+      </c>
       <c r="AK24" s="4" t="n"/>
       <c r="AL24" s="4" t="n"/>
       <c r="AM24" s="4" t="n"/>
@@ -43329,7 +43347,9 @@
       <c r="N39" s="4" t="n"/>
       <c r="O39" s="4" t="n"/>
       <c r="P39" s="4" t="n"/>
-      <c r="Q39" s="4" t="n"/>
+      <c r="Q39" s="4" t="n">
+        <v>29.9</v>
+      </c>
       <c r="R39" s="4" t="n"/>
       <c r="S39" s="4" t="n"/>
       <c r="T39" s="4" t="n"/>
@@ -43339,7 +43359,9 @@
       <c r="X39" s="4" t="n"/>
       <c r="Y39" s="4" t="n"/>
       <c r="Z39" s="4" t="n"/>
-      <c r="AA39" s="4" t="n"/>
+      <c r="AA39" s="4" t="n">
+        <v>30.2</v>
+      </c>
       <c r="AB39" s="4" t="n"/>
       <c r="AC39" s="4" t="n"/>
       <c r="AD39" s="4" t="n"/>
@@ -45890,7 +45912,9 @@
       <c r="K73" s="4" t="n"/>
       <c r="L73" s="4" t="n"/>
       <c r="M73" s="4" t="n"/>
-      <c r="N73" s="4" t="n"/>
+      <c r="N73" s="4" t="n">
+        <v>19.4</v>
+      </c>
       <c r="O73" s="4" t="n"/>
       <c r="P73" s="4" t="n"/>
       <c r="Q73" s="4" t="n"/>
@@ -45908,9 +45932,13 @@
       <c r="AC73" s="4" t="n"/>
       <c r="AD73" s="4" t="n"/>
       <c r="AE73" s="4" t="n"/>
-      <c r="AF73" s="4" t="n"/>
+      <c r="AF73" s="4" t="n">
+        <v>19.5</v>
+      </c>
       <c r="AG73" s="4" t="n"/>
-      <c r="AH73" s="4" t="n"/>
+      <c r="AH73" s="4" t="n">
+        <v>19.6</v>
+      </c>
       <c r="AI73" s="4" t="n"/>
       <c r="AJ73" s="4" t="n"/>
       <c r="AK73" s="4" t="n"/>
@@ -46039,7 +46067,9 @@
       <c r="N75" s="4" t="n"/>
       <c r="O75" s="4" t="n"/>
       <c r="P75" s="4" t="n"/>
-      <c r="Q75" s="4" t="n"/>
+      <c r="Q75" s="4" t="n">
+        <v>27.1</v>
+      </c>
       <c r="R75" s="4" t="n"/>
       <c r="S75" s="4" t="n"/>
       <c r="T75" s="4" t="n"/>
@@ -46047,10 +46077,18 @@
       <c r="V75" s="4" t="n"/>
       <c r="W75" s="4" t="n"/>
       <c r="X75" s="4" t="n"/>
-      <c r="Y75" s="4" t="n"/>
-      <c r="Z75" s="4" t="n"/>
-      <c r="AA75" s="4" t="n"/>
-      <c r="AB75" s="4" t="n"/>
+      <c r="Y75" s="4" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="Z75" s="4" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="AA75" s="4" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="AB75" s="4" t="n">
+        <v>27.15</v>
+      </c>
       <c r="AC75" s="4" t="n"/>
       <c r="AD75" s="4" t="n"/>
       <c r="AE75" s="4" t="n"/>
@@ -46489,13 +46527,15 @@
       <c r="D81" s="4" t="n"/>
       <c r="E81" s="4" t="n"/>
       <c r="F81" s="4" t="n"/>
-      <c r="G81" s="4" t="n"/>
+      <c r="G81" s="4" t="n">
+        <v>64.40000000000001</v>
+      </c>
       <c r="H81" s="4" t="n"/>
       <c r="I81" s="4" t="n"/>
-      <c r="J81" s="4" t="n"/>
-      <c r="K81" s="4" t="n">
-        <v>64.79000000000001</v>
-      </c>
+      <c r="J81" s="4" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="K81" s="4" t="n"/>
       <c r="L81" s="4" t="n"/>
       <c r="M81" s="4" t="n">
         <v>63.8</v>
@@ -46562,15 +46602,21 @@
       <c r="D82" s="4" t="n"/>
       <c r="E82" s="4" t="n"/>
       <c r="F82" s="4" t="n"/>
-      <c r="G82" s="4" t="n"/>
+      <c r="G82" s="4" t="n">
+        <v>55.5</v>
+      </c>
       <c r="H82" s="4" t="n"/>
       <c r="I82" s="4" t="n"/>
-      <c r="J82" s="4" t="n"/>
+      <c r="J82" s="4" t="n">
+        <v>54.8</v>
+      </c>
       <c r="K82" s="4" t="n">
         <v>53.3</v>
       </c>
       <c r="L82" s="4" t="n"/>
-      <c r="M82" s="4" t="n"/>
+      <c r="M82" s="4" t="n">
+        <v>54.3</v>
+      </c>
       <c r="N82" s="4" t="n"/>
       <c r="O82" s="4" t="n"/>
       <c r="P82" s="4" t="n"/>
@@ -48055,7 +48101,11 @@
       </c>
       <c r="O10" s="4" t="n"/>
       <c r="P10" s="4" t="n"/>
-      <c r="Q10" s="4" t="n"/>
+      <c r="Q10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="R10" s="4" t="n"/>
       <c r="S10" s="4" t="n"/>
       <c r="T10" s="4" t="n"/>
@@ -48065,7 +48115,11 @@
       <c r="X10" s="4" t="n"/>
       <c r="Y10" s="4" t="n"/>
       <c r="Z10" s="4" t="n"/>
-      <c r="AA10" s="4" t="n"/>
+      <c r="AA10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AB10" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -49022,11 +49076,23 @@
         </is>
       </c>
       <c r="H19" s="4" t="n"/>
-      <c r="I19" s="4" t="n"/>
-      <c r="J19" s="4" t="n"/>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="K19" s="4" t="n"/>
       <c r="L19" s="4" t="n"/>
-      <c r="M19" s="4" t="n"/>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -54715,7 +54781,11 @@
       <c r="AC73" s="4" t="n"/>
       <c r="AD73" s="4" t="n"/>
       <c r="AE73" s="4" t="n"/>
-      <c r="AF73" s="4" t="n"/>
+      <c r="AF73" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AG73" s="4" t="n"/>
       <c r="AH73" s="4" t="inlineStr">
         <is>
@@ -54914,8 +54984,16 @@
       <c r="V75" s="4" t="n"/>
       <c r="W75" s="4" t="n"/>
       <c r="X75" s="4" t="n"/>
-      <c r="Y75" s="4" t="n"/>
-      <c r="Z75" s="4" t="n"/>
+      <c r="Y75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Z75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AA75" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -55506,15 +55584,19 @@
       <c r="D81" s="4" t="n"/>
       <c r="E81" s="4" t="n"/>
       <c r="F81" s="4" t="n"/>
-      <c r="G81" s="4" t="n"/>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H81" s="4" t="n"/>
       <c r="I81" s="4" t="n"/>
-      <c r="J81" s="4" t="n"/>
-      <c r="K81" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K81" s="4" t="n"/>
       <c r="L81" s="4" t="n"/>
       <c r="M81" s="4" t="inlineStr">
         <is>
@@ -55585,17 +55667,29 @@
       <c r="D82" s="4" t="n"/>
       <c r="E82" s="4" t="n"/>
       <c r="F82" s="4" t="n"/>
-      <c r="G82" s="4" t="n"/>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H82" s="4" t="n"/>
       <c r="I82" s="4" t="n"/>
-      <c r="J82" s="4" t="n"/>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="K82" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
       <c r="L82" s="4" t="n"/>
-      <c r="M82" s="4" t="n"/>
+      <c r="M82" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N82" s="4" t="n"/>
       <c r="O82" s="4" t="n"/>
       <c r="P82" s="4" t="n"/>
@@ -59136,7 +59230,7 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>23.1</v>
+        <v>22.89</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -703,12 +703,12 @@
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
+          <t>莫斯勒</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
           <t>肥龙</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>莫斯勒</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
@@ -1175,10 +1175,10 @@
       </c>
       <c r="Y5" s="4" t="n"/>
       <c r="Z5" s="4" t="n"/>
-      <c r="AA5" s="4" t="n">
+      <c r="AA5" s="4" t="n"/>
+      <c r="AB5" s="4" t="n">
         <v>17.5</v>
       </c>
-      <c r="AB5" s="4" t="n"/>
       <c r="AC5" s="4" t="n"/>
       <c r="AD5" s="4" t="n">
         <v>18.39</v>
@@ -1263,7 +1263,7 @@
         <v>17.59</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>18.16</v>
+        <v>17.8</v>
       </c>
       <c r="U6" s="4" t="n"/>
       <c r="V6" s="4" t="n"/>
@@ -1355,10 +1355,10 @@
       <c r="X7" s="4" t="n"/>
       <c r="Y7" s="4" t="n"/>
       <c r="Z7" s="4" t="n"/>
-      <c r="AA7" s="4" t="n"/>
-      <c r="AB7" s="4" t="n">
+      <c r="AA7" s="4" t="n">
         <v>24.36</v>
       </c>
+      <c r="AB7" s="4" t="n"/>
       <c r="AC7" s="4" t="n"/>
       <c r="AD7" s="4" t="n"/>
       <c r="AE7" s="4" t="n"/>
@@ -1447,10 +1447,10 @@
       <c r="Z8" s="4" t="n">
         <v>26.998</v>
       </c>
-      <c r="AA8" s="4" t="n"/>
-      <c r="AB8" s="4" t="n">
+      <c r="AA8" s="4" t="n">
         <v>26.89</v>
       </c>
+      <c r="AB8" s="4" t="n"/>
       <c r="AC8" s="4" t="n"/>
       <c r="AD8" s="4" t="n"/>
       <c r="AE8" s="4" t="n"/>
@@ -1694,7 +1694,9 @@
       <c r="M11" s="4" t="n"/>
       <c r="N11" s="4" t="n"/>
       <c r="O11" s="4" t="n"/>
-      <c r="P11" s="4" t="n"/>
+      <c r="P11" s="4" t="n">
+        <v>35.3</v>
+      </c>
       <c r="Q11" s="4" t="n"/>
       <c r="R11" s="4" t="n"/>
       <c r="S11" s="4" t="n"/>
@@ -1705,10 +1707,10 @@
       <c r="X11" s="4" t="n"/>
       <c r="Y11" s="4" t="n"/>
       <c r="Z11" s="4" t="n"/>
-      <c r="AA11" s="4" t="n"/>
-      <c r="AB11" s="4" t="n">
+      <c r="AA11" s="4" t="n">
         <v>34.2</v>
       </c>
+      <c r="AB11" s="4" t="n"/>
       <c r="AC11" s="4" t="n"/>
       <c r="AD11" s="4" t="n"/>
       <c r="AE11" s="4" t="n"/>
@@ -1789,10 +1791,10 @@
       </c>
       <c r="Y12" s="4" t="n"/>
       <c r="Z12" s="4" t="n"/>
-      <c r="AA12" s="4" t="n">
+      <c r="AA12" s="4" t="n"/>
+      <c r="AB12" s="4" t="n">
         <v>21.3</v>
       </c>
-      <c r="AB12" s="4" t="n"/>
       <c r="AC12" s="4" t="n"/>
       <c r="AD12" s="4" t="n"/>
       <c r="AE12" s="4" t="n"/>
@@ -1877,10 +1879,10 @@
       <c r="Z13" s="4" t="n">
         <v>40.25</v>
       </c>
-      <c r="AA13" s="4" t="n"/>
-      <c r="AB13" s="4" t="n">
+      <c r="AA13" s="4" t="n">
         <v>40.3</v>
       </c>
+      <c r="AB13" s="4" t="n"/>
       <c r="AC13" s="4" t="n"/>
       <c r="AD13" s="4" t="n"/>
       <c r="AE13" s="4" t="n"/>
@@ -1975,10 +1977,10 @@
       <c r="X14" s="4" t="n"/>
       <c r="Y14" s="4" t="n"/>
       <c r="Z14" s="4" t="n"/>
-      <c r="AA14" s="4" t="n"/>
-      <c r="AB14" s="4" t="n">
+      <c r="AA14" s="4" t="n">
         <v>24.9</v>
       </c>
+      <c r="AB14" s="4" t="n"/>
       <c r="AC14" s="4" t="n"/>
       <c r="AD14" s="4" t="n"/>
       <c r="AE14" s="4" t="n">
@@ -2071,10 +2073,10 @@
       <c r="Z15" s="4" t="n">
         <v>27.65</v>
       </c>
-      <c r="AA15" s="4" t="n"/>
-      <c r="AB15" s="4" t="n">
+      <c r="AA15" s="4" t="n">
         <v>28</v>
       </c>
+      <c r="AB15" s="4" t="n"/>
       <c r="AC15" s="4" t="n"/>
       <c r="AD15" s="4" t="n"/>
       <c r="AE15" s="4" t="n"/>
@@ -2151,10 +2153,10 @@
       <c r="X16" s="4" t="n"/>
       <c r="Y16" s="4" t="n"/>
       <c r="Z16" s="4" t="n"/>
-      <c r="AA16" s="4" t="n"/>
-      <c r="AB16" s="4" t="n">
+      <c r="AA16" s="4" t="n">
         <v>37.4</v>
       </c>
+      <c r="AB16" s="4" t="n"/>
       <c r="AC16" s="4" t="n"/>
       <c r="AD16" s="4" t="n"/>
       <c r="AE16" s="4" t="n"/>
@@ -2207,7 +2209,7 @@
         <v>28.5</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>29.3</v>
+        <v>29.12</v>
       </c>
       <c r="I17" s="4" t="n">
         <v>29.6</v>
@@ -2216,7 +2218,7 @@
         <v>29.5</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>29.3</v>
+        <v>29.29</v>
       </c>
       <c r="L17" s="4" t="n">
         <v>29.3</v>
@@ -2333,10 +2335,10 @@
         <v>24.19</v>
       </c>
       <c r="Z18" s="4" t="n"/>
-      <c r="AA18" s="4" t="n">
+      <c r="AA18" s="4" t="n"/>
+      <c r="AB18" s="4" t="n">
         <v>23.1</v>
       </c>
-      <c r="AB18" s="4" t="n"/>
       <c r="AC18" s="4" t="n"/>
       <c r="AD18" s="4" t="n"/>
       <c r="AE18" s="4" t="n">
@@ -2511,10 +2513,10 @@
       <c r="X20" s="4" t="n"/>
       <c r="Y20" s="4" t="n"/>
       <c r="Z20" s="4" t="n"/>
-      <c r="AA20" s="4" t="n"/>
-      <c r="AB20" s="4" t="n">
+      <c r="AA20" s="4" t="n">
         <v>22.35</v>
       </c>
+      <c r="AB20" s="4" t="n"/>
       <c r="AC20" s="4" t="n">
         <v>22.5</v>
       </c>
@@ -2693,10 +2695,10 @@
       <c r="X22" s="4" t="n"/>
       <c r="Y22" s="4" t="n"/>
       <c r="Z22" s="4" t="n"/>
-      <c r="AA22" s="4" t="n">
+      <c r="AA22" s="4" t="n"/>
+      <c r="AB22" s="4" t="n">
         <v>30.7</v>
       </c>
-      <c r="AB22" s="4" t="n"/>
       <c r="AC22" s="4" t="n"/>
       <c r="AD22" s="4" t="n"/>
       <c r="AE22" s="4" t="n"/>
@@ -2857,10 +2859,10 @@
       <c r="X24" s="4" t="n"/>
       <c r="Y24" s="4" t="n"/>
       <c r="Z24" s="4" t="n"/>
-      <c r="AA24" s="4" t="n">
+      <c r="AA24" s="4" t="n"/>
+      <c r="AB24" s="4" t="n">
         <v>22.45</v>
       </c>
-      <c r="AB24" s="4" t="n"/>
       <c r="AC24" s="4" t="n"/>
       <c r="AD24" s="4" t="n"/>
       <c r="AE24" s="4" t="n"/>
@@ -3027,10 +3029,10 @@
       <c r="X26" s="4" t="n"/>
       <c r="Y26" s="4" t="n"/>
       <c r="Z26" s="4" t="n"/>
-      <c r="AA26" s="4" t="n">
+      <c r="AA26" s="4" t="n"/>
+      <c r="AB26" s="4" t="n">
         <v>18.55</v>
       </c>
-      <c r="AB26" s="4" t="n"/>
       <c r="AC26" s="4" t="n"/>
       <c r="AD26" s="4" t="n"/>
       <c r="AE26" s="4" t="n"/>
@@ -4481,10 +4483,10 @@
       <c r="X43" s="4" t="n"/>
       <c r="Y43" s="4" t="n"/>
       <c r="Z43" s="4" t="n"/>
-      <c r="AA43" s="4" t="n"/>
-      <c r="AB43" s="4" t="n">
+      <c r="AA43" s="4" t="n">
         <v>37.6</v>
       </c>
+      <c r="AB43" s="4" t="n"/>
       <c r="AC43" s="4" t="n"/>
       <c r="AD43" s="4" t="n"/>
       <c r="AE43" s="4" t="n"/>
@@ -4694,7 +4696,7 @@
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>30.89</v>
+        <v>30.83</v>
       </c>
       <c r="D46" s="4" t="n">
         <v>31.15</v>
@@ -4707,10 +4709,10 @@
         <v>30.8</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>31.6</v>
+        <v>31.49</v>
       </c>
       <c r="I46" s="4" t="n">
-        <v>31.8</v>
+        <v>31.69</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>32.2</v>
@@ -4724,7 +4726,7 @@
       <c r="O46" s="4" t="n"/>
       <c r="P46" s="4" t="n"/>
       <c r="Q46" s="4" t="n">
-        <v>31.8</v>
+        <v>31.29</v>
       </c>
       <c r="R46" s="4" t="n"/>
       <c r="S46" s="4" t="n">
@@ -5101,10 +5103,10 @@
       <c r="Z50" s="4" t="n">
         <v>26.79</v>
       </c>
-      <c r="AA50" s="4" t="n"/>
-      <c r="AB50" s="4" t="n">
+      <c r="AA50" s="4" t="n">
         <v>26.6</v>
       </c>
+      <c r="AB50" s="4" t="n"/>
       <c r="AC50" s="4" t="n">
         <v>26.6</v>
       </c>
@@ -6391,10 +6393,10 @@
       <c r="Z65" s="4" t="n">
         <v>31.7</v>
       </c>
-      <c r="AA65" s="4" t="n"/>
-      <c r="AB65" s="4" t="n">
+      <c r="AA65" s="4" t="n">
         <v>31.8</v>
       </c>
+      <c r="AB65" s="4" t="n"/>
       <c r="AC65" s="4" t="n"/>
       <c r="AD65" s="4" t="n"/>
       <c r="AE65" s="4" t="n"/>
@@ -6649,10 +6651,10 @@
         <v>28.06</v>
       </c>
       <c r="Z68" s="4" t="n"/>
-      <c r="AA68" s="4" t="n">
+      <c r="AA68" s="4" t="n"/>
+      <c r="AB68" s="4" t="n">
         <v>27.05</v>
       </c>
-      <c r="AB68" s="4" t="n"/>
       <c r="AC68" s="4" t="n"/>
       <c r="AD68" s="4" t="n"/>
       <c r="AE68" s="4" t="n"/>
@@ -7159,10 +7161,10 @@
       <c r="Z74" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="AA74" s="4" t="n"/>
-      <c r="AB74" s="4" t="n">
+      <c r="AA74" s="4" t="n">
         <v>33.5</v>
       </c>
+      <c r="AB74" s="4" t="n"/>
       <c r="AC74" s="4" t="n"/>
       <c r="AD74" s="4" t="n"/>
       <c r="AE74" s="4" t="n"/>
@@ -7247,10 +7249,10 @@
       <c r="X75" s="4" t="n"/>
       <c r="Y75" s="4" t="n"/>
       <c r="Z75" s="4" t="n"/>
-      <c r="AA75" s="4" t="n">
+      <c r="AA75" s="4" t="n"/>
+      <c r="AB75" s="4" t="n">
         <v>25.89</v>
       </c>
-      <c r="AB75" s="4" t="n"/>
       <c r="AC75" s="4" t="n"/>
       <c r="AD75" s="4" t="n"/>
       <c r="AE75" s="4" t="n"/>
@@ -8360,27 +8362,27 @@
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
+          <t>莫斯勒★1</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>莫斯勒★3</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>莫斯勒★6</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
           <t>肥龙★3</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>肥龙★6</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>莫斯勒★1</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>莫斯勒★3</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>莫斯勒★6</t>
         </is>
       </c>
       <c r="BE1" s="1" t="inlineStr">
@@ -9270,11 +9272,11 @@
       <c r="AW8" s="4" t="n"/>
       <c r="AX8" s="4" t="n"/>
       <c r="AY8" s="4" t="n"/>
-      <c r="AZ8" s="4" t="n"/>
+      <c r="AZ8" s="4" t="n">
+        <v>28.39</v>
+      </c>
       <c r="BA8" s="4" t="n"/>
-      <c r="BB8" s="4" t="n">
-        <v>28.39</v>
-      </c>
+      <c r="BB8" s="4" t="n"/>
       <c r="BC8" s="4" t="n"/>
       <c r="BD8" s="4" t="n"/>
       <c r="BE8" s="4" t="n"/>
@@ -9596,11 +9598,11 @@
         <v>37.99</v>
       </c>
       <c r="AY11" s="4" t="n"/>
-      <c r="AZ11" s="4" t="n"/>
+      <c r="AZ11" s="4" t="n">
+        <v>36.85</v>
+      </c>
       <c r="BA11" s="4" t="n"/>
-      <c r="BB11" s="4" t="n">
-        <v>36.85</v>
-      </c>
+      <c r="BB11" s="4" t="n"/>
       <c r="BC11" s="4" t="n"/>
       <c r="BD11" s="4" t="n"/>
       <c r="BE11" s="4" t="n"/>
@@ -9705,12 +9707,12 @@
       <c r="AX12" s="4" t="n"/>
       <c r="AY12" s="4" t="n"/>
       <c r="AZ12" s="4" t="n"/>
-      <c r="BA12" s="4" t="n">
-        <v>21.5</v>
-      </c>
+      <c r="BA12" s="4" t="n"/>
       <c r="BB12" s="4" t="n"/>
       <c r="BC12" s="4" t="n"/>
-      <c r="BD12" s="4" t="n"/>
+      <c r="BD12" s="4" t="n">
+        <v>21.5</v>
+      </c>
       <c r="BE12" s="4" t="n"/>
       <c r="BF12" s="4" t="n"/>
       <c r="BG12" s="4" t="n"/>
@@ -9859,7 +9861,9 @@
           <t>东方巴黎</t>
         </is>
       </c>
-      <c r="C14" s="4" t="n"/>
+      <c r="C14" s="4" t="n">
+        <v>26.15</v>
+      </c>
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
       <c r="F14" s="4" t="n">
@@ -9962,7 +9966,7 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>26.15</v>
+        <v>29.2</v>
       </c>
       <c r="D15" s="4" t="n"/>
       <c r="E15" s="4" t="n"/>
@@ -10346,15 +10350,15 @@
       <c r="AW18" s="4" t="n"/>
       <c r="AX18" s="4" t="n"/>
       <c r="AY18" s="4" t="n"/>
-      <c r="AZ18" s="4" t="n">
+      <c r="AZ18" s="4" t="n"/>
+      <c r="BA18" s="4" t="n"/>
+      <c r="BB18" s="4" t="n"/>
+      <c r="BC18" s="4" t="n">
         <v>24.5</v>
       </c>
-      <c r="BA18" s="4" t="n">
+      <c r="BD18" s="4" t="n">
         <v>23.42</v>
       </c>
-      <c r="BB18" s="4" t="n"/>
-      <c r="BC18" s="4" t="n"/>
-      <c r="BD18" s="4" t="n"/>
       <c r="BE18" s="4" t="n"/>
       <c r="BF18" s="4" t="n"/>
       <c r="BG18" s="4" t="n"/>
@@ -11205,12 +11209,12 @@
       <c r="AX26" s="4" t="n"/>
       <c r="AY26" s="4" t="n"/>
       <c r="AZ26" s="4" t="n"/>
-      <c r="BA26" s="4" t="n">
-        <v>18.45</v>
-      </c>
+      <c r="BA26" s="4" t="n"/>
       <c r="BB26" s="4" t="n"/>
       <c r="BC26" s="4" t="n"/>
-      <c r="BD26" s="4" t="n"/>
+      <c r="BD26" s="4" t="n">
+        <v>18.45</v>
+      </c>
       <c r="BE26" s="4" t="n"/>
       <c r="BF26" s="4" t="n"/>
       <c r="BG26" s="4" t="n"/>
@@ -11433,12 +11437,12 @@
       <c r="AX28" s="4" t="n"/>
       <c r="AY28" s="4" t="n"/>
       <c r="AZ28" s="4" t="n"/>
-      <c r="BA28" s="4" t="n">
-        <v>32.6</v>
-      </c>
+      <c r="BA28" s="4" t="n"/>
       <c r="BB28" s="4" t="n"/>
       <c r="BC28" s="4" t="n"/>
-      <c r="BD28" s="4" t="n"/>
+      <c r="BD28" s="4" t="n">
+        <v>32.6</v>
+      </c>
       <c r="BE28" s="4" t="n"/>
       <c r="BF28" s="4" t="n"/>
       <c r="BG28" s="4" t="n"/>
@@ -11869,12 +11873,12 @@
       </c>
       <c r="AY32" s="4" t="n"/>
       <c r="AZ32" s="4" t="n"/>
-      <c r="BA32" s="4" t="n">
-        <v>28.1</v>
-      </c>
+      <c r="BA32" s="4" t="n"/>
       <c r="BB32" s="4" t="n"/>
       <c r="BC32" s="4" t="n"/>
-      <c r="BD32" s="4" t="n"/>
+      <c r="BD32" s="4" t="n">
+        <v>28.1</v>
+      </c>
       <c r="BE32" s="4" t="n"/>
       <c r="BF32" s="4" t="n"/>
       <c r="BG32" s="4" t="n">
@@ -12959,12 +12963,12 @@
       </c>
       <c r="AY42" s="4" t="n"/>
       <c r="AZ42" s="4" t="n"/>
-      <c r="BA42" s="4" t="n">
-        <v>21.9</v>
-      </c>
+      <c r="BA42" s="4" t="n"/>
       <c r="BB42" s="4" t="n"/>
       <c r="BC42" s="4" t="n"/>
-      <c r="BD42" s="4" t="n"/>
+      <c r="BD42" s="4" t="n">
+        <v>21.9</v>
+      </c>
       <c r="BE42" s="4" t="n"/>
       <c r="BF42" s="4" t="n"/>
       <c r="BG42" s="4" t="n"/>
@@ -13929,12 +13933,12 @@
       <c r="AX51" s="4" t="n"/>
       <c r="AY51" s="4" t="n"/>
       <c r="AZ51" s="4" t="n"/>
-      <c r="BA51" s="4" t="n">
-        <v>23.79</v>
-      </c>
+      <c r="BA51" s="4" t="n"/>
       <c r="BB51" s="4" t="n"/>
       <c r="BC51" s="4" t="n"/>
-      <c r="BD51" s="4" t="n"/>
+      <c r="BD51" s="4" t="n">
+        <v>23.79</v>
+      </c>
       <c r="BE51" s="4" t="n"/>
       <c r="BF51" s="4" t="n"/>
       <c r="BG51" s="4" t="n"/>
@@ -17205,9 +17209,13 @@
       <c r="J82" s="4" t="n">
         <v>53.3</v>
       </c>
-      <c r="K82" s="4" t="n"/>
+      <c r="K82" s="4" t="n">
+        <v>52.3</v>
+      </c>
       <c r="L82" s="4" t="n"/>
-      <c r="M82" s="4" t="n"/>
+      <c r="M82" s="4" t="n">
+        <v>51</v>
+      </c>
       <c r="N82" s="4" t="n"/>
       <c r="O82" s="4" t="n"/>
       <c r="P82" s="4" t="n"/>
@@ -17321,7 +17329,9 @@
       <c r="T83" s="4" t="n"/>
       <c r="U83" s="4" t="n"/>
       <c r="V83" s="4" t="n"/>
-      <c r="W83" s="4" t="n"/>
+      <c r="W83" s="4" t="n">
+        <v>26.29</v>
+      </c>
       <c r="X83" s="4" t="n"/>
       <c r="Y83" s="4" t="n"/>
       <c r="Z83" s="4" t="n"/>
@@ -17896,27 +17906,27 @@
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
+          <t>莫斯勒★1</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>莫斯勒★3</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>莫斯勒★6</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
           <t>肥龙★3</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>肥龙★6</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>莫斯勒★1</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>莫斯勒★3</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>莫斯勒★6</t>
         </is>
       </c>
       <c r="BE1" s="1" t="inlineStr">
@@ -18327,14 +18337,14 @@
       </c>
       <c r="AY3" s="4" t="n"/>
       <c r="AZ3" s="4" t="n"/>
-      <c r="BA3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BA3" s="4" t="n"/>
       <c r="BB3" s="4" t="n"/>
       <c r="BC3" s="4" t="n"/>
-      <c r="BD3" s="4" t="n"/>
+      <c r="BD3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE3" s="4" t="n"/>
       <c r="BF3" s="4" t="n"/>
       <c r="BG3" s="4" t="inlineStr">
@@ -18611,14 +18621,14 @@
       <c r="AX5" s="4" t="n"/>
       <c r="AY5" s="4" t="n"/>
       <c r="AZ5" s="4" t="n"/>
-      <c r="BA5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BA5" s="4" t="n"/>
       <c r="BB5" s="4" t="n"/>
       <c r="BC5" s="4" t="n"/>
-      <c r="BD5" s="4" t="n"/>
+      <c r="BD5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE5" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -19096,13 +19106,13 @@
         </is>
       </c>
       <c r="AY8" s="4" t="n"/>
-      <c r="AZ8" s="4" t="n"/>
+      <c r="AZ8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BA8" s="4" t="n"/>
-      <c r="BB8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BB8" s="4" t="n"/>
       <c r="BC8" s="4" t="n"/>
       <c r="BD8" s="4" t="n"/>
       <c r="BE8" s="4" t="n"/>
@@ -19243,14 +19253,14 @@
       <c r="AX9" s="4" t="n"/>
       <c r="AY9" s="4" t="n"/>
       <c r="AZ9" s="4" t="n"/>
-      <c r="BA9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BA9" s="4" t="n"/>
       <c r="BB9" s="4" t="n"/>
       <c r="BC9" s="4" t="n"/>
-      <c r="BD9" s="4" t="n"/>
+      <c r="BD9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE9" s="4" t="n"/>
       <c r="BF9" s="4" t="inlineStr">
         <is>
@@ -19582,13 +19592,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AZ11" s="4" t="n"/>
+      <c r="AZ11" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BA11" s="4" t="n"/>
-      <c r="BB11" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BB11" s="4" t="n"/>
       <c r="BC11" s="4" t="n"/>
       <c r="BD11" s="4" t="n"/>
       <c r="BE11" s="4" t="n"/>
@@ -19733,14 +19743,14 @@
       </c>
       <c r="AY12" s="4" t="n"/>
       <c r="AZ12" s="4" t="n"/>
-      <c r="BA12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BA12" s="4" t="n"/>
       <c r="BB12" s="4" t="n"/>
       <c r="BC12" s="4" t="n"/>
-      <c r="BD12" s="4" t="n"/>
+      <c r="BD12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE12" s="4" t="n"/>
       <c r="BF12" s="4" t="n"/>
       <c r="BG12" s="4" t="inlineStr">
@@ -20211,14 +20221,14 @@
       </c>
       <c r="AY15" s="4" t="n"/>
       <c r="AZ15" s="4" t="n"/>
-      <c r="BA15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BA15" s="4" t="n"/>
       <c r="BB15" s="4" t="n"/>
       <c r="BC15" s="4" t="n"/>
-      <c r="BD15" s="4" t="n"/>
+      <c r="BD15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE15" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -20676,19 +20686,19 @@
         </is>
       </c>
       <c r="AY18" s="4" t="n"/>
-      <c r="AZ18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AZ18" s="4" t="n"/>
+      <c r="BA18" s="4" t="n"/>
       <c r="BB18" s="4" t="n"/>
-      <c r="BC18" s="4" t="n"/>
-      <c r="BD18" s="4" t="n"/>
+      <c r="BC18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BD18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE18" s="4" t="n"/>
       <c r="BF18" s="4" t="n"/>
       <c r="BG18" s="4" t="inlineStr">
@@ -21301,14 +21311,14 @@
       </c>
       <c r="AY22" s="4" t="n"/>
       <c r="AZ22" s="4" t="n"/>
-      <c r="BA22" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BA22" s="4" t="n"/>
       <c r="BB22" s="4" t="n"/>
       <c r="BC22" s="4" t="n"/>
-      <c r="BD22" s="4" t="n"/>
+      <c r="BD22" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE22" s="4" t="n"/>
       <c r="BF22" s="4" t="n"/>
       <c r="BG22" s="4" t="inlineStr">
@@ -21593,14 +21603,14 @@
       </c>
       <c r="AY24" s="4" t="n"/>
       <c r="AZ24" s="4" t="n"/>
-      <c r="BA24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BA24" s="4" t="n"/>
       <c r="BB24" s="4" t="n"/>
       <c r="BC24" s="4" t="n"/>
-      <c r="BD24" s="4" t="n"/>
+      <c r="BD24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE24" s="4" t="n"/>
       <c r="BF24" s="4" t="n"/>
       <c r="BG24" s="4" t="inlineStr">
@@ -21735,14 +21745,14 @@
       <c r="AX25" s="4" t="n"/>
       <c r="AY25" s="4" t="n"/>
       <c r="AZ25" s="4" t="n"/>
-      <c r="BA25" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BA25" s="4" t="n"/>
       <c r="BB25" s="4" t="n"/>
       <c r="BC25" s="4" t="n"/>
-      <c r="BD25" s="4" t="n"/>
+      <c r="BD25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE25" s="4" t="n"/>
       <c r="BF25" s="4" t="n"/>
       <c r="BG25" s="4" t="inlineStr">
@@ -21889,14 +21899,14 @@
       </c>
       <c r="AY26" s="4" t="n"/>
       <c r="AZ26" s="4" t="n"/>
-      <c r="BA26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BA26" s="4" t="n"/>
       <c r="BB26" s="4" t="n"/>
       <c r="BC26" s="4" t="n"/>
-      <c r="BD26" s="4" t="n"/>
+      <c r="BD26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE26" s="4" t="n"/>
       <c r="BF26" s="4" t="n"/>
       <c r="BG26" s="4" t="inlineStr">
@@ -22213,14 +22223,14 @@
       </c>
       <c r="AY28" s="4" t="n"/>
       <c r="AZ28" s="4" t="n"/>
-      <c r="BA28" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BA28" s="4" t="n"/>
       <c r="BB28" s="4" t="n"/>
       <c r="BC28" s="4" t="n"/>
-      <c r="BD28" s="4" t="n"/>
+      <c r="BD28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE28" s="4" t="n"/>
       <c r="BF28" s="4" t="n"/>
       <c r="BG28" s="4" t="inlineStr">
@@ -22363,18 +22373,18 @@
       </c>
       <c r="AY29" s="4" t="n"/>
       <c r="AZ29" s="4" t="n"/>
-      <c r="BA29" s="4" t="n"/>
-      <c r="BB29" s="4" t="n"/>
-      <c r="BC29" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BD29" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BA29" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BB29" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BC29" s="4" t="n"/>
+      <c r="BD29" s="4" t="n"/>
       <c r="BE29" s="4" t="n"/>
       <c r="BF29" s="4" t="n"/>
       <c r="BG29" s="4" t="inlineStr">
@@ -22809,14 +22819,14 @@
         </is>
       </c>
       <c r="AZ32" s="4" t="n"/>
-      <c r="BA32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BA32" s="4" t="n"/>
       <c r="BB32" s="4" t="n"/>
       <c r="BC32" s="4" t="n"/>
-      <c r="BD32" s="4" t="n"/>
+      <c r="BD32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE32" s="4" t="n"/>
       <c r="BF32" s="4" t="n"/>
       <c r="BG32" s="4" t="inlineStr">
@@ -23137,14 +23147,14 @@
       </c>
       <c r="AY34" s="4" t="n"/>
       <c r="AZ34" s="4" t="n"/>
-      <c r="BA34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BA34" s="4" t="n"/>
       <c r="BB34" s="4" t="n"/>
       <c r="BC34" s="4" t="n"/>
-      <c r="BD34" s="4" t="n"/>
+      <c r="BD34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE34" s="4" t="n"/>
       <c r="BF34" s="4" t="n"/>
       <c r="BG34" s="4" t="inlineStr">
@@ -23709,14 +23719,14 @@
       <c r="AX38" s="4" t="n"/>
       <c r="AY38" s="4" t="n"/>
       <c r="AZ38" s="4" t="n"/>
-      <c r="BA38" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BA38" s="4" t="n"/>
       <c r="BB38" s="4" t="n"/>
       <c r="BC38" s="4" t="n"/>
-      <c r="BD38" s="4" t="n"/>
+      <c r="BD38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE38" s="4" t="n"/>
       <c r="BF38" s="4" t="n"/>
       <c r="BG38" s="4" t="inlineStr">
@@ -23867,14 +23877,14 @@
       </c>
       <c r="AY39" s="4" t="n"/>
       <c r="AZ39" s="4" t="n"/>
-      <c r="BA39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BA39" s="4" t="n"/>
       <c r="BB39" s="4" t="n"/>
       <c r="BC39" s="4" t="n"/>
-      <c r="BD39" s="4" t="n"/>
+      <c r="BD39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE39" s="4" t="n"/>
       <c r="BF39" s="4" t="n"/>
       <c r="BG39" s="4" t="inlineStr">
@@ -24349,14 +24359,14 @@
       </c>
       <c r="AY42" s="4" t="n"/>
       <c r="AZ42" s="4" t="n"/>
-      <c r="BA42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BA42" s="4" t="n"/>
       <c r="BB42" s="4" t="n"/>
       <c r="BC42" s="4" t="n"/>
-      <c r="BD42" s="4" t="n"/>
+      <c r="BD42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE42" s="4" t="n"/>
       <c r="BF42" s="4" t="n"/>
       <c r="BG42" s="4" t="inlineStr">
@@ -24503,14 +24513,14 @@
       </c>
       <c r="AY43" s="4" t="n"/>
       <c r="AZ43" s="4" t="n"/>
-      <c r="BA43" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BA43" s="4" t="n"/>
       <c r="BB43" s="4" t="n"/>
       <c r="BC43" s="4" t="n"/>
-      <c r="BD43" s="4" t="n"/>
+      <c r="BD43" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE43" s="4" t="n"/>
       <c r="BF43" s="4" t="n"/>
       <c r="BG43" s="4" t="inlineStr">
@@ -24641,14 +24651,14 @@
       <c r="AX44" s="4" t="n"/>
       <c r="AY44" s="4" t="n"/>
       <c r="AZ44" s="4" t="n"/>
-      <c r="BA44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BA44" s="4" t="n"/>
       <c r="BB44" s="4" t="n"/>
       <c r="BC44" s="4" t="n"/>
-      <c r="BD44" s="4" t="n"/>
+      <c r="BD44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE44" s="4" t="n"/>
       <c r="BF44" s="4" t="inlineStr">
         <is>
@@ -25735,14 +25745,14 @@
       </c>
       <c r="AY51" s="4" t="n"/>
       <c r="AZ51" s="4" t="n"/>
-      <c r="BA51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BA51" s="4" t="n"/>
       <c r="BB51" s="4" t="n"/>
       <c r="BC51" s="4" t="n"/>
-      <c r="BD51" s="4" t="n"/>
+      <c r="BD51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE51" s="4" t="n"/>
       <c r="BF51" s="4" t="inlineStr">
         <is>
@@ -26825,14 +26835,14 @@
       </c>
       <c r="AY58" s="4" t="n"/>
       <c r="AZ58" s="4" t="n"/>
-      <c r="BA58" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BA58" s="4" t="n"/>
       <c r="BB58" s="4" t="n"/>
       <c r="BC58" s="4" t="n"/>
-      <c r="BD58" s="4" t="n"/>
+      <c r="BD58" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE58" s="4" t="n"/>
       <c r="BF58" s="4" t="n"/>
       <c r="BG58" s="4" t="inlineStr">
@@ -27405,14 +27415,14 @@
       <c r="AX62" s="4" t="n"/>
       <c r="AY62" s="4" t="n"/>
       <c r="AZ62" s="4" t="n"/>
-      <c r="BA62" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BA62" s="4" t="n"/>
       <c r="BB62" s="4" t="n"/>
       <c r="BC62" s="4" t="n"/>
-      <c r="BD62" s="4" t="n"/>
+      <c r="BD62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE62" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -27871,14 +27881,14 @@
         </is>
       </c>
       <c r="AZ65" s="4" t="n"/>
-      <c r="BA65" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BA65" s="4" t="n"/>
       <c r="BB65" s="4" t="n"/>
       <c r="BC65" s="4" t="n"/>
-      <c r="BD65" s="4" t="n"/>
+      <c r="BD65" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE65" s="4" t="n"/>
       <c r="BF65" s="4" t="n"/>
       <c r="BG65" s="4" t="inlineStr">
@@ -28159,14 +28169,14 @@
       <c r="AX67" s="4" t="n"/>
       <c r="AY67" s="4" t="n"/>
       <c r="AZ67" s="4" t="n"/>
-      <c r="BA67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BA67" s="4" t="n"/>
       <c r="BB67" s="4" t="n"/>
       <c r="BC67" s="4" t="n"/>
-      <c r="BD67" s="4" t="n"/>
+      <c r="BD67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE67" s="4" t="n"/>
       <c r="BF67" s="4" t="inlineStr">
         <is>
@@ -28333,14 +28343,14 @@
       </c>
       <c r="AY68" s="4" t="n"/>
       <c r="AZ68" s="4" t="n"/>
-      <c r="BA68" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BA68" s="4" t="n"/>
       <c r="BB68" s="4" t="n"/>
       <c r="BC68" s="4" t="n"/>
-      <c r="BD68" s="4" t="n"/>
+      <c r="BD68" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE68" s="4" t="n"/>
       <c r="BF68" s="4" t="n"/>
       <c r="BG68" s="4" t="inlineStr">
@@ -28495,14 +28505,14 @@
       <c r="AX69" s="4" t="n"/>
       <c r="AY69" s="4" t="n"/>
       <c r="AZ69" s="4" t="n"/>
-      <c r="BA69" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BA69" s="4" t="n"/>
       <c r="BB69" s="4" t="n"/>
       <c r="BC69" s="4" t="n"/>
-      <c r="BD69" s="4" t="n"/>
+      <c r="BD69" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE69" s="4" t="n"/>
       <c r="BF69" s="4" t="n"/>
       <c r="BG69" s="4" t="inlineStr">
@@ -29249,14 +29259,14 @@
       </c>
       <c r="AY74" s="4" t="n"/>
       <c r="AZ74" s="4" t="n"/>
-      <c r="BA74" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BA74" s="4" t="n"/>
       <c r="BB74" s="4" t="n"/>
       <c r="BC74" s="4" t="n"/>
-      <c r="BD74" s="4" t="n"/>
+      <c r="BD74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE74" s="4" t="n"/>
       <c r="BF74" s="4" t="n"/>
       <c r="BG74" s="4" t="inlineStr">
@@ -29407,14 +29417,14 @@
       </c>
       <c r="AY75" s="4" t="n"/>
       <c r="AZ75" s="4" t="n"/>
-      <c r="BA75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BA75" s="4" t="n"/>
       <c r="BB75" s="4" t="n"/>
       <c r="BC75" s="4" t="n"/>
-      <c r="BD75" s="4" t="n"/>
+      <c r="BD75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE75" s="4" t="n"/>
       <c r="BF75" s="4" t="n"/>
       <c r="BG75" s="4" t="inlineStr">
@@ -30012,13 +30022,13 @@
       <c r="AY79" s="4" t="n"/>
       <c r="AZ79" s="4" t="n"/>
       <c r="BA79" s="4" t="n"/>
-      <c r="BB79" s="4" t="n"/>
+      <c r="BB79" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC79" s="4" t="n"/>
-      <c r="BD79" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BD79" s="4" t="n"/>
       <c r="BE79" s="4" t="n"/>
       <c r="BF79" s="4" t="n"/>
       <c r="BG79" s="4" t="inlineStr">
@@ -30351,9 +30361,17 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="K82" s="4" t="n"/>
+      <c r="K82" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="L82" s="4" t="n"/>
-      <c r="M82" s="4" t="n"/>
+      <c r="M82" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N82" s="4" t="n"/>
       <c r="O82" s="4" t="n"/>
       <c r="P82" s="4" t="n"/>
@@ -30477,7 +30495,11 @@
       <c r="T83" s="4" t="n"/>
       <c r="U83" s="4" t="n"/>
       <c r="V83" s="4" t="n"/>
-      <c r="W83" s="4" t="n"/>
+      <c r="W83" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="X83" s="4" t="n"/>
       <c r="Y83" s="4" t="n"/>
       <c r="Z83" s="4" t="n"/>
@@ -34820,17 +34842,17 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>玻璃</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>9x8</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>速尾</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>玻璃</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -35024,10 +35046,10 @@
       <c r="D2" s="4" t="n"/>
       <c r="E2" s="4" t="n"/>
       <c r="F2" s="4" t="n"/>
-      <c r="G2" s="4" t="n">
+      <c r="G2" s="4" t="n"/>
+      <c r="H2" s="4" t="n">
         <v>18.89</v>
       </c>
-      <c r="H2" s="4" t="n"/>
       <c r="I2" s="4" t="n"/>
       <c r="J2" s="4" t="n"/>
       <c r="K2" s="4" t="n"/>
@@ -35084,11 +35106,11 @@
       </c>
       <c r="E3" s="4" t="n"/>
       <c r="F3" s="4" t="n"/>
-      <c r="G3" s="4" t="n"/>
+      <c r="G3" s="4" t="n">
+        <v>28.42</v>
+      </c>
       <c r="H3" s="4" t="n"/>
-      <c r="I3" s="4" t="n">
-        <v>28.42</v>
-      </c>
+      <c r="I3" s="4" t="n"/>
       <c r="J3" s="4" t="n">
         <v>28.45</v>
       </c>
@@ -35151,10 +35173,10 @@
         <v>30.95</v>
       </c>
       <c r="G4" s="4" t="n"/>
-      <c r="H4" s="4" t="n">
+      <c r="H4" s="4" t="n"/>
+      <c r="I4" s="4" t="n">
         <v>31.69</v>
       </c>
-      <c r="I4" s="4" t="n"/>
       <c r="J4" s="4" t="n">
         <v>30.8</v>
       </c>
@@ -35213,13 +35235,13 @@
       <c r="E5" s="4" t="n"/>
       <c r="F5" s="4" t="n"/>
       <c r="G5" s="4" t="n">
+        <v>17.99</v>
+      </c>
+      <c r="H5" s="4" t="n">
         <v>18.15</v>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="I5" s="4" t="n">
         <v>18.03</v>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>17.99</v>
       </c>
       <c r="J5" s="4" t="n"/>
       <c r="K5" s="4" t="n">
@@ -35286,10 +35308,10 @@
       <c r="D6" s="4" t="n"/>
       <c r="E6" s="4" t="n"/>
       <c r="F6" s="4" t="n"/>
-      <c r="G6" s="4" t="n">
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="4" t="n">
         <v>17.95</v>
       </c>
-      <c r="H6" s="4" t="n"/>
       <c r="I6" s="4" t="n"/>
       <c r="J6" s="4" t="n"/>
       <c r="K6" s="4" t="n"/>
@@ -35348,11 +35370,11 @@
         <v>24.39</v>
       </c>
       <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n"/>
+      <c r="G7" s="4" t="n">
+        <v>24.69</v>
+      </c>
       <c r="H7" s="4" t="n"/>
-      <c r="I7" s="4" t="n">
-        <v>24.69</v>
-      </c>
+      <c r="I7" s="4" t="n"/>
       <c r="J7" s="4" t="n"/>
       <c r="K7" s="4" t="n">
         <v>24.99</v>
@@ -35410,12 +35432,12 @@
       <c r="F8" s="4" t="n">
         <v>27.73</v>
       </c>
-      <c r="G8" s="4" t="n"/>
-      <c r="H8" s="4" t="n">
+      <c r="G8" s="4" t="n">
+        <v>27.72</v>
+      </c>
+      <c r="H8" s="4" t="n"/>
+      <c r="I8" s="4" t="n">
         <v>28.59</v>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>27.72</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>28.1</v>
@@ -35476,11 +35498,11 @@
       </c>
       <c r="E9" s="4" t="n"/>
       <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="n"/>
+      <c r="G9" s="4" t="n">
+        <v>20.09</v>
+      </c>
       <c r="H9" s="4" t="n"/>
-      <c r="I9" s="4" t="n">
-        <v>20.09</v>
-      </c>
+      <c r="I9" s="4" t="n"/>
       <c r="J9" s="4" t="n"/>
       <c r="K9" s="4" t="n"/>
       <c r="L9" s="4" t="n">
@@ -35546,13 +35568,13 @@
       <c r="D10" s="4" t="n"/>
       <c r="E10" s="4" t="n"/>
       <c r="F10" s="4" t="n"/>
-      <c r="G10" s="4" t="n">
+      <c r="G10" s="4" t="n"/>
+      <c r="H10" s="4" t="n">
         <v>23.42</v>
       </c>
-      <c r="H10" s="4" t="n">
+      <c r="I10" s="4" t="n">
         <v>23.43</v>
       </c>
-      <c r="I10" s="4" t="n"/>
       <c r="J10" s="4" t="n"/>
       <c r="K10" s="4" t="n"/>
       <c r="L10" s="4" t="n"/>
@@ -35610,11 +35632,11 @@
       <c r="F11" s="4" t="n">
         <v>35.25</v>
       </c>
-      <c r="G11" s="4" t="n"/>
+      <c r="G11" s="4" t="n">
+        <v>35.49</v>
+      </c>
       <c r="H11" s="4" t="n"/>
-      <c r="I11" s="4" t="n">
-        <v>35.49</v>
-      </c>
+      <c r="I11" s="4" t="n"/>
       <c r="J11" s="4" t="n"/>
       <c r="K11" s="4" t="n"/>
       <c r="L11" s="4" t="n"/>
@@ -35663,10 +35685,10 @@
       <c r="E12" s="4" t="n"/>
       <c r="F12" s="4" t="n"/>
       <c r="G12" s="4" t="n"/>
-      <c r="H12" s="4" t="n">
+      <c r="H12" s="4" t="n"/>
+      <c r="I12" s="4" t="n">
         <v>21.83</v>
       </c>
-      <c r="I12" s="4" t="n"/>
       <c r="J12" s="4" t="n"/>
       <c r="K12" s="4" t="n">
         <v>21.55</v>
@@ -35792,10 +35814,10 @@
         <v>25.29</v>
       </c>
       <c r="F14" s="4" t="n"/>
-      <c r="G14" s="4" t="n">
+      <c r="G14" s="4" t="n"/>
+      <c r="H14" s="4" t="n">
         <v>26.19</v>
       </c>
-      <c r="H14" s="4" t="n"/>
       <c r="I14" s="4" t="n"/>
       <c r="J14" s="4" t="n"/>
       <c r="K14" s="4" t="n"/>
@@ -35847,7 +35869,7 @@
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>28.85</v>
+        <v>28.8</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>28.69</v>
@@ -35858,11 +35880,13 @@
       <c r="F15" s="4" t="n">
         <v>28.9</v>
       </c>
-      <c r="G15" s="4" t="n"/>
-      <c r="H15" s="4" t="n">
+      <c r="G15" s="4" t="n">
+        <v>28.82</v>
+      </c>
+      <c r="H15" s="4" t="n"/>
+      <c r="I15" s="4" t="n">
         <v>29.49</v>
       </c>
-      <c r="I15" s="4" t="n"/>
       <c r="J15" s="4" t="n"/>
       <c r="K15" s="4" t="n"/>
       <c r="L15" s="4" t="n"/>
@@ -35979,13 +36003,13 @@
       </c>
       <c r="F17" s="4" t="n"/>
       <c r="G17" s="4" t="n">
+        <v>29.75</v>
+      </c>
+      <c r="H17" s="4" t="n">
         <v>30.69</v>
       </c>
-      <c r="H17" s="4" t="n">
+      <c r="I17" s="4" t="n">
         <v>30.59</v>
-      </c>
-      <c r="I17" s="4" t="n">
-        <v>29.75</v>
       </c>
       <c r="J17" s="4" t="n"/>
       <c r="K17" s="4" t="n"/>
@@ -36041,10 +36065,10 @@
       <c r="E18" s="4" t="n"/>
       <c r="F18" s="4" t="n"/>
       <c r="G18" s="4" t="n"/>
-      <c r="H18" s="4" t="n">
+      <c r="H18" s="4" t="n"/>
+      <c r="I18" s="4" t="n">
         <v>23.72</v>
       </c>
-      <c r="I18" s="4" t="n"/>
       <c r="J18" s="4" t="n">
         <v>23.98</v>
       </c>
@@ -36116,10 +36140,10 @@
       <c r="F19" s="4" t="n">
         <v>32.19</v>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="G19" s="4" t="n"/>
+      <c r="H19" s="4" t="n">
         <v>33.05</v>
       </c>
-      <c r="H19" s="4" t="n"/>
       <c r="I19" s="4" t="n"/>
       <c r="J19" s="4" t="n"/>
       <c r="K19" s="4" t="n"/>
@@ -36172,10 +36196,10 @@
         <v>22.09</v>
       </c>
       <c r="F20" s="4" t="n"/>
-      <c r="G20" s="4" t="n">
+      <c r="G20" s="4" t="n"/>
+      <c r="H20" s="4" t="n">
         <v>22.4</v>
       </c>
-      <c r="H20" s="4" t="n"/>
       <c r="I20" s="4" t="n"/>
       <c r="J20" s="4" t="n"/>
       <c r="K20" s="4" t="n"/>
@@ -36473,10 +36497,10 @@
       <c r="E25" s="4" t="n"/>
       <c r="F25" s="4" t="n"/>
       <c r="G25" s="4" t="n"/>
-      <c r="H25" s="4" t="n">
+      <c r="H25" s="4" t="n"/>
+      <c r="I25" s="4" t="n">
         <v>24.35</v>
       </c>
-      <c r="I25" s="4" t="n"/>
       <c r="J25" s="4" t="n"/>
       <c r="K25" s="4" t="n"/>
       <c r="L25" s="4" t="n">
@@ -36537,10 +36561,10 @@
       <c r="E26" s="4" t="n"/>
       <c r="F26" s="4" t="n"/>
       <c r="G26" s="4" t="n"/>
-      <c r="H26" s="4" t="n">
+      <c r="H26" s="4" t="n"/>
+      <c r="I26" s="4" t="n">
         <v>18.89</v>
       </c>
-      <c r="I26" s="4" t="n"/>
       <c r="J26" s="4" t="n"/>
       <c r="K26" s="4" t="n">
         <v>18.6</v>
@@ -36600,11 +36624,11 @@
       <c r="D27" s="4" t="n"/>
       <c r="E27" s="4" t="n"/>
       <c r="F27" s="4" t="n"/>
-      <c r="G27" s="4" t="n"/>
+      <c r="G27" s="4" t="n">
+        <v>32.85</v>
+      </c>
       <c r="H27" s="4" t="n"/>
-      <c r="I27" s="4" t="n">
-        <v>32.85</v>
-      </c>
+      <c r="I27" s="4" t="n"/>
       <c r="J27" s="4" t="n">
         <v>32.79</v>
       </c>
@@ -36661,10 +36685,10 @@
       </c>
       <c r="F28" s="4" t="n"/>
       <c r="G28" s="4" t="n"/>
-      <c r="H28" s="4" t="n">
+      <c r="H28" s="4" t="n"/>
+      <c r="I28" s="4" t="n">
         <v>33.09</v>
       </c>
-      <c r="I28" s="4" t="n"/>
       <c r="J28" s="4" t="n"/>
       <c r="K28" s="4" t="n">
         <v>33.05</v>
@@ -36722,11 +36746,11 @@
         <v>17.29</v>
       </c>
       <c r="F29" s="4" t="n"/>
-      <c r="G29" s="4" t="n"/>
+      <c r="G29" s="4" t="n">
+        <v>17.89</v>
+      </c>
       <c r="H29" s="4" t="n"/>
-      <c r="I29" s="4" t="n">
-        <v>17.89</v>
-      </c>
+      <c r="I29" s="4" t="n"/>
       <c r="J29" s="4" t="n"/>
       <c r="K29" s="4" t="n"/>
       <c r="L29" s="4" t="n"/>
@@ -36784,10 +36808,10 @@
       <c r="D30" s="4" t="n"/>
       <c r="E30" s="4" t="n"/>
       <c r="F30" s="4" t="n"/>
-      <c r="G30" s="4" t="n">
+      <c r="G30" s="4" t="n"/>
+      <c r="H30" s="4" t="n">
         <v>23.1</v>
       </c>
-      <c r="H30" s="4" t="n"/>
       <c r="I30" s="4" t="n"/>
       <c r="J30" s="4" t="n"/>
       <c r="K30" s="4" t="n"/>
@@ -36844,13 +36868,13 @@
       <c r="D31" s="4" t="n"/>
       <c r="E31" s="4" t="n"/>
       <c r="F31" s="4" t="n"/>
-      <c r="G31" s="4" t="n">
+      <c r="G31" s="4" t="n"/>
+      <c r="H31" s="4" t="n">
         <v>18.99</v>
       </c>
-      <c r="H31" s="4" t="n">
+      <c r="I31" s="4" t="n">
         <v>19.35</v>
       </c>
-      <c r="I31" s="4" t="n"/>
       <c r="J31" s="4" t="n"/>
       <c r="K31" s="4" t="n"/>
       <c r="L31" s="4" t="n"/>
@@ -36914,13 +36938,13 @@
       <c r="F32" s="4" t="n">
         <v>27.8</v>
       </c>
-      <c r="G32" s="4" t="n">
+      <c r="G32" s="4" t="n"/>
+      <c r="H32" s="4" t="n">
         <v>29.06</v>
       </c>
-      <c r="H32" s="4" t="n">
+      <c r="I32" s="4" t="n">
         <v>28.39</v>
       </c>
-      <c r="I32" s="4" t="n"/>
       <c r="J32" s="4" t="n"/>
       <c r="K32" s="4" t="n"/>
       <c r="L32" s="4" t="n"/>
@@ -36980,10 +37004,10 @@
       <c r="D33" s="4" t="n"/>
       <c r="E33" s="4" t="n"/>
       <c r="F33" s="4" t="n"/>
-      <c r="G33" s="4" t="n">
+      <c r="G33" s="4" t="n"/>
+      <c r="H33" s="4" t="n">
         <v>19.89</v>
       </c>
-      <c r="H33" s="4" t="n"/>
       <c r="I33" s="4" t="n"/>
       <c r="J33" s="4" t="n"/>
       <c r="K33" s="4" t="n"/>
@@ -37047,10 +37071,10 @@
       </c>
       <c r="F34" s="4" t="n"/>
       <c r="G34" s="4" t="n"/>
-      <c r="H34" s="4" t="n">
+      <c r="H34" s="4" t="n"/>
+      <c r="I34" s="4" t="n">
         <v>35.49</v>
       </c>
-      <c r="I34" s="4" t="n"/>
       <c r="J34" s="4" t="n">
         <v>34.7</v>
       </c>
@@ -37102,13 +37126,13 @@
       <c r="D35" s="4" t="n"/>
       <c r="E35" s="4" t="n"/>
       <c r="F35" s="4" t="n"/>
-      <c r="G35" s="4" t="n">
+      <c r="G35" s="4" t="n"/>
+      <c r="H35" s="4" t="n">
         <v>23.59</v>
       </c>
-      <c r="H35" s="4" t="n">
+      <c r="I35" s="4" t="n">
         <v>23.6</v>
       </c>
-      <c r="I35" s="4" t="n"/>
       <c r="J35" s="4" t="n"/>
       <c r="K35" s="4" t="n"/>
       <c r="L35" s="4" t="n"/>
@@ -37168,10 +37192,10 @@
       <c r="F36" s="4" t="n">
         <v>34.6</v>
       </c>
-      <c r="G36" s="4" t="n">
+      <c r="G36" s="4" t="n"/>
+      <c r="H36" s="4" t="n">
         <v>35.89</v>
       </c>
-      <c r="H36" s="4" t="n"/>
       <c r="I36" s="4" t="n"/>
       <c r="J36" s="4" t="n"/>
       <c r="K36" s="4" t="n"/>
@@ -37228,10 +37252,10 @@
         <v>22.45</v>
       </c>
       <c r="F37" s="4" t="n"/>
-      <c r="G37" s="4" t="n">
+      <c r="G37" s="4" t="n"/>
+      <c r="H37" s="4" t="n">
         <v>23.05</v>
       </c>
-      <c r="H37" s="4" t="n"/>
       <c r="I37" s="4" t="n"/>
       <c r="J37" s="4" t="n"/>
       <c r="K37" s="4" t="n"/>
@@ -37284,13 +37308,13 @@
       <c r="D38" s="4" t="n"/>
       <c r="E38" s="4" t="n"/>
       <c r="F38" s="4" t="n"/>
-      <c r="G38" s="4" t="n">
+      <c r="G38" s="4" t="n"/>
+      <c r="H38" s="4" t="n">
         <v>21.48</v>
       </c>
-      <c r="H38" s="4" t="n">
+      <c r="I38" s="4" t="n">
         <v>20.99</v>
       </c>
-      <c r="I38" s="4" t="n"/>
       <c r="J38" s="4" t="n"/>
       <c r="K38" s="4" t="n">
         <v>21.09</v>
@@ -37353,10 +37377,10 @@
       <c r="E39" s="4" t="n"/>
       <c r="F39" s="4" t="n"/>
       <c r="G39" s="4" t="n"/>
-      <c r="H39" s="4" t="n">
+      <c r="H39" s="4" t="n"/>
+      <c r="I39" s="4" t="n">
         <v>29.75</v>
       </c>
-      <c r="I39" s="4" t="n"/>
       <c r="J39" s="4" t="n"/>
       <c r="K39" s="4" t="n">
         <v>29.95</v>
@@ -37417,9 +37441,11 @@
         <v>33.59</v>
       </c>
       <c r="G40" s="4" t="n">
+        <v>33.99</v>
+      </c>
+      <c r="H40" s="4" t="n">
         <v>34.9</v>
       </c>
-      <c r="H40" s="4" t="n"/>
       <c r="I40" s="4" t="n"/>
       <c r="J40" s="4" t="n"/>
       <c r="K40" s="4" t="n"/>
@@ -37480,11 +37506,11 @@
       <c r="F41" s="4" t="n">
         <v>30.39</v>
       </c>
-      <c r="G41" s="4" t="n"/>
+      <c r="G41" s="4" t="n">
+        <v>30.29</v>
+      </c>
       <c r="H41" s="4" t="n"/>
-      <c r="I41" s="4" t="n">
-        <v>30.29</v>
-      </c>
+      <c r="I41" s="4" t="n"/>
       <c r="J41" s="4" t="n"/>
       <c r="K41" s="4" t="n"/>
       <c r="L41" s="4" t="n"/>
@@ -37534,10 +37560,10 @@
       </c>
       <c r="E42" s="4" t="n"/>
       <c r="F42" s="4" t="n"/>
-      <c r="G42" s="4" t="n">
+      <c r="G42" s="4" t="n"/>
+      <c r="H42" s="4" t="n">
         <v>22.3</v>
       </c>
-      <c r="H42" s="4" t="n"/>
       <c r="I42" s="4" t="n"/>
       <c r="J42" s="4" t="n"/>
       <c r="K42" s="4" t="n"/>
@@ -37604,11 +37630,11 @@
       <c r="F43" s="4" t="n">
         <v>38.09</v>
       </c>
-      <c r="G43" s="4" t="n"/>
+      <c r="G43" s="4" t="n">
+        <v>38.2</v>
+      </c>
       <c r="H43" s="4" t="n"/>
-      <c r="I43" s="4" t="n">
-        <v>38.2</v>
-      </c>
+      <c r="I43" s="4" t="n"/>
       <c r="J43" s="4" t="n"/>
       <c r="K43" s="4" t="n"/>
       <c r="L43" s="4" t="n"/>
@@ -37656,10 +37682,10 @@
       <c r="D44" s="4" t="n"/>
       <c r="E44" s="4" t="n"/>
       <c r="F44" s="4" t="n"/>
-      <c r="G44" s="4" t="n">
+      <c r="G44" s="4" t="n"/>
+      <c r="H44" s="4" t="n">
         <v>22.25</v>
       </c>
-      <c r="H44" s="4" t="n"/>
       <c r="I44" s="4" t="n"/>
       <c r="J44" s="4" t="n"/>
       <c r="K44" s="4" t="n"/>
@@ -37733,10 +37759,10 @@
       </c>
       <c r="F45" s="4" t="n"/>
       <c r="G45" s="4" t="n"/>
-      <c r="H45" s="4" t="n">
+      <c r="H45" s="4" t="n"/>
+      <c r="I45" s="4" t="n">
         <v>40.69</v>
       </c>
-      <c r="I45" s="4" t="n"/>
       <c r="J45" s="4" t="n"/>
       <c r="K45" s="4" t="n"/>
       <c r="L45" s="4" t="n"/>
@@ -37794,11 +37820,11 @@
       <c r="F46" s="4" t="n">
         <v>32.29</v>
       </c>
-      <c r="G46" s="4" t="n"/>
+      <c r="G46" s="4" t="n">
+        <v>32.49</v>
+      </c>
       <c r="H46" s="4" t="n"/>
-      <c r="I46" s="4" t="n">
-        <v>32.49</v>
-      </c>
+      <c r="I46" s="4" t="n"/>
       <c r="J46" s="4" t="n"/>
       <c r="K46" s="4" t="n"/>
       <c r="L46" s="4" t="n"/>
@@ -38020,10 +38046,10 @@
         <v>25.99</v>
       </c>
       <c r="F50" s="4" t="n"/>
-      <c r="G50" s="4" t="n">
+      <c r="G50" s="4" t="n"/>
+      <c r="H50" s="4" t="n">
         <v>26.59</v>
       </c>
-      <c r="H50" s="4" t="n"/>
       <c r="I50" s="4" t="n"/>
       <c r="J50" s="4" t="n"/>
       <c r="K50" s="4" t="n"/>
@@ -38079,12 +38105,14 @@
       <c r="E51" s="4" t="n"/>
       <c r="F51" s="4" t="n"/>
       <c r="G51" s="4" t="n">
+        <v>24.09</v>
+      </c>
+      <c r="H51" s="4" t="n">
         <v>24.39</v>
       </c>
-      <c r="H51" s="4" t="n">
+      <c r="I51" s="4" t="n">
         <v>24.29</v>
       </c>
-      <c r="I51" s="4" t="n"/>
       <c r="J51" s="4" t="n"/>
       <c r="K51" s="4" t="n">
         <v>23.79</v>
@@ -38146,11 +38174,11 @@
       <c r="F52" s="4" t="n">
         <v>32.3</v>
       </c>
-      <c r="G52" s="4" t="n"/>
+      <c r="G52" s="4" t="n">
+        <v>32.05</v>
+      </c>
       <c r="H52" s="4" t="n"/>
-      <c r="I52" s="4" t="n">
-        <v>32.05</v>
-      </c>
+      <c r="I52" s="4" t="n"/>
       <c r="J52" s="4" t="n"/>
       <c r="K52" s="4" t="n"/>
       <c r="L52" s="4" t="n"/>
@@ -38323,9 +38351,11 @@
       </c>
       <c r="F55" s="4" t="n"/>
       <c r="G55" s="4" t="n">
+        <v>32.85</v>
+      </c>
+      <c r="H55" s="4" t="n">
         <v>32.73</v>
       </c>
-      <c r="H55" s="4" t="n"/>
       <c r="I55" s="4" t="n"/>
       <c r="J55" s="4" t="n"/>
       <c r="K55" s="4" t="n"/>
@@ -38384,11 +38414,11 @@
       <c r="F56" s="4" t="n">
         <v>35.6</v>
       </c>
-      <c r="G56" s="4" t="n"/>
+      <c r="G56" s="4" t="n">
+        <v>35.95</v>
+      </c>
       <c r="H56" s="4" t="n"/>
-      <c r="I56" s="4" t="n">
-        <v>35.95</v>
-      </c>
+      <c r="I56" s="4" t="n"/>
       <c r="J56" s="4" t="n"/>
       <c r="K56" s="4" t="n"/>
       <c r="L56" s="4" t="n"/>
@@ -38446,11 +38476,11 @@
         <v>34.55</v>
       </c>
       <c r="F57" s="4" t="n"/>
-      <c r="G57" s="4" t="n"/>
+      <c r="G57" s="4" t="n">
+        <v>35.55</v>
+      </c>
       <c r="H57" s="4" t="n"/>
-      <c r="I57" s="4" t="n">
-        <v>35.55</v>
-      </c>
+      <c r="I57" s="4" t="n"/>
       <c r="J57" s="4" t="n"/>
       <c r="K57" s="4" t="n"/>
       <c r="L57" s="4" t="n"/>
@@ -38506,11 +38536,11 @@
       <c r="F58" s="4" t="n">
         <v>24.43</v>
       </c>
-      <c r="G58" s="4" t="n"/>
+      <c r="G58" s="4" t="n">
+        <v>24.59</v>
+      </c>
       <c r="H58" s="4" t="n"/>
-      <c r="I58" s="4" t="n">
-        <v>24.59</v>
-      </c>
+      <c r="I58" s="4" t="n"/>
       <c r="J58" s="4" t="n"/>
       <c r="K58" s="4" t="n"/>
       <c r="L58" s="4" t="n"/>
@@ -38565,9 +38595,11 @@
       <c r="E59" s="4" t="n"/>
       <c r="F59" s="4" t="n"/>
       <c r="G59" s="4" t="n">
+        <v>21.29</v>
+      </c>
+      <c r="H59" s="4" t="n">
         <v>21.19</v>
       </c>
-      <c r="H59" s="4" t="n"/>
       <c r="I59" s="4" t="n"/>
       <c r="J59" s="4" t="n"/>
       <c r="K59" s="4" t="n"/>
@@ -38686,10 +38718,10 @@
       </c>
       <c r="E61" s="4" t="n"/>
       <c r="F61" s="4" t="n"/>
-      <c r="G61" s="4" t="n">
+      <c r="G61" s="4" t="n"/>
+      <c r="H61" s="4" t="n">
         <v>21.72</v>
       </c>
-      <c r="H61" s="4" t="n"/>
       <c r="I61" s="4" t="n"/>
       <c r="J61" s="4" t="n"/>
       <c r="K61" s="4" t="n"/>
@@ -38765,13 +38797,13 @@
         <v>29.85</v>
       </c>
       <c r="G62" s="4" t="n">
+        <v>29.99</v>
+      </c>
+      <c r="H62" s="4" t="n">
         <v>31.49</v>
       </c>
-      <c r="H62" s="4" t="n">
+      <c r="I62" s="4" t="n">
         <v>30.89</v>
-      </c>
-      <c r="I62" s="4" t="n">
-        <v>29.99</v>
       </c>
       <c r="J62" s="4" t="n"/>
       <c r="K62" s="4" t="n"/>
@@ -38823,12 +38855,12 @@
       <c r="E63" s="4" t="n"/>
       <c r="F63" s="4" t="n"/>
       <c r="G63" s="4" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="H63" s="4" t="n">
         <v>24.5</v>
       </c>
-      <c r="H63" s="4" t="n"/>
-      <c r="I63" s="4" t="n">
-        <v>23.8</v>
-      </c>
+      <c r="I63" s="4" t="n"/>
       <c r="J63" s="4" t="n"/>
       <c r="K63" s="4" t="n"/>
       <c r="L63" s="4" t="n"/>
@@ -38884,7 +38916,9 @@
       <c r="F64" s="4" t="n">
         <v>33.8</v>
       </c>
-      <c r="G64" s="4" t="n"/>
+      <c r="G64" s="4" t="n">
+        <v>33.89</v>
+      </c>
       <c r="H64" s="4" t="n"/>
       <c r="I64" s="4" t="n"/>
       <c r="J64" s="4" t="n"/>
@@ -38945,10 +38979,10 @@
         <v>32.9</v>
       </c>
       <c r="G65" s="4" t="n"/>
-      <c r="H65" s="4" t="n">
+      <c r="H65" s="4" t="n"/>
+      <c r="I65" s="4" t="n">
         <v>33.79</v>
       </c>
-      <c r="I65" s="4" t="n"/>
       <c r="J65" s="4" t="n"/>
       <c r="K65" s="4" t="n"/>
       <c r="L65" s="4" t="n"/>
@@ -39053,10 +39087,10 @@
       <c r="E67" s="4" t="n"/>
       <c r="F67" s="4" t="n"/>
       <c r="G67" s="4" t="n"/>
-      <c r="H67" s="4" t="n">
+      <c r="H67" s="4" t="n"/>
+      <c r="I67" s="4" t="n">
         <v>18.09</v>
       </c>
-      <c r="I67" s="4" t="n"/>
       <c r="J67" s="4" t="n"/>
       <c r="K67" s="4" t="n"/>
       <c r="L67" s="4" t="n"/>
@@ -39116,11 +39150,11 @@
       <c r="D68" s="4" t="n"/>
       <c r="E68" s="4" t="n"/>
       <c r="F68" s="4" t="n"/>
-      <c r="G68" s="4" t="n"/>
+      <c r="G68" s="4" t="n">
+        <v>27.5</v>
+      </c>
       <c r="H68" s="4" t="n"/>
-      <c r="I68" s="4" t="n">
-        <v>27.5</v>
-      </c>
+      <c r="I68" s="4" t="n"/>
       <c r="J68" s="4" t="n"/>
       <c r="K68" s="4" t="n"/>
       <c r="L68" s="4" t="n"/>
@@ -39182,11 +39216,11 @@
       <c r="F69" s="4" t="n">
         <v>32.97</v>
       </c>
-      <c r="G69" s="4" t="n"/>
+      <c r="G69" s="4" t="n">
+        <v>33.79</v>
+      </c>
       <c r="H69" s="4" t="n"/>
-      <c r="I69" s="4" t="n">
-        <v>33.79</v>
-      </c>
+      <c r="I69" s="4" t="n"/>
       <c r="J69" s="4" t="n"/>
       <c r="K69" s="4" t="n"/>
       <c r="L69" s="4" t="n"/>
@@ -39237,10 +39271,10 @@
       <c r="E70" s="4" t="n"/>
       <c r="F70" s="4" t="n"/>
       <c r="G70" s="4" t="n"/>
-      <c r="H70" s="4" t="n">
+      <c r="H70" s="4" t="n"/>
+      <c r="I70" s="4" t="n">
         <v>21.63</v>
       </c>
-      <c r="I70" s="4" t="n"/>
       <c r="J70" s="4" t="n"/>
       <c r="K70" s="4" t="n"/>
       <c r="L70" s="4" t="n">
@@ -39302,11 +39336,11 @@
       <c r="F71" s="4" t="n">
         <v>38.07</v>
       </c>
-      <c r="G71" s="4" t="n"/>
+      <c r="G71" s="4" t="n">
+        <v>38.3</v>
+      </c>
       <c r="H71" s="4" t="n"/>
-      <c r="I71" s="4" t="n">
-        <v>38.3</v>
-      </c>
+      <c r="I71" s="4" t="n"/>
       <c r="J71" s="4" t="n">
         <v>38.79</v>
       </c>
@@ -39360,13 +39394,13 @@
         <v>25.6</v>
       </c>
       <c r="F72" s="4" t="n"/>
-      <c r="G72" s="4" t="n">
+      <c r="G72" s="4" t="n"/>
+      <c r="H72" s="4" t="n">
         <v>25.93</v>
       </c>
-      <c r="H72" s="4" t="n">
+      <c r="I72" s="4" t="n">
         <v>25.85</v>
       </c>
-      <c r="I72" s="4" t="n"/>
       <c r="J72" s="4" t="n"/>
       <c r="K72" s="4" t="n"/>
       <c r="L72" s="4" t="n">
@@ -39430,10 +39464,10 @@
       <c r="D73" s="4" t="n"/>
       <c r="E73" s="4" t="n"/>
       <c r="F73" s="4" t="n"/>
-      <c r="G73" s="4" t="n">
+      <c r="G73" s="4" t="n"/>
+      <c r="H73" s="4" t="n">
         <v>19.19</v>
       </c>
-      <c r="H73" s="4" t="n"/>
       <c r="I73" s="4" t="n"/>
       <c r="J73" s="4" t="n"/>
       <c r="K73" s="4" t="n"/>
@@ -39491,10 +39525,10 @@
       <c r="E74" s="4" t="n"/>
       <c r="F74" s="4" t="n"/>
       <c r="G74" s="4" t="n"/>
-      <c r="H74" s="4" t="n">
+      <c r="H74" s="4" t="n"/>
+      <c r="I74" s="4" t="n">
         <v>33.95</v>
       </c>
-      <c r="I74" s="4" t="n"/>
       <c r="J74" s="4" t="n">
         <v>34.79</v>
       </c>
@@ -39549,10 +39583,10 @@
       <c r="E75" s="4" t="n"/>
       <c r="F75" s="4" t="n"/>
       <c r="G75" s="4" t="n"/>
-      <c r="H75" s="4" t="n">
+      <c r="H75" s="4" t="n"/>
+      <c r="I75" s="4" t="n">
         <v>26.69</v>
       </c>
-      <c r="I75" s="4" t="n"/>
       <c r="J75" s="4" t="n"/>
       <c r="K75" s="4" t="n">
         <v>26.25</v>
@@ -39604,10 +39638,10 @@
       <c r="D76" s="4" t="n"/>
       <c r="E76" s="4" t="n"/>
       <c r="F76" s="4" t="n"/>
-      <c r="G76" s="4" t="n">
+      <c r="G76" s="4" t="n"/>
+      <c r="H76" s="4" t="n">
         <v>16.6</v>
       </c>
-      <c r="H76" s="4" t="n"/>
       <c r="I76" s="4" t="n"/>
       <c r="J76" s="4" t="n"/>
       <c r="K76" s="4" t="n"/>
@@ -39728,11 +39762,11 @@
       <c r="F78" s="4" t="n">
         <v>31.2</v>
       </c>
-      <c r="G78" s="4" t="n"/>
+      <c r="G78" s="4" t="n">
+        <v>31.59</v>
+      </c>
       <c r="H78" s="4" t="n"/>
-      <c r="I78" s="4" t="n">
-        <v>31.59</v>
-      </c>
+      <c r="I78" s="4" t="n"/>
       <c r="J78" s="4" t="n">
         <v>31.8</v>
       </c>
@@ -39906,11 +39940,11 @@
       <c r="F81" s="4" t="n">
         <v>63.6</v>
       </c>
-      <c r="G81" s="4" t="n"/>
+      <c r="G81" s="4" t="n">
+        <v>63.99</v>
+      </c>
       <c r="H81" s="4" t="n"/>
-      <c r="I81" s="4" t="n">
-        <v>63.99</v>
-      </c>
+      <c r="I81" s="4" t="n"/>
       <c r="J81" s="4" t="n"/>
       <c r="K81" s="4" t="n"/>
       <c r="L81" s="4" t="n"/>
@@ -40075,10 +40109,10 @@
         <v>26.59</v>
       </c>
       <c r="G84" s="4" t="n"/>
-      <c r="H84" s="4" t="n">
+      <c r="H84" s="4" t="n"/>
+      <c r="I84" s="4" t="n">
         <v>27.39</v>
       </c>
-      <c r="I84" s="4" t="n"/>
       <c r="J84" s="4" t="n"/>
       <c r="K84" s="4" t="n"/>
       <c r="L84" s="4" t="n"/>
@@ -40284,37 +40318,37 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>玻璃★1</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>玻璃★2</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>玻璃★3</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>9x8★6</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>速尾★4</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>速尾★5</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>速尾★6</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>玻璃★1</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>玻璃★2</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>玻璃★3</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
@@ -40545,12 +40579,12 @@
       <c r="K2" s="4" t="n"/>
       <c r="L2" s="4" t="n"/>
       <c r="M2" s="4" t="n"/>
-      <c r="N2" s="4" t="n">
-        <v>19.1</v>
-      </c>
+      <c r="N2" s="4" t="n"/>
       <c r="O2" s="4" t="n"/>
       <c r="P2" s="4" t="n"/>
-      <c r="Q2" s="4" t="n"/>
+      <c r="Q2" s="4" t="n">
+        <v>19.1</v>
+      </c>
       <c r="R2" s="4" t="n"/>
       <c r="S2" s="4" t="n"/>
       <c r="T2" s="4" t="n"/>
@@ -40766,12 +40800,12 @@
       <c r="K5" s="4" t="n"/>
       <c r="L5" s="4" t="n"/>
       <c r="M5" s="4" t="n"/>
-      <c r="N5" s="4" t="n">
-        <v>18.2</v>
-      </c>
+      <c r="N5" s="4" t="n"/>
       <c r="O5" s="4" t="n"/>
       <c r="P5" s="4" t="n"/>
-      <c r="Q5" s="4" t="n"/>
+      <c r="Q5" s="4" t="n">
+        <v>18.2</v>
+      </c>
       <c r="R5" s="4" t="n"/>
       <c r="S5" s="4" t="n"/>
       <c r="T5" s="4" t="n"/>
@@ -40843,12 +40877,12 @@
       <c r="K6" s="4" t="n"/>
       <c r="L6" s="4" t="n"/>
       <c r="M6" s="4" t="n"/>
-      <c r="N6" s="4" t="n">
-        <v>18.05</v>
-      </c>
+      <c r="N6" s="4" t="n"/>
       <c r="O6" s="4" t="n"/>
       <c r="P6" s="4" t="n"/>
-      <c r="Q6" s="4" t="n"/>
+      <c r="Q6" s="4" t="n">
+        <v>18.05</v>
+      </c>
       <c r="R6" s="4" t="n"/>
       <c r="S6" s="4" t="n"/>
       <c r="T6" s="4" t="n"/>
@@ -40997,13 +41031,13 @@
         <v>27.75</v>
       </c>
       <c r="M8" s="4" t="n"/>
-      <c r="N8" s="4" t="n"/>
+      <c r="N8" s="4" t="n">
+        <v>28.23</v>
+      </c>
       <c r="O8" s="4" t="n"/>
       <c r="P8" s="4" t="n"/>
       <c r="Q8" s="4" t="n"/>
-      <c r="R8" s="4" t="n">
-        <v>28.23</v>
-      </c>
+      <c r="R8" s="4" t="n"/>
       <c r="S8" s="4" t="n"/>
       <c r="T8" s="4" t="n"/>
       <c r="U8" s="4" t="n">
@@ -41071,12 +41105,12 @@
       <c r="L9" s="4" t="n"/>
       <c r="M9" s="4" t="n"/>
       <c r="N9" s="4" t="n"/>
-      <c r="O9" s="4" t="n">
-        <v>20.52</v>
-      </c>
+      <c r="O9" s="4" t="n"/>
       <c r="P9" s="4" t="n"/>
       <c r="Q9" s="4" t="n"/>
-      <c r="R9" s="4" t="n"/>
+      <c r="R9" s="4" t="n">
+        <v>20.52</v>
+      </c>
       <c r="S9" s="4" t="n"/>
       <c r="T9" s="4" t="n"/>
       <c r="U9" s="4" t="n"/>
@@ -41145,17 +41179,17 @@
       <c r="K10" s="4" t="n"/>
       <c r="L10" s="4" t="n"/>
       <c r="M10" s="4" t="n"/>
-      <c r="N10" s="4" t="n">
-        <v>23.5</v>
-      </c>
+      <c r="N10" s="4" t="n"/>
       <c r="O10" s="4" t="n"/>
       <c r="P10" s="4" t="n"/>
       <c r="Q10" s="4" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="R10" s="4" t="n"/>
       <c r="S10" s="4" t="n"/>
-      <c r="T10" s="4" t="n"/>
+      <c r="T10" s="4" t="n">
+        <v>23.4</v>
+      </c>
       <c r="U10" s="4" t="n"/>
       <c r="V10" s="4" t="n"/>
       <c r="W10" s="4" t="n"/>
@@ -41296,12 +41330,12 @@
       <c r="L12" s="4" t="n"/>
       <c r="M12" s="4" t="n"/>
       <c r="N12" s="4" t="n"/>
-      <c r="O12" s="4" t="n">
-        <v>21.99</v>
-      </c>
+      <c r="O12" s="4" t="n"/>
       <c r="P12" s="4" t="n"/>
       <c r="Q12" s="4" t="n"/>
-      <c r="R12" s="4" t="n"/>
+      <c r="R12" s="4" t="n">
+        <v>21.99</v>
+      </c>
       <c r="S12" s="4" t="n"/>
       <c r="T12" s="4" t="n"/>
       <c r="U12" s="4" t="n"/>
@@ -41459,13 +41493,13 @@
       <c r="K14" s="4" t="n"/>
       <c r="L14" s="4" t="n"/>
       <c r="M14" s="4" t="n"/>
-      <c r="N14" s="4" t="n"/>
+      <c r="N14" s="4" t="n">
+        <v>26.15</v>
+      </c>
       <c r="O14" s="4" t="n"/>
       <c r="P14" s="4" t="n"/>
       <c r="Q14" s="4" t="n"/>
-      <c r="R14" s="4" t="n">
-        <v>26.15</v>
-      </c>
+      <c r="R14" s="4" t="n"/>
       <c r="S14" s="4" t="n"/>
       <c r="T14" s="4" t="n"/>
       <c r="U14" s="4" t="n"/>
@@ -41692,13 +41726,13 @@
       <c r="K17" s="4" t="n"/>
       <c r="L17" s="4" t="n"/>
       <c r="M17" s="4" t="n"/>
-      <c r="N17" s="4" t="n"/>
+      <c r="N17" s="4" t="n">
+        <v>30.49</v>
+      </c>
       <c r="O17" s="4" t="n"/>
       <c r="P17" s="4" t="n"/>
       <c r="Q17" s="4" t="n"/>
-      <c r="R17" s="4" t="n">
-        <v>30.49</v>
-      </c>
+      <c r="R17" s="4" t="n"/>
       <c r="S17" s="4" t="n"/>
       <c r="T17" s="4" t="n"/>
       <c r="U17" s="4" t="n"/>
@@ -41766,12 +41800,12 @@
       <c r="L18" s="4" t="n"/>
       <c r="M18" s="4" t="n"/>
       <c r="N18" s="4" t="n"/>
-      <c r="O18" s="4" t="n">
-        <v>24.59</v>
-      </c>
+      <c r="O18" s="4" t="n"/>
       <c r="P18" s="4" t="n"/>
       <c r="Q18" s="4" t="n"/>
-      <c r="R18" s="4" t="n"/>
+      <c r="R18" s="4" t="n">
+        <v>24.59</v>
+      </c>
       <c r="S18" s="4" t="n"/>
       <c r="T18" s="4" t="n"/>
       <c r="U18" s="4" t="n"/>
@@ -41846,12 +41880,12 @@
       <c r="M19" s="4" t="n">
         <v>32.5</v>
       </c>
-      <c r="N19" s="4" t="n">
-        <v>33.4</v>
-      </c>
+      <c r="N19" s="4" t="n"/>
       <c r="O19" s="4" t="n"/>
       <c r="P19" s="4" t="n"/>
-      <c r="Q19" s="4" t="n"/>
+      <c r="Q19" s="4" t="n">
+        <v>33.4</v>
+      </c>
       <c r="R19" s="4" t="n"/>
       <c r="S19" s="4" t="n"/>
       <c r="T19" s="4" t="n"/>
@@ -41919,12 +41953,12 @@
         <v>22.4</v>
       </c>
       <c r="M20" s="4" t="n"/>
-      <c r="N20" s="4" t="n">
-        <v>22.59</v>
-      </c>
+      <c r="N20" s="4" t="n"/>
       <c r="O20" s="4" t="n"/>
       <c r="P20" s="4" t="n"/>
-      <c r="Q20" s="4" t="n"/>
+      <c r="Q20" s="4" t="n">
+        <v>22.59</v>
+      </c>
       <c r="R20" s="4" t="n"/>
       <c r="S20" s="4" t="n"/>
       <c r="T20" s="4" t="n"/>
@@ -42214,16 +42248,16 @@
       <c r="L24" s="4" t="n"/>
       <c r="M24" s="4" t="n"/>
       <c r="N24" s="4" t="n"/>
-      <c r="O24" s="4" t="n">
+      <c r="O24" s="4" t="n"/>
+      <c r="P24" s="4" t="n"/>
+      <c r="Q24" s="4" t="n"/>
+      <c r="R24" s="4" t="n">
         <v>23.69</v>
       </c>
-      <c r="P24" s="4" t="n"/>
-      <c r="Q24" s="4" t="n">
+      <c r="S24" s="4" t="n"/>
+      <c r="T24" s="4" t="n">
         <v>23.3</v>
       </c>
-      <c r="R24" s="4" t="n"/>
-      <c r="S24" s="4" t="n"/>
-      <c r="T24" s="4" t="n"/>
       <c r="U24" s="4" t="n"/>
       <c r="V24" s="4" t="n"/>
       <c r="W24" s="4" t="n"/>
@@ -42368,12 +42402,12 @@
       <c r="N26" s="4" t="n"/>
       <c r="O26" s="4" t="n"/>
       <c r="P26" s="4" t="n"/>
-      <c r="Q26" s="4" t="n">
-        <v>18.99</v>
-      </c>
+      <c r="Q26" s="4" t="n"/>
       <c r="R26" s="4" t="n"/>
       <c r="S26" s="4" t="n"/>
-      <c r="T26" s="4" t="n"/>
+      <c r="T26" s="4" t="n">
+        <v>18.99</v>
+      </c>
       <c r="U26" s="4" t="n"/>
       <c r="V26" s="4" t="n"/>
       <c r="W26" s="4" t="n"/>
@@ -42444,12 +42478,12 @@
       <c r="K27" s="4" t="n"/>
       <c r="L27" s="4" t="n"/>
       <c r="M27" s="4" t="n"/>
-      <c r="N27" s="4" t="n">
-        <v>35.2</v>
-      </c>
+      <c r="N27" s="4" t="n"/>
       <c r="O27" s="4" t="n"/>
       <c r="P27" s="4" t="n"/>
-      <c r="Q27" s="4" t="n"/>
+      <c r="Q27" s="4" t="n">
+        <v>35.2</v>
+      </c>
       <c r="R27" s="4" t="n"/>
       <c r="S27" s="4" t="n"/>
       <c r="T27" s="4" t="n"/>
@@ -42522,12 +42556,12 @@
       <c r="N28" s="4" t="n"/>
       <c r="O28" s="4" t="n"/>
       <c r="P28" s="4" t="n"/>
-      <c r="Q28" s="4" t="n">
-        <v>33.5</v>
-      </c>
+      <c r="Q28" s="4" t="n"/>
       <c r="R28" s="4" t="n"/>
       <c r="S28" s="4" t="n"/>
-      <c r="T28" s="4" t="n"/>
+      <c r="T28" s="4" t="n">
+        <v>33.5</v>
+      </c>
       <c r="U28" s="4" t="n"/>
       <c r="V28" s="4" t="n"/>
       <c r="W28" s="4" t="n"/>
@@ -42673,12 +42707,12 @@
       <c r="K30" s="4" t="n"/>
       <c r="L30" s="4" t="n"/>
       <c r="M30" s="4" t="n"/>
-      <c r="N30" s="4" t="n">
-        <v>23.19</v>
-      </c>
+      <c r="N30" s="4" t="n"/>
       <c r="O30" s="4" t="n"/>
       <c r="P30" s="4" t="n"/>
-      <c r="Q30" s="4" t="n"/>
+      <c r="Q30" s="4" t="n">
+        <v>23.19</v>
+      </c>
       <c r="R30" s="4" t="n"/>
       <c r="S30" s="4" t="n"/>
       <c r="T30" s="4" t="n"/>
@@ -42742,12 +42776,12 @@
       <c r="K31" s="4" t="n"/>
       <c r="L31" s="4" t="n"/>
       <c r="M31" s="4" t="n"/>
-      <c r="N31" s="4" t="n">
-        <v>19.19</v>
-      </c>
+      <c r="N31" s="4" t="n"/>
       <c r="O31" s="4" t="n"/>
       <c r="P31" s="4" t="n"/>
-      <c r="Q31" s="4" t="n"/>
+      <c r="Q31" s="4" t="n">
+        <v>19.19</v>
+      </c>
       <c r="R31" s="4" t="n"/>
       <c r="S31" s="4" t="n"/>
       <c r="T31" s="4" t="n"/>
@@ -42819,12 +42853,12 @@
       <c r="K32" s="4" t="n"/>
       <c r="L32" s="4" t="n"/>
       <c r="M32" s="4" t="n"/>
-      <c r="N32" s="4" t="n">
-        <v>29.4</v>
-      </c>
+      <c r="N32" s="4" t="n"/>
       <c r="O32" s="4" t="n"/>
       <c r="P32" s="4" t="n"/>
-      <c r="Q32" s="4" t="n"/>
+      <c r="Q32" s="4" t="n">
+        <v>29.4</v>
+      </c>
       <c r="R32" s="4" t="n"/>
       <c r="S32" s="4" t="n"/>
       <c r="T32" s="4" t="n"/>
@@ -42900,12 +42934,12 @@
       <c r="K33" s="4" t="n"/>
       <c r="L33" s="4" t="n"/>
       <c r="M33" s="4" t="n"/>
-      <c r="N33" s="4" t="n">
-        <v>19.99</v>
-      </c>
+      <c r="N33" s="4" t="n"/>
       <c r="O33" s="4" t="n"/>
       <c r="P33" s="4" t="n"/>
-      <c r="Q33" s="4" t="n"/>
+      <c r="Q33" s="4" t="n">
+        <v>19.99</v>
+      </c>
       <c r="R33" s="4" t="n"/>
       <c r="S33" s="4" t="n"/>
       <c r="T33" s="4" t="n"/>
@@ -42977,12 +43011,12 @@
       <c r="M34" s="4" t="n"/>
       <c r="N34" s="4" t="n"/>
       <c r="O34" s="4" t="n"/>
-      <c r="P34" s="4" t="n">
-        <v>36.79</v>
-      </c>
+      <c r="P34" s="4" t="n"/>
       <c r="Q34" s="4" t="n"/>
       <c r="R34" s="4" t="n"/>
-      <c r="S34" s="4" t="n"/>
+      <c r="S34" s="4" t="n">
+        <v>36.79</v>
+      </c>
       <c r="T34" s="4" t="n"/>
       <c r="U34" s="4" t="n"/>
       <c r="V34" s="4" t="n"/>
@@ -43044,12 +43078,12 @@
       <c r="K35" s="4" t="n"/>
       <c r="L35" s="4" t="n"/>
       <c r="M35" s="4" t="n"/>
-      <c r="N35" s="4" t="n">
-        <v>23.7</v>
-      </c>
+      <c r="N35" s="4" t="n"/>
       <c r="O35" s="4" t="n"/>
       <c r="P35" s="4" t="n"/>
-      <c r="Q35" s="4" t="n"/>
+      <c r="Q35" s="4" t="n">
+        <v>23.7</v>
+      </c>
       <c r="R35" s="4" t="n"/>
       <c r="S35" s="4" t="n"/>
       <c r="T35" s="4" t="n"/>
@@ -43347,12 +43381,12 @@
       <c r="N39" s="4" t="n"/>
       <c r="O39" s="4" t="n"/>
       <c r="P39" s="4" t="n"/>
-      <c r="Q39" s="4" t="n">
-        <v>29.9</v>
-      </c>
+      <c r="Q39" s="4" t="n"/>
       <c r="R39" s="4" t="n"/>
       <c r="S39" s="4" t="n"/>
-      <c r="T39" s="4" t="n"/>
+      <c r="T39" s="4" t="n">
+        <v>29.9</v>
+      </c>
       <c r="U39" s="4" t="n"/>
       <c r="V39" s="4" t="n"/>
       <c r="W39" s="4" t="n"/>
@@ -43429,12 +43463,12 @@
       <c r="M40" s="4" t="n">
         <v>34.3</v>
       </c>
-      <c r="N40" s="4" t="n">
-        <v>35.2</v>
-      </c>
+      <c r="N40" s="4" t="n"/>
       <c r="O40" s="4" t="n"/>
       <c r="P40" s="4" t="n"/>
-      <c r="Q40" s="4" t="n"/>
+      <c r="Q40" s="4" t="n">
+        <v>35.2</v>
+      </c>
       <c r="R40" s="4" t="n"/>
       <c r="S40" s="4" t="n"/>
       <c r="T40" s="4" t="n"/>
@@ -43583,12 +43617,12 @@
       <c r="K42" s="4" t="n"/>
       <c r="L42" s="4" t="n"/>
       <c r="M42" s="4" t="n"/>
-      <c r="N42" s="4" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="N42" s="4" t="n"/>
       <c r="O42" s="4" t="n"/>
       <c r="P42" s="4" t="n"/>
-      <c r="Q42" s="4" t="n"/>
+      <c r="Q42" s="4" t="n">
+        <v>22.5</v>
+      </c>
       <c r="R42" s="4" t="n"/>
       <c r="S42" s="4" t="n"/>
       <c r="T42" s="4" t="n"/>
@@ -43729,12 +43763,12 @@
       <c r="K44" s="4" t="n"/>
       <c r="L44" s="4" t="n"/>
       <c r="M44" s="4" t="n"/>
-      <c r="N44" s="4" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="N44" s="4" t="n"/>
       <c r="O44" s="4" t="n"/>
       <c r="P44" s="4" t="n"/>
-      <c r="Q44" s="4" t="n"/>
+      <c r="Q44" s="4" t="n">
+        <v>22.5</v>
+      </c>
       <c r="R44" s="4" t="n"/>
       <c r="S44" s="4" t="n"/>
       <c r="T44" s="4" t="n"/>
@@ -43812,13 +43846,13 @@
       <c r="M45" s="4" t="n">
         <v>39.19</v>
       </c>
-      <c r="N45" s="4" t="n"/>
+      <c r="N45" s="4" t="n">
+        <v>39.79</v>
+      </c>
       <c r="O45" s="4" t="n"/>
       <c r="P45" s="4" t="n"/>
       <c r="Q45" s="4" t="n"/>
-      <c r="R45" s="4" t="n">
-        <v>39.79</v>
-      </c>
+      <c r="R45" s="4" t="n"/>
       <c r="S45" s="4" t="n"/>
       <c r="T45" s="4" t="n"/>
       <c r="U45" s="4" t="n"/>
@@ -43966,19 +44000,19 @@
       <c r="M47" s="4" t="n">
         <v>40.99</v>
       </c>
-      <c r="N47" s="4" t="n"/>
-      <c r="O47" s="4" t="n"/>
-      <c r="P47" s="4" t="n"/>
+      <c r="N47" s="4" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="O47" s="4" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="P47" s="4" t="n">
+        <v>41.3</v>
+      </c>
       <c r="Q47" s="4" t="n"/>
-      <c r="R47" s="4" t="n">
-        <v>41.5</v>
-      </c>
-      <c r="S47" s="4" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="T47" s="4" t="n">
-        <v>41.3</v>
-      </c>
+      <c r="R47" s="4" t="n"/>
+      <c r="S47" s="4" t="n"/>
+      <c r="T47" s="4" t="n"/>
       <c r="U47" s="4" t="n"/>
       <c r="V47" s="4" t="n"/>
       <c r="W47" s="4" t="n"/>
@@ -44047,15 +44081,15 @@
       <c r="M48" s="4" t="n"/>
       <c r="N48" s="4" t="n"/>
       <c r="O48" s="4" t="n"/>
-      <c r="P48" s="4" t="n">
+      <c r="P48" s="4" t="n"/>
+      <c r="Q48" s="4" t="n"/>
+      <c r="R48" s="4" t="n"/>
+      <c r="S48" s="4" t="n">
         <v>25.79</v>
       </c>
-      <c r="Q48" s="4" t="n">
+      <c r="T48" s="4" t="n">
         <v>25.2</v>
       </c>
-      <c r="R48" s="4" t="n"/>
-      <c r="S48" s="4" t="n"/>
-      <c r="T48" s="4" t="n"/>
       <c r="U48" s="4" t="n"/>
       <c r="V48" s="4" t="n"/>
       <c r="W48" s="4" t="n"/>
@@ -44124,12 +44158,12 @@
       </c>
       <c r="L49" s="4" t="n"/>
       <c r="M49" s="4" t="n"/>
-      <c r="N49" s="4" t="n">
-        <v>30.79</v>
-      </c>
+      <c r="N49" s="4" t="n"/>
       <c r="O49" s="4" t="n"/>
       <c r="P49" s="4" t="n"/>
-      <c r="Q49" s="4" t="n"/>
+      <c r="Q49" s="4" t="n">
+        <v>30.79</v>
+      </c>
       <c r="R49" s="4" t="n"/>
       <c r="S49" s="4" t="n"/>
       <c r="T49" s="4" t="n"/>
@@ -44195,12 +44229,12 @@
       <c r="K50" s="4" t="n"/>
       <c r="L50" s="4" t="n"/>
       <c r="M50" s="4" t="n"/>
-      <c r="N50" s="4" t="n">
-        <v>26.67</v>
-      </c>
+      <c r="N50" s="4" t="n"/>
       <c r="O50" s="4" t="n"/>
       <c r="P50" s="4" t="n"/>
-      <c r="Q50" s="4" t="n"/>
+      <c r="Q50" s="4" t="n">
+        <v>26.67</v>
+      </c>
       <c r="R50" s="4" t="n"/>
       <c r="S50" s="4" t="n"/>
       <c r="T50" s="4" t="n"/>
@@ -44264,12 +44298,12 @@
       <c r="K51" s="4" t="n"/>
       <c r="L51" s="4" t="n"/>
       <c r="M51" s="4" t="n"/>
-      <c r="N51" s="4" t="n">
-        <v>24.5</v>
-      </c>
+      <c r="N51" s="4" t="n"/>
       <c r="O51" s="4" t="n"/>
       <c r="P51" s="4" t="n"/>
-      <c r="Q51" s="4" t="n"/>
+      <c r="Q51" s="4" t="n">
+        <v>24.5</v>
+      </c>
       <c r="R51" s="4" t="n"/>
       <c r="S51" s="4" t="n"/>
       <c r="T51" s="4" t="n"/>
@@ -44335,19 +44369,19 @@
       <c r="K52" s="4" t="n"/>
       <c r="L52" s="4" t="n"/>
       <c r="M52" s="4" t="n"/>
-      <c r="N52" s="4" t="n"/>
-      <c r="O52" s="4" t="n"/>
-      <c r="P52" s="4" t="n"/>
+      <c r="N52" s="4" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="O52" s="4" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="P52" s="4" t="n">
+        <v>32.3</v>
+      </c>
       <c r="Q52" s="4" t="n"/>
-      <c r="R52" s="4" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="S52" s="4" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="T52" s="4" t="n">
-        <v>32.3</v>
-      </c>
+      <c r="R52" s="4" t="n"/>
+      <c r="S52" s="4" t="n"/>
+      <c r="T52" s="4" t="n"/>
       <c r="U52" s="4" t="n"/>
       <c r="V52" s="4" t="n"/>
       <c r="W52" s="4" t="n"/>
@@ -44562,12 +44596,12 @@
       <c r="K55" s="4" t="n"/>
       <c r="L55" s="4" t="n"/>
       <c r="M55" s="4" t="n"/>
-      <c r="N55" s="4" t="n">
-        <v>32.99</v>
-      </c>
+      <c r="N55" s="4" t="n"/>
       <c r="O55" s="4" t="n"/>
       <c r="P55" s="4" t="n"/>
-      <c r="Q55" s="4" t="n"/>
+      <c r="Q55" s="4" t="n">
+        <v>32.99</v>
+      </c>
       <c r="R55" s="4" t="n"/>
       <c r="S55" s="4" t="n"/>
       <c r="T55" s="4" t="n"/>
@@ -44714,17 +44748,17 @@
         <v>35</v>
       </c>
       <c r="M57" s="4" t="n"/>
-      <c r="N57" s="4" t="n"/>
+      <c r="N57" s="4" t="n">
+        <v>36.4</v>
+      </c>
       <c r="O57" s="4" t="n"/>
-      <c r="P57" s="4" t="n"/>
+      <c r="P57" s="4" t="n">
+        <v>36.19</v>
+      </c>
       <c r="Q57" s="4" t="n"/>
-      <c r="R57" s="4" t="n">
-        <v>36.4</v>
-      </c>
+      <c r="R57" s="4" t="n"/>
       <c r="S57" s="4" t="n"/>
-      <c r="T57" s="4" t="n">
-        <v>36.19</v>
-      </c>
+      <c r="T57" s="4" t="n"/>
       <c r="U57" s="4" t="n"/>
       <c r="V57" s="4" t="n">
         <v>36.94</v>
@@ -44864,12 +44898,12 @@
       <c r="K59" s="4" t="n"/>
       <c r="L59" s="4" t="n"/>
       <c r="M59" s="4" t="n"/>
-      <c r="N59" s="4" t="n">
-        <v>21.35</v>
-      </c>
+      <c r="N59" s="4" t="n"/>
       <c r="O59" s="4" t="n"/>
       <c r="P59" s="4" t="n"/>
-      <c r="Q59" s="4" t="n"/>
+      <c r="Q59" s="4" t="n">
+        <v>21.35</v>
+      </c>
       <c r="R59" s="4" t="n"/>
       <c r="S59" s="4" t="n"/>
       <c r="T59" s="4" t="n"/>
@@ -45022,12 +45056,12 @@
       <c r="K61" s="4" t="n"/>
       <c r="L61" s="4" t="n"/>
       <c r="M61" s="4" t="n"/>
-      <c r="N61" s="4" t="n">
-        <v>21.89</v>
-      </c>
+      <c r="N61" s="4" t="n"/>
       <c r="O61" s="4" t="n"/>
       <c r="P61" s="4" t="n"/>
-      <c r="Q61" s="4" t="n"/>
+      <c r="Q61" s="4" t="n">
+        <v>21.89</v>
+      </c>
       <c r="R61" s="4" t="n"/>
       <c r="S61" s="4" t="n"/>
       <c r="T61" s="4" t="n"/>
@@ -45097,17 +45131,17 @@
       <c r="M62" s="4" t="n">
         <v>31.1</v>
       </c>
-      <c r="N62" s="4" t="n">
-        <v>31.9</v>
-      </c>
+      <c r="N62" s="4" t="n"/>
       <c r="O62" s="4" t="n"/>
       <c r="P62" s="4" t="n"/>
       <c r="Q62" s="4" t="n">
-        <v>31.29</v>
+        <v>31.9</v>
       </c>
       <c r="R62" s="4" t="n"/>
       <c r="S62" s="4" t="n"/>
-      <c r="T62" s="4" t="n"/>
+      <c r="T62" s="4" t="n">
+        <v>31.29</v>
+      </c>
       <c r="U62" s="4" t="n"/>
       <c r="V62" s="4" t="n"/>
       <c r="W62" s="4" t="n"/>
@@ -45176,17 +45210,17 @@
       </c>
       <c r="L63" s="4" t="n"/>
       <c r="M63" s="4" t="n"/>
-      <c r="N63" s="4" t="n"/>
+      <c r="N63" s="4" t="n">
+        <v>24.39</v>
+      </c>
       <c r="O63" s="4" t="n"/>
-      <c r="P63" s="4" t="n"/>
+      <c r="P63" s="4" t="n">
+        <v>23.95</v>
+      </c>
       <c r="Q63" s="4" t="n"/>
-      <c r="R63" s="4" t="n">
-        <v>24.39</v>
-      </c>
+      <c r="R63" s="4" t="n"/>
       <c r="S63" s="4" t="n"/>
-      <c r="T63" s="4" t="n">
-        <v>23.95</v>
-      </c>
+      <c r="T63" s="4" t="n"/>
       <c r="U63" s="4" t="n"/>
       <c r="V63" s="4" t="n">
         <v>25.39</v>
@@ -45257,12 +45291,12 @@
         <v>33.6</v>
       </c>
       <c r="M64" s="4" t="n"/>
-      <c r="N64" s="4" t="n">
-        <v>24.6</v>
-      </c>
+      <c r="N64" s="4" t="n"/>
       <c r="O64" s="4" t="n"/>
       <c r="P64" s="4" t="n"/>
-      <c r="Q64" s="4" t="n"/>
+      <c r="Q64" s="4" t="n">
+        <v>24.6</v>
+      </c>
       <c r="R64" s="4" t="n"/>
       <c r="S64" s="4" t="n"/>
       <c r="T64" s="4" t="n"/>
@@ -45552,12 +45586,12 @@
       <c r="N68" s="4" t="n"/>
       <c r="O68" s="4" t="n"/>
       <c r="P68" s="4" t="n"/>
-      <c r="Q68" s="4" t="n">
-        <v>28.1</v>
-      </c>
+      <c r="Q68" s="4" t="n"/>
       <c r="R68" s="4" t="n"/>
       <c r="S68" s="4" t="n"/>
-      <c r="T68" s="4" t="n"/>
+      <c r="T68" s="4" t="n">
+        <v>28.1</v>
+      </c>
       <c r="U68" s="4" t="n"/>
       <c r="V68" s="4" t="n"/>
       <c r="W68" s="4" t="n"/>
@@ -45835,12 +45869,12 @@
       <c r="K72" s="4" t="n"/>
       <c r="L72" s="4" t="n"/>
       <c r="M72" s="4" t="n"/>
-      <c r="N72" s="4" t="n">
-        <v>26.15</v>
-      </c>
+      <c r="N72" s="4" t="n"/>
       <c r="O72" s="4" t="n"/>
       <c r="P72" s="4" t="n"/>
-      <c r="Q72" s="4" t="n"/>
+      <c r="Q72" s="4" t="n">
+        <v>26.15</v>
+      </c>
       <c r="R72" s="4" t="n"/>
       <c r="S72" s="4" t="n"/>
       <c r="T72" s="4" t="n"/>
@@ -45912,12 +45946,12 @@
       <c r="K73" s="4" t="n"/>
       <c r="L73" s="4" t="n"/>
       <c r="M73" s="4" t="n"/>
-      <c r="N73" s="4" t="n">
-        <v>19.4</v>
-      </c>
+      <c r="N73" s="4" t="n"/>
       <c r="O73" s="4" t="n"/>
       <c r="P73" s="4" t="n"/>
-      <c r="Q73" s="4" t="n"/>
+      <c r="Q73" s="4" t="n">
+        <v>19.4</v>
+      </c>
       <c r="R73" s="4" t="n"/>
       <c r="S73" s="4" t="n"/>
       <c r="T73" s="4" t="n"/>
@@ -45994,12 +46028,12 @@
       <c r="N74" s="4" t="n"/>
       <c r="O74" s="4" t="n"/>
       <c r="P74" s="4" t="n"/>
-      <c r="Q74" s="4" t="n">
-        <v>34.39</v>
-      </c>
+      <c r="Q74" s="4" t="n"/>
       <c r="R74" s="4" t="n"/>
       <c r="S74" s="4" t="n"/>
-      <c r="T74" s="4" t="n"/>
+      <c r="T74" s="4" t="n">
+        <v>34.39</v>
+      </c>
       <c r="U74" s="4" t="n">
         <v>35.5</v>
       </c>
@@ -46067,12 +46101,12 @@
       <c r="N75" s="4" t="n"/>
       <c r="O75" s="4" t="n"/>
       <c r="P75" s="4" t="n"/>
-      <c r="Q75" s="4" t="n">
-        <v>27.1</v>
-      </c>
+      <c r="Q75" s="4" t="n"/>
       <c r="R75" s="4" t="n"/>
       <c r="S75" s="4" t="n"/>
-      <c r="T75" s="4" t="n"/>
+      <c r="T75" s="4" t="n">
+        <v>27.1</v>
+      </c>
       <c r="U75" s="4" t="n"/>
       <c r="V75" s="4" t="n"/>
       <c r="W75" s="4" t="n"/>
@@ -46143,12 +46177,12 @@
       <c r="K76" s="4" t="n"/>
       <c r="L76" s="4" t="n"/>
       <c r="M76" s="4" t="n"/>
-      <c r="N76" s="4" t="n">
-        <v>16.99</v>
-      </c>
+      <c r="N76" s="4" t="n"/>
       <c r="O76" s="4" t="n"/>
       <c r="P76" s="4" t="n"/>
-      <c r="Q76" s="4" t="n"/>
+      <c r="Q76" s="4" t="n">
+        <v>16.99</v>
+      </c>
       <c r="R76" s="4" t="n"/>
       <c r="S76" s="4" t="n"/>
       <c r="T76" s="4" t="n"/>
@@ -46306,13 +46340,13 @@
         <v>31.6</v>
       </c>
       <c r="N78" s="4" t="n"/>
-      <c r="O78" s="4" t="n"/>
+      <c r="O78" s="4" t="n">
+        <v>32.2</v>
+      </c>
       <c r="P78" s="4" t="n"/>
       <c r="Q78" s="4" t="n"/>
       <c r="R78" s="4" t="n"/>
-      <c r="S78" s="4" t="n">
-        <v>32.2</v>
-      </c>
+      <c r="S78" s="4" t="n"/>
       <c r="T78" s="4" t="n"/>
       <c r="U78" s="4" t="n"/>
       <c r="V78" s="4" t="n"/>
@@ -46385,13 +46419,13 @@
         <v>23.2</v>
       </c>
       <c r="N79" s="4" t="n"/>
-      <c r="O79" s="4" t="n"/>
+      <c r="O79" s="4" t="n">
+        <v>23.3</v>
+      </c>
       <c r="P79" s="4" t="n"/>
       <c r="Q79" s="4" t="n"/>
       <c r="R79" s="4" t="n"/>
-      <c r="S79" s="4" t="n">
-        <v>23.3</v>
-      </c>
+      <c r="S79" s="4" t="n"/>
       <c r="T79" s="4" t="n"/>
       <c r="U79" s="4" t="n"/>
       <c r="V79" s="4" t="n"/>
@@ -46463,13 +46497,13 @@
       <c r="M80" s="4" t="n"/>
       <c r="N80" s="4" t="n"/>
       <c r="O80" s="4" t="n"/>
-      <c r="P80" s="4" t="n"/>
+      <c r="P80" s="4" t="n">
+        <v>29.49</v>
+      </c>
       <c r="Q80" s="4" t="n"/>
       <c r="R80" s="4" t="n"/>
       <c r="S80" s="4" t="n"/>
-      <c r="T80" s="4" t="n">
-        <v>29.49</v>
-      </c>
+      <c r="T80" s="4" t="n"/>
       <c r="U80" s="4" t="n"/>
       <c r="V80" s="4" t="n"/>
       <c r="W80" s="4" t="n"/>
@@ -46541,13 +46575,13 @@
         <v>63.8</v>
       </c>
       <c r="N81" s="4" t="n"/>
-      <c r="O81" s="4" t="n"/>
+      <c r="O81" s="4" t="n">
+        <v>65.39</v>
+      </c>
       <c r="P81" s="4" t="n"/>
       <c r="Q81" s="4" t="n"/>
       <c r="R81" s="4" t="n"/>
-      <c r="S81" s="4" t="n">
-        <v>65.39</v>
-      </c>
+      <c r="S81" s="4" t="n"/>
       <c r="T81" s="4" t="n"/>
       <c r="U81" s="4" t="n"/>
       <c r="V81" s="4" t="n"/>
@@ -46770,12 +46804,12 @@
       <c r="N84" s="4" t="n"/>
       <c r="O84" s="4" t="n"/>
       <c r="P84" s="4" t="n"/>
-      <c r="Q84" s="4" t="n">
-        <v>27.6</v>
-      </c>
+      <c r="Q84" s="4" t="n"/>
       <c r="R84" s="4" t="n"/>
       <c r="S84" s="4" t="n"/>
-      <c r="T84" s="4" t="n"/>
+      <c r="T84" s="4" t="n">
+        <v>27.6</v>
+      </c>
       <c r="U84" s="4" t="n"/>
       <c r="V84" s="4" t="n"/>
       <c r="W84" s="4" t="n"/>
@@ -46989,37 +47023,37 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>玻璃★1</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>玻璃★2</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>玻璃★3</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>9x8★6</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>速尾★4</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>速尾★5</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>速尾★6</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>玻璃★1</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>玻璃★2</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>玻璃★3</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
@@ -47250,14 +47284,14 @@
       <c r="K2" s="4" t="n"/>
       <c r="L2" s="4" t="n"/>
       <c r="M2" s="4" t="n"/>
-      <c r="N2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N2" s="4" t="n"/>
       <c r="O2" s="4" t="n"/>
       <c r="P2" s="4" t="n"/>
-      <c r="Q2" s="4" t="n"/>
+      <c r="Q2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="R2" s="4" t="n"/>
       <c r="S2" s="4" t="n"/>
       <c r="T2" s="4" t="n"/>
@@ -47352,14 +47386,14 @@
       <c r="N3" s="4" t="n"/>
       <c r="O3" s="4" t="n"/>
       <c r="P3" s="4" t="n"/>
-      <c r="Q3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q3" s="4" t="n"/>
       <c r="R3" s="4" t="n"/>
       <c r="S3" s="4" t="n"/>
-      <c r="T3" s="4" t="n"/>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U3" s="4" t="n"/>
       <c r="V3" s="4" t="inlineStr">
         <is>
@@ -47459,14 +47493,14 @@
       <c r="N4" s="4" t="n"/>
       <c r="O4" s="4" t="n"/>
       <c r="P4" s="4" t="n"/>
-      <c r="Q4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q4" s="4" t="n"/>
       <c r="R4" s="4" t="n"/>
       <c r="S4" s="4" t="n"/>
-      <c r="T4" s="4" t="n"/>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U4" s="4" t="n"/>
       <c r="V4" s="4" t="n"/>
       <c r="W4" s="4" t="n"/>
@@ -47555,11 +47589,7 @@
       <c r="K5" s="4" t="n"/>
       <c r="L5" s="4" t="n"/>
       <c r="M5" s="4" t="n"/>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N5" s="4" t="n"/>
       <c r="O5" s="4" t="n"/>
       <c r="P5" s="4" t="n"/>
       <c r="Q5" s="4" t="inlineStr">
@@ -47569,7 +47599,11 @@
       </c>
       <c r="R5" s="4" t="n"/>
       <c r="S5" s="4" t="n"/>
-      <c r="T5" s="4" t="n"/>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U5" s="4" t="n"/>
       <c r="V5" s="4" t="n"/>
       <c r="W5" s="4" t="n"/>
@@ -47654,14 +47688,14 @@
       <c r="K6" s="4" t="n"/>
       <c r="L6" s="4" t="n"/>
       <c r="M6" s="4" t="n"/>
-      <c r="N6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N6" s="4" t="n"/>
       <c r="O6" s="4" t="n"/>
       <c r="P6" s="4" t="n"/>
-      <c r="Q6" s="4" t="n"/>
+      <c r="Q6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="R6" s="4" t="n"/>
       <c r="S6" s="4" t="n"/>
       <c r="T6" s="4" t="n"/>
@@ -47753,14 +47787,14 @@
       </c>
       <c r="L7" s="4" t="n"/>
       <c r="M7" s="4" t="n"/>
-      <c r="N7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N7" s="4" t="n"/>
       <c r="O7" s="4" t="n"/>
       <c r="P7" s="4" t="n"/>
-      <c r="Q7" s="4" t="n"/>
+      <c r="Q7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="R7" s="4" t="n"/>
       <c r="S7" s="4" t="n"/>
       <c r="T7" s="4" t="n"/>
@@ -47880,21 +47914,21 @@
         </is>
       </c>
       <c r="M8" s="4" t="n"/>
-      <c r="N8" s="4" t="n"/>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O8" s="4" t="n"/>
       <c r="P8" s="4" t="n"/>
-      <c r="Q8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q8" s="4" t="n"/>
+      <c r="R8" s="4" t="n"/>
       <c r="S8" s="4" t="n"/>
-      <c r="T8" s="4" t="n"/>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U8" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -47979,19 +48013,19 @@
       <c r="K9" s="4" t="n"/>
       <c r="L9" s="4" t="n"/>
       <c r="M9" s="4" t="n"/>
-      <c r="N9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N9" s="4" t="n"/>
+      <c r="O9" s="4" t="n"/>
       <c r="P9" s="4" t="n"/>
-      <c r="Q9" s="4" t="n"/>
-      <c r="R9" s="4" t="n"/>
+      <c r="Q9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="S9" s="4" t="n"/>
       <c r="T9" s="4" t="n"/>
       <c r="U9" s="4" t="n"/>
@@ -48094,11 +48128,7 @@
       <c r="K10" s="4" t="n"/>
       <c r="L10" s="4" t="n"/>
       <c r="M10" s="4" t="n"/>
-      <c r="N10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N10" s="4" t="n"/>
       <c r="O10" s="4" t="n"/>
       <c r="P10" s="4" t="n"/>
       <c r="Q10" s="4" t="inlineStr">
@@ -48108,7 +48138,11 @@
       </c>
       <c r="R10" s="4" t="n"/>
       <c r="S10" s="4" t="n"/>
-      <c r="T10" s="4" t="n"/>
+      <c r="T10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U10" s="4" t="n"/>
       <c r="V10" s="4" t="n"/>
       <c r="W10" s="4" t="n"/>
@@ -48300,25 +48334,25 @@
       <c r="K12" s="4" t="n"/>
       <c r="L12" s="4" t="n"/>
       <c r="M12" s="4" t="n"/>
-      <c r="N12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N12" s="4" t="n"/>
+      <c r="O12" s="4" t="n"/>
       <c r="P12" s="4" t="n"/>
       <c r="Q12" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R12" s="4" t="n"/>
+      <c r="R12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="S12" s="4" t="n"/>
-      <c r="T12" s="4" t="n"/>
+      <c r="T12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U12" s="4" t="n"/>
       <c r="V12" s="4" t="n"/>
       <c r="W12" s="4" t="n"/>
@@ -48426,14 +48460,14 @@
       <c r="N13" s="4" t="n"/>
       <c r="O13" s="4" t="n"/>
       <c r="P13" s="4" t="n"/>
-      <c r="Q13" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q13" s="4" t="n"/>
       <c r="R13" s="4" t="n"/>
       <c r="S13" s="4" t="n"/>
-      <c r="T13" s="4" t="n"/>
+      <c r="T13" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U13" s="4" t="n"/>
       <c r="V13" s="4" t="n"/>
       <c r="W13" s="4" t="n"/>
@@ -48537,12 +48571,12 @@
       </c>
       <c r="O14" s="4" t="n"/>
       <c r="P14" s="4" t="n"/>
-      <c r="Q14" s="4" t="n"/>
-      <c r="R14" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q14" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R14" s="4" t="n"/>
       <c r="S14" s="4" t="n"/>
       <c r="T14" s="4" t="n"/>
       <c r="U14" s="4" t="n"/>
@@ -48641,11 +48675,7 @@
       </c>
       <c r="L15" s="4" t="n"/>
       <c r="M15" s="4" t="n"/>
-      <c r="N15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N15" s="4" t="n"/>
       <c r="O15" s="4" t="n"/>
       <c r="P15" s="4" t="n"/>
       <c r="Q15" s="4" t="inlineStr">
@@ -48655,7 +48685,11 @@
       </c>
       <c r="R15" s="4" t="n"/>
       <c r="S15" s="4" t="n"/>
-      <c r="T15" s="4" t="n"/>
+      <c r="T15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U15" s="4" t="n"/>
       <c r="V15" s="4" t="n"/>
       <c r="W15" s="4" t="n"/>
@@ -48870,12 +48904,12 @@
       </c>
       <c r="O17" s="4" t="n"/>
       <c r="P17" s="4" t="n"/>
-      <c r="Q17" s="4" t="n"/>
-      <c r="R17" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q17" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R17" s="4" t="n"/>
       <c r="S17" s="4" t="n"/>
       <c r="T17" s="4" t="n"/>
       <c r="U17" s="4" t="n"/>
@@ -48967,20 +49001,20 @@
       <c r="L18" s="4" t="n"/>
       <c r="M18" s="4" t="n"/>
       <c r="N18" s="4" t="n"/>
-      <c r="O18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O18" s="4" t="n"/>
       <c r="P18" s="4" t="n"/>
-      <c r="Q18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R18" s="4" t="n"/>
+      <c r="Q18" s="4" t="n"/>
+      <c r="R18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="S18" s="4" t="n"/>
-      <c r="T18" s="4" t="n"/>
+      <c r="T18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U18" s="4" t="n"/>
       <c r="V18" s="4" t="n"/>
       <c r="W18" s="4" t="n"/>
@@ -49093,11 +49127,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N19" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N19" s="4" t="n"/>
       <c r="O19" s="4" t="n"/>
       <c r="P19" s="4" t="n"/>
       <c r="Q19" s="4" t="inlineStr">
@@ -49107,7 +49137,11 @@
       </c>
       <c r="R19" s="4" t="n"/>
       <c r="S19" s="4" t="n"/>
-      <c r="T19" s="4" t="n"/>
+      <c r="T19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U19" s="4" t="n"/>
       <c r="V19" s="4" t="n"/>
       <c r="W19" s="4" t="n"/>
@@ -49196,14 +49230,14 @@
         </is>
       </c>
       <c r="M20" s="4" t="n"/>
-      <c r="N20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N20" s="4" t="n"/>
       <c r="O20" s="4" t="n"/>
       <c r="P20" s="4" t="n"/>
-      <c r="Q20" s="4" t="n"/>
+      <c r="Q20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="R20" s="4" t="n"/>
       <c r="S20" s="4" t="n"/>
       <c r="T20" s="4" t="n"/>
@@ -49302,14 +49336,14 @@
       <c r="N21" s="4" t="n"/>
       <c r="O21" s="4" t="n"/>
       <c r="P21" s="4" t="n"/>
-      <c r="Q21" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q21" s="4" t="n"/>
       <c r="R21" s="4" t="n"/>
       <c r="S21" s="4" t="n"/>
-      <c r="T21" s="4" t="n"/>
+      <c r="T21" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U21" s="4" t="n"/>
       <c r="V21" s="4" t="inlineStr">
         <is>
@@ -49504,14 +49538,14 @@
       <c r="N23" s="4" t="n"/>
       <c r="O23" s="4" t="n"/>
       <c r="P23" s="4" t="n"/>
-      <c r="Q23" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q23" s="4" t="n"/>
       <c r="R23" s="4" t="n"/>
       <c r="S23" s="4" t="n"/>
-      <c r="T23" s="4" t="n"/>
+      <c r="T23" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U23" s="4" t="n"/>
       <c r="V23" s="4" t="inlineStr">
         <is>
@@ -49592,25 +49626,25 @@
       <c r="K24" s="4" t="n"/>
       <c r="L24" s="4" t="n"/>
       <c r="M24" s="4" t="n"/>
-      <c r="N24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N24" s="4" t="n"/>
+      <c r="O24" s="4" t="n"/>
       <c r="P24" s="4" t="n"/>
       <c r="Q24" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R24" s="4" t="n"/>
+      <c r="R24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="S24" s="4" t="n"/>
-      <c r="T24" s="4" t="n"/>
+      <c r="T24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U24" s="4" t="n"/>
       <c r="V24" s="4" t="n"/>
       <c r="W24" s="4" t="n"/>
@@ -49702,14 +49736,14 @@
       <c r="N25" s="4" t="n"/>
       <c r="O25" s="4" t="n"/>
       <c r="P25" s="4" t="n"/>
-      <c r="Q25" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q25" s="4" t="n"/>
       <c r="R25" s="4" t="n"/>
       <c r="S25" s="4" t="n"/>
-      <c r="T25" s="4" t="n"/>
+      <c r="T25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U25" s="4" t="n"/>
       <c r="V25" s="4" t="n"/>
       <c r="W25" s="4" t="n"/>
@@ -49802,11 +49836,7 @@
       <c r="K26" s="4" t="n"/>
       <c r="L26" s="4" t="n"/>
       <c r="M26" s="4" t="n"/>
-      <c r="N26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N26" s="4" t="n"/>
       <c r="O26" s="4" t="n"/>
       <c r="P26" s="4" t="n"/>
       <c r="Q26" s="4" t="inlineStr">
@@ -49816,7 +49846,11 @@
       </c>
       <c r="R26" s="4" t="n"/>
       <c r="S26" s="4" t="n"/>
-      <c r="T26" s="4" t="n"/>
+      <c r="T26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U26" s="4" t="n"/>
       <c r="V26" s="4" t="n"/>
       <c r="W26" s="4" t="n"/>
@@ -49921,14 +49955,14 @@
       <c r="K27" s="4" t="n"/>
       <c r="L27" s="4" t="n"/>
       <c r="M27" s="4" t="n"/>
-      <c r="N27" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N27" s="4" t="n"/>
       <c r="O27" s="4" t="n"/>
       <c r="P27" s="4" t="n"/>
-      <c r="Q27" s="4" t="n"/>
+      <c r="Q27" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="R27" s="4" t="n"/>
       <c r="S27" s="4" t="n"/>
       <c r="T27" s="4" t="n"/>
@@ -50027,14 +50061,14 @@
       <c r="N28" s="4" t="n"/>
       <c r="O28" s="4" t="n"/>
       <c r="P28" s="4" t="n"/>
-      <c r="Q28" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q28" s="4" t="n"/>
       <c r="R28" s="4" t="n"/>
       <c r="S28" s="4" t="n"/>
-      <c r="T28" s="4" t="n"/>
+      <c r="T28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U28" s="4" t="n"/>
       <c r="V28" s="4" t="n"/>
       <c r="W28" s="4" t="n"/>
@@ -50222,14 +50256,14 @@
       <c r="K30" s="4" t="n"/>
       <c r="L30" s="4" t="n"/>
       <c r="M30" s="4" t="n"/>
-      <c r="N30" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N30" s="4" t="n"/>
       <c r="O30" s="4" t="n"/>
       <c r="P30" s="4" t="n"/>
-      <c r="Q30" s="4" t="n"/>
+      <c r="Q30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="R30" s="4" t="n"/>
       <c r="S30" s="4" t="n"/>
       <c r="T30" s="4" t="n"/>
@@ -50321,14 +50355,14 @@
       <c r="K31" s="4" t="n"/>
       <c r="L31" s="4" t="n"/>
       <c r="M31" s="4" t="n"/>
-      <c r="N31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N31" s="4" t="n"/>
       <c r="O31" s="4" t="n"/>
       <c r="P31" s="4" t="n"/>
-      <c r="Q31" s="4" t="n"/>
+      <c r="Q31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="R31" s="4" t="n"/>
       <c r="S31" s="4" t="n"/>
       <c r="T31" s="4" t="n"/>
@@ -50436,14 +50470,14 @@
       <c r="K32" s="4" t="n"/>
       <c r="L32" s="4" t="n"/>
       <c r="M32" s="4" t="n"/>
-      <c r="N32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N32" s="4" t="n"/>
       <c r="O32" s="4" t="n"/>
       <c r="P32" s="4" t="n"/>
-      <c r="Q32" s="4" t="n"/>
+      <c r="Q32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="R32" s="4" t="n"/>
       <c r="S32" s="4" t="n"/>
       <c r="T32" s="4" t="n"/>
@@ -50543,14 +50577,14 @@
       <c r="K33" s="4" t="n"/>
       <c r="L33" s="4" t="n"/>
       <c r="M33" s="4" t="n"/>
-      <c r="N33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N33" s="4" t="n"/>
       <c r="O33" s="4" t="n"/>
       <c r="P33" s="4" t="n"/>
-      <c r="Q33" s="4" t="n"/>
+      <c r="Q33" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="R33" s="4" t="n"/>
       <c r="S33" s="4" t="n"/>
       <c r="T33" s="4" t="n"/>
@@ -50652,19 +50686,19 @@
       <c r="M34" s="4" t="n"/>
       <c r="N34" s="4" t="n"/>
       <c r="O34" s="4" t="n"/>
-      <c r="P34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="P34" s="4" t="n"/>
+      <c r="Q34" s="4" t="n"/>
       <c r="R34" s="4" t="n"/>
-      <c r="S34" s="4" t="n"/>
-      <c r="T34" s="4" t="n"/>
+      <c r="S34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U34" s="4" t="n"/>
       <c r="V34" s="4" t="n"/>
       <c r="W34" s="4" t="n"/>
@@ -50749,14 +50783,14 @@
       <c r="K35" s="4" t="n"/>
       <c r="L35" s="4" t="n"/>
       <c r="M35" s="4" t="n"/>
-      <c r="N35" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N35" s="4" t="n"/>
       <c r="O35" s="4" t="n"/>
       <c r="P35" s="4" t="n"/>
-      <c r="Q35" s="4" t="n"/>
+      <c r="Q35" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="R35" s="4" t="n"/>
       <c r="S35" s="4" t="n"/>
       <c r="T35" s="4" t="n"/>
@@ -50860,11 +50894,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N36" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N36" s="4" t="n"/>
       <c r="O36" s="4" t="n"/>
       <c r="P36" s="4" t="n"/>
       <c r="Q36" s="4" t="inlineStr">
@@ -50874,7 +50904,11 @@
       </c>
       <c r="R36" s="4" t="n"/>
       <c r="S36" s="4" t="n"/>
-      <c r="T36" s="4" t="n"/>
+      <c r="T36" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U36" s="4" t="n"/>
       <c r="V36" s="4" t="n"/>
       <c r="W36" s="4" t="n"/>
@@ -50975,14 +51009,14 @@
         </is>
       </c>
       <c r="M37" s="4" t="n"/>
-      <c r="N37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N37" s="4" t="n"/>
       <c r="O37" s="4" t="n"/>
       <c r="P37" s="4" t="n"/>
-      <c r="Q37" s="4" t="n"/>
+      <c r="Q37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="R37" s="4" t="n"/>
       <c r="S37" s="4" t="n"/>
       <c r="T37" s="4" t="n"/>
@@ -51070,11 +51104,7 @@
       <c r="K38" s="4" t="n"/>
       <c r="L38" s="4" t="n"/>
       <c r="M38" s="4" t="n"/>
-      <c r="N38" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N38" s="4" t="n"/>
       <c r="O38" s="4" t="n"/>
       <c r="P38" s="4" t="n"/>
       <c r="Q38" s="4" t="inlineStr">
@@ -51084,7 +51114,11 @@
       </c>
       <c r="R38" s="4" t="n"/>
       <c r="S38" s="4" t="n"/>
-      <c r="T38" s="4" t="n"/>
+      <c r="T38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U38" s="4" t="n"/>
       <c r="V38" s="4" t="n"/>
       <c r="W38" s="4" t="n"/>
@@ -51184,14 +51218,14 @@
       <c r="N39" s="4" t="n"/>
       <c r="O39" s="4" t="n"/>
       <c r="P39" s="4" t="n"/>
-      <c r="Q39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q39" s="4" t="n"/>
       <c r="R39" s="4" t="n"/>
       <c r="S39" s="4" t="n"/>
-      <c r="T39" s="4" t="n"/>
+      <c r="T39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U39" s="4" t="n"/>
       <c r="V39" s="4" t="n"/>
       <c r="W39" s="4" t="n"/>
@@ -51316,14 +51350,14 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N40" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N40" s="4" t="n"/>
       <c r="O40" s="4" t="n"/>
       <c r="P40" s="4" t="n"/>
-      <c r="Q40" s="4" t="n"/>
+      <c r="Q40" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="R40" s="4" t="n"/>
       <c r="S40" s="4" t="n"/>
       <c r="T40" s="4" t="n"/>
@@ -51510,14 +51544,14 @@
       <c r="K42" s="4" t="n"/>
       <c r="L42" s="4" t="n"/>
       <c r="M42" s="4" t="n"/>
-      <c r="N42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N42" s="4" t="n"/>
       <c r="O42" s="4" t="n"/>
       <c r="P42" s="4" t="n"/>
-      <c r="Q42" s="4" t="n"/>
+      <c r="Q42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="R42" s="4" t="n"/>
       <c r="S42" s="4" t="n"/>
       <c r="T42" s="4" t="n"/>
@@ -51704,14 +51738,14 @@
       <c r="K44" s="4" t="n"/>
       <c r="L44" s="4" t="n"/>
       <c r="M44" s="4" t="n"/>
-      <c r="N44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N44" s="4" t="n"/>
       <c r="O44" s="4" t="n"/>
       <c r="P44" s="4" t="n"/>
-      <c r="Q44" s="4" t="n"/>
+      <c r="Q44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="R44" s="4" t="n"/>
       <c r="S44" s="4" t="n"/>
       <c r="T44" s="4" t="n"/>
@@ -51826,12 +51860,12 @@
       </c>
       <c r="O45" s="4" t="n"/>
       <c r="P45" s="4" t="n"/>
-      <c r="Q45" s="4" t="n"/>
-      <c r="R45" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q45" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R45" s="4" t="n"/>
       <c r="S45" s="4" t="n"/>
       <c r="T45" s="4" t="n"/>
       <c r="U45" s="4" t="n"/>
@@ -51938,14 +51972,14 @@
         </is>
       </c>
       <c r="M46" s="4" t="n"/>
-      <c r="N46" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N46" s="4" t="n"/>
       <c r="O46" s="4" t="n"/>
       <c r="P46" s="4" t="n"/>
-      <c r="Q46" s="4" t="n"/>
+      <c r="Q46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="R46" s="4" t="n"/>
       <c r="S46" s="4" t="n"/>
       <c r="T46" s="4" t="n"/>
@@ -52046,24 +52080,24 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="O47" s="4" t="n"/>
-      <c r="P47" s="4" t="n"/>
-      <c r="Q47" s="4" t="n"/>
-      <c r="R47" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S47" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T47" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O47" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P47" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q47" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R47" s="4" t="n"/>
+      <c r="S47" s="4" t="n"/>
+      <c r="T47" s="4" t="n"/>
       <c r="U47" s="4" t="n"/>
       <c r="V47" s="4" t="n"/>
       <c r="W47" s="4" t="n"/>
@@ -52160,25 +52194,25 @@
       <c r="K48" s="4" t="n"/>
       <c r="L48" s="4" t="n"/>
       <c r="M48" s="4" t="n"/>
-      <c r="N48" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N48" s="4" t="n"/>
       <c r="O48" s="4" t="n"/>
-      <c r="P48" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="P48" s="4" t="n"/>
       <c r="Q48" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
       <c r="R48" s="4" t="n"/>
-      <c r="S48" s="4" t="n"/>
-      <c r="T48" s="4" t="n"/>
+      <c r="S48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U48" s="4" t="n"/>
       <c r="V48" s="4" t="n"/>
       <c r="W48" s="4" t="n"/>
@@ -52271,14 +52305,14 @@
       </c>
       <c r="L49" s="4" t="n"/>
       <c r="M49" s="4" t="n"/>
-      <c r="N49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N49" s="4" t="n"/>
       <c r="O49" s="4" t="n"/>
       <c r="P49" s="4" t="n"/>
-      <c r="Q49" s="4" t="n"/>
+      <c r="Q49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="R49" s="4" t="n"/>
       <c r="S49" s="4" t="n"/>
       <c r="T49" s="4" t="n"/>
@@ -52366,14 +52400,14 @@
       <c r="K50" s="4" t="n"/>
       <c r="L50" s="4" t="n"/>
       <c r="M50" s="4" t="n"/>
-      <c r="N50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N50" s="4" t="n"/>
       <c r="O50" s="4" t="n"/>
       <c r="P50" s="4" t="n"/>
-      <c r="Q50" s="4" t="n"/>
+      <c r="Q50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="R50" s="4" t="n"/>
       <c r="S50" s="4" t="n"/>
       <c r="T50" s="4" t="n"/>
@@ -52465,14 +52499,14 @@
       <c r="K51" s="4" t="n"/>
       <c r="L51" s="4" t="n"/>
       <c r="M51" s="4" t="n"/>
-      <c r="N51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N51" s="4" t="n"/>
       <c r="O51" s="4" t="n"/>
       <c r="P51" s="4" t="n"/>
-      <c r="Q51" s="4" t="n"/>
+      <c r="Q51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="R51" s="4" t="n"/>
       <c r="S51" s="4" t="n"/>
       <c r="T51" s="4" t="n"/>
@@ -52576,25 +52610,25 @@
       <c r="K52" s="4" t="n"/>
       <c r="L52" s="4" t="n"/>
       <c r="M52" s="4" t="n"/>
-      <c r="N52" s="4" t="n"/>
-      <c r="O52" s="4" t="n"/>
-      <c r="P52" s="4" t="n"/>
+      <c r="N52" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O52" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P52" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="Q52" s="4" t="n"/>
-      <c r="R52" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S52" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T52" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="R52" s="4" t="n"/>
+      <c r="S52" s="4" t="n"/>
+      <c r="T52" s="4" t="n"/>
       <c r="U52" s="4" t="n"/>
       <c r="V52" s="4" t="n"/>
       <c r="W52" s="4" t="n"/>
@@ -52686,14 +52720,14 @@
       <c r="N53" s="4" t="n"/>
       <c r="O53" s="4" t="n"/>
       <c r="P53" s="4" t="n"/>
-      <c r="Q53" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q53" s="4" t="n"/>
       <c r="R53" s="4" t="n"/>
       <c r="S53" s="4" t="n"/>
-      <c r="T53" s="4" t="n"/>
+      <c r="T53" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U53" s="4" t="n"/>
       <c r="V53" s="4" t="inlineStr">
         <is>
@@ -52881,14 +52915,14 @@
       <c r="K55" s="4" t="n"/>
       <c r="L55" s="4" t="n"/>
       <c r="M55" s="4" t="n"/>
-      <c r="N55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N55" s="4" t="n"/>
       <c r="O55" s="4" t="n"/>
       <c r="P55" s="4" t="n"/>
-      <c r="Q55" s="4" t="n"/>
+      <c r="Q55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="R55" s="4" t="n"/>
       <c r="S55" s="4" t="n"/>
       <c r="T55" s="4" t="n"/>
@@ -52988,14 +53022,14 @@
       <c r="K56" s="4" t="n"/>
       <c r="L56" s="4" t="n"/>
       <c r="M56" s="4" t="n"/>
-      <c r="N56" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N56" s="4" t="n"/>
       <c r="O56" s="4" t="n"/>
       <c r="P56" s="4" t="n"/>
-      <c r="Q56" s="4" t="n"/>
+      <c r="Q56" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="R56" s="4" t="n"/>
       <c r="S56" s="4" t="n"/>
       <c r="T56" s="4" t="n"/>
@@ -53091,19 +53125,19 @@
         </is>
       </c>
       <c r="M57" s="4" t="n"/>
-      <c r="N57" s="4" t="n"/>
+      <c r="N57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O57" s="4" t="n"/>
-      <c r="P57" s="4" t="n"/>
-      <c r="Q57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="P57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q57" s="4" t="n"/>
+      <c r="R57" s="4" t="n"/>
       <c r="S57" s="4" t="n"/>
       <c r="T57" s="4" t="inlineStr">
         <is>
@@ -53293,14 +53327,14 @@
       <c r="K59" s="4" t="n"/>
       <c r="L59" s="4" t="n"/>
       <c r="M59" s="4" t="n"/>
-      <c r="N59" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N59" s="4" t="n"/>
       <c r="O59" s="4" t="n"/>
       <c r="P59" s="4" t="n"/>
-      <c r="Q59" s="4" t="n"/>
+      <c r="Q59" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="R59" s="4" t="n"/>
       <c r="S59" s="4" t="n"/>
       <c r="T59" s="4" t="n"/>
@@ -53503,14 +53537,14 @@
       <c r="K61" s="4" t="n"/>
       <c r="L61" s="4" t="n"/>
       <c r="M61" s="4" t="n"/>
-      <c r="N61" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N61" s="4" t="n"/>
       <c r="O61" s="4" t="n"/>
       <c r="P61" s="4" t="n"/>
-      <c r="Q61" s="4" t="n"/>
+      <c r="Q61" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="R61" s="4" t="n"/>
       <c r="S61" s="4" t="n"/>
       <c r="T61" s="4" t="n"/>
@@ -53626,11 +53660,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N62" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N62" s="4" t="n"/>
       <c r="O62" s="4" t="n"/>
       <c r="P62" s="4" t="n"/>
       <c r="Q62" s="4" t="inlineStr">
@@ -53640,7 +53670,11 @@
       </c>
       <c r="R62" s="4" t="n"/>
       <c r="S62" s="4" t="n"/>
-      <c r="T62" s="4" t="n"/>
+      <c r="T62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U62" s="4" t="n"/>
       <c r="V62" s="4" t="n"/>
       <c r="W62" s="4" t="n"/>
@@ -53743,19 +53777,19 @@
         </is>
       </c>
       <c r="O63" s="4" t="n"/>
-      <c r="P63" s="4" t="n"/>
-      <c r="Q63" s="4" t="n"/>
-      <c r="R63" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="P63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R63" s="4" t="n"/>
       <c r="S63" s="4" t="n"/>
-      <c r="T63" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T63" s="4" t="n"/>
       <c r="U63" s="4" t="n"/>
       <c r="V63" s="4" t="inlineStr">
         <is>
@@ -53860,11 +53894,7 @@
         </is>
       </c>
       <c r="M64" s="4" t="n"/>
-      <c r="N64" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N64" s="4" t="n"/>
       <c r="O64" s="4" t="n"/>
       <c r="P64" s="4" t="n"/>
       <c r="Q64" s="4" t="inlineStr">
@@ -53874,7 +53904,11 @@
       </c>
       <c r="R64" s="4" t="n"/>
       <c r="S64" s="4" t="n"/>
-      <c r="T64" s="4" t="n"/>
+      <c r="T64" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U64" s="4" t="n"/>
       <c r="V64" s="4" t="n"/>
       <c r="W64" s="4" t="n"/>
@@ -53962,14 +53996,14 @@
       <c r="N65" s="4" t="n"/>
       <c r="O65" s="4" t="n"/>
       <c r="P65" s="4" t="n"/>
-      <c r="Q65" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q65" s="4" t="n"/>
       <c r="R65" s="4" t="n"/>
       <c r="S65" s="4" t="n"/>
-      <c r="T65" s="4" t="n"/>
+      <c r="T65" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U65" s="4" t="n"/>
       <c r="V65" s="4" t="inlineStr">
         <is>
@@ -54149,11 +54183,7 @@
       <c r="K67" s="4" t="n"/>
       <c r="L67" s="4" t="n"/>
       <c r="M67" s="4" t="n"/>
-      <c r="N67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N67" s="4" t="n"/>
       <c r="O67" s="4" t="n"/>
       <c r="P67" s="4" t="n"/>
       <c r="Q67" s="4" t="inlineStr">
@@ -54163,7 +54193,11 @@
       </c>
       <c r="R67" s="4" t="n"/>
       <c r="S67" s="4" t="n"/>
-      <c r="T67" s="4" t="n"/>
+      <c r="T67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U67" s="4" t="n"/>
       <c r="V67" s="4" t="n"/>
       <c r="W67" s="4" t="n"/>
@@ -54279,14 +54313,14 @@
       <c r="N68" s="4" t="n"/>
       <c r="O68" s="4" t="n"/>
       <c r="P68" s="4" t="n"/>
-      <c r="Q68" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q68" s="4" t="n"/>
       <c r="R68" s="4" t="n"/>
       <c r="S68" s="4" t="n"/>
-      <c r="T68" s="4" t="n"/>
+      <c r="T68" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U68" s="4" t="n"/>
       <c r="V68" s="4" t="n"/>
       <c r="W68" s="4" t="n"/>
@@ -54375,14 +54409,14 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N69" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N69" s="4" t="n"/>
       <c r="O69" s="4" t="n"/>
       <c r="P69" s="4" t="n"/>
-      <c r="Q69" s="4" t="n"/>
+      <c r="Q69" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="R69" s="4" t="n"/>
       <c r="S69" s="4" t="n"/>
       <c r="T69" s="4" t="n"/>
@@ -54462,14 +54496,14 @@
       <c r="K70" s="4" t="n"/>
       <c r="L70" s="4" t="n"/>
       <c r="M70" s="4" t="n"/>
-      <c r="N70" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N70" s="4" t="n"/>
       <c r="O70" s="4" t="n"/>
       <c r="P70" s="4" t="n"/>
-      <c r="Q70" s="4" t="n"/>
+      <c r="Q70" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="R70" s="4" t="n"/>
       <c r="S70" s="4" t="n"/>
       <c r="T70" s="4" t="n"/>
@@ -54652,11 +54686,7 @@
       <c r="K72" s="4" t="n"/>
       <c r="L72" s="4" t="n"/>
       <c r="M72" s="4" t="n"/>
-      <c r="N72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N72" s="4" t="n"/>
       <c r="O72" s="4" t="n"/>
       <c r="P72" s="4" t="n"/>
       <c r="Q72" s="4" t="inlineStr">
@@ -54666,7 +54696,11 @@
       </c>
       <c r="R72" s="4" t="n"/>
       <c r="S72" s="4" t="n"/>
-      <c r="T72" s="4" t="n"/>
+      <c r="T72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U72" s="4" t="n"/>
       <c r="V72" s="4" t="n"/>
       <c r="W72" s="4" t="n"/>
@@ -54755,14 +54789,14 @@
       <c r="K73" s="4" t="n"/>
       <c r="L73" s="4" t="n"/>
       <c r="M73" s="4" t="n"/>
-      <c r="N73" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N73" s="4" t="n"/>
       <c r="O73" s="4" t="n"/>
       <c r="P73" s="4" t="n"/>
-      <c r="Q73" s="4" t="n"/>
+      <c r="Q73" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="R73" s="4" t="n"/>
       <c r="S73" s="4" t="n"/>
       <c r="T73" s="4" t="n"/>
@@ -54870,11 +54904,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N74" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N74" s="4" t="n"/>
       <c r="O74" s="4" t="n"/>
       <c r="P74" s="4" t="n"/>
       <c r="Q74" s="4" t="inlineStr">
@@ -54884,7 +54914,11 @@
       </c>
       <c r="R74" s="4" t="n"/>
       <c r="S74" s="4" t="n"/>
-      <c r="T74" s="4" t="n"/>
+      <c r="T74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U74" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -54972,14 +55006,14 @@
       <c r="N75" s="4" t="n"/>
       <c r="O75" s="4" t="n"/>
       <c r="P75" s="4" t="n"/>
-      <c r="Q75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q75" s="4" t="n"/>
       <c r="R75" s="4" t="n"/>
       <c r="S75" s="4" t="n"/>
-      <c r="T75" s="4" t="n"/>
+      <c r="T75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U75" s="4" t="n"/>
       <c r="V75" s="4" t="n"/>
       <c r="W75" s="4" t="n"/>
@@ -55076,14 +55110,14 @@
       <c r="K76" s="4" t="n"/>
       <c r="L76" s="4" t="n"/>
       <c r="M76" s="4" t="n"/>
-      <c r="N76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N76" s="4" t="n"/>
       <c r="O76" s="4" t="n"/>
       <c r="P76" s="4" t="n"/>
-      <c r="Q76" s="4" t="n"/>
+      <c r="Q76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="R76" s="4" t="n"/>
       <c r="S76" s="4" t="n"/>
       <c r="T76" s="4" t="n"/>
@@ -55295,15 +55329,15 @@
         </is>
       </c>
       <c r="N78" s="4" t="n"/>
-      <c r="O78" s="4" t="n"/>
+      <c r="O78" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P78" s="4" t="n"/>
       <c r="Q78" s="4" t="n"/>
       <c r="R78" s="4" t="n"/>
-      <c r="S78" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="S78" s="4" t="n"/>
       <c r="T78" s="4" t="n"/>
       <c r="U78" s="4" t="n"/>
       <c r="V78" s="4" t="n"/>
@@ -55398,15 +55432,15 @@
         </is>
       </c>
       <c r="N79" s="4" t="n"/>
-      <c r="O79" s="4" t="n"/>
+      <c r="O79" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P79" s="4" t="n"/>
       <c r="Q79" s="4" t="n"/>
       <c r="R79" s="4" t="n"/>
-      <c r="S79" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="S79" s="4" t="n"/>
       <c r="T79" s="4" t="n"/>
       <c r="U79" s="4" t="n"/>
       <c r="V79" s="4" t="n"/>
@@ -55502,15 +55536,15 @@
       <c r="M80" s="4" t="n"/>
       <c r="N80" s="4" t="n"/>
       <c r="O80" s="4" t="n"/>
-      <c r="P80" s="4" t="n"/>
+      <c r="P80" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="Q80" s="4" t="n"/>
       <c r="R80" s="4" t="n"/>
       <c r="S80" s="4" t="n"/>
-      <c r="T80" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T80" s="4" t="n"/>
       <c r="U80" s="4" t="n"/>
       <c r="V80" s="4" t="n"/>
       <c r="W80" s="4" t="n"/>
@@ -55604,15 +55638,15 @@
         </is>
       </c>
       <c r="N81" s="4" t="n"/>
-      <c r="O81" s="4" t="n"/>
+      <c r="O81" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P81" s="4" t="n"/>
       <c r="Q81" s="4" t="n"/>
       <c r="R81" s="4" t="n"/>
-      <c r="S81" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="S81" s="4" t="n"/>
       <c r="T81" s="4" t="n"/>
       <c r="U81" s="4" t="n"/>
       <c r="V81" s="4" t="n"/>
@@ -55859,14 +55893,14 @@
       <c r="N84" s="4" t="n"/>
       <c r="O84" s="4" t="n"/>
       <c r="P84" s="4" t="n"/>
-      <c r="Q84" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q84" s="4" t="n"/>
       <c r="R84" s="4" t="n"/>
       <c r="S84" s="4" t="n"/>
-      <c r="T84" s="4" t="n"/>
+      <c r="T84" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U84" s="4" t="n"/>
       <c r="V84" s="4" t="n"/>
       <c r="W84" s="4" t="n"/>
@@ -55987,17 +56021,17 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>玻璃</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>9x8</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>速尾</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>玻璃</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -56063,12 +56097,12 @@
         </is>
       </c>
       <c r="C2" s="4" t="n"/>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F2" s="4" t="n"/>
       <c r="G2" s="4" t="n"/>
       <c r="H2" s="4" t="n"/>
@@ -56105,12 +56139,12 @@
         </is>
       </c>
       <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="n"/>
       <c r="F3" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -56136,12 +56170,12 @@
       </c>
       <c r="C4" s="4" t="n"/>
       <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G4" s="4" t="n"/>
       <c r="H4" s="4" t="n"/>
       <c r="I4" s="4" t="n"/>
@@ -56161,17 +56195,17 @@
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D5" s="4" t="n"/>
       <c r="E5" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F5" s="4" t="n"/>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -56207,12 +56241,12 @@
         </is>
       </c>
       <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F6" s="4" t="n"/>
       <c r="G6" s="4" t="n"/>
       <c r="H6" s="4" t="n"/>
@@ -56250,12 +56284,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="n"/>
       <c r="G7" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -56284,12 +56318,12 @@
       </c>
       <c r="C8" s="4" t="n"/>
       <c r="D8" s="4" t="n"/>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="n"/>
+      <c r="E8" s="4" t="n"/>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G8" s="4" t="n"/>
       <c r="H8" s="4" t="n"/>
       <c r="I8" s="4" t="n"/>
@@ -56309,12 +56343,12 @@
         </is>
       </c>
       <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="n"/>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F9" s="4" t="n"/>
       <c r="G9" s="4" t="inlineStr">
         <is>
@@ -56355,12 +56389,12 @@
         </is>
       </c>
       <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F10" s="4" t="n"/>
       <c r="G10" s="4" t="inlineStr">
         <is>
@@ -56409,13 +56443,13 @@
         </is>
       </c>
       <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E11" s="4" t="n"/>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="F11" s="4" t="n"/>
       <c r="G11" s="4" t="n"/>
       <c r="H11" s="4" t="n"/>
       <c r="I11" s="4" t="n"/>
@@ -56435,17 +56469,17 @@
         </is>
       </c>
       <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D12" s="4" t="n"/>
       <c r="E12" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F12" s="4" t="n"/>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -56478,12 +56512,12 @@
       </c>
       <c r="C13" s="4" t="n"/>
       <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="n"/>
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G13" s="4" t="n"/>
       <c r="H13" s="4" t="n"/>
       <c r="I13" s="4" t="n"/>
@@ -56512,12 +56546,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E14" s="4" t="n"/>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="n"/>
       <c r="G14" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -56545,17 +56579,17 @@
         </is>
       </c>
       <c r="C15" s="4" t="n"/>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D15" s="4" t="n"/>
       <c r="E15" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F15" s="4" t="n"/>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G15" s="4" t="n"/>
       <c r="H15" s="4" t="n"/>
       <c r="I15" s="4" t="inlineStr">
@@ -56583,13 +56617,13 @@
         </is>
       </c>
       <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="F16" s="4" t="n"/>
       <c r="G16" s="4" t="n"/>
       <c r="H16" s="4" t="n"/>
       <c r="I16" s="4" t="n"/>
@@ -56614,12 +56648,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E17" s="4" t="n"/>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="n"/>
       <c r="G17" s="4" t="n"/>
       <c r="H17" s="4" t="n"/>
       <c r="I17" s="4" t="inlineStr">
@@ -56660,12 +56694,12 @@
       </c>
       <c r="C18" s="4" t="n"/>
       <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="n"/>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -56697,17 +56731,17 @@
         </is>
       </c>
       <c r="C19" s="4" t="n"/>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D19" s="4" t="n"/>
       <c r="E19" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F19" s="4" t="n"/>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G19" s="4" t="n"/>
       <c r="H19" s="4" t="n"/>
       <c r="I19" s="4" t="n"/>
@@ -56735,12 +56769,12 @@
         </is>
       </c>
       <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F20" s="4" t="n"/>
       <c r="G20" s="4" t="n"/>
       <c r="H20" s="4" t="n"/>
@@ -56778,12 +56812,12 @@
       </c>
       <c r="C21" s="4" t="n"/>
       <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="n"/>
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G21" s="4" t="n"/>
       <c r="H21" s="4" t="n"/>
       <c r="I21" s="4" t="n"/>
@@ -56833,12 +56867,12 @@
         </is>
       </c>
       <c r="C23" s="4" t="n"/>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="n"/>
       <c r="F23" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -56863,17 +56897,17 @@
         </is>
       </c>
       <c r="C24" s="4" t="n"/>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D24" s="4" t="n"/>
       <c r="E24" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F24" s="4" t="n"/>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -56906,12 +56940,12 @@
       </c>
       <c r="C25" s="4" t="n"/>
       <c r="D25" s="4" t="n"/>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="n"/>
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -56943,12 +56977,12 @@
         </is>
       </c>
       <c r="C26" s="4" t="n"/>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="n"/>
+      <c r="D26" s="4" t="n"/>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F26" s="4" t="n"/>
       <c r="G26" s="4" t="inlineStr">
         <is>
@@ -57016,12 +57050,12 @@
       </c>
       <c r="C28" s="4" t="n"/>
       <c r="D28" s="4" t="n"/>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -57053,13 +57087,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D29" s="4" t="n"/>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E29" s="4" t="n"/>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="F29" s="4" t="n"/>
       <c r="G29" s="4" t="n"/>
       <c r="H29" s="4" t="n"/>
       <c r="I29" s="4" t="n"/>
@@ -57083,12 +57117,12 @@
         </is>
       </c>
       <c r="C30" s="4" t="n"/>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="n"/>
+      <c r="D30" s="4" t="n"/>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F30" s="4" t="n"/>
       <c r="G30" s="4" t="n"/>
       <c r="H30" s="4" t="n"/>
@@ -57125,12 +57159,12 @@
         </is>
       </c>
       <c r="C31" s="4" t="n"/>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="n"/>
+      <c r="D31" s="4" t="n"/>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F31" s="4" t="n"/>
       <c r="G31" s="4" t="n"/>
       <c r="H31" s="4" t="n"/>
@@ -57163,12 +57197,12 @@
         </is>
       </c>
       <c r="C32" s="4" t="n"/>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="n"/>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F32" s="4" t="n"/>
       <c r="G32" s="4" t="n"/>
       <c r="H32" s="4" t="n"/>
@@ -57197,12 +57231,12 @@
         </is>
       </c>
       <c r="C33" s="4" t="n"/>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="n"/>
+      <c r="D33" s="4" t="n"/>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F33" s="4" t="n"/>
       <c r="G33" s="4" t="n"/>
       <c r="H33" s="4" t="n"/>
@@ -57240,12 +57274,12 @@
       </c>
       <c r="C34" s="4" t="n"/>
       <c r="D34" s="4" t="n"/>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="n"/>
+      <c r="E34" s="4" t="n"/>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G34" s="4" t="n"/>
       <c r="H34" s="4" t="n"/>
       <c r="I34" s="4" t="n"/>
@@ -57265,12 +57299,12 @@
         </is>
       </c>
       <c r="C35" s="4" t="n"/>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="n"/>
+      <c r="D35" s="4" t="n"/>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F35" s="4" t="n"/>
       <c r="G35" s="4" t="n"/>
       <c r="H35" s="4" t="n"/>
@@ -57303,17 +57337,17 @@
         </is>
       </c>
       <c r="C36" s="4" t="n"/>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D36" s="4" t="n"/>
       <c r="E36" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F36" s="4" t="n"/>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G36" s="4" t="n"/>
       <c r="H36" s="4" t="n"/>
       <c r="I36" s="4" t="n"/>
@@ -57341,12 +57375,12 @@
         </is>
       </c>
       <c r="C37" s="4" t="n"/>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="n"/>
+      <c r="D37" s="4" t="n"/>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F37" s="4" t="n"/>
       <c r="G37" s="4" t="n"/>
       <c r="H37" s="4" t="n"/>
@@ -57375,17 +57409,17 @@
         </is>
       </c>
       <c r="C38" s="4" t="n"/>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D38" s="4" t="n"/>
       <c r="E38" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F38" s="4" t="n"/>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -57418,12 +57452,12 @@
       </c>
       <c r="C39" s="4" t="n"/>
       <c r="D39" s="4" t="n"/>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="n"/>
+      <c r="E39" s="4" t="n"/>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -57459,12 +57493,12 @@
         </is>
       </c>
       <c r="C40" s="4" t="n"/>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="n"/>
+      <c r="D40" s="4" t="n"/>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F40" s="4" t="n"/>
       <c r="G40" s="4" t="n"/>
       <c r="H40" s="4" t="n"/>
@@ -57497,13 +57531,13 @@
         </is>
       </c>
       <c r="C41" s="4" t="n"/>
-      <c r="D41" s="4" t="n"/>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E41" s="4" t="n"/>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="F41" s="4" t="n"/>
       <c r="G41" s="4" t="n"/>
       <c r="H41" s="4" t="n"/>
       <c r="I41" s="4" t="n"/>
@@ -57523,12 +57557,12 @@
         </is>
       </c>
       <c r="C42" s="4" t="n"/>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="n"/>
+      <c r="D42" s="4" t="n"/>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F42" s="4" t="n"/>
       <c r="G42" s="4" t="inlineStr">
         <is>
@@ -57561,13 +57595,13 @@
         </is>
       </c>
       <c r="C43" s="4" t="n"/>
-      <c r="D43" s="4" t="n"/>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E43" s="4" t="n"/>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="F43" s="4" t="n"/>
       <c r="G43" s="4" t="n"/>
       <c r="H43" s="4" t="n"/>
       <c r="I43" s="4" t="n"/>
@@ -57591,12 +57625,12 @@
         </is>
       </c>
       <c r="C44" s="4" t="n"/>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="n"/>
+      <c r="D44" s="4" t="n"/>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F44" s="4" t="n"/>
       <c r="G44" s="4" t="n"/>
       <c r="H44" s="4" t="n"/>
@@ -57633,13 +57667,13 @@
         </is>
       </c>
       <c r="C45" s="4" t="n"/>
-      <c r="D45" s="4" t="n"/>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E45" s="4" t="n"/>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="F45" s="4" t="n"/>
       <c r="G45" s="4" t="n"/>
       <c r="H45" s="4" t="n"/>
       <c r="I45" s="4" t="n"/>
@@ -57664,12 +57698,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E46" s="4" t="n"/>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="n"/>
       <c r="G46" s="4" t="n"/>
       <c r="H46" s="4" t="n"/>
       <c r="I46" s="4" t="n"/>
@@ -57702,12 +57736,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E47" s="4" t="n"/>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="n"/>
       <c r="G47" s="4" t="n"/>
       <c r="H47" s="4" t="n"/>
       <c r="I47" s="4" t="n"/>
@@ -57736,12 +57770,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E48" s="4" t="n"/>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="n"/>
       <c r="G48" s="4" t="n"/>
       <c r="H48" s="4" t="n"/>
       <c r="I48" s="4" t="n"/>
@@ -57765,12 +57799,12 @@
         </is>
       </c>
       <c r="C49" s="4" t="n"/>
-      <c r="D49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E49" s="4" t="n"/>
+      <c r="D49" s="4" t="n"/>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F49" s="4" t="n"/>
       <c r="G49" s="4" t="n"/>
       <c r="H49" s="4" t="n"/>
@@ -57803,12 +57837,12 @@
         </is>
       </c>
       <c r="C50" s="4" t="n"/>
-      <c r="D50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="n"/>
+      <c r="D50" s="4" t="n"/>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F50" s="4" t="n"/>
       <c r="G50" s="4" t="n"/>
       <c r="H50" s="4" t="n"/>
@@ -57841,12 +57875,12 @@
         </is>
       </c>
       <c r="C51" s="4" t="n"/>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E51" s="4" t="n"/>
+      <c r="D51" s="4" t="n"/>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F51" s="4" t="n"/>
       <c r="G51" s="4" t="inlineStr">
         <is>
@@ -57883,13 +57917,13 @@
         </is>
       </c>
       <c r="C52" s="4" t="n"/>
-      <c r="D52" s="4" t="n"/>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E52" s="4" t="n"/>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="F52" s="4" t="n"/>
       <c r="G52" s="4" t="n"/>
       <c r="H52" s="4" t="n"/>
       <c r="I52" s="4" t="n"/>
@@ -57918,12 +57952,12 @@
       </c>
       <c r="C53" s="4" t="n"/>
       <c r="D53" s="4" t="n"/>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="n"/>
+      <c r="E53" s="4" t="n"/>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G53" s="4" t="n"/>
       <c r="H53" s="4" t="n"/>
       <c r="I53" s="4" t="n"/>
@@ -57965,12 +57999,12 @@
         </is>
       </c>
       <c r="C55" s="4" t="n"/>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="n"/>
+      <c r="D55" s="4" t="n"/>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F55" s="4" t="n"/>
       <c r="G55" s="4" t="n"/>
       <c r="H55" s="4" t="n"/>
@@ -58003,12 +58037,12 @@
         </is>
       </c>
       <c r="C56" s="4" t="n"/>
-      <c r="D56" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E56" s="4" t="n"/>
+      <c r="D56" s="4" t="n"/>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F56" s="4" t="n"/>
       <c r="G56" s="4" t="n"/>
       <c r="H56" s="4" t="n"/>
@@ -58033,12 +58067,12 @@
         </is>
       </c>
       <c r="C57" s="4" t="n"/>
-      <c r="D57" s="4" t="n"/>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="n"/>
       <c r="F57" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -58085,12 +58119,12 @@
         </is>
       </c>
       <c r="C59" s="4" t="n"/>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E59" s="4" t="n"/>
+      <c r="D59" s="4" t="n"/>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F59" s="4" t="n"/>
       <c r="G59" s="4" t="n"/>
       <c r="H59" s="4" t="n"/>
@@ -58127,13 +58161,13 @@
         </is>
       </c>
       <c r="C60" s="4" t="n"/>
-      <c r="D60" s="4" t="n"/>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E60" s="4" t="n"/>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="F60" s="4" t="n"/>
       <c r="G60" s="4" t="n"/>
       <c r="H60" s="4" t="n"/>
       <c r="I60" s="4" t="n"/>
@@ -58157,12 +58191,12 @@
         </is>
       </c>
       <c r="C61" s="4" t="n"/>
-      <c r="D61" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E61" s="4" t="n"/>
+      <c r="D61" s="4" t="n"/>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F61" s="4" t="n"/>
       <c r="G61" s="4" t="inlineStr">
         <is>
@@ -58207,17 +58241,17 @@
         </is>
       </c>
       <c r="C62" s="4" t="n"/>
-      <c r="D62" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D62" s="4" t="n"/>
       <c r="E62" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F62" s="4" t="n"/>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G62" s="4" t="n"/>
       <c r="H62" s="4" t="n"/>
       <c r="I62" s="4" t="inlineStr">
@@ -58254,12 +58288,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E63" s="4" t="n"/>
-      <c r="F63" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="n"/>
       <c r="G63" s="4" t="n"/>
       <c r="H63" s="4" t="n"/>
       <c r="I63" s="4" t="inlineStr">
@@ -58288,12 +58322,12 @@
       </c>
       <c r="C64" s="4" t="n"/>
       <c r="D64" s="4" t="n"/>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F64" s="4" t="n"/>
+      <c r="E64" s="4" t="n"/>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G64" s="4" t="n"/>
       <c r="H64" s="4" t="n"/>
       <c r="I64" s="4" t="n"/>
@@ -58318,12 +58352,12 @@
       </c>
       <c r="C65" s="4" t="n"/>
       <c r="D65" s="4" t="n"/>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="n"/>
+      <c r="E65" s="4" t="n"/>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G65" s="4" t="n"/>
       <c r="H65" s="4" t="n"/>
       <c r="I65" s="4" t="n"/>
@@ -58365,17 +58399,17 @@
         </is>
       </c>
       <c r="C67" s="4" t="n"/>
-      <c r="D67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D67" s="4" t="n"/>
       <c r="E67" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F67" s="4" t="n"/>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -58420,12 +58454,12 @@
       </c>
       <c r="C68" s="4" t="n"/>
       <c r="D68" s="4" t="n"/>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F68" s="4" t="n"/>
+      <c r="E68" s="4" t="n"/>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G68" s="4" t="n"/>
       <c r="H68" s="4" t="n"/>
       <c r="I68" s="4" t="n"/>
@@ -58454,12 +58488,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E69" s="4" t="n"/>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="n"/>
       <c r="G69" s="4" t="n"/>
       <c r="H69" s="4" t="n"/>
       <c r="I69" s="4" t="n"/>
@@ -58483,12 +58517,12 @@
         </is>
       </c>
       <c r="C70" s="4" t="n"/>
-      <c r="D70" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E70" s="4" t="n"/>
+      <c r="D70" s="4" t="n"/>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F70" s="4" t="n"/>
       <c r="G70" s="4" t="inlineStr">
         <is>
@@ -58525,13 +58559,13 @@
         </is>
       </c>
       <c r="C71" s="4" t="n"/>
-      <c r="D71" s="4" t="n"/>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E71" s="4" t="n"/>
-      <c r="F71" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="F71" s="4" t="n"/>
       <c r="G71" s="4" t="n"/>
       <c r="H71" s="4" t="n"/>
       <c r="I71" s="4" t="n"/>
@@ -58551,17 +58585,17 @@
         </is>
       </c>
       <c r="C72" s="4" t="n"/>
-      <c r="D72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D72" s="4" t="n"/>
       <c r="E72" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F72" s="4" t="n"/>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G72" s="4" t="n"/>
       <c r="H72" s="4" t="n"/>
       <c r="I72" s="4" t="inlineStr">
@@ -58601,12 +58635,12 @@
         </is>
       </c>
       <c r="C73" s="4" t="n"/>
-      <c r="D73" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E73" s="4" t="n"/>
+      <c r="D73" s="4" t="n"/>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F73" s="4" t="n"/>
       <c r="G73" s="4" t="n"/>
       <c r="H73" s="4" t="n"/>
@@ -58639,17 +58673,17 @@
         </is>
       </c>
       <c r="C74" s="4" t="n"/>
-      <c r="D74" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D74" s="4" t="n"/>
       <c r="E74" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F74" s="4" t="n"/>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G74" s="4" t="n"/>
       <c r="H74" s="4" t="n"/>
       <c r="I74" s="4" t="inlineStr">
@@ -58674,12 +58708,12 @@
       </c>
       <c r="C75" s="4" t="n"/>
       <c r="D75" s="4" t="n"/>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="n"/>
+      <c r="E75" s="4" t="n"/>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -58715,12 +58749,12 @@
         </is>
       </c>
       <c r="C76" s="4" t="n"/>
-      <c r="D76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E76" s="4" t="n"/>
+      <c r="D76" s="4" t="n"/>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F76" s="4" t="n"/>
       <c r="G76" s="4" t="n"/>
       <c r="H76" s="4" t="n"/>
@@ -58753,13 +58787,13 @@
         </is>
       </c>
       <c r="C77" s="4" t="n"/>
-      <c r="D77" s="4" t="n"/>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E77" s="4" t="n"/>
-      <c r="F77" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="F77" s="4" t="n"/>
       <c r="G77" s="4" t="n"/>
       <c r="H77" s="4" t="n"/>
       <c r="I77" s="4" t="n"/>
@@ -58801,13 +58835,13 @@
         </is>
       </c>
       <c r="C79" s="4" t="n"/>
-      <c r="D79" s="4" t="n"/>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E79" s="4" t="n"/>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="F79" s="4" t="n"/>
       <c r="G79" s="4" t="n"/>
       <c r="H79" s="4" t="n"/>
       <c r="I79" s="4" t="n"/>
@@ -58827,13 +58861,13 @@
         </is>
       </c>
       <c r="C80" s="4" t="n"/>
-      <c r="D80" s="4" t="n"/>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E80" s="4" t="n"/>
-      <c r="F80" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="F80" s="4" t="n"/>
       <c r="G80" s="4" t="n"/>
       <c r="H80" s="4" t="n"/>
       <c r="I80" s="4" t="n"/>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -34847,14 +34847,14 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>速尾</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>9x8</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>速尾</t>
-        </is>
-      </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>ssc</t>
@@ -34872,42 +34872,42 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>狼崽</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>21c</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>万达</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>狼崽</t>
-        </is>
-      </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>fp1</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>sgt</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>火山</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>法拉第</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>秋王</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>fp1</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
@@ -35047,10 +35047,10 @@
       <c r="E2" s="4" t="n"/>
       <c r="F2" s="4" t="n"/>
       <c r="G2" s="4" t="n"/>
-      <c r="H2" s="4" t="n">
+      <c r="H2" s="4" t="n"/>
+      <c r="I2" s="4" t="n">
         <v>18.89</v>
       </c>
-      <c r="I2" s="4" t="n"/>
       <c r="J2" s="4" t="n"/>
       <c r="K2" s="4" t="n"/>
       <c r="L2" s="4" t="n"/>
@@ -35060,10 +35060,10 @@
       <c r="P2" s="4" t="n"/>
       <c r="Q2" s="4" t="n"/>
       <c r="R2" s="4" t="n"/>
-      <c r="S2" s="4" t="n">
+      <c r="S2" s="4" t="n"/>
+      <c r="T2" s="4" t="n">
         <v>19.15</v>
       </c>
-      <c r="T2" s="4" t="n"/>
       <c r="U2" s="4" t="n"/>
       <c r="V2" s="4" t="n"/>
       <c r="W2" s="4" t="n">
@@ -35118,11 +35118,11 @@
         <v>28.49</v>
       </c>
       <c r="L3" s="4" t="n"/>
-      <c r="M3" s="4" t="n"/>
+      <c r="M3" s="4" t="n">
+        <v>29.6</v>
+      </c>
       <c r="N3" s="4" t="n"/>
-      <c r="O3" s="4" t="n">
-        <v>29.6</v>
-      </c>
+      <c r="O3" s="4" t="n"/>
       <c r="P3" s="4" t="n"/>
       <c r="Q3" s="4" t="n"/>
       <c r="R3" s="4" t="n"/>
@@ -35173,20 +35173,20 @@
         <v>30.95</v>
       </c>
       <c r="G4" s="4" t="n"/>
-      <c r="H4" s="4" t="n"/>
-      <c r="I4" s="4" t="n">
+      <c r="H4" s="4" t="n">
         <v>31.69</v>
       </c>
+      <c r="I4" s="4" t="n"/>
       <c r="J4" s="4" t="n">
         <v>30.8</v>
       </c>
       <c r="K4" s="4" t="n"/>
       <c r="L4" s="4" t="n"/>
-      <c r="M4" s="4" t="n"/>
+      <c r="M4" s="4" t="n">
+        <v>32.29</v>
+      </c>
       <c r="N4" s="4" t="n"/>
-      <c r="O4" s="4" t="n">
-        <v>32.29</v>
-      </c>
+      <c r="O4" s="4" t="n"/>
       <c r="P4" s="4" t="n"/>
       <c r="Q4" s="4" t="n"/>
       <c r="R4" s="4" t="n"/>
@@ -35238,10 +35238,10 @@
         <v>17.99</v>
       </c>
       <c r="H5" s="4" t="n">
+        <v>18.03</v>
+      </c>
+      <c r="I5" s="4" t="n">
         <v>18.15</v>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>18.03</v>
       </c>
       <c r="J5" s="4" t="n"/>
       <c r="K5" s="4" t="n">
@@ -35253,13 +35253,13 @@
       <c r="M5" s="4" t="n"/>
       <c r="N5" s="4" t="n"/>
       <c r="O5" s="4" t="n"/>
-      <c r="P5" s="4" t="n">
+      <c r="P5" s="4" t="n"/>
+      <c r="Q5" s="4" t="n">
         <v>18.39</v>
       </c>
-      <c r="Q5" s="4" t="n">
+      <c r="R5" s="4" t="n">
         <v>18.46</v>
       </c>
-      <c r="R5" s="4" t="n"/>
       <c r="S5" s="4" t="n"/>
       <c r="T5" s="4" t="n"/>
       <c r="U5" s="4" t="n"/>
@@ -35309,10 +35309,10 @@
       <c r="E6" s="4" t="n"/>
       <c r="F6" s="4" t="n"/>
       <c r="G6" s="4" t="n"/>
-      <c r="H6" s="4" t="n">
+      <c r="H6" s="4" t="n"/>
+      <c r="I6" s="4" t="n">
         <v>17.95</v>
       </c>
-      <c r="I6" s="4" t="n"/>
       <c r="J6" s="4" t="n"/>
       <c r="K6" s="4" t="n"/>
       <c r="L6" s="4" t="n"/>
@@ -35322,10 +35322,10 @@
       <c r="P6" s="4" t="n"/>
       <c r="Q6" s="4" t="n"/>
       <c r="R6" s="4" t="n"/>
-      <c r="S6" s="4" t="n">
+      <c r="S6" s="4" t="n"/>
+      <c r="T6" s="4" t="n">
         <v>17.99</v>
       </c>
-      <c r="T6" s="4" t="n"/>
       <c r="U6" s="4" t="n"/>
       <c r="V6" s="4" t="n"/>
       <c r="W6" s="4" t="n"/>
@@ -35435,20 +35435,20 @@
       <c r="G8" s="4" t="n">
         <v>27.72</v>
       </c>
-      <c r="H8" s="4" t="n"/>
-      <c r="I8" s="4" t="n">
+      <c r="H8" s="4" t="n">
         <v>28.59</v>
       </c>
+      <c r="I8" s="4" t="n"/>
       <c r="J8" s="4" t="n">
         <v>28.1</v>
       </c>
       <c r="K8" s="4" t="n"/>
       <c r="L8" s="4" t="n"/>
-      <c r="M8" s="4" t="n"/>
+      <c r="M8" s="4" t="n">
+        <v>28.9</v>
+      </c>
       <c r="N8" s="4" t="n"/>
-      <c r="O8" s="4" t="n">
-        <v>28.9</v>
-      </c>
+      <c r="O8" s="4" t="n"/>
       <c r="P8" s="4" t="n"/>
       <c r="Q8" s="4" t="n"/>
       <c r="R8" s="4" t="n"/>
@@ -35508,24 +35508,24 @@
       <c r="L9" s="4" t="n">
         <v>19.55</v>
       </c>
-      <c r="M9" s="4" t="n">
+      <c r="M9" s="4" t="n"/>
+      <c r="N9" s="4" t="n">
         <v>19.47</v>
       </c>
-      <c r="N9" s="4" t="n"/>
       <c r="O9" s="4" t="n"/>
       <c r="P9" s="4" t="n">
+        <v>19.85</v>
+      </c>
+      <c r="Q9" s="4" t="n">
         <v>20.19</v>
       </c>
-      <c r="Q9" s="4" t="n">
+      <c r="R9" s="4" t="n">
         <v>20.39</v>
       </c>
-      <c r="R9" s="4" t="n">
+      <c r="S9" s="4" t="n">
         <v>19.69</v>
       </c>
-      <c r="S9" s="4" t="n"/>
-      <c r="T9" s="4" t="n">
-        <v>19.85</v>
-      </c>
+      <c r="T9" s="4" t="n"/>
       <c r="U9" s="4" t="n"/>
       <c r="V9" s="4" t="n"/>
       <c r="W9" s="4" t="n"/>
@@ -35570,25 +35570,25 @@
       <c r="F10" s="4" t="n"/>
       <c r="G10" s="4" t="n"/>
       <c r="H10" s="4" t="n">
+        <v>23.43</v>
+      </c>
+      <c r="I10" s="4" t="n">
         <v>23.42</v>
-      </c>
-      <c r="I10" s="4" t="n">
-        <v>23.43</v>
       </c>
       <c r="J10" s="4" t="n"/>
       <c r="K10" s="4" t="n"/>
       <c r="L10" s="4" t="n"/>
-      <c r="M10" s="4" t="n">
+      <c r="M10" s="4" t="n"/>
+      <c r="N10" s="4" t="n">
         <v>23.11</v>
       </c>
-      <c r="N10" s="4" t="n"/>
       <c r="O10" s="4" t="n"/>
       <c r="P10" s="4" t="n"/>
       <c r="Q10" s="4" t="n"/>
-      <c r="R10" s="4" t="n">
+      <c r="R10" s="4" t="n"/>
+      <c r="S10" s="4" t="n">
         <v>23.29</v>
       </c>
-      <c r="S10" s="4" t="n"/>
       <c r="T10" s="4" t="n"/>
       <c r="U10" s="4" t="n"/>
       <c r="V10" s="4" t="n"/>
@@ -35685,10 +35685,10 @@
       <c r="E12" s="4" t="n"/>
       <c r="F12" s="4" t="n"/>
       <c r="G12" s="4" t="n"/>
-      <c r="H12" s="4" t="n"/>
-      <c r="I12" s="4" t="n">
+      <c r="H12" s="4" t="n">
         <v>21.83</v>
       </c>
+      <c r="I12" s="4" t="n"/>
       <c r="J12" s="4" t="n"/>
       <c r="K12" s="4" t="n">
         <v>21.55</v>
@@ -35696,17 +35696,17 @@
       <c r="L12" s="4" t="n">
         <v>21.75</v>
       </c>
-      <c r="M12" s="4" t="n">
+      <c r="M12" s="4" t="n"/>
+      <c r="N12" s="4" t="n">
         <v>21.39</v>
       </c>
-      <c r="N12" s="4" t="n"/>
       <c r="O12" s="4" t="n"/>
       <c r="P12" s="4" t="n"/>
       <c r="Q12" s="4" t="n"/>
-      <c r="R12" s="4" t="n">
+      <c r="R12" s="4" t="n"/>
+      <c r="S12" s="4" t="n">
         <v>21.81</v>
       </c>
-      <c r="S12" s="4" t="n"/>
       <c r="T12" s="4" t="n"/>
       <c r="U12" s="4" t="n"/>
       <c r="V12" s="4" t="n"/>
@@ -35815,10 +35815,10 @@
       </c>
       <c r="F14" s="4" t="n"/>
       <c r="G14" s="4" t="n"/>
-      <c r="H14" s="4" t="n">
+      <c r="H14" s="4" t="n"/>
+      <c r="I14" s="4" t="n">
         <v>26.19</v>
       </c>
-      <c r="I14" s="4" t="n"/>
       <c r="J14" s="4" t="n"/>
       <c r="K14" s="4" t="n"/>
       <c r="L14" s="4" t="n"/>
@@ -35826,10 +35826,10 @@
       <c r="N14" s="4" t="n"/>
       <c r="O14" s="4" t="n"/>
       <c r="P14" s="4" t="n"/>
-      <c r="Q14" s="4" t="n">
+      <c r="Q14" s="4" t="n"/>
+      <c r="R14" s="4" t="n">
         <v>26.6</v>
       </c>
-      <c r="R14" s="4" t="n"/>
       <c r="S14" s="4" t="n"/>
       <c r="T14" s="4" t="n"/>
       <c r="U14" s="4" t="n">
@@ -35883,18 +35883,18 @@
       <c r="G15" s="4" t="n">
         <v>28.82</v>
       </c>
-      <c r="H15" s="4" t="n"/>
-      <c r="I15" s="4" t="n">
+      <c r="H15" s="4" t="n">
         <v>29.49</v>
       </c>
+      <c r="I15" s="4" t="n"/>
       <c r="J15" s="4" t="n"/>
       <c r="K15" s="4" t="n"/>
       <c r="L15" s="4" t="n"/>
-      <c r="M15" s="4" t="n"/>
+      <c r="M15" s="4" t="n">
+        <v>30.09</v>
+      </c>
       <c r="N15" s="4" t="n"/>
-      <c r="O15" s="4" t="n">
-        <v>30.09</v>
-      </c>
+      <c r="O15" s="4" t="n"/>
       <c r="P15" s="4" t="n"/>
       <c r="Q15" s="4" t="n"/>
       <c r="R15" s="4" t="n"/>
@@ -36006,10 +36006,10 @@
         <v>29.75</v>
       </c>
       <c r="H17" s="4" t="n">
+        <v>30.59</v>
+      </c>
+      <c r="I17" s="4" t="n">
         <v>30.69</v>
-      </c>
-      <c r="I17" s="4" t="n">
-        <v>30.59</v>
       </c>
       <c r="J17" s="4" t="n"/>
       <c r="K17" s="4" t="n"/>
@@ -36065,10 +36065,10 @@
       <c r="E18" s="4" t="n"/>
       <c r="F18" s="4" t="n"/>
       <c r="G18" s="4" t="n"/>
-      <c r="H18" s="4" t="n"/>
-      <c r="I18" s="4" t="n">
+      <c r="H18" s="4" t="n">
         <v>23.72</v>
       </c>
+      <c r="I18" s="4" t="n"/>
       <c r="J18" s="4" t="n">
         <v>23.98</v>
       </c>
@@ -36078,22 +36078,22 @@
       <c r="L18" s="4" t="n">
         <v>23.69</v>
       </c>
-      <c r="M18" s="4" t="n"/>
+      <c r="M18" s="4" t="n">
+        <v>24.19</v>
+      </c>
       <c r="N18" s="4" t="n"/>
-      <c r="O18" s="4" t="n">
-        <v>24.19</v>
-      </c>
+      <c r="O18" s="4" t="n"/>
       <c r="P18" s="4" t="n"/>
-      <c r="Q18" s="4" t="n">
+      <c r="Q18" s="4" t="n"/>
+      <c r="R18" s="4" t="n">
         <v>24.49</v>
       </c>
-      <c r="R18" s="4" t="n">
+      <c r="S18" s="4" t="n">
         <v>23.75</v>
       </c>
-      <c r="S18" s="4" t="n">
+      <c r="T18" s="4" t="n">
         <v>24.5</v>
       </c>
-      <c r="T18" s="4" t="n"/>
       <c r="U18" s="4" t="n"/>
       <c r="V18" s="4" t="n"/>
       <c r="W18" s="4" t="n"/>
@@ -36141,23 +36141,23 @@
         <v>32.19</v>
       </c>
       <c r="G19" s="4" t="n"/>
-      <c r="H19" s="4" t="n">
+      <c r="H19" s="4" t="n"/>
+      <c r="I19" s="4" t="n">
         <v>33.05</v>
       </c>
-      <c r="I19" s="4" t="n"/>
       <c r="J19" s="4" t="n"/>
       <c r="K19" s="4" t="n"/>
       <c r="L19" s="4" t="n"/>
       <c r="M19" s="4" t="n"/>
       <c r="N19" s="4" t="n"/>
       <c r="O19" s="4" t="n"/>
-      <c r="P19" s="4" t="n"/>
+      <c r="P19" s="4" t="n">
+        <v>33.07</v>
+      </c>
       <c r="Q19" s="4" t="n"/>
       <c r="R19" s="4" t="n"/>
       <c r="S19" s="4" t="n"/>
-      <c r="T19" s="4" t="n">
-        <v>33.07</v>
-      </c>
+      <c r="T19" s="4" t="n"/>
       <c r="U19" s="4" t="n"/>
       <c r="V19" s="4" t="n"/>
       <c r="W19" s="4" t="n"/>
@@ -36197,18 +36197,18 @@
       </c>
       <c r="F20" s="4" t="n"/>
       <c r="G20" s="4" t="n"/>
-      <c r="H20" s="4" t="n">
+      <c r="H20" s="4" t="n"/>
+      <c r="I20" s="4" t="n">
         <v>22.4</v>
       </c>
-      <c r="I20" s="4" t="n"/>
       <c r="J20" s="4" t="n"/>
       <c r="K20" s="4" t="n"/>
       <c r="L20" s="4" t="n"/>
       <c r="M20" s="4" t="n"/>
-      <c r="N20" s="4" t="n">
+      <c r="N20" s="4" t="n"/>
+      <c r="O20" s="4" t="n">
         <v>22.59</v>
       </c>
-      <c r="O20" s="4" t="n"/>
       <c r="P20" s="4" t="n"/>
       <c r="Q20" s="4" t="n"/>
       <c r="R20" s="4" t="n"/>
@@ -36337,10 +36337,10 @@
       <c r="O22" s="4" t="n"/>
       <c r="P22" s="4" t="n"/>
       <c r="Q22" s="4" t="n"/>
-      <c r="R22" s="4" t="n">
+      <c r="R22" s="4" t="n"/>
+      <c r="S22" s="4" t="n">
         <v>31.89</v>
       </c>
-      <c r="S22" s="4" t="n"/>
       <c r="T22" s="4" t="n"/>
       <c r="U22" s="4" t="n"/>
       <c r="V22" s="4" t="n"/>
@@ -36448,17 +36448,17 @@
       <c r="L24" s="4" t="n">
         <v>22.78</v>
       </c>
-      <c r="M24" s="4" t="n">
+      <c r="M24" s="4" t="n"/>
+      <c r="N24" s="4" t="n">
         <v>22.69</v>
       </c>
-      <c r="N24" s="4" t="n"/>
       <c r="O24" s="4" t="n"/>
       <c r="P24" s="4" t="n"/>
       <c r="Q24" s="4" t="n"/>
-      <c r="R24" s="4" t="n">
+      <c r="R24" s="4" t="n"/>
+      <c r="S24" s="4" t="n">
         <v>22.89</v>
       </c>
-      <c r="S24" s="4" t="n"/>
       <c r="T24" s="4" t="n"/>
       <c r="U24" s="4" t="n"/>
       <c r="V24" s="4" t="n"/>
@@ -36497,25 +36497,25 @@
       <c r="E25" s="4" t="n"/>
       <c r="F25" s="4" t="n"/>
       <c r="G25" s="4" t="n"/>
-      <c r="H25" s="4" t="n"/>
-      <c r="I25" s="4" t="n">
+      <c r="H25" s="4" t="n">
         <v>24.35</v>
       </c>
+      <c r="I25" s="4" t="n"/>
       <c r="J25" s="4" t="n"/>
       <c r="K25" s="4" t="n"/>
       <c r="L25" s="4" t="n">
         <v>24.03</v>
       </c>
-      <c r="M25" s="4" t="n">
+      <c r="M25" s="4" t="n"/>
+      <c r="N25" s="4" t="n">
         <v>24.13</v>
       </c>
-      <c r="N25" s="4" t="n"/>
       <c r="O25" s="4" t="n"/>
       <c r="P25" s="4" t="n"/>
-      <c r="Q25" s="4" t="n">
+      <c r="Q25" s="4" t="n"/>
+      <c r="R25" s="4" t="n">
         <v>24.89</v>
       </c>
-      <c r="R25" s="4" t="n"/>
       <c r="S25" s="4" t="n"/>
       <c r="T25" s="4" t="n"/>
       <c r="U25" s="4" t="n"/>
@@ -36561,10 +36561,10 @@
       <c r="E26" s="4" t="n"/>
       <c r="F26" s="4" t="n"/>
       <c r="G26" s="4" t="n"/>
-      <c r="H26" s="4" t="n"/>
-      <c r="I26" s="4" t="n">
+      <c r="H26" s="4" t="n">
         <v>18.89</v>
       </c>
+      <c r="I26" s="4" t="n"/>
       <c r="J26" s="4" t="n"/>
       <c r="K26" s="4" t="n">
         <v>18.6</v>
@@ -36572,17 +36572,17 @@
       <c r="L26" s="4" t="n">
         <v>18.65</v>
       </c>
-      <c r="M26" s="4" t="n">
+      <c r="M26" s="4" t="n"/>
+      <c r="N26" s="4" t="n">
         <v>18.59</v>
       </c>
-      <c r="N26" s="4" t="n"/>
       <c r="O26" s="4" t="n"/>
       <c r="P26" s="4" t="n"/>
       <c r="Q26" s="4" t="n"/>
-      <c r="R26" s="4" t="n">
+      <c r="R26" s="4" t="n"/>
+      <c r="S26" s="4" t="n">
         <v>18.69</v>
       </c>
-      <c r="S26" s="4" t="n"/>
       <c r="T26" s="4" t="n"/>
       <c r="U26" s="4" t="n"/>
       <c r="V26" s="4" t="n"/>
@@ -36685,10 +36685,10 @@
       </c>
       <c r="F28" s="4" t="n"/>
       <c r="G28" s="4" t="n"/>
-      <c r="H28" s="4" t="n"/>
-      <c r="I28" s="4" t="n">
+      <c r="H28" s="4" t="n">
         <v>33.09</v>
       </c>
+      <c r="I28" s="4" t="n"/>
       <c r="J28" s="4" t="n"/>
       <c r="K28" s="4" t="n">
         <v>33.05</v>
@@ -36696,11 +36696,11 @@
       <c r="L28" s="4" t="n">
         <v>32.75</v>
       </c>
-      <c r="M28" s="4" t="n"/>
+      <c r="M28" s="4" t="n">
+        <v>33.79</v>
+      </c>
       <c r="N28" s="4" t="n"/>
-      <c r="O28" s="4" t="n">
-        <v>33.79</v>
-      </c>
+      <c r="O28" s="4" t="n"/>
       <c r="P28" s="4" t="n"/>
       <c r="Q28" s="4" t="n"/>
       <c r="R28" s="4" t="n"/>
@@ -36754,11 +36754,11 @@
       <c r="J29" s="4" t="n"/>
       <c r="K29" s="4" t="n"/>
       <c r="L29" s="4" t="n"/>
-      <c r="M29" s="4" t="n"/>
+      <c r="M29" s="4" t="n">
+        <v>19.39</v>
+      </c>
       <c r="N29" s="4" t="n"/>
-      <c r="O29" s="4" t="n">
-        <v>19.39</v>
-      </c>
+      <c r="O29" s="4" t="n"/>
       <c r="P29" s="4" t="n"/>
       <c r="Q29" s="4" t="n"/>
       <c r="R29" s="4" t="n"/>
@@ -36809,22 +36809,22 @@
       <c r="E30" s="4" t="n"/>
       <c r="F30" s="4" t="n"/>
       <c r="G30" s="4" t="n"/>
-      <c r="H30" s="4" t="n">
+      <c r="H30" s="4" t="n"/>
+      <c r="I30" s="4" t="n">
         <v>23.1</v>
       </c>
-      <c r="I30" s="4" t="n"/>
       <c r="J30" s="4" t="n"/>
       <c r="K30" s="4" t="n"/>
       <c r="L30" s="4" t="n"/>
       <c r="M30" s="4" t="n"/>
-      <c r="N30" s="4" t="n">
+      <c r="N30" s="4" t="n"/>
+      <c r="O30" s="4" t="n">
         <v>23.29</v>
       </c>
-      <c r="O30" s="4" t="n"/>
-      <c r="P30" s="4" t="n">
+      <c r="P30" s="4" t="n"/>
+      <c r="Q30" s="4" t="n">
         <v>23.39</v>
       </c>
-      <c r="Q30" s="4" t="n"/>
       <c r="R30" s="4" t="n"/>
       <c r="S30" s="4" t="n"/>
       <c r="T30" s="4" t="n"/>
@@ -36870,10 +36870,10 @@
       <c r="F31" s="4" t="n"/>
       <c r="G31" s="4" t="n"/>
       <c r="H31" s="4" t="n">
+        <v>19.35</v>
+      </c>
+      <c r="I31" s="4" t="n">
         <v>18.99</v>
-      </c>
-      <c r="I31" s="4" t="n">
-        <v>19.35</v>
       </c>
       <c r="J31" s="4" t="n"/>
       <c r="K31" s="4" t="n"/>
@@ -36881,15 +36881,15 @@
       <c r="M31" s="4" t="n"/>
       <c r="N31" s="4" t="n"/>
       <c r="O31" s="4" t="n"/>
-      <c r="P31" s="4" t="n">
+      <c r="P31" s="4" t="n"/>
+      <c r="Q31" s="4" t="n">
         <v>19.3</v>
       </c>
-      <c r="Q31" s="4" t="n"/>
       <c r="R31" s="4" t="n"/>
-      <c r="S31" s="4" t="n">
+      <c r="S31" s="4" t="n"/>
+      <c r="T31" s="4" t="n">
         <v>19.27</v>
       </c>
-      <c r="T31" s="4" t="n"/>
       <c r="U31" s="4" t="n"/>
       <c r="V31" s="4" t="n"/>
       <c r="W31" s="4" t="n">
@@ -36940,10 +36940,10 @@
       </c>
       <c r="G32" s="4" t="n"/>
       <c r="H32" s="4" t="n">
+        <v>28.39</v>
+      </c>
+      <c r="I32" s="4" t="n">
         <v>29.06</v>
-      </c>
-      <c r="I32" s="4" t="n">
-        <v>28.39</v>
       </c>
       <c r="J32" s="4" t="n"/>
       <c r="K32" s="4" t="n"/>
@@ -37005,22 +37005,22 @@
       <c r="E33" s="4" t="n"/>
       <c r="F33" s="4" t="n"/>
       <c r="G33" s="4" t="n"/>
-      <c r="H33" s="4" t="n">
+      <c r="H33" s="4" t="n"/>
+      <c r="I33" s="4" t="n">
         <v>19.89</v>
       </c>
-      <c r="I33" s="4" t="n"/>
       <c r="J33" s="4" t="n"/>
       <c r="K33" s="4" t="n"/>
       <c r="L33" s="4" t="n"/>
       <c r="M33" s="4" t="n"/>
-      <c r="N33" s="4" t="n">
+      <c r="N33" s="4" t="n"/>
+      <c r="O33" s="4" t="n">
         <v>20.21</v>
       </c>
-      <c r="O33" s="4" t="n"/>
-      <c r="P33" s="4" t="n">
+      <c r="P33" s="4" t="n"/>
+      <c r="Q33" s="4" t="n">
         <v>20.49</v>
       </c>
-      <c r="Q33" s="4" t="n"/>
       <c r="R33" s="4" t="n"/>
       <c r="S33" s="4" t="n"/>
       <c r="T33" s="4" t="n"/>
@@ -37071,10 +37071,10 @@
       </c>
       <c r="F34" s="4" t="n"/>
       <c r="G34" s="4" t="n"/>
-      <c r="H34" s="4" t="n"/>
-      <c r="I34" s="4" t="n">
+      <c r="H34" s="4" t="n">
         <v>35.49</v>
       </c>
+      <c r="I34" s="4" t="n"/>
       <c r="J34" s="4" t="n">
         <v>34.7</v>
       </c>
@@ -37128,19 +37128,19 @@
       <c r="F35" s="4" t="n"/>
       <c r="G35" s="4" t="n"/>
       <c r="H35" s="4" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="I35" s="4" t="n">
         <v>23.59</v>
-      </c>
-      <c r="I35" s="4" t="n">
-        <v>23.6</v>
       </c>
       <c r="J35" s="4" t="n"/>
       <c r="K35" s="4" t="n"/>
       <c r="L35" s="4" t="n"/>
       <c r="M35" s="4" t="n"/>
-      <c r="N35" s="4" t="n">
+      <c r="N35" s="4" t="n"/>
+      <c r="O35" s="4" t="n">
         <v>23.69</v>
       </c>
-      <c r="O35" s="4" t="n"/>
       <c r="P35" s="4" t="n"/>
       <c r="Q35" s="4" t="n"/>
       <c r="R35" s="4" t="n"/>
@@ -37193,10 +37193,10 @@
         <v>34.6</v>
       </c>
       <c r="G36" s="4" t="n"/>
-      <c r="H36" s="4" t="n">
+      <c r="H36" s="4" t="n"/>
+      <c r="I36" s="4" t="n">
         <v>35.89</v>
       </c>
-      <c r="I36" s="4" t="n"/>
       <c r="J36" s="4" t="n"/>
       <c r="K36" s="4" t="n"/>
       <c r="L36" s="4" t="n"/>
@@ -37253,20 +37253,20 @@
       </c>
       <c r="F37" s="4" t="n"/>
       <c r="G37" s="4" t="n"/>
-      <c r="H37" s="4" t="n">
+      <c r="H37" s="4" t="n"/>
+      <c r="I37" s="4" t="n">
         <v>23.05</v>
       </c>
-      <c r="I37" s="4" t="n"/>
       <c r="J37" s="4" t="n"/>
       <c r="K37" s="4" t="n"/>
       <c r="L37" s="4" t="n"/>
       <c r="M37" s="4" t="n"/>
       <c r="N37" s="4" t="n"/>
       <c r="O37" s="4" t="n"/>
-      <c r="P37" s="4" t="n">
+      <c r="P37" s="4" t="n"/>
+      <c r="Q37" s="4" t="n">
         <v>23.59</v>
       </c>
-      <c r="Q37" s="4" t="n"/>
       <c r="R37" s="4" t="n"/>
       <c r="S37" s="4" t="n"/>
       <c r="T37" s="4" t="n"/>
@@ -37310,10 +37310,10 @@
       <c r="F38" s="4" t="n"/>
       <c r="G38" s="4" t="n"/>
       <c r="H38" s="4" t="n">
+        <v>20.99</v>
+      </c>
+      <c r="I38" s="4" t="n">
         <v>21.48</v>
-      </c>
-      <c r="I38" s="4" t="n">
-        <v>20.99</v>
       </c>
       <c r="J38" s="4" t="n"/>
       <c r="K38" s="4" t="n">
@@ -37322,22 +37322,22 @@
       <c r="L38" s="4" t="n">
         <v>20.6</v>
       </c>
-      <c r="M38" s="4" t="n">
+      <c r="M38" s="4" t="n"/>
+      <c r="N38" s="4" t="n">
         <v>20.56</v>
       </c>
-      <c r="N38" s="4" t="n"/>
       <c r="O38" s="4" t="n"/>
       <c r="P38" s="4" t="n"/>
-      <c r="Q38" s="4" t="n">
+      <c r="Q38" s="4" t="n"/>
+      <c r="R38" s="4" t="n">
         <v>21.79</v>
       </c>
-      <c r="R38" s="4" t="n">
+      <c r="S38" s="4" t="n">
         <v>21.19</v>
       </c>
-      <c r="S38" s="4" t="n">
+      <c r="T38" s="4" t="n">
         <v>21.59</v>
       </c>
-      <c r="T38" s="4" t="n"/>
       <c r="U38" s="4" t="n"/>
       <c r="V38" s="4" t="n"/>
       <c r="W38" s="4" t="n"/>
@@ -37377,10 +37377,10 @@
       <c r="E39" s="4" t="n"/>
       <c r="F39" s="4" t="n"/>
       <c r="G39" s="4" t="n"/>
-      <c r="H39" s="4" t="n"/>
-      <c r="I39" s="4" t="n">
+      <c r="H39" s="4" t="n">
         <v>29.75</v>
       </c>
+      <c r="I39" s="4" t="n"/>
       <c r="J39" s="4" t="n"/>
       <c r="K39" s="4" t="n">
         <v>29.95</v>
@@ -37443,10 +37443,10 @@
       <c r="G40" s="4" t="n">
         <v>33.99</v>
       </c>
-      <c r="H40" s="4" t="n">
+      <c r="H40" s="4" t="n"/>
+      <c r="I40" s="4" t="n">
         <v>34.9</v>
       </c>
-      <c r="I40" s="4" t="n"/>
       <c r="J40" s="4" t="n"/>
       <c r="K40" s="4" t="n"/>
       <c r="L40" s="4" t="n"/>
@@ -37561,29 +37561,29 @@
       <c r="E42" s="4" t="n"/>
       <c r="F42" s="4" t="n"/>
       <c r="G42" s="4" t="n"/>
-      <c r="H42" s="4" t="n">
+      <c r="H42" s="4" t="n"/>
+      <c r="I42" s="4" t="n">
         <v>22.3</v>
       </c>
-      <c r="I42" s="4" t="n"/>
       <c r="J42" s="4" t="n"/>
       <c r="K42" s="4" t="n"/>
       <c r="L42" s="4" t="n">
         <v>22.05</v>
       </c>
       <c r="M42" s="4" t="n">
+        <v>22.89</v>
+      </c>
+      <c r="N42" s="4" t="n">
         <v>21.95</v>
       </c>
-      <c r="N42" s="4" t="n"/>
-      <c r="O42" s="4" t="n">
-        <v>22.89</v>
-      </c>
-      <c r="P42" s="4" t="n"/>
+      <c r="O42" s="4" t="n"/>
+      <c r="P42" s="4" t="n">
+        <v>22.79</v>
+      </c>
       <c r="Q42" s="4" t="n"/>
       <c r="R42" s="4" t="n"/>
       <c r="S42" s="4" t="n"/>
-      <c r="T42" s="4" t="n">
-        <v>22.79</v>
-      </c>
+      <c r="T42" s="4" t="n"/>
       <c r="U42" s="4" t="n"/>
       <c r="V42" s="4" t="n"/>
       <c r="W42" s="4" t="n"/>
@@ -37683,29 +37683,29 @@
       <c r="E44" s="4" t="n"/>
       <c r="F44" s="4" t="n"/>
       <c r="G44" s="4" t="n"/>
-      <c r="H44" s="4" t="n">
+      <c r="H44" s="4" t="n"/>
+      <c r="I44" s="4" t="n">
         <v>22.25</v>
       </c>
-      <c r="I44" s="4" t="n"/>
       <c r="J44" s="4" t="n"/>
       <c r="K44" s="4" t="n"/>
       <c r="L44" s="4" t="n">
         <v>22.6</v>
       </c>
-      <c r="M44" s="4" t="n">
+      <c r="M44" s="4" t="n"/>
+      <c r="N44" s="4" t="n">
         <v>22.45</v>
       </c>
-      <c r="N44" s="4" t="n"/>
       <c r="O44" s="4" t="n"/>
-      <c r="P44" s="4" t="n">
+      <c r="P44" s="4" t="n"/>
+      <c r="Q44" s="4" t="n">
         <v>22.4</v>
       </c>
-      <c r="Q44" s="4" t="n"/>
       <c r="R44" s="4" t="n"/>
-      <c r="S44" s="4" t="n">
+      <c r="S44" s="4" t="n"/>
+      <c r="T44" s="4" t="n">
         <v>22.19</v>
       </c>
-      <c r="T44" s="4" t="n"/>
       <c r="U44" s="4" t="n"/>
       <c r="V44" s="4" t="n"/>
       <c r="W44" s="4" t="n"/>
@@ -37759,10 +37759,10 @@
       </c>
       <c r="F45" s="4" t="n"/>
       <c r="G45" s="4" t="n"/>
-      <c r="H45" s="4" t="n"/>
-      <c r="I45" s="4" t="n">
+      <c r="H45" s="4" t="n">
         <v>40.69</v>
       </c>
+      <c r="I45" s="4" t="n"/>
       <c r="J45" s="4" t="n"/>
       <c r="K45" s="4" t="n"/>
       <c r="L45" s="4" t="n"/>
@@ -37934,18 +37934,18 @@
         <v>24.79</v>
       </c>
       <c r="L48" s="4" t="n"/>
-      <c r="M48" s="4" t="n"/>
+      <c r="M48" s="4" t="n">
+        <v>25.59</v>
+      </c>
       <c r="N48" s="4" t="n"/>
-      <c r="O48" s="4" t="n">
-        <v>25.59</v>
-      </c>
+      <c r="O48" s="4" t="n"/>
       <c r="P48" s="4" t="n"/>
       <c r="Q48" s="4" t="n"/>
       <c r="R48" s="4" t="n"/>
-      <c r="S48" s="4" t="n">
+      <c r="S48" s="4" t="n"/>
+      <c r="T48" s="4" t="n">
         <v>25.79</v>
       </c>
-      <c r="T48" s="4" t="n"/>
       <c r="U48" s="4" t="n"/>
       <c r="V48" s="4" t="n"/>
       <c r="W48" s="4" t="n"/>
@@ -37997,10 +37997,10 @@
       <c r="K49" s="4" t="n"/>
       <c r="L49" s="4" t="n"/>
       <c r="M49" s="4" t="n"/>
-      <c r="N49" s="4" t="n">
+      <c r="N49" s="4" t="n"/>
+      <c r="O49" s="4" t="n">
         <v>30.99</v>
       </c>
-      <c r="O49" s="4" t="n"/>
       <c r="P49" s="4" t="n"/>
       <c r="Q49" s="4" t="n"/>
       <c r="R49" s="4" t="n"/>
@@ -38047,18 +38047,18 @@
       </c>
       <c r="F50" s="4" t="n"/>
       <c r="G50" s="4" t="n"/>
-      <c r="H50" s="4" t="n">
+      <c r="H50" s="4" t="n"/>
+      <c r="I50" s="4" t="n">
         <v>26.59</v>
       </c>
-      <c r="I50" s="4" t="n"/>
       <c r="J50" s="4" t="n"/>
       <c r="K50" s="4" t="n"/>
       <c r="L50" s="4" t="n"/>
       <c r="M50" s="4" t="n"/>
-      <c r="N50" s="4" t="n">
+      <c r="N50" s="4" t="n"/>
+      <c r="O50" s="4" t="n">
         <v>26.75</v>
       </c>
-      <c r="O50" s="4" t="n"/>
       <c r="P50" s="4" t="n"/>
       <c r="Q50" s="4" t="n"/>
       <c r="R50" s="4" t="n"/>
@@ -38108,10 +38108,10 @@
         <v>24.09</v>
       </c>
       <c r="H51" s="4" t="n">
+        <v>24.29</v>
+      </c>
+      <c r="I51" s="4" t="n">
         <v>24.39</v>
-      </c>
-      <c r="I51" s="4" t="n">
-        <v>24.29</v>
       </c>
       <c r="J51" s="4" t="n"/>
       <c r="K51" s="4" t="n">
@@ -38120,10 +38120,10 @@
       <c r="L51" s="4" t="n">
         <v>23.75</v>
       </c>
-      <c r="M51" s="4" t="n">
+      <c r="M51" s="4" t="n"/>
+      <c r="N51" s="4" t="n">
         <v>23.48</v>
       </c>
-      <c r="N51" s="4" t="n"/>
       <c r="O51" s="4" t="n"/>
       <c r="P51" s="4" t="n"/>
       <c r="Q51" s="4" t="n"/>
@@ -38353,18 +38353,18 @@
       <c r="G55" s="4" t="n">
         <v>32.85</v>
       </c>
-      <c r="H55" s="4" t="n">
+      <c r="H55" s="4" t="n"/>
+      <c r="I55" s="4" t="n">
         <v>32.73</v>
       </c>
-      <c r="I55" s="4" t="n"/>
       <c r="J55" s="4" t="n"/>
       <c r="K55" s="4" t="n"/>
       <c r="L55" s="4" t="n"/>
       <c r="M55" s="4" t="n"/>
-      <c r="N55" s="4" t="n">
+      <c r="N55" s="4" t="n"/>
+      <c r="O55" s="4" t="n">
         <v>33.3</v>
       </c>
-      <c r="O55" s="4" t="n"/>
       <c r="P55" s="4" t="n"/>
       <c r="Q55" s="4" t="n"/>
       <c r="R55" s="4" t="n"/>
@@ -38544,11 +38544,11 @@
       <c r="J58" s="4" t="n"/>
       <c r="K58" s="4" t="n"/>
       <c r="L58" s="4" t="n"/>
-      <c r="M58" s="4" t="n"/>
+      <c r="M58" s="4" t="n">
+        <v>26.2</v>
+      </c>
       <c r="N58" s="4" t="n"/>
-      <c r="O58" s="4" t="n">
-        <v>26.2</v>
-      </c>
+      <c r="O58" s="4" t="n"/>
       <c r="P58" s="4" t="n"/>
       <c r="Q58" s="4" t="n"/>
       <c r="R58" s="4" t="n"/>
@@ -38597,25 +38597,25 @@
       <c r="G59" s="4" t="n">
         <v>21.29</v>
       </c>
-      <c r="H59" s="4" t="n">
+      <c r="H59" s="4" t="n"/>
+      <c r="I59" s="4" t="n">
         <v>21.19</v>
       </c>
-      <c r="I59" s="4" t="n"/>
       <c r="J59" s="4" t="n"/>
       <c r="K59" s="4" t="n"/>
       <c r="L59" s="4" t="n"/>
       <c r="M59" s="4" t="n"/>
       <c r="N59" s="4" t="n"/>
       <c r="O59" s="4" t="n"/>
-      <c r="P59" s="4" t="n"/>
-      <c r="Q59" s="4" t="n">
+      <c r="P59" s="4" t="n">
+        <v>21.22</v>
+      </c>
+      <c r="Q59" s="4" t="n"/>
+      <c r="R59" s="4" t="n">
         <v>22.13</v>
       </c>
-      <c r="R59" s="4" t="n"/>
       <c r="S59" s="4" t="n"/>
-      <c r="T59" s="4" t="n">
-        <v>21.22</v>
-      </c>
+      <c r="T59" s="4" t="n"/>
       <c r="U59" s="4" t="n"/>
       <c r="V59" s="4" t="n"/>
       <c r="W59" s="4" t="n"/>
@@ -38719,29 +38719,29 @@
       <c r="E61" s="4" t="n"/>
       <c r="F61" s="4" t="n"/>
       <c r="G61" s="4" t="n"/>
-      <c r="H61" s="4" t="n">
+      <c r="H61" s="4" t="n"/>
+      <c r="I61" s="4" t="n">
         <v>21.72</v>
       </c>
-      <c r="I61" s="4" t="n"/>
       <c r="J61" s="4" t="n"/>
       <c r="K61" s="4" t="n"/>
       <c r="L61" s="4" t="n">
         <v>21.75</v>
       </c>
-      <c r="M61" s="4" t="n">
+      <c r="M61" s="4" t="n"/>
+      <c r="N61" s="4" t="n">
         <v>21.82</v>
       </c>
-      <c r="N61" s="4" t="n"/>
       <c r="O61" s="4" t="n"/>
-      <c r="P61" s="4" t="n"/>
-      <c r="Q61" s="4" t="n">
+      <c r="P61" s="4" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="Q61" s="4" t="n"/>
+      <c r="R61" s="4" t="n">
         <v>22.5</v>
       </c>
-      <c r="R61" s="4" t="n"/>
       <c r="S61" s="4" t="n"/>
-      <c r="T61" s="4" t="n">
-        <v>21.75</v>
-      </c>
+      <c r="T61" s="4" t="n"/>
       <c r="U61" s="4" t="n"/>
       <c r="V61" s="4" t="n"/>
       <c r="W61" s="4" t="n"/>
@@ -38800,10 +38800,10 @@
         <v>29.99</v>
       </c>
       <c r="H62" s="4" t="n">
+        <v>30.89</v>
+      </c>
+      <c r="I62" s="4" t="n">
         <v>31.49</v>
-      </c>
-      <c r="I62" s="4" t="n">
-        <v>30.89</v>
       </c>
       <c r="J62" s="4" t="n"/>
       <c r="K62" s="4" t="n"/>
@@ -38857,20 +38857,20 @@
       <c r="G63" s="4" t="n">
         <v>23.8</v>
       </c>
-      <c r="H63" s="4" t="n">
+      <c r="H63" s="4" t="n"/>
+      <c r="I63" s="4" t="n">
         <v>24.5</v>
       </c>
-      <c r="I63" s="4" t="n"/>
       <c r="J63" s="4" t="n"/>
       <c r="K63" s="4" t="n"/>
       <c r="L63" s="4" t="n"/>
       <c r="M63" s="4" t="n"/>
       <c r="N63" s="4" t="n"/>
       <c r="O63" s="4" t="n"/>
-      <c r="P63" s="4" t="n">
+      <c r="P63" s="4" t="n"/>
+      <c r="Q63" s="4" t="n">
         <v>24.89</v>
       </c>
-      <c r="Q63" s="4" t="n"/>
       <c r="R63" s="4" t="n"/>
       <c r="S63" s="4" t="n"/>
       <c r="T63" s="4" t="n"/>
@@ -38979,10 +38979,10 @@
         <v>32.9</v>
       </c>
       <c r="G65" s="4" t="n"/>
-      <c r="H65" s="4" t="n"/>
-      <c r="I65" s="4" t="n">
+      <c r="H65" s="4" t="n">
         <v>33.79</v>
       </c>
+      <c r="I65" s="4" t="n"/>
       <c r="J65" s="4" t="n"/>
       <c r="K65" s="4" t="n"/>
       <c r="L65" s="4" t="n"/>
@@ -39087,27 +39087,27 @@
       <c r="E67" s="4" t="n"/>
       <c r="F67" s="4" t="n"/>
       <c r="G67" s="4" t="n"/>
-      <c r="H67" s="4" t="n"/>
-      <c r="I67" s="4" t="n">
+      <c r="H67" s="4" t="n">
         <v>18.09</v>
       </c>
+      <c r="I67" s="4" t="n"/>
       <c r="J67" s="4" t="n"/>
       <c r="K67" s="4" t="n"/>
       <c r="L67" s="4" t="n"/>
-      <c r="M67" s="4" t="n">
+      <c r="M67" s="4" t="n"/>
+      <c r="N67" s="4" t="n">
         <v>17.95</v>
       </c>
-      <c r="N67" s="4" t="n"/>
       <c r="O67" s="4" t="n"/>
       <c r="P67" s="4" t="n"/>
       <c r="Q67" s="4" t="n"/>
-      <c r="R67" s="4" t="n">
+      <c r="R67" s="4" t="n"/>
+      <c r="S67" s="4" t="n">
         <v>18.13</v>
       </c>
-      <c r="S67" s="4" t="n">
+      <c r="T67" s="4" t="n">
         <v>18.55</v>
       </c>
-      <c r="T67" s="4" t="n"/>
       <c r="U67" s="4" t="n"/>
       <c r="V67" s="4" t="n"/>
       <c r="W67" s="4" t="n"/>
@@ -39158,11 +39158,11 @@
       <c r="J68" s="4" t="n"/>
       <c r="K68" s="4" t="n"/>
       <c r="L68" s="4" t="n"/>
-      <c r="M68" s="4" t="n"/>
+      <c r="M68" s="4" t="n">
+        <v>28.06</v>
+      </c>
       <c r="N68" s="4" t="n"/>
-      <c r="O68" s="4" t="n">
-        <v>28.06</v>
-      </c>
+      <c r="O68" s="4" t="n"/>
       <c r="P68" s="4" t="n"/>
       <c r="Q68" s="4" t="n"/>
       <c r="R68" s="4" t="n"/>
@@ -39271,25 +39271,25 @@
       <c r="E70" s="4" t="n"/>
       <c r="F70" s="4" t="n"/>
       <c r="G70" s="4" t="n"/>
-      <c r="H70" s="4" t="n"/>
-      <c r="I70" s="4" t="n">
+      <c r="H70" s="4" t="n">
         <v>21.63</v>
       </c>
+      <c r="I70" s="4" t="n"/>
       <c r="J70" s="4" t="n"/>
       <c r="K70" s="4" t="n"/>
       <c r="L70" s="4" t="n">
         <v>21.29</v>
       </c>
-      <c r="M70" s="4" t="n">
+      <c r="M70" s="4" t="n"/>
+      <c r="N70" s="4" t="n">
         <v>20.99</v>
       </c>
-      <c r="N70" s="4" t="n"/>
       <c r="O70" s="4" t="n"/>
       <c r="P70" s="4" t="n"/>
-      <c r="Q70" s="4" t="n">
+      <c r="Q70" s="4" t="n"/>
+      <c r="R70" s="4" t="n">
         <v>22.03</v>
       </c>
-      <c r="R70" s="4" t="n"/>
       <c r="S70" s="4" t="n"/>
       <c r="T70" s="4" t="n"/>
       <c r="U70" s="4" t="n"/>
@@ -39396,10 +39396,10 @@
       <c r="F72" s="4" t="n"/>
       <c r="G72" s="4" t="n"/>
       <c r="H72" s="4" t="n">
+        <v>25.85</v>
+      </c>
+      <c r="I72" s="4" t="n">
         <v>25.93</v>
-      </c>
-      <c r="I72" s="4" t="n">
-        <v>25.85</v>
       </c>
       <c r="J72" s="4" t="n"/>
       <c r="K72" s="4" t="n"/>
@@ -39407,10 +39407,10 @@
         <v>25.79</v>
       </c>
       <c r="M72" s="4" t="n"/>
-      <c r="N72" s="4" t="n">
+      <c r="N72" s="4" t="n"/>
+      <c r="O72" s="4" t="n">
         <v>26.1</v>
       </c>
-      <c r="O72" s="4" t="n"/>
       <c r="P72" s="4" t="n"/>
       <c r="Q72" s="4" t="n"/>
       <c r="R72" s="4" t="n"/>
@@ -39465,27 +39465,27 @@
       <c r="E73" s="4" t="n"/>
       <c r="F73" s="4" t="n"/>
       <c r="G73" s="4" t="n"/>
-      <c r="H73" s="4" t="n">
+      <c r="H73" s="4" t="n"/>
+      <c r="I73" s="4" t="n">
         <v>19.19</v>
       </c>
-      <c r="I73" s="4" t="n"/>
       <c r="J73" s="4" t="n"/>
       <c r="K73" s="4" t="n"/>
       <c r="L73" s="4" t="n"/>
       <c r="M73" s="4" t="n"/>
-      <c r="N73" s="4" t="n">
+      <c r="N73" s="4" t="n"/>
+      <c r="O73" s="4" t="n">
         <v>19.4</v>
       </c>
-      <c r="O73" s="4" t="n"/>
-      <c r="P73" s="4" t="n">
+      <c r="P73" s="4" t="n"/>
+      <c r="Q73" s="4" t="n">
         <v>19.39</v>
       </c>
-      <c r="Q73" s="4" t="n"/>
       <c r="R73" s="4" t="n"/>
-      <c r="S73" s="4" t="n">
+      <c r="S73" s="4" t="n"/>
+      <c r="T73" s="4" t="n">
         <v>19.35</v>
       </c>
-      <c r="T73" s="4" t="n"/>
       <c r="U73" s="4" t="n"/>
       <c r="V73" s="4" t="n"/>
       <c r="W73" s="4" t="n"/>
@@ -39525,20 +39525,20 @@
       <c r="E74" s="4" t="n"/>
       <c r="F74" s="4" t="n"/>
       <c r="G74" s="4" t="n"/>
-      <c r="H74" s="4" t="n"/>
-      <c r="I74" s="4" t="n">
+      <c r="H74" s="4" t="n">
         <v>33.95</v>
       </c>
+      <c r="I74" s="4" t="n"/>
       <c r="J74" s="4" t="n">
         <v>34.79</v>
       </c>
       <c r="K74" s="4" t="n"/>
       <c r="L74" s="4" t="n"/>
       <c r="M74" s="4" t="n"/>
-      <c r="N74" s="4" t="n">
+      <c r="N74" s="4" t="n"/>
+      <c r="O74" s="4" t="n">
         <v>35.2</v>
       </c>
-      <c r="O74" s="4" t="n"/>
       <c r="P74" s="4" t="n"/>
       <c r="Q74" s="4" t="n"/>
       <c r="R74" s="4" t="n"/>
@@ -39583,10 +39583,10 @@
       <c r="E75" s="4" t="n"/>
       <c r="F75" s="4" t="n"/>
       <c r="G75" s="4" t="n"/>
-      <c r="H75" s="4" t="n"/>
-      <c r="I75" s="4" t="n">
+      <c r="H75" s="4" t="n">
         <v>26.69</v>
       </c>
+      <c r="I75" s="4" t="n"/>
       <c r="J75" s="4" t="n"/>
       <c r="K75" s="4" t="n">
         <v>26.25</v>
@@ -39597,10 +39597,10 @@
       <c r="O75" s="4" t="n"/>
       <c r="P75" s="4" t="n"/>
       <c r="Q75" s="4" t="n"/>
-      <c r="R75" s="4" t="n">
+      <c r="R75" s="4" t="n"/>
+      <c r="S75" s="4" t="n">
         <v>27.49</v>
       </c>
-      <c r="S75" s="4" t="n"/>
       <c r="T75" s="4" t="n"/>
       <c r="U75" s="4" t="n"/>
       <c r="V75" s="4" t="n"/>
@@ -39639,22 +39639,22 @@
       <c r="E76" s="4" t="n"/>
       <c r="F76" s="4" t="n"/>
       <c r="G76" s="4" t="n"/>
-      <c r="H76" s="4" t="n">
+      <c r="H76" s="4" t="n"/>
+      <c r="I76" s="4" t="n">
         <v>16.6</v>
       </c>
-      <c r="I76" s="4" t="n"/>
       <c r="J76" s="4" t="n"/>
       <c r="K76" s="4" t="n"/>
       <c r="L76" s="4" t="n"/>
       <c r="M76" s="4" t="n"/>
-      <c r="N76" s="4" t="n">
+      <c r="N76" s="4" t="n"/>
+      <c r="O76" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="O76" s="4" t="n"/>
-      <c r="P76" s="4" t="n">
+      <c r="P76" s="4" t="n"/>
+      <c r="Q76" s="4" t="n">
         <v>17.09</v>
       </c>
-      <c r="Q76" s="4" t="n"/>
       <c r="R76" s="4" t="n"/>
       <c r="S76" s="4" t="n"/>
       <c r="T76" s="4" t="n"/>
@@ -40109,10 +40109,10 @@
         <v>26.59</v>
       </c>
       <c r="G84" s="4" t="n"/>
-      <c r="H84" s="4" t="n"/>
-      <c r="I84" s="4" t="n">
+      <c r="H84" s="4" t="n">
         <v>27.39</v>
       </c>
+      <c r="I84" s="4" t="n"/>
       <c r="J84" s="4" t="n"/>
       <c r="K84" s="4" t="n"/>
       <c r="L84" s="4" t="n"/>
@@ -40333,24 +40333,24 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>速尾★4</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>速尾★5</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>速尾★6</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>9x8★6</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>速尾★4</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>速尾★5</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>速尾★6</t>
-        </is>
-      </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
           <t>ssc★1</t>
@@ -40393,59 +40393,59 @@
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
+          <t>狼崽★5</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
           <t>21c★1</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>21c★4</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>21c★6</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>万达★6</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>狼崽★5</t>
-        </is>
-      </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
+          <t>fp1★5</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>fp1★6</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
           <t>sgt★6</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>火山★5</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>法拉第★6</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>秋王★6</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>fp1★5</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>fp1★6</t>
-        </is>
-      </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>莫斯勒★1</t>
@@ -40528,22 +40528,22 @@
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
+          <t>英灵殿★6</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
           <t>ts900★6</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>风扇★5</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>cs★6</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>英灵殿★6</t>
         </is>
       </c>
       <c r="BH1" s="1" t="inlineStr">
@@ -40582,12 +40582,12 @@
       <c r="N2" s="4" t="n"/>
       <c r="O2" s="4" t="n"/>
       <c r="P2" s="4" t="n"/>
-      <c r="Q2" s="4" t="n">
-        <v>19.1</v>
-      </c>
+      <c r="Q2" s="4" t="n"/>
       <c r="R2" s="4" t="n"/>
       <c r="S2" s="4" t="n"/>
-      <c r="T2" s="4" t="n"/>
+      <c r="T2" s="4" t="n">
+        <v>19.1</v>
+      </c>
       <c r="U2" s="4" t="n"/>
       <c r="V2" s="4" t="n"/>
       <c r="W2" s="4" t="n"/>
@@ -40599,15 +40599,15 @@
       <c r="AC2" s="4" t="n"/>
       <c r="AD2" s="4" t="n"/>
       <c r="AE2" s="4" t="n"/>
-      <c r="AF2" s="4" t="n">
+      <c r="AF2" s="4" t="n"/>
+      <c r="AG2" s="4" t="n">
         <v>19.2</v>
       </c>
-      <c r="AG2" s="4" t="n"/>
-      <c r="AH2" s="4" t="n">
+      <c r="AH2" s="4" t="n"/>
+      <c r="AI2" s="4" t="n"/>
+      <c r="AJ2" s="4" t="n">
         <v>19.3</v>
       </c>
-      <c r="AI2" s="4" t="n"/>
-      <c r="AJ2" s="4" t="n"/>
       <c r="AK2" s="4" t="n"/>
       <c r="AL2" s="4" t="n"/>
       <c r="AM2" s="4" t="n"/>
@@ -40661,12 +40661,16 @@
       <c r="R3" s="4" t="n"/>
       <c r="S3" s="4" t="n"/>
       <c r="T3" s="4" t="n"/>
-      <c r="U3" s="4" t="n"/>
+      <c r="U3" s="4" t="n">
+        <v>29.19</v>
+      </c>
       <c r="V3" s="4" t="n">
-        <v>29.3</v>
+        <v>29.09</v>
       </c>
       <c r="W3" s="4" t="n"/>
-      <c r="X3" s="4" t="n"/>
+      <c r="X3" s="4" t="n">
+        <v>28.5</v>
+      </c>
       <c r="Y3" s="4" t="n"/>
       <c r="Z3" s="4" t="n"/>
       <c r="AA3" s="4" t="n"/>
@@ -40803,12 +40807,12 @@
       <c r="N5" s="4" t="n"/>
       <c r="O5" s="4" t="n"/>
       <c r="P5" s="4" t="n"/>
-      <c r="Q5" s="4" t="n">
-        <v>18.2</v>
-      </c>
+      <c r="Q5" s="4" t="n"/>
       <c r="R5" s="4" t="n"/>
       <c r="S5" s="4" t="n"/>
-      <c r="T5" s="4" t="n"/>
+      <c r="T5" s="4" t="n">
+        <v>18.2</v>
+      </c>
       <c r="U5" s="4" t="n"/>
       <c r="V5" s="4" t="n"/>
       <c r="W5" s="4" t="n"/>
@@ -40880,12 +40884,12 @@
       <c r="N6" s="4" t="n"/>
       <c r="O6" s="4" t="n"/>
       <c r="P6" s="4" t="n"/>
-      <c r="Q6" s="4" t="n">
-        <v>18.05</v>
-      </c>
+      <c r="Q6" s="4" t="n"/>
       <c r="R6" s="4" t="n"/>
       <c r="S6" s="4" t="n"/>
-      <c r="T6" s="4" t="n"/>
+      <c r="T6" s="4" t="n">
+        <v>18.05</v>
+      </c>
       <c r="U6" s="4" t="n"/>
       <c r="V6" s="4" t="n"/>
       <c r="W6" s="4" t="n"/>
@@ -41107,10 +41111,10 @@
       <c r="N9" s="4" t="n"/>
       <c r="O9" s="4" t="n"/>
       <c r="P9" s="4" t="n"/>
-      <c r="Q9" s="4" t="n"/>
-      <c r="R9" s="4" t="n">
+      <c r="Q9" s="4" t="n">
         <v>20.52</v>
       </c>
+      <c r="R9" s="4" t="n"/>
       <c r="S9" s="4" t="n"/>
       <c r="T9" s="4" t="n"/>
       <c r="U9" s="4" t="n"/>
@@ -41128,10 +41132,12 @@
       <c r="AG9" s="4" t="n"/>
       <c r="AH9" s="4" t="n"/>
       <c r="AI9" s="4" t="n">
+        <v>19.89</v>
+      </c>
+      <c r="AJ9" s="4" t="n"/>
+      <c r="AK9" s="4" t="n">
         <v>20.49</v>
       </c>
-      <c r="AJ9" s="4" t="n"/>
-      <c r="AK9" s="4" t="n"/>
       <c r="AL9" s="4" t="n"/>
       <c r="AM9" s="4" t="n"/>
       <c r="AN9" s="4" t="n"/>
@@ -41182,13 +41188,13 @@
       <c r="N10" s="4" t="n"/>
       <c r="O10" s="4" t="n"/>
       <c r="P10" s="4" t="n"/>
-      <c r="Q10" s="4" t="n">
+      <c r="Q10" s="4" t="n"/>
+      <c r="R10" s="4" t="n"/>
+      <c r="S10" s="4" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="T10" s="4" t="n">
         <v>23.5</v>
-      </c>
-      <c r="R10" s="4" t="n"/>
-      <c r="S10" s="4" t="n"/>
-      <c r="T10" s="4" t="n">
-        <v>23.4</v>
       </c>
       <c r="U10" s="4" t="n"/>
       <c r="V10" s="4" t="n"/>
@@ -41273,13 +41279,13 @@
       <c r="Z11" s="4" t="n"/>
       <c r="AA11" s="4" t="n"/>
       <c r="AB11" s="4" t="n"/>
-      <c r="AC11" s="4" t="n"/>
+      <c r="AC11" s="4" t="n">
+        <v>37.99</v>
+      </c>
       <c r="AD11" s="4" t="n"/>
       <c r="AE11" s="4" t="n"/>
       <c r="AF11" s="4" t="n"/>
-      <c r="AG11" s="4" t="n">
-        <v>37.99</v>
-      </c>
+      <c r="AG11" s="4" t="n"/>
       <c r="AH11" s="4" t="n"/>
       <c r="AI11" s="4" t="n"/>
       <c r="AJ11" s="4" t="n"/>
@@ -41332,10 +41338,10 @@
       <c r="N12" s="4" t="n"/>
       <c r="O12" s="4" t="n"/>
       <c r="P12" s="4" t="n"/>
-      <c r="Q12" s="4" t="n"/>
-      <c r="R12" s="4" t="n">
+      <c r="Q12" s="4" t="n">
         <v>21.99</v>
       </c>
+      <c r="R12" s="4" t="n"/>
       <c r="S12" s="4" t="n"/>
       <c r="T12" s="4" t="n"/>
       <c r="U12" s="4" t="n"/>
@@ -41351,21 +41357,21 @@
         <v>21.89</v>
       </c>
       <c r="AC12" s="4" t="n"/>
-      <c r="AD12" s="4" t="n">
+      <c r="AD12" s="4" t="n"/>
+      <c r="AE12" s="4" t="n">
         <v>21.8</v>
       </c>
-      <c r="AE12" s="4" t="n">
+      <c r="AF12" s="4" t="n">
         <v>21.69</v>
       </c>
-      <c r="AF12" s="4" t="n"/>
       <c r="AG12" s="4" t="n"/>
       <c r="AH12" s="4" t="n"/>
       <c r="AI12" s="4" t="n"/>
-      <c r="AJ12" s="4" t="n">
+      <c r="AJ12" s="4" t="n"/>
+      <c r="AK12" s="4" t="n"/>
+      <c r="AL12" s="4" t="n">
         <v>22.1</v>
       </c>
-      <c r="AK12" s="4" t="n"/>
-      <c r="AL12" s="4" t="n"/>
       <c r="AM12" s="4" t="n"/>
       <c r="AN12" s="4" t="n"/>
       <c r="AO12" s="4" t="n"/>
@@ -41515,13 +41521,13 @@
       <c r="AE14" s="4" t="n"/>
       <c r="AF14" s="4" t="n"/>
       <c r="AG14" s="4" t="n"/>
-      <c r="AH14" s="4" t="n"/>
+      <c r="AH14" s="4" t="n">
+        <v>26.69</v>
+      </c>
       <c r="AI14" s="4" t="n"/>
       <c r="AJ14" s="4" t="n"/>
       <c r="AK14" s="4" t="n"/>
-      <c r="AL14" s="4" t="n">
-        <v>26.69</v>
-      </c>
+      <c r="AL14" s="4" t="n"/>
       <c r="AM14" s="4" t="n"/>
       <c r="AN14" s="4" t="n"/>
       <c r="AO14" s="4" t="n"/>
@@ -41587,13 +41593,13 @@
       <c r="Z15" s="4" t="n"/>
       <c r="AA15" s="4" t="n"/>
       <c r="AB15" s="4" t="n"/>
-      <c r="AC15" s="4" t="n"/>
+      <c r="AC15" s="4" t="n">
+        <v>30.4</v>
+      </c>
       <c r="AD15" s="4" t="n"/>
       <c r="AE15" s="4" t="n"/>
       <c r="AF15" s="4" t="n"/>
-      <c r="AG15" s="4" t="n">
-        <v>30.4</v>
-      </c>
+      <c r="AG15" s="4" t="n"/>
       <c r="AH15" s="4" t="n"/>
       <c r="AI15" s="4" t="n"/>
       <c r="AJ15" s="4" t="n"/>
@@ -41662,7 +41668,9 @@
       <c r="R16" s="4" t="n"/>
       <c r="S16" s="4" t="n"/>
       <c r="T16" s="4" t="n"/>
-      <c r="U16" s="4" t="n"/>
+      <c r="U16" s="4" t="n">
+        <v>40.3</v>
+      </c>
       <c r="V16" s="4" t="n">
         <v>39.9</v>
       </c>
@@ -41802,10 +41810,10 @@
       <c r="N18" s="4" t="n"/>
       <c r="O18" s="4" t="n"/>
       <c r="P18" s="4" t="n"/>
-      <c r="Q18" s="4" t="n"/>
-      <c r="R18" s="4" t="n">
+      <c r="Q18" s="4" t="n">
         <v>24.59</v>
       </c>
+      <c r="R18" s="4" t="n"/>
       <c r="S18" s="4" t="n"/>
       <c r="T18" s="4" t="n"/>
       <c r="U18" s="4" t="n"/>
@@ -41818,13 +41826,13 @@
       <c r="Z18" s="4" t="n"/>
       <c r="AA18" s="4" t="n"/>
       <c r="AB18" s="4" t="n"/>
-      <c r="AC18" s="4" t="n"/>
+      <c r="AC18" s="4" t="n">
+        <v>24.79</v>
+      </c>
       <c r="AD18" s="4" t="n"/>
       <c r="AE18" s="4" t="n"/>
       <c r="AF18" s="4" t="n"/>
-      <c r="AG18" s="4" t="n">
-        <v>24.79</v>
-      </c>
+      <c r="AG18" s="4" t="n"/>
       <c r="AH18" s="4" t="n"/>
       <c r="AI18" s="4" t="n"/>
       <c r="AJ18" s="4" t="n"/>
@@ -41883,12 +41891,12 @@
       <c r="N19" s="4" t="n"/>
       <c r="O19" s="4" t="n"/>
       <c r="P19" s="4" t="n"/>
-      <c r="Q19" s="4" t="n">
-        <v>33.4</v>
-      </c>
+      <c r="Q19" s="4" t="n"/>
       <c r="R19" s="4" t="n"/>
       <c r="S19" s="4" t="n"/>
-      <c r="T19" s="4" t="n"/>
+      <c r="T19" s="4" t="n">
+        <v>33.4</v>
+      </c>
       <c r="U19" s="4" t="n"/>
       <c r="V19" s="4" t="n"/>
       <c r="W19" s="4" t="n"/>
@@ -41956,12 +41964,12 @@
       <c r="N20" s="4" t="n"/>
       <c r="O20" s="4" t="n"/>
       <c r="P20" s="4" t="n"/>
-      <c r="Q20" s="4" t="n">
-        <v>22.59</v>
-      </c>
+      <c r="Q20" s="4" t="n"/>
       <c r="R20" s="4" t="n"/>
       <c r="S20" s="4" t="n"/>
-      <c r="T20" s="4" t="n"/>
+      <c r="T20" s="4" t="n">
+        <v>22.59</v>
+      </c>
       <c r="U20" s="4" t="n"/>
       <c r="V20" s="4" t="n"/>
       <c r="W20" s="4" t="n"/>
@@ -41973,10 +41981,10 @@
       <c r="AC20" s="4" t="n"/>
       <c r="AD20" s="4" t="n"/>
       <c r="AE20" s="4" t="n"/>
-      <c r="AF20" s="4" t="n">
+      <c r="AF20" s="4" t="n"/>
+      <c r="AG20" s="4" t="n">
         <v>22.85</v>
       </c>
-      <c r="AG20" s="4" t="n"/>
       <c r="AH20" s="4" t="n"/>
       <c r="AI20" s="4" t="n"/>
       <c r="AJ20" s="4" t="n"/>
@@ -42195,7 +42203,9 @@
       <c r="Z23" s="4" t="n"/>
       <c r="AA23" s="4" t="n"/>
       <c r="AB23" s="4" t="n"/>
-      <c r="AC23" s="4" t="n"/>
+      <c r="AC23" s="4" t="n">
+        <v>32.3</v>
+      </c>
       <c r="AD23" s="4" t="n"/>
       <c r="AE23" s="4" t="n"/>
       <c r="AF23" s="4" t="n"/>
@@ -42250,14 +42260,14 @@
       <c r="N24" s="4" t="n"/>
       <c r="O24" s="4" t="n"/>
       <c r="P24" s="4" t="n"/>
-      <c r="Q24" s="4" t="n"/>
-      <c r="R24" s="4" t="n">
+      <c r="Q24" s="4" t="n">
         <v>23.69</v>
       </c>
-      <c r="S24" s="4" t="n"/>
-      <c r="T24" s="4" t="n">
+      <c r="R24" s="4" t="n"/>
+      <c r="S24" s="4" t="n">
         <v>23.3</v>
       </c>
+      <c r="T24" s="4" t="n"/>
       <c r="U24" s="4" t="n"/>
       <c r="V24" s="4" t="n"/>
       <c r="W24" s="4" t="n"/>
@@ -42277,11 +42287,11 @@
       <c r="AG24" s="4" t="n"/>
       <c r="AH24" s="4" t="n"/>
       <c r="AI24" s="4" t="n"/>
-      <c r="AJ24" s="4" t="n">
+      <c r="AJ24" s="4" t="n"/>
+      <c r="AK24" s="4" t="n"/>
+      <c r="AL24" s="4" t="n">
         <v>23.03</v>
       </c>
-      <c r="AK24" s="4" t="n"/>
-      <c r="AL24" s="4" t="n"/>
       <c r="AM24" s="4" t="n"/>
       <c r="AN24" s="4" t="n"/>
       <c r="AO24" s="4" t="n"/>
@@ -42347,11 +42357,11 @@
       <c r="AF25" s="4" t="n"/>
       <c r="AG25" s="4" t="n"/>
       <c r="AH25" s="4" t="n"/>
-      <c r="AI25" s="4" t="n">
+      <c r="AI25" s="4" t="n"/>
+      <c r="AJ25" s="4" t="n"/>
+      <c r="AK25" s="4" t="n">
         <v>25.5</v>
       </c>
-      <c r="AJ25" s="4" t="n"/>
-      <c r="AK25" s="4" t="n"/>
       <c r="AL25" s="4" t="n"/>
       <c r="AM25" s="4" t="n"/>
       <c r="AN25" s="4" t="n"/>
@@ -42404,10 +42414,10 @@
       <c r="P26" s="4" t="n"/>
       <c r="Q26" s="4" t="n"/>
       <c r="R26" s="4" t="n"/>
-      <c r="S26" s="4" t="n"/>
-      <c r="T26" s="4" t="n">
+      <c r="S26" s="4" t="n">
         <v>18.99</v>
       </c>
+      <c r="T26" s="4" t="n"/>
       <c r="U26" s="4" t="n"/>
       <c r="V26" s="4" t="n"/>
       <c r="W26" s="4" t="n"/>
@@ -42420,15 +42430,15 @@
       <c r="AB26" s="4" t="n">
         <v>18.95</v>
       </c>
-      <c r="AC26" s="4" t="n"/>
+      <c r="AC26" s="4" t="n">
+        <v>19.5</v>
+      </c>
       <c r="AD26" s="4" t="n"/>
-      <c r="AE26" s="4" t="n">
+      <c r="AE26" s="4" t="n"/>
+      <c r="AF26" s="4" t="n">
         <v>18.9</v>
       </c>
-      <c r="AF26" s="4" t="n"/>
-      <c r="AG26" s="4" t="n">
-        <v>19.5</v>
-      </c>
+      <c r="AG26" s="4" t="n"/>
       <c r="AH26" s="4" t="n"/>
       <c r="AI26" s="4" t="n"/>
       <c r="AJ26" s="4" t="n"/>
@@ -42481,13 +42491,15 @@
       <c r="N27" s="4" t="n"/>
       <c r="O27" s="4" t="n"/>
       <c r="P27" s="4" t="n"/>
-      <c r="Q27" s="4" t="n">
-        <v>35.2</v>
-      </c>
+      <c r="Q27" s="4" t="n"/>
       <c r="R27" s="4" t="n"/>
       <c r="S27" s="4" t="n"/>
-      <c r="T27" s="4" t="n"/>
-      <c r="U27" s="4" t="n"/>
+      <c r="T27" s="4" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="U27" s="4" t="n">
+        <v>34.19</v>
+      </c>
       <c r="V27" s="4" t="n">
         <v>33.9</v>
       </c>
@@ -42558,10 +42570,10 @@
       <c r="P28" s="4" t="n"/>
       <c r="Q28" s="4" t="n"/>
       <c r="R28" s="4" t="n"/>
-      <c r="S28" s="4" t="n"/>
-      <c r="T28" s="4" t="n">
+      <c r="S28" s="4" t="n">
         <v>33.5</v>
       </c>
+      <c r="T28" s="4" t="n"/>
       <c r="U28" s="4" t="n"/>
       <c r="V28" s="4" t="n"/>
       <c r="W28" s="4" t="n"/>
@@ -42574,10 +42586,10 @@
       <c r="AB28" s="4" t="n">
         <v>33.19</v>
       </c>
-      <c r="AC28" s="4" t="n">
+      <c r="AC28" s="4" t="n"/>
+      <c r="AD28" s="4" t="n">
         <v>33.79</v>
       </c>
-      <c r="AD28" s="4" t="n"/>
       <c r="AE28" s="4" t="n"/>
       <c r="AF28" s="4" t="n"/>
       <c r="AG28" s="4" t="n"/>
@@ -42710,12 +42722,12 @@
       <c r="N30" s="4" t="n"/>
       <c r="O30" s="4" t="n"/>
       <c r="P30" s="4" t="n"/>
-      <c r="Q30" s="4" t="n">
-        <v>23.19</v>
-      </c>
+      <c r="Q30" s="4" t="n"/>
       <c r="R30" s="4" t="n"/>
       <c r="S30" s="4" t="n"/>
-      <c r="T30" s="4" t="n"/>
+      <c r="T30" s="4" t="n">
+        <v>23.19</v>
+      </c>
       <c r="U30" s="4" t="n"/>
       <c r="V30" s="4" t="n"/>
       <c r="W30" s="4" t="n"/>
@@ -42779,12 +42791,12 @@
       <c r="N31" s="4" t="n"/>
       <c r="O31" s="4" t="n"/>
       <c r="P31" s="4" t="n"/>
-      <c r="Q31" s="4" t="n">
-        <v>19.19</v>
-      </c>
+      <c r="Q31" s="4" t="n"/>
       <c r="R31" s="4" t="n"/>
       <c r="S31" s="4" t="n"/>
-      <c r="T31" s="4" t="n"/>
+      <c r="T31" s="4" t="n">
+        <v>19.19</v>
+      </c>
       <c r="U31" s="4" t="n"/>
       <c r="V31" s="4" t="n"/>
       <c r="W31" s="4" t="n"/>
@@ -42796,10 +42808,10 @@
       <c r="AC31" s="4" t="n"/>
       <c r="AD31" s="4" t="n"/>
       <c r="AE31" s="4" t="n"/>
-      <c r="AF31" s="4" t="n">
+      <c r="AF31" s="4" t="n"/>
+      <c r="AG31" s="4" t="n">
         <v>19.45</v>
       </c>
-      <c r="AG31" s="4" t="n"/>
       <c r="AH31" s="4" t="n"/>
       <c r="AI31" s="4" t="n"/>
       <c r="AJ31" s="4" t="n"/>
@@ -42856,12 +42868,12 @@
       <c r="N32" s="4" t="n"/>
       <c r="O32" s="4" t="n"/>
       <c r="P32" s="4" t="n"/>
-      <c r="Q32" s="4" t="n">
-        <v>29.4</v>
-      </c>
+      <c r="Q32" s="4" t="n"/>
       <c r="R32" s="4" t="n"/>
       <c r="S32" s="4" t="n"/>
-      <c r="T32" s="4" t="n"/>
+      <c r="T32" s="4" t="n">
+        <v>29.4</v>
+      </c>
       <c r="U32" s="4" t="n"/>
       <c r="V32" s="4" t="n"/>
       <c r="W32" s="4" t="n"/>
@@ -42870,19 +42882,19 @@
       <c r="Z32" s="4" t="n"/>
       <c r="AA32" s="4" t="n"/>
       <c r="AB32" s="4" t="n"/>
-      <c r="AC32" s="4" t="n"/>
+      <c r="AC32" s="4" t="n">
+        <v>29.3</v>
+      </c>
       <c r="AD32" s="4" t="n"/>
       <c r="AE32" s="4" t="n"/>
       <c r="AF32" s="4" t="n"/>
-      <c r="AG32" s="4" t="n">
-        <v>29.3</v>
-      </c>
+      <c r="AG32" s="4" t="n"/>
       <c r="AH32" s="4" t="n"/>
-      <c r="AI32" s="4" t="n">
+      <c r="AI32" s="4" t="n"/>
+      <c r="AJ32" s="4" t="n"/>
+      <c r="AK32" s="4" t="n">
         <v>29.6</v>
       </c>
-      <c r="AJ32" s="4" t="n"/>
-      <c r="AK32" s="4" t="n"/>
       <c r="AL32" s="4" t="n"/>
       <c r="AM32" s="4" t="n"/>
       <c r="AN32" s="4" t="n"/>
@@ -42937,12 +42949,12 @@
       <c r="N33" s="4" t="n"/>
       <c r="O33" s="4" t="n"/>
       <c r="P33" s="4" t="n"/>
-      <c r="Q33" s="4" t="n">
-        <v>19.99</v>
-      </c>
+      <c r="Q33" s="4" t="n"/>
       <c r="R33" s="4" t="n"/>
       <c r="S33" s="4" t="n"/>
-      <c r="T33" s="4" t="n"/>
+      <c r="T33" s="4" t="n">
+        <v>19.99</v>
+      </c>
       <c r="U33" s="4" t="n"/>
       <c r="V33" s="4" t="n"/>
       <c r="W33" s="4" t="n"/>
@@ -42954,15 +42966,15 @@
       <c r="AC33" s="4" t="n"/>
       <c r="AD33" s="4" t="n"/>
       <c r="AE33" s="4" t="n"/>
-      <c r="AF33" s="4" t="n">
+      <c r="AF33" s="4" t="n"/>
+      <c r="AG33" s="4" t="n">
         <v>20.4</v>
       </c>
-      <c r="AG33" s="4" t="n"/>
-      <c r="AH33" s="4" t="n">
+      <c r="AH33" s="4" t="n"/>
+      <c r="AI33" s="4" t="n"/>
+      <c r="AJ33" s="4" t="n">
         <v>20.5</v>
       </c>
-      <c r="AI33" s="4" t="n"/>
-      <c r="AJ33" s="4" t="n"/>
       <c r="AK33" s="4" t="n"/>
       <c r="AL33" s="4" t="n"/>
       <c r="AM33" s="4" t="n"/>
@@ -43012,11 +43024,13 @@
       <c r="N34" s="4" t="n"/>
       <c r="O34" s="4" t="n"/>
       <c r="P34" s="4" t="n"/>
-      <c r="Q34" s="4" t="n"/>
-      <c r="R34" s="4" t="n"/>
-      <c r="S34" s="4" t="n">
-        <v>36.79</v>
-      </c>
+      <c r="Q34" s="4" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="R34" s="4" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="S34" s="4" t="n"/>
       <c r="T34" s="4" t="n"/>
       <c r="U34" s="4" t="n"/>
       <c r="V34" s="4" t="n"/>
@@ -43081,12 +43095,12 @@
       <c r="N35" s="4" t="n"/>
       <c r="O35" s="4" t="n"/>
       <c r="P35" s="4" t="n"/>
-      <c r="Q35" s="4" t="n">
-        <v>23.7</v>
-      </c>
+      <c r="Q35" s="4" t="n"/>
       <c r="R35" s="4" t="n"/>
       <c r="S35" s="4" t="n"/>
-      <c r="T35" s="4" t="n"/>
+      <c r="T35" s="4" t="n">
+        <v>23.7</v>
+      </c>
       <c r="U35" s="4" t="n"/>
       <c r="V35" s="4" t="n"/>
       <c r="W35" s="4" t="n"/>
@@ -43100,11 +43114,11 @@
       <c r="AE35" s="4" t="n"/>
       <c r="AF35" s="4" t="n"/>
       <c r="AG35" s="4" t="n"/>
-      <c r="AH35" s="4" t="n">
+      <c r="AH35" s="4" t="n"/>
+      <c r="AI35" s="4" t="n"/>
+      <c r="AJ35" s="4" t="n">
         <v>24.09</v>
       </c>
-      <c r="AI35" s="4" t="n"/>
-      <c r="AJ35" s="4" t="n"/>
       <c r="AK35" s="4" t="n"/>
       <c r="AL35" s="4" t="n"/>
       <c r="AM35" s="4" t="n"/>
@@ -43126,7 +43140,9 @@
       <c r="BA35" s="4" t="n"/>
       <c r="BB35" s="4" t="n"/>
       <c r="BC35" s="4" t="n"/>
-      <c r="BD35" s="4" t="n"/>
+      <c r="BD35" s="4" t="n">
+        <v>24.9</v>
+      </c>
       <c r="BE35" s="4" t="n"/>
       <c r="BF35" s="4" t="n"/>
       <c r="BG35" s="4" t="n"/>
@@ -43258,7 +43274,9 @@
       <c r="AE37" s="4" t="n"/>
       <c r="AF37" s="4" t="n"/>
       <c r="AG37" s="4" t="n"/>
-      <c r="AH37" s="4" t="n"/>
+      <c r="AH37" s="4" t="n">
+        <v>23.67</v>
+      </c>
       <c r="AI37" s="4" t="n"/>
       <c r="AJ37" s="4" t="n"/>
       <c r="AK37" s="4" t="n"/>
@@ -43321,21 +43339,21 @@
       <c r="AA38" s="4" t="n"/>
       <c r="AB38" s="4" t="n"/>
       <c r="AC38" s="4" t="n"/>
-      <c r="AD38" s="4" t="n">
+      <c r="AD38" s="4" t="n"/>
+      <c r="AE38" s="4" t="n">
         <v>21.1</v>
       </c>
-      <c r="AE38" s="4" t="n"/>
       <c r="AF38" s="4" t="n"/>
       <c r="AG38" s="4" t="n"/>
-      <c r="AH38" s="4" t="n"/>
-      <c r="AI38" s="4" t="n">
+      <c r="AH38" s="4" t="n">
+        <v>21.59</v>
+      </c>
+      <c r="AI38" s="4" t="n"/>
+      <c r="AJ38" s="4" t="n"/>
+      <c r="AK38" s="4" t="n">
         <v>21.99</v>
       </c>
-      <c r="AJ38" s="4" t="n"/>
-      <c r="AK38" s="4" t="n"/>
-      <c r="AL38" s="4" t="n">
-        <v>21.59</v>
-      </c>
+      <c r="AL38" s="4" t="n"/>
       <c r="AM38" s="4" t="n"/>
       <c r="AN38" s="4" t="n"/>
       <c r="AO38" s="4" t="n"/>
@@ -43383,10 +43401,10 @@
       <c r="P39" s="4" t="n"/>
       <c r="Q39" s="4" t="n"/>
       <c r="R39" s="4" t="n"/>
-      <c r="S39" s="4" t="n"/>
-      <c r="T39" s="4" t="n">
+      <c r="S39" s="4" t="n">
         <v>29.9</v>
       </c>
+      <c r="T39" s="4" t="n"/>
       <c r="U39" s="4" t="n"/>
       <c r="V39" s="4" t="n"/>
       <c r="W39" s="4" t="n"/>
@@ -43402,13 +43420,13 @@
       <c r="AE39" s="4" t="n"/>
       <c r="AF39" s="4" t="n"/>
       <c r="AG39" s="4" t="n"/>
-      <c r="AH39" s="4" t="n"/>
+      <c r="AH39" s="4" t="n">
+        <v>30.89</v>
+      </c>
       <c r="AI39" s="4" t="n"/>
       <c r="AJ39" s="4" t="n"/>
       <c r="AK39" s="4" t="n"/>
-      <c r="AL39" s="4" t="n">
-        <v>30.89</v>
-      </c>
+      <c r="AL39" s="4" t="n"/>
       <c r="AM39" s="4" t="n"/>
       <c r="AN39" s="4" t="n"/>
       <c r="AO39" s="4" t="n"/>
@@ -43466,12 +43484,12 @@
       <c r="N40" s="4" t="n"/>
       <c r="O40" s="4" t="n"/>
       <c r="P40" s="4" t="n"/>
-      <c r="Q40" s="4" t="n">
-        <v>35.2</v>
-      </c>
+      <c r="Q40" s="4" t="n"/>
       <c r="R40" s="4" t="n"/>
       <c r="S40" s="4" t="n"/>
-      <c r="T40" s="4" t="n"/>
+      <c r="T40" s="4" t="n">
+        <v>35.2</v>
+      </c>
       <c r="U40" s="4" t="n"/>
       <c r="V40" s="4" t="n"/>
       <c r="W40" s="4" t="n"/>
@@ -43483,11 +43501,13 @@
       <c r="AC40" s="4" t="n"/>
       <c r="AD40" s="4" t="n"/>
       <c r="AE40" s="4" t="n"/>
-      <c r="AF40" s="4" t="n">
+      <c r="AF40" s="4" t="n"/>
+      <c r="AG40" s="4" t="n">
         <v>35.4</v>
       </c>
-      <c r="AG40" s="4" t="n"/>
-      <c r="AH40" s="4" t="n"/>
+      <c r="AH40" s="4" t="n">
+        <v>35.86</v>
+      </c>
       <c r="AI40" s="4" t="n"/>
       <c r="AJ40" s="4" t="n"/>
       <c r="AK40" s="4" t="n"/>
@@ -43620,13 +43640,15 @@
       <c r="N42" s="4" t="n"/>
       <c r="O42" s="4" t="n"/>
       <c r="P42" s="4" t="n"/>
-      <c r="Q42" s="4" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="Q42" s="4" t="n"/>
       <c r="R42" s="4" t="n"/>
       <c r="S42" s="4" t="n"/>
-      <c r="T42" s="4" t="n"/>
-      <c r="U42" s="4" t="n"/>
+      <c r="T42" s="4" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="U42" s="4" t="n">
+        <v>23.3</v>
+      </c>
       <c r="V42" s="4" t="n"/>
       <c r="W42" s="4" t="n"/>
       <c r="X42" s="4" t="n"/>
@@ -43636,13 +43658,13 @@
       <c r="AB42" s="4" t="n">
         <v>22.3</v>
       </c>
-      <c r="AC42" s="4" t="n"/>
+      <c r="AC42" s="4" t="n">
+        <v>22.8</v>
+      </c>
       <c r="AD42" s="4" t="n"/>
       <c r="AE42" s="4" t="n"/>
       <c r="AF42" s="4" t="n"/>
-      <c r="AG42" s="4" t="n">
-        <v>22.8</v>
-      </c>
+      <c r="AG42" s="4" t="n"/>
       <c r="AH42" s="4" t="n"/>
       <c r="AI42" s="4" t="n"/>
       <c r="AJ42" s="4" t="n"/>
@@ -43766,12 +43788,12 @@
       <c r="N44" s="4" t="n"/>
       <c r="O44" s="4" t="n"/>
       <c r="P44" s="4" t="n"/>
-      <c r="Q44" s="4" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="Q44" s="4" t="n"/>
       <c r="R44" s="4" t="n"/>
       <c r="S44" s="4" t="n"/>
-      <c r="T44" s="4" t="n"/>
+      <c r="T44" s="4" t="n">
+        <v>22.5</v>
+      </c>
       <c r="U44" s="4" t="n"/>
       <c r="V44" s="4" t="n"/>
       <c r="W44" s="4" t="n"/>
@@ -43783,10 +43805,10 @@
       <c r="AC44" s="4" t="n"/>
       <c r="AD44" s="4" t="n"/>
       <c r="AE44" s="4" t="n"/>
-      <c r="AF44" s="4" t="n">
+      <c r="AF44" s="4" t="n"/>
+      <c r="AG44" s="4" t="n">
         <v>22.6</v>
       </c>
-      <c r="AG44" s="4" t="n"/>
       <c r="AH44" s="4" t="n"/>
       <c r="AI44" s="4" t="n"/>
       <c r="AJ44" s="4" t="n"/>
@@ -43855,9 +43877,11 @@
       <c r="R45" s="4" t="n"/>
       <c r="S45" s="4" t="n"/>
       <c r="T45" s="4" t="n"/>
-      <c r="U45" s="4" t="n"/>
+      <c r="U45" s="4" t="n">
+        <v>41.59</v>
+      </c>
       <c r="V45" s="4" t="n">
-        <v>40.3</v>
+        <v>40.99</v>
       </c>
       <c r="W45" s="4" t="n"/>
       <c r="X45" s="4" t="n"/>
@@ -44083,13 +44107,13 @@
       <c r="O48" s="4" t="n"/>
       <c r="P48" s="4" t="n"/>
       <c r="Q48" s="4" t="n"/>
-      <c r="R48" s="4" t="n"/>
+      <c r="R48" s="4" t="n">
+        <v>25.79</v>
+      </c>
       <c r="S48" s="4" t="n">
-        <v>25.79</v>
-      </c>
-      <c r="T48" s="4" t="n">
         <v>25.2</v>
       </c>
+      <c r="T48" s="4" t="n"/>
       <c r="U48" s="4" t="n"/>
       <c r="V48" s="4" t="n"/>
       <c r="W48" s="4" t="n"/>
@@ -44098,13 +44122,13 @@
       <c r="Z48" s="4" t="n"/>
       <c r="AA48" s="4" t="n"/>
       <c r="AB48" s="4" t="n"/>
-      <c r="AC48" s="4" t="n"/>
+      <c r="AC48" s="4" t="n">
+        <v>25.8</v>
+      </c>
       <c r="AD48" s="4" t="n"/>
       <c r="AE48" s="4" t="n"/>
       <c r="AF48" s="4" t="n"/>
-      <c r="AG48" s="4" t="n">
-        <v>25.8</v>
-      </c>
+      <c r="AG48" s="4" t="n"/>
       <c r="AH48" s="4" t="n"/>
       <c r="AI48" s="4" t="n"/>
       <c r="AJ48" s="4" t="n"/>
@@ -44161,12 +44185,12 @@
       <c r="N49" s="4" t="n"/>
       <c r="O49" s="4" t="n"/>
       <c r="P49" s="4" t="n"/>
-      <c r="Q49" s="4" t="n">
-        <v>30.79</v>
-      </c>
+      <c r="Q49" s="4" t="n"/>
       <c r="R49" s="4" t="n"/>
       <c r="S49" s="4" t="n"/>
-      <c r="T49" s="4" t="n"/>
+      <c r="T49" s="4" t="n">
+        <v>30.79</v>
+      </c>
       <c r="U49" s="4" t="n"/>
       <c r="V49" s="4" t="n"/>
       <c r="W49" s="4" t="n"/>
@@ -44202,12 +44226,12 @@
       <c r="BA49" s="4" t="n"/>
       <c r="BB49" s="4" t="n"/>
       <c r="BC49" s="4" t="n"/>
-      <c r="BD49" s="4" t="n"/>
+      <c r="BD49" s="4" t="n">
+        <v>31.69</v>
+      </c>
       <c r="BE49" s="4" t="n"/>
       <c r="BF49" s="4" t="n"/>
-      <c r="BG49" s="4" t="n">
-        <v>31.69</v>
-      </c>
+      <c r="BG49" s="4" t="n"/>
       <c r="BH49" s="4" t="n"/>
       <c r="BI49" s="4" t="n"/>
     </row>
@@ -44232,12 +44256,12 @@
       <c r="N50" s="4" t="n"/>
       <c r="O50" s="4" t="n"/>
       <c r="P50" s="4" t="n"/>
-      <c r="Q50" s="4" t="n">
-        <v>26.67</v>
-      </c>
+      <c r="Q50" s="4" t="n"/>
       <c r="R50" s="4" t="n"/>
       <c r="S50" s="4" t="n"/>
-      <c r="T50" s="4" t="n"/>
+      <c r="T50" s="4" t="n">
+        <v>26.67</v>
+      </c>
       <c r="U50" s="4" t="n"/>
       <c r="V50" s="4" t="n"/>
       <c r="W50" s="4" t="n"/>
@@ -44301,12 +44325,12 @@
       <c r="N51" s="4" t="n"/>
       <c r="O51" s="4" t="n"/>
       <c r="P51" s="4" t="n"/>
-      <c r="Q51" s="4" t="n">
-        <v>24.5</v>
-      </c>
+      <c r="Q51" s="4" t="n"/>
       <c r="R51" s="4" t="n"/>
       <c r="S51" s="4" t="n"/>
-      <c r="T51" s="4" t="n"/>
+      <c r="T51" s="4" t="n">
+        <v>24.5</v>
+      </c>
       <c r="U51" s="4" t="n"/>
       <c r="V51" s="4" t="n"/>
       <c r="W51" s="4" t="n"/>
@@ -44344,10 +44368,10 @@
       <c r="BC51" s="4" t="n"/>
       <c r="BD51" s="4" t="n"/>
       <c r="BE51" s="4" t="n"/>
-      <c r="BF51" s="4" t="n">
+      <c r="BF51" s="4" t="n"/>
+      <c r="BG51" s="4" t="n">
         <v>24.95</v>
       </c>
-      <c r="BG51" s="4" t="n"/>
       <c r="BH51" s="4" t="n"/>
       <c r="BI51" s="4" t="n"/>
     </row>
@@ -44378,7 +44402,9 @@
       <c r="P52" s="4" t="n">
         <v>32.3</v>
       </c>
-      <c r="Q52" s="4" t="n"/>
+      <c r="Q52" s="4" t="n">
+        <v>34.1</v>
+      </c>
       <c r="R52" s="4" t="n"/>
       <c r="S52" s="4" t="n"/>
       <c r="T52" s="4" t="n"/>
@@ -44599,12 +44625,12 @@
       <c r="N55" s="4" t="n"/>
       <c r="O55" s="4" t="n"/>
       <c r="P55" s="4" t="n"/>
-      <c r="Q55" s="4" t="n">
-        <v>32.99</v>
-      </c>
+      <c r="Q55" s="4" t="n"/>
       <c r="R55" s="4" t="n"/>
       <c r="S55" s="4" t="n"/>
-      <c r="T55" s="4" t="n"/>
+      <c r="T55" s="4" t="n">
+        <v>32.99</v>
+      </c>
       <c r="U55" s="4" t="n"/>
       <c r="V55" s="4" t="n"/>
       <c r="W55" s="4" t="n"/>
@@ -44616,10 +44642,10 @@
       <c r="AC55" s="4" t="n"/>
       <c r="AD55" s="4" t="n"/>
       <c r="AE55" s="4" t="n"/>
-      <c r="AF55" s="4" t="n">
+      <c r="AF55" s="4" t="n"/>
+      <c r="AG55" s="4" t="n">
         <v>33.29</v>
       </c>
-      <c r="AG55" s="4" t="n"/>
       <c r="AH55" s="4" t="n"/>
       <c r="AI55" s="4" t="n"/>
       <c r="AJ55" s="4" t="n"/>
@@ -44759,7 +44785,9 @@
       <c r="R57" s="4" t="n"/>
       <c r="S57" s="4" t="n"/>
       <c r="T57" s="4" t="n"/>
-      <c r="U57" s="4" t="n"/>
+      <c r="U57" s="4" t="n">
+        <v>37.29</v>
+      </c>
       <c r="V57" s="4" t="n">
         <v>36.94</v>
       </c>
@@ -44830,7 +44858,9 @@
       <c r="N58" s="4" t="n"/>
       <c r="O58" s="4" t="n"/>
       <c r="P58" s="4" t="n"/>
-      <c r="Q58" s="4" t="n"/>
+      <c r="Q58" s="4" t="n">
+        <v>26.8</v>
+      </c>
       <c r="R58" s="4" t="n"/>
       <c r="S58" s="4" t="n"/>
       <c r="T58" s="4" t="n"/>
@@ -44901,12 +44931,12 @@
       <c r="N59" s="4" t="n"/>
       <c r="O59" s="4" t="n"/>
       <c r="P59" s="4" t="n"/>
-      <c r="Q59" s="4" t="n">
-        <v>21.35</v>
-      </c>
+      <c r="Q59" s="4" t="n"/>
       <c r="R59" s="4" t="n"/>
       <c r="S59" s="4" t="n"/>
-      <c r="T59" s="4" t="n"/>
+      <c r="T59" s="4" t="n">
+        <v>21.35</v>
+      </c>
       <c r="U59" s="4" t="n"/>
       <c r="V59" s="4" t="n"/>
       <c r="W59" s="4" t="n"/>
@@ -44921,13 +44951,13 @@
       <c r="AF59" s="4" t="n"/>
       <c r="AG59" s="4" t="n"/>
       <c r="AH59" s="4" t="n"/>
-      <c r="AI59" s="4" t="n"/>
+      <c r="AI59" s="4" t="n">
+        <v>21.45</v>
+      </c>
       <c r="AJ59" s="4" t="n"/>
       <c r="AK59" s="4" t="n"/>
       <c r="AL59" s="4" t="n"/>
-      <c r="AM59" s="4" t="n">
-        <v>21.45</v>
-      </c>
+      <c r="AM59" s="4" t="n"/>
       <c r="AN59" s="4" t="n"/>
       <c r="AO59" s="4" t="n"/>
       <c r="AP59" s="4" t="n"/>
@@ -45059,12 +45089,12 @@
       <c r="N61" s="4" t="n"/>
       <c r="O61" s="4" t="n"/>
       <c r="P61" s="4" t="n"/>
-      <c r="Q61" s="4" t="n">
-        <v>21.89</v>
-      </c>
+      <c r="Q61" s="4" t="n"/>
       <c r="R61" s="4" t="n"/>
       <c r="S61" s="4" t="n"/>
-      <c r="T61" s="4" t="n"/>
+      <c r="T61" s="4" t="n">
+        <v>21.89</v>
+      </c>
       <c r="U61" s="4" t="n"/>
       <c r="V61" s="4" t="n"/>
       <c r="W61" s="4" t="n"/>
@@ -45135,12 +45165,14 @@
       <c r="O62" s="4" t="n"/>
       <c r="P62" s="4" t="n"/>
       <c r="Q62" s="4" t="n">
+        <v>32.45</v>
+      </c>
+      <c r="R62" s="4" t="n"/>
+      <c r="S62" s="4" t="n">
+        <v>31.29</v>
+      </c>
+      <c r="T62" s="4" t="n">
         <v>31.9</v>
-      </c>
-      <c r="R62" s="4" t="n"/>
-      <c r="S62" s="4" t="n"/>
-      <c r="T62" s="4" t="n">
-        <v>31.29</v>
       </c>
       <c r="U62" s="4" t="n"/>
       <c r="V62" s="4" t="n"/>
@@ -45236,11 +45268,11 @@
       <c r="AE63" s="4" t="n"/>
       <c r="AF63" s="4" t="n"/>
       <c r="AG63" s="4" t="n"/>
-      <c r="AH63" s="4" t="n">
+      <c r="AH63" s="4" t="n"/>
+      <c r="AI63" s="4" t="n"/>
+      <c r="AJ63" s="4" t="n">
         <v>25.1</v>
       </c>
-      <c r="AI63" s="4" t="n"/>
-      <c r="AJ63" s="4" t="n"/>
       <c r="AK63" s="4" t="n"/>
       <c r="AL63" s="4" t="n"/>
       <c r="AM63" s="4" t="n"/>
@@ -45294,12 +45326,12 @@
       <c r="N64" s="4" t="n"/>
       <c r="O64" s="4" t="n"/>
       <c r="P64" s="4" t="n"/>
-      <c r="Q64" s="4" t="n">
-        <v>24.6</v>
-      </c>
+      <c r="Q64" s="4" t="n"/>
       <c r="R64" s="4" t="n"/>
       <c r="S64" s="4" t="n"/>
-      <c r="T64" s="4" t="n"/>
+      <c r="T64" s="4" t="n">
+        <v>24.6</v>
+      </c>
       <c r="U64" s="4" t="n"/>
       <c r="V64" s="4" t="n"/>
       <c r="W64" s="4" t="n"/>
@@ -45511,9 +45543,13 @@
       <c r="N67" s="4" t="n"/>
       <c r="O67" s="4" t="n"/>
       <c r="P67" s="4" t="n"/>
-      <c r="Q67" s="4" t="n"/>
+      <c r="Q67" s="4" t="n">
+        <v>18.9</v>
+      </c>
       <c r="R67" s="4" t="n"/>
-      <c r="S67" s="4" t="n"/>
+      <c r="S67" s="4" t="n">
+        <v>18.49</v>
+      </c>
       <c r="T67" s="4" t="n"/>
       <c r="U67" s="4" t="n"/>
       <c r="V67" s="4" t="n"/>
@@ -45529,14 +45565,14 @@
       <c r="AF67" s="4" t="n"/>
       <c r="AG67" s="4" t="n"/>
       <c r="AH67" s="4" t="n"/>
-      <c r="AI67" s="4" t="n">
+      <c r="AI67" s="4" t="n"/>
+      <c r="AJ67" s="4" t="n"/>
+      <c r="AK67" s="4" t="n">
         <v>18.9</v>
       </c>
-      <c r="AJ67" s="4" t="n">
+      <c r="AL67" s="4" t="n">
         <v>18.39</v>
       </c>
-      <c r="AK67" s="4" t="n"/>
-      <c r="AL67" s="4" t="n"/>
       <c r="AM67" s="4" t="n"/>
       <c r="AN67" s="4" t="n"/>
       <c r="AO67" s="4" t="n"/>
@@ -45588,10 +45624,10 @@
       <c r="P68" s="4" t="n"/>
       <c r="Q68" s="4" t="n"/>
       <c r="R68" s="4" t="n"/>
-      <c r="S68" s="4" t="n"/>
-      <c r="T68" s="4" t="n">
+      <c r="S68" s="4" t="n">
         <v>28.1</v>
       </c>
+      <c r="T68" s="4" t="n"/>
       <c r="U68" s="4" t="n"/>
       <c r="V68" s="4" t="n"/>
       <c r="W68" s="4" t="n"/>
@@ -45744,18 +45780,18 @@
       <c r="AB70" s="4" t="n"/>
       <c r="AC70" s="4" t="n"/>
       <c r="AD70" s="4" t="n"/>
-      <c r="AE70" s="4" t="n">
+      <c r="AE70" s="4" t="n"/>
+      <c r="AF70" s="4" t="n">
         <v>21.19</v>
       </c>
-      <c r="AF70" s="4" t="n"/>
       <c r="AG70" s="4" t="n"/>
-      <c r="AH70" s="4" t="n"/>
+      <c r="AH70" s="4" t="n">
+        <v>21.53</v>
+      </c>
       <c r="AI70" s="4" t="n"/>
       <c r="AJ70" s="4" t="n"/>
       <c r="AK70" s="4" t="n"/>
-      <c r="AL70" s="4" t="n">
-        <v>21.53</v>
-      </c>
+      <c r="AL70" s="4" t="n"/>
       <c r="AM70" s="4" t="n"/>
       <c r="AN70" s="4" t="n"/>
       <c r="AO70" s="4" t="n"/>
@@ -45872,12 +45908,12 @@
       <c r="N72" s="4" t="n"/>
       <c r="O72" s="4" t="n"/>
       <c r="P72" s="4" t="n"/>
-      <c r="Q72" s="4" t="n">
-        <v>26.15</v>
-      </c>
+      <c r="Q72" s="4" t="n"/>
       <c r="R72" s="4" t="n"/>
       <c r="S72" s="4" t="n"/>
-      <c r="T72" s="4" t="n"/>
+      <c r="T72" s="4" t="n">
+        <v>26.15</v>
+      </c>
       <c r="U72" s="4" t="n"/>
       <c r="V72" s="4" t="n"/>
       <c r="W72" s="4" t="n"/>
@@ -45889,11 +45925,13 @@
       <c r="AC72" s="4" t="n"/>
       <c r="AD72" s="4" t="n"/>
       <c r="AE72" s="4" t="n"/>
-      <c r="AF72" s="4" t="n">
+      <c r="AF72" s="4" t="n"/>
+      <c r="AG72" s="4" t="n">
         <v>26.25</v>
       </c>
-      <c r="AG72" s="4" t="n"/>
-      <c r="AH72" s="4" t="n"/>
+      <c r="AH72" s="4" t="n">
+        <v>26.49</v>
+      </c>
       <c r="AI72" s="4" t="n"/>
       <c r="AJ72" s="4" t="n"/>
       <c r="AK72" s="4" t="n"/>
@@ -45949,12 +45987,12 @@
       <c r="N73" s="4" t="n"/>
       <c r="O73" s="4" t="n"/>
       <c r="P73" s="4" t="n"/>
-      <c r="Q73" s="4" t="n">
-        <v>19.4</v>
-      </c>
+      <c r="Q73" s="4" t="n"/>
       <c r="R73" s="4" t="n"/>
       <c r="S73" s="4" t="n"/>
-      <c r="T73" s="4" t="n"/>
+      <c r="T73" s="4" t="n">
+        <v>19.4</v>
+      </c>
       <c r="U73" s="4" t="n"/>
       <c r="V73" s="4" t="n"/>
       <c r="W73" s="4" t="n"/>
@@ -45966,15 +46004,17 @@
       <c r="AC73" s="4" t="n"/>
       <c r="AD73" s="4" t="n"/>
       <c r="AE73" s="4" t="n"/>
-      <c r="AF73" s="4" t="n">
+      <c r="AF73" s="4" t="n"/>
+      <c r="AG73" s="4" t="n">
         <v>19.5</v>
       </c>
-      <c r="AG73" s="4" t="n"/>
       <c r="AH73" s="4" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="AI73" s="4" t="n"/>
+      <c r="AJ73" s="4" t="n">
         <v>19.6</v>
       </c>
-      <c r="AI73" s="4" t="n"/>
-      <c r="AJ73" s="4" t="n"/>
       <c r="AK73" s="4" t="n"/>
       <c r="AL73" s="4" t="n"/>
       <c r="AM73" s="4" t="n"/>
@@ -46030,12 +46070,12 @@
       <c r="P74" s="4" t="n"/>
       <c r="Q74" s="4" t="n"/>
       <c r="R74" s="4" t="n"/>
-      <c r="S74" s="4" t="n"/>
-      <c r="T74" s="4" t="n">
+      <c r="S74" s="4" t="n">
         <v>34.39</v>
       </c>
+      <c r="T74" s="4" t="n"/>
       <c r="U74" s="4" t="n">
-        <v>35.5</v>
+        <v>35.6</v>
       </c>
       <c r="V74" s="4" t="n">
         <v>35.35</v>
@@ -46103,10 +46143,10 @@
       <c r="P75" s="4" t="n"/>
       <c r="Q75" s="4" t="n"/>
       <c r="R75" s="4" t="n"/>
-      <c r="S75" s="4" t="n"/>
-      <c r="T75" s="4" t="n">
+      <c r="S75" s="4" t="n">
         <v>27.1</v>
       </c>
+      <c r="T75" s="4" t="n"/>
       <c r="U75" s="4" t="n"/>
       <c r="V75" s="4" t="n"/>
       <c r="W75" s="4" t="n"/>
@@ -46123,13 +46163,13 @@
       <c r="AB75" s="4" t="n">
         <v>27.15</v>
       </c>
-      <c r="AC75" s="4" t="n"/>
+      <c r="AC75" s="4" t="n">
+        <v>27.5</v>
+      </c>
       <c r="AD75" s="4" t="n"/>
       <c r="AE75" s="4" t="n"/>
       <c r="AF75" s="4" t="n"/>
-      <c r="AG75" s="4" t="n">
-        <v>27.5</v>
-      </c>
+      <c r="AG75" s="4" t="n"/>
       <c r="AH75" s="4" t="n"/>
       <c r="AI75" s="4" t="n"/>
       <c r="AJ75" s="4" t="n"/>
@@ -46180,12 +46220,12 @@
       <c r="N76" s="4" t="n"/>
       <c r="O76" s="4" t="n"/>
       <c r="P76" s="4" t="n"/>
-      <c r="Q76" s="4" t="n">
-        <v>16.99</v>
-      </c>
+      <c r="Q76" s="4" t="n"/>
       <c r="R76" s="4" t="n"/>
       <c r="S76" s="4" t="n"/>
-      <c r="T76" s="4" t="n"/>
+      <c r="T76" s="4" t="n">
+        <v>16.99</v>
+      </c>
       <c r="U76" s="4" t="n"/>
       <c r="V76" s="4" t="n"/>
       <c r="W76" s="4" t="n"/>
@@ -46197,15 +46237,15 @@
       <c r="AC76" s="4" t="n"/>
       <c r="AD76" s="4" t="n"/>
       <c r="AE76" s="4" t="n"/>
-      <c r="AF76" s="4" t="n">
+      <c r="AF76" s="4" t="n"/>
+      <c r="AG76" s="4" t="n">
         <v>17.4</v>
       </c>
-      <c r="AG76" s="4" t="n"/>
-      <c r="AH76" s="4" t="n">
+      <c r="AH76" s="4" t="n"/>
+      <c r="AI76" s="4" t="n"/>
+      <c r="AJ76" s="4" t="n">
         <v>17.45</v>
       </c>
-      <c r="AI76" s="4" t="n"/>
-      <c r="AJ76" s="4" t="n"/>
       <c r="AK76" s="4" t="n"/>
       <c r="AL76" s="4" t="n"/>
       <c r="AM76" s="4" t="n"/>
@@ -46427,7 +46467,9 @@
       <c r="R79" s="4" t="n"/>
       <c r="S79" s="4" t="n"/>
       <c r="T79" s="4" t="n"/>
-      <c r="U79" s="4" t="n"/>
+      <c r="U79" s="4" t="n">
+        <v>24.29</v>
+      </c>
       <c r="V79" s="4" t="n"/>
       <c r="W79" s="4" t="n"/>
       <c r="X79" s="4" t="n"/>
@@ -46654,7 +46696,9 @@
       <c r="N82" s="4" t="n"/>
       <c r="O82" s="4" t="n"/>
       <c r="P82" s="4" t="n"/>
-      <c r="Q82" s="4" t="n"/>
+      <c r="Q82" s="4" t="n">
+        <v>57.7</v>
+      </c>
       <c r="R82" s="4" t="n"/>
       <c r="S82" s="4" t="n"/>
       <c r="T82" s="4" t="n"/>
@@ -46806,10 +46850,10 @@
       <c r="P84" s="4" t="n"/>
       <c r="Q84" s="4" t="n"/>
       <c r="R84" s="4" t="n"/>
-      <c r="S84" s="4" t="n"/>
-      <c r="T84" s="4" t="n">
+      <c r="S84" s="4" t="n">
         <v>27.6</v>
       </c>
+      <c r="T84" s="4" t="n"/>
       <c r="U84" s="4" t="n"/>
       <c r="V84" s="4" t="n"/>
       <c r="W84" s="4" t="n"/>
@@ -46818,10 +46862,10 @@
       <c r="Z84" s="4" t="n"/>
       <c r="AA84" s="4" t="n"/>
       <c r="AB84" s="4" t="n"/>
-      <c r="AC84" s="4" t="n">
+      <c r="AC84" s="4" t="n"/>
+      <c r="AD84" s="4" t="n">
         <v>29.43</v>
       </c>
-      <c r="AD84" s="4" t="n"/>
       <c r="AE84" s="4" t="n"/>
       <c r="AF84" s="4" t="n"/>
       <c r="AG84" s="4" t="n"/>
@@ -47038,24 +47082,24 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>速尾★4</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>速尾★5</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>速尾★6</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>9x8★6</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>速尾★4</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>速尾★5</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>速尾★6</t>
-        </is>
-      </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
           <t>ssc★1</t>
@@ -47098,59 +47142,59 @@
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
+          <t>狼崽★5</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
           <t>21c★1</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>21c★4</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>21c★6</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>万达★6</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>狼崽★5</t>
-        </is>
-      </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
+          <t>fp1★5</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>fp1★6</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
           <t>sgt★6</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>火山★5</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>法拉第★6</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>秋王★6</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>fp1★5</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>fp1★6</t>
-        </is>
-      </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>莫斯勒★1</t>
@@ -47233,22 +47277,22 @@
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
+          <t>英灵殿★6</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
           <t>ts900★6</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>风扇★5</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>cs★6</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>英灵殿★6</t>
         </is>
       </c>
       <c r="BH1" s="1" t="inlineStr">
@@ -47287,14 +47331,14 @@
       <c r="N2" s="4" t="n"/>
       <c r="O2" s="4" t="n"/>
       <c r="P2" s="4" t="n"/>
-      <c r="Q2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q2" s="4" t="n"/>
       <c r="R2" s="4" t="n"/>
       <c r="S2" s="4" t="n"/>
-      <c r="T2" s="4" t="n"/>
+      <c r="T2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U2" s="4" t="n"/>
       <c r="V2" s="4" t="n"/>
       <c r="W2" s="4" t="n"/>
@@ -47306,24 +47350,24 @@
       <c r="AC2" s="4" t="n"/>
       <c r="AD2" s="4" t="n"/>
       <c r="AE2" s="4" t="n"/>
-      <c r="AF2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AG2" s="4" t="n"/>
-      <c r="AH2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AI2" s="4" t="n"/>
-      <c r="AJ2" s="4" t="n"/>
-      <c r="AK2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AF2" s="4" t="n"/>
+      <c r="AG2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AH2" s="4" t="n"/>
+      <c r="AI2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AJ2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AK2" s="4" t="n"/>
       <c r="AL2" s="4" t="n"/>
       <c r="AM2" s="4" t="inlineStr">
         <is>
@@ -47388,20 +47432,28 @@
       <c r="P3" s="4" t="n"/>
       <c r="Q3" s="4" t="n"/>
       <c r="R3" s="4" t="n"/>
-      <c r="S3" s="4" t="n"/>
-      <c r="T3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U3" s="4" t="n"/>
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T3" s="4" t="n"/>
+      <c r="U3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="V3" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
       <c r="W3" s="4" t="n"/>
-      <c r="X3" s="4" t="n"/>
+      <c r="X3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="Y3" s="4" t="n"/>
       <c r="Z3" s="4" t="n"/>
       <c r="AA3" s="4" t="inlineStr">
@@ -47410,28 +47462,28 @@
         </is>
       </c>
       <c r="AB3" s="4" t="n"/>
-      <c r="AC3" s="4" t="n"/>
+      <c r="AC3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD3" s="4" t="n"/>
       <c r="AE3" s="4" t="n"/>
       <c r="AF3" s="4" t="n"/>
-      <c r="AG3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG3" s="4" t="n"/>
       <c r="AH3" s="4" t="n"/>
-      <c r="AI3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AJ3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK3" s="4" t="n"/>
-      <c r="AL3" s="4" t="n"/>
+      <c r="AI3" s="4" t="n"/>
+      <c r="AJ3" s="4" t="n"/>
+      <c r="AK3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AL3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AM3" s="4" t="n"/>
       <c r="AN3" s="4" t="n"/>
       <c r="AO3" s="4" t="inlineStr">
@@ -47495,12 +47547,12 @@
       <c r="P4" s="4" t="n"/>
       <c r="Q4" s="4" t="n"/>
       <c r="R4" s="4" t="n"/>
-      <c r="S4" s="4" t="n"/>
-      <c r="T4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T4" s="4" t="n"/>
       <c r="U4" s="4" t="n"/>
       <c r="V4" s="4" t="n"/>
       <c r="W4" s="4" t="n"/>
@@ -47517,23 +47569,23 @@
         </is>
       </c>
       <c r="AB4" s="4" t="n"/>
-      <c r="AC4" s="4" t="n"/>
+      <c r="AC4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD4" s="4" t="n"/>
       <c r="AE4" s="4" t="n"/>
       <c r="AF4" s="4" t="n"/>
-      <c r="AG4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG4" s="4" t="n"/>
       <c r="AH4" s="4" t="n"/>
-      <c r="AI4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AI4" s="4" t="n"/>
       <c r="AJ4" s="4" t="n"/>
-      <c r="AK4" s="4" t="n"/>
+      <c r="AK4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL4" s="4" t="n"/>
       <c r="AM4" s="4" t="n"/>
       <c r="AN4" s="4" t="n"/>
@@ -47592,13 +47644,13 @@
       <c r="N5" s="4" t="n"/>
       <c r="O5" s="4" t="n"/>
       <c r="P5" s="4" t="n"/>
-      <c r="Q5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q5" s="4" t="n"/>
       <c r="R5" s="4" t="n"/>
-      <c r="S5" s="4" t="n"/>
+      <c r="S5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="T5" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -47632,13 +47684,13 @@
         </is>
       </c>
       <c r="AJ5" s="4" t="n"/>
-      <c r="AK5" s="4" t="n"/>
+      <c r="AK5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL5" s="4" t="n"/>
-      <c r="AM5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AM5" s="4" t="n"/>
       <c r="AN5" s="4" t="n"/>
       <c r="AO5" s="4" t="n"/>
       <c r="AP5" s="4" t="n"/>
@@ -47691,14 +47743,14 @@
       <c r="N6" s="4" t="n"/>
       <c r="O6" s="4" t="n"/>
       <c r="P6" s="4" t="n"/>
-      <c r="Q6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q6" s="4" t="n"/>
       <c r="R6" s="4" t="n"/>
       <c r="S6" s="4" t="n"/>
-      <c r="T6" s="4" t="n"/>
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U6" s="4" t="n"/>
       <c r="V6" s="4" t="n"/>
       <c r="W6" s="4" t="n"/>
@@ -47710,26 +47762,26 @@
       <c r="AC6" s="4" t="n"/>
       <c r="AD6" s="4" t="n"/>
       <c r="AE6" s="4" t="n"/>
-      <c r="AF6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AG6" s="4" t="n"/>
-      <c r="AH6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AF6" s="4" t="n"/>
+      <c r="AG6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AH6" s="4" t="n"/>
       <c r="AI6" s="4" t="n"/>
-      <c r="AJ6" s="4" t="n"/>
-      <c r="AK6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AJ6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AK6" s="4" t="n"/>
       <c r="AL6" s="4" t="n"/>
-      <c r="AM6" s="4" t="n"/>
+      <c r="AM6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AN6" s="4" t="n"/>
       <c r="AO6" s="4" t="n"/>
       <c r="AP6" s="4" t="n"/>
@@ -47790,14 +47842,14 @@
       <c r="N7" s="4" t="n"/>
       <c r="O7" s="4" t="n"/>
       <c r="P7" s="4" t="n"/>
-      <c r="Q7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q7" s="4" t="n"/>
       <c r="R7" s="4" t="n"/>
       <c r="S7" s="4" t="n"/>
-      <c r="T7" s="4" t="n"/>
+      <c r="T7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U7" s="4" t="n"/>
       <c r="V7" s="4" t="n"/>
       <c r="W7" s="4" t="n"/>
@@ -47810,33 +47862,33 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AC7" s="4" t="n"/>
+      <c r="AC7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD7" s="4" t="n"/>
       <c r="AE7" s="4" t="n"/>
       <c r="AF7" s="4" t="n"/>
-      <c r="AG7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AH7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG7" s="4" t="n"/>
+      <c r="AH7" s="4" t="n"/>
       <c r="AI7" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AJ7" s="4" t="n"/>
-      <c r="AK7" s="4" t="n"/>
+      <c r="AJ7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AK7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL7" s="4" t="n"/>
-      <c r="AM7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AM7" s="4" t="n"/>
       <c r="AN7" s="4" t="n"/>
       <c r="AO7" s="4" t="inlineStr">
         <is>
@@ -47923,12 +47975,12 @@
       <c r="P8" s="4" t="n"/>
       <c r="Q8" s="4" t="n"/>
       <c r="R8" s="4" t="n"/>
-      <c r="S8" s="4" t="n"/>
-      <c r="T8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="S8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T8" s="4" t="n"/>
       <c r="U8" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -47941,23 +47993,23 @@
       <c r="Z8" s="4" t="n"/>
       <c r="AA8" s="4" t="n"/>
       <c r="AB8" s="4" t="n"/>
-      <c r="AC8" s="4" t="n"/>
+      <c r="AC8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD8" s="4" t="n"/>
       <c r="AE8" s="4" t="n"/>
       <c r="AF8" s="4" t="n"/>
-      <c r="AG8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG8" s="4" t="n"/>
       <c r="AH8" s="4" t="n"/>
-      <c r="AI8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AI8" s="4" t="n"/>
       <c r="AJ8" s="4" t="n"/>
-      <c r="AK8" s="4" t="n"/>
+      <c r="AK8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL8" s="4" t="n"/>
       <c r="AM8" s="4" t="n"/>
       <c r="AN8" s="4" t="inlineStr">
@@ -48021,13 +48073,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="R9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="R9" s="4" t="n"/>
       <c r="S9" s="4" t="n"/>
-      <c r="T9" s="4" t="n"/>
+      <c r="T9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U9" s="4" t="n"/>
       <c r="V9" s="4" t="n"/>
       <c r="W9" s="4" t="n"/>
@@ -48046,18 +48098,14 @@
       </c>
       <c r="AC9" s="4" t="n"/>
       <c r="AD9" s="4" t="n"/>
-      <c r="AE9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AF9" s="4" t="n"/>
+      <c r="AE9" s="4" t="n"/>
+      <c r="AF9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AG9" s="4" t="n"/>
-      <c r="AH9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AH9" s="4" t="n"/>
       <c r="AI9" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -48068,13 +48116,17 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AK9" s="4" t="n"/>
-      <c r="AL9" s="4" t="n"/>
-      <c r="AM9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AK9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AL9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AM9" s="4" t="n"/>
       <c r="AN9" s="4" t="n"/>
       <c r="AO9" s="4" t="n"/>
       <c r="AP9" s="4" t="n"/>
@@ -48091,12 +48143,12 @@
       <c r="BA9" s="4" t="n"/>
       <c r="BB9" s="4" t="n"/>
       <c r="BC9" s="4" t="n"/>
-      <c r="BD9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BE9" s="4" t="n"/>
+      <c r="BD9" s="4" t="n"/>
+      <c r="BE9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BF9" s="4" t="n"/>
       <c r="BG9" s="4" t="n"/>
       <c r="BH9" s="4" t="n"/>
@@ -48131,13 +48183,13 @@
       <c r="N10" s="4" t="n"/>
       <c r="O10" s="4" t="n"/>
       <c r="P10" s="4" t="n"/>
-      <c r="Q10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q10" s="4" t="n"/>
       <c r="R10" s="4" t="n"/>
-      <c r="S10" s="4" t="n"/>
+      <c r="S10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="T10" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -48161,30 +48213,30 @@
       </c>
       <c r="AC10" s="4" t="n"/>
       <c r="AD10" s="4" t="n"/>
-      <c r="AE10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AE10" s="4" t="n"/>
       <c r="AF10" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AG10" s="4" t="n"/>
+      <c r="AG10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AH10" s="4" t="n"/>
-      <c r="AI10" s="4" t="n"/>
-      <c r="AJ10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AL10" s="4" t="n"/>
+      <c r="AI10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AJ10" s="4" t="n"/>
+      <c r="AK10" s="4" t="n"/>
+      <c r="AL10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AM10" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -48266,23 +48318,23 @@
       <c r="Z11" s="4" t="n"/>
       <c r="AA11" s="4" t="n"/>
       <c r="AB11" s="4" t="n"/>
-      <c r="AC11" s="4" t="n"/>
+      <c r="AC11" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD11" s="4" t="n"/>
       <c r="AE11" s="4" t="n"/>
       <c r="AF11" s="4" t="n"/>
-      <c r="AG11" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG11" s="4" t="n"/>
       <c r="AH11" s="4" t="n"/>
-      <c r="AI11" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AI11" s="4" t="n"/>
       <c r="AJ11" s="4" t="n"/>
-      <c r="AK11" s="4" t="n"/>
+      <c r="AK11" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL11" s="4" t="n"/>
       <c r="AM11" s="4" t="n"/>
       <c r="AN11" s="4" t="inlineStr">
@@ -48342,12 +48394,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="R12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S12" s="4" t="n"/>
+      <c r="R12" s="4" t="n"/>
+      <c r="S12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="T12" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -48369,36 +48421,36 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AC12" s="4" t="n"/>
-      <c r="AD12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AC12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AD12" s="4" t="n"/>
       <c r="AE12" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AF12" s="4" t="n"/>
-      <c r="AG12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AF12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AG12" s="4" t="n"/>
       <c r="AH12" s="4" t="n"/>
-      <c r="AI12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AJ12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK12" s="4" t="n"/>
-      <c r="AL12" s="4" t="n"/>
+      <c r="AI12" s="4" t="n"/>
+      <c r="AJ12" s="4" t="n"/>
+      <c r="AK12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AL12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AM12" s="4" t="n"/>
       <c r="AN12" s="4" t="n"/>
       <c r="AO12" s="4" t="n"/>
@@ -48462,12 +48514,12 @@
       <c r="P13" s="4" t="n"/>
       <c r="Q13" s="4" t="n"/>
       <c r="R13" s="4" t="n"/>
-      <c r="S13" s="4" t="n"/>
-      <c r="T13" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="S13" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T13" s="4" t="n"/>
       <c r="U13" s="4" t="n"/>
       <c r="V13" s="4" t="n"/>
       <c r="W13" s="4" t="n"/>
@@ -48476,23 +48528,23 @@
       <c r="Z13" s="4" t="n"/>
       <c r="AA13" s="4" t="n"/>
       <c r="AB13" s="4" t="n"/>
-      <c r="AC13" s="4" t="n"/>
+      <c r="AC13" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD13" s="4" t="n"/>
       <c r="AE13" s="4" t="n"/>
       <c r="AF13" s="4" t="n"/>
-      <c r="AG13" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG13" s="4" t="n"/>
       <c r="AH13" s="4" t="n"/>
-      <c r="AI13" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AI13" s="4" t="n"/>
       <c r="AJ13" s="4" t="n"/>
-      <c r="AK13" s="4" t="n"/>
+      <c r="AK13" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL13" s="4" t="n"/>
       <c r="AM13" s="4" t="n"/>
       <c r="AN13" s="4" t="n"/>
@@ -48571,14 +48623,14 @@
       </c>
       <c r="O14" s="4" t="n"/>
       <c r="P14" s="4" t="n"/>
-      <c r="Q14" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q14" s="4" t="n"/>
       <c r="R14" s="4" t="n"/>
       <c r="S14" s="4" t="n"/>
-      <c r="T14" s="4" t="n"/>
+      <c r="T14" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U14" s="4" t="n"/>
       <c r="V14" s="4" t="n"/>
       <c r="W14" s="4" t="n"/>
@@ -48591,32 +48643,32 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AC14" s="4" t="n"/>
+      <c r="AC14" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD14" s="4" t="n"/>
-      <c r="AE14" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AF14" s="4" t="n"/>
-      <c r="AG14" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AH14" s="4" t="n"/>
-      <c r="AI14" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AE14" s="4" t="n"/>
+      <c r="AF14" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AG14" s="4" t="n"/>
+      <c r="AH14" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AI14" s="4" t="n"/>
       <c r="AJ14" s="4" t="n"/>
-      <c r="AK14" s="4" t="n"/>
-      <c r="AL14" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AK14" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AL14" s="4" t="n"/>
       <c r="AM14" s="4" t="n"/>
       <c r="AN14" s="4" t="n"/>
       <c r="AO14" s="4" t="n"/>
@@ -48678,13 +48730,13 @@
       <c r="N15" s="4" t="n"/>
       <c r="O15" s="4" t="n"/>
       <c r="P15" s="4" t="n"/>
-      <c r="Q15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q15" s="4" t="n"/>
       <c r="R15" s="4" t="n"/>
-      <c r="S15" s="4" t="n"/>
+      <c r="S15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="T15" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -48702,27 +48754,27 @@
         </is>
       </c>
       <c r="AB15" s="4" t="n"/>
-      <c r="AC15" s="4" t="n"/>
+      <c r="AC15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD15" s="4" t="n"/>
       <c r="AE15" s="4" t="n"/>
-      <c r="AF15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AF15" s="4" t="n"/>
       <c r="AG15" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
       <c r="AH15" s="4" t="n"/>
-      <c r="AI15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AI15" s="4" t="n"/>
       <c r="AJ15" s="4" t="n"/>
-      <c r="AK15" s="4" t="n"/>
+      <c r="AK15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL15" s="4" t="n"/>
       <c r="AM15" s="4" t="n"/>
       <c r="AN15" s="4" t="n"/>
@@ -48813,7 +48865,11 @@
       <c r="R16" s="4" t="n"/>
       <c r="S16" s="4" t="n"/>
       <c r="T16" s="4" t="n"/>
-      <c r="U16" s="4" t="n"/>
+      <c r="U16" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="V16" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -48825,23 +48881,23 @@
       <c r="Z16" s="4" t="n"/>
       <c r="AA16" s="4" t="n"/>
       <c r="AB16" s="4" t="n"/>
-      <c r="AC16" s="4" t="n"/>
+      <c r="AC16" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD16" s="4" t="n"/>
       <c r="AE16" s="4" t="n"/>
       <c r="AF16" s="4" t="n"/>
-      <c r="AG16" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG16" s="4" t="n"/>
       <c r="AH16" s="4" t="n"/>
-      <c r="AI16" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AI16" s="4" t="n"/>
       <c r="AJ16" s="4" t="n"/>
-      <c r="AK16" s="4" t="n"/>
+      <c r="AK16" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL16" s="4" t="n"/>
       <c r="AM16" s="4" t="n"/>
       <c r="AN16" s="4" t="n"/>
@@ -48904,14 +48960,14 @@
       </c>
       <c r="O17" s="4" t="n"/>
       <c r="P17" s="4" t="n"/>
-      <c r="Q17" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q17" s="4" t="n"/>
       <c r="R17" s="4" t="n"/>
       <c r="S17" s="4" t="n"/>
-      <c r="T17" s="4" t="n"/>
+      <c r="T17" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U17" s="4" t="n"/>
       <c r="V17" s="4" t="n"/>
       <c r="W17" s="4" t="n"/>
@@ -48920,14 +48976,14 @@
       <c r="Z17" s="4" t="n"/>
       <c r="AA17" s="4" t="n"/>
       <c r="AB17" s="4" t="n"/>
-      <c r="AC17" s="4" t="n"/>
+      <c r="AC17" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD17" s="4" t="n"/>
       <c r="AE17" s="4" t="n"/>
-      <c r="AF17" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AF17" s="4" t="n"/>
       <c r="AG17" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -49003,18 +49059,18 @@
       <c r="N18" s="4" t="n"/>
       <c r="O18" s="4" t="n"/>
       <c r="P18" s="4" t="n"/>
-      <c r="Q18" s="4" t="n"/>
-      <c r="R18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S18" s="4" t="n"/>
-      <c r="T18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R18" s="4" t="n"/>
+      <c r="S18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T18" s="4" t="n"/>
       <c r="U18" s="4" t="n"/>
       <c r="V18" s="4" t="n"/>
       <c r="W18" s="4" t="n"/>
@@ -49035,32 +49091,32 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AC18" s="4" t="n"/>
+      <c r="AC18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD18" s="4" t="n"/>
-      <c r="AE18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AF18" s="4" t="n"/>
-      <c r="AG18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AE18" s="4" t="n"/>
+      <c r="AF18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AG18" s="4" t="n"/>
       <c r="AH18" s="4" t="n"/>
-      <c r="AI18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AJ18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK18" s="4" t="n"/>
-      <c r="AL18" s="4" t="n"/>
+      <c r="AI18" s="4" t="n"/>
+      <c r="AJ18" s="4" t="n"/>
+      <c r="AK18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AL18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AM18" s="4" t="n"/>
       <c r="AN18" s="4" t="n"/>
       <c r="AO18" s="4" t="n"/>
@@ -49130,13 +49186,13 @@
       <c r="N19" s="4" t="n"/>
       <c r="O19" s="4" t="n"/>
       <c r="P19" s="4" t="n"/>
-      <c r="Q19" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q19" s="4" t="n"/>
       <c r="R19" s="4" t="n"/>
-      <c r="S19" s="4" t="n"/>
+      <c r="S19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="T19" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -49150,15 +49206,15 @@
       <c r="Z19" s="4" t="n"/>
       <c r="AA19" s="4" t="n"/>
       <c r="AB19" s="4" t="n"/>
-      <c r="AC19" s="4" t="n"/>
+      <c r="AC19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD19" s="4" t="n"/>
       <c r="AE19" s="4" t="n"/>
       <c r="AF19" s="4" t="n"/>
-      <c r="AG19" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG19" s="4" t="n"/>
       <c r="AH19" s="4" t="n"/>
       <c r="AI19" s="4" t="inlineStr">
         <is>
@@ -49166,13 +49222,13 @@
         </is>
       </c>
       <c r="AJ19" s="4" t="n"/>
-      <c r="AK19" s="4" t="n"/>
+      <c r="AK19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL19" s="4" t="n"/>
-      <c r="AM19" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AM19" s="4" t="n"/>
       <c r="AN19" s="4" t="n"/>
       <c r="AO19" s="4" t="n"/>
       <c r="AP19" s="4" t="n"/>
@@ -49233,14 +49289,14 @@
       <c r="N20" s="4" t="n"/>
       <c r="O20" s="4" t="n"/>
       <c r="P20" s="4" t="n"/>
-      <c r="Q20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q20" s="4" t="n"/>
       <c r="R20" s="4" t="n"/>
       <c r="S20" s="4" t="n"/>
-      <c r="T20" s="4" t="n"/>
+      <c r="T20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U20" s="4" t="n"/>
       <c r="V20" s="4" t="n"/>
       <c r="W20" s="4" t="n"/>
@@ -49252,20 +49308,20 @@
       <c r="AC20" s="4" t="n"/>
       <c r="AD20" s="4" t="n"/>
       <c r="AE20" s="4" t="n"/>
-      <c r="AF20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AG20" s="4" t="n"/>
+      <c r="AF20" s="4" t="n"/>
+      <c r="AG20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AH20" s="4" t="n"/>
-      <c r="AI20" s="4" t="n"/>
+      <c r="AI20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AJ20" s="4" t="n"/>
-      <c r="AK20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AK20" s="4" t="n"/>
       <c r="AL20" s="4" t="n"/>
       <c r="AM20" s="4" t="inlineStr">
         <is>
@@ -49338,12 +49394,12 @@
       <c r="P21" s="4" t="n"/>
       <c r="Q21" s="4" t="n"/>
       <c r="R21" s="4" t="n"/>
-      <c r="S21" s="4" t="n"/>
-      <c r="T21" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="S21" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T21" s="4" t="n"/>
       <c r="U21" s="4" t="n"/>
       <c r="V21" s="4" t="inlineStr">
         <is>
@@ -49360,23 +49416,23 @@
         </is>
       </c>
       <c r="AB21" s="4" t="n"/>
-      <c r="AC21" s="4" t="n"/>
+      <c r="AC21" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD21" s="4" t="n"/>
       <c r="AE21" s="4" t="n"/>
       <c r="AF21" s="4" t="n"/>
-      <c r="AG21" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG21" s="4" t="n"/>
       <c r="AH21" s="4" t="n"/>
-      <c r="AI21" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AI21" s="4" t="n"/>
       <c r="AJ21" s="4" t="n"/>
-      <c r="AK21" s="4" t="n"/>
+      <c r="AK21" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL21" s="4" t="n"/>
       <c r="AM21" s="4" t="n"/>
       <c r="AN21" s="4" t="n"/>
@@ -49463,28 +49519,28 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AC22" s="4" t="n"/>
+      <c r="AC22" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD22" s="4" t="n"/>
       <c r="AE22" s="4" t="n"/>
       <c r="AF22" s="4" t="n"/>
-      <c r="AG22" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG22" s="4" t="n"/>
       <c r="AH22" s="4" t="n"/>
-      <c r="AI22" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AJ22" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK22" s="4" t="n"/>
-      <c r="AL22" s="4" t="n"/>
+      <c r="AI22" s="4" t="n"/>
+      <c r="AJ22" s="4" t="n"/>
+      <c r="AK22" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AL22" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AM22" s="4" t="n"/>
       <c r="AN22" s="4" t="n"/>
       <c r="AO22" s="4" t="n"/>
@@ -49540,12 +49596,12 @@
       <c r="P23" s="4" t="n"/>
       <c r="Q23" s="4" t="n"/>
       <c r="R23" s="4" t="n"/>
-      <c r="S23" s="4" t="n"/>
-      <c r="T23" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="S23" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T23" s="4" t="n"/>
       <c r="U23" s="4" t="n"/>
       <c r="V23" s="4" t="inlineStr">
         <is>
@@ -49562,23 +49618,23 @@
       <c r="Z23" s="4" t="n"/>
       <c r="AA23" s="4" t="n"/>
       <c r="AB23" s="4" t="n"/>
-      <c r="AC23" s="4" t="n"/>
+      <c r="AC23" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD23" s="4" t="n"/>
       <c r="AE23" s="4" t="n"/>
       <c r="AF23" s="4" t="n"/>
-      <c r="AG23" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG23" s="4" t="n"/>
       <c r="AH23" s="4" t="n"/>
-      <c r="AI23" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AI23" s="4" t="n"/>
       <c r="AJ23" s="4" t="n"/>
-      <c r="AK23" s="4" t="n"/>
+      <c r="AK23" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL23" s="4" t="n"/>
       <c r="AM23" s="4" t="n"/>
       <c r="AN23" s="4" t="n"/>
@@ -49634,12 +49690,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="R24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S24" s="4" t="n"/>
+      <c r="R24" s="4" t="n"/>
+      <c r="S24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="T24" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -49661,37 +49717,37 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AC24" s="4" t="n"/>
+      <c r="AC24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD24" s="4" t="n"/>
-      <c r="AE24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AF24" s="4" t="n"/>
-      <c r="AG24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AE24" s="4" t="n"/>
+      <c r="AF24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AG24" s="4" t="n"/>
       <c r="AH24" s="4" t="n"/>
       <c r="AI24" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AJ24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK24" s="4" t="n"/>
-      <c r="AL24" s="4" t="n"/>
-      <c r="AM24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AJ24" s="4" t="n"/>
+      <c r="AK24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AL24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AM24" s="4" t="n"/>
       <c r="AN24" s="4" t="n"/>
       <c r="AO24" s="4" t="n"/>
       <c r="AP24" s="4" t="n"/>
@@ -49738,12 +49794,12 @@
       <c r="P25" s="4" t="n"/>
       <c r="Q25" s="4" t="n"/>
       <c r="R25" s="4" t="n"/>
-      <c r="S25" s="4" t="n"/>
-      <c r="T25" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="S25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T25" s="4" t="n"/>
       <c r="U25" s="4" t="n"/>
       <c r="V25" s="4" t="n"/>
       <c r="W25" s="4" t="n"/>
@@ -49762,26 +49818,26 @@
       </c>
       <c r="AC25" s="4" t="n"/>
       <c r="AD25" s="4" t="n"/>
-      <c r="AE25" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AF25" s="4" t="n"/>
+      <c r="AE25" s="4" t="n"/>
+      <c r="AF25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AG25" s="4" t="n"/>
       <c r="AH25" s="4" t="n"/>
-      <c r="AI25" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AJ25" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK25" s="4" t="n"/>
-      <c r="AL25" s="4" t="n"/>
+      <c r="AI25" s="4" t="n"/>
+      <c r="AJ25" s="4" t="n"/>
+      <c r="AK25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AL25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AM25" s="4" t="n"/>
       <c r="AN25" s="4" t="n"/>
       <c r="AO25" s="4" t="n"/>
@@ -49839,13 +49895,13 @@
       <c r="N26" s="4" t="n"/>
       <c r="O26" s="4" t="n"/>
       <c r="P26" s="4" t="n"/>
-      <c r="Q26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q26" s="4" t="n"/>
       <c r="R26" s="4" t="n"/>
-      <c r="S26" s="4" t="n"/>
+      <c r="S26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="T26" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -49867,13 +49923,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AC26" s="4" t="n"/>
+      <c r="AC26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD26" s="4" t="n"/>
-      <c r="AE26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AE26" s="4" t="n"/>
       <c r="AF26" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -49958,15 +50014,19 @@
       <c r="N27" s="4" t="n"/>
       <c r="O27" s="4" t="n"/>
       <c r="P27" s="4" t="n"/>
-      <c r="Q27" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q27" s="4" t="n"/>
       <c r="R27" s="4" t="n"/>
       <c r="S27" s="4" t="n"/>
-      <c r="T27" s="4" t="n"/>
-      <c r="U27" s="4" t="n"/>
+      <c r="T27" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U27" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="V27" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -49982,23 +50042,23 @@
         </is>
       </c>
       <c r="AB27" s="4" t="n"/>
-      <c r="AC27" s="4" t="n"/>
+      <c r="AC27" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD27" s="4" t="n"/>
       <c r="AE27" s="4" t="n"/>
       <c r="AF27" s="4" t="n"/>
-      <c r="AG27" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG27" s="4" t="n"/>
       <c r="AH27" s="4" t="n"/>
-      <c r="AI27" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AI27" s="4" t="n"/>
       <c r="AJ27" s="4" t="n"/>
-      <c r="AK27" s="4" t="n"/>
+      <c r="AK27" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL27" s="4" t="n"/>
       <c r="AM27" s="4" t="n"/>
       <c r="AN27" s="4" t="n"/>
@@ -50063,12 +50123,12 @@
       <c r="P28" s="4" t="n"/>
       <c r="Q28" s="4" t="n"/>
       <c r="R28" s="4" t="n"/>
-      <c r="S28" s="4" t="n"/>
-      <c r="T28" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="S28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T28" s="4" t="n"/>
       <c r="U28" s="4" t="n"/>
       <c r="V28" s="4" t="n"/>
       <c r="W28" s="4" t="n"/>
@@ -50090,26 +50150,26 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AD28" s="4" t="n"/>
-      <c r="AE28" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AF28" s="4" t="n"/>
-      <c r="AG28" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AD28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AE28" s="4" t="n"/>
+      <c r="AF28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AG28" s="4" t="n"/>
       <c r="AH28" s="4" t="n"/>
-      <c r="AI28" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AI28" s="4" t="n"/>
       <c r="AJ28" s="4" t="n"/>
-      <c r="AK28" s="4" t="n"/>
+      <c r="AK28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL28" s="4" t="n"/>
       <c r="AM28" s="4" t="n"/>
       <c r="AN28" s="4" t="n"/>
@@ -50180,23 +50240,23 @@
       <c r="Z29" s="4" t="n"/>
       <c r="AA29" s="4" t="n"/>
       <c r="AB29" s="4" t="n"/>
-      <c r="AC29" s="4" t="n"/>
+      <c r="AC29" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD29" s="4" t="n"/>
       <c r="AE29" s="4" t="n"/>
       <c r="AF29" s="4" t="n"/>
-      <c r="AG29" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG29" s="4" t="n"/>
       <c r="AH29" s="4" t="n"/>
-      <c r="AI29" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AI29" s="4" t="n"/>
       <c r="AJ29" s="4" t="n"/>
-      <c r="AK29" s="4" t="n"/>
+      <c r="AK29" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL29" s="4" t="n"/>
       <c r="AM29" s="4" t="n"/>
       <c r="AN29" s="4" t="n"/>
@@ -50259,14 +50319,14 @@
       <c r="N30" s="4" t="n"/>
       <c r="O30" s="4" t="n"/>
       <c r="P30" s="4" t="n"/>
-      <c r="Q30" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q30" s="4" t="n"/>
       <c r="R30" s="4" t="n"/>
       <c r="S30" s="4" t="n"/>
-      <c r="T30" s="4" t="n"/>
+      <c r="T30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U30" s="4" t="n"/>
       <c r="V30" s="4" t="n"/>
       <c r="W30" s="4" t="n"/>
@@ -50278,20 +50338,20 @@
       <c r="AC30" s="4" t="n"/>
       <c r="AD30" s="4" t="n"/>
       <c r="AE30" s="4" t="n"/>
-      <c r="AF30" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AG30" s="4" t="n"/>
+      <c r="AF30" s="4" t="n"/>
+      <c r="AG30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AH30" s="4" t="n"/>
-      <c r="AI30" s="4" t="n"/>
+      <c r="AI30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AJ30" s="4" t="n"/>
-      <c r="AK30" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AK30" s="4" t="n"/>
       <c r="AL30" s="4" t="n"/>
       <c r="AM30" s="4" t="inlineStr">
         <is>
@@ -50358,14 +50418,14 @@
       <c r="N31" s="4" t="n"/>
       <c r="O31" s="4" t="n"/>
       <c r="P31" s="4" t="n"/>
-      <c r="Q31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q31" s="4" t="n"/>
       <c r="R31" s="4" t="n"/>
       <c r="S31" s="4" t="n"/>
-      <c r="T31" s="4" t="n"/>
+      <c r="T31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U31" s="4" t="n"/>
       <c r="V31" s="4" t="n"/>
       <c r="W31" s="4" t="n"/>
@@ -50377,30 +50437,30 @@
       <c r="AC31" s="4" t="n"/>
       <c r="AD31" s="4" t="n"/>
       <c r="AE31" s="4" t="n"/>
-      <c r="AF31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AG31" s="4" t="n"/>
-      <c r="AH31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AI31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AJ31" s="4" t="n"/>
+      <c r="AF31" s="4" t="n"/>
+      <c r="AG31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AH31" s="4" t="n"/>
+      <c r="AI31" s="4" t="n"/>
+      <c r="AJ31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AK31" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
       <c r="AL31" s="4" t="n"/>
-      <c r="AM31" s="4" t="n"/>
+      <c r="AM31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AN31" s="4" t="n"/>
       <c r="AO31" s="4" t="n"/>
       <c r="AP31" s="4" t="n"/>
@@ -50473,14 +50533,14 @@
       <c r="N32" s="4" t="n"/>
       <c r="O32" s="4" t="n"/>
       <c r="P32" s="4" t="n"/>
-      <c r="Q32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q32" s="4" t="n"/>
       <c r="R32" s="4" t="n"/>
       <c r="S32" s="4" t="n"/>
-      <c r="T32" s="4" t="n"/>
+      <c r="T32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U32" s="4" t="n"/>
       <c r="V32" s="4" t="n"/>
       <c r="W32" s="4" t="n"/>
@@ -50493,15 +50553,15 @@
         </is>
       </c>
       <c r="AB32" s="4" t="n"/>
-      <c r="AC32" s="4" t="n"/>
+      <c r="AC32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD32" s="4" t="n"/>
       <c r="AE32" s="4" t="n"/>
       <c r="AF32" s="4" t="n"/>
-      <c r="AG32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG32" s="4" t="n"/>
       <c r="AH32" s="4" t="n"/>
       <c r="AI32" s="4" t="inlineStr">
         <is>
@@ -50509,13 +50569,13 @@
         </is>
       </c>
       <c r="AJ32" s="4" t="n"/>
-      <c r="AK32" s="4" t="n"/>
+      <c r="AK32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL32" s="4" t="n"/>
-      <c r="AM32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AM32" s="4" t="n"/>
       <c r="AN32" s="4" t="n"/>
       <c r="AO32" s="4" t="n"/>
       <c r="AP32" s="4" t="n"/>
@@ -50540,14 +50600,14 @@
         </is>
       </c>
       <c r="BC32" s="4" t="n"/>
-      <c r="BD32" s="4" t="n"/>
+      <c r="BD32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE32" s="4" t="n"/>
       <c r="BF32" s="4" t="n"/>
-      <c r="BG32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BG32" s="4" t="n"/>
       <c r="BH32" s="4" t="n"/>
       <c r="BI32" s="4" t="inlineStr">
         <is>
@@ -50580,14 +50640,14 @@
       <c r="N33" s="4" t="n"/>
       <c r="O33" s="4" t="n"/>
       <c r="P33" s="4" t="n"/>
-      <c r="Q33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q33" s="4" t="n"/>
       <c r="R33" s="4" t="n"/>
       <c r="S33" s="4" t="n"/>
-      <c r="T33" s="4" t="n"/>
+      <c r="T33" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U33" s="4" t="n"/>
       <c r="V33" s="4" t="n"/>
       <c r="W33" s="4" t="n"/>
@@ -50599,24 +50659,24 @@
       <c r="AC33" s="4" t="n"/>
       <c r="AD33" s="4" t="n"/>
       <c r="AE33" s="4" t="n"/>
-      <c r="AF33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AG33" s="4" t="n"/>
-      <c r="AH33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AI33" s="4" t="n"/>
-      <c r="AJ33" s="4" t="n"/>
-      <c r="AK33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AF33" s="4" t="n"/>
+      <c r="AG33" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AH33" s="4" t="n"/>
+      <c r="AI33" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AJ33" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AK33" s="4" t="n"/>
       <c r="AL33" s="4" t="n"/>
       <c r="AM33" s="4" t="inlineStr">
         <is>
@@ -50687,18 +50747,22 @@
       <c r="N34" s="4" t="n"/>
       <c r="O34" s="4" t="n"/>
       <c r="P34" s="4" t="n"/>
-      <c r="Q34" s="4" t="n"/>
-      <c r="R34" s="4" t="n"/>
+      <c r="Q34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="S34" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="T34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T34" s="4" t="n"/>
       <c r="U34" s="4" t="n"/>
       <c r="V34" s="4" t="n"/>
       <c r="W34" s="4" t="n"/>
@@ -50711,23 +50775,23 @@
         </is>
       </c>
       <c r="AB34" s="4" t="n"/>
-      <c r="AC34" s="4" t="n"/>
+      <c r="AC34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD34" s="4" t="n"/>
       <c r="AE34" s="4" t="n"/>
       <c r="AF34" s="4" t="n"/>
-      <c r="AG34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG34" s="4" t="n"/>
       <c r="AH34" s="4" t="n"/>
-      <c r="AI34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AI34" s="4" t="n"/>
       <c r="AJ34" s="4" t="n"/>
-      <c r="AK34" s="4" t="n"/>
+      <c r="AK34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL34" s="4" t="n"/>
       <c r="AM34" s="4" t="n"/>
       <c r="AN34" s="4" t="n"/>
@@ -50786,14 +50850,14 @@
       <c r="N35" s="4" t="n"/>
       <c r="O35" s="4" t="n"/>
       <c r="P35" s="4" t="n"/>
-      <c r="Q35" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q35" s="4" t="n"/>
       <c r="R35" s="4" t="n"/>
       <c r="S35" s="4" t="n"/>
-      <c r="T35" s="4" t="n"/>
+      <c r="T35" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U35" s="4" t="n"/>
       <c r="V35" s="4" t="n"/>
       <c r="W35" s="4" t="n"/>
@@ -50805,26 +50869,26 @@
       <c r="AC35" s="4" t="n"/>
       <c r="AD35" s="4" t="n"/>
       <c r="AE35" s="4" t="n"/>
-      <c r="AF35" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AG35" s="4" t="n"/>
-      <c r="AH35" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AI35" s="4" t="n"/>
-      <c r="AJ35" s="4" t="n"/>
+      <c r="AF35" s="4" t="n"/>
+      <c r="AG35" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AH35" s="4" t="n"/>
+      <c r="AI35" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AJ35" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AK35" s="4" t="n"/>
       <c r="AL35" s="4" t="n"/>
-      <c r="AM35" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AM35" s="4" t="n"/>
       <c r="AN35" s="4" t="n"/>
       <c r="AO35" s="4" t="n"/>
       <c r="AP35" s="4" t="n"/>
@@ -50853,7 +50917,11 @@
         </is>
       </c>
       <c r="BC35" s="4" t="n"/>
-      <c r="BD35" s="4" t="n"/>
+      <c r="BD35" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE35" s="4" t="n"/>
       <c r="BF35" s="4" t="n"/>
       <c r="BG35" s="4" t="n"/>
@@ -50897,13 +50965,13 @@
       <c r="N36" s="4" t="n"/>
       <c r="O36" s="4" t="n"/>
       <c r="P36" s="4" t="n"/>
-      <c r="Q36" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q36" s="4" t="n"/>
       <c r="R36" s="4" t="n"/>
-      <c r="S36" s="4" t="n"/>
+      <c r="S36" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="T36" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -50921,15 +50989,15 @@
         </is>
       </c>
       <c r="AB36" s="4" t="n"/>
-      <c r="AC36" s="4" t="n"/>
+      <c r="AC36" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD36" s="4" t="n"/>
       <c r="AE36" s="4" t="n"/>
       <c r="AF36" s="4" t="n"/>
-      <c r="AG36" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG36" s="4" t="n"/>
       <c r="AH36" s="4" t="n"/>
       <c r="AI36" s="4" t="inlineStr">
         <is>
@@ -50937,13 +51005,13 @@
         </is>
       </c>
       <c r="AJ36" s="4" t="n"/>
-      <c r="AK36" s="4" t="n"/>
+      <c r="AK36" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL36" s="4" t="n"/>
-      <c r="AM36" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AM36" s="4" t="n"/>
       <c r="AN36" s="4" t="n"/>
       <c r="AO36" s="4" t="n"/>
       <c r="AP36" s="4" t="n"/>
@@ -51012,14 +51080,14 @@
       <c r="N37" s="4" t="n"/>
       <c r="O37" s="4" t="n"/>
       <c r="P37" s="4" t="n"/>
-      <c r="Q37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q37" s="4" t="n"/>
       <c r="R37" s="4" t="n"/>
       <c r="S37" s="4" t="n"/>
-      <c r="T37" s="4" t="n"/>
+      <c r="T37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U37" s="4" t="n"/>
       <c r="V37" s="4" t="n"/>
       <c r="W37" s="4" t="n"/>
@@ -51043,14 +51111,18 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AJ37" s="4" t="n"/>
-      <c r="AK37" s="4" t="n"/>
+      <c r="AJ37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AK37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL37" s="4" t="n"/>
-      <c r="AM37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AM37" s="4" t="n"/>
       <c r="AN37" s="4" t="n"/>
       <c r="AO37" s="4" t="n"/>
       <c r="AP37" s="4" t="n"/>
@@ -51071,14 +51143,14 @@
       <c r="BA37" s="4" t="n"/>
       <c r="BB37" s="4" t="n"/>
       <c r="BC37" s="4" t="n"/>
-      <c r="BD37" s="4" t="n"/>
+      <c r="BD37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE37" s="4" t="n"/>
       <c r="BF37" s="4" t="n"/>
-      <c r="BG37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BG37" s="4" t="n"/>
       <c r="BH37" s="4" t="n"/>
       <c r="BI37" s="4" t="inlineStr">
         <is>
@@ -51107,13 +51179,13 @@
       <c r="N38" s="4" t="n"/>
       <c r="O38" s="4" t="n"/>
       <c r="P38" s="4" t="n"/>
-      <c r="Q38" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q38" s="4" t="n"/>
       <c r="R38" s="4" t="n"/>
-      <c r="S38" s="4" t="n"/>
+      <c r="S38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="T38" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -51136,40 +51208,40 @@
         </is>
       </c>
       <c r="AC38" s="4" t="n"/>
-      <c r="AD38" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AD38" s="4" t="n"/>
       <c r="AE38" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AF38" s="4" t="n"/>
+      <c r="AF38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AG38" s="4" t="n"/>
-      <c r="AH38" s="4" t="n"/>
+      <c r="AH38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AI38" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AJ38" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AK38" s="4" t="n"/>
+      <c r="AJ38" s="4" t="n"/>
+      <c r="AK38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL38" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AM38" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AM38" s="4" t="n"/>
       <c r="AN38" s="4" t="n"/>
       <c r="AO38" s="4" t="n"/>
       <c r="AP38" s="4" t="n"/>
@@ -51186,14 +51258,14 @@
       <c r="BA38" s="4" t="n"/>
       <c r="BB38" s="4" t="n"/>
       <c r="BC38" s="4" t="n"/>
-      <c r="BD38" s="4" t="n"/>
+      <c r="BD38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE38" s="4" t="n"/>
       <c r="BF38" s="4" t="n"/>
-      <c r="BG38" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BG38" s="4" t="n"/>
       <c r="BH38" s="4" t="n"/>
       <c r="BI38" s="4" t="n"/>
     </row>
@@ -51220,12 +51292,12 @@
       <c r="P39" s="4" t="n"/>
       <c r="Q39" s="4" t="n"/>
       <c r="R39" s="4" t="n"/>
-      <c r="S39" s="4" t="n"/>
-      <c r="T39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="S39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T39" s="4" t="n"/>
       <c r="U39" s="4" t="n"/>
       <c r="V39" s="4" t="n"/>
       <c r="W39" s="4" t="n"/>
@@ -51242,20 +51314,24 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AC39" s="4" t="n"/>
+      <c r="AC39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD39" s="4" t="n"/>
-      <c r="AE39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AF39" s="4" t="n"/>
-      <c r="AG39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AH39" s="4" t="n"/>
+      <c r="AE39" s="4" t="n"/>
+      <c r="AF39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AG39" s="4" t="n"/>
+      <c r="AH39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AI39" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -51267,11 +51343,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AL39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AL39" s="4" t="n"/>
       <c r="AM39" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -51293,14 +51365,14 @@
       <c r="BA39" s="4" t="n"/>
       <c r="BB39" s="4" t="n"/>
       <c r="BC39" s="4" t="n"/>
-      <c r="BD39" s="4" t="n"/>
+      <c r="BD39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE39" s="4" t="n"/>
       <c r="BF39" s="4" t="n"/>
-      <c r="BG39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BG39" s="4" t="n"/>
       <c r="BH39" s="4" t="n"/>
       <c r="BI39" s="4" t="n"/>
     </row>
@@ -51353,14 +51425,14 @@
       <c r="N40" s="4" t="n"/>
       <c r="O40" s="4" t="n"/>
       <c r="P40" s="4" t="n"/>
-      <c r="Q40" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q40" s="4" t="n"/>
       <c r="R40" s="4" t="n"/>
       <c r="S40" s="4" t="n"/>
-      <c r="T40" s="4" t="n"/>
+      <c r="T40" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U40" s="4" t="n"/>
       <c r="V40" s="4" t="n"/>
       <c r="W40" s="4" t="n"/>
@@ -51372,22 +51444,26 @@
       <c r="AC40" s="4" t="n"/>
       <c r="AD40" s="4" t="n"/>
       <c r="AE40" s="4" t="n"/>
-      <c r="AF40" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AG40" s="4" t="n"/>
-      <c r="AH40" s="4" t="n"/>
-      <c r="AI40" s="4" t="n"/>
+      <c r="AF40" s="4" t="n"/>
+      <c r="AG40" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AH40" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AI40" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AJ40" s="4" t="n"/>
       <c r="AK40" s="4" t="n"/>
       <c r="AL40" s="4" t="n"/>
-      <c r="AM40" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AM40" s="4" t="n"/>
       <c r="AN40" s="4" t="n"/>
       <c r="AO40" s="4" t="n"/>
       <c r="AP40" s="4" t="n"/>
@@ -51412,14 +51488,14 @@
       <c r="BA40" s="4" t="n"/>
       <c r="BB40" s="4" t="n"/>
       <c r="BC40" s="4" t="n"/>
-      <c r="BD40" s="4" t="n"/>
+      <c r="BD40" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE40" s="4" t="n"/>
       <c r="BF40" s="4" t="n"/>
-      <c r="BG40" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BG40" s="4" t="n"/>
       <c r="BH40" s="4" t="n"/>
       <c r="BI40" s="4" t="n"/>
     </row>
@@ -51476,23 +51552,23 @@
       <c r="Z41" s="4" t="n"/>
       <c r="AA41" s="4" t="n"/>
       <c r="AB41" s="4" t="n"/>
-      <c r="AC41" s="4" t="n"/>
+      <c r="AC41" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD41" s="4" t="n"/>
       <c r="AE41" s="4" t="n"/>
       <c r="AF41" s="4" t="n"/>
-      <c r="AG41" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG41" s="4" t="n"/>
       <c r="AH41" s="4" t="n"/>
-      <c r="AI41" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AI41" s="4" t="n"/>
       <c r="AJ41" s="4" t="n"/>
-      <c r="AK41" s="4" t="n"/>
+      <c r="AK41" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL41" s="4" t="n"/>
       <c r="AM41" s="4" t="n"/>
       <c r="AN41" s="4" t="n"/>
@@ -51547,15 +51623,19 @@
       <c r="N42" s="4" t="n"/>
       <c r="O42" s="4" t="n"/>
       <c r="P42" s="4" t="n"/>
-      <c r="Q42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q42" s="4" t="n"/>
       <c r="R42" s="4" t="n"/>
       <c r="S42" s="4" t="n"/>
-      <c r="T42" s="4" t="n"/>
-      <c r="U42" s="4" t="n"/>
+      <c r="T42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="V42" s="4" t="n"/>
       <c r="W42" s="4" t="n"/>
       <c r="X42" s="4" t="n"/>
@@ -51571,19 +51651,19 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AC42" s="4" t="n"/>
+      <c r="AC42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD42" s="4" t="n"/>
-      <c r="AE42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AF42" s="4" t="n"/>
-      <c r="AG42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AE42" s="4" t="n"/>
+      <c r="AF42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AG42" s="4" t="n"/>
       <c r="AH42" s="4" t="n"/>
       <c r="AI42" s="4" t="inlineStr">
         <is>
@@ -51591,13 +51671,13 @@
         </is>
       </c>
       <c r="AJ42" s="4" t="n"/>
-      <c r="AK42" s="4" t="n"/>
+      <c r="AK42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL42" s="4" t="n"/>
-      <c r="AM42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AM42" s="4" t="n"/>
       <c r="AN42" s="4" t="n"/>
       <c r="AO42" s="4" t="n"/>
       <c r="AP42" s="4" t="n"/>
@@ -51674,15 +51754,15 @@
         </is>
       </c>
       <c r="AB43" s="4" t="n"/>
-      <c r="AC43" s="4" t="n"/>
+      <c r="AC43" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD43" s="4" t="n"/>
       <c r="AE43" s="4" t="n"/>
       <c r="AF43" s="4" t="n"/>
-      <c r="AG43" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG43" s="4" t="n"/>
       <c r="AH43" s="4" t="n"/>
       <c r="AI43" s="4" t="inlineStr">
         <is>
@@ -51690,13 +51770,13 @@
         </is>
       </c>
       <c r="AJ43" s="4" t="n"/>
-      <c r="AK43" s="4" t="n"/>
+      <c r="AK43" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL43" s="4" t="n"/>
-      <c r="AM43" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AM43" s="4" t="n"/>
       <c r="AN43" s="4" t="n"/>
       <c r="AO43" s="4" t="n"/>
       <c r="AP43" s="4" t="n"/>
@@ -51741,14 +51821,14 @@
       <c r="N44" s="4" t="n"/>
       <c r="O44" s="4" t="n"/>
       <c r="P44" s="4" t="n"/>
-      <c r="Q44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q44" s="4" t="n"/>
       <c r="R44" s="4" t="n"/>
       <c r="S44" s="4" t="n"/>
-      <c r="T44" s="4" t="n"/>
+      <c r="T44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U44" s="4" t="n"/>
       <c r="V44" s="4" t="n"/>
       <c r="W44" s="4" t="n"/>
@@ -51760,30 +51840,30 @@
       <c r="AC44" s="4" t="n"/>
       <c r="AD44" s="4" t="n"/>
       <c r="AE44" s="4" t="n"/>
-      <c r="AF44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AG44" s="4" t="n"/>
-      <c r="AH44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AI44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AJ44" s="4" t="n"/>
+      <c r="AF44" s="4" t="n"/>
+      <c r="AG44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AH44" s="4" t="n"/>
+      <c r="AI44" s="4" t="n"/>
+      <c r="AJ44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AK44" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
       <c r="AL44" s="4" t="n"/>
-      <c r="AM44" s="4" t="n"/>
+      <c r="AM44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AN44" s="4" t="n"/>
       <c r="AO44" s="4" t="n"/>
       <c r="AP44" s="4" t="n"/>
@@ -51860,15 +51940,19 @@
       </c>
       <c r="O45" s="4" t="n"/>
       <c r="P45" s="4" t="n"/>
-      <c r="Q45" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q45" s="4" t="n"/>
       <c r="R45" s="4" t="n"/>
       <c r="S45" s="4" t="n"/>
-      <c r="T45" s="4" t="n"/>
-      <c r="U45" s="4" t="n"/>
+      <c r="T45" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U45" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="V45" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -51880,23 +51964,23 @@
       <c r="Z45" s="4" t="n"/>
       <c r="AA45" s="4" t="n"/>
       <c r="AB45" s="4" t="n"/>
-      <c r="AC45" s="4" t="n"/>
+      <c r="AC45" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD45" s="4" t="n"/>
       <c r="AE45" s="4" t="n"/>
       <c r="AF45" s="4" t="n"/>
-      <c r="AG45" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG45" s="4" t="n"/>
       <c r="AH45" s="4" t="n"/>
-      <c r="AI45" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AI45" s="4" t="n"/>
       <c r="AJ45" s="4" t="n"/>
-      <c r="AK45" s="4" t="n"/>
+      <c r="AK45" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL45" s="4" t="n"/>
       <c r="AM45" s="4" t="n"/>
       <c r="AN45" s="4" t="inlineStr">
@@ -51975,14 +52059,14 @@
       <c r="N46" s="4" t="n"/>
       <c r="O46" s="4" t="n"/>
       <c r="P46" s="4" t="n"/>
-      <c r="Q46" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q46" s="4" t="n"/>
       <c r="R46" s="4" t="n"/>
       <c r="S46" s="4" t="n"/>
-      <c r="T46" s="4" t="n"/>
+      <c r="T46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U46" s="4" t="n"/>
       <c r="V46" s="4" t="n"/>
       <c r="W46" s="4" t="n"/>
@@ -51991,15 +52075,15 @@
       <c r="Z46" s="4" t="n"/>
       <c r="AA46" s="4" t="n"/>
       <c r="AB46" s="4" t="n"/>
-      <c r="AC46" s="4" t="n"/>
+      <c r="AC46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD46" s="4" t="n"/>
       <c r="AE46" s="4" t="n"/>
       <c r="AF46" s="4" t="n"/>
-      <c r="AG46" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG46" s="4" t="n"/>
       <c r="AH46" s="4" t="n"/>
       <c r="AI46" s="4" t="inlineStr">
         <is>
@@ -52007,13 +52091,13 @@
         </is>
       </c>
       <c r="AJ46" s="4" t="n"/>
-      <c r="AK46" s="4" t="n"/>
+      <c r="AK46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL46" s="4" t="n"/>
-      <c r="AM46" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AM46" s="4" t="n"/>
       <c r="AN46" s="4" t="n"/>
       <c r="AO46" s="4" t="inlineStr">
         <is>
@@ -52090,14 +52174,14 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="Q47" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q47" s="4" t="n"/>
       <c r="R47" s="4" t="n"/>
       <c r="S47" s="4" t="n"/>
-      <c r="T47" s="4" t="n"/>
+      <c r="T47" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U47" s="4" t="n"/>
       <c r="V47" s="4" t="n"/>
       <c r="W47" s="4" t="n"/>
@@ -52106,15 +52190,15 @@
       <c r="Z47" s="4" t="n"/>
       <c r="AA47" s="4" t="n"/>
       <c r="AB47" s="4" t="n"/>
-      <c r="AC47" s="4" t="n"/>
+      <c r="AC47" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD47" s="4" t="n"/>
       <c r="AE47" s="4" t="n"/>
       <c r="AF47" s="4" t="n"/>
-      <c r="AG47" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG47" s="4" t="n"/>
       <c r="AH47" s="4" t="n"/>
       <c r="AI47" s="4" t="inlineStr">
         <is>
@@ -52122,13 +52206,13 @@
         </is>
       </c>
       <c r="AJ47" s="4" t="n"/>
-      <c r="AK47" s="4" t="n"/>
+      <c r="AK47" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL47" s="4" t="n"/>
-      <c r="AM47" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AM47" s="4" t="n"/>
       <c r="AN47" s="4" t="n"/>
       <c r="AO47" s="4" t="inlineStr">
         <is>
@@ -52197,12 +52281,12 @@
       <c r="N48" s="4" t="n"/>
       <c r="O48" s="4" t="n"/>
       <c r="P48" s="4" t="n"/>
-      <c r="Q48" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R48" s="4" t="n"/>
+      <c r="Q48" s="4" t="n"/>
+      <c r="R48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -52225,27 +52309,27 @@
         </is>
       </c>
       <c r="AB48" s="4" t="n"/>
-      <c r="AC48" s="4" t="n"/>
+      <c r="AC48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD48" s="4" t="n"/>
       <c r="AE48" s="4" t="n"/>
       <c r="AF48" s="4" t="n"/>
-      <c r="AG48" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AH48" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AI48" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AJ48" s="4" t="n"/>
-      <c r="AK48" s="4" t="n"/>
+      <c r="AG48" s="4" t="n"/>
+      <c r="AH48" s="4" t="n"/>
+      <c r="AI48" s="4" t="n"/>
+      <c r="AJ48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AK48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL48" s="4" t="n"/>
       <c r="AM48" s="4" t="n"/>
       <c r="AN48" s="4" t="n"/>
@@ -52308,14 +52392,14 @@
       <c r="N49" s="4" t="n"/>
       <c r="O49" s="4" t="n"/>
       <c r="P49" s="4" t="n"/>
-      <c r="Q49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q49" s="4" t="n"/>
       <c r="R49" s="4" t="n"/>
       <c r="S49" s="4" t="n"/>
-      <c r="T49" s="4" t="n"/>
+      <c r="T49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U49" s="4" t="n"/>
       <c r="V49" s="4" t="n"/>
       <c r="W49" s="4" t="n"/>
@@ -52327,22 +52411,22 @@
       <c r="AC49" s="4" t="n"/>
       <c r="AD49" s="4" t="n"/>
       <c r="AE49" s="4" t="n"/>
-      <c r="AF49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AG49" s="4" t="n"/>
+      <c r="AF49" s="4" t="n"/>
+      <c r="AG49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AH49" s="4" t="n"/>
-      <c r="AI49" s="4" t="n"/>
+      <c r="AI49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AJ49" s="4" t="n"/>
       <c r="AK49" s="4" t="n"/>
       <c r="AL49" s="4" t="n"/>
-      <c r="AM49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AM49" s="4" t="n"/>
       <c r="AN49" s="4" t="n"/>
       <c r="AO49" s="4" t="n"/>
       <c r="AP49" s="4" t="n"/>
@@ -52367,14 +52451,14 @@
       <c r="BA49" s="4" t="n"/>
       <c r="BB49" s="4" t="n"/>
       <c r="BC49" s="4" t="n"/>
-      <c r="BD49" s="4" t="n"/>
+      <c r="BD49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE49" s="4" t="n"/>
       <c r="BF49" s="4" t="n"/>
-      <c r="BG49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BG49" s="4" t="n"/>
       <c r="BH49" s="4" t="n"/>
       <c r="BI49" s="4" t="inlineStr">
         <is>
@@ -52403,14 +52487,14 @@
       <c r="N50" s="4" t="n"/>
       <c r="O50" s="4" t="n"/>
       <c r="P50" s="4" t="n"/>
-      <c r="Q50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q50" s="4" t="n"/>
       <c r="R50" s="4" t="n"/>
       <c r="S50" s="4" t="n"/>
-      <c r="T50" s="4" t="n"/>
+      <c r="T50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U50" s="4" t="n"/>
       <c r="V50" s="4" t="n"/>
       <c r="W50" s="4" t="n"/>
@@ -52422,22 +52506,22 @@
       <c r="AC50" s="4" t="n"/>
       <c r="AD50" s="4" t="n"/>
       <c r="AE50" s="4" t="n"/>
-      <c r="AF50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AG50" s="4" t="n"/>
+      <c r="AF50" s="4" t="n"/>
+      <c r="AG50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AH50" s="4" t="n"/>
-      <c r="AI50" s="4" t="n"/>
+      <c r="AI50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AJ50" s="4" t="n"/>
       <c r="AK50" s="4" t="n"/>
       <c r="AL50" s="4" t="n"/>
-      <c r="AM50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AM50" s="4" t="n"/>
       <c r="AN50" s="4" t="n"/>
       <c r="AO50" s="4" t="n"/>
       <c r="AP50" s="4" t="n"/>
@@ -52467,12 +52551,12 @@
       </c>
       <c r="BC50" s="4" t="n"/>
       <c r="BD50" s="4" t="n"/>
-      <c r="BE50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BF50" s="4" t="n"/>
+      <c r="BE50" s="4" t="n"/>
+      <c r="BF50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BG50" s="4" t="n"/>
       <c r="BH50" s="4" t="n"/>
       <c r="BI50" s="4" t="inlineStr">
@@ -52502,14 +52586,14 @@
       <c r="N51" s="4" t="n"/>
       <c r="O51" s="4" t="n"/>
       <c r="P51" s="4" t="n"/>
-      <c r="Q51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q51" s="4" t="n"/>
       <c r="R51" s="4" t="n"/>
       <c r="S51" s="4" t="n"/>
-      <c r="T51" s="4" t="n"/>
+      <c r="T51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U51" s="4" t="n"/>
       <c r="V51" s="4" t="n"/>
       <c r="W51" s="4" t="n"/>
@@ -52526,30 +52610,30 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AC51" s="4" t="n"/>
+      <c r="AC51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD51" s="4" t="n"/>
-      <c r="AE51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AF51" s="4" t="n"/>
-      <c r="AG51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AH51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AE51" s="4" t="n"/>
+      <c r="AF51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AG51" s="4" t="n"/>
+      <c r="AH51" s="4" t="n"/>
       <c r="AI51" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AJ51" s="4" t="n"/>
+      <c r="AJ51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AK51" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -52579,12 +52663,12 @@
       <c r="BC51" s="4" t="n"/>
       <c r="BD51" s="4" t="n"/>
       <c r="BE51" s="4" t="n"/>
-      <c r="BF51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BG51" s="4" t="n"/>
+      <c r="BF51" s="4" t="n"/>
+      <c r="BG51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BH51" s="4" t="n"/>
       <c r="BI51" s="4" t="n"/>
     </row>
@@ -52625,7 +52709,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="Q52" s="4" t="n"/>
+      <c r="Q52" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="R52" s="4" t="n"/>
       <c r="S52" s="4" t="n"/>
       <c r="T52" s="4" t="n"/>
@@ -52637,15 +52725,15 @@
       <c r="Z52" s="4" t="n"/>
       <c r="AA52" s="4" t="n"/>
       <c r="AB52" s="4" t="n"/>
-      <c r="AC52" s="4" t="n"/>
+      <c r="AC52" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD52" s="4" t="n"/>
       <c r="AE52" s="4" t="n"/>
       <c r="AF52" s="4" t="n"/>
-      <c r="AG52" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG52" s="4" t="n"/>
       <c r="AH52" s="4" t="n"/>
       <c r="AI52" s="4" t="inlineStr">
         <is>
@@ -52653,13 +52741,13 @@
         </is>
       </c>
       <c r="AJ52" s="4" t="n"/>
-      <c r="AK52" s="4" t="n"/>
+      <c r="AK52" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL52" s="4" t="n"/>
-      <c r="AM52" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AM52" s="4" t="n"/>
       <c r="AN52" s="4" t="n"/>
       <c r="AO52" s="4" t="inlineStr">
         <is>
@@ -52722,12 +52810,12 @@
       <c r="P53" s="4" t="n"/>
       <c r="Q53" s="4" t="n"/>
       <c r="R53" s="4" t="n"/>
-      <c r="S53" s="4" t="n"/>
-      <c r="T53" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="S53" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T53" s="4" t="n"/>
       <c r="U53" s="4" t="n"/>
       <c r="V53" s="4" t="inlineStr">
         <is>
@@ -52748,23 +52836,23 @@
       <c r="Z53" s="4" t="n"/>
       <c r="AA53" s="4" t="n"/>
       <c r="AB53" s="4" t="n"/>
-      <c r="AC53" s="4" t="n"/>
+      <c r="AC53" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD53" s="4" t="n"/>
       <c r="AE53" s="4" t="n"/>
       <c r="AF53" s="4" t="n"/>
-      <c r="AG53" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG53" s="4" t="n"/>
       <c r="AH53" s="4" t="n"/>
-      <c r="AI53" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AI53" s="4" t="n"/>
       <c r="AJ53" s="4" t="n"/>
-      <c r="AK53" s="4" t="n"/>
+      <c r="AK53" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL53" s="4" t="n"/>
       <c r="AM53" s="4" t="n"/>
       <c r="AN53" s="4" t="n"/>
@@ -52843,23 +52931,23 @@
       <c r="Z54" s="4" t="n"/>
       <c r="AA54" s="4" t="n"/>
       <c r="AB54" s="4" t="n"/>
-      <c r="AC54" s="4" t="n"/>
+      <c r="AC54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD54" s="4" t="n"/>
       <c r="AE54" s="4" t="n"/>
       <c r="AF54" s="4" t="n"/>
-      <c r="AG54" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG54" s="4" t="n"/>
       <c r="AH54" s="4" t="n"/>
-      <c r="AI54" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AI54" s="4" t="n"/>
       <c r="AJ54" s="4" t="n"/>
-      <c r="AK54" s="4" t="n"/>
+      <c r="AK54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL54" s="4" t="n"/>
       <c r="AM54" s="4" t="n"/>
       <c r="AN54" s="4" t="n"/>
@@ -52918,14 +53006,14 @@
       <c r="N55" s="4" t="n"/>
       <c r="O55" s="4" t="n"/>
       <c r="P55" s="4" t="n"/>
-      <c r="Q55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q55" s="4" t="n"/>
       <c r="R55" s="4" t="n"/>
       <c r="S55" s="4" t="n"/>
-      <c r="T55" s="4" t="n"/>
+      <c r="T55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U55" s="4" t="n"/>
       <c r="V55" s="4" t="n"/>
       <c r="W55" s="4" t="n"/>
@@ -52937,22 +53025,22 @@
       <c r="AC55" s="4" t="n"/>
       <c r="AD55" s="4" t="n"/>
       <c r="AE55" s="4" t="n"/>
-      <c r="AF55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AG55" s="4" t="n"/>
+      <c r="AF55" s="4" t="n"/>
+      <c r="AG55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AH55" s="4" t="n"/>
-      <c r="AI55" s="4" t="n"/>
+      <c r="AI55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AJ55" s="4" t="n"/>
       <c r="AK55" s="4" t="n"/>
       <c r="AL55" s="4" t="n"/>
-      <c r="AM55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AM55" s="4" t="n"/>
       <c r="AN55" s="4" t="n"/>
       <c r="AO55" s="4" t="n"/>
       <c r="AP55" s="4" t="n"/>
@@ -53025,14 +53113,14 @@
       <c r="N56" s="4" t="n"/>
       <c r="O56" s="4" t="n"/>
       <c r="P56" s="4" t="n"/>
-      <c r="Q56" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q56" s="4" t="n"/>
       <c r="R56" s="4" t="n"/>
       <c r="S56" s="4" t="n"/>
-      <c r="T56" s="4" t="n"/>
+      <c r="T56" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U56" s="4" t="n"/>
       <c r="V56" s="4" t="inlineStr">
         <is>
@@ -53045,23 +53133,23 @@
       <c r="Z56" s="4" t="n"/>
       <c r="AA56" s="4" t="n"/>
       <c r="AB56" s="4" t="n"/>
-      <c r="AC56" s="4" t="n"/>
+      <c r="AC56" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD56" s="4" t="n"/>
       <c r="AE56" s="4" t="n"/>
       <c r="AF56" s="4" t="n"/>
-      <c r="AG56" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG56" s="4" t="n"/>
       <c r="AH56" s="4" t="n"/>
-      <c r="AI56" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AI56" s="4" t="n"/>
       <c r="AJ56" s="4" t="n"/>
-      <c r="AK56" s="4" t="n"/>
+      <c r="AK56" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL56" s="4" t="n"/>
       <c r="AM56" s="4" t="n"/>
       <c r="AN56" s="4" t="n"/>
@@ -53138,13 +53226,17 @@
       </c>
       <c r="Q57" s="4" t="n"/>
       <c r="R57" s="4" t="n"/>
-      <c r="S57" s="4" t="n"/>
-      <c r="T57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U57" s="4" t="n"/>
+      <c r="S57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T57" s="4" t="n"/>
+      <c r="U57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="V57" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -53156,23 +53248,23 @@
       <c r="Z57" s="4" t="n"/>
       <c r="AA57" s="4" t="n"/>
       <c r="AB57" s="4" t="n"/>
-      <c r="AC57" s="4" t="n"/>
+      <c r="AC57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD57" s="4" t="n"/>
       <c r="AE57" s="4" t="n"/>
       <c r="AF57" s="4" t="n"/>
-      <c r="AG57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG57" s="4" t="n"/>
       <c r="AH57" s="4" t="n"/>
-      <c r="AI57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AI57" s="4" t="n"/>
       <c r="AJ57" s="4" t="n"/>
-      <c r="AK57" s="4" t="n"/>
+      <c r="AK57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL57" s="4" t="n"/>
       <c r="AM57" s="4" t="n"/>
       <c r="AN57" s="4" t="n"/>
@@ -53239,7 +53331,11 @@
       <c r="N58" s="4" t="n"/>
       <c r="O58" s="4" t="n"/>
       <c r="P58" s="4" t="n"/>
-      <c r="Q58" s="4" t="n"/>
+      <c r="Q58" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="R58" s="4" t="n"/>
       <c r="S58" s="4" t="n"/>
       <c r="T58" s="4" t="n"/>
@@ -53255,23 +53351,23 @@
         </is>
       </c>
       <c r="AB58" s="4" t="n"/>
-      <c r="AC58" s="4" t="n"/>
+      <c r="AC58" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD58" s="4" t="n"/>
       <c r="AE58" s="4" t="n"/>
       <c r="AF58" s="4" t="n"/>
-      <c r="AG58" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG58" s="4" t="n"/>
       <c r="AH58" s="4" t="n"/>
-      <c r="AI58" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AI58" s="4" t="n"/>
       <c r="AJ58" s="4" t="n"/>
-      <c r="AK58" s="4" t="n"/>
+      <c r="AK58" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL58" s="4" t="n"/>
       <c r="AM58" s="4" t="n"/>
       <c r="AN58" s="4" t="n"/>
@@ -53330,14 +53426,14 @@
       <c r="N59" s="4" t="n"/>
       <c r="O59" s="4" t="n"/>
       <c r="P59" s="4" t="n"/>
-      <c r="Q59" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q59" s="4" t="n"/>
       <c r="R59" s="4" t="n"/>
       <c r="S59" s="4" t="n"/>
-      <c r="T59" s="4" t="n"/>
+      <c r="T59" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U59" s="4" t="n"/>
       <c r="V59" s="4" t="n"/>
       <c r="W59" s="4" t="n"/>
@@ -53349,12 +53445,12 @@
       <c r="AC59" s="4" t="n"/>
       <c r="AD59" s="4" t="n"/>
       <c r="AE59" s="4" t="n"/>
-      <c r="AF59" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AG59" s="4" t="n"/>
+      <c r="AF59" s="4" t="n"/>
+      <c r="AG59" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AH59" s="4" t="n"/>
       <c r="AI59" s="4" t="inlineStr">
         <is>
@@ -53465,23 +53561,23 @@
       <c r="Z60" s="4" t="n"/>
       <c r="AA60" s="4" t="n"/>
       <c r="AB60" s="4" t="n"/>
-      <c r="AC60" s="4" t="n"/>
+      <c r="AC60" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD60" s="4" t="n"/>
       <c r="AE60" s="4" t="n"/>
       <c r="AF60" s="4" t="n"/>
-      <c r="AG60" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG60" s="4" t="n"/>
       <c r="AH60" s="4" t="n"/>
-      <c r="AI60" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AI60" s="4" t="n"/>
       <c r="AJ60" s="4" t="n"/>
-      <c r="AK60" s="4" t="n"/>
+      <c r="AK60" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL60" s="4" t="n"/>
       <c r="AM60" s="4" t="n"/>
       <c r="AN60" s="4" t="n"/>
@@ -53540,14 +53636,14 @@
       <c r="N61" s="4" t="n"/>
       <c r="O61" s="4" t="n"/>
       <c r="P61" s="4" t="n"/>
-      <c r="Q61" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q61" s="4" t="n"/>
       <c r="R61" s="4" t="n"/>
       <c r="S61" s="4" t="n"/>
-      <c r="T61" s="4" t="n"/>
+      <c r="T61" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U61" s="4" t="n"/>
       <c r="V61" s="4" t="n"/>
       <c r="W61" s="4" t="n"/>
@@ -53562,17 +53658,17 @@
       </c>
       <c r="AC61" s="4" t="n"/>
       <c r="AD61" s="4" t="n"/>
-      <c r="AE61" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AE61" s="4" t="n"/>
       <c r="AF61" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AG61" s="4" t="n"/>
+      <c r="AG61" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AH61" s="4" t="n"/>
       <c r="AI61" s="4" t="inlineStr">
         <is>
@@ -53669,7 +53765,11 @@
         </is>
       </c>
       <c r="R62" s="4" t="n"/>
-      <c r="S62" s="4" t="n"/>
+      <c r="S62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="T62" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -53690,22 +53790,22 @@
       <c r="AC62" s="4" t="n"/>
       <c r="AD62" s="4" t="n"/>
       <c r="AE62" s="4" t="n"/>
-      <c r="AF62" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AG62" s="4" t="n"/>
+      <c r="AF62" s="4" t="n"/>
+      <c r="AG62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AH62" s="4" t="n"/>
-      <c r="AI62" s="4" t="n"/>
+      <c r="AI62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AJ62" s="4" t="n"/>
       <c r="AK62" s="4" t="n"/>
       <c r="AL62" s="4" t="n"/>
-      <c r="AM62" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AM62" s="4" t="n"/>
       <c r="AN62" s="4" t="n"/>
       <c r="AO62" s="4" t="n"/>
       <c r="AP62" s="4" t="n"/>
@@ -53782,14 +53882,14 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="Q63" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q63" s="4" t="n"/>
       <c r="R63" s="4" t="n"/>
       <c r="S63" s="4" t="n"/>
-      <c r="T63" s="4" t="n"/>
+      <c r="T63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U63" s="4" t="n"/>
       <c r="V63" s="4" t="inlineStr">
         <is>
@@ -53802,37 +53902,37 @@
       <c r="Z63" s="4" t="n"/>
       <c r="AA63" s="4" t="n"/>
       <c r="AB63" s="4" t="n"/>
-      <c r="AC63" s="4" t="n"/>
+      <c r="AC63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD63" s="4" t="n"/>
       <c r="AE63" s="4" t="n"/>
-      <c r="AF63" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AF63" s="4" t="n"/>
       <c r="AG63" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AH63" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AH63" s="4" t="n"/>
       <c r="AI63" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AJ63" s="4" t="n"/>
-      <c r="AK63" s="4" t="n"/>
+      <c r="AJ63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AK63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL63" s="4" t="n"/>
-      <c r="AM63" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AM63" s="4" t="n"/>
       <c r="AN63" s="4" t="n"/>
       <c r="AO63" s="4" t="inlineStr">
         <is>
@@ -53897,13 +53997,13 @@
       <c r="N64" s="4" t="n"/>
       <c r="O64" s="4" t="n"/>
       <c r="P64" s="4" t="n"/>
-      <c r="Q64" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q64" s="4" t="n"/>
       <c r="R64" s="4" t="n"/>
-      <c r="S64" s="4" t="n"/>
+      <c r="S64" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="T64" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -53921,23 +54021,23 @@
         </is>
       </c>
       <c r="AB64" s="4" t="n"/>
-      <c r="AC64" s="4" t="n"/>
+      <c r="AC64" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD64" s="4" t="n"/>
       <c r="AE64" s="4" t="n"/>
       <c r="AF64" s="4" t="n"/>
-      <c r="AG64" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG64" s="4" t="n"/>
       <c r="AH64" s="4" t="n"/>
-      <c r="AI64" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AI64" s="4" t="n"/>
       <c r="AJ64" s="4" t="n"/>
-      <c r="AK64" s="4" t="n"/>
+      <c r="AK64" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL64" s="4" t="n"/>
       <c r="AM64" s="4" t="n"/>
       <c r="AN64" s="4" t="n"/>
@@ -53998,12 +54098,12 @@
       <c r="P65" s="4" t="n"/>
       <c r="Q65" s="4" t="n"/>
       <c r="R65" s="4" t="n"/>
-      <c r="S65" s="4" t="n"/>
-      <c r="T65" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="S65" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T65" s="4" t="n"/>
       <c r="U65" s="4" t="n"/>
       <c r="V65" s="4" t="inlineStr">
         <is>
@@ -54020,23 +54120,23 @@
         </is>
       </c>
       <c r="AB65" s="4" t="n"/>
-      <c r="AC65" s="4" t="n"/>
+      <c r="AC65" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD65" s="4" t="n"/>
       <c r="AE65" s="4" t="n"/>
       <c r="AF65" s="4" t="n"/>
-      <c r="AG65" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG65" s="4" t="n"/>
       <c r="AH65" s="4" t="n"/>
-      <c r="AI65" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AI65" s="4" t="n"/>
       <c r="AJ65" s="4" t="n"/>
-      <c r="AK65" s="4" t="n"/>
+      <c r="AK65" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL65" s="4" t="n"/>
       <c r="AM65" s="4" t="n"/>
       <c r="AN65" s="4" t="n"/>
@@ -54119,23 +54219,23 @@
       <c r="Z66" s="4" t="n"/>
       <c r="AA66" s="4" t="n"/>
       <c r="AB66" s="4" t="n"/>
-      <c r="AC66" s="4" t="n"/>
+      <c r="AC66" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD66" s="4" t="n"/>
       <c r="AE66" s="4" t="n"/>
       <c r="AF66" s="4" t="n"/>
-      <c r="AG66" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG66" s="4" t="n"/>
       <c r="AH66" s="4" t="n"/>
-      <c r="AI66" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AI66" s="4" t="n"/>
       <c r="AJ66" s="4" t="n"/>
-      <c r="AK66" s="4" t="n"/>
+      <c r="AK66" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL66" s="4" t="n"/>
       <c r="AM66" s="4" t="n"/>
       <c r="AN66" s="4" t="n"/>
@@ -54192,7 +54292,11 @@
         </is>
       </c>
       <c r="R67" s="4" t="n"/>
-      <c r="S67" s="4" t="n"/>
+      <c r="S67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="T67" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -54216,18 +54320,14 @@
       </c>
       <c r="AC67" s="4" t="n"/>
       <c r="AD67" s="4" t="n"/>
-      <c r="AE67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AF67" s="4" t="n"/>
+      <c r="AE67" s="4" t="n"/>
+      <c r="AF67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AG67" s="4" t="n"/>
-      <c r="AH67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AH67" s="4" t="n"/>
       <c r="AI67" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -54243,7 +54343,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AL67" s="4" t="n"/>
+      <c r="AL67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AM67" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -54315,12 +54419,12 @@
       <c r="P68" s="4" t="n"/>
       <c r="Q68" s="4" t="n"/>
       <c r="R68" s="4" t="n"/>
-      <c r="S68" s="4" t="n"/>
-      <c r="T68" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="S68" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T68" s="4" t="n"/>
       <c r="U68" s="4" t="n"/>
       <c r="V68" s="4" t="n"/>
       <c r="W68" s="4" t="n"/>
@@ -54333,23 +54437,23 @@
         </is>
       </c>
       <c r="AB68" s="4" t="n"/>
-      <c r="AC68" s="4" t="n"/>
+      <c r="AC68" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD68" s="4" t="n"/>
       <c r="AE68" s="4" t="n"/>
       <c r="AF68" s="4" t="n"/>
-      <c r="AG68" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG68" s="4" t="n"/>
       <c r="AH68" s="4" t="n"/>
-      <c r="AI68" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AI68" s="4" t="n"/>
       <c r="AJ68" s="4" t="n"/>
-      <c r="AK68" s="4" t="n"/>
+      <c r="AK68" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL68" s="4" t="n"/>
       <c r="AM68" s="4" t="n"/>
       <c r="AN68" s="4" t="n"/>
@@ -54412,14 +54516,14 @@
       <c r="N69" s="4" t="n"/>
       <c r="O69" s="4" t="n"/>
       <c r="P69" s="4" t="n"/>
-      <c r="Q69" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q69" s="4" t="n"/>
       <c r="R69" s="4" t="n"/>
       <c r="S69" s="4" t="n"/>
-      <c r="T69" s="4" t="n"/>
+      <c r="T69" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U69" s="4" t="n"/>
       <c r="V69" s="4" t="n"/>
       <c r="W69" s="4" t="n"/>
@@ -54440,13 +54544,13 @@
         </is>
       </c>
       <c r="AJ69" s="4" t="n"/>
-      <c r="AK69" s="4" t="n"/>
+      <c r="AK69" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL69" s="4" t="n"/>
-      <c r="AM69" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AM69" s="4" t="n"/>
       <c r="AN69" s="4" t="n"/>
       <c r="AO69" s="4" t="n"/>
       <c r="AP69" s="4" t="n"/>
@@ -54499,14 +54603,14 @@
       <c r="N70" s="4" t="n"/>
       <c r="O70" s="4" t="n"/>
       <c r="P70" s="4" t="n"/>
-      <c r="Q70" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q70" s="4" t="n"/>
       <c r="R70" s="4" t="n"/>
       <c r="S70" s="4" t="n"/>
-      <c r="T70" s="4" t="n"/>
+      <c r="T70" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U70" s="4" t="n"/>
       <c r="V70" s="4" t="n"/>
       <c r="W70" s="4" t="n"/>
@@ -54521,14 +54625,18 @@
       </c>
       <c r="AC70" s="4" t="n"/>
       <c r="AD70" s="4" t="n"/>
-      <c r="AE70" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AF70" s="4" t="n"/>
+      <c r="AE70" s="4" t="n"/>
+      <c r="AF70" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AG70" s="4" t="n"/>
-      <c r="AH70" s="4" t="n"/>
+      <c r="AH70" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AI70" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -54540,11 +54648,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AL70" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AL70" s="4" t="n"/>
       <c r="AM70" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -54566,14 +54670,14 @@
       <c r="BA70" s="4" t="n"/>
       <c r="BB70" s="4" t="n"/>
       <c r="BC70" s="4" t="n"/>
-      <c r="BD70" s="4" t="n"/>
+      <c r="BD70" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE70" s="4" t="n"/>
       <c r="BF70" s="4" t="n"/>
-      <c r="BG70" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BG70" s="4" t="n"/>
       <c r="BH70" s="4" t="n"/>
       <c r="BI70" s="4" t="n"/>
     </row>
@@ -54622,23 +54726,23 @@
       <c r="Z71" s="4" t="n"/>
       <c r="AA71" s="4" t="n"/>
       <c r="AB71" s="4" t="n"/>
-      <c r="AC71" s="4" t="n"/>
+      <c r="AC71" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD71" s="4" t="n"/>
       <c r="AE71" s="4" t="n"/>
       <c r="AF71" s="4" t="n"/>
-      <c r="AG71" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG71" s="4" t="n"/>
       <c r="AH71" s="4" t="n"/>
-      <c r="AI71" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AI71" s="4" t="n"/>
       <c r="AJ71" s="4" t="n"/>
-      <c r="AK71" s="4" t="n"/>
+      <c r="AK71" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL71" s="4" t="n"/>
       <c r="AM71" s="4" t="n"/>
       <c r="AN71" s="4" t="n"/>
@@ -54689,13 +54793,13 @@
       <c r="N72" s="4" t="n"/>
       <c r="O72" s="4" t="n"/>
       <c r="P72" s="4" t="n"/>
-      <c r="Q72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q72" s="4" t="n"/>
       <c r="R72" s="4" t="n"/>
-      <c r="S72" s="4" t="n"/>
+      <c r="S72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="T72" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -54712,24 +54816,28 @@
       <c r="AC72" s="4" t="n"/>
       <c r="AD72" s="4" t="n"/>
       <c r="AE72" s="4" t="n"/>
-      <c r="AF72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AG72" s="4" t="n"/>
+      <c r="AF72" s="4" t="n"/>
+      <c r="AG72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AH72" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AI72" s="4" t="n"/>
-      <c r="AJ72" s="4" t="n"/>
-      <c r="AK72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AI72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AJ72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AK72" s="4" t="n"/>
       <c r="AL72" s="4" t="n"/>
       <c r="AM72" s="4" t="inlineStr">
         <is>
@@ -54792,14 +54900,14 @@
       <c r="N73" s="4" t="n"/>
       <c r="O73" s="4" t="n"/>
       <c r="P73" s="4" t="n"/>
-      <c r="Q73" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q73" s="4" t="n"/>
       <c r="R73" s="4" t="n"/>
       <c r="S73" s="4" t="n"/>
-      <c r="T73" s="4" t="n"/>
+      <c r="T73" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U73" s="4" t="n"/>
       <c r="V73" s="4" t="n"/>
       <c r="W73" s="4" t="n"/>
@@ -54815,12 +54923,12 @@
       <c r="AC73" s="4" t="n"/>
       <c r="AD73" s="4" t="n"/>
       <c r="AE73" s="4" t="n"/>
-      <c r="AF73" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AG73" s="4" t="n"/>
+      <c r="AF73" s="4" t="n"/>
+      <c r="AG73" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AH73" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -54831,7 +54939,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AJ73" s="4" t="n"/>
+      <c r="AJ73" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AK73" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -54907,13 +55019,13 @@
       <c r="N74" s="4" t="n"/>
       <c r="O74" s="4" t="n"/>
       <c r="P74" s="4" t="n"/>
-      <c r="Q74" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q74" s="4" t="n"/>
       <c r="R74" s="4" t="n"/>
-      <c r="S74" s="4" t="n"/>
+      <c r="S74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="T74" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -54939,27 +55051,27 @@
         </is>
       </c>
       <c r="AB74" s="4" t="n"/>
-      <c r="AC74" s="4" t="n"/>
+      <c r="AC74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD74" s="4" t="n"/>
       <c r="AE74" s="4" t="n"/>
-      <c r="AF74" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AF74" s="4" t="n"/>
       <c r="AG74" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
       <c r="AH74" s="4" t="n"/>
-      <c r="AI74" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AI74" s="4" t="n"/>
       <c r="AJ74" s="4" t="n"/>
-      <c r="AK74" s="4" t="n"/>
+      <c r="AK74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL74" s="4" t="n"/>
       <c r="AM74" s="4" t="n"/>
       <c r="AN74" s="4" t="n"/>
@@ -55008,12 +55120,12 @@
       <c r="P75" s="4" t="n"/>
       <c r="Q75" s="4" t="n"/>
       <c r="R75" s="4" t="n"/>
-      <c r="S75" s="4" t="n"/>
-      <c r="T75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="S75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T75" s="4" t="n"/>
       <c r="U75" s="4" t="n"/>
       <c r="V75" s="4" t="n"/>
       <c r="W75" s="4" t="n"/>
@@ -55038,25 +55150,21 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AC75" s="4" t="n"/>
+      <c r="AC75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD75" s="4" t="n"/>
-      <c r="AE75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AF75" s="4" t="n"/>
-      <c r="AG75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AE75" s="4" t="n"/>
+      <c r="AF75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AG75" s="4" t="n"/>
       <c r="AH75" s="4" t="n"/>
-      <c r="AI75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AI75" s="4" t="n"/>
       <c r="AJ75" s="4" t="n"/>
       <c r="AK75" s="4" t="inlineStr">
         <is>
@@ -55064,7 +55172,11 @@
         </is>
       </c>
       <c r="AL75" s="4" t="n"/>
-      <c r="AM75" s="4" t="n"/>
+      <c r="AM75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AN75" s="4" t="n"/>
       <c r="AO75" s="4" t="n"/>
       <c r="AP75" s="4" t="n"/>
@@ -55113,14 +55225,14 @@
       <c r="N76" s="4" t="n"/>
       <c r="O76" s="4" t="n"/>
       <c r="P76" s="4" t="n"/>
-      <c r="Q76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q76" s="4" t="n"/>
       <c r="R76" s="4" t="n"/>
       <c r="S76" s="4" t="n"/>
-      <c r="T76" s="4" t="n"/>
+      <c r="T76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U76" s="4" t="n"/>
       <c r="V76" s="4" t="n"/>
       <c r="W76" s="4" t="n"/>
@@ -55132,19 +55244,19 @@
       <c r="AC76" s="4" t="n"/>
       <c r="AD76" s="4" t="n"/>
       <c r="AE76" s="4" t="n"/>
-      <c r="AF76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AG76" s="4" t="n"/>
-      <c r="AH76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AF76" s="4" t="n"/>
+      <c r="AG76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AH76" s="4" t="n"/>
       <c r="AI76" s="4" t="n"/>
-      <c r="AJ76" s="4" t="n"/>
+      <c r="AJ76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AK76" s="4" t="n"/>
       <c r="AL76" s="4" t="n"/>
       <c r="AM76" s="4" t="n"/>
@@ -55173,12 +55285,12 @@
       </c>
       <c r="BC76" s="4" t="n"/>
       <c r="BD76" s="4" t="n"/>
-      <c r="BE76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BF76" s="4" t="n"/>
+      <c r="BE76" s="4" t="n"/>
+      <c r="BF76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BG76" s="4" t="n"/>
       <c r="BH76" s="4" t="inlineStr">
         <is>
@@ -55252,23 +55364,23 @@
       <c r="Z77" s="4" t="n"/>
       <c r="AA77" s="4" t="n"/>
       <c r="AB77" s="4" t="n"/>
-      <c r="AC77" s="4" t="n"/>
+      <c r="AC77" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD77" s="4" t="n"/>
       <c r="AE77" s="4" t="n"/>
       <c r="AF77" s="4" t="n"/>
-      <c r="AG77" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG77" s="4" t="n"/>
       <c r="AH77" s="4" t="n"/>
-      <c r="AI77" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AI77" s="4" t="n"/>
       <c r="AJ77" s="4" t="n"/>
-      <c r="AK77" s="4" t="n"/>
+      <c r="AK77" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL77" s="4" t="n"/>
       <c r="AM77" s="4" t="n"/>
       <c r="AN77" s="4" t="n"/>
@@ -55351,23 +55463,23 @@
       <c r="Z78" s="4" t="n"/>
       <c r="AA78" s="4" t="n"/>
       <c r="AB78" s="4" t="n"/>
-      <c r="AC78" s="4" t="n"/>
+      <c r="AC78" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD78" s="4" t="n"/>
       <c r="AE78" s="4" t="n"/>
       <c r="AF78" s="4" t="n"/>
-      <c r="AG78" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG78" s="4" t="n"/>
       <c r="AH78" s="4" t="n"/>
-      <c r="AI78" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AI78" s="4" t="n"/>
       <c r="AJ78" s="4" t="n"/>
-      <c r="AK78" s="4" t="n"/>
+      <c r="AK78" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL78" s="4" t="n"/>
       <c r="AM78" s="4" t="n"/>
       <c r="AN78" s="4" t="n"/>
@@ -55442,7 +55554,11 @@
       <c r="R79" s="4" t="n"/>
       <c r="S79" s="4" t="n"/>
       <c r="T79" s="4" t="n"/>
-      <c r="U79" s="4" t="n"/>
+      <c r="U79" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="V79" s="4" t="n"/>
       <c r="W79" s="4" t="n"/>
       <c r="X79" s="4" t="n"/>
@@ -55454,23 +55570,23 @@
       </c>
       <c r="AA79" s="4" t="n"/>
       <c r="AB79" s="4" t="n"/>
-      <c r="AC79" s="4" t="n"/>
+      <c r="AC79" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD79" s="4" t="n"/>
       <c r="AE79" s="4" t="n"/>
       <c r="AF79" s="4" t="n"/>
-      <c r="AG79" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG79" s="4" t="n"/>
       <c r="AH79" s="4" t="n"/>
-      <c r="AI79" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AI79" s="4" t="n"/>
       <c r="AJ79" s="4" t="n"/>
-      <c r="AK79" s="4" t="n"/>
+      <c r="AK79" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL79" s="4" t="n"/>
       <c r="AM79" s="4" t="n"/>
       <c r="AN79" s="4" t="n"/>
@@ -55553,23 +55669,23 @@
       <c r="Z80" s="4" t="n"/>
       <c r="AA80" s="4" t="n"/>
       <c r="AB80" s="4" t="n"/>
-      <c r="AC80" s="4" t="n"/>
+      <c r="AC80" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD80" s="4" t="n"/>
       <c r="AE80" s="4" t="n"/>
       <c r="AF80" s="4" t="n"/>
-      <c r="AG80" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG80" s="4" t="n"/>
       <c r="AH80" s="4" t="n"/>
-      <c r="AI80" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AI80" s="4" t="n"/>
       <c r="AJ80" s="4" t="n"/>
-      <c r="AK80" s="4" t="n"/>
+      <c r="AK80" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AL80" s="4" t="n"/>
       <c r="AM80" s="4" t="n"/>
       <c r="AN80" s="4" t="n"/>
@@ -55727,7 +55843,11 @@
       <c r="N82" s="4" t="n"/>
       <c r="O82" s="4" t="n"/>
       <c r="P82" s="4" t="n"/>
-      <c r="Q82" s="4" t="n"/>
+      <c r="Q82" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="R82" s="4" t="n"/>
       <c r="S82" s="4" t="n"/>
       <c r="T82" s="4" t="n"/>
@@ -55895,12 +56015,12 @@
       <c r="P84" s="4" t="n"/>
       <c r="Q84" s="4" t="n"/>
       <c r="R84" s="4" t="n"/>
-      <c r="S84" s="4" t="n"/>
-      <c r="T84" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="S84" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T84" s="4" t="n"/>
       <c r="U84" s="4" t="n"/>
       <c r="V84" s="4" t="n"/>
       <c r="W84" s="4" t="n"/>
@@ -55909,12 +56029,12 @@
       <c r="Z84" s="4" t="n"/>
       <c r="AA84" s="4" t="n"/>
       <c r="AB84" s="4" t="n"/>
-      <c r="AC84" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AD84" s="4" t="n"/>
+      <c r="AC84" s="4" t="n"/>
+      <c r="AD84" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE84" s="4" t="n"/>
       <c r="AF84" s="4" t="n"/>
       <c r="AG84" s="4" t="n"/>
@@ -56026,14 +56146,14 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>速尾</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>9x8</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>速尾</t>
-        </is>
-      </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
           <t>c2</t>
@@ -56051,12 +56171,12 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>fp1</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>秋王</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>fp1</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
@@ -56098,12 +56218,12 @@
       </c>
       <c r="C2" s="4" t="n"/>
       <c r="D2" s="4" t="n"/>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="n"/>
+      <c r="E2" s="4" t="n"/>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G2" s="4" t="n"/>
       <c r="H2" s="4" t="n"/>
       <c r="I2" s="4" t="inlineStr">
@@ -56144,12 +56264,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E3" s="4" t="n"/>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="n"/>
       <c r="G3" s="4" t="n"/>
       <c r="H3" s="4" t="n"/>
       <c r="I3" s="4" t="n"/>
@@ -56170,12 +56290,12 @@
       </c>
       <c r="C4" s="4" t="n"/>
       <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="n"/>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="n"/>
       <c r="G4" s="4" t="n"/>
       <c r="H4" s="4" t="n"/>
       <c r="I4" s="4" t="n"/>
@@ -56213,12 +56333,12 @@
       </c>
       <c r="H5" s="4" t="n"/>
       <c r="I5" s="4" t="n"/>
-      <c r="J5" s="4" t="n"/>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="n"/>
       <c r="L5" s="4" t="n"/>
       <c r="M5" s="4" t="inlineStr">
         <is>
@@ -56242,12 +56362,12 @@
       </c>
       <c r="C6" s="4" t="n"/>
       <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G6" s="4" t="n"/>
       <c r="H6" s="4" t="n"/>
       <c r="I6" s="4" t="inlineStr">
@@ -56255,12 +56375,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="n"/>
+      <c r="J6" s="4" t="n"/>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="L6" s="4" t="n"/>
       <c r="M6" s="4" t="n"/>
       <c r="N6" s="4" t="inlineStr">
@@ -56284,12 +56404,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="n"/>
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -56297,12 +56417,12 @@
       </c>
       <c r="H7" s="4" t="n"/>
       <c r="I7" s="4" t="n"/>
-      <c r="J7" s="4" t="n"/>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="n"/>
       <c r="L7" s="4" t="n"/>
       <c r="M7" s="4" t="n"/>
       <c r="N7" s="4" t="n"/>
@@ -56318,12 +56438,12 @@
       </c>
       <c r="C8" s="4" t="n"/>
       <c r="D8" s="4" t="n"/>
-      <c r="E8" s="4" t="n"/>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="n"/>
       <c r="G8" s="4" t="n"/>
       <c r="H8" s="4" t="n"/>
       <c r="I8" s="4" t="n"/>
@@ -56344,12 +56464,12 @@
       </c>
       <c r="C9" s="4" t="n"/>
       <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="n"/>
+      <c r="E9" s="4" t="n"/>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -56361,12 +56481,12 @@
         </is>
       </c>
       <c r="I9" s="4" t="n"/>
-      <c r="J9" s="4" t="n"/>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="n"/>
       <c r="L9" s="4" t="n"/>
       <c r="M9" s="4" t="n"/>
       <c r="N9" s="4" t="n"/>
@@ -56390,12 +56510,12 @@
       </c>
       <c r="C10" s="4" t="n"/>
       <c r="D10" s="4" t="n"/>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="n"/>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -56512,12 +56632,12 @@
       </c>
       <c r="C13" s="4" t="n"/>
       <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="n"/>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="n"/>
       <c r="G13" s="4" t="n"/>
       <c r="H13" s="4" t="n"/>
       <c r="I13" s="4" t="n"/>
@@ -56546,12 +56666,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -56648,12 +56768,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="n"/>
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G17" s="4" t="n"/>
       <c r="H17" s="4" t="n"/>
       <c r="I17" s="4" t="inlineStr">
@@ -56694,12 +56814,12 @@
       </c>
       <c r="C18" s="4" t="n"/>
       <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="n"/>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="n"/>
       <c r="G18" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -56745,12 +56865,12 @@
       <c r="G19" s="4" t="n"/>
       <c r="H19" s="4" t="n"/>
       <c r="I19" s="4" t="n"/>
-      <c r="J19" s="4" t="n"/>
-      <c r="K19" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="n"/>
       <c r="L19" s="4" t="n"/>
       <c r="M19" s="4" t="inlineStr">
         <is>
@@ -56770,12 +56890,12 @@
       </c>
       <c r="C20" s="4" t="n"/>
       <c r="D20" s="4" t="n"/>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="n"/>
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G20" s="4" t="n"/>
       <c r="H20" s="4" t="n"/>
       <c r="I20" s="4" t="inlineStr">
@@ -56812,12 +56932,12 @@
       </c>
       <c r="C21" s="4" t="n"/>
       <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="n"/>
       <c r="G21" s="4" t="n"/>
       <c r="H21" s="4" t="n"/>
       <c r="I21" s="4" t="n"/>
@@ -56872,12 +56992,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E23" s="4" t="n"/>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="n"/>
       <c r="G23" s="4" t="n"/>
       <c r="H23" s="4" t="n"/>
       <c r="I23" s="4" t="n"/>
@@ -56919,12 +57039,12 @@
         </is>
       </c>
       <c r="I24" s="4" t="n"/>
-      <c r="J24" s="4" t="n"/>
-      <c r="K24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="n"/>
       <c r="L24" s="4" t="n"/>
       <c r="M24" s="4" t="n"/>
       <c r="N24" s="4" t="n"/>
@@ -56940,12 +57060,12 @@
       </c>
       <c r="C25" s="4" t="n"/>
       <c r="D25" s="4" t="n"/>
-      <c r="E25" s="4" t="n"/>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="n"/>
       <c r="G25" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -56978,12 +57098,12 @@
       </c>
       <c r="C26" s="4" t="n"/>
       <c r="D26" s="4" t="n"/>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="n"/>
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -57050,12 +57170,12 @@
       </c>
       <c r="C28" s="4" t="n"/>
       <c r="D28" s="4" t="n"/>
-      <c r="E28" s="4" t="n"/>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="n"/>
       <c r="G28" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -57118,12 +57238,12 @@
       </c>
       <c r="C30" s="4" t="n"/>
       <c r="D30" s="4" t="n"/>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="n"/>
+      <c r="E30" s="4" t="n"/>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G30" s="4" t="n"/>
       <c r="H30" s="4" t="n"/>
       <c r="I30" s="4" t="inlineStr">
@@ -57160,21 +57280,21 @@
       </c>
       <c r="C31" s="4" t="n"/>
       <c r="D31" s="4" t="n"/>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="n"/>
+      <c r="E31" s="4" t="n"/>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G31" s="4" t="n"/>
       <c r="H31" s="4" t="n"/>
       <c r="I31" s="4" t="n"/>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K31" s="4" t="n"/>
+      <c r="J31" s="4" t="n"/>
+      <c r="K31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -57198,21 +57318,21 @@
       </c>
       <c r="C32" s="4" t="n"/>
       <c r="D32" s="4" t="n"/>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="n"/>
+      <c r="E32" s="4" t="n"/>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G32" s="4" t="n"/>
       <c r="H32" s="4" t="n"/>
       <c r="I32" s="4" t="n"/>
-      <c r="J32" s="4" t="n"/>
-      <c r="K32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="n"/>
       <c r="L32" s="4" t="n"/>
       <c r="M32" s="4" t="n"/>
       <c r="N32" s="4" t="n"/>
@@ -57232,12 +57352,12 @@
       </c>
       <c r="C33" s="4" t="n"/>
       <c r="D33" s="4" t="n"/>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="n"/>
+      <c r="E33" s="4" t="n"/>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G33" s="4" t="n"/>
       <c r="H33" s="4" t="n"/>
       <c r="I33" s="4" t="inlineStr">
@@ -57274,12 +57394,12 @@
       </c>
       <c r="C34" s="4" t="n"/>
       <c r="D34" s="4" t="n"/>
-      <c r="E34" s="4" t="n"/>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="n"/>
       <c r="G34" s="4" t="n"/>
       <c r="H34" s="4" t="n"/>
       <c r="I34" s="4" t="n"/>
@@ -57300,12 +57420,12 @@
       </c>
       <c r="C35" s="4" t="n"/>
       <c r="D35" s="4" t="n"/>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="n"/>
+      <c r="E35" s="4" t="n"/>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G35" s="4" t="n"/>
       <c r="H35" s="4" t="n"/>
       <c r="I35" s="4" t="inlineStr">
@@ -57313,12 +57433,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="J35" s="4" t="n"/>
-      <c r="K35" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="n"/>
       <c r="L35" s="4" t="n"/>
       <c r="M35" s="4" t="inlineStr">
         <is>
@@ -57351,12 +57471,12 @@
       <c r="G36" s="4" t="n"/>
       <c r="H36" s="4" t="n"/>
       <c r="I36" s="4" t="n"/>
-      <c r="J36" s="4" t="n"/>
-      <c r="K36" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="n"/>
       <c r="L36" s="4" t="n"/>
       <c r="M36" s="4" t="n"/>
       <c r="N36" s="4" t="n"/>
@@ -57376,21 +57496,21 @@
       </c>
       <c r="C37" s="4" t="n"/>
       <c r="D37" s="4" t="n"/>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="n"/>
+      <c r="E37" s="4" t="n"/>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G37" s="4" t="n"/>
       <c r="H37" s="4" t="n"/>
       <c r="I37" s="4" t="n"/>
-      <c r="J37" s="4" t="n"/>
-      <c r="K37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="n"/>
       <c r="L37" s="4" t="n"/>
       <c r="M37" s="4" t="inlineStr">
         <is>
@@ -57431,12 +57551,12 @@
         </is>
       </c>
       <c r="I38" s="4" t="n"/>
-      <c r="J38" s="4" t="n"/>
-      <c r="K38" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="n"/>
       <c r="L38" s="4" t="n"/>
       <c r="M38" s="4" t="n"/>
       <c r="N38" s="4" t="n"/>
@@ -57452,12 +57572,12 @@
       </c>
       <c r="C39" s="4" t="n"/>
       <c r="D39" s="4" t="n"/>
-      <c r="E39" s="4" t="n"/>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="n"/>
       <c r="G39" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -57494,21 +57614,21 @@
       </c>
       <c r="C40" s="4" t="n"/>
       <c r="D40" s="4" t="n"/>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="n"/>
+      <c r="E40" s="4" t="n"/>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G40" s="4" t="n"/>
       <c r="H40" s="4" t="n"/>
       <c r="I40" s="4" t="n"/>
-      <c r="J40" s="4" t="n"/>
-      <c r="K40" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="n"/>
       <c r="L40" s="4" t="n"/>
       <c r="M40" s="4" t="inlineStr">
         <is>
@@ -57558,12 +57678,12 @@
       </c>
       <c r="C42" s="4" t="n"/>
       <c r="D42" s="4" t="n"/>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="n"/>
+      <c r="E42" s="4" t="n"/>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -57575,12 +57695,12 @@
         </is>
       </c>
       <c r="I42" s="4" t="n"/>
-      <c r="J42" s="4" t="n"/>
-      <c r="K42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="n"/>
       <c r="L42" s="4" t="n"/>
       <c r="M42" s="4" t="n"/>
       <c r="N42" s="4" t="n"/>
@@ -57605,12 +57725,12 @@
       <c r="G43" s="4" t="n"/>
       <c r="H43" s="4" t="n"/>
       <c r="I43" s="4" t="n"/>
-      <c r="J43" s="4" t="n"/>
-      <c r="K43" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K43" s="4" t="n"/>
       <c r="L43" s="4" t="n"/>
       <c r="M43" s="4" t="n"/>
       <c r="N43" s="4" t="n"/>
@@ -57626,12 +57746,12 @@
       </c>
       <c r="C44" s="4" t="n"/>
       <c r="D44" s="4" t="n"/>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="n"/>
+      <c r="E44" s="4" t="n"/>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G44" s="4" t="n"/>
       <c r="H44" s="4" t="n"/>
       <c r="I44" s="4" t="inlineStr">
@@ -57639,12 +57759,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K44" s="4" t="n"/>
+      <c r="J44" s="4" t="n"/>
+      <c r="K44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="L44" s="4" t="n"/>
       <c r="M44" s="4" t="n"/>
       <c r="N44" s="4" t="n"/>
@@ -57698,21 +57818,21 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="n"/>
+      <c r="E46" s="4" t="n"/>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G46" s="4" t="n"/>
       <c r="H46" s="4" t="n"/>
       <c r="I46" s="4" t="n"/>
-      <c r="J46" s="4" t="n"/>
-      <c r="K46" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K46" s="4" t="n"/>
       <c r="L46" s="4" t="n"/>
       <c r="M46" s="4" t="inlineStr">
         <is>
@@ -57736,21 +57856,21 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="n"/>
+      <c r="E47" s="4" t="n"/>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G47" s="4" t="n"/>
       <c r="H47" s="4" t="n"/>
       <c r="I47" s="4" t="n"/>
-      <c r="J47" s="4" t="n"/>
-      <c r="K47" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K47" s="4" t="n"/>
       <c r="L47" s="4" t="n"/>
       <c r="M47" s="4" t="n"/>
       <c r="N47" s="4" t="n"/>
@@ -57770,12 +57890,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="n"/>
+      <c r="E48" s="4" t="n"/>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G48" s="4" t="n"/>
       <c r="H48" s="4" t="n"/>
       <c r="I48" s="4" t="n"/>
@@ -57800,12 +57920,12 @@
       </c>
       <c r="C49" s="4" t="n"/>
       <c r="D49" s="4" t="n"/>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="n"/>
+      <c r="E49" s="4" t="n"/>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G49" s="4" t="n"/>
       <c r="H49" s="4" t="n"/>
       <c r="I49" s="4" t="inlineStr">
@@ -57813,12 +57933,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="J49" s="4" t="n"/>
-      <c r="K49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K49" s="4" t="n"/>
       <c r="L49" s="4" t="n"/>
       <c r="M49" s="4" t="inlineStr">
         <is>
@@ -57838,12 +57958,12 @@
       </c>
       <c r="C50" s="4" t="n"/>
       <c r="D50" s="4" t="n"/>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="n"/>
+      <c r="E50" s="4" t="n"/>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G50" s="4" t="n"/>
       <c r="H50" s="4" t="n"/>
       <c r="I50" s="4" t="inlineStr">
@@ -57851,12 +57971,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="J50" s="4" t="n"/>
-      <c r="K50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K50" s="4" t="n"/>
       <c r="L50" s="4" t="n"/>
       <c r="M50" s="4" t="inlineStr">
         <is>
@@ -57876,12 +57996,12 @@
       </c>
       <c r="C51" s="4" t="n"/>
       <c r="D51" s="4" t="n"/>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="n"/>
+      <c r="E51" s="4" t="n"/>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -57927,12 +58047,12 @@
       <c r="G52" s="4" t="n"/>
       <c r="H52" s="4" t="n"/>
       <c r="I52" s="4" t="n"/>
-      <c r="J52" s="4" t="n"/>
-      <c r="K52" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K52" s="4" t="n"/>
       <c r="L52" s="4" t="n"/>
       <c r="M52" s="4" t="n"/>
       <c r="N52" s="4" t="n"/>
@@ -57952,12 +58072,12 @@
       </c>
       <c r="C53" s="4" t="n"/>
       <c r="D53" s="4" t="n"/>
-      <c r="E53" s="4" t="n"/>
-      <c r="F53" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="n"/>
       <c r="G53" s="4" t="n"/>
       <c r="H53" s="4" t="n"/>
       <c r="I53" s="4" t="n"/>
@@ -58000,12 +58120,12 @@
       </c>
       <c r="C55" s="4" t="n"/>
       <c r="D55" s="4" t="n"/>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="n"/>
+      <c r="E55" s="4" t="n"/>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G55" s="4" t="n"/>
       <c r="H55" s="4" t="n"/>
       <c r="I55" s="4" t="inlineStr">
@@ -58013,12 +58133,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="J55" s="4" t="n"/>
-      <c r="K55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K55" s="4" t="n"/>
       <c r="L55" s="4" t="n"/>
       <c r="M55" s="4" t="inlineStr">
         <is>
@@ -58038,12 +58158,12 @@
       </c>
       <c r="C56" s="4" t="n"/>
       <c r="D56" s="4" t="n"/>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="n"/>
+      <c r="E56" s="4" t="n"/>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G56" s="4" t="n"/>
       <c r="H56" s="4" t="n"/>
       <c r="I56" s="4" t="n"/>
@@ -58072,12 +58192,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E57" s="4" t="n"/>
-      <c r="F57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="n"/>
       <c r="G57" s="4" t="n"/>
       <c r="H57" s="4" t="n"/>
       <c r="I57" s="4" t="n"/>
@@ -58120,12 +58240,12 @@
       </c>
       <c r="C59" s="4" t="n"/>
       <c r="D59" s="4" t="n"/>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="n"/>
+      <c r="E59" s="4" t="n"/>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G59" s="4" t="n"/>
       <c r="H59" s="4" t="n"/>
       <c r="I59" s="4" t="inlineStr">
@@ -58192,12 +58312,12 @@
       </c>
       <c r="C61" s="4" t="n"/>
       <c r="D61" s="4" t="n"/>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="n"/>
+      <c r="E61" s="4" t="n"/>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -58259,12 +58379,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="J62" s="4" t="n"/>
-      <c r="K62" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K62" s="4" t="n"/>
       <c r="L62" s="4" t="n"/>
       <c r="M62" s="4" t="inlineStr">
         <is>
@@ -58288,12 +58408,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="n"/>
+      <c r="E63" s="4" t="n"/>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G63" s="4" t="n"/>
       <c r="H63" s="4" t="n"/>
       <c r="I63" s="4" t="inlineStr">
@@ -58301,12 +58421,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="J63" s="4" t="n"/>
-      <c r="K63" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K63" s="4" t="n"/>
       <c r="L63" s="4" t="n"/>
       <c r="M63" s="4" t="n"/>
       <c r="N63" s="4" t="n"/>
@@ -58322,12 +58442,12 @@
       </c>
       <c r="C64" s="4" t="n"/>
       <c r="D64" s="4" t="n"/>
-      <c r="E64" s="4" t="n"/>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="n"/>
       <c r="G64" s="4" t="n"/>
       <c r="H64" s="4" t="n"/>
       <c r="I64" s="4" t="n"/>
@@ -58352,12 +58472,12 @@
       </c>
       <c r="C65" s="4" t="n"/>
       <c r="D65" s="4" t="n"/>
-      <c r="E65" s="4" t="n"/>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="n"/>
       <c r="G65" s="4" t="n"/>
       <c r="H65" s="4" t="n"/>
       <c r="I65" s="4" t="n"/>
@@ -58454,12 +58574,12 @@
       </c>
       <c r="C68" s="4" t="n"/>
       <c r="D68" s="4" t="n"/>
-      <c r="E68" s="4" t="n"/>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="n"/>
       <c r="G68" s="4" t="n"/>
       <c r="H68" s="4" t="n"/>
       <c r="I68" s="4" t="n"/>
@@ -58488,21 +58608,21 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="n"/>
+      <c r="E69" s="4" t="n"/>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G69" s="4" t="n"/>
       <c r="H69" s="4" t="n"/>
       <c r="I69" s="4" t="n"/>
-      <c r="J69" s="4" t="n"/>
-      <c r="K69" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="K69" s="4" t="n"/>
       <c r="L69" s="4" t="n"/>
       <c r="M69" s="4" t="n"/>
       <c r="N69" s="4" t="n"/>
@@ -58518,12 +58638,12 @@
       </c>
       <c r="C70" s="4" t="n"/>
       <c r="D70" s="4" t="n"/>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F70" s="4" t="n"/>
+      <c r="E70" s="4" t="n"/>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -58636,12 +58756,12 @@
       </c>
       <c r="C73" s="4" t="n"/>
       <c r="D73" s="4" t="n"/>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F73" s="4" t="n"/>
+      <c r="E73" s="4" t="n"/>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G73" s="4" t="n"/>
       <c r="H73" s="4" t="n"/>
       <c r="I73" s="4" t="n"/>
@@ -58708,12 +58828,12 @@
       </c>
       <c r="C75" s="4" t="n"/>
       <c r="D75" s="4" t="n"/>
-      <c r="E75" s="4" t="n"/>
-      <c r="F75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="n"/>
       <c r="G75" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -58725,12 +58845,12 @@
         </is>
       </c>
       <c r="I75" s="4" t="n"/>
-      <c r="J75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="K75" s="4" t="n"/>
+      <c r="J75" s="4" t="n"/>
+      <c r="K75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="L75" s="4" t="n"/>
       <c r="M75" s="4" t="n"/>
       <c r="N75" s="4" t="inlineStr">
@@ -58750,12 +58870,12 @@
       </c>
       <c r="C76" s="4" t="n"/>
       <c r="D76" s="4" t="n"/>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F76" s="4" t="n"/>
+      <c r="E76" s="4" t="n"/>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G76" s="4" t="n"/>
       <c r="H76" s="4" t="n"/>
       <c r="I76" s="4" t="inlineStr">

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -47389,7 +47389,11 @@
       <c r="AV2" s="4" t="n"/>
       <c r="AW2" s="4" t="n"/>
       <c r="AX2" s="4" t="n"/>
-      <c r="AY2" s="4" t="n"/>
+      <c r="AY2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ2" s="4" t="n"/>
       <c r="BA2" s="4" t="n"/>
       <c r="BB2" s="4" t="n"/>
@@ -47504,7 +47508,11 @@
       <c r="AV3" s="4" t="n"/>
       <c r="AW3" s="4" t="n"/>
       <c r="AX3" s="4" t="n"/>
-      <c r="AY3" s="4" t="n"/>
+      <c r="AY3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ3" s="4" t="n"/>
       <c r="BA3" s="4" t="n"/>
       <c r="BB3" s="4" t="n"/>
@@ -47603,7 +47611,11 @@
       <c r="AV4" s="4" t="n"/>
       <c r="AW4" s="4" t="n"/>
       <c r="AX4" s="4" t="n"/>
-      <c r="AY4" s="4" t="n"/>
+      <c r="AY4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ4" s="4" t="n"/>
       <c r="BA4" s="4" t="n"/>
       <c r="BB4" s="4" t="n"/>
@@ -47706,7 +47718,11 @@
       <c r="AV5" s="4" t="n"/>
       <c r="AW5" s="4" t="n"/>
       <c r="AX5" s="4" t="n"/>
-      <c r="AY5" s="4" t="n"/>
+      <c r="AY5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ5" s="4" t="n"/>
       <c r="BA5" s="4" t="n"/>
       <c r="BB5" s="4" t="n"/>
@@ -47797,7 +47813,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AY6" s="4" t="n"/>
+      <c r="AY6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ6" s="4" t="n"/>
       <c r="BA6" s="4" t="n"/>
       <c r="BB6" s="4" t="n"/>
@@ -47908,7 +47928,11 @@
       <c r="AV7" s="4" t="n"/>
       <c r="AW7" s="4" t="n"/>
       <c r="AX7" s="4" t="n"/>
-      <c r="AY7" s="4" t="n"/>
+      <c r="AY7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ7" s="4" t="n"/>
       <c r="BA7" s="4" t="n"/>
       <c r="BB7" s="4" t="n"/>
@@ -48035,7 +48059,11 @@
       <c r="AV8" s="4" t="n"/>
       <c r="AW8" s="4" t="n"/>
       <c r="AX8" s="4" t="n"/>
-      <c r="AY8" s="4" t="n"/>
+      <c r="AY8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ8" s="4" t="n"/>
       <c r="BA8" s="4" t="n"/>
       <c r="BB8" s="4" t="n"/>
@@ -48138,7 +48166,11 @@
       <c r="AV9" s="4" t="n"/>
       <c r="AW9" s="4" t="n"/>
       <c r="AX9" s="4" t="n"/>
-      <c r="AY9" s="4" t="n"/>
+      <c r="AY9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ9" s="4" t="n"/>
       <c r="BA9" s="4" t="n"/>
       <c r="BB9" s="4" t="n"/>
@@ -48257,7 +48289,11 @@
       <c r="AV10" s="4" t="n"/>
       <c r="AW10" s="4" t="n"/>
       <c r="AX10" s="4" t="n"/>
-      <c r="AY10" s="4" t="n"/>
+      <c r="AY10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ10" s="4" t="n"/>
       <c r="BA10" s="4" t="n"/>
       <c r="BB10" s="4" t="n"/>
@@ -48356,7 +48392,11 @@
       <c r="AV11" s="4" t="n"/>
       <c r="AW11" s="4" t="n"/>
       <c r="AX11" s="4" t="n"/>
-      <c r="AY11" s="4" t="n"/>
+      <c r="AY11" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ11" s="4" t="n"/>
       <c r="BA11" s="4" t="n"/>
       <c r="BB11" s="4" t="n"/>
@@ -48566,7 +48606,11 @@
       <c r="AV13" s="4" t="n"/>
       <c r="AW13" s="4" t="n"/>
       <c r="AX13" s="4" t="n"/>
-      <c r="AY13" s="4" t="n"/>
+      <c r="AY13" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ13" s="4" t="n"/>
       <c r="BA13" s="4" t="n"/>
       <c r="BB13" s="4" t="n"/>
@@ -48681,7 +48725,11 @@
       <c r="AV14" s="4" t="n"/>
       <c r="AW14" s="4" t="n"/>
       <c r="AX14" s="4" t="n"/>
-      <c r="AY14" s="4" t="n"/>
+      <c r="AY14" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ14" s="4" t="n"/>
       <c r="BA14" s="4" t="n"/>
       <c r="BB14" s="4" t="n"/>
@@ -48804,7 +48852,11 @@
       <c r="AV15" s="4" t="n"/>
       <c r="AW15" s="4" t="n"/>
       <c r="AX15" s="4" t="n"/>
-      <c r="AY15" s="4" t="n"/>
+      <c r="AY15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ15" s="4" t="n"/>
       <c r="BA15" s="4" t="n"/>
       <c r="BB15" s="4" t="n"/>
@@ -48915,7 +48967,11 @@
       <c r="AV16" s="4" t="n"/>
       <c r="AW16" s="4" t="n"/>
       <c r="AX16" s="4" t="n"/>
-      <c r="AY16" s="4" t="n"/>
+      <c r="AY16" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ16" s="4" t="n"/>
       <c r="BA16" s="4" t="n"/>
       <c r="BB16" s="4" t="n"/>
@@ -49022,7 +49078,11 @@
       <c r="AV17" s="4" t="n"/>
       <c r="AW17" s="4" t="n"/>
       <c r="AX17" s="4" t="n"/>
-      <c r="AY17" s="4" t="n"/>
+      <c r="AY17" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ17" s="4" t="n"/>
       <c r="BA17" s="4" t="n"/>
       <c r="BB17" s="4" t="n"/>
@@ -49248,7 +49308,11 @@
       <c r="AV19" s="4" t="n"/>
       <c r="AW19" s="4" t="n"/>
       <c r="AX19" s="4" t="n"/>
-      <c r="AY19" s="4" t="n"/>
+      <c r="AY19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ19" s="4" t="n"/>
       <c r="BA19" s="4" t="n"/>
       <c r="BB19" s="4" t="n"/>
@@ -49351,7 +49415,11 @@
       <c r="AV20" s="4" t="n"/>
       <c r="AW20" s="4" t="n"/>
       <c r="AX20" s="4" t="n"/>
-      <c r="AY20" s="4" t="n"/>
+      <c r="AY20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ20" s="4" t="n"/>
       <c r="BA20" s="4" t="n"/>
       <c r="BB20" s="4" t="n"/>
@@ -49450,7 +49518,11 @@
       <c r="AV21" s="4" t="n"/>
       <c r="AW21" s="4" t="n"/>
       <c r="AX21" s="4" t="n"/>
-      <c r="AY21" s="4" t="n"/>
+      <c r="AY21" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ21" s="4" t="n"/>
       <c r="BA21" s="4" t="n"/>
       <c r="BB21" s="4" t="n"/>
@@ -49553,7 +49625,11 @@
       <c r="AV22" s="4" t="n"/>
       <c r="AW22" s="4" t="n"/>
       <c r="AX22" s="4" t="n"/>
-      <c r="AY22" s="4" t="n"/>
+      <c r="AY22" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ22" s="4" t="n"/>
       <c r="BA22" s="4" t="n"/>
       <c r="BB22" s="4" t="n"/>
@@ -49652,7 +49728,11 @@
       <c r="AV23" s="4" t="n"/>
       <c r="AW23" s="4" t="n"/>
       <c r="AX23" s="4" t="n"/>
-      <c r="AY23" s="4" t="n"/>
+      <c r="AY23" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ23" s="4" t="n"/>
       <c r="BA23" s="4" t="n"/>
       <c r="BB23" s="4" t="n"/>
@@ -49759,7 +49839,11 @@
       <c r="AV24" s="4" t="n"/>
       <c r="AW24" s="4" t="n"/>
       <c r="AX24" s="4" t="n"/>
-      <c r="AY24" s="4" t="n"/>
+      <c r="AY24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ24" s="4" t="n"/>
       <c r="BA24" s="4" t="n"/>
       <c r="BB24" s="4" t="n"/>
@@ -50080,7 +50164,11 @@
       <c r="AV27" s="4" t="n"/>
       <c r="AW27" s="4" t="n"/>
       <c r="AX27" s="4" t="n"/>
-      <c r="AY27" s="4" t="n"/>
+      <c r="AY27" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ27" s="4" t="n"/>
       <c r="BA27" s="4" t="n"/>
       <c r="BB27" s="4" t="n"/>
@@ -50183,7 +50271,11 @@
       <c r="AV28" s="4" t="n"/>
       <c r="AW28" s="4" t="n"/>
       <c r="AX28" s="4" t="n"/>
-      <c r="AY28" s="4" t="n"/>
+      <c r="AY28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ28" s="4" t="n"/>
       <c r="BA28" s="4" t="n"/>
       <c r="BB28" s="4" t="n"/>
@@ -50274,7 +50366,11 @@
       <c r="AV29" s="4" t="n"/>
       <c r="AW29" s="4" t="n"/>
       <c r="AX29" s="4" t="n"/>
-      <c r="AY29" s="4" t="n"/>
+      <c r="AY29" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ29" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -50381,7 +50477,11 @@
       <c r="AV30" s="4" t="n"/>
       <c r="AW30" s="4" t="n"/>
       <c r="AX30" s="4" t="n"/>
-      <c r="AY30" s="4" t="n"/>
+      <c r="AY30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ30" s="4" t="n"/>
       <c r="BA30" s="4" t="n"/>
       <c r="BB30" s="4" t="n"/>
@@ -50591,7 +50691,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AY32" s="4" t="n"/>
+      <c r="AY32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ32" s="4" t="n"/>
       <c r="BA32" s="4" t="n"/>
       <c r="BB32" s="4" t="inlineStr">
@@ -50698,7 +50802,11 @@
       <c r="AV33" s="4" t="n"/>
       <c r="AW33" s="4" t="n"/>
       <c r="AX33" s="4" t="n"/>
-      <c r="AY33" s="4" t="n"/>
+      <c r="AY33" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ33" s="4" t="n"/>
       <c r="BA33" s="4" t="n"/>
       <c r="BB33" s="4" t="inlineStr">
@@ -50908,7 +51016,11 @@
       <c r="AV35" s="4" t="n"/>
       <c r="AW35" s="4" t="n"/>
       <c r="AX35" s="4" t="n"/>
-      <c r="AY35" s="4" t="n"/>
+      <c r="AY35" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ35" s="4" t="n"/>
       <c r="BA35" s="4" t="n"/>
       <c r="BB35" s="4" t="inlineStr">
@@ -51023,7 +51135,11 @@
       <c r="AV36" s="4" t="n"/>
       <c r="AW36" s="4" t="n"/>
       <c r="AX36" s="4" t="n"/>
-      <c r="AY36" s="4" t="n"/>
+      <c r="AY36" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ36" s="4" t="n"/>
       <c r="BA36" s="4" t="n"/>
       <c r="BB36" s="4" t="n"/>
@@ -51138,7 +51254,11 @@
       <c r="AV37" s="4" t="n"/>
       <c r="AW37" s="4" t="n"/>
       <c r="AX37" s="4" t="n"/>
-      <c r="AY37" s="4" t="n"/>
+      <c r="AY37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ37" s="4" t="n"/>
       <c r="BA37" s="4" t="n"/>
       <c r="BB37" s="4" t="n"/>
@@ -51253,7 +51373,11 @@
       <c r="AV38" s="4" t="n"/>
       <c r="AW38" s="4" t="n"/>
       <c r="AX38" s="4" t="n"/>
-      <c r="AY38" s="4" t="n"/>
+      <c r="AY38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ38" s="4" t="n"/>
       <c r="BA38" s="4" t="n"/>
       <c r="BB38" s="4" t="n"/>
@@ -51360,7 +51484,11 @@
       <c r="AV39" s="4" t="n"/>
       <c r="AW39" s="4" t="n"/>
       <c r="AX39" s="4" t="n"/>
-      <c r="AY39" s="4" t="n"/>
+      <c r="AY39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ39" s="4" t="n"/>
       <c r="BA39" s="4" t="n"/>
       <c r="BB39" s="4" t="n"/>
@@ -51483,7 +51611,11 @@
       <c r="AV40" s="4" t="n"/>
       <c r="AW40" s="4" t="n"/>
       <c r="AX40" s="4" t="n"/>
-      <c r="AY40" s="4" t="n"/>
+      <c r="AY40" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ40" s="4" t="n"/>
       <c r="BA40" s="4" t="n"/>
       <c r="BB40" s="4" t="n"/>
@@ -51582,7 +51714,11 @@
       <c r="AV41" s="4" t="n"/>
       <c r="AW41" s="4" t="n"/>
       <c r="AX41" s="4" t="n"/>
-      <c r="AY41" s="4" t="n"/>
+      <c r="AY41" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ41" s="4" t="n"/>
       <c r="BA41" s="4" t="n"/>
       <c r="BB41" s="4" t="n"/>
@@ -51689,7 +51825,11 @@
       <c r="AV42" s="4" t="n"/>
       <c r="AW42" s="4" t="n"/>
       <c r="AX42" s="4" t="n"/>
-      <c r="AY42" s="4" t="n"/>
+      <c r="AY42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ42" s="4" t="n"/>
       <c r="BA42" s="4" t="n"/>
       <c r="BB42" s="4" t="n"/>
@@ -51788,7 +51928,11 @@
       <c r="AV43" s="4" t="n"/>
       <c r="AW43" s="4" t="n"/>
       <c r="AX43" s="4" t="n"/>
-      <c r="AY43" s="4" t="n"/>
+      <c r="AY43" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ43" s="4" t="n"/>
       <c r="BA43" s="4" t="n"/>
       <c r="BB43" s="4" t="n"/>
@@ -51879,7 +52023,11 @@
       <c r="AV44" s="4" t="n"/>
       <c r="AW44" s="4" t="n"/>
       <c r="AX44" s="4" t="n"/>
-      <c r="AY44" s="4" t="n"/>
+      <c r="AY44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ44" s="4" t="n"/>
       <c r="BA44" s="4" t="n"/>
       <c r="BB44" s="4" t="n"/>
@@ -52002,7 +52150,11 @@
       <c r="AV45" s="4" t="n"/>
       <c r="AW45" s="4" t="n"/>
       <c r="AX45" s="4" t="n"/>
-      <c r="AY45" s="4" t="n"/>
+      <c r="AY45" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ45" s="4" t="n"/>
       <c r="BA45" s="4" t="n"/>
       <c r="BB45" s="4" t="n"/>
@@ -52121,7 +52273,11 @@
       <c r="AV46" s="4" t="n"/>
       <c r="AW46" s="4" t="n"/>
       <c r="AX46" s="4" t="n"/>
-      <c r="AY46" s="4" t="n"/>
+      <c r="AY46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ46" s="4" t="n"/>
       <c r="BA46" s="4" t="n"/>
       <c r="BB46" s="4" t="n"/>
@@ -52228,7 +52384,11 @@
       <c r="AV47" s="4" t="n"/>
       <c r="AW47" s="4" t="n"/>
       <c r="AX47" s="4" t="n"/>
-      <c r="AY47" s="4" t="n"/>
+      <c r="AY47" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ47" s="4" t="n"/>
       <c r="BA47" s="4" t="n"/>
       <c r="BB47" s="4" t="inlineStr">
@@ -52351,7 +52511,11 @@
       <c r="AV48" s="4" t="n"/>
       <c r="AW48" s="4" t="n"/>
       <c r="AX48" s="4" t="n"/>
-      <c r="AY48" s="4" t="n"/>
+      <c r="AY48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ48" s="4" t="n"/>
       <c r="BA48" s="4" t="n"/>
       <c r="BB48" s="4" t="n"/>
@@ -52446,7 +52610,11 @@
       <c r="AV49" s="4" t="n"/>
       <c r="AW49" s="4" t="n"/>
       <c r="AX49" s="4" t="n"/>
-      <c r="AY49" s="4" t="n"/>
+      <c r="AY49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ49" s="4" t="n"/>
       <c r="BA49" s="4" t="n"/>
       <c r="BB49" s="4" t="n"/>
@@ -52541,7 +52709,11 @@
       <c r="AV50" s="4" t="n"/>
       <c r="AW50" s="4" t="n"/>
       <c r="AX50" s="4" t="n"/>
-      <c r="AY50" s="4" t="n"/>
+      <c r="AY50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ50" s="4" t="n"/>
       <c r="BA50" s="4" t="n"/>
       <c r="BB50" s="4" t="inlineStr">
@@ -52656,7 +52828,11 @@
       <c r="AV51" s="4" t="n"/>
       <c r="AW51" s="4" t="n"/>
       <c r="AX51" s="4" t="n"/>
-      <c r="AY51" s="4" t="n"/>
+      <c r="AY51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ51" s="4" t="n"/>
       <c r="BA51" s="4" t="n"/>
       <c r="BB51" s="4" t="n"/>
@@ -52767,7 +52943,11 @@
       <c r="AV52" s="4" t="n"/>
       <c r="AW52" s="4" t="n"/>
       <c r="AX52" s="4" t="n"/>
-      <c r="AY52" s="4" t="n"/>
+      <c r="AY52" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ52" s="4" t="n"/>
       <c r="BA52" s="4" t="n"/>
       <c r="BB52" s="4" t="n"/>
@@ -52870,7 +53050,11 @@
       <c r="AV53" s="4" t="n"/>
       <c r="AW53" s="4" t="n"/>
       <c r="AX53" s="4" t="n"/>
-      <c r="AY53" s="4" t="n"/>
+      <c r="AY53" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ53" s="4" t="n"/>
       <c r="BA53" s="4" t="n"/>
       <c r="BB53" s="4" t="n"/>
@@ -52969,7 +53153,11 @@
       <c r="AV54" s="4" t="n"/>
       <c r="AW54" s="4" t="n"/>
       <c r="AX54" s="4" t="n"/>
-      <c r="AY54" s="4" t="n"/>
+      <c r="AY54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ54" s="4" t="n"/>
       <c r="BA54" s="4" t="inlineStr">
         <is>
@@ -53064,7 +53252,11 @@
       <c r="AV55" s="4" t="n"/>
       <c r="AW55" s="4" t="n"/>
       <c r="AX55" s="4" t="n"/>
-      <c r="AY55" s="4" t="n"/>
+      <c r="AY55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ55" s="4" t="n"/>
       <c r="BA55" s="4" t="n"/>
       <c r="BB55" s="4" t="inlineStr">
@@ -53167,7 +53359,11 @@
       <c r="AV56" s="4" t="n"/>
       <c r="AW56" s="4" t="n"/>
       <c r="AX56" s="4" t="n"/>
-      <c r="AY56" s="4" t="n"/>
+      <c r="AY56" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ56" s="4" t="n"/>
       <c r="BA56" s="4" t="n"/>
       <c r="BB56" s="4" t="n"/>
@@ -53282,7 +53478,11 @@
       <c r="AV57" s="4" t="n"/>
       <c r="AW57" s="4" t="n"/>
       <c r="AX57" s="4" t="n"/>
-      <c r="AY57" s="4" t="n"/>
+      <c r="AY57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ57" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -53385,7 +53585,11 @@
       <c r="AV58" s="4" t="n"/>
       <c r="AW58" s="4" t="n"/>
       <c r="AX58" s="4" t="n"/>
-      <c r="AY58" s="4" t="n"/>
+      <c r="AY58" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ58" s="4" t="n"/>
       <c r="BA58" s="4" t="n"/>
       <c r="BB58" s="4" t="n"/>
@@ -53484,7 +53688,11 @@
       <c r="AV59" s="4" t="n"/>
       <c r="AW59" s="4" t="n"/>
       <c r="AX59" s="4" t="n"/>
-      <c r="AY59" s="4" t="n"/>
+      <c r="AY59" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ59" s="4" t="n"/>
       <c r="BA59" s="4" t="n"/>
       <c r="BB59" s="4" t="n"/>
@@ -53595,7 +53803,11 @@
       <c r="AV60" s="4" t="n"/>
       <c r="AW60" s="4" t="n"/>
       <c r="AX60" s="4" t="n"/>
-      <c r="AY60" s="4" t="n"/>
+      <c r="AY60" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ60" s="4" t="n"/>
       <c r="BA60" s="4" t="n"/>
       <c r="BB60" s="4" t="n"/>
@@ -53714,7 +53926,11 @@
       </c>
       <c r="AW61" s="4" t="n"/>
       <c r="AX61" s="4" t="n"/>
-      <c r="AY61" s="4" t="n"/>
+      <c r="AY61" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ61" s="4" t="n"/>
       <c r="BA61" s="4" t="n"/>
       <c r="BB61" s="4" t="n"/>
@@ -53821,7 +54037,11 @@
       <c r="AV62" s="4" t="n"/>
       <c r="AW62" s="4" t="n"/>
       <c r="AX62" s="4" t="n"/>
-      <c r="AY62" s="4" t="n"/>
+      <c r="AY62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ62" s="4" t="n"/>
       <c r="BA62" s="4" t="n"/>
       <c r="BB62" s="4" t="n"/>
@@ -53948,7 +54168,11 @@
       <c r="AV63" s="4" t="n"/>
       <c r="AW63" s="4" t="n"/>
       <c r="AX63" s="4" t="n"/>
-      <c r="AY63" s="4" t="n"/>
+      <c r="AY63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ63" s="4" t="n"/>
       <c r="BA63" s="4" t="n"/>
       <c r="BB63" s="4" t="n"/>
@@ -54055,7 +54279,11 @@
       <c r="AV64" s="4" t="n"/>
       <c r="AW64" s="4" t="n"/>
       <c r="AX64" s="4" t="n"/>
-      <c r="AY64" s="4" t="n"/>
+      <c r="AY64" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ64" s="4" t="n"/>
       <c r="BA64" s="4" t="n"/>
       <c r="BB64" s="4" t="n"/>
@@ -54253,7 +54481,11 @@
       <c r="AV66" s="4" t="n"/>
       <c r="AW66" s="4" t="n"/>
       <c r="AX66" s="4" t="n"/>
-      <c r="AY66" s="4" t="n"/>
+      <c r="AY66" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ66" s="4" t="n"/>
       <c r="BA66" s="4" t="n"/>
       <c r="BB66" s="4" t="n"/>
@@ -54368,7 +54600,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AY67" s="4" t="n"/>
+      <c r="AY67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ67" s="4" t="n"/>
       <c r="BA67" s="4" t="n"/>
       <c r="BB67" s="4" t="inlineStr">
@@ -54570,7 +54806,11 @@
       <c r="AV69" s="4" t="n"/>
       <c r="AW69" s="4" t="n"/>
       <c r="AX69" s="4" t="n"/>
-      <c r="AY69" s="4" t="n"/>
+      <c r="AY69" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ69" s="4" t="n"/>
       <c r="BA69" s="4" t="n"/>
       <c r="BB69" s="4" t="n"/>
@@ -54665,7 +54905,11 @@
       <c r="AV70" s="4" t="n"/>
       <c r="AW70" s="4" t="n"/>
       <c r="AX70" s="4" t="n"/>
-      <c r="AY70" s="4" t="n"/>
+      <c r="AY70" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ70" s="4" t="n"/>
       <c r="BA70" s="4" t="n"/>
       <c r="BB70" s="4" t="n"/>
@@ -54760,7 +55004,11 @@
       <c r="AV71" s="4" t="n"/>
       <c r="AW71" s="4" t="n"/>
       <c r="AX71" s="4" t="n"/>
-      <c r="AY71" s="4" t="n"/>
+      <c r="AY71" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ71" s="4" t="n"/>
       <c r="BA71" s="4" t="n"/>
       <c r="BB71" s="4" t="n"/>
@@ -54859,7 +55107,11 @@
       <c r="AV72" s="4" t="n"/>
       <c r="AW72" s="4" t="n"/>
       <c r="AX72" s="4" t="n"/>
-      <c r="AY72" s="4" t="n"/>
+      <c r="AY72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ72" s="4" t="n"/>
       <c r="BA72" s="4" t="n"/>
       <c r="BB72" s="4" t="inlineStr">
@@ -54970,7 +55222,11 @@
       <c r="AV73" s="4" t="n"/>
       <c r="AW73" s="4" t="n"/>
       <c r="AX73" s="4" t="n"/>
-      <c r="AY73" s="4" t="n"/>
+      <c r="AY73" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ73" s="4" t="n"/>
       <c r="BA73" s="4" t="n"/>
       <c r="BB73" s="4" t="n"/>
@@ -55085,7 +55341,11 @@
       <c r="AV74" s="4" t="n"/>
       <c r="AW74" s="4" t="n"/>
       <c r="AX74" s="4" t="n"/>
-      <c r="AY74" s="4" t="n"/>
+      <c r="AY74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ74" s="4" t="n"/>
       <c r="BA74" s="4" t="n"/>
       <c r="BB74" s="4" t="n"/>
@@ -55192,7 +55452,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AY75" s="4" t="n"/>
+      <c r="AY75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ75" s="4" t="n"/>
       <c r="BA75" s="4" t="n"/>
       <c r="BB75" s="4" t="n"/>
@@ -55275,7 +55539,11 @@
       <c r="AV76" s="4" t="n"/>
       <c r="AW76" s="4" t="n"/>
       <c r="AX76" s="4" t="n"/>
-      <c r="AY76" s="4" t="n"/>
+      <c r="AY76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ76" s="4" t="n"/>
       <c r="BA76" s="4" t="n"/>
       <c r="BB76" s="4" t="inlineStr">
@@ -55398,7 +55666,11 @@
       <c r="AV77" s="4" t="n"/>
       <c r="AW77" s="4" t="n"/>
       <c r="AX77" s="4" t="n"/>
-      <c r="AY77" s="4" t="n"/>
+      <c r="AY77" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ77" s="4" t="n"/>
       <c r="BA77" s="4" t="n"/>
       <c r="BB77" s="4" t="n"/>
@@ -55501,7 +55773,11 @@
       <c r="AV78" s="4" t="n"/>
       <c r="AW78" s="4" t="n"/>
       <c r="AX78" s="4" t="n"/>
-      <c r="AY78" s="4" t="n"/>
+      <c r="AY78" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ78" s="4" t="n"/>
       <c r="BA78" s="4" t="n"/>
       <c r="BB78" s="4" t="n"/>
@@ -55608,7 +55884,11 @@
       <c r="AV79" s="4" t="n"/>
       <c r="AW79" s="4" t="n"/>
       <c r="AX79" s="4" t="n"/>
-      <c r="AY79" s="4" t="n"/>
+      <c r="AY79" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ79" s="4" t="n"/>
       <c r="BA79" s="4" t="n"/>
       <c r="BB79" s="4" t="n"/>
@@ -55703,7 +55983,11 @@
       <c r="AV80" s="4" t="n"/>
       <c r="AW80" s="4" t="n"/>
       <c r="AX80" s="4" t="n"/>
-      <c r="AY80" s="4" t="n"/>
+      <c r="AY80" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ80" s="4" t="n"/>
       <c r="BA80" s="4" t="inlineStr">
         <is>
@@ -55794,7 +56078,11 @@
       <c r="AV81" s="4" t="n"/>
       <c r="AW81" s="4" t="n"/>
       <c r="AX81" s="4" t="n"/>
-      <c r="AY81" s="4" t="n"/>
+      <c r="AY81" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ81" s="4" t="n"/>
       <c r="BA81" s="4" t="n"/>
       <c r="BB81" s="4" t="n"/>
@@ -55881,7 +56169,11 @@
       <c r="AV82" s="4" t="n"/>
       <c r="AW82" s="4" t="n"/>
       <c r="AX82" s="4" t="n"/>
-      <c r="AY82" s="4" t="n"/>
+      <c r="AY82" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ82" s="4" t="n"/>
       <c r="BA82" s="4" t="n"/>
       <c r="BB82" s="4" t="n"/>
@@ -55960,7 +56252,11 @@
       <c r="AV83" s="4" t="n"/>
       <c r="AW83" s="4" t="n"/>
       <c r="AX83" s="4" t="n"/>
-      <c r="AY83" s="4" t="n"/>
+      <c r="AY83" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ83" s="4" t="n"/>
       <c r="BA83" s="4" t="n"/>
       <c r="BB83" s="4" t="n"/>
@@ -56055,7 +56351,11 @@
       <c r="AV84" s="4" t="n"/>
       <c r="AW84" s="4" t="n"/>
       <c r="AX84" s="4" t="n"/>
-      <c r="AY84" s="4" t="n"/>
+      <c r="AY84" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ84" s="4" t="n"/>
       <c r="BA84" s="4" t="n"/>
       <c r="BB84" s="4" t="n"/>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -23,8 +23,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'五区_普通'!$A$1:$CJ$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'五区_自动'!$A$1:$U$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'四区_理论'!$A$1:$AR$84</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'四区_高手'!$A$1:$BI$84</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'四区_普通'!$A$1:$BI$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'四区_高手'!$A$1:$BJ$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'四区_普通'!$A$1:$BJ$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'四区_自动'!$A$1:$P$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'特殊跑法'!$A$1:$G$172</definedName>
   </definedNames>
@@ -34872,19 +34872,19 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>万达</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>狼崽</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>21c</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>万达</t>
-        </is>
-      </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
           <t>fp1</t>
@@ -34947,32 +34947,32 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
+          <t>att</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
           <t>无敌牛</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>divo</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>er9</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>狼王</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>小牛</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>att</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
@@ -35118,10 +35118,10 @@
         <v>28.49</v>
       </c>
       <c r="L3" s="4" t="n"/>
-      <c r="M3" s="4" t="n">
+      <c r="M3" s="4" t="n"/>
+      <c r="N3" s="4" t="n">
         <v>29.6</v>
       </c>
-      <c r="N3" s="4" t="n"/>
       <c r="O3" s="4" t="n"/>
       <c r="P3" s="4" t="n"/>
       <c r="Q3" s="4" t="n"/>
@@ -35138,10 +35138,10 @@
       <c r="AB3" s="4" t="n"/>
       <c r="AC3" s="4" t="n"/>
       <c r="AD3" s="4" t="n"/>
-      <c r="AE3" s="4" t="n">
+      <c r="AE3" s="4" t="n"/>
+      <c r="AF3" s="4" t="n">
         <v>29.29</v>
       </c>
-      <c r="AF3" s="4" t="n"/>
       <c r="AG3" s="4" t="n"/>
       <c r="AH3" s="4" t="n"/>
       <c r="AI3" s="4" t="n"/>
@@ -35182,10 +35182,10 @@
       </c>
       <c r="K4" s="4" t="n"/>
       <c r="L4" s="4" t="n"/>
-      <c r="M4" s="4" t="n">
+      <c r="M4" s="4" t="n"/>
+      <c r="N4" s="4" t="n">
         <v>32.29</v>
       </c>
-      <c r="N4" s="4" t="n"/>
       <c r="O4" s="4" t="n"/>
       <c r="P4" s="4" t="n"/>
       <c r="Q4" s="4" t="n"/>
@@ -35270,10 +35270,10 @@
       <c r="Z5" s="4" t="n"/>
       <c r="AA5" s="4" t="n"/>
       <c r="AB5" s="4" t="n"/>
-      <c r="AC5" s="4" t="n">
+      <c r="AC5" s="4" t="n"/>
+      <c r="AD5" s="4" t="n">
         <v>18.29</v>
       </c>
-      <c r="AD5" s="4" t="n"/>
       <c r="AE5" s="4" t="n"/>
       <c r="AF5" s="4" t="n"/>
       <c r="AG5" s="4" t="n"/>
@@ -35339,10 +35339,10 @@
       <c r="AC6" s="4" t="n"/>
       <c r="AD6" s="4" t="n"/>
       <c r="AE6" s="4" t="n"/>
-      <c r="AF6" s="4" t="n">
+      <c r="AF6" s="4" t="n"/>
+      <c r="AG6" s="4" t="n">
         <v>18.6</v>
       </c>
-      <c r="AG6" s="4" t="n"/>
       <c r="AH6" s="4" t="n"/>
       <c r="AI6" s="4" t="n"/>
       <c r="AJ6" s="4" t="n"/>
@@ -35444,10 +35444,10 @@
       </c>
       <c r="K8" s="4" t="n"/>
       <c r="L8" s="4" t="n"/>
-      <c r="M8" s="4" t="n">
+      <c r="M8" s="4" t="n"/>
+      <c r="N8" s="4" t="n">
         <v>28.9</v>
       </c>
-      <c r="N8" s="4" t="n"/>
       <c r="O8" s="4" t="n"/>
       <c r="P8" s="4" t="n"/>
       <c r="Q8" s="4" t="n"/>
@@ -35509,10 +35509,10 @@
         <v>19.55</v>
       </c>
       <c r="M9" s="4" t="n"/>
-      <c r="N9" s="4" t="n">
+      <c r="N9" s="4" t="n"/>
+      <c r="O9" s="4" t="n">
         <v>19.47</v>
       </c>
-      <c r="O9" s="4" t="n"/>
       <c r="P9" s="4" t="n">
         <v>19.85</v>
       </c>
@@ -35579,10 +35579,10 @@
       <c r="K10" s="4" t="n"/>
       <c r="L10" s="4" t="n"/>
       <c r="M10" s="4" t="n"/>
-      <c r="N10" s="4" t="n">
+      <c r="N10" s="4" t="n"/>
+      <c r="O10" s="4" t="n">
         <v>23.11</v>
       </c>
-      <c r="O10" s="4" t="n"/>
       <c r="P10" s="4" t="n"/>
       <c r="Q10" s="4" t="n"/>
       <c r="R10" s="4" t="n"/>
@@ -35697,10 +35697,10 @@
         <v>21.75</v>
       </c>
       <c r="M12" s="4" t="n"/>
-      <c r="N12" s="4" t="n">
+      <c r="N12" s="4" t="n"/>
+      <c r="O12" s="4" t="n">
         <v>21.39</v>
       </c>
-      <c r="O12" s="4" t="n"/>
       <c r="P12" s="4" t="n"/>
       <c r="Q12" s="4" t="n"/>
       <c r="R12" s="4" t="n"/>
@@ -35717,14 +35717,14 @@
       </c>
       <c r="Z12" s="4" t="n"/>
       <c r="AA12" s="4" t="n"/>
-      <c r="AB12" s="4" t="n"/>
+      <c r="AB12" s="4" t="n">
+        <v>21.85</v>
+      </c>
       <c r="AC12" s="4" t="n"/>
       <c r="AD12" s="4" t="n"/>
       <c r="AE12" s="4" t="n"/>
       <c r="AF12" s="4" t="n"/>
-      <c r="AG12" s="4" t="n">
-        <v>21.85</v>
-      </c>
+      <c r="AG12" s="4" t="n"/>
       <c r="AH12" s="4" t="n"/>
       <c r="AI12" s="4" t="n"/>
       <c r="AJ12" s="4" t="n"/>
@@ -35890,10 +35890,10 @@
       <c r="J15" s="4" t="n"/>
       <c r="K15" s="4" t="n"/>
       <c r="L15" s="4" t="n"/>
-      <c r="M15" s="4" t="n">
+      <c r="M15" s="4" t="n"/>
+      <c r="N15" s="4" t="n">
         <v>30.09</v>
       </c>
-      <c r="N15" s="4" t="n"/>
       <c r="O15" s="4" t="n"/>
       <c r="P15" s="4" t="n"/>
       <c r="Q15" s="4" t="n"/>
@@ -36078,10 +36078,10 @@
       <c r="L18" s="4" t="n">
         <v>23.69</v>
       </c>
-      <c r="M18" s="4" t="n">
+      <c r="M18" s="4" t="n"/>
+      <c r="N18" s="4" t="n">
         <v>24.19</v>
       </c>
-      <c r="N18" s="4" t="n"/>
       <c r="O18" s="4" t="n"/>
       <c r="P18" s="4" t="n"/>
       <c r="Q18" s="4" t="n"/>
@@ -36104,10 +36104,10 @@
       <c r="AB18" s="4" t="n"/>
       <c r="AC18" s="4" t="n"/>
       <c r="AD18" s="4" t="n"/>
-      <c r="AE18" s="4" t="n">
+      <c r="AE18" s="4" t="n"/>
+      <c r="AF18" s="4" t="n">
         <v>23.99</v>
       </c>
-      <c r="AF18" s="4" t="n"/>
       <c r="AG18" s="4" t="n"/>
       <c r="AH18" s="4" t="n">
         <v>23.79</v>
@@ -36204,11 +36204,11 @@
       <c r="J20" s="4" t="n"/>
       <c r="K20" s="4" t="n"/>
       <c r="L20" s="4" t="n"/>
-      <c r="M20" s="4" t="n"/>
+      <c r="M20" s="4" t="n">
+        <v>22.59</v>
+      </c>
       <c r="N20" s="4" t="n"/>
-      <c r="O20" s="4" t="n">
-        <v>22.59</v>
-      </c>
+      <c r="O20" s="4" t="n"/>
       <c r="P20" s="4" t="n"/>
       <c r="Q20" s="4" t="n"/>
       <c r="R20" s="4" t="n"/>
@@ -36223,16 +36223,16 @@
       <c r="Y20" s="4" t="n"/>
       <c r="Z20" s="4" t="n"/>
       <c r="AA20" s="4" t="n"/>
-      <c r="AB20" s="4" t="n">
+      <c r="AB20" s="4" t="n"/>
+      <c r="AC20" s="4" t="n">
         <v>23.3</v>
       </c>
-      <c r="AC20" s="4" t="n"/>
       <c r="AD20" s="4" t="n"/>
       <c r="AE20" s="4" t="n"/>
-      <c r="AF20" s="4" t="n">
+      <c r="AF20" s="4" t="n"/>
+      <c r="AG20" s="4" t="n">
         <v>23.5</v>
       </c>
-      <c r="AG20" s="4" t="n"/>
       <c r="AH20" s="4" t="n"/>
       <c r="AI20" s="4" t="n"/>
       <c r="AJ20" s="4" t="n"/>
@@ -36449,10 +36449,10 @@
         <v>22.78</v>
       </c>
       <c r="M24" s="4" t="n"/>
-      <c r="N24" s="4" t="n">
+      <c r="N24" s="4" t="n"/>
+      <c r="O24" s="4" t="n">
         <v>22.69</v>
       </c>
-      <c r="O24" s="4" t="n"/>
       <c r="P24" s="4" t="n"/>
       <c r="Q24" s="4" t="n"/>
       <c r="R24" s="4" t="n"/>
@@ -36507,10 +36507,10 @@
         <v>24.03</v>
       </c>
       <c r="M25" s="4" t="n"/>
-      <c r="N25" s="4" t="n">
+      <c r="N25" s="4" t="n"/>
+      <c r="O25" s="4" t="n">
         <v>24.13</v>
       </c>
-      <c r="O25" s="4" t="n"/>
       <c r="P25" s="4" t="n"/>
       <c r="Q25" s="4" t="n"/>
       <c r="R25" s="4" t="n">
@@ -36525,14 +36525,14 @@
       <c r="Y25" s="4" t="n"/>
       <c r="Z25" s="4" t="n"/>
       <c r="AA25" s="4" t="n"/>
-      <c r="AB25" s="4" t="n"/>
+      <c r="AB25" s="4" t="n">
+        <v>24.22</v>
+      </c>
       <c r="AC25" s="4" t="n"/>
       <c r="AD25" s="4" t="n"/>
       <c r="AE25" s="4" t="n"/>
       <c r="AF25" s="4" t="n"/>
-      <c r="AG25" s="4" t="n">
-        <v>24.22</v>
-      </c>
+      <c r="AG25" s="4" t="n"/>
       <c r="AH25" s="4" t="n"/>
       <c r="AI25" s="4" t="n"/>
       <c r="AJ25" s="4" t="n"/>
@@ -36573,10 +36573,10 @@
         <v>18.65</v>
       </c>
       <c r="M26" s="4" t="n"/>
-      <c r="N26" s="4" t="n">
+      <c r="N26" s="4" t="n"/>
+      <c r="O26" s="4" t="n">
         <v>18.59</v>
       </c>
-      <c r="O26" s="4" t="n"/>
       <c r="P26" s="4" t="n"/>
       <c r="Q26" s="4" t="n"/>
       <c r="R26" s="4" t="n"/>
@@ -36594,10 +36594,10 @@
       <c r="AB26" s="4" t="n"/>
       <c r="AC26" s="4" t="n"/>
       <c r="AD26" s="4" t="n"/>
-      <c r="AE26" s="4" t="n">
+      <c r="AE26" s="4" t="n"/>
+      <c r="AF26" s="4" t="n">
         <v>18.99</v>
       </c>
-      <c r="AF26" s="4" t="n"/>
       <c r="AG26" s="4" t="n"/>
       <c r="AH26" s="4" t="n"/>
       <c r="AI26" s="4" t="n"/>
@@ -36696,10 +36696,10 @@
       <c r="L28" s="4" t="n">
         <v>32.75</v>
       </c>
-      <c r="M28" s="4" t="n">
+      <c r="M28" s="4" t="n"/>
+      <c r="N28" s="4" t="n">
         <v>33.79</v>
       </c>
-      <c r="N28" s="4" t="n"/>
       <c r="O28" s="4" t="n"/>
       <c r="P28" s="4" t="n"/>
       <c r="Q28" s="4" t="n"/>
@@ -36754,10 +36754,10 @@
       <c r="J29" s="4" t="n"/>
       <c r="K29" s="4" t="n"/>
       <c r="L29" s="4" t="n"/>
-      <c r="M29" s="4" t="n">
+      <c r="M29" s="4" t="n"/>
+      <c r="N29" s="4" t="n">
         <v>19.39</v>
       </c>
-      <c r="N29" s="4" t="n"/>
       <c r="O29" s="4" t="n"/>
       <c r="P29" s="4" t="n"/>
       <c r="Q29" s="4" t="n"/>
@@ -36816,11 +36816,11 @@
       <c r="J30" s="4" t="n"/>
       <c r="K30" s="4" t="n"/>
       <c r="L30" s="4" t="n"/>
-      <c r="M30" s="4" t="n"/>
+      <c r="M30" s="4" t="n">
+        <v>23.29</v>
+      </c>
       <c r="N30" s="4" t="n"/>
-      <c r="O30" s="4" t="n">
-        <v>23.29</v>
-      </c>
+      <c r="O30" s="4" t="n"/>
       <c r="P30" s="4" t="n"/>
       <c r="Q30" s="4" t="n">
         <v>23.39</v>
@@ -36837,10 +36837,10 @@
       <c r="Y30" s="4" t="n"/>
       <c r="Z30" s="4" t="n"/>
       <c r="AA30" s="4" t="n"/>
-      <c r="AB30" s="4" t="n">
+      <c r="AB30" s="4" t="n"/>
+      <c r="AC30" s="4" t="n">
         <v>23.95</v>
       </c>
-      <c r="AC30" s="4" t="n"/>
       <c r="AD30" s="4" t="n"/>
       <c r="AE30" s="4" t="n"/>
       <c r="AF30" s="4" t="n"/>
@@ -36902,10 +36902,10 @@
       <c r="Z31" s="4" t="n"/>
       <c r="AA31" s="4" t="n"/>
       <c r="AB31" s="4" t="n"/>
-      <c r="AC31" s="4" t="n">
+      <c r="AC31" s="4" t="n"/>
+      <c r="AD31" s="4" t="n">
         <v>19.25</v>
       </c>
-      <c r="AD31" s="4" t="n"/>
       <c r="AE31" s="4" t="n"/>
       <c r="AF31" s="4" t="n"/>
       <c r="AG31" s="4" t="n"/>
@@ -37012,11 +37012,11 @@
       <c r="J33" s="4" t="n"/>
       <c r="K33" s="4" t="n"/>
       <c r="L33" s="4" t="n"/>
-      <c r="M33" s="4" t="n"/>
+      <c r="M33" s="4" t="n">
+        <v>20.21</v>
+      </c>
       <c r="N33" s="4" t="n"/>
-      <c r="O33" s="4" t="n">
-        <v>20.21</v>
-      </c>
+      <c r="O33" s="4" t="n"/>
       <c r="P33" s="4" t="n"/>
       <c r="Q33" s="4" t="n">
         <v>20.49</v>
@@ -37136,11 +37136,11 @@
       <c r="J35" s="4" t="n"/>
       <c r="K35" s="4" t="n"/>
       <c r="L35" s="4" t="n"/>
-      <c r="M35" s="4" t="n"/>
+      <c r="M35" s="4" t="n">
+        <v>23.69</v>
+      </c>
       <c r="N35" s="4" t="n"/>
-      <c r="O35" s="4" t="n">
-        <v>23.69</v>
-      </c>
+      <c r="O35" s="4" t="n"/>
       <c r="P35" s="4" t="n"/>
       <c r="Q35" s="4" t="n"/>
       <c r="R35" s="4" t="n"/>
@@ -37323,10 +37323,10 @@
         <v>20.6</v>
       </c>
       <c r="M38" s="4" t="n"/>
-      <c r="N38" s="4" t="n">
+      <c r="N38" s="4" t="n"/>
+      <c r="O38" s="4" t="n">
         <v>20.56</v>
       </c>
-      <c r="O38" s="4" t="n"/>
       <c r="P38" s="4" t="n"/>
       <c r="Q38" s="4" t="n"/>
       <c r="R38" s="4" t="n">
@@ -37349,10 +37349,10 @@
       <c r="AC38" s="4" t="n"/>
       <c r="AD38" s="4" t="n"/>
       <c r="AE38" s="4" t="n"/>
-      <c r="AF38" s="4" t="n">
+      <c r="AF38" s="4" t="n"/>
+      <c r="AG38" s="4" t="n">
         <v>21.87</v>
       </c>
-      <c r="AG38" s="4" t="n"/>
       <c r="AH38" s="4" t="n"/>
       <c r="AI38" s="4" t="n"/>
       <c r="AJ38" s="4" t="n"/>
@@ -37406,10 +37406,10 @@
       <c r="AB39" s="4" t="n"/>
       <c r="AC39" s="4" t="n"/>
       <c r="AD39" s="4" t="n"/>
-      <c r="AE39" s="4" t="n">
+      <c r="AE39" s="4" t="n"/>
+      <c r="AF39" s="4" t="n">
         <v>30.7</v>
       </c>
-      <c r="AF39" s="4" t="n"/>
       <c r="AG39" s="4" t="n"/>
       <c r="AH39" s="4" t="n"/>
       <c r="AI39" s="4" t="n"/>
@@ -37570,13 +37570,13 @@
       <c r="L42" s="4" t="n">
         <v>22.05</v>
       </c>
-      <c r="M42" s="4" t="n">
+      <c r="M42" s="4" t="n"/>
+      <c r="N42" s="4" t="n">
         <v>22.89</v>
       </c>
-      <c r="N42" s="4" t="n">
+      <c r="O42" s="4" t="n">
         <v>21.95</v>
       </c>
-      <c r="O42" s="4" t="n"/>
       <c r="P42" s="4" t="n">
         <v>22.79</v>
       </c>
@@ -37593,10 +37593,10 @@
       <c r="AA42" s="4" t="n"/>
       <c r="AB42" s="4" t="n"/>
       <c r="AC42" s="4" t="n"/>
-      <c r="AD42" s="4" t="n">
+      <c r="AD42" s="4" t="n"/>
+      <c r="AE42" s="4" t="n">
         <v>22.7</v>
       </c>
-      <c r="AE42" s="4" t="n"/>
       <c r="AF42" s="4" t="n"/>
       <c r="AG42" s="4" t="n"/>
       <c r="AH42" s="4" t="n"/>
@@ -37693,10 +37693,10 @@
         <v>22.6</v>
       </c>
       <c r="M44" s="4" t="n"/>
-      <c r="N44" s="4" t="n">
+      <c r="N44" s="4" t="n"/>
+      <c r="O44" s="4" t="n">
         <v>22.45</v>
       </c>
-      <c r="O44" s="4" t="n"/>
       <c r="P44" s="4" t="n"/>
       <c r="Q44" s="4" t="n">
         <v>22.4</v>
@@ -37718,13 +37718,13 @@
       </c>
       <c r="AA44" s="4" t="n"/>
       <c r="AB44" s="4" t="n"/>
-      <c r="AC44" s="4" t="n">
+      <c r="AC44" s="4" t="n"/>
+      <c r="AD44" s="4" t="n">
         <v>22.59</v>
       </c>
-      <c r="AD44" s="4" t="n">
+      <c r="AE44" s="4" t="n">
         <v>22.6</v>
       </c>
-      <c r="AE44" s="4" t="n"/>
       <c r="AF44" s="4" t="n"/>
       <c r="AG44" s="4" t="n"/>
       <c r="AH44" s="4" t="n"/>
@@ -37934,10 +37934,10 @@
         <v>24.79</v>
       </c>
       <c r="L48" s="4" t="n"/>
-      <c r="M48" s="4" t="n">
+      <c r="M48" s="4" t="n"/>
+      <c r="N48" s="4" t="n">
         <v>25.59</v>
       </c>
-      <c r="N48" s="4" t="n"/>
       <c r="O48" s="4" t="n"/>
       <c r="P48" s="4" t="n"/>
       <c r="Q48" s="4" t="n"/>
@@ -37996,11 +37996,11 @@
       <c r="J49" s="4" t="n"/>
       <c r="K49" s="4" t="n"/>
       <c r="L49" s="4" t="n"/>
-      <c r="M49" s="4" t="n"/>
+      <c r="M49" s="4" t="n">
+        <v>30.99</v>
+      </c>
       <c r="N49" s="4" t="n"/>
-      <c r="O49" s="4" t="n">
-        <v>30.99</v>
-      </c>
+      <c r="O49" s="4" t="n"/>
       <c r="P49" s="4" t="n"/>
       <c r="Q49" s="4" t="n"/>
       <c r="R49" s="4" t="n"/>
@@ -38054,11 +38054,11 @@
       <c r="J50" s="4" t="n"/>
       <c r="K50" s="4" t="n"/>
       <c r="L50" s="4" t="n"/>
-      <c r="M50" s="4" t="n"/>
+      <c r="M50" s="4" t="n">
+        <v>26.75</v>
+      </c>
       <c r="N50" s="4" t="n"/>
-      <c r="O50" s="4" t="n">
-        <v>26.75</v>
-      </c>
+      <c r="O50" s="4" t="n"/>
       <c r="P50" s="4" t="n"/>
       <c r="Q50" s="4" t="n"/>
       <c r="R50" s="4" t="n"/>
@@ -38071,10 +38071,10 @@
       <c r="Y50" s="4" t="n"/>
       <c r="Z50" s="4" t="n"/>
       <c r="AA50" s="4" t="n"/>
-      <c r="AB50" s="4" t="n">
+      <c r="AB50" s="4" t="n"/>
+      <c r="AC50" s="4" t="n">
         <v>27.69</v>
       </c>
-      <c r="AC50" s="4" t="n"/>
       <c r="AD50" s="4" t="n"/>
       <c r="AE50" s="4" t="n"/>
       <c r="AF50" s="4" t="n"/>
@@ -38121,10 +38121,10 @@
         <v>23.75</v>
       </c>
       <c r="M51" s="4" t="n"/>
-      <c r="N51" s="4" t="n">
+      <c r="N51" s="4" t="n"/>
+      <c r="O51" s="4" t="n">
         <v>23.48</v>
       </c>
-      <c r="O51" s="4" t="n"/>
       <c r="P51" s="4" t="n"/>
       <c r="Q51" s="4" t="n"/>
       <c r="R51" s="4" t="n"/>
@@ -38137,14 +38137,14 @@
       <c r="Y51" s="4" t="n"/>
       <c r="Z51" s="4" t="n"/>
       <c r="AA51" s="4" t="n"/>
-      <c r="AB51" s="4" t="n"/>
+      <c r="AB51" s="4" t="n">
+        <v>23.99</v>
+      </c>
       <c r="AC51" s="4" t="n"/>
       <c r="AD51" s="4" t="n"/>
       <c r="AE51" s="4" t="n"/>
       <c r="AF51" s="4" t="n"/>
-      <c r="AG51" s="4" t="n">
-        <v>23.99</v>
-      </c>
+      <c r="AG51" s="4" t="n"/>
       <c r="AH51" s="4" t="n"/>
       <c r="AI51" s="4" t="n"/>
       <c r="AJ51" s="4" t="n"/>
@@ -38360,11 +38360,11 @@
       <c r="J55" s="4" t="n"/>
       <c r="K55" s="4" t="n"/>
       <c r="L55" s="4" t="n"/>
-      <c r="M55" s="4" t="n"/>
+      <c r="M55" s="4" t="n">
+        <v>33.3</v>
+      </c>
       <c r="N55" s="4" t="n"/>
-      <c r="O55" s="4" t="n">
-        <v>33.3</v>
-      </c>
+      <c r="O55" s="4" t="n"/>
       <c r="P55" s="4" t="n"/>
       <c r="Q55" s="4" t="n"/>
       <c r="R55" s="4" t="n"/>
@@ -38379,10 +38379,10 @@
       <c r="Y55" s="4" t="n"/>
       <c r="Z55" s="4" t="n"/>
       <c r="AA55" s="4" t="n"/>
-      <c r="AB55" s="4" t="n">
+      <c r="AB55" s="4" t="n"/>
+      <c r="AC55" s="4" t="n">
         <v>34.65</v>
       </c>
-      <c r="AC55" s="4" t="n"/>
       <c r="AD55" s="4" t="n"/>
       <c r="AE55" s="4" t="n"/>
       <c r="AF55" s="4" t="n"/>
@@ -38544,10 +38544,10 @@
       <c r="J58" s="4" t="n"/>
       <c r="K58" s="4" t="n"/>
       <c r="L58" s="4" t="n"/>
-      <c r="M58" s="4" t="n">
+      <c r="M58" s="4" t="n"/>
+      <c r="N58" s="4" t="n">
         <v>26.2</v>
       </c>
-      <c r="N58" s="4" t="n"/>
       <c r="O58" s="4" t="n"/>
       <c r="P58" s="4" t="n"/>
       <c r="Q58" s="4" t="n"/>
@@ -38729,10 +38729,10 @@
         <v>21.75</v>
       </c>
       <c r="M61" s="4" t="n"/>
-      <c r="N61" s="4" t="n">
+      <c r="N61" s="4" t="n"/>
+      <c r="O61" s="4" t="n">
         <v>21.82</v>
       </c>
-      <c r="O61" s="4" t="n"/>
       <c r="P61" s="4" t="n">
         <v>21.75</v>
       </c>
@@ -38751,14 +38751,14 @@
         <v>22.15</v>
       </c>
       <c r="AA61" s="4" t="n"/>
-      <c r="AB61" s="4" t="n">
+      <c r="AB61" s="4" t="n"/>
+      <c r="AC61" s="4" t="n">
         <v>22.4</v>
       </c>
-      <c r="AC61" s="4" t="n"/>
-      <c r="AD61" s="4" t="n">
+      <c r="AD61" s="4" t="n"/>
+      <c r="AE61" s="4" t="n">
         <v>21.8</v>
       </c>
-      <c r="AE61" s="4" t="n"/>
       <c r="AF61" s="4" t="n"/>
       <c r="AG61" s="4" t="n"/>
       <c r="AH61" s="4" t="n"/>
@@ -39095,10 +39095,10 @@
       <c r="K67" s="4" t="n"/>
       <c r="L67" s="4" t="n"/>
       <c r="M67" s="4" t="n"/>
-      <c r="N67" s="4" t="n">
+      <c r="N67" s="4" t="n"/>
+      <c r="O67" s="4" t="n">
         <v>17.95</v>
       </c>
-      <c r="O67" s="4" t="n"/>
       <c r="P67" s="4" t="n"/>
       <c r="Q67" s="4" t="n"/>
       <c r="R67" s="4" t="n"/>
@@ -39118,10 +39118,10 @@
       <c r="Z67" s="4" t="n"/>
       <c r="AA67" s="4" t="n"/>
       <c r="AB67" s="4" t="n"/>
-      <c r="AC67" s="4" t="n">
+      <c r="AC67" s="4" t="n"/>
+      <c r="AD67" s="4" t="n">
         <v>18.23</v>
       </c>
-      <c r="AD67" s="4" t="n"/>
       <c r="AE67" s="4" t="n"/>
       <c r="AF67" s="4" t="n"/>
       <c r="AG67" s="4" t="n"/>
@@ -39158,10 +39158,10 @@
       <c r="J68" s="4" t="n"/>
       <c r="K68" s="4" t="n"/>
       <c r="L68" s="4" t="n"/>
-      <c r="M68" s="4" t="n">
+      <c r="M68" s="4" t="n"/>
+      <c r="N68" s="4" t="n">
         <v>28.06</v>
       </c>
-      <c r="N68" s="4" t="n"/>
       <c r="O68" s="4" t="n"/>
       <c r="P68" s="4" t="n"/>
       <c r="Q68" s="4" t="n"/>
@@ -39281,10 +39281,10 @@
         <v>21.29</v>
       </c>
       <c r="M70" s="4" t="n"/>
-      <c r="N70" s="4" t="n">
+      <c r="N70" s="4" t="n"/>
+      <c r="O70" s="4" t="n">
         <v>20.99</v>
       </c>
-      <c r="O70" s="4" t="n"/>
       <c r="P70" s="4" t="n"/>
       <c r="Q70" s="4" t="n"/>
       <c r="R70" s="4" t="n">
@@ -39406,11 +39406,11 @@
       <c r="L72" s="4" t="n">
         <v>25.79</v>
       </c>
-      <c r="M72" s="4" t="n"/>
+      <c r="M72" s="4" t="n">
+        <v>26.1</v>
+      </c>
       <c r="N72" s="4" t="n"/>
-      <c r="O72" s="4" t="n">
-        <v>26.1</v>
-      </c>
+      <c r="O72" s="4" t="n"/>
       <c r="P72" s="4" t="n"/>
       <c r="Q72" s="4" t="n"/>
       <c r="R72" s="4" t="n"/>
@@ -39429,10 +39429,10 @@
       </c>
       <c r="AB72" s="4" t="n"/>
       <c r="AC72" s="4" t="n"/>
-      <c r="AD72" s="4" t="n">
+      <c r="AD72" s="4" t="n"/>
+      <c r="AE72" s="4" t="n">
         <v>25.95</v>
       </c>
-      <c r="AE72" s="4" t="n"/>
       <c r="AF72" s="4" t="n"/>
       <c r="AG72" s="4" t="n"/>
       <c r="AH72" s="4" t="n"/>
@@ -39472,11 +39472,11 @@
       <c r="J73" s="4" t="n"/>
       <c r="K73" s="4" t="n"/>
       <c r="L73" s="4" t="n"/>
-      <c r="M73" s="4" t="n"/>
+      <c r="M73" s="4" t="n">
+        <v>19.4</v>
+      </c>
       <c r="N73" s="4" t="n"/>
-      <c r="O73" s="4" t="n">
-        <v>19.4</v>
-      </c>
+      <c r="O73" s="4" t="n"/>
       <c r="P73" s="4" t="n"/>
       <c r="Q73" s="4" t="n">
         <v>19.39</v>
@@ -39534,11 +39534,11 @@
       </c>
       <c r="K74" s="4" t="n"/>
       <c r="L74" s="4" t="n"/>
-      <c r="M74" s="4" t="n"/>
+      <c r="M74" s="4" t="n">
+        <v>35.2</v>
+      </c>
       <c r="N74" s="4" t="n"/>
-      <c r="O74" s="4" t="n">
-        <v>35.2</v>
-      </c>
+      <c r="O74" s="4" t="n"/>
       <c r="P74" s="4" t="n"/>
       <c r="Q74" s="4" t="n"/>
       <c r="R74" s="4" t="n"/>
@@ -39646,11 +39646,11 @@
       <c r="J76" s="4" t="n"/>
       <c r="K76" s="4" t="n"/>
       <c r="L76" s="4" t="n"/>
-      <c r="M76" s="4" t="n"/>
+      <c r="M76" s="4" t="n">
+        <v>17</v>
+      </c>
       <c r="N76" s="4" t="n"/>
-      <c r="O76" s="4" t="n">
-        <v>17</v>
-      </c>
+      <c r="O76" s="4" t="n"/>
       <c r="P76" s="4" t="n"/>
       <c r="Q76" s="4" t="n">
         <v>17.09</v>
@@ -40184,7 +40184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI84"/>
+  <dimension ref="A1:BJ84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -40248,6 +40248,7 @@
     <col width="7.5" customWidth="1" min="59" max="59"/>
     <col width="7.5" customWidth="1" min="60" max="60"/>
     <col width="7.5" customWidth="1" min="61" max="61"/>
+    <col width="7.5" customWidth="1" min="62" max="62"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -40393,29 +40394,29 @@
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
+          <t>万达★6</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
           <t>狼崽★5</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>21c★1</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>21c★4</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>21c★6</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>万达★6</t>
-        </is>
-      </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>fp1★5</t>
@@ -40483,75 +40484,80 @@
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
+          <t>att★2</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>att★6</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
           <t>无敌牛★5</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>er9★6</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>狼王★6</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>小牛★6</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>att★6</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>大超★1</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>大超★3</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>fe3★5</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>六子★6</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>英灵殿★6</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>ts900★6</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>风扇★5</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>cs★6</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>600lt★5</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>5n★4</t>
         </is>
@@ -40596,17 +40602,17 @@
       <c r="Z2" s="4" t="n"/>
       <c r="AA2" s="4" t="n"/>
       <c r="AB2" s="4" t="n"/>
-      <c r="AC2" s="4" t="n"/>
+      <c r="AC2" s="4" t="n">
+        <v>19.3</v>
+      </c>
       <c r="AD2" s="4" t="n"/>
       <c r="AE2" s="4" t="n"/>
       <c r="AF2" s="4" t="n"/>
-      <c r="AG2" s="4" t="n">
-        <v>19.2</v>
-      </c>
+      <c r="AG2" s="4" t="n"/>
       <c r="AH2" s="4" t="n"/>
       <c r="AI2" s="4" t="n"/>
       <c r="AJ2" s="4" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AK2" s="4" t="n"/>
       <c r="AL2" s="4" t="n"/>
@@ -40633,6 +40639,7 @@
       <c r="BG2" s="4" t="n"/>
       <c r="BH2" s="4" t="n"/>
       <c r="BI2" s="4" t="n"/>
+      <c r="BJ2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n"/>
@@ -40708,6 +40715,7 @@
       <c r="BG3" s="4" t="n"/>
       <c r="BH3" s="4" t="n"/>
       <c r="BI3" s="4" t="n"/>
+      <c r="BJ3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n"/>
@@ -40781,6 +40789,7 @@
       <c r="BG4" s="4" t="n"/>
       <c r="BH4" s="4" t="n"/>
       <c r="BI4" s="4" t="n"/>
+      <c r="BJ4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n"/>
@@ -40807,7 +40816,9 @@
       <c r="N5" s="4" t="n"/>
       <c r="O5" s="4" t="n"/>
       <c r="P5" s="4" t="n"/>
-      <c r="Q5" s="4" t="n"/>
+      <c r="Q5" s="4" t="n">
+        <v>18.48</v>
+      </c>
       <c r="R5" s="4" t="n"/>
       <c r="S5" s="4" t="n"/>
       <c r="T5" s="4" t="n">
@@ -40858,6 +40869,7 @@
       <c r="BG5" s="4" t="n"/>
       <c r="BH5" s="4" t="n"/>
       <c r="BI5" s="4" t="n"/>
+      <c r="BJ5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -40931,6 +40943,7 @@
       <c r="BG6" s="4" t="n"/>
       <c r="BH6" s="4" t="n"/>
       <c r="BI6" s="4" t="n"/>
+      <c r="BJ6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
@@ -41002,6 +41015,7 @@
       <c r="BG7" s="4" t="n"/>
       <c r="BH7" s="4" t="n"/>
       <c r="BI7" s="4" t="n"/>
+      <c r="BJ7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
@@ -41089,6 +41103,7 @@
       <c r="BG8" s="4" t="n"/>
       <c r="BH8" s="4" t="n"/>
       <c r="BI8" s="4" t="n"/>
+      <c r="BJ8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n"/>
@@ -41162,6 +41177,7 @@
       <c r="BG9" s="4" t="n"/>
       <c r="BH9" s="4" t="n"/>
       <c r="BI9" s="4" t="n"/>
+      <c r="BJ9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -41241,6 +41257,7 @@
       <c r="BG10" s="4" t="n"/>
       <c r="BH10" s="4" t="n"/>
       <c r="BI10" s="4" t="n"/>
+      <c r="BJ10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
@@ -41279,10 +41296,10 @@
       <c r="Z11" s="4" t="n"/>
       <c r="AA11" s="4" t="n"/>
       <c r="AB11" s="4" t="n"/>
-      <c r="AC11" s="4" t="n">
+      <c r="AC11" s="4" t="n"/>
+      <c r="AD11" s="4" t="n">
         <v>37.99</v>
       </c>
-      <c r="AD11" s="4" t="n"/>
       <c r="AE11" s="4" t="n"/>
       <c r="AF11" s="4" t="n"/>
       <c r="AG11" s="4" t="n"/>
@@ -41316,6 +41333,7 @@
       <c r="BG11" s="4" t="n"/>
       <c r="BH11" s="4" t="n"/>
       <c r="BI11" s="4" t="n"/>
+      <c r="BJ11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
@@ -41358,13 +41376,13 @@
       </c>
       <c r="AC12" s="4" t="n"/>
       <c r="AD12" s="4" t="n"/>
-      <c r="AE12" s="4" t="n">
+      <c r="AE12" s="4" t="n"/>
+      <c r="AF12" s="4" t="n">
         <v>21.8</v>
       </c>
-      <c r="AF12" s="4" t="n">
+      <c r="AG12" s="4" t="n">
         <v>21.69</v>
       </c>
-      <c r="AG12" s="4" t="n"/>
       <c r="AH12" s="4" t="n"/>
       <c r="AI12" s="4" t="n"/>
       <c r="AJ12" s="4" t="n"/>
@@ -41381,12 +41399,12 @@
       <c r="AS12" s="4" t="n"/>
       <c r="AT12" s="4" t="n"/>
       <c r="AU12" s="4" t="n"/>
-      <c r="AV12" s="4" t="n"/>
+      <c r="AV12" s="4" t="n">
+        <v>22.19</v>
+      </c>
       <c r="AW12" s="4" t="n"/>
       <c r="AX12" s="4" t="n"/>
-      <c r="AY12" s="4" t="n">
-        <v>22.19</v>
-      </c>
+      <c r="AY12" s="4" t="n"/>
       <c r="AZ12" s="4" t="n"/>
       <c r="BA12" s="4" t="n"/>
       <c r="BB12" s="4" t="n"/>
@@ -41397,6 +41415,7 @@
       <c r="BG12" s="4" t="n"/>
       <c r="BH12" s="4" t="n"/>
       <c r="BI12" s="4" t="n"/>
+      <c r="BJ12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
@@ -41468,6 +41487,7 @@
       <c r="BG13" s="4" t="n"/>
       <c r="BH13" s="4" t="n"/>
       <c r="BI13" s="4" t="n"/>
+      <c r="BJ13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -41481,7 +41501,9 @@
         </is>
       </c>
       <c r="C14" s="4" t="n"/>
-      <c r="D14" s="4" t="n"/>
+      <c r="D14" s="4" t="n">
+        <v>26</v>
+      </c>
       <c r="E14" s="4" t="n">
         <v>25.89</v>
       </c>
@@ -41551,6 +41573,7 @@
       <c r="BG14" s="4" t="n"/>
       <c r="BH14" s="4" t="n"/>
       <c r="BI14" s="4" t="n"/>
+      <c r="BJ14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
@@ -41593,10 +41616,10 @@
       <c r="Z15" s="4" t="n"/>
       <c r="AA15" s="4" t="n"/>
       <c r="AB15" s="4" t="n"/>
-      <c r="AC15" s="4" t="n">
+      <c r="AC15" s="4" t="n"/>
+      <c r="AD15" s="4" t="n">
         <v>30.4</v>
       </c>
-      <c r="AD15" s="4" t="n"/>
       <c r="AE15" s="4" t="n"/>
       <c r="AF15" s="4" t="n"/>
       <c r="AG15" s="4" t="n"/>
@@ -41630,6 +41653,7 @@
       <c r="BG15" s="4" t="n"/>
       <c r="BH15" s="4" t="n"/>
       <c r="BI15" s="4" t="n"/>
+      <c r="BJ15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
@@ -41713,6 +41737,7 @@
       <c r="BG16" s="4" t="n"/>
       <c r="BH16" s="4" t="n"/>
       <c r="BI16" s="4" t="n"/>
+      <c r="BJ16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
@@ -41756,7 +41781,9 @@
       <c r="AE17" s="4" t="n"/>
       <c r="AF17" s="4" t="n"/>
       <c r="AG17" s="4" t="n"/>
-      <c r="AH17" s="4" t="n"/>
+      <c r="AH17" s="4" t="n">
+        <v>31.49</v>
+      </c>
       <c r="AI17" s="4" t="n"/>
       <c r="AJ17" s="4" t="n"/>
       <c r="AK17" s="4" t="n"/>
@@ -41784,6 +41811,7 @@
       <c r="BG17" s="4" t="n"/>
       <c r="BH17" s="4" t="n"/>
       <c r="BI17" s="4" t="n"/>
+      <c r="BJ17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -41826,10 +41854,10 @@
       <c r="Z18" s="4" t="n"/>
       <c r="AA18" s="4" t="n"/>
       <c r="AB18" s="4" t="n"/>
-      <c r="AC18" s="4" t="n">
+      <c r="AC18" s="4" t="n"/>
+      <c r="AD18" s="4" t="n">
         <v>24.79</v>
       </c>
-      <c r="AD18" s="4" t="n"/>
       <c r="AE18" s="4" t="n"/>
       <c r="AF18" s="4" t="n"/>
       <c r="AG18" s="4" t="n"/>
@@ -41861,6 +41889,7 @@
       <c r="BG18" s="4" t="n"/>
       <c r="BH18" s="4" t="n"/>
       <c r="BI18" s="4" t="n"/>
+      <c r="BJ18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
@@ -41938,6 +41967,7 @@
       <c r="BG19" s="4" t="n"/>
       <c r="BH19" s="4" t="n"/>
       <c r="BI19" s="4" t="n"/>
+      <c r="BJ19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
@@ -41978,13 +42008,13 @@
       <c r="Z20" s="4" t="n"/>
       <c r="AA20" s="4" t="n"/>
       <c r="AB20" s="4" t="n"/>
-      <c r="AC20" s="4" t="n"/>
+      <c r="AC20" s="4" t="n">
+        <v>22.85</v>
+      </c>
       <c r="AD20" s="4" t="n"/>
       <c r="AE20" s="4" t="n"/>
       <c r="AF20" s="4" t="n"/>
-      <c r="AG20" s="4" t="n">
-        <v>22.85</v>
-      </c>
+      <c r="AG20" s="4" t="n"/>
       <c r="AH20" s="4" t="n"/>
       <c r="AI20" s="4" t="n"/>
       <c r="AJ20" s="4" t="n"/>
@@ -42013,6 +42043,7 @@
       <c r="BG20" s="4" t="n"/>
       <c r="BH20" s="4" t="n"/>
       <c r="BI20" s="4" t="n"/>
+      <c r="BJ20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
@@ -42084,6 +42115,7 @@
       <c r="BG21" s="4" t="n"/>
       <c r="BH21" s="4" t="n"/>
       <c r="BI21" s="4" t="n"/>
+      <c r="BJ21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -42161,6 +42193,7 @@
       <c r="BG22" s="4" t="n"/>
       <c r="BH22" s="4" t="n"/>
       <c r="BI22" s="4" t="n"/>
+      <c r="BJ22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
@@ -42203,10 +42236,10 @@
       <c r="Z23" s="4" t="n"/>
       <c r="AA23" s="4" t="n"/>
       <c r="AB23" s="4" t="n"/>
-      <c r="AC23" s="4" t="n">
+      <c r="AC23" s="4" t="n"/>
+      <c r="AD23" s="4" t="n">
         <v>32.3</v>
       </c>
-      <c r="AD23" s="4" t="n"/>
       <c r="AE23" s="4" t="n"/>
       <c r="AF23" s="4" t="n"/>
       <c r="AG23" s="4" t="n"/>
@@ -42238,6 +42271,7 @@
       <c r="BG23" s="4" t="n"/>
       <c r="BH23" s="4" t="n"/>
       <c r="BI23" s="4" t="n"/>
+      <c r="BJ23" s="4" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
@@ -42315,6 +42349,7 @@
       <c r="BG24" s="4" t="n"/>
       <c r="BH24" s="4" t="n"/>
       <c r="BI24" s="4" t="n"/>
+      <c r="BJ24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
@@ -42386,6 +42421,7 @@
       <c r="BG25" s="4" t="n"/>
       <c r="BH25" s="4" t="n"/>
       <c r="BI25" s="4" t="n"/>
+      <c r="BJ25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -42430,15 +42466,15 @@
       <c r="AB26" s="4" t="n">
         <v>18.95</v>
       </c>
-      <c r="AC26" s="4" t="n">
+      <c r="AC26" s="4" t="n"/>
+      <c r="AD26" s="4" t="n">
         <v>19.5</v>
       </c>
-      <c r="AD26" s="4" t="n"/>
       <c r="AE26" s="4" t="n"/>
-      <c r="AF26" s="4" t="n">
+      <c r="AF26" s="4" t="n"/>
+      <c r="AG26" s="4" t="n">
         <v>18.9</v>
       </c>
-      <c r="AG26" s="4" t="n"/>
       <c r="AH26" s="4" t="n"/>
       <c r="AI26" s="4" t="n"/>
       <c r="AJ26" s="4" t="n"/>
@@ -42467,6 +42503,7 @@
       <c r="BG26" s="4" t="n"/>
       <c r="BH26" s="4" t="n"/>
       <c r="BI26" s="4" t="n"/>
+      <c r="BJ26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n"/>
@@ -42542,6 +42579,7 @@
       <c r="BG27" s="4" t="n"/>
       <c r="BH27" s="4" t="n"/>
       <c r="BI27" s="4" t="n"/>
+      <c r="BJ27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
@@ -42587,10 +42625,10 @@
         <v>33.19</v>
       </c>
       <c r="AC28" s="4" t="n"/>
-      <c r="AD28" s="4" t="n">
+      <c r="AD28" s="4" t="n"/>
+      <c r="AE28" s="4" t="n">
         <v>33.79</v>
       </c>
-      <c r="AE28" s="4" t="n"/>
       <c r="AF28" s="4" t="n"/>
       <c r="AG28" s="4" t="n"/>
       <c r="AH28" s="4" t="n"/>
@@ -42621,6 +42659,7 @@
       <c r="BG28" s="4" t="n"/>
       <c r="BH28" s="4" t="n"/>
       <c r="BI28" s="4" t="n"/>
+      <c r="BJ28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n"/>
@@ -42682,13 +42721,13 @@
       <c r="AW29" s="4" t="n"/>
       <c r="AX29" s="4" t="n"/>
       <c r="AY29" s="4" t="n"/>
-      <c r="AZ29" s="4" t="n">
+      <c r="AZ29" s="4" t="n"/>
+      <c r="BA29" s="4" t="n">
         <v>18.6</v>
       </c>
-      <c r="BA29" s="4" t="n">
+      <c r="BB29" s="4" t="n">
         <v>18.4</v>
       </c>
-      <c r="BB29" s="4" t="n"/>
       <c r="BC29" s="4" t="n"/>
       <c r="BD29" s="4" t="n"/>
       <c r="BE29" s="4" t="n"/>
@@ -42696,6 +42735,7 @@
       <c r="BG29" s="4" t="n"/>
       <c r="BH29" s="4" t="n"/>
       <c r="BI29" s="4" t="n"/>
+      <c r="BJ29" s="4" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -42769,6 +42809,7 @@
       <c r="BG30" s="4" t="n"/>
       <c r="BH30" s="4" t="n"/>
       <c r="BI30" s="4" t="n"/>
+      <c r="BJ30" s="4" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n"/>
@@ -42805,13 +42846,13 @@
       <c r="Z31" s="4" t="n"/>
       <c r="AA31" s="4" t="n"/>
       <c r="AB31" s="4" t="n"/>
-      <c r="AC31" s="4" t="n"/>
+      <c r="AC31" s="4" t="n">
+        <v>19.45</v>
+      </c>
       <c r="AD31" s="4" t="n"/>
       <c r="AE31" s="4" t="n"/>
       <c r="AF31" s="4" t="n"/>
-      <c r="AG31" s="4" t="n">
-        <v>19.45</v>
-      </c>
+      <c r="AG31" s="4" t="n"/>
       <c r="AH31" s="4" t="n"/>
       <c r="AI31" s="4" t="n"/>
       <c r="AJ31" s="4" t="n"/>
@@ -42842,6 +42883,7 @@
       <c r="BG31" s="4" t="n"/>
       <c r="BH31" s="4" t="n"/>
       <c r="BI31" s="4" t="n"/>
+      <c r="BJ31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n"/>
@@ -42882,14 +42924,16 @@
       <c r="Z32" s="4" t="n"/>
       <c r="AA32" s="4" t="n"/>
       <c r="AB32" s="4" t="n"/>
-      <c r="AC32" s="4" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="AD32" s="4" t="n"/>
+      <c r="AC32" s="4" t="n"/>
+      <c r="AD32" s="4" t="n">
+        <v>29.5</v>
+      </c>
       <c r="AE32" s="4" t="n"/>
       <c r="AF32" s="4" t="n"/>
       <c r="AG32" s="4" t="n"/>
-      <c r="AH32" s="4" t="n"/>
+      <c r="AH32" s="4" t="n">
+        <v>29.8</v>
+      </c>
       <c r="AI32" s="4" t="n"/>
       <c r="AJ32" s="4" t="n"/>
       <c r="AK32" s="4" t="n">
@@ -42907,22 +42951,23 @@
       <c r="AU32" s="4" t="n"/>
       <c r="AV32" s="4" t="n"/>
       <c r="AW32" s="4" t="n"/>
-      <c r="AX32" s="4" t="n">
+      <c r="AX32" s="4" t="n"/>
+      <c r="AY32" s="4" t="n"/>
+      <c r="AZ32" s="4" t="n">
         <v>30.1</v>
       </c>
-      <c r="AY32" s="4" t="n"/>
-      <c r="AZ32" s="4" t="n"/>
       <c r="BA32" s="4" t="n"/>
-      <c r="BB32" s="4" t="n">
+      <c r="BB32" s="4" t="n"/>
+      <c r="BC32" s="4" t="n">
         <v>29.56</v>
       </c>
-      <c r="BC32" s="4" t="n"/>
       <c r="BD32" s="4" t="n"/>
       <c r="BE32" s="4" t="n"/>
       <c r="BF32" s="4" t="n"/>
       <c r="BG32" s="4" t="n"/>
       <c r="BH32" s="4" t="n"/>
       <c r="BI32" s="4" t="n"/>
+      <c r="BJ32" s="4" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -42963,13 +43008,13 @@
       <c r="Z33" s="4" t="n"/>
       <c r="AA33" s="4" t="n"/>
       <c r="AB33" s="4" t="n"/>
-      <c r="AC33" s="4" t="n"/>
+      <c r="AC33" s="4" t="n">
+        <v>20.4</v>
+      </c>
       <c r="AD33" s="4" t="n"/>
       <c r="AE33" s="4" t="n"/>
       <c r="AF33" s="4" t="n"/>
-      <c r="AG33" s="4" t="n">
-        <v>20.4</v>
-      </c>
+      <c r="AG33" s="4" t="n"/>
       <c r="AH33" s="4" t="n"/>
       <c r="AI33" s="4" t="n"/>
       <c r="AJ33" s="4" t="n">
@@ -43000,6 +43045,7 @@
       <c r="BG33" s="4" t="n"/>
       <c r="BH33" s="4" t="n"/>
       <c r="BI33" s="4" t="n"/>
+      <c r="BJ33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n"/>
@@ -43033,7 +43079,9 @@
       <c r="S34" s="4" t="n"/>
       <c r="T34" s="4" t="n"/>
       <c r="U34" s="4" t="n"/>
-      <c r="V34" s="4" t="n"/>
+      <c r="V34" s="4" t="n">
+        <v>35.39</v>
+      </c>
       <c r="W34" s="4" t="n"/>
       <c r="X34" s="4" t="n"/>
       <c r="Y34" s="4" t="n"/>
@@ -43058,7 +43106,9 @@
       <c r="AR34" s="4" t="n"/>
       <c r="AS34" s="4" t="n"/>
       <c r="AT34" s="4" t="n"/>
-      <c r="AU34" s="4" t="n"/>
+      <c r="AU34" s="4" t="n">
+        <v>35.7</v>
+      </c>
       <c r="AV34" s="4" t="n"/>
       <c r="AW34" s="4" t="n"/>
       <c r="AX34" s="4" t="n"/>
@@ -43073,6 +43123,7 @@
       <c r="BG34" s="4" t="n"/>
       <c r="BH34" s="4" t="n"/>
       <c r="BI34" s="4" t="n"/>
+      <c r="BJ34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n"/>
@@ -43140,14 +43191,15 @@
       <c r="BA35" s="4" t="n"/>
       <c r="BB35" s="4" t="n"/>
       <c r="BC35" s="4" t="n"/>
-      <c r="BD35" s="4" t="n">
+      <c r="BD35" s="4" t="n"/>
+      <c r="BE35" s="4" t="n">
         <v>24.9</v>
       </c>
-      <c r="BE35" s="4" t="n"/>
       <c r="BF35" s="4" t="n"/>
       <c r="BG35" s="4" t="n"/>
       <c r="BH35" s="4" t="n"/>
       <c r="BI35" s="4" t="n"/>
+      <c r="BJ35" s="4" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n"/>
@@ -43221,6 +43273,7 @@
       <c r="BG36" s="4" t="n"/>
       <c r="BH36" s="4" t="n"/>
       <c r="BI36" s="4" t="n"/>
+      <c r="BJ36" s="4" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -43304,6 +43357,7 @@
       <c r="BG37" s="4" t="n"/>
       <c r="BH37" s="4" t="n"/>
       <c r="BI37" s="4" t="n"/>
+      <c r="BJ37" s="4" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n"/>
@@ -43340,10 +43394,10 @@
       <c r="AB38" s="4" t="n"/>
       <c r="AC38" s="4" t="n"/>
       <c r="AD38" s="4" t="n"/>
-      <c r="AE38" s="4" t="n">
+      <c r="AE38" s="4" t="n"/>
+      <c r="AF38" s="4" t="n">
         <v>21.1</v>
       </c>
-      <c r="AF38" s="4" t="n"/>
       <c r="AG38" s="4" t="n"/>
       <c r="AH38" s="4" t="n">
         <v>21.59</v>
@@ -43377,6 +43431,7 @@
       <c r="BG38" s="4" t="n"/>
       <c r="BH38" s="4" t="n"/>
       <c r="BI38" s="4" t="n"/>
+      <c r="BJ38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n"/>
@@ -43450,6 +43505,7 @@
       <c r="BG39" s="4" t="n"/>
       <c r="BH39" s="4" t="n"/>
       <c r="BI39" s="4" t="n"/>
+      <c r="BJ39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n"/>
@@ -43498,13 +43554,13 @@
       <c r="Z40" s="4" t="n"/>
       <c r="AA40" s="4" t="n"/>
       <c r="AB40" s="4" t="n"/>
-      <c r="AC40" s="4" t="n"/>
+      <c r="AC40" s="4" t="n">
+        <v>35.4</v>
+      </c>
       <c r="AD40" s="4" t="n"/>
       <c r="AE40" s="4" t="n"/>
       <c r="AF40" s="4" t="n"/>
-      <c r="AG40" s="4" t="n">
-        <v>35.4</v>
-      </c>
+      <c r="AG40" s="4" t="n"/>
       <c r="AH40" s="4" t="n">
         <v>35.86</v>
       </c>
@@ -43537,6 +43593,7 @@
       <c r="BG40" s="4" t="n"/>
       <c r="BH40" s="4" t="n"/>
       <c r="BI40" s="4" t="n"/>
+      <c r="BJ40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -43614,6 +43671,7 @@
       <c r="BG41" s="4" t="n"/>
       <c r="BH41" s="4" t="n"/>
       <c r="BI41" s="4" t="n"/>
+      <c r="BJ41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n"/>
@@ -43658,10 +43716,10 @@
       <c r="AB42" s="4" t="n">
         <v>22.3</v>
       </c>
-      <c r="AC42" s="4" t="n">
+      <c r="AC42" s="4" t="n"/>
+      <c r="AD42" s="4" t="n">
         <v>22.8</v>
       </c>
-      <c r="AD42" s="4" t="n"/>
       <c r="AE42" s="4" t="n"/>
       <c r="AF42" s="4" t="n"/>
       <c r="AG42" s="4" t="n"/>
@@ -43693,6 +43751,7 @@
       <c r="BG42" s="4" t="n"/>
       <c r="BH42" s="4" t="n"/>
       <c r="BI42" s="4" t="n"/>
+      <c r="BJ42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n"/>
@@ -43766,6 +43825,7 @@
       <c r="BG43" s="4" t="n"/>
       <c r="BH43" s="4" t="n"/>
       <c r="BI43" s="4" t="n"/>
+      <c r="BJ43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n"/>
@@ -43802,13 +43862,13 @@
       <c r="Z44" s="4" t="n"/>
       <c r="AA44" s="4" t="n"/>
       <c r="AB44" s="4" t="n"/>
-      <c r="AC44" s="4" t="n"/>
+      <c r="AC44" s="4" t="n">
+        <v>22.6</v>
+      </c>
       <c r="AD44" s="4" t="n"/>
       <c r="AE44" s="4" t="n"/>
       <c r="AF44" s="4" t="n"/>
-      <c r="AG44" s="4" t="n">
-        <v>22.6</v>
-      </c>
+      <c r="AG44" s="4" t="n"/>
       <c r="AH44" s="4" t="n"/>
       <c r="AI44" s="4" t="n"/>
       <c r="AJ44" s="4" t="n"/>
@@ -43837,6 +43897,7 @@
       <c r="BG44" s="4" t="n"/>
       <c r="BH44" s="4" t="n"/>
       <c r="BI44" s="4" t="n"/>
+      <c r="BJ44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -43926,6 +43987,7 @@
       <c r="BG45" s="4" t="n"/>
       <c r="BH45" s="4" t="n"/>
       <c r="BI45" s="4" t="n"/>
+      <c r="BJ45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n"/>
@@ -44003,6 +44065,7 @@
       <c r="BG46" s="4" t="n"/>
       <c r="BH46" s="4" t="n"/>
       <c r="BI46" s="4" t="n"/>
+      <c r="BJ46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n"/>
@@ -44063,7 +44126,9 @@
       <c r="AR47" s="4" t="n"/>
       <c r="AS47" s="4" t="n"/>
       <c r="AT47" s="4" t="n"/>
-      <c r="AU47" s="4" t="n"/>
+      <c r="AU47" s="4" t="n">
+        <v>45.1</v>
+      </c>
       <c r="AV47" s="4" t="n"/>
       <c r="AW47" s="4" t="n"/>
       <c r="AX47" s="4" t="n"/>
@@ -44078,6 +44143,7 @@
       <c r="BG47" s="4" t="n"/>
       <c r="BH47" s="4" t="n"/>
       <c r="BI47" s="4" t="n"/>
+      <c r="BJ47" s="4" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n"/>
@@ -44122,10 +44188,10 @@
       <c r="Z48" s="4" t="n"/>
       <c r="AA48" s="4" t="n"/>
       <c r="AB48" s="4" t="n"/>
-      <c r="AC48" s="4" t="n">
+      <c r="AC48" s="4" t="n"/>
+      <c r="AD48" s="4" t="n">
         <v>25.8</v>
       </c>
-      <c r="AD48" s="4" t="n"/>
       <c r="AE48" s="4" t="n"/>
       <c r="AF48" s="4" t="n"/>
       <c r="AG48" s="4" t="n"/>
@@ -44157,6 +44223,7 @@
       <c r="BG48" s="4" t="n"/>
       <c r="BH48" s="4" t="n"/>
       <c r="BI48" s="4" t="n"/>
+      <c r="BJ48" s="4" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -44226,14 +44293,15 @@
       <c r="BA49" s="4" t="n"/>
       <c r="BB49" s="4" t="n"/>
       <c r="BC49" s="4" t="n"/>
-      <c r="BD49" s="4" t="n">
+      <c r="BD49" s="4" t="n"/>
+      <c r="BE49" s="4" t="n">
         <v>31.69</v>
       </c>
-      <c r="BE49" s="4" t="n"/>
       <c r="BF49" s="4" t="n"/>
       <c r="BG49" s="4" t="n"/>
       <c r="BH49" s="4" t="n"/>
       <c r="BI49" s="4" t="n"/>
+      <c r="BJ49" s="4" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="n"/>
@@ -44270,7 +44338,9 @@
       <c r="Z50" s="4" t="n"/>
       <c r="AA50" s="4" t="n"/>
       <c r="AB50" s="4" t="n"/>
-      <c r="AC50" s="4" t="n"/>
+      <c r="AC50" s="4" t="n">
+        <v>27.09</v>
+      </c>
       <c r="AD50" s="4" t="n"/>
       <c r="AE50" s="4" t="n"/>
       <c r="AF50" s="4" t="n"/>
@@ -44303,6 +44373,7 @@
       <c r="BG50" s="4" t="n"/>
       <c r="BH50" s="4" t="n"/>
       <c r="BI50" s="4" t="n"/>
+      <c r="BJ50" s="4" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n"/>
@@ -44337,8 +44408,12 @@
       <c r="X51" s="4" t="n"/>
       <c r="Y51" s="4" t="n"/>
       <c r="Z51" s="4" t="n"/>
-      <c r="AA51" s="4" t="n"/>
-      <c r="AB51" s="4" t="n"/>
+      <c r="AA51" s="4" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="AB51" s="4" t="n">
+        <v>23.95</v>
+      </c>
       <c r="AC51" s="4" t="n"/>
       <c r="AD51" s="4" t="n"/>
       <c r="AE51" s="4" t="n"/>
@@ -44369,11 +44444,12 @@
       <c r="BD51" s="4" t="n"/>
       <c r="BE51" s="4" t="n"/>
       <c r="BF51" s="4" t="n"/>
-      <c r="BG51" s="4" t="n">
+      <c r="BG51" s="4" t="n"/>
+      <c r="BH51" s="4" t="n">
         <v>24.95</v>
       </c>
-      <c r="BH51" s="4" t="n"/>
       <c r="BI51" s="4" t="n"/>
+      <c r="BJ51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n"/>
@@ -44384,9 +44460,15 @@
       </c>
       <c r="C52" s="4" t="n"/>
       <c r="D52" s="4" t="n"/>
-      <c r="E52" s="4" t="n"/>
-      <c r="F52" s="4" t="n"/>
-      <c r="G52" s="4" t="n"/>
+      <c r="E52" s="4" t="n">
+        <v>32.79</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>32.55</v>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>32.45</v>
+      </c>
       <c r="H52" s="4" t="n"/>
       <c r="I52" s="4" t="n"/>
       <c r="J52" s="4" t="n"/>
@@ -44394,7 +44476,7 @@
       <c r="L52" s="4" t="n"/>
       <c r="M52" s="4" t="n"/>
       <c r="N52" s="4" t="n">
-        <v>32.5</v>
+        <v>32.6</v>
       </c>
       <c r="O52" s="4" t="n">
         <v>32.4</v>
@@ -44414,7 +44496,9 @@
       <c r="X52" s="4" t="n"/>
       <c r="Y52" s="4" t="n"/>
       <c r="Z52" s="4" t="n"/>
-      <c r="AA52" s="4" t="n"/>
+      <c r="AA52" s="4" t="n">
+        <v>33.7</v>
+      </c>
       <c r="AB52" s="4" t="n"/>
       <c r="AC52" s="4" t="n"/>
       <c r="AD52" s="4" t="n"/>
@@ -44451,6 +44535,7 @@
       <c r="BG52" s="4" t="n"/>
       <c r="BH52" s="4" t="n"/>
       <c r="BI52" s="4" t="n"/>
+      <c r="BJ52" s="4" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -44530,6 +44615,7 @@
       <c r="BG53" s="4" t="n"/>
       <c r="BH53" s="4" t="n"/>
       <c r="BI53" s="4" t="n"/>
+      <c r="BJ53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n"/>
@@ -44603,6 +44689,7 @@
       <c r="BG54" s="4" t="n"/>
       <c r="BH54" s="4" t="n"/>
       <c r="BI54" s="4" t="n"/>
+      <c r="BJ54" s="4" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n"/>
@@ -44639,13 +44726,13 @@
       <c r="Z55" s="4" t="n"/>
       <c r="AA55" s="4" t="n"/>
       <c r="AB55" s="4" t="n"/>
-      <c r="AC55" s="4" t="n"/>
+      <c r="AC55" s="4" t="n">
+        <v>33.29</v>
+      </c>
       <c r="AD55" s="4" t="n"/>
       <c r="AE55" s="4" t="n"/>
       <c r="AF55" s="4" t="n"/>
-      <c r="AG55" s="4" t="n">
-        <v>33.29</v>
-      </c>
+      <c r="AG55" s="4" t="n"/>
       <c r="AH55" s="4" t="n"/>
       <c r="AI55" s="4" t="n"/>
       <c r="AJ55" s="4" t="n"/>
@@ -44674,6 +44761,7 @@
       <c r="BG55" s="4" t="n"/>
       <c r="BH55" s="4" t="n"/>
       <c r="BI55" s="4" t="n"/>
+      <c r="BJ55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n"/>
@@ -44747,6 +44835,7 @@
       <c r="BG56" s="4" t="n"/>
       <c r="BH56" s="4" t="n"/>
       <c r="BI56" s="4" t="n"/>
+      <c r="BJ56" s="4" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -44820,13 +44909,13 @@
       <c r="AW57" s="4" t="n"/>
       <c r="AX57" s="4" t="n"/>
       <c r="AY57" s="4" t="n"/>
-      <c r="AZ57" s="4" t="n">
+      <c r="AZ57" s="4" t="n"/>
+      <c r="BA57" s="4" t="n">
         <v>36.39</v>
       </c>
-      <c r="BA57" s="4" t="n">
+      <c r="BB57" s="4" t="n">
         <v>35.9</v>
       </c>
-      <c r="BB57" s="4" t="n"/>
       <c r="BC57" s="4" t="n"/>
       <c r="BD57" s="4" t="n"/>
       <c r="BE57" s="4" t="n"/>
@@ -44834,6 +44923,7 @@
       <c r="BG57" s="4" t="n"/>
       <c r="BH57" s="4" t="n"/>
       <c r="BI57" s="4" t="n"/>
+      <c r="BJ57" s="4" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="n"/>
@@ -44865,7 +44955,9 @@
       <c r="S58" s="4" t="n"/>
       <c r="T58" s="4" t="n"/>
       <c r="U58" s="4" t="n"/>
-      <c r="V58" s="4" t="n"/>
+      <c r="V58" s="4" t="n">
+        <v>25.4</v>
+      </c>
       <c r="W58" s="4" t="n"/>
       <c r="X58" s="4" t="n"/>
       <c r="Y58" s="4" t="n"/>
@@ -44905,6 +44997,7 @@
       <c r="BG58" s="4" t="n"/>
       <c r="BH58" s="4" t="n"/>
       <c r="BI58" s="4" t="n"/>
+      <c r="BJ58" s="4" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n"/>
@@ -44980,6 +45073,7 @@
       <c r="BG59" s="4" t="n"/>
       <c r="BH59" s="4" t="n"/>
       <c r="BI59" s="4" t="n"/>
+      <c r="BJ59" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n"/>
@@ -45061,6 +45155,7 @@
       <c r="BG60" s="4" t="n"/>
       <c r="BH60" s="4" t="n"/>
       <c r="BI60" s="4" t="n"/>
+      <c r="BJ60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -45136,6 +45231,7 @@
       <c r="BG61" s="4" t="n"/>
       <c r="BH61" s="4" t="n"/>
       <c r="BI61" s="4" t="n"/>
+      <c r="BJ61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="n"/>
@@ -45215,6 +45311,7 @@
       <c r="BG62" s="4" t="n"/>
       <c r="BH62" s="4" t="n"/>
       <c r="BI62" s="4" t="n"/>
+      <c r="BJ62" s="4" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n"/>
@@ -45252,7 +45349,9 @@
       <c r="Q63" s="4" t="n"/>
       <c r="R63" s="4" t="n"/>
       <c r="S63" s="4" t="n"/>
-      <c r="T63" s="4" t="n"/>
+      <c r="T63" s="4" t="n">
+        <v>24.6</v>
+      </c>
       <c r="U63" s="4" t="n"/>
       <c r="V63" s="4" t="n">
         <v>25.39</v>
@@ -45298,6 +45397,7 @@
       <c r="BG63" s="4" t="n"/>
       <c r="BH63" s="4" t="n"/>
       <c r="BI63" s="4" t="n"/>
+      <c r="BJ63" s="4" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n"/>
@@ -45329,9 +45429,7 @@
       <c r="Q64" s="4" t="n"/>
       <c r="R64" s="4" t="n"/>
       <c r="S64" s="4" t="n"/>
-      <c r="T64" s="4" t="n">
-        <v>24.6</v>
-      </c>
+      <c r="T64" s="4" t="n"/>
       <c r="U64" s="4" t="n"/>
       <c r="V64" s="4" t="n"/>
       <c r="W64" s="4" t="n"/>
@@ -45340,7 +45438,9 @@
       <c r="Z64" s="4" t="n"/>
       <c r="AA64" s="4" t="n"/>
       <c r="AB64" s="4" t="n"/>
-      <c r="AC64" s="4" t="n"/>
+      <c r="AC64" s="4" t="n">
+        <v>37.05</v>
+      </c>
       <c r="AD64" s="4" t="n"/>
       <c r="AE64" s="4" t="n"/>
       <c r="AF64" s="4" t="n"/>
@@ -45373,6 +45473,7 @@
       <c r="BG64" s="4" t="n"/>
       <c r="BH64" s="4" t="n"/>
       <c r="BI64" s="4" t="n"/>
+      <c r="BJ64" s="4" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -45446,6 +45547,7 @@
       <c r="BG65" s="4" t="n"/>
       <c r="BH65" s="4" t="n"/>
       <c r="BI65" s="4" t="n"/>
+      <c r="BJ65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="n"/>
@@ -45521,6 +45623,7 @@
       <c r="BG66" s="4" t="n"/>
       <c r="BH66" s="4" t="n"/>
       <c r="BI66" s="4" t="n"/>
+      <c r="BJ66" s="4" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n"/>
@@ -45596,6 +45699,7 @@
       <c r="BG67" s="4" t="n"/>
       <c r="BH67" s="4" t="n"/>
       <c r="BI67" s="4" t="n"/>
+      <c r="BJ67" s="4" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n"/>
@@ -45671,6 +45775,7 @@
       <c r="BG68" s="4" t="n"/>
       <c r="BH68" s="4" t="n"/>
       <c r="BI68" s="4" t="n"/>
+      <c r="BJ68" s="4" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -45744,6 +45849,7 @@
       <c r="BG69" s="4" t="n"/>
       <c r="BH69" s="4" t="n"/>
       <c r="BI69" s="4" t="n"/>
+      <c r="BJ69" s="4" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="n"/>
@@ -45781,10 +45887,10 @@
       <c r="AC70" s="4" t="n"/>
       <c r="AD70" s="4" t="n"/>
       <c r="AE70" s="4" t="n"/>
-      <c r="AF70" s="4" t="n">
+      <c r="AF70" s="4" t="n"/>
+      <c r="AG70" s="4" t="n">
         <v>21.19</v>
       </c>
-      <c r="AG70" s="4" t="n"/>
       <c r="AH70" s="4" t="n">
         <v>21.53</v>
       </c>
@@ -45815,6 +45921,7 @@
       <c r="BG70" s="4" t="n"/>
       <c r="BH70" s="4" t="n"/>
       <c r="BI70" s="4" t="n"/>
+      <c r="BJ70" s="4" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n"/>
@@ -45886,6 +45993,7 @@
       <c r="BG71" s="4" t="n"/>
       <c r="BH71" s="4" t="n"/>
       <c r="BI71" s="4" t="n"/>
+      <c r="BJ71" s="4" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n"/>
@@ -45922,13 +46030,13 @@
       <c r="Z72" s="4" t="n"/>
       <c r="AA72" s="4" t="n"/>
       <c r="AB72" s="4" t="n"/>
-      <c r="AC72" s="4" t="n"/>
+      <c r="AC72" s="4" t="n">
+        <v>26.25</v>
+      </c>
       <c r="AD72" s="4" t="n"/>
       <c r="AE72" s="4" t="n"/>
       <c r="AF72" s="4" t="n"/>
-      <c r="AG72" s="4" t="n">
-        <v>26.25</v>
-      </c>
+      <c r="AG72" s="4" t="n"/>
       <c r="AH72" s="4" t="n">
         <v>26.49</v>
       </c>
@@ -45951,16 +46059,17 @@
       <c r="AY72" s="4" t="n"/>
       <c r="AZ72" s="4" t="n"/>
       <c r="BA72" s="4" t="n"/>
-      <c r="BB72" s="4" t="n">
+      <c r="BB72" s="4" t="n"/>
+      <c r="BC72" s="4" t="n">
         <v>26.39</v>
       </c>
-      <c r="BC72" s="4" t="n"/>
       <c r="BD72" s="4" t="n"/>
       <c r="BE72" s="4" t="n"/>
       <c r="BF72" s="4" t="n"/>
       <c r="BG72" s="4" t="n"/>
       <c r="BH72" s="4" t="n"/>
       <c r="BI72" s="4" t="n"/>
+      <c r="BJ72" s="4" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -46001,13 +46110,13 @@
       <c r="Z73" s="4" t="n"/>
       <c r="AA73" s="4" t="n"/>
       <c r="AB73" s="4" t="n"/>
-      <c r="AC73" s="4" t="n"/>
+      <c r="AC73" s="4" t="n">
+        <v>19.5</v>
+      </c>
       <c r="AD73" s="4" t="n"/>
       <c r="AE73" s="4" t="n"/>
       <c r="AF73" s="4" t="n"/>
-      <c r="AG73" s="4" t="n">
-        <v>19.5</v>
-      </c>
+      <c r="AG73" s="4" t="n"/>
       <c r="AH73" s="4" t="n">
         <v>20.49</v>
       </c>
@@ -46040,6 +46149,7 @@
       <c r="BG73" s="4" t="n"/>
       <c r="BH73" s="4" t="n"/>
       <c r="BI73" s="4" t="n"/>
+      <c r="BJ73" s="4" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="n"/>
@@ -46119,6 +46229,7 @@
       <c r="BG74" s="4" t="n"/>
       <c r="BH74" s="4" t="n"/>
       <c r="BI74" s="4" t="n"/>
+      <c r="BJ74" s="4" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n"/>
@@ -46163,10 +46274,10 @@
       <c r="AB75" s="4" t="n">
         <v>27.15</v>
       </c>
-      <c r="AC75" s="4" t="n">
+      <c r="AC75" s="4" t="n"/>
+      <c r="AD75" s="4" t="n">
         <v>27.5</v>
       </c>
-      <c r="AD75" s="4" t="n"/>
       <c r="AE75" s="4" t="n"/>
       <c r="AF75" s="4" t="n"/>
       <c r="AG75" s="4" t="n"/>
@@ -46198,6 +46309,7 @@
       <c r="BG75" s="4" t="n"/>
       <c r="BH75" s="4" t="n"/>
       <c r="BI75" s="4" t="n"/>
+      <c r="BJ75" s="4" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="n"/>
@@ -46234,13 +46346,13 @@
       <c r="Z76" s="4" t="n"/>
       <c r="AA76" s="4" t="n"/>
       <c r="AB76" s="4" t="n"/>
-      <c r="AC76" s="4" t="n"/>
+      <c r="AC76" s="4" t="n">
+        <v>17.4</v>
+      </c>
       <c r="AD76" s="4" t="n"/>
       <c r="AE76" s="4" t="n"/>
       <c r="AF76" s="4" t="n"/>
-      <c r="AG76" s="4" t="n">
-        <v>17.4</v>
-      </c>
+      <c r="AG76" s="4" t="n"/>
       <c r="AH76" s="4" t="n"/>
       <c r="AI76" s="4" t="n"/>
       <c r="AJ76" s="4" t="n">
@@ -46271,6 +46383,7 @@
       <c r="BG76" s="4" t="n"/>
       <c r="BH76" s="4" t="n"/>
       <c r="BI76" s="4" t="n"/>
+      <c r="BJ76" s="4" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -46354,6 +46467,7 @@
       <c r="BG77" s="4" t="n"/>
       <c r="BH77" s="4" t="n"/>
       <c r="BI77" s="4" t="n"/>
+      <c r="BJ77" s="4" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="n"/>
@@ -46433,6 +46547,7 @@
       <c r="BG78" s="4" t="n"/>
       <c r="BH78" s="4" t="n"/>
       <c r="BI78" s="4" t="n"/>
+      <c r="BJ78" s="4" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n"/>
@@ -46514,6 +46629,7 @@
       <c r="BG79" s="4" t="n"/>
       <c r="BH79" s="4" t="n"/>
       <c r="BI79" s="4" t="n"/>
+      <c r="BJ79" s="4" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="n"/>
@@ -46587,6 +46703,7 @@
       <c r="BG80" s="4" t="n"/>
       <c r="BH80" s="4" t="n"/>
       <c r="BI80" s="4" t="n"/>
+      <c r="BJ80" s="4" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
@@ -46666,6 +46783,7 @@
       <c r="BG81" s="4" t="n"/>
       <c r="BH81" s="4" t="n"/>
       <c r="BI81" s="4" t="n"/>
+      <c r="BJ81" s="4" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="n"/>
@@ -46743,6 +46861,7 @@
       <c r="BG82" s="4" t="n"/>
       <c r="BH82" s="4" t="n"/>
       <c r="BI82" s="4" t="n"/>
+      <c r="BJ82" s="4" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n"/>
@@ -46776,7 +46895,9 @@
       <c r="S83" s="4" t="n"/>
       <c r="T83" s="4" t="n"/>
       <c r="U83" s="4" t="n"/>
-      <c r="V83" s="4" t="n"/>
+      <c r="V83" s="4" t="n">
+        <v>27.1</v>
+      </c>
       <c r="W83" s="4" t="n"/>
       <c r="X83" s="4" t="n"/>
       <c r="Y83" s="4" t="n"/>
@@ -46816,6 +46937,7 @@
       <c r="BG83" s="4" t="n"/>
       <c r="BH83" s="4" t="n"/>
       <c r="BI83" s="4" t="n"/>
+      <c r="BJ83" s="4" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="n"/>
@@ -46863,10 +46985,10 @@
       <c r="AA84" s="4" t="n"/>
       <c r="AB84" s="4" t="n"/>
       <c r="AC84" s="4" t="n"/>
-      <c r="AD84" s="4" t="n">
+      <c r="AD84" s="4" t="n"/>
+      <c r="AE84" s="4" t="n">
         <v>29.43</v>
       </c>
-      <c r="AE84" s="4" t="n"/>
       <c r="AF84" s="4" t="n"/>
       <c r="AG84" s="4" t="n"/>
       <c r="AH84" s="4" t="n"/>
@@ -46897,9 +47019,10 @@
       <c r="BG84" s="4" t="n"/>
       <c r="BH84" s="4" t="n"/>
       <c r="BI84" s="4" t="n"/>
+      <c r="BJ84" s="4" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BI84"/>
+  <autoFilter ref="A1:BJ84"/>
   <mergeCells count="21">
     <mergeCell ref="A61:A64"/>
     <mergeCell ref="A69:A72"/>
@@ -46933,7 +47056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI84"/>
+  <dimension ref="A1:BJ84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -46997,6 +47120,7 @@
     <col width="7.5" customWidth="1" min="59" max="59"/>
     <col width="7.5" customWidth="1" min="60" max="60"/>
     <col width="7.5" customWidth="1" min="61" max="61"/>
+    <col width="7.5" customWidth="1" min="62" max="62"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -47142,29 +47266,29 @@
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
+          <t>万达★6</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
           <t>狼崽★5</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>21c★1</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>21c★4</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>21c★6</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>万达★6</t>
-        </is>
-      </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>fp1★5</t>
@@ -47232,75 +47356,80 @@
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
+          <t>att★2</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>att★6</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
           <t>无敌牛★5</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>er9★6</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>狼王★6</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>小牛★6</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>att★6</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>大超★1</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>大超★3</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>fe3★5</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>六子★6</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>英灵殿★6</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>ts900★6</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>风扇★5</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>cs★6</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>600lt★5</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>5n★4</t>
         </is>
@@ -47347,15 +47476,15 @@
       <c r="Z2" s="4" t="n"/>
       <c r="AA2" s="4" t="n"/>
       <c r="AB2" s="4" t="n"/>
-      <c r="AC2" s="4" t="n"/>
+      <c r="AC2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD2" s="4" t="n"/>
       <c r="AE2" s="4" t="n"/>
       <c r="AF2" s="4" t="n"/>
-      <c r="AG2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG2" s="4" t="n"/>
       <c r="AH2" s="4" t="n"/>
       <c r="AI2" s="4" t="inlineStr">
         <is>
@@ -47386,14 +47515,14 @@
       </c>
       <c r="AT2" s="4" t="n"/>
       <c r="AU2" s="4" t="n"/>
-      <c r="AV2" s="4" t="n"/>
+      <c r="AV2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW2" s="4" t="n"/>
       <c r="AX2" s="4" t="n"/>
-      <c r="AY2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY2" s="4" t="n"/>
       <c r="AZ2" s="4" t="n"/>
       <c r="BA2" s="4" t="n"/>
       <c r="BB2" s="4" t="n"/>
@@ -47403,7 +47532,8 @@
       <c r="BF2" s="4" t="n"/>
       <c r="BG2" s="4" t="n"/>
       <c r="BH2" s="4" t="n"/>
-      <c r="BI2" s="4" t="inlineStr">
+      <c r="BI2" s="4" t="n"/>
+      <c r="BJ2" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -47466,12 +47596,12 @@
         </is>
       </c>
       <c r="AB3" s="4" t="n"/>
-      <c r="AC3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AD3" s="4" t="n"/>
+      <c r="AC3" s="4" t="n"/>
+      <c r="AD3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE3" s="4" t="n"/>
       <c r="AF3" s="4" t="n"/>
       <c r="AG3" s="4" t="n"/>
@@ -47505,14 +47635,14 @@
       <c r="AS3" s="4" t="n"/>
       <c r="AT3" s="4" t="n"/>
       <c r="AU3" s="4" t="n"/>
-      <c r="AV3" s="4" t="n"/>
+      <c r="AV3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW3" s="4" t="n"/>
       <c r="AX3" s="4" t="n"/>
-      <c r="AY3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY3" s="4" t="n"/>
       <c r="AZ3" s="4" t="n"/>
       <c r="BA3" s="4" t="n"/>
       <c r="BB3" s="4" t="n"/>
@@ -47523,6 +47653,7 @@
       <c r="BG3" s="4" t="n"/>
       <c r="BH3" s="4" t="n"/>
       <c r="BI3" s="4" t="n"/>
+      <c r="BJ3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n"/>
@@ -47577,12 +47708,12 @@
         </is>
       </c>
       <c r="AB4" s="4" t="n"/>
-      <c r="AC4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AD4" s="4" t="n"/>
+      <c r="AC4" s="4" t="n"/>
+      <c r="AD4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE4" s="4" t="n"/>
       <c r="AF4" s="4" t="n"/>
       <c r="AG4" s="4" t="n"/>
@@ -47608,14 +47739,14 @@
       <c r="AS4" s="4" t="n"/>
       <c r="AT4" s="4" t="n"/>
       <c r="AU4" s="4" t="n"/>
-      <c r="AV4" s="4" t="n"/>
+      <c r="AV4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW4" s="4" t="n"/>
       <c r="AX4" s="4" t="n"/>
-      <c r="AY4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY4" s="4" t="n"/>
       <c r="AZ4" s="4" t="n"/>
       <c r="BA4" s="4" t="n"/>
       <c r="BB4" s="4" t="n"/>
@@ -47626,6 +47757,7 @@
       <c r="BG4" s="4" t="n"/>
       <c r="BH4" s="4" t="n"/>
       <c r="BI4" s="4" t="n"/>
+      <c r="BJ4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n"/>
@@ -47656,7 +47788,11 @@
       <c r="N5" s="4" t="n"/>
       <c r="O5" s="4" t="n"/>
       <c r="P5" s="4" t="n"/>
-      <c r="Q5" s="4" t="n"/>
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="R5" s="4" t="n"/>
       <c r="S5" s="4" t="inlineStr">
         <is>
@@ -47715,14 +47851,14 @@
       </c>
       <c r="AT5" s="4" t="n"/>
       <c r="AU5" s="4" t="n"/>
-      <c r="AV5" s="4" t="n"/>
+      <c r="AV5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW5" s="4" t="n"/>
       <c r="AX5" s="4" t="n"/>
-      <c r="AY5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY5" s="4" t="n"/>
       <c r="AZ5" s="4" t="n"/>
       <c r="BA5" s="4" t="n"/>
       <c r="BB5" s="4" t="n"/>
@@ -47733,6 +47869,7 @@
       <c r="BG5" s="4" t="n"/>
       <c r="BH5" s="4" t="n"/>
       <c r="BI5" s="4" t="n"/>
+      <c r="BJ5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -47775,15 +47912,15 @@
       <c r="Z6" s="4" t="n"/>
       <c r="AA6" s="4" t="n"/>
       <c r="AB6" s="4" t="n"/>
-      <c r="AC6" s="4" t="n"/>
+      <c r="AC6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD6" s="4" t="n"/>
       <c r="AE6" s="4" t="n"/>
       <c r="AF6" s="4" t="n"/>
-      <c r="AG6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG6" s="4" t="n"/>
       <c r="AH6" s="4" t="n"/>
       <c r="AI6" s="4" t="n"/>
       <c r="AJ6" s="4" t="inlineStr">
@@ -47806,19 +47943,19 @@
       <c r="AS6" s="4" t="n"/>
       <c r="AT6" s="4" t="n"/>
       <c r="AU6" s="4" t="n"/>
-      <c r="AV6" s="4" t="n"/>
+      <c r="AV6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW6" s="4" t="n"/>
-      <c r="AX6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AY6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AZ6" s="4" t="n"/>
+      <c r="AX6" s="4" t="n"/>
+      <c r="AY6" s="4" t="n"/>
+      <c r="AZ6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BA6" s="4" t="n"/>
       <c r="BB6" s="4" t="n"/>
       <c r="BC6" s="4" t="n"/>
@@ -47827,7 +47964,8 @@
       <c r="BF6" s="4" t="n"/>
       <c r="BG6" s="4" t="n"/>
       <c r="BH6" s="4" t="n"/>
-      <c r="BI6" s="4" t="inlineStr">
+      <c r="BI6" s="4" t="n"/>
+      <c r="BJ6" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -47882,12 +48020,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AC7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AD7" s="4" t="n"/>
+      <c r="AC7" s="4" t="n"/>
+      <c r="AD7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE7" s="4" t="n"/>
       <c r="AF7" s="4" t="n"/>
       <c r="AG7" s="4" t="n"/>
@@ -47925,14 +48063,14 @@
       <c r="AS7" s="4" t="n"/>
       <c r="AT7" s="4" t="n"/>
       <c r="AU7" s="4" t="n"/>
-      <c r="AV7" s="4" t="n"/>
+      <c r="AV7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW7" s="4" t="n"/>
       <c r="AX7" s="4" t="n"/>
-      <c r="AY7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY7" s="4" t="n"/>
       <c r="AZ7" s="4" t="n"/>
       <c r="BA7" s="4" t="n"/>
       <c r="BB7" s="4" t="n"/>
@@ -47943,6 +48081,7 @@
       <c r="BG7" s="4" t="n"/>
       <c r="BH7" s="4" t="n"/>
       <c r="BI7" s="4" t="n"/>
+      <c r="BJ7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
@@ -48017,12 +48156,12 @@
       <c r="Z8" s="4" t="n"/>
       <c r="AA8" s="4" t="n"/>
       <c r="AB8" s="4" t="n"/>
-      <c r="AC8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AD8" s="4" t="n"/>
+      <c r="AC8" s="4" t="n"/>
+      <c r="AD8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE8" s="4" t="n"/>
       <c r="AF8" s="4" t="n"/>
       <c r="AG8" s="4" t="n"/>
@@ -48056,14 +48195,14 @@
       <c r="AS8" s="4" t="n"/>
       <c r="AT8" s="4" t="n"/>
       <c r="AU8" s="4" t="n"/>
-      <c r="AV8" s="4" t="n"/>
+      <c r="AV8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW8" s="4" t="n"/>
       <c r="AX8" s="4" t="n"/>
-      <c r="AY8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY8" s="4" t="n"/>
       <c r="AZ8" s="4" t="n"/>
       <c r="BA8" s="4" t="n"/>
       <c r="BB8" s="4" t="n"/>
@@ -48074,6 +48213,7 @@
       <c r="BG8" s="4" t="n"/>
       <c r="BH8" s="4" t="n"/>
       <c r="BI8" s="4" t="n"/>
+      <c r="BJ8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n"/>
@@ -48127,12 +48267,12 @@
       <c r="AC9" s="4" t="n"/>
       <c r="AD9" s="4" t="n"/>
       <c r="AE9" s="4" t="n"/>
-      <c r="AF9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AG9" s="4" t="n"/>
+      <c r="AF9" s="4" t="n"/>
+      <c r="AG9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AH9" s="4" t="n"/>
       <c r="AI9" s="4" t="inlineStr">
         <is>
@@ -48163,28 +48303,29 @@
       <c r="AS9" s="4" t="n"/>
       <c r="AT9" s="4" t="n"/>
       <c r="AU9" s="4" t="n"/>
-      <c r="AV9" s="4" t="n"/>
+      <c r="AV9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW9" s="4" t="n"/>
       <c r="AX9" s="4" t="n"/>
-      <c r="AY9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY9" s="4" t="n"/>
       <c r="AZ9" s="4" t="n"/>
       <c r="BA9" s="4" t="n"/>
       <c r="BB9" s="4" t="n"/>
       <c r="BC9" s="4" t="n"/>
       <c r="BD9" s="4" t="n"/>
-      <c r="BE9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BF9" s="4" t="n"/>
+      <c r="BE9" s="4" t="n"/>
+      <c r="BF9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BG9" s="4" t="n"/>
       <c r="BH9" s="4" t="n"/>
-      <c r="BI9" s="4" t="inlineStr">
+      <c r="BI9" s="4" t="n"/>
+      <c r="BJ9" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -48243,14 +48384,14 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AC10" s="4" t="n"/>
+      <c r="AC10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD10" s="4" t="n"/>
       <c r="AE10" s="4" t="n"/>
-      <c r="AF10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AF10" s="4" t="n"/>
       <c r="AG10" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -48286,28 +48427,29 @@
       </c>
       <c r="AT10" s="4" t="n"/>
       <c r="AU10" s="4" t="n"/>
-      <c r="AV10" s="4" t="n"/>
+      <c r="AV10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW10" s="4" t="n"/>
       <c r="AX10" s="4" t="n"/>
-      <c r="AY10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY10" s="4" t="n"/>
       <c r="AZ10" s="4" t="n"/>
       <c r="BA10" s="4" t="n"/>
       <c r="BB10" s="4" t="n"/>
-      <c r="BC10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BD10" s="4" t="n"/>
+      <c r="BC10" s="4" t="n"/>
+      <c r="BD10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE10" s="4" t="n"/>
       <c r="BF10" s="4" t="n"/>
       <c r="BG10" s="4" t="n"/>
       <c r="BH10" s="4" t="n"/>
       <c r="BI10" s="4" t="n"/>
+      <c r="BJ10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
@@ -48354,12 +48496,12 @@
       <c r="Z11" s="4" t="n"/>
       <c r="AA11" s="4" t="n"/>
       <c r="AB11" s="4" t="n"/>
-      <c r="AC11" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AD11" s="4" t="n"/>
+      <c r="AC11" s="4" t="n"/>
+      <c r="AD11" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE11" s="4" t="n"/>
       <c r="AF11" s="4" t="n"/>
       <c r="AG11" s="4" t="n"/>
@@ -48389,14 +48531,14 @@
       <c r="AS11" s="4" t="n"/>
       <c r="AT11" s="4" t="n"/>
       <c r="AU11" s="4" t="n"/>
-      <c r="AV11" s="4" t="n"/>
+      <c r="AV11" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW11" s="4" t="n"/>
       <c r="AX11" s="4" t="n"/>
-      <c r="AY11" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY11" s="4" t="n"/>
       <c r="AZ11" s="4" t="n"/>
       <c r="BA11" s="4" t="n"/>
       <c r="BB11" s="4" t="n"/>
@@ -48407,6 +48549,7 @@
       <c r="BG11" s="4" t="n"/>
       <c r="BH11" s="4" t="n"/>
       <c r="BI11" s="4" t="n"/>
+      <c r="BJ11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
@@ -48461,23 +48604,23 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AC12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AD12" s="4" t="n"/>
-      <c r="AE12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AC12" s="4" t="n"/>
+      <c r="AD12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AE12" s="4" t="n"/>
       <c r="AF12" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AG12" s="4" t="n"/>
+      <c r="AG12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AH12" s="4" t="n"/>
       <c r="AI12" s="4" t="n"/>
       <c r="AJ12" s="4" t="n"/>
@@ -48500,28 +48643,29 @@
       <c r="AS12" s="4" t="n"/>
       <c r="AT12" s="4" t="n"/>
       <c r="AU12" s="4" t="n"/>
-      <c r="AV12" s="4" t="n"/>
+      <c r="AV12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW12" s="4" t="n"/>
       <c r="AX12" s="4" t="n"/>
-      <c r="AY12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY12" s="4" t="n"/>
       <c r="AZ12" s="4" t="n"/>
       <c r="BA12" s="4" t="n"/>
       <c r="BB12" s="4" t="n"/>
-      <c r="BC12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BD12" s="4" t="n"/>
+      <c r="BC12" s="4" t="n"/>
+      <c r="BD12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE12" s="4" t="n"/>
       <c r="BF12" s="4" t="n"/>
       <c r="BG12" s="4" t="n"/>
       <c r="BH12" s="4" t="n"/>
       <c r="BI12" s="4" t="n"/>
+      <c r="BJ12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
@@ -48568,12 +48712,12 @@
       <c r="Z13" s="4" t="n"/>
       <c r="AA13" s="4" t="n"/>
       <c r="AB13" s="4" t="n"/>
-      <c r="AC13" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AD13" s="4" t="n"/>
+      <c r="AC13" s="4" t="n"/>
+      <c r="AD13" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE13" s="4" t="n"/>
       <c r="AF13" s="4" t="n"/>
       <c r="AG13" s="4" t="n"/>
@@ -48603,14 +48747,14 @@
       <c r="AS13" s="4" t="n"/>
       <c r="AT13" s="4" t="n"/>
       <c r="AU13" s="4" t="n"/>
-      <c r="AV13" s="4" t="n"/>
+      <c r="AV13" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW13" s="4" t="n"/>
       <c r="AX13" s="4" t="n"/>
-      <c r="AY13" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY13" s="4" t="n"/>
       <c r="AZ13" s="4" t="n"/>
       <c r="BA13" s="4" t="n"/>
       <c r="BB13" s="4" t="n"/>
@@ -48621,6 +48765,7 @@
       <c r="BG13" s="4" t="n"/>
       <c r="BH13" s="4" t="n"/>
       <c r="BI13" s="4" t="n"/>
+      <c r="BJ13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -48634,7 +48779,11 @@
         </is>
       </c>
       <c r="C14" s="4" t="n"/>
-      <c r="D14" s="4" t="n"/>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -48687,19 +48836,19 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AC14" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AD14" s="4" t="n"/>
+      <c r="AC14" s="4" t="n"/>
+      <c r="AD14" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE14" s="4" t="n"/>
-      <c r="AF14" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AG14" s="4" t="n"/>
+      <c r="AF14" s="4" t="n"/>
+      <c r="AG14" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AH14" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -48722,14 +48871,14 @@
       <c r="AS14" s="4" t="n"/>
       <c r="AT14" s="4" t="n"/>
       <c r="AU14" s="4" t="n"/>
-      <c r="AV14" s="4" t="n"/>
+      <c r="AV14" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW14" s="4" t="n"/>
       <c r="AX14" s="4" t="n"/>
-      <c r="AY14" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY14" s="4" t="n"/>
       <c r="AZ14" s="4" t="n"/>
       <c r="BA14" s="4" t="n"/>
       <c r="BB14" s="4" t="n"/>
@@ -48740,6 +48889,7 @@
       <c r="BG14" s="4" t="n"/>
       <c r="BH14" s="4" t="n"/>
       <c r="BI14" s="4" t="n"/>
+      <c r="BJ14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
@@ -48807,14 +48957,14 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AD15" s="4" t="n"/>
+      <c r="AD15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE15" s="4" t="n"/>
       <c r="AF15" s="4" t="n"/>
-      <c r="AG15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG15" s="4" t="n"/>
       <c r="AH15" s="4" t="n"/>
       <c r="AI15" s="4" t="n"/>
       <c r="AJ15" s="4" t="n"/>
@@ -48849,14 +48999,14 @@
       </c>
       <c r="AT15" s="4" t="n"/>
       <c r="AU15" s="4" t="n"/>
-      <c r="AV15" s="4" t="n"/>
+      <c r="AV15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW15" s="4" t="n"/>
       <c r="AX15" s="4" t="n"/>
-      <c r="AY15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY15" s="4" t="n"/>
       <c r="AZ15" s="4" t="n"/>
       <c r="BA15" s="4" t="n"/>
       <c r="BB15" s="4" t="n"/>
@@ -48867,6 +49017,7 @@
       <c r="BG15" s="4" t="n"/>
       <c r="BH15" s="4" t="n"/>
       <c r="BI15" s="4" t="n"/>
+      <c r="BJ15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
@@ -48933,12 +49084,12 @@
       <c r="Z16" s="4" t="n"/>
       <c r="AA16" s="4" t="n"/>
       <c r="AB16" s="4" t="n"/>
-      <c r="AC16" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AD16" s="4" t="n"/>
+      <c r="AC16" s="4" t="n"/>
+      <c r="AD16" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE16" s="4" t="n"/>
       <c r="AF16" s="4" t="n"/>
       <c r="AG16" s="4" t="n"/>
@@ -48964,14 +49115,14 @@
       <c r="AS16" s="4" t="n"/>
       <c r="AT16" s="4" t="n"/>
       <c r="AU16" s="4" t="n"/>
-      <c r="AV16" s="4" t="n"/>
+      <c r="AV16" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW16" s="4" t="n"/>
       <c r="AX16" s="4" t="n"/>
-      <c r="AY16" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY16" s="4" t="n"/>
       <c r="AZ16" s="4" t="n"/>
       <c r="BA16" s="4" t="n"/>
       <c r="BB16" s="4" t="n"/>
@@ -48982,6 +49133,7 @@
       <c r="BG16" s="4" t="n"/>
       <c r="BH16" s="4" t="n"/>
       <c r="BI16" s="4" t="n"/>
+      <c r="BJ16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
@@ -49037,15 +49189,19 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AD17" s="4" t="n"/>
+      <c r="AD17" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE17" s="4" t="n"/>
       <c r="AF17" s="4" t="n"/>
-      <c r="AG17" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AH17" s="4" t="n"/>
+      <c r="AG17" s="4" t="n"/>
+      <c r="AH17" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AI17" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -49075,14 +49231,14 @@
       </c>
       <c r="AT17" s="4" t="n"/>
       <c r="AU17" s="4" t="n"/>
-      <c r="AV17" s="4" t="n"/>
+      <c r="AV17" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW17" s="4" t="n"/>
       <c r="AX17" s="4" t="n"/>
-      <c r="AY17" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY17" s="4" t="n"/>
       <c r="AZ17" s="4" t="n"/>
       <c r="BA17" s="4" t="n"/>
       <c r="BB17" s="4" t="n"/>
@@ -49093,6 +49249,7 @@
       <c r="BG17" s="4" t="n"/>
       <c r="BH17" s="4" t="n"/>
       <c r="BI17" s="4" t="n"/>
+      <c r="BJ17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -49151,19 +49308,19 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AC18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AD18" s="4" t="n"/>
+      <c r="AC18" s="4" t="n"/>
+      <c r="AD18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE18" s="4" t="n"/>
-      <c r="AF18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AG18" s="4" t="n"/>
+      <c r="AF18" s="4" t="n"/>
+      <c r="AG18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AH18" s="4" t="n"/>
       <c r="AI18" s="4" t="n"/>
       <c r="AJ18" s="4" t="n"/>
@@ -49186,28 +49343,29 @@
       <c r="AS18" s="4" t="n"/>
       <c r="AT18" s="4" t="n"/>
       <c r="AU18" s="4" t="n"/>
-      <c r="AV18" s="4" t="n"/>
+      <c r="AV18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW18" s="4" t="n"/>
       <c r="AX18" s="4" t="n"/>
-      <c r="AY18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY18" s="4" t="n"/>
       <c r="AZ18" s="4" t="n"/>
       <c r="BA18" s="4" t="n"/>
       <c r="BB18" s="4" t="n"/>
-      <c r="BC18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BD18" s="4" t="n"/>
+      <c r="BC18" s="4" t="n"/>
+      <c r="BD18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE18" s="4" t="n"/>
       <c r="BF18" s="4" t="n"/>
       <c r="BG18" s="4" t="n"/>
       <c r="BH18" s="4" t="n"/>
       <c r="BI18" s="4" t="n"/>
+      <c r="BJ18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
@@ -49266,12 +49424,12 @@
       <c r="Z19" s="4" t="n"/>
       <c r="AA19" s="4" t="n"/>
       <c r="AB19" s="4" t="n"/>
-      <c r="AC19" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AD19" s="4" t="n"/>
+      <c r="AC19" s="4" t="n"/>
+      <c r="AD19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE19" s="4" t="n"/>
       <c r="AF19" s="4" t="n"/>
       <c r="AG19" s="4" t="n"/>
@@ -49305,14 +49463,14 @@
       </c>
       <c r="AT19" s="4" t="n"/>
       <c r="AU19" s="4" t="n"/>
-      <c r="AV19" s="4" t="n"/>
+      <c r="AV19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW19" s="4" t="n"/>
       <c r="AX19" s="4" t="n"/>
-      <c r="AY19" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY19" s="4" t="n"/>
       <c r="AZ19" s="4" t="n"/>
       <c r="BA19" s="4" t="n"/>
       <c r="BB19" s="4" t="n"/>
@@ -49323,6 +49481,7 @@
       <c r="BG19" s="4" t="n"/>
       <c r="BH19" s="4" t="n"/>
       <c r="BI19" s="4" t="n"/>
+      <c r="BJ19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
@@ -49369,15 +49528,15 @@
       <c r="Z20" s="4" t="n"/>
       <c r="AA20" s="4" t="n"/>
       <c r="AB20" s="4" t="n"/>
-      <c r="AC20" s="4" t="n"/>
+      <c r="AC20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD20" s="4" t="n"/>
       <c r="AE20" s="4" t="n"/>
       <c r="AF20" s="4" t="n"/>
-      <c r="AG20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG20" s="4" t="n"/>
       <c r="AH20" s="4" t="n"/>
       <c r="AI20" s="4" t="inlineStr">
         <is>
@@ -49407,19 +49566,19 @@
         </is>
       </c>
       <c r="AT20" s="4" t="n"/>
-      <c r="AU20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AV20" s="4" t="n"/>
-      <c r="AW20" s="4" t="n"/>
+      <c r="AU20" s="4" t="n"/>
+      <c r="AV20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AW20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AX20" s="4" t="n"/>
-      <c r="AY20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY20" s="4" t="n"/>
       <c r="AZ20" s="4" t="n"/>
       <c r="BA20" s="4" t="n"/>
       <c r="BB20" s="4" t="n"/>
@@ -49429,7 +49588,8 @@
       <c r="BF20" s="4" t="n"/>
       <c r="BG20" s="4" t="n"/>
       <c r="BH20" s="4" t="n"/>
-      <c r="BI20" s="4" t="inlineStr">
+      <c r="BI20" s="4" t="n"/>
+      <c r="BJ20" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -49484,12 +49644,12 @@
         </is>
       </c>
       <c r="AB21" s="4" t="n"/>
-      <c r="AC21" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AD21" s="4" t="n"/>
+      <c r="AC21" s="4" t="n"/>
+      <c r="AD21" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE21" s="4" t="n"/>
       <c r="AF21" s="4" t="n"/>
       <c r="AG21" s="4" t="n"/>
@@ -49515,14 +49675,14 @@
       <c r="AS21" s="4" t="n"/>
       <c r="AT21" s="4" t="n"/>
       <c r="AU21" s="4" t="n"/>
-      <c r="AV21" s="4" t="n"/>
+      <c r="AV21" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW21" s="4" t="n"/>
       <c r="AX21" s="4" t="n"/>
-      <c r="AY21" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY21" s="4" t="n"/>
       <c r="AZ21" s="4" t="n"/>
       <c r="BA21" s="4" t="n"/>
       <c r="BB21" s="4" t="n"/>
@@ -49533,6 +49693,7 @@
       <c r="BG21" s="4" t="n"/>
       <c r="BH21" s="4" t="n"/>
       <c r="BI21" s="4" t="n"/>
+      <c r="BJ21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -49591,12 +49752,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AC22" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AD22" s="4" t="n"/>
+      <c r="AC22" s="4" t="n"/>
+      <c r="AD22" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE22" s="4" t="n"/>
       <c r="AF22" s="4" t="n"/>
       <c r="AG22" s="4" t="n"/>
@@ -49622,14 +49783,14 @@
       <c r="AS22" s="4" t="n"/>
       <c r="AT22" s="4" t="n"/>
       <c r="AU22" s="4" t="n"/>
-      <c r="AV22" s="4" t="n"/>
+      <c r="AV22" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW22" s="4" t="n"/>
       <c r="AX22" s="4" t="n"/>
-      <c r="AY22" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY22" s="4" t="n"/>
       <c r="AZ22" s="4" t="n"/>
       <c r="BA22" s="4" t="n"/>
       <c r="BB22" s="4" t="n"/>
@@ -49640,6 +49801,7 @@
       <c r="BG22" s="4" t="n"/>
       <c r="BH22" s="4" t="n"/>
       <c r="BI22" s="4" t="n"/>
+      <c r="BJ22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
@@ -49694,12 +49856,12 @@
       <c r="Z23" s="4" t="n"/>
       <c r="AA23" s="4" t="n"/>
       <c r="AB23" s="4" t="n"/>
-      <c r="AC23" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AD23" s="4" t="n"/>
+      <c r="AC23" s="4" t="n"/>
+      <c r="AD23" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE23" s="4" t="n"/>
       <c r="AF23" s="4" t="n"/>
       <c r="AG23" s="4" t="n"/>
@@ -49725,14 +49887,14 @@
       <c r="AS23" s="4" t="n"/>
       <c r="AT23" s="4" t="n"/>
       <c r="AU23" s="4" t="n"/>
-      <c r="AV23" s="4" t="n"/>
+      <c r="AV23" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW23" s="4" t="n"/>
       <c r="AX23" s="4" t="n"/>
-      <c r="AY23" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY23" s="4" t="n"/>
       <c r="AZ23" s="4" t="n"/>
       <c r="BA23" s="4" t="n"/>
       <c r="BB23" s="4" t="n"/>
@@ -49743,6 +49905,7 @@
       <c r="BG23" s="4" t="n"/>
       <c r="BH23" s="4" t="n"/>
       <c r="BI23" s="4" t="n"/>
+      <c r="BJ23" s="4" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
@@ -49797,19 +49960,19 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AC24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AD24" s="4" t="n"/>
+      <c r="AC24" s="4" t="n"/>
+      <c r="AD24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE24" s="4" t="n"/>
-      <c r="AF24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AG24" s="4" t="n"/>
+      <c r="AF24" s="4" t="n"/>
+      <c r="AG24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AH24" s="4" t="n"/>
       <c r="AI24" s="4" t="inlineStr">
         <is>
@@ -49836,14 +49999,14 @@
       <c r="AS24" s="4" t="n"/>
       <c r="AT24" s="4" t="n"/>
       <c r="AU24" s="4" t="n"/>
-      <c r="AV24" s="4" t="n"/>
+      <c r="AV24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW24" s="4" t="n"/>
       <c r="AX24" s="4" t="n"/>
-      <c r="AY24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY24" s="4" t="n"/>
       <c r="AZ24" s="4" t="n"/>
       <c r="BA24" s="4" t="n"/>
       <c r="BB24" s="4" t="n"/>
@@ -49854,6 +50017,7 @@
       <c r="BG24" s="4" t="n"/>
       <c r="BH24" s="4" t="n"/>
       <c r="BI24" s="4" t="n"/>
+      <c r="BJ24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
@@ -49903,12 +50067,12 @@
       <c r="AC25" s="4" t="n"/>
       <c r="AD25" s="4" t="n"/>
       <c r="AE25" s="4" t="n"/>
-      <c r="AF25" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AG25" s="4" t="n"/>
+      <c r="AF25" s="4" t="n"/>
+      <c r="AG25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AH25" s="4" t="n"/>
       <c r="AI25" s="4" t="n"/>
       <c r="AJ25" s="4" t="n"/>
@@ -49931,14 +50095,14 @@
       <c r="AS25" s="4" t="n"/>
       <c r="AT25" s="4" t="n"/>
       <c r="AU25" s="4" t="n"/>
-      <c r="AV25" s="4" t="n"/>
+      <c r="AV25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW25" s="4" t="n"/>
       <c r="AX25" s="4" t="n"/>
-      <c r="AY25" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY25" s="4" t="n"/>
       <c r="AZ25" s="4" t="n"/>
       <c r="BA25" s="4" t="n"/>
       <c r="BB25" s="4" t="n"/>
@@ -49948,7 +50112,8 @@
       <c r="BF25" s="4" t="n"/>
       <c r="BG25" s="4" t="n"/>
       <c r="BH25" s="4" t="n"/>
-      <c r="BI25" s="4" t="inlineStr">
+      <c r="BI25" s="4" t="n"/>
+      <c r="BJ25" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -50012,13 +50177,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AD26" s="4" t="n"/>
+      <c r="AD26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE26" s="4" t="n"/>
-      <c r="AF26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AF26" s="4" t="n"/>
       <c r="AG26" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -50050,12 +50215,12 @@
       <c r="AS26" s="4" t="n"/>
       <c r="AT26" s="4" t="n"/>
       <c r="AU26" s="4" t="n"/>
-      <c r="AV26" s="4" t="n"/>
-      <c r="AW26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AW26" s="4" t="n"/>
       <c r="AX26" s="4" t="n"/>
       <c r="AY26" s="4" t="inlineStr">
         <is>
@@ -50072,6 +50237,7 @@
       <c r="BG26" s="4" t="n"/>
       <c r="BH26" s="4" t="n"/>
       <c r="BI26" s="4" t="n"/>
+      <c r="BJ26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n"/>
@@ -50126,12 +50292,12 @@
         </is>
       </c>
       <c r="AB27" s="4" t="n"/>
-      <c r="AC27" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AD27" s="4" t="n"/>
+      <c r="AC27" s="4" t="n"/>
+      <c r="AD27" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE27" s="4" t="n"/>
       <c r="AF27" s="4" t="n"/>
       <c r="AG27" s="4" t="n"/>
@@ -50161,14 +50327,14 @@
       <c r="AS27" s="4" t="n"/>
       <c r="AT27" s="4" t="n"/>
       <c r="AU27" s="4" t="n"/>
-      <c r="AV27" s="4" t="n"/>
+      <c r="AV27" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW27" s="4" t="n"/>
       <c r="AX27" s="4" t="n"/>
-      <c r="AY27" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY27" s="4" t="n"/>
       <c r="AZ27" s="4" t="n"/>
       <c r="BA27" s="4" t="n"/>
       <c r="BB27" s="4" t="n"/>
@@ -50179,6 +50345,7 @@
       <c r="BG27" s="4" t="n"/>
       <c r="BH27" s="4" t="n"/>
       <c r="BI27" s="4" t="n"/>
+      <c r="BJ27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
@@ -50233,23 +50400,23 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AC28" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AC28" s="4" t="n"/>
       <c r="AD28" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AE28" s="4" t="n"/>
-      <c r="AF28" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AG28" s="4" t="n"/>
+      <c r="AE28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AF28" s="4" t="n"/>
+      <c r="AG28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AH28" s="4" t="n"/>
       <c r="AI28" s="4" t="n"/>
       <c r="AJ28" s="4" t="n"/>
@@ -50268,14 +50435,14 @@
       <c r="AS28" s="4" t="n"/>
       <c r="AT28" s="4" t="n"/>
       <c r="AU28" s="4" t="n"/>
-      <c r="AV28" s="4" t="n"/>
+      <c r="AV28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW28" s="4" t="n"/>
       <c r="AX28" s="4" t="n"/>
-      <c r="AY28" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY28" s="4" t="n"/>
       <c r="AZ28" s="4" t="n"/>
       <c r="BA28" s="4" t="n"/>
       <c r="BB28" s="4" t="n"/>
@@ -50286,6 +50453,7 @@
       <c r="BG28" s="4" t="n"/>
       <c r="BH28" s="4" t="n"/>
       <c r="BI28" s="4" t="n"/>
+      <c r="BJ28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n"/>
@@ -50332,12 +50500,12 @@
       <c r="Z29" s="4" t="n"/>
       <c r="AA29" s="4" t="n"/>
       <c r="AB29" s="4" t="n"/>
-      <c r="AC29" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AD29" s="4" t="n"/>
+      <c r="AC29" s="4" t="n"/>
+      <c r="AD29" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE29" s="4" t="n"/>
       <c r="AF29" s="4" t="n"/>
       <c r="AG29" s="4" t="n"/>
@@ -50363,25 +50531,25 @@
       <c r="AS29" s="4" t="n"/>
       <c r="AT29" s="4" t="n"/>
       <c r="AU29" s="4" t="n"/>
-      <c r="AV29" s="4" t="n"/>
+      <c r="AV29" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW29" s="4" t="n"/>
       <c r="AX29" s="4" t="n"/>
-      <c r="AY29" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AZ29" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY29" s="4" t="n"/>
+      <c r="AZ29" s="4" t="n"/>
       <c r="BA29" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BB29" s="4" t="n"/>
+      <c r="BB29" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC29" s="4" t="n"/>
       <c r="BD29" s="4" t="n"/>
       <c r="BE29" s="4" t="n"/>
@@ -50389,6 +50557,7 @@
       <c r="BG29" s="4" t="n"/>
       <c r="BH29" s="4" t="n"/>
       <c r="BI29" s="4" t="n"/>
+      <c r="BJ29" s="4" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -50431,15 +50600,15 @@
       <c r="Z30" s="4" t="n"/>
       <c r="AA30" s="4" t="n"/>
       <c r="AB30" s="4" t="n"/>
-      <c r="AC30" s="4" t="n"/>
+      <c r="AC30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD30" s="4" t="n"/>
       <c r="AE30" s="4" t="n"/>
       <c r="AF30" s="4" t="n"/>
-      <c r="AG30" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG30" s="4" t="n"/>
       <c r="AH30" s="4" t="n"/>
       <c r="AI30" s="4" t="inlineStr">
         <is>
@@ -50469,19 +50638,19 @@
         </is>
       </c>
       <c r="AT30" s="4" t="n"/>
-      <c r="AU30" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AV30" s="4" t="n"/>
-      <c r="AW30" s="4" t="n"/>
+      <c r="AU30" s="4" t="n"/>
+      <c r="AV30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AW30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AX30" s="4" t="n"/>
-      <c r="AY30" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY30" s="4" t="n"/>
       <c r="AZ30" s="4" t="n"/>
       <c r="BA30" s="4" t="n"/>
       <c r="BB30" s="4" t="n"/>
@@ -50491,7 +50660,8 @@
       <c r="BF30" s="4" t="n"/>
       <c r="BG30" s="4" t="n"/>
       <c r="BH30" s="4" t="n"/>
-      <c r="BI30" s="4" t="inlineStr">
+      <c r="BI30" s="4" t="n"/>
+      <c r="BJ30" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -50534,15 +50704,15 @@
       <c r="Z31" s="4" t="n"/>
       <c r="AA31" s="4" t="n"/>
       <c r="AB31" s="4" t="n"/>
-      <c r="AC31" s="4" t="n"/>
+      <c r="AC31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD31" s="4" t="n"/>
       <c r="AE31" s="4" t="n"/>
       <c r="AF31" s="4" t="n"/>
-      <c r="AG31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG31" s="4" t="n"/>
       <c r="AH31" s="4" t="n"/>
       <c r="AI31" s="4" t="n"/>
       <c r="AJ31" s="4" t="inlineStr">
@@ -50577,28 +50747,29 @@
       </c>
       <c r="AT31" s="4" t="n"/>
       <c r="AU31" s="4" t="n"/>
-      <c r="AV31" s="4" t="n"/>
+      <c r="AV31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW31" s="4" t="n"/>
       <c r="AX31" s="4" t="n"/>
-      <c r="AY31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY31" s="4" t="n"/>
       <c r="AZ31" s="4" t="n"/>
       <c r="BA31" s="4" t="n"/>
       <c r="BB31" s="4" t="n"/>
-      <c r="BC31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BD31" s="4" t="n"/>
+      <c r="BC31" s="4" t="n"/>
+      <c r="BD31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE31" s="4" t="n"/>
       <c r="BF31" s="4" t="n"/>
       <c r="BG31" s="4" t="n"/>
       <c r="BH31" s="4" t="n"/>
-      <c r="BI31" s="4" t="inlineStr">
+      <c r="BI31" s="4" t="n"/>
+      <c r="BJ31" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -50653,16 +50824,20 @@
         </is>
       </c>
       <c r="AB32" s="4" t="n"/>
-      <c r="AC32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AD32" s="4" t="n"/>
+      <c r="AC32" s="4" t="n"/>
+      <c r="AD32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE32" s="4" t="n"/>
       <c r="AF32" s="4" t="n"/>
       <c r="AG32" s="4" t="n"/>
-      <c r="AH32" s="4" t="n"/>
+      <c r="AH32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AI32" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -50684,36 +50859,37 @@
       <c r="AS32" s="4" t="n"/>
       <c r="AT32" s="4" t="n"/>
       <c r="AU32" s="4" t="n"/>
-      <c r="AV32" s="4" t="n"/>
+      <c r="AV32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW32" s="4" t="n"/>
-      <c r="AX32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AY32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AZ32" s="4" t="n"/>
+      <c r="AX32" s="4" t="n"/>
+      <c r="AY32" s="4" t="n"/>
+      <c r="AZ32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BA32" s="4" t="n"/>
-      <c r="BB32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BC32" s="4" t="n"/>
-      <c r="BD32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BE32" s="4" t="n"/>
+      <c r="BB32" s="4" t="n"/>
+      <c r="BC32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BD32" s="4" t="n"/>
+      <c r="BE32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BF32" s="4" t="n"/>
       <c r="BG32" s="4" t="n"/>
       <c r="BH32" s="4" t="n"/>
-      <c r="BI32" s="4" t="inlineStr">
+      <c r="BI32" s="4" t="n"/>
+      <c r="BJ32" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -50760,15 +50936,15 @@
       <c r="Z33" s="4" t="n"/>
       <c r="AA33" s="4" t="n"/>
       <c r="AB33" s="4" t="n"/>
-      <c r="AC33" s="4" t="n"/>
+      <c r="AC33" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD33" s="4" t="n"/>
       <c r="AE33" s="4" t="n"/>
       <c r="AF33" s="4" t="n"/>
-      <c r="AG33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG33" s="4" t="n"/>
       <c r="AH33" s="4" t="n"/>
       <c r="AI33" s="4" t="inlineStr">
         <is>
@@ -50799,28 +50975,29 @@
       </c>
       <c r="AT33" s="4" t="n"/>
       <c r="AU33" s="4" t="n"/>
-      <c r="AV33" s="4" t="n"/>
+      <c r="AV33" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW33" s="4" t="n"/>
       <c r="AX33" s="4" t="n"/>
-      <c r="AY33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY33" s="4" t="n"/>
       <c r="AZ33" s="4" t="n"/>
       <c r="BA33" s="4" t="n"/>
-      <c r="BB33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BC33" s="4" t="n"/>
+      <c r="BB33" s="4" t="n"/>
+      <c r="BC33" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BD33" s="4" t="n"/>
       <c r="BE33" s="4" t="n"/>
       <c r="BF33" s="4" t="n"/>
       <c r="BG33" s="4" t="n"/>
       <c r="BH33" s="4" t="n"/>
-      <c r="BI33" s="4" t="inlineStr">
+      <c r="BI33" s="4" t="n"/>
+      <c r="BJ33" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -50872,7 +51049,11 @@
       </c>
       <c r="T34" s="4" t="n"/>
       <c r="U34" s="4" t="n"/>
-      <c r="V34" s="4" t="n"/>
+      <c r="V34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="W34" s="4" t="n"/>
       <c r="X34" s="4" t="n"/>
       <c r="Y34" s="4" t="n"/>
@@ -50883,12 +51064,12 @@
         </is>
       </c>
       <c r="AB34" s="4" t="n"/>
-      <c r="AC34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AD34" s="4" t="n"/>
+      <c r="AC34" s="4" t="n"/>
+      <c r="AD34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE34" s="4" t="n"/>
       <c r="AF34" s="4" t="n"/>
       <c r="AG34" s="4" t="n"/>
@@ -50913,15 +51094,19 @@
       <c r="AR34" s="4" t="n"/>
       <c r="AS34" s="4" t="n"/>
       <c r="AT34" s="4" t="n"/>
-      <c r="AU34" s="4" t="n"/>
-      <c r="AV34" s="4" t="n"/>
+      <c r="AU34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AV34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW34" s="4" t="n"/>
       <c r="AX34" s="4" t="n"/>
-      <c r="AY34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY34" s="4" t="n"/>
       <c r="AZ34" s="4" t="n"/>
       <c r="BA34" s="4" t="n"/>
       <c r="BB34" s="4" t="n"/>
@@ -50931,7 +51116,8 @@
       <c r="BF34" s="4" t="n"/>
       <c r="BG34" s="4" t="n"/>
       <c r="BH34" s="4" t="n"/>
-      <c r="BI34" s="4" t="inlineStr">
+      <c r="BI34" s="4" t="n"/>
+      <c r="BJ34" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -50974,15 +51160,15 @@
       <c r="Z35" s="4" t="n"/>
       <c r="AA35" s="4" t="n"/>
       <c r="AB35" s="4" t="n"/>
-      <c r="AC35" s="4" t="n"/>
+      <c r="AC35" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD35" s="4" t="n"/>
       <c r="AE35" s="4" t="n"/>
       <c r="AF35" s="4" t="n"/>
-      <c r="AG35" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG35" s="4" t="n"/>
       <c r="AH35" s="4" t="n"/>
       <c r="AI35" s="4" t="inlineStr">
         <is>
@@ -51013,32 +51199,33 @@
       </c>
       <c r="AT35" s="4" t="n"/>
       <c r="AU35" s="4" t="n"/>
-      <c r="AV35" s="4" t="n"/>
+      <c r="AV35" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW35" s="4" t="n"/>
       <c r="AX35" s="4" t="n"/>
-      <c r="AY35" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY35" s="4" t="n"/>
       <c r="AZ35" s="4" t="n"/>
       <c r="BA35" s="4" t="n"/>
-      <c r="BB35" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BC35" s="4" t="n"/>
-      <c r="BD35" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BE35" s="4" t="n"/>
+      <c r="BB35" s="4" t="n"/>
+      <c r="BC35" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BD35" s="4" t="n"/>
+      <c r="BE35" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BF35" s="4" t="n"/>
       <c r="BG35" s="4" t="n"/>
       <c r="BH35" s="4" t="n"/>
-      <c r="BI35" s="4" t="inlineStr">
+      <c r="BI35" s="4" t="n"/>
+      <c r="BJ35" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -51101,12 +51288,12 @@
         </is>
       </c>
       <c r="AB36" s="4" t="n"/>
-      <c r="AC36" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AD36" s="4" t="n"/>
+      <c r="AC36" s="4" t="n"/>
+      <c r="AD36" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE36" s="4" t="n"/>
       <c r="AF36" s="4" t="n"/>
       <c r="AG36" s="4" t="n"/>
@@ -51132,14 +51319,14 @@
       <c r="AS36" s="4" t="n"/>
       <c r="AT36" s="4" t="n"/>
       <c r="AU36" s="4" t="n"/>
-      <c r="AV36" s="4" t="n"/>
+      <c r="AV36" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW36" s="4" t="n"/>
       <c r="AX36" s="4" t="n"/>
-      <c r="AY36" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY36" s="4" t="n"/>
       <c r="AZ36" s="4" t="n"/>
       <c r="BA36" s="4" t="n"/>
       <c r="BB36" s="4" t="n"/>
@@ -51150,6 +51337,7 @@
       <c r="BG36" s="4" t="n"/>
       <c r="BH36" s="4" t="n"/>
       <c r="BI36" s="4" t="n"/>
+      <c r="BJ36" s="4" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -51251,28 +51439,29 @@
       </c>
       <c r="AT37" s="4" t="n"/>
       <c r="AU37" s="4" t="n"/>
-      <c r="AV37" s="4" t="n"/>
+      <c r="AV37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW37" s="4" t="n"/>
       <c r="AX37" s="4" t="n"/>
-      <c r="AY37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY37" s="4" t="n"/>
       <c r="AZ37" s="4" t="n"/>
       <c r="BA37" s="4" t="n"/>
       <c r="BB37" s="4" t="n"/>
       <c r="BC37" s="4" t="n"/>
-      <c r="BD37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BE37" s="4" t="n"/>
+      <c r="BD37" s="4" t="n"/>
+      <c r="BE37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BF37" s="4" t="n"/>
       <c r="BG37" s="4" t="n"/>
       <c r="BH37" s="4" t="n"/>
-      <c r="BI37" s="4" t="inlineStr">
+      <c r="BI37" s="4" t="n"/>
+      <c r="BJ37" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -51329,17 +51518,17 @@
       </c>
       <c r="AC38" s="4" t="n"/>
       <c r="AD38" s="4" t="n"/>
-      <c r="AE38" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AE38" s="4" t="n"/>
       <c r="AF38" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AG38" s="4" t="n"/>
+      <c r="AG38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AH38" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -51370,28 +51559,29 @@
       <c r="AS38" s="4" t="n"/>
       <c r="AT38" s="4" t="n"/>
       <c r="AU38" s="4" t="n"/>
-      <c r="AV38" s="4" t="n"/>
+      <c r="AV38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW38" s="4" t="n"/>
       <c r="AX38" s="4" t="n"/>
-      <c r="AY38" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY38" s="4" t="n"/>
       <c r="AZ38" s="4" t="n"/>
       <c r="BA38" s="4" t="n"/>
       <c r="BB38" s="4" t="n"/>
       <c r="BC38" s="4" t="n"/>
-      <c r="BD38" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BE38" s="4" t="n"/>
+      <c r="BD38" s="4" t="n"/>
+      <c r="BE38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BF38" s="4" t="n"/>
       <c r="BG38" s="4" t="n"/>
       <c r="BH38" s="4" t="n"/>
       <c r="BI38" s="4" t="n"/>
+      <c r="BJ38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n"/>
@@ -51438,19 +51628,19 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AC39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AD39" s="4" t="n"/>
+      <c r="AC39" s="4" t="n"/>
+      <c r="AD39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE39" s="4" t="n"/>
-      <c r="AF39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AG39" s="4" t="n"/>
+      <c r="AF39" s="4" t="n"/>
+      <c r="AG39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AH39" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -51481,28 +51671,29 @@
       <c r="AS39" s="4" t="n"/>
       <c r="AT39" s="4" t="n"/>
       <c r="AU39" s="4" t="n"/>
-      <c r="AV39" s="4" t="n"/>
+      <c r="AV39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW39" s="4" t="n"/>
       <c r="AX39" s="4" t="n"/>
-      <c r="AY39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY39" s="4" t="n"/>
       <c r="AZ39" s="4" t="n"/>
       <c r="BA39" s="4" t="n"/>
       <c r="BB39" s="4" t="n"/>
       <c r="BC39" s="4" t="n"/>
-      <c r="BD39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BE39" s="4" t="n"/>
+      <c r="BD39" s="4" t="n"/>
+      <c r="BE39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BF39" s="4" t="n"/>
       <c r="BG39" s="4" t="n"/>
       <c r="BH39" s="4" t="n"/>
       <c r="BI39" s="4" t="n"/>
+      <c r="BJ39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n"/>
@@ -51569,15 +51760,15 @@
       <c r="Z40" s="4" t="n"/>
       <c r="AA40" s="4" t="n"/>
       <c r="AB40" s="4" t="n"/>
-      <c r="AC40" s="4" t="n"/>
+      <c r="AC40" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD40" s="4" t="n"/>
       <c r="AE40" s="4" t="n"/>
       <c r="AF40" s="4" t="n"/>
-      <c r="AG40" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG40" s="4" t="n"/>
       <c r="AH40" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -51608,28 +51799,29 @@
       </c>
       <c r="AT40" s="4" t="n"/>
       <c r="AU40" s="4" t="n"/>
-      <c r="AV40" s="4" t="n"/>
+      <c r="AV40" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW40" s="4" t="n"/>
       <c r="AX40" s="4" t="n"/>
-      <c r="AY40" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY40" s="4" t="n"/>
       <c r="AZ40" s="4" t="n"/>
       <c r="BA40" s="4" t="n"/>
       <c r="BB40" s="4" t="n"/>
       <c r="BC40" s="4" t="n"/>
-      <c r="BD40" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BE40" s="4" t="n"/>
+      <c r="BD40" s="4" t="n"/>
+      <c r="BE40" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BF40" s="4" t="n"/>
       <c r="BG40" s="4" t="n"/>
       <c r="BH40" s="4" t="n"/>
       <c r="BI40" s="4" t="n"/>
+      <c r="BJ40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -51684,12 +51876,12 @@
       <c r="Z41" s="4" t="n"/>
       <c r="AA41" s="4" t="n"/>
       <c r="AB41" s="4" t="n"/>
-      <c r="AC41" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AD41" s="4" t="n"/>
+      <c r="AC41" s="4" t="n"/>
+      <c r="AD41" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE41" s="4" t="n"/>
       <c r="AF41" s="4" t="n"/>
       <c r="AG41" s="4" t="n"/>
@@ -51711,14 +51903,14 @@
       <c r="AS41" s="4" t="n"/>
       <c r="AT41" s="4" t="n"/>
       <c r="AU41" s="4" t="n"/>
-      <c r="AV41" s="4" t="n"/>
+      <c r="AV41" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW41" s="4" t="n"/>
       <c r="AX41" s="4" t="n"/>
-      <c r="AY41" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY41" s="4" t="n"/>
       <c r="AZ41" s="4" t="n"/>
       <c r="BA41" s="4" t="n"/>
       <c r="BB41" s="4" t="n"/>
@@ -51729,6 +51921,7 @@
       <c r="BG41" s="4" t="n"/>
       <c r="BH41" s="4" t="n"/>
       <c r="BI41" s="4" t="n"/>
+      <c r="BJ41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n"/>
@@ -51787,19 +51980,19 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AC42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AD42" s="4" t="n"/>
+      <c r="AC42" s="4" t="n"/>
+      <c r="AD42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE42" s="4" t="n"/>
-      <c r="AF42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AG42" s="4" t="n"/>
+      <c r="AF42" s="4" t="n"/>
+      <c r="AG42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AH42" s="4" t="n"/>
       <c r="AI42" s="4" t="inlineStr">
         <is>
@@ -51822,14 +52015,14 @@
       <c r="AS42" s="4" t="n"/>
       <c r="AT42" s="4" t="n"/>
       <c r="AU42" s="4" t="n"/>
-      <c r="AV42" s="4" t="n"/>
+      <c r="AV42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW42" s="4" t="n"/>
       <c r="AX42" s="4" t="n"/>
-      <c r="AY42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY42" s="4" t="n"/>
       <c r="AZ42" s="4" t="n"/>
       <c r="BA42" s="4" t="n"/>
       <c r="BB42" s="4" t="n"/>
@@ -51840,6 +52033,7 @@
       <c r="BG42" s="4" t="n"/>
       <c r="BH42" s="4" t="n"/>
       <c r="BI42" s="4" t="n"/>
+      <c r="BJ42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n"/>
@@ -51894,12 +52088,12 @@
         </is>
       </c>
       <c r="AB43" s="4" t="n"/>
-      <c r="AC43" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AD43" s="4" t="n"/>
+      <c r="AC43" s="4" t="n"/>
+      <c r="AD43" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE43" s="4" t="n"/>
       <c r="AF43" s="4" t="n"/>
       <c r="AG43" s="4" t="n"/>
@@ -51925,14 +52119,14 @@
       <c r="AS43" s="4" t="n"/>
       <c r="AT43" s="4" t="n"/>
       <c r="AU43" s="4" t="n"/>
-      <c r="AV43" s="4" t="n"/>
+      <c r="AV43" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW43" s="4" t="n"/>
       <c r="AX43" s="4" t="n"/>
-      <c r="AY43" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY43" s="4" t="n"/>
       <c r="AZ43" s="4" t="n"/>
       <c r="BA43" s="4" t="n"/>
       <c r="BB43" s="4" t="n"/>
@@ -51943,6 +52137,7 @@
       <c r="BG43" s="4" t="n"/>
       <c r="BH43" s="4" t="n"/>
       <c r="BI43" s="4" t="n"/>
+      <c r="BJ43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n"/>
@@ -51981,15 +52176,15 @@
       <c r="Z44" s="4" t="n"/>
       <c r="AA44" s="4" t="n"/>
       <c r="AB44" s="4" t="n"/>
-      <c r="AC44" s="4" t="n"/>
+      <c r="AC44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD44" s="4" t="n"/>
       <c r="AE44" s="4" t="n"/>
       <c r="AF44" s="4" t="n"/>
-      <c r="AG44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG44" s="4" t="n"/>
       <c r="AH44" s="4" t="n"/>
       <c r="AI44" s="4" t="n"/>
       <c r="AJ44" s="4" t="inlineStr">
@@ -52020,28 +52215,29 @@
       <c r="AS44" s="4" t="n"/>
       <c r="AT44" s="4" t="n"/>
       <c r="AU44" s="4" t="n"/>
-      <c r="AV44" s="4" t="n"/>
+      <c r="AV44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW44" s="4" t="n"/>
       <c r="AX44" s="4" t="n"/>
-      <c r="AY44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY44" s="4" t="n"/>
       <c r="AZ44" s="4" t="n"/>
       <c r="BA44" s="4" t="n"/>
       <c r="BB44" s="4" t="n"/>
-      <c r="BC44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BD44" s="4" t="n"/>
+      <c r="BC44" s="4" t="n"/>
+      <c r="BD44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE44" s="4" t="n"/>
       <c r="BF44" s="4" t="n"/>
       <c r="BG44" s="4" t="n"/>
       <c r="BH44" s="4" t="n"/>
       <c r="BI44" s="4" t="n"/>
+      <c r="BJ44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -52112,12 +52308,12 @@
       <c r="Z45" s="4" t="n"/>
       <c r="AA45" s="4" t="n"/>
       <c r="AB45" s="4" t="n"/>
-      <c r="AC45" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AD45" s="4" t="n"/>
+      <c r="AC45" s="4" t="n"/>
+      <c r="AD45" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE45" s="4" t="n"/>
       <c r="AF45" s="4" t="n"/>
       <c r="AG45" s="4" t="n"/>
@@ -52147,14 +52343,14 @@
       <c r="AS45" s="4" t="n"/>
       <c r="AT45" s="4" t="n"/>
       <c r="AU45" s="4" t="n"/>
-      <c r="AV45" s="4" t="n"/>
+      <c r="AV45" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW45" s="4" t="n"/>
       <c r="AX45" s="4" t="n"/>
-      <c r="AY45" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY45" s="4" t="n"/>
       <c r="AZ45" s="4" t="n"/>
       <c r="BA45" s="4" t="n"/>
       <c r="BB45" s="4" t="n"/>
@@ -52165,6 +52361,7 @@
       <c r="BG45" s="4" t="n"/>
       <c r="BH45" s="4" t="n"/>
       <c r="BI45" s="4" t="n"/>
+      <c r="BJ45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n"/>
@@ -52227,12 +52424,12 @@
       <c r="Z46" s="4" t="n"/>
       <c r="AA46" s="4" t="n"/>
       <c r="AB46" s="4" t="n"/>
-      <c r="AC46" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AD46" s="4" t="n"/>
+      <c r="AC46" s="4" t="n"/>
+      <c r="AD46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE46" s="4" t="n"/>
       <c r="AF46" s="4" t="n"/>
       <c r="AG46" s="4" t="n"/>
@@ -52270,14 +52467,14 @@
       </c>
       <c r="AT46" s="4" t="n"/>
       <c r="AU46" s="4" t="n"/>
-      <c r="AV46" s="4" t="n"/>
+      <c r="AV46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW46" s="4" t="n"/>
       <c r="AX46" s="4" t="n"/>
-      <c r="AY46" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY46" s="4" t="n"/>
       <c r="AZ46" s="4" t="n"/>
       <c r="BA46" s="4" t="n"/>
       <c r="BB46" s="4" t="n"/>
@@ -52288,6 +52485,7 @@
       <c r="BG46" s="4" t="n"/>
       <c r="BH46" s="4" t="n"/>
       <c r="BI46" s="4" t="n"/>
+      <c r="BJ46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n"/>
@@ -52346,12 +52544,12 @@
       <c r="Z47" s="4" t="n"/>
       <c r="AA47" s="4" t="n"/>
       <c r="AB47" s="4" t="n"/>
-      <c r="AC47" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AD47" s="4" t="n"/>
+      <c r="AC47" s="4" t="n"/>
+      <c r="AD47" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE47" s="4" t="n"/>
       <c r="AF47" s="4" t="n"/>
       <c r="AG47" s="4" t="n"/>
@@ -52380,29 +52578,34 @@
       <c r="AR47" s="4" t="n"/>
       <c r="AS47" s="4" t="n"/>
       <c r="AT47" s="4" t="n"/>
-      <c r="AU47" s="4" t="n"/>
-      <c r="AV47" s="4" t="n"/>
+      <c r="AU47" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AV47" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW47" s="4" t="n"/>
       <c r="AX47" s="4" t="n"/>
-      <c r="AY47" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY47" s="4" t="n"/>
       <c r="AZ47" s="4" t="n"/>
       <c r="BA47" s="4" t="n"/>
-      <c r="BB47" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BC47" s="4" t="n"/>
+      <c r="BB47" s="4" t="n"/>
+      <c r="BC47" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BD47" s="4" t="n"/>
       <c r="BE47" s="4" t="n"/>
       <c r="BF47" s="4" t="n"/>
       <c r="BG47" s="4" t="n"/>
       <c r="BH47" s="4" t="n"/>
       <c r="BI47" s="4" t="n"/>
+      <c r="BJ47" s="4" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n"/>
@@ -52469,12 +52672,12 @@
         </is>
       </c>
       <c r="AB48" s="4" t="n"/>
-      <c r="AC48" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AD48" s="4" t="n"/>
+      <c r="AC48" s="4" t="n"/>
+      <c r="AD48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE48" s="4" t="n"/>
       <c r="AF48" s="4" t="n"/>
       <c r="AG48" s="4" t="n"/>
@@ -52508,14 +52711,14 @@
         </is>
       </c>
       <c r="AU48" s="4" t="n"/>
-      <c r="AV48" s="4" t="n"/>
+      <c r="AV48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW48" s="4" t="n"/>
       <c r="AX48" s="4" t="n"/>
-      <c r="AY48" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY48" s="4" t="n"/>
       <c r="AZ48" s="4" t="n"/>
       <c r="BA48" s="4" t="n"/>
       <c r="BB48" s="4" t="n"/>
@@ -52526,6 +52729,7 @@
       <c r="BG48" s="4" t="n"/>
       <c r="BH48" s="4" t="n"/>
       <c r="BI48" s="4" t="n"/>
+      <c r="BJ48" s="4" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -52572,15 +52776,15 @@
       <c r="Z49" s="4" t="n"/>
       <c r="AA49" s="4" t="n"/>
       <c r="AB49" s="4" t="n"/>
-      <c r="AC49" s="4" t="n"/>
+      <c r="AC49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD49" s="4" t="n"/>
       <c r="AE49" s="4" t="n"/>
       <c r="AF49" s="4" t="n"/>
-      <c r="AG49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG49" s="4" t="n"/>
       <c r="AH49" s="4" t="n"/>
       <c r="AI49" s="4" t="inlineStr">
         <is>
@@ -52607,28 +52811,29 @@
       </c>
       <c r="AT49" s="4" t="n"/>
       <c r="AU49" s="4" t="n"/>
-      <c r="AV49" s="4" t="n"/>
+      <c r="AV49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW49" s="4" t="n"/>
       <c r="AX49" s="4" t="n"/>
-      <c r="AY49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY49" s="4" t="n"/>
       <c r="AZ49" s="4" t="n"/>
       <c r="BA49" s="4" t="n"/>
       <c r="BB49" s="4" t="n"/>
       <c r="BC49" s="4" t="n"/>
-      <c r="BD49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BE49" s="4" t="n"/>
+      <c r="BD49" s="4" t="n"/>
+      <c r="BE49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BF49" s="4" t="n"/>
       <c r="BG49" s="4" t="n"/>
       <c r="BH49" s="4" t="n"/>
-      <c r="BI49" s="4" t="inlineStr">
+      <c r="BI49" s="4" t="n"/>
+      <c r="BJ49" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -52671,15 +52876,15 @@
       <c r="Z50" s="4" t="n"/>
       <c r="AA50" s="4" t="n"/>
       <c r="AB50" s="4" t="n"/>
-      <c r="AC50" s="4" t="n"/>
+      <c r="AC50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD50" s="4" t="n"/>
       <c r="AE50" s="4" t="n"/>
       <c r="AF50" s="4" t="n"/>
-      <c r="AG50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG50" s="4" t="n"/>
       <c r="AH50" s="4" t="n"/>
       <c r="AI50" s="4" t="inlineStr">
         <is>
@@ -52701,37 +52906,38 @@
         </is>
       </c>
       <c r="AT50" s="4" t="n"/>
-      <c r="AU50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AV50" s="4" t="n"/>
-      <c r="AW50" s="4" t="n"/>
+      <c r="AU50" s="4" t="n"/>
+      <c r="AV50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AW50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AX50" s="4" t="n"/>
-      <c r="AY50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY50" s="4" t="n"/>
       <c r="AZ50" s="4" t="n"/>
       <c r="BA50" s="4" t="n"/>
-      <c r="BB50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BC50" s="4" t="n"/>
+      <c r="BB50" s="4" t="n"/>
+      <c r="BC50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BD50" s="4" t="n"/>
       <c r="BE50" s="4" t="n"/>
-      <c r="BF50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BG50" s="4" t="n"/>
+      <c r="BF50" s="4" t="n"/>
+      <c r="BG50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BH50" s="4" t="n"/>
-      <c r="BI50" s="4" t="inlineStr">
+      <c r="BI50" s="4" t="n"/>
+      <c r="BJ50" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -52782,19 +52988,19 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AC51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AD51" s="4" t="n"/>
+      <c r="AC51" s="4" t="n"/>
+      <c r="AD51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE51" s="4" t="n"/>
-      <c r="AF51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AG51" s="4" t="n"/>
+      <c r="AF51" s="4" t="n"/>
+      <c r="AG51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AH51" s="4" t="n"/>
       <c r="AI51" s="4" t="inlineStr">
         <is>
@@ -52825,14 +53031,14 @@
       <c r="AS51" s="4" t="n"/>
       <c r="AT51" s="4" t="n"/>
       <c r="AU51" s="4" t="n"/>
-      <c r="AV51" s="4" t="n"/>
+      <c r="AV51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW51" s="4" t="n"/>
       <c r="AX51" s="4" t="n"/>
-      <c r="AY51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY51" s="4" t="n"/>
       <c r="AZ51" s="4" t="n"/>
       <c r="BA51" s="4" t="n"/>
       <c r="BB51" s="4" t="n"/>
@@ -52840,13 +53046,14 @@
       <c r="BD51" s="4" t="n"/>
       <c r="BE51" s="4" t="n"/>
       <c r="BF51" s="4" t="n"/>
-      <c r="BG51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH51" s="4" t="n"/>
+      <c r="BG51" s="4" t="n"/>
+      <c r="BH51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI51" s="4" t="n"/>
+      <c r="BJ51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n"/>
@@ -52857,8 +53064,16 @@
       </c>
       <c r="C52" s="4" t="n"/>
       <c r="D52" s="4" t="n"/>
-      <c r="E52" s="4" t="n"/>
-      <c r="F52" s="4" t="n"/>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -52899,14 +53114,18 @@
       <c r="X52" s="4" t="n"/>
       <c r="Y52" s="4" t="n"/>
       <c r="Z52" s="4" t="n"/>
-      <c r="AA52" s="4" t="n"/>
+      <c r="AA52" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AB52" s="4" t="n"/>
-      <c r="AC52" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AD52" s="4" t="n"/>
+      <c r="AC52" s="4" t="n"/>
+      <c r="AD52" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE52" s="4" t="n"/>
       <c r="AF52" s="4" t="n"/>
       <c r="AG52" s="4" t="n"/>
@@ -52940,14 +53159,14 @@
       <c r="AS52" s="4" t="n"/>
       <c r="AT52" s="4" t="n"/>
       <c r="AU52" s="4" t="n"/>
-      <c r="AV52" s="4" t="n"/>
+      <c r="AV52" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW52" s="4" t="n"/>
       <c r="AX52" s="4" t="n"/>
-      <c r="AY52" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY52" s="4" t="n"/>
       <c r="AZ52" s="4" t="n"/>
       <c r="BA52" s="4" t="n"/>
       <c r="BB52" s="4" t="n"/>
@@ -52958,6 +53177,7 @@
       <c r="BG52" s="4" t="n"/>
       <c r="BH52" s="4" t="n"/>
       <c r="BI52" s="4" t="n"/>
+      <c r="BJ52" s="4" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -53016,12 +53236,12 @@
       <c r="Z53" s="4" t="n"/>
       <c r="AA53" s="4" t="n"/>
       <c r="AB53" s="4" t="n"/>
-      <c r="AC53" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AD53" s="4" t="n"/>
+      <c r="AC53" s="4" t="n"/>
+      <c r="AD53" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE53" s="4" t="n"/>
       <c r="AF53" s="4" t="n"/>
       <c r="AG53" s="4" t="n"/>
@@ -53047,14 +53267,14 @@
       <c r="AS53" s="4" t="n"/>
       <c r="AT53" s="4" t="n"/>
       <c r="AU53" s="4" t="n"/>
-      <c r="AV53" s="4" t="n"/>
+      <c r="AV53" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW53" s="4" t="n"/>
       <c r="AX53" s="4" t="n"/>
-      <c r="AY53" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY53" s="4" t="n"/>
       <c r="AZ53" s="4" t="n"/>
       <c r="BA53" s="4" t="n"/>
       <c r="BB53" s="4" t="n"/>
@@ -53065,6 +53285,7 @@
       <c r="BG53" s="4" t="n"/>
       <c r="BH53" s="4" t="n"/>
       <c r="BI53" s="4" t="n"/>
+      <c r="BJ53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n"/>
@@ -53115,12 +53336,12 @@
       <c r="Z54" s="4" t="n"/>
       <c r="AA54" s="4" t="n"/>
       <c r="AB54" s="4" t="n"/>
-      <c r="AC54" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AD54" s="4" t="n"/>
+      <c r="AC54" s="4" t="n"/>
+      <c r="AD54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE54" s="4" t="n"/>
       <c r="AF54" s="4" t="n"/>
       <c r="AG54" s="4" t="n"/>
@@ -53150,21 +53371,21 @@
       <c r="AS54" s="4" t="n"/>
       <c r="AT54" s="4" t="n"/>
       <c r="AU54" s="4" t="n"/>
-      <c r="AV54" s="4" t="n"/>
+      <c r="AV54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW54" s="4" t="n"/>
       <c r="AX54" s="4" t="n"/>
-      <c r="AY54" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY54" s="4" t="n"/>
       <c r="AZ54" s="4" t="n"/>
-      <c r="BA54" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB54" s="4" t="n"/>
+      <c r="BA54" s="4" t="n"/>
+      <c r="BB54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC54" s="4" t="n"/>
       <c r="BD54" s="4" t="n"/>
       <c r="BE54" s="4" t="n"/>
@@ -53172,6 +53393,7 @@
       <c r="BG54" s="4" t="n"/>
       <c r="BH54" s="4" t="n"/>
       <c r="BI54" s="4" t="n"/>
+      <c r="BJ54" s="4" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n"/>
@@ -53210,15 +53432,15 @@
       <c r="Z55" s="4" t="n"/>
       <c r="AA55" s="4" t="n"/>
       <c r="AB55" s="4" t="n"/>
-      <c r="AC55" s="4" t="n"/>
+      <c r="AC55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD55" s="4" t="n"/>
       <c r="AE55" s="4" t="n"/>
       <c r="AF55" s="4" t="n"/>
-      <c r="AG55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG55" s="4" t="n"/>
       <c r="AH55" s="4" t="n"/>
       <c r="AI55" s="4" t="inlineStr">
         <is>
@@ -53244,33 +53466,34 @@
         </is>
       </c>
       <c r="AT55" s="4" t="n"/>
-      <c r="AU55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AV55" s="4" t="n"/>
-      <c r="AW55" s="4" t="n"/>
+      <c r="AU55" s="4" t="n"/>
+      <c r="AV55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AW55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AX55" s="4" t="n"/>
-      <c r="AY55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY55" s="4" t="n"/>
       <c r="AZ55" s="4" t="n"/>
       <c r="BA55" s="4" t="n"/>
-      <c r="BB55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BC55" s="4" t="n"/>
+      <c r="BB55" s="4" t="n"/>
+      <c r="BC55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BD55" s="4" t="n"/>
       <c r="BE55" s="4" t="n"/>
       <c r="BF55" s="4" t="n"/>
       <c r="BG55" s="4" t="n"/>
       <c r="BH55" s="4" t="n"/>
-      <c r="BI55" s="4" t="inlineStr">
+      <c r="BI55" s="4" t="n"/>
+      <c r="BJ55" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -53325,12 +53548,12 @@
       <c r="Z56" s="4" t="n"/>
       <c r="AA56" s="4" t="n"/>
       <c r="AB56" s="4" t="n"/>
-      <c r="AC56" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AD56" s="4" t="n"/>
+      <c r="AC56" s="4" t="n"/>
+      <c r="AD56" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE56" s="4" t="n"/>
       <c r="AF56" s="4" t="n"/>
       <c r="AG56" s="4" t="n"/>
@@ -53356,14 +53579,14 @@
       <c r="AS56" s="4" t="n"/>
       <c r="AT56" s="4" t="n"/>
       <c r="AU56" s="4" t="n"/>
-      <c r="AV56" s="4" t="n"/>
+      <c r="AV56" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW56" s="4" t="n"/>
       <c r="AX56" s="4" t="n"/>
-      <c r="AY56" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY56" s="4" t="n"/>
       <c r="AZ56" s="4" t="n"/>
       <c r="BA56" s="4" t="n"/>
       <c r="BB56" s="4" t="n"/>
@@ -53374,6 +53597,7 @@
       <c r="BG56" s="4" t="n"/>
       <c r="BH56" s="4" t="n"/>
       <c r="BI56" s="4" t="n"/>
+      <c r="BJ56" s="4" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -53444,12 +53668,12 @@
       <c r="Z57" s="4" t="n"/>
       <c r="AA57" s="4" t="n"/>
       <c r="AB57" s="4" t="n"/>
-      <c r="AC57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AD57" s="4" t="n"/>
+      <c r="AC57" s="4" t="n"/>
+      <c r="AD57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE57" s="4" t="n"/>
       <c r="AF57" s="4" t="n"/>
       <c r="AG57" s="4" t="n"/>
@@ -53475,25 +53699,25 @@
       <c r="AS57" s="4" t="n"/>
       <c r="AT57" s="4" t="n"/>
       <c r="AU57" s="4" t="n"/>
-      <c r="AV57" s="4" t="n"/>
+      <c r="AV57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW57" s="4" t="n"/>
       <c r="AX57" s="4" t="n"/>
-      <c r="AY57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AZ57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY57" s="4" t="n"/>
+      <c r="AZ57" s="4" t="n"/>
       <c r="BA57" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BB57" s="4" t="n"/>
+      <c r="BB57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC57" s="4" t="n"/>
       <c r="BD57" s="4" t="n"/>
       <c r="BE57" s="4" t="n"/>
@@ -53501,6 +53725,7 @@
       <c r="BG57" s="4" t="n"/>
       <c r="BH57" s="4" t="n"/>
       <c r="BI57" s="4" t="n"/>
+      <c r="BJ57" s="4" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="n"/>
@@ -53540,7 +53765,11 @@
       <c r="S58" s="4" t="n"/>
       <c r="T58" s="4" t="n"/>
       <c r="U58" s="4" t="n"/>
-      <c r="V58" s="4" t="n"/>
+      <c r="V58" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="W58" s="4" t="n"/>
       <c r="X58" s="4" t="n"/>
       <c r="Y58" s="4" t="n"/>
@@ -53551,12 +53780,12 @@
         </is>
       </c>
       <c r="AB58" s="4" t="n"/>
-      <c r="AC58" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AD58" s="4" t="n"/>
+      <c r="AC58" s="4" t="n"/>
+      <c r="AD58" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE58" s="4" t="n"/>
       <c r="AF58" s="4" t="n"/>
       <c r="AG58" s="4" t="n"/>
@@ -53582,14 +53811,14 @@
       <c r="AS58" s="4" t="n"/>
       <c r="AT58" s="4" t="n"/>
       <c r="AU58" s="4" t="n"/>
-      <c r="AV58" s="4" t="n"/>
+      <c r="AV58" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW58" s="4" t="n"/>
       <c r="AX58" s="4" t="n"/>
-      <c r="AY58" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY58" s="4" t="n"/>
       <c r="AZ58" s="4" t="n"/>
       <c r="BA58" s="4" t="n"/>
       <c r="BB58" s="4" t="n"/>
@@ -53600,6 +53829,7 @@
       <c r="BG58" s="4" t="n"/>
       <c r="BH58" s="4" t="n"/>
       <c r="BI58" s="4" t="n"/>
+      <c r="BJ58" s="4" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n"/>
@@ -53646,15 +53876,15 @@
       <c r="Z59" s="4" t="n"/>
       <c r="AA59" s="4" t="n"/>
       <c r="AB59" s="4" t="n"/>
-      <c r="AC59" s="4" t="n"/>
+      <c r="AC59" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD59" s="4" t="n"/>
       <c r="AE59" s="4" t="n"/>
       <c r="AF59" s="4" t="n"/>
-      <c r="AG59" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG59" s="4" t="n"/>
       <c r="AH59" s="4" t="n"/>
       <c r="AI59" s="4" t="inlineStr">
         <is>
@@ -53685,14 +53915,14 @@
       </c>
       <c r="AT59" s="4" t="n"/>
       <c r="AU59" s="4" t="n"/>
-      <c r="AV59" s="4" t="n"/>
+      <c r="AV59" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW59" s="4" t="n"/>
       <c r="AX59" s="4" t="n"/>
-      <c r="AY59" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY59" s="4" t="n"/>
       <c r="AZ59" s="4" t="n"/>
       <c r="BA59" s="4" t="n"/>
       <c r="BB59" s="4" t="n"/>
@@ -53703,6 +53933,7 @@
       <c r="BG59" s="4" t="n"/>
       <c r="BH59" s="4" t="n"/>
       <c r="BI59" s="4" t="n"/>
+      <c r="BJ59" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n"/>
@@ -53769,12 +54000,12 @@
       <c r="Z60" s="4" t="n"/>
       <c r="AA60" s="4" t="n"/>
       <c r="AB60" s="4" t="n"/>
-      <c r="AC60" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AD60" s="4" t="n"/>
+      <c r="AC60" s="4" t="n"/>
+      <c r="AD60" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE60" s="4" t="n"/>
       <c r="AF60" s="4" t="n"/>
       <c r="AG60" s="4" t="n"/>
@@ -53800,14 +54031,14 @@
       <c r="AS60" s="4" t="n"/>
       <c r="AT60" s="4" t="n"/>
       <c r="AU60" s="4" t="n"/>
-      <c r="AV60" s="4" t="n"/>
+      <c r="AV60" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW60" s="4" t="n"/>
       <c r="AX60" s="4" t="n"/>
-      <c r="AY60" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY60" s="4" t="n"/>
       <c r="AZ60" s="4" t="n"/>
       <c r="BA60" s="4" t="n"/>
       <c r="BB60" s="4" t="n"/>
@@ -53818,6 +54049,7 @@
       <c r="BG60" s="4" t="n"/>
       <c r="BH60" s="4" t="n"/>
       <c r="BI60" s="4" t="n"/>
+      <c r="BJ60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -53868,14 +54100,14 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AC61" s="4" t="n"/>
+      <c r="AC61" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD61" s="4" t="n"/>
       <c r="AE61" s="4" t="n"/>
-      <c r="AF61" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AF61" s="4" t="n"/>
       <c r="AG61" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -53914,23 +54146,23 @@
         </is>
       </c>
       <c r="AT61" s="4" t="n"/>
-      <c r="AU61" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU61" s="4" t="n"/>
       <c r="AV61" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AW61" s="4" t="n"/>
-      <c r="AX61" s="4" t="n"/>
-      <c r="AY61" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AW61" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AX61" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AY61" s="4" t="n"/>
       <c r="AZ61" s="4" t="n"/>
       <c r="BA61" s="4" t="n"/>
       <c r="BB61" s="4" t="n"/>
@@ -53941,6 +54173,7 @@
       <c r="BG61" s="4" t="n"/>
       <c r="BH61" s="4" t="n"/>
       <c r="BI61" s="4" t="n"/>
+      <c r="BJ61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="n"/>
@@ -54003,15 +54236,15 @@
         </is>
       </c>
       <c r="AB62" s="4" t="n"/>
-      <c r="AC62" s="4" t="n"/>
+      <c r="AC62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD62" s="4" t="n"/>
       <c r="AE62" s="4" t="n"/>
       <c r="AF62" s="4" t="n"/>
-      <c r="AG62" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG62" s="4" t="n"/>
       <c r="AH62" s="4" t="n"/>
       <c r="AI62" s="4" t="inlineStr">
         <is>
@@ -54034,14 +54267,14 @@
       </c>
       <c r="AT62" s="4" t="n"/>
       <c r="AU62" s="4" t="n"/>
-      <c r="AV62" s="4" t="n"/>
+      <c r="AV62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW62" s="4" t="n"/>
       <c r="AX62" s="4" t="n"/>
-      <c r="AY62" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY62" s="4" t="n"/>
       <c r="AZ62" s="4" t="n"/>
       <c r="BA62" s="4" t="n"/>
       <c r="BB62" s="4" t="n"/>
@@ -54051,7 +54284,8 @@
       <c r="BF62" s="4" t="n"/>
       <c r="BG62" s="4" t="n"/>
       <c r="BH62" s="4" t="n"/>
-      <c r="BI62" s="4" t="inlineStr">
+      <c r="BI62" s="4" t="n"/>
+      <c r="BJ62" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -54127,14 +54361,14 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AD63" s="4" t="n"/>
+      <c r="AD63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE63" s="4" t="n"/>
       <c r="AF63" s="4" t="n"/>
-      <c r="AG63" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG63" s="4" t="n"/>
       <c r="AH63" s="4" t="n"/>
       <c r="AI63" s="4" t="inlineStr">
         <is>
@@ -54165,14 +54399,14 @@
       <c r="AS63" s="4" t="n"/>
       <c r="AT63" s="4" t="n"/>
       <c r="AU63" s="4" t="n"/>
-      <c r="AV63" s="4" t="n"/>
+      <c r="AV63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW63" s="4" t="n"/>
       <c r="AX63" s="4" t="n"/>
-      <c r="AY63" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY63" s="4" t="n"/>
       <c r="AZ63" s="4" t="n"/>
       <c r="BA63" s="4" t="n"/>
       <c r="BB63" s="4" t="n"/>
@@ -54183,6 +54417,7 @@
       <c r="BG63" s="4" t="n"/>
       <c r="BH63" s="4" t="n"/>
       <c r="BI63" s="4" t="n"/>
+      <c r="BJ63" s="4" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n"/>
@@ -54228,11 +54463,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="T64" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T64" s="4" t="n"/>
       <c r="U64" s="4" t="n"/>
       <c r="V64" s="4" t="n"/>
       <c r="W64" s="4" t="n"/>
@@ -54250,7 +54481,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AD64" s="4" t="n"/>
+      <c r="AD64" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE64" s="4" t="n"/>
       <c r="AF64" s="4" t="n"/>
       <c r="AG64" s="4" t="n"/>
@@ -54276,14 +54511,14 @@
       <c r="AS64" s="4" t="n"/>
       <c r="AT64" s="4" t="n"/>
       <c r="AU64" s="4" t="n"/>
-      <c r="AV64" s="4" t="n"/>
+      <c r="AV64" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW64" s="4" t="n"/>
       <c r="AX64" s="4" t="n"/>
-      <c r="AY64" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY64" s="4" t="n"/>
       <c r="AZ64" s="4" t="n"/>
       <c r="BA64" s="4" t="n"/>
       <c r="BB64" s="4" t="n"/>
@@ -54294,6 +54529,7 @@
       <c r="BG64" s="4" t="n"/>
       <c r="BH64" s="4" t="n"/>
       <c r="BI64" s="4" t="n"/>
+      <c r="BJ64" s="4" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -54348,12 +54584,12 @@
         </is>
       </c>
       <c r="AB65" s="4" t="n"/>
-      <c r="AC65" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AD65" s="4" t="n"/>
+      <c r="AC65" s="4" t="n"/>
+      <c r="AD65" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE65" s="4" t="n"/>
       <c r="AF65" s="4" t="n"/>
       <c r="AG65" s="4" t="n"/>
@@ -54375,14 +54611,14 @@
       <c r="AS65" s="4" t="n"/>
       <c r="AT65" s="4" t="n"/>
       <c r="AU65" s="4" t="n"/>
-      <c r="AV65" s="4" t="n"/>
+      <c r="AV65" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW65" s="4" t="n"/>
       <c r="AX65" s="4" t="n"/>
-      <c r="AY65" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY65" s="4" t="n"/>
       <c r="AZ65" s="4" t="n"/>
       <c r="BA65" s="4" t="n"/>
       <c r="BB65" s="4" t="n"/>
@@ -54393,6 +54629,7 @@
       <c r="BG65" s="4" t="n"/>
       <c r="BH65" s="4" t="n"/>
       <c r="BI65" s="4" t="n"/>
+      <c r="BJ65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="n"/>
@@ -54447,12 +54684,12 @@
       <c r="Z66" s="4" t="n"/>
       <c r="AA66" s="4" t="n"/>
       <c r="AB66" s="4" t="n"/>
-      <c r="AC66" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AD66" s="4" t="n"/>
+      <c r="AC66" s="4" t="n"/>
+      <c r="AD66" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE66" s="4" t="n"/>
       <c r="AF66" s="4" t="n"/>
       <c r="AG66" s="4" t="n"/>
@@ -54478,14 +54715,14 @@
       <c r="AS66" s="4" t="n"/>
       <c r="AT66" s="4" t="n"/>
       <c r="AU66" s="4" t="n"/>
-      <c r="AV66" s="4" t="n"/>
+      <c r="AV66" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW66" s="4" t="n"/>
       <c r="AX66" s="4" t="n"/>
-      <c r="AY66" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY66" s="4" t="n"/>
       <c r="AZ66" s="4" t="n"/>
       <c r="BA66" s="4" t="n"/>
       <c r="BB66" s="4" t="n"/>
@@ -54496,6 +54733,7 @@
       <c r="BG66" s="4" t="n"/>
       <c r="BH66" s="4" t="n"/>
       <c r="BI66" s="4" t="n"/>
+      <c r="BJ66" s="4" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n"/>
@@ -54553,12 +54791,12 @@
       <c r="AC67" s="4" t="n"/>
       <c r="AD67" s="4" t="n"/>
       <c r="AE67" s="4" t="n"/>
-      <c r="AF67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AG67" s="4" t="n"/>
+      <c r="AF67" s="4" t="n"/>
+      <c r="AG67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AH67" s="4" t="n"/>
       <c r="AI67" s="4" t="inlineStr">
         <is>
@@ -54593,36 +54831,37 @@
       <c r="AS67" s="4" t="n"/>
       <c r="AT67" s="4" t="n"/>
       <c r="AU67" s="4" t="n"/>
-      <c r="AV67" s="4" t="n"/>
+      <c r="AV67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW67" s="4" t="n"/>
-      <c r="AX67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AY67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AZ67" s="4" t="n"/>
+      <c r="AX67" s="4" t="n"/>
+      <c r="AY67" s="4" t="n"/>
+      <c r="AZ67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BA67" s="4" t="n"/>
-      <c r="BB67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BB67" s="4" t="n"/>
       <c r="BC67" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BD67" s="4" t="n"/>
+      <c r="BD67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE67" s="4" t="n"/>
       <c r="BF67" s="4" t="n"/>
       <c r="BG67" s="4" t="n"/>
       <c r="BH67" s="4" t="n"/>
       <c r="BI67" s="4" t="n"/>
+      <c r="BJ67" s="4" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n"/>
@@ -54673,12 +54912,12 @@
         </is>
       </c>
       <c r="AB68" s="4" t="n"/>
-      <c r="AC68" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AD68" s="4" t="n"/>
+      <c r="AC68" s="4" t="n"/>
+      <c r="AD68" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE68" s="4" t="n"/>
       <c r="AF68" s="4" t="n"/>
       <c r="AG68" s="4" t="n"/>
@@ -54700,14 +54939,14 @@
       <c r="AS68" s="4" t="n"/>
       <c r="AT68" s="4" t="n"/>
       <c r="AU68" s="4" t="n"/>
-      <c r="AV68" s="4" t="n"/>
+      <c r="AV68" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW68" s="4" t="n"/>
       <c r="AX68" s="4" t="n"/>
-      <c r="AY68" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY68" s="4" t="n"/>
       <c r="AZ68" s="4" t="n"/>
       <c r="BA68" s="4" t="n"/>
       <c r="BB68" s="4" t="n"/>
@@ -54718,6 +54957,7 @@
       <c r="BG68" s="4" t="n"/>
       <c r="BH68" s="4" t="n"/>
       <c r="BI68" s="4" t="n"/>
+      <c r="BJ68" s="4" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -54803,14 +55043,14 @@
         </is>
       </c>
       <c r="AU69" s="4" t="n"/>
-      <c r="AV69" s="4" t="n"/>
+      <c r="AV69" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW69" s="4" t="n"/>
       <c r="AX69" s="4" t="n"/>
-      <c r="AY69" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY69" s="4" t="n"/>
       <c r="AZ69" s="4" t="n"/>
       <c r="BA69" s="4" t="n"/>
       <c r="BB69" s="4" t="n"/>
@@ -54821,6 +55061,7 @@
       <c r="BG69" s="4" t="n"/>
       <c r="BH69" s="4" t="n"/>
       <c r="BI69" s="4" t="n"/>
+      <c r="BJ69" s="4" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="n"/>
@@ -54866,12 +55107,12 @@
       <c r="AC70" s="4" t="n"/>
       <c r="AD70" s="4" t="n"/>
       <c r="AE70" s="4" t="n"/>
-      <c r="AF70" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AG70" s="4" t="n"/>
+      <c r="AF70" s="4" t="n"/>
+      <c r="AG70" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AH70" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -54902,28 +55143,29 @@
       <c r="AS70" s="4" t="n"/>
       <c r="AT70" s="4" t="n"/>
       <c r="AU70" s="4" t="n"/>
-      <c r="AV70" s="4" t="n"/>
+      <c r="AV70" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW70" s="4" t="n"/>
       <c r="AX70" s="4" t="n"/>
-      <c r="AY70" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY70" s="4" t="n"/>
       <c r="AZ70" s="4" t="n"/>
       <c r="BA70" s="4" t="n"/>
       <c r="BB70" s="4" t="n"/>
       <c r="BC70" s="4" t="n"/>
-      <c r="BD70" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BE70" s="4" t="n"/>
+      <c r="BD70" s="4" t="n"/>
+      <c r="BE70" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BF70" s="4" t="n"/>
       <c r="BG70" s="4" t="n"/>
       <c r="BH70" s="4" t="n"/>
       <c r="BI70" s="4" t="n"/>
+      <c r="BJ70" s="4" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n"/>
@@ -54970,12 +55212,12 @@
       <c r="Z71" s="4" t="n"/>
       <c r="AA71" s="4" t="n"/>
       <c r="AB71" s="4" t="n"/>
-      <c r="AC71" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AD71" s="4" t="n"/>
+      <c r="AC71" s="4" t="n"/>
+      <c r="AD71" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE71" s="4" t="n"/>
       <c r="AF71" s="4" t="n"/>
       <c r="AG71" s="4" t="n"/>
@@ -55001,14 +55243,14 @@
       <c r="AS71" s="4" t="n"/>
       <c r="AT71" s="4" t="n"/>
       <c r="AU71" s="4" t="n"/>
-      <c r="AV71" s="4" t="n"/>
+      <c r="AV71" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW71" s="4" t="n"/>
       <c r="AX71" s="4" t="n"/>
-      <c r="AY71" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY71" s="4" t="n"/>
       <c r="AZ71" s="4" t="n"/>
       <c r="BA71" s="4" t="n"/>
       <c r="BB71" s="4" t="n"/>
@@ -55019,6 +55261,7 @@
       <c r="BG71" s="4" t="n"/>
       <c r="BH71" s="4" t="n"/>
       <c r="BI71" s="4" t="n"/>
+      <c r="BJ71" s="4" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n"/>
@@ -55061,15 +55304,15 @@
       <c r="Z72" s="4" t="n"/>
       <c r="AA72" s="4" t="n"/>
       <c r="AB72" s="4" t="n"/>
-      <c r="AC72" s="4" t="n"/>
+      <c r="AC72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD72" s="4" t="n"/>
       <c r="AE72" s="4" t="n"/>
       <c r="AF72" s="4" t="n"/>
-      <c r="AG72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG72" s="4" t="n"/>
       <c r="AH72" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -55104,28 +55347,29 @@
         </is>
       </c>
       <c r="AU72" s="4" t="n"/>
-      <c r="AV72" s="4" t="n"/>
+      <c r="AV72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW72" s="4" t="n"/>
       <c r="AX72" s="4" t="n"/>
-      <c r="AY72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY72" s="4" t="n"/>
       <c r="AZ72" s="4" t="n"/>
       <c r="BA72" s="4" t="n"/>
-      <c r="BB72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BC72" s="4" t="n"/>
+      <c r="BB72" s="4" t="n"/>
+      <c r="BC72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BD72" s="4" t="n"/>
       <c r="BE72" s="4" t="n"/>
       <c r="BF72" s="4" t="n"/>
       <c r="BG72" s="4" t="n"/>
       <c r="BH72" s="4" t="n"/>
       <c r="BI72" s="4" t="n"/>
+      <c r="BJ72" s="4" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -55172,15 +55416,15 @@
         </is>
       </c>
       <c r="AB73" s="4" t="n"/>
-      <c r="AC73" s="4" t="n"/>
+      <c r="AC73" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD73" s="4" t="n"/>
       <c r="AE73" s="4" t="n"/>
       <c r="AF73" s="4" t="n"/>
-      <c r="AG73" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG73" s="4" t="n"/>
       <c r="AH73" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -55219,14 +55463,14 @@
       </c>
       <c r="AT73" s="4" t="n"/>
       <c r="AU73" s="4" t="n"/>
-      <c r="AV73" s="4" t="n"/>
+      <c r="AV73" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW73" s="4" t="n"/>
       <c r="AX73" s="4" t="n"/>
-      <c r="AY73" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY73" s="4" t="n"/>
       <c r="AZ73" s="4" t="n"/>
       <c r="BA73" s="4" t="n"/>
       <c r="BB73" s="4" t="n"/>
@@ -55236,7 +55480,8 @@
       <c r="BF73" s="4" t="n"/>
       <c r="BG73" s="4" t="n"/>
       <c r="BH73" s="4" t="n"/>
-      <c r="BI73" s="4" t="inlineStr">
+      <c r="BI73" s="4" t="n"/>
+      <c r="BJ73" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -55312,14 +55557,14 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AD74" s="4" t="n"/>
+      <c r="AD74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE74" s="4" t="n"/>
       <c r="AF74" s="4" t="n"/>
-      <c r="AG74" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG74" s="4" t="n"/>
       <c r="AH74" s="4" t="n"/>
       <c r="AI74" s="4" t="n"/>
       <c r="AJ74" s="4" t="n"/>
@@ -55338,14 +55583,14 @@
       <c r="AS74" s="4" t="n"/>
       <c r="AT74" s="4" t="n"/>
       <c r="AU74" s="4" t="n"/>
-      <c r="AV74" s="4" t="n"/>
+      <c r="AV74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW74" s="4" t="n"/>
       <c r="AX74" s="4" t="n"/>
-      <c r="AY74" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY74" s="4" t="n"/>
       <c r="AZ74" s="4" t="n"/>
       <c r="BA74" s="4" t="n"/>
       <c r="BB74" s="4" t="n"/>
@@ -55356,6 +55601,7 @@
       <c r="BG74" s="4" t="n"/>
       <c r="BH74" s="4" t="n"/>
       <c r="BI74" s="4" t="n"/>
+      <c r="BJ74" s="4" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n"/>
@@ -55410,19 +55656,19 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AC75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AD75" s="4" t="n"/>
+      <c r="AC75" s="4" t="n"/>
+      <c r="AD75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE75" s="4" t="n"/>
-      <c r="AF75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AG75" s="4" t="n"/>
+      <c r="AF75" s="4" t="n"/>
+      <c r="AG75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AH75" s="4" t="n"/>
       <c r="AI75" s="4" t="n"/>
       <c r="AJ75" s="4" t="n"/>
@@ -55445,19 +55691,19 @@
       <c r="AS75" s="4" t="n"/>
       <c r="AT75" s="4" t="n"/>
       <c r="AU75" s="4" t="n"/>
-      <c r="AV75" s="4" t="n"/>
+      <c r="AV75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW75" s="4" t="n"/>
-      <c r="AX75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AY75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AZ75" s="4" t="n"/>
+      <c r="AX75" s="4" t="n"/>
+      <c r="AY75" s="4" t="n"/>
+      <c r="AZ75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BA75" s="4" t="n"/>
       <c r="BB75" s="4" t="n"/>
       <c r="BC75" s="4" t="n"/>
@@ -55467,6 +55713,7 @@
       <c r="BG75" s="4" t="n"/>
       <c r="BH75" s="4" t="n"/>
       <c r="BI75" s="4" t="n"/>
+      <c r="BJ75" s="4" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="n"/>
@@ -55505,15 +55752,15 @@
       <c r="Z76" s="4" t="n"/>
       <c r="AA76" s="4" t="n"/>
       <c r="AB76" s="4" t="n"/>
-      <c r="AC76" s="4" t="n"/>
+      <c r="AC76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD76" s="4" t="n"/>
       <c r="AE76" s="4" t="n"/>
       <c r="AF76" s="4" t="n"/>
-      <c r="AG76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AG76" s="4" t="n"/>
       <c r="AH76" s="4" t="n"/>
       <c r="AI76" s="4" t="n"/>
       <c r="AJ76" s="4" t="inlineStr">
@@ -55536,36 +55783,37 @@
       </c>
       <c r="AT76" s="4" t="n"/>
       <c r="AU76" s="4" t="n"/>
-      <c r="AV76" s="4" t="n"/>
+      <c r="AV76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW76" s="4" t="n"/>
       <c r="AX76" s="4" t="n"/>
-      <c r="AY76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY76" s="4" t="n"/>
       <c r="AZ76" s="4" t="n"/>
       <c r="BA76" s="4" t="n"/>
-      <c r="BB76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BC76" s="4" t="n"/>
+      <c r="BB76" s="4" t="n"/>
+      <c r="BC76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BD76" s="4" t="n"/>
       <c r="BE76" s="4" t="n"/>
-      <c r="BF76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BG76" s="4" t="n"/>
-      <c r="BH76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BF76" s="4" t="n"/>
+      <c r="BG76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BH76" s="4" t="n"/>
       <c r="BI76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BJ76" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -55632,12 +55880,12 @@
       <c r="Z77" s="4" t="n"/>
       <c r="AA77" s="4" t="n"/>
       <c r="AB77" s="4" t="n"/>
-      <c r="AC77" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AD77" s="4" t="n"/>
+      <c r="AC77" s="4" t="n"/>
+      <c r="AD77" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE77" s="4" t="n"/>
       <c r="AF77" s="4" t="n"/>
       <c r="AG77" s="4" t="n"/>
@@ -55663,14 +55911,14 @@
       <c r="AS77" s="4" t="n"/>
       <c r="AT77" s="4" t="n"/>
       <c r="AU77" s="4" t="n"/>
-      <c r="AV77" s="4" t="n"/>
+      <c r="AV77" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW77" s="4" t="n"/>
       <c r="AX77" s="4" t="n"/>
-      <c r="AY77" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY77" s="4" t="n"/>
       <c r="AZ77" s="4" t="n"/>
       <c r="BA77" s="4" t="n"/>
       <c r="BB77" s="4" t="n"/>
@@ -55681,6 +55929,7 @@
       <c r="BG77" s="4" t="n"/>
       <c r="BH77" s="4" t="n"/>
       <c r="BI77" s="4" t="n"/>
+      <c r="BJ77" s="4" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="n"/>
@@ -55735,12 +55984,12 @@
       <c r="Z78" s="4" t="n"/>
       <c r="AA78" s="4" t="n"/>
       <c r="AB78" s="4" t="n"/>
-      <c r="AC78" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AD78" s="4" t="n"/>
+      <c r="AC78" s="4" t="n"/>
+      <c r="AD78" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE78" s="4" t="n"/>
       <c r="AF78" s="4" t="n"/>
       <c r="AG78" s="4" t="n"/>
@@ -55770,14 +56019,14 @@
       <c r="AS78" s="4" t="n"/>
       <c r="AT78" s="4" t="n"/>
       <c r="AU78" s="4" t="n"/>
-      <c r="AV78" s="4" t="n"/>
+      <c r="AV78" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW78" s="4" t="n"/>
       <c r="AX78" s="4" t="n"/>
-      <c r="AY78" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY78" s="4" t="n"/>
       <c r="AZ78" s="4" t="n"/>
       <c r="BA78" s="4" t="n"/>
       <c r="BB78" s="4" t="n"/>
@@ -55788,6 +56037,7 @@
       <c r="BG78" s="4" t="n"/>
       <c r="BH78" s="4" t="n"/>
       <c r="BI78" s="4" t="n"/>
+      <c r="BJ78" s="4" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n"/>
@@ -55846,12 +56096,12 @@
       </c>
       <c r="AA79" s="4" t="n"/>
       <c r="AB79" s="4" t="n"/>
-      <c r="AC79" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AD79" s="4" t="n"/>
+      <c r="AC79" s="4" t="n"/>
+      <c r="AD79" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE79" s="4" t="n"/>
       <c r="AF79" s="4" t="n"/>
       <c r="AG79" s="4" t="n"/>
@@ -55881,14 +56131,14 @@
       <c r="AS79" s="4" t="n"/>
       <c r="AT79" s="4" t="n"/>
       <c r="AU79" s="4" t="n"/>
-      <c r="AV79" s="4" t="n"/>
+      <c r="AV79" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW79" s="4" t="n"/>
       <c r="AX79" s="4" t="n"/>
-      <c r="AY79" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY79" s="4" t="n"/>
       <c r="AZ79" s="4" t="n"/>
       <c r="BA79" s="4" t="n"/>
       <c r="BB79" s="4" t="n"/>
@@ -55899,6 +56149,7 @@
       <c r="BG79" s="4" t="n"/>
       <c r="BH79" s="4" t="n"/>
       <c r="BI79" s="4" t="n"/>
+      <c r="BJ79" s="4" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="n"/>
@@ -55949,12 +56200,12 @@
       <c r="Z80" s="4" t="n"/>
       <c r="AA80" s="4" t="n"/>
       <c r="AB80" s="4" t="n"/>
-      <c r="AC80" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AD80" s="4" t="n"/>
+      <c r="AC80" s="4" t="n"/>
+      <c r="AD80" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AE80" s="4" t="n"/>
       <c r="AF80" s="4" t="n"/>
       <c r="AG80" s="4" t="n"/>
@@ -55980,21 +56231,21 @@
       <c r="AS80" s="4" t="n"/>
       <c r="AT80" s="4" t="n"/>
       <c r="AU80" s="4" t="n"/>
-      <c r="AV80" s="4" t="n"/>
+      <c r="AV80" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW80" s="4" t="n"/>
       <c r="AX80" s="4" t="n"/>
-      <c r="AY80" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY80" s="4" t="n"/>
       <c r="AZ80" s="4" t="n"/>
-      <c r="BA80" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BB80" s="4" t="n"/>
+      <c r="BA80" s="4" t="n"/>
+      <c r="BB80" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC80" s="4" t="n"/>
       <c r="BD80" s="4" t="n"/>
       <c r="BE80" s="4" t="n"/>
@@ -56002,6 +56253,7 @@
       <c r="BG80" s="4" t="n"/>
       <c r="BH80" s="4" t="n"/>
       <c r="BI80" s="4" t="n"/>
+      <c r="BJ80" s="4" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
@@ -56075,14 +56327,14 @@
       <c r="AS81" s="4" t="n"/>
       <c r="AT81" s="4" t="n"/>
       <c r="AU81" s="4" t="n"/>
-      <c r="AV81" s="4" t="n"/>
+      <c r="AV81" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW81" s="4" t="n"/>
       <c r="AX81" s="4" t="n"/>
-      <c r="AY81" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY81" s="4" t="n"/>
       <c r="AZ81" s="4" t="n"/>
       <c r="BA81" s="4" t="n"/>
       <c r="BB81" s="4" t="n"/>
@@ -56093,6 +56345,7 @@
       <c r="BG81" s="4" t="n"/>
       <c r="BH81" s="4" t="n"/>
       <c r="BI81" s="4" t="n"/>
+      <c r="BJ81" s="4" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="n"/>
@@ -56166,14 +56419,14 @@
       <c r="AS82" s="4" t="n"/>
       <c r="AT82" s="4" t="n"/>
       <c r="AU82" s="4" t="n"/>
-      <c r="AV82" s="4" t="n"/>
+      <c r="AV82" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW82" s="4" t="n"/>
       <c r="AX82" s="4" t="n"/>
-      <c r="AY82" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY82" s="4" t="n"/>
       <c r="AZ82" s="4" t="n"/>
       <c r="BA82" s="4" t="n"/>
       <c r="BB82" s="4" t="n"/>
@@ -56184,6 +56437,7 @@
       <c r="BG82" s="4" t="n"/>
       <c r="BH82" s="4" t="n"/>
       <c r="BI82" s="4" t="n"/>
+      <c r="BJ82" s="4" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n"/>
@@ -56223,7 +56477,11 @@
       <c r="S83" s="4" t="n"/>
       <c r="T83" s="4" t="n"/>
       <c r="U83" s="4" t="n"/>
-      <c r="V83" s="4" t="n"/>
+      <c r="V83" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="W83" s="4" t="n"/>
       <c r="X83" s="4" t="n"/>
       <c r="Y83" s="4" t="n"/>
@@ -56249,14 +56507,14 @@
       <c r="AS83" s="4" t="n"/>
       <c r="AT83" s="4" t="n"/>
       <c r="AU83" s="4" t="n"/>
-      <c r="AV83" s="4" t="n"/>
+      <c r="AV83" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW83" s="4" t="n"/>
       <c r="AX83" s="4" t="n"/>
-      <c r="AY83" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY83" s="4" t="n"/>
       <c r="AZ83" s="4" t="n"/>
       <c r="BA83" s="4" t="n"/>
       <c r="BB83" s="4" t="n"/>
@@ -56267,6 +56525,7 @@
       <c r="BG83" s="4" t="n"/>
       <c r="BH83" s="4" t="n"/>
       <c r="BI83" s="4" t="n"/>
+      <c r="BJ83" s="4" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="n"/>
@@ -56326,12 +56585,12 @@
       <c r="AA84" s="4" t="n"/>
       <c r="AB84" s="4" t="n"/>
       <c r="AC84" s="4" t="n"/>
-      <c r="AD84" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AE84" s="4" t="n"/>
+      <c r="AD84" s="4" t="n"/>
+      <c r="AE84" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AF84" s="4" t="n"/>
       <c r="AG84" s="4" t="n"/>
       <c r="AH84" s="4" t="n"/>
@@ -56348,14 +56607,14 @@
       <c r="AS84" s="4" t="n"/>
       <c r="AT84" s="4" t="n"/>
       <c r="AU84" s="4" t="n"/>
-      <c r="AV84" s="4" t="n"/>
+      <c r="AV84" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW84" s="4" t="n"/>
       <c r="AX84" s="4" t="n"/>
-      <c r="AY84" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY84" s="4" t="n"/>
       <c r="AZ84" s="4" t="n"/>
       <c r="BA84" s="4" t="n"/>
       <c r="BB84" s="4" t="n"/>
@@ -56366,9 +56625,10 @@
       <c r="BG84" s="4" t="n"/>
       <c r="BH84" s="4" t="n"/>
       <c r="BI84" s="4" t="n"/>
+      <c r="BJ84" s="4" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BI84"/>
+  <autoFilter ref="A1:BJ84"/>
   <mergeCells count="21">
     <mergeCell ref="A61:A64"/>
     <mergeCell ref="A69:A72"/>
@@ -56461,12 +56721,12 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>万达</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>21c</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>万达</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -56525,12 +56785,12 @@
         </is>
       </c>
       <c r="G2" s="4" t="n"/>
-      <c r="H2" s="4" t="n"/>
-      <c r="I2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="n"/>
       <c r="J2" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -56669,12 +56929,12 @@
         </is>
       </c>
       <c r="G6" s="4" t="n"/>
-      <c r="H6" s="4" t="n"/>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="n"/>
       <c r="J6" s="4" t="n"/>
       <c r="K6" s="4" t="inlineStr">
         <is>
@@ -56775,12 +57035,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="n"/>
+      <c r="H9" s="4" t="n"/>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -56905,12 +57165,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="n"/>
+      <c r="H12" s="4" t="n"/>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J12" s="4" t="n"/>
       <c r="K12" s="4" t="n"/>
       <c r="L12" s="4" t="n"/>
@@ -56977,12 +57237,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="n"/>
+      <c r="H14" s="4" t="n"/>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J14" s="4" t="n"/>
       <c r="K14" s="4" t="n"/>
       <c r="L14" s="4" t="n"/>
@@ -57011,12 +57271,12 @@
         </is>
       </c>
       <c r="G15" s="4" t="n"/>
-      <c r="H15" s="4" t="n"/>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="n"/>
       <c r="J15" s="4" t="n"/>
       <c r="K15" s="4" t="n"/>
       <c r="L15" s="4" t="n"/>
@@ -57075,12 +57335,12 @@
         </is>
       </c>
       <c r="G17" s="4" t="n"/>
-      <c r="H17" s="4" t="n"/>
-      <c r="I17" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="n"/>
       <c r="J17" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -57125,12 +57385,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I18" s="4" t="n"/>
+      <c r="H18" s="4" t="n"/>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J18" s="4" t="n"/>
       <c r="K18" s="4" t="n"/>
       <c r="L18" s="4" t="n"/>
@@ -57197,12 +57457,12 @@
         </is>
       </c>
       <c r="G20" s="4" t="n"/>
-      <c r="H20" s="4" t="n"/>
-      <c r="I20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="n"/>
       <c r="J20" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -57333,12 +57593,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I24" s="4" t="n"/>
+      <c r="H24" s="4" t="n"/>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -57371,12 +57631,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I25" s="4" t="n"/>
+      <c r="H25" s="4" t="n"/>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J25" s="4" t="n"/>
       <c r="K25" s="4" t="n"/>
       <c r="L25" s="4" t="n"/>
@@ -57481,12 +57741,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H28" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I28" s="4" t="n"/>
+      <c r="H28" s="4" t="n"/>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J28" s="4" t="n"/>
       <c r="K28" s="4" t="n"/>
       <c r="L28" s="4" t="n"/>
@@ -57545,12 +57805,12 @@
         </is>
       </c>
       <c r="G30" s="4" t="n"/>
-      <c r="H30" s="4" t="n"/>
-      <c r="I30" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="n"/>
       <c r="J30" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -57659,12 +57919,12 @@
         </is>
       </c>
       <c r="G33" s="4" t="n"/>
-      <c r="H33" s="4" t="n"/>
-      <c r="I33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="n"/>
       <c r="J33" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -57727,12 +57987,12 @@
         </is>
       </c>
       <c r="G35" s="4" t="n"/>
-      <c r="H35" s="4" t="n"/>
-      <c r="I35" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="n"/>
       <c r="J35" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -57845,12 +58105,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H38" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I38" s="4" t="n"/>
+      <c r="H38" s="4" t="n"/>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -57883,12 +58143,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I39" s="4" t="n"/>
+      <c r="H39" s="4" t="n"/>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -57989,12 +58249,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I42" s="4" t="n"/>
+      <c r="H42" s="4" t="n"/>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -58053,12 +58313,12 @@
         </is>
       </c>
       <c r="G44" s="4" t="n"/>
-      <c r="H44" s="4" t="n"/>
-      <c r="I44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I44" s="4" t="n"/>
       <c r="J44" s="4" t="n"/>
       <c r="K44" s="4" t="inlineStr">
         <is>
@@ -58227,12 +58487,12 @@
         </is>
       </c>
       <c r="G49" s="4" t="n"/>
-      <c r="H49" s="4" t="n"/>
-      <c r="I49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="n"/>
       <c r="J49" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -58265,12 +58525,12 @@
         </is>
       </c>
       <c r="G50" s="4" t="n"/>
-      <c r="H50" s="4" t="n"/>
-      <c r="I50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="n"/>
       <c r="J50" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -58307,12 +58567,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I51" s="4" t="n"/>
+      <c r="H51" s="4" t="n"/>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -58427,12 +58687,12 @@
         </is>
       </c>
       <c r="G55" s="4" t="n"/>
-      <c r="H55" s="4" t="n"/>
-      <c r="I55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="n"/>
       <c r="J55" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -58547,12 +58807,12 @@
         </is>
       </c>
       <c r="G59" s="4" t="n"/>
-      <c r="H59" s="4" t="n"/>
-      <c r="I59" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="n"/>
       <c r="J59" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -58673,12 +58933,12 @@
         </is>
       </c>
       <c r="G62" s="4" t="n"/>
-      <c r="H62" s="4" t="n"/>
-      <c r="I62" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I62" s="4" t="n"/>
       <c r="J62" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -58715,12 +58975,12 @@
         </is>
       </c>
       <c r="G63" s="4" t="n"/>
-      <c r="H63" s="4" t="n"/>
-      <c r="I63" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I63" s="4" t="n"/>
       <c r="J63" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -58835,12 +59095,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I67" s="4" t="n"/>
+      <c r="H67" s="4" t="n"/>
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J67" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -58949,12 +59209,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H70" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I70" s="4" t="n"/>
+      <c r="H70" s="4" t="n"/>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -59017,12 +59277,12 @@
         </is>
       </c>
       <c r="G72" s="4" t="n"/>
-      <c r="H72" s="4" t="n"/>
-      <c r="I72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I72" s="4" t="n"/>
       <c r="J72" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -59105,12 +59365,12 @@
         </is>
       </c>
       <c r="G74" s="4" t="n"/>
-      <c r="H74" s="4" t="n"/>
-      <c r="I74" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I74" s="4" t="n"/>
       <c r="J74" s="4" t="n"/>
       <c r="K74" s="4" t="n"/>
       <c r="L74" s="4" t="n"/>
@@ -59139,12 +59399,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I75" s="4" t="n"/>
+      <c r="H75" s="4" t="n"/>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J75" s="4" t="n"/>
       <c r="K75" s="4" t="inlineStr">
         <is>
@@ -59177,12 +59437,12 @@
         </is>
       </c>
       <c r="G76" s="4" t="n"/>
-      <c r="H76" s="4" t="n"/>
-      <c r="I76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I76" s="4" t="n"/>
       <c r="J76" s="4" t="n"/>
       <c r="K76" s="4" t="n"/>
       <c r="L76" s="4" t="n"/>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -29,10 +29,10 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'四区_高手'!$A$1:$BJ$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'四区_普通'!$A$1:$BJ$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'四区_自动'!$A$1:$P$84</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'五区_理论_特殊跑法'!$A$1:$BG$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'五区_高手_特殊跑法'!$A$1:$BG$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'四区_理论_特殊跑法'!$A$1:$BG$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'四区_高手_特殊跑法'!$A$1:$BG$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'五区_理论_特殊跑法'!$A$1:$AO$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'五区_高手_特殊跑法'!$A$1:$R$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'四区_理论_特殊跑法'!$A$1:$U$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'四区_高手_特殊跑法'!$A$1:$G$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -7750,7 +7750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG21"/>
+  <dimension ref="A1:R21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7771,47 +7771,6 @@
     <col width="7.5" customWidth="1" min="16" max="16"/>
     <col width="7.5" customWidth="1" min="17" max="17"/>
     <col width="7.5" customWidth="1" min="18" max="18"/>
-    <col width="7.5" customWidth="1" min="19" max="19"/>
-    <col width="7.5" customWidth="1" min="20" max="20"/>
-    <col width="7.5" customWidth="1" min="21" max="21"/>
-    <col width="7.5" customWidth="1" min="22" max="22"/>
-    <col width="7.5" customWidth="1" min="23" max="23"/>
-    <col width="7.5" customWidth="1" min="24" max="24"/>
-    <col width="7.5" customWidth="1" min="25" max="25"/>
-    <col width="7.5" customWidth="1" min="26" max="26"/>
-    <col width="7.5" customWidth="1" min="27" max="27"/>
-    <col width="7.5" customWidth="1" min="28" max="28"/>
-    <col width="7.5" customWidth="1" min="29" max="29"/>
-    <col width="7.5" customWidth="1" min="30" max="30"/>
-    <col width="7.5" customWidth="1" min="31" max="31"/>
-    <col width="7.5" customWidth="1" min="32" max="32"/>
-    <col width="7.5" customWidth="1" min="33" max="33"/>
-    <col width="7.5" customWidth="1" min="34" max="34"/>
-    <col width="7.5" customWidth="1" min="35" max="35"/>
-    <col width="7.5" customWidth="1" min="36" max="36"/>
-    <col width="7.5" customWidth="1" min="37" max="37"/>
-    <col width="7.5" customWidth="1" min="38" max="38"/>
-    <col width="7.5" customWidth="1" min="39" max="39"/>
-    <col width="7.5" customWidth="1" min="40" max="40"/>
-    <col width="7.5" customWidth="1" min="41" max="41"/>
-    <col width="7.5" customWidth="1" min="42" max="42"/>
-    <col width="7.5" customWidth="1" min="43" max="43"/>
-    <col width="7.5" customWidth="1" min="44" max="44"/>
-    <col width="7.5" customWidth="1" min="45" max="45"/>
-    <col width="7.5" customWidth="1" min="46" max="46"/>
-    <col width="7.5" customWidth="1" min="47" max="47"/>
-    <col width="7.5" customWidth="1" min="48" max="48"/>
-    <col width="7.5" customWidth="1" min="49" max="49"/>
-    <col width="7.5" customWidth="1" min="50" max="50"/>
-    <col width="7.5" customWidth="1" min="51" max="51"/>
-    <col width="7.5" customWidth="1" min="52" max="52"/>
-    <col width="7.5" customWidth="1" min="53" max="53"/>
-    <col width="7.5" customWidth="1" min="54" max="54"/>
-    <col width="7.5" customWidth="1" min="55" max="55"/>
-    <col width="7.5" customWidth="1" min="56" max="56"/>
-    <col width="7.5" customWidth="1" min="57" max="57"/>
-    <col width="7.5" customWidth="1" min="58" max="58"/>
-    <col width="7.5" customWidth="1" min="59" max="59"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7837,277 +7796,72 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>玻璃</t>
+          <t>杰皇★6</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>杰皇★6</t>
+          <t>r兔★6</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>杰皇</t>
+          <t>f5★6</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>恶魔</t>
+          <t>c2★6</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>r兔★6</t>
+          <t>9x8★6</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>r兔</t>
+          <t>黑龙★6</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>f5r</t>
+          <t>白龙★6</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>f5★6</t>
+          <t>万达★6</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>f5</t>
+          <t>速尾★6</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>杰哥</t>
+          <t>sf90★6</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>c2★6</t>
+          <t>sgt★6</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>c2</t>
+          <t>秋王★6</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>杰弟</t>
+          <t>小牛★6</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>银电</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>21c</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>9x8★6</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>9x8</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>黑龙★6</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>黑龙</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>ssc</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>陀飞轮</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>白龙★6</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>白龙</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>fp1★6</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>fp1</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>爱音</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>万达★6</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>万达</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>速尾★6</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>速尾</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>肥龙</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>sf90★6</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>sf90</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>sgt★6</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>sgt</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>火山</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>猫头鹰</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>秋王★6</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>秋王</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>风龙</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>小牛★6</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>小牛</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
           <t>fe3★5</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>fe3</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>法拉第</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>六子</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>帕梅</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>ps龙</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>ts900</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>divo</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>att</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>650s</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>英灵殿</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>帝国</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>狼王</t>
         </is>
       </c>
     </row>
@@ -8142,47 +7896,6 @@
       <c r="P2" s="4" t="n"/>
       <c r="Q2" s="4" t="n"/>
       <c r="R2" s="4" t="n"/>
-      <c r="S2" s="4" t="n"/>
-      <c r="T2" s="4" t="n"/>
-      <c r="U2" s="4" t="n"/>
-      <c r="V2" s="4" t="n"/>
-      <c r="W2" s="4" t="n"/>
-      <c r="X2" s="4" t="n"/>
-      <c r="Y2" s="4" t="n"/>
-      <c r="Z2" s="4" t="n"/>
-      <c r="AA2" s="4" t="n"/>
-      <c r="AB2" s="4" t="n"/>
-      <c r="AC2" s="4" t="n"/>
-      <c r="AD2" s="4" t="n"/>
-      <c r="AE2" s="4" t="n"/>
-      <c r="AF2" s="4" t="n"/>
-      <c r="AG2" s="4" t="n"/>
-      <c r="AH2" s="4" t="n"/>
-      <c r="AI2" s="4" t="n"/>
-      <c r="AJ2" s="4" t="n"/>
-      <c r="AK2" s="4" t="n"/>
-      <c r="AL2" s="4" t="n"/>
-      <c r="AM2" s="4" t="n"/>
-      <c r="AN2" s="4" t="n"/>
-      <c r="AO2" s="4" t="n"/>
-      <c r="AP2" s="4" t="n"/>
-      <c r="AQ2" s="4" t="n"/>
-      <c r="AR2" s="4" t="n"/>
-      <c r="AS2" s="4" t="n"/>
-      <c r="AT2" s="4" t="n"/>
-      <c r="AU2" s="4" t="n"/>
-      <c r="AV2" s="4" t="n"/>
-      <c r="AW2" s="4" t="n"/>
-      <c r="AX2" s="4" t="n"/>
-      <c r="AY2" s="4" t="n"/>
-      <c r="AZ2" s="4" t="n"/>
-      <c r="BA2" s="4" t="n"/>
-      <c r="BB2" s="4" t="n"/>
-      <c r="BC2" s="4" t="n"/>
-      <c r="BD2" s="4" t="n"/>
-      <c r="BE2" s="4" t="n"/>
-      <c r="BF2" s="4" t="n"/>
-      <c r="BG2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="n"/>
@@ -8211,47 +7924,6 @@
       <c r="P3" s="4" t="n"/>
       <c r="Q3" s="4" t="n"/>
       <c r="R3" s="4" t="n"/>
-      <c r="S3" s="4" t="n"/>
-      <c r="T3" s="4" t="n"/>
-      <c r="U3" s="4" t="n"/>
-      <c r="V3" s="4" t="n"/>
-      <c r="W3" s="4" t="n"/>
-      <c r="X3" s="4" t="n"/>
-      <c r="Y3" s="4" t="n"/>
-      <c r="Z3" s="4" t="n"/>
-      <c r="AA3" s="4" t="n"/>
-      <c r="AB3" s="4" t="n"/>
-      <c r="AC3" s="4" t="n"/>
-      <c r="AD3" s="4" t="n"/>
-      <c r="AE3" s="4" t="n"/>
-      <c r="AF3" s="4" t="n"/>
-      <c r="AG3" s="4" t="n"/>
-      <c r="AH3" s="4" t="n"/>
-      <c r="AI3" s="4" t="n"/>
-      <c r="AJ3" s="4" t="n"/>
-      <c r="AK3" s="4" t="n"/>
-      <c r="AL3" s="4" t="n"/>
-      <c r="AM3" s="4" t="n"/>
-      <c r="AN3" s="4" t="n"/>
-      <c r="AO3" s="4" t="n"/>
-      <c r="AP3" s="4" t="n"/>
-      <c r="AQ3" s="4" t="n"/>
-      <c r="AR3" s="4" t="n"/>
-      <c r="AS3" s="4" t="n"/>
-      <c r="AT3" s="4" t="n"/>
-      <c r="AU3" s="4" t="n"/>
-      <c r="AV3" s="4" t="n"/>
-      <c r="AW3" s="4" t="n"/>
-      <c r="AX3" s="4" t="n"/>
-      <c r="AY3" s="4" t="n"/>
-      <c r="AZ3" s="4" t="n"/>
-      <c r="BA3" s="4" t="n"/>
-      <c r="BB3" s="4" t="n"/>
-      <c r="BC3" s="4" t="n"/>
-      <c r="BD3" s="4" t="n"/>
-      <c r="BE3" s="4" t="n"/>
-      <c r="BF3" s="4" t="n"/>
-      <c r="BG3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -8271,64 +7943,23 @@
       </c>
       <c r="D4" s="4" t="n"/>
       <c r="E4" s="4" t="n"/>
-      <c r="F4" s="4" t="n"/>
+      <c r="F4" s="4" t="n">
+        <v>23.7</v>
+      </c>
       <c r="G4" s="4" t="n"/>
-      <c r="H4" s="4" t="n"/>
-      <c r="I4" s="4" t="n">
-        <v>23.7</v>
-      </c>
+      <c r="H4" s="4" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="I4" s="4" t="n"/>
       <c r="J4" s="4" t="n"/>
       <c r="K4" s="4" t="n"/>
       <c r="L4" s="4" t="n"/>
       <c r="M4" s="4" t="n"/>
       <c r="N4" s="4" t="n"/>
-      <c r="O4" s="4" t="n">
-        <v>24.3</v>
-      </c>
+      <c r="O4" s="4" t="n"/>
       <c r="P4" s="4" t="n"/>
       <c r="Q4" s="4" t="n"/>
       <c r="R4" s="4" t="n"/>
-      <c r="S4" s="4" t="n"/>
-      <c r="T4" s="4" t="n"/>
-      <c r="U4" s="4" t="n"/>
-      <c r="V4" s="4" t="n"/>
-      <c r="W4" s="4" t="n"/>
-      <c r="X4" s="4" t="n"/>
-      <c r="Y4" s="4" t="n"/>
-      <c r="Z4" s="4" t="n"/>
-      <c r="AA4" s="4" t="n"/>
-      <c r="AB4" s="4" t="n"/>
-      <c r="AC4" s="4" t="n"/>
-      <c r="AD4" s="4" t="n"/>
-      <c r="AE4" s="4" t="n"/>
-      <c r="AF4" s="4" t="n"/>
-      <c r="AG4" s="4" t="n"/>
-      <c r="AH4" s="4" t="n"/>
-      <c r="AI4" s="4" t="n"/>
-      <c r="AJ4" s="4" t="n"/>
-      <c r="AK4" s="4" t="n"/>
-      <c r="AL4" s="4" t="n"/>
-      <c r="AM4" s="4" t="n"/>
-      <c r="AN4" s="4" t="n"/>
-      <c r="AO4" s="4" t="n"/>
-      <c r="AP4" s="4" t="n"/>
-      <c r="AQ4" s="4" t="n"/>
-      <c r="AR4" s="4" t="n"/>
-      <c r="AS4" s="4" t="n"/>
-      <c r="AT4" s="4" t="n"/>
-      <c r="AU4" s="4" t="n"/>
-      <c r="AV4" s="4" t="n"/>
-      <c r="AW4" s="4" t="n"/>
-      <c r="AX4" s="4" t="n"/>
-      <c r="AY4" s="4" t="n"/>
-      <c r="AZ4" s="4" t="n"/>
-      <c r="BA4" s="4" t="n"/>
-      <c r="BB4" s="4" t="n"/>
-      <c r="BC4" s="4" t="n"/>
-      <c r="BD4" s="4" t="n"/>
-      <c r="BE4" s="4" t="n"/>
-      <c r="BF4" s="4" t="n"/>
-      <c r="BG4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -8348,14 +7979,18 @@
       </c>
       <c r="D5" s="4" t="n"/>
       <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
+      <c r="F5" s="4" t="n">
+        <v>22.2</v>
+      </c>
       <c r="G5" s="4" t="n"/>
       <c r="H5" s="4" t="n"/>
       <c r="I5" s="4" t="n">
-        <v>22.2</v>
+        <v>22.9</v>
       </c>
       <c r="J5" s="4" t="n"/>
-      <c r="K5" s="4" t="n"/>
+      <c r="K5" s="4" t="n">
+        <v>22.5</v>
+      </c>
       <c r="L5" s="4" t="n"/>
       <c r="M5" s="4" t="n"/>
       <c r="N5" s="4" t="n"/>
@@ -8363,51 +7998,6 @@
       <c r="P5" s="4" t="n"/>
       <c r="Q5" s="4" t="n"/>
       <c r="R5" s="4" t="n"/>
-      <c r="S5" s="4" t="n"/>
-      <c r="T5" s="4" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="U5" s="4" t="n"/>
-      <c r="V5" s="4" t="n"/>
-      <c r="W5" s="4" t="n"/>
-      <c r="X5" s="4" t="n"/>
-      <c r="Y5" s="4" t="n"/>
-      <c r="Z5" s="4" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="AA5" s="4" t="n"/>
-      <c r="AB5" s="4" t="n"/>
-      <c r="AC5" s="4" t="n"/>
-      <c r="AD5" s="4" t="n"/>
-      <c r="AE5" s="4" t="n"/>
-      <c r="AF5" s="4" t="n"/>
-      <c r="AG5" s="4" t="n"/>
-      <c r="AH5" s="4" t="n"/>
-      <c r="AI5" s="4" t="n"/>
-      <c r="AJ5" s="4" t="n"/>
-      <c r="AK5" s="4" t="n"/>
-      <c r="AL5" s="4" t="n"/>
-      <c r="AM5" s="4" t="n"/>
-      <c r="AN5" s="4" t="n"/>
-      <c r="AO5" s="4" t="n"/>
-      <c r="AP5" s="4" t="n"/>
-      <c r="AQ5" s="4" t="n"/>
-      <c r="AR5" s="4" t="n"/>
-      <c r="AS5" s="4" t="n"/>
-      <c r="AT5" s="4" t="n"/>
-      <c r="AU5" s="4" t="n"/>
-      <c r="AV5" s="4" t="n"/>
-      <c r="AW5" s="4" t="n"/>
-      <c r="AX5" s="4" t="n"/>
-      <c r="AY5" s="4" t="n"/>
-      <c r="AZ5" s="4" t="n"/>
-      <c r="BA5" s="4" t="n"/>
-      <c r="BB5" s="4" t="n"/>
-      <c r="BC5" s="4" t="n"/>
-      <c r="BD5" s="4" t="n"/>
-      <c r="BE5" s="4" t="n"/>
-      <c r="BF5" s="4" t="n"/>
-      <c r="BG5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -8429,60 +8019,19 @@
       <c r="E6" s="4" t="n"/>
       <c r="F6" s="4" t="n"/>
       <c r="G6" s="4" t="n"/>
-      <c r="H6" s="4" t="n"/>
+      <c r="H6" s="4" t="n">
+        <v>22.29</v>
+      </c>
       <c r="I6" s="4" t="n"/>
       <c r="J6" s="4" t="n"/>
       <c r="K6" s="4" t="n"/>
       <c r="L6" s="4" t="n"/>
       <c r="M6" s="4" t="n"/>
       <c r="N6" s="4" t="n"/>
-      <c r="O6" s="4" t="n">
-        <v>22.29</v>
-      </c>
+      <c r="O6" s="4" t="n"/>
       <c r="P6" s="4" t="n"/>
       <c r="Q6" s="4" t="n"/>
       <c r="R6" s="4" t="n"/>
-      <c r="S6" s="4" t="n"/>
-      <c r="T6" s="4" t="n"/>
-      <c r="U6" s="4" t="n"/>
-      <c r="V6" s="4" t="n"/>
-      <c r="W6" s="4" t="n"/>
-      <c r="X6" s="4" t="n"/>
-      <c r="Y6" s="4" t="n"/>
-      <c r="Z6" s="4" t="n"/>
-      <c r="AA6" s="4" t="n"/>
-      <c r="AB6" s="4" t="n"/>
-      <c r="AC6" s="4" t="n"/>
-      <c r="AD6" s="4" t="n"/>
-      <c r="AE6" s="4" t="n"/>
-      <c r="AF6" s="4" t="n"/>
-      <c r="AG6" s="4" t="n"/>
-      <c r="AH6" s="4" t="n"/>
-      <c r="AI6" s="4" t="n"/>
-      <c r="AJ6" s="4" t="n"/>
-      <c r="AK6" s="4" t="n"/>
-      <c r="AL6" s="4" t="n"/>
-      <c r="AM6" s="4" t="n"/>
-      <c r="AN6" s="4" t="n"/>
-      <c r="AO6" s="4" t="n"/>
-      <c r="AP6" s="4" t="n"/>
-      <c r="AQ6" s="4" t="n"/>
-      <c r="AR6" s="4" t="n"/>
-      <c r="AS6" s="4" t="n"/>
-      <c r="AT6" s="4" t="n"/>
-      <c r="AU6" s="4" t="n"/>
-      <c r="AV6" s="4" t="n"/>
-      <c r="AW6" s="4" t="n"/>
-      <c r="AX6" s="4" t="n"/>
-      <c r="AY6" s="4" t="n"/>
-      <c r="AZ6" s="4" t="n"/>
-      <c r="BA6" s="4" t="n"/>
-      <c r="BB6" s="4" t="n"/>
-      <c r="BC6" s="4" t="n"/>
-      <c r="BD6" s="4" t="n"/>
-      <c r="BE6" s="4" t="n"/>
-      <c r="BF6" s="4" t="n"/>
-      <c r="BG6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -8515,47 +8064,6 @@
       <c r="P7" s="4" t="n"/>
       <c r="Q7" s="4" t="n"/>
       <c r="R7" s="4" t="n"/>
-      <c r="S7" s="4" t="n"/>
-      <c r="T7" s="4" t="n"/>
-      <c r="U7" s="4" t="n"/>
-      <c r="V7" s="4" t="n"/>
-      <c r="W7" s="4" t="n"/>
-      <c r="X7" s="4" t="n"/>
-      <c r="Y7" s="4" t="n"/>
-      <c r="Z7" s="4" t="n"/>
-      <c r="AA7" s="4" t="n"/>
-      <c r="AB7" s="4" t="n"/>
-      <c r="AC7" s="4" t="n"/>
-      <c r="AD7" s="4" t="n"/>
-      <c r="AE7" s="4" t="n"/>
-      <c r="AF7" s="4" t="n"/>
-      <c r="AG7" s="4" t="n"/>
-      <c r="AH7" s="4" t="n"/>
-      <c r="AI7" s="4" t="n"/>
-      <c r="AJ7" s="4" t="n"/>
-      <c r="AK7" s="4" t="n"/>
-      <c r="AL7" s="4" t="n"/>
-      <c r="AM7" s="4" t="n"/>
-      <c r="AN7" s="4" t="n"/>
-      <c r="AO7" s="4" t="n"/>
-      <c r="AP7" s="4" t="n"/>
-      <c r="AQ7" s="4" t="n"/>
-      <c r="AR7" s="4" t="n"/>
-      <c r="AS7" s="4" t="n"/>
-      <c r="AT7" s="4" t="n"/>
-      <c r="AU7" s="4" t="n"/>
-      <c r="AV7" s="4" t="n"/>
-      <c r="AW7" s="4" t="n"/>
-      <c r="AX7" s="4" t="n"/>
-      <c r="AY7" s="4" t="n"/>
-      <c r="AZ7" s="4" t="n"/>
-      <c r="BA7" s="4" t="n"/>
-      <c r="BB7" s="4" t="n"/>
-      <c r="BC7" s="4" t="n"/>
-      <c r="BD7" s="4" t="n"/>
-      <c r="BE7" s="4" t="n"/>
-      <c r="BF7" s="4" t="n"/>
-      <c r="BG7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -8575,64 +8083,23 @@
       </c>
       <c r="D8" s="4" t="n"/>
       <c r="E8" s="4" t="n"/>
-      <c r="F8" s="4" t="n"/>
+      <c r="F8" s="4" t="n">
+        <v>18.2</v>
+      </c>
       <c r="G8" s="4" t="n"/>
       <c r="H8" s="4" t="n"/>
-      <c r="I8" s="4" t="n">
-        <v>18.2</v>
-      </c>
+      <c r="I8" s="4" t="n"/>
       <c r="J8" s="4" t="n"/>
       <c r="K8" s="4" t="n"/>
       <c r="L8" s="4" t="n"/>
       <c r="M8" s="4" t="n"/>
       <c r="N8" s="4" t="n"/>
       <c r="O8" s="4" t="n"/>
-      <c r="P8" s="4" t="n"/>
+      <c r="P8" s="4" t="n">
+        <v>18.9</v>
+      </c>
       <c r="Q8" s="4" t="n"/>
       <c r="R8" s="4" t="n"/>
-      <c r="S8" s="4" t="n"/>
-      <c r="T8" s="4" t="n"/>
-      <c r="U8" s="4" t="n"/>
-      <c r="V8" s="4" t="n"/>
-      <c r="W8" s="4" t="n"/>
-      <c r="X8" s="4" t="n"/>
-      <c r="Y8" s="4" t="n"/>
-      <c r="Z8" s="4" t="n"/>
-      <c r="AA8" s="4" t="n"/>
-      <c r="AB8" s="4" t="n"/>
-      <c r="AC8" s="4" t="n"/>
-      <c r="AD8" s="4" t="n"/>
-      <c r="AE8" s="4" t="n"/>
-      <c r="AF8" s="4" t="n"/>
-      <c r="AG8" s="4" t="n"/>
-      <c r="AH8" s="4" t="n"/>
-      <c r="AI8" s="4" t="n"/>
-      <c r="AJ8" s="4" t="n"/>
-      <c r="AK8" s="4" t="n"/>
-      <c r="AL8" s="4" t="n"/>
-      <c r="AM8" s="4" t="n"/>
-      <c r="AN8" s="4" t="n"/>
-      <c r="AO8" s="4" t="n"/>
-      <c r="AP8" s="4" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="AQ8" s="4" t="n"/>
-      <c r="AR8" s="4" t="n"/>
-      <c r="AS8" s="4" t="n"/>
-      <c r="AT8" s="4" t="n"/>
-      <c r="AU8" s="4" t="n"/>
-      <c r="AV8" s="4" t="n"/>
-      <c r="AW8" s="4" t="n"/>
-      <c r="AX8" s="4" t="n"/>
-      <c r="AY8" s="4" t="n"/>
-      <c r="AZ8" s="4" t="n"/>
-      <c r="BA8" s="4" t="n"/>
-      <c r="BB8" s="4" t="n"/>
-      <c r="BC8" s="4" t="n"/>
-      <c r="BD8" s="4" t="n"/>
-      <c r="BE8" s="4" t="n"/>
-      <c r="BF8" s="4" t="n"/>
-      <c r="BG8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -8665,47 +8132,6 @@
       <c r="P9" s="4" t="n"/>
       <c r="Q9" s="4" t="n"/>
       <c r="R9" s="4" t="n"/>
-      <c r="S9" s="4" t="n"/>
-      <c r="T9" s="4" t="n"/>
-      <c r="U9" s="4" t="n"/>
-      <c r="V9" s="4" t="n"/>
-      <c r="W9" s="4" t="n"/>
-      <c r="X9" s="4" t="n"/>
-      <c r="Y9" s="4" t="n"/>
-      <c r="Z9" s="4" t="n"/>
-      <c r="AA9" s="4" t="n"/>
-      <c r="AB9" s="4" t="n"/>
-      <c r="AC9" s="4" t="n"/>
-      <c r="AD9" s="4" t="n"/>
-      <c r="AE9" s="4" t="n"/>
-      <c r="AF9" s="4" t="n"/>
-      <c r="AG9" s="4" t="n"/>
-      <c r="AH9" s="4" t="n"/>
-      <c r="AI9" s="4" t="n"/>
-      <c r="AJ9" s="4" t="n"/>
-      <c r="AK9" s="4" t="n"/>
-      <c r="AL9" s="4" t="n"/>
-      <c r="AM9" s="4" t="n"/>
-      <c r="AN9" s="4" t="n"/>
-      <c r="AO9" s="4" t="n"/>
-      <c r="AP9" s="4" t="n"/>
-      <c r="AQ9" s="4" t="n"/>
-      <c r="AR9" s="4" t="n"/>
-      <c r="AS9" s="4" t="n"/>
-      <c r="AT9" s="4" t="n"/>
-      <c r="AU9" s="4" t="n"/>
-      <c r="AV9" s="4" t="n"/>
-      <c r="AW9" s="4" t="n"/>
-      <c r="AX9" s="4" t="n"/>
-      <c r="AY9" s="4" t="n"/>
-      <c r="AZ9" s="4" t="n"/>
-      <c r="BA9" s="4" t="n"/>
-      <c r="BB9" s="4" t="n"/>
-      <c r="BC9" s="4" t="n"/>
-      <c r="BD9" s="4" t="n"/>
-      <c r="BE9" s="4" t="n"/>
-      <c r="BF9" s="4" t="n"/>
-      <c r="BG9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n"/>
@@ -8734,47 +8160,6 @@
       <c r="P10" s="4" t="n"/>
       <c r="Q10" s="4" t="n"/>
       <c r="R10" s="4" t="n"/>
-      <c r="S10" s="4" t="n"/>
-      <c r="T10" s="4" t="n"/>
-      <c r="U10" s="4" t="n"/>
-      <c r="V10" s="4" t="n"/>
-      <c r="W10" s="4" t="n"/>
-      <c r="X10" s="4" t="n"/>
-      <c r="Y10" s="4" t="n"/>
-      <c r="Z10" s="4" t="n"/>
-      <c r="AA10" s="4" t="n"/>
-      <c r="AB10" s="4" t="n"/>
-      <c r="AC10" s="4" t="n"/>
-      <c r="AD10" s="4" t="n"/>
-      <c r="AE10" s="4" t="n"/>
-      <c r="AF10" s="4" t="n"/>
-      <c r="AG10" s="4" t="n"/>
-      <c r="AH10" s="4" t="n"/>
-      <c r="AI10" s="4" t="n"/>
-      <c r="AJ10" s="4" t="n"/>
-      <c r="AK10" s="4" t="n"/>
-      <c r="AL10" s="4" t="n"/>
-      <c r="AM10" s="4" t="n"/>
-      <c r="AN10" s="4" t="n"/>
-      <c r="AO10" s="4" t="n"/>
-      <c r="AP10" s="4" t="n"/>
-      <c r="AQ10" s="4" t="n"/>
-      <c r="AR10" s="4" t="n"/>
-      <c r="AS10" s="4" t="n"/>
-      <c r="AT10" s="4" t="n"/>
-      <c r="AU10" s="4" t="n"/>
-      <c r="AV10" s="4" t="n"/>
-      <c r="AW10" s="4" t="n"/>
-      <c r="AX10" s="4" t="n"/>
-      <c r="AY10" s="4" t="n"/>
-      <c r="AZ10" s="4" t="n"/>
-      <c r="BA10" s="4" t="n"/>
-      <c r="BB10" s="4" t="n"/>
-      <c r="BC10" s="4" t="n"/>
-      <c r="BD10" s="4" t="n"/>
-      <c r="BE10" s="4" t="n"/>
-      <c r="BF10" s="4" t="n"/>
-      <c r="BG10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -8794,12 +8179,12 @@
       </c>
       <c r="D11" s="4" t="n"/>
       <c r="E11" s="4" t="n"/>
-      <c r="F11" s="4" t="n"/>
+      <c r="F11" s="4" t="n">
+        <v>27.9</v>
+      </c>
       <c r="G11" s="4" t="n"/>
       <c r="H11" s="4" t="n"/>
-      <c r="I11" s="4" t="n">
-        <v>27.9</v>
-      </c>
+      <c r="I11" s="4" t="n"/>
       <c r="J11" s="4" t="n"/>
       <c r="K11" s="4" t="n"/>
       <c r="L11" s="4" t="n"/>
@@ -8809,47 +8194,6 @@
       <c r="P11" s="4" t="n"/>
       <c r="Q11" s="4" t="n"/>
       <c r="R11" s="4" t="n"/>
-      <c r="S11" s="4" t="n"/>
-      <c r="T11" s="4" t="n"/>
-      <c r="U11" s="4" t="n"/>
-      <c r="V11" s="4" t="n"/>
-      <c r="W11" s="4" t="n"/>
-      <c r="X11" s="4" t="n"/>
-      <c r="Y11" s="4" t="n"/>
-      <c r="Z11" s="4" t="n"/>
-      <c r="AA11" s="4" t="n"/>
-      <c r="AB11" s="4" t="n"/>
-      <c r="AC11" s="4" t="n"/>
-      <c r="AD11" s="4" t="n"/>
-      <c r="AE11" s="4" t="n"/>
-      <c r="AF11" s="4" t="n"/>
-      <c r="AG11" s="4" t="n"/>
-      <c r="AH11" s="4" t="n"/>
-      <c r="AI11" s="4" t="n"/>
-      <c r="AJ11" s="4" t="n"/>
-      <c r="AK11" s="4" t="n"/>
-      <c r="AL11" s="4" t="n"/>
-      <c r="AM11" s="4" t="n"/>
-      <c r="AN11" s="4" t="n"/>
-      <c r="AO11" s="4" t="n"/>
-      <c r="AP11" s="4" t="n"/>
-      <c r="AQ11" s="4" t="n"/>
-      <c r="AR11" s="4" t="n"/>
-      <c r="AS11" s="4" t="n"/>
-      <c r="AT11" s="4" t="n"/>
-      <c r="AU11" s="4" t="n"/>
-      <c r="AV11" s="4" t="n"/>
-      <c r="AW11" s="4" t="n"/>
-      <c r="AX11" s="4" t="n"/>
-      <c r="AY11" s="4" t="n"/>
-      <c r="AZ11" s="4" t="n"/>
-      <c r="BA11" s="4" t="n"/>
-      <c r="BB11" s="4" t="n"/>
-      <c r="BC11" s="4" t="n"/>
-      <c r="BD11" s="4" t="n"/>
-      <c r="BE11" s="4" t="n"/>
-      <c r="BF11" s="4" t="n"/>
-      <c r="BG11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -8882,47 +8226,6 @@
       <c r="P12" s="4" t="n"/>
       <c r="Q12" s="4" t="n"/>
       <c r="R12" s="4" t="n"/>
-      <c r="S12" s="4" t="n"/>
-      <c r="T12" s="4" t="n"/>
-      <c r="U12" s="4" t="n"/>
-      <c r="V12" s="4" t="n"/>
-      <c r="W12" s="4" t="n"/>
-      <c r="X12" s="4" t="n"/>
-      <c r="Y12" s="4" t="n"/>
-      <c r="Z12" s="4" t="n"/>
-      <c r="AA12" s="4" t="n"/>
-      <c r="AB12" s="4" t="n"/>
-      <c r="AC12" s="4" t="n"/>
-      <c r="AD12" s="4" t="n"/>
-      <c r="AE12" s="4" t="n"/>
-      <c r="AF12" s="4" t="n"/>
-      <c r="AG12" s="4" t="n"/>
-      <c r="AH12" s="4" t="n"/>
-      <c r="AI12" s="4" t="n"/>
-      <c r="AJ12" s="4" t="n"/>
-      <c r="AK12" s="4" t="n"/>
-      <c r="AL12" s="4" t="n"/>
-      <c r="AM12" s="4" t="n"/>
-      <c r="AN12" s="4" t="n"/>
-      <c r="AO12" s="4" t="n"/>
-      <c r="AP12" s="4" t="n"/>
-      <c r="AQ12" s="4" t="n"/>
-      <c r="AR12" s="4" t="n"/>
-      <c r="AS12" s="4" t="n"/>
-      <c r="AT12" s="4" t="n"/>
-      <c r="AU12" s="4" t="n"/>
-      <c r="AV12" s="4" t="n"/>
-      <c r="AW12" s="4" t="n"/>
-      <c r="AX12" s="4" t="n"/>
-      <c r="AY12" s="4" t="n"/>
-      <c r="AZ12" s="4" t="n"/>
-      <c r="BA12" s="4" t="n"/>
-      <c r="BB12" s="4" t="n"/>
-      <c r="BC12" s="4" t="n"/>
-      <c r="BD12" s="4" t="n"/>
-      <c r="BE12" s="4" t="n"/>
-      <c r="BF12" s="4" t="n"/>
-      <c r="BG12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -8955,47 +8258,6 @@
       <c r="P13" s="4" t="n"/>
       <c r="Q13" s="4" t="n"/>
       <c r="R13" s="4" t="n"/>
-      <c r="S13" s="4" t="n"/>
-      <c r="T13" s="4" t="n"/>
-      <c r="U13" s="4" t="n"/>
-      <c r="V13" s="4" t="n"/>
-      <c r="W13" s="4" t="n"/>
-      <c r="X13" s="4" t="n"/>
-      <c r="Y13" s="4" t="n"/>
-      <c r="Z13" s="4" t="n"/>
-      <c r="AA13" s="4" t="n"/>
-      <c r="AB13" s="4" t="n"/>
-      <c r="AC13" s="4" t="n"/>
-      <c r="AD13" s="4" t="n"/>
-      <c r="AE13" s="4" t="n"/>
-      <c r="AF13" s="4" t="n"/>
-      <c r="AG13" s="4" t="n"/>
-      <c r="AH13" s="4" t="n"/>
-      <c r="AI13" s="4" t="n"/>
-      <c r="AJ13" s="4" t="n"/>
-      <c r="AK13" s="4" t="n"/>
-      <c r="AL13" s="4" t="n"/>
-      <c r="AM13" s="4" t="n"/>
-      <c r="AN13" s="4" t="n"/>
-      <c r="AO13" s="4" t="n"/>
-      <c r="AP13" s="4" t="n"/>
-      <c r="AQ13" s="4" t="n"/>
-      <c r="AR13" s="4" t="n"/>
-      <c r="AS13" s="4" t="n"/>
-      <c r="AT13" s="4" t="n"/>
-      <c r="AU13" s="4" t="n"/>
-      <c r="AV13" s="4" t="n"/>
-      <c r="AW13" s="4" t="n"/>
-      <c r="AX13" s="4" t="n"/>
-      <c r="AY13" s="4" t="n"/>
-      <c r="AZ13" s="4" t="n"/>
-      <c r="BA13" s="4" t="n"/>
-      <c r="BB13" s="4" t="n"/>
-      <c r="BC13" s="4" t="n"/>
-      <c r="BD13" s="4" t="n"/>
-      <c r="BE13" s="4" t="n"/>
-      <c r="BF13" s="4" t="n"/>
-      <c r="BG13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n"/>
@@ -9014,61 +8276,20 @@
       </c>
       <c r="E14" s="4" t="n"/>
       <c r="F14" s="4" t="n"/>
-      <c r="G14" s="4" t="n"/>
+      <c r="G14" s="4" t="n">
+        <v>38.7</v>
+      </c>
       <c r="H14" s="4" t="n"/>
       <c r="I14" s="4" t="n"/>
       <c r="J14" s="4" t="n"/>
       <c r="K14" s="4" t="n"/>
-      <c r="L14" s="4" t="n">
-        <v>38.7</v>
-      </c>
+      <c r="L14" s="4" t="n"/>
       <c r="M14" s="4" t="n"/>
       <c r="N14" s="4" t="n"/>
       <c r="O14" s="4" t="n"/>
       <c r="P14" s="4" t="n"/>
       <c r="Q14" s="4" t="n"/>
       <c r="R14" s="4" t="n"/>
-      <c r="S14" s="4" t="n"/>
-      <c r="T14" s="4" t="n"/>
-      <c r="U14" s="4" t="n"/>
-      <c r="V14" s="4" t="n"/>
-      <c r="W14" s="4" t="n"/>
-      <c r="X14" s="4" t="n"/>
-      <c r="Y14" s="4" t="n"/>
-      <c r="Z14" s="4" t="n"/>
-      <c r="AA14" s="4" t="n"/>
-      <c r="AB14" s="4" t="n"/>
-      <c r="AC14" s="4" t="n"/>
-      <c r="AD14" s="4" t="n"/>
-      <c r="AE14" s="4" t="n"/>
-      <c r="AF14" s="4" t="n"/>
-      <c r="AG14" s="4" t="n"/>
-      <c r="AH14" s="4" t="n"/>
-      <c r="AI14" s="4" t="n"/>
-      <c r="AJ14" s="4" t="n"/>
-      <c r="AK14" s="4" t="n"/>
-      <c r="AL14" s="4" t="n"/>
-      <c r="AM14" s="4" t="n"/>
-      <c r="AN14" s="4" t="n"/>
-      <c r="AO14" s="4" t="n"/>
-      <c r="AP14" s="4" t="n"/>
-      <c r="AQ14" s="4" t="n"/>
-      <c r="AR14" s="4" t="n"/>
-      <c r="AS14" s="4" t="n"/>
-      <c r="AT14" s="4" t="n"/>
-      <c r="AU14" s="4" t="n"/>
-      <c r="AV14" s="4" t="n"/>
-      <c r="AW14" s="4" t="n"/>
-      <c r="AX14" s="4" t="n"/>
-      <c r="AY14" s="4" t="n"/>
-      <c r="AZ14" s="4" t="n"/>
-      <c r="BA14" s="4" t="n"/>
-      <c r="BB14" s="4" t="n"/>
-      <c r="BC14" s="4" t="n"/>
-      <c r="BD14" s="4" t="n"/>
-      <c r="BE14" s="4" t="n"/>
-      <c r="BF14" s="4" t="n"/>
-      <c r="BG14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -9101,47 +8322,6 @@
       <c r="P15" s="4" t="n"/>
       <c r="Q15" s="4" t="n"/>
       <c r="R15" s="4" t="n"/>
-      <c r="S15" s="4" t="n"/>
-      <c r="T15" s="4" t="n"/>
-      <c r="U15" s="4" t="n"/>
-      <c r="V15" s="4" t="n"/>
-      <c r="W15" s="4" t="n"/>
-      <c r="X15" s="4" t="n"/>
-      <c r="Y15" s="4" t="n"/>
-      <c r="Z15" s="4" t="n"/>
-      <c r="AA15" s="4" t="n"/>
-      <c r="AB15" s="4" t="n"/>
-      <c r="AC15" s="4" t="n"/>
-      <c r="AD15" s="4" t="n"/>
-      <c r="AE15" s="4" t="n"/>
-      <c r="AF15" s="4" t="n"/>
-      <c r="AG15" s="4" t="n"/>
-      <c r="AH15" s="4" t="n"/>
-      <c r="AI15" s="4" t="n"/>
-      <c r="AJ15" s="4" t="n"/>
-      <c r="AK15" s="4" t="n"/>
-      <c r="AL15" s="4" t="n"/>
-      <c r="AM15" s="4" t="n"/>
-      <c r="AN15" s="4" t="n"/>
-      <c r="AO15" s="4" t="n"/>
-      <c r="AP15" s="4" t="n"/>
-      <c r="AQ15" s="4" t="n"/>
-      <c r="AR15" s="4" t="n"/>
-      <c r="AS15" s="4" t="n"/>
-      <c r="AT15" s="4" t="n"/>
-      <c r="AU15" s="4" t="n"/>
-      <c r="AV15" s="4" t="n"/>
-      <c r="AW15" s="4" t="n"/>
-      <c r="AX15" s="4" t="n"/>
-      <c r="AY15" s="4" t="n"/>
-      <c r="AZ15" s="4" t="n"/>
-      <c r="BA15" s="4" t="n"/>
-      <c r="BB15" s="4" t="n"/>
-      <c r="BC15" s="4" t="n"/>
-      <c r="BD15" s="4" t="n"/>
-      <c r="BE15" s="4" t="n"/>
-      <c r="BF15" s="4" t="n"/>
-      <c r="BG15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
@@ -9170,47 +8350,6 @@
       <c r="P16" s="4" t="n"/>
       <c r="Q16" s="4" t="n"/>
       <c r="R16" s="4" t="n"/>
-      <c r="S16" s="4" t="n"/>
-      <c r="T16" s="4" t="n"/>
-      <c r="U16" s="4" t="n"/>
-      <c r="V16" s="4" t="n"/>
-      <c r="W16" s="4" t="n"/>
-      <c r="X16" s="4" t="n"/>
-      <c r="Y16" s="4" t="n"/>
-      <c r="Z16" s="4" t="n"/>
-      <c r="AA16" s="4" t="n"/>
-      <c r="AB16" s="4" t="n"/>
-      <c r="AC16" s="4" t="n"/>
-      <c r="AD16" s="4" t="n"/>
-      <c r="AE16" s="4" t="n"/>
-      <c r="AF16" s="4" t="n"/>
-      <c r="AG16" s="4" t="n"/>
-      <c r="AH16" s="4" t="n"/>
-      <c r="AI16" s="4" t="n"/>
-      <c r="AJ16" s="4" t="n"/>
-      <c r="AK16" s="4" t="n"/>
-      <c r="AL16" s="4" t="n"/>
-      <c r="AM16" s="4" t="n"/>
-      <c r="AN16" s="4" t="n"/>
-      <c r="AO16" s="4" t="n"/>
-      <c r="AP16" s="4" t="n"/>
-      <c r="AQ16" s="4" t="n"/>
-      <c r="AR16" s="4" t="n"/>
-      <c r="AS16" s="4" t="n"/>
-      <c r="AT16" s="4" t="n"/>
-      <c r="AU16" s="4" t="n"/>
-      <c r="AV16" s="4" t="n"/>
-      <c r="AW16" s="4" t="n"/>
-      <c r="AX16" s="4" t="n"/>
-      <c r="AY16" s="4" t="n"/>
-      <c r="AZ16" s="4" t="n"/>
-      <c r="BA16" s="4" t="n"/>
-      <c r="BB16" s="4" t="n"/>
-      <c r="BC16" s="4" t="n"/>
-      <c r="BD16" s="4" t="n"/>
-      <c r="BE16" s="4" t="n"/>
-      <c r="BF16" s="4" t="n"/>
-      <c r="BG16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
@@ -9239,47 +8378,6 @@
       <c r="P17" s="4" t="n"/>
       <c r="Q17" s="4" t="n"/>
       <c r="R17" s="4" t="n"/>
-      <c r="S17" s="4" t="n"/>
-      <c r="T17" s="4" t="n"/>
-      <c r="U17" s="4" t="n"/>
-      <c r="V17" s="4" t="n"/>
-      <c r="W17" s="4" t="n"/>
-      <c r="X17" s="4" t="n"/>
-      <c r="Y17" s="4" t="n"/>
-      <c r="Z17" s="4" t="n"/>
-      <c r="AA17" s="4" t="n"/>
-      <c r="AB17" s="4" t="n"/>
-      <c r="AC17" s="4" t="n"/>
-      <c r="AD17" s="4" t="n"/>
-      <c r="AE17" s="4" t="n"/>
-      <c r="AF17" s="4" t="n"/>
-      <c r="AG17" s="4" t="n"/>
-      <c r="AH17" s="4" t="n"/>
-      <c r="AI17" s="4" t="n"/>
-      <c r="AJ17" s="4" t="n"/>
-      <c r="AK17" s="4" t="n"/>
-      <c r="AL17" s="4" t="n"/>
-      <c r="AM17" s="4" t="n"/>
-      <c r="AN17" s="4" t="n"/>
-      <c r="AO17" s="4" t="n"/>
-      <c r="AP17" s="4" t="n"/>
-      <c r="AQ17" s="4" t="n"/>
-      <c r="AR17" s="4" t="n"/>
-      <c r="AS17" s="4" t="n"/>
-      <c r="AT17" s="4" t="n"/>
-      <c r="AU17" s="4" t="n"/>
-      <c r="AV17" s="4" t="n"/>
-      <c r="AW17" s="4" t="n"/>
-      <c r="AX17" s="4" t="n"/>
-      <c r="AY17" s="4" t="n"/>
-      <c r="AZ17" s="4" t="n"/>
-      <c r="BA17" s="4" t="n"/>
-      <c r="BB17" s="4" t="n"/>
-      <c r="BC17" s="4" t="n"/>
-      <c r="BD17" s="4" t="n"/>
-      <c r="BE17" s="4" t="n"/>
-      <c r="BF17" s="4" t="n"/>
-      <c r="BG17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n"/>
@@ -9308,47 +8406,6 @@
       <c r="P18" s="4" t="n"/>
       <c r="Q18" s="4" t="n"/>
       <c r="R18" s="4" t="n"/>
-      <c r="S18" s="4" t="n"/>
-      <c r="T18" s="4" t="n"/>
-      <c r="U18" s="4" t="n"/>
-      <c r="V18" s="4" t="n"/>
-      <c r="W18" s="4" t="n"/>
-      <c r="X18" s="4" t="n"/>
-      <c r="Y18" s="4" t="n"/>
-      <c r="Z18" s="4" t="n"/>
-      <c r="AA18" s="4" t="n"/>
-      <c r="AB18" s="4" t="n"/>
-      <c r="AC18" s="4" t="n"/>
-      <c r="AD18" s="4" t="n"/>
-      <c r="AE18" s="4" t="n"/>
-      <c r="AF18" s="4" t="n"/>
-      <c r="AG18" s="4" t="n"/>
-      <c r="AH18" s="4" t="n"/>
-      <c r="AI18" s="4" t="n"/>
-      <c r="AJ18" s="4" t="n"/>
-      <c r="AK18" s="4" t="n"/>
-      <c r="AL18" s="4" t="n"/>
-      <c r="AM18" s="4" t="n"/>
-      <c r="AN18" s="4" t="n"/>
-      <c r="AO18" s="4" t="n"/>
-      <c r="AP18" s="4" t="n"/>
-      <c r="AQ18" s="4" t="n"/>
-      <c r="AR18" s="4" t="n"/>
-      <c r="AS18" s="4" t="n"/>
-      <c r="AT18" s="4" t="n"/>
-      <c r="AU18" s="4" t="n"/>
-      <c r="AV18" s="4" t="n"/>
-      <c r="AW18" s="4" t="n"/>
-      <c r="AX18" s="4" t="n"/>
-      <c r="AY18" s="4" t="n"/>
-      <c r="AZ18" s="4" t="n"/>
-      <c r="BA18" s="4" t="n"/>
-      <c r="BB18" s="4" t="n"/>
-      <c r="BC18" s="4" t="n"/>
-      <c r="BD18" s="4" t="n"/>
-      <c r="BE18" s="4" t="n"/>
-      <c r="BF18" s="4" t="n"/>
-      <c r="BG18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -9381,47 +8438,6 @@
       <c r="P19" s="4" t="n"/>
       <c r="Q19" s="4" t="n"/>
       <c r="R19" s="4" t="n"/>
-      <c r="S19" s="4" t="n"/>
-      <c r="T19" s="4" t="n"/>
-      <c r="U19" s="4" t="n"/>
-      <c r="V19" s="4" t="n"/>
-      <c r="W19" s="4" t="n"/>
-      <c r="X19" s="4" t="n"/>
-      <c r="Y19" s="4" t="n"/>
-      <c r="Z19" s="4" t="n"/>
-      <c r="AA19" s="4" t="n"/>
-      <c r="AB19" s="4" t="n"/>
-      <c r="AC19" s="4" t="n"/>
-      <c r="AD19" s="4" t="n"/>
-      <c r="AE19" s="4" t="n"/>
-      <c r="AF19" s="4" t="n"/>
-      <c r="AG19" s="4" t="n"/>
-      <c r="AH19" s="4" t="n"/>
-      <c r="AI19" s="4" t="n"/>
-      <c r="AJ19" s="4" t="n"/>
-      <c r="AK19" s="4" t="n"/>
-      <c r="AL19" s="4" t="n"/>
-      <c r="AM19" s="4" t="n"/>
-      <c r="AN19" s="4" t="n"/>
-      <c r="AO19" s="4" t="n"/>
-      <c r="AP19" s="4" t="n"/>
-      <c r="AQ19" s="4" t="n"/>
-      <c r="AR19" s="4" t="n"/>
-      <c r="AS19" s="4" t="n"/>
-      <c r="AT19" s="4" t="n"/>
-      <c r="AU19" s="4" t="n"/>
-      <c r="AV19" s="4" t="n"/>
-      <c r="AW19" s="4" t="n"/>
-      <c r="AX19" s="4" t="n"/>
-      <c r="AY19" s="4" t="n"/>
-      <c r="AZ19" s="4" t="n"/>
-      <c r="BA19" s="4" t="n"/>
-      <c r="BB19" s="4" t="n"/>
-      <c r="BC19" s="4" t="n"/>
-      <c r="BD19" s="4" t="n"/>
-      <c r="BE19" s="4" t="n"/>
-      <c r="BF19" s="4" t="n"/>
-      <c r="BG19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -9450,53 +8466,12 @@
       <c r="L20" s="4" t="n"/>
       <c r="M20" s="4" t="n"/>
       <c r="N20" s="4" t="n"/>
-      <c r="O20" s="4" t="n"/>
+      <c r="O20" s="4" t="n">
+        <v>18.9</v>
+      </c>
       <c r="P20" s="4" t="n"/>
       <c r="Q20" s="4" t="n"/>
       <c r="R20" s="4" t="n"/>
-      <c r="S20" s="4" t="n"/>
-      <c r="T20" s="4" t="n"/>
-      <c r="U20" s="4" t="n"/>
-      <c r="V20" s="4" t="n"/>
-      <c r="W20" s="4" t="n"/>
-      <c r="X20" s="4" t="n"/>
-      <c r="Y20" s="4" t="n"/>
-      <c r="Z20" s="4" t="n"/>
-      <c r="AA20" s="4" t="n"/>
-      <c r="AB20" s="4" t="n"/>
-      <c r="AC20" s="4" t="n"/>
-      <c r="AD20" s="4" t="n"/>
-      <c r="AE20" s="4" t="n"/>
-      <c r="AF20" s="4" t="n"/>
-      <c r="AG20" s="4" t="n"/>
-      <c r="AH20" s="4" t="n"/>
-      <c r="AI20" s="4" t="n"/>
-      <c r="AJ20" s="4" t="n"/>
-      <c r="AK20" s="4" t="n"/>
-      <c r="AL20" s="4" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="AM20" s="4" t="n"/>
-      <c r="AN20" s="4" t="n"/>
-      <c r="AO20" s="4" t="n"/>
-      <c r="AP20" s="4" t="n"/>
-      <c r="AQ20" s="4" t="n"/>
-      <c r="AR20" s="4" t="n"/>
-      <c r="AS20" s="4" t="n"/>
-      <c r="AT20" s="4" t="n"/>
-      <c r="AU20" s="4" t="n"/>
-      <c r="AV20" s="4" t="n"/>
-      <c r="AW20" s="4" t="n"/>
-      <c r="AX20" s="4" t="n"/>
-      <c r="AY20" s="4" t="n"/>
-      <c r="AZ20" s="4" t="n"/>
-      <c r="BA20" s="4" t="n"/>
-      <c r="BB20" s="4" t="n"/>
-      <c r="BC20" s="4" t="n"/>
-      <c r="BD20" s="4" t="n"/>
-      <c r="BE20" s="4" t="n"/>
-      <c r="BF20" s="4" t="n"/>
-      <c r="BG20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -9515,10 +8490,10 @@
         </is>
       </c>
       <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="4" t="n">
+      <c r="E21" s="4" t="n">
         <v>27.6</v>
       </c>
+      <c r="F21" s="4" t="n"/>
       <c r="G21" s="4" t="n"/>
       <c r="H21" s="4" t="n"/>
       <c r="I21" s="4" t="n"/>
@@ -9531,50 +8506,9 @@
       <c r="P21" s="4" t="n"/>
       <c r="Q21" s="4" t="n"/>
       <c r="R21" s="4" t="n"/>
-      <c r="S21" s="4" t="n"/>
-      <c r="T21" s="4" t="n"/>
-      <c r="U21" s="4" t="n"/>
-      <c r="V21" s="4" t="n"/>
-      <c r="W21" s="4" t="n"/>
-      <c r="X21" s="4" t="n"/>
-      <c r="Y21" s="4" t="n"/>
-      <c r="Z21" s="4" t="n"/>
-      <c r="AA21" s="4" t="n"/>
-      <c r="AB21" s="4" t="n"/>
-      <c r="AC21" s="4" t="n"/>
-      <c r="AD21" s="4" t="n"/>
-      <c r="AE21" s="4" t="n"/>
-      <c r="AF21" s="4" t="n"/>
-      <c r="AG21" s="4" t="n"/>
-      <c r="AH21" s="4" t="n"/>
-      <c r="AI21" s="4" t="n"/>
-      <c r="AJ21" s="4" t="n"/>
-      <c r="AK21" s="4" t="n"/>
-      <c r="AL21" s="4" t="n"/>
-      <c r="AM21" s="4" t="n"/>
-      <c r="AN21" s="4" t="n"/>
-      <c r="AO21" s="4" t="n"/>
-      <c r="AP21" s="4" t="n"/>
-      <c r="AQ21" s="4" t="n"/>
-      <c r="AR21" s="4" t="n"/>
-      <c r="AS21" s="4" t="n"/>
-      <c r="AT21" s="4" t="n"/>
-      <c r="AU21" s="4" t="n"/>
-      <c r="AV21" s="4" t="n"/>
-      <c r="AW21" s="4" t="n"/>
-      <c r="AX21" s="4" t="n"/>
-      <c r="AY21" s="4" t="n"/>
-      <c r="AZ21" s="4" t="n"/>
-      <c r="BA21" s="4" t="n"/>
-      <c r="BB21" s="4" t="n"/>
-      <c r="BC21" s="4" t="n"/>
-      <c r="BD21" s="4" t="n"/>
-      <c r="BE21" s="4" t="n"/>
-      <c r="BF21" s="4" t="n"/>
-      <c r="BG21" s="4" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BG21"/>
+  <autoFilter ref="A1:R21"/>
   <mergeCells count="14">
     <mergeCell ref="A8"/>
     <mergeCell ref="A6"/>
@@ -9601,7 +8535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG21"/>
+  <dimension ref="A1:U21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9625,44 +8559,6 @@
     <col width="7.5" customWidth="1" min="19" max="19"/>
     <col width="7.5" customWidth="1" min="20" max="20"/>
     <col width="7.5" customWidth="1" min="21" max="21"/>
-    <col width="7.5" customWidth="1" min="22" max="22"/>
-    <col width="7.5" customWidth="1" min="23" max="23"/>
-    <col width="7.5" customWidth="1" min="24" max="24"/>
-    <col width="7.5" customWidth="1" min="25" max="25"/>
-    <col width="7.5" customWidth="1" min="26" max="26"/>
-    <col width="7.5" customWidth="1" min="27" max="27"/>
-    <col width="7.5" customWidth="1" min="28" max="28"/>
-    <col width="7.5" customWidth="1" min="29" max="29"/>
-    <col width="7.5" customWidth="1" min="30" max="30"/>
-    <col width="7.5" customWidth="1" min="31" max="31"/>
-    <col width="7.5" customWidth="1" min="32" max="32"/>
-    <col width="7.5" customWidth="1" min="33" max="33"/>
-    <col width="7.5" customWidth="1" min="34" max="34"/>
-    <col width="7.5" customWidth="1" min="35" max="35"/>
-    <col width="7.5" customWidth="1" min="36" max="36"/>
-    <col width="7.5" customWidth="1" min="37" max="37"/>
-    <col width="7.5" customWidth="1" min="38" max="38"/>
-    <col width="7.5" customWidth="1" min="39" max="39"/>
-    <col width="7.5" customWidth="1" min="40" max="40"/>
-    <col width="7.5" customWidth="1" min="41" max="41"/>
-    <col width="7.5" customWidth="1" min="42" max="42"/>
-    <col width="7.5" customWidth="1" min="43" max="43"/>
-    <col width="7.5" customWidth="1" min="44" max="44"/>
-    <col width="7.5" customWidth="1" min="45" max="45"/>
-    <col width="7.5" customWidth="1" min="46" max="46"/>
-    <col width="7.5" customWidth="1" min="47" max="47"/>
-    <col width="7.5" customWidth="1" min="48" max="48"/>
-    <col width="7.5" customWidth="1" min="49" max="49"/>
-    <col width="7.5" customWidth="1" min="50" max="50"/>
-    <col width="7.5" customWidth="1" min="51" max="51"/>
-    <col width="7.5" customWidth="1" min="52" max="52"/>
-    <col width="7.5" customWidth="1" min="53" max="53"/>
-    <col width="7.5" customWidth="1" min="54" max="54"/>
-    <col width="7.5" customWidth="1" min="55" max="55"/>
-    <col width="7.5" customWidth="1" min="56" max="56"/>
-    <col width="7.5" customWidth="1" min="57" max="57"/>
-    <col width="7.5" customWidth="1" min="58" max="58"/>
-    <col width="7.5" customWidth="1" min="59" max="59"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9693,272 +8589,82 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>恶魔</t>
+          <t>速尾</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>f5★6</t>
+          <t>9x8</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>f5</t>
+          <t>肥龙</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>玻璃★6</t>
+          <t>c2</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>玻璃</t>
+          <t>万达</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>速尾★6</t>
+          <t>21c</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>速尾</t>
+          <t>fp1</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>9x8★6</t>
+          <t>sgt</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>9x8</t>
+          <t>火山</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>ssc</t>
+          <t>法拉第</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>肥龙</t>
+          <t>秋王</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>c2★6</t>
+          <t>狼王</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>c2</t>
+          <t>小牛</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>万达★6</t>
+          <t>fe3</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>万达</t>
+          <t>六子</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>21c</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>fp1★6</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>fp1</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>sgt★6</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>sgt</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>火山</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>法拉第</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>秋王★6</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>秋王</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>白龙★6</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>白龙</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>sf90★6</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>sf90</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>att</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>divo</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>狼王</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>小牛★6</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>小牛</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>fe3★5</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>fe3</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>杰弟</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>六子</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>英灵殿</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
           <t>帕梅</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>ts900</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>650s</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>f5r</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>ps龙</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>r兔★6</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>r兔</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>帝国</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>杰皇★6</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>杰皇</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>猫头鹰</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>银电</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>陀飞轮</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>风龙</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>黑龙★6</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>黑龙</t>
         </is>
       </c>
     </row>
@@ -9981,63 +8687,25 @@
       <c r="D2" s="4" t="n"/>
       <c r="E2" s="4" t="n"/>
       <c r="F2" s="4" t="n"/>
-      <c r="G2" s="4" t="n"/>
+      <c r="G2" s="4" t="n">
+        <v>16.9</v>
+      </c>
       <c r="H2" s="4" t="n"/>
       <c r="I2" s="4" t="n"/>
       <c r="J2" s="4" t="n"/>
       <c r="K2" s="4" t="n"/>
       <c r="L2" s="4" t="n"/>
       <c r="M2" s="4" t="n"/>
-      <c r="N2" s="4" t="n">
-        <v>16.9</v>
-      </c>
+      <c r="N2" s="4" t="n"/>
       <c r="O2" s="4" t="n"/>
       <c r="P2" s="4" t="n"/>
       <c r="Q2" s="4" t="n"/>
       <c r="R2" s="4" t="n"/>
       <c r="S2" s="4" t="n"/>
       <c r="T2" s="4" t="n"/>
-      <c r="U2" s="4" t="n"/>
-      <c r="V2" s="4" t="n"/>
-      <c r="W2" s="4" t="n"/>
-      <c r="X2" s="4" t="n"/>
-      <c r="Y2" s="4" t="n"/>
-      <c r="Z2" s="4" t="n"/>
-      <c r="AA2" s="4" t="n"/>
-      <c r="AB2" s="4" t="n"/>
-      <c r="AC2" s="4" t="n"/>
-      <c r="AD2" s="4" t="n"/>
-      <c r="AE2" s="4" t="n"/>
-      <c r="AF2" s="4" t="n"/>
-      <c r="AG2" s="4" t="n"/>
-      <c r="AH2" s="4" t="n"/>
-      <c r="AI2" s="4" t="n"/>
-      <c r="AJ2" s="4" t="n"/>
-      <c r="AK2" s="4" t="n"/>
-      <c r="AL2" s="4" t="n"/>
-      <c r="AM2" s="4" t="n"/>
-      <c r="AN2" s="4" t="n"/>
-      <c r="AO2" s="4" t="n"/>
-      <c r="AP2" s="4" t="n"/>
-      <c r="AQ2" s="4" t="n"/>
-      <c r="AR2" s="4" t="n">
+      <c r="U2" s="4" t="n">
         <v>18.9</v>
       </c>
-      <c r="AS2" s="4" t="n"/>
-      <c r="AT2" s="4" t="n"/>
-      <c r="AU2" s="4" t="n"/>
-      <c r="AV2" s="4" t="n"/>
-      <c r="AW2" s="4" t="n"/>
-      <c r="AX2" s="4" t="n"/>
-      <c r="AY2" s="4" t="n"/>
-      <c r="AZ2" s="4" t="n"/>
-      <c r="BA2" s="4" t="n"/>
-      <c r="BB2" s="4" t="n"/>
-      <c r="BC2" s="4" t="n"/>
-      <c r="BD2" s="4" t="n"/>
-      <c r="BE2" s="4" t="n"/>
-      <c r="BF2" s="4" t="n"/>
-      <c r="BG2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="n"/>
@@ -10069,44 +8737,6 @@
       <c r="S3" s="4" t="n"/>
       <c r="T3" s="4" t="n"/>
       <c r="U3" s="4" t="n"/>
-      <c r="V3" s="4" t="n"/>
-      <c r="W3" s="4" t="n"/>
-      <c r="X3" s="4" t="n"/>
-      <c r="Y3" s="4" t="n"/>
-      <c r="Z3" s="4" t="n"/>
-      <c r="AA3" s="4" t="n"/>
-      <c r="AB3" s="4" t="n"/>
-      <c r="AC3" s="4" t="n"/>
-      <c r="AD3" s="4" t="n"/>
-      <c r="AE3" s="4" t="n"/>
-      <c r="AF3" s="4" t="n"/>
-      <c r="AG3" s="4" t="n"/>
-      <c r="AH3" s="4" t="n"/>
-      <c r="AI3" s="4" t="n"/>
-      <c r="AJ3" s="4" t="n"/>
-      <c r="AK3" s="4" t="n"/>
-      <c r="AL3" s="4" t="n"/>
-      <c r="AM3" s="4" t="n"/>
-      <c r="AN3" s="4" t="n"/>
-      <c r="AO3" s="4" t="n"/>
-      <c r="AP3" s="4" t="n"/>
-      <c r="AQ3" s="4" t="n"/>
-      <c r="AR3" s="4" t="n"/>
-      <c r="AS3" s="4" t="n"/>
-      <c r="AT3" s="4" t="n"/>
-      <c r="AU3" s="4" t="n"/>
-      <c r="AV3" s="4" t="n"/>
-      <c r="AW3" s="4" t="n"/>
-      <c r="AX3" s="4" t="n"/>
-      <c r="AY3" s="4" t="n"/>
-      <c r="AZ3" s="4" t="n"/>
-      <c r="BA3" s="4" t="n"/>
-      <c r="BB3" s="4" t="n"/>
-      <c r="BC3" s="4" t="n"/>
-      <c r="BD3" s="4" t="n"/>
-      <c r="BE3" s="4" t="n"/>
-      <c r="BF3" s="4" t="n"/>
-      <c r="BG3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -10127,65 +8757,27 @@
       <c r="D4" s="4" t="n"/>
       <c r="E4" s="4" t="n"/>
       <c r="F4" s="4" t="n"/>
-      <c r="G4" s="4" t="n"/>
+      <c r="G4" s="4" t="n">
+        <v>24.99</v>
+      </c>
       <c r="H4" s="4" t="n"/>
-      <c r="I4" s="4" t="n"/>
+      <c r="I4" s="4" t="n">
+        <v>24.59</v>
+      </c>
       <c r="J4" s="4" t="n"/>
       <c r="K4" s="4" t="n"/>
-      <c r="L4" s="4" t="n"/>
+      <c r="L4" s="4" t="n">
+        <v>24.59</v>
+      </c>
       <c r="M4" s="4" t="n"/>
-      <c r="N4" s="4" t="n">
-        <v>24.99</v>
-      </c>
+      <c r="N4" s="4" t="n"/>
       <c r="O4" s="4" t="n"/>
       <c r="P4" s="4" t="n"/>
       <c r="Q4" s="4" t="n"/>
-      <c r="R4" s="4" t="n">
-        <v>24.59</v>
-      </c>
+      <c r="R4" s="4" t="n"/>
       <c r="S4" s="4" t="n"/>
       <c r="T4" s="4" t="n"/>
       <c r="U4" s="4" t="n"/>
-      <c r="V4" s="4" t="n"/>
-      <c r="W4" s="4" t="n">
-        <v>24.59</v>
-      </c>
-      <c r="X4" s="4" t="n"/>
-      <c r="Y4" s="4" t="n"/>
-      <c r="Z4" s="4" t="n"/>
-      <c r="AA4" s="4" t="n"/>
-      <c r="AB4" s="4" t="n"/>
-      <c r="AC4" s="4" t="n"/>
-      <c r="AD4" s="4" t="n"/>
-      <c r="AE4" s="4" t="n"/>
-      <c r="AF4" s="4" t="n"/>
-      <c r="AG4" s="4" t="n"/>
-      <c r="AH4" s="4" t="n"/>
-      <c r="AI4" s="4" t="n"/>
-      <c r="AJ4" s="4" t="n"/>
-      <c r="AK4" s="4" t="n"/>
-      <c r="AL4" s="4" t="n"/>
-      <c r="AM4" s="4" t="n"/>
-      <c r="AN4" s="4" t="n"/>
-      <c r="AO4" s="4" t="n"/>
-      <c r="AP4" s="4" t="n"/>
-      <c r="AQ4" s="4" t="n"/>
-      <c r="AR4" s="4" t="n"/>
-      <c r="AS4" s="4" t="n"/>
-      <c r="AT4" s="4" t="n"/>
-      <c r="AU4" s="4" t="n"/>
-      <c r="AV4" s="4" t="n"/>
-      <c r="AW4" s="4" t="n"/>
-      <c r="AX4" s="4" t="n"/>
-      <c r="AY4" s="4" t="n"/>
-      <c r="AZ4" s="4" t="n"/>
-      <c r="BA4" s="4" t="n"/>
-      <c r="BB4" s="4" t="n"/>
-      <c r="BC4" s="4" t="n"/>
-      <c r="BD4" s="4" t="n"/>
-      <c r="BE4" s="4" t="n"/>
-      <c r="BF4" s="4" t="n"/>
-      <c r="BG4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -10206,65 +8798,27 @@
       <c r="D5" s="4" t="n"/>
       <c r="E5" s="4" t="n"/>
       <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
+      <c r="G5" s="4" t="n">
+        <v>22.5</v>
+      </c>
       <c r="H5" s="4" t="n"/>
       <c r="I5" s="4" t="n"/>
       <c r="J5" s="4" t="n"/>
-      <c r="K5" s="4" t="n"/>
+      <c r="K5" s="4" t="n">
+        <v>22.35</v>
+      </c>
       <c r="L5" s="4" t="n"/>
       <c r="M5" s="4" t="n"/>
-      <c r="N5" s="4" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="N5" s="4" t="n"/>
       <c r="O5" s="4" t="n"/>
-      <c r="P5" s="4" t="n"/>
+      <c r="P5" s="4" t="n">
+        <v>22.39</v>
+      </c>
       <c r="Q5" s="4" t="n"/>
       <c r="R5" s="4" t="n"/>
       <c r="S5" s="4" t="n"/>
       <c r="T5" s="4" t="n"/>
-      <c r="U5" s="4" t="n">
-        <v>22.35</v>
-      </c>
-      <c r="V5" s="4" t="n"/>
-      <c r="W5" s="4" t="n"/>
-      <c r="X5" s="4" t="n"/>
-      <c r="Y5" s="4" t="n"/>
-      <c r="Z5" s="4" t="n"/>
-      <c r="AA5" s="4" t="n"/>
-      <c r="AB5" s="4" t="n"/>
-      <c r="AC5" s="4" t="n">
-        <v>22.39</v>
-      </c>
-      <c r="AD5" s="4" t="n"/>
-      <c r="AE5" s="4" t="n"/>
-      <c r="AF5" s="4" t="n"/>
-      <c r="AG5" s="4" t="n"/>
-      <c r="AH5" s="4" t="n"/>
-      <c r="AI5" s="4" t="n"/>
-      <c r="AJ5" s="4" t="n"/>
-      <c r="AK5" s="4" t="n"/>
-      <c r="AL5" s="4" t="n"/>
-      <c r="AM5" s="4" t="n"/>
-      <c r="AN5" s="4" t="n"/>
-      <c r="AO5" s="4" t="n"/>
-      <c r="AP5" s="4" t="n"/>
-      <c r="AQ5" s="4" t="n"/>
-      <c r="AR5" s="4" t="n"/>
-      <c r="AS5" s="4" t="n"/>
-      <c r="AT5" s="4" t="n"/>
-      <c r="AU5" s="4" t="n"/>
-      <c r="AV5" s="4" t="n"/>
-      <c r="AW5" s="4" t="n"/>
-      <c r="AX5" s="4" t="n"/>
-      <c r="AY5" s="4" t="n"/>
-      <c r="AZ5" s="4" t="n"/>
-      <c r="BA5" s="4" t="n"/>
-      <c r="BB5" s="4" t="n"/>
-      <c r="BC5" s="4" t="n"/>
-      <c r="BD5" s="4" t="n"/>
-      <c r="BE5" s="4" t="n"/>
-      <c r="BF5" s="4" t="n"/>
-      <c r="BG5" s="4" t="n"/>
+      <c r="U5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -10287,69 +8841,31 @@
         <v>22.39</v>
       </c>
       <c r="F6" s="4" t="n"/>
-      <c r="G6" s="4" t="n"/>
-      <c r="H6" s="4" t="n"/>
-      <c r="I6" s="4" t="n"/>
+      <c r="G6" s="4" t="n">
+        <v>23.58</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>22.54</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>22.52</v>
+      </c>
       <c r="J6" s="4" t="n"/>
-      <c r="K6" s="4" t="n"/>
+      <c r="K6" s="4" t="n">
+        <v>22.57</v>
+      </c>
       <c r="L6" s="4" t="n"/>
       <c r="M6" s="4" t="n"/>
-      <c r="N6" s="4" t="n">
-        <v>23.58</v>
-      </c>
+      <c r="N6" s="4" t="n"/>
       <c r="O6" s="4" t="n"/>
       <c r="P6" s="4" t="n">
-        <v>22.54</v>
+        <v>23.25</v>
       </c>
       <c r="Q6" s="4" t="n"/>
-      <c r="R6" s="4" t="n">
-        <v>22.52</v>
-      </c>
+      <c r="R6" s="4" t="n"/>
       <c r="S6" s="4" t="n"/>
       <c r="T6" s="4" t="n"/>
-      <c r="U6" s="4" t="n">
-        <v>22.57</v>
-      </c>
-      <c r="V6" s="4" t="n"/>
-      <c r="W6" s="4" t="n"/>
-      <c r="X6" s="4" t="n"/>
-      <c r="Y6" s="4" t="n"/>
-      <c r="Z6" s="4" t="n"/>
-      <c r="AA6" s="4" t="n"/>
-      <c r="AB6" s="4" t="n"/>
-      <c r="AC6" s="4" t="n">
-        <v>23.25</v>
-      </c>
-      <c r="AD6" s="4" t="n"/>
-      <c r="AE6" s="4" t="n"/>
-      <c r="AF6" s="4" t="n"/>
-      <c r="AG6" s="4" t="n"/>
-      <c r="AH6" s="4" t="n"/>
-      <c r="AI6" s="4" t="n"/>
-      <c r="AJ6" s="4" t="n"/>
-      <c r="AK6" s="4" t="n"/>
-      <c r="AL6" s="4" t="n"/>
-      <c r="AM6" s="4" t="n"/>
-      <c r="AN6" s="4" t="n"/>
-      <c r="AO6" s="4" t="n"/>
-      <c r="AP6" s="4" t="n"/>
-      <c r="AQ6" s="4" t="n"/>
-      <c r="AR6" s="4" t="n"/>
-      <c r="AS6" s="4" t="n"/>
-      <c r="AT6" s="4" t="n"/>
-      <c r="AU6" s="4" t="n"/>
-      <c r="AV6" s="4" t="n"/>
-      <c r="AW6" s="4" t="n"/>
-      <c r="AX6" s="4" t="n"/>
-      <c r="AY6" s="4" t="n"/>
-      <c r="AZ6" s="4" t="n"/>
-      <c r="BA6" s="4" t="n"/>
-      <c r="BB6" s="4" t="n"/>
-      <c r="BC6" s="4" t="n"/>
-      <c r="BD6" s="4" t="n"/>
-      <c r="BE6" s="4" t="n"/>
-      <c r="BF6" s="4" t="n"/>
-      <c r="BG6" s="4" t="n"/>
+      <c r="U6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -10369,72 +8885,34 @@
       </c>
       <c r="D7" s="4" t="n"/>
       <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="n"/>
+      <c r="F7" s="4" t="n">
+        <v>18.75</v>
+      </c>
       <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n"/>
+      <c r="H7" s="4" t="n">
+        <v>18.45</v>
+      </c>
       <c r="I7" s="4" t="n"/>
       <c r="J7" s="4" t="n"/>
-      <c r="K7" s="4" t="n"/>
-      <c r="L7" s="4" t="n">
-        <v>18.75</v>
-      </c>
+      <c r="K7" s="4" t="n">
+        <v>18.19</v>
+      </c>
+      <c r="L7" s="4" t="n"/>
       <c r="M7" s="4" t="n"/>
       <c r="N7" s="4" t="n"/>
-      <c r="O7" s="4" t="n"/>
+      <c r="O7" s="4" t="n">
+        <v>18.39</v>
+      </c>
       <c r="P7" s="4" t="n">
-        <v>18.45</v>
-      </c>
-      <c r="Q7" s="4" t="n"/>
+        <v>18.7</v>
+      </c>
+      <c r="Q7" s="4" t="n">
+        <v>18.7</v>
+      </c>
       <c r="R7" s="4" t="n"/>
       <c r="S7" s="4" t="n"/>
       <c r="T7" s="4" t="n"/>
-      <c r="U7" s="4" t="n">
-        <v>18.19</v>
-      </c>
-      <c r="V7" s="4" t="n"/>
-      <c r="W7" s="4" t="n"/>
-      <c r="X7" s="4" t="n"/>
-      <c r="Y7" s="4" t="n"/>
-      <c r="Z7" s="4" t="n"/>
-      <c r="AA7" s="4" t="n">
-        <v>18.39</v>
-      </c>
-      <c r="AB7" s="4" t="n"/>
-      <c r="AC7" s="4" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="AD7" s="4" t="n"/>
-      <c r="AE7" s="4" t="n"/>
-      <c r="AF7" s="4" t="n"/>
-      <c r="AG7" s="4" t="n"/>
-      <c r="AH7" s="4" t="n"/>
-      <c r="AI7" s="4" t="n"/>
-      <c r="AJ7" s="4" t="n">
-        <v>18.7</v>
-      </c>
-      <c r="AK7" s="4" t="n"/>
-      <c r="AL7" s="4" t="n"/>
-      <c r="AM7" s="4" t="n"/>
-      <c r="AN7" s="4" t="n"/>
-      <c r="AO7" s="4" t="n"/>
-      <c r="AP7" s="4" t="n"/>
-      <c r="AQ7" s="4" t="n"/>
-      <c r="AR7" s="4" t="n"/>
-      <c r="AS7" s="4" t="n"/>
-      <c r="AT7" s="4" t="n"/>
-      <c r="AU7" s="4" t="n"/>
-      <c r="AV7" s="4" t="n"/>
-      <c r="AW7" s="4" t="n"/>
-      <c r="AX7" s="4" t="n"/>
-      <c r="AY7" s="4" t="n"/>
-      <c r="AZ7" s="4" t="n"/>
-      <c r="BA7" s="4" t="n"/>
-      <c r="BB7" s="4" t="n"/>
-      <c r="BC7" s="4" t="n"/>
-      <c r="BD7" s="4" t="n"/>
-      <c r="BE7" s="4" t="n"/>
-      <c r="BF7" s="4" t="n"/>
-      <c r="BG7" s="4" t="n"/>
+      <c r="U7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -10470,44 +8948,6 @@
       <c r="S8" s="4" t="n"/>
       <c r="T8" s="4" t="n"/>
       <c r="U8" s="4" t="n"/>
-      <c r="V8" s="4" t="n"/>
-      <c r="W8" s="4" t="n"/>
-      <c r="X8" s="4" t="n"/>
-      <c r="Y8" s="4" t="n"/>
-      <c r="Z8" s="4" t="n"/>
-      <c r="AA8" s="4" t="n"/>
-      <c r="AB8" s="4" t="n"/>
-      <c r="AC8" s="4" t="n"/>
-      <c r="AD8" s="4" t="n"/>
-      <c r="AE8" s="4" t="n"/>
-      <c r="AF8" s="4" t="n"/>
-      <c r="AG8" s="4" t="n"/>
-      <c r="AH8" s="4" t="n"/>
-      <c r="AI8" s="4" t="n"/>
-      <c r="AJ8" s="4" t="n"/>
-      <c r="AK8" s="4" t="n"/>
-      <c r="AL8" s="4" t="n"/>
-      <c r="AM8" s="4" t="n"/>
-      <c r="AN8" s="4" t="n"/>
-      <c r="AO8" s="4" t="n"/>
-      <c r="AP8" s="4" t="n"/>
-      <c r="AQ8" s="4" t="n"/>
-      <c r="AR8" s="4" t="n"/>
-      <c r="AS8" s="4" t="n"/>
-      <c r="AT8" s="4" t="n"/>
-      <c r="AU8" s="4" t="n"/>
-      <c r="AV8" s="4" t="n"/>
-      <c r="AW8" s="4" t="n"/>
-      <c r="AX8" s="4" t="n"/>
-      <c r="AY8" s="4" t="n"/>
-      <c r="AZ8" s="4" t="n"/>
-      <c r="BA8" s="4" t="n"/>
-      <c r="BB8" s="4" t="n"/>
-      <c r="BC8" s="4" t="n"/>
-      <c r="BD8" s="4" t="n"/>
-      <c r="BE8" s="4" t="n"/>
-      <c r="BF8" s="4" t="n"/>
-      <c r="BG8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -10543,44 +8983,6 @@
       <c r="S9" s="4" t="n"/>
       <c r="T9" s="4" t="n"/>
       <c r="U9" s="4" t="n"/>
-      <c r="V9" s="4" t="n"/>
-      <c r="W9" s="4" t="n"/>
-      <c r="X9" s="4" t="n"/>
-      <c r="Y9" s="4" t="n"/>
-      <c r="Z9" s="4" t="n"/>
-      <c r="AA9" s="4" t="n"/>
-      <c r="AB9" s="4" t="n"/>
-      <c r="AC9" s="4" t="n"/>
-      <c r="AD9" s="4" t="n"/>
-      <c r="AE9" s="4" t="n"/>
-      <c r="AF9" s="4" t="n"/>
-      <c r="AG9" s="4" t="n"/>
-      <c r="AH9" s="4" t="n"/>
-      <c r="AI9" s="4" t="n"/>
-      <c r="AJ9" s="4" t="n"/>
-      <c r="AK9" s="4" t="n"/>
-      <c r="AL9" s="4" t="n"/>
-      <c r="AM9" s="4" t="n"/>
-      <c r="AN9" s="4" t="n"/>
-      <c r="AO9" s="4" t="n"/>
-      <c r="AP9" s="4" t="n"/>
-      <c r="AQ9" s="4" t="n"/>
-      <c r="AR9" s="4" t="n"/>
-      <c r="AS9" s="4" t="n"/>
-      <c r="AT9" s="4" t="n"/>
-      <c r="AU9" s="4" t="n"/>
-      <c r="AV9" s="4" t="n"/>
-      <c r="AW9" s="4" t="n"/>
-      <c r="AX9" s="4" t="n"/>
-      <c r="AY9" s="4" t="n"/>
-      <c r="AZ9" s="4" t="n"/>
-      <c r="BA9" s="4" t="n"/>
-      <c r="BB9" s="4" t="n"/>
-      <c r="BC9" s="4" t="n"/>
-      <c r="BD9" s="4" t="n"/>
-      <c r="BE9" s="4" t="n"/>
-      <c r="BF9" s="4" t="n"/>
-      <c r="BG9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n"/>
@@ -10614,44 +9016,6 @@
       <c r="S10" s="4" t="n"/>
       <c r="T10" s="4" t="n"/>
       <c r="U10" s="4" t="n"/>
-      <c r="V10" s="4" t="n"/>
-      <c r="W10" s="4" t="n"/>
-      <c r="X10" s="4" t="n"/>
-      <c r="Y10" s="4" t="n"/>
-      <c r="Z10" s="4" t="n"/>
-      <c r="AA10" s="4" t="n"/>
-      <c r="AB10" s="4" t="n"/>
-      <c r="AC10" s="4" t="n"/>
-      <c r="AD10" s="4" t="n"/>
-      <c r="AE10" s="4" t="n"/>
-      <c r="AF10" s="4" t="n"/>
-      <c r="AG10" s="4" t="n"/>
-      <c r="AH10" s="4" t="n"/>
-      <c r="AI10" s="4" t="n"/>
-      <c r="AJ10" s="4" t="n"/>
-      <c r="AK10" s="4" t="n"/>
-      <c r="AL10" s="4" t="n"/>
-      <c r="AM10" s="4" t="n"/>
-      <c r="AN10" s="4" t="n"/>
-      <c r="AO10" s="4" t="n"/>
-      <c r="AP10" s="4" t="n"/>
-      <c r="AQ10" s="4" t="n"/>
-      <c r="AR10" s="4" t="n"/>
-      <c r="AS10" s="4" t="n"/>
-      <c r="AT10" s="4" t="n"/>
-      <c r="AU10" s="4" t="n"/>
-      <c r="AV10" s="4" t="n"/>
-      <c r="AW10" s="4" t="n"/>
-      <c r="AX10" s="4" t="n"/>
-      <c r="AY10" s="4" t="n"/>
-      <c r="AZ10" s="4" t="n"/>
-      <c r="BA10" s="4" t="n"/>
-      <c r="BB10" s="4" t="n"/>
-      <c r="BC10" s="4" t="n"/>
-      <c r="BD10" s="4" t="n"/>
-      <c r="BE10" s="4" t="n"/>
-      <c r="BF10" s="4" t="n"/>
-      <c r="BG10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -10673,66 +9037,28 @@
       <c r="E11" s="4" t="n"/>
       <c r="F11" s="4" t="n"/>
       <c r="G11" s="4" t="n"/>
-      <c r="H11" s="4" t="n"/>
-      <c r="I11" s="4" t="n"/>
+      <c r="H11" s="4" t="n">
+        <v>29.39</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>29.38</v>
+      </c>
       <c r="J11" s="4" t="n"/>
-      <c r="K11" s="4" t="n"/>
+      <c r="K11" s="4" t="n">
+        <v>29.45</v>
+      </c>
       <c r="L11" s="4" t="n"/>
       <c r="M11" s="4" t="n"/>
-      <c r="N11" s="4" t="n"/>
+      <c r="N11" s="4" t="n">
+        <v>30.59</v>
+      </c>
       <c r="O11" s="4" t="n"/>
-      <c r="P11" s="4" t="n">
-        <v>29.39</v>
-      </c>
+      <c r="P11" s="4" t="n"/>
       <c r="Q11" s="4" t="n"/>
-      <c r="R11" s="4" t="n">
-        <v>29.38</v>
-      </c>
+      <c r="R11" s="4" t="n"/>
       <c r="S11" s="4" t="n"/>
       <c r="T11" s="4" t="n"/>
-      <c r="U11" s="4" t="n">
-        <v>29.45</v>
-      </c>
-      <c r="V11" s="4" t="n"/>
-      <c r="W11" s="4" t="n"/>
-      <c r="X11" s="4" t="n"/>
-      <c r="Y11" s="4" t="n"/>
-      <c r="Z11" s="4" t="n">
-        <v>30.59</v>
-      </c>
-      <c r="AA11" s="4" t="n"/>
-      <c r="AB11" s="4" t="n"/>
-      <c r="AC11" s="4" t="n"/>
-      <c r="AD11" s="4" t="n"/>
-      <c r="AE11" s="4" t="n"/>
-      <c r="AF11" s="4" t="n"/>
-      <c r="AG11" s="4" t="n"/>
-      <c r="AH11" s="4" t="n"/>
-      <c r="AI11" s="4" t="n"/>
-      <c r="AJ11" s="4" t="n"/>
-      <c r="AK11" s="4" t="n"/>
-      <c r="AL11" s="4" t="n"/>
-      <c r="AM11" s="4" t="n"/>
-      <c r="AN11" s="4" t="n"/>
-      <c r="AO11" s="4" t="n"/>
-      <c r="AP11" s="4" t="n"/>
-      <c r="AQ11" s="4" t="n"/>
-      <c r="AR11" s="4" t="n"/>
-      <c r="AS11" s="4" t="n"/>
-      <c r="AT11" s="4" t="n"/>
-      <c r="AU11" s="4" t="n"/>
-      <c r="AV11" s="4" t="n"/>
-      <c r="AW11" s="4" t="n"/>
-      <c r="AX11" s="4" t="n"/>
-      <c r="AY11" s="4" t="n"/>
-      <c r="AZ11" s="4" t="n"/>
-      <c r="BA11" s="4" t="n"/>
-      <c r="BB11" s="4" t="n"/>
-      <c r="BC11" s="4" t="n"/>
-      <c r="BD11" s="4" t="n"/>
-      <c r="BE11" s="4" t="n"/>
-      <c r="BF11" s="4" t="n"/>
-      <c r="BG11" s="4" t="n"/>
+      <c r="U11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -10759,57 +9085,19 @@
       <c r="J12" s="4" t="n"/>
       <c r="K12" s="4" t="n"/>
       <c r="L12" s="4" t="n"/>
-      <c r="M12" s="4" t="n"/>
+      <c r="M12" s="4" t="n">
+        <v>20.4</v>
+      </c>
       <c r="N12" s="4" t="n"/>
       <c r="O12" s="4" t="n"/>
       <c r="P12" s="4" t="n"/>
       <c r="Q12" s="4" t="n"/>
       <c r="R12" s="4" t="n"/>
       <c r="S12" s="4" t="n"/>
-      <c r="T12" s="4" t="n"/>
+      <c r="T12" s="4" t="n">
+        <v>21.5</v>
+      </c>
       <c r="U12" s="4" t="n"/>
-      <c r="V12" s="4" t="n"/>
-      <c r="W12" s="4" t="n"/>
-      <c r="X12" s="4" t="n"/>
-      <c r="Y12" s="4" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="Z12" s="4" t="n"/>
-      <c r="AA12" s="4" t="n"/>
-      <c r="AB12" s="4" t="n"/>
-      <c r="AC12" s="4" t="n"/>
-      <c r="AD12" s="4" t="n"/>
-      <c r="AE12" s="4" t="n"/>
-      <c r="AF12" s="4" t="n"/>
-      <c r="AG12" s="4" t="n"/>
-      <c r="AH12" s="4" t="n"/>
-      <c r="AI12" s="4" t="n"/>
-      <c r="AJ12" s="4" t="n"/>
-      <c r="AK12" s="4" t="n"/>
-      <c r="AL12" s="4" t="n"/>
-      <c r="AM12" s="4" t="n"/>
-      <c r="AN12" s="4" t="n"/>
-      <c r="AO12" s="4" t="n"/>
-      <c r="AP12" s="4" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="AQ12" s="4" t="n"/>
-      <c r="AR12" s="4" t="n"/>
-      <c r="AS12" s="4" t="n"/>
-      <c r="AT12" s="4" t="n"/>
-      <c r="AU12" s="4" t="n"/>
-      <c r="AV12" s="4" t="n"/>
-      <c r="AW12" s="4" t="n"/>
-      <c r="AX12" s="4" t="n"/>
-      <c r="AY12" s="4" t="n"/>
-      <c r="AZ12" s="4" t="n"/>
-      <c r="BA12" s="4" t="n"/>
-      <c r="BB12" s="4" t="n"/>
-      <c r="BC12" s="4" t="n"/>
-      <c r="BD12" s="4" t="n"/>
-      <c r="BE12" s="4" t="n"/>
-      <c r="BF12" s="4" t="n"/>
-      <c r="BG12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -10830,16 +9118,16 @@
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
       <c r="F13" s="4" t="n"/>
-      <c r="G13" s="4" t="n"/>
+      <c r="G13" s="4" t="n">
+        <v>21.39</v>
+      </c>
       <c r="H13" s="4" t="n"/>
       <c r="I13" s="4" t="n"/>
       <c r="J13" s="4" t="n"/>
       <c r="K13" s="4" t="n"/>
       <c r="L13" s="4" t="n"/>
       <c r="M13" s="4" t="n"/>
-      <c r="N13" s="4" t="n">
-        <v>21.39</v>
-      </c>
+      <c r="N13" s="4" t="n"/>
       <c r="O13" s="4" t="n"/>
       <c r="P13" s="4" t="n"/>
       <c r="Q13" s="4" t="n"/>
@@ -10847,44 +9135,6 @@
       <c r="S13" s="4" t="n"/>
       <c r="T13" s="4" t="n"/>
       <c r="U13" s="4" t="n"/>
-      <c r="V13" s="4" t="n"/>
-      <c r="W13" s="4" t="n"/>
-      <c r="X13" s="4" t="n"/>
-      <c r="Y13" s="4" t="n"/>
-      <c r="Z13" s="4" t="n"/>
-      <c r="AA13" s="4" t="n"/>
-      <c r="AB13" s="4" t="n"/>
-      <c r="AC13" s="4" t="n"/>
-      <c r="AD13" s="4" t="n"/>
-      <c r="AE13" s="4" t="n"/>
-      <c r="AF13" s="4" t="n"/>
-      <c r="AG13" s="4" t="n"/>
-      <c r="AH13" s="4" t="n"/>
-      <c r="AI13" s="4" t="n"/>
-      <c r="AJ13" s="4" t="n"/>
-      <c r="AK13" s="4" t="n"/>
-      <c r="AL13" s="4" t="n"/>
-      <c r="AM13" s="4" t="n"/>
-      <c r="AN13" s="4" t="n"/>
-      <c r="AO13" s="4" t="n"/>
-      <c r="AP13" s="4" t="n"/>
-      <c r="AQ13" s="4" t="n"/>
-      <c r="AR13" s="4" t="n"/>
-      <c r="AS13" s="4" t="n"/>
-      <c r="AT13" s="4" t="n"/>
-      <c r="AU13" s="4" t="n"/>
-      <c r="AV13" s="4" t="n"/>
-      <c r="AW13" s="4" t="n"/>
-      <c r="AX13" s="4" t="n"/>
-      <c r="AY13" s="4" t="n"/>
-      <c r="AZ13" s="4" t="n"/>
-      <c r="BA13" s="4" t="n"/>
-      <c r="BB13" s="4" t="n"/>
-      <c r="BC13" s="4" t="n"/>
-      <c r="BD13" s="4" t="n"/>
-      <c r="BE13" s="4" t="n"/>
-      <c r="BF13" s="4" t="n"/>
-      <c r="BG13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n"/>
@@ -10913,49 +9163,11 @@
       <c r="P14" s="4" t="n"/>
       <c r="Q14" s="4" t="n"/>
       <c r="R14" s="4" t="n"/>
-      <c r="S14" s="4" t="n"/>
+      <c r="S14" s="4" t="n">
+        <v>25.5</v>
+      </c>
       <c r="T14" s="4" t="n"/>
       <c r="U14" s="4" t="n"/>
-      <c r="V14" s="4" t="n"/>
-      <c r="W14" s="4" t="n"/>
-      <c r="X14" s="4" t="n"/>
-      <c r="Y14" s="4" t="n"/>
-      <c r="Z14" s="4" t="n"/>
-      <c r="AA14" s="4" t="n"/>
-      <c r="AB14" s="4" t="n"/>
-      <c r="AC14" s="4" t="n"/>
-      <c r="AD14" s="4" t="n"/>
-      <c r="AE14" s="4" t="n"/>
-      <c r="AF14" s="4" t="n"/>
-      <c r="AG14" s="4" t="n"/>
-      <c r="AH14" s="4" t="n"/>
-      <c r="AI14" s="4" t="n"/>
-      <c r="AJ14" s="4" t="n"/>
-      <c r="AK14" s="4" t="n"/>
-      <c r="AL14" s="4" t="n"/>
-      <c r="AM14" s="4" t="n"/>
-      <c r="AN14" s="4" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="AO14" s="4" t="n"/>
-      <c r="AP14" s="4" t="n"/>
-      <c r="AQ14" s="4" t="n"/>
-      <c r="AR14" s="4" t="n"/>
-      <c r="AS14" s="4" t="n"/>
-      <c r="AT14" s="4" t="n"/>
-      <c r="AU14" s="4" t="n"/>
-      <c r="AV14" s="4" t="n"/>
-      <c r="AW14" s="4" t="n"/>
-      <c r="AX14" s="4" t="n"/>
-      <c r="AY14" s="4" t="n"/>
-      <c r="AZ14" s="4" t="n"/>
-      <c r="BA14" s="4" t="n"/>
-      <c r="BB14" s="4" t="n"/>
-      <c r="BC14" s="4" t="n"/>
-      <c r="BD14" s="4" t="n"/>
-      <c r="BE14" s="4" t="n"/>
-      <c r="BF14" s="4" t="n"/>
-      <c r="BG14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -10976,16 +9188,16 @@
       <c r="D15" s="4" t="n"/>
       <c r="E15" s="4" t="n"/>
       <c r="F15" s="4" t="n"/>
-      <c r="G15" s="4" t="n"/>
+      <c r="G15" s="4" t="n">
+        <v>14.7</v>
+      </c>
       <c r="H15" s="4" t="n"/>
       <c r="I15" s="4" t="n"/>
       <c r="J15" s="4" t="n"/>
       <c r="K15" s="4" t="n"/>
       <c r="L15" s="4" t="n"/>
       <c r="M15" s="4" t="n"/>
-      <c r="N15" s="4" t="n">
-        <v>14.7</v>
-      </c>
+      <c r="N15" s="4" t="n"/>
       <c r="O15" s="4" t="n"/>
       <c r="P15" s="4" t="n"/>
       <c r="Q15" s="4" t="n"/>
@@ -10993,44 +9205,6 @@
       <c r="S15" s="4" t="n"/>
       <c r="T15" s="4" t="n"/>
       <c r="U15" s="4" t="n"/>
-      <c r="V15" s="4" t="n"/>
-      <c r="W15" s="4" t="n"/>
-      <c r="X15" s="4" t="n"/>
-      <c r="Y15" s="4" t="n"/>
-      <c r="Z15" s="4" t="n"/>
-      <c r="AA15" s="4" t="n"/>
-      <c r="AB15" s="4" t="n"/>
-      <c r="AC15" s="4" t="n"/>
-      <c r="AD15" s="4" t="n"/>
-      <c r="AE15" s="4" t="n"/>
-      <c r="AF15" s="4" t="n"/>
-      <c r="AG15" s="4" t="n"/>
-      <c r="AH15" s="4" t="n"/>
-      <c r="AI15" s="4" t="n"/>
-      <c r="AJ15" s="4" t="n"/>
-      <c r="AK15" s="4" t="n"/>
-      <c r="AL15" s="4" t="n"/>
-      <c r="AM15" s="4" t="n"/>
-      <c r="AN15" s="4" t="n"/>
-      <c r="AO15" s="4" t="n"/>
-      <c r="AP15" s="4" t="n"/>
-      <c r="AQ15" s="4" t="n"/>
-      <c r="AR15" s="4" t="n"/>
-      <c r="AS15" s="4" t="n"/>
-      <c r="AT15" s="4" t="n"/>
-      <c r="AU15" s="4" t="n"/>
-      <c r="AV15" s="4" t="n"/>
-      <c r="AW15" s="4" t="n"/>
-      <c r="AX15" s="4" t="n"/>
-      <c r="AY15" s="4" t="n"/>
-      <c r="AZ15" s="4" t="n"/>
-      <c r="BA15" s="4" t="n"/>
-      <c r="BB15" s="4" t="n"/>
-      <c r="BC15" s="4" t="n"/>
-      <c r="BD15" s="4" t="n"/>
-      <c r="BE15" s="4" t="n"/>
-      <c r="BF15" s="4" t="n"/>
-      <c r="BG15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
@@ -11053,7 +9227,9 @@
       <c r="J16" s="4" t="n"/>
       <c r="K16" s="4" t="n"/>
       <c r="L16" s="4" t="n"/>
-      <c r="M16" s="4" t="n"/>
+      <c r="M16" s="4" t="n">
+        <v>20.6</v>
+      </c>
       <c r="N16" s="4" t="n"/>
       <c r="O16" s="4" t="n"/>
       <c r="P16" s="4" t="n"/>
@@ -11062,46 +9238,6 @@
       <c r="S16" s="4" t="n"/>
       <c r="T16" s="4" t="n"/>
       <c r="U16" s="4" t="n"/>
-      <c r="V16" s="4" t="n"/>
-      <c r="W16" s="4" t="n"/>
-      <c r="X16" s="4" t="n"/>
-      <c r="Y16" s="4" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="Z16" s="4" t="n"/>
-      <c r="AA16" s="4" t="n"/>
-      <c r="AB16" s="4" t="n"/>
-      <c r="AC16" s="4" t="n"/>
-      <c r="AD16" s="4" t="n"/>
-      <c r="AE16" s="4" t="n"/>
-      <c r="AF16" s="4" t="n"/>
-      <c r="AG16" s="4" t="n"/>
-      <c r="AH16" s="4" t="n"/>
-      <c r="AI16" s="4" t="n"/>
-      <c r="AJ16" s="4" t="n"/>
-      <c r="AK16" s="4" t="n"/>
-      <c r="AL16" s="4" t="n"/>
-      <c r="AM16" s="4" t="n"/>
-      <c r="AN16" s="4" t="n"/>
-      <c r="AO16" s="4" t="n"/>
-      <c r="AP16" s="4" t="n"/>
-      <c r="AQ16" s="4" t="n"/>
-      <c r="AR16" s="4" t="n"/>
-      <c r="AS16" s="4" t="n"/>
-      <c r="AT16" s="4" t="n"/>
-      <c r="AU16" s="4" t="n"/>
-      <c r="AV16" s="4" t="n"/>
-      <c r="AW16" s="4" t="n"/>
-      <c r="AX16" s="4" t="n"/>
-      <c r="AY16" s="4" t="n"/>
-      <c r="AZ16" s="4" t="n"/>
-      <c r="BA16" s="4" t="n"/>
-      <c r="BB16" s="4" t="n"/>
-      <c r="BC16" s="4" t="n"/>
-      <c r="BD16" s="4" t="n"/>
-      <c r="BE16" s="4" t="n"/>
-      <c r="BF16" s="4" t="n"/>
-      <c r="BG16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
@@ -11121,62 +9257,24 @@
       <c r="G17" s="4" t="n"/>
       <c r="H17" s="4" t="n"/>
       <c r="I17" s="4" t="n"/>
-      <c r="J17" s="4" t="n"/>
+      <c r="J17" s="4" t="n">
+        <v>26.7</v>
+      </c>
       <c r="K17" s="4" t="n"/>
       <c r="L17" s="4" t="n"/>
-      <c r="M17" s="4" t="n"/>
+      <c r="M17" s="4" t="n">
+        <v>28</v>
+      </c>
       <c r="N17" s="4" t="n"/>
       <c r="O17" s="4" t="n"/>
       <c r="P17" s="4" t="n"/>
       <c r="Q17" s="4" t="n"/>
-      <c r="R17" s="4" t="n"/>
+      <c r="R17" s="4" t="n">
+        <v>29</v>
+      </c>
       <c r="S17" s="4" t="n"/>
-      <c r="T17" s="4" t="n">
-        <v>26.7</v>
-      </c>
+      <c r="T17" s="4" t="n"/>
       <c r="U17" s="4" t="n"/>
-      <c r="V17" s="4" t="n"/>
-      <c r="W17" s="4" t="n"/>
-      <c r="X17" s="4" t="n"/>
-      <c r="Y17" s="4" t="n">
-        <v>28</v>
-      </c>
-      <c r="Z17" s="4" t="n"/>
-      <c r="AA17" s="4" t="n"/>
-      <c r="AB17" s="4" t="n"/>
-      <c r="AC17" s="4" t="n"/>
-      <c r="AD17" s="4" t="n"/>
-      <c r="AE17" s="4" t="n"/>
-      <c r="AF17" s="4" t="n"/>
-      <c r="AG17" s="4" t="n"/>
-      <c r="AH17" s="4" t="n"/>
-      <c r="AI17" s="4" t="n"/>
-      <c r="AJ17" s="4" t="n"/>
-      <c r="AK17" s="4" t="n"/>
-      <c r="AL17" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="AM17" s="4" t="n"/>
-      <c r="AN17" s="4" t="n"/>
-      <c r="AO17" s="4" t="n"/>
-      <c r="AP17" s="4" t="n"/>
-      <c r="AQ17" s="4" t="n"/>
-      <c r="AR17" s="4" t="n"/>
-      <c r="AS17" s="4" t="n"/>
-      <c r="AT17" s="4" t="n"/>
-      <c r="AU17" s="4" t="n"/>
-      <c r="AV17" s="4" t="n"/>
-      <c r="AW17" s="4" t="n"/>
-      <c r="AX17" s="4" t="n"/>
-      <c r="AY17" s="4" t="n"/>
-      <c r="AZ17" s="4" t="n"/>
-      <c r="BA17" s="4" t="n"/>
-      <c r="BB17" s="4" t="n"/>
-      <c r="BC17" s="4" t="n"/>
-      <c r="BD17" s="4" t="n"/>
-      <c r="BE17" s="4" t="n"/>
-      <c r="BF17" s="4" t="n"/>
-      <c r="BG17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n"/>
@@ -11208,44 +9306,6 @@
       <c r="S18" s="4" t="n"/>
       <c r="T18" s="4" t="n"/>
       <c r="U18" s="4" t="n"/>
-      <c r="V18" s="4" t="n"/>
-      <c r="W18" s="4" t="n"/>
-      <c r="X18" s="4" t="n"/>
-      <c r="Y18" s="4" t="n"/>
-      <c r="Z18" s="4" t="n"/>
-      <c r="AA18" s="4" t="n"/>
-      <c r="AB18" s="4" t="n"/>
-      <c r="AC18" s="4" t="n"/>
-      <c r="AD18" s="4" t="n"/>
-      <c r="AE18" s="4" t="n"/>
-      <c r="AF18" s="4" t="n"/>
-      <c r="AG18" s="4" t="n"/>
-      <c r="AH18" s="4" t="n"/>
-      <c r="AI18" s="4" t="n"/>
-      <c r="AJ18" s="4" t="n"/>
-      <c r="AK18" s="4" t="n"/>
-      <c r="AL18" s="4" t="n"/>
-      <c r="AM18" s="4" t="n"/>
-      <c r="AN18" s="4" t="n"/>
-      <c r="AO18" s="4" t="n"/>
-      <c r="AP18" s="4" t="n"/>
-      <c r="AQ18" s="4" t="n"/>
-      <c r="AR18" s="4" t="n"/>
-      <c r="AS18" s="4" t="n"/>
-      <c r="AT18" s="4" t="n"/>
-      <c r="AU18" s="4" t="n"/>
-      <c r="AV18" s="4" t="n"/>
-      <c r="AW18" s="4" t="n"/>
-      <c r="AX18" s="4" t="n"/>
-      <c r="AY18" s="4" t="n"/>
-      <c r="AZ18" s="4" t="n"/>
-      <c r="BA18" s="4" t="n"/>
-      <c r="BB18" s="4" t="n"/>
-      <c r="BC18" s="4" t="n"/>
-      <c r="BD18" s="4" t="n"/>
-      <c r="BE18" s="4" t="n"/>
-      <c r="BF18" s="4" t="n"/>
-      <c r="BG18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -11281,44 +9341,6 @@
       <c r="S19" s="4" t="n"/>
       <c r="T19" s="4" t="n"/>
       <c r="U19" s="4" t="n"/>
-      <c r="V19" s="4" t="n"/>
-      <c r="W19" s="4" t="n"/>
-      <c r="X19" s="4" t="n"/>
-      <c r="Y19" s="4" t="n"/>
-      <c r="Z19" s="4" t="n"/>
-      <c r="AA19" s="4" t="n"/>
-      <c r="AB19" s="4" t="n"/>
-      <c r="AC19" s="4" t="n"/>
-      <c r="AD19" s="4" t="n"/>
-      <c r="AE19" s="4" t="n"/>
-      <c r="AF19" s="4" t="n"/>
-      <c r="AG19" s="4" t="n"/>
-      <c r="AH19" s="4" t="n"/>
-      <c r="AI19" s="4" t="n"/>
-      <c r="AJ19" s="4" t="n"/>
-      <c r="AK19" s="4" t="n"/>
-      <c r="AL19" s="4" t="n"/>
-      <c r="AM19" s="4" t="n"/>
-      <c r="AN19" s="4" t="n"/>
-      <c r="AO19" s="4" t="n"/>
-      <c r="AP19" s="4" t="n"/>
-      <c r="AQ19" s="4" t="n"/>
-      <c r="AR19" s="4" t="n"/>
-      <c r="AS19" s="4" t="n"/>
-      <c r="AT19" s="4" t="n"/>
-      <c r="AU19" s="4" t="n"/>
-      <c r="AV19" s="4" t="n"/>
-      <c r="AW19" s="4" t="n"/>
-      <c r="AX19" s="4" t="n"/>
-      <c r="AY19" s="4" t="n"/>
-      <c r="AZ19" s="4" t="n"/>
-      <c r="BA19" s="4" t="n"/>
-      <c r="BB19" s="4" t="n"/>
-      <c r="BC19" s="4" t="n"/>
-      <c r="BD19" s="4" t="n"/>
-      <c r="BE19" s="4" t="n"/>
-      <c r="BF19" s="4" t="n"/>
-      <c r="BG19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -11339,69 +9361,31 @@
       <c r="D20" s="4" t="n"/>
       <c r="E20" s="4" t="n"/>
       <c r="F20" s="4" t="n"/>
-      <c r="G20" s="4" t="n"/>
-      <c r="H20" s="4" t="n"/>
+      <c r="G20" s="4" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>18.69</v>
+      </c>
       <c r="I20" s="4" t="n"/>
-      <c r="J20" s="4" t="n"/>
+      <c r="J20" s="4" t="n">
+        <v>19.15</v>
+      </c>
       <c r="K20" s="4" t="n"/>
       <c r="L20" s="4" t="n"/>
-      <c r="M20" s="4" t="n"/>
-      <c r="N20" s="4" t="n">
-        <v>18.95</v>
-      </c>
+      <c r="M20" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="N20" s="4" t="n"/>
       <c r="O20" s="4" t="n"/>
       <c r="P20" s="4" t="n">
-        <v>18.69</v>
+        <v>18.99</v>
       </c>
       <c r="Q20" s="4" t="n"/>
       <c r="R20" s="4" t="n"/>
       <c r="S20" s="4" t="n"/>
-      <c r="T20" s="4" t="n">
-        <v>19.15</v>
-      </c>
+      <c r="T20" s="4" t="n"/>
       <c r="U20" s="4" t="n"/>
-      <c r="V20" s="4" t="n"/>
-      <c r="W20" s="4" t="n"/>
-      <c r="X20" s="4" t="n"/>
-      <c r="Y20" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="Z20" s="4" t="n"/>
-      <c r="AA20" s="4" t="n"/>
-      <c r="AB20" s="4" t="n"/>
-      <c r="AC20" s="4" t="n">
-        <v>18.99</v>
-      </c>
-      <c r="AD20" s="4" t="n"/>
-      <c r="AE20" s="4" t="n"/>
-      <c r="AF20" s="4" t="n"/>
-      <c r="AG20" s="4" t="n"/>
-      <c r="AH20" s="4" t="n"/>
-      <c r="AI20" s="4" t="n"/>
-      <c r="AJ20" s="4" t="n"/>
-      <c r="AK20" s="4" t="n"/>
-      <c r="AL20" s="4" t="n"/>
-      <c r="AM20" s="4" t="n"/>
-      <c r="AN20" s="4" t="n"/>
-      <c r="AO20" s="4" t="n"/>
-      <c r="AP20" s="4" t="n"/>
-      <c r="AQ20" s="4" t="n"/>
-      <c r="AR20" s="4" t="n"/>
-      <c r="AS20" s="4" t="n"/>
-      <c r="AT20" s="4" t="n"/>
-      <c r="AU20" s="4" t="n"/>
-      <c r="AV20" s="4" t="n"/>
-      <c r="AW20" s="4" t="n"/>
-      <c r="AX20" s="4" t="n"/>
-      <c r="AY20" s="4" t="n"/>
-      <c r="AZ20" s="4" t="n"/>
-      <c r="BA20" s="4" t="n"/>
-      <c r="BB20" s="4" t="n"/>
-      <c r="BC20" s="4" t="n"/>
-      <c r="BD20" s="4" t="n"/>
-      <c r="BE20" s="4" t="n"/>
-      <c r="BF20" s="4" t="n"/>
-      <c r="BG20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -11437,47 +9421,9 @@
       <c r="S21" s="4" t="n"/>
       <c r="T21" s="4" t="n"/>
       <c r="U21" s="4" t="n"/>
-      <c r="V21" s="4" t="n"/>
-      <c r="W21" s="4" t="n"/>
-      <c r="X21" s="4" t="n"/>
-      <c r="Y21" s="4" t="n"/>
-      <c r="Z21" s="4" t="n"/>
-      <c r="AA21" s="4" t="n"/>
-      <c r="AB21" s="4" t="n"/>
-      <c r="AC21" s="4" t="n"/>
-      <c r="AD21" s="4" t="n"/>
-      <c r="AE21" s="4" t="n"/>
-      <c r="AF21" s="4" t="n"/>
-      <c r="AG21" s="4" t="n"/>
-      <c r="AH21" s="4" t="n"/>
-      <c r="AI21" s="4" t="n"/>
-      <c r="AJ21" s="4" t="n"/>
-      <c r="AK21" s="4" t="n"/>
-      <c r="AL21" s="4" t="n"/>
-      <c r="AM21" s="4" t="n"/>
-      <c r="AN21" s="4" t="n"/>
-      <c r="AO21" s="4" t="n"/>
-      <c r="AP21" s="4" t="n"/>
-      <c r="AQ21" s="4" t="n"/>
-      <c r="AR21" s="4" t="n"/>
-      <c r="AS21" s="4" t="n"/>
-      <c r="AT21" s="4" t="n"/>
-      <c r="AU21" s="4" t="n"/>
-      <c r="AV21" s="4" t="n"/>
-      <c r="AW21" s="4" t="n"/>
-      <c r="AX21" s="4" t="n"/>
-      <c r="AY21" s="4" t="n"/>
-      <c r="AZ21" s="4" t="n"/>
-      <c r="BA21" s="4" t="n"/>
-      <c r="BB21" s="4" t="n"/>
-      <c r="BC21" s="4" t="n"/>
-      <c r="BD21" s="4" t="n"/>
-      <c r="BE21" s="4" t="n"/>
-      <c r="BF21" s="4" t="n"/>
-      <c r="BG21" s="4" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BG21"/>
+  <autoFilter ref="A1:U21"/>
   <mergeCells count="14">
     <mergeCell ref="A8"/>
     <mergeCell ref="A6"/>
@@ -11504,7 +9450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11514,58 +9460,6 @@
     <col width="7.5" customWidth="1" min="5" max="5"/>
     <col width="7.5" customWidth="1" min="6" max="6"/>
     <col width="7.5" customWidth="1" min="7" max="7"/>
-    <col width="7.5" customWidth="1" min="8" max="8"/>
-    <col width="7.5" customWidth="1" min="9" max="9"/>
-    <col width="7.5" customWidth="1" min="10" max="10"/>
-    <col width="7.5" customWidth="1" min="11" max="11"/>
-    <col width="7.5" customWidth="1" min="12" max="12"/>
-    <col width="7.5" customWidth="1" min="13" max="13"/>
-    <col width="7.5" customWidth="1" min="14" max="14"/>
-    <col width="7.5" customWidth="1" min="15" max="15"/>
-    <col width="7.5" customWidth="1" min="16" max="16"/>
-    <col width="7.5" customWidth="1" min="17" max="17"/>
-    <col width="7.5" customWidth="1" min="18" max="18"/>
-    <col width="7.5" customWidth="1" min="19" max="19"/>
-    <col width="7.5" customWidth="1" min="20" max="20"/>
-    <col width="7.5" customWidth="1" min="21" max="21"/>
-    <col width="7.5" customWidth="1" min="22" max="22"/>
-    <col width="7.5" customWidth="1" min="23" max="23"/>
-    <col width="7.5" customWidth="1" min="24" max="24"/>
-    <col width="7.5" customWidth="1" min="25" max="25"/>
-    <col width="7.5" customWidth="1" min="26" max="26"/>
-    <col width="7.5" customWidth="1" min="27" max="27"/>
-    <col width="7.5" customWidth="1" min="28" max="28"/>
-    <col width="7.5" customWidth="1" min="29" max="29"/>
-    <col width="7.5" customWidth="1" min="30" max="30"/>
-    <col width="7.5" customWidth="1" min="31" max="31"/>
-    <col width="7.5" customWidth="1" min="32" max="32"/>
-    <col width="7.5" customWidth="1" min="33" max="33"/>
-    <col width="7.5" customWidth="1" min="34" max="34"/>
-    <col width="7.5" customWidth="1" min="35" max="35"/>
-    <col width="7.5" customWidth="1" min="36" max="36"/>
-    <col width="7.5" customWidth="1" min="37" max="37"/>
-    <col width="7.5" customWidth="1" min="38" max="38"/>
-    <col width="7.5" customWidth="1" min="39" max="39"/>
-    <col width="7.5" customWidth="1" min="40" max="40"/>
-    <col width="7.5" customWidth="1" min="41" max="41"/>
-    <col width="7.5" customWidth="1" min="42" max="42"/>
-    <col width="7.5" customWidth="1" min="43" max="43"/>
-    <col width="7.5" customWidth="1" min="44" max="44"/>
-    <col width="7.5" customWidth="1" min="45" max="45"/>
-    <col width="7.5" customWidth="1" min="46" max="46"/>
-    <col width="7.5" customWidth="1" min="47" max="47"/>
-    <col width="7.5" customWidth="1" min="48" max="48"/>
-    <col width="7.5" customWidth="1" min="49" max="49"/>
-    <col width="7.5" customWidth="1" min="50" max="50"/>
-    <col width="7.5" customWidth="1" min="51" max="51"/>
-    <col width="7.5" customWidth="1" min="52" max="52"/>
-    <col width="7.5" customWidth="1" min="53" max="53"/>
-    <col width="7.5" customWidth="1" min="54" max="54"/>
-    <col width="7.5" customWidth="1" min="55" max="55"/>
-    <col width="7.5" customWidth="1" min="56" max="56"/>
-    <col width="7.5" customWidth="1" min="57" max="57"/>
-    <col width="7.5" customWidth="1" min="58" max="58"/>
-    <col width="7.5" customWidth="1" min="59" max="59"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11586,282 +9480,22 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>杰哥</t>
+          <t>9x8★6</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>爱音</t>
+          <t>c2★6</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>恶魔</t>
+          <t>fp1★6</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>f5★6</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>f5</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>玻璃★6</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>玻璃</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>速尾★6</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>速尾</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>9x8★6</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>9x8</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>ssc</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>肥龙</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>c2★6</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>c2</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>万达★6</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>万达</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>21c</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>fp1★6</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>fp1</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
           <t>sgt★6</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>sgt</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>火山</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>法拉第</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>秋王★6</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>秋王</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>白龙★6</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>白龙</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>sf90★6</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>sf90</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>att</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>divo</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>狼王</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>小牛★6</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>小牛</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>fe3★5</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>fe3</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>杰弟</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>六子</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>英灵殿</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>帕梅</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>ts900</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>650s</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>f5r</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>ps龙</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>r兔★6</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>r兔</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>帝国</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>杰皇★6</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>杰皇</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>猫头鹰</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>银电</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>陀飞轮</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>风龙</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>黑龙★6</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>黑龙</t>
         </is>
       </c>
     </row>
@@ -11885,58 +9519,6 @@
       <c r="E2" s="4" t="n"/>
       <c r="F2" s="4" t="n"/>
       <c r="G2" s="4" t="n"/>
-      <c r="H2" s="4" t="n"/>
-      <c r="I2" s="4" t="n"/>
-      <c r="J2" s="4" t="n"/>
-      <c r="K2" s="4" t="n"/>
-      <c r="L2" s="4" t="n"/>
-      <c r="M2" s="4" t="n"/>
-      <c r="N2" s="4" t="n"/>
-      <c r="O2" s="4" t="n"/>
-      <c r="P2" s="4" t="n"/>
-      <c r="Q2" s="4" t="n"/>
-      <c r="R2" s="4" t="n"/>
-      <c r="S2" s="4" t="n"/>
-      <c r="T2" s="4" t="n"/>
-      <c r="U2" s="4" t="n"/>
-      <c r="V2" s="4" t="n"/>
-      <c r="W2" s="4" t="n"/>
-      <c r="X2" s="4" t="n"/>
-      <c r="Y2" s="4" t="n"/>
-      <c r="Z2" s="4" t="n"/>
-      <c r="AA2" s="4" t="n"/>
-      <c r="AB2" s="4" t="n"/>
-      <c r="AC2" s="4" t="n"/>
-      <c r="AD2" s="4" t="n"/>
-      <c r="AE2" s="4" t="n"/>
-      <c r="AF2" s="4" t="n"/>
-      <c r="AG2" s="4" t="n"/>
-      <c r="AH2" s="4" t="n"/>
-      <c r="AI2" s="4" t="n"/>
-      <c r="AJ2" s="4" t="n"/>
-      <c r="AK2" s="4" t="n"/>
-      <c r="AL2" s="4" t="n"/>
-      <c r="AM2" s="4" t="n"/>
-      <c r="AN2" s="4" t="n"/>
-      <c r="AO2" s="4" t="n"/>
-      <c r="AP2" s="4" t="n"/>
-      <c r="AQ2" s="4" t="n"/>
-      <c r="AR2" s="4" t="n"/>
-      <c r="AS2" s="4" t="n"/>
-      <c r="AT2" s="4" t="n"/>
-      <c r="AU2" s="4" t="n"/>
-      <c r="AV2" s="4" t="n"/>
-      <c r="AW2" s="4" t="n"/>
-      <c r="AX2" s="4" t="n"/>
-      <c r="AY2" s="4" t="n"/>
-      <c r="AZ2" s="4" t="n"/>
-      <c r="BA2" s="4" t="n"/>
-      <c r="BB2" s="4" t="n"/>
-      <c r="BC2" s="4" t="n"/>
-      <c r="BD2" s="4" t="n"/>
-      <c r="BE2" s="4" t="n"/>
-      <c r="BF2" s="4" t="n"/>
-      <c r="BG2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="n"/>
@@ -11954,58 +9536,6 @@
       <c r="E3" s="4" t="n"/>
       <c r="F3" s="4" t="n"/>
       <c r="G3" s="4" t="n"/>
-      <c r="H3" s="4" t="n"/>
-      <c r="I3" s="4" t="n"/>
-      <c r="J3" s="4" t="n"/>
-      <c r="K3" s="4" t="n"/>
-      <c r="L3" s="4" t="n"/>
-      <c r="M3" s="4" t="n"/>
-      <c r="N3" s="4" t="n"/>
-      <c r="O3" s="4" t="n"/>
-      <c r="P3" s="4" t="n"/>
-      <c r="Q3" s="4" t="n"/>
-      <c r="R3" s="4" t="n"/>
-      <c r="S3" s="4" t="n"/>
-      <c r="T3" s="4" t="n"/>
-      <c r="U3" s="4" t="n"/>
-      <c r="V3" s="4" t="n"/>
-      <c r="W3" s="4" t="n"/>
-      <c r="X3" s="4" t="n"/>
-      <c r="Y3" s="4" t="n"/>
-      <c r="Z3" s="4" t="n"/>
-      <c r="AA3" s="4" t="n"/>
-      <c r="AB3" s="4" t="n"/>
-      <c r="AC3" s="4" t="n"/>
-      <c r="AD3" s="4" t="n"/>
-      <c r="AE3" s="4" t="n"/>
-      <c r="AF3" s="4" t="n"/>
-      <c r="AG3" s="4" t="n"/>
-      <c r="AH3" s="4" t="n"/>
-      <c r="AI3" s="4" t="n"/>
-      <c r="AJ3" s="4" t="n"/>
-      <c r="AK3" s="4" t="n"/>
-      <c r="AL3" s="4" t="n"/>
-      <c r="AM3" s="4" t="n"/>
-      <c r="AN3" s="4" t="n"/>
-      <c r="AO3" s="4" t="n"/>
-      <c r="AP3" s="4" t="n"/>
-      <c r="AQ3" s="4" t="n"/>
-      <c r="AR3" s="4" t="n"/>
-      <c r="AS3" s="4" t="n"/>
-      <c r="AT3" s="4" t="n"/>
-      <c r="AU3" s="4" t="n"/>
-      <c r="AV3" s="4" t="n"/>
-      <c r="AW3" s="4" t="n"/>
-      <c r="AX3" s="4" t="n"/>
-      <c r="AY3" s="4" t="n"/>
-      <c r="AZ3" s="4" t="n"/>
-      <c r="BA3" s="4" t="n"/>
-      <c r="BB3" s="4" t="n"/>
-      <c r="BC3" s="4" t="n"/>
-      <c r="BD3" s="4" t="n"/>
-      <c r="BE3" s="4" t="n"/>
-      <c r="BF3" s="4" t="n"/>
-      <c r="BG3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -12025,62 +9555,10 @@
       </c>
       <c r="D4" s="4" t="n"/>
       <c r="E4" s="4" t="n"/>
-      <c r="F4" s="4" t="n"/>
+      <c r="F4" s="4" t="n">
+        <v>24.79</v>
+      </c>
       <c r="G4" s="4" t="n"/>
-      <c r="H4" s="4" t="n"/>
-      <c r="I4" s="4" t="n"/>
-      <c r="J4" s="4" t="n"/>
-      <c r="K4" s="4" t="n"/>
-      <c r="L4" s="4" t="n"/>
-      <c r="M4" s="4" t="n"/>
-      <c r="N4" s="4" t="n"/>
-      <c r="O4" s="4" t="n"/>
-      <c r="P4" s="4" t="n"/>
-      <c r="Q4" s="4" t="n"/>
-      <c r="R4" s="4" t="n"/>
-      <c r="S4" s="4" t="n"/>
-      <c r="T4" s="4" t="n"/>
-      <c r="U4" s="4" t="n"/>
-      <c r="V4" s="4" t="n">
-        <v>24.79</v>
-      </c>
-      <c r="W4" s="4" t="n"/>
-      <c r="X4" s="4" t="n"/>
-      <c r="Y4" s="4" t="n"/>
-      <c r="Z4" s="4" t="n"/>
-      <c r="AA4" s="4" t="n"/>
-      <c r="AB4" s="4" t="n"/>
-      <c r="AC4" s="4" t="n"/>
-      <c r="AD4" s="4" t="n"/>
-      <c r="AE4" s="4" t="n"/>
-      <c r="AF4" s="4" t="n"/>
-      <c r="AG4" s="4" t="n"/>
-      <c r="AH4" s="4" t="n"/>
-      <c r="AI4" s="4" t="n"/>
-      <c r="AJ4" s="4" t="n"/>
-      <c r="AK4" s="4" t="n"/>
-      <c r="AL4" s="4" t="n"/>
-      <c r="AM4" s="4" t="n"/>
-      <c r="AN4" s="4" t="n"/>
-      <c r="AO4" s="4" t="n"/>
-      <c r="AP4" s="4" t="n"/>
-      <c r="AQ4" s="4" t="n"/>
-      <c r="AR4" s="4" t="n"/>
-      <c r="AS4" s="4" t="n"/>
-      <c r="AT4" s="4" t="n"/>
-      <c r="AU4" s="4" t="n"/>
-      <c r="AV4" s="4" t="n"/>
-      <c r="AW4" s="4" t="n"/>
-      <c r="AX4" s="4" t="n"/>
-      <c r="AY4" s="4" t="n"/>
-      <c r="AZ4" s="4" t="n"/>
-      <c r="BA4" s="4" t="n"/>
-      <c r="BB4" s="4" t="n"/>
-      <c r="BC4" s="4" t="n"/>
-      <c r="BD4" s="4" t="n"/>
-      <c r="BE4" s="4" t="n"/>
-      <c r="BF4" s="4" t="n"/>
-      <c r="BG4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -12098,64 +9576,12 @@
           <t>跳船</t>
         </is>
       </c>
-      <c r="D5" s="4" t="n"/>
+      <c r="D5" s="4" t="n">
+        <v>22.9</v>
+      </c>
       <c r="E5" s="4" t="n"/>
       <c r="F5" s="4" t="n"/>
       <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="n"/>
-      <c r="J5" s="4" t="n"/>
-      <c r="K5" s="4" t="n"/>
-      <c r="L5" s="4" t="n"/>
-      <c r="M5" s="4" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="N5" s="4" t="n"/>
-      <c r="O5" s="4" t="n"/>
-      <c r="P5" s="4" t="n"/>
-      <c r="Q5" s="4" t="n"/>
-      <c r="R5" s="4" t="n"/>
-      <c r="S5" s="4" t="n"/>
-      <c r="T5" s="4" t="n"/>
-      <c r="U5" s="4" t="n"/>
-      <c r="V5" s="4" t="n"/>
-      <c r="W5" s="4" t="n"/>
-      <c r="X5" s="4" t="n"/>
-      <c r="Y5" s="4" t="n"/>
-      <c r="Z5" s="4" t="n"/>
-      <c r="AA5" s="4" t="n"/>
-      <c r="AB5" s="4" t="n"/>
-      <c r="AC5" s="4" t="n"/>
-      <c r="AD5" s="4" t="n"/>
-      <c r="AE5" s="4" t="n"/>
-      <c r="AF5" s="4" t="n"/>
-      <c r="AG5" s="4" t="n"/>
-      <c r="AH5" s="4" t="n"/>
-      <c r="AI5" s="4" t="n"/>
-      <c r="AJ5" s="4" t="n"/>
-      <c r="AK5" s="4" t="n"/>
-      <c r="AL5" s="4" t="n"/>
-      <c r="AM5" s="4" t="n"/>
-      <c r="AN5" s="4" t="n"/>
-      <c r="AO5" s="4" t="n"/>
-      <c r="AP5" s="4" t="n"/>
-      <c r="AQ5" s="4" t="n"/>
-      <c r="AR5" s="4" t="n"/>
-      <c r="AS5" s="4" t="n"/>
-      <c r="AT5" s="4" t="n"/>
-      <c r="AU5" s="4" t="n"/>
-      <c r="AV5" s="4" t="n"/>
-      <c r="AW5" s="4" t="n"/>
-      <c r="AX5" s="4" t="n"/>
-      <c r="AY5" s="4" t="n"/>
-      <c r="AZ5" s="4" t="n"/>
-      <c r="BA5" s="4" t="n"/>
-      <c r="BB5" s="4" t="n"/>
-      <c r="BC5" s="4" t="n"/>
-      <c r="BD5" s="4" t="n"/>
-      <c r="BE5" s="4" t="n"/>
-      <c r="BF5" s="4" t="n"/>
-      <c r="BG5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -12174,63 +9600,11 @@
         </is>
       </c>
       <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="n"/>
+      <c r="E6" s="4" t="n">
+        <v>22.6</v>
+      </c>
       <c r="F6" s="4" t="n"/>
       <c r="G6" s="4" t="n"/>
-      <c r="H6" s="4" t="n"/>
-      <c r="I6" s="4" t="n"/>
-      <c r="J6" s="4" t="n"/>
-      <c r="K6" s="4" t="n"/>
-      <c r="L6" s="4" t="n"/>
-      <c r="M6" s="4" t="n"/>
-      <c r="N6" s="4" t="n"/>
-      <c r="O6" s="4" t="n"/>
-      <c r="P6" s="4" t="n"/>
-      <c r="Q6" s="4" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="R6" s="4" t="n"/>
-      <c r="S6" s="4" t="n"/>
-      <c r="T6" s="4" t="n"/>
-      <c r="U6" s="4" t="n"/>
-      <c r="V6" s="4" t="n"/>
-      <c r="W6" s="4" t="n"/>
-      <c r="X6" s="4" t="n"/>
-      <c r="Y6" s="4" t="n"/>
-      <c r="Z6" s="4" t="n"/>
-      <c r="AA6" s="4" t="n"/>
-      <c r="AB6" s="4" t="n"/>
-      <c r="AC6" s="4" t="n"/>
-      <c r="AD6" s="4" t="n"/>
-      <c r="AE6" s="4" t="n"/>
-      <c r="AF6" s="4" t="n"/>
-      <c r="AG6" s="4" t="n"/>
-      <c r="AH6" s="4" t="n"/>
-      <c r="AI6" s="4" t="n"/>
-      <c r="AJ6" s="4" t="n"/>
-      <c r="AK6" s="4" t="n"/>
-      <c r="AL6" s="4" t="n"/>
-      <c r="AM6" s="4" t="n"/>
-      <c r="AN6" s="4" t="n"/>
-      <c r="AO6" s="4" t="n"/>
-      <c r="AP6" s="4" t="n"/>
-      <c r="AQ6" s="4" t="n"/>
-      <c r="AR6" s="4" t="n"/>
-      <c r="AS6" s="4" t="n"/>
-      <c r="AT6" s="4" t="n"/>
-      <c r="AU6" s="4" t="n"/>
-      <c r="AV6" s="4" t="n"/>
-      <c r="AW6" s="4" t="n"/>
-      <c r="AX6" s="4" t="n"/>
-      <c r="AY6" s="4" t="n"/>
-      <c r="AZ6" s="4" t="n"/>
-      <c r="BA6" s="4" t="n"/>
-      <c r="BB6" s="4" t="n"/>
-      <c r="BC6" s="4" t="n"/>
-      <c r="BD6" s="4" t="n"/>
-      <c r="BE6" s="4" t="n"/>
-      <c r="BF6" s="4" t="n"/>
-      <c r="BG6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -12252,58 +9626,6 @@
       <c r="E7" s="4" t="n"/>
       <c r="F7" s="4" t="n"/>
       <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n"/>
-      <c r="I7" s="4" t="n"/>
-      <c r="J7" s="4" t="n"/>
-      <c r="K7" s="4" t="n"/>
-      <c r="L7" s="4" t="n"/>
-      <c r="M7" s="4" t="n"/>
-      <c r="N7" s="4" t="n"/>
-      <c r="O7" s="4" t="n"/>
-      <c r="P7" s="4" t="n"/>
-      <c r="Q7" s="4" t="n"/>
-      <c r="R7" s="4" t="n"/>
-      <c r="S7" s="4" t="n"/>
-      <c r="T7" s="4" t="n"/>
-      <c r="U7" s="4" t="n"/>
-      <c r="V7" s="4" t="n"/>
-      <c r="W7" s="4" t="n"/>
-      <c r="X7" s="4" t="n"/>
-      <c r="Y7" s="4" t="n"/>
-      <c r="Z7" s="4" t="n"/>
-      <c r="AA7" s="4" t="n"/>
-      <c r="AB7" s="4" t="n"/>
-      <c r="AC7" s="4" t="n"/>
-      <c r="AD7" s="4" t="n"/>
-      <c r="AE7" s="4" t="n"/>
-      <c r="AF7" s="4" t="n"/>
-      <c r="AG7" s="4" t="n"/>
-      <c r="AH7" s="4" t="n"/>
-      <c r="AI7" s="4" t="n"/>
-      <c r="AJ7" s="4" t="n"/>
-      <c r="AK7" s="4" t="n"/>
-      <c r="AL7" s="4" t="n"/>
-      <c r="AM7" s="4" t="n"/>
-      <c r="AN7" s="4" t="n"/>
-      <c r="AO7" s="4" t="n"/>
-      <c r="AP7" s="4" t="n"/>
-      <c r="AQ7" s="4" t="n"/>
-      <c r="AR7" s="4" t="n"/>
-      <c r="AS7" s="4" t="n"/>
-      <c r="AT7" s="4" t="n"/>
-      <c r="AU7" s="4" t="n"/>
-      <c r="AV7" s="4" t="n"/>
-      <c r="AW7" s="4" t="n"/>
-      <c r="AX7" s="4" t="n"/>
-      <c r="AY7" s="4" t="n"/>
-      <c r="AZ7" s="4" t="n"/>
-      <c r="BA7" s="4" t="n"/>
-      <c r="BB7" s="4" t="n"/>
-      <c r="BC7" s="4" t="n"/>
-      <c r="BD7" s="4" t="n"/>
-      <c r="BE7" s="4" t="n"/>
-      <c r="BF7" s="4" t="n"/>
-      <c r="BG7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -12325,58 +9647,6 @@
       <c r="E8" s="4" t="n"/>
       <c r="F8" s="4" t="n"/>
       <c r="G8" s="4" t="n"/>
-      <c r="H8" s="4" t="n"/>
-      <c r="I8" s="4" t="n"/>
-      <c r="J8" s="4" t="n"/>
-      <c r="K8" s="4" t="n"/>
-      <c r="L8" s="4" t="n"/>
-      <c r="M8" s="4" t="n"/>
-      <c r="N8" s="4" t="n"/>
-      <c r="O8" s="4" t="n"/>
-      <c r="P8" s="4" t="n"/>
-      <c r="Q8" s="4" t="n"/>
-      <c r="R8" s="4" t="n"/>
-      <c r="S8" s="4" t="n"/>
-      <c r="T8" s="4" t="n"/>
-      <c r="U8" s="4" t="n"/>
-      <c r="V8" s="4" t="n"/>
-      <c r="W8" s="4" t="n"/>
-      <c r="X8" s="4" t="n"/>
-      <c r="Y8" s="4" t="n"/>
-      <c r="Z8" s="4" t="n"/>
-      <c r="AA8" s="4" t="n"/>
-      <c r="AB8" s="4" t="n"/>
-      <c r="AC8" s="4" t="n"/>
-      <c r="AD8" s="4" t="n"/>
-      <c r="AE8" s="4" t="n"/>
-      <c r="AF8" s="4" t="n"/>
-      <c r="AG8" s="4" t="n"/>
-      <c r="AH8" s="4" t="n"/>
-      <c r="AI8" s="4" t="n"/>
-      <c r="AJ8" s="4" t="n"/>
-      <c r="AK8" s="4" t="n"/>
-      <c r="AL8" s="4" t="n"/>
-      <c r="AM8" s="4" t="n"/>
-      <c r="AN8" s="4" t="n"/>
-      <c r="AO8" s="4" t="n"/>
-      <c r="AP8" s="4" t="n"/>
-      <c r="AQ8" s="4" t="n"/>
-      <c r="AR8" s="4" t="n"/>
-      <c r="AS8" s="4" t="n"/>
-      <c r="AT8" s="4" t="n"/>
-      <c r="AU8" s="4" t="n"/>
-      <c r="AV8" s="4" t="n"/>
-      <c r="AW8" s="4" t="n"/>
-      <c r="AX8" s="4" t="n"/>
-      <c r="AY8" s="4" t="n"/>
-      <c r="AZ8" s="4" t="n"/>
-      <c r="BA8" s="4" t="n"/>
-      <c r="BB8" s="4" t="n"/>
-      <c r="BC8" s="4" t="n"/>
-      <c r="BD8" s="4" t="n"/>
-      <c r="BE8" s="4" t="n"/>
-      <c r="BF8" s="4" t="n"/>
-      <c r="BG8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -12398,58 +9668,6 @@
       <c r="E9" s="4" t="n"/>
       <c r="F9" s="4" t="n"/>
       <c r="G9" s="4" t="n"/>
-      <c r="H9" s="4" t="n"/>
-      <c r="I9" s="4" t="n"/>
-      <c r="J9" s="4" t="n"/>
-      <c r="K9" s="4" t="n"/>
-      <c r="L9" s="4" t="n"/>
-      <c r="M9" s="4" t="n"/>
-      <c r="N9" s="4" t="n"/>
-      <c r="O9" s="4" t="n"/>
-      <c r="P9" s="4" t="n"/>
-      <c r="Q9" s="4" t="n"/>
-      <c r="R9" s="4" t="n"/>
-      <c r="S9" s="4" t="n"/>
-      <c r="T9" s="4" t="n"/>
-      <c r="U9" s="4" t="n"/>
-      <c r="V9" s="4" t="n"/>
-      <c r="W9" s="4" t="n"/>
-      <c r="X9" s="4" t="n"/>
-      <c r="Y9" s="4" t="n"/>
-      <c r="Z9" s="4" t="n"/>
-      <c r="AA9" s="4" t="n"/>
-      <c r="AB9" s="4" t="n"/>
-      <c r="AC9" s="4" t="n"/>
-      <c r="AD9" s="4" t="n"/>
-      <c r="AE9" s="4" t="n"/>
-      <c r="AF9" s="4" t="n"/>
-      <c r="AG9" s="4" t="n"/>
-      <c r="AH9" s="4" t="n"/>
-      <c r="AI9" s="4" t="n"/>
-      <c r="AJ9" s="4" t="n"/>
-      <c r="AK9" s="4" t="n"/>
-      <c r="AL9" s="4" t="n"/>
-      <c r="AM9" s="4" t="n"/>
-      <c r="AN9" s="4" t="n"/>
-      <c r="AO9" s="4" t="n"/>
-      <c r="AP9" s="4" t="n"/>
-      <c r="AQ9" s="4" t="n"/>
-      <c r="AR9" s="4" t="n"/>
-      <c r="AS9" s="4" t="n"/>
-      <c r="AT9" s="4" t="n"/>
-      <c r="AU9" s="4" t="n"/>
-      <c r="AV9" s="4" t="n"/>
-      <c r="AW9" s="4" t="n"/>
-      <c r="AX9" s="4" t="n"/>
-      <c r="AY9" s="4" t="n"/>
-      <c r="AZ9" s="4" t="n"/>
-      <c r="BA9" s="4" t="n"/>
-      <c r="BB9" s="4" t="n"/>
-      <c r="BC9" s="4" t="n"/>
-      <c r="BD9" s="4" t="n"/>
-      <c r="BE9" s="4" t="n"/>
-      <c r="BF9" s="4" t="n"/>
-      <c r="BG9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n"/>
@@ -12467,58 +9685,6 @@
       <c r="E10" s="4" t="n"/>
       <c r="F10" s="4" t="n"/>
       <c r="G10" s="4" t="n"/>
-      <c r="H10" s="4" t="n"/>
-      <c r="I10" s="4" t="n"/>
-      <c r="J10" s="4" t="n"/>
-      <c r="K10" s="4" t="n"/>
-      <c r="L10" s="4" t="n"/>
-      <c r="M10" s="4" t="n"/>
-      <c r="N10" s="4" t="n"/>
-      <c r="O10" s="4" t="n"/>
-      <c r="P10" s="4" t="n"/>
-      <c r="Q10" s="4" t="n"/>
-      <c r="R10" s="4" t="n"/>
-      <c r="S10" s="4" t="n"/>
-      <c r="T10" s="4" t="n"/>
-      <c r="U10" s="4" t="n"/>
-      <c r="V10" s="4" t="n"/>
-      <c r="W10" s="4" t="n"/>
-      <c r="X10" s="4" t="n"/>
-      <c r="Y10" s="4" t="n"/>
-      <c r="Z10" s="4" t="n"/>
-      <c r="AA10" s="4" t="n"/>
-      <c r="AB10" s="4" t="n"/>
-      <c r="AC10" s="4" t="n"/>
-      <c r="AD10" s="4" t="n"/>
-      <c r="AE10" s="4" t="n"/>
-      <c r="AF10" s="4" t="n"/>
-      <c r="AG10" s="4" t="n"/>
-      <c r="AH10" s="4" t="n"/>
-      <c r="AI10" s="4" t="n"/>
-      <c r="AJ10" s="4" t="n"/>
-      <c r="AK10" s="4" t="n"/>
-      <c r="AL10" s="4" t="n"/>
-      <c r="AM10" s="4" t="n"/>
-      <c r="AN10" s="4" t="n"/>
-      <c r="AO10" s="4" t="n"/>
-      <c r="AP10" s="4" t="n"/>
-      <c r="AQ10" s="4" t="n"/>
-      <c r="AR10" s="4" t="n"/>
-      <c r="AS10" s="4" t="n"/>
-      <c r="AT10" s="4" t="n"/>
-      <c r="AU10" s="4" t="n"/>
-      <c r="AV10" s="4" t="n"/>
-      <c r="AW10" s="4" t="n"/>
-      <c r="AX10" s="4" t="n"/>
-      <c r="AY10" s="4" t="n"/>
-      <c r="AZ10" s="4" t="n"/>
-      <c r="BA10" s="4" t="n"/>
-      <c r="BB10" s="4" t="n"/>
-      <c r="BC10" s="4" t="n"/>
-      <c r="BD10" s="4" t="n"/>
-      <c r="BE10" s="4" t="n"/>
-      <c r="BF10" s="4" t="n"/>
-      <c r="BG10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -12540,58 +9706,6 @@
       <c r="E11" s="4" t="n"/>
       <c r="F11" s="4" t="n"/>
       <c r="G11" s="4" t="n"/>
-      <c r="H11" s="4" t="n"/>
-      <c r="I11" s="4" t="n"/>
-      <c r="J11" s="4" t="n"/>
-      <c r="K11" s="4" t="n"/>
-      <c r="L11" s="4" t="n"/>
-      <c r="M11" s="4" t="n"/>
-      <c r="N11" s="4" t="n"/>
-      <c r="O11" s="4" t="n"/>
-      <c r="P11" s="4" t="n"/>
-      <c r="Q11" s="4" t="n"/>
-      <c r="R11" s="4" t="n"/>
-      <c r="S11" s="4" t="n"/>
-      <c r="T11" s="4" t="n"/>
-      <c r="U11" s="4" t="n"/>
-      <c r="V11" s="4" t="n"/>
-      <c r="W11" s="4" t="n"/>
-      <c r="X11" s="4" t="n"/>
-      <c r="Y11" s="4" t="n"/>
-      <c r="Z11" s="4" t="n"/>
-      <c r="AA11" s="4" t="n"/>
-      <c r="AB11" s="4" t="n"/>
-      <c r="AC11" s="4" t="n"/>
-      <c r="AD11" s="4" t="n"/>
-      <c r="AE11" s="4" t="n"/>
-      <c r="AF11" s="4" t="n"/>
-      <c r="AG11" s="4" t="n"/>
-      <c r="AH11" s="4" t="n"/>
-      <c r="AI11" s="4" t="n"/>
-      <c r="AJ11" s="4" t="n"/>
-      <c r="AK11" s="4" t="n"/>
-      <c r="AL11" s="4" t="n"/>
-      <c r="AM11" s="4" t="n"/>
-      <c r="AN11" s="4" t="n"/>
-      <c r="AO11" s="4" t="n"/>
-      <c r="AP11" s="4" t="n"/>
-      <c r="AQ11" s="4" t="n"/>
-      <c r="AR11" s="4" t="n"/>
-      <c r="AS11" s="4" t="n"/>
-      <c r="AT11" s="4" t="n"/>
-      <c r="AU11" s="4" t="n"/>
-      <c r="AV11" s="4" t="n"/>
-      <c r="AW11" s="4" t="n"/>
-      <c r="AX11" s="4" t="n"/>
-      <c r="AY11" s="4" t="n"/>
-      <c r="AZ11" s="4" t="n"/>
-      <c r="BA11" s="4" t="n"/>
-      <c r="BB11" s="4" t="n"/>
-      <c r="BC11" s="4" t="n"/>
-      <c r="BD11" s="4" t="n"/>
-      <c r="BE11" s="4" t="n"/>
-      <c r="BF11" s="4" t="n"/>
-      <c r="BG11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -12613,58 +9727,6 @@
       <c r="E12" s="4" t="n"/>
       <c r="F12" s="4" t="n"/>
       <c r="G12" s="4" t="n"/>
-      <c r="H12" s="4" t="n"/>
-      <c r="I12" s="4" t="n"/>
-      <c r="J12" s="4" t="n"/>
-      <c r="K12" s="4" t="n"/>
-      <c r="L12" s="4" t="n"/>
-      <c r="M12" s="4" t="n"/>
-      <c r="N12" s="4" t="n"/>
-      <c r="O12" s="4" t="n"/>
-      <c r="P12" s="4" t="n"/>
-      <c r="Q12" s="4" t="n"/>
-      <c r="R12" s="4" t="n"/>
-      <c r="S12" s="4" t="n"/>
-      <c r="T12" s="4" t="n"/>
-      <c r="U12" s="4" t="n"/>
-      <c r="V12" s="4" t="n"/>
-      <c r="W12" s="4" t="n"/>
-      <c r="X12" s="4" t="n"/>
-      <c r="Y12" s="4" t="n"/>
-      <c r="Z12" s="4" t="n"/>
-      <c r="AA12" s="4" t="n"/>
-      <c r="AB12" s="4" t="n"/>
-      <c r="AC12" s="4" t="n"/>
-      <c r="AD12" s="4" t="n"/>
-      <c r="AE12" s="4" t="n"/>
-      <c r="AF12" s="4" t="n"/>
-      <c r="AG12" s="4" t="n"/>
-      <c r="AH12" s="4" t="n"/>
-      <c r="AI12" s="4" t="n"/>
-      <c r="AJ12" s="4" t="n"/>
-      <c r="AK12" s="4" t="n"/>
-      <c r="AL12" s="4" t="n"/>
-      <c r="AM12" s="4" t="n"/>
-      <c r="AN12" s="4" t="n"/>
-      <c r="AO12" s="4" t="n"/>
-      <c r="AP12" s="4" t="n"/>
-      <c r="AQ12" s="4" t="n"/>
-      <c r="AR12" s="4" t="n"/>
-      <c r="AS12" s="4" t="n"/>
-      <c r="AT12" s="4" t="n"/>
-      <c r="AU12" s="4" t="n"/>
-      <c r="AV12" s="4" t="n"/>
-      <c r="AW12" s="4" t="n"/>
-      <c r="AX12" s="4" t="n"/>
-      <c r="AY12" s="4" t="n"/>
-      <c r="AZ12" s="4" t="n"/>
-      <c r="BA12" s="4" t="n"/>
-      <c r="BB12" s="4" t="n"/>
-      <c r="BC12" s="4" t="n"/>
-      <c r="BD12" s="4" t="n"/>
-      <c r="BE12" s="4" t="n"/>
-      <c r="BF12" s="4" t="n"/>
-      <c r="BG12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -12686,58 +9748,6 @@
       <c r="E13" s="4" t="n"/>
       <c r="F13" s="4" t="n"/>
       <c r="G13" s="4" t="n"/>
-      <c r="H13" s="4" t="n"/>
-      <c r="I13" s="4" t="n"/>
-      <c r="J13" s="4" t="n"/>
-      <c r="K13" s="4" t="n"/>
-      <c r="L13" s="4" t="n"/>
-      <c r="M13" s="4" t="n"/>
-      <c r="N13" s="4" t="n"/>
-      <c r="O13" s="4" t="n"/>
-      <c r="P13" s="4" t="n"/>
-      <c r="Q13" s="4" t="n"/>
-      <c r="R13" s="4" t="n"/>
-      <c r="S13" s="4" t="n"/>
-      <c r="T13" s="4" t="n"/>
-      <c r="U13" s="4" t="n"/>
-      <c r="V13" s="4" t="n"/>
-      <c r="W13" s="4" t="n"/>
-      <c r="X13" s="4" t="n"/>
-      <c r="Y13" s="4" t="n"/>
-      <c r="Z13" s="4" t="n"/>
-      <c r="AA13" s="4" t="n"/>
-      <c r="AB13" s="4" t="n"/>
-      <c r="AC13" s="4" t="n"/>
-      <c r="AD13" s="4" t="n"/>
-      <c r="AE13" s="4" t="n"/>
-      <c r="AF13" s="4" t="n"/>
-      <c r="AG13" s="4" t="n"/>
-      <c r="AH13" s="4" t="n"/>
-      <c r="AI13" s="4" t="n"/>
-      <c r="AJ13" s="4" t="n"/>
-      <c r="AK13" s="4" t="n"/>
-      <c r="AL13" s="4" t="n"/>
-      <c r="AM13" s="4" t="n"/>
-      <c r="AN13" s="4" t="n"/>
-      <c r="AO13" s="4" t="n"/>
-      <c r="AP13" s="4" t="n"/>
-      <c r="AQ13" s="4" t="n"/>
-      <c r="AR13" s="4" t="n"/>
-      <c r="AS13" s="4" t="n"/>
-      <c r="AT13" s="4" t="n"/>
-      <c r="AU13" s="4" t="n"/>
-      <c r="AV13" s="4" t="n"/>
-      <c r="AW13" s="4" t="n"/>
-      <c r="AX13" s="4" t="n"/>
-      <c r="AY13" s="4" t="n"/>
-      <c r="AZ13" s="4" t="n"/>
-      <c r="BA13" s="4" t="n"/>
-      <c r="BB13" s="4" t="n"/>
-      <c r="BC13" s="4" t="n"/>
-      <c r="BD13" s="4" t="n"/>
-      <c r="BE13" s="4" t="n"/>
-      <c r="BF13" s="4" t="n"/>
-      <c r="BG13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n"/>
@@ -12755,58 +9765,6 @@
       <c r="E14" s="4" t="n"/>
       <c r="F14" s="4" t="n"/>
       <c r="G14" s="4" t="n"/>
-      <c r="H14" s="4" t="n"/>
-      <c r="I14" s="4" t="n"/>
-      <c r="J14" s="4" t="n"/>
-      <c r="K14" s="4" t="n"/>
-      <c r="L14" s="4" t="n"/>
-      <c r="M14" s="4" t="n"/>
-      <c r="N14" s="4" t="n"/>
-      <c r="O14" s="4" t="n"/>
-      <c r="P14" s="4" t="n"/>
-      <c r="Q14" s="4" t="n"/>
-      <c r="R14" s="4" t="n"/>
-      <c r="S14" s="4" t="n"/>
-      <c r="T14" s="4" t="n"/>
-      <c r="U14" s="4" t="n"/>
-      <c r="V14" s="4" t="n"/>
-      <c r="W14" s="4" t="n"/>
-      <c r="X14" s="4" t="n"/>
-      <c r="Y14" s="4" t="n"/>
-      <c r="Z14" s="4" t="n"/>
-      <c r="AA14" s="4" t="n"/>
-      <c r="AB14" s="4" t="n"/>
-      <c r="AC14" s="4" t="n"/>
-      <c r="AD14" s="4" t="n"/>
-      <c r="AE14" s="4" t="n"/>
-      <c r="AF14" s="4" t="n"/>
-      <c r="AG14" s="4" t="n"/>
-      <c r="AH14" s="4" t="n"/>
-      <c r="AI14" s="4" t="n"/>
-      <c r="AJ14" s="4" t="n"/>
-      <c r="AK14" s="4" t="n"/>
-      <c r="AL14" s="4" t="n"/>
-      <c r="AM14" s="4" t="n"/>
-      <c r="AN14" s="4" t="n"/>
-      <c r="AO14" s="4" t="n"/>
-      <c r="AP14" s="4" t="n"/>
-      <c r="AQ14" s="4" t="n"/>
-      <c r="AR14" s="4" t="n"/>
-      <c r="AS14" s="4" t="n"/>
-      <c r="AT14" s="4" t="n"/>
-      <c r="AU14" s="4" t="n"/>
-      <c r="AV14" s="4" t="n"/>
-      <c r="AW14" s="4" t="n"/>
-      <c r="AX14" s="4" t="n"/>
-      <c r="AY14" s="4" t="n"/>
-      <c r="AZ14" s="4" t="n"/>
-      <c r="BA14" s="4" t="n"/>
-      <c r="BB14" s="4" t="n"/>
-      <c r="BC14" s="4" t="n"/>
-      <c r="BD14" s="4" t="n"/>
-      <c r="BE14" s="4" t="n"/>
-      <c r="BF14" s="4" t="n"/>
-      <c r="BG14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -12828,58 +9786,6 @@
       <c r="E15" s="4" t="n"/>
       <c r="F15" s="4" t="n"/>
       <c r="G15" s="4" t="n"/>
-      <c r="H15" s="4" t="n"/>
-      <c r="I15" s="4" t="n"/>
-      <c r="J15" s="4" t="n"/>
-      <c r="K15" s="4" t="n"/>
-      <c r="L15" s="4" t="n"/>
-      <c r="M15" s="4" t="n"/>
-      <c r="N15" s="4" t="n"/>
-      <c r="O15" s="4" t="n"/>
-      <c r="P15" s="4" t="n"/>
-      <c r="Q15" s="4" t="n"/>
-      <c r="R15" s="4" t="n"/>
-      <c r="S15" s="4" t="n"/>
-      <c r="T15" s="4" t="n"/>
-      <c r="U15" s="4" t="n"/>
-      <c r="V15" s="4" t="n"/>
-      <c r="W15" s="4" t="n"/>
-      <c r="X15" s="4" t="n"/>
-      <c r="Y15" s="4" t="n"/>
-      <c r="Z15" s="4" t="n"/>
-      <c r="AA15" s="4" t="n"/>
-      <c r="AB15" s="4" t="n"/>
-      <c r="AC15" s="4" t="n"/>
-      <c r="AD15" s="4" t="n"/>
-      <c r="AE15" s="4" t="n"/>
-      <c r="AF15" s="4" t="n"/>
-      <c r="AG15" s="4" t="n"/>
-      <c r="AH15" s="4" t="n"/>
-      <c r="AI15" s="4" t="n"/>
-      <c r="AJ15" s="4" t="n"/>
-      <c r="AK15" s="4" t="n"/>
-      <c r="AL15" s="4" t="n"/>
-      <c r="AM15" s="4" t="n"/>
-      <c r="AN15" s="4" t="n"/>
-      <c r="AO15" s="4" t="n"/>
-      <c r="AP15" s="4" t="n"/>
-      <c r="AQ15" s="4" t="n"/>
-      <c r="AR15" s="4" t="n"/>
-      <c r="AS15" s="4" t="n"/>
-      <c r="AT15" s="4" t="n"/>
-      <c r="AU15" s="4" t="n"/>
-      <c r="AV15" s="4" t="n"/>
-      <c r="AW15" s="4" t="n"/>
-      <c r="AX15" s="4" t="n"/>
-      <c r="AY15" s="4" t="n"/>
-      <c r="AZ15" s="4" t="n"/>
-      <c r="BA15" s="4" t="n"/>
-      <c r="BB15" s="4" t="n"/>
-      <c r="BC15" s="4" t="n"/>
-      <c r="BD15" s="4" t="n"/>
-      <c r="BE15" s="4" t="n"/>
-      <c r="BF15" s="4" t="n"/>
-      <c r="BG15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
@@ -12897,58 +9803,6 @@
       <c r="E16" s="4" t="n"/>
       <c r="F16" s="4" t="n"/>
       <c r="G16" s="4" t="n"/>
-      <c r="H16" s="4" t="n"/>
-      <c r="I16" s="4" t="n"/>
-      <c r="J16" s="4" t="n"/>
-      <c r="K16" s="4" t="n"/>
-      <c r="L16" s="4" t="n"/>
-      <c r="M16" s="4" t="n"/>
-      <c r="N16" s="4" t="n"/>
-      <c r="O16" s="4" t="n"/>
-      <c r="P16" s="4" t="n"/>
-      <c r="Q16" s="4" t="n"/>
-      <c r="R16" s="4" t="n"/>
-      <c r="S16" s="4" t="n"/>
-      <c r="T16" s="4" t="n"/>
-      <c r="U16" s="4" t="n"/>
-      <c r="V16" s="4" t="n"/>
-      <c r="W16" s="4" t="n"/>
-      <c r="X16" s="4" t="n"/>
-      <c r="Y16" s="4" t="n"/>
-      <c r="Z16" s="4" t="n"/>
-      <c r="AA16" s="4" t="n"/>
-      <c r="AB16" s="4" t="n"/>
-      <c r="AC16" s="4" t="n"/>
-      <c r="AD16" s="4" t="n"/>
-      <c r="AE16" s="4" t="n"/>
-      <c r="AF16" s="4" t="n"/>
-      <c r="AG16" s="4" t="n"/>
-      <c r="AH16" s="4" t="n"/>
-      <c r="AI16" s="4" t="n"/>
-      <c r="AJ16" s="4" t="n"/>
-      <c r="AK16" s="4" t="n"/>
-      <c r="AL16" s="4" t="n"/>
-      <c r="AM16" s="4" t="n"/>
-      <c r="AN16" s="4" t="n"/>
-      <c r="AO16" s="4" t="n"/>
-      <c r="AP16" s="4" t="n"/>
-      <c r="AQ16" s="4" t="n"/>
-      <c r="AR16" s="4" t="n"/>
-      <c r="AS16" s="4" t="n"/>
-      <c r="AT16" s="4" t="n"/>
-      <c r="AU16" s="4" t="n"/>
-      <c r="AV16" s="4" t="n"/>
-      <c r="AW16" s="4" t="n"/>
-      <c r="AX16" s="4" t="n"/>
-      <c r="AY16" s="4" t="n"/>
-      <c r="AZ16" s="4" t="n"/>
-      <c r="BA16" s="4" t="n"/>
-      <c r="BB16" s="4" t="n"/>
-      <c r="BC16" s="4" t="n"/>
-      <c r="BD16" s="4" t="n"/>
-      <c r="BE16" s="4" t="n"/>
-      <c r="BF16" s="4" t="n"/>
-      <c r="BG16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
@@ -12966,58 +9820,6 @@
       <c r="E17" s="4" t="n"/>
       <c r="F17" s="4" t="n"/>
       <c r="G17" s="4" t="n"/>
-      <c r="H17" s="4" t="n"/>
-      <c r="I17" s="4" t="n"/>
-      <c r="J17" s="4" t="n"/>
-      <c r="K17" s="4" t="n"/>
-      <c r="L17" s="4" t="n"/>
-      <c r="M17" s="4" t="n"/>
-      <c r="N17" s="4" t="n"/>
-      <c r="O17" s="4" t="n"/>
-      <c r="P17" s="4" t="n"/>
-      <c r="Q17" s="4" t="n"/>
-      <c r="R17" s="4" t="n"/>
-      <c r="S17" s="4" t="n"/>
-      <c r="T17" s="4" t="n"/>
-      <c r="U17" s="4" t="n"/>
-      <c r="V17" s="4" t="n"/>
-      <c r="W17" s="4" t="n"/>
-      <c r="X17" s="4" t="n"/>
-      <c r="Y17" s="4" t="n"/>
-      <c r="Z17" s="4" t="n"/>
-      <c r="AA17" s="4" t="n"/>
-      <c r="AB17" s="4" t="n"/>
-      <c r="AC17" s="4" t="n"/>
-      <c r="AD17" s="4" t="n"/>
-      <c r="AE17" s="4" t="n"/>
-      <c r="AF17" s="4" t="n"/>
-      <c r="AG17" s="4" t="n"/>
-      <c r="AH17" s="4" t="n"/>
-      <c r="AI17" s="4" t="n"/>
-      <c r="AJ17" s="4" t="n"/>
-      <c r="AK17" s="4" t="n"/>
-      <c r="AL17" s="4" t="n"/>
-      <c r="AM17" s="4" t="n"/>
-      <c r="AN17" s="4" t="n"/>
-      <c r="AO17" s="4" t="n"/>
-      <c r="AP17" s="4" t="n"/>
-      <c r="AQ17" s="4" t="n"/>
-      <c r="AR17" s="4" t="n"/>
-      <c r="AS17" s="4" t="n"/>
-      <c r="AT17" s="4" t="n"/>
-      <c r="AU17" s="4" t="n"/>
-      <c r="AV17" s="4" t="n"/>
-      <c r="AW17" s="4" t="n"/>
-      <c r="AX17" s="4" t="n"/>
-      <c r="AY17" s="4" t="n"/>
-      <c r="AZ17" s="4" t="n"/>
-      <c r="BA17" s="4" t="n"/>
-      <c r="BB17" s="4" t="n"/>
-      <c r="BC17" s="4" t="n"/>
-      <c r="BD17" s="4" t="n"/>
-      <c r="BE17" s="4" t="n"/>
-      <c r="BF17" s="4" t="n"/>
-      <c r="BG17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n"/>
@@ -13035,58 +9837,6 @@
       <c r="E18" s="4" t="n"/>
       <c r="F18" s="4" t="n"/>
       <c r="G18" s="4" t="n"/>
-      <c r="H18" s="4" t="n"/>
-      <c r="I18" s="4" t="n"/>
-      <c r="J18" s="4" t="n"/>
-      <c r="K18" s="4" t="n"/>
-      <c r="L18" s="4" t="n"/>
-      <c r="M18" s="4" t="n"/>
-      <c r="N18" s="4" t="n"/>
-      <c r="O18" s="4" t="n"/>
-      <c r="P18" s="4" t="n"/>
-      <c r="Q18" s="4" t="n"/>
-      <c r="R18" s="4" t="n"/>
-      <c r="S18" s="4" t="n"/>
-      <c r="T18" s="4" t="n"/>
-      <c r="U18" s="4" t="n"/>
-      <c r="V18" s="4" t="n"/>
-      <c r="W18" s="4" t="n"/>
-      <c r="X18" s="4" t="n"/>
-      <c r="Y18" s="4" t="n"/>
-      <c r="Z18" s="4" t="n"/>
-      <c r="AA18" s="4" t="n"/>
-      <c r="AB18" s="4" t="n"/>
-      <c r="AC18" s="4" t="n"/>
-      <c r="AD18" s="4" t="n"/>
-      <c r="AE18" s="4" t="n"/>
-      <c r="AF18" s="4" t="n"/>
-      <c r="AG18" s="4" t="n"/>
-      <c r="AH18" s="4" t="n"/>
-      <c r="AI18" s="4" t="n"/>
-      <c r="AJ18" s="4" t="n"/>
-      <c r="AK18" s="4" t="n"/>
-      <c r="AL18" s="4" t="n"/>
-      <c r="AM18" s="4" t="n"/>
-      <c r="AN18" s="4" t="n"/>
-      <c r="AO18" s="4" t="n"/>
-      <c r="AP18" s="4" t="n"/>
-      <c r="AQ18" s="4" t="n"/>
-      <c r="AR18" s="4" t="n"/>
-      <c r="AS18" s="4" t="n"/>
-      <c r="AT18" s="4" t="n"/>
-      <c r="AU18" s="4" t="n"/>
-      <c r="AV18" s="4" t="n"/>
-      <c r="AW18" s="4" t="n"/>
-      <c r="AX18" s="4" t="n"/>
-      <c r="AY18" s="4" t="n"/>
-      <c r="AZ18" s="4" t="n"/>
-      <c r="BA18" s="4" t="n"/>
-      <c r="BB18" s="4" t="n"/>
-      <c r="BC18" s="4" t="n"/>
-      <c r="BD18" s="4" t="n"/>
-      <c r="BE18" s="4" t="n"/>
-      <c r="BF18" s="4" t="n"/>
-      <c r="BG18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -13108,58 +9858,6 @@
       <c r="E19" s="4" t="n"/>
       <c r="F19" s="4" t="n"/>
       <c r="G19" s="4" t="n"/>
-      <c r="H19" s="4" t="n"/>
-      <c r="I19" s="4" t="n"/>
-      <c r="J19" s="4" t="n"/>
-      <c r="K19" s="4" t="n"/>
-      <c r="L19" s="4" t="n"/>
-      <c r="M19" s="4" t="n"/>
-      <c r="N19" s="4" t="n"/>
-      <c r="O19" s="4" t="n"/>
-      <c r="P19" s="4" t="n"/>
-      <c r="Q19" s="4" t="n"/>
-      <c r="R19" s="4" t="n"/>
-      <c r="S19" s="4" t="n"/>
-      <c r="T19" s="4" t="n"/>
-      <c r="U19" s="4" t="n"/>
-      <c r="V19" s="4" t="n"/>
-      <c r="W19" s="4" t="n"/>
-      <c r="X19" s="4" t="n"/>
-      <c r="Y19" s="4" t="n"/>
-      <c r="Z19" s="4" t="n"/>
-      <c r="AA19" s="4" t="n"/>
-      <c r="AB19" s="4" t="n"/>
-      <c r="AC19" s="4" t="n"/>
-      <c r="AD19" s="4" t="n"/>
-      <c r="AE19" s="4" t="n"/>
-      <c r="AF19" s="4" t="n"/>
-      <c r="AG19" s="4" t="n"/>
-      <c r="AH19" s="4" t="n"/>
-      <c r="AI19" s="4" t="n"/>
-      <c r="AJ19" s="4" t="n"/>
-      <c r="AK19" s="4" t="n"/>
-      <c r="AL19" s="4" t="n"/>
-      <c r="AM19" s="4" t="n"/>
-      <c r="AN19" s="4" t="n"/>
-      <c r="AO19" s="4" t="n"/>
-      <c r="AP19" s="4" t="n"/>
-      <c r="AQ19" s="4" t="n"/>
-      <c r="AR19" s="4" t="n"/>
-      <c r="AS19" s="4" t="n"/>
-      <c r="AT19" s="4" t="n"/>
-      <c r="AU19" s="4" t="n"/>
-      <c r="AV19" s="4" t="n"/>
-      <c r="AW19" s="4" t="n"/>
-      <c r="AX19" s="4" t="n"/>
-      <c r="AY19" s="4" t="n"/>
-      <c r="AZ19" s="4" t="n"/>
-      <c r="BA19" s="4" t="n"/>
-      <c r="BB19" s="4" t="n"/>
-      <c r="BC19" s="4" t="n"/>
-      <c r="BD19" s="4" t="n"/>
-      <c r="BE19" s="4" t="n"/>
-      <c r="BF19" s="4" t="n"/>
-      <c r="BG19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -13180,61 +9878,9 @@
       <c r="D20" s="4" t="n"/>
       <c r="E20" s="4" t="n"/>
       <c r="F20" s="4" t="n"/>
-      <c r="G20" s="4" t="n"/>
-      <c r="H20" s="4" t="n"/>
-      <c r="I20" s="4" t="n"/>
-      <c r="J20" s="4" t="n"/>
-      <c r="K20" s="4" t="n"/>
-      <c r="L20" s="4" t="n"/>
-      <c r="M20" s="4" t="n"/>
-      <c r="N20" s="4" t="n"/>
-      <c r="O20" s="4" t="n"/>
-      <c r="P20" s="4" t="n"/>
-      <c r="Q20" s="4" t="n"/>
-      <c r="R20" s="4" t="n"/>
-      <c r="S20" s="4" t="n"/>
-      <c r="T20" s="4" t="n"/>
-      <c r="U20" s="4" t="n"/>
-      <c r="V20" s="4" t="n"/>
-      <c r="W20" s="4" t="n"/>
-      <c r="X20" s="4" t="n">
+      <c r="G20" s="4" t="n">
         <v>18.9</v>
       </c>
-      <c r="Y20" s="4" t="n"/>
-      <c r="Z20" s="4" t="n"/>
-      <c r="AA20" s="4" t="n"/>
-      <c r="AB20" s="4" t="n"/>
-      <c r="AC20" s="4" t="n"/>
-      <c r="AD20" s="4" t="n"/>
-      <c r="AE20" s="4" t="n"/>
-      <c r="AF20" s="4" t="n"/>
-      <c r="AG20" s="4" t="n"/>
-      <c r="AH20" s="4" t="n"/>
-      <c r="AI20" s="4" t="n"/>
-      <c r="AJ20" s="4" t="n"/>
-      <c r="AK20" s="4" t="n"/>
-      <c r="AL20" s="4" t="n"/>
-      <c r="AM20" s="4" t="n"/>
-      <c r="AN20" s="4" t="n"/>
-      <c r="AO20" s="4" t="n"/>
-      <c r="AP20" s="4" t="n"/>
-      <c r="AQ20" s="4" t="n"/>
-      <c r="AR20" s="4" t="n"/>
-      <c r="AS20" s="4" t="n"/>
-      <c r="AT20" s="4" t="n"/>
-      <c r="AU20" s="4" t="n"/>
-      <c r="AV20" s="4" t="n"/>
-      <c r="AW20" s="4" t="n"/>
-      <c r="AX20" s="4" t="n"/>
-      <c r="AY20" s="4" t="n"/>
-      <c r="AZ20" s="4" t="n"/>
-      <c r="BA20" s="4" t="n"/>
-      <c r="BB20" s="4" t="n"/>
-      <c r="BC20" s="4" t="n"/>
-      <c r="BD20" s="4" t="n"/>
-      <c r="BE20" s="4" t="n"/>
-      <c r="BF20" s="4" t="n"/>
-      <c r="BG20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -13256,61 +9902,9 @@
       <c r="E21" s="4" t="n"/>
       <c r="F21" s="4" t="n"/>
       <c r="G21" s="4" t="n"/>
-      <c r="H21" s="4" t="n"/>
-      <c r="I21" s="4" t="n"/>
-      <c r="J21" s="4" t="n"/>
-      <c r="K21" s="4" t="n"/>
-      <c r="L21" s="4" t="n"/>
-      <c r="M21" s="4" t="n"/>
-      <c r="N21" s="4" t="n"/>
-      <c r="O21" s="4" t="n"/>
-      <c r="P21" s="4" t="n"/>
-      <c r="Q21" s="4" t="n"/>
-      <c r="R21" s="4" t="n"/>
-      <c r="S21" s="4" t="n"/>
-      <c r="T21" s="4" t="n"/>
-      <c r="U21" s="4" t="n"/>
-      <c r="V21" s="4" t="n"/>
-      <c r="W21" s="4" t="n"/>
-      <c r="X21" s="4" t="n"/>
-      <c r="Y21" s="4" t="n"/>
-      <c r="Z21" s="4" t="n"/>
-      <c r="AA21" s="4" t="n"/>
-      <c r="AB21" s="4" t="n"/>
-      <c r="AC21" s="4" t="n"/>
-      <c r="AD21" s="4" t="n"/>
-      <c r="AE21" s="4" t="n"/>
-      <c r="AF21" s="4" t="n"/>
-      <c r="AG21" s="4" t="n"/>
-      <c r="AH21" s="4" t="n"/>
-      <c r="AI21" s="4" t="n"/>
-      <c r="AJ21" s="4" t="n"/>
-      <c r="AK21" s="4" t="n"/>
-      <c r="AL21" s="4" t="n"/>
-      <c r="AM21" s="4" t="n"/>
-      <c r="AN21" s="4" t="n"/>
-      <c r="AO21" s="4" t="n"/>
-      <c r="AP21" s="4" t="n"/>
-      <c r="AQ21" s="4" t="n"/>
-      <c r="AR21" s="4" t="n"/>
-      <c r="AS21" s="4" t="n"/>
-      <c r="AT21" s="4" t="n"/>
-      <c r="AU21" s="4" t="n"/>
-      <c r="AV21" s="4" t="n"/>
-      <c r="AW21" s="4" t="n"/>
-      <c r="AX21" s="4" t="n"/>
-      <c r="AY21" s="4" t="n"/>
-      <c r="AZ21" s="4" t="n"/>
-      <c r="BA21" s="4" t="n"/>
-      <c r="BB21" s="4" t="n"/>
-      <c r="BC21" s="4" t="n"/>
-      <c r="BD21" s="4" t="n"/>
-      <c r="BE21" s="4" t="n"/>
-      <c r="BF21" s="4" t="n"/>
-      <c r="BG21" s="4" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BG21"/>
+  <autoFilter ref="A1:G21"/>
   <mergeCells count="14">
     <mergeCell ref="A8"/>
     <mergeCell ref="A6"/>
@@ -65012,7 +61606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG21"/>
+  <dimension ref="A1:AO21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -65056,24 +61650,6 @@
     <col width="7.5" customWidth="1" min="39" max="39"/>
     <col width="7.5" customWidth="1" min="40" max="40"/>
     <col width="7.5" customWidth="1" min="41" max="41"/>
-    <col width="7.5" customWidth="1" min="42" max="42"/>
-    <col width="7.5" customWidth="1" min="43" max="43"/>
-    <col width="7.5" customWidth="1" min="44" max="44"/>
-    <col width="7.5" customWidth="1" min="45" max="45"/>
-    <col width="7.5" customWidth="1" min="46" max="46"/>
-    <col width="7.5" customWidth="1" min="47" max="47"/>
-    <col width="7.5" customWidth="1" min="48" max="48"/>
-    <col width="7.5" customWidth="1" min="49" max="49"/>
-    <col width="7.5" customWidth="1" min="50" max="50"/>
-    <col width="7.5" customWidth="1" min="51" max="51"/>
-    <col width="7.5" customWidth="1" min="52" max="52"/>
-    <col width="7.5" customWidth="1" min="53" max="53"/>
-    <col width="7.5" customWidth="1" min="54" max="54"/>
-    <col width="7.5" customWidth="1" min="55" max="55"/>
-    <col width="7.5" customWidth="1" min="56" max="56"/>
-    <col width="7.5" customWidth="1" min="57" max="57"/>
-    <col width="7.5" customWidth="1" min="58" max="58"/>
-    <col width="7.5" customWidth="1" min="59" max="59"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -65094,282 +61670,192 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>玻璃★6</t>
+          <t>玻璃</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>玻璃</t>
+          <t>杰皇</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>杰皇★6</t>
+          <t>恶魔</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>杰皇</t>
+          <t>r兔</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>恶魔</t>
+          <t>f5r</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>r兔★6</t>
+          <t>f5</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>r兔</t>
+          <t>杰哥</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>f5r</t>
+          <t>c2</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>f5★6</t>
+          <t>杰弟</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>f5</t>
+          <t>银电</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>杰哥</t>
+          <t>21c</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>c2★6</t>
+          <t>9x8</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>c2</t>
+          <t>黑龙</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>杰弟</t>
+          <t>ssc</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>银电</t>
+          <t>陀飞轮</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>21c</t>
+          <t>白龙</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>9x8★6</t>
+          <t>fp1</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>9x8</t>
+          <t>万达</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>黑龙★6</t>
+          <t>速尾</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>黑龙</t>
+          <t>肥龙</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>ssc</t>
+          <t>sf90</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>陀飞轮</t>
+          <t>sgt</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>白龙★6</t>
+          <t>火山</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>白龙</t>
+          <t>猫头鹰</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>fp1★6</t>
+          <t>秋王</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>fp1</t>
+          <t>风龙</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>爱音</t>
+          <t>小牛</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>万达★6</t>
+          <t>fe3</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>万达</t>
+          <t>法拉第</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>速尾★6</t>
+          <t>六子</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>速尾</t>
+          <t>帕梅</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>肥龙</t>
+          <t>ps龙</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>sf90★6</t>
+          <t>ts900</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>sf90</t>
+          <t>divo</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>sgt★6</t>
+          <t>att</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>sgt</t>
+          <t>650s</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>火山</t>
+          <t>英灵殿</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>猫头鹰</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>秋王★6</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>秋王</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>风龙</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>小牛★6</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>小牛</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>fe3★5</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>fe3</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>法拉第</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>六子</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>帕梅</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>ps龙</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>ts900</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>divo</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>att</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>650s</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>英灵殿</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
           <t>帝国</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>狼王</t>
         </is>
       </c>
     </row>
@@ -65400,15 +61886,15 @@
       <c r="L2" s="4" t="n"/>
       <c r="M2" s="4" t="n"/>
       <c r="N2" s="4" t="n"/>
-      <c r="O2" s="4" t="n"/>
+      <c r="O2" s="4" t="n">
+        <v>16.9</v>
+      </c>
       <c r="P2" s="4" t="n"/>
       <c r="Q2" s="4" t="n"/>
       <c r="R2" s="4" t="n"/>
       <c r="S2" s="4" t="n"/>
       <c r="T2" s="4" t="n"/>
-      <c r="U2" s="4" t="n">
-        <v>16.9</v>
-      </c>
+      <c r="U2" s="4" t="n"/>
       <c r="V2" s="4" t="n"/>
       <c r="W2" s="4" t="n"/>
       <c r="X2" s="4" t="n"/>
@@ -65421,7 +61907,9 @@
       <c r="AE2" s="4" t="n"/>
       <c r="AF2" s="4" t="n"/>
       <c r="AG2" s="4" t="n"/>
-      <c r="AH2" s="4" t="n"/>
+      <c r="AH2" s="4" t="n">
+        <v>18.9</v>
+      </c>
       <c r="AI2" s="4" t="n"/>
       <c r="AJ2" s="4" t="n"/>
       <c r="AK2" s="4" t="n"/>
@@ -65429,26 +61917,6 @@
       <c r="AM2" s="4" t="n"/>
       <c r="AN2" s="4" t="n"/>
       <c r="AO2" s="4" t="n"/>
-      <c r="AP2" s="4" t="n"/>
-      <c r="AQ2" s="4" t="n"/>
-      <c r="AR2" s="4" t="n"/>
-      <c r="AS2" s="4" t="n"/>
-      <c r="AT2" s="4" t="n"/>
-      <c r="AU2" s="4" t="n"/>
-      <c r="AV2" s="4" t="n"/>
-      <c r="AW2" s="4" t="n"/>
-      <c r="AX2" s="4" t="n"/>
-      <c r="AY2" s="4" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="AZ2" s="4" t="n"/>
-      <c r="BA2" s="4" t="n"/>
-      <c r="BB2" s="4" t="n"/>
-      <c r="BC2" s="4" t="n"/>
-      <c r="BD2" s="4" t="n"/>
-      <c r="BE2" s="4" t="n"/>
-      <c r="BF2" s="4" t="n"/>
-      <c r="BG2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="n"/>
@@ -65463,11 +61931,11 @@
         </is>
       </c>
       <c r="D3" s="4" t="n"/>
-      <c r="E3" s="4" t="n"/>
+      <c r="E3" s="4" t="n">
+        <v>23.49</v>
+      </c>
       <c r="F3" s="4" t="n"/>
-      <c r="G3" s="4" t="n">
-        <v>23.49</v>
-      </c>
+      <c r="G3" s="4" t="n"/>
       <c r="H3" s="4" t="n"/>
       <c r="I3" s="4" t="n"/>
       <c r="J3" s="4" t="n"/>
@@ -65476,16 +61944,16 @@
       <c r="M3" s="4" t="n"/>
       <c r="N3" s="4" t="n"/>
       <c r="O3" s="4" t="n"/>
-      <c r="P3" s="4" t="n"/>
+      <c r="P3" s="4" t="n">
+        <v>25.5</v>
+      </c>
       <c r="Q3" s="4" t="n"/>
       <c r="R3" s="4" t="n"/>
       <c r="S3" s="4" t="n"/>
       <c r="T3" s="4" t="n"/>
       <c r="U3" s="4" t="n"/>
       <c r="V3" s="4" t="n"/>
-      <c r="W3" s="4" t="n">
-        <v>25.5</v>
-      </c>
+      <c r="W3" s="4" t="n"/>
       <c r="X3" s="4" t="n"/>
       <c r="Y3" s="4" t="n"/>
       <c r="Z3" s="4" t="n"/>
@@ -65504,24 +61972,6 @@
       <c r="AM3" s="4" t="n"/>
       <c r="AN3" s="4" t="n"/>
       <c r="AO3" s="4" t="n"/>
-      <c r="AP3" s="4" t="n"/>
-      <c r="AQ3" s="4" t="n"/>
-      <c r="AR3" s="4" t="n"/>
-      <c r="AS3" s="4" t="n"/>
-      <c r="AT3" s="4" t="n"/>
-      <c r="AU3" s="4" t="n"/>
-      <c r="AV3" s="4" t="n"/>
-      <c r="AW3" s="4" t="n"/>
-      <c r="AX3" s="4" t="n"/>
-      <c r="AY3" s="4" t="n"/>
-      <c r="AZ3" s="4" t="n"/>
-      <c r="BA3" s="4" t="n"/>
-      <c r="BB3" s="4" t="n"/>
-      <c r="BC3" s="4" t="n"/>
-      <c r="BD3" s="4" t="n"/>
-      <c r="BE3" s="4" t="n"/>
-      <c r="BF3" s="4" t="n"/>
-      <c r="BG3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -65542,41 +61992,41 @@
       <c r="D4" s="4" t="n"/>
       <c r="E4" s="4" t="n"/>
       <c r="F4" s="4" t="n"/>
-      <c r="G4" s="4" t="n"/>
+      <c r="G4" s="4" t="n">
+        <v>22.89</v>
+      </c>
       <c r="H4" s="4" t="n"/>
       <c r="I4" s="4" t="n"/>
-      <c r="J4" s="4" t="n">
-        <v>22.89</v>
-      </c>
-      <c r="K4" s="4" t="n"/>
-      <c r="L4" s="4" t="n"/>
+      <c r="J4" s="4" t="n"/>
+      <c r="K4" s="4" t="n">
+        <v>23.38</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>23.5</v>
+      </c>
       <c r="M4" s="4" t="n"/>
       <c r="N4" s="4" t="n"/>
-      <c r="O4" s="4" t="n"/>
+      <c r="O4" s="4" t="n">
+        <v>24.99</v>
+      </c>
       <c r="P4" s="4" t="n">
-        <v>23.38</v>
-      </c>
-      <c r="Q4" s="4" t="n">
-        <v>23.5</v>
-      </c>
+        <v>23.6</v>
+      </c>
+      <c r="Q4" s="4" t="n"/>
       <c r="R4" s="4" t="n"/>
       <c r="S4" s="4" t="n"/>
-      <c r="T4" s="4" t="n"/>
-      <c r="U4" s="4" t="n">
-        <v>24.99</v>
-      </c>
+      <c r="T4" s="4" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="U4" s="4" t="n"/>
       <c r="V4" s="4" t="n"/>
-      <c r="W4" s="4" t="n">
-        <v>23.6</v>
-      </c>
+      <c r="W4" s="4" t="n"/>
       <c r="X4" s="4" t="n"/>
       <c r="Y4" s="4" t="n"/>
       <c r="Z4" s="4" t="n"/>
       <c r="AA4" s="4" t="n"/>
       <c r="AB4" s="4" t="n"/>
-      <c r="AC4" s="4" t="n">
-        <v>23.9</v>
-      </c>
+      <c r="AC4" s="4" t="n"/>
       <c r="AD4" s="4" t="n"/>
       <c r="AE4" s="4" t="n"/>
       <c r="AF4" s="4" t="n"/>
@@ -65589,24 +62039,6 @@
       <c r="AM4" s="4" t="n"/>
       <c r="AN4" s="4" t="n"/>
       <c r="AO4" s="4" t="n"/>
-      <c r="AP4" s="4" t="n"/>
-      <c r="AQ4" s="4" t="n"/>
-      <c r="AR4" s="4" t="n"/>
-      <c r="AS4" s="4" t="n"/>
-      <c r="AT4" s="4" t="n"/>
-      <c r="AU4" s="4" t="n"/>
-      <c r="AV4" s="4" t="n"/>
-      <c r="AW4" s="4" t="n"/>
-      <c r="AX4" s="4" t="n"/>
-      <c r="AY4" s="4" t="n"/>
-      <c r="AZ4" s="4" t="n"/>
-      <c r="BA4" s="4" t="n"/>
-      <c r="BB4" s="4" t="n"/>
-      <c r="BC4" s="4" t="n"/>
-      <c r="BD4" s="4" t="n"/>
-      <c r="BE4" s="4" t="n"/>
-      <c r="BF4" s="4" t="n"/>
-      <c r="BG4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -65627,39 +62059,39 @@
       <c r="D5" s="4" t="n"/>
       <c r="E5" s="4" t="n"/>
       <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
+      <c r="G5" s="4" t="n">
+        <v>21.7</v>
+      </c>
       <c r="H5" s="4" t="n"/>
       <c r="I5" s="4" t="n"/>
-      <c r="J5" s="4" t="n">
+      <c r="J5" s="4" t="n"/>
+      <c r="K5" s="4" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="M5" s="4" t="n"/>
+      <c r="N5" s="4" t="n">
         <v>21.7</v>
       </c>
-      <c r="K5" s="4" t="n"/>
-      <c r="L5" s="4" t="n"/>
-      <c r="M5" s="4" t="n"/>
-      <c r="N5" s="4" t="n"/>
-      <c r="O5" s="4" t="n"/>
-      <c r="P5" s="4" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="Q5" s="4" t="n">
-        <v>22.1</v>
-      </c>
+      <c r="O5" s="4" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="P5" s="4" t="n"/>
+      <c r="Q5" s="4" t="n"/>
       <c r="R5" s="4" t="n"/>
       <c r="S5" s="4" t="n">
-        <v>21.7</v>
+        <v>21.9</v>
       </c>
       <c r="T5" s="4" t="n"/>
-      <c r="U5" s="4" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="U5" s="4" t="n"/>
       <c r="V5" s="4" t="n"/>
       <c r="W5" s="4" t="n"/>
       <c r="X5" s="4" t="n"/>
       <c r="Y5" s="4" t="n"/>
       <c r="Z5" s="4" t="n"/>
-      <c r="AA5" s="4" t="n">
-        <v>21.9</v>
-      </c>
+      <c r="AA5" s="4" t="n"/>
       <c r="AB5" s="4" t="n"/>
       <c r="AC5" s="4" t="n"/>
       <c r="AD5" s="4" t="n"/>
@@ -65674,24 +62106,6 @@
       <c r="AM5" s="4" t="n"/>
       <c r="AN5" s="4" t="n"/>
       <c r="AO5" s="4" t="n"/>
-      <c r="AP5" s="4" t="n"/>
-      <c r="AQ5" s="4" t="n"/>
-      <c r="AR5" s="4" t="n"/>
-      <c r="AS5" s="4" t="n"/>
-      <c r="AT5" s="4" t="n"/>
-      <c r="AU5" s="4" t="n"/>
-      <c r="AV5" s="4" t="n"/>
-      <c r="AW5" s="4" t="n"/>
-      <c r="AX5" s="4" t="n"/>
-      <c r="AY5" s="4" t="n"/>
-      <c r="AZ5" s="4" t="n"/>
-      <c r="BA5" s="4" t="n"/>
-      <c r="BB5" s="4" t="n"/>
-      <c r="BC5" s="4" t="n"/>
-      <c r="BD5" s="4" t="n"/>
-      <c r="BE5" s="4" t="n"/>
-      <c r="BF5" s="4" t="n"/>
-      <c r="BG5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -65709,82 +62123,64 @@
           <t>滑栏杆</t>
         </is>
       </c>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="n">
+      <c r="D6" s="4" t="n">
         <v>22.34</v>
       </c>
+      <c r="E6" s="4" t="n"/>
       <c r="F6" s="4" t="n"/>
       <c r="G6" s="4" t="n"/>
       <c r="H6" s="4" t="n"/>
       <c r="I6" s="4" t="n"/>
       <c r="J6" s="4" t="n"/>
-      <c r="K6" s="4" t="n"/>
-      <c r="L6" s="4" t="n"/>
+      <c r="K6" s="4" t="n">
+        <v>22.19</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>22.26</v>
+      </c>
       <c r="M6" s="4" t="n"/>
-      <c r="N6" s="4" t="n"/>
-      <c r="O6" s="4" t="n"/>
-      <c r="P6" s="4" t="n">
-        <v>22.19</v>
-      </c>
-      <c r="Q6" s="4" t="n">
-        <v>22.26</v>
-      </c>
-      <c r="R6" s="4" t="n"/>
-      <c r="S6" s="4" t="n">
+      <c r="N6" s="4" t="n">
         <v>22.09</v>
       </c>
+      <c r="O6" s="4" t="n">
+        <v>23.58</v>
+      </c>
+      <c r="P6" s="4" t="n"/>
+      <c r="Q6" s="4" t="n"/>
+      <c r="R6" s="4" t="n">
+        <v>21.95</v>
+      </c>
+      <c r="S6" s="4" t="n"/>
       <c r="T6" s="4" t="n"/>
-      <c r="U6" s="4" t="n">
-        <v>23.58</v>
-      </c>
+      <c r="U6" s="4" t="n"/>
       <c r="V6" s="4" t="n"/>
       <c r="W6" s="4" t="n"/>
       <c r="X6" s="4" t="n"/>
-      <c r="Y6" s="4" t="n">
-        <v>21.95</v>
-      </c>
+      <c r="Y6" s="4" t="n"/>
       <c r="Z6" s="4" t="n"/>
       <c r="AA6" s="4" t="n"/>
-      <c r="AB6" s="4" t="n"/>
+      <c r="AB6" s="4" t="n">
+        <v>23.11</v>
+      </c>
       <c r="AC6" s="4" t="n"/>
       <c r="AD6" s="4" t="n"/>
       <c r="AE6" s="4" t="n"/>
       <c r="AF6" s="4" t="n"/>
       <c r="AG6" s="4" t="n"/>
       <c r="AH6" s="4" t="n"/>
-      <c r="AI6" s="4" t="n"/>
-      <c r="AJ6" s="4" t="n"/>
-      <c r="AK6" s="4" t="n"/>
+      <c r="AI6" s="4" t="n">
+        <v>22.82</v>
+      </c>
+      <c r="AJ6" s="4" t="n">
+        <v>22.83</v>
+      </c>
+      <c r="AK6" s="4" t="n">
+        <v>22.89</v>
+      </c>
       <c r="AL6" s="4" t="n"/>
       <c r="AM6" s="4" t="n"/>
       <c r="AN6" s="4" t="n"/>
       <c r="AO6" s="4" t="n"/>
-      <c r="AP6" s="4" t="n"/>
-      <c r="AQ6" s="4" t="n">
-        <v>23.11</v>
-      </c>
-      <c r="AR6" s="4" t="n"/>
-      <c r="AS6" s="4" t="n"/>
-      <c r="AT6" s="4" t="n"/>
-      <c r="AU6" s="4" t="n"/>
-      <c r="AV6" s="4" t="n"/>
-      <c r="AW6" s="4" t="n"/>
-      <c r="AX6" s="4" t="n"/>
-      <c r="AY6" s="4" t="n"/>
-      <c r="AZ6" s="4" t="n">
-        <v>22.82</v>
-      </c>
-      <c r="BA6" s="4" t="n">
-        <v>22.83</v>
-      </c>
-      <c r="BB6" s="4" t="n">
-        <v>22.89</v>
-      </c>
-      <c r="BC6" s="4" t="n"/>
-      <c r="BD6" s="4" t="n"/>
-      <c r="BE6" s="4" t="n"/>
-      <c r="BF6" s="4" t="n"/>
-      <c r="BG6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -65802,86 +62198,68 @@
           <t>滑雪</t>
         </is>
       </c>
-      <c r="D7" s="4" t="n"/>
-      <c r="E7" s="4" t="n">
+      <c r="D7" s="4" t="n">
         <v>17.99</v>
       </c>
+      <c r="E7" s="4" t="n"/>
       <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n"/>
+      <c r="G7" s="4" t="n">
+        <v>17.5</v>
+      </c>
       <c r="H7" s="4" t="n"/>
       <c r="I7" s="4" t="n"/>
-      <c r="J7" s="4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="K7" s="4" t="n"/>
+      <c r="J7" s="4" t="n"/>
+      <c r="K7" s="4" t="n">
+        <v>17.89</v>
+      </c>
       <c r="L7" s="4" t="n"/>
       <c r="M7" s="4" t="n"/>
-      <c r="N7" s="4" t="n"/>
+      <c r="N7" s="4" t="n">
+        <v>17.59</v>
+      </c>
       <c r="O7" s="4" t="n"/>
       <c r="P7" s="4" t="n">
-        <v>17.89</v>
+        <v>17.79</v>
       </c>
       <c r="Q7" s="4" t="n"/>
       <c r="R7" s="4" t="n"/>
       <c r="S7" s="4" t="n">
-        <v>17.59</v>
+        <v>17.95</v>
       </c>
       <c r="T7" s="4" t="n"/>
       <c r="U7" s="4" t="n"/>
       <c r="V7" s="4" t="n"/>
       <c r="W7" s="4" t="n">
-        <v>17.79</v>
+        <v>18.05</v>
       </c>
       <c r="X7" s="4" t="n"/>
       <c r="Y7" s="4" t="n"/>
       <c r="Z7" s="4" t="n"/>
       <c r="AA7" s="4" t="n">
-        <v>17.95</v>
-      </c>
-      <c r="AB7" s="4" t="n"/>
-      <c r="AC7" s="4" t="n"/>
+        <v>17.88</v>
+      </c>
+      <c r="AB7" s="4" t="n">
+        <v>18.37</v>
+      </c>
+      <c r="AC7" s="4" t="n">
+        <v>17.98</v>
+      </c>
       <c r="AD7" s="4" t="n"/>
       <c r="AE7" s="4" t="n"/>
-      <c r="AF7" s="4" t="n"/>
+      <c r="AF7" s="4" t="n">
+        <v>18.07</v>
+      </c>
       <c r="AG7" s="4" t="n"/>
       <c r="AH7" s="4" t="n"/>
-      <c r="AI7" s="4" t="n">
-        <v>18.05</v>
-      </c>
+      <c r="AI7" s="4" t="n"/>
       <c r="AJ7" s="4" t="n"/>
       <c r="AK7" s="4" t="n"/>
       <c r="AL7" s="4" t="n"/>
       <c r="AM7" s="4" t="n"/>
       <c r="AN7" s="4" t="n"/>
       <c r="AO7" s="4" t="n">
-        <v>17.88</v>
-      </c>
-      <c r="AP7" s="4" t="n"/>
-      <c r="AQ7" s="4" t="n">
-        <v>18.37</v>
-      </c>
-      <c r="AR7" s="4" t="n">
-        <v>17.98</v>
-      </c>
-      <c r="AS7" s="4" t="n"/>
-      <c r="AT7" s="4" t="n"/>
-      <c r="AU7" s="4" t="n"/>
-      <c r="AV7" s="4" t="n"/>
-      <c r="AW7" s="4" t="n">
-        <v>18.07</v>
-      </c>
-      <c r="AX7" s="4" t="n"/>
-      <c r="AY7" s="4" t="n"/>
-      <c r="AZ7" s="4" t="n"/>
-      <c r="BA7" s="4" t="n"/>
-      <c r="BB7" s="4" t="n"/>
-      <c r="BC7" s="4" t="n"/>
-      <c r="BD7" s="4" t="n"/>
-      <c r="BE7" s="4" t="n"/>
-      <c r="BF7" s="4" t="n">
         <v>18.09</v>
       </c>
-      <c r="BG7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -65902,12 +62280,12 @@
       <c r="D8" s="4" t="n"/>
       <c r="E8" s="4" t="n"/>
       <c r="F8" s="4" t="n"/>
-      <c r="G8" s="4" t="n"/>
+      <c r="G8" s="4" t="n">
+        <v>18</v>
+      </c>
       <c r="H8" s="4" t="n"/>
       <c r="I8" s="4" t="n"/>
-      <c r="J8" s="4" t="n">
-        <v>18</v>
-      </c>
+      <c r="J8" s="4" t="n"/>
       <c r="K8" s="4" t="n"/>
       <c r="L8" s="4" t="n"/>
       <c r="M8" s="4" t="n"/>
@@ -65916,7 +62294,9 @@
       <c r="P8" s="4" t="n"/>
       <c r="Q8" s="4" t="n"/>
       <c r="R8" s="4" t="n"/>
-      <c r="S8" s="4" t="n"/>
+      <c r="S8" s="4" t="n">
+        <v>18.1</v>
+      </c>
       <c r="T8" s="4" t="n"/>
       <c r="U8" s="4" t="n"/>
       <c r="V8" s="4" t="n"/>
@@ -65924,10 +62304,10 @@
       <c r="X8" s="4" t="n"/>
       <c r="Y8" s="4" t="n"/>
       <c r="Z8" s="4" t="n"/>
-      <c r="AA8" s="4" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="AB8" s="4" t="n"/>
+      <c r="AA8" s="4" t="n"/>
+      <c r="AB8" s="4" t="n">
+        <v>18.75</v>
+      </c>
       <c r="AC8" s="4" t="n"/>
       <c r="AD8" s="4" t="n"/>
       <c r="AE8" s="4" t="n"/>
@@ -65941,26 +62321,6 @@
       <c r="AM8" s="4" t="n"/>
       <c r="AN8" s="4" t="n"/>
       <c r="AO8" s="4" t="n"/>
-      <c r="AP8" s="4" t="n"/>
-      <c r="AQ8" s="4" t="n">
-        <v>18.75</v>
-      </c>
-      <c r="AR8" s="4" t="n"/>
-      <c r="AS8" s="4" t="n"/>
-      <c r="AT8" s="4" t="n"/>
-      <c r="AU8" s="4" t="n"/>
-      <c r="AV8" s="4" t="n"/>
-      <c r="AW8" s="4" t="n"/>
-      <c r="AX8" s="4" t="n"/>
-      <c r="AY8" s="4" t="n"/>
-      <c r="AZ8" s="4" t="n"/>
-      <c r="BA8" s="4" t="n"/>
-      <c r="BB8" s="4" t="n"/>
-      <c r="BC8" s="4" t="n"/>
-      <c r="BD8" s="4" t="n"/>
-      <c r="BE8" s="4" t="n"/>
-      <c r="BF8" s="4" t="n"/>
-      <c r="BG8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -65993,7 +62353,9 @@
       <c r="P9" s="4" t="n"/>
       <c r="Q9" s="4" t="n"/>
       <c r="R9" s="4" t="n"/>
-      <c r="S9" s="4" t="n"/>
+      <c r="S9" s="4" t="n">
+        <v>18</v>
+      </c>
       <c r="T9" s="4" t="n"/>
       <c r="U9" s="4" t="n"/>
       <c r="V9" s="4" t="n"/>
@@ -66001,9 +62363,7 @@
       <c r="X9" s="4" t="n"/>
       <c r="Y9" s="4" t="n"/>
       <c r="Z9" s="4" t="n"/>
-      <c r="AA9" s="4" t="n">
-        <v>18</v>
-      </c>
+      <c r="AA9" s="4" t="n"/>
       <c r="AB9" s="4" t="n"/>
       <c r="AC9" s="4" t="n"/>
       <c r="AD9" s="4" t="n"/>
@@ -66018,24 +62378,6 @@
       <c r="AM9" s="4" t="n"/>
       <c r="AN9" s="4" t="n"/>
       <c r="AO9" s="4" t="n"/>
-      <c r="AP9" s="4" t="n"/>
-      <c r="AQ9" s="4" t="n"/>
-      <c r="AR9" s="4" t="n"/>
-      <c r="AS9" s="4" t="n"/>
-      <c r="AT9" s="4" t="n"/>
-      <c r="AU9" s="4" t="n"/>
-      <c r="AV9" s="4" t="n"/>
-      <c r="AW9" s="4" t="n"/>
-      <c r="AX9" s="4" t="n"/>
-      <c r="AY9" s="4" t="n"/>
-      <c r="AZ9" s="4" t="n"/>
-      <c r="BA9" s="4" t="n"/>
-      <c r="BB9" s="4" t="n"/>
-      <c r="BC9" s="4" t="n"/>
-      <c r="BD9" s="4" t="n"/>
-      <c r="BE9" s="4" t="n"/>
-      <c r="BF9" s="4" t="n"/>
-      <c r="BG9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n"/>
@@ -66050,26 +62392,26 @@
         </is>
       </c>
       <c r="D10" s="4" t="n"/>
-      <c r="E10" s="4" t="n"/>
-      <c r="F10" s="4" t="n"/>
-      <c r="G10" s="4" t="n">
+      <c r="E10" s="4" t="n">
         <v>31.49</v>
       </c>
+      <c r="F10" s="4" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="G10" s="4" t="n"/>
       <c r="H10" s="4" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="I10" s="4" t="n"/>
-      <c r="J10" s="4" t="n"/>
-      <c r="K10" s="4" t="n">
         <v>31.2</v>
       </c>
+      <c r="I10" s="4" t="n">
+        <v>32.37</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>33.19</v>
+      </c>
+      <c r="K10" s="4" t="n"/>
       <c r="L10" s="4" t="n"/>
-      <c r="M10" s="4" t="n">
-        <v>32.37</v>
-      </c>
-      <c r="N10" s="4" t="n">
-        <v>33.19</v>
-      </c>
+      <c r="M10" s="4" t="n"/>
+      <c r="N10" s="4" t="n"/>
       <c r="O10" s="4" t="n"/>
       <c r="P10" s="4" t="n"/>
       <c r="Q10" s="4" t="n"/>
@@ -66097,24 +62439,6 @@
       <c r="AM10" s="4" t="n"/>
       <c r="AN10" s="4" t="n"/>
       <c r="AO10" s="4" t="n"/>
-      <c r="AP10" s="4" t="n"/>
-      <c r="AQ10" s="4" t="n"/>
-      <c r="AR10" s="4" t="n"/>
-      <c r="AS10" s="4" t="n"/>
-      <c r="AT10" s="4" t="n"/>
-      <c r="AU10" s="4" t="n"/>
-      <c r="AV10" s="4" t="n"/>
-      <c r="AW10" s="4" t="n"/>
-      <c r="AX10" s="4" t="n"/>
-      <c r="AY10" s="4" t="n"/>
-      <c r="AZ10" s="4" t="n"/>
-      <c r="BA10" s="4" t="n"/>
-      <c r="BB10" s="4" t="n"/>
-      <c r="BC10" s="4" t="n"/>
-      <c r="BD10" s="4" t="n"/>
-      <c r="BE10" s="4" t="n"/>
-      <c r="BF10" s="4" t="n"/>
-      <c r="BG10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -66133,47 +62457,51 @@
         </is>
       </c>
       <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="n"/>
+      <c r="E11" s="4" t="n">
+        <v>27.6</v>
+      </c>
       <c r="F11" s="4" t="n"/>
       <c r="G11" s="4" t="n">
-        <v>27.6</v>
+        <v>27.3</v>
       </c>
       <c r="H11" s="4" t="n"/>
       <c r="I11" s="4" t="n"/>
-      <c r="J11" s="4" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="K11" s="4" t="n"/>
+      <c r="J11" s="4" t="n"/>
+      <c r="K11" s="4" t="n">
+        <v>27.98</v>
+      </c>
       <c r="L11" s="4" t="n"/>
-      <c r="M11" s="4" t="n"/>
-      <c r="N11" s="4" t="n"/>
+      <c r="M11" s="4" t="n">
+        <v>27.55</v>
+      </c>
+      <c r="N11" s="4" t="n">
+        <v>27.96</v>
+      </c>
       <c r="O11" s="4" t="n"/>
       <c r="P11" s="4" t="n">
-        <v>27.98</v>
-      </c>
-      <c r="Q11" s="4" t="n"/>
+        <v>28.69</v>
+      </c>
+      <c r="Q11" s="4" t="n">
+        <v>28.85</v>
+      </c>
       <c r="R11" s="4" t="n">
-        <v>27.55</v>
+        <v>27.25</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>27.96</v>
+        <v>28.87</v>
       </c>
       <c r="T11" s="4" t="n"/>
       <c r="U11" s="4" t="n"/>
       <c r="V11" s="4" t="n"/>
       <c r="W11" s="4" t="n">
-        <v>28.69</v>
-      </c>
-      <c r="X11" s="4" t="n">
-        <v>28.85</v>
-      </c>
-      <c r="Y11" s="4" t="n">
-        <v>27.25</v>
-      </c>
-      <c r="Z11" s="4" t="n"/>
-      <c r="AA11" s="4" t="n">
-        <v>28.87</v>
-      </c>
+        <v>28.99</v>
+      </c>
+      <c r="X11" s="4" t="n"/>
+      <c r="Y11" s="4" t="n"/>
+      <c r="Z11" s="4" t="n">
+        <v>30.59</v>
+      </c>
+      <c r="AA11" s="4" t="n"/>
       <c r="AB11" s="4" t="n"/>
       <c r="AC11" s="4" t="n"/>
       <c r="AD11" s="4" t="n"/>
@@ -66181,39 +62509,17 @@
       <c r="AF11" s="4" t="n"/>
       <c r="AG11" s="4" t="n"/>
       <c r="AH11" s="4" t="n"/>
-      <c r="AI11" s="4" t="n">
-        <v>28.99</v>
-      </c>
+      <c r="AI11" s="4" t="n"/>
       <c r="AJ11" s="4" t="n"/>
       <c r="AK11" s="4" t="n"/>
-      <c r="AL11" s="4" t="n"/>
+      <c r="AL11" s="4" t="n">
+        <v>28.89</v>
+      </c>
       <c r="AM11" s="4" t="n"/>
       <c r="AN11" s="4" t="n">
-        <v>30.59</v>
+        <v>30.19</v>
       </c>
       <c r="AO11" s="4" t="n"/>
-      <c r="AP11" s="4" t="n"/>
-      <c r="AQ11" s="4" t="n"/>
-      <c r="AR11" s="4" t="n"/>
-      <c r="AS11" s="4" t="n"/>
-      <c r="AT11" s="4" t="n"/>
-      <c r="AU11" s="4" t="n"/>
-      <c r="AV11" s="4" t="n"/>
-      <c r="AW11" s="4" t="n"/>
-      <c r="AX11" s="4" t="n"/>
-      <c r="AY11" s="4" t="n"/>
-      <c r="AZ11" s="4" t="n"/>
-      <c r="BA11" s="4" t="n"/>
-      <c r="BB11" s="4" t="n"/>
-      <c r="BC11" s="4" t="n">
-        <v>28.89</v>
-      </c>
-      <c r="BD11" s="4" t="n"/>
-      <c r="BE11" s="4" t="n">
-        <v>30.19</v>
-      </c>
-      <c r="BF11" s="4" t="n"/>
-      <c r="BG11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -66246,57 +62552,39 @@
       <c r="P12" s="4" t="n"/>
       <c r="Q12" s="4" t="n"/>
       <c r="R12" s="4" t="n"/>
-      <c r="S12" s="4" t="n"/>
+      <c r="S12" s="4" t="n">
+        <v>20.4</v>
+      </c>
       <c r="T12" s="4" t="n"/>
       <c r="U12" s="4" t="n"/>
-      <c r="V12" s="4" t="n"/>
+      <c r="V12" s="4" t="n">
+        <v>21</v>
+      </c>
       <c r="W12" s="4" t="n"/>
       <c r="X12" s="4" t="n"/>
-      <c r="Y12" s="4" t="n"/>
+      <c r="Y12" s="4" t="n">
+        <v>20.4</v>
+      </c>
       <c r="Z12" s="4" t="n"/>
-      <c r="AA12" s="4" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="AB12" s="4" t="n"/>
+      <c r="AA12" s="4" t="n"/>
+      <c r="AB12" s="4" t="n">
+        <v>19.8</v>
+      </c>
       <c r="AC12" s="4" t="n"/>
       <c r="AD12" s="4" t="n"/>
       <c r="AE12" s="4" t="n"/>
       <c r="AF12" s="4" t="n"/>
-      <c r="AG12" s="4" t="n"/>
-      <c r="AH12" s="4" t="n">
-        <v>21</v>
-      </c>
+      <c r="AG12" s="4" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="AH12" s="4" t="n"/>
       <c r="AI12" s="4" t="n"/>
       <c r="AJ12" s="4" t="n"/>
       <c r="AK12" s="4" t="n"/>
       <c r="AL12" s="4" t="n"/>
-      <c r="AM12" s="4" t="n">
-        <v>20.4</v>
-      </c>
+      <c r="AM12" s="4" t="n"/>
       <c r="AN12" s="4" t="n"/>
       <c r="AO12" s="4" t="n"/>
-      <c r="AP12" s="4" t="n"/>
-      <c r="AQ12" s="4" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="AR12" s="4" t="n"/>
-      <c r="AS12" s="4" t="n"/>
-      <c r="AT12" s="4" t="n"/>
-      <c r="AU12" s="4" t="n"/>
-      <c r="AV12" s="4" t="n"/>
-      <c r="AW12" s="4" t="n"/>
-      <c r="AX12" s="4" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="AY12" s="4" t="n"/>
-      <c r="AZ12" s="4" t="n"/>
-      <c r="BA12" s="4" t="n"/>
-      <c r="BB12" s="4" t="n"/>
-      <c r="BC12" s="4" t="n"/>
-      <c r="BD12" s="4" t="n"/>
-      <c r="BE12" s="4" t="n"/>
-      <c r="BF12" s="4" t="n"/>
-      <c r="BG12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -66325,15 +62613,15 @@
       <c r="L13" s="4" t="n"/>
       <c r="M13" s="4" t="n"/>
       <c r="N13" s="4" t="n"/>
-      <c r="O13" s="4" t="n"/>
+      <c r="O13" s="4" t="n">
+        <v>21.39</v>
+      </c>
       <c r="P13" s="4" t="n"/>
       <c r="Q13" s="4" t="n"/>
       <c r="R13" s="4" t="n"/>
       <c r="S13" s="4" t="n"/>
       <c r="T13" s="4" t="n"/>
-      <c r="U13" s="4" t="n">
-        <v>21.39</v>
-      </c>
+      <c r="U13" s="4" t="n"/>
       <c r="V13" s="4" t="n"/>
       <c r="W13" s="4" t="n"/>
       <c r="X13" s="4" t="n"/>
@@ -66354,24 +62642,6 @@
       <c r="AM13" s="4" t="n"/>
       <c r="AN13" s="4" t="n"/>
       <c r="AO13" s="4" t="n"/>
-      <c r="AP13" s="4" t="n"/>
-      <c r="AQ13" s="4" t="n"/>
-      <c r="AR13" s="4" t="n"/>
-      <c r="AS13" s="4" t="n"/>
-      <c r="AT13" s="4" t="n"/>
-      <c r="AU13" s="4" t="n"/>
-      <c r="AV13" s="4" t="n"/>
-      <c r="AW13" s="4" t="n"/>
-      <c r="AX13" s="4" t="n"/>
-      <c r="AY13" s="4" t="n"/>
-      <c r="AZ13" s="4" t="n"/>
-      <c r="BA13" s="4" t="n"/>
-      <c r="BB13" s="4" t="n"/>
-      <c r="BC13" s="4" t="n"/>
-      <c r="BD13" s="4" t="n"/>
-      <c r="BE13" s="4" t="n"/>
-      <c r="BF13" s="4" t="n"/>
-      <c r="BG13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n"/>
@@ -66385,22 +62655,22 @@
           <t>跳图</t>
         </is>
       </c>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="n">
+      <c r="D14" s="4" t="n">
         <v>23.4</v>
       </c>
+      <c r="E14" s="4" t="n"/>
       <c r="F14" s="4" t="n"/>
-      <c r="G14" s="4" t="n"/>
+      <c r="G14" s="4" t="n">
+        <v>23.5</v>
+      </c>
       <c r="H14" s="4" t="n"/>
-      <c r="I14" s="4" t="n"/>
-      <c r="J14" s="4" t="n">
-        <v>23.5</v>
-      </c>
+      <c r="I14" s="4" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="J14" s="4" t="n"/>
       <c r="K14" s="4" t="n"/>
       <c r="L14" s="4" t="n"/>
-      <c r="M14" s="4" t="n">
-        <v>23.6</v>
-      </c>
+      <c r="M14" s="4" t="n"/>
       <c r="N14" s="4" t="n"/>
       <c r="O14" s="4" t="n"/>
       <c r="P14" s="4" t="n"/>
@@ -66418,7 +62688,9 @@
       <c r="AB14" s="4" t="n"/>
       <c r="AC14" s="4" t="n"/>
       <c r="AD14" s="4" t="n"/>
-      <c r="AE14" s="4" t="n"/>
+      <c r="AE14" s="4" t="n">
+        <v>25.5</v>
+      </c>
       <c r="AF14" s="4" t="n"/>
       <c r="AG14" s="4" t="n"/>
       <c r="AH14" s="4" t="n"/>
@@ -66429,26 +62701,6 @@
       <c r="AM14" s="4" t="n"/>
       <c r="AN14" s="4" t="n"/>
       <c r="AO14" s="4" t="n"/>
-      <c r="AP14" s="4" t="n"/>
-      <c r="AQ14" s="4" t="n"/>
-      <c r="AR14" s="4" t="n"/>
-      <c r="AS14" s="4" t="n"/>
-      <c r="AT14" s="4" t="n"/>
-      <c r="AU14" s="4" t="n"/>
-      <c r="AV14" s="4" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="AW14" s="4" t="n"/>
-      <c r="AX14" s="4" t="n"/>
-      <c r="AY14" s="4" t="n"/>
-      <c r="AZ14" s="4" t="n"/>
-      <c r="BA14" s="4" t="n"/>
-      <c r="BB14" s="4" t="n"/>
-      <c r="BC14" s="4" t="n"/>
-      <c r="BD14" s="4" t="n"/>
-      <c r="BE14" s="4" t="n"/>
-      <c r="BF14" s="4" t="n"/>
-      <c r="BG14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -66477,22 +62729,24 @@
       <c r="L15" s="4" t="n"/>
       <c r="M15" s="4" t="n"/>
       <c r="N15" s="4" t="n"/>
-      <c r="O15" s="4" t="n"/>
+      <c r="O15" s="4" t="n">
+        <v>14.7</v>
+      </c>
       <c r="P15" s="4" t="n"/>
       <c r="Q15" s="4" t="n"/>
       <c r="R15" s="4" t="n"/>
       <c r="S15" s="4" t="n"/>
       <c r="T15" s="4" t="n"/>
-      <c r="U15" s="4" t="n">
-        <v>14.7</v>
-      </c>
+      <c r="U15" s="4" t="n"/>
       <c r="V15" s="4" t="n"/>
       <c r="W15" s="4" t="n"/>
       <c r="X15" s="4" t="n"/>
       <c r="Y15" s="4" t="n"/>
       <c r="Z15" s="4" t="n"/>
       <c r="AA15" s="4" t="n"/>
-      <c r="AB15" s="4" t="n"/>
+      <c r="AB15" s="4" t="n">
+        <v>16</v>
+      </c>
       <c r="AC15" s="4" t="n"/>
       <c r="AD15" s="4" t="n"/>
       <c r="AE15" s="4" t="n"/>
@@ -66503,31 +62757,11 @@
       <c r="AJ15" s="4" t="n"/>
       <c r="AK15" s="4" t="n"/>
       <c r="AL15" s="4" t="n"/>
-      <c r="AM15" s="4" t="n"/>
+      <c r="AM15" s="4" t="n">
+        <v>16.8</v>
+      </c>
       <c r="AN15" s="4" t="n"/>
       <c r="AO15" s="4" t="n"/>
-      <c r="AP15" s="4" t="n"/>
-      <c r="AQ15" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR15" s="4" t="n"/>
-      <c r="AS15" s="4" t="n"/>
-      <c r="AT15" s="4" t="n"/>
-      <c r="AU15" s="4" t="n"/>
-      <c r="AV15" s="4" t="n"/>
-      <c r="AW15" s="4" t="n"/>
-      <c r="AX15" s="4" t="n"/>
-      <c r="AY15" s="4" t="n"/>
-      <c r="AZ15" s="4" t="n"/>
-      <c r="BA15" s="4" t="n"/>
-      <c r="BB15" s="4" t="n"/>
-      <c r="BC15" s="4" t="n"/>
-      <c r="BD15" s="4" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="BE15" s="4" t="n"/>
-      <c r="BF15" s="4" t="n"/>
-      <c r="BG15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
@@ -66561,8 +62795,12 @@
       <c r="U16" s="4" t="n"/>
       <c r="V16" s="4" t="n"/>
       <c r="W16" s="4" t="n"/>
-      <c r="X16" s="4" t="n"/>
-      <c r="Y16" s="4" t="n"/>
+      <c r="X16" s="4" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="Y16" s="4" t="n">
+        <v>20.6</v>
+      </c>
       <c r="Z16" s="4" t="n"/>
       <c r="AA16" s="4" t="n"/>
       <c r="AB16" s="4" t="n"/>
@@ -66574,33 +62812,11 @@
       <c r="AH16" s="4" t="n"/>
       <c r="AI16" s="4" t="n"/>
       <c r="AJ16" s="4" t="n"/>
-      <c r="AK16" s="4" t="n">
-        <v>18.6</v>
-      </c>
+      <c r="AK16" s="4" t="n"/>
       <c r="AL16" s="4" t="n"/>
-      <c r="AM16" s="4" t="n">
-        <v>20.6</v>
-      </c>
+      <c r="AM16" s="4" t="n"/>
       <c r="AN16" s="4" t="n"/>
       <c r="AO16" s="4" t="n"/>
-      <c r="AP16" s="4" t="n"/>
-      <c r="AQ16" s="4" t="n"/>
-      <c r="AR16" s="4" t="n"/>
-      <c r="AS16" s="4" t="n"/>
-      <c r="AT16" s="4" t="n"/>
-      <c r="AU16" s="4" t="n"/>
-      <c r="AV16" s="4" t="n"/>
-      <c r="AW16" s="4" t="n"/>
-      <c r="AX16" s="4" t="n"/>
-      <c r="AY16" s="4" t="n"/>
-      <c r="AZ16" s="4" t="n"/>
-      <c r="BA16" s="4" t="n"/>
-      <c r="BB16" s="4" t="n"/>
-      <c r="BC16" s="4" t="n"/>
-      <c r="BD16" s="4" t="n"/>
-      <c r="BE16" s="4" t="n"/>
-      <c r="BF16" s="4" t="n"/>
-      <c r="BG16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
@@ -66631,51 +62847,33 @@
       <c r="R17" s="4" t="n"/>
       <c r="S17" s="4" t="n"/>
       <c r="T17" s="4" t="n"/>
-      <c r="U17" s="4" t="n"/>
+      <c r="U17" s="4" t="n">
+        <v>26.7</v>
+      </c>
       <c r="V17" s="4" t="n"/>
       <c r="W17" s="4" t="n"/>
       <c r="X17" s="4" t="n"/>
-      <c r="Y17" s="4" t="n"/>
+      <c r="Y17" s="4" t="n">
+        <v>28</v>
+      </c>
       <c r="Z17" s="4" t="n"/>
       <c r="AA17" s="4" t="n"/>
       <c r="AB17" s="4" t="n"/>
       <c r="AC17" s="4" t="n"/>
-      <c r="AD17" s="4" t="n"/>
+      <c r="AD17" s="4" t="n">
+        <v>29</v>
+      </c>
       <c r="AE17" s="4" t="n"/>
-      <c r="AF17" s="4" t="n">
-        <v>26.7</v>
-      </c>
+      <c r="AF17" s="4" t="n"/>
       <c r="AG17" s="4" t="n"/>
       <c r="AH17" s="4" t="n"/>
       <c r="AI17" s="4" t="n"/>
       <c r="AJ17" s="4" t="n"/>
       <c r="AK17" s="4" t="n"/>
       <c r="AL17" s="4" t="n"/>
-      <c r="AM17" s="4" t="n">
-        <v>28</v>
-      </c>
+      <c r="AM17" s="4" t="n"/>
       <c r="AN17" s="4" t="n"/>
       <c r="AO17" s="4" t="n"/>
-      <c r="AP17" s="4" t="n"/>
-      <c r="AQ17" s="4" t="n"/>
-      <c r="AR17" s="4" t="n"/>
-      <c r="AS17" s="4" t="n"/>
-      <c r="AT17" s="4" t="n">
-        <v>29</v>
-      </c>
-      <c r="AU17" s="4" t="n"/>
-      <c r="AV17" s="4" t="n"/>
-      <c r="AW17" s="4" t="n"/>
-      <c r="AX17" s="4" t="n"/>
-      <c r="AY17" s="4" t="n"/>
-      <c r="AZ17" s="4" t="n"/>
-      <c r="BA17" s="4" t="n"/>
-      <c r="BB17" s="4" t="n"/>
-      <c r="BC17" s="4" t="n"/>
-      <c r="BD17" s="4" t="n"/>
-      <c r="BE17" s="4" t="n"/>
-      <c r="BF17" s="4" t="n"/>
-      <c r="BG17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n"/>
@@ -66690,11 +62888,11 @@
         </is>
       </c>
       <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="n"/>
+      <c r="E18" s="4" t="n">
+        <v>30.8</v>
+      </c>
       <c r="F18" s="4" t="n"/>
-      <c r="G18" s="4" t="n">
-        <v>30.8</v>
-      </c>
+      <c r="G18" s="4" t="n"/>
       <c r="H18" s="4" t="n"/>
       <c r="I18" s="4" t="n"/>
       <c r="J18" s="4" t="n"/>
@@ -66729,24 +62927,6 @@
       <c r="AM18" s="4" t="n"/>
       <c r="AN18" s="4" t="n"/>
       <c r="AO18" s="4" t="n"/>
-      <c r="AP18" s="4" t="n"/>
-      <c r="AQ18" s="4" t="n"/>
-      <c r="AR18" s="4" t="n"/>
-      <c r="AS18" s="4" t="n"/>
-      <c r="AT18" s="4" t="n"/>
-      <c r="AU18" s="4" t="n"/>
-      <c r="AV18" s="4" t="n"/>
-      <c r="AW18" s="4" t="n"/>
-      <c r="AX18" s="4" t="n"/>
-      <c r="AY18" s="4" t="n"/>
-      <c r="AZ18" s="4" t="n"/>
-      <c r="BA18" s="4" t="n"/>
-      <c r="BB18" s="4" t="n"/>
-      <c r="BC18" s="4" t="n"/>
-      <c r="BD18" s="4" t="n"/>
-      <c r="BE18" s="4" t="n"/>
-      <c r="BF18" s="4" t="n"/>
-      <c r="BG18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -66765,19 +62945,19 @@
         </is>
       </c>
       <c r="D19" s="4" t="n"/>
-      <c r="E19" s="4" t="n"/>
+      <c r="E19" s="4" t="n">
+        <v>19.5</v>
+      </c>
       <c r="F19" s="4" t="n"/>
-      <c r="G19" s="4" t="n">
-        <v>19.5</v>
-      </c>
+      <c r="G19" s="4" t="n"/>
       <c r="H19" s="4" t="n"/>
-      <c r="I19" s="4" t="n"/>
+      <c r="I19" s="4" t="n">
+        <v>19.9</v>
+      </c>
       <c r="J19" s="4" t="n"/>
       <c r="K19" s="4" t="n"/>
       <c r="L19" s="4" t="n"/>
-      <c r="M19" s="4" t="n">
-        <v>19.9</v>
-      </c>
+      <c r="M19" s="4" t="n"/>
       <c r="N19" s="4" t="n"/>
       <c r="O19" s="4" t="n"/>
       <c r="P19" s="4" t="n"/>
@@ -66806,24 +62986,6 @@
       <c r="AM19" s="4" t="n"/>
       <c r="AN19" s="4" t="n"/>
       <c r="AO19" s="4" t="n"/>
-      <c r="AP19" s="4" t="n"/>
-      <c r="AQ19" s="4" t="n"/>
-      <c r="AR19" s="4" t="n"/>
-      <c r="AS19" s="4" t="n"/>
-      <c r="AT19" s="4" t="n"/>
-      <c r="AU19" s="4" t="n"/>
-      <c r="AV19" s="4" t="n"/>
-      <c r="AW19" s="4" t="n"/>
-      <c r="AX19" s="4" t="n"/>
-      <c r="AY19" s="4" t="n"/>
-      <c r="AZ19" s="4" t="n"/>
-      <c r="BA19" s="4" t="n"/>
-      <c r="BB19" s="4" t="n"/>
-      <c r="BC19" s="4" t="n"/>
-      <c r="BD19" s="4" t="n"/>
-      <c r="BE19" s="4" t="n"/>
-      <c r="BF19" s="4" t="n"/>
-      <c r="BG19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -66844,77 +63006,59 @@
       <c r="D20" s="4" t="n"/>
       <c r="E20" s="4" t="n"/>
       <c r="F20" s="4" t="n"/>
-      <c r="G20" s="4" t="n"/>
+      <c r="G20" s="4" t="n">
+        <v>17.5</v>
+      </c>
       <c r="H20" s="4" t="n"/>
       <c r="I20" s="4" t="n"/>
-      <c r="J20" s="4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="K20" s="4" t="n"/>
+      <c r="J20" s="4" t="n"/>
+      <c r="K20" s="4" t="n">
+        <v>18.6</v>
+      </c>
       <c r="L20" s="4" t="n"/>
       <c r="M20" s="4" t="n"/>
-      <c r="N20" s="4" t="n"/>
-      <c r="O20" s="4" t="n"/>
-      <c r="P20" s="4" t="n">
-        <v>18.6</v>
-      </c>
+      <c r="N20" s="4" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="O20" s="4" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="P20" s="4" t="n"/>
       <c r="Q20" s="4" t="n"/>
       <c r="R20" s="4" t="n"/>
       <c r="S20" s="4" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="T20" s="4" t="n"/>
       <c r="U20" s="4" t="n">
-        <v>18.95</v>
+        <v>19.15</v>
       </c>
       <c r="V20" s="4" t="n"/>
       <c r="W20" s="4" t="n"/>
-      <c r="X20" s="4" t="n"/>
-      <c r="Y20" s="4" t="n"/>
+      <c r="X20" s="4" t="n">
+        <v>19.199</v>
+      </c>
+      <c r="Y20" s="4" t="n">
+        <v>19</v>
+      </c>
       <c r="Z20" s="4" t="n"/>
-      <c r="AA20" s="4" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="AB20" s="4" t="n"/>
+      <c r="AA20" s="4" t="n"/>
+      <c r="AB20" s="4" t="n">
+        <v>18.8</v>
+      </c>
       <c r="AC20" s="4" t="n"/>
       <c r="AD20" s="4" t="n"/>
       <c r="AE20" s="4" t="n"/>
-      <c r="AF20" s="4" t="n">
-        <v>19.15</v>
-      </c>
+      <c r="AF20" s="4" t="n"/>
       <c r="AG20" s="4" t="n"/>
       <c r="AH20" s="4" t="n"/>
       <c r="AI20" s="4" t="n"/>
       <c r="AJ20" s="4" t="n"/>
-      <c r="AK20" s="4" t="n">
-        <v>19.199</v>
-      </c>
+      <c r="AK20" s="4" t="n"/>
       <c r="AL20" s="4" t="n"/>
-      <c r="AM20" s="4" t="n">
-        <v>19</v>
-      </c>
+      <c r="AM20" s="4" t="n"/>
       <c r="AN20" s="4" t="n"/>
       <c r="AO20" s="4" t="n"/>
-      <c r="AP20" s="4" t="n"/>
-      <c r="AQ20" s="4" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="AR20" s="4" t="n"/>
-      <c r="AS20" s="4" t="n"/>
-      <c r="AT20" s="4" t="n"/>
-      <c r="AU20" s="4" t="n"/>
-      <c r="AV20" s="4" t="n"/>
-      <c r="AW20" s="4" t="n"/>
-      <c r="AX20" s="4" t="n"/>
-      <c r="AY20" s="4" t="n"/>
-      <c r="AZ20" s="4" t="n"/>
-      <c r="BA20" s="4" t="n"/>
-      <c r="BB20" s="4" t="n"/>
-      <c r="BC20" s="4" t="n"/>
-      <c r="BD20" s="4" t="n"/>
-      <c r="BE20" s="4" t="n"/>
-      <c r="BF20" s="4" t="n"/>
-      <c r="BG20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -66933,26 +63077,26 @@
         </is>
       </c>
       <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="n"/>
+      <c r="E21" s="4" t="n">
+        <v>25.53</v>
+      </c>
       <c r="F21" s="4" t="n"/>
       <c r="G21" s="4" t="n">
-        <v>25.53</v>
+        <v>25.25</v>
       </c>
       <c r="H21" s="4" t="n"/>
-      <c r="I21" s="4" t="n"/>
-      <c r="J21" s="4" t="n">
-        <v>25.25</v>
-      </c>
-      <c r="K21" s="4" t="n"/>
+      <c r="I21" s="4" t="n">
+        <v>26.52</v>
+      </c>
+      <c r="J21" s="4" t="n"/>
+      <c r="K21" s="4" t="n">
+        <v>25.9</v>
+      </c>
       <c r="L21" s="4" t="n"/>
-      <c r="M21" s="4" t="n">
-        <v>26.52</v>
-      </c>
+      <c r="M21" s="4" t="n"/>
       <c r="N21" s="4" t="n"/>
       <c r="O21" s="4" t="n"/>
-      <c r="P21" s="4" t="n">
-        <v>25.9</v>
-      </c>
+      <c r="P21" s="4" t="n"/>
       <c r="Q21" s="4" t="n"/>
       <c r="R21" s="4" t="n"/>
       <c r="S21" s="4" t="n"/>
@@ -66978,27 +63122,9 @@
       <c r="AM21" s="4" t="n"/>
       <c r="AN21" s="4" t="n"/>
       <c r="AO21" s="4" t="n"/>
-      <c r="AP21" s="4" t="n"/>
-      <c r="AQ21" s="4" t="n"/>
-      <c r="AR21" s="4" t="n"/>
-      <c r="AS21" s="4" t="n"/>
-      <c r="AT21" s="4" t="n"/>
-      <c r="AU21" s="4" t="n"/>
-      <c r="AV21" s="4" t="n"/>
-      <c r="AW21" s="4" t="n"/>
-      <c r="AX21" s="4" t="n"/>
-      <c r="AY21" s="4" t="n"/>
-      <c r="AZ21" s="4" t="n"/>
-      <c r="BA21" s="4" t="n"/>
-      <c r="BB21" s="4" t="n"/>
-      <c r="BC21" s="4" t="n"/>
-      <c r="BD21" s="4" t="n"/>
-      <c r="BE21" s="4" t="n"/>
-      <c r="BF21" s="4" t="n"/>
-      <c r="BG21" s="4" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BG21"/>
+  <autoFilter ref="A1:AO21"/>
   <mergeCells count="14">
     <mergeCell ref="A8"/>
     <mergeCell ref="A6"/>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -8272,7 +8272,7 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>38.6</v>
+        <v>23.9</v>
       </c>
       <c r="E14" s="4" t="n"/>
       <c r="F14" s="4" t="n"/>
@@ -8462,7 +8462,9 @@
       <c r="H20" s="4" t="n"/>
       <c r="I20" s="4" t="n"/>
       <c r="J20" s="4" t="n"/>
-      <c r="K20" s="4" t="n"/>
+      <c r="K20" s="4" t="n">
+        <v>18.6</v>
+      </c>
       <c r="L20" s="4" t="n"/>
       <c r="M20" s="4" t="n"/>
       <c r="N20" s="4" t="n"/>
@@ -8491,7 +8493,7 @@
       </c>
       <c r="D21" s="4" t="n"/>
       <c r="E21" s="4" t="n">
-        <v>27.6</v>
+        <v>25.9</v>
       </c>
       <c r="F21" s="4" t="n"/>
       <c r="G21" s="4" t="n"/>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -30,9 +30,9 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'四区_普通'!$A$1:$BJ$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'四区_自动'!$A$1:$P$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'五区_理论_特殊跑法'!$A$1:$AO$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'五区_高手_特殊跑法'!$A$1:$R$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'五区_高手_特殊跑法'!$A$1:$T$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'四区_理论_特殊跑法'!$A$1:$U$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'四区_高手_特殊跑法'!$A$1:$G$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'四区_高手_特殊跑法'!$A$1:$I$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2739,12 +2739,8 @@
           <t>铁道迷</t>
         </is>
       </c>
-      <c r="C24" s="4" t="n">
-        <v>22.22</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>21.9</v>
-      </c>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
       <c r="E24" s="4" t="n"/>
       <c r="F24" s="4" t="n">
         <v>21.5</v>
@@ -2753,24 +2749,24 @@
       <c r="H24" s="4" t="n"/>
       <c r="I24" s="4" t="n"/>
       <c r="J24" s="4" t="n">
-        <v>22.2</v>
+        <v>22.35</v>
       </c>
       <c r="K24" s="4" t="n"/>
       <c r="L24" s="4" t="n"/>
       <c r="M24" s="4" t="n">
-        <v>22.09</v>
+        <v>22.25</v>
       </c>
       <c r="N24" s="4" t="n"/>
       <c r="O24" s="4" t="n">
-        <v>22.11</v>
+        <v>22.32</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>22.5</v>
+        <v>22.57</v>
       </c>
       <c r="Q24" s="4" t="n"/>
       <c r="R24" s="4" t="n"/>
       <c r="S24" s="4" t="n">
-        <v>22.31</v>
+        <v>22.6</v>
       </c>
       <c r="T24" s="4" t="n"/>
       <c r="U24" s="4" t="n"/>
@@ -2783,13 +2779,13 @@
       <c r="Z24" s="4" t="n"/>
       <c r="AA24" s="4" t="n"/>
       <c r="AB24" s="4" t="n">
-        <v>22.45</v>
+        <v>22.62</v>
       </c>
       <c r="AC24" s="4" t="n"/>
       <c r="AD24" s="4" t="n"/>
       <c r="AE24" s="4" t="n"/>
       <c r="AF24" s="4" t="n">
-        <v>22.42</v>
+        <v>22.55</v>
       </c>
       <c r="AG24" s="4" t="n"/>
       <c r="AH24" s="4" t="n"/>
@@ -7750,7 +7746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R21"/>
+  <dimension ref="A1:T21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7771,6 +7767,8 @@
     <col width="7.5" customWidth="1" min="16" max="16"/>
     <col width="7.5" customWidth="1" min="17" max="17"/>
     <col width="7.5" customWidth="1" min="18" max="18"/>
+    <col width="7.5" customWidth="1" min="19" max="19"/>
+    <col width="7.5" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7816,50 +7814,60 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>21c★6</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>9x8★6</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>黑龙★6</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>cc850★6</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>白龙★6</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>万达★6</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>速尾★6</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>sf90★6</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>sgt★6</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>秋王★6</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>小牛★6</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>fe3★5</t>
         </is>
@@ -7896,6 +7904,8 @@
       <c r="P2" s="4" t="n"/>
       <c r="Q2" s="4" t="n"/>
       <c r="R2" s="4" t="n"/>
+      <c r="S2" s="4" t="n"/>
+      <c r="T2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="n"/>
@@ -7924,6 +7934,8 @@
       <c r="P3" s="4" t="n"/>
       <c r="Q3" s="4" t="n"/>
       <c r="R3" s="4" t="n"/>
+      <c r="S3" s="4" t="n"/>
+      <c r="T3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -7960,6 +7972,8 @@
       <c r="P4" s="4" t="n"/>
       <c r="Q4" s="4" t="n"/>
       <c r="R4" s="4" t="n"/>
+      <c r="S4" s="4" t="n"/>
+      <c r="T4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -7984,20 +7998,26 @@
       </c>
       <c r="G5" s="4" t="n"/>
       <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="J5" s="4" t="n"/>
-      <c r="K5" s="4" t="n">
+      <c r="I5" s="4" t="n"/>
+      <c r="J5" s="4" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="K5" s="4" t="n"/>
+      <c r="L5" s="4" t="n"/>
+      <c r="M5" s="4" t="n">
         <v>22.5</v>
       </c>
-      <c r="L5" s="4" t="n"/>
-      <c r="M5" s="4" t="n"/>
       <c r="N5" s="4" t="n"/>
       <c r="O5" s="4" t="n"/>
-      <c r="P5" s="4" t="n"/>
+      <c r="P5" s="4" t="n">
+        <v>22.97</v>
+      </c>
       <c r="Q5" s="4" t="n"/>
-      <c r="R5" s="4" t="n"/>
+      <c r="R5" s="4" t="n">
+        <v>22.69</v>
+      </c>
+      <c r="S5" s="4" t="n"/>
+      <c r="T5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -8022,16 +8042,24 @@
       <c r="H6" s="4" t="n">
         <v>22.29</v>
       </c>
-      <c r="I6" s="4" t="n"/>
+      <c r="I6" s="4" t="n">
+        <v>22.19</v>
+      </c>
       <c r="J6" s="4" t="n"/>
-      <c r="K6" s="4" t="n"/>
+      <c r="K6" s="4" t="n">
+        <v>22.26</v>
+      </c>
       <c r="L6" s="4" t="n"/>
-      <c r="M6" s="4" t="n"/>
+      <c r="M6" s="4" t="n">
+        <v>22.5</v>
+      </c>
       <c r="N6" s="4" t="n"/>
       <c r="O6" s="4" t="n"/>
       <c r="P6" s="4" t="n"/>
       <c r="Q6" s="4" t="n"/>
       <c r="R6" s="4" t="n"/>
+      <c r="S6" s="4" t="n"/>
+      <c r="T6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -8064,6 +8092,8 @@
       <c r="P7" s="4" t="n"/>
       <c r="Q7" s="4" t="n"/>
       <c r="R7" s="4" t="n"/>
+      <c r="S7" s="4" t="n"/>
+      <c r="T7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -8095,11 +8125,13 @@
       <c r="M8" s="4" t="n"/>
       <c r="N8" s="4" t="n"/>
       <c r="O8" s="4" t="n"/>
-      <c r="P8" s="4" t="n">
+      <c r="P8" s="4" t="n"/>
+      <c r="Q8" s="4" t="n"/>
+      <c r="R8" s="4" t="n">
         <v>18.9</v>
       </c>
-      <c r="Q8" s="4" t="n"/>
-      <c r="R8" s="4" t="n"/>
+      <c r="S8" s="4" t="n"/>
+      <c r="T8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -8132,6 +8164,8 @@
       <c r="P9" s="4" t="n"/>
       <c r="Q9" s="4" t="n"/>
       <c r="R9" s="4" t="n"/>
+      <c r="S9" s="4" t="n"/>
+      <c r="T9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n"/>
@@ -8160,6 +8194,8 @@
       <c r="P10" s="4" t="n"/>
       <c r="Q10" s="4" t="n"/>
       <c r="R10" s="4" t="n"/>
+      <c r="S10" s="4" t="n"/>
+      <c r="T10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -8194,6 +8230,8 @@
       <c r="P11" s="4" t="n"/>
       <c r="Q11" s="4" t="n"/>
       <c r="R11" s="4" t="n"/>
+      <c r="S11" s="4" t="n"/>
+      <c r="T11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -8222,10 +8260,14 @@
       <c r="L12" s="4" t="n"/>
       <c r="M12" s="4" t="n"/>
       <c r="N12" s="4" t="n"/>
-      <c r="O12" s="4" t="n"/>
+      <c r="O12" s="4" t="n">
+        <v>22.99</v>
+      </c>
       <c r="P12" s="4" t="n"/>
       <c r="Q12" s="4" t="n"/>
       <c r="R12" s="4" t="n"/>
+      <c r="S12" s="4" t="n"/>
+      <c r="T12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -8258,6 +8300,8 @@
       <c r="P13" s="4" t="n"/>
       <c r="Q13" s="4" t="n"/>
       <c r="R13" s="4" t="n"/>
+      <c r="S13" s="4" t="n"/>
+      <c r="T13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n"/>
@@ -8272,24 +8316,30 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>23.9</v>
+        <v>24.3</v>
       </c>
       <c r="E14" s="4" t="n"/>
       <c r="F14" s="4" t="n"/>
       <c r="G14" s="4" t="n">
-        <v>38.7</v>
+        <v>24.5</v>
       </c>
       <c r="H14" s="4" t="n"/>
       <c r="I14" s="4" t="n"/>
       <c r="J14" s="4" t="n"/>
       <c r="K14" s="4" t="n"/>
-      <c r="L14" s="4" t="n"/>
+      <c r="L14" s="4" t="n">
+        <v>24.9</v>
+      </c>
       <c r="M14" s="4" t="n"/>
       <c r="N14" s="4" t="n"/>
       <c r="O14" s="4" t="n"/>
       <c r="P14" s="4" t="n"/>
       <c r="Q14" s="4" t="n"/>
       <c r="R14" s="4" t="n"/>
+      <c r="S14" s="4" t="n"/>
+      <c r="T14" s="4" t="n">
+        <v>25.8</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -8322,6 +8372,8 @@
       <c r="P15" s="4" t="n"/>
       <c r="Q15" s="4" t="n"/>
       <c r="R15" s="4" t="n"/>
+      <c r="S15" s="4" t="n"/>
+      <c r="T15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
@@ -8348,8 +8400,12 @@
       <c r="N16" s="4" t="n"/>
       <c r="O16" s="4" t="n"/>
       <c r="P16" s="4" t="n"/>
-      <c r="Q16" s="4" t="n"/>
+      <c r="Q16" s="4" t="n">
+        <v>22.9</v>
+      </c>
       <c r="R16" s="4" t="n"/>
+      <c r="S16" s="4" t="n"/>
+      <c r="T16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
@@ -8373,11 +8429,19 @@
       <c r="K17" s="4" t="n"/>
       <c r="L17" s="4" t="n"/>
       <c r="M17" s="4" t="n"/>
-      <c r="N17" s="4" t="n"/>
+      <c r="N17" s="4" t="n">
+        <v>26.9</v>
+      </c>
       <c r="O17" s="4" t="n"/>
       <c r="P17" s="4" t="n"/>
-      <c r="Q17" s="4" t="n"/>
+      <c r="Q17" s="4" t="n">
+        <v>27.8</v>
+      </c>
       <c r="R17" s="4" t="n"/>
+      <c r="S17" s="4" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="T17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n"/>
@@ -8406,6 +8470,8 @@
       <c r="P18" s="4" t="n"/>
       <c r="Q18" s="4" t="n"/>
       <c r="R18" s="4" t="n"/>
+      <c r="S18" s="4" t="n"/>
+      <c r="T18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -8438,6 +8504,8 @@
       <c r="P19" s="4" t="n"/>
       <c r="Q19" s="4" t="n"/>
       <c r="R19" s="4" t="n"/>
+      <c r="S19" s="4" t="n"/>
+      <c r="T19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -8462,18 +8530,20 @@
       <c r="H20" s="4" t="n"/>
       <c r="I20" s="4" t="n"/>
       <c r="J20" s="4" t="n"/>
-      <c r="K20" s="4" t="n">
+      <c r="K20" s="4" t="n"/>
+      <c r="L20" s="4" t="n"/>
+      <c r="M20" s="4" t="n">
         <v>18.6</v>
       </c>
-      <c r="L20" s="4" t="n"/>
-      <c r="M20" s="4" t="n"/>
       <c r="N20" s="4" t="n"/>
-      <c r="O20" s="4" t="n">
+      <c r="O20" s="4" t="n"/>
+      <c r="P20" s="4" t="n"/>
+      <c r="Q20" s="4" t="n">
         <v>18.9</v>
       </c>
-      <c r="P20" s="4" t="n"/>
-      <c r="Q20" s="4" t="n"/>
       <c r="R20" s="4" t="n"/>
+      <c r="S20" s="4" t="n"/>
+      <c r="T20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -8508,9 +8578,11 @@
       <c r="P21" s="4" t="n"/>
       <c r="Q21" s="4" t="n"/>
       <c r="R21" s="4" t="n"/>
+      <c r="S21" s="4" t="n"/>
+      <c r="T21" s="4" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R21"/>
+  <autoFilter ref="A1:T21"/>
   <mergeCells count="14">
     <mergeCell ref="A8"/>
     <mergeCell ref="A6"/>
@@ -9452,7 +9524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9462,6 +9534,8 @@
     <col width="7.5" customWidth="1" min="5" max="5"/>
     <col width="7.5" customWidth="1" min="6" max="6"/>
     <col width="7.5" customWidth="1" min="7" max="7"/>
+    <col width="7.5" customWidth="1" min="8" max="8"/>
+    <col width="7.5" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9482,22 +9556,32 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>玻璃★3</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>9x8★6</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>c2★6</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>fp1★6</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>sgt★6</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>fe3★5</t>
         </is>
       </c>
     </row>
@@ -9521,6 +9605,8 @@
       <c r="E2" s="4" t="n"/>
       <c r="F2" s="4" t="n"/>
       <c r="G2" s="4" t="n"/>
+      <c r="H2" s="4" t="n"/>
+      <c r="I2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="n"/>
@@ -9538,6 +9624,8 @@
       <c r="E3" s="4" t="n"/>
       <c r="F3" s="4" t="n"/>
       <c r="G3" s="4" t="n"/>
+      <c r="H3" s="4" t="n"/>
+      <c r="I3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -9557,10 +9645,12 @@
       </c>
       <c r="D4" s="4" t="n"/>
       <c r="E4" s="4" t="n"/>
-      <c r="F4" s="4" t="n">
+      <c r="F4" s="4" t="n"/>
+      <c r="G4" s="4" t="n">
         <v>24.79</v>
       </c>
-      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="4" t="n"/>
+      <c r="I4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -9578,12 +9668,14 @@
           <t>跳船</t>
         </is>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n">
         <v>22.9</v>
       </c>
-      <c r="E5" s="4" t="n"/>
       <c r="F5" s="4" t="n"/>
       <c r="G5" s="4" t="n"/>
+      <c r="H5" s="4" t="n"/>
+      <c r="I5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -9602,11 +9694,13 @@
         </is>
       </c>
       <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="4" t="n">
         <v>22.6</v>
       </c>
-      <c r="F6" s="4" t="n"/>
       <c r="G6" s="4" t="n"/>
+      <c r="H6" s="4" t="n"/>
+      <c r="I6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -9628,6 +9722,8 @@
       <c r="E7" s="4" t="n"/>
       <c r="F7" s="4" t="n"/>
       <c r="G7" s="4" t="n"/>
+      <c r="H7" s="4" t="n"/>
+      <c r="I7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -9649,6 +9745,8 @@
       <c r="E8" s="4" t="n"/>
       <c r="F8" s="4" t="n"/>
       <c r="G8" s="4" t="n"/>
+      <c r="H8" s="4" t="n"/>
+      <c r="I8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -9670,6 +9768,8 @@
       <c r="E9" s="4" t="n"/>
       <c r="F9" s="4" t="n"/>
       <c r="G9" s="4" t="n"/>
+      <c r="H9" s="4" t="n"/>
+      <c r="I9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n"/>
@@ -9687,6 +9787,8 @@
       <c r="E10" s="4" t="n"/>
       <c r="F10" s="4" t="n"/>
       <c r="G10" s="4" t="n"/>
+      <c r="H10" s="4" t="n"/>
+      <c r="I10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -9708,6 +9810,8 @@
       <c r="E11" s="4" t="n"/>
       <c r="F11" s="4" t="n"/>
       <c r="G11" s="4" t="n"/>
+      <c r="H11" s="4" t="n"/>
+      <c r="I11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -9729,6 +9833,8 @@
       <c r="E12" s="4" t="n"/>
       <c r="F12" s="4" t="n"/>
       <c r="G12" s="4" t="n"/>
+      <c r="H12" s="4" t="n"/>
+      <c r="I12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -9750,6 +9856,8 @@
       <c r="E13" s="4" t="n"/>
       <c r="F13" s="4" t="n"/>
       <c r="G13" s="4" t="n"/>
+      <c r="H13" s="4" t="n"/>
+      <c r="I13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n"/>
@@ -9763,10 +9871,16 @@
           <t>跳图</t>
         </is>
       </c>
-      <c r="D14" s="4" t="n"/>
+      <c r="D14" s="4" t="n">
+        <v>24.8</v>
+      </c>
       <c r="E14" s="4" t="n"/>
       <c r="F14" s="4" t="n"/>
       <c r="G14" s="4" t="n"/>
+      <c r="H14" s="4" t="n"/>
+      <c r="I14" s="4" t="n">
+        <v>25.8</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -9788,6 +9902,8 @@
       <c r="E15" s="4" t="n"/>
       <c r="F15" s="4" t="n"/>
       <c r="G15" s="4" t="n"/>
+      <c r="H15" s="4" t="n"/>
+      <c r="I15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
@@ -9805,6 +9921,8 @@
       <c r="E16" s="4" t="n"/>
       <c r="F16" s="4" t="n"/>
       <c r="G16" s="4" t="n"/>
+      <c r="H16" s="4" t="n"/>
+      <c r="I16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
@@ -9822,6 +9940,8 @@
       <c r="E17" s="4" t="n"/>
       <c r="F17" s="4" t="n"/>
       <c r="G17" s="4" t="n"/>
+      <c r="H17" s="4" t="n"/>
+      <c r="I17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n"/>
@@ -9839,6 +9959,8 @@
       <c r="E18" s="4" t="n"/>
       <c r="F18" s="4" t="n"/>
       <c r="G18" s="4" t="n"/>
+      <c r="H18" s="4" t="n"/>
+      <c r="I18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -9860,6 +9982,8 @@
       <c r="E19" s="4" t="n"/>
       <c r="F19" s="4" t="n"/>
       <c r="G19" s="4" t="n"/>
+      <c r="H19" s="4" t="n"/>
+      <c r="I19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -9880,9 +10004,11 @@
       <c r="D20" s="4" t="n"/>
       <c r="E20" s="4" t="n"/>
       <c r="F20" s="4" t="n"/>
-      <c r="G20" s="4" t="n">
+      <c r="G20" s="4" t="n"/>
+      <c r="H20" s="4" t="n">
         <v>18.9</v>
       </c>
+      <c r="I20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -9904,9 +10030,11 @@
       <c r="E21" s="4" t="n"/>
       <c r="F21" s="4" t="n"/>
       <c r="G21" s="4" t="n"/>
+      <c r="H21" s="4" t="n"/>
+      <c r="I21" s="4" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G21"/>
+  <autoFilter ref="A1:I21"/>
   <mergeCells count="14">
     <mergeCell ref="A8"/>
     <mergeCell ref="A6"/>
@@ -12874,7 +13002,9 @@
       <c r="K24" s="4" t="n"/>
       <c r="L24" s="4" t="n"/>
       <c r="M24" s="4" t="n"/>
-      <c r="N24" s="4" t="n"/>
+      <c r="N24" s="4" t="n">
+        <v>21.87</v>
+      </c>
       <c r="O24" s="4" t="n"/>
       <c r="P24" s="4" t="n"/>
       <c r="Q24" s="4" t="n"/>
@@ -12884,14 +13014,22 @@
       <c r="U24" s="4" t="n"/>
       <c r="V24" s="4" t="n"/>
       <c r="W24" s="4" t="n"/>
-      <c r="X24" s="4" t="n"/>
-      <c r="Y24" s="4" t="n"/>
+      <c r="X24" s="4" t="n">
+        <v>22.43</v>
+      </c>
+      <c r="Y24" s="4" t="n">
+        <v>22.45</v>
+      </c>
       <c r="Z24" s="4" t="n"/>
       <c r="AA24" s="4" t="n"/>
       <c r="AB24" s="4" t="n"/>
-      <c r="AC24" s="4" t="n"/>
+      <c r="AC24" s="4" t="n">
+        <v>22.39</v>
+      </c>
       <c r="AD24" s="4" t="n"/>
-      <c r="AE24" s="4" t="n"/>
+      <c r="AE24" s="4" t="n">
+        <v>22.47</v>
+      </c>
       <c r="AF24" s="4" t="n"/>
       <c r="AG24" s="4" t="n"/>
       <c r="AH24" s="4" t="n"/>
@@ -62126,11 +62264,15 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>22.34</v>
-      </c>
-      <c r="E6" s="4" t="n"/>
+        <v>22.09</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>21.9</v>
+      </c>
       <c r="F6" s="4" t="n"/>
-      <c r="G6" s="4" t="n"/>
+      <c r="G6" s="4" t="n">
+        <v>21.49</v>
+      </c>
       <c r="H6" s="4" t="n"/>
       <c r="I6" s="4" t="n"/>
       <c r="J6" s="4" t="n"/>
@@ -62147,12 +62289,18 @@
       <c r="O6" s="4" t="n">
         <v>23.58</v>
       </c>
-      <c r="P6" s="4" t="n"/>
-      <c r="Q6" s="4" t="n"/>
+      <c r="P6" s="4" t="n">
+        <v>22.14</v>
+      </c>
+      <c r="Q6" s="4" t="n">
+        <v>22.39</v>
+      </c>
       <c r="R6" s="4" t="n">
         <v>21.95</v>
       </c>
-      <c r="S6" s="4" t="n"/>
+      <c r="S6" s="4" t="n">
+        <v>22.3</v>
+      </c>
       <c r="T6" s="4" t="n"/>
       <c r="U6" s="4" t="n"/>
       <c r="V6" s="4" t="n"/>
@@ -62160,7 +62308,9 @@
       <c r="X6" s="4" t="n"/>
       <c r="Y6" s="4" t="n"/>
       <c r="Z6" s="4" t="n"/>
-      <c r="AA6" s="4" t="n"/>
+      <c r="AA6" s="4" t="n">
+        <v>22.42</v>
+      </c>
       <c r="AB6" s="4" t="n">
         <v>23.11</v>
       </c>
@@ -62856,18 +63006,20 @@
       <c r="W17" s="4" t="n"/>
       <c r="X17" s="4" t="n"/>
       <c r="Y17" s="4" t="n">
-        <v>28</v>
+        <v>27.5</v>
       </c>
       <c r="Z17" s="4" t="n"/>
       <c r="AA17" s="4" t="n"/>
       <c r="AB17" s="4" t="n"/>
       <c r="AC17" s="4" t="n"/>
       <c r="AD17" s="4" t="n">
-        <v>29</v>
+        <v>28.5</v>
       </c>
       <c r="AE17" s="4" t="n"/>
       <c r="AF17" s="4" t="n"/>
-      <c r="AG17" s="4" t="n"/>
+      <c r="AG17" s="4" t="n">
+        <v>27.9</v>
+      </c>
       <c r="AH17" s="4" t="n"/>
       <c r="AI17" s="4" t="n"/>
       <c r="AJ17" s="4" t="n"/>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -8539,7 +8539,7 @@
       <c r="O20" s="4" t="n"/>
       <c r="P20" s="4" t="n"/>
       <c r="Q20" s="4" t="n">
-        <v>18.9</v>
+        <v>19.2</v>
       </c>
       <c r="R20" s="4" t="n"/>
       <c r="S20" s="4" t="n"/>
@@ -10006,7 +10006,7 @@
       <c r="F20" s="4" t="n"/>
       <c r="G20" s="4" t="n"/>
       <c r="H20" s="4" t="n">
-        <v>18.9</v>
+        <v>19.2</v>
       </c>
       <c r="I20" s="4" t="n"/>
     </row>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -43507,7 +43507,9 @@
       <c r="S13" s="4" t="n"/>
       <c r="T13" s="4" t="n"/>
       <c r="U13" s="4" t="n"/>
-      <c r="V13" s="4" t="n"/>
+      <c r="V13" s="4" t="n">
+        <v>42.65</v>
+      </c>
       <c r="W13" s="4" t="n"/>
       <c r="X13" s="4" t="n"/>
       <c r="Y13" s="4" t="n"/>
@@ -50765,7 +50767,11 @@
       </c>
       <c r="T13" s="4" t="n"/>
       <c r="U13" s="4" t="n"/>
-      <c r="V13" s="4" t="n"/>
+      <c r="V13" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="W13" s="4" t="n"/>
       <c r="X13" s="4" t="n"/>
       <c r="Y13" s="4" t="n"/>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -21,7 +21,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="四区_高手_特殊跑法" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'五区_理论'!$A$1:$BA$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'五区_理论'!$A$1:$BB$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'五区_高手'!$A$1:$CJ$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'五区_普通'!$A$1:$CJ$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'五区_自动'!$A$1:$U$84</definedName>
@@ -32,7 +32,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'五区_理论_特殊跑法'!$A$1:$AO$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'五区_高手_特殊跑法'!$A$1:$T$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'四区_理论_特殊跑法'!$A$1:$U$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'四区_高手_特殊跑法'!$A$1:$I$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'四区_高手_特殊跑法'!$A$1:$K$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -515,7 +515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA84"/>
+  <dimension ref="A1:BB84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -571,6 +571,7 @@
     <col width="7.5" customWidth="1" min="51" max="51"/>
     <col width="7.5" customWidth="1" min="52" max="52"/>
     <col width="7.5" customWidth="1" min="53" max="53"/>
+    <col width="7.5" customWidth="1" min="54" max="54"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -686,19 +687,19 @@
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
+          <t>狼崽</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
           <t>大超</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>速尾</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>狼崽</t>
-        </is>
-      </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>300+</t>
@@ -786,49 +787,49 @@
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
+          <t>biome</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
           <t>六子</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>霓虹gtr</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>帕梅</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>ps龙</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>ts900</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>divo</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>统治</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>att</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>biome</t>
-        </is>
-      </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>风扇</t>
@@ -837,6 +838,11 @@
       <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>dose</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>600lt</t>
         </is>
       </c>
     </row>
@@ -934,6 +940,7 @@
       <c r="AY2" s="4" t="n"/>
       <c r="AZ2" s="4" t="n"/>
       <c r="BA2" s="4" t="n"/>
+      <c r="BB2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n"/>
@@ -980,11 +987,11 @@
       <c r="T3" s="4" t="n"/>
       <c r="U3" s="4" t="n"/>
       <c r="V3" s="4" t="n"/>
-      <c r="W3" s="4" t="n"/>
+      <c r="W3" s="4" t="n">
+        <v>29.6</v>
+      </c>
       <c r="X3" s="4" t="n"/>
-      <c r="Y3" s="4" t="n">
-        <v>29.6</v>
-      </c>
+      <c r="Y3" s="4" t="n"/>
       <c r="Z3" s="4" t="n"/>
       <c r="AA3" s="4" t="n"/>
       <c r="AB3" s="4" t="n"/>
@@ -1013,6 +1020,7 @@
       <c r="AY3" s="4" t="n"/>
       <c r="AZ3" s="4" t="n"/>
       <c r="BA3" s="4" t="n"/>
+      <c r="BB3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n"/>
@@ -1063,11 +1071,11 @@
       <c r="T4" s="4" t="n"/>
       <c r="U4" s="4" t="n"/>
       <c r="V4" s="4" t="n"/>
-      <c r="W4" s="4" t="n"/>
+      <c r="W4" s="4" t="n">
+        <v>32.29</v>
+      </c>
       <c r="X4" s="4" t="n"/>
-      <c r="Y4" s="4" t="n">
-        <v>32.29</v>
-      </c>
+      <c r="Y4" s="4" t="n"/>
       <c r="Z4" s="4" t="n">
         <v>29.65</v>
       </c>
@@ -1098,6 +1106,7 @@
       <c r="AY4" s="4" t="n"/>
       <c r="AZ4" s="4" t="n"/>
       <c r="BA4" s="4" t="n"/>
+      <c r="BB4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n"/>
@@ -1149,10 +1158,10 @@
       <c r="U5" s="4" t="n"/>
       <c r="V5" s="4" t="n"/>
       <c r="W5" s="4" t="n"/>
-      <c r="X5" s="4" t="n">
+      <c r="X5" s="4" t="n"/>
+      <c r="Y5" s="4" t="n">
         <v>17.78</v>
       </c>
-      <c r="Y5" s="4" t="n"/>
       <c r="Z5" s="4" t="n"/>
       <c r="AA5" s="4" t="n"/>
       <c r="AB5" s="4" t="n">
@@ -1193,6 +1202,7 @@
       <c r="AY5" s="4" t="n"/>
       <c r="AZ5" s="4" t="n"/>
       <c r="BA5" s="4" t="n"/>
+      <c r="BB5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1272,16 +1282,17 @@
       <c r="AQ6" s="4" t="n"/>
       <c r="AR6" s="4" t="n"/>
       <c r="AS6" s="4" t="n"/>
-      <c r="AT6" s="4" t="n">
+      <c r="AT6" s="4" t="n"/>
+      <c r="AU6" s="4" t="n">
         <v>17.89</v>
       </c>
-      <c r="AU6" s="4" t="n"/>
       <c r="AV6" s="4" t="n"/>
       <c r="AW6" s="4" t="n"/>
       <c r="AX6" s="4" t="n"/>
       <c r="AY6" s="4" t="n"/>
       <c r="AZ6" s="4" t="n"/>
       <c r="BA6" s="4" t="n"/>
+      <c r="BB6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
@@ -1357,6 +1368,7 @@
       <c r="AY7" s="4" t="n"/>
       <c r="AZ7" s="4" t="n"/>
       <c r="BA7" s="4" t="n"/>
+      <c r="BB7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
@@ -1407,12 +1419,12 @@
       <c r="T8" s="4" t="n"/>
       <c r="U8" s="4" t="n"/>
       <c r="V8" s="4" t="n"/>
-      <c r="W8" s="4" t="n"/>
-      <c r="X8" s="4" t="n">
+      <c r="W8" s="4" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="X8" s="4" t="n"/>
+      <c r="Y8" s="4" t="n">
         <v>27.94</v>
-      </c>
-      <c r="Y8" s="4" t="n">
-        <v>28.9</v>
       </c>
       <c r="Z8" s="4" t="n">
         <v>26.998</v>
@@ -1446,6 +1458,7 @@
       <c r="AY8" s="4" t="n"/>
       <c r="AZ8" s="4" t="n"/>
       <c r="BA8" s="4" t="n"/>
+      <c r="BB8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n"/>
@@ -1531,6 +1544,7 @@
       <c r="AY9" s="4" t="n"/>
       <c r="AZ9" s="4" t="n"/>
       <c r="BA9" s="4" t="n"/>
+      <c r="BB9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1620,6 +1634,7 @@
       <c r="AY10" s="4" t="n"/>
       <c r="AZ10" s="4" t="n"/>
       <c r="BA10" s="4" t="n"/>
+      <c r="BB10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
@@ -1697,6 +1712,7 @@
       <c r="AY11" s="4" t="n"/>
       <c r="AZ11" s="4" t="n"/>
       <c r="BA11" s="4" t="n"/>
+      <c r="BB11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
@@ -1744,10 +1760,10 @@
       <c r="U12" s="4" t="n"/>
       <c r="V12" s="4" t="n"/>
       <c r="W12" s="4" t="n"/>
-      <c r="X12" s="4" t="n">
+      <c r="X12" s="4" t="n"/>
+      <c r="Y12" s="4" t="n">
         <v>21.54</v>
       </c>
-      <c r="Y12" s="4" t="n"/>
       <c r="Z12" s="4" t="n"/>
       <c r="AA12" s="4" t="n"/>
       <c r="AB12" s="4" t="n">
@@ -1784,6 +1800,7 @@
       <c r="AY12" s="4" t="n"/>
       <c r="AZ12" s="4" t="n"/>
       <c r="BA12" s="4" t="n"/>
+      <c r="BB12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
@@ -1863,6 +1880,7 @@
       <c r="AY13" s="4" t="n"/>
       <c r="AZ13" s="4" t="n"/>
       <c r="BA13" s="4" t="n"/>
+      <c r="BB13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1960,6 +1978,7 @@
       <c r="AY14" s="4" t="n"/>
       <c r="AZ14" s="4" t="n"/>
       <c r="BA14" s="4" t="n"/>
+      <c r="BB14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
@@ -2014,11 +2033,11 @@
       <c r="T15" s="4" t="n"/>
       <c r="U15" s="4" t="n"/>
       <c r="V15" s="4" t="n"/>
-      <c r="W15" s="4" t="n"/>
+      <c r="W15" s="4" t="n">
+        <v>30.09</v>
+      </c>
       <c r="X15" s="4" t="n"/>
-      <c r="Y15" s="4" t="n">
-        <v>30.09</v>
-      </c>
+      <c r="Y15" s="4" t="n"/>
       <c r="Z15" s="4" t="n">
         <v>27.65</v>
       </c>
@@ -2053,6 +2072,7 @@
       <c r="AY15" s="4" t="n"/>
       <c r="AZ15" s="4" t="n"/>
       <c r="BA15" s="4" t="n"/>
+      <c r="BB15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
@@ -2128,6 +2148,7 @@
       <c r="AY16" s="4" t="n"/>
       <c r="AZ16" s="4" t="n"/>
       <c r="BA16" s="4" t="n"/>
+      <c r="BB16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
@@ -2219,6 +2240,7 @@
       <c r="AY17" s="4" t="n"/>
       <c r="AZ17" s="4" t="n"/>
       <c r="BA17" s="4" t="n"/>
+      <c r="BB17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -2269,11 +2291,11 @@
       <c r="T18" s="4" t="n"/>
       <c r="U18" s="4" t="n"/>
       <c r="V18" s="4" t="n"/>
-      <c r="W18" s="4" t="n"/>
+      <c r="W18" s="4" t="n">
+        <v>24.19</v>
+      </c>
       <c r="X18" s="4" t="n"/>
-      <c r="Y18" s="4" t="n">
-        <v>24.19</v>
-      </c>
+      <c r="Y18" s="4" t="n"/>
       <c r="Z18" s="4" t="n"/>
       <c r="AA18" s="4" t="n"/>
       <c r="AB18" s="4" t="n">
@@ -2301,13 +2323,14 @@
       <c r="AT18" s="4" t="n"/>
       <c r="AU18" s="4" t="n"/>
       <c r="AV18" s="4" t="n"/>
-      <c r="AW18" s="4" t="n">
+      <c r="AW18" s="4" t="n"/>
+      <c r="AX18" s="4" t="n">
         <v>23.59</v>
       </c>
-      <c r="AX18" s="4" t="n"/>
       <c r="AY18" s="4" t="n"/>
       <c r="AZ18" s="4" t="n"/>
       <c r="BA18" s="4" t="n"/>
+      <c r="BB18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
@@ -2391,6 +2414,7 @@
       <c r="AY19" s="4" t="n"/>
       <c r="AZ19" s="4" t="n"/>
       <c r="BA19" s="4" t="n"/>
+      <c r="BB19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
@@ -2475,10 +2499,10 @@
       <c r="AP20" s="4" t="n"/>
       <c r="AQ20" s="4" t="n"/>
       <c r="AR20" s="4" t="n"/>
-      <c r="AS20" s="4" t="n">
+      <c r="AS20" s="4" t="n"/>
+      <c r="AT20" s="4" t="n">
         <v>23.75</v>
       </c>
-      <c r="AT20" s="4" t="n"/>
       <c r="AU20" s="4" t="n"/>
       <c r="AV20" s="4" t="n"/>
       <c r="AW20" s="4" t="n"/>
@@ -2486,6 +2510,7 @@
       <c r="AY20" s="4" t="n"/>
       <c r="AZ20" s="4" t="n"/>
       <c r="BA20" s="4" t="n"/>
+      <c r="BB20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
@@ -2534,10 +2559,10 @@
       <c r="T21" s="4" t="n"/>
       <c r="U21" s="4" t="n"/>
       <c r="V21" s="4" t="n"/>
-      <c r="W21" s="4" t="n">
+      <c r="W21" s="4" t="n"/>
+      <c r="X21" s="4" t="n">
         <v>29.89</v>
       </c>
-      <c r="X21" s="4" t="n"/>
       <c r="Y21" s="4" t="n"/>
       <c r="Z21" s="4" t="n">
         <v>30</v>
@@ -2569,6 +2594,7 @@
       <c r="AY21" s="4" t="n"/>
       <c r="AZ21" s="4" t="n"/>
       <c r="BA21" s="4" t="n"/>
+      <c r="BB21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2617,10 +2643,10 @@
       <c r="T22" s="4" t="n"/>
       <c r="U22" s="4" t="n"/>
       <c r="V22" s="4" t="n"/>
-      <c r="W22" s="4" t="n">
+      <c r="W22" s="4" t="n"/>
+      <c r="X22" s="4" t="n">
         <v>30.1</v>
       </c>
-      <c r="X22" s="4" t="n"/>
       <c r="Y22" s="4" t="n"/>
       <c r="Z22" s="4" t="n"/>
       <c r="AA22" s="4" t="n"/>
@@ -2652,6 +2678,7 @@
       <c r="AY22" s="4" t="n"/>
       <c r="AZ22" s="4" t="n"/>
       <c r="BA22" s="4" t="n"/>
+      <c r="BB22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
@@ -2698,10 +2725,10 @@
       <c r="T23" s="4" t="n"/>
       <c r="U23" s="4" t="n"/>
       <c r="V23" s="4" t="n"/>
-      <c r="W23" s="4" t="n">
+      <c r="W23" s="4" t="n"/>
+      <c r="X23" s="4" t="n">
         <v>29.75</v>
       </c>
-      <c r="X23" s="4" t="n"/>
       <c r="Y23" s="4" t="n"/>
       <c r="Z23" s="4" t="n"/>
       <c r="AA23" s="4" t="n"/>
@@ -2731,6 +2758,7 @@
       <c r="AY23" s="4" t="n"/>
       <c r="AZ23" s="4" t="n"/>
       <c r="BA23" s="4" t="n"/>
+      <c r="BB23" s="4" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
@@ -2771,10 +2799,10 @@
       <c r="T24" s="4" t="n"/>
       <c r="U24" s="4" t="n"/>
       <c r="V24" s="4" t="n"/>
-      <c r="W24" s="4" t="n">
+      <c r="W24" s="4" t="n"/>
+      <c r="X24" s="4" t="n">
         <v>22.52</v>
       </c>
-      <c r="X24" s="4" t="n"/>
       <c r="Y24" s="4" t="n"/>
       <c r="Z24" s="4" t="n"/>
       <c r="AA24" s="4" t="n"/>
@@ -2808,6 +2836,7 @@
       <c r="AY24" s="4" t="n"/>
       <c r="AZ24" s="4" t="n"/>
       <c r="BA24" s="4" t="n"/>
+      <c r="BB24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
@@ -2883,12 +2912,13 @@
       <c r="AU25" s="4" t="n"/>
       <c r="AV25" s="4" t="n"/>
       <c r="AW25" s="4" t="n"/>
-      <c r="AX25" s="4" t="n">
+      <c r="AX25" s="4" t="n"/>
+      <c r="AY25" s="4" t="n">
         <v>23.9</v>
       </c>
-      <c r="AY25" s="4" t="n"/>
       <c r="AZ25" s="4" t="n"/>
       <c r="BA25" s="4" t="n"/>
+      <c r="BB25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2935,10 +2965,10 @@
       <c r="T26" s="4" t="n"/>
       <c r="U26" s="4" t="n"/>
       <c r="V26" s="4" t="n"/>
-      <c r="W26" s="4" t="n">
+      <c r="W26" s="4" t="n"/>
+      <c r="X26" s="4" t="n">
         <v>18.3</v>
       </c>
-      <c r="X26" s="4" t="n"/>
       <c r="Y26" s="4" t="n"/>
       <c r="Z26" s="4" t="n"/>
       <c r="AA26" s="4" t="n"/>
@@ -2974,6 +3004,7 @@
       <c r="AY26" s="4" t="n"/>
       <c r="AZ26" s="4" t="n"/>
       <c r="BA26" s="4" t="n"/>
+      <c r="BB26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n"/>
@@ -3051,6 +3082,7 @@
       <c r="AY27" s="4" t="n"/>
       <c r="AZ27" s="4" t="n"/>
       <c r="BA27" s="4" t="n"/>
+      <c r="BB27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
@@ -3099,11 +3131,11 @@
       <c r="T28" s="4" t="n"/>
       <c r="U28" s="4" t="n"/>
       <c r="V28" s="4" t="n"/>
-      <c r="W28" s="4" t="n"/>
+      <c r="W28" s="4" t="n">
+        <v>33.79</v>
+      </c>
       <c r="X28" s="4" t="n"/>
-      <c r="Y28" s="4" t="n">
-        <v>33.79</v>
-      </c>
+      <c r="Y28" s="4" t="n"/>
       <c r="Z28" s="4" t="n"/>
       <c r="AA28" s="4" t="n"/>
       <c r="AB28" s="4" t="n"/>
@@ -3134,6 +3166,7 @@
       <c r="AY28" s="4" t="n"/>
       <c r="AZ28" s="4" t="n"/>
       <c r="BA28" s="4" t="n"/>
+      <c r="BB28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n"/>
@@ -3175,12 +3208,12 @@
       <c r="U29" s="4" t="n"/>
       <c r="V29" s="4" t="n"/>
       <c r="W29" s="4" t="n">
+        <v>19.39</v>
+      </c>
+      <c r="X29" s="4" t="n">
         <v>17.5</v>
       </c>
-      <c r="X29" s="4" t="n"/>
-      <c r="Y29" s="4" t="n">
-        <v>19.39</v>
-      </c>
+      <c r="Y29" s="4" t="n"/>
       <c r="Z29" s="4" t="n"/>
       <c r="AA29" s="4" t="n"/>
       <c r="AB29" s="4" t="n"/>
@@ -3209,6 +3242,7 @@
       <c r="AY29" s="4" t="n"/>
       <c r="AZ29" s="4" t="n"/>
       <c r="BA29" s="4" t="n"/>
+      <c r="BB29" s="4" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -3308,6 +3342,7 @@
       <c r="AY30" s="4" t="n"/>
       <c r="AZ30" s="4" t="n"/>
       <c r="BA30" s="4" t="n"/>
+      <c r="BB30" s="4" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n"/>
@@ -3387,14 +3422,15 @@
       <c r="AS31" s="4" t="n"/>
       <c r="AT31" s="4" t="n"/>
       <c r="AU31" s="4" t="n"/>
-      <c r="AV31" s="4" t="n">
+      <c r="AV31" s="4" t="n"/>
+      <c r="AW31" s="4" t="n">
         <v>18.87</v>
       </c>
-      <c r="AW31" s="4" t="n"/>
       <c r="AX31" s="4" t="n"/>
       <c r="AY31" s="4" t="n"/>
       <c r="AZ31" s="4" t="n"/>
       <c r="BA31" s="4" t="n"/>
+      <c r="BB31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n"/>
@@ -3470,10 +3506,10 @@
       <c r="AO32" s="4" t="n"/>
       <c r="AP32" s="4" t="n"/>
       <c r="AQ32" s="4" t="n"/>
-      <c r="AR32" s="4" t="n">
+      <c r="AR32" s="4" t="n"/>
+      <c r="AS32" s="4" t="n">
         <v>28.79</v>
       </c>
-      <c r="AS32" s="4" t="n"/>
       <c r="AT32" s="4" t="n"/>
       <c r="AU32" s="4" t="n"/>
       <c r="AV32" s="4" t="n"/>
@@ -3482,6 +3518,7 @@
       <c r="AY32" s="4" t="n"/>
       <c r="AZ32" s="4" t="n"/>
       <c r="BA32" s="4" t="n"/>
+      <c r="BB32" s="4" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -3566,10 +3603,10 @@
       <c r="AP33" s="4" t="n"/>
       <c r="AQ33" s="4" t="n"/>
       <c r="AR33" s="4" t="n"/>
-      <c r="AS33" s="4" t="n">
+      <c r="AS33" s="4" t="n"/>
+      <c r="AT33" s="4" t="n">
         <v>21.09</v>
       </c>
-      <c r="AT33" s="4" t="n"/>
       <c r="AU33" s="4" t="n"/>
       <c r="AV33" s="4" t="n"/>
       <c r="AW33" s="4" t="n"/>
@@ -3577,6 +3614,7 @@
       <c r="AY33" s="4" t="n"/>
       <c r="AZ33" s="4" t="n"/>
       <c r="BA33" s="4" t="n"/>
+      <c r="BB33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n"/>
@@ -3652,6 +3690,7 @@
       <c r="AY34" s="4" t="n"/>
       <c r="AZ34" s="4" t="n"/>
       <c r="BA34" s="4" t="n"/>
+      <c r="BB34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n"/>
@@ -3703,10 +3742,10 @@
         <v>23.69</v>
       </c>
       <c r="W35" s="4" t="n"/>
-      <c r="X35" s="4" t="n">
+      <c r="X35" s="4" t="n"/>
+      <c r="Y35" s="4" t="n">
         <v>22.95</v>
       </c>
-      <c r="Y35" s="4" t="n"/>
       <c r="Z35" s="4" t="n"/>
       <c r="AA35" s="4" t="n"/>
       <c r="AB35" s="4" t="n"/>
@@ -3739,6 +3778,7 @@
       <c r="AY35" s="4" t="n"/>
       <c r="AZ35" s="4" t="n"/>
       <c r="BA35" s="4" t="n"/>
+      <c r="BB35" s="4" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n"/>
@@ -3816,6 +3856,7 @@
       <c r="AY36" s="4" t="n"/>
       <c r="AZ36" s="4" t="n"/>
       <c r="BA36" s="4" t="n"/>
+      <c r="BB36" s="4" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -3905,6 +3946,7 @@
       <c r="AY37" s="4" t="n"/>
       <c r="AZ37" s="4" t="n"/>
       <c r="BA37" s="4" t="n"/>
+      <c r="BB37" s="4" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n"/>
@@ -3984,6 +4026,7 @@
       <c r="AY38" s="4" t="n"/>
       <c r="AZ38" s="4" t="n"/>
       <c r="BA38" s="4" t="n"/>
+      <c r="BB38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n"/>
@@ -4049,6 +4092,7 @@
       <c r="AY39" s="4" t="n"/>
       <c r="AZ39" s="4" t="n"/>
       <c r="BA39" s="4" t="n"/>
+      <c r="BB39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n"/>
@@ -4132,6 +4176,7 @@
       <c r="AY40" s="4" t="n"/>
       <c r="AZ40" s="4" t="n"/>
       <c r="BA40" s="4" t="n"/>
+      <c r="BB40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -4209,6 +4254,7 @@
       <c r="AY41" s="4" t="n"/>
       <c r="AZ41" s="4" t="n"/>
       <c r="BA41" s="4" t="n"/>
+      <c r="BB41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n"/>
@@ -4261,11 +4307,11 @@
         <v>21.15</v>
       </c>
       <c r="V42" s="4" t="n"/>
-      <c r="W42" s="4" t="n"/>
+      <c r="W42" s="4" t="n">
+        <v>22.89</v>
+      </c>
       <c r="X42" s="4" t="n"/>
-      <c r="Y42" s="4" t="n">
-        <v>22.89</v>
-      </c>
+      <c r="Y42" s="4" t="n"/>
       <c r="Z42" s="4" t="n"/>
       <c r="AA42" s="4" t="n"/>
       <c r="AB42" s="4" t="n"/>
@@ -4296,6 +4342,7 @@
       <c r="AY42" s="4" t="n"/>
       <c r="AZ42" s="4" t="n"/>
       <c r="BA42" s="4" t="n"/>
+      <c r="BB42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n"/>
@@ -4375,6 +4422,7 @@
       <c r="AY43" s="4" t="n"/>
       <c r="AZ43" s="4" t="n"/>
       <c r="BA43" s="4" t="n"/>
+      <c r="BB43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n"/>
@@ -4449,10 +4497,10 @@
       <c r="AN44" s="4" t="n"/>
       <c r="AO44" s="4" t="n"/>
       <c r="AP44" s="4" t="n"/>
-      <c r="AQ44" s="4" t="n">
+      <c r="AQ44" s="4" t="n"/>
+      <c r="AR44" s="4" t="n">
         <v>22.65</v>
       </c>
-      <c r="AR44" s="4" t="n"/>
       <c r="AS44" s="4" t="n"/>
       <c r="AT44" s="4" t="n"/>
       <c r="AU44" s="4" t="n"/>
@@ -4462,6 +4510,7 @@
       <c r="AY44" s="4" t="n"/>
       <c r="AZ44" s="4" t="n"/>
       <c r="BA44" s="4" t="n"/>
+      <c r="BB44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -4539,6 +4588,7 @@
       <c r="AY45" s="4" t="n"/>
       <c r="AZ45" s="4" t="n"/>
       <c r="BA45" s="4" t="n"/>
+      <c r="BB45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n"/>
@@ -4587,10 +4637,10 @@
       <c r="T46" s="4" t="n"/>
       <c r="U46" s="4" t="n"/>
       <c r="V46" s="4" t="n"/>
-      <c r="W46" s="4" t="n">
+      <c r="W46" s="4" t="n"/>
+      <c r="X46" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="X46" s="4" t="n"/>
       <c r="Y46" s="4" t="n"/>
       <c r="Z46" s="4" t="n"/>
       <c r="AA46" s="4" t="n"/>
@@ -4620,6 +4670,7 @@
       <c r="AY46" s="4" t="n"/>
       <c r="AZ46" s="4" t="n"/>
       <c r="BA46" s="4" t="n"/>
+      <c r="BB46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n"/>
@@ -4699,6 +4750,7 @@
       <c r="AY47" s="4" t="n"/>
       <c r="AZ47" s="4" t="n"/>
       <c r="BA47" s="4" t="n"/>
+      <c r="BB47" s="4" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n"/>
@@ -4755,11 +4807,11 @@
         <v>23.87</v>
       </c>
       <c r="V48" s="4" t="n"/>
-      <c r="W48" s="4" t="n"/>
+      <c r="W48" s="4" t="n">
+        <v>25.59</v>
+      </c>
       <c r="X48" s="4" t="n"/>
-      <c r="Y48" s="4" t="n">
-        <v>25.59</v>
-      </c>
+      <c r="Y48" s="4" t="n"/>
       <c r="Z48" s="4" t="n"/>
       <c r="AA48" s="4" t="n"/>
       <c r="AB48" s="4" t="n"/>
@@ -4788,6 +4840,7 @@
       <c r="AY48" s="4" t="n"/>
       <c r="AZ48" s="4" t="n"/>
       <c r="BA48" s="4" t="n"/>
+      <c r="BB48" s="4" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -4879,6 +4932,7 @@
       <c r="BA49" s="4" t="n">
         <v>30.59</v>
       </c>
+      <c r="BB49" s="4" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="n"/>
@@ -4982,6 +5036,7 @@
         <v>26.89</v>
       </c>
       <c r="BA50" s="4" t="n"/>
+      <c r="BB50" s="4" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n"/>
@@ -5067,6 +5122,7 @@
       <c r="AY51" s="4" t="n"/>
       <c r="AZ51" s="4" t="n"/>
       <c r="BA51" s="4" t="n"/>
+      <c r="BB51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n"/>
@@ -5144,6 +5200,7 @@
       <c r="AY52" s="4" t="n"/>
       <c r="AZ52" s="4" t="n"/>
       <c r="BA52" s="4" t="n"/>
+      <c r="BB52" s="4" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -5192,10 +5249,10 @@
       <c r="T53" s="4" t="n"/>
       <c r="U53" s="4" t="n"/>
       <c r="V53" s="4" t="n"/>
-      <c r="W53" s="4" t="n">
+      <c r="W53" s="4" t="n"/>
+      <c r="X53" s="4" t="n">
         <v>31.72</v>
       </c>
-      <c r="X53" s="4" t="n"/>
       <c r="Y53" s="4" t="n"/>
       <c r="Z53" s="4" t="n">
         <v>32.09</v>
@@ -5227,6 +5284,7 @@
       <c r="AY53" s="4" t="n"/>
       <c r="AZ53" s="4" t="n"/>
       <c r="BA53" s="4" t="n"/>
+      <c r="BB53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n"/>
@@ -5302,6 +5360,7 @@
       <c r="AY54" s="4" t="n"/>
       <c r="AZ54" s="4" t="n"/>
       <c r="BA54" s="4" t="n"/>
+      <c r="BB54" s="4" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n"/>
@@ -5389,6 +5448,7 @@
       <c r="AY55" s="4" t="n"/>
       <c r="AZ55" s="4" t="n"/>
       <c r="BA55" s="4" t="n"/>
+      <c r="BB55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n"/>
@@ -5462,6 +5522,7 @@
       <c r="AY56" s="4" t="n"/>
       <c r="AZ56" s="4" t="n"/>
       <c r="BA56" s="4" t="n"/>
+      <c r="BB56" s="4" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -5516,10 +5577,10 @@
       <c r="T57" s="4" t="n"/>
       <c r="U57" s="4" t="n"/>
       <c r="V57" s="4" t="n"/>
-      <c r="W57" s="4" t="n">
+      <c r="W57" s="4" t="n"/>
+      <c r="X57" s="4" t="n">
         <v>34.3</v>
       </c>
-      <c r="X57" s="4" t="n"/>
       <c r="Y57" s="4" t="n"/>
       <c r="Z57" s="4" t="n">
         <v>34.79</v>
@@ -5551,6 +5612,7 @@
       <c r="AY57" s="4" t="n"/>
       <c r="AZ57" s="4" t="n"/>
       <c r="BA57" s="4" t="n"/>
+      <c r="BB57" s="4" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="n"/>
@@ -5590,12 +5652,12 @@
       <c r="U58" s="4" t="n"/>
       <c r="V58" s="4" t="n"/>
       <c r="W58" s="4" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="X58" s="4" t="n">
         <v>24.19</v>
       </c>
-      <c r="X58" s="4" t="n"/>
-      <c r="Y58" s="4" t="n">
-        <v>26.2</v>
-      </c>
+      <c r="Y58" s="4" t="n"/>
       <c r="Z58" s="4" t="n"/>
       <c r="AA58" s="4" t="n"/>
       <c r="AB58" s="4" t="n"/>
@@ -5624,6 +5686,7 @@
       <c r="AY58" s="4" t="n"/>
       <c r="AZ58" s="4" t="n"/>
       <c r="BA58" s="4" t="n"/>
+      <c r="BB58" s="4" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n"/>
@@ -5707,6 +5770,7 @@
       <c r="AY59" s="4" t="n"/>
       <c r="AZ59" s="4" t="n"/>
       <c r="BA59" s="4" t="n"/>
+      <c r="BB59" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n"/>
@@ -5750,10 +5814,10 @@
       <c r="U60" s="4" t="n"/>
       <c r="V60" s="4" t="n"/>
       <c r="W60" s="4" t="n"/>
-      <c r="X60" s="4" t="n">
+      <c r="X60" s="4" t="n"/>
+      <c r="Y60" s="4" t="n">
         <v>36.5</v>
       </c>
-      <c r="Y60" s="4" t="n"/>
       <c r="Z60" s="4" t="n"/>
       <c r="AA60" s="4" t="n"/>
       <c r="AB60" s="4" t="n"/>
@@ -5782,6 +5846,9 @@
       <c r="AY60" s="4" t="n"/>
       <c r="AZ60" s="4" t="n"/>
       <c r="BA60" s="4" t="n"/>
+      <c r="BB60" s="4" t="n">
+        <v>38.65</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -5834,10 +5901,10 @@
       </c>
       <c r="U61" s="4" t="n"/>
       <c r="V61" s="4" t="n"/>
-      <c r="W61" s="4" t="n">
+      <c r="W61" s="4" t="n"/>
+      <c r="X61" s="4" t="n">
         <v>21.1</v>
       </c>
-      <c r="X61" s="4" t="n"/>
       <c r="Y61" s="4" t="n"/>
       <c r="Z61" s="4" t="n"/>
       <c r="AA61" s="4" t="n"/>
@@ -5865,22 +5932,23 @@
       <c r="AO61" s="4" t="n"/>
       <c r="AP61" s="4" t="n"/>
       <c r="AQ61" s="4" t="n">
+        <v>21.92</v>
+      </c>
+      <c r="AR61" s="4" t="n">
         <v>22.3</v>
       </c>
-      <c r="AR61" s="4" t="n">
+      <c r="AS61" s="4" t="n">
         <v>21.89</v>
       </c>
-      <c r="AS61" s="4" t="n"/>
       <c r="AT61" s="4" t="n"/>
       <c r="AU61" s="4" t="n"/>
       <c r="AV61" s="4" t="n"/>
       <c r="AW61" s="4" t="n"/>
       <c r="AX61" s="4" t="n"/>
-      <c r="AY61" s="4" t="n">
-        <v>21.92</v>
-      </c>
+      <c r="AY61" s="4" t="n"/>
       <c r="AZ61" s="4" t="n"/>
       <c r="BA61" s="4" t="n"/>
+      <c r="BB61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="n"/>
@@ -5968,6 +6036,7 @@
       <c r="AY62" s="4" t="n"/>
       <c r="AZ62" s="4" t="n"/>
       <c r="BA62" s="4" t="n"/>
+      <c r="BB62" s="4" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n"/>
@@ -6021,10 +6090,10 @@
       <c r="U63" s="4" t="n"/>
       <c r="V63" s="4" t="n"/>
       <c r="W63" s="4" t="n"/>
-      <c r="X63" s="4" t="n">
+      <c r="X63" s="4" t="n"/>
+      <c r="Y63" s="4" t="n">
         <v>23.58</v>
       </c>
-      <c r="Y63" s="4" t="n"/>
       <c r="Z63" s="4" t="n"/>
       <c r="AA63" s="4" t="n"/>
       <c r="AB63" s="4" t="n"/>
@@ -6055,6 +6124,7 @@
       <c r="AY63" s="4" t="n"/>
       <c r="AZ63" s="4" t="n"/>
       <c r="BA63" s="4" t="n"/>
+      <c r="BB63" s="4" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n"/>
@@ -6128,6 +6198,7 @@
       <c r="AY64" s="4" t="n"/>
       <c r="AZ64" s="4" t="n"/>
       <c r="BA64" s="4" t="n"/>
+      <c r="BB64" s="4" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -6217,6 +6288,7 @@
       <c r="AY65" s="4" t="n"/>
       <c r="AZ65" s="4" t="n"/>
       <c r="BA65" s="4" t="n"/>
+      <c r="BB65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="n"/>
@@ -6296,6 +6368,7 @@
       <c r="AY66" s="4" t="n"/>
       <c r="AZ66" s="4" t="n"/>
       <c r="BA66" s="4" t="n"/>
+      <c r="BB66" s="4" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n"/>
@@ -6341,10 +6414,10 @@
       <c r="U67" s="4" t="n"/>
       <c r="V67" s="4" t="n"/>
       <c r="W67" s="4" t="n"/>
-      <c r="X67" s="4" t="n">
+      <c r="X67" s="4" t="n"/>
+      <c r="Y67" s="4" t="n">
         <v>17.8</v>
       </c>
-      <c r="Y67" s="4" t="n"/>
       <c r="Z67" s="4" t="n"/>
       <c r="AA67" s="4" t="n"/>
       <c r="AB67" s="4" t="n"/>
@@ -6372,15 +6445,16 @@
       <c r="AR67" s="4" t="n"/>
       <c r="AS67" s="4" t="n"/>
       <c r="AT67" s="4" t="n"/>
-      <c r="AU67" s="4" t="n">
+      <c r="AU67" s="4" t="n"/>
+      <c r="AV67" s="4" t="n">
         <v>17.8</v>
       </c>
-      <c r="AV67" s="4" t="n"/>
       <c r="AW67" s="4" t="n"/>
       <c r="AX67" s="4" t="n"/>
       <c r="AY67" s="4" t="n"/>
       <c r="AZ67" s="4" t="n"/>
       <c r="BA67" s="4" t="n"/>
+      <c r="BB67" s="4" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n"/>
@@ -6429,12 +6503,12 @@
       <c r="T68" s="4" t="n"/>
       <c r="U68" s="4" t="n"/>
       <c r="V68" s="4" t="n"/>
-      <c r="W68" s="4" t="n"/>
-      <c r="X68" s="4" t="n">
+      <c r="W68" s="4" t="n">
+        <v>28.06</v>
+      </c>
+      <c r="X68" s="4" t="n"/>
+      <c r="Y68" s="4" t="n">
         <v>27.29</v>
-      </c>
-      <c r="Y68" s="4" t="n">
-        <v>28.06</v>
       </c>
       <c r="Z68" s="4" t="n"/>
       <c r="AA68" s="4" t="n"/>
@@ -6466,6 +6540,7 @@
       <c r="AY68" s="4" t="n"/>
       <c r="AZ68" s="4" t="n"/>
       <c r="BA68" s="4" t="n"/>
+      <c r="BB68" s="4" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -6543,6 +6618,7 @@
       <c r="AY69" s="4" t="n"/>
       <c r="AZ69" s="4" t="n"/>
       <c r="BA69" s="4" t="n"/>
+      <c r="BB69" s="4" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="n"/>
@@ -6589,10 +6665,10 @@
       <c r="T70" s="4" t="n"/>
       <c r="U70" s="4" t="n"/>
       <c r="V70" s="4" t="n"/>
-      <c r="W70" s="4" t="n">
+      <c r="W70" s="4" t="n"/>
+      <c r="X70" s="4" t="n">
         <v>20.7</v>
       </c>
-      <c r="X70" s="4" t="n"/>
       <c r="Y70" s="4" t="n"/>
       <c r="Z70" s="4" t="n"/>
       <c r="AA70" s="4" t="n"/>
@@ -6626,6 +6702,7 @@
       <c r="AY70" s="4" t="n"/>
       <c r="AZ70" s="4" t="n"/>
       <c r="BA70" s="4" t="n"/>
+      <c r="BB70" s="4" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n"/>
@@ -6670,10 +6747,10 @@
       <c r="T71" s="4" t="n"/>
       <c r="U71" s="4" t="n"/>
       <c r="V71" s="4" t="n"/>
-      <c r="W71" s="4" t="n">
+      <c r="W71" s="4" t="n"/>
+      <c r="X71" s="4" t="n">
         <v>36.9</v>
       </c>
-      <c r="X71" s="4" t="n"/>
       <c r="Y71" s="4" t="n"/>
       <c r="Z71" s="4" t="n"/>
       <c r="AA71" s="4" t="n"/>
@@ -6703,6 +6780,7 @@
       <c r="AY71" s="4" t="n"/>
       <c r="AZ71" s="4" t="n"/>
       <c r="BA71" s="4" t="n"/>
+      <c r="BB71" s="4" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n"/>
@@ -6783,7 +6861,9 @@
       <c r="AN72" s="4" t="n"/>
       <c r="AO72" s="4" t="n"/>
       <c r="AP72" s="4" t="n"/>
-      <c r="AQ72" s="4" t="n"/>
+      <c r="AQ72" s="4" t="n">
+        <v>26.15</v>
+      </c>
       <c r="AR72" s="4" t="n"/>
       <c r="AS72" s="4" t="n"/>
       <c r="AT72" s="4" t="n"/>
@@ -6794,6 +6874,7 @@
       <c r="AY72" s="4" t="n"/>
       <c r="AZ72" s="4" t="n"/>
       <c r="BA72" s="4" t="n"/>
+      <c r="BB72" s="4" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -6875,6 +6956,7 @@
       <c r="AY73" s="4" t="n"/>
       <c r="AZ73" s="4" t="n"/>
       <c r="BA73" s="4" t="n"/>
+      <c r="BB73" s="4" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="n"/>
@@ -6921,10 +7003,10 @@
       <c r="V74" s="4" t="n">
         <v>35.2</v>
       </c>
-      <c r="W74" s="4" t="n">
+      <c r="W74" s="4" t="n"/>
+      <c r="X74" s="4" t="n">
         <v>33.49</v>
       </c>
-      <c r="X74" s="4" t="n"/>
       <c r="Y74" s="4" t="n"/>
       <c r="Z74" s="4" t="n">
         <v>33</v>
@@ -6958,6 +7040,7 @@
       <c r="AY74" s="4" t="n"/>
       <c r="AZ74" s="4" t="n"/>
       <c r="BA74" s="4" t="n"/>
+      <c r="BB74" s="4" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n"/>
@@ -7043,6 +7126,7 @@
       <c r="AY75" s="4" t="n"/>
       <c r="AZ75" s="4" t="n"/>
       <c r="BA75" s="4" t="n"/>
+      <c r="BB75" s="4" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="n"/>
@@ -7120,6 +7204,7 @@
       <c r="AY76" s="4" t="n"/>
       <c r="AZ76" s="4" t="n"/>
       <c r="BA76" s="4" t="n"/>
+      <c r="BB76" s="4" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -7197,6 +7282,7 @@
       <c r="AY77" s="4" t="n"/>
       <c r="AZ77" s="4" t="n"/>
       <c r="BA77" s="4" t="n"/>
+      <c r="BB77" s="4" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="n"/>
@@ -7266,6 +7352,7 @@
       <c r="AY78" s="4" t="n"/>
       <c r="AZ78" s="4" t="n"/>
       <c r="BA78" s="4" t="n"/>
+      <c r="BB78" s="4" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n"/>
@@ -7341,6 +7428,7 @@
       <c r="AY79" s="4" t="n"/>
       <c r="AZ79" s="4" t="n"/>
       <c r="BA79" s="4" t="n"/>
+      <c r="BB79" s="4" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="n"/>
@@ -7414,6 +7502,7 @@
       <c r="AY80" s="4" t="n"/>
       <c r="AZ80" s="4" t="n"/>
       <c r="BA80" s="4" t="n"/>
+      <c r="BB80" s="4" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
@@ -7487,6 +7576,7 @@
       <c r="AY81" s="4" t="n"/>
       <c r="AZ81" s="4" t="n"/>
       <c r="BA81" s="4" t="n"/>
+      <c r="BB81" s="4" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="n"/>
@@ -7526,10 +7616,10 @@
       <c r="U82" s="4" t="n"/>
       <c r="V82" s="4" t="n"/>
       <c r="W82" s="4" t="n"/>
-      <c r="X82" s="4" t="n">
+      <c r="X82" s="4" t="n"/>
+      <c r="Y82" s="4" t="n">
         <v>55.6</v>
       </c>
-      <c r="Y82" s="4" t="n"/>
       <c r="Z82" s="4" t="n"/>
       <c r="AA82" s="4" t="n"/>
       <c r="AB82" s="4" t="n"/>
@@ -7558,6 +7648,7 @@
       <c r="AY82" s="4" t="n"/>
       <c r="AZ82" s="4" t="n"/>
       <c r="BA82" s="4" t="n"/>
+      <c r="BB82" s="4" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n"/>
@@ -7629,6 +7720,7 @@
       <c r="AY83" s="4" t="n"/>
       <c r="AZ83" s="4" t="n"/>
       <c r="BA83" s="4" t="n"/>
+      <c r="BB83" s="4" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="n"/>
@@ -7710,9 +7802,10 @@
       <c r="AY84" s="4" t="n"/>
       <c r="AZ84" s="4" t="n"/>
       <c r="BA84" s="4" t="n"/>
+      <c r="BB84" s="4" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BA84"/>
+  <autoFilter ref="A1:BB84"/>
   <mergeCells count="21">
     <mergeCell ref="A61:A64"/>
     <mergeCell ref="A69:A72"/>
@@ -8663,12 +8756,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>9x8</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>速尾</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>9x8</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -8760,10 +8853,10 @@
       </c>
       <c r="D2" s="4" t="n"/>
       <c r="E2" s="4" t="n"/>
-      <c r="F2" s="4" t="n"/>
-      <c r="G2" s="4" t="n">
+      <c r="F2" s="4" t="n">
         <v>16.9</v>
       </c>
+      <c r="G2" s="4" t="n"/>
       <c r="H2" s="4" t="n"/>
       <c r="I2" s="4" t="n"/>
       <c r="J2" s="4" t="n"/>
@@ -8830,10 +8923,10 @@
       </c>
       <c r="D4" s="4" t="n"/>
       <c r="E4" s="4" t="n"/>
-      <c r="F4" s="4" t="n"/>
-      <c r="G4" s="4" t="n">
+      <c r="F4" s="4" t="n">
         <v>24.99</v>
       </c>
+      <c r="G4" s="4" t="n"/>
       <c r="H4" s="4" t="n"/>
       <c r="I4" s="4" t="n">
         <v>24.59</v>
@@ -8871,10 +8964,10 @@
       </c>
       <c r="D5" s="4" t="n"/>
       <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n">
+      <c r="F5" s="4" t="n">
         <v>22.5</v>
       </c>
+      <c r="G5" s="4" t="n"/>
       <c r="H5" s="4" t="n"/>
       <c r="I5" s="4" t="n"/>
       <c r="J5" s="4" t="n"/>
@@ -8914,10 +9007,10 @@
       <c r="E6" s="4" t="n">
         <v>22.39</v>
       </c>
-      <c r="F6" s="4" t="n"/>
-      <c r="G6" s="4" t="n">
+      <c r="F6" s="4" t="n">
         <v>23.58</v>
       </c>
+      <c r="G6" s="4" t="n"/>
       <c r="H6" s="4" t="n">
         <v>22.54</v>
       </c>
@@ -8959,10 +9052,10 @@
       </c>
       <c r="D7" s="4" t="n"/>
       <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="n">
+      <c r="F7" s="4" t="n"/>
+      <c r="G7" s="4" t="n">
         <v>18.75</v>
       </c>
-      <c r="G7" s="4" t="n"/>
       <c r="H7" s="4" t="n">
         <v>18.45</v>
       </c>
@@ -9191,10 +9284,10 @@
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
-      <c r="F13" s="4" t="n"/>
-      <c r="G13" s="4" t="n">
+      <c r="F13" s="4" t="n">
         <v>21.39</v>
       </c>
+      <c r="G13" s="4" t="n"/>
       <c r="H13" s="4" t="n"/>
       <c r="I13" s="4" t="n"/>
       <c r="J13" s="4" t="n"/>
@@ -9261,10 +9354,10 @@
       </c>
       <c r="D15" s="4" t="n"/>
       <c r="E15" s="4" t="n"/>
-      <c r="F15" s="4" t="n"/>
-      <c r="G15" s="4" t="n">
+      <c r="F15" s="4" t="n">
         <v>14.7</v>
       </c>
+      <c r="G15" s="4" t="n"/>
       <c r="H15" s="4" t="n"/>
       <c r="I15" s="4" t="n"/>
       <c r="J15" s="4" t="n"/>
@@ -9337,17 +9430,19 @@
       <c r="K17" s="4" t="n"/>
       <c r="L17" s="4" t="n"/>
       <c r="M17" s="4" t="n">
-        <v>28</v>
+        <v>27.5</v>
       </c>
       <c r="N17" s="4" t="n"/>
       <c r="O17" s="4" t="n"/>
       <c r="P17" s="4" t="n"/>
       <c r="Q17" s="4" t="n"/>
       <c r="R17" s="4" t="n">
-        <v>29</v>
+        <v>28.5</v>
       </c>
       <c r="S17" s="4" t="n"/>
-      <c r="T17" s="4" t="n"/>
+      <c r="T17" s="4" t="n">
+        <v>27.9</v>
+      </c>
       <c r="U17" s="4" t="n"/>
     </row>
     <row r="18">
@@ -9434,10 +9529,10 @@
       </c>
       <c r="D20" s="4" t="n"/>
       <c r="E20" s="4" t="n"/>
-      <c r="F20" s="4" t="n"/>
-      <c r="G20" s="4" t="n">
+      <c r="F20" s="4" t="n">
         <v>18.95</v>
       </c>
+      <c r="G20" s="4" t="n"/>
       <c r="H20" s="4" t="n">
         <v>18.69</v>
       </c>
@@ -9524,7 +9619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9536,6 +9631,8 @@
     <col width="7.5" customWidth="1" min="7" max="7"/>
     <col width="7.5" customWidth="1" min="8" max="8"/>
     <col width="7.5" customWidth="1" min="9" max="9"/>
+    <col width="7.5" customWidth="1" min="10" max="10"/>
+    <col width="7.5" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9556,14 +9653,14 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>9x8★6</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>玻璃★3</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>9x8★6</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>c2★6</t>
@@ -9571,15 +9668,25 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>万达★6</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>fp1★6</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>sgt★6</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>小牛★6</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>fe3★5</t>
         </is>
@@ -9607,6 +9714,8 @@
       <c r="G2" s="4" t="n"/>
       <c r="H2" s="4" t="n"/>
       <c r="I2" s="4" t="n"/>
+      <c r="J2" s="4" t="n"/>
+      <c r="K2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="n"/>
@@ -9626,6 +9735,8 @@
       <c r="G3" s="4" t="n"/>
       <c r="H3" s="4" t="n"/>
       <c r="I3" s="4" t="n"/>
+      <c r="J3" s="4" t="n"/>
+      <c r="K3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -9646,11 +9757,13 @@
       <c r="D4" s="4" t="n"/>
       <c r="E4" s="4" t="n"/>
       <c r="F4" s="4" t="n"/>
-      <c r="G4" s="4" t="n">
+      <c r="G4" s="4" t="n"/>
+      <c r="H4" s="4" t="n">
         <v>24.79</v>
       </c>
-      <c r="H4" s="4" t="n"/>
       <c r="I4" s="4" t="n"/>
+      <c r="J4" s="4" t="n"/>
+      <c r="K4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -9668,14 +9781,16 @@
           <t>跳船</t>
         </is>
       </c>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n">
-        <v>22.9</v>
-      </c>
+      <c r="D5" s="4" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="E5" s="4" t="n"/>
       <c r="F5" s="4" t="n"/>
       <c r="G5" s="4" t="n"/>
       <c r="H5" s="4" t="n"/>
       <c r="I5" s="4" t="n"/>
+      <c r="J5" s="4" t="n"/>
+      <c r="K5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -9701,6 +9816,8 @@
       <c r="G6" s="4" t="n"/>
       <c r="H6" s="4" t="n"/>
       <c r="I6" s="4" t="n"/>
+      <c r="J6" s="4" t="n"/>
+      <c r="K6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -9724,6 +9841,8 @@
       <c r="G7" s="4" t="n"/>
       <c r="H7" s="4" t="n"/>
       <c r="I7" s="4" t="n"/>
+      <c r="J7" s="4" t="n"/>
+      <c r="K7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -9747,6 +9866,8 @@
       <c r="G8" s="4" t="n"/>
       <c r="H8" s="4" t="n"/>
       <c r="I8" s="4" t="n"/>
+      <c r="J8" s="4" t="n"/>
+      <c r="K8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -9770,6 +9891,8 @@
       <c r="G9" s="4" t="n"/>
       <c r="H9" s="4" t="n"/>
       <c r="I9" s="4" t="n"/>
+      <c r="J9" s="4" t="n"/>
+      <c r="K9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n"/>
@@ -9789,6 +9912,8 @@
       <c r="G10" s="4" t="n"/>
       <c r="H10" s="4" t="n"/>
       <c r="I10" s="4" t="n"/>
+      <c r="J10" s="4" t="n"/>
+      <c r="K10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -9812,6 +9937,8 @@
       <c r="G11" s="4" t="n"/>
       <c r="H11" s="4" t="n"/>
       <c r="I11" s="4" t="n"/>
+      <c r="J11" s="4" t="n"/>
+      <c r="K11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -9835,6 +9962,8 @@
       <c r="G12" s="4" t="n"/>
       <c r="H12" s="4" t="n"/>
       <c r="I12" s="4" t="n"/>
+      <c r="J12" s="4" t="n"/>
+      <c r="K12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -9858,6 +9987,8 @@
       <c r="G13" s="4" t="n"/>
       <c r="H13" s="4" t="n"/>
       <c r="I13" s="4" t="n"/>
+      <c r="J13" s="4" t="n"/>
+      <c r="K13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n"/>
@@ -9871,14 +10002,16 @@
           <t>跳图</t>
         </is>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n">
         <v>24.8</v>
       </c>
-      <c r="E14" s="4" t="n"/>
       <c r="F14" s="4" t="n"/>
       <c r="G14" s="4" t="n"/>
       <c r="H14" s="4" t="n"/>
-      <c r="I14" s="4" t="n">
+      <c r="I14" s="4" t="n"/>
+      <c r="J14" s="4" t="n"/>
+      <c r="K14" s="4" t="n">
         <v>25.8</v>
       </c>
     </row>
@@ -9904,6 +10037,8 @@
       <c r="G15" s="4" t="n"/>
       <c r="H15" s="4" t="n"/>
       <c r="I15" s="4" t="n"/>
+      <c r="J15" s="4" t="n"/>
+      <c r="K15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
@@ -9922,7 +10057,11 @@
       <c r="F16" s="4" t="n"/>
       <c r="G16" s="4" t="n"/>
       <c r="H16" s="4" t="n"/>
-      <c r="I16" s="4" t="n"/>
+      <c r="I16" s="4" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="J16" s="4" t="n"/>
+      <c r="K16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n"/>
@@ -9939,9 +10078,17 @@
       <c r="D17" s="4" t="n"/>
       <c r="E17" s="4" t="n"/>
       <c r="F17" s="4" t="n"/>
-      <c r="G17" s="4" t="n"/>
+      <c r="G17" s="4" t="n">
+        <v>26.9</v>
+      </c>
       <c r="H17" s="4" t="n"/>
-      <c r="I17" s="4" t="n"/>
+      <c r="I17" s="4" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="K17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n"/>
@@ -9961,6 +10108,8 @@
       <c r="G18" s="4" t="n"/>
       <c r="H18" s="4" t="n"/>
       <c r="I18" s="4" t="n"/>
+      <c r="J18" s="4" t="n"/>
+      <c r="K18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -9984,6 +10133,8 @@
       <c r="G19" s="4" t="n"/>
       <c r="H19" s="4" t="n"/>
       <c r="I19" s="4" t="n"/>
+      <c r="J19" s="4" t="n"/>
+      <c r="K19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -10005,10 +10156,12 @@
       <c r="E20" s="4" t="n"/>
       <c r="F20" s="4" t="n"/>
       <c r="G20" s="4" t="n"/>
-      <c r="H20" s="4" t="n">
+      <c r="H20" s="4" t="n"/>
+      <c r="I20" s="4" t="n">
         <v>19.2</v>
       </c>
-      <c r="I20" s="4" t="n"/>
+      <c r="J20" s="4" t="n"/>
+      <c r="K20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
@@ -10032,9 +10185,11 @@
       <c r="G21" s="4" t="n"/>
       <c r="H21" s="4" t="n"/>
       <c r="I21" s="4" t="n"/>
+      <c r="J21" s="4" t="n"/>
+      <c r="K21" s="4" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I21"/>
+  <autoFilter ref="A1:K21"/>
   <mergeCells count="14">
     <mergeCell ref="A8"/>
     <mergeCell ref="A6"/>
@@ -10377,34 +10532,34 @@
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
+          <t>狼崽★5</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
           <t>大超★1</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>大超★3</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>大超★6</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>速尾★4</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>速尾★6</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>狼崽★5</t>
-        </is>
-      </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>300+★6</t>
@@ -10547,12 +10702,12 @@
       </c>
       <c r="CA1" s="1" t="inlineStr">
         <is>
+          <t>600lt★5</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
           <t>5n★4</t>
-        </is>
-      </c>
-      <c r="CB1" s="1" t="inlineStr">
-        <is>
-          <t>600lt★5</t>
         </is>
       </c>
       <c r="CC1" s="1" t="inlineStr">
@@ -10983,10 +11138,10 @@
       <c r="AT5" s="4" t="n"/>
       <c r="AU5" s="4" t="n"/>
       <c r="AV5" s="4" t="n"/>
-      <c r="AW5" s="4" t="n">
+      <c r="AW5" s="4" t="n"/>
+      <c r="AX5" s="4" t="n">
         <v>17.96</v>
       </c>
-      <c r="AX5" s="4" t="n"/>
       <c r="AY5" s="4" t="n"/>
       <c r="AZ5" s="4" t="n"/>
       <c r="BA5" s="4" t="n"/>
@@ -11426,10 +11581,10 @@
       <c r="AS9" s="4" t="n"/>
       <c r="AT9" s="4" t="n"/>
       <c r="AU9" s="4" t="n"/>
-      <c r="AV9" s="4" t="n">
+      <c r="AV9" s="4" t="n"/>
+      <c r="AW9" s="4" t="n">
         <v>20.52</v>
       </c>
-      <c r="AW9" s="4" t="n"/>
       <c r="AX9" s="4" t="n"/>
       <c r="AY9" s="4" t="n"/>
       <c r="AZ9" s="4" t="n"/>
@@ -11639,14 +11794,14 @@
       <c r="AP11" s="4" t="n"/>
       <c r="AQ11" s="4" t="n"/>
       <c r="AR11" s="4" t="n"/>
-      <c r="AS11" s="4" t="n"/>
+      <c r="AS11" s="4" t="n">
+        <v>37.99</v>
+      </c>
       <c r="AT11" s="4" t="n"/>
       <c r="AU11" s="4" t="n"/>
       <c r="AV11" s="4" t="n"/>
       <c r="AW11" s="4" t="n"/>
-      <c r="AX11" s="4" t="n">
-        <v>37.99</v>
-      </c>
+      <c r="AX11" s="4" t="n"/>
       <c r="AY11" s="4" t="n"/>
       <c r="AZ11" s="4" t="n">
         <v>36.85</v>
@@ -12071,7 +12226,9 @@
       <c r="AP15" s="4" t="n"/>
       <c r="AQ15" s="4" t="n"/>
       <c r="AR15" s="4" t="n"/>
-      <c r="AS15" s="4" t="n"/>
+      <c r="AS15" s="4" t="n">
+        <v>30.4</v>
+      </c>
       <c r="AT15" s="4" t="n"/>
       <c r="AU15" s="4" t="n"/>
       <c r="AV15" s="4" t="n"/>
@@ -12391,13 +12548,15 @@
       <c r="AP18" s="4" t="n"/>
       <c r="AQ18" s="4" t="n"/>
       <c r="AR18" s="4" t="n"/>
-      <c r="AS18" s="4" t="n"/>
+      <c r="AS18" s="4" t="n">
+        <v>24.79</v>
+      </c>
       <c r="AT18" s="4" t="n"/>
       <c r="AU18" s="4" t="n"/>
-      <c r="AV18" s="4" t="n">
+      <c r="AV18" s="4" t="n"/>
+      <c r="AW18" s="4" t="n">
         <v>24.59</v>
       </c>
-      <c r="AW18" s="4" t="n"/>
       <c r="AX18" s="4" t="n"/>
       <c r="AY18" s="4" t="n"/>
       <c r="AZ18" s="4" t="n"/>
@@ -12939,7 +13098,9 @@
       <c r="AP23" s="4" t="n"/>
       <c r="AQ23" s="4" t="n"/>
       <c r="AR23" s="4" t="n"/>
-      <c r="AS23" s="4" t="n"/>
+      <c r="AS23" s="4" t="n">
+        <v>32.3</v>
+      </c>
       <c r="AT23" s="4" t="n"/>
       <c r="AU23" s="4" t="n"/>
       <c r="AV23" s="4" t="n"/>
@@ -13048,10 +13209,10 @@
       <c r="AS24" s="4" t="n"/>
       <c r="AT24" s="4" t="n"/>
       <c r="AU24" s="4" t="n"/>
-      <c r="AV24" s="4" t="n">
+      <c r="AV24" s="4" t="n"/>
+      <c r="AW24" s="4" t="n">
         <v>23.69</v>
       </c>
-      <c r="AW24" s="4" t="n"/>
       <c r="AX24" s="4" t="n"/>
       <c r="AY24" s="4" t="n"/>
       <c r="AZ24" s="4" t="n"/>
@@ -13261,7 +13422,9 @@
       <c r="AP26" s="4" t="n"/>
       <c r="AQ26" s="4" t="n"/>
       <c r="AR26" s="4" t="n"/>
-      <c r="AS26" s="4" t="n"/>
+      <c r="AS26" s="4" t="n">
+        <v>19.5</v>
+      </c>
       <c r="AT26" s="4" t="n"/>
       <c r="AU26" s="4" t="n"/>
       <c r="AV26" s="4" t="n"/>
@@ -13491,10 +13654,10 @@
       <c r="AT28" s="4" t="n"/>
       <c r="AU28" s="4" t="n"/>
       <c r="AV28" s="4" t="n"/>
-      <c r="AW28" s="4" t="n">
+      <c r="AW28" s="4" t="n"/>
+      <c r="AX28" s="4" t="n">
         <v>32.9</v>
       </c>
-      <c r="AX28" s="4" t="n"/>
       <c r="AY28" s="4" t="n"/>
       <c r="AZ28" s="4" t="n"/>
       <c r="BA28" s="4" t="n"/>
@@ -13921,15 +14084,15 @@
         <v>27.4</v>
       </c>
       <c r="AR32" s="4" t="n"/>
-      <c r="AS32" s="4" t="n"/>
+      <c r="AS32" s="4" t="n">
+        <v>29.3</v>
+      </c>
       <c r="AT32" s="4" t="n"/>
       <c r="AU32" s="4" t="n"/>
       <c r="AV32" s="4" t="n"/>
-      <c r="AW32" s="4" t="n">
+      <c r="AW32" s="4" t="n"/>
+      <c r="AX32" s="4" t="n">
         <v>28.3</v>
-      </c>
-      <c r="AX32" s="4" t="n">
-        <v>29.3</v>
       </c>
       <c r="AY32" s="4" t="n"/>
       <c r="AZ32" s="4" t="n"/>
@@ -14237,7 +14400,7 @@
       <c r="AB35" s="4" t="n"/>
       <c r="AC35" s="4" t="n"/>
       <c r="AD35" s="4" t="n">
-        <v>23.74</v>
+        <v>23.7</v>
       </c>
       <c r="AE35" s="4" t="n"/>
       <c r="AF35" s="4" t="n"/>
@@ -15013,14 +15176,14 @@
         <v>21.4</v>
       </c>
       <c r="AR42" s="4" t="n"/>
-      <c r="AS42" s="4" t="n"/>
+      <c r="AS42" s="4" t="n">
+        <v>22.8</v>
+      </c>
       <c r="AT42" s="4" t="n"/>
       <c r="AU42" s="4" t="n"/>
       <c r="AV42" s="4" t="n"/>
       <c r="AW42" s="4" t="n"/>
-      <c r="AX42" s="4" t="n">
-        <v>22.8</v>
-      </c>
+      <c r="AX42" s="4" t="n"/>
       <c r="AY42" s="4" t="n"/>
       <c r="AZ42" s="4" t="n"/>
       <c r="BA42" s="4" t="n"/>
@@ -15661,14 +15824,14 @@
         <v>24.5</v>
       </c>
       <c r="AR48" s="4" t="n"/>
-      <c r="AS48" s="4" t="n"/>
+      <c r="AS48" s="4" t="n">
+        <v>25.8</v>
+      </c>
       <c r="AT48" s="4" t="n"/>
       <c r="AU48" s="4" t="n"/>
       <c r="AV48" s="4" t="n"/>
       <c r="AW48" s="4" t="n"/>
-      <c r="AX48" s="4" t="n">
-        <v>25.8</v>
-      </c>
+      <c r="AX48" s="4" t="n"/>
       <c r="AY48" s="4" t="n"/>
       <c r="AZ48" s="4" t="n"/>
       <c r="BA48" s="4" t="n"/>
@@ -15876,7 +16039,9 @@
       <c r="AO50" s="4" t="n"/>
       <c r="AP50" s="4" t="n"/>
       <c r="AQ50" s="4" t="n"/>
-      <c r="AR50" s="4" t="n"/>
+      <c r="AR50" s="4" t="n">
+        <v>27.09</v>
+      </c>
       <c r="AS50" s="4" t="n"/>
       <c r="AT50" s="4" t="n"/>
       <c r="AU50" s="4" t="n"/>
@@ -16643,10 +16808,10 @@
       <c r="AP57" s="4" t="n"/>
       <c r="AQ57" s="4" t="n"/>
       <c r="AR57" s="4" t="n"/>
-      <c r="AS57" s="4" t="n">
+      <c r="AS57" s="4" t="n"/>
+      <c r="AT57" s="4" t="n">
         <v>36.39</v>
       </c>
-      <c r="AT57" s="4" t="n"/>
       <c r="AU57" s="4" t="n"/>
       <c r="AV57" s="4" t="n"/>
       <c r="AW57" s="4" t="n"/>
@@ -17165,7 +17330,7 @@
       <c r="AB62" s="4" t="n"/>
       <c r="AC62" s="4" t="n"/>
       <c r="AD62" s="4" t="n">
-        <v>31.95</v>
+        <v>31.9</v>
       </c>
       <c r="AE62" s="4" t="n"/>
       <c r="AF62" s="4" t="n"/>
@@ -17264,7 +17429,9 @@
       <c r="AA63" s="4" t="n"/>
       <c r="AB63" s="4" t="n"/>
       <c r="AC63" s="4" t="n"/>
-      <c r="AD63" s="4" t="n"/>
+      <c r="AD63" s="4" t="n">
+        <v>24.6</v>
+      </c>
       <c r="AE63" s="4" t="n"/>
       <c r="AF63" s="4" t="n"/>
       <c r="AG63" s="4" t="n"/>
@@ -17390,7 +17557,9 @@
         <v>34.35</v>
       </c>
       <c r="AQ64" s="4" t="n"/>
-      <c r="AR64" s="4" t="n"/>
+      <c r="AR64" s="4" t="n">
+        <v>37.05</v>
+      </c>
       <c r="AS64" s="4" t="n"/>
       <c r="AT64" s="4" t="n"/>
       <c r="AU64" s="4" t="n"/>
@@ -17715,10 +17884,10 @@
       <c r="AT67" s="4" t="n"/>
       <c r="AU67" s="4" t="n"/>
       <c r="AV67" s="4" t="n"/>
-      <c r="AW67" s="4" t="n">
+      <c r="AW67" s="4" t="n"/>
+      <c r="AX67" s="4" t="n">
         <v>18.09</v>
       </c>
-      <c r="AX67" s="4" t="n"/>
       <c r="AY67" s="4" t="n"/>
       <c r="AZ67" s="4" t="n"/>
       <c r="BA67" s="4" t="n"/>
@@ -17823,10 +17992,10 @@
       <c r="AT68" s="4" t="n"/>
       <c r="AU68" s="4" t="n"/>
       <c r="AV68" s="4" t="n"/>
-      <c r="AW68" s="4" t="n">
+      <c r="AW68" s="4" t="n"/>
+      <c r="AX68" s="4" t="n">
         <v>27.68</v>
       </c>
-      <c r="AX68" s="4" t="n"/>
       <c r="AY68" s="4" t="n"/>
       <c r="AZ68" s="4" t="n"/>
       <c r="BA68" s="4" t="n"/>
@@ -18571,14 +18740,14 @@
       <c r="AP75" s="4" t="n"/>
       <c r="AQ75" s="4" t="n"/>
       <c r="AR75" s="4" t="n"/>
-      <c r="AS75" s="4" t="n"/>
+      <c r="AS75" s="4" t="n">
+        <v>27.5</v>
+      </c>
       <c r="AT75" s="4" t="n"/>
       <c r="AU75" s="4" t="n"/>
       <c r="AV75" s="4" t="n"/>
       <c r="AW75" s="4" t="n"/>
-      <c r="AX75" s="4" t="n">
-        <v>27.5</v>
-      </c>
+      <c r="AX75" s="4" t="n"/>
       <c r="AY75" s="4" t="n"/>
       <c r="AZ75" s="4" t="n"/>
       <c r="BA75" s="4" t="n"/>
@@ -19931,34 +20100,34 @@
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
+          <t>狼崽★5</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
           <t>大超★1</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>大超★3</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>大超★6</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>速尾★4</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>速尾★6</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>狼崽★5</t>
-        </is>
-      </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>300+★6</t>
@@ -20101,12 +20270,12 @@
       </c>
       <c r="CA1" s="1" t="inlineStr">
         <is>
+          <t>600lt★5</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
           <t>5n★4</t>
-        </is>
-      </c>
-      <c r="CB1" s="1" t="inlineStr">
-        <is>
-          <t>600lt★5</t>
         </is>
       </c>
       <c r="CC1" s="1" t="inlineStr">
@@ -20381,15 +20550,15 @@
         </is>
       </c>
       <c r="AR3" s="4" t="n"/>
-      <c r="AS3" s="4" t="n"/>
+      <c r="AS3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT3" s="4" t="n"/>
       <c r="AU3" s="4" t="n"/>
       <c r="AV3" s="4" t="n"/>
-      <c r="AW3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AW3" s="4" t="n"/>
       <c r="AX3" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -20519,16 +20688,16 @@
         </is>
       </c>
       <c r="AR4" s="4" t="n"/>
-      <c r="AS4" s="4" t="n"/>
+      <c r="AS4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT4" s="4" t="n"/>
       <c r="AU4" s="4" t="n"/>
       <c r="AV4" s="4" t="n"/>
       <c r="AW4" s="4" t="n"/>
-      <c r="AX4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AX4" s="4" t="n"/>
       <c r="AY4" s="4" t="n"/>
       <c r="AZ4" s="4" t="n"/>
       <c r="BA4" s="4" t="n"/>
@@ -20673,12 +20842,12 @@
       <c r="AT5" s="4" t="n"/>
       <c r="AU5" s="4" t="n"/>
       <c r="AV5" s="4" t="n"/>
-      <c r="AW5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AX5" s="4" t="n"/>
+      <c r="AW5" s="4" t="n"/>
+      <c r="AX5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AY5" s="4" t="n"/>
       <c r="AZ5" s="4" t="n"/>
       <c r="BA5" s="4" t="n"/>
@@ -20861,12 +21030,12 @@
       <c r="BX6" s="4" t="n"/>
       <c r="BY6" s="4" t="n"/>
       <c r="BZ6" s="4" t="n"/>
-      <c r="CA6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CB6" s="4" t="n"/>
+      <c r="CA6" s="4" t="n"/>
+      <c r="CB6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CC6" s="4" t="n"/>
       <c r="CD6" s="4" t="n"/>
       <c r="CE6" s="4" t="n"/>
@@ -20973,16 +21142,16 @@
         </is>
       </c>
       <c r="AR7" s="4" t="n"/>
-      <c r="AS7" s="4" t="n"/>
+      <c r="AS7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT7" s="4" t="n"/>
       <c r="AU7" s="4" t="n"/>
       <c r="AV7" s="4" t="n"/>
       <c r="AW7" s="4" t="n"/>
-      <c r="AX7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AX7" s="4" t="n"/>
       <c r="AY7" s="4" t="n"/>
       <c r="AZ7" s="4" t="n"/>
       <c r="BA7" s="4" t="n"/>
@@ -21151,15 +21320,15 @@
         </is>
       </c>
       <c r="AR8" s="4" t="n"/>
-      <c r="AS8" s="4" t="n"/>
+      <c r="AS8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT8" s="4" t="n"/>
       <c r="AU8" s="4" t="n"/>
       <c r="AV8" s="4" t="n"/>
-      <c r="AW8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AW8" s="4" t="n"/>
       <c r="AX8" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -21304,12 +21473,12 @@
       <c r="AS9" s="4" t="n"/>
       <c r="AT9" s="4" t="n"/>
       <c r="AU9" s="4" t="n"/>
-      <c r="AV9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AW9" s="4" t="n"/>
+      <c r="AV9" s="4" t="n"/>
+      <c r="AW9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AX9" s="4" t="n"/>
       <c r="AY9" s="4" t="n"/>
       <c r="AZ9" s="4" t="n"/>
@@ -21359,12 +21528,12 @@
       <c r="BX9" s="4" t="n"/>
       <c r="BY9" s="4" t="n"/>
       <c r="BZ9" s="4" t="n"/>
-      <c r="CA9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CB9" s="4" t="n"/>
+      <c r="CA9" s="4" t="n"/>
+      <c r="CB9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CC9" s="4" t="n"/>
       <c r="CD9" s="4" t="n"/>
       <c r="CE9" s="4" t="n"/>
@@ -21637,16 +21806,16 @@
         </is>
       </c>
       <c r="AR11" s="4" t="n"/>
-      <c r="AS11" s="4" t="n"/>
+      <c r="AS11" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT11" s="4" t="n"/>
       <c r="AU11" s="4" t="n"/>
       <c r="AV11" s="4" t="n"/>
       <c r="AW11" s="4" t="n"/>
-      <c r="AX11" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AX11" s="4" t="n"/>
       <c r="AY11" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -21787,15 +21956,15 @@
       <c r="AP12" s="4" t="n"/>
       <c r="AQ12" s="4" t="n"/>
       <c r="AR12" s="4" t="n"/>
-      <c r="AS12" s="4" t="n"/>
+      <c r="AS12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT12" s="4" t="n"/>
       <c r="AU12" s="4" t="n"/>
       <c r="AV12" s="4" t="n"/>
-      <c r="AW12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AW12" s="4" t="n"/>
       <c r="AX12" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -21945,16 +22114,16 @@
         </is>
       </c>
       <c r="AR13" s="4" t="n"/>
-      <c r="AS13" s="4" t="n"/>
+      <c r="AS13" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT13" s="4" t="n"/>
       <c r="AU13" s="4" t="n"/>
       <c r="AV13" s="4" t="n"/>
       <c r="AW13" s="4" t="n"/>
-      <c r="AX13" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AX13" s="4" t="n"/>
       <c r="AY13" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -22111,16 +22280,16 @@
         </is>
       </c>
       <c r="AR14" s="4" t="n"/>
-      <c r="AS14" s="4" t="n"/>
+      <c r="AS14" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT14" s="4" t="n"/>
       <c r="AU14" s="4" t="n"/>
       <c r="AV14" s="4" t="n"/>
       <c r="AW14" s="4" t="n"/>
-      <c r="AX14" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AX14" s="4" t="n"/>
       <c r="AY14" s="4" t="n"/>
       <c r="AZ14" s="4" t="n"/>
       <c r="BA14" s="4" t="n"/>
@@ -22265,15 +22434,15 @@
         </is>
       </c>
       <c r="AR15" s="4" t="n"/>
-      <c r="AS15" s="4" t="n"/>
+      <c r="AS15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT15" s="4" t="n"/>
       <c r="AU15" s="4" t="n"/>
       <c r="AV15" s="4" t="n"/>
-      <c r="AW15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AW15" s="4" t="n"/>
       <c r="AX15" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -22435,16 +22604,16 @@
         </is>
       </c>
       <c r="AR16" s="4" t="n"/>
-      <c r="AS16" s="4" t="n"/>
+      <c r="AS16" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT16" s="4" t="n"/>
       <c r="AU16" s="4" t="n"/>
       <c r="AV16" s="4" t="n"/>
       <c r="AW16" s="4" t="n"/>
-      <c r="AX16" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AX16" s="4" t="n"/>
       <c r="AY16" s="4" t="n"/>
       <c r="AZ16" s="4" t="n"/>
       <c r="BA16" s="4" t="n"/>
@@ -22585,16 +22754,16 @@
         </is>
       </c>
       <c r="AR17" s="4" t="n"/>
-      <c r="AS17" s="4" t="n"/>
+      <c r="AS17" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT17" s="4" t="n"/>
       <c r="AU17" s="4" t="n"/>
       <c r="AV17" s="4" t="n"/>
       <c r="AW17" s="4" t="n"/>
-      <c r="AX17" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AX17" s="4" t="n"/>
       <c r="AY17" s="4" t="n"/>
       <c r="AZ17" s="4" t="n"/>
       <c r="BA17" s="4" t="n"/>
@@ -22727,14 +22896,14 @@
       <c r="AP18" s="4" t="n"/>
       <c r="AQ18" s="4" t="n"/>
       <c r="AR18" s="4" t="n"/>
-      <c r="AS18" s="4" t="n"/>
+      <c r="AS18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT18" s="4" t="n"/>
       <c r="AU18" s="4" t="n"/>
-      <c r="AV18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV18" s="4" t="n"/>
       <c r="AW18" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -22897,15 +23066,15 @@
         </is>
       </c>
       <c r="AR19" s="4" t="n"/>
-      <c r="AS19" s="4" t="n"/>
+      <c r="AS19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT19" s="4" t="n"/>
       <c r="AU19" s="4" t="n"/>
       <c r="AV19" s="4" t="n"/>
-      <c r="AW19" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AW19" s="4" t="n"/>
       <c r="AX19" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -23105,12 +23274,12 @@
       <c r="BX20" s="4" t="n"/>
       <c r="BY20" s="4" t="n"/>
       <c r="BZ20" s="4" t="n"/>
-      <c r="CA20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CB20" s="4" t="n"/>
+      <c r="CA20" s="4" t="n"/>
+      <c r="CB20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CC20" s="4" t="n"/>
       <c r="CD20" s="4" t="n"/>
       <c r="CE20" s="4" t="n"/>
@@ -23201,16 +23370,16 @@
         </is>
       </c>
       <c r="AR21" s="4" t="n"/>
-      <c r="AS21" s="4" t="n"/>
+      <c r="AS21" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT21" s="4" t="n"/>
       <c r="AU21" s="4" t="n"/>
       <c r="AV21" s="4" t="n"/>
       <c r="AW21" s="4" t="n"/>
-      <c r="AX21" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AX21" s="4" t="n"/>
       <c r="AY21" s="4" t="n"/>
       <c r="AZ21" s="4" t="n"/>
       <c r="BA21" s="4" t="n"/>
@@ -23355,20 +23524,20 @@
         </is>
       </c>
       <c r="AR22" s="4" t="n"/>
-      <c r="AS22" s="4" t="n"/>
+      <c r="AS22" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT22" s="4" t="n"/>
-      <c r="AU22" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AV22" s="4" t="n"/>
+      <c r="AU22" s="4" t="n"/>
+      <c r="AV22" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW22" s="4" t="n"/>
-      <c r="AX22" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AX22" s="4" t="n"/>
       <c r="AY22" s="4" t="n"/>
       <c r="AZ22" s="4" t="n"/>
       <c r="BA22" s="4" t="n"/>
@@ -23509,15 +23678,15 @@
         </is>
       </c>
       <c r="AR23" s="4" t="n"/>
-      <c r="AS23" s="4" t="n"/>
+      <c r="AS23" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT23" s="4" t="n"/>
       <c r="AU23" s="4" t="n"/>
       <c r="AV23" s="4" t="n"/>
-      <c r="AW23" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AW23" s="4" t="n"/>
       <c r="AX23" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -23647,20 +23816,20 @@
         </is>
       </c>
       <c r="AR24" s="4" t="n"/>
-      <c r="AS24" s="4" t="n"/>
+      <c r="AS24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT24" s="4" t="n"/>
       <c r="AU24" s="4" t="n"/>
-      <c r="AV24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AW24" s="4" t="n"/>
-      <c r="AX24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV24" s="4" t="n"/>
+      <c r="AW24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AX24" s="4" t="n"/>
       <c r="AY24" s="4" t="n"/>
       <c r="AZ24" s="4" t="n"/>
       <c r="BA24" s="4" t="n"/>
@@ -23797,12 +23966,12 @@
       <c r="AT25" s="4" t="n"/>
       <c r="AU25" s="4" t="n"/>
       <c r="AV25" s="4" t="n"/>
-      <c r="AW25" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AX25" s="4" t="n"/>
+      <c r="AW25" s="4" t="n"/>
+      <c r="AX25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AY25" s="4" t="n"/>
       <c r="AZ25" s="4" t="n"/>
       <c r="BA25" s="4" t="n"/>
@@ -23839,12 +24008,12 @@
       <c r="BX25" s="4" t="n"/>
       <c r="BY25" s="4" t="n"/>
       <c r="BZ25" s="4" t="n"/>
-      <c r="CA25" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CB25" s="4" t="n"/>
+      <c r="CA25" s="4" t="n"/>
+      <c r="CB25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CC25" s="4" t="n"/>
       <c r="CD25" s="4" t="n"/>
       <c r="CE25" s="4" t="n"/>
@@ -23947,16 +24116,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AS26" s="4" t="n"/>
+      <c r="AS26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT26" s="4" t="n"/>
       <c r="AU26" s="4" t="n"/>
       <c r="AV26" s="4" t="n"/>
       <c r="AW26" s="4" t="n"/>
-      <c r="AX26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AX26" s="4" t="n"/>
       <c r="AY26" s="4" t="n"/>
       <c r="AZ26" s="4" t="n"/>
       <c r="BA26" s="4" t="n"/>
@@ -24129,16 +24298,16 @@
         </is>
       </c>
       <c r="AR27" s="4" t="n"/>
-      <c r="AS27" s="4" t="n"/>
+      <c r="AS27" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT27" s="4" t="n"/>
       <c r="AU27" s="4" t="n"/>
       <c r="AV27" s="4" t="n"/>
       <c r="AW27" s="4" t="n"/>
-      <c r="AX27" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AX27" s="4" t="n"/>
       <c r="AY27" s="4" t="n"/>
       <c r="AZ27" s="4" t="n"/>
       <c r="BA27" s="4" t="n"/>
@@ -24267,15 +24436,15 @@
         </is>
       </c>
       <c r="AR28" s="4" t="n"/>
-      <c r="AS28" s="4" t="n"/>
+      <c r="AS28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT28" s="4" t="n"/>
       <c r="AU28" s="4" t="n"/>
       <c r="AV28" s="4" t="n"/>
-      <c r="AW28" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AW28" s="4" t="n"/>
       <c r="AX28" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -24413,24 +24582,24 @@
         </is>
       </c>
       <c r="AR29" s="4" t="n"/>
-      <c r="AS29" s="4" t="n"/>
-      <c r="AT29" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AS29" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AT29" s="4" t="n"/>
       <c r="AU29" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AV29" s="4" t="n"/>
+      <c r="AV29" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW29" s="4" t="n"/>
-      <c r="AX29" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AX29" s="4" t="n"/>
       <c r="AY29" s="4" t="n"/>
       <c r="AZ29" s="4" t="n"/>
       <c r="BA29" s="4" t="inlineStr">
@@ -24609,12 +24778,12 @@
       <c r="BX30" s="4" t="n"/>
       <c r="BY30" s="4" t="n"/>
       <c r="BZ30" s="4" t="n"/>
-      <c r="CA30" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CB30" s="4" t="n"/>
+      <c r="CA30" s="4" t="n"/>
+      <c r="CB30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CC30" s="4" t="n"/>
       <c r="CD30" s="4" t="n"/>
       <c r="CE30" s="4" t="n"/>
@@ -24739,12 +24908,12 @@
       <c r="BX31" s="4" t="n"/>
       <c r="BY31" s="4" t="n"/>
       <c r="BZ31" s="4" t="n"/>
-      <c r="CA31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CB31" s="4" t="n"/>
+      <c r="CA31" s="4" t="n"/>
+      <c r="CB31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CC31" s="4" t="n"/>
       <c r="CD31" s="4" t="n"/>
       <c r="CE31" s="4" t="n"/>
@@ -24859,15 +25028,15 @@
         </is>
       </c>
       <c r="AR32" s="4" t="n"/>
-      <c r="AS32" s="4" t="n"/>
+      <c r="AS32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT32" s="4" t="n"/>
       <c r="AU32" s="4" t="n"/>
       <c r="AV32" s="4" t="n"/>
-      <c r="AW32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AW32" s="4" t="n"/>
       <c r="AX32" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -24937,12 +25106,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="CA32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CB32" s="4" t="n"/>
+      <c r="CA32" s="4" t="n"/>
+      <c r="CB32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CC32" s="4" t="n"/>
       <c r="CD32" s="4" t="inlineStr">
         <is>
@@ -25191,15 +25360,15 @@
         </is>
       </c>
       <c r="AR34" s="4" t="n"/>
-      <c r="AS34" s="4" t="n"/>
+      <c r="AS34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT34" s="4" t="n"/>
       <c r="AU34" s="4" t="n"/>
       <c r="AV34" s="4" t="n"/>
-      <c r="AW34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AW34" s="4" t="n"/>
       <c r="AX34" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -25241,12 +25410,12 @@
       <c r="BX34" s="4" t="n"/>
       <c r="BY34" s="4" t="n"/>
       <c r="BZ34" s="4" t="n"/>
-      <c r="CA34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CB34" s="4" t="n"/>
+      <c r="CA34" s="4" t="n"/>
+      <c r="CB34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CC34" s="4" t="n"/>
       <c r="CD34" s="4" t="n"/>
       <c r="CE34" s="4" t="n"/>
@@ -25467,15 +25636,15 @@
         </is>
       </c>
       <c r="AR36" s="4" t="n"/>
-      <c r="AS36" s="4" t="n"/>
+      <c r="AS36" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT36" s="4" t="n"/>
       <c r="AU36" s="4" t="n"/>
       <c r="AV36" s="4" t="n"/>
-      <c r="AW36" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AW36" s="4" t="n"/>
       <c r="AX36" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -25671,12 +25840,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="CA37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CB37" s="4" t="n"/>
+      <c r="CA37" s="4" t="n"/>
+      <c r="CB37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CC37" s="4" t="n"/>
       <c r="CD37" s="4" t="n"/>
       <c r="CE37" s="4" t="n"/>
@@ -25771,12 +25940,12 @@
       <c r="AT38" s="4" t="n"/>
       <c r="AU38" s="4" t="n"/>
       <c r="AV38" s="4" t="n"/>
-      <c r="AW38" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AX38" s="4" t="n"/>
+      <c r="AW38" s="4" t="n"/>
+      <c r="AX38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AY38" s="4" t="n"/>
       <c r="AZ38" s="4" t="n"/>
       <c r="BA38" s="4" t="n"/>
@@ -25921,15 +26090,15 @@
       <c r="AP39" s="4" t="n"/>
       <c r="AQ39" s="4" t="n"/>
       <c r="AR39" s="4" t="n"/>
-      <c r="AS39" s="4" t="n"/>
+      <c r="AS39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT39" s="4" t="n"/>
       <c r="AU39" s="4" t="n"/>
       <c r="AV39" s="4" t="n"/>
-      <c r="AW39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AW39" s="4" t="n"/>
       <c r="AX39" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -26249,15 +26418,15 @@
         </is>
       </c>
       <c r="AR41" s="4" t="n"/>
-      <c r="AS41" s="4" t="n"/>
+      <c r="AS41" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT41" s="4" t="n"/>
       <c r="AU41" s="4" t="n"/>
       <c r="AV41" s="4" t="n"/>
-      <c r="AW41" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AW41" s="4" t="n"/>
       <c r="AX41" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -26407,16 +26576,16 @@
         </is>
       </c>
       <c r="AR42" s="4" t="n"/>
-      <c r="AS42" s="4" t="n"/>
+      <c r="AS42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT42" s="4" t="n"/>
       <c r="AU42" s="4" t="n"/>
       <c r="AV42" s="4" t="n"/>
       <c r="AW42" s="4" t="n"/>
-      <c r="AX42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AX42" s="4" t="n"/>
       <c r="AY42" s="4" t="n"/>
       <c r="AZ42" s="4" t="n"/>
       <c r="BA42" s="4" t="n"/>
@@ -26561,16 +26730,16 @@
         </is>
       </c>
       <c r="AR43" s="4" t="n"/>
-      <c r="AS43" s="4" t="n"/>
+      <c r="AS43" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT43" s="4" t="n"/>
       <c r="AU43" s="4" t="n"/>
       <c r="AV43" s="4" t="n"/>
       <c r="AW43" s="4" t="n"/>
-      <c r="AX43" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AX43" s="4" t="n"/>
       <c r="AY43" s="4" t="n"/>
       <c r="AZ43" s="4" t="n"/>
       <c r="BA43" s="4" t="n"/>
@@ -26869,16 +27038,16 @@
         </is>
       </c>
       <c r="AR45" s="4" t="n"/>
-      <c r="AS45" s="4" t="n"/>
+      <c r="AS45" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT45" s="4" t="n"/>
       <c r="AU45" s="4" t="n"/>
       <c r="AV45" s="4" t="n"/>
       <c r="AW45" s="4" t="n"/>
-      <c r="AX45" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AX45" s="4" t="n"/>
       <c r="AY45" s="4" t="n"/>
       <c r="AZ45" s="4" t="n"/>
       <c r="BA45" s="4" t="n"/>
@@ -27023,16 +27192,16 @@
         </is>
       </c>
       <c r="AR46" s="4" t="n"/>
-      <c r="AS46" s="4" t="n"/>
+      <c r="AS46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT46" s="4" t="n"/>
       <c r="AU46" s="4" t="n"/>
       <c r="AV46" s="4" t="n"/>
       <c r="AW46" s="4" t="n"/>
-      <c r="AX46" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AX46" s="4" t="n"/>
       <c r="AY46" s="4" t="n"/>
       <c r="AZ46" s="4" t="n"/>
       <c r="BA46" s="4" t="n"/>
@@ -27181,16 +27350,16 @@
         </is>
       </c>
       <c r="AR47" s="4" t="n"/>
-      <c r="AS47" s="4" t="n"/>
+      <c r="AS47" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT47" s="4" t="n"/>
       <c r="AU47" s="4" t="n"/>
       <c r="AV47" s="4" t="n"/>
       <c r="AW47" s="4" t="n"/>
-      <c r="AX47" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AX47" s="4" t="n"/>
       <c r="AY47" s="4" t="n"/>
       <c r="AZ47" s="4" t="n"/>
       <c r="BA47" s="4" t="n"/>
@@ -27335,16 +27504,16 @@
         </is>
       </c>
       <c r="AR48" s="4" t="n"/>
-      <c r="AS48" s="4" t="n"/>
+      <c r="AS48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT48" s="4" t="n"/>
       <c r="AU48" s="4" t="n"/>
       <c r="AV48" s="4" t="n"/>
       <c r="AW48" s="4" t="n"/>
-      <c r="AX48" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AX48" s="4" t="n"/>
       <c r="AY48" s="4" t="n"/>
       <c r="AZ48" s="4" t="n"/>
       <c r="BA48" s="4" t="n"/>
@@ -27539,12 +27708,12 @@
       <c r="BX49" s="4" t="n"/>
       <c r="BY49" s="4" t="n"/>
       <c r="BZ49" s="4" t="n"/>
-      <c r="CA49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CB49" s="4" t="n"/>
+      <c r="CA49" s="4" t="n"/>
+      <c r="CB49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CC49" s="4" t="n"/>
       <c r="CD49" s="4" t="n"/>
       <c r="CE49" s="4" t="n"/>
@@ -27793,16 +27962,16 @@
       <c r="AP51" s="4" t="n"/>
       <c r="AQ51" s="4" t="n"/>
       <c r="AR51" s="4" t="n"/>
-      <c r="AS51" s="4" t="n"/>
+      <c r="AS51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT51" s="4" t="n"/>
       <c r="AU51" s="4" t="n"/>
       <c r="AV51" s="4" t="n"/>
       <c r="AW51" s="4" t="n"/>
-      <c r="AX51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AX51" s="4" t="n"/>
       <c r="AY51" s="4" t="n"/>
       <c r="AZ51" s="4" t="n"/>
       <c r="BA51" s="4" t="n"/>
@@ -27943,16 +28112,16 @@
         </is>
       </c>
       <c r="AR52" s="4" t="n"/>
-      <c r="AS52" s="4" t="n"/>
+      <c r="AS52" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT52" s="4" t="n"/>
       <c r="AU52" s="4" t="n"/>
       <c r="AV52" s="4" t="n"/>
       <c r="AW52" s="4" t="n"/>
-      <c r="AX52" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AX52" s="4" t="n"/>
       <c r="AY52" s="4" t="n"/>
       <c r="AZ52" s="4" t="n"/>
       <c r="BA52" s="4" t="n"/>
@@ -28097,15 +28266,15 @@
         </is>
       </c>
       <c r="AR53" s="4" t="n"/>
-      <c r="AS53" s="4" t="n"/>
+      <c r="AS53" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT53" s="4" t="n"/>
       <c r="AU53" s="4" t="n"/>
       <c r="AV53" s="4" t="n"/>
-      <c r="AW53" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AW53" s="4" t="n"/>
       <c r="AX53" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -28255,16 +28424,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AS54" s="4" t="n"/>
+      <c r="AS54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT54" s="4" t="n"/>
       <c r="AU54" s="4" t="n"/>
       <c r="AV54" s="4" t="n"/>
       <c r="AW54" s="4" t="n"/>
-      <c r="AX54" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AX54" s="4" t="n"/>
       <c r="AY54" s="4" t="n"/>
       <c r="AZ54" s="4" t="n"/>
       <c r="BA54" s="4" t="n"/>
@@ -28547,16 +28716,16 @@
         </is>
       </c>
       <c r="AR56" s="4" t="n"/>
-      <c r="AS56" s="4" t="n"/>
+      <c r="AS56" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT56" s="4" t="n"/>
       <c r="AU56" s="4" t="n"/>
       <c r="AV56" s="4" t="n"/>
       <c r="AW56" s="4" t="n"/>
-      <c r="AX56" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AX56" s="4" t="n"/>
       <c r="AY56" s="4" t="n"/>
       <c r="AZ56" s="4" t="n"/>
       <c r="BA56" s="4" t="n"/>
@@ -28710,14 +28879,14 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AT57" s="4" t="n"/>
+      <c r="AT57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU57" s="4" t="n"/>
       <c r="AV57" s="4" t="n"/>
-      <c r="AW57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AW57" s="4" t="n"/>
       <c r="AX57" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -28883,16 +29052,16 @@
         </is>
       </c>
       <c r="AR58" s="4" t="n"/>
-      <c r="AS58" s="4" t="n"/>
+      <c r="AS58" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT58" s="4" t="n"/>
       <c r="AU58" s="4" t="n"/>
       <c r="AV58" s="4" t="n"/>
       <c r="AW58" s="4" t="n"/>
-      <c r="AX58" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AX58" s="4" t="n"/>
       <c r="AY58" s="4" t="n"/>
       <c r="AZ58" s="4" t="n"/>
       <c r="BA58" s="4" t="n"/>
@@ -29163,16 +29332,16 @@
         </is>
       </c>
       <c r="AR60" s="4" t="n"/>
-      <c r="AS60" s="4" t="n"/>
+      <c r="AS60" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT60" s="4" t="n"/>
       <c r="AU60" s="4" t="n"/>
       <c r="AV60" s="4" t="n"/>
       <c r="AW60" s="4" t="n"/>
-      <c r="AX60" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AX60" s="4" t="n"/>
       <c r="AY60" s="4" t="n"/>
       <c r="AZ60" s="4" t="n"/>
       <c r="BA60" s="4" t="n"/>
@@ -29467,12 +29636,12 @@
       <c r="AT62" s="4" t="n"/>
       <c r="AU62" s="4" t="n"/>
       <c r="AV62" s="4" t="n"/>
-      <c r="AW62" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AX62" s="4" t="n"/>
+      <c r="AW62" s="4" t="n"/>
+      <c r="AX62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AY62" s="4" t="n"/>
       <c r="AZ62" s="4" t="n"/>
       <c r="BA62" s="4" t="n"/>
@@ -29621,16 +29790,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AS63" s="4" t="n"/>
+      <c r="AS63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT63" s="4" t="n"/>
       <c r="AU63" s="4" t="n"/>
       <c r="AV63" s="4" t="n"/>
       <c r="AW63" s="4" t="n"/>
-      <c r="AX63" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AX63" s="4" t="n"/>
       <c r="AY63" s="4" t="n"/>
       <c r="AZ63" s="4" t="n"/>
       <c r="BA63" s="4" t="n"/>
@@ -29778,16 +29947,20 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AR64" s="4" t="n"/>
-      <c r="AS64" s="4" t="n"/>
+      <c r="AR64" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS64" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT64" s="4" t="n"/>
       <c r="AU64" s="4" t="n"/>
       <c r="AV64" s="4" t="n"/>
-      <c r="AW64" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AW64" s="4" t="n"/>
       <c r="AX64" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -29921,15 +30094,15 @@
         </is>
       </c>
       <c r="AR65" s="4" t="n"/>
-      <c r="AS65" s="4" t="n"/>
+      <c r="AS65" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT65" s="4" t="n"/>
       <c r="AU65" s="4" t="n"/>
       <c r="AV65" s="4" t="n"/>
-      <c r="AW65" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AW65" s="4" t="n"/>
       <c r="AX65" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -30083,16 +30256,16 @@
         </is>
       </c>
       <c r="AR66" s="4" t="n"/>
-      <c r="AS66" s="4" t="n"/>
+      <c r="AS66" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT66" s="4" t="n"/>
       <c r="AU66" s="4" t="n"/>
       <c r="AV66" s="4" t="n"/>
       <c r="AW66" s="4" t="n"/>
-      <c r="AX66" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AX66" s="4" t="n"/>
       <c r="AY66" s="4" t="n"/>
       <c r="AZ66" s="4" t="n"/>
       <c r="BA66" s="4" t="n"/>
@@ -30221,12 +30394,12 @@
       <c r="AT67" s="4" t="n"/>
       <c r="AU67" s="4" t="n"/>
       <c r="AV67" s="4" t="n"/>
-      <c r="AW67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AX67" s="4" t="n"/>
+      <c r="AW67" s="4" t="n"/>
+      <c r="AX67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AY67" s="4" t="n"/>
       <c r="AZ67" s="4" t="n"/>
       <c r="BA67" s="4" t="n"/>
@@ -30387,15 +30560,15 @@
         </is>
       </c>
       <c r="AR68" s="4" t="n"/>
-      <c r="AS68" s="4" t="n"/>
+      <c r="AS68" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT68" s="4" t="n"/>
       <c r="AU68" s="4" t="n"/>
       <c r="AV68" s="4" t="n"/>
-      <c r="AW68" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AW68" s="4" t="n"/>
       <c r="AX68" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -30857,16 +31030,16 @@
         </is>
       </c>
       <c r="AR71" s="4" t="n"/>
-      <c r="AS71" s="4" t="n"/>
+      <c r="AS71" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT71" s="4" t="n"/>
       <c r="AU71" s="4" t="n"/>
       <c r="AV71" s="4" t="n"/>
       <c r="AW71" s="4" t="n"/>
-      <c r="AX71" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AX71" s="4" t="n"/>
       <c r="AY71" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -31015,12 +31188,12 @@
       <c r="AT72" s="4" t="n"/>
       <c r="AU72" s="4" t="n"/>
       <c r="AV72" s="4" t="n"/>
-      <c r="AW72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AX72" s="4" t="n"/>
+      <c r="AW72" s="4" t="n"/>
+      <c r="AX72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AY72" s="4" t="n"/>
       <c r="AZ72" s="4" t="n"/>
       <c r="BA72" s="4" t="n"/>
@@ -31199,12 +31372,12 @@
       <c r="BX73" s="4" t="n"/>
       <c r="BY73" s="4" t="n"/>
       <c r="BZ73" s="4" t="n"/>
-      <c r="CA73" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CB73" s="4" t="n"/>
+      <c r="CA73" s="4" t="n"/>
+      <c r="CB73" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CC73" s="4" t="n"/>
       <c r="CD73" s="4" t="n"/>
       <c r="CE73" s="4" t="n"/>
@@ -31303,15 +31476,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AS74" s="4" t="n"/>
+      <c r="AS74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT74" s="4" t="n"/>
       <c r="AU74" s="4" t="n"/>
       <c r="AV74" s="4" t="n"/>
-      <c r="AW74" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AW74" s="4" t="n"/>
       <c r="AX74" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -31461,15 +31634,15 @@
         </is>
       </c>
       <c r="AR75" s="4" t="n"/>
-      <c r="AS75" s="4" t="n"/>
+      <c r="AS75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT75" s="4" t="n"/>
       <c r="AU75" s="4" t="n"/>
       <c r="AV75" s="4" t="n"/>
-      <c r="AW75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AW75" s="4" t="n"/>
       <c r="AX75" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -31769,20 +31942,20 @@
         </is>
       </c>
       <c r="AR77" s="4" t="n"/>
-      <c r="AS77" s="4" t="n"/>
+      <c r="AS77" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT77" s="4" t="n"/>
-      <c r="AU77" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AV77" s="4" t="n"/>
+      <c r="AU77" s="4" t="n"/>
+      <c r="AV77" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW77" s="4" t="n"/>
-      <c r="AX77" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AX77" s="4" t="n"/>
       <c r="AY77" s="4" t="n"/>
       <c r="AZ77" s="4" t="n"/>
       <c r="BA77" s="4" t="n"/>
@@ -31923,16 +32096,16 @@
         </is>
       </c>
       <c r="AR78" s="4" t="n"/>
-      <c r="AS78" s="4" t="n"/>
+      <c r="AS78" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT78" s="4" t="n"/>
       <c r="AU78" s="4" t="n"/>
       <c r="AV78" s="4" t="n"/>
       <c r="AW78" s="4" t="n"/>
-      <c r="AX78" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AX78" s="4" t="n"/>
       <c r="AY78" s="4" t="n"/>
       <c r="AZ78" s="4" t="n"/>
       <c r="BA78" s="4" t="n"/>
@@ -32069,16 +32242,16 @@
         </is>
       </c>
       <c r="AR79" s="4" t="n"/>
-      <c r="AS79" s="4" t="n"/>
+      <c r="AS79" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT79" s="4" t="n"/>
       <c r="AU79" s="4" t="n"/>
       <c r="AV79" s="4" t="n"/>
       <c r="AW79" s="4" t="n"/>
-      <c r="AX79" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AX79" s="4" t="n"/>
       <c r="AY79" s="4" t="n"/>
       <c r="AZ79" s="4" t="n"/>
       <c r="BA79" s="4" t="n"/>
@@ -32215,20 +32388,20 @@
         </is>
       </c>
       <c r="AR80" s="4" t="n"/>
-      <c r="AS80" s="4" t="n"/>
+      <c r="AS80" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT80" s="4" t="n"/>
-      <c r="AU80" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AV80" s="4" t="n"/>
+      <c r="AU80" s="4" t="n"/>
+      <c r="AV80" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AW80" s="4" t="n"/>
-      <c r="AX80" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AX80" s="4" t="n"/>
       <c r="AY80" s="4" t="n"/>
       <c r="AZ80" s="4" t="n"/>
       <c r="BA80" s="4" t="n"/>
@@ -36902,17 +37075,17 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>9x8</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>玻璃</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>速尾</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>9x8</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -37106,11 +37279,11 @@
       <c r="D2" s="4" t="n"/>
       <c r="E2" s="4" t="n"/>
       <c r="F2" s="4" t="n"/>
-      <c r="G2" s="4" t="n"/>
+      <c r="G2" s="4" t="n">
+        <v>18.89</v>
+      </c>
       <c r="H2" s="4" t="n"/>
-      <c r="I2" s="4" t="n">
-        <v>18.89</v>
-      </c>
+      <c r="I2" s="4" t="n"/>
       <c r="J2" s="4" t="n"/>
       <c r="K2" s="4" t="n"/>
       <c r="L2" s="4" t="n"/>
@@ -37166,10 +37339,10 @@
       </c>
       <c r="E3" s="4" t="n"/>
       <c r="F3" s="4" t="n"/>
-      <c r="G3" s="4" t="n">
+      <c r="G3" s="4" t="n"/>
+      <c r="H3" s="4" t="n">
         <v>28.42</v>
       </c>
-      <c r="H3" s="4" t="n"/>
       <c r="I3" s="4" t="n"/>
       <c r="J3" s="4" t="n">
         <v>28.45</v>
@@ -37233,10 +37406,10 @@
         <v>30.95</v>
       </c>
       <c r="G4" s="4" t="n"/>
-      <c r="H4" s="4" t="n">
+      <c r="H4" s="4" t="n"/>
+      <c r="I4" s="4" t="n">
         <v>31.69</v>
       </c>
-      <c r="I4" s="4" t="n"/>
       <c r="J4" s="4" t="n">
         <v>30.8</v>
       </c>
@@ -37295,13 +37468,13 @@
       <c r="E5" s="4" t="n"/>
       <c r="F5" s="4" t="n"/>
       <c r="G5" s="4" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="H5" s="4" t="n">
         <v>17.99</v>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="I5" s="4" t="n">
         <v>18.03</v>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>18.15</v>
       </c>
       <c r="J5" s="4" t="n"/>
       <c r="K5" s="4" t="n">
@@ -37368,11 +37541,11 @@
       <c r="D6" s="4" t="n"/>
       <c r="E6" s="4" t="n"/>
       <c r="F6" s="4" t="n"/>
-      <c r="G6" s="4" t="n"/>
+      <c r="G6" s="4" t="n">
+        <v>17.95</v>
+      </c>
       <c r="H6" s="4" t="n"/>
-      <c r="I6" s="4" t="n">
-        <v>17.95</v>
-      </c>
+      <c r="I6" s="4" t="n"/>
       <c r="J6" s="4" t="n"/>
       <c r="K6" s="4" t="n"/>
       <c r="L6" s="4" t="n"/>
@@ -37430,10 +37603,10 @@
         <v>24.39</v>
       </c>
       <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n">
+      <c r="G7" s="4" t="n"/>
+      <c r="H7" s="4" t="n">
         <v>24.69</v>
       </c>
-      <c r="H7" s="4" t="n"/>
       <c r="I7" s="4" t="n"/>
       <c r="J7" s="4" t="n"/>
       <c r="K7" s="4" t="n">
@@ -37492,13 +37665,13 @@
       <c r="F8" s="4" t="n">
         <v>27.73</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G8" s="4" t="n"/>
+      <c r="H8" s="4" t="n">
         <v>27.72</v>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="I8" s="4" t="n">
         <v>28.59</v>
       </c>
-      <c r="I8" s="4" t="n"/>
       <c r="J8" s="4" t="n">
         <v>28.1</v>
       </c>
@@ -37558,10 +37731,10 @@
       </c>
       <c r="E9" s="4" t="n"/>
       <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="n">
+      <c r="G9" s="4" t="n"/>
+      <c r="H9" s="4" t="n">
         <v>20.09</v>
       </c>
-      <c r="H9" s="4" t="n"/>
       <c r="I9" s="4" t="n"/>
       <c r="J9" s="4" t="n"/>
       <c r="K9" s="4" t="n"/>
@@ -37628,12 +37801,12 @@
       <c r="D10" s="4" t="n"/>
       <c r="E10" s="4" t="n"/>
       <c r="F10" s="4" t="n"/>
-      <c r="G10" s="4" t="n"/>
-      <c r="H10" s="4" t="n">
+      <c r="G10" s="4" t="n">
+        <v>23.42</v>
+      </c>
+      <c r="H10" s="4" t="n"/>
+      <c r="I10" s="4" t="n">
         <v>23.43</v>
-      </c>
-      <c r="I10" s="4" t="n">
-        <v>23.42</v>
       </c>
       <c r="J10" s="4" t="n"/>
       <c r="K10" s="4" t="n"/>
@@ -37692,10 +37865,10 @@
       <c r="F11" s="4" t="n">
         <v>35.25</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="G11" s="4" t="n"/>
+      <c r="H11" s="4" t="n">
         <v>35.49</v>
       </c>
-      <c r="H11" s="4" t="n"/>
       <c r="I11" s="4" t="n"/>
       <c r="J11" s="4" t="n"/>
       <c r="K11" s="4" t="n"/>
@@ -37745,10 +37918,10 @@
       <c r="E12" s="4" t="n"/>
       <c r="F12" s="4" t="n"/>
       <c r="G12" s="4" t="n"/>
-      <c r="H12" s="4" t="n">
+      <c r="H12" s="4" t="n"/>
+      <c r="I12" s="4" t="n">
         <v>21.83</v>
       </c>
-      <c r="I12" s="4" t="n"/>
       <c r="J12" s="4" t="n"/>
       <c r="K12" s="4" t="n">
         <v>21.55</v>
@@ -37874,11 +38047,11 @@
         <v>25.29</v>
       </c>
       <c r="F14" s="4" t="n"/>
-      <c r="G14" s="4" t="n"/>
+      <c r="G14" s="4" t="n">
+        <v>26.19</v>
+      </c>
       <c r="H14" s="4" t="n"/>
-      <c r="I14" s="4" t="n">
-        <v>26.19</v>
-      </c>
+      <c r="I14" s="4" t="n"/>
       <c r="J14" s="4" t="n"/>
       <c r="K14" s="4" t="n"/>
       <c r="L14" s="4" t="n"/>
@@ -37941,12 +38114,14 @@
         <v>28.9</v>
       </c>
       <c r="G15" s="4" t="n">
+        <v>29.19</v>
+      </c>
+      <c r="H15" s="4" t="n">
         <v>28.82</v>
       </c>
-      <c r="H15" s="4" t="n">
+      <c r="I15" s="4" t="n">
         <v>29.49</v>
       </c>
-      <c r="I15" s="4" t="n"/>
       <c r="J15" s="4" t="n"/>
       <c r="K15" s="4" t="n"/>
       <c r="L15" s="4" t="n"/>
@@ -38063,13 +38238,13 @@
       </c>
       <c r="F17" s="4" t="n"/>
       <c r="G17" s="4" t="n">
+        <v>30.69</v>
+      </c>
+      <c r="H17" s="4" t="n">
         <v>29.75</v>
       </c>
-      <c r="H17" s="4" t="n">
+      <c r="I17" s="4" t="n">
         <v>30.59</v>
-      </c>
-      <c r="I17" s="4" t="n">
-        <v>30.69</v>
       </c>
       <c r="J17" s="4" t="n"/>
       <c r="K17" s="4" t="n"/>
@@ -38125,10 +38300,10 @@
       <c r="E18" s="4" t="n"/>
       <c r="F18" s="4" t="n"/>
       <c r="G18" s="4" t="n"/>
-      <c r="H18" s="4" t="n">
+      <c r="H18" s="4" t="n"/>
+      <c r="I18" s="4" t="n">
         <v>23.72</v>
       </c>
-      <c r="I18" s="4" t="n"/>
       <c r="J18" s="4" t="n">
         <v>23.98</v>
       </c>
@@ -38200,11 +38375,11 @@
       <c r="F19" s="4" t="n">
         <v>32.19</v>
       </c>
-      <c r="G19" s="4" t="n"/>
+      <c r="G19" s="4" t="n">
+        <v>33.05</v>
+      </c>
       <c r="H19" s="4" t="n"/>
-      <c r="I19" s="4" t="n">
-        <v>33.05</v>
-      </c>
+      <c r="I19" s="4" t="n"/>
       <c r="J19" s="4" t="n"/>
       <c r="K19" s="4" t="n"/>
       <c r="L19" s="4" t="n"/>
@@ -38256,11 +38431,11 @@
         <v>22.09</v>
       </c>
       <c r="F20" s="4" t="n"/>
-      <c r="G20" s="4" t="n"/>
+      <c r="G20" s="4" t="n">
+        <v>22.4</v>
+      </c>
       <c r="H20" s="4" t="n"/>
-      <c r="I20" s="4" t="n">
-        <v>22.4</v>
-      </c>
+      <c r="I20" s="4" t="n"/>
       <c r="J20" s="4" t="n"/>
       <c r="K20" s="4" t="n"/>
       <c r="L20" s="4" t="n"/>
@@ -38557,10 +38732,10 @@
       <c r="E25" s="4" t="n"/>
       <c r="F25" s="4" t="n"/>
       <c r="G25" s="4" t="n"/>
-      <c r="H25" s="4" t="n">
+      <c r="H25" s="4" t="n"/>
+      <c r="I25" s="4" t="n">
         <v>24.35</v>
       </c>
-      <c r="I25" s="4" t="n"/>
       <c r="J25" s="4" t="n"/>
       <c r="K25" s="4" t="n"/>
       <c r="L25" s="4" t="n">
@@ -38621,10 +38796,10 @@
       <c r="E26" s="4" t="n"/>
       <c r="F26" s="4" t="n"/>
       <c r="G26" s="4" t="n"/>
-      <c r="H26" s="4" t="n">
+      <c r="H26" s="4" t="n"/>
+      <c r="I26" s="4" t="n">
         <v>18.89</v>
       </c>
-      <c r="I26" s="4" t="n"/>
       <c r="J26" s="4" t="n"/>
       <c r="K26" s="4" t="n">
         <v>18.6</v>
@@ -38684,10 +38859,10 @@
       <c r="D27" s="4" t="n"/>
       <c r="E27" s="4" t="n"/>
       <c r="F27" s="4" t="n"/>
-      <c r="G27" s="4" t="n">
+      <c r="G27" s="4" t="n"/>
+      <c r="H27" s="4" t="n">
         <v>32.85</v>
       </c>
-      <c r="H27" s="4" t="n"/>
       <c r="I27" s="4" t="n"/>
       <c r="J27" s="4" t="n">
         <v>32.79</v>
@@ -38745,10 +38920,10 @@
       </c>
       <c r="F28" s="4" t="n"/>
       <c r="G28" s="4" t="n"/>
-      <c r="H28" s="4" t="n">
+      <c r="H28" s="4" t="n"/>
+      <c r="I28" s="4" t="n">
         <v>33.09</v>
       </c>
-      <c r="I28" s="4" t="n"/>
       <c r="J28" s="4" t="n"/>
       <c r="K28" s="4" t="n">
         <v>33.05</v>
@@ -38806,10 +38981,10 @@
         <v>17.29</v>
       </c>
       <c r="F29" s="4" t="n"/>
-      <c r="G29" s="4" t="n">
+      <c r="G29" s="4" t="n"/>
+      <c r="H29" s="4" t="n">
         <v>17.89</v>
       </c>
-      <c r="H29" s="4" t="n"/>
       <c r="I29" s="4" t="n"/>
       <c r="J29" s="4" t="n"/>
       <c r="K29" s="4" t="n"/>
@@ -38868,11 +39043,11 @@
       <c r="D30" s="4" t="n"/>
       <c r="E30" s="4" t="n"/>
       <c r="F30" s="4" t="n"/>
-      <c r="G30" s="4" t="n"/>
+      <c r="G30" s="4" t="n">
+        <v>23.1</v>
+      </c>
       <c r="H30" s="4" t="n"/>
-      <c r="I30" s="4" t="n">
-        <v>23.1</v>
-      </c>
+      <c r="I30" s="4" t="n"/>
       <c r="J30" s="4" t="n"/>
       <c r="K30" s="4" t="n"/>
       <c r="L30" s="4" t="n"/>
@@ -38928,12 +39103,12 @@
       <c r="D31" s="4" t="n"/>
       <c r="E31" s="4" t="n"/>
       <c r="F31" s="4" t="n"/>
-      <c r="G31" s="4" t="n"/>
-      <c r="H31" s="4" t="n">
+      <c r="G31" s="4" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="H31" s="4" t="n"/>
+      <c r="I31" s="4" t="n">
         <v>19.35</v>
-      </c>
-      <c r="I31" s="4" t="n">
-        <v>18.99</v>
       </c>
       <c r="J31" s="4" t="n"/>
       <c r="K31" s="4" t="n"/>
@@ -38998,12 +39173,12 @@
       <c r="F32" s="4" t="n">
         <v>27.8</v>
       </c>
-      <c r="G32" s="4" t="n"/>
-      <c r="H32" s="4" t="n">
+      <c r="G32" s="4" t="n">
+        <v>29.06</v>
+      </c>
+      <c r="H32" s="4" t="n"/>
+      <c r="I32" s="4" t="n">
         <v>28.39</v>
-      </c>
-      <c r="I32" s="4" t="n">
-        <v>29.06</v>
       </c>
       <c r="J32" s="4" t="n"/>
       <c r="K32" s="4" t="n"/>
@@ -39064,11 +39239,11 @@
       <c r="D33" s="4" t="n"/>
       <c r="E33" s="4" t="n"/>
       <c r="F33" s="4" t="n"/>
-      <c r="G33" s="4" t="n"/>
+      <c r="G33" s="4" t="n">
+        <v>19.89</v>
+      </c>
       <c r="H33" s="4" t="n"/>
-      <c r="I33" s="4" t="n">
-        <v>19.89</v>
-      </c>
+      <c r="I33" s="4" t="n"/>
       <c r="J33" s="4" t="n"/>
       <c r="K33" s="4" t="n"/>
       <c r="L33" s="4" t="n"/>
@@ -39131,10 +39306,10 @@
       </c>
       <c r="F34" s="4" t="n"/>
       <c r="G34" s="4" t="n"/>
-      <c r="H34" s="4" t="n">
+      <c r="H34" s="4" t="n"/>
+      <c r="I34" s="4" t="n">
         <v>35.49</v>
       </c>
-      <c r="I34" s="4" t="n"/>
       <c r="J34" s="4" t="n">
         <v>34.7</v>
       </c>
@@ -39186,12 +39361,12 @@
       <c r="D35" s="4" t="n"/>
       <c r="E35" s="4" t="n"/>
       <c r="F35" s="4" t="n"/>
-      <c r="G35" s="4" t="n"/>
-      <c r="H35" s="4" t="n">
+      <c r="G35" s="4" t="n">
+        <v>23.59</v>
+      </c>
+      <c r="H35" s="4" t="n"/>
+      <c r="I35" s="4" t="n">
         <v>23.6</v>
-      </c>
-      <c r="I35" s="4" t="n">
-        <v>23.59</v>
       </c>
       <c r="J35" s="4" t="n"/>
       <c r="K35" s="4" t="n"/>
@@ -39252,11 +39427,11 @@
       <c r="F36" s="4" t="n">
         <v>34.6</v>
       </c>
-      <c r="G36" s="4" t="n"/>
+      <c r="G36" s="4" t="n">
+        <v>35.89</v>
+      </c>
       <c r="H36" s="4" t="n"/>
-      <c r="I36" s="4" t="n">
-        <v>35.89</v>
-      </c>
+      <c r="I36" s="4" t="n"/>
       <c r="J36" s="4" t="n"/>
       <c r="K36" s="4" t="n"/>
       <c r="L36" s="4" t="n"/>
@@ -39312,11 +39487,11 @@
         <v>22.45</v>
       </c>
       <c r="F37" s="4" t="n"/>
-      <c r="G37" s="4" t="n"/>
+      <c r="G37" s="4" t="n">
+        <v>23.05</v>
+      </c>
       <c r="H37" s="4" t="n"/>
-      <c r="I37" s="4" t="n">
-        <v>23.05</v>
-      </c>
+      <c r="I37" s="4" t="n"/>
       <c r="J37" s="4" t="n"/>
       <c r="K37" s="4" t="n"/>
       <c r="L37" s="4" t="n"/>
@@ -39368,12 +39543,12 @@
       <c r="D38" s="4" t="n"/>
       <c r="E38" s="4" t="n"/>
       <c r="F38" s="4" t="n"/>
-      <c r="G38" s="4" t="n"/>
-      <c r="H38" s="4" t="n">
+      <c r="G38" s="4" t="n">
+        <v>21.48</v>
+      </c>
+      <c r="H38" s="4" t="n"/>
+      <c r="I38" s="4" t="n">
         <v>20.99</v>
-      </c>
-      <c r="I38" s="4" t="n">
-        <v>21.48</v>
       </c>
       <c r="J38" s="4" t="n"/>
       <c r="K38" s="4" t="n">
@@ -39437,10 +39612,10 @@
       <c r="E39" s="4" t="n"/>
       <c r="F39" s="4" t="n"/>
       <c r="G39" s="4" t="n"/>
-      <c r="H39" s="4" t="n">
+      <c r="H39" s="4" t="n"/>
+      <c r="I39" s="4" t="n">
         <v>29.75</v>
       </c>
-      <c r="I39" s="4" t="n"/>
       <c r="J39" s="4" t="n"/>
       <c r="K39" s="4" t="n">
         <v>29.95</v>
@@ -39501,12 +39676,12 @@
         <v>33.59</v>
       </c>
       <c r="G40" s="4" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="H40" s="4" t="n">
         <v>33.99</v>
       </c>
-      <c r="H40" s="4" t="n"/>
-      <c r="I40" s="4" t="n">
-        <v>34.9</v>
-      </c>
+      <c r="I40" s="4" t="n"/>
       <c r="J40" s="4" t="n"/>
       <c r="K40" s="4" t="n"/>
       <c r="L40" s="4" t="n"/>
@@ -39566,10 +39741,10 @@
       <c r="F41" s="4" t="n">
         <v>30.39</v>
       </c>
-      <c r="G41" s="4" t="n">
+      <c r="G41" s="4" t="n"/>
+      <c r="H41" s="4" t="n">
         <v>30.29</v>
       </c>
-      <c r="H41" s="4" t="n"/>
       <c r="I41" s="4" t="n"/>
       <c r="J41" s="4" t="n"/>
       <c r="K41" s="4" t="n"/>
@@ -39620,11 +39795,11 @@
       </c>
       <c r="E42" s="4" t="n"/>
       <c r="F42" s="4" t="n"/>
-      <c r="G42" s="4" t="n"/>
+      <c r="G42" s="4" t="n">
+        <v>22.3</v>
+      </c>
       <c r="H42" s="4" t="n"/>
-      <c r="I42" s="4" t="n">
-        <v>22.3</v>
-      </c>
+      <c r="I42" s="4" t="n"/>
       <c r="J42" s="4" t="n"/>
       <c r="K42" s="4" t="n"/>
       <c r="L42" s="4" t="n">
@@ -39690,10 +39865,10 @@
       <c r="F43" s="4" t="n">
         <v>38.09</v>
       </c>
-      <c r="G43" s="4" t="n">
+      <c r="G43" s="4" t="n"/>
+      <c r="H43" s="4" t="n">
         <v>38.2</v>
       </c>
-      <c r="H43" s="4" t="n"/>
       <c r="I43" s="4" t="n"/>
       <c r="J43" s="4" t="n"/>
       <c r="K43" s="4" t="n"/>
@@ -39742,11 +39917,11 @@
       <c r="D44" s="4" t="n"/>
       <c r="E44" s="4" t="n"/>
       <c r="F44" s="4" t="n"/>
-      <c r="G44" s="4" t="n"/>
+      <c r="G44" s="4" t="n">
+        <v>22.25</v>
+      </c>
       <c r="H44" s="4" t="n"/>
-      <c r="I44" s="4" t="n">
-        <v>22.25</v>
-      </c>
+      <c r="I44" s="4" t="n"/>
       <c r="J44" s="4" t="n"/>
       <c r="K44" s="4" t="n"/>
       <c r="L44" s="4" t="n">
@@ -39819,10 +39994,10 @@
       </c>
       <c r="F45" s="4" t="n"/>
       <c r="G45" s="4" t="n"/>
-      <c r="H45" s="4" t="n">
+      <c r="H45" s="4" t="n"/>
+      <c r="I45" s="4" t="n">
         <v>40.69</v>
       </c>
-      <c r="I45" s="4" t="n"/>
       <c r="J45" s="4" t="n"/>
       <c r="K45" s="4" t="n"/>
       <c r="L45" s="4" t="n"/>
@@ -39880,10 +40055,10 @@
       <c r="F46" s="4" t="n">
         <v>32.29</v>
       </c>
-      <c r="G46" s="4" t="n">
+      <c r="G46" s="4" t="n"/>
+      <c r="H46" s="4" t="n">
         <v>32.49</v>
       </c>
-      <c r="H46" s="4" t="n"/>
       <c r="I46" s="4" t="n"/>
       <c r="J46" s="4" t="n"/>
       <c r="K46" s="4" t="n"/>
@@ -40106,11 +40281,11 @@
         <v>25.99</v>
       </c>
       <c r="F50" s="4" t="n"/>
-      <c r="G50" s="4" t="n"/>
+      <c r="G50" s="4" t="n">
+        <v>26.59</v>
+      </c>
       <c r="H50" s="4" t="n"/>
-      <c r="I50" s="4" t="n">
-        <v>26.59</v>
-      </c>
+      <c r="I50" s="4" t="n"/>
       <c r="J50" s="4" t="n"/>
       <c r="K50" s="4" t="n"/>
       <c r="L50" s="4" t="n"/>
@@ -40165,13 +40340,13 @@
       <c r="E51" s="4" t="n"/>
       <c r="F51" s="4" t="n"/>
       <c r="G51" s="4" t="n">
+        <v>24.39</v>
+      </c>
+      <c r="H51" s="4" t="n">
         <v>24.09</v>
       </c>
-      <c r="H51" s="4" t="n">
+      <c r="I51" s="4" t="n">
         <v>24.29</v>
-      </c>
-      <c r="I51" s="4" t="n">
-        <v>24.39</v>
       </c>
       <c r="J51" s="4" t="n"/>
       <c r="K51" s="4" t="n">
@@ -40234,10 +40409,10 @@
       <c r="F52" s="4" t="n">
         <v>32.3</v>
       </c>
-      <c r="G52" s="4" t="n">
+      <c r="G52" s="4" t="n"/>
+      <c r="H52" s="4" t="n">
         <v>32.05</v>
       </c>
-      <c r="H52" s="4" t="n"/>
       <c r="I52" s="4" t="n"/>
       <c r="J52" s="4" t="n"/>
       <c r="K52" s="4" t="n"/>
@@ -40411,12 +40586,12 @@
       </c>
       <c r="F55" s="4" t="n"/>
       <c r="G55" s="4" t="n">
+        <v>32.73</v>
+      </c>
+      <c r="H55" s="4" t="n">
         <v>32.85</v>
       </c>
-      <c r="H55" s="4" t="n"/>
-      <c r="I55" s="4" t="n">
-        <v>32.73</v>
-      </c>
+      <c r="I55" s="4" t="n"/>
       <c r="J55" s="4" t="n"/>
       <c r="K55" s="4" t="n"/>
       <c r="L55" s="4" t="n"/>
@@ -40474,10 +40649,10 @@
       <c r="F56" s="4" t="n">
         <v>35.6</v>
       </c>
-      <c r="G56" s="4" t="n">
+      <c r="G56" s="4" t="n"/>
+      <c r="H56" s="4" t="n">
         <v>35.95</v>
       </c>
-      <c r="H56" s="4" t="n"/>
       <c r="I56" s="4" t="n"/>
       <c r="J56" s="4" t="n"/>
       <c r="K56" s="4" t="n"/>
@@ -40536,10 +40711,10 @@
         <v>34.55</v>
       </c>
       <c r="F57" s="4" t="n"/>
-      <c r="G57" s="4" t="n">
+      <c r="G57" s="4" t="n"/>
+      <c r="H57" s="4" t="n">
         <v>35.55</v>
       </c>
-      <c r="H57" s="4" t="n"/>
       <c r="I57" s="4" t="n"/>
       <c r="J57" s="4" t="n"/>
       <c r="K57" s="4" t="n"/>
@@ -40596,10 +40771,10 @@
       <c r="F58" s="4" t="n">
         <v>24.43</v>
       </c>
-      <c r="G58" s="4" t="n">
+      <c r="G58" s="4" t="n"/>
+      <c r="H58" s="4" t="n">
         <v>24.59</v>
       </c>
-      <c r="H58" s="4" t="n"/>
       <c r="I58" s="4" t="n"/>
       <c r="J58" s="4" t="n"/>
       <c r="K58" s="4" t="n"/>
@@ -40655,12 +40830,12 @@
       <c r="E59" s="4" t="n"/>
       <c r="F59" s="4" t="n"/>
       <c r="G59" s="4" t="n">
+        <v>21.19</v>
+      </c>
+      <c r="H59" s="4" t="n">
         <v>21.29</v>
       </c>
-      <c r="H59" s="4" t="n"/>
-      <c r="I59" s="4" t="n">
-        <v>21.19</v>
-      </c>
+      <c r="I59" s="4" t="n"/>
       <c r="J59" s="4" t="n"/>
       <c r="K59" s="4" t="n"/>
       <c r="L59" s="4" t="n"/>
@@ -40778,11 +40953,11 @@
       </c>
       <c r="E61" s="4" t="n"/>
       <c r="F61" s="4" t="n"/>
-      <c r="G61" s="4" t="n"/>
+      <c r="G61" s="4" t="n">
+        <v>21.72</v>
+      </c>
       <c r="H61" s="4" t="n"/>
-      <c r="I61" s="4" t="n">
-        <v>21.72</v>
-      </c>
+      <c r="I61" s="4" t="n"/>
       <c r="J61" s="4" t="n"/>
       <c r="K61" s="4" t="n"/>
       <c r="L61" s="4" t="n">
@@ -40857,13 +41032,13 @@
         <v>29.85</v>
       </c>
       <c r="G62" s="4" t="n">
+        <v>31.49</v>
+      </c>
+      <c r="H62" s="4" t="n">
         <v>29.99</v>
       </c>
-      <c r="H62" s="4" t="n">
+      <c r="I62" s="4" t="n">
         <v>30.89</v>
-      </c>
-      <c r="I62" s="4" t="n">
-        <v>31.49</v>
       </c>
       <c r="J62" s="4" t="n"/>
       <c r="K62" s="4" t="n"/>
@@ -40915,12 +41090,12 @@
       <c r="E63" s="4" t="n"/>
       <c r="F63" s="4" t="n"/>
       <c r="G63" s="4" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="H63" s="4" t="n">
         <v>23.8</v>
       </c>
-      <c r="H63" s="4" t="n"/>
-      <c r="I63" s="4" t="n">
-        <v>24.5</v>
-      </c>
+      <c r="I63" s="4" t="n"/>
       <c r="J63" s="4" t="n"/>
       <c r="K63" s="4" t="n"/>
       <c r="L63" s="4" t="n"/>
@@ -40976,10 +41151,10 @@
       <c r="F64" s="4" t="n">
         <v>33.8</v>
       </c>
-      <c r="G64" s="4" t="n">
+      <c r="G64" s="4" t="n"/>
+      <c r="H64" s="4" t="n">
         <v>33.89</v>
       </c>
-      <c r="H64" s="4" t="n"/>
       <c r="I64" s="4" t="n"/>
       <c r="J64" s="4" t="n"/>
       <c r="K64" s="4" t="n"/>
@@ -41039,10 +41214,10 @@
         <v>32.9</v>
       </c>
       <c r="G65" s="4" t="n"/>
-      <c r="H65" s="4" t="n">
+      <c r="H65" s="4" t="n"/>
+      <c r="I65" s="4" t="n">
         <v>33.79</v>
       </c>
-      <c r="I65" s="4" t="n"/>
       <c r="J65" s="4" t="n"/>
       <c r="K65" s="4" t="n"/>
       <c r="L65" s="4" t="n"/>
@@ -41147,10 +41322,10 @@
       <c r="E67" s="4" t="n"/>
       <c r="F67" s="4" t="n"/>
       <c r="G67" s="4" t="n"/>
-      <c r="H67" s="4" t="n">
+      <c r="H67" s="4" t="n"/>
+      <c r="I67" s="4" t="n">
         <v>18.09</v>
       </c>
-      <c r="I67" s="4" t="n"/>
       <c r="J67" s="4" t="n"/>
       <c r="K67" s="4" t="n"/>
       <c r="L67" s="4" t="n"/>
@@ -41210,10 +41385,10 @@
       <c r="D68" s="4" t="n"/>
       <c r="E68" s="4" t="n"/>
       <c r="F68" s="4" t="n"/>
-      <c r="G68" s="4" t="n">
+      <c r="G68" s="4" t="n"/>
+      <c r="H68" s="4" t="n">
         <v>27.5</v>
       </c>
-      <c r="H68" s="4" t="n"/>
       <c r="I68" s="4" t="n"/>
       <c r="J68" s="4" t="n"/>
       <c r="K68" s="4" t="n"/>
@@ -41276,10 +41451,10 @@
       <c r="F69" s="4" t="n">
         <v>32.97</v>
       </c>
-      <c r="G69" s="4" t="n">
+      <c r="G69" s="4" t="n"/>
+      <c r="H69" s="4" t="n">
         <v>33.79</v>
       </c>
-      <c r="H69" s="4" t="n"/>
       <c r="I69" s="4" t="n"/>
       <c r="J69" s="4" t="n"/>
       <c r="K69" s="4" t="n"/>
@@ -41331,10 +41506,10 @@
       <c r="E70" s="4" t="n"/>
       <c r="F70" s="4" t="n"/>
       <c r="G70" s="4" t="n"/>
-      <c r="H70" s="4" t="n">
+      <c r="H70" s="4" t="n"/>
+      <c r="I70" s="4" t="n">
         <v>21.63</v>
       </c>
-      <c r="I70" s="4" t="n"/>
       <c r="J70" s="4" t="n"/>
       <c r="K70" s="4" t="n"/>
       <c r="L70" s="4" t="n">
@@ -41396,10 +41571,10 @@
       <c r="F71" s="4" t="n">
         <v>38.07</v>
       </c>
-      <c r="G71" s="4" t="n">
+      <c r="G71" s="4" t="n"/>
+      <c r="H71" s="4" t="n">
         <v>38.3</v>
       </c>
-      <c r="H71" s="4" t="n"/>
       <c r="I71" s="4" t="n"/>
       <c r="J71" s="4" t="n">
         <v>38.79</v>
@@ -41454,12 +41629,12 @@
         <v>25.6</v>
       </c>
       <c r="F72" s="4" t="n"/>
-      <c r="G72" s="4" t="n"/>
-      <c r="H72" s="4" t="n">
+      <c r="G72" s="4" t="n">
+        <v>25.93</v>
+      </c>
+      <c r="H72" s="4" t="n"/>
+      <c r="I72" s="4" t="n">
         <v>25.85</v>
-      </c>
-      <c r="I72" s="4" t="n">
-        <v>25.93</v>
       </c>
       <c r="J72" s="4" t="n"/>
       <c r="K72" s="4" t="n"/>
@@ -41524,11 +41699,11 @@
       <c r="D73" s="4" t="n"/>
       <c r="E73" s="4" t="n"/>
       <c r="F73" s="4" t="n"/>
-      <c r="G73" s="4" t="n"/>
+      <c r="G73" s="4" t="n">
+        <v>19.19</v>
+      </c>
       <c r="H73" s="4" t="n"/>
-      <c r="I73" s="4" t="n">
-        <v>19.19</v>
-      </c>
+      <c r="I73" s="4" t="n"/>
       <c r="J73" s="4" t="n"/>
       <c r="K73" s="4" t="n"/>
       <c r="L73" s="4" t="n"/>
@@ -41585,10 +41760,10 @@
       <c r="E74" s="4" t="n"/>
       <c r="F74" s="4" t="n"/>
       <c r="G74" s="4" t="n"/>
-      <c r="H74" s="4" t="n">
+      <c r="H74" s="4" t="n"/>
+      <c r="I74" s="4" t="n">
         <v>33.95</v>
       </c>
-      <c r="I74" s="4" t="n"/>
       <c r="J74" s="4" t="n">
         <v>34.79</v>
       </c>
@@ -41643,10 +41818,10 @@
       <c r="E75" s="4" t="n"/>
       <c r="F75" s="4" t="n"/>
       <c r="G75" s="4" t="n"/>
-      <c r="H75" s="4" t="n">
+      <c r="H75" s="4" t="n"/>
+      <c r="I75" s="4" t="n">
         <v>26.69</v>
       </c>
-      <c r="I75" s="4" t="n"/>
       <c r="J75" s="4" t="n"/>
       <c r="K75" s="4" t="n">
         <v>26.25</v>
@@ -41698,11 +41873,11 @@
       <c r="D76" s="4" t="n"/>
       <c r="E76" s="4" t="n"/>
       <c r="F76" s="4" t="n"/>
-      <c r="G76" s="4" t="n"/>
+      <c r="G76" s="4" t="n">
+        <v>16.6</v>
+      </c>
       <c r="H76" s="4" t="n"/>
-      <c r="I76" s="4" t="n">
-        <v>16.6</v>
-      </c>
+      <c r="I76" s="4" t="n"/>
       <c r="J76" s="4" t="n"/>
       <c r="K76" s="4" t="n"/>
       <c r="L76" s="4" t="n"/>
@@ -41822,10 +41997,10 @@
       <c r="F78" s="4" t="n">
         <v>31.2</v>
       </c>
-      <c r="G78" s="4" t="n">
+      <c r="G78" s="4" t="n"/>
+      <c r="H78" s="4" t="n">
         <v>31.59</v>
       </c>
-      <c r="H78" s="4" t="n"/>
       <c r="I78" s="4" t="n"/>
       <c r="J78" s="4" t="n">
         <v>31.8</v>
@@ -42000,10 +42175,10 @@
       <c r="F81" s="4" t="n">
         <v>63.6</v>
       </c>
-      <c r="G81" s="4" t="n">
+      <c r="G81" s="4" t="n"/>
+      <c r="H81" s="4" t="n">
         <v>63.99</v>
       </c>
-      <c r="H81" s="4" t="n"/>
       <c r="I81" s="4" t="n"/>
       <c r="J81" s="4" t="n"/>
       <c r="K81" s="4" t="n"/>
@@ -42169,10 +42344,10 @@
         <v>26.59</v>
       </c>
       <c r="G84" s="4" t="n"/>
-      <c r="H84" s="4" t="n">
+      <c r="H84" s="4" t="n"/>
+      <c r="I84" s="4" t="n">
         <v>27.39</v>
       </c>
-      <c r="I84" s="4" t="n"/>
       <c r="J84" s="4" t="n"/>
       <c r="K84" s="4" t="n"/>
       <c r="L84" s="4" t="n"/>
@@ -42379,37 +42554,37 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>9x8★6</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>玻璃★1</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>玻璃★2</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>玻璃★3</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>速尾★4</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>速尾★5</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>速尾★6</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>9x8★6</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
@@ -42645,15 +42820,15 @@
       <c r="K2" s="4" t="n"/>
       <c r="L2" s="4" t="n"/>
       <c r="M2" s="4" t="n"/>
-      <c r="N2" s="4" t="n"/>
+      <c r="N2" s="4" t="n">
+        <v>19.1</v>
+      </c>
       <c r="O2" s="4" t="n"/>
       <c r="P2" s="4" t="n"/>
       <c r="Q2" s="4" t="n"/>
       <c r="R2" s="4" t="n"/>
       <c r="S2" s="4" t="n"/>
-      <c r="T2" s="4" t="n">
-        <v>19.1</v>
-      </c>
+      <c r="T2" s="4" t="n"/>
       <c r="U2" s="4" t="n"/>
       <c r="V2" s="4" t="n"/>
       <c r="W2" s="4" t="n"/>
@@ -42663,7 +42838,7 @@
       <c r="AA2" s="4" t="n"/>
       <c r="AB2" s="4" t="n"/>
       <c r="AC2" s="4" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="AD2" s="4" t="n"/>
       <c r="AE2" s="4" t="n"/>
@@ -42672,7 +42847,7 @@
       <c r="AH2" s="4" t="n"/>
       <c r="AI2" s="4" t="n"/>
       <c r="AJ2" s="4" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="AK2" s="4" t="n"/>
       <c r="AL2" s="4" t="n"/>
@@ -42873,17 +43048,17 @@
       <c r="K5" s="4" t="n"/>
       <c r="L5" s="4" t="n"/>
       <c r="M5" s="4" t="n"/>
-      <c r="N5" s="4" t="n"/>
+      <c r="N5" s="4" t="n">
+        <v>18.2</v>
+      </c>
       <c r="O5" s="4" t="n"/>
       <c r="P5" s="4" t="n"/>
-      <c r="Q5" s="4" t="n">
+      <c r="Q5" s="4" t="n"/>
+      <c r="R5" s="4" t="n">
         <v>18.48</v>
       </c>
-      <c r="R5" s="4" t="n"/>
       <c r="S5" s="4" t="n"/>
-      <c r="T5" s="4" t="n">
-        <v>18.2</v>
-      </c>
+      <c r="T5" s="4" t="n"/>
       <c r="U5" s="4" t="n"/>
       <c r="V5" s="4" t="n"/>
       <c r="W5" s="4" t="n"/>
@@ -42953,15 +43128,15 @@
       <c r="K6" s="4" t="n"/>
       <c r="L6" s="4" t="n"/>
       <c r="M6" s="4" t="n"/>
-      <c r="N6" s="4" t="n"/>
+      <c r="N6" s="4" t="n">
+        <v>18.05</v>
+      </c>
       <c r="O6" s="4" t="n"/>
       <c r="P6" s="4" t="n"/>
       <c r="Q6" s="4" t="n"/>
       <c r="R6" s="4" t="n"/>
       <c r="S6" s="4" t="n"/>
-      <c r="T6" s="4" t="n">
-        <v>18.05</v>
-      </c>
+      <c r="T6" s="4" t="n"/>
       <c r="U6" s="4" t="n"/>
       <c r="V6" s="4" t="n"/>
       <c r="W6" s="4" t="n"/>
@@ -43109,10 +43284,10 @@
         <v>27.75</v>
       </c>
       <c r="M8" s="4" t="n"/>
-      <c r="N8" s="4" t="n">
+      <c r="N8" s="4" t="n"/>
+      <c r="O8" s="4" t="n">
         <v>28.23</v>
       </c>
-      <c r="O8" s="4" t="n"/>
       <c r="P8" s="4" t="n"/>
       <c r="Q8" s="4" t="n"/>
       <c r="R8" s="4" t="n"/>
@@ -43186,10 +43361,10 @@
       <c r="N9" s="4" t="n"/>
       <c r="O9" s="4" t="n"/>
       <c r="P9" s="4" t="n"/>
-      <c r="Q9" s="4" t="n">
+      <c r="Q9" s="4" t="n"/>
+      <c r="R9" s="4" t="n">
         <v>20.52</v>
       </c>
-      <c r="R9" s="4" t="n"/>
       <c r="S9" s="4" t="n"/>
       <c r="T9" s="4" t="n"/>
       <c r="U9" s="4" t="n"/>
@@ -43261,16 +43436,16 @@
       <c r="K10" s="4" t="n"/>
       <c r="L10" s="4" t="n"/>
       <c r="M10" s="4" t="n"/>
-      <c r="N10" s="4" t="n"/>
+      <c r="N10" s="4" t="n">
+        <v>23.5</v>
+      </c>
       <c r="O10" s="4" t="n"/>
       <c r="P10" s="4" t="n"/>
       <c r="Q10" s="4" t="n"/>
       <c r="R10" s="4" t="n"/>
-      <c r="S10" s="4" t="n">
+      <c r="S10" s="4" t="n"/>
+      <c r="T10" s="4" t="n">
         <v>23.4</v>
-      </c>
-      <c r="T10" s="4" t="n">
-        <v>23.5</v>
       </c>
       <c r="U10" s="4" t="n"/>
       <c r="V10" s="4" t="n"/>
@@ -43416,10 +43591,10 @@
       <c r="N12" s="4" t="n"/>
       <c r="O12" s="4" t="n"/>
       <c r="P12" s="4" t="n"/>
-      <c r="Q12" s="4" t="n">
+      <c r="Q12" s="4" t="n"/>
+      <c r="R12" s="4" t="n">
         <v>21.99</v>
       </c>
-      <c r="R12" s="4" t="n"/>
       <c r="S12" s="4" t="n"/>
       <c r="T12" s="4" t="n"/>
       <c r="U12" s="4" t="n"/>
@@ -43583,10 +43758,10 @@
       <c r="K14" s="4" t="n"/>
       <c r="L14" s="4" t="n"/>
       <c r="M14" s="4" t="n"/>
-      <c r="N14" s="4" t="n">
+      <c r="N14" s="4" t="n"/>
+      <c r="O14" s="4" t="n">
         <v>26.15</v>
       </c>
-      <c r="O14" s="4" t="n"/>
       <c r="P14" s="4" t="n"/>
       <c r="Q14" s="4" t="n"/>
       <c r="R14" s="4" t="n"/>
@@ -43663,7 +43838,9 @@
       </c>
       <c r="L15" s="4" t="n"/>
       <c r="M15" s="4" t="n"/>
-      <c r="N15" s="4" t="n"/>
+      <c r="N15" s="4" t="n">
+        <v>29.59</v>
+      </c>
       <c r="O15" s="4" t="n"/>
       <c r="P15" s="4" t="n"/>
       <c r="Q15" s="4" t="n"/>
@@ -43821,10 +43998,10 @@
       <c r="K17" s="4" t="n"/>
       <c r="L17" s="4" t="n"/>
       <c r="M17" s="4" t="n"/>
-      <c r="N17" s="4" t="n">
+      <c r="N17" s="4" t="n"/>
+      <c r="O17" s="4" t="n">
         <v>30.49</v>
       </c>
-      <c r="O17" s="4" t="n"/>
       <c r="P17" s="4" t="n"/>
       <c r="Q17" s="4" t="n"/>
       <c r="R17" s="4" t="n"/>
@@ -43900,10 +44077,10 @@
       <c r="N18" s="4" t="n"/>
       <c r="O18" s="4" t="n"/>
       <c r="P18" s="4" t="n"/>
-      <c r="Q18" s="4" t="n">
+      <c r="Q18" s="4" t="n"/>
+      <c r="R18" s="4" t="n">
         <v>24.59</v>
       </c>
-      <c r="R18" s="4" t="n"/>
       <c r="S18" s="4" t="n"/>
       <c r="T18" s="4" t="n"/>
       <c r="U18" s="4" t="n"/>
@@ -43979,15 +44156,15 @@
       <c r="M19" s="4" t="n">
         <v>32.5</v>
       </c>
-      <c r="N19" s="4" t="n"/>
+      <c r="N19" s="4" t="n">
+        <v>33.4</v>
+      </c>
       <c r="O19" s="4" t="n"/>
       <c r="P19" s="4" t="n"/>
       <c r="Q19" s="4" t="n"/>
       <c r="R19" s="4" t="n"/>
       <c r="S19" s="4" t="n"/>
-      <c r="T19" s="4" t="n">
-        <v>33.4</v>
-      </c>
+      <c r="T19" s="4" t="n"/>
       <c r="U19" s="4" t="n"/>
       <c r="V19" s="4" t="n"/>
       <c r="W19" s="4" t="n"/>
@@ -44053,15 +44230,15 @@
         <v>22.4</v>
       </c>
       <c r="M20" s="4" t="n"/>
-      <c r="N20" s="4" t="n"/>
+      <c r="N20" s="4" t="n">
+        <v>22.59</v>
+      </c>
       <c r="O20" s="4" t="n"/>
       <c r="P20" s="4" t="n"/>
       <c r="Q20" s="4" t="n"/>
       <c r="R20" s="4" t="n"/>
       <c r="S20" s="4" t="n"/>
-      <c r="T20" s="4" t="n">
-        <v>22.59</v>
-      </c>
+      <c r="T20" s="4" t="n"/>
       <c r="U20" s="4" t="n"/>
       <c r="V20" s="4" t="n"/>
       <c r="W20" s="4" t="n"/>
@@ -44071,7 +44248,7 @@
       <c r="AA20" s="4" t="n"/>
       <c r="AB20" s="4" t="n"/>
       <c r="AC20" s="4" t="n">
-        <v>22.85</v>
+        <v>22.8</v>
       </c>
       <c r="AD20" s="4" t="n"/>
       <c r="AE20" s="4" t="n"/>
@@ -44356,14 +44533,14 @@
       <c r="N24" s="4" t="n"/>
       <c r="O24" s="4" t="n"/>
       <c r="P24" s="4" t="n"/>
-      <c r="Q24" s="4" t="n">
+      <c r="Q24" s="4" t="n"/>
+      <c r="R24" s="4" t="n">
         <v>23.69</v>
       </c>
-      <c r="R24" s="4" t="n"/>
-      <c r="S24" s="4" t="n">
+      <c r="S24" s="4" t="n"/>
+      <c r="T24" s="4" t="n">
         <v>23.3</v>
       </c>
-      <c r="T24" s="4" t="n"/>
       <c r="U24" s="4" t="n"/>
       <c r="V24" s="4" t="n"/>
       <c r="W24" s="4" t="n"/>
@@ -44512,10 +44689,10 @@
       <c r="P26" s="4" t="n"/>
       <c r="Q26" s="4" t="n"/>
       <c r="R26" s="4" t="n"/>
-      <c r="S26" s="4" t="n">
+      <c r="S26" s="4" t="n"/>
+      <c r="T26" s="4" t="n">
         <v>18.99</v>
       </c>
-      <c r="T26" s="4" t="n"/>
       <c r="U26" s="4" t="n"/>
       <c r="V26" s="4" t="n"/>
       <c r="W26" s="4" t="n"/>
@@ -44587,15 +44764,15 @@
       <c r="K27" s="4" t="n"/>
       <c r="L27" s="4" t="n"/>
       <c r="M27" s="4" t="n"/>
-      <c r="N27" s="4" t="n"/>
+      <c r="N27" s="4" t="n">
+        <v>35.2</v>
+      </c>
       <c r="O27" s="4" t="n"/>
       <c r="P27" s="4" t="n"/>
       <c r="Q27" s="4" t="n"/>
       <c r="R27" s="4" t="n"/>
       <c r="S27" s="4" t="n"/>
-      <c r="T27" s="4" t="n">
-        <v>35.2</v>
-      </c>
+      <c r="T27" s="4" t="n"/>
       <c r="U27" s="4" t="n">
         <v>34.19</v>
       </c>
@@ -44670,10 +44847,10 @@
       <c r="P28" s="4" t="n"/>
       <c r="Q28" s="4" t="n"/>
       <c r="R28" s="4" t="n"/>
-      <c r="S28" s="4" t="n">
+      <c r="S28" s="4" t="n"/>
+      <c r="T28" s="4" t="n">
         <v>33.5</v>
       </c>
-      <c r="T28" s="4" t="n"/>
       <c r="U28" s="4" t="n"/>
       <c r="V28" s="4" t="n"/>
       <c r="W28" s="4" t="n"/>
@@ -44821,15 +44998,15 @@
       <c r="K30" s="4" t="n"/>
       <c r="L30" s="4" t="n"/>
       <c r="M30" s="4" t="n"/>
-      <c r="N30" s="4" t="n"/>
+      <c r="N30" s="4" t="n">
+        <v>23.19</v>
+      </c>
       <c r="O30" s="4" t="n"/>
       <c r="P30" s="4" t="n"/>
       <c r="Q30" s="4" t="n"/>
       <c r="R30" s="4" t="n"/>
       <c r="S30" s="4" t="n"/>
-      <c r="T30" s="4" t="n">
-        <v>23.19</v>
-      </c>
+      <c r="T30" s="4" t="n"/>
       <c r="U30" s="4" t="n"/>
       <c r="V30" s="4" t="n"/>
       <c r="W30" s="4" t="n"/>
@@ -44891,15 +45068,15 @@
       <c r="K31" s="4" t="n"/>
       <c r="L31" s="4" t="n"/>
       <c r="M31" s="4" t="n"/>
-      <c r="N31" s="4" t="n"/>
+      <c r="N31" s="4" t="n">
+        <v>19.19</v>
+      </c>
       <c r="O31" s="4" t="n"/>
       <c r="P31" s="4" t="n"/>
       <c r="Q31" s="4" t="n"/>
       <c r="R31" s="4" t="n"/>
       <c r="S31" s="4" t="n"/>
-      <c r="T31" s="4" t="n">
-        <v>19.19</v>
-      </c>
+      <c r="T31" s="4" t="n"/>
       <c r="U31" s="4" t="n"/>
       <c r="V31" s="4" t="n"/>
       <c r="W31" s="4" t="n"/>
@@ -44969,15 +45146,15 @@
       <c r="K32" s="4" t="n"/>
       <c r="L32" s="4" t="n"/>
       <c r="M32" s="4" t="n"/>
-      <c r="N32" s="4" t="n"/>
+      <c r="N32" s="4" t="n">
+        <v>29.4</v>
+      </c>
       <c r="O32" s="4" t="n"/>
       <c r="P32" s="4" t="n"/>
       <c r="Q32" s="4" t="n"/>
       <c r="R32" s="4" t="n"/>
       <c r="S32" s="4" t="n"/>
-      <c r="T32" s="4" t="n">
-        <v>29.4</v>
-      </c>
+      <c r="T32" s="4" t="n"/>
       <c r="U32" s="4" t="n"/>
       <c r="V32" s="4" t="n"/>
       <c r="W32" s="4" t="n"/>
@@ -44988,7 +45165,7 @@
       <c r="AB32" s="4" t="n"/>
       <c r="AC32" s="4" t="n"/>
       <c r="AD32" s="4" t="n">
-        <v>29.5</v>
+        <v>29.3</v>
       </c>
       <c r="AE32" s="4" t="n"/>
       <c r="AF32" s="4" t="n"/>
@@ -45053,15 +45230,15 @@
       <c r="K33" s="4" t="n"/>
       <c r="L33" s="4" t="n"/>
       <c r="M33" s="4" t="n"/>
-      <c r="N33" s="4" t="n"/>
+      <c r="N33" s="4" t="n">
+        <v>19.99</v>
+      </c>
       <c r="O33" s="4" t="n"/>
       <c r="P33" s="4" t="n"/>
       <c r="Q33" s="4" t="n"/>
       <c r="R33" s="4" t="n"/>
       <c r="S33" s="4" t="n"/>
-      <c r="T33" s="4" t="n">
-        <v>19.99</v>
-      </c>
+      <c r="T33" s="4" t="n"/>
       <c r="U33" s="4" t="n"/>
       <c r="V33" s="4" t="n"/>
       <c r="W33" s="4" t="n"/>
@@ -45132,13 +45309,13 @@
       <c r="N34" s="4" t="n"/>
       <c r="O34" s="4" t="n"/>
       <c r="P34" s="4" t="n"/>
-      <c r="Q34" s="4" t="n">
+      <c r="Q34" s="4" t="n"/>
+      <c r="R34" s="4" t="n">
         <v>35.8</v>
       </c>
-      <c r="R34" s="4" t="n">
+      <c r="S34" s="4" t="n">
         <v>35.6</v>
       </c>
-      <c r="S34" s="4" t="n"/>
       <c r="T34" s="4" t="n"/>
       <c r="U34" s="4" t="n"/>
       <c r="V34" s="4" t="n">
@@ -45205,15 +45382,15 @@
       <c r="K35" s="4" t="n"/>
       <c r="L35" s="4" t="n"/>
       <c r="M35" s="4" t="n"/>
-      <c r="N35" s="4" t="n"/>
+      <c r="N35" s="4" t="n">
+        <v>23.7</v>
+      </c>
       <c r="O35" s="4" t="n"/>
       <c r="P35" s="4" t="n"/>
       <c r="Q35" s="4" t="n"/>
       <c r="R35" s="4" t="n"/>
       <c r="S35" s="4" t="n"/>
-      <c r="T35" s="4" t="n">
-        <v>23.7</v>
-      </c>
+      <c r="T35" s="4" t="n"/>
       <c r="U35" s="4" t="n"/>
       <c r="V35" s="4" t="n"/>
       <c r="W35" s="4" t="n"/>
@@ -45369,7 +45546,9 @@
         <v>22.69</v>
       </c>
       <c r="M37" s="4" t="n"/>
-      <c r="N37" s="4" t="n"/>
+      <c r="N37" s="4" t="n">
+        <v>23.29</v>
+      </c>
       <c r="O37" s="4" t="n"/>
       <c r="P37" s="4" t="n"/>
       <c r="Q37" s="4" t="n"/>
@@ -45518,10 +45697,10 @@
       <c r="P39" s="4" t="n"/>
       <c r="Q39" s="4" t="n"/>
       <c r="R39" s="4" t="n"/>
-      <c r="S39" s="4" t="n">
+      <c r="S39" s="4" t="n"/>
+      <c r="T39" s="4" t="n">
         <v>29.9</v>
       </c>
-      <c r="T39" s="4" t="n"/>
       <c r="U39" s="4" t="n"/>
       <c r="V39" s="4" t="n"/>
       <c r="W39" s="4" t="n"/>
@@ -45599,15 +45778,15 @@
       <c r="M40" s="4" t="n">
         <v>34.3</v>
       </c>
-      <c r="N40" s="4" t="n"/>
+      <c r="N40" s="4" t="n">
+        <v>35.2</v>
+      </c>
       <c r="O40" s="4" t="n"/>
       <c r="P40" s="4" t="n"/>
       <c r="Q40" s="4" t="n"/>
       <c r="R40" s="4" t="n"/>
       <c r="S40" s="4" t="n"/>
-      <c r="T40" s="4" t="n">
-        <v>35.2</v>
-      </c>
+      <c r="T40" s="4" t="n"/>
       <c r="U40" s="4" t="n"/>
       <c r="V40" s="4" t="n"/>
       <c r="W40" s="4" t="n"/>
@@ -45757,15 +45936,15 @@
       <c r="K42" s="4" t="n"/>
       <c r="L42" s="4" t="n"/>
       <c r="M42" s="4" t="n"/>
-      <c r="N42" s="4" t="n"/>
+      <c r="N42" s="4" t="n">
+        <v>22.5</v>
+      </c>
       <c r="O42" s="4" t="n"/>
       <c r="P42" s="4" t="n"/>
       <c r="Q42" s="4" t="n"/>
       <c r="R42" s="4" t="n"/>
       <c r="S42" s="4" t="n"/>
-      <c r="T42" s="4" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="T42" s="4" t="n"/>
       <c r="U42" s="4" t="n">
         <v>23.3</v>
       </c>
@@ -45907,15 +46086,15 @@
       <c r="K44" s="4" t="n"/>
       <c r="L44" s="4" t="n"/>
       <c r="M44" s="4" t="n"/>
-      <c r="N44" s="4" t="n"/>
+      <c r="N44" s="4" t="n">
+        <v>22.5</v>
+      </c>
       <c r="O44" s="4" t="n"/>
       <c r="P44" s="4" t="n"/>
       <c r="Q44" s="4" t="n"/>
       <c r="R44" s="4" t="n"/>
       <c r="S44" s="4" t="n"/>
-      <c r="T44" s="4" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="T44" s="4" t="n"/>
       <c r="U44" s="4" t="n"/>
       <c r="V44" s="4" t="n"/>
       <c r="W44" s="4" t="n"/>
@@ -45991,10 +46170,10 @@
       <c r="M45" s="4" t="n">
         <v>39.19</v>
       </c>
-      <c r="N45" s="4" t="n">
+      <c r="N45" s="4" t="n"/>
+      <c r="O45" s="4" t="n">
         <v>39.79</v>
       </c>
-      <c r="O45" s="4" t="n"/>
       <c r="P45" s="4" t="n"/>
       <c r="Q45" s="4" t="n"/>
       <c r="R45" s="4" t="n"/>
@@ -46149,16 +46328,16 @@
       <c r="M47" s="4" t="n">
         <v>40.99</v>
       </c>
-      <c r="N47" s="4" t="n">
+      <c r="N47" s="4" t="n"/>
+      <c r="O47" s="4" t="n">
         <v>41.5</v>
       </c>
-      <c r="O47" s="4" t="n">
+      <c r="P47" s="4" t="n">
         <v>41.4</v>
       </c>
-      <c r="P47" s="4" t="n">
+      <c r="Q47" s="4" t="n">
         <v>41.3</v>
       </c>
-      <c r="Q47" s="4" t="n"/>
       <c r="R47" s="4" t="n"/>
       <c r="S47" s="4" t="n"/>
       <c r="T47" s="4" t="n"/>
@@ -46235,13 +46414,13 @@
       <c r="O48" s="4" t="n"/>
       <c r="P48" s="4" t="n"/>
       <c r="Q48" s="4" t="n"/>
-      <c r="R48" s="4" t="n">
+      <c r="R48" s="4" t="n"/>
+      <c r="S48" s="4" t="n">
         <v>25.79</v>
       </c>
-      <c r="S48" s="4" t="n">
+      <c r="T48" s="4" t="n">
         <v>25.2</v>
       </c>
-      <c r="T48" s="4" t="n"/>
       <c r="U48" s="4" t="n"/>
       <c r="V48" s="4" t="n"/>
       <c r="W48" s="4" t="n"/>
@@ -46311,15 +46490,15 @@
       </c>
       <c r="L49" s="4" t="n"/>
       <c r="M49" s="4" t="n"/>
-      <c r="N49" s="4" t="n"/>
+      <c r="N49" s="4" t="n">
+        <v>30.79</v>
+      </c>
       <c r="O49" s="4" t="n"/>
       <c r="P49" s="4" t="n"/>
       <c r="Q49" s="4" t="n"/>
       <c r="R49" s="4" t="n"/>
       <c r="S49" s="4" t="n"/>
-      <c r="T49" s="4" t="n">
-        <v>30.79</v>
-      </c>
+      <c r="T49" s="4" t="n"/>
       <c r="U49" s="4" t="n"/>
       <c r="V49" s="4" t="n"/>
       <c r="W49" s="4" t="n"/>
@@ -46383,15 +46562,15 @@
       <c r="K50" s="4" t="n"/>
       <c r="L50" s="4" t="n"/>
       <c r="M50" s="4" t="n"/>
-      <c r="N50" s="4" t="n"/>
+      <c r="N50" s="4" t="n">
+        <v>26.67</v>
+      </c>
       <c r="O50" s="4" t="n"/>
       <c r="P50" s="4" t="n"/>
       <c r="Q50" s="4" t="n"/>
       <c r="R50" s="4" t="n"/>
       <c r="S50" s="4" t="n"/>
-      <c r="T50" s="4" t="n">
-        <v>26.67</v>
-      </c>
+      <c r="T50" s="4" t="n"/>
       <c r="U50" s="4" t="n"/>
       <c r="V50" s="4" t="n"/>
       <c r="W50" s="4" t="n"/>
@@ -46455,15 +46634,15 @@
       <c r="K51" s="4" t="n"/>
       <c r="L51" s="4" t="n"/>
       <c r="M51" s="4" t="n"/>
-      <c r="N51" s="4" t="n"/>
+      <c r="N51" s="4" t="n">
+        <v>24.5</v>
+      </c>
       <c r="O51" s="4" t="n"/>
       <c r="P51" s="4" t="n"/>
       <c r="Q51" s="4" t="n"/>
       <c r="R51" s="4" t="n"/>
       <c r="S51" s="4" t="n"/>
-      <c r="T51" s="4" t="n">
-        <v>24.5</v>
-      </c>
+      <c r="T51" s="4" t="n"/>
       <c r="U51" s="4" t="n"/>
       <c r="V51" s="4" t="n"/>
       <c r="W51" s="4" t="n"/>
@@ -46537,19 +46716,19 @@
       <c r="K52" s="4" t="n"/>
       <c r="L52" s="4" t="n"/>
       <c r="M52" s="4" t="n"/>
-      <c r="N52" s="4" t="n">
+      <c r="N52" s="4" t="n"/>
+      <c r="O52" s="4" t="n">
         <v>32.6</v>
       </c>
-      <c r="O52" s="4" t="n">
+      <c r="P52" s="4" t="n">
         <v>32.4</v>
       </c>
-      <c r="P52" s="4" t="n">
+      <c r="Q52" s="4" t="n">
         <v>32.3</v>
       </c>
-      <c r="Q52" s="4" t="n">
+      <c r="R52" s="4" t="n">
         <v>34.1</v>
       </c>
-      <c r="R52" s="4" t="n"/>
       <c r="S52" s="4" t="n"/>
       <c r="T52" s="4" t="n"/>
       <c r="U52" s="4" t="n"/>
@@ -46771,15 +46950,15 @@
       <c r="K55" s="4" t="n"/>
       <c r="L55" s="4" t="n"/>
       <c r="M55" s="4" t="n"/>
-      <c r="N55" s="4" t="n"/>
+      <c r="N55" s="4" t="n">
+        <v>32.99</v>
+      </c>
       <c r="O55" s="4" t="n"/>
       <c r="P55" s="4" t="n"/>
       <c r="Q55" s="4" t="n"/>
       <c r="R55" s="4" t="n"/>
       <c r="S55" s="4" t="n"/>
-      <c r="T55" s="4" t="n">
-        <v>32.99</v>
-      </c>
+      <c r="T55" s="4" t="n"/>
       <c r="U55" s="4" t="n"/>
       <c r="V55" s="4" t="n"/>
       <c r="W55" s="4" t="n"/>
@@ -46925,14 +47104,14 @@
         <v>35</v>
       </c>
       <c r="M57" s="4" t="n"/>
-      <c r="N57" s="4" t="n">
+      <c r="N57" s="4" t="n"/>
+      <c r="O57" s="4" t="n">
         <v>36.4</v>
       </c>
-      <c r="O57" s="4" t="n"/>
-      <c r="P57" s="4" t="n">
+      <c r="P57" s="4" t="n"/>
+      <c r="Q57" s="4" t="n">
         <v>36.19</v>
       </c>
-      <c r="Q57" s="4" t="n"/>
       <c r="R57" s="4" t="n"/>
       <c r="S57" s="4" t="n"/>
       <c r="T57" s="4" t="n"/>
@@ -47010,10 +47189,10 @@
       <c r="N58" s="4" t="n"/>
       <c r="O58" s="4" t="n"/>
       <c r="P58" s="4" t="n"/>
-      <c r="Q58" s="4" t="n">
+      <c r="Q58" s="4" t="n"/>
+      <c r="R58" s="4" t="n">
         <v>26.8</v>
       </c>
-      <c r="R58" s="4" t="n"/>
       <c r="S58" s="4" t="n"/>
       <c r="T58" s="4" t="n"/>
       <c r="U58" s="4" t="n"/>
@@ -47083,15 +47262,15 @@
       <c r="K59" s="4" t="n"/>
       <c r="L59" s="4" t="n"/>
       <c r="M59" s="4" t="n"/>
-      <c r="N59" s="4" t="n"/>
+      <c r="N59" s="4" t="n">
+        <v>21.35</v>
+      </c>
       <c r="O59" s="4" t="n"/>
       <c r="P59" s="4" t="n"/>
       <c r="Q59" s="4" t="n"/>
       <c r="R59" s="4" t="n"/>
       <c r="S59" s="4" t="n"/>
-      <c r="T59" s="4" t="n">
-        <v>21.35</v>
-      </c>
+      <c r="T59" s="4" t="n"/>
       <c r="U59" s="4" t="n"/>
       <c r="V59" s="4" t="n"/>
       <c r="W59" s="4" t="n"/>
@@ -47243,15 +47422,15 @@
       <c r="K61" s="4" t="n"/>
       <c r="L61" s="4" t="n"/>
       <c r="M61" s="4" t="n"/>
-      <c r="N61" s="4" t="n"/>
+      <c r="N61" s="4" t="n">
+        <v>21.89</v>
+      </c>
       <c r="O61" s="4" t="n"/>
       <c r="P61" s="4" t="n"/>
       <c r="Q61" s="4" t="n"/>
       <c r="R61" s="4" t="n"/>
       <c r="S61" s="4" t="n"/>
-      <c r="T61" s="4" t="n">
-        <v>21.89</v>
-      </c>
+      <c r="T61" s="4" t="n"/>
       <c r="U61" s="4" t="n"/>
       <c r="V61" s="4" t="n"/>
       <c r="W61" s="4" t="n"/>
@@ -47319,18 +47498,18 @@
       <c r="M62" s="4" t="n">
         <v>31.1</v>
       </c>
-      <c r="N62" s="4" t="n"/>
+      <c r="N62" s="4" t="n">
+        <v>31.9</v>
+      </c>
       <c r="O62" s="4" t="n"/>
       <c r="P62" s="4" t="n"/>
-      <c r="Q62" s="4" t="n">
+      <c r="Q62" s="4" t="n"/>
+      <c r="R62" s="4" t="n">
         <v>32.45</v>
       </c>
-      <c r="R62" s="4" t="n"/>
-      <c r="S62" s="4" t="n">
+      <c r="S62" s="4" t="n"/>
+      <c r="T62" s="4" t="n">
         <v>31.29</v>
-      </c>
-      <c r="T62" s="4" t="n">
-        <v>31.9</v>
       </c>
       <c r="U62" s="4" t="n"/>
       <c r="V62" s="4" t="n"/>
@@ -47402,18 +47581,18 @@
       <c r="L63" s="4" t="n"/>
       <c r="M63" s="4" t="n"/>
       <c r="N63" s="4" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="O63" s="4" t="n">
         <v>24.39</v>
       </c>
-      <c r="O63" s="4" t="n"/>
-      <c r="P63" s="4" t="n">
+      <c r="P63" s="4" t="n"/>
+      <c r="Q63" s="4" t="n">
         <v>23.95</v>
       </c>
-      <c r="Q63" s="4" t="n"/>
       <c r="R63" s="4" t="n"/>
       <c r="S63" s="4" t="n"/>
-      <c r="T63" s="4" t="n">
-        <v>24.6</v>
-      </c>
+      <c r="T63" s="4" t="n"/>
       <c r="U63" s="4" t="n"/>
       <c r="V63" s="4" t="n">
         <v>25.39</v>
@@ -47485,7 +47664,9 @@
         <v>33.6</v>
       </c>
       <c r="M64" s="4" t="n"/>
-      <c r="N64" s="4" t="n"/>
+      <c r="N64" s="4" t="n">
+        <v>24.6</v>
+      </c>
       <c r="O64" s="4" t="n"/>
       <c r="P64" s="4" t="n"/>
       <c r="Q64" s="4" t="n"/>
@@ -47708,14 +47889,14 @@
       <c r="N67" s="4" t="n"/>
       <c r="O67" s="4" t="n"/>
       <c r="P67" s="4" t="n"/>
-      <c r="Q67" s="4" t="n">
+      <c r="Q67" s="4" t="n"/>
+      <c r="R67" s="4" t="n">
         <v>18.9</v>
       </c>
-      <c r="R67" s="4" t="n"/>
-      <c r="S67" s="4" t="n">
+      <c r="S67" s="4" t="n"/>
+      <c r="T67" s="4" t="n">
         <v>18.49</v>
       </c>
-      <c r="T67" s="4" t="n"/>
       <c r="U67" s="4" t="n"/>
       <c r="V67" s="4" t="n"/>
       <c r="W67" s="4" t="n"/>
@@ -47790,10 +47971,10 @@
       <c r="P68" s="4" t="n"/>
       <c r="Q68" s="4" t="n"/>
       <c r="R68" s="4" t="n"/>
-      <c r="S68" s="4" t="n">
+      <c r="S68" s="4" t="n"/>
+      <c r="T68" s="4" t="n">
         <v>28.1</v>
       </c>
-      <c r="T68" s="4" t="n"/>
       <c r="U68" s="4" t="n"/>
       <c r="V68" s="4" t="n"/>
       <c r="W68" s="4" t="n"/>
@@ -47863,7 +48044,9 @@
       <c r="M69" s="4" t="n">
         <v>33.8</v>
       </c>
-      <c r="N69" s="4" t="n"/>
+      <c r="N69" s="4" t="n">
+        <v>35.36</v>
+      </c>
       <c r="O69" s="4" t="n"/>
       <c r="P69" s="4" t="n"/>
       <c r="Q69" s="4" t="n"/>
@@ -48075,15 +48258,15 @@
       <c r="K72" s="4" t="n"/>
       <c r="L72" s="4" t="n"/>
       <c r="M72" s="4" t="n"/>
-      <c r="N72" s="4" t="n"/>
+      <c r="N72" s="4" t="n">
+        <v>26.15</v>
+      </c>
       <c r="O72" s="4" t="n"/>
       <c r="P72" s="4" t="n"/>
       <c r="Q72" s="4" t="n"/>
       <c r="R72" s="4" t="n"/>
       <c r="S72" s="4" t="n"/>
-      <c r="T72" s="4" t="n">
-        <v>26.15</v>
-      </c>
+      <c r="T72" s="4" t="n"/>
       <c r="U72" s="4" t="n"/>
       <c r="V72" s="4" t="n"/>
       <c r="W72" s="4" t="n"/>
@@ -48155,15 +48338,15 @@
       <c r="K73" s="4" t="n"/>
       <c r="L73" s="4" t="n"/>
       <c r="M73" s="4" t="n"/>
-      <c r="N73" s="4" t="n"/>
+      <c r="N73" s="4" t="n">
+        <v>19.4</v>
+      </c>
       <c r="O73" s="4" t="n"/>
       <c r="P73" s="4" t="n"/>
       <c r="Q73" s="4" t="n"/>
       <c r="R73" s="4" t="n"/>
       <c r="S73" s="4" t="n"/>
-      <c r="T73" s="4" t="n">
-        <v>19.4</v>
-      </c>
+      <c r="T73" s="4" t="n"/>
       <c r="U73" s="4" t="n"/>
       <c r="V73" s="4" t="n"/>
       <c r="W73" s="4" t="n"/>
@@ -48242,10 +48425,10 @@
       <c r="P74" s="4" t="n"/>
       <c r="Q74" s="4" t="n"/>
       <c r="R74" s="4" t="n"/>
-      <c r="S74" s="4" t="n">
+      <c r="S74" s="4" t="n"/>
+      <c r="T74" s="4" t="n">
         <v>34.39</v>
       </c>
-      <c r="T74" s="4" t="n"/>
       <c r="U74" s="4" t="n">
         <v>35.6</v>
       </c>
@@ -48316,10 +48499,10 @@
       <c r="P75" s="4" t="n"/>
       <c r="Q75" s="4" t="n"/>
       <c r="R75" s="4" t="n"/>
-      <c r="S75" s="4" t="n">
+      <c r="S75" s="4" t="n"/>
+      <c r="T75" s="4" t="n">
         <v>27.1</v>
       </c>
-      <c r="T75" s="4" t="n"/>
       <c r="U75" s="4" t="n"/>
       <c r="V75" s="4" t="n"/>
       <c r="W75" s="4" t="n"/>
@@ -48391,15 +48574,15 @@
       <c r="K76" s="4" t="n"/>
       <c r="L76" s="4" t="n"/>
       <c r="M76" s="4" t="n"/>
-      <c r="N76" s="4" t="n"/>
+      <c r="N76" s="4" t="n">
+        <v>16.99</v>
+      </c>
       <c r="O76" s="4" t="n"/>
       <c r="P76" s="4" t="n"/>
       <c r="Q76" s="4" t="n"/>
       <c r="R76" s="4" t="n"/>
       <c r="S76" s="4" t="n"/>
-      <c r="T76" s="4" t="n">
-        <v>16.99</v>
-      </c>
+      <c r="T76" s="4" t="n"/>
       <c r="U76" s="4" t="n"/>
       <c r="V76" s="4" t="n"/>
       <c r="W76" s="4" t="n"/>
@@ -48556,10 +48739,10 @@
         <v>31.6</v>
       </c>
       <c r="N78" s="4" t="n"/>
-      <c r="O78" s="4" t="n">
+      <c r="O78" s="4" t="n"/>
+      <c r="P78" s="4" t="n">
         <v>32.2</v>
       </c>
-      <c r="P78" s="4" t="n"/>
       <c r="Q78" s="4" t="n"/>
       <c r="R78" s="4" t="n"/>
       <c r="S78" s="4" t="n"/>
@@ -48636,10 +48819,10 @@
         <v>23.2</v>
       </c>
       <c r="N79" s="4" t="n"/>
-      <c r="O79" s="4" t="n">
+      <c r="O79" s="4" t="n"/>
+      <c r="P79" s="4" t="n">
         <v>23.3</v>
       </c>
-      <c r="P79" s="4" t="n"/>
       <c r="Q79" s="4" t="n"/>
       <c r="R79" s="4" t="n"/>
       <c r="S79" s="4" t="n"/>
@@ -48717,10 +48900,10 @@
       <c r="M80" s="4" t="n"/>
       <c r="N80" s="4" t="n"/>
       <c r="O80" s="4" t="n"/>
-      <c r="P80" s="4" t="n">
+      <c r="P80" s="4" t="n"/>
+      <c r="Q80" s="4" t="n">
         <v>29.49</v>
       </c>
-      <c r="Q80" s="4" t="n"/>
       <c r="R80" s="4" t="n"/>
       <c r="S80" s="4" t="n"/>
       <c r="T80" s="4" t="n"/>
@@ -48796,10 +48979,10 @@
         <v>63.8</v>
       </c>
       <c r="N81" s="4" t="n"/>
-      <c r="O81" s="4" t="n">
+      <c r="O81" s="4" t="n"/>
+      <c r="P81" s="4" t="n">
         <v>65.39</v>
       </c>
-      <c r="P81" s="4" t="n"/>
       <c r="Q81" s="4" t="n"/>
       <c r="R81" s="4" t="n"/>
       <c r="S81" s="4" t="n"/>
@@ -48876,10 +49059,10 @@
       <c r="N82" s="4" t="n"/>
       <c r="O82" s="4" t="n"/>
       <c r="P82" s="4" t="n"/>
-      <c r="Q82" s="4" t="n">
+      <c r="Q82" s="4" t="n"/>
+      <c r="R82" s="4" t="n">
         <v>57.7</v>
       </c>
-      <c r="R82" s="4" t="n"/>
       <c r="S82" s="4" t="n"/>
       <c r="T82" s="4" t="n"/>
       <c r="U82" s="4" t="n"/>
@@ -49034,10 +49217,10 @@
       <c r="P84" s="4" t="n"/>
       <c r="Q84" s="4" t="n"/>
       <c r="R84" s="4" t="n"/>
-      <c r="S84" s="4" t="n">
+      <c r="S84" s="4" t="n"/>
+      <c r="T84" s="4" t="n">
         <v>27.6</v>
       </c>
-      <c r="T84" s="4" t="n"/>
       <c r="U84" s="4" t="n"/>
       <c r="V84" s="4" t="n"/>
       <c r="W84" s="4" t="n"/>
@@ -49253,37 +49436,37 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>9x8★6</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>玻璃★1</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>玻璃★2</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>玻璃★3</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>速尾★4</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>速尾★5</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>速尾★6</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>9x8★6</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
@@ -49519,17 +49702,17 @@
       <c r="K2" s="4" t="n"/>
       <c r="L2" s="4" t="n"/>
       <c r="M2" s="4" t="n"/>
-      <c r="N2" s="4" t="n"/>
+      <c r="N2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O2" s="4" t="n"/>
       <c r="P2" s="4" t="n"/>
       <c r="Q2" s="4" t="n"/>
       <c r="R2" s="4" t="n"/>
       <c r="S2" s="4" t="n"/>
-      <c r="T2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T2" s="4" t="n"/>
       <c r="U2" s="4" t="n"/>
       <c r="V2" s="4" t="n"/>
       <c r="W2" s="4" t="n"/>
@@ -49628,12 +49811,12 @@
       <c r="P3" s="4" t="n"/>
       <c r="Q3" s="4" t="n"/>
       <c r="R3" s="4" t="n"/>
-      <c r="S3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T3" s="4" t="n"/>
+      <c r="S3" s="4" t="n"/>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U3" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -49748,12 +49931,12 @@
       <c r="P4" s="4" t="n"/>
       <c r="Q4" s="4" t="n"/>
       <c r="R4" s="4" t="n"/>
-      <c r="S4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T4" s="4" t="n"/>
+      <c r="S4" s="4" t="n"/>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U4" s="4" t="n"/>
       <c r="V4" s="4" t="n"/>
       <c r="W4" s="4" t="n"/>
@@ -49847,20 +50030,20 @@
       <c r="K5" s="4" t="n"/>
       <c r="L5" s="4" t="n"/>
       <c r="M5" s="4" t="n"/>
-      <c r="N5" s="4" t="n"/>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O5" s="4" t="n"/>
       <c r="P5" s="4" t="n"/>
-      <c r="Q5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R5" s="4" t="n"/>
-      <c r="S5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q5" s="4" t="n"/>
+      <c r="R5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S5" s="4" t="n"/>
       <c r="T5" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -49955,17 +50138,17 @@
       <c r="K6" s="4" t="n"/>
       <c r="L6" s="4" t="n"/>
       <c r="M6" s="4" t="n"/>
-      <c r="N6" s="4" t="n"/>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O6" s="4" t="n"/>
       <c r="P6" s="4" t="n"/>
       <c r="Q6" s="4" t="n"/>
       <c r="R6" s="4" t="n"/>
       <c r="S6" s="4" t="n"/>
-      <c r="T6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T6" s="4" t="n"/>
       <c r="U6" s="4" t="n"/>
       <c r="V6" s="4" t="n"/>
       <c r="W6" s="4" t="n"/>
@@ -50059,17 +50242,17 @@
       </c>
       <c r="L7" s="4" t="n"/>
       <c r="M7" s="4" t="n"/>
-      <c r="N7" s="4" t="n"/>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O7" s="4" t="n"/>
       <c r="P7" s="4" t="n"/>
       <c r="Q7" s="4" t="n"/>
       <c r="R7" s="4" t="n"/>
       <c r="S7" s="4" t="n"/>
-      <c r="T7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T7" s="4" t="n"/>
       <c r="U7" s="4" t="n"/>
       <c r="V7" s="4" t="n"/>
       <c r="W7" s="4" t="n"/>
@@ -50191,21 +50374,21 @@
         </is>
       </c>
       <c r="M8" s="4" t="n"/>
-      <c r="N8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O8" s="4" t="n"/>
+      <c r="N8" s="4" t="n"/>
+      <c r="O8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P8" s="4" t="n"/>
       <c r="Q8" s="4" t="n"/>
       <c r="R8" s="4" t="n"/>
-      <c r="S8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T8" s="4" t="n"/>
+      <c r="S8" s="4" t="n"/>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U8" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -50295,21 +50478,21 @@
       <c r="K9" s="4" t="n"/>
       <c r="L9" s="4" t="n"/>
       <c r="M9" s="4" t="n"/>
-      <c r="N9" s="4" t="n"/>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O9" s="4" t="n"/>
       <c r="P9" s="4" t="n"/>
-      <c r="Q9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R9" s="4" t="n"/>
+      <c r="Q9" s="4" t="n"/>
+      <c r="R9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="S9" s="4" t="n"/>
-      <c r="T9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T9" s="4" t="n"/>
       <c r="U9" s="4" t="n"/>
       <c r="V9" s="4" t="n"/>
       <c r="W9" s="4" t="n"/>
@@ -50415,16 +50598,16 @@
       <c r="K10" s="4" t="n"/>
       <c r="L10" s="4" t="n"/>
       <c r="M10" s="4" t="n"/>
-      <c r="N10" s="4" t="n"/>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O10" s="4" t="n"/>
       <c r="P10" s="4" t="n"/>
       <c r="Q10" s="4" t="n"/>
       <c r="R10" s="4" t="n"/>
-      <c r="S10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="S10" s="4" t="n"/>
       <c r="T10" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -50631,20 +50814,20 @@
       <c r="K12" s="4" t="n"/>
       <c r="L12" s="4" t="n"/>
       <c r="M12" s="4" t="n"/>
-      <c r="N12" s="4" t="n"/>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O12" s="4" t="n"/>
       <c r="P12" s="4" t="n"/>
-      <c r="Q12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R12" s="4" t="n"/>
-      <c r="S12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q12" s="4" t="n"/>
+      <c r="R12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S12" s="4" t="n"/>
       <c r="T12" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -50760,12 +50943,12 @@
       <c r="P13" s="4" t="n"/>
       <c r="Q13" s="4" t="n"/>
       <c r="R13" s="4" t="n"/>
-      <c r="S13" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T13" s="4" t="n"/>
+      <c r="S13" s="4" t="n"/>
+      <c r="T13" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U13" s="4" t="n"/>
       <c r="V13" s="4" t="inlineStr">
         <is>
@@ -50880,16 +51063,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="O14" s="4" t="n"/>
+      <c r="O14" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P14" s="4" t="n"/>
       <c r="Q14" s="4" t="n"/>
       <c r="R14" s="4" t="n"/>
       <c r="S14" s="4" t="n"/>
-      <c r="T14" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T14" s="4" t="n"/>
       <c r="U14" s="4" t="n"/>
       <c r="V14" s="4" t="n"/>
       <c r="W14" s="4" t="n"/>
@@ -50991,16 +51174,16 @@
       </c>
       <c r="L15" s="4" t="n"/>
       <c r="M15" s="4" t="n"/>
-      <c r="N15" s="4" t="n"/>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O15" s="4" t="n"/>
       <c r="P15" s="4" t="n"/>
       <c r="Q15" s="4" t="n"/>
       <c r="R15" s="4" t="n"/>
-      <c r="S15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="S15" s="4" t="n"/>
       <c r="T15" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -51232,16 +51415,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="O17" s="4" t="n"/>
+      <c r="O17" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P17" s="4" t="n"/>
       <c r="Q17" s="4" t="n"/>
       <c r="R17" s="4" t="n"/>
       <c r="S17" s="4" t="n"/>
-      <c r="T17" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T17" s="4" t="n"/>
       <c r="U17" s="4" t="n"/>
       <c r="V17" s="4" t="n"/>
       <c r="W17" s="4" t="n"/>
@@ -51342,18 +51525,18 @@
       <c r="N18" s="4" t="n"/>
       <c r="O18" s="4" t="n"/>
       <c r="P18" s="4" t="n"/>
-      <c r="Q18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R18" s="4" t="n"/>
-      <c r="S18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T18" s="4" t="n"/>
+      <c r="Q18" s="4" t="n"/>
+      <c r="R18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S18" s="4" t="n"/>
+      <c r="T18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U18" s="4" t="n"/>
       <c r="V18" s="4" t="n"/>
       <c r="W18" s="4" t="n"/>
@@ -51467,16 +51650,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N19" s="4" t="n"/>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O19" s="4" t="n"/>
       <c r="P19" s="4" t="n"/>
       <c r="Q19" s="4" t="n"/>
       <c r="R19" s="4" t="n"/>
-      <c r="S19" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="S19" s="4" t="n"/>
       <c r="T19" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -51575,17 +51758,17 @@
         </is>
       </c>
       <c r="M20" s="4" t="n"/>
-      <c r="N20" s="4" t="n"/>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O20" s="4" t="n"/>
       <c r="P20" s="4" t="n"/>
       <c r="Q20" s="4" t="n"/>
       <c r="R20" s="4" t="n"/>
       <c r="S20" s="4" t="n"/>
-      <c r="T20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T20" s="4" t="n"/>
       <c r="U20" s="4" t="n"/>
       <c r="V20" s="4" t="n"/>
       <c r="W20" s="4" t="n"/>
@@ -51688,12 +51871,12 @@
       <c r="P21" s="4" t="n"/>
       <c r="Q21" s="4" t="n"/>
       <c r="R21" s="4" t="n"/>
-      <c r="S21" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T21" s="4" t="n"/>
+      <c r="S21" s="4" t="n"/>
+      <c r="T21" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U21" s="4" t="n"/>
       <c r="V21" s="4" t="inlineStr">
         <is>
@@ -51900,12 +52083,12 @@
       <c r="P23" s="4" t="n"/>
       <c r="Q23" s="4" t="n"/>
       <c r="R23" s="4" t="n"/>
-      <c r="S23" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T23" s="4" t="n"/>
+      <c r="S23" s="4" t="n"/>
+      <c r="T23" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U23" s="4" t="n"/>
       <c r="V23" s="4" t="inlineStr">
         <is>
@@ -51991,20 +52174,20 @@
       <c r="K24" s="4" t="n"/>
       <c r="L24" s="4" t="n"/>
       <c r="M24" s="4" t="n"/>
-      <c r="N24" s="4" t="n"/>
+      <c r="N24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O24" s="4" t="n"/>
       <c r="P24" s="4" t="n"/>
-      <c r="Q24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R24" s="4" t="n"/>
-      <c r="S24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q24" s="4" t="n"/>
+      <c r="R24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S24" s="4" t="n"/>
       <c r="T24" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -52108,12 +52291,12 @@
       <c r="P25" s="4" t="n"/>
       <c r="Q25" s="4" t="n"/>
       <c r="R25" s="4" t="n"/>
-      <c r="S25" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T25" s="4" t="n"/>
+      <c r="S25" s="4" t="n"/>
+      <c r="T25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U25" s="4" t="n"/>
       <c r="V25" s="4" t="n"/>
       <c r="W25" s="4" t="n"/>
@@ -52207,16 +52390,16 @@
       <c r="K26" s="4" t="n"/>
       <c r="L26" s="4" t="n"/>
       <c r="M26" s="4" t="n"/>
-      <c r="N26" s="4" t="n"/>
+      <c r="N26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O26" s="4" t="n"/>
       <c r="P26" s="4" t="n"/>
       <c r="Q26" s="4" t="n"/>
       <c r="R26" s="4" t="n"/>
-      <c r="S26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="S26" s="4" t="n"/>
       <c r="T26" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -52327,17 +52510,17 @@
       <c r="K27" s="4" t="n"/>
       <c r="L27" s="4" t="n"/>
       <c r="M27" s="4" t="n"/>
-      <c r="N27" s="4" t="n"/>
+      <c r="N27" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O27" s="4" t="n"/>
       <c r="P27" s="4" t="n"/>
       <c r="Q27" s="4" t="n"/>
       <c r="R27" s="4" t="n"/>
       <c r="S27" s="4" t="n"/>
-      <c r="T27" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T27" s="4" t="n"/>
       <c r="U27" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -52444,12 +52627,12 @@
       <c r="P28" s="4" t="n"/>
       <c r="Q28" s="4" t="n"/>
       <c r="R28" s="4" t="n"/>
-      <c r="S28" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T28" s="4" t="n"/>
+      <c r="S28" s="4" t="n"/>
+      <c r="T28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U28" s="4" t="n"/>
       <c r="V28" s="4" t="n"/>
       <c r="W28" s="4" t="n"/>
@@ -52647,17 +52830,17 @@
       <c r="K30" s="4" t="n"/>
       <c r="L30" s="4" t="n"/>
       <c r="M30" s="4" t="n"/>
-      <c r="N30" s="4" t="n"/>
+      <c r="N30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O30" s="4" t="n"/>
       <c r="P30" s="4" t="n"/>
       <c r="Q30" s="4" t="n"/>
       <c r="R30" s="4" t="n"/>
       <c r="S30" s="4" t="n"/>
-      <c r="T30" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T30" s="4" t="n"/>
       <c r="U30" s="4" t="n"/>
       <c r="V30" s="4" t="n"/>
       <c r="W30" s="4" t="n"/>
@@ -52751,17 +52934,17 @@
       <c r="K31" s="4" t="n"/>
       <c r="L31" s="4" t="n"/>
       <c r="M31" s="4" t="n"/>
-      <c r="N31" s="4" t="n"/>
+      <c r="N31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O31" s="4" t="n"/>
       <c r="P31" s="4" t="n"/>
       <c r="Q31" s="4" t="n"/>
       <c r="R31" s="4" t="n"/>
       <c r="S31" s="4" t="n"/>
-      <c r="T31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T31" s="4" t="n"/>
       <c r="U31" s="4" t="n"/>
       <c r="V31" s="4" t="n"/>
       <c r="W31" s="4" t="n"/>
@@ -52867,17 +53050,17 @@
       <c r="K32" s="4" t="n"/>
       <c r="L32" s="4" t="n"/>
       <c r="M32" s="4" t="n"/>
-      <c r="N32" s="4" t="n"/>
+      <c r="N32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O32" s="4" t="n"/>
       <c r="P32" s="4" t="n"/>
       <c r="Q32" s="4" t="n"/>
       <c r="R32" s="4" t="n"/>
       <c r="S32" s="4" t="n"/>
-      <c r="T32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T32" s="4" t="n"/>
       <c r="U32" s="4" t="n"/>
       <c r="V32" s="4" t="n"/>
       <c r="W32" s="4" t="n"/>
@@ -52983,17 +53166,17 @@
       <c r="K33" s="4" t="n"/>
       <c r="L33" s="4" t="n"/>
       <c r="M33" s="4" t="n"/>
-      <c r="N33" s="4" t="n"/>
+      <c r="N33" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O33" s="4" t="n"/>
       <c r="P33" s="4" t="n"/>
       <c r="Q33" s="4" t="n"/>
       <c r="R33" s="4" t="n"/>
       <c r="S33" s="4" t="n"/>
-      <c r="T33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T33" s="4" t="n"/>
       <c r="U33" s="4" t="n"/>
       <c r="V33" s="4" t="n"/>
       <c r="W33" s="4" t="n"/>
@@ -53098,11 +53281,7 @@
       <c r="N34" s="4" t="n"/>
       <c r="O34" s="4" t="n"/>
       <c r="P34" s="4" t="n"/>
-      <c r="Q34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q34" s="4" t="n"/>
       <c r="R34" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -53113,7 +53292,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="T34" s="4" t="n"/>
+      <c r="T34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U34" s="4" t="n"/>
       <c r="V34" s="4" t="inlineStr">
         <is>
@@ -53207,17 +53390,17 @@
       <c r="K35" s="4" t="n"/>
       <c r="L35" s="4" t="n"/>
       <c r="M35" s="4" t="n"/>
-      <c r="N35" s="4" t="n"/>
+      <c r="N35" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O35" s="4" t="n"/>
       <c r="P35" s="4" t="n"/>
       <c r="Q35" s="4" t="n"/>
       <c r="R35" s="4" t="n"/>
       <c r="S35" s="4" t="n"/>
-      <c r="T35" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T35" s="4" t="n"/>
       <c r="U35" s="4" t="n"/>
       <c r="V35" s="4" t="n"/>
       <c r="W35" s="4" t="n"/>
@@ -53327,16 +53510,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N36" s="4" t="n"/>
+      <c r="N36" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O36" s="4" t="n"/>
       <c r="P36" s="4" t="n"/>
       <c r="Q36" s="4" t="n"/>
       <c r="R36" s="4" t="n"/>
-      <c r="S36" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="S36" s="4" t="n"/>
       <c r="T36" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -53447,17 +53630,17 @@
         </is>
       </c>
       <c r="M37" s="4" t="n"/>
-      <c r="N37" s="4" t="n"/>
+      <c r="N37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O37" s="4" t="n"/>
       <c r="P37" s="4" t="n"/>
       <c r="Q37" s="4" t="n"/>
       <c r="R37" s="4" t="n"/>
       <c r="S37" s="4" t="n"/>
-      <c r="T37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T37" s="4" t="n"/>
       <c r="U37" s="4" t="n"/>
       <c r="V37" s="4" t="n"/>
       <c r="W37" s="4" t="n"/>
@@ -53551,16 +53734,16 @@
       <c r="K38" s="4" t="n"/>
       <c r="L38" s="4" t="n"/>
       <c r="M38" s="4" t="n"/>
-      <c r="N38" s="4" t="n"/>
+      <c r="N38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O38" s="4" t="n"/>
       <c r="P38" s="4" t="n"/>
       <c r="Q38" s="4" t="n"/>
       <c r="R38" s="4" t="n"/>
-      <c r="S38" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="S38" s="4" t="n"/>
       <c r="T38" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -53672,12 +53855,12 @@
       <c r="P39" s="4" t="n"/>
       <c r="Q39" s="4" t="n"/>
       <c r="R39" s="4" t="n"/>
-      <c r="S39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T39" s="4" t="n"/>
+      <c r="S39" s="4" t="n"/>
+      <c r="T39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U39" s="4" t="n"/>
       <c r="V39" s="4" t="n"/>
       <c r="W39" s="4" t="n"/>
@@ -53807,17 +53990,17 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N40" s="4" t="n"/>
+      <c r="N40" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O40" s="4" t="n"/>
       <c r="P40" s="4" t="n"/>
       <c r="Q40" s="4" t="n"/>
       <c r="R40" s="4" t="n"/>
       <c r="S40" s="4" t="n"/>
-      <c r="T40" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T40" s="4" t="n"/>
       <c r="U40" s="4" t="n"/>
       <c r="V40" s="4" t="n"/>
       <c r="W40" s="4" t="n"/>
@@ -54015,17 +54198,17 @@
       <c r="K42" s="4" t="n"/>
       <c r="L42" s="4" t="n"/>
       <c r="M42" s="4" t="n"/>
-      <c r="N42" s="4" t="n"/>
+      <c r="N42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O42" s="4" t="n"/>
       <c r="P42" s="4" t="n"/>
       <c r="Q42" s="4" t="n"/>
       <c r="R42" s="4" t="n"/>
       <c r="S42" s="4" t="n"/>
-      <c r="T42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T42" s="4" t="n"/>
       <c r="U42" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -54223,17 +54406,17 @@
       <c r="K44" s="4" t="n"/>
       <c r="L44" s="4" t="n"/>
       <c r="M44" s="4" t="n"/>
-      <c r="N44" s="4" t="n"/>
+      <c r="N44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O44" s="4" t="n"/>
       <c r="P44" s="4" t="n"/>
       <c r="Q44" s="4" t="n"/>
       <c r="R44" s="4" t="n"/>
       <c r="S44" s="4" t="n"/>
-      <c r="T44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T44" s="4" t="n"/>
       <c r="U44" s="4" t="n"/>
       <c r="V44" s="4" t="n"/>
       <c r="W44" s="4" t="n"/>
@@ -54348,16 +54531,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="O45" s="4" t="n"/>
+      <c r="O45" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="P45" s="4" t="n"/>
       <c r="Q45" s="4" t="n"/>
       <c r="R45" s="4" t="n"/>
       <c r="S45" s="4" t="n"/>
-      <c r="T45" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T45" s="4" t="n"/>
       <c r="U45" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -54471,17 +54654,17 @@
         </is>
       </c>
       <c r="M46" s="4" t="n"/>
-      <c r="N46" s="4" t="n"/>
+      <c r="N46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O46" s="4" t="n"/>
       <c r="P46" s="4" t="n"/>
       <c r="Q46" s="4" t="n"/>
       <c r="R46" s="4" t="n"/>
       <c r="S46" s="4" t="n"/>
-      <c r="T46" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T46" s="4" t="n"/>
       <c r="U46" s="4" t="n"/>
       <c r="V46" s="4" t="n"/>
       <c r="W46" s="4" t="n"/>
@@ -54594,14 +54777,14 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="Q47" s="4" t="n"/>
+      <c r="Q47" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="R47" s="4" t="n"/>
       <c r="S47" s="4" t="n"/>
-      <c r="T47" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T47" s="4" t="n"/>
       <c r="U47" s="4" t="n"/>
       <c r="V47" s="4" t="n"/>
       <c r="W47" s="4" t="n"/>
@@ -54707,15 +54890,15 @@
       <c r="K48" s="4" t="n"/>
       <c r="L48" s="4" t="n"/>
       <c r="M48" s="4" t="n"/>
-      <c r="N48" s="4" t="n"/>
+      <c r="N48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O48" s="4" t="n"/>
       <c r="P48" s="4" t="n"/>
       <c r="Q48" s="4" t="n"/>
-      <c r="R48" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="R48" s="4" t="n"/>
       <c r="S48" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -54823,17 +55006,17 @@
       </c>
       <c r="L49" s="4" t="n"/>
       <c r="M49" s="4" t="n"/>
-      <c r="N49" s="4" t="n"/>
+      <c r="N49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O49" s="4" t="n"/>
       <c r="P49" s="4" t="n"/>
       <c r="Q49" s="4" t="n"/>
       <c r="R49" s="4" t="n"/>
       <c r="S49" s="4" t="n"/>
-      <c r="T49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T49" s="4" t="n"/>
       <c r="U49" s="4" t="n"/>
       <c r="V49" s="4" t="n"/>
       <c r="W49" s="4" t="n"/>
@@ -54923,17 +55106,17 @@
       <c r="K50" s="4" t="n"/>
       <c r="L50" s="4" t="n"/>
       <c r="M50" s="4" t="n"/>
-      <c r="N50" s="4" t="n"/>
+      <c r="N50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O50" s="4" t="n"/>
       <c r="P50" s="4" t="n"/>
       <c r="Q50" s="4" t="n"/>
       <c r="R50" s="4" t="n"/>
       <c r="S50" s="4" t="n"/>
-      <c r="T50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T50" s="4" t="n"/>
       <c r="U50" s="4" t="n"/>
       <c r="V50" s="4" t="n"/>
       <c r="W50" s="4" t="n"/>
@@ -55027,17 +55210,17 @@
       <c r="K51" s="4" t="n"/>
       <c r="L51" s="4" t="n"/>
       <c r="M51" s="4" t="n"/>
-      <c r="N51" s="4" t="n"/>
+      <c r="N51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O51" s="4" t="n"/>
       <c r="P51" s="4" t="n"/>
       <c r="Q51" s="4" t="n"/>
       <c r="R51" s="4" t="n"/>
       <c r="S51" s="4" t="n"/>
-      <c r="T51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T51" s="4" t="n"/>
       <c r="U51" s="4" t="n"/>
       <c r="V51" s="4" t="n"/>
       <c r="W51" s="4" t="n"/>
@@ -55151,11 +55334,7 @@
       <c r="K52" s="4" t="n"/>
       <c r="L52" s="4" t="n"/>
       <c r="M52" s="4" t="n"/>
-      <c r="N52" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N52" s="4" t="n"/>
       <c r="O52" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -55171,7 +55350,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="R52" s="4" t="n"/>
+      <c r="R52" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="S52" s="4" t="n"/>
       <c r="T52" s="4" t="n"/>
       <c r="U52" s="4" t="n"/>
@@ -55276,12 +55459,12 @@
       <c r="P53" s="4" t="n"/>
       <c r="Q53" s="4" t="n"/>
       <c r="R53" s="4" t="n"/>
-      <c r="S53" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T53" s="4" t="n"/>
+      <c r="S53" s="4" t="n"/>
+      <c r="T53" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U53" s="4" t="n"/>
       <c r="V53" s="4" t="inlineStr">
         <is>
@@ -55402,7 +55585,11 @@
       <c r="Z54" s="4" t="n"/>
       <c r="AA54" s="4" t="n"/>
       <c r="AB54" s="4" t="n"/>
-      <c r="AC54" s="4" t="n"/>
+      <c r="AC54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD54" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -55413,7 +55600,11 @@
       <c r="AG54" s="4" t="n"/>
       <c r="AH54" s="4" t="n"/>
       <c r="AI54" s="4" t="n"/>
-      <c r="AJ54" s="4" t="n"/>
+      <c r="AJ54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AK54" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -55445,7 +55636,11 @@
       <c r="AW54" s="4" t="n"/>
       <c r="AX54" s="4" t="n"/>
       <c r="AY54" s="4" t="n"/>
-      <c r="AZ54" s="4" t="n"/>
+      <c r="AZ54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BA54" s="4" t="n"/>
       <c r="BB54" s="4" t="inlineStr">
         <is>
@@ -55479,17 +55674,17 @@
       <c r="K55" s="4" t="n"/>
       <c r="L55" s="4" t="n"/>
       <c r="M55" s="4" t="n"/>
-      <c r="N55" s="4" t="n"/>
+      <c r="N55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O55" s="4" t="n"/>
       <c r="P55" s="4" t="n"/>
       <c r="Q55" s="4" t="n"/>
       <c r="R55" s="4" t="n"/>
       <c r="S55" s="4" t="n"/>
-      <c r="T55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T55" s="4" t="n"/>
       <c r="U55" s="4" t="n"/>
       <c r="V55" s="4" t="n"/>
       <c r="W55" s="4" t="n"/>
@@ -55591,17 +55786,17 @@
       <c r="K56" s="4" t="n"/>
       <c r="L56" s="4" t="n"/>
       <c r="M56" s="4" t="n"/>
-      <c r="N56" s="4" t="n"/>
+      <c r="N56" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O56" s="4" t="n"/>
       <c r="P56" s="4" t="n"/>
       <c r="Q56" s="4" t="n"/>
       <c r="R56" s="4" t="n"/>
       <c r="S56" s="4" t="n"/>
-      <c r="T56" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T56" s="4" t="n"/>
       <c r="U56" s="4" t="n"/>
       <c r="V56" s="4" t="inlineStr">
         <is>
@@ -55699,25 +55894,25 @@
         </is>
       </c>
       <c r="M57" s="4" t="n"/>
-      <c r="N57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="O57" s="4" t="n"/>
-      <c r="P57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q57" s="4" t="n"/>
+      <c r="N57" s="4" t="n"/>
+      <c r="O57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P57" s="4" t="n"/>
+      <c r="Q57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="R57" s="4" t="n"/>
-      <c r="S57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T57" s="4" t="n"/>
+      <c r="S57" s="4" t="n"/>
+      <c r="T57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U57" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -55822,12 +56017,12 @@
       <c r="N58" s="4" t="n"/>
       <c r="O58" s="4" t="n"/>
       <c r="P58" s="4" t="n"/>
-      <c r="Q58" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R58" s="4" t="n"/>
+      <c r="Q58" s="4" t="n"/>
+      <c r="R58" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="S58" s="4" t="n"/>
       <c r="T58" s="4" t="n"/>
       <c r="U58" s="4" t="n"/>
@@ -55923,17 +56118,17 @@
       <c r="K59" s="4" t="n"/>
       <c r="L59" s="4" t="n"/>
       <c r="M59" s="4" t="n"/>
-      <c r="N59" s="4" t="n"/>
+      <c r="N59" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O59" s="4" t="n"/>
       <c r="P59" s="4" t="n"/>
       <c r="Q59" s="4" t="n"/>
       <c r="R59" s="4" t="n"/>
       <c r="S59" s="4" t="n"/>
-      <c r="T59" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T59" s="4" t="n"/>
       <c r="U59" s="4" t="n"/>
       <c r="V59" s="4" t="n"/>
       <c r="W59" s="4" t="n"/>
@@ -56143,17 +56338,17 @@
       <c r="K61" s="4" t="n"/>
       <c r="L61" s="4" t="n"/>
       <c r="M61" s="4" t="n"/>
-      <c r="N61" s="4" t="n"/>
+      <c r="N61" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O61" s="4" t="n"/>
       <c r="P61" s="4" t="n"/>
       <c r="Q61" s="4" t="n"/>
       <c r="R61" s="4" t="n"/>
       <c r="S61" s="4" t="n"/>
-      <c r="T61" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T61" s="4" t="n"/>
       <c r="U61" s="4" t="n"/>
       <c r="V61" s="4" t="n"/>
       <c r="W61" s="4" t="n"/>
@@ -56271,20 +56466,20 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N62" s="4" t="n"/>
+      <c r="N62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O62" s="4" t="n"/>
       <c r="P62" s="4" t="n"/>
-      <c r="Q62" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R62" s="4" t="n"/>
-      <c r="S62" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q62" s="4" t="n"/>
+      <c r="R62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S62" s="4" t="n"/>
       <c r="T62" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -56396,20 +56591,20 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="O63" s="4" t="n"/>
-      <c r="P63" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q63" s="4" t="n"/>
+      <c r="O63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P63" s="4" t="n"/>
+      <c r="Q63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="R63" s="4" t="n"/>
       <c r="S63" s="4" t="n"/>
-      <c r="T63" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T63" s="4" t="n"/>
       <c r="U63" s="4" t="n"/>
       <c r="V63" s="4" t="inlineStr">
         <is>
@@ -56519,17 +56714,21 @@
         </is>
       </c>
       <c r="M64" s="4" t="n"/>
-      <c r="N64" s="4" t="n"/>
+      <c r="N64" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O64" s="4" t="n"/>
       <c r="P64" s="4" t="n"/>
       <c r="Q64" s="4" t="n"/>
       <c r="R64" s="4" t="n"/>
-      <c r="S64" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T64" s="4" t="n"/>
+      <c r="S64" s="4" t="n"/>
+      <c r="T64" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U64" s="4" t="n"/>
       <c r="V64" s="4" t="n"/>
       <c r="W64" s="4" t="n"/>
@@ -56628,12 +56827,12 @@
       <c r="P65" s="4" t="n"/>
       <c r="Q65" s="4" t="n"/>
       <c r="R65" s="4" t="n"/>
-      <c r="S65" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T65" s="4" t="n"/>
+      <c r="S65" s="4" t="n"/>
+      <c r="T65" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U65" s="4" t="n"/>
       <c r="V65" s="4" t="inlineStr">
         <is>
@@ -56819,20 +57018,20 @@
       <c r="K67" s="4" t="n"/>
       <c r="L67" s="4" t="n"/>
       <c r="M67" s="4" t="n"/>
-      <c r="N67" s="4" t="n"/>
+      <c r="N67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O67" s="4" t="n"/>
       <c r="P67" s="4" t="n"/>
-      <c r="Q67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R67" s="4" t="n"/>
-      <c r="S67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q67" s="4" t="n"/>
+      <c r="R67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S67" s="4" t="n"/>
       <c r="T67" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -56960,12 +57159,12 @@
       <c r="P68" s="4" t="n"/>
       <c r="Q68" s="4" t="n"/>
       <c r="R68" s="4" t="n"/>
-      <c r="S68" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T68" s="4" t="n"/>
+      <c r="S68" s="4" t="n"/>
+      <c r="T68" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U68" s="4" t="n"/>
       <c r="V68" s="4" t="n"/>
       <c r="W68" s="4" t="n"/>
@@ -57055,17 +57254,17 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N69" s="4" t="n"/>
+      <c r="N69" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O69" s="4" t="n"/>
       <c r="P69" s="4" t="n"/>
       <c r="Q69" s="4" t="n"/>
       <c r="R69" s="4" t="n"/>
       <c r="S69" s="4" t="n"/>
-      <c r="T69" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T69" s="4" t="n"/>
       <c r="U69" s="4" t="n"/>
       <c r="V69" s="4" t="n"/>
       <c r="W69" s="4" t="n"/>
@@ -57147,17 +57346,17 @@
       <c r="K70" s="4" t="n"/>
       <c r="L70" s="4" t="n"/>
       <c r="M70" s="4" t="n"/>
-      <c r="N70" s="4" t="n"/>
+      <c r="N70" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O70" s="4" t="n"/>
       <c r="P70" s="4" t="n"/>
       <c r="Q70" s="4" t="n"/>
       <c r="R70" s="4" t="n"/>
       <c r="S70" s="4" t="n"/>
-      <c r="T70" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T70" s="4" t="n"/>
       <c r="U70" s="4" t="n"/>
       <c r="V70" s="4" t="n"/>
       <c r="W70" s="4" t="n"/>
@@ -57347,16 +57546,16 @@
       <c r="K72" s="4" t="n"/>
       <c r="L72" s="4" t="n"/>
       <c r="M72" s="4" t="n"/>
-      <c r="N72" s="4" t="n"/>
+      <c r="N72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O72" s="4" t="n"/>
       <c r="P72" s="4" t="n"/>
       <c r="Q72" s="4" t="n"/>
       <c r="R72" s="4" t="n"/>
-      <c r="S72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="S72" s="4" t="n"/>
       <c r="T72" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -57459,17 +57658,17 @@
       <c r="K73" s="4" t="n"/>
       <c r="L73" s="4" t="n"/>
       <c r="M73" s="4" t="n"/>
-      <c r="N73" s="4" t="n"/>
+      <c r="N73" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O73" s="4" t="n"/>
       <c r="P73" s="4" t="n"/>
       <c r="Q73" s="4" t="n"/>
       <c r="R73" s="4" t="n"/>
       <c r="S73" s="4" t="n"/>
-      <c r="T73" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T73" s="4" t="n"/>
       <c r="U73" s="4" t="n"/>
       <c r="V73" s="4" t="n"/>
       <c r="W73" s="4" t="n"/>
@@ -57583,16 +57782,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N74" s="4" t="n"/>
+      <c r="N74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O74" s="4" t="n"/>
       <c r="P74" s="4" t="n"/>
       <c r="Q74" s="4" t="n"/>
       <c r="R74" s="4" t="n"/>
-      <c r="S74" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="S74" s="4" t="n"/>
       <c r="T74" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -57692,12 +57891,12 @@
       <c r="P75" s="4" t="n"/>
       <c r="Q75" s="4" t="n"/>
       <c r="R75" s="4" t="n"/>
-      <c r="S75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T75" s="4" t="n"/>
+      <c r="S75" s="4" t="n"/>
+      <c r="T75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U75" s="4" t="n"/>
       <c r="V75" s="4" t="n"/>
       <c r="W75" s="4" t="n"/>
@@ -57799,17 +57998,17 @@
       <c r="K76" s="4" t="n"/>
       <c r="L76" s="4" t="n"/>
       <c r="M76" s="4" t="n"/>
-      <c r="N76" s="4" t="n"/>
+      <c r="N76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O76" s="4" t="n"/>
       <c r="P76" s="4" t="n"/>
       <c r="Q76" s="4" t="n"/>
       <c r="R76" s="4" t="n"/>
       <c r="S76" s="4" t="n"/>
-      <c r="T76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T76" s="4" t="n"/>
       <c r="U76" s="4" t="n"/>
       <c r="V76" s="4" t="n"/>
       <c r="W76" s="4" t="n"/>
@@ -58028,12 +58227,12 @@
         </is>
       </c>
       <c r="N78" s="4" t="n"/>
-      <c r="O78" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P78" s="4" t="n"/>
+      <c r="O78" s="4" t="n"/>
+      <c r="P78" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="Q78" s="4" t="n"/>
       <c r="R78" s="4" t="n"/>
       <c r="S78" s="4" t="n"/>
@@ -58136,12 +58335,12 @@
         </is>
       </c>
       <c r="N79" s="4" t="n"/>
-      <c r="O79" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P79" s="4" t="n"/>
+      <c r="O79" s="4" t="n"/>
+      <c r="P79" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="Q79" s="4" t="n"/>
       <c r="R79" s="4" t="n"/>
       <c r="S79" s="4" t="n"/>
@@ -58249,12 +58448,12 @@
       <c r="M80" s="4" t="n"/>
       <c r="N80" s="4" t="n"/>
       <c r="O80" s="4" t="n"/>
-      <c r="P80" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q80" s="4" t="n"/>
+      <c r="P80" s="4" t="n"/>
+      <c r="Q80" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="R80" s="4" t="n"/>
       <c r="S80" s="4" t="n"/>
       <c r="T80" s="4" t="n"/>
@@ -58356,12 +58555,12 @@
         </is>
       </c>
       <c r="N81" s="4" t="n"/>
-      <c r="O81" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P81" s="4" t="n"/>
+      <c r="O81" s="4" t="n"/>
+      <c r="P81" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="Q81" s="4" t="n"/>
       <c r="R81" s="4" t="n"/>
       <c r="S81" s="4" t="n"/>
@@ -58450,12 +58649,12 @@
       <c r="N82" s="4" t="n"/>
       <c r="O82" s="4" t="n"/>
       <c r="P82" s="4" t="n"/>
-      <c r="Q82" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R82" s="4" t="n"/>
+      <c r="Q82" s="4" t="n"/>
+      <c r="R82" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="S82" s="4" t="n"/>
       <c r="T82" s="4" t="n"/>
       <c r="U82" s="4" t="n"/>
@@ -58636,12 +58835,12 @@
       <c r="P84" s="4" t="n"/>
       <c r="Q84" s="4" t="n"/>
       <c r="R84" s="4" t="n"/>
-      <c r="S84" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="T84" s="4" t="n"/>
+      <c r="S84" s="4" t="n"/>
+      <c r="T84" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U84" s="4" t="n"/>
       <c r="V84" s="4" t="n"/>
       <c r="W84" s="4" t="n"/>
@@ -58767,17 +58966,17 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>9x8</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>玻璃</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>速尾</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>9x8</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -58843,13 +59042,13 @@
         </is>
       </c>
       <c r="C2" s="4" t="n"/>
-      <c r="D2" s="4" t="n"/>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E2" s="4" t="n"/>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="F2" s="4" t="n"/>
       <c r="G2" s="4" t="n"/>
       <c r="H2" s="4" t="inlineStr">
         <is>
@@ -58885,17 +59084,17 @@
         </is>
       </c>
       <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D3" s="4" t="n"/>
       <c r="E3" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F3" s="4" t="n"/>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G3" s="4" t="n"/>
       <c r="H3" s="4" t="n"/>
       <c r="I3" s="4" t="n"/>
@@ -58916,12 +59115,12 @@
       </c>
       <c r="C4" s="4" t="n"/>
       <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G4" s="4" t="n"/>
       <c r="H4" s="4" t="n"/>
       <c r="I4" s="4" t="n"/>
@@ -58941,12 +59140,12 @@
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="n"/>
       <c r="F5" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -58987,13 +59186,13 @@
         </is>
       </c>
       <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E6" s="4" t="n"/>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="F6" s="4" t="n"/>
       <c r="G6" s="4" t="n"/>
       <c r="H6" s="4" t="inlineStr">
         <is>
@@ -59030,12 +59229,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="n"/>
       <c r="G7" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -59064,12 +59263,12 @@
       </c>
       <c r="C8" s="4" t="n"/>
       <c r="D8" s="4" t="n"/>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="n"/>
+      <c r="E8" s="4" t="n"/>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G8" s="4" t="n"/>
       <c r="H8" s="4" t="n"/>
       <c r="I8" s="4" t="n"/>
@@ -59089,13 +59288,13 @@
         </is>
       </c>
       <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E9" s="4" t="n"/>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="F9" s="4" t="n"/>
       <c r="G9" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -59135,13 +59334,13 @@
         </is>
       </c>
       <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n"/>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E10" s="4" t="n"/>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="F10" s="4" t="n"/>
       <c r="G10" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -59189,12 +59388,12 @@
         </is>
       </c>
       <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F11" s="4" t="n"/>
       <c r="G11" s="4" t="n"/>
       <c r="H11" s="4" t="n"/>
@@ -59215,12 +59414,12 @@
         </is>
       </c>
       <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="n"/>
       <c r="F12" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -59258,12 +59457,12 @@
       </c>
       <c r="C13" s="4" t="n"/>
       <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="n"/>
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G13" s="4" t="n"/>
       <c r="H13" s="4" t="n"/>
       <c r="I13" s="4" t="n"/>
@@ -59292,12 +59491,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E14" s="4" t="n"/>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="n"/>
       <c r="G14" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -59325,12 +59524,12 @@
         </is>
       </c>
       <c r="C15" s="4" t="n"/>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="n"/>
       <c r="F15" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -59363,12 +59562,12 @@
         </is>
       </c>
       <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="n"/>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F16" s="4" t="n"/>
       <c r="G16" s="4" t="n"/>
       <c r="H16" s="4" t="n"/>
@@ -59394,12 +59593,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E17" s="4" t="n"/>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="n"/>
       <c r="G17" s="4" t="n"/>
       <c r="H17" s="4" t="inlineStr">
         <is>
@@ -59440,12 +59639,12 @@
       </c>
       <c r="C18" s="4" t="n"/>
       <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="n"/>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -59477,12 +59676,12 @@
         </is>
       </c>
       <c r="C19" s="4" t="n"/>
-      <c r="D19" s="4" t="n"/>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="n"/>
       <c r="F19" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -59515,13 +59714,13 @@
         </is>
       </c>
       <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="n"/>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E20" s="4" t="n"/>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="F20" s="4" t="n"/>
       <c r="G20" s="4" t="n"/>
       <c r="H20" s="4" t="inlineStr">
         <is>
@@ -59558,12 +59757,12 @@
       </c>
       <c r="C21" s="4" t="n"/>
       <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="n"/>
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G21" s="4" t="n"/>
       <c r="H21" s="4" t="n"/>
       <c r="I21" s="4" t="n"/>
@@ -59613,17 +59812,17 @@
         </is>
       </c>
       <c r="C23" s="4" t="n"/>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D23" s="4" t="n"/>
       <c r="E23" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F23" s="4" t="n"/>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G23" s="4" t="n"/>
       <c r="H23" s="4" t="n"/>
       <c r="I23" s="4" t="n"/>
@@ -59643,12 +59842,12 @@
         </is>
       </c>
       <c r="C24" s="4" t="n"/>
-      <c r="D24" s="4" t="n"/>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="n"/>
       <c r="F24" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -59686,12 +59885,12 @@
       </c>
       <c r="C25" s="4" t="n"/>
       <c r="D25" s="4" t="n"/>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="n"/>
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -59723,13 +59922,13 @@
         </is>
       </c>
       <c r="C26" s="4" t="n"/>
-      <c r="D26" s="4" t="n"/>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E26" s="4" t="n"/>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="F26" s="4" t="n"/>
       <c r="G26" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -59796,12 +59995,12 @@
       </c>
       <c r="C28" s="4" t="n"/>
       <c r="D28" s="4" t="n"/>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -59833,12 +60032,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="n"/>
+      <c r="D29" s="4" t="n"/>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F29" s="4" t="n"/>
       <c r="G29" s="4" t="n"/>
       <c r="H29" s="4" t="n"/>
@@ -59863,13 +60062,13 @@
         </is>
       </c>
       <c r="C30" s="4" t="n"/>
-      <c r="D30" s="4" t="n"/>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E30" s="4" t="n"/>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="F30" s="4" t="n"/>
       <c r="G30" s="4" t="n"/>
       <c r="H30" s="4" t="inlineStr">
         <is>
@@ -59905,13 +60104,13 @@
         </is>
       </c>
       <c r="C31" s="4" t="n"/>
-      <c r="D31" s="4" t="n"/>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E31" s="4" t="n"/>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="F31" s="4" t="n"/>
       <c r="G31" s="4" t="n"/>
       <c r="H31" s="4" t="n"/>
       <c r="I31" s="4" t="n"/>
@@ -59943,13 +60142,13 @@
         </is>
       </c>
       <c r="C32" s="4" t="n"/>
-      <c r="D32" s="4" t="n"/>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E32" s="4" t="n"/>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="F32" s="4" t="n"/>
       <c r="G32" s="4" t="n"/>
       <c r="H32" s="4" t="n"/>
       <c r="I32" s="4" t="n"/>
@@ -59977,13 +60176,13 @@
         </is>
       </c>
       <c r="C33" s="4" t="n"/>
-      <c r="D33" s="4" t="n"/>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E33" s="4" t="n"/>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="F33" s="4" t="n"/>
       <c r="G33" s="4" t="n"/>
       <c r="H33" s="4" t="inlineStr">
         <is>
@@ -60020,12 +60219,12 @@
       </c>
       <c r="C34" s="4" t="n"/>
       <c r="D34" s="4" t="n"/>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="n"/>
+      <c r="E34" s="4" t="n"/>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G34" s="4" t="n"/>
       <c r="H34" s="4" t="n"/>
       <c r="I34" s="4" t="n"/>
@@ -60045,13 +60244,13 @@
         </is>
       </c>
       <c r="C35" s="4" t="n"/>
-      <c r="D35" s="4" t="n"/>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E35" s="4" t="n"/>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="F35" s="4" t="n"/>
       <c r="G35" s="4" t="n"/>
       <c r="H35" s="4" t="inlineStr">
         <is>
@@ -60083,12 +60282,12 @@
         </is>
       </c>
       <c r="C36" s="4" t="n"/>
-      <c r="D36" s="4" t="n"/>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="n"/>
       <c r="F36" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -60121,13 +60320,13 @@
         </is>
       </c>
       <c r="C37" s="4" t="n"/>
-      <c r="D37" s="4" t="n"/>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E37" s="4" t="n"/>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="F37" s="4" t="n"/>
       <c r="G37" s="4" t="n"/>
       <c r="H37" s="4" t="n"/>
       <c r="I37" s="4" t="n"/>
@@ -60155,12 +60354,12 @@
         </is>
       </c>
       <c r="C38" s="4" t="n"/>
-      <c r="D38" s="4" t="n"/>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="n"/>
       <c r="F38" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -60198,12 +60397,12 @@
       </c>
       <c r="C39" s="4" t="n"/>
       <c r="D39" s="4" t="n"/>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="n"/>
+      <c r="E39" s="4" t="n"/>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -60239,13 +60438,13 @@
         </is>
       </c>
       <c r="C40" s="4" t="n"/>
-      <c r="D40" s="4" t="n"/>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E40" s="4" t="n"/>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="F40" s="4" t="n"/>
       <c r="G40" s="4" t="n"/>
       <c r="H40" s="4" t="n"/>
       <c r="I40" s="4" t="n"/>
@@ -60277,12 +60476,12 @@
         </is>
       </c>
       <c r="C41" s="4" t="n"/>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="n"/>
+      <c r="D41" s="4" t="n"/>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F41" s="4" t="n"/>
       <c r="G41" s="4" t="n"/>
       <c r="H41" s="4" t="n"/>
@@ -60303,13 +60502,13 @@
         </is>
       </c>
       <c r="C42" s="4" t="n"/>
-      <c r="D42" s="4" t="n"/>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E42" s="4" t="n"/>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="F42" s="4" t="n"/>
       <c r="G42" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -60341,12 +60540,12 @@
         </is>
       </c>
       <c r="C43" s="4" t="n"/>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="n"/>
+      <c r="D43" s="4" t="n"/>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F43" s="4" t="n"/>
       <c r="G43" s="4" t="n"/>
       <c r="H43" s="4" t="n"/>
@@ -60371,13 +60570,13 @@
         </is>
       </c>
       <c r="C44" s="4" t="n"/>
-      <c r="D44" s="4" t="n"/>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E44" s="4" t="n"/>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="F44" s="4" t="n"/>
       <c r="G44" s="4" t="n"/>
       <c r="H44" s="4" t="inlineStr">
         <is>
@@ -60413,12 +60612,12 @@
         </is>
       </c>
       <c r="C45" s="4" t="n"/>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="n"/>
+      <c r="D45" s="4" t="n"/>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F45" s="4" t="n"/>
       <c r="G45" s="4" t="n"/>
       <c r="H45" s="4" t="n"/>
@@ -60444,12 +60643,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E46" s="4" t="n"/>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="n"/>
       <c r="G46" s="4" t="n"/>
       <c r="H46" s="4" t="n"/>
       <c r="I46" s="4" t="n"/>
@@ -60482,12 +60681,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E47" s="4" t="n"/>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="n"/>
       <c r="G47" s="4" t="n"/>
       <c r="H47" s="4" t="n"/>
       <c r="I47" s="4" t="n"/>
@@ -60516,12 +60715,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E48" s="4" t="n"/>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="n"/>
       <c r="G48" s="4" t="n"/>
       <c r="H48" s="4" t="n"/>
       <c r="I48" s="4" t="n"/>
@@ -60545,13 +60744,13 @@
         </is>
       </c>
       <c r="C49" s="4" t="n"/>
-      <c r="D49" s="4" t="n"/>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E49" s="4" t="n"/>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="F49" s="4" t="n"/>
       <c r="G49" s="4" t="n"/>
       <c r="H49" s="4" t="inlineStr">
         <is>
@@ -60583,13 +60782,13 @@
         </is>
       </c>
       <c r="C50" s="4" t="n"/>
-      <c r="D50" s="4" t="n"/>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E50" s="4" t="n"/>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="F50" s="4" t="n"/>
       <c r="G50" s="4" t="n"/>
       <c r="H50" s="4" t="inlineStr">
         <is>
@@ -60621,13 +60820,13 @@
         </is>
       </c>
       <c r="C51" s="4" t="n"/>
-      <c r="D51" s="4" t="n"/>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E51" s="4" t="n"/>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="F51" s="4" t="n"/>
       <c r="G51" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -60663,12 +60862,12 @@
         </is>
       </c>
       <c r="C52" s="4" t="n"/>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E52" s="4" t="n"/>
+      <c r="D52" s="4" t="n"/>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F52" s="4" t="n"/>
       <c r="G52" s="4" t="n"/>
       <c r="H52" s="4" t="n"/>
@@ -60698,12 +60897,12 @@
       </c>
       <c r="C53" s="4" t="n"/>
       <c r="D53" s="4" t="n"/>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="n"/>
+      <c r="E53" s="4" t="n"/>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G53" s="4" t="n"/>
       <c r="H53" s="4" t="n"/>
       <c r="I53" s="4" t="n"/>
@@ -60745,13 +60944,13 @@
         </is>
       </c>
       <c r="C55" s="4" t="n"/>
-      <c r="D55" s="4" t="n"/>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E55" s="4" t="n"/>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="F55" s="4" t="n"/>
       <c r="G55" s="4" t="n"/>
       <c r="H55" s="4" t="inlineStr">
         <is>
@@ -60783,13 +60982,13 @@
         </is>
       </c>
       <c r="C56" s="4" t="n"/>
-      <c r="D56" s="4" t="n"/>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E56" s="4" t="n"/>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="F56" s="4" t="n"/>
       <c r="G56" s="4" t="n"/>
       <c r="H56" s="4" t="n"/>
       <c r="I56" s="4" t="n"/>
@@ -60813,17 +61012,17 @@
         </is>
       </c>
       <c r="C57" s="4" t="n"/>
-      <c r="D57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D57" s="4" t="n"/>
       <c r="E57" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F57" s="4" t="n"/>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G57" s="4" t="n"/>
       <c r="H57" s="4" t="n"/>
       <c r="I57" s="4" t="n"/>
@@ -60865,13 +61064,13 @@
         </is>
       </c>
       <c r="C59" s="4" t="n"/>
-      <c r="D59" s="4" t="n"/>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E59" s="4" t="n"/>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="F59" s="4" t="n"/>
       <c r="G59" s="4" t="n"/>
       <c r="H59" s="4" t="inlineStr">
         <is>
@@ -60907,12 +61106,12 @@
         </is>
       </c>
       <c r="C60" s="4" t="n"/>
-      <c r="D60" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E60" s="4" t="n"/>
+      <c r="D60" s="4" t="n"/>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F60" s="4" t="n"/>
       <c r="G60" s="4" t="n"/>
       <c r="H60" s="4" t="n"/>
@@ -60937,13 +61136,13 @@
         </is>
       </c>
       <c r="C61" s="4" t="n"/>
-      <c r="D61" s="4" t="n"/>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E61" s="4" t="n"/>
-      <c r="F61" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="F61" s="4" t="n"/>
       <c r="G61" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -60987,12 +61186,12 @@
         </is>
       </c>
       <c r="C62" s="4" t="n"/>
-      <c r="D62" s="4" t="n"/>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="n"/>
       <c r="F62" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -61034,12 +61233,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E63" s="4" t="n"/>
-      <c r="F63" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="n"/>
       <c r="G63" s="4" t="n"/>
       <c r="H63" s="4" t="inlineStr">
         <is>
@@ -61068,12 +61267,12 @@
       </c>
       <c r="C64" s="4" t="n"/>
       <c r="D64" s="4" t="n"/>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F64" s="4" t="n"/>
+      <c r="E64" s="4" t="n"/>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G64" s="4" t="n"/>
       <c r="H64" s="4" t="n"/>
       <c r="I64" s="4" t="n"/>
@@ -61098,12 +61297,12 @@
       </c>
       <c r="C65" s="4" t="n"/>
       <c r="D65" s="4" t="n"/>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="n"/>
+      <c r="E65" s="4" t="n"/>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G65" s="4" t="n"/>
       <c r="H65" s="4" t="n"/>
       <c r="I65" s="4" t="n"/>
@@ -61145,12 +61344,12 @@
         </is>
       </c>
       <c r="C67" s="4" t="n"/>
-      <c r="D67" s="4" t="n"/>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="n"/>
       <c r="F67" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -61200,12 +61399,12 @@
       </c>
       <c r="C68" s="4" t="n"/>
       <c r="D68" s="4" t="n"/>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F68" s="4" t="n"/>
+      <c r="E68" s="4" t="n"/>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G68" s="4" t="n"/>
       <c r="H68" s="4" t="n"/>
       <c r="I68" s="4" t="n"/>
@@ -61234,12 +61433,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E69" s="4" t="n"/>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="n"/>
       <c r="G69" s="4" t="n"/>
       <c r="H69" s="4" t="n"/>
       <c r="I69" s="4" t="n"/>
@@ -61263,13 +61462,13 @@
         </is>
       </c>
       <c r="C70" s="4" t="n"/>
-      <c r="D70" s="4" t="n"/>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E70" s="4" t="n"/>
-      <c r="F70" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="F70" s="4" t="n"/>
       <c r="G70" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -61305,12 +61504,12 @@
         </is>
       </c>
       <c r="C71" s="4" t="n"/>
-      <c r="D71" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E71" s="4" t="n"/>
+      <c r="D71" s="4" t="n"/>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F71" s="4" t="n"/>
       <c r="G71" s="4" t="n"/>
       <c r="H71" s="4" t="n"/>
@@ -61331,12 +61530,12 @@
         </is>
       </c>
       <c r="C72" s="4" t="n"/>
-      <c r="D72" s="4" t="n"/>
-      <c r="E72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="n"/>
       <c r="F72" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -61381,13 +61580,13 @@
         </is>
       </c>
       <c r="C73" s="4" t="n"/>
-      <c r="D73" s="4" t="n"/>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E73" s="4" t="n"/>
-      <c r="F73" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="F73" s="4" t="n"/>
       <c r="G73" s="4" t="n"/>
       <c r="H73" s="4" t="n"/>
       <c r="I73" s="4" t="n"/>
@@ -61419,12 +61618,12 @@
         </is>
       </c>
       <c r="C74" s="4" t="n"/>
-      <c r="D74" s="4" t="n"/>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="n"/>
       <c r="F74" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -61454,12 +61653,12 @@
       </c>
       <c r="C75" s="4" t="n"/>
       <c r="D75" s="4" t="n"/>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="n"/>
+      <c r="E75" s="4" t="n"/>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -61495,13 +61694,13 @@
         </is>
       </c>
       <c r="C76" s="4" t="n"/>
-      <c r="D76" s="4" t="n"/>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E76" s="4" t="n"/>
-      <c r="F76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="F76" s="4" t="n"/>
       <c r="G76" s="4" t="n"/>
       <c r="H76" s="4" t="inlineStr">
         <is>
@@ -61533,12 +61732,12 @@
         </is>
       </c>
       <c r="C77" s="4" t="n"/>
-      <c r="D77" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E77" s="4" t="n"/>
+      <c r="D77" s="4" t="n"/>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F77" s="4" t="n"/>
       <c r="G77" s="4" t="n"/>
       <c r="H77" s="4" t="n"/>
@@ -61581,12 +61780,12 @@
         </is>
       </c>
       <c r="C79" s="4" t="n"/>
-      <c r="D79" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E79" s="4" t="n"/>
+      <c r="D79" s="4" t="n"/>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F79" s="4" t="n"/>
       <c r="G79" s="4" t="n"/>
       <c r="H79" s="4" t="n"/>
@@ -61607,12 +61806,12 @@
         </is>
       </c>
       <c r="C80" s="4" t="n"/>
-      <c r="D80" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E80" s="4" t="n"/>
+      <c r="D80" s="4" t="n"/>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F80" s="4" t="n"/>
       <c r="G80" s="4" t="n"/>
       <c r="H80" s="4" t="n"/>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -8215,7 +8215,9 @@
       <c r="J8" s="4" t="n"/>
       <c r="K8" s="4" t="n"/>
       <c r="L8" s="4" t="n"/>
-      <c r="M8" s="4" t="n"/>
+      <c r="M8" s="4" t="n">
+        <v>18.5</v>
+      </c>
       <c r="N8" s="4" t="n"/>
       <c r="O8" s="4" t="n"/>
       <c r="P8" s="4" t="n"/>
@@ -8384,7 +8386,9 @@
       <c r="G13" s="4" t="n"/>
       <c r="H13" s="4" t="n"/>
       <c r="I13" s="4" t="n"/>
-      <c r="J13" s="4" t="n"/>
+      <c r="J13" s="4" t="n">
+        <v>21.46</v>
+      </c>
       <c r="K13" s="4" t="n"/>
       <c r="L13" s="4" t="n"/>
       <c r="M13" s="4" t="n"/>
@@ -8412,7 +8416,9 @@
         <v>24.3</v>
       </c>
       <c r="E14" s="4" t="n"/>
-      <c r="F14" s="4" t="n"/>
+      <c r="F14" s="4" t="n">
+        <v>23.7</v>
+      </c>
       <c r="G14" s="4" t="n">
         <v>24.5</v>
       </c>
@@ -8618,7 +8624,9 @@
       </c>
       <c r="D20" s="4" t="n"/>
       <c r="E20" s="4" t="n"/>
-      <c r="F20" s="4" t="n"/>
+      <c r="F20" s="4" t="n">
+        <v>18.4</v>
+      </c>
       <c r="G20" s="4" t="n"/>
       <c r="H20" s="4" t="n"/>
       <c r="I20" s="4" t="n"/>
@@ -8658,7 +8666,9 @@
       <c r="E21" s="4" t="n">
         <v>25.9</v>
       </c>
-      <c r="F21" s="4" t="n"/>
+      <c r="F21" s="4" t="n">
+        <v>25.6</v>
+      </c>
       <c r="G21" s="4" t="n"/>
       <c r="H21" s="4" t="n"/>
       <c r="I21" s="4" t="n"/>
@@ -9981,7 +9991,9 @@
           <t>跳图</t>
         </is>
       </c>
-      <c r="D13" s="4" t="n"/>
+      <c r="D13" s="4" t="n">
+        <v>21.46</v>
+      </c>
       <c r="E13" s="4" t="n"/>
       <c r="F13" s="4" t="n"/>
       <c r="G13" s="4" t="n"/>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -22,8 +22,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'五区_理论'!$A$1:$BB$84</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'五区_高手'!$A$1:$CJ$84</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'五区_普通'!$A$1:$CJ$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'五区_高手'!$A$1:$CK$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'五区_普通'!$A$1:$CK$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'五区_自动'!$A$1:$U$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'四区_理论'!$A$1:$AR$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'四区_高手'!$A$1:$BJ$84</definedName>
@@ -10228,7 +10228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ84"/>
+  <dimension ref="A1:CK84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10319,6 +10319,7 @@
     <col width="7.5" customWidth="1" min="86" max="86"/>
     <col width="7.5" customWidth="1" min="87" max="87"/>
     <col width="7.5" customWidth="1" min="88" max="88"/>
+    <col width="7.5" customWidth="1" min="89" max="89"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10534,230 +10535,235 @@
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
+          <t>爱音★5</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
           <t>爱音★6</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>万达★6</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>狼崽★5</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>大超★1</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>大超★3</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>大超★6</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>速尾★4</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>速尾★6</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>300+★6</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>莫斯勒★1</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>莫斯勒★3</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>莫斯勒★6</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>肥龙★3</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>肥龙★6</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>sf90★6</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>sgt★6</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>火山★5</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>猫头鹰★6</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>秋王★6</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>塞纳★6</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>无敌牛★5</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>风龙★6</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>冬王★6</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>小牛★6</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>fe3★5</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>499p★6</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>法拉第★6</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>六子★6</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>霓虹gtr★6</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>ps龙★6</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>ts900★6</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>att★6</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>风扇★5</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>保时捷919★6</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>650s★6</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>英灵殿★6</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>600lt★5</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>5n★4</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>c1★6</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>gtr50★5</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>urs★6</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>复仇★6</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>狼王★6</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>纳兰★6</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>自燃★6</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>西安★6</t>
         </is>
@@ -10823,10 +10829,10 @@
       <c r="AO2" s="4" t="n"/>
       <c r="AP2" s="4" t="n"/>
       <c r="AQ2" s="4" t="n"/>
-      <c r="AR2" s="4" t="n">
+      <c r="AR2" s="4" t="n"/>
+      <c r="AS2" s="4" t="n">
         <v>19.2</v>
       </c>
-      <c r="AS2" s="4" t="n"/>
       <c r="AT2" s="4" t="n"/>
       <c r="AU2" s="4" t="n"/>
       <c r="AV2" s="4" t="n"/>
@@ -10838,18 +10844,18 @@
       <c r="BB2" s="4" t="n"/>
       <c r="BC2" s="4" t="n"/>
       <c r="BD2" s="4" t="n"/>
-      <c r="BE2" s="4" t="n">
+      <c r="BE2" s="4" t="n"/>
+      <c r="BF2" s="4" t="n">
         <v>19.25</v>
       </c>
-      <c r="BF2" s="4" t="n">
+      <c r="BG2" s="4" t="n">
         <v>19.3</v>
       </c>
-      <c r="BG2" s="4" t="n"/>
       <c r="BH2" s="4" t="n"/>
-      <c r="BI2" s="4" t="n">
+      <c r="BI2" s="4" t="n"/>
+      <c r="BJ2" s="4" t="n">
         <v>19.03</v>
       </c>
-      <c r="BJ2" s="4" t="n"/>
       <c r="BK2" s="4" t="n"/>
       <c r="BL2" s="4" t="n"/>
       <c r="BM2" s="4" t="n"/>
@@ -10876,6 +10882,7 @@
       <c r="CH2" s="4" t="n"/>
       <c r="CI2" s="4" t="n"/>
       <c r="CJ2" s="4" t="n"/>
+      <c r="CK2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n"/>
@@ -10984,6 +10991,7 @@
       <c r="CH3" s="4" t="n"/>
       <c r="CI3" s="4" t="n"/>
       <c r="CJ3" s="4" t="n"/>
+      <c r="CK3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n"/>
@@ -11084,6 +11092,7 @@
       <c r="CH4" s="4" t="n"/>
       <c r="CI4" s="4" t="n"/>
       <c r="CJ4" s="4" t="n"/>
+      <c r="CK4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n"/>
@@ -11151,10 +11160,10 @@
       <c r="AU5" s="4" t="n"/>
       <c r="AV5" s="4" t="n"/>
       <c r="AW5" s="4" t="n"/>
-      <c r="AX5" s="4" t="n">
+      <c r="AX5" s="4" t="n"/>
+      <c r="AY5" s="4" t="n">
         <v>17.96</v>
       </c>
-      <c r="AY5" s="4" t="n"/>
       <c r="AZ5" s="4" t="n"/>
       <c r="BA5" s="4" t="n"/>
       <c r="BB5" s="4" t="n"/>
@@ -11192,6 +11201,7 @@
       <c r="CH5" s="4" t="n"/>
       <c r="CI5" s="4" t="n"/>
       <c r="CJ5" s="4" t="n"/>
+      <c r="CK5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -11272,10 +11282,10 @@
       <c r="BF6" s="4" t="n"/>
       <c r="BG6" s="4" t="n"/>
       <c r="BH6" s="4" t="n"/>
-      <c r="BI6" s="4" t="n">
+      <c r="BI6" s="4" t="n"/>
+      <c r="BJ6" s="4" t="n">
         <v>18.03</v>
       </c>
-      <c r="BJ6" s="4" t="n"/>
       <c r="BK6" s="4" t="n"/>
       <c r="BL6" s="4" t="n"/>
       <c r="BM6" s="4" t="n"/>
@@ -11285,10 +11295,10 @@
       <c r="BQ6" s="4" t="n"/>
       <c r="BR6" s="4" t="n"/>
       <c r="BS6" s="4" t="n"/>
-      <c r="BT6" s="4" t="n">
+      <c r="BT6" s="4" t="n"/>
+      <c r="BU6" s="4" t="n">
         <v>17.8</v>
       </c>
-      <c r="BU6" s="4" t="n"/>
       <c r="BV6" s="4" t="n"/>
       <c r="BW6" s="4" t="n"/>
       <c r="BX6" s="4" t="n"/>
@@ -11304,6 +11314,7 @@
       <c r="CH6" s="4" t="n"/>
       <c r="CI6" s="4" t="n"/>
       <c r="CJ6" s="4" t="n"/>
+      <c r="CK6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
@@ -11406,6 +11417,7 @@
       <c r="CH7" s="4" t="n"/>
       <c r="CI7" s="4" t="n"/>
       <c r="CJ7" s="4" t="n"/>
+      <c r="CK7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
@@ -11489,10 +11501,10 @@
       <c r="AW8" s="4" t="n"/>
       <c r="AX8" s="4" t="n"/>
       <c r="AY8" s="4" t="n"/>
-      <c r="AZ8" s="4" t="n">
+      <c r="AZ8" s="4" t="n"/>
+      <c r="BA8" s="4" t="n">
         <v>28.39</v>
       </c>
-      <c r="BA8" s="4" t="n"/>
       <c r="BB8" s="4" t="n"/>
       <c r="BC8" s="4" t="n"/>
       <c r="BD8" s="4" t="n"/>
@@ -11528,6 +11540,7 @@
       <c r="CH8" s="4" t="n"/>
       <c r="CI8" s="4" t="n"/>
       <c r="CJ8" s="4" t="n"/>
+      <c r="CK8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n"/>
@@ -11594,10 +11607,10 @@
       <c r="AT9" s="4" t="n"/>
       <c r="AU9" s="4" t="n"/>
       <c r="AV9" s="4" t="n"/>
-      <c r="AW9" s="4" t="n">
+      <c r="AW9" s="4" t="n"/>
+      <c r="AX9" s="4" t="n">
         <v>20.52</v>
       </c>
-      <c r="AX9" s="4" t="n"/>
       <c r="AY9" s="4" t="n"/>
       <c r="AZ9" s="4" t="n"/>
       <c r="BA9" s="4" t="n"/>
@@ -11606,10 +11619,10 @@
       <c r="BD9" s="4" t="n"/>
       <c r="BE9" s="4" t="n"/>
       <c r="BF9" s="4" t="n"/>
-      <c r="BG9" s="4" t="n">
+      <c r="BG9" s="4" t="n"/>
+      <c r="BH9" s="4" t="n">
         <v>20.49</v>
       </c>
-      <c r="BH9" s="4" t="n"/>
       <c r="BI9" s="4" t="n"/>
       <c r="BJ9" s="4" t="n"/>
       <c r="BK9" s="4" t="n"/>
@@ -11638,6 +11651,7 @@
       <c r="CH9" s="4" t="n"/>
       <c r="CI9" s="4" t="n"/>
       <c r="CJ9" s="4" t="n"/>
+      <c r="CK9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -11748,6 +11762,7 @@
       <c r="CH10" s="4" t="n"/>
       <c r="CI10" s="4" t="n"/>
       <c r="CJ10" s="4" t="n"/>
+      <c r="CK10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
@@ -11806,19 +11821,19 @@
       <c r="AP11" s="4" t="n"/>
       <c r="AQ11" s="4" t="n"/>
       <c r="AR11" s="4" t="n"/>
-      <c r="AS11" s="4" t="n">
+      <c r="AS11" s="4" t="n"/>
+      <c r="AT11" s="4" t="n">
         <v>37.99</v>
       </c>
-      <c r="AT11" s="4" t="n"/>
       <c r="AU11" s="4" t="n"/>
       <c r="AV11" s="4" t="n"/>
       <c r="AW11" s="4" t="n"/>
       <c r="AX11" s="4" t="n"/>
       <c r="AY11" s="4" t="n"/>
-      <c r="AZ11" s="4" t="n">
+      <c r="AZ11" s="4" t="n"/>
+      <c r="BA11" s="4" t="n">
         <v>36.85</v>
       </c>
-      <c r="BA11" s="4" t="n"/>
       <c r="BB11" s="4" t="n"/>
       <c r="BC11" s="4" t="n"/>
       <c r="BD11" s="4" t="n"/>
@@ -11854,6 +11869,7 @@
       <c r="CH11" s="4" t="n"/>
       <c r="CI11" s="4" t="n"/>
       <c r="CJ11" s="4" t="n"/>
+      <c r="CK11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
@@ -11927,10 +11943,10 @@
       <c r="BA12" s="4" t="n"/>
       <c r="BB12" s="4" t="n"/>
       <c r="BC12" s="4" t="n"/>
-      <c r="BD12" s="4" t="n">
+      <c r="BD12" s="4" t="n"/>
+      <c r="BE12" s="4" t="n">
         <v>21.5</v>
       </c>
-      <c r="BE12" s="4" t="n"/>
       <c r="BF12" s="4" t="n"/>
       <c r="BG12" s="4" t="n"/>
       <c r="BH12" s="4" t="n"/>
@@ -11962,6 +11978,7 @@
       <c r="CH12" s="4" t="n"/>
       <c r="CI12" s="4" t="n"/>
       <c r="CJ12" s="4" t="n"/>
+      <c r="CK12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
@@ -12066,6 +12083,7 @@
       <c r="CH13" s="4" t="n"/>
       <c r="CI13" s="4" t="n"/>
       <c r="CJ13" s="4" t="n"/>
+      <c r="CK13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -12174,6 +12192,7 @@
       <c r="CH14" s="4" t="n"/>
       <c r="CI14" s="4" t="n"/>
       <c r="CJ14" s="4" t="n"/>
+      <c r="CK14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
@@ -12238,10 +12257,10 @@
       <c r="AP15" s="4" t="n"/>
       <c r="AQ15" s="4" t="n"/>
       <c r="AR15" s="4" t="n"/>
-      <c r="AS15" s="4" t="n">
+      <c r="AS15" s="4" t="n"/>
+      <c r="AT15" s="4" t="n">
         <v>30.4</v>
       </c>
-      <c r="AT15" s="4" t="n"/>
       <c r="AU15" s="4" t="n"/>
       <c r="AV15" s="4" t="n"/>
       <c r="AW15" s="4" t="n"/>
@@ -12257,10 +12276,10 @@
       <c r="BG15" s="4" t="n"/>
       <c r="BH15" s="4" t="n"/>
       <c r="BI15" s="4" t="n"/>
-      <c r="BJ15" s="4" t="n">
+      <c r="BJ15" s="4" t="n"/>
+      <c r="BK15" s="4" t="n">
         <v>29.7</v>
       </c>
-      <c r="BK15" s="4" t="n"/>
       <c r="BL15" s="4" t="n"/>
       <c r="BM15" s="4" t="n"/>
       <c r="BN15" s="4" t="n"/>
@@ -12286,6 +12305,7 @@
       <c r="CH15" s="4" t="n"/>
       <c r="CI15" s="4" t="n"/>
       <c r="CJ15" s="4" t="n"/>
+      <c r="CK15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
@@ -12398,6 +12418,7 @@
       <c r="CH16" s="4" t="n"/>
       <c r="CI16" s="4" t="n"/>
       <c r="CJ16" s="4" t="n"/>
+      <c r="CK16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
@@ -12498,6 +12519,7 @@
       <c r="CH17" s="4" t="n"/>
       <c r="CI17" s="4" t="n"/>
       <c r="CJ17" s="4" t="n"/>
+      <c r="CK17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -12560,27 +12582,27 @@
       <c r="AP18" s="4" t="n"/>
       <c r="AQ18" s="4" t="n"/>
       <c r="AR18" s="4" t="n"/>
-      <c r="AS18" s="4" t="n">
+      <c r="AS18" s="4" t="n"/>
+      <c r="AT18" s="4" t="n">
         <v>24.79</v>
       </c>
-      <c r="AT18" s="4" t="n"/>
       <c r="AU18" s="4" t="n"/>
       <c r="AV18" s="4" t="n"/>
-      <c r="AW18" s="4" t="n">
+      <c r="AW18" s="4" t="n"/>
+      <c r="AX18" s="4" t="n">
         <v>24.59</v>
       </c>
-      <c r="AX18" s="4" t="n"/>
       <c r="AY18" s="4" t="n"/>
       <c r="AZ18" s="4" t="n"/>
       <c r="BA18" s="4" t="n"/>
       <c r="BB18" s="4" t="n"/>
-      <c r="BC18" s="4" t="n">
+      <c r="BC18" s="4" t="n"/>
+      <c r="BD18" s="4" t="n">
         <v>24.5</v>
       </c>
-      <c r="BD18" s="4" t="n">
+      <c r="BE18" s="4" t="n">
         <v>23.42</v>
       </c>
-      <c r="BE18" s="4" t="n"/>
       <c r="BF18" s="4" t="n"/>
       <c r="BG18" s="4" t="n"/>
       <c r="BH18" s="4" t="n"/>
@@ -12612,6 +12634,7 @@
       <c r="CH18" s="4" t="n"/>
       <c r="CI18" s="4" t="n"/>
       <c r="CJ18" s="4" t="n"/>
+      <c r="CK18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
@@ -12674,10 +12697,10 @@
       </c>
       <c r="AO19" s="4" t="n"/>
       <c r="AP19" s="4" t="n"/>
-      <c r="AQ19" s="4" t="n">
+      <c r="AQ19" s="4" t="n"/>
+      <c r="AR19" s="4" t="n">
         <v>31.6</v>
       </c>
-      <c r="AR19" s="4" t="n"/>
       <c r="AS19" s="4" t="n"/>
       <c r="AT19" s="4" t="n"/>
       <c r="AU19" s="4" t="n"/>
@@ -12722,6 +12745,7 @@
       <c r="CH19" s="4" t="n"/>
       <c r="CI19" s="4" t="n"/>
       <c r="CJ19" s="4" t="n"/>
+      <c r="CK19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
@@ -12784,13 +12808,13 @@
       </c>
       <c r="AO20" s="4" t="n"/>
       <c r="AP20" s="4" t="n"/>
-      <c r="AQ20" s="4" t="n">
+      <c r="AQ20" s="4" t="n"/>
+      <c r="AR20" s="4" t="n">
         <v>22.19</v>
       </c>
-      <c r="AR20" s="4" t="n">
+      <c r="AS20" s="4" t="n">
         <v>22.8</v>
       </c>
-      <c r="AS20" s="4" t="n"/>
       <c r="AT20" s="4" t="n"/>
       <c r="AU20" s="4" t="n"/>
       <c r="AV20" s="4" t="n"/>
@@ -12802,17 +12826,17 @@
       <c r="BB20" s="4" t="n"/>
       <c r="BC20" s="4" t="n"/>
       <c r="BD20" s="4" t="n"/>
-      <c r="BE20" s="4" t="n">
+      <c r="BE20" s="4" t="n"/>
+      <c r="BF20" s="4" t="n">
         <v>22.6</v>
       </c>
-      <c r="BF20" s="4" t="n"/>
       <c r="BG20" s="4" t="n"/>
       <c r="BH20" s="4" t="n"/>
       <c r="BI20" s="4" t="n"/>
-      <c r="BJ20" s="4" t="n">
+      <c r="BJ20" s="4" t="n"/>
+      <c r="BK20" s="4" t="n">
         <v>22.9</v>
       </c>
-      <c r="BK20" s="4" t="n"/>
       <c r="BL20" s="4" t="n"/>
       <c r="BM20" s="4" t="n"/>
       <c r="BN20" s="4" t="n"/>
@@ -12838,6 +12862,7 @@
       <c r="CH20" s="4" t="n"/>
       <c r="CI20" s="4" t="n"/>
       <c r="CJ20" s="4" t="n"/>
+      <c r="CK20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
@@ -12940,6 +12965,7 @@
       <c r="CH21" s="4" t="n"/>
       <c r="CI21" s="4" t="n"/>
       <c r="CJ21" s="4" t="n"/>
+      <c r="CK21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -13044,6 +13070,7 @@
       <c r="CH22" s="4" t="n"/>
       <c r="CI22" s="4" t="n"/>
       <c r="CJ22" s="4" t="n"/>
+      <c r="CK22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
@@ -13110,10 +13137,10 @@
       <c r="AP23" s="4" t="n"/>
       <c r="AQ23" s="4" t="n"/>
       <c r="AR23" s="4" t="n"/>
-      <c r="AS23" s="4" t="n">
+      <c r="AS23" s="4" t="n"/>
+      <c r="AT23" s="4" t="n">
         <v>32.3</v>
       </c>
-      <c r="AT23" s="4" t="n"/>
       <c r="AU23" s="4" t="n"/>
       <c r="AV23" s="4" t="n"/>
       <c r="AW23" s="4" t="n"/>
@@ -13156,6 +13183,7 @@
       <c r="CH23" s="4" t="n"/>
       <c r="CI23" s="4" t="n"/>
       <c r="CJ23" s="4" t="n"/>
+      <c r="CK23" s="4" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
@@ -13222,10 +13250,10 @@
       <c r="AT24" s="4" t="n"/>
       <c r="AU24" s="4" t="n"/>
       <c r="AV24" s="4" t="n"/>
-      <c r="AW24" s="4" t="n">
+      <c r="AW24" s="4" t="n"/>
+      <c r="AX24" s="4" t="n">
         <v>23.69</v>
       </c>
-      <c r="AX24" s="4" t="n"/>
       <c r="AY24" s="4" t="n"/>
       <c r="AZ24" s="4" t="n"/>
       <c r="BA24" s="4" t="n"/>
@@ -13264,6 +13292,7 @@
       <c r="CH24" s="4" t="n"/>
       <c r="CI24" s="4" t="n"/>
       <c r="CJ24" s="4" t="n"/>
+      <c r="CK24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
@@ -13336,10 +13365,10 @@
       <c r="BD25" s="4" t="n"/>
       <c r="BE25" s="4" t="n"/>
       <c r="BF25" s="4" t="n"/>
-      <c r="BG25" s="4" t="n">
+      <c r="BG25" s="4" t="n"/>
+      <c r="BH25" s="4" t="n">
         <v>25.5</v>
       </c>
-      <c r="BH25" s="4" t="n"/>
       <c r="BI25" s="4" t="n"/>
       <c r="BJ25" s="4" t="n"/>
       <c r="BK25" s="4" t="n"/>
@@ -13368,6 +13397,7 @@
       <c r="CH25" s="4" t="n"/>
       <c r="CI25" s="4" t="n"/>
       <c r="CJ25" s="4" t="n"/>
+      <c r="CK25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -13434,10 +13464,10 @@
       <c r="AP26" s="4" t="n"/>
       <c r="AQ26" s="4" t="n"/>
       <c r="AR26" s="4" t="n"/>
-      <c r="AS26" s="4" t="n">
+      <c r="AS26" s="4" t="n"/>
+      <c r="AT26" s="4" t="n">
         <v>19.5</v>
       </c>
-      <c r="AT26" s="4" t="n"/>
       <c r="AU26" s="4" t="n"/>
       <c r="AV26" s="4" t="n"/>
       <c r="AW26" s="4" t="n"/>
@@ -13447,10 +13477,10 @@
       <c r="BA26" s="4" t="n"/>
       <c r="BB26" s="4" t="n"/>
       <c r="BC26" s="4" t="n"/>
-      <c r="BD26" s="4" t="n">
+      <c r="BD26" s="4" t="n"/>
+      <c r="BE26" s="4" t="n">
         <v>18.45</v>
       </c>
-      <c r="BE26" s="4" t="n"/>
       <c r="BF26" s="4" t="n"/>
       <c r="BG26" s="4" t="n"/>
       <c r="BH26" s="4" t="n"/>
@@ -13482,6 +13512,7 @@
       <c r="CH26" s="4" t="n"/>
       <c r="CI26" s="4" t="n"/>
       <c r="CJ26" s="4" t="n"/>
+      <c r="CK26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n"/>
@@ -13604,6 +13635,7 @@
       <c r="CH27" s="4" t="n"/>
       <c r="CI27" s="4" t="n"/>
       <c r="CJ27" s="4" t="n"/>
+      <c r="CK27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
@@ -13667,18 +13699,18 @@
       <c r="AU28" s="4" t="n"/>
       <c r="AV28" s="4" t="n"/>
       <c r="AW28" s="4" t="n"/>
-      <c r="AX28" s="4" t="n">
+      <c r="AX28" s="4" t="n"/>
+      <c r="AY28" s="4" t="n">
         <v>32.9</v>
       </c>
-      <c r="AY28" s="4" t="n"/>
       <c r="AZ28" s="4" t="n"/>
       <c r="BA28" s="4" t="n"/>
       <c r="BB28" s="4" t="n"/>
       <c r="BC28" s="4" t="n"/>
-      <c r="BD28" s="4" t="n">
+      <c r="BD28" s="4" t="n"/>
+      <c r="BE28" s="4" t="n">
         <v>32.6</v>
       </c>
-      <c r="BE28" s="4" t="n"/>
       <c r="BF28" s="4" t="n"/>
       <c r="BG28" s="4" t="n"/>
       <c r="BH28" s="4" t="n"/>
@@ -13710,6 +13742,7 @@
       <c r="CH28" s="4" t="n"/>
       <c r="CI28" s="4" t="n"/>
       <c r="CJ28" s="4" t="n"/>
+      <c r="CK28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n"/>
@@ -13808,6 +13841,7 @@
       <c r="CH29" s="4" t="n"/>
       <c r="CI29" s="4" t="n"/>
       <c r="CJ29" s="4" t="n"/>
+      <c r="CK29" s="4" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -13916,6 +13950,7 @@
       <c r="CH30" s="4" t="n"/>
       <c r="CI30" s="4" t="n"/>
       <c r="CJ30" s="4" t="n"/>
+      <c r="CK30" s="4" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n"/>
@@ -13971,10 +14006,10 @@
       <c r="AO31" s="4" t="n"/>
       <c r="AP31" s="4" t="n"/>
       <c r="AQ31" s="4" t="n"/>
-      <c r="AR31" s="4" t="n">
+      <c r="AR31" s="4" t="n"/>
+      <c r="AS31" s="4" t="n">
         <v>19.45</v>
       </c>
-      <c r="AS31" s="4" t="n"/>
       <c r="AT31" s="4" t="n"/>
       <c r="AU31" s="4" t="n"/>
       <c r="AV31" s="4" t="n"/>
@@ -13986,10 +14021,10 @@
       <c r="BB31" s="4" t="n"/>
       <c r="BC31" s="4" t="n"/>
       <c r="BD31" s="4" t="n"/>
-      <c r="BE31" s="4" t="n">
+      <c r="BE31" s="4" t="n"/>
+      <c r="BF31" s="4" t="n">
         <v>19.23</v>
       </c>
-      <c r="BF31" s="4" t="n"/>
       <c r="BG31" s="4" t="n"/>
       <c r="BH31" s="4" t="n"/>
       <c r="BI31" s="4" t="n"/>
@@ -14020,6 +14055,7 @@
       <c r="CH31" s="4" t="n"/>
       <c r="CI31" s="4" t="n"/>
       <c r="CJ31" s="4" t="n"/>
+      <c r="CK31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n"/>
@@ -14092,65 +14128,65 @@
         <v>28.15</v>
       </c>
       <c r="AP32" s="4" t="n"/>
-      <c r="AQ32" s="4" t="n">
+      <c r="AQ32" s="4" t="n"/>
+      <c r="AR32" s="4" t="n">
         <v>27.4</v>
       </c>
-      <c r="AR32" s="4" t="n"/>
-      <c r="AS32" s="4" t="n">
+      <c r="AS32" s="4" t="n"/>
+      <c r="AT32" s="4" t="n">
         <v>29.3</v>
       </c>
-      <c r="AT32" s="4" t="n"/>
       <c r="AU32" s="4" t="n"/>
       <c r="AV32" s="4" t="n"/>
       <c r="AW32" s="4" t="n"/>
-      <c r="AX32" s="4" t="n">
+      <c r="AX32" s="4" t="n"/>
+      <c r="AY32" s="4" t="n">
         <v>28.3</v>
       </c>
-      <c r="AY32" s="4" t="n"/>
       <c r="AZ32" s="4" t="n"/>
       <c r="BA32" s="4" t="n"/>
       <c r="BB32" s="4" t="n"/>
       <c r="BC32" s="4" t="n"/>
-      <c r="BD32" s="4" t="n">
+      <c r="BD32" s="4" t="n"/>
+      <c r="BE32" s="4" t="n">
         <v>28.1</v>
       </c>
-      <c r="BE32" s="4" t="n"/>
       <c r="BF32" s="4" t="n"/>
-      <c r="BG32" s="4" t="n">
+      <c r="BG32" s="4" t="n"/>
+      <c r="BH32" s="4" t="n">
         <v>29.6</v>
       </c>
-      <c r="BH32" s="4" t="n"/>
       <c r="BI32" s="4" t="n"/>
       <c r="BJ32" s="4" t="n"/>
       <c r="BK32" s="4" t="n"/>
       <c r="BL32" s="4" t="n"/>
       <c r="BM32" s="4" t="n"/>
-      <c r="BN32" s="4" t="n">
+      <c r="BN32" s="4" t="n"/>
+      <c r="BO32" s="4" t="n">
         <v>30.1</v>
       </c>
-      <c r="BO32" s="4" t="n">
+      <c r="BP32" s="4" t="n">
         <v>29.56</v>
       </c>
-      <c r="BP32" s="4" t="n"/>
       <c r="BQ32" s="4" t="n"/>
       <c r="BR32" s="4" t="n"/>
-      <c r="BS32" s="4" t="n">
+      <c r="BS32" s="4" t="n"/>
+      <c r="BT32" s="4" t="n">
         <v>29.2</v>
       </c>
-      <c r="BT32" s="4" t="n"/>
       <c r="BU32" s="4" t="n"/>
       <c r="BV32" s="4" t="n"/>
       <c r="BW32" s="4" t="n"/>
-      <c r="BX32" s="4" t="n">
+      <c r="BX32" s="4" t="n"/>
+      <c r="BY32" s="4" t="n">
         <v>29.1</v>
       </c>
-      <c r="BY32" s="4" t="n">
+      <c r="BZ32" s="4" t="n">
         <v>29.5</v>
       </c>
-      <c r="BZ32" s="4" t="n">
+      <c r="CA32" s="4" t="n">
         <v>29.7</v>
       </c>
-      <c r="CA32" s="4" t="n"/>
       <c r="CB32" s="4" t="n"/>
       <c r="CC32" s="4" t="n"/>
       <c r="CD32" s="4" t="n"/>
@@ -14160,6 +14196,7 @@
       <c r="CH32" s="4" t="n"/>
       <c r="CI32" s="4" t="n"/>
       <c r="CJ32" s="4" t="n"/>
+      <c r="CK32" s="4" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -14217,10 +14254,10 @@
       <c r="AO33" s="4" t="n"/>
       <c r="AP33" s="4" t="n"/>
       <c r="AQ33" s="4" t="n"/>
-      <c r="AR33" s="4" t="n">
+      <c r="AR33" s="4" t="n"/>
+      <c r="AS33" s="4" t="n">
         <v>20.4</v>
       </c>
-      <c r="AS33" s="4" t="n"/>
       <c r="AT33" s="4" t="n"/>
       <c r="AU33" s="4" t="n"/>
       <c r="AV33" s="4" t="n"/>
@@ -14232,13 +14269,13 @@
       <c r="BB33" s="4" t="n"/>
       <c r="BC33" s="4" t="n"/>
       <c r="BD33" s="4" t="n"/>
-      <c r="BE33" s="4" t="n">
+      <c r="BE33" s="4" t="n"/>
+      <c r="BF33" s="4" t="n">
         <v>19.95</v>
       </c>
-      <c r="BF33" s="4" t="n">
+      <c r="BG33" s="4" t="n">
         <v>20.5</v>
       </c>
-      <c r="BG33" s="4" t="n"/>
       <c r="BH33" s="4" t="n"/>
       <c r="BI33" s="4" t="n"/>
       <c r="BJ33" s="4" t="n"/>
@@ -14268,6 +14305,7 @@
       <c r="CH33" s="4" t="n"/>
       <c r="CI33" s="4" t="n"/>
       <c r="CJ33" s="4" t="n"/>
+      <c r="CK33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n"/>
@@ -14370,6 +14408,7 @@
       <c r="CH34" s="4" t="n"/>
       <c r="CI34" s="4" t="n"/>
       <c r="CJ34" s="4" t="n"/>
+      <c r="CK34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n"/>
@@ -14442,13 +14481,13 @@
       <c r="BB35" s="4" t="n"/>
       <c r="BC35" s="4" t="n"/>
       <c r="BD35" s="4" t="n"/>
-      <c r="BE35" s="4" t="n">
+      <c r="BE35" s="4" t="n"/>
+      <c r="BF35" s="4" t="n">
         <v>23.4</v>
       </c>
-      <c r="BF35" s="4" t="n">
+      <c r="BG35" s="4" t="n">
         <v>24.09</v>
       </c>
-      <c r="BG35" s="4" t="n"/>
       <c r="BH35" s="4" t="n"/>
       <c r="BI35" s="4" t="n"/>
       <c r="BJ35" s="4" t="n"/>
@@ -14478,6 +14517,7 @@
       <c r="CH35" s="4" t="n"/>
       <c r="CI35" s="4" t="n"/>
       <c r="CJ35" s="4" t="n"/>
+      <c r="CK35" s="4" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n"/>
@@ -14582,6 +14622,7 @@
       <c r="CH36" s="4" t="n"/>
       <c r="CI36" s="4" t="n"/>
       <c r="CJ36" s="4" t="n"/>
+      <c r="CK36" s="4" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -14696,6 +14737,7 @@
       <c r="CH37" s="4" t="n"/>
       <c r="CI37" s="4" t="n"/>
       <c r="CJ37" s="4" t="n"/>
+      <c r="CK37" s="4" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n"/>
@@ -14770,10 +14812,10 @@
       <c r="BD38" s="4" t="n"/>
       <c r="BE38" s="4" t="n"/>
       <c r="BF38" s="4" t="n"/>
-      <c r="BG38" s="4" t="n">
+      <c r="BG38" s="4" t="n"/>
+      <c r="BH38" s="4" t="n">
         <v>21.99</v>
       </c>
-      <c r="BH38" s="4" t="n"/>
       <c r="BI38" s="4" t="n"/>
       <c r="BJ38" s="4" t="n"/>
       <c r="BK38" s="4" t="n"/>
@@ -14802,6 +14844,7 @@
       <c r="CH38" s="4" t="n"/>
       <c r="CI38" s="4" t="n"/>
       <c r="CJ38" s="4" t="n"/>
+      <c r="CK38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n"/>
@@ -14906,6 +14949,7 @@
       <c r="CH39" s="4" t="n"/>
       <c r="CI39" s="4" t="n"/>
       <c r="CJ39" s="4" t="n"/>
+      <c r="CK39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n"/>
@@ -14965,10 +15009,10 @@
       <c r="AO40" s="4" t="n"/>
       <c r="AP40" s="4" t="n"/>
       <c r="AQ40" s="4" t="n"/>
-      <c r="AR40" s="4" t="n">
+      <c r="AR40" s="4" t="n"/>
+      <c r="AS40" s="4" t="n">
         <v>35.4</v>
       </c>
-      <c r="AS40" s="4" t="n"/>
       <c r="AT40" s="4" t="n"/>
       <c r="AU40" s="4" t="n"/>
       <c r="AV40" s="4" t="n"/>
@@ -14985,10 +15029,10 @@
       <c r="BG40" s="4" t="n"/>
       <c r="BH40" s="4" t="n"/>
       <c r="BI40" s="4" t="n"/>
-      <c r="BJ40" s="4" t="n">
+      <c r="BJ40" s="4" t="n"/>
+      <c r="BK40" s="4" t="n">
         <v>35.3</v>
       </c>
-      <c r="BK40" s="4" t="n"/>
       <c r="BL40" s="4" t="n"/>
       <c r="BM40" s="4" t="n"/>
       <c r="BN40" s="4" t="n"/>
@@ -15014,6 +15058,7 @@
       <c r="CH40" s="4" t="n"/>
       <c r="CI40" s="4" t="n"/>
       <c r="CJ40" s="4" t="n"/>
+      <c r="CK40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -15120,6 +15165,7 @@
       <c r="CH41" s="4" t="n"/>
       <c r="CI41" s="4" t="n"/>
       <c r="CJ41" s="4" t="n"/>
+      <c r="CK41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n"/>
@@ -15184,14 +15230,14 @@
       </c>
       <c r="AO42" s="4" t="n"/>
       <c r="AP42" s="4" t="n"/>
-      <c r="AQ42" s="4" t="n">
+      <c r="AQ42" s="4" t="n"/>
+      <c r="AR42" s="4" t="n">
         <v>21.4</v>
       </c>
-      <c r="AR42" s="4" t="n"/>
-      <c r="AS42" s="4" t="n">
+      <c r="AS42" s="4" t="n"/>
+      <c r="AT42" s="4" t="n">
         <v>22.8</v>
       </c>
-      <c r="AT42" s="4" t="n"/>
       <c r="AU42" s="4" t="n"/>
       <c r="AV42" s="4" t="n"/>
       <c r="AW42" s="4" t="n"/>
@@ -15201,10 +15247,10 @@
       <c r="BA42" s="4" t="n"/>
       <c r="BB42" s="4" t="n"/>
       <c r="BC42" s="4" t="n"/>
-      <c r="BD42" s="4" t="n">
+      <c r="BD42" s="4" t="n"/>
+      <c r="BE42" s="4" t="n">
         <v>21.9</v>
       </c>
-      <c r="BE42" s="4" t="n"/>
       <c r="BF42" s="4" t="n"/>
       <c r="BG42" s="4" t="n"/>
       <c r="BH42" s="4" t="n"/>
@@ -15236,6 +15282,7 @@
       <c r="CH42" s="4" t="n"/>
       <c r="CI42" s="4" t="n"/>
       <c r="CJ42" s="4" t="n"/>
+      <c r="CK42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n"/>
@@ -15315,10 +15362,10 @@
       <c r="BG43" s="4" t="n"/>
       <c r="BH43" s="4" t="n"/>
       <c r="BI43" s="4" t="n"/>
-      <c r="BJ43" s="4" t="n">
+      <c r="BJ43" s="4" t="n"/>
+      <c r="BK43" s="4" t="n">
         <v>40.1</v>
       </c>
-      <c r="BK43" s="4" t="n"/>
       <c r="BL43" s="4" t="n"/>
       <c r="BM43" s="4" t="n"/>
       <c r="BN43" s="4" t="n"/>
@@ -15344,6 +15391,7 @@
       <c r="CH43" s="4" t="n"/>
       <c r="CI43" s="4" t="n"/>
       <c r="CJ43" s="4" t="n"/>
+      <c r="CK43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n"/>
@@ -15403,10 +15451,10 @@
       <c r="AO44" s="4" t="n"/>
       <c r="AP44" s="4" t="n"/>
       <c r="AQ44" s="4" t="n"/>
-      <c r="AR44" s="4" t="n">
+      <c r="AR44" s="4" t="n"/>
+      <c r="AS44" s="4" t="n">
         <v>22.6</v>
       </c>
-      <c r="AS44" s="4" t="n"/>
       <c r="AT44" s="4" t="n"/>
       <c r="AU44" s="4" t="n"/>
       <c r="AV44" s="4" t="n"/>
@@ -15450,6 +15498,7 @@
       <c r="CH44" s="4" t="n"/>
       <c r="CI44" s="4" t="n"/>
       <c r="CJ44" s="4" t="n"/>
+      <c r="CK44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -15560,6 +15609,7 @@
       <c r="CH45" s="4" t="n"/>
       <c r="CI45" s="4" t="n"/>
       <c r="CJ45" s="4" t="n"/>
+      <c r="CK45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n"/>
@@ -15645,10 +15695,10 @@
       <c r="BM46" s="4" t="n"/>
       <c r="BN46" s="4" t="n"/>
       <c r="BO46" s="4" t="n"/>
-      <c r="BP46" s="4" t="n">
+      <c r="BP46" s="4" t="n"/>
+      <c r="BQ46" s="4" t="n">
         <v>34.22</v>
       </c>
-      <c r="BQ46" s="4" t="n"/>
       <c r="BR46" s="4" t="n"/>
       <c r="BS46" s="4" t="n"/>
       <c r="BT46" s="4" t="n"/>
@@ -15668,6 +15718,7 @@
       <c r="CH46" s="4" t="n"/>
       <c r="CI46" s="4" t="n"/>
       <c r="CJ46" s="4" t="n"/>
+      <c r="CK46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n"/>
@@ -15770,6 +15821,7 @@
       <c r="CH47" s="4" t="n"/>
       <c r="CI47" s="4" t="n"/>
       <c r="CJ47" s="4" t="n"/>
+      <c r="CK47" s="4" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n"/>
@@ -15832,14 +15884,14 @@
       <c r="AN48" s="4" t="n"/>
       <c r="AO48" s="4" t="n"/>
       <c r="AP48" s="4" t="n"/>
-      <c r="AQ48" s="4" t="n">
+      <c r="AQ48" s="4" t="n"/>
+      <c r="AR48" s="4" t="n">
         <v>24.5</v>
       </c>
-      <c r="AR48" s="4" t="n"/>
-      <c r="AS48" s="4" t="n">
+      <c r="AS48" s="4" t="n"/>
+      <c r="AT48" s="4" t="n">
         <v>25.8</v>
       </c>
-      <c r="AT48" s="4" t="n"/>
       <c r="AU48" s="4" t="n"/>
       <c r="AV48" s="4" t="n"/>
       <c r="AW48" s="4" t="n"/>
@@ -15882,6 +15934,7 @@
       <c r="CH48" s="4" t="n"/>
       <c r="CI48" s="4" t="n"/>
       <c r="CJ48" s="4" t="n"/>
+      <c r="CK48" s="4" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -15969,10 +16022,10 @@
       <c r="BM49" s="4" t="n"/>
       <c r="BN49" s="4" t="n"/>
       <c r="BO49" s="4" t="n"/>
-      <c r="BP49" s="4" t="n">
+      <c r="BP49" s="4" t="n"/>
+      <c r="BQ49" s="4" t="n">
         <v>31.71</v>
       </c>
-      <c r="BQ49" s="4" t="n"/>
       <c r="BR49" s="4" t="n"/>
       <c r="BS49" s="4" t="n"/>
       <c r="BT49" s="4" t="n"/>
@@ -15992,6 +16045,7 @@
       <c r="CH49" s="4" t="n"/>
       <c r="CI49" s="4" t="n"/>
       <c r="CJ49" s="4" t="n"/>
+      <c r="CK49" s="4" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="n"/>
@@ -16051,10 +16105,10 @@
       <c r="AO50" s="4" t="n"/>
       <c r="AP50" s="4" t="n"/>
       <c r="AQ50" s="4" t="n"/>
-      <c r="AR50" s="4" t="n">
+      <c r="AR50" s="4" t="n"/>
+      <c r="AS50" s="4" t="n">
         <v>27.09</v>
       </c>
-      <c r="AS50" s="4" t="n"/>
       <c r="AT50" s="4" t="n"/>
       <c r="AU50" s="4" t="n"/>
       <c r="AV50" s="4" t="n"/>
@@ -16077,10 +16131,10 @@
       <c r="BM50" s="4" t="n"/>
       <c r="BN50" s="4" t="n"/>
       <c r="BO50" s="4" t="n"/>
-      <c r="BP50" s="4" t="n">
+      <c r="BP50" s="4" t="n"/>
+      <c r="BQ50" s="4" t="n">
         <v>27.61</v>
       </c>
-      <c r="BQ50" s="4" t="n"/>
       <c r="BR50" s="4" t="n"/>
       <c r="BS50" s="4" t="n"/>
       <c r="BT50" s="4" t="n"/>
@@ -16100,6 +16154,7 @@
       <c r="CH50" s="4" t="n"/>
       <c r="CI50" s="4" t="n"/>
       <c r="CJ50" s="4" t="n"/>
+      <c r="CK50" s="4" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n"/>
@@ -16173,10 +16228,10 @@
       <c r="BA51" s="4" t="n"/>
       <c r="BB51" s="4" t="n"/>
       <c r="BC51" s="4" t="n"/>
-      <c r="BD51" s="4" t="n">
+      <c r="BD51" s="4" t="n"/>
+      <c r="BE51" s="4" t="n">
         <v>23.79</v>
       </c>
-      <c r="BE51" s="4" t="n"/>
       <c r="BF51" s="4" t="n"/>
       <c r="BG51" s="4" t="n"/>
       <c r="BH51" s="4" t="n"/>
@@ -16208,6 +16263,7 @@
       <c r="CH51" s="4" t="n"/>
       <c r="CI51" s="4" t="n"/>
       <c r="CJ51" s="4" t="n"/>
+      <c r="CK51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n"/>
@@ -16285,10 +16341,10 @@
       <c r="BG52" s="4" t="n"/>
       <c r="BH52" s="4" t="n"/>
       <c r="BI52" s="4" t="n"/>
-      <c r="BJ52" s="4" t="n">
+      <c r="BJ52" s="4" t="n"/>
+      <c r="BK52" s="4" t="n">
         <v>34.29</v>
       </c>
-      <c r="BK52" s="4" t="n"/>
       <c r="BL52" s="4" t="n"/>
       <c r="BM52" s="4" t="n"/>
       <c r="BN52" s="4" t="n"/>
@@ -16314,6 +16370,7 @@
       <c r="CH52" s="4" t="n"/>
       <c r="CI52" s="4" t="n"/>
       <c r="CJ52" s="4" t="n"/>
+      <c r="CK52" s="4" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -16432,6 +16489,7 @@
       <c r="CH53" s="4" t="n"/>
       <c r="CI53" s="4" t="n"/>
       <c r="CJ53" s="4" t="n"/>
+      <c r="CK53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n"/>
@@ -16538,6 +16596,7 @@
       <c r="CH54" s="4" t="n"/>
       <c r="CI54" s="4" t="n"/>
       <c r="CJ54" s="4" t="n"/>
+      <c r="CK54" s="4" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n"/>
@@ -16599,10 +16658,10 @@
       <c r="AO55" s="4" t="n"/>
       <c r="AP55" s="4" t="n"/>
       <c r="AQ55" s="4" t="n"/>
-      <c r="AR55" s="4" t="n">
+      <c r="AR55" s="4" t="n"/>
+      <c r="AS55" s="4" t="n">
         <v>33.29</v>
       </c>
-      <c r="AS55" s="4" t="n"/>
       <c r="AT55" s="4" t="n"/>
       <c r="AU55" s="4" t="n"/>
       <c r="AV55" s="4" t="n"/>
@@ -16646,6 +16705,7 @@
       <c r="CH55" s="4" t="n"/>
       <c r="CI55" s="4" t="n"/>
       <c r="CJ55" s="4" t="n"/>
+      <c r="CK55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n"/>
@@ -16750,6 +16810,7 @@
       <c r="CH56" s="4" t="n"/>
       <c r="CI56" s="4" t="n"/>
       <c r="CJ56" s="4" t="n"/>
+      <c r="CK56" s="4" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -16821,10 +16882,10 @@
       <c r="AQ57" s="4" t="n"/>
       <c r="AR57" s="4" t="n"/>
       <c r="AS57" s="4" t="n"/>
-      <c r="AT57" s="4" t="n">
+      <c r="AT57" s="4" t="n"/>
+      <c r="AU57" s="4" t="n">
         <v>36.39</v>
       </c>
-      <c r="AU57" s="4" t="n"/>
       <c r="AV57" s="4" t="n"/>
       <c r="AW57" s="4" t="n"/>
       <c r="AX57" s="4" t="n"/>
@@ -16866,6 +16927,7 @@
       <c r="CH57" s="4" t="n"/>
       <c r="CI57" s="4" t="n"/>
       <c r="CJ57" s="4" t="n"/>
+      <c r="CK57" s="4" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="n"/>
@@ -16980,6 +17042,7 @@
       <c r="CH58" s="4" t="n"/>
       <c r="CI58" s="4" t="n"/>
       <c r="CJ58" s="4" t="n"/>
+      <c r="CK58" s="4" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n"/>
@@ -17084,6 +17147,7 @@
       <c r="CH59" s="4" t="n"/>
       <c r="CI59" s="4" t="n"/>
       <c r="CJ59" s="4" t="n"/>
+      <c r="CK59" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n"/>
@@ -17186,6 +17250,7 @@
       <c r="CH60" s="4" t="n"/>
       <c r="CI60" s="4" t="n"/>
       <c r="CJ60" s="4" t="n"/>
+      <c r="CK60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -17264,10 +17329,10 @@
       <c r="BB61" s="4" t="n"/>
       <c r="BC61" s="4" t="n"/>
       <c r="BD61" s="4" t="n"/>
-      <c r="BE61" s="4" t="n">
+      <c r="BE61" s="4" t="n"/>
+      <c r="BF61" s="4" t="n">
         <v>21.85</v>
       </c>
-      <c r="BF61" s="4" t="n"/>
       <c r="BG61" s="4" t="n"/>
       <c r="BH61" s="4" t="n"/>
       <c r="BI61" s="4" t="n"/>
@@ -17298,6 +17363,7 @@
       <c r="CH61" s="4" t="n"/>
       <c r="CI61" s="4" t="n"/>
       <c r="CJ61" s="4" t="n"/>
+      <c r="CK61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="n"/>
@@ -17402,6 +17468,7 @@
       <c r="CH62" s="4" t="n"/>
       <c r="CI62" s="4" t="n"/>
       <c r="CJ62" s="4" t="n"/>
+      <c r="CK62" s="4" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n"/>
@@ -17471,10 +17538,10 @@
       <c r="BC63" s="4" t="n"/>
       <c r="BD63" s="4" t="n"/>
       <c r="BE63" s="4" t="n"/>
-      <c r="BF63" s="4" t="n">
+      <c r="BF63" s="4" t="n"/>
+      <c r="BG63" s="4" t="n">
         <v>25.1</v>
       </c>
-      <c r="BG63" s="4" t="n"/>
       <c r="BH63" s="4" t="n"/>
       <c r="BI63" s="4" t="n"/>
       <c r="BJ63" s="4" t="n"/>
@@ -17504,6 +17571,7 @@
       <c r="CH63" s="4" t="n"/>
       <c r="CI63" s="4" t="n"/>
       <c r="CJ63" s="4" t="n"/>
+      <c r="CK63" s="4" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n"/>
@@ -17569,10 +17637,10 @@
         <v>34.35</v>
       </c>
       <c r="AQ64" s="4" t="n"/>
-      <c r="AR64" s="4" t="n">
+      <c r="AR64" s="4" t="n"/>
+      <c r="AS64" s="4" t="n">
         <v>37.05</v>
       </c>
-      <c r="AS64" s="4" t="n"/>
       <c r="AT64" s="4" t="n"/>
       <c r="AU64" s="4" t="n"/>
       <c r="AV64" s="4" t="n"/>
@@ -17616,6 +17684,7 @@
       <c r="CH64" s="4" t="n"/>
       <c r="CI64" s="4" t="n"/>
       <c r="CJ64" s="4" t="n"/>
+      <c r="CK64" s="4" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -17724,6 +17793,7 @@
       <c r="CH65" s="4" t="n"/>
       <c r="CI65" s="4" t="n"/>
       <c r="CJ65" s="4" t="n"/>
+      <c r="CK65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="n"/>
@@ -17832,6 +17902,7 @@
       <c r="CH66" s="4" t="n"/>
       <c r="CI66" s="4" t="n"/>
       <c r="CJ66" s="4" t="n"/>
+      <c r="CK66" s="4" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n"/>
@@ -17897,10 +17968,10 @@
       <c r="AU67" s="4" t="n"/>
       <c r="AV67" s="4" t="n"/>
       <c r="AW67" s="4" t="n"/>
-      <c r="AX67" s="4" t="n">
+      <c r="AX67" s="4" t="n"/>
+      <c r="AY67" s="4" t="n">
         <v>18.09</v>
       </c>
-      <c r="AY67" s="4" t="n"/>
       <c r="AZ67" s="4" t="n"/>
       <c r="BA67" s="4" t="n"/>
       <c r="BB67" s="4" t="n"/>
@@ -17908,24 +17979,24 @@
       <c r="BD67" s="4" t="n"/>
       <c r="BE67" s="4" t="n"/>
       <c r="BF67" s="4" t="n"/>
-      <c r="BG67" s="4" t="n">
+      <c r="BG67" s="4" t="n"/>
+      <c r="BH67" s="4" t="n">
         <v>18.9</v>
       </c>
-      <c r="BH67" s="4" t="n"/>
-      <c r="BI67" s="4" t="n">
+      <c r="BI67" s="4" t="n"/>
+      <c r="BJ67" s="4" t="n">
         <v>18.5</v>
       </c>
-      <c r="BJ67" s="4" t="n"/>
       <c r="BK67" s="4" t="n"/>
       <c r="BL67" s="4" t="n"/>
       <c r="BM67" s="4" t="n"/>
       <c r="BN67" s="4" t="n"/>
       <c r="BO67" s="4" t="n"/>
       <c r="BP67" s="4" t="n"/>
-      <c r="BQ67" s="4" t="n">
+      <c r="BQ67" s="4" t="n"/>
+      <c r="BR67" s="4" t="n">
         <v>18.3</v>
       </c>
-      <c r="BR67" s="4" t="n"/>
       <c r="BS67" s="4" t="n"/>
       <c r="BT67" s="4" t="n"/>
       <c r="BU67" s="4" t="n"/>
@@ -17944,6 +18015,7 @@
       <c r="CH67" s="4" t="n"/>
       <c r="CI67" s="4" t="n"/>
       <c r="CJ67" s="4" t="n"/>
+      <c r="CK67" s="4" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n"/>
@@ -18005,10 +18077,10 @@
       <c r="AU68" s="4" t="n"/>
       <c r="AV68" s="4" t="n"/>
       <c r="AW68" s="4" t="n"/>
-      <c r="AX68" s="4" t="n">
+      <c r="AX68" s="4" t="n"/>
+      <c r="AY68" s="4" t="n">
         <v>27.68</v>
       </c>
-      <c r="AY68" s="4" t="n"/>
       <c r="AZ68" s="4" t="n"/>
       <c r="BA68" s="4" t="n"/>
       <c r="BB68" s="4" t="n"/>
@@ -18046,6 +18118,7 @@
       <c r="CH68" s="4" t="n"/>
       <c r="CI68" s="4" t="n"/>
       <c r="CJ68" s="4" t="n"/>
+      <c r="CK68" s="4" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -18106,10 +18179,10 @@
       <c r="AN69" s="4" t="n"/>
       <c r="AO69" s="4" t="n"/>
       <c r="AP69" s="4" t="n"/>
-      <c r="AQ69" s="4" t="n">
+      <c r="AQ69" s="4" t="n"/>
+      <c r="AR69" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="AR69" s="4" t="n"/>
       <c r="AS69" s="4" t="n"/>
       <c r="AT69" s="4" t="n"/>
       <c r="AU69" s="4" t="n"/>
@@ -18154,6 +18227,7 @@
       <c r="CH69" s="4" t="n"/>
       <c r="CI69" s="4" t="n"/>
       <c r="CJ69" s="4" t="n"/>
+      <c r="CK69" s="4" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="n"/>
@@ -18256,6 +18330,7 @@
       <c r="CH70" s="4" t="n"/>
       <c r="CI70" s="4" t="n"/>
       <c r="CJ70" s="4" t="n"/>
+      <c r="CK70" s="4" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n"/>
@@ -18364,6 +18439,7 @@
       <c r="CH71" s="4" t="n"/>
       <c r="CI71" s="4" t="n"/>
       <c r="CJ71" s="4" t="n"/>
+      <c r="CK71" s="4" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n"/>
@@ -18424,11 +18500,13 @@
       <c r="AN72" s="4" t="n"/>
       <c r="AO72" s="4" t="n"/>
       <c r="AP72" s="4" t="n"/>
-      <c r="AQ72" s="4" t="n"/>
-      <c r="AR72" s="4" t="n">
+      <c r="AQ72" s="4" t="n">
+        <v>24.72</v>
+      </c>
+      <c r="AR72" s="4" t="n"/>
+      <c r="AS72" s="4" t="n">
         <v>26.25</v>
       </c>
-      <c r="AS72" s="4" t="n"/>
       <c r="AT72" s="4" t="n"/>
       <c r="AU72" s="4" t="n"/>
       <c r="AV72" s="4" t="n"/>
@@ -18450,10 +18528,10 @@
       <c r="BL72" s="4" t="n"/>
       <c r="BM72" s="4" t="n"/>
       <c r="BN72" s="4" t="n"/>
-      <c r="BO72" s="4" t="n">
+      <c r="BO72" s="4" t="n"/>
+      <c r="BP72" s="4" t="n">
         <v>26.39</v>
       </c>
-      <c r="BP72" s="4" t="n"/>
       <c r="BQ72" s="4" t="n"/>
       <c r="BR72" s="4" t="n"/>
       <c r="BS72" s="4" t="n"/>
@@ -18474,6 +18552,7 @@
       <c r="CH72" s="4" t="n"/>
       <c r="CI72" s="4" t="n"/>
       <c r="CJ72" s="4" t="n"/>
+      <c r="CK72" s="4" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -18533,10 +18612,10 @@
       <c r="AO73" s="4" t="n"/>
       <c r="AP73" s="4" t="n"/>
       <c r="AQ73" s="4" t="n"/>
-      <c r="AR73" s="4" t="n">
+      <c r="AR73" s="4" t="n"/>
+      <c r="AS73" s="4" t="n">
         <v>19.5</v>
       </c>
-      <c r="AS73" s="4" t="n"/>
       <c r="AT73" s="4" t="n"/>
       <c r="AU73" s="4" t="n"/>
       <c r="AV73" s="4" t="n"/>
@@ -18549,10 +18628,10 @@
       <c r="BC73" s="4" t="n"/>
       <c r="BD73" s="4" t="n"/>
       <c r="BE73" s="4" t="n"/>
-      <c r="BF73" s="4" t="n">
+      <c r="BF73" s="4" t="n"/>
+      <c r="BG73" s="4" t="n">
         <v>19.6</v>
       </c>
-      <c r="BG73" s="4" t="n"/>
       <c r="BH73" s="4" t="n"/>
       <c r="BI73" s="4" t="n"/>
       <c r="BJ73" s="4" t="n"/>
@@ -18582,6 +18661,7 @@
       <c r="CH73" s="4" t="n"/>
       <c r="CI73" s="4" t="n"/>
       <c r="CJ73" s="4" t="n"/>
+      <c r="CK73" s="4" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="n"/>
@@ -18686,6 +18766,7 @@
       <c r="CH74" s="4" t="n"/>
       <c r="CI74" s="4" t="n"/>
       <c r="CJ74" s="4" t="n"/>
+      <c r="CK74" s="4" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n"/>
@@ -18752,10 +18833,10 @@
       <c r="AP75" s="4" t="n"/>
       <c r="AQ75" s="4" t="n"/>
       <c r="AR75" s="4" t="n"/>
-      <c r="AS75" s="4" t="n">
+      <c r="AS75" s="4" t="n"/>
+      <c r="AT75" s="4" t="n">
         <v>27.5</v>
       </c>
-      <c r="AT75" s="4" t="n"/>
       <c r="AU75" s="4" t="n"/>
       <c r="AV75" s="4" t="n"/>
       <c r="AW75" s="4" t="n"/>
@@ -18798,6 +18879,7 @@
       <c r="CH75" s="4" t="n"/>
       <c r="CI75" s="4" t="n"/>
       <c r="CJ75" s="4" t="n"/>
+      <c r="CK75" s="4" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="n"/>
@@ -18849,10 +18931,10 @@
       <c r="AO76" s="4" t="n"/>
       <c r="AP76" s="4" t="n"/>
       <c r="AQ76" s="4" t="n"/>
-      <c r="AR76" s="4" t="n">
+      <c r="AR76" s="4" t="n"/>
+      <c r="AS76" s="4" t="n">
         <v>17.4</v>
       </c>
-      <c r="AS76" s="4" t="n"/>
       <c r="AT76" s="4" t="n"/>
       <c r="AU76" s="4" t="n"/>
       <c r="AV76" s="4" t="n"/>
@@ -18864,13 +18946,13 @@
       <c r="BB76" s="4" t="n"/>
       <c r="BC76" s="4" t="n"/>
       <c r="BD76" s="4" t="n"/>
-      <c r="BE76" s="4" t="n">
+      <c r="BE76" s="4" t="n"/>
+      <c r="BF76" s="4" t="n">
         <v>17.29</v>
       </c>
-      <c r="BF76" s="4" t="n">
+      <c r="BG76" s="4" t="n">
         <v>17.45</v>
       </c>
-      <c r="BG76" s="4" t="n"/>
       <c r="BH76" s="4" t="n"/>
       <c r="BI76" s="4" t="n"/>
       <c r="BJ76" s="4" t="n"/>
@@ -18900,6 +18982,7 @@
       <c r="CH76" s="4" t="n"/>
       <c r="CI76" s="4" t="n"/>
       <c r="CJ76" s="4" t="n"/>
+      <c r="CK76" s="4" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -19004,6 +19087,7 @@
       <c r="CH77" s="4" t="n"/>
       <c r="CI77" s="4" t="n"/>
       <c r="CJ77" s="4" t="n"/>
+      <c r="CK77" s="4" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="n"/>
@@ -19110,6 +19194,7 @@
       <c r="CH78" s="4" t="n"/>
       <c r="CI78" s="4" t="n"/>
       <c r="CJ78" s="4" t="n"/>
+      <c r="CK78" s="4" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n"/>
@@ -19220,6 +19305,7 @@
       <c r="CH79" s="4" t="n"/>
       <c r="CI79" s="4" t="n"/>
       <c r="CJ79" s="4" t="n"/>
+      <c r="CK79" s="4" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="n"/>
@@ -19320,6 +19406,7 @@
       <c r="CH80" s="4" t="n"/>
       <c r="CI80" s="4" t="n"/>
       <c r="CJ80" s="4" t="n"/>
+      <c r="CK80" s="4" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
@@ -19432,6 +19519,7 @@
       <c r="CH81" s="4" t="n"/>
       <c r="CI81" s="4" t="n"/>
       <c r="CJ81" s="4" t="n"/>
+      <c r="CK81" s="4" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="n"/>
@@ -19534,6 +19622,7 @@
       <c r="CH82" s="4" t="n"/>
       <c r="CI82" s="4" t="n"/>
       <c r="CJ82" s="4" t="n"/>
+      <c r="CK82" s="4" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n"/>
@@ -19640,6 +19729,7 @@
       <c r="CH83" s="4" t="n"/>
       <c r="CI83" s="4" t="n"/>
       <c r="CJ83" s="4" t="n"/>
+      <c r="CK83" s="4" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="n"/>
@@ -19654,7 +19744,9 @@
       <c r="F84" s="4" t="n"/>
       <c r="G84" s="4" t="n"/>
       <c r="H84" s="4" t="n"/>
-      <c r="I84" s="4" t="n"/>
+      <c r="I84" s="4" t="n">
+        <v>25.88</v>
+      </c>
       <c r="J84" s="4" t="n">
         <v>26.69</v>
       </c>
@@ -19733,10 +19825,10 @@
       <c r="BI84" s="4" t="n"/>
       <c r="BJ84" s="4" t="n"/>
       <c r="BK84" s="4" t="n"/>
-      <c r="BL84" s="4" t="n">
+      <c r="BL84" s="4" t="n"/>
+      <c r="BM84" s="4" t="n">
         <v>26.29</v>
       </c>
-      <c r="BM84" s="4" t="n"/>
       <c r="BN84" s="4" t="n"/>
       <c r="BO84" s="4" t="n"/>
       <c r="BP84" s="4" t="n"/>
@@ -19760,9 +19852,10 @@
       <c r="CH84" s="4" t="n"/>
       <c r="CI84" s="4" t="n"/>
       <c r="CJ84" s="4" t="n"/>
+      <c r="CK84" s="4" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:CJ84"/>
+  <autoFilter ref="A1:CK84"/>
   <mergeCells count="21">
     <mergeCell ref="A61:A64"/>
     <mergeCell ref="A69:A72"/>
@@ -19796,7 +19889,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ84"/>
+  <dimension ref="A1:CK84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -19887,6 +19980,7 @@
     <col width="7.5" customWidth="1" min="86" max="86"/>
     <col width="7.5" customWidth="1" min="87" max="87"/>
     <col width="7.5" customWidth="1" min="88" max="88"/>
+    <col width="7.5" customWidth="1" min="89" max="89"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20102,230 +20196,235 @@
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
+          <t>爱音★5</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
           <t>爱音★6</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>万达★6</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>狼崽★5</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>大超★1</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>大超★3</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>大超★6</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>速尾★4</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>速尾★6</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>300+★6</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>莫斯勒★1</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>莫斯勒★3</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>莫斯勒★6</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>肥龙★3</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>肥龙★6</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>sf90★6</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>sgt★6</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>火山★5</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>猫头鹰★6</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>秋王★6</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>塞纳★6</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>无敌牛★5</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>风龙★6</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>冬王★6</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>小牛★6</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>fe3★5</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>499p★6</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>法拉第★6</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>六子★6</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>霓虹gtr★6</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>ps龙★6</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>ts900★6</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>att★6</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>风扇★5</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>保时捷919★6</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>650s★6</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>英灵殿★6</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>600lt★5</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>5n★4</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>c1★6</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>gtr50★5</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>urs★6</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>复仇★6</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>狼王★6</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>纳兰★6</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>自燃★6</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>西安★6</t>
         </is>
@@ -20410,17 +20509,17 @@
       </c>
       <c r="AO2" s="4" t="n"/>
       <c r="AP2" s="4" t="n"/>
-      <c r="AQ2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AQ2" s="4" t="n"/>
       <c r="AR2" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AS2" s="4" t="n"/>
+      <c r="AS2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT2" s="4" t="n"/>
       <c r="AU2" s="4" t="n"/>
       <c r="AV2" s="4" t="n"/>
@@ -20432,24 +20531,24 @@
       <c r="BB2" s="4" t="n"/>
       <c r="BC2" s="4" t="n"/>
       <c r="BD2" s="4" t="n"/>
-      <c r="BE2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BE2" s="4" t="n"/>
       <c r="BF2" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BG2" s="4" t="n"/>
+      <c r="BG2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BH2" s="4" t="n"/>
-      <c r="BI2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BJ2" s="4" t="n"/>
+      <c r="BI2" s="4" t="n"/>
+      <c r="BJ2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BK2" s="4" t="n"/>
       <c r="BL2" s="4" t="n"/>
       <c r="BM2" s="4" t="n"/>
@@ -20476,6 +20575,7 @@
       <c r="CH2" s="4" t="n"/>
       <c r="CI2" s="4" t="n"/>
       <c r="CJ2" s="4" t="n"/>
+      <c r="CK2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n"/>
@@ -20556,44 +20656,44 @@
         </is>
       </c>
       <c r="AP3" s="4" t="n"/>
-      <c r="AQ3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR3" s="4" t="n"/>
-      <c r="AS3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT3" s="4" t="n"/>
+      <c r="AQ3" s="4" t="n"/>
+      <c r="AR3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS3" s="4" t="n"/>
+      <c r="AT3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU3" s="4" t="n"/>
       <c r="AV3" s="4" t="n"/>
       <c r="AW3" s="4" t="n"/>
-      <c r="AX3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AY3" s="4" t="n"/>
+      <c r="AX3" s="4" t="n"/>
+      <c r="AY3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ3" s="4" t="n"/>
       <c r="BA3" s="4" t="n"/>
       <c r="BB3" s="4" t="n"/>
       <c r="BC3" s="4" t="n"/>
-      <c r="BD3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BE3" s="4" t="n"/>
+      <c r="BD3" s="4" t="n"/>
+      <c r="BE3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BF3" s="4" t="n"/>
-      <c r="BG3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH3" s="4" t="n"/>
+      <c r="BG3" s="4" t="n"/>
+      <c r="BH3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI3" s="4" t="n"/>
       <c r="BJ3" s="4" t="n"/>
       <c r="BK3" s="4" t="n"/>
@@ -20621,7 +20721,8 @@
       <c r="CG3" s="4" t="n"/>
       <c r="CH3" s="4" t="n"/>
       <c r="CI3" s="4" t="n"/>
-      <c r="CJ3" s="4" t="inlineStr">
+      <c r="CJ3" s="4" t="n"/>
+      <c r="CK3" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -20694,18 +20795,18 @@
       <c r="AN4" s="4" t="n"/>
       <c r="AO4" s="4" t="n"/>
       <c r="AP4" s="4" t="n"/>
-      <c r="AQ4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR4" s="4" t="n"/>
-      <c r="AS4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT4" s="4" t="n"/>
+      <c r="AQ4" s="4" t="n"/>
+      <c r="AR4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS4" s="4" t="n"/>
+      <c r="AT4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU4" s="4" t="n"/>
       <c r="AV4" s="4" t="n"/>
       <c r="AW4" s="4" t="n"/>
@@ -20718,12 +20819,12 @@
       <c r="BD4" s="4" t="n"/>
       <c r="BE4" s="4" t="n"/>
       <c r="BF4" s="4" t="n"/>
-      <c r="BG4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH4" s="4" t="n"/>
+      <c r="BG4" s="4" t="n"/>
+      <c r="BH4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI4" s="4" t="n"/>
       <c r="BJ4" s="4" t="n"/>
       <c r="BK4" s="4" t="n"/>
@@ -20747,15 +20848,16 @@
       <c r="CC4" s="4" t="n"/>
       <c r="CD4" s="4" t="n"/>
       <c r="CE4" s="4" t="n"/>
-      <c r="CF4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CG4" s="4" t="n"/>
+      <c r="CF4" s="4" t="n"/>
+      <c r="CG4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CH4" s="4" t="n"/>
       <c r="CI4" s="4" t="n"/>
       <c r="CJ4" s="4" t="n"/>
+      <c r="CK4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n"/>
@@ -20844,44 +20946,44 @@
       </c>
       <c r="AO5" s="4" t="n"/>
       <c r="AP5" s="4" t="n"/>
-      <c r="AQ5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR5" s="4" t="n"/>
+      <c r="AQ5" s="4" t="n"/>
+      <c r="AR5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS5" s="4" t="n"/>
       <c r="AT5" s="4" t="n"/>
       <c r="AU5" s="4" t="n"/>
       <c r="AV5" s="4" t="n"/>
       <c r="AW5" s="4" t="n"/>
-      <c r="AX5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AY5" s="4" t="n"/>
+      <c r="AX5" s="4" t="n"/>
+      <c r="AY5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ5" s="4" t="n"/>
       <c r="BA5" s="4" t="n"/>
       <c r="BB5" s="4" t="n"/>
       <c r="BC5" s="4" t="n"/>
-      <c r="BD5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BD5" s="4" t="n"/>
       <c r="BE5" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BF5" s="4" t="n"/>
-      <c r="BG5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH5" s="4" t="n"/>
+      <c r="BF5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BG5" s="4" t="n"/>
+      <c r="BH5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI5" s="4" t="n"/>
       <c r="BJ5" s="4" t="n"/>
       <c r="BK5" s="4" t="n"/>
@@ -20907,13 +21009,14 @@
       <c r="CE5" s="4" t="n"/>
       <c r="CF5" s="4" t="n"/>
       <c r="CG5" s="4" t="n"/>
-      <c r="CH5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CI5" s="4" t="n"/>
+      <c r="CH5" s="4" t="n"/>
+      <c r="CI5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CJ5" s="4" t="n"/>
+      <c r="CK5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -20987,12 +21090,12 @@
       <c r="AO6" s="4" t="n"/>
       <c r="AP6" s="4" t="n"/>
       <c r="AQ6" s="4" t="n"/>
-      <c r="AR6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS6" s="4" t="n"/>
+      <c r="AR6" s="4" t="n"/>
+      <c r="AS6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT6" s="4" t="n"/>
       <c r="AU6" s="4" t="n"/>
       <c r="AV6" s="4" t="n"/>
@@ -21005,50 +21108,50 @@
       <c r="BC6" s="4" t="n"/>
       <c r="BD6" s="4" t="n"/>
       <c r="BE6" s="4" t="n"/>
-      <c r="BF6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BG6" s="4" t="n"/>
+      <c r="BF6" s="4" t="n"/>
+      <c r="BG6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BH6" s="4" t="n"/>
-      <c r="BI6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BJ6" s="4" t="n"/>
+      <c r="BI6" s="4" t="n"/>
+      <c r="BJ6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BK6" s="4" t="n"/>
       <c r="BL6" s="4" t="n"/>
       <c r="BM6" s="4" t="n"/>
-      <c r="BN6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BO6" s="4" t="n"/>
+      <c r="BN6" s="4" t="n"/>
+      <c r="BO6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BP6" s="4" t="n"/>
       <c r="BQ6" s="4" t="n"/>
       <c r="BR6" s="4" t="n"/>
       <c r="BS6" s="4" t="n"/>
-      <c r="BT6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BU6" s="4" t="n"/>
+      <c r="BT6" s="4" t="n"/>
+      <c r="BU6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BV6" s="4" t="n"/>
       <c r="BW6" s="4" t="n"/>
       <c r="BX6" s="4" t="n"/>
       <c r="BY6" s="4" t="n"/>
       <c r="BZ6" s="4" t="n"/>
       <c r="CA6" s="4" t="n"/>
-      <c r="CB6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CC6" s="4" t="n"/>
+      <c r="CB6" s="4" t="n"/>
+      <c r="CC6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CD6" s="4" t="n"/>
       <c r="CE6" s="4" t="n"/>
       <c r="CF6" s="4" t="n"/>
@@ -21056,6 +21159,7 @@
       <c r="CH6" s="4" t="n"/>
       <c r="CI6" s="4" t="n"/>
       <c r="CJ6" s="4" t="n"/>
+      <c r="CK6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
@@ -21148,18 +21252,18 @@
       </c>
       <c r="AO7" s="4" t="n"/>
       <c r="AP7" s="4" t="n"/>
-      <c r="AQ7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR7" s="4" t="n"/>
-      <c r="AS7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT7" s="4" t="n"/>
+      <c r="AQ7" s="4" t="n"/>
+      <c r="AR7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS7" s="4" t="n"/>
+      <c r="AT7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU7" s="4" t="n"/>
       <c r="AV7" s="4" t="n"/>
       <c r="AW7" s="4" t="n"/>
@@ -21171,17 +21275,17 @@
       <c r="BC7" s="4" t="n"/>
       <c r="BD7" s="4" t="n"/>
       <c r="BE7" s="4" t="n"/>
-      <c r="BF7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BF7" s="4" t="n"/>
       <c r="BG7" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BH7" s="4" t="n"/>
+      <c r="BH7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI7" s="4" t="n"/>
       <c r="BJ7" s="4" t="n"/>
       <c r="BK7" s="4" t="n"/>
@@ -21210,6 +21314,7 @@
       <c r="CH7" s="4" t="n"/>
       <c r="CI7" s="4" t="n"/>
       <c r="CJ7" s="4" t="n"/>
+      <c r="CK7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
@@ -21326,44 +21431,44 @@
       <c r="AN8" s="4" t="n"/>
       <c r="AO8" s="4" t="n"/>
       <c r="AP8" s="4" t="n"/>
-      <c r="AQ8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR8" s="4" t="n"/>
-      <c r="AS8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT8" s="4" t="n"/>
+      <c r="AQ8" s="4" t="n"/>
+      <c r="AR8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS8" s="4" t="n"/>
+      <c r="AT8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU8" s="4" t="n"/>
       <c r="AV8" s="4" t="n"/>
       <c r="AW8" s="4" t="n"/>
-      <c r="AX8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AY8" s="4" t="n"/>
-      <c r="AZ8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA8" s="4" t="n"/>
+      <c r="AX8" s="4" t="n"/>
+      <c r="AY8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AZ8" s="4" t="n"/>
+      <c r="BA8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB8" s="4" t="n"/>
       <c r="BC8" s="4" t="n"/>
       <c r="BD8" s="4" t="n"/>
       <c r="BE8" s="4" t="n"/>
       <c r="BF8" s="4" t="n"/>
-      <c r="BG8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH8" s="4" t="n"/>
+      <c r="BG8" s="4" t="n"/>
+      <c r="BH8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI8" s="4" t="n"/>
       <c r="BJ8" s="4" t="n"/>
       <c r="BK8" s="4" t="n"/>
@@ -21387,15 +21492,16 @@
       <c r="CC8" s="4" t="n"/>
       <c r="CD8" s="4" t="n"/>
       <c r="CE8" s="4" t="n"/>
-      <c r="CF8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CG8" s="4" t="n"/>
+      <c r="CF8" s="4" t="n"/>
+      <c r="CG8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CH8" s="4" t="n"/>
       <c r="CI8" s="4" t="n"/>
       <c r="CJ8" s="4" t="n"/>
+      <c r="CK8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n"/>
@@ -21476,44 +21582,44 @@
       </c>
       <c r="AO9" s="4" t="n"/>
       <c r="AP9" s="4" t="n"/>
-      <c r="AQ9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR9" s="4" t="n"/>
+      <c r="AQ9" s="4" t="n"/>
+      <c r="AR9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS9" s="4" t="n"/>
       <c r="AT9" s="4" t="n"/>
       <c r="AU9" s="4" t="n"/>
       <c r="AV9" s="4" t="n"/>
-      <c r="AW9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AX9" s="4" t="n"/>
+      <c r="AW9" s="4" t="n"/>
+      <c r="AX9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AY9" s="4" t="n"/>
       <c r="AZ9" s="4" t="n"/>
       <c r="BA9" s="4" t="n"/>
       <c r="BB9" s="4" t="n"/>
       <c r="BC9" s="4" t="n"/>
-      <c r="BD9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BE9" s="4" t="n"/>
-      <c r="BF9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BD9" s="4" t="n"/>
+      <c r="BE9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BF9" s="4" t="n"/>
       <c r="BG9" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BH9" s="4" t="n"/>
+      <c r="BH9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI9" s="4" t="n"/>
       <c r="BJ9" s="4" t="n"/>
       <c r="BK9" s="4" t="n"/>
@@ -21522,42 +21628,43 @@
       <c r="BN9" s="4" t="n"/>
       <c r="BO9" s="4" t="n"/>
       <c r="BP9" s="4" t="n"/>
-      <c r="BQ9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BR9" s="4" t="n"/>
+      <c r="BQ9" s="4" t="n"/>
+      <c r="BR9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BS9" s="4" t="n"/>
-      <c r="BT9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BU9" s="4" t="n"/>
+      <c r="BT9" s="4" t="n"/>
+      <c r="BU9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BV9" s="4" t="n"/>
       <c r="BW9" s="4" t="n"/>
       <c r="BX9" s="4" t="n"/>
       <c r="BY9" s="4" t="n"/>
       <c r="BZ9" s="4" t="n"/>
       <c r="CA9" s="4" t="n"/>
-      <c r="CB9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CC9" s="4" t="n"/>
+      <c r="CB9" s="4" t="n"/>
+      <c r="CC9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CD9" s="4" t="n"/>
       <c r="CE9" s="4" t="n"/>
       <c r="CF9" s="4" t="n"/>
       <c r="CG9" s="4" t="n"/>
-      <c r="CH9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CI9" s="4" t="n"/>
+      <c r="CH9" s="4" t="n"/>
+      <c r="CI9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CJ9" s="4" t="n"/>
+      <c r="CK9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -21650,17 +21757,17 @@
       </c>
       <c r="AO10" s="4" t="n"/>
       <c r="AP10" s="4" t="n"/>
-      <c r="AQ10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AQ10" s="4" t="n"/>
       <c r="AR10" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AS10" s="4" t="n"/>
+      <c r="AS10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT10" s="4" t="n"/>
       <c r="AU10" s="4" t="n"/>
       <c r="AV10" s="4" t="n"/>
@@ -21672,37 +21779,37 @@
       <c r="BB10" s="4" t="n"/>
       <c r="BC10" s="4" t="n"/>
       <c r="BD10" s="4" t="n"/>
-      <c r="BE10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BF10" s="4" t="n"/>
+      <c r="BE10" s="4" t="n"/>
+      <c r="BF10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BG10" s="4" t="n"/>
       <c r="BH10" s="4" t="n"/>
-      <c r="BI10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BJ10" s="4" t="n"/>
+      <c r="BI10" s="4" t="n"/>
+      <c r="BJ10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BK10" s="4" t="n"/>
       <c r="BL10" s="4" t="n"/>
       <c r="BM10" s="4" t="n"/>
       <c r="BN10" s="4" t="n"/>
       <c r="BO10" s="4" t="n"/>
       <c r="BP10" s="4" t="n"/>
-      <c r="BQ10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BQ10" s="4" t="n"/>
       <c r="BR10" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BS10" s="4" t="n"/>
+      <c r="BS10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BT10" s="4" t="n"/>
       <c r="BU10" s="4" t="n"/>
       <c r="BV10" s="4" t="n"/>
@@ -21720,6 +21827,7 @@
       <c r="CH10" s="4" t="n"/>
       <c r="CI10" s="4" t="n"/>
       <c r="CJ10" s="4" t="n"/>
+      <c r="CK10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
@@ -21812,44 +21920,44 @@
       <c r="AN11" s="4" t="n"/>
       <c r="AO11" s="4" t="n"/>
       <c r="AP11" s="4" t="n"/>
-      <c r="AQ11" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR11" s="4" t="n"/>
-      <c r="AS11" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT11" s="4" t="n"/>
+      <c r="AQ11" s="4" t="n"/>
+      <c r="AR11" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS11" s="4" t="n"/>
+      <c r="AT11" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU11" s="4" t="n"/>
       <c r="AV11" s="4" t="n"/>
       <c r="AW11" s="4" t="n"/>
       <c r="AX11" s="4" t="n"/>
-      <c r="AY11" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AY11" s="4" t="n"/>
       <c r="AZ11" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BA11" s="4" t="n"/>
+      <c r="BA11" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB11" s="4" t="n"/>
       <c r="BC11" s="4" t="n"/>
       <c r="BD11" s="4" t="n"/>
       <c r="BE11" s="4" t="n"/>
       <c r="BF11" s="4" t="n"/>
-      <c r="BG11" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH11" s="4" t="n"/>
+      <c r="BG11" s="4" t="n"/>
+      <c r="BH11" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI11" s="4" t="n"/>
       <c r="BJ11" s="4" t="n"/>
       <c r="BK11" s="4" t="n"/>
@@ -21878,6 +21986,7 @@
       <c r="CH11" s="4" t="n"/>
       <c r="CI11" s="4" t="n"/>
       <c r="CJ11" s="4" t="n"/>
+      <c r="CK11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
@@ -21968,38 +22077,38 @@
       <c r="AP12" s="4" t="n"/>
       <c r="AQ12" s="4" t="n"/>
       <c r="AR12" s="4" t="n"/>
-      <c r="AS12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT12" s="4" t="n"/>
+      <c r="AS12" s="4" t="n"/>
+      <c r="AT12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU12" s="4" t="n"/>
       <c r="AV12" s="4" t="n"/>
       <c r="AW12" s="4" t="n"/>
-      <c r="AX12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AY12" s="4" t="n"/>
+      <c r="AX12" s="4" t="n"/>
+      <c r="AY12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ12" s="4" t="n"/>
       <c r="BA12" s="4" t="n"/>
       <c r="BB12" s="4" t="n"/>
       <c r="BC12" s="4" t="n"/>
-      <c r="BD12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BE12" s="4" t="n"/>
+      <c r="BD12" s="4" t="n"/>
+      <c r="BE12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BF12" s="4" t="n"/>
-      <c r="BG12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH12" s="4" t="n"/>
+      <c r="BG12" s="4" t="n"/>
+      <c r="BH12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI12" s="4" t="n"/>
       <c r="BJ12" s="4" t="n"/>
       <c r="BK12" s="4" t="n"/>
@@ -22009,12 +22118,12 @@
       <c r="BO12" s="4" t="n"/>
       <c r="BP12" s="4" t="n"/>
       <c r="BQ12" s="4" t="n"/>
-      <c r="BR12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BS12" s="4" t="n"/>
+      <c r="BR12" s="4" t="n"/>
+      <c r="BS12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BT12" s="4" t="n"/>
       <c r="BU12" s="4" t="n"/>
       <c r="BV12" s="4" t="n"/>
@@ -22029,13 +22138,14 @@
       <c r="CE12" s="4" t="n"/>
       <c r="CF12" s="4" t="n"/>
       <c r="CG12" s="4" t="n"/>
-      <c r="CH12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CI12" s="4" t="n"/>
+      <c r="CH12" s="4" t="n"/>
+      <c r="CI12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CJ12" s="4" t="n"/>
+      <c r="CK12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
@@ -22120,40 +22230,40 @@
       <c r="AN13" s="4" t="n"/>
       <c r="AO13" s="4" t="n"/>
       <c r="AP13" s="4" t="n"/>
-      <c r="AQ13" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR13" s="4" t="n"/>
-      <c r="AS13" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT13" s="4" t="n"/>
+      <c r="AQ13" s="4" t="n"/>
+      <c r="AR13" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS13" s="4" t="n"/>
+      <c r="AT13" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU13" s="4" t="n"/>
       <c r="AV13" s="4" t="n"/>
       <c r="AW13" s="4" t="n"/>
       <c r="AX13" s="4" t="n"/>
-      <c r="AY13" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AZ13" s="4" t="n"/>
+      <c r="AY13" s="4" t="n"/>
+      <c r="AZ13" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BA13" s="4" t="n"/>
       <c r="BB13" s="4" t="n"/>
       <c r="BC13" s="4" t="n"/>
       <c r="BD13" s="4" t="n"/>
       <c r="BE13" s="4" t="n"/>
       <c r="BF13" s="4" t="n"/>
-      <c r="BG13" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH13" s="4" t="n"/>
+      <c r="BG13" s="4" t="n"/>
+      <c r="BH13" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI13" s="4" t="n"/>
       <c r="BJ13" s="4" t="n"/>
       <c r="BK13" s="4" t="n"/>
@@ -22182,6 +22292,7 @@
       <c r="CH13" s="4" t="n"/>
       <c r="CI13" s="4" t="n"/>
       <c r="CJ13" s="4" t="n"/>
+      <c r="CK13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -22286,18 +22397,18 @@
       <c r="AN14" s="4" t="n"/>
       <c r="AO14" s="4" t="n"/>
       <c r="AP14" s="4" t="n"/>
-      <c r="AQ14" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR14" s="4" t="n"/>
-      <c r="AS14" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT14" s="4" t="n"/>
+      <c r="AQ14" s="4" t="n"/>
+      <c r="AR14" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS14" s="4" t="n"/>
+      <c r="AT14" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU14" s="4" t="n"/>
       <c r="AV14" s="4" t="n"/>
       <c r="AW14" s="4" t="n"/>
@@ -22310,12 +22421,12 @@
       <c r="BD14" s="4" t="n"/>
       <c r="BE14" s="4" t="n"/>
       <c r="BF14" s="4" t="n"/>
-      <c r="BG14" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH14" s="4" t="n"/>
+      <c r="BG14" s="4" t="n"/>
+      <c r="BH14" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI14" s="4" t="n"/>
       <c r="BJ14" s="4" t="n"/>
       <c r="BK14" s="4" t="n"/>
@@ -22344,6 +22455,7 @@
       <c r="CH14" s="4" t="n"/>
       <c r="CI14" s="4" t="n"/>
       <c r="CJ14" s="4" t="n"/>
+      <c r="CK14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
@@ -22440,55 +22552,55 @@
       <c r="AN15" s="4" t="n"/>
       <c r="AO15" s="4" t="n"/>
       <c r="AP15" s="4" t="n"/>
-      <c r="AQ15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR15" s="4" t="n"/>
-      <c r="AS15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT15" s="4" t="n"/>
+      <c r="AQ15" s="4" t="n"/>
+      <c r="AR15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS15" s="4" t="n"/>
+      <c r="AT15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU15" s="4" t="n"/>
       <c r="AV15" s="4" t="n"/>
       <c r="AW15" s="4" t="n"/>
-      <c r="AX15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AY15" s="4" t="n"/>
+      <c r="AX15" s="4" t="n"/>
+      <c r="AY15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ15" s="4" t="n"/>
       <c r="BA15" s="4" t="n"/>
       <c r="BB15" s="4" t="n"/>
       <c r="BC15" s="4" t="n"/>
-      <c r="BD15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BD15" s="4" t="n"/>
       <c r="BE15" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BF15" s="4" t="n"/>
-      <c r="BG15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH15" s="4" t="n"/>
+      <c r="BF15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BG15" s="4" t="n"/>
+      <c r="BH15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI15" s="4" t="n"/>
-      <c r="BJ15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BK15" s="4" t="n"/>
+      <c r="BJ15" s="4" t="n"/>
+      <c r="BK15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BL15" s="4" t="n"/>
       <c r="BM15" s="4" t="n"/>
       <c r="BN15" s="4" t="n"/>
@@ -22514,6 +22626,7 @@
       <c r="CH15" s="4" t="n"/>
       <c r="CI15" s="4" t="n"/>
       <c r="CJ15" s="4" t="n"/>
+      <c r="CK15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
@@ -22610,18 +22723,18 @@
       <c r="AN16" s="4" t="n"/>
       <c r="AO16" s="4" t="n"/>
       <c r="AP16" s="4" t="n"/>
-      <c r="AQ16" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR16" s="4" t="n"/>
-      <c r="AS16" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT16" s="4" t="n"/>
+      <c r="AQ16" s="4" t="n"/>
+      <c r="AR16" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS16" s="4" t="n"/>
+      <c r="AT16" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU16" s="4" t="n"/>
       <c r="AV16" s="4" t="n"/>
       <c r="AW16" s="4" t="n"/>
@@ -22634,12 +22747,12 @@
       <c r="BD16" s="4" t="n"/>
       <c r="BE16" s="4" t="n"/>
       <c r="BF16" s="4" t="n"/>
-      <c r="BG16" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH16" s="4" t="n"/>
+      <c r="BG16" s="4" t="n"/>
+      <c r="BH16" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI16" s="4" t="n"/>
       <c r="BJ16" s="4" t="n"/>
       <c r="BK16" s="4" t="n"/>
@@ -22668,6 +22781,7 @@
       <c r="CH16" s="4" t="n"/>
       <c r="CI16" s="4" t="n"/>
       <c r="CJ16" s="4" t="n"/>
+      <c r="CK16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
@@ -22760,18 +22874,18 @@
       </c>
       <c r="AO17" s="4" t="n"/>
       <c r="AP17" s="4" t="n"/>
-      <c r="AQ17" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR17" s="4" t="n"/>
-      <c r="AS17" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT17" s="4" t="n"/>
+      <c r="AQ17" s="4" t="n"/>
+      <c r="AR17" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS17" s="4" t="n"/>
+      <c r="AT17" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU17" s="4" t="n"/>
       <c r="AV17" s="4" t="n"/>
       <c r="AW17" s="4" t="n"/>
@@ -22784,12 +22898,12 @@
       <c r="BD17" s="4" t="n"/>
       <c r="BE17" s="4" t="n"/>
       <c r="BF17" s="4" t="n"/>
-      <c r="BG17" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH17" s="4" t="n"/>
+      <c r="BG17" s="4" t="n"/>
+      <c r="BH17" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI17" s="4" t="n"/>
       <c r="BJ17" s="4" t="n"/>
       <c r="BK17" s="4" t="n"/>
@@ -22818,6 +22932,7 @@
       <c r="CH17" s="4" t="n"/>
       <c r="CI17" s="4" t="n"/>
       <c r="CJ17" s="4" t="n"/>
+      <c r="CK17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -22908,46 +23023,46 @@
       <c r="AP18" s="4" t="n"/>
       <c r="AQ18" s="4" t="n"/>
       <c r="AR18" s="4" t="n"/>
-      <c r="AS18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT18" s="4" t="n"/>
+      <c r="AS18" s="4" t="n"/>
+      <c r="AT18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU18" s="4" t="n"/>
       <c r="AV18" s="4" t="n"/>
-      <c r="AW18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AW18" s="4" t="n"/>
       <c r="AX18" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AY18" s="4" t="n"/>
+      <c r="AY18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ18" s="4" t="n"/>
       <c r="BA18" s="4" t="n"/>
       <c r="BB18" s="4" t="n"/>
-      <c r="BC18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BC18" s="4" t="n"/>
       <c r="BD18" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BE18" s="4" t="n"/>
+      <c r="BE18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BF18" s="4" t="n"/>
-      <c r="BG18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH18" s="4" t="n"/>
+      <c r="BG18" s="4" t="n"/>
+      <c r="BH18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI18" s="4" t="n"/>
       <c r="BJ18" s="4" t="n"/>
       <c r="BK18" s="4" t="n"/>
@@ -22956,17 +23071,17 @@
       <c r="BN18" s="4" t="n"/>
       <c r="BO18" s="4" t="n"/>
       <c r="BP18" s="4" t="n"/>
-      <c r="BQ18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BQ18" s="4" t="n"/>
       <c r="BR18" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BS18" s="4" t="n"/>
+      <c r="BS18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BT18" s="4" t="n"/>
       <c r="BU18" s="4" t="n"/>
       <c r="BV18" s="4" t="n"/>
@@ -22981,13 +23096,14 @@
       <c r="CE18" s="4" t="n"/>
       <c r="CF18" s="4" t="n"/>
       <c r="CG18" s="4" t="n"/>
-      <c r="CH18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CI18" s="4" t="n"/>
+      <c r="CH18" s="4" t="n"/>
+      <c r="CI18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CJ18" s="4" t="n"/>
+      <c r="CK18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
@@ -23072,51 +23188,51 @@
       </c>
       <c r="AO19" s="4" t="n"/>
       <c r="AP19" s="4" t="n"/>
-      <c r="AQ19" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR19" s="4" t="n"/>
-      <c r="AS19" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT19" s="4" t="n"/>
+      <c r="AQ19" s="4" t="n"/>
+      <c r="AR19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS19" s="4" t="n"/>
+      <c r="AT19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU19" s="4" t="n"/>
       <c r="AV19" s="4" t="n"/>
       <c r="AW19" s="4" t="n"/>
-      <c r="AX19" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AY19" s="4" t="n"/>
+      <c r="AX19" s="4" t="n"/>
+      <c r="AY19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ19" s="4" t="n"/>
       <c r="BA19" s="4" t="n"/>
       <c r="BB19" s="4" t="n"/>
       <c r="BC19" s="4" t="n"/>
       <c r="BD19" s="4" t="n"/>
-      <c r="BE19" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BF19" s="4" t="n"/>
-      <c r="BG19" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH19" s="4" t="n"/>
+      <c r="BE19" s="4" t="n"/>
+      <c r="BF19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BG19" s="4" t="n"/>
+      <c r="BH19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI19" s="4" t="n"/>
-      <c r="BJ19" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BK19" s="4" t="n"/>
+      <c r="BJ19" s="4" t="n"/>
+      <c r="BK19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BL19" s="4" t="n"/>
       <c r="BM19" s="4" t="n"/>
       <c r="BN19" s="4" t="n"/>
@@ -23139,17 +23255,18 @@
       <c r="CE19" s="4" t="n"/>
       <c r="CF19" s="4" t="n"/>
       <c r="CG19" s="4" t="n"/>
-      <c r="CH19" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="CH19" s="4" t="n"/>
       <c r="CI19" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
       <c r="CJ19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CK19" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -23230,17 +23347,17 @@
       </c>
       <c r="AO20" s="4" t="n"/>
       <c r="AP20" s="4" t="n"/>
-      <c r="AQ20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AQ20" s="4" t="n"/>
       <c r="AR20" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AS20" s="4" t="n"/>
+      <c r="AS20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT20" s="4" t="n"/>
       <c r="AU20" s="4" t="n"/>
       <c r="AV20" s="4" t="n"/>
@@ -23252,26 +23369,26 @@
       <c r="BB20" s="4" t="n"/>
       <c r="BC20" s="4" t="n"/>
       <c r="BD20" s="4" t="n"/>
-      <c r="BE20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BF20" s="4" t="n"/>
+      <c r="BE20" s="4" t="n"/>
+      <c r="BF20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BG20" s="4" t="n"/>
       <c r="BH20" s="4" t="n"/>
       <c r="BI20" s="4" t="n"/>
-      <c r="BJ20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BJ20" s="4" t="n"/>
       <c r="BK20" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BL20" s="4" t="n"/>
+      <c r="BL20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BM20" s="4" t="n"/>
       <c r="BN20" s="4" t="n"/>
       <c r="BO20" s="4" t="n"/>
@@ -23287,12 +23404,12 @@
       <c r="BY20" s="4" t="n"/>
       <c r="BZ20" s="4" t="n"/>
       <c r="CA20" s="4" t="n"/>
-      <c r="CB20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CC20" s="4" t="n"/>
+      <c r="CB20" s="4" t="n"/>
+      <c r="CC20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CD20" s="4" t="n"/>
       <c r="CE20" s="4" t="n"/>
       <c r="CF20" s="4" t="n"/>
@@ -23300,6 +23417,7 @@
       <c r="CH20" s="4" t="n"/>
       <c r="CI20" s="4" t="n"/>
       <c r="CJ20" s="4" t="n"/>
+      <c r="CK20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
@@ -23376,18 +23494,18 @@
       <c r="AN21" s="4" t="n"/>
       <c r="AO21" s="4" t="n"/>
       <c r="AP21" s="4" t="n"/>
-      <c r="AQ21" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR21" s="4" t="n"/>
-      <c r="AS21" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT21" s="4" t="n"/>
+      <c r="AQ21" s="4" t="n"/>
+      <c r="AR21" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS21" s="4" t="n"/>
+      <c r="AT21" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU21" s="4" t="n"/>
       <c r="AV21" s="4" t="n"/>
       <c r="AW21" s="4" t="n"/>
@@ -23400,12 +23518,12 @@
       <c r="BD21" s="4" t="n"/>
       <c r="BE21" s="4" t="n"/>
       <c r="BF21" s="4" t="n"/>
-      <c r="BG21" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH21" s="4" t="n"/>
+      <c r="BG21" s="4" t="n"/>
+      <c r="BH21" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI21" s="4" t="n"/>
       <c r="BJ21" s="4" t="n"/>
       <c r="BK21" s="4" t="n"/>
@@ -23419,12 +23537,12 @@
       <c r="BS21" s="4" t="n"/>
       <c r="BT21" s="4" t="n"/>
       <c r="BU21" s="4" t="n"/>
-      <c r="BV21" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BW21" s="4" t="n"/>
+      <c r="BV21" s="4" t="n"/>
+      <c r="BW21" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BX21" s="4" t="n"/>
       <c r="BY21" s="4" t="n"/>
       <c r="BZ21" s="4" t="n"/>
@@ -23438,6 +23556,7 @@
       <c r="CH21" s="4" t="n"/>
       <c r="CI21" s="4" t="n"/>
       <c r="CJ21" s="4" t="n"/>
+      <c r="CK21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -23530,44 +23649,44 @@
       <c r="AN22" s="4" t="n"/>
       <c r="AO22" s="4" t="n"/>
       <c r="AP22" s="4" t="n"/>
-      <c r="AQ22" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR22" s="4" t="n"/>
-      <c r="AS22" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT22" s="4" t="n"/>
+      <c r="AQ22" s="4" t="n"/>
+      <c r="AR22" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS22" s="4" t="n"/>
+      <c r="AT22" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU22" s="4" t="n"/>
-      <c r="AV22" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AW22" s="4" t="n"/>
+      <c r="AV22" s="4" t="n"/>
+      <c r="AW22" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AX22" s="4" t="n"/>
       <c r="AY22" s="4" t="n"/>
       <c r="AZ22" s="4" t="n"/>
       <c r="BA22" s="4" t="n"/>
       <c r="BB22" s="4" t="n"/>
       <c r="BC22" s="4" t="n"/>
-      <c r="BD22" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BE22" s="4" t="n"/>
+      <c r="BD22" s="4" t="n"/>
+      <c r="BE22" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BF22" s="4" t="n"/>
-      <c r="BG22" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH22" s="4" t="n"/>
+      <c r="BG22" s="4" t="n"/>
+      <c r="BH22" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI22" s="4" t="n"/>
       <c r="BJ22" s="4" t="n"/>
       <c r="BK22" s="4" t="n"/>
@@ -23581,12 +23700,12 @@
       <c r="BS22" s="4" t="n"/>
       <c r="BT22" s="4" t="n"/>
       <c r="BU22" s="4" t="n"/>
-      <c r="BV22" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BW22" s="4" t="n"/>
+      <c r="BV22" s="4" t="n"/>
+      <c r="BW22" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BX22" s="4" t="n"/>
       <c r="BY22" s="4" t="n"/>
       <c r="BZ22" s="4" t="n"/>
@@ -23600,6 +23719,7 @@
       <c r="CH22" s="4" t="n"/>
       <c r="CI22" s="4" t="n"/>
       <c r="CJ22" s="4" t="n"/>
+      <c r="CK22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
@@ -23684,27 +23804,27 @@
       <c r="AN23" s="4" t="n"/>
       <c r="AO23" s="4" t="n"/>
       <c r="AP23" s="4" t="n"/>
-      <c r="AQ23" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR23" s="4" t="n"/>
-      <c r="AS23" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT23" s="4" t="n"/>
+      <c r="AQ23" s="4" t="n"/>
+      <c r="AR23" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS23" s="4" t="n"/>
+      <c r="AT23" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU23" s="4" t="n"/>
       <c r="AV23" s="4" t="n"/>
       <c r="AW23" s="4" t="n"/>
-      <c r="AX23" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AY23" s="4" t="n"/>
+      <c r="AX23" s="4" t="n"/>
+      <c r="AY23" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ23" s="4" t="n"/>
       <c r="BA23" s="4" t="n"/>
       <c r="BB23" s="4" t="n"/>
@@ -23712,12 +23832,12 @@
       <c r="BD23" s="4" t="n"/>
       <c r="BE23" s="4" t="n"/>
       <c r="BF23" s="4" t="n"/>
-      <c r="BG23" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH23" s="4" t="n"/>
+      <c r="BG23" s="4" t="n"/>
+      <c r="BH23" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI23" s="4" t="n"/>
       <c r="BJ23" s="4" t="n"/>
       <c r="BK23" s="4" t="n"/>
@@ -23746,6 +23866,7 @@
       <c r="CH23" s="4" t="n"/>
       <c r="CI23" s="4" t="n"/>
       <c r="CJ23" s="4" t="n"/>
+      <c r="CK23" s="4" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
@@ -23822,44 +23943,44 @@
       <c r="AN24" s="4" t="n"/>
       <c r="AO24" s="4" t="n"/>
       <c r="AP24" s="4" t="n"/>
-      <c r="AQ24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR24" s="4" t="n"/>
-      <c r="AS24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT24" s="4" t="n"/>
+      <c r="AQ24" s="4" t="n"/>
+      <c r="AR24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS24" s="4" t="n"/>
+      <c r="AT24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU24" s="4" t="n"/>
       <c r="AV24" s="4" t="n"/>
-      <c r="AW24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AX24" s="4" t="n"/>
+      <c r="AW24" s="4" t="n"/>
+      <c r="AX24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AY24" s="4" t="n"/>
       <c r="AZ24" s="4" t="n"/>
       <c r="BA24" s="4" t="n"/>
       <c r="BB24" s="4" t="n"/>
       <c r="BC24" s="4" t="n"/>
-      <c r="BD24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BE24" s="4" t="n"/>
+      <c r="BD24" s="4" t="n"/>
+      <c r="BE24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BF24" s="4" t="n"/>
-      <c r="BG24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH24" s="4" t="n"/>
+      <c r="BG24" s="4" t="n"/>
+      <c r="BH24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI24" s="4" t="n"/>
       <c r="BJ24" s="4" t="n"/>
       <c r="BK24" s="4" t="n"/>
@@ -23868,21 +23989,21 @@
       <c r="BN24" s="4" t="n"/>
       <c r="BO24" s="4" t="n"/>
       <c r="BP24" s="4" t="n"/>
-      <c r="BQ24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BR24" s="4" t="n"/>
+      <c r="BQ24" s="4" t="n"/>
+      <c r="BR24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BS24" s="4" t="n"/>
       <c r="BT24" s="4" t="n"/>
       <c r="BU24" s="4" t="n"/>
-      <c r="BV24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BW24" s="4" t="n"/>
+      <c r="BV24" s="4" t="n"/>
+      <c r="BW24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BX24" s="4" t="n"/>
       <c r="BY24" s="4" t="n"/>
       <c r="BZ24" s="4" t="n"/>
@@ -23893,13 +24014,14 @@
       <c r="CE24" s="4" t="n"/>
       <c r="CF24" s="4" t="n"/>
       <c r="CG24" s="4" t="n"/>
-      <c r="CH24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CI24" s="4" t="n"/>
+      <c r="CH24" s="4" t="n"/>
+      <c r="CI24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CJ24" s="4" t="n"/>
+      <c r="CK24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
@@ -23979,29 +24101,29 @@
       <c r="AU25" s="4" t="n"/>
       <c r="AV25" s="4" t="n"/>
       <c r="AW25" s="4" t="n"/>
-      <c r="AX25" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AY25" s="4" t="n"/>
+      <c r="AX25" s="4" t="n"/>
+      <c r="AY25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ25" s="4" t="n"/>
       <c r="BA25" s="4" t="n"/>
       <c r="BB25" s="4" t="n"/>
       <c r="BC25" s="4" t="n"/>
-      <c r="BD25" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BE25" s="4" t="n"/>
+      <c r="BD25" s="4" t="n"/>
+      <c r="BE25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BF25" s="4" t="n"/>
-      <c r="BG25" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH25" s="4" t="n"/>
+      <c r="BG25" s="4" t="n"/>
+      <c r="BH25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI25" s="4" t="n"/>
       <c r="BJ25" s="4" t="n"/>
       <c r="BK25" s="4" t="n"/>
@@ -24021,23 +24143,24 @@
       <c r="BY25" s="4" t="n"/>
       <c r="BZ25" s="4" t="n"/>
       <c r="CA25" s="4" t="n"/>
-      <c r="CB25" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CC25" s="4" t="n"/>
+      <c r="CB25" s="4" t="n"/>
+      <c r="CC25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CD25" s="4" t="n"/>
       <c r="CE25" s="4" t="n"/>
       <c r="CF25" s="4" t="n"/>
       <c r="CG25" s="4" t="n"/>
-      <c r="CH25" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CI25" s="4" t="n"/>
+      <c r="CH25" s="4" t="n"/>
+      <c r="CI25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CJ25" s="4" t="n"/>
+      <c r="CK25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -24123,17 +24246,17 @@
       <c r="AO26" s="4" t="n"/>
       <c r="AP26" s="4" t="n"/>
       <c r="AQ26" s="4" t="n"/>
-      <c r="AR26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AR26" s="4" t="n"/>
       <c r="AS26" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AT26" s="4" t="n"/>
+      <c r="AT26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU26" s="4" t="n"/>
       <c r="AV26" s="4" t="n"/>
       <c r="AW26" s="4" t="n"/>
@@ -24143,25 +24266,25 @@
       <c r="BA26" s="4" t="n"/>
       <c r="BB26" s="4" t="n"/>
       <c r="BC26" s="4" t="n"/>
-      <c r="BD26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BE26" s="4" t="n"/>
+      <c r="BD26" s="4" t="n"/>
+      <c r="BE26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BF26" s="4" t="n"/>
-      <c r="BG26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH26" s="4" t="n"/>
-      <c r="BI26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BJ26" s="4" t="n"/>
+      <c r="BG26" s="4" t="n"/>
+      <c r="BH26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI26" s="4" t="n"/>
+      <c r="BJ26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BK26" s="4" t="n"/>
       <c r="BL26" s="4" t="n"/>
       <c r="BM26" s="4" t="n"/>
@@ -24184,14 +24307,15 @@
       <c r="CD26" s="4" t="n"/>
       <c r="CE26" s="4" t="n"/>
       <c r="CF26" s="4" t="n"/>
-      <c r="CG26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CH26" s="4" t="n"/>
+      <c r="CG26" s="4" t="n"/>
+      <c r="CH26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CI26" s="4" t="n"/>
       <c r="CJ26" s="4" t="n"/>
+      <c r="CK26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n"/>
@@ -24304,18 +24428,18 @@
       <c r="AN27" s="4" t="n"/>
       <c r="AO27" s="4" t="n"/>
       <c r="AP27" s="4" t="n"/>
-      <c r="AQ27" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR27" s="4" t="n"/>
-      <c r="AS27" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT27" s="4" t="n"/>
+      <c r="AQ27" s="4" t="n"/>
+      <c r="AR27" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS27" s="4" t="n"/>
+      <c r="AT27" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU27" s="4" t="n"/>
       <c r="AV27" s="4" t="n"/>
       <c r="AW27" s="4" t="n"/>
@@ -24328,12 +24452,12 @@
       <c r="BD27" s="4" t="n"/>
       <c r="BE27" s="4" t="n"/>
       <c r="BF27" s="4" t="n"/>
-      <c r="BG27" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH27" s="4" t="n"/>
+      <c r="BG27" s="4" t="n"/>
+      <c r="BH27" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI27" s="4" t="n"/>
       <c r="BJ27" s="4" t="n"/>
       <c r="BK27" s="4" t="n"/>
@@ -24362,6 +24486,7 @@
       <c r="CH27" s="4" t="n"/>
       <c r="CI27" s="4" t="n"/>
       <c r="CJ27" s="4" t="n"/>
+      <c r="CK27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
@@ -24442,44 +24567,44 @@
       <c r="AN28" s="4" t="n"/>
       <c r="AO28" s="4" t="n"/>
       <c r="AP28" s="4" t="n"/>
-      <c r="AQ28" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR28" s="4" t="n"/>
-      <c r="AS28" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT28" s="4" t="n"/>
+      <c r="AQ28" s="4" t="n"/>
+      <c r="AR28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS28" s="4" t="n"/>
+      <c r="AT28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU28" s="4" t="n"/>
       <c r="AV28" s="4" t="n"/>
       <c r="AW28" s="4" t="n"/>
-      <c r="AX28" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AY28" s="4" t="n"/>
+      <c r="AX28" s="4" t="n"/>
+      <c r="AY28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ28" s="4" t="n"/>
       <c r="BA28" s="4" t="n"/>
       <c r="BB28" s="4" t="n"/>
       <c r="BC28" s="4" t="n"/>
-      <c r="BD28" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BE28" s="4" t="n"/>
+      <c r="BD28" s="4" t="n"/>
+      <c r="BE28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BF28" s="4" t="n"/>
-      <c r="BG28" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH28" s="4" t="n"/>
+      <c r="BG28" s="4" t="n"/>
+      <c r="BH28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI28" s="4" t="n"/>
       <c r="BJ28" s="4" t="n"/>
       <c r="BK28" s="4" t="n"/>
@@ -24507,7 +24632,8 @@
       <c r="CG28" s="4" t="n"/>
       <c r="CH28" s="4" t="n"/>
       <c r="CI28" s="4" t="n"/>
-      <c r="CJ28" s="4" t="inlineStr">
+      <c r="CJ28" s="4" t="n"/>
+      <c r="CK28" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -24588,52 +24714,52 @@
       <c r="AN29" s="4" t="n"/>
       <c r="AO29" s="4" t="n"/>
       <c r="AP29" s="4" t="n"/>
-      <c r="AQ29" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR29" s="4" t="n"/>
-      <c r="AS29" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT29" s="4" t="n"/>
-      <c r="AU29" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AQ29" s="4" t="n"/>
+      <c r="AR29" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS29" s="4" t="n"/>
+      <c r="AT29" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AU29" s="4" t="n"/>
       <c r="AV29" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AW29" s="4" t="n"/>
+      <c r="AW29" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AX29" s="4" t="n"/>
       <c r="AY29" s="4" t="n"/>
       <c r="AZ29" s="4" t="n"/>
-      <c r="BA29" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BA29" s="4" t="n"/>
       <c r="BB29" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BC29" s="4" t="n"/>
+      <c r="BC29" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BD29" s="4" t="n"/>
       <c r="BE29" s="4" t="n"/>
       <c r="BF29" s="4" t="n"/>
-      <c r="BG29" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH29" s="4" t="n"/>
+      <c r="BG29" s="4" t="n"/>
+      <c r="BH29" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI29" s="4" t="n"/>
       <c r="BJ29" s="4" t="n"/>
       <c r="BK29" s="4" t="n"/>
@@ -24647,12 +24773,12 @@
       <c r="BS29" s="4" t="n"/>
       <c r="BT29" s="4" t="n"/>
       <c r="BU29" s="4" t="n"/>
-      <c r="BV29" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BW29" s="4" t="n"/>
+      <c r="BV29" s="4" t="n"/>
+      <c r="BW29" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BX29" s="4" t="n"/>
       <c r="BY29" s="4" t="n"/>
       <c r="BZ29" s="4" t="n"/>
@@ -24666,6 +24792,7 @@
       <c r="CH29" s="4" t="n"/>
       <c r="CI29" s="4" t="n"/>
       <c r="CJ29" s="4" t="n"/>
+      <c r="CK29" s="4" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -24756,26 +24883,26 @@
       <c r="BB30" s="4" t="n"/>
       <c r="BC30" s="4" t="n"/>
       <c r="BD30" s="4" t="n"/>
-      <c r="BE30" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BF30" s="4" t="n"/>
+      <c r="BE30" s="4" t="n"/>
+      <c r="BF30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BG30" s="4" t="n"/>
       <c r="BH30" s="4" t="n"/>
-      <c r="BI30" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BJ30" s="4" t="n"/>
-      <c r="BK30" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BL30" s="4" t="n"/>
+      <c r="BI30" s="4" t="n"/>
+      <c r="BJ30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BK30" s="4" t="n"/>
+      <c r="BL30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BM30" s="4" t="n"/>
       <c r="BN30" s="4" t="n"/>
       <c r="BO30" s="4" t="n"/>
@@ -24791,12 +24918,12 @@
       <c r="BY30" s="4" t="n"/>
       <c r="BZ30" s="4" t="n"/>
       <c r="CA30" s="4" t="n"/>
-      <c r="CB30" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CC30" s="4" t="n"/>
+      <c r="CB30" s="4" t="n"/>
+      <c r="CC30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CD30" s="4" t="n"/>
       <c r="CE30" s="4" t="n"/>
       <c r="CF30" s="4" t="n"/>
@@ -24804,6 +24931,7 @@
       <c r="CH30" s="4" t="n"/>
       <c r="CI30" s="4" t="n"/>
       <c r="CJ30" s="4" t="n"/>
+      <c r="CK30" s="4" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n"/>
@@ -24865,12 +24993,12 @@
       <c r="AO31" s="4" t="n"/>
       <c r="AP31" s="4" t="n"/>
       <c r="AQ31" s="4" t="n"/>
-      <c r="AR31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS31" s="4" t="n"/>
+      <c r="AR31" s="4" t="n"/>
+      <c r="AS31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT31" s="4" t="n"/>
       <c r="AU31" s="4" t="n"/>
       <c r="AV31" s="4" t="n"/>
@@ -24882,24 +25010,24 @@
       <c r="BB31" s="4" t="n"/>
       <c r="BC31" s="4" t="n"/>
       <c r="BD31" s="4" t="n"/>
-      <c r="BE31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BE31" s="4" t="n"/>
       <c r="BF31" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BG31" s="4" t="n"/>
+      <c r="BG31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BH31" s="4" t="n"/>
-      <c r="BI31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BJ31" s="4" t="n"/>
+      <c r="BI31" s="4" t="n"/>
+      <c r="BJ31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BK31" s="4" t="n"/>
       <c r="BL31" s="4" t="n"/>
       <c r="BM31" s="4" t="n"/>
@@ -24907,12 +25035,12 @@
       <c r="BO31" s="4" t="n"/>
       <c r="BP31" s="4" t="n"/>
       <c r="BQ31" s="4" t="n"/>
-      <c r="BR31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BS31" s="4" t="n"/>
+      <c r="BR31" s="4" t="n"/>
+      <c r="BS31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BT31" s="4" t="n"/>
       <c r="BU31" s="4" t="n"/>
       <c r="BV31" s="4" t="n"/>
@@ -24921,12 +25049,12 @@
       <c r="BY31" s="4" t="n"/>
       <c r="BZ31" s="4" t="n"/>
       <c r="CA31" s="4" t="n"/>
-      <c r="CB31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CC31" s="4" t="n"/>
+      <c r="CB31" s="4" t="n"/>
+      <c r="CC31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CD31" s="4" t="n"/>
       <c r="CE31" s="4" t="n"/>
       <c r="CF31" s="4" t="n"/>
@@ -24934,6 +25062,7 @@
       <c r="CH31" s="4" t="n"/>
       <c r="CI31" s="4" t="n"/>
       <c r="CJ31" s="4" t="n"/>
+      <c r="CK31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n"/>
@@ -25034,80 +25163,76 @@
         </is>
       </c>
       <c r="AP32" s="4" t="n"/>
-      <c r="AQ32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR32" s="4" t="n"/>
-      <c r="AS32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT32" s="4" t="n"/>
+      <c r="AQ32" s="4" t="n"/>
+      <c r="AR32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS32" s="4" t="n"/>
+      <c r="AT32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU32" s="4" t="n"/>
       <c r="AV32" s="4" t="n"/>
       <c r="AW32" s="4" t="n"/>
-      <c r="AX32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AX32" s="4" t="n"/>
       <c r="AY32" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AZ32" s="4" t="n"/>
+      <c r="AZ32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BA32" s="4" t="n"/>
       <c r="BB32" s="4" t="n"/>
       <c r="BC32" s="4" t="n"/>
-      <c r="BD32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BE32" s="4" t="n"/>
+      <c r="BD32" s="4" t="n"/>
+      <c r="BE32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BF32" s="4" t="n"/>
-      <c r="BG32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH32" s="4" t="n"/>
+      <c r="BG32" s="4" t="n"/>
+      <c r="BH32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI32" s="4" t="n"/>
       <c r="BJ32" s="4" t="n"/>
       <c r="BK32" s="4" t="n"/>
       <c r="BL32" s="4" t="n"/>
       <c r="BM32" s="4" t="n"/>
-      <c r="BN32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BN32" s="4" t="n"/>
       <c r="BO32" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BP32" s="4" t="n"/>
+      <c r="BP32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BQ32" s="4" t="n"/>
       <c r="BR32" s="4" t="n"/>
-      <c r="BS32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BT32" s="4" t="n"/>
+      <c r="BS32" s="4" t="n"/>
+      <c r="BT32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BU32" s="4" t="n"/>
       <c r="BV32" s="4" t="n"/>
       <c r="BW32" s="4" t="n"/>
-      <c r="BX32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BX32" s="4" t="n"/>
       <c r="BY32" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -25118,28 +25243,33 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="CA32" s="4" t="n"/>
-      <c r="CB32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CC32" s="4" t="n"/>
-      <c r="CD32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CE32" s="4" t="n"/>
+      <c r="CA32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CB32" s="4" t="n"/>
+      <c r="CC32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CD32" s="4" t="n"/>
+      <c r="CE32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CF32" s="4" t="n"/>
       <c r="CG32" s="4" t="n"/>
-      <c r="CH32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CI32" s="4" t="n"/>
-      <c r="CJ32" s="4" t="inlineStr">
+      <c r="CH32" s="4" t="n"/>
+      <c r="CI32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CJ32" s="4" t="n"/>
+      <c r="CK32" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -25213,12 +25343,12 @@
       <c r="AO33" s="4" t="n"/>
       <c r="AP33" s="4" t="n"/>
       <c r="AQ33" s="4" t="n"/>
-      <c r="AR33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS33" s="4" t="n"/>
+      <c r="AR33" s="4" t="n"/>
+      <c r="AS33" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT33" s="4" t="n"/>
       <c r="AU33" s="4" t="n"/>
       <c r="AV33" s="4" t="n"/>
@@ -25230,24 +25360,24 @@
       <c r="BB33" s="4" t="n"/>
       <c r="BC33" s="4" t="n"/>
       <c r="BD33" s="4" t="n"/>
-      <c r="BE33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BE33" s="4" t="n"/>
       <c r="BF33" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BG33" s="4" t="n"/>
+      <c r="BG33" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BH33" s="4" t="n"/>
-      <c r="BI33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BJ33" s="4" t="n"/>
+      <c r="BI33" s="4" t="n"/>
+      <c r="BJ33" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BK33" s="4" t="n"/>
       <c r="BL33" s="4" t="n"/>
       <c r="BM33" s="4" t="n"/>
@@ -25274,6 +25404,7 @@
       <c r="CH33" s="4" t="n"/>
       <c r="CI33" s="4" t="n"/>
       <c r="CJ33" s="4" t="n"/>
+      <c r="CK33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n"/>
@@ -25366,44 +25497,44 @@
       <c r="AN34" s="4" t="n"/>
       <c r="AO34" s="4" t="n"/>
       <c r="AP34" s="4" t="n"/>
-      <c r="AQ34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR34" s="4" t="n"/>
-      <c r="AS34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT34" s="4" t="n"/>
+      <c r="AQ34" s="4" t="n"/>
+      <c r="AR34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS34" s="4" t="n"/>
+      <c r="AT34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU34" s="4" t="n"/>
       <c r="AV34" s="4" t="n"/>
       <c r="AW34" s="4" t="n"/>
-      <c r="AX34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AY34" s="4" t="n"/>
+      <c r="AX34" s="4" t="n"/>
+      <c r="AY34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ34" s="4" t="n"/>
       <c r="BA34" s="4" t="n"/>
       <c r="BB34" s="4" t="n"/>
       <c r="BC34" s="4" t="n"/>
-      <c r="BD34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BE34" s="4" t="n"/>
+      <c r="BD34" s="4" t="n"/>
+      <c r="BE34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BF34" s="4" t="n"/>
-      <c r="BG34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH34" s="4" t="n"/>
+      <c r="BG34" s="4" t="n"/>
+      <c r="BH34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI34" s="4" t="n"/>
       <c r="BJ34" s="4" t="n"/>
       <c r="BK34" s="4" t="n"/>
@@ -25423,12 +25554,12 @@
       <c r="BY34" s="4" t="n"/>
       <c r="BZ34" s="4" t="n"/>
       <c r="CA34" s="4" t="n"/>
-      <c r="CB34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CC34" s="4" t="n"/>
+      <c r="CB34" s="4" t="n"/>
+      <c r="CC34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CD34" s="4" t="n"/>
       <c r="CE34" s="4" t="n"/>
       <c r="CF34" s="4" t="n"/>
@@ -25436,6 +25567,7 @@
       <c r="CH34" s="4" t="n"/>
       <c r="CI34" s="4" t="n"/>
       <c r="CJ34" s="4" t="n"/>
+      <c r="CK34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n"/>
@@ -25522,17 +25654,17 @@
       <c r="BB35" s="4" t="n"/>
       <c r="BC35" s="4" t="n"/>
       <c r="BD35" s="4" t="n"/>
-      <c r="BE35" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BE35" s="4" t="n"/>
       <c r="BF35" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BG35" s="4" t="n"/>
+      <c r="BG35" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BH35" s="4" t="n"/>
       <c r="BI35" s="4" t="n"/>
       <c r="BJ35" s="4" t="n"/>
@@ -25562,6 +25694,7 @@
       <c r="CH35" s="4" t="n"/>
       <c r="CI35" s="4" t="n"/>
       <c r="CJ35" s="4" t="n"/>
+      <c r="CK35" s="4" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n"/>
@@ -25642,27 +25775,27 @@
       </c>
       <c r="AO36" s="4" t="n"/>
       <c r="AP36" s="4" t="n"/>
-      <c r="AQ36" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR36" s="4" t="n"/>
-      <c r="AS36" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT36" s="4" t="n"/>
+      <c r="AQ36" s="4" t="n"/>
+      <c r="AR36" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS36" s="4" t="n"/>
+      <c r="AT36" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU36" s="4" t="n"/>
       <c r="AV36" s="4" t="n"/>
       <c r="AW36" s="4" t="n"/>
-      <c r="AX36" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AY36" s="4" t="n"/>
+      <c r="AX36" s="4" t="n"/>
+      <c r="AY36" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ36" s="4" t="n"/>
       <c r="BA36" s="4" t="n"/>
       <c r="BB36" s="4" t="n"/>
@@ -25670,12 +25803,12 @@
       <c r="BD36" s="4" t="n"/>
       <c r="BE36" s="4" t="n"/>
       <c r="BF36" s="4" t="n"/>
-      <c r="BG36" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH36" s="4" t="n"/>
+      <c r="BG36" s="4" t="n"/>
+      <c r="BH36" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI36" s="4" t="n"/>
       <c r="BJ36" s="4" t="n"/>
       <c r="BK36" s="4" t="n"/>
@@ -25702,12 +25835,13 @@
       <c r="CF36" s="4" t="n"/>
       <c r="CG36" s="4" t="n"/>
       <c r="CH36" s="4" t="n"/>
-      <c r="CI36" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CJ36" s="4" t="n"/>
+      <c r="CI36" s="4" t="n"/>
+      <c r="CJ36" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CK36" s="4" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -25796,12 +25930,12 @@
       </c>
       <c r="AO37" s="4" t="n"/>
       <c r="AP37" s="4" t="n"/>
-      <c r="AQ37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR37" s="4" t="n"/>
+      <c r="AQ37" s="4" t="n"/>
+      <c r="AR37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS37" s="4" t="n"/>
       <c r="AT37" s="4" t="n"/>
       <c r="AU37" s="4" t="n"/>
@@ -25814,11 +25948,7 @@
       <c r="BB37" s="4" t="n"/>
       <c r="BC37" s="4" t="n"/>
       <c r="BD37" s="4" t="n"/>
-      <c r="BE37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BE37" s="4" t="n"/>
       <c r="BF37" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -25829,7 +25959,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="BH37" s="4" t="n"/>
+      <c r="BH37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI37" s="4" t="n"/>
       <c r="BJ37" s="4" t="n"/>
       <c r="BK37" s="4" t="n"/>
@@ -25847,18 +25981,18 @@
       <c r="BW37" s="4" t="n"/>
       <c r="BX37" s="4" t="n"/>
       <c r="BY37" s="4" t="n"/>
-      <c r="BZ37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CA37" s="4" t="n"/>
-      <c r="CB37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CC37" s="4" t="n"/>
+      <c r="BZ37" s="4" t="n"/>
+      <c r="CA37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CB37" s="4" t="n"/>
+      <c r="CC37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CD37" s="4" t="n"/>
       <c r="CE37" s="4" t="n"/>
       <c r="CF37" s="4" t="n"/>
@@ -25866,6 +26000,7 @@
       <c r="CH37" s="4" t="n"/>
       <c r="CI37" s="4" t="n"/>
       <c r="CJ37" s="4" t="n"/>
+      <c r="CK37" s="4" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n"/>
@@ -25953,29 +26088,29 @@
       <c r="AU38" s="4" t="n"/>
       <c r="AV38" s="4" t="n"/>
       <c r="AW38" s="4" t="n"/>
-      <c r="AX38" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AY38" s="4" t="n"/>
+      <c r="AX38" s="4" t="n"/>
+      <c r="AY38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ38" s="4" t="n"/>
       <c r="BA38" s="4" t="n"/>
       <c r="BB38" s="4" t="n"/>
       <c r="BC38" s="4" t="n"/>
-      <c r="BD38" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BE38" s="4" t="n"/>
+      <c r="BD38" s="4" t="n"/>
+      <c r="BE38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BF38" s="4" t="n"/>
-      <c r="BG38" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH38" s="4" t="n"/>
+      <c r="BG38" s="4" t="n"/>
+      <c r="BH38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI38" s="4" t="n"/>
       <c r="BJ38" s="4" t="n"/>
       <c r="BK38" s="4" t="n"/>
@@ -25984,12 +26119,12 @@
       <c r="BN38" s="4" t="n"/>
       <c r="BO38" s="4" t="n"/>
       <c r="BP38" s="4" t="n"/>
-      <c r="BQ38" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BR38" s="4" t="n"/>
+      <c r="BQ38" s="4" t="n"/>
+      <c r="BR38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BS38" s="4" t="n"/>
       <c r="BT38" s="4" t="n"/>
       <c r="BU38" s="4" t="n"/>
@@ -25997,25 +26132,26 @@
       <c r="BW38" s="4" t="n"/>
       <c r="BX38" s="4" t="n"/>
       <c r="BY38" s="4" t="n"/>
-      <c r="BZ38" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CA38" s="4" t="n"/>
+      <c r="BZ38" s="4" t="n"/>
+      <c r="CA38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CB38" s="4" t="n"/>
       <c r="CC38" s="4" t="n"/>
       <c r="CD38" s="4" t="n"/>
       <c r="CE38" s="4" t="n"/>
       <c r="CF38" s="4" t="n"/>
       <c r="CG38" s="4" t="n"/>
-      <c r="CH38" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CI38" s="4" t="n"/>
+      <c r="CH38" s="4" t="n"/>
+      <c r="CI38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CJ38" s="4" t="n"/>
+      <c r="CK38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n"/>
@@ -26102,44 +26238,44 @@
       <c r="AP39" s="4" t="n"/>
       <c r="AQ39" s="4" t="n"/>
       <c r="AR39" s="4" t="n"/>
-      <c r="AS39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT39" s="4" t="n"/>
+      <c r="AS39" s="4" t="n"/>
+      <c r="AT39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU39" s="4" t="n"/>
       <c r="AV39" s="4" t="n"/>
       <c r="AW39" s="4" t="n"/>
-      <c r="AX39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AY39" s="4" t="n"/>
+      <c r="AX39" s="4" t="n"/>
+      <c r="AY39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ39" s="4" t="n"/>
       <c r="BA39" s="4" t="n"/>
       <c r="BB39" s="4" t="n"/>
       <c r="BC39" s="4" t="n"/>
-      <c r="BD39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BE39" s="4" t="n"/>
+      <c r="BD39" s="4" t="n"/>
+      <c r="BE39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BF39" s="4" t="n"/>
-      <c r="BG39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH39" s="4" t="n"/>
-      <c r="BI39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BJ39" s="4" t="n"/>
+      <c r="BG39" s="4" t="n"/>
+      <c r="BH39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI39" s="4" t="n"/>
+      <c r="BJ39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BK39" s="4" t="n"/>
       <c r="BL39" s="4" t="n"/>
       <c r="BM39" s="4" t="n"/>
@@ -26155,12 +26291,12 @@
       <c r="BW39" s="4" t="n"/>
       <c r="BX39" s="4" t="n"/>
       <c r="BY39" s="4" t="n"/>
-      <c r="BZ39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CA39" s="4" t="n"/>
+      <c r="BZ39" s="4" t="n"/>
+      <c r="CA39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CB39" s="4" t="n"/>
       <c r="CC39" s="4" t="n"/>
       <c r="CD39" s="4" t="n"/>
@@ -26170,6 +26306,7 @@
       <c r="CH39" s="4" t="n"/>
       <c r="CI39" s="4" t="n"/>
       <c r="CJ39" s="4" t="n"/>
+      <c r="CK39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n"/>
@@ -26270,17 +26407,17 @@
       </c>
       <c r="AO40" s="4" t="n"/>
       <c r="AP40" s="4" t="n"/>
-      <c r="AQ40" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AQ40" s="4" t="n"/>
       <c r="AR40" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AS40" s="4" t="n"/>
+      <c r="AS40" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT40" s="4" t="n"/>
       <c r="AU40" s="4" t="n"/>
       <c r="AV40" s="4" t="n"/>
@@ -26292,21 +26429,21 @@
       <c r="BB40" s="4" t="n"/>
       <c r="BC40" s="4" t="n"/>
       <c r="BD40" s="4" t="n"/>
-      <c r="BE40" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BF40" s="4" t="n"/>
+      <c r="BE40" s="4" t="n"/>
+      <c r="BF40" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BG40" s="4" t="n"/>
       <c r="BH40" s="4" t="n"/>
       <c r="BI40" s="4" t="n"/>
-      <c r="BJ40" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BK40" s="4" t="n"/>
+      <c r="BJ40" s="4" t="n"/>
+      <c r="BK40" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BL40" s="4" t="n"/>
       <c r="BM40" s="4" t="n"/>
       <c r="BN40" s="4" t="n"/>
@@ -26321,12 +26458,12 @@
       <c r="BW40" s="4" t="n"/>
       <c r="BX40" s="4" t="n"/>
       <c r="BY40" s="4" t="n"/>
-      <c r="BZ40" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CA40" s="4" t="n"/>
+      <c r="BZ40" s="4" t="n"/>
+      <c r="CA40" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CB40" s="4" t="n"/>
       <c r="CC40" s="4" t="n"/>
       <c r="CD40" s="4" t="n"/>
@@ -26335,7 +26472,8 @@
       <c r="CG40" s="4" t="n"/>
       <c r="CH40" s="4" t="n"/>
       <c r="CI40" s="4" t="n"/>
-      <c r="CJ40" s="4" t="inlineStr">
+      <c r="CJ40" s="4" t="n"/>
+      <c r="CK40" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -26424,27 +26562,27 @@
       <c r="AN41" s="4" t="n"/>
       <c r="AO41" s="4" t="n"/>
       <c r="AP41" s="4" t="n"/>
-      <c r="AQ41" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR41" s="4" t="n"/>
-      <c r="AS41" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT41" s="4" t="n"/>
+      <c r="AQ41" s="4" t="n"/>
+      <c r="AR41" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS41" s="4" t="n"/>
+      <c r="AT41" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU41" s="4" t="n"/>
       <c r="AV41" s="4" t="n"/>
       <c r="AW41" s="4" t="n"/>
-      <c r="AX41" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AY41" s="4" t="n"/>
+      <c r="AX41" s="4" t="n"/>
+      <c r="AY41" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ41" s="4" t="n"/>
       <c r="BA41" s="4" t="n"/>
       <c r="BB41" s="4" t="n"/>
@@ -26452,18 +26590,18 @@
       <c r="BD41" s="4" t="n"/>
       <c r="BE41" s="4" t="n"/>
       <c r="BF41" s="4" t="n"/>
-      <c r="BG41" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH41" s="4" t="n"/>
-      <c r="BI41" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BJ41" s="4" t="n"/>
+      <c r="BG41" s="4" t="n"/>
+      <c r="BH41" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI41" s="4" t="n"/>
+      <c r="BJ41" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BK41" s="4" t="n"/>
       <c r="BL41" s="4" t="n"/>
       <c r="BM41" s="4" t="n"/>
@@ -26490,6 +26628,7 @@
       <c r="CH41" s="4" t="n"/>
       <c r="CI41" s="4" t="n"/>
       <c r="CJ41" s="4" t="n"/>
+      <c r="CK41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n"/>
@@ -26582,18 +26721,18 @@
       </c>
       <c r="AO42" s="4" t="n"/>
       <c r="AP42" s="4" t="n"/>
-      <c r="AQ42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR42" s="4" t="n"/>
-      <c r="AS42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT42" s="4" t="n"/>
+      <c r="AQ42" s="4" t="n"/>
+      <c r="AR42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS42" s="4" t="n"/>
+      <c r="AT42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU42" s="4" t="n"/>
       <c r="AV42" s="4" t="n"/>
       <c r="AW42" s="4" t="n"/>
@@ -26603,29 +26742,29 @@
       <c r="BA42" s="4" t="n"/>
       <c r="BB42" s="4" t="n"/>
       <c r="BC42" s="4" t="n"/>
-      <c r="BD42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BE42" s="4" t="n"/>
+      <c r="BD42" s="4" t="n"/>
+      <c r="BE42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BF42" s="4" t="n"/>
-      <c r="BG42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH42" s="4" t="n"/>
+      <c r="BG42" s="4" t="n"/>
+      <c r="BH42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI42" s="4" t="n"/>
       <c r="BJ42" s="4" t="n"/>
       <c r="BK42" s="4" t="n"/>
       <c r="BL42" s="4" t="n"/>
-      <c r="BM42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BN42" s="4" t="n"/>
+      <c r="BM42" s="4" t="n"/>
+      <c r="BN42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BO42" s="4" t="n"/>
       <c r="BP42" s="4" t="n"/>
       <c r="BQ42" s="4" t="n"/>
@@ -26645,13 +26784,14 @@
       <c r="CE42" s="4" t="n"/>
       <c r="CF42" s="4" t="n"/>
       <c r="CG42" s="4" t="n"/>
-      <c r="CH42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CI42" s="4" t="n"/>
+      <c r="CH42" s="4" t="n"/>
+      <c r="CI42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CJ42" s="4" t="n"/>
+      <c r="CK42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n"/>
@@ -26736,18 +26876,18 @@
       </c>
       <c r="AO43" s="4" t="n"/>
       <c r="AP43" s="4" t="n"/>
-      <c r="AQ43" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR43" s="4" t="n"/>
-      <c r="AS43" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT43" s="4" t="n"/>
+      <c r="AQ43" s="4" t="n"/>
+      <c r="AR43" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS43" s="4" t="n"/>
+      <c r="AT43" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU43" s="4" t="n"/>
       <c r="AV43" s="4" t="n"/>
       <c r="AW43" s="4" t="n"/>
@@ -26757,26 +26897,26 @@
       <c r="BA43" s="4" t="n"/>
       <c r="BB43" s="4" t="n"/>
       <c r="BC43" s="4" t="n"/>
-      <c r="BD43" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BE43" s="4" t="n"/>
+      <c r="BD43" s="4" t="n"/>
+      <c r="BE43" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BF43" s="4" t="n"/>
-      <c r="BG43" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH43" s="4" t="n"/>
+      <c r="BG43" s="4" t="n"/>
+      <c r="BH43" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI43" s="4" t="n"/>
-      <c r="BJ43" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BK43" s="4" t="n"/>
+      <c r="BJ43" s="4" t="n"/>
+      <c r="BK43" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BL43" s="4" t="n"/>
       <c r="BM43" s="4" t="n"/>
       <c r="BN43" s="4" t="n"/>
@@ -26801,7 +26941,8 @@
       <c r="CG43" s="4" t="n"/>
       <c r="CH43" s="4" t="n"/>
       <c r="CI43" s="4" t="n"/>
-      <c r="CJ43" s="4" t="inlineStr">
+      <c r="CJ43" s="4" t="n"/>
+      <c r="CK43" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -26879,12 +27020,12 @@
       <c r="AO44" s="4" t="n"/>
       <c r="AP44" s="4" t="n"/>
       <c r="AQ44" s="4" t="n"/>
-      <c r="AR44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS44" s="4" t="n"/>
+      <c r="AR44" s="4" t="n"/>
+      <c r="AS44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT44" s="4" t="n"/>
       <c r="AU44" s="4" t="n"/>
       <c r="AV44" s="4" t="n"/>
@@ -26895,29 +27036,29 @@
       <c r="BA44" s="4" t="n"/>
       <c r="BB44" s="4" t="n"/>
       <c r="BC44" s="4" t="n"/>
-      <c r="BD44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BE44" s="4" t="n"/>
-      <c r="BF44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BD44" s="4" t="n"/>
+      <c r="BE44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BF44" s="4" t="n"/>
       <c r="BG44" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BH44" s="4" t="n"/>
-      <c r="BI44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BJ44" s="4" t="n"/>
+      <c r="BH44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI44" s="4" t="n"/>
+      <c r="BJ44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BK44" s="4" t="n"/>
       <c r="BL44" s="4" t="n"/>
       <c r="BM44" s="4" t="n"/>
@@ -26925,12 +27066,12 @@
       <c r="BO44" s="4" t="n"/>
       <c r="BP44" s="4" t="n"/>
       <c r="BQ44" s="4" t="n"/>
-      <c r="BR44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BS44" s="4" t="n"/>
+      <c r="BR44" s="4" t="n"/>
+      <c r="BS44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BT44" s="4" t="n"/>
       <c r="BU44" s="4" t="n"/>
       <c r="BV44" s="4" t="n"/>
@@ -26948,6 +27089,7 @@
       <c r="CH44" s="4" t="n"/>
       <c r="CI44" s="4" t="n"/>
       <c r="CJ44" s="4" t="n"/>
+      <c r="CK44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -27044,18 +27186,18 @@
       <c r="AN45" s="4" t="n"/>
       <c r="AO45" s="4" t="n"/>
       <c r="AP45" s="4" t="n"/>
-      <c r="AQ45" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR45" s="4" t="n"/>
-      <c r="AS45" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT45" s="4" t="n"/>
+      <c r="AQ45" s="4" t="n"/>
+      <c r="AR45" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS45" s="4" t="n"/>
+      <c r="AT45" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU45" s="4" t="n"/>
       <c r="AV45" s="4" t="n"/>
       <c r="AW45" s="4" t="n"/>
@@ -27068,12 +27210,12 @@
       <c r="BD45" s="4" t="n"/>
       <c r="BE45" s="4" t="n"/>
       <c r="BF45" s="4" t="n"/>
-      <c r="BG45" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH45" s="4" t="n"/>
+      <c r="BG45" s="4" t="n"/>
+      <c r="BH45" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI45" s="4" t="n"/>
       <c r="BJ45" s="4" t="n"/>
       <c r="BK45" s="4" t="n"/>
@@ -27101,7 +27243,8 @@
       <c r="CG45" s="4" t="n"/>
       <c r="CH45" s="4" t="n"/>
       <c r="CI45" s="4" t="n"/>
-      <c r="CJ45" s="4" t="inlineStr">
+      <c r="CJ45" s="4" t="n"/>
+      <c r="CK45" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -27198,18 +27341,18 @@
       </c>
       <c r="AO46" s="4" t="n"/>
       <c r="AP46" s="4" t="n"/>
-      <c r="AQ46" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR46" s="4" t="n"/>
-      <c r="AS46" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT46" s="4" t="n"/>
+      <c r="AQ46" s="4" t="n"/>
+      <c r="AR46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS46" s="4" t="n"/>
+      <c r="AT46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU46" s="4" t="n"/>
       <c r="AV46" s="4" t="n"/>
       <c r="AW46" s="4" t="n"/>
@@ -27220,35 +27363,35 @@
       <c r="BB46" s="4" t="n"/>
       <c r="BC46" s="4" t="n"/>
       <c r="BD46" s="4" t="n"/>
-      <c r="BE46" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BF46" s="4" t="n"/>
-      <c r="BG46" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH46" s="4" t="n"/>
+      <c r="BE46" s="4" t="n"/>
+      <c r="BF46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BG46" s="4" t="n"/>
+      <c r="BH46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI46" s="4" t="n"/>
-      <c r="BJ46" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BK46" s="4" t="n"/>
+      <c r="BJ46" s="4" t="n"/>
+      <c r="BK46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BL46" s="4" t="n"/>
       <c r="BM46" s="4" t="n"/>
       <c r="BN46" s="4" t="n"/>
       <c r="BO46" s="4" t="n"/>
-      <c r="BP46" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BQ46" s="4" t="n"/>
+      <c r="BP46" s="4" t="n"/>
+      <c r="BQ46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BR46" s="4" t="n"/>
       <c r="BS46" s="4" t="n"/>
       <c r="BT46" s="4" t="n"/>
@@ -27268,6 +27411,7 @@
       <c r="CH46" s="4" t="n"/>
       <c r="CI46" s="4" t="n"/>
       <c r="CJ46" s="4" t="n"/>
+      <c r="CK46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n"/>
@@ -27356,18 +27500,18 @@
       </c>
       <c r="AO47" s="4" t="n"/>
       <c r="AP47" s="4" t="n"/>
-      <c r="AQ47" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR47" s="4" t="n"/>
-      <c r="AS47" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT47" s="4" t="n"/>
+      <c r="AQ47" s="4" t="n"/>
+      <c r="AR47" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS47" s="4" t="n"/>
+      <c r="AT47" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU47" s="4" t="n"/>
       <c r="AV47" s="4" t="n"/>
       <c r="AW47" s="4" t="n"/>
@@ -27380,24 +27524,24 @@
       <c r="BD47" s="4" t="n"/>
       <c r="BE47" s="4" t="n"/>
       <c r="BF47" s="4" t="n"/>
-      <c r="BG47" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH47" s="4" t="n"/>
+      <c r="BG47" s="4" t="n"/>
+      <c r="BH47" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI47" s="4" t="n"/>
       <c r="BJ47" s="4" t="n"/>
       <c r="BK47" s="4" t="n"/>
       <c r="BL47" s="4" t="n"/>
       <c r="BM47" s="4" t="n"/>
       <c r="BN47" s="4" t="n"/>
-      <c r="BO47" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BP47" s="4" t="n"/>
+      <c r="BO47" s="4" t="n"/>
+      <c r="BP47" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BQ47" s="4" t="n"/>
       <c r="BR47" s="4" t="n"/>
       <c r="BS47" s="4" t="n"/>
@@ -27417,7 +27561,8 @@
       <c r="CG47" s="4" t="n"/>
       <c r="CH47" s="4" t="n"/>
       <c r="CI47" s="4" t="n"/>
-      <c r="CJ47" s="4" t="inlineStr">
+      <c r="CJ47" s="4" t="n"/>
+      <c r="CK47" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -27510,18 +27655,18 @@
       <c r="AN48" s="4" t="n"/>
       <c r="AO48" s="4" t="n"/>
       <c r="AP48" s="4" t="n"/>
-      <c r="AQ48" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR48" s="4" t="n"/>
-      <c r="AS48" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT48" s="4" t="n"/>
+      <c r="AQ48" s="4" t="n"/>
+      <c r="AR48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS48" s="4" t="n"/>
+      <c r="AT48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU48" s="4" t="n"/>
       <c r="AV48" s="4" t="n"/>
       <c r="AW48" s="4" t="n"/>
@@ -27533,17 +27678,17 @@
       <c r="BC48" s="4" t="n"/>
       <c r="BD48" s="4" t="n"/>
       <c r="BE48" s="4" t="n"/>
-      <c r="BF48" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BF48" s="4" t="n"/>
       <c r="BG48" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BH48" s="4" t="n"/>
+      <c r="BH48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI48" s="4" t="n"/>
       <c r="BJ48" s="4" t="n"/>
       <c r="BK48" s="4" t="n"/>
@@ -27566,16 +27711,17 @@
       <c r="CB48" s="4" t="n"/>
       <c r="CC48" s="4" t="n"/>
       <c r="CD48" s="4" t="n"/>
-      <c r="CE48" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CF48" s="4" t="n"/>
+      <c r="CE48" s="4" t="n"/>
+      <c r="CF48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CG48" s="4" t="n"/>
       <c r="CH48" s="4" t="n"/>
       <c r="CI48" s="4" t="n"/>
-      <c r="CJ48" s="4" t="inlineStr">
+      <c r="CJ48" s="4" t="n"/>
+      <c r="CK48" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -27664,17 +27810,17 @@
       </c>
       <c r="AO49" s="4" t="n"/>
       <c r="AP49" s="4" t="n"/>
-      <c r="AQ49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AQ49" s="4" t="n"/>
       <c r="AR49" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AS49" s="4" t="n"/>
+      <c r="AS49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT49" s="4" t="n"/>
       <c r="AU49" s="4" t="n"/>
       <c r="AV49" s="4" t="n"/>
@@ -27686,31 +27832,31 @@
       <c r="BB49" s="4" t="n"/>
       <c r="BC49" s="4" t="n"/>
       <c r="BD49" s="4" t="n"/>
-      <c r="BE49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BF49" s="4" t="n"/>
+      <c r="BE49" s="4" t="n"/>
+      <c r="BF49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BG49" s="4" t="n"/>
       <c r="BH49" s="4" t="n"/>
       <c r="BI49" s="4" t="n"/>
-      <c r="BJ49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BK49" s="4" t="n"/>
+      <c r="BJ49" s="4" t="n"/>
+      <c r="BK49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BL49" s="4" t="n"/>
       <c r="BM49" s="4" t="n"/>
       <c r="BN49" s="4" t="n"/>
       <c r="BO49" s="4" t="n"/>
-      <c r="BP49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BQ49" s="4" t="n"/>
+      <c r="BP49" s="4" t="n"/>
+      <c r="BQ49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BR49" s="4" t="n"/>
       <c r="BS49" s="4" t="n"/>
       <c r="BT49" s="4" t="n"/>
@@ -27721,19 +27867,20 @@
       <c r="BY49" s="4" t="n"/>
       <c r="BZ49" s="4" t="n"/>
       <c r="CA49" s="4" t="n"/>
-      <c r="CB49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CC49" s="4" t="n"/>
+      <c r="CB49" s="4" t="n"/>
+      <c r="CC49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CD49" s="4" t="n"/>
       <c r="CE49" s="4" t="n"/>
       <c r="CF49" s="4" t="n"/>
       <c r="CG49" s="4" t="n"/>
       <c r="CH49" s="4" t="n"/>
       <c r="CI49" s="4" t="n"/>
-      <c r="CJ49" s="4" t="inlineStr">
+      <c r="CJ49" s="4" t="n"/>
+      <c r="CK49" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -27814,17 +27961,17 @@
       </c>
       <c r="AO50" s="4" t="n"/>
       <c r="AP50" s="4" t="n"/>
-      <c r="AQ50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AQ50" s="4" t="n"/>
       <c r="AR50" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AS50" s="4" t="n"/>
+      <c r="AS50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT50" s="4" t="n"/>
       <c r="AU50" s="4" t="n"/>
       <c r="AV50" s="4" t="n"/>
@@ -27836,46 +27983,46 @@
       <c r="BB50" s="4" t="n"/>
       <c r="BC50" s="4" t="n"/>
       <c r="BD50" s="4" t="n"/>
-      <c r="BE50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BF50" s="4" t="n"/>
+      <c r="BE50" s="4" t="n"/>
+      <c r="BF50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BG50" s="4" t="n"/>
       <c r="BH50" s="4" t="n"/>
       <c r="BI50" s="4" t="n"/>
       <c r="BJ50" s="4" t="n"/>
-      <c r="BK50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BL50" s="4" t="n"/>
+      <c r="BK50" s="4" t="n"/>
+      <c r="BL50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BM50" s="4" t="n"/>
       <c r="BN50" s="4" t="n"/>
-      <c r="BO50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BO50" s="4" t="n"/>
       <c r="BP50" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BQ50" s="4" t="n"/>
+      <c r="BQ50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BR50" s="4" t="n"/>
       <c r="BS50" s="4" t="n"/>
       <c r="BT50" s="4" t="n"/>
       <c r="BU50" s="4" t="n"/>
       <c r="BV50" s="4" t="n"/>
-      <c r="BW50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BX50" s="4" t="n"/>
+      <c r="BW50" s="4" t="n"/>
+      <c r="BX50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BY50" s="4" t="n"/>
       <c r="BZ50" s="4" t="n"/>
       <c r="CA50" s="4" t="n"/>
@@ -27888,6 +28035,7 @@
       <c r="CH50" s="4" t="n"/>
       <c r="CI50" s="4" t="n"/>
       <c r="CJ50" s="4" t="n"/>
+      <c r="CK50" s="4" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n"/>
@@ -27974,12 +28122,12 @@
       <c r="AP51" s="4" t="n"/>
       <c r="AQ51" s="4" t="n"/>
       <c r="AR51" s="4" t="n"/>
-      <c r="AS51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT51" s="4" t="n"/>
+      <c r="AS51" s="4" t="n"/>
+      <c r="AT51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU51" s="4" t="n"/>
       <c r="AV51" s="4" t="n"/>
       <c r="AW51" s="4" t="n"/>
@@ -27989,29 +28137,29 @@
       <c r="BA51" s="4" t="n"/>
       <c r="BB51" s="4" t="n"/>
       <c r="BC51" s="4" t="n"/>
-      <c r="BD51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BE51" s="4" t="n"/>
-      <c r="BF51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BD51" s="4" t="n"/>
+      <c r="BE51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BF51" s="4" t="n"/>
       <c r="BG51" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BH51" s="4" t="n"/>
-      <c r="BI51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BJ51" s="4" t="n"/>
+      <c r="BH51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI51" s="4" t="n"/>
+      <c r="BJ51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BK51" s="4" t="n"/>
       <c r="BL51" s="4" t="n"/>
       <c r="BM51" s="4" t="n"/>
@@ -28035,13 +28183,14 @@
       <c r="CE51" s="4" t="n"/>
       <c r="CF51" s="4" t="n"/>
       <c r="CG51" s="4" t="n"/>
-      <c r="CH51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CI51" s="4" t="n"/>
+      <c r="CH51" s="4" t="n"/>
+      <c r="CI51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CJ51" s="4" t="n"/>
+      <c r="CK51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n"/>
@@ -28118,18 +28267,18 @@
       </c>
       <c r="AO52" s="4" t="n"/>
       <c r="AP52" s="4" t="n"/>
-      <c r="AQ52" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR52" s="4" t="n"/>
-      <c r="AS52" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT52" s="4" t="n"/>
+      <c r="AQ52" s="4" t="n"/>
+      <c r="AR52" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS52" s="4" t="n"/>
+      <c r="AT52" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU52" s="4" t="n"/>
       <c r="AV52" s="4" t="n"/>
       <c r="AW52" s="4" t="n"/>
@@ -28142,19 +28291,19 @@
       <c r="BD52" s="4" t="n"/>
       <c r="BE52" s="4" t="n"/>
       <c r="BF52" s="4" t="n"/>
-      <c r="BG52" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH52" s="4" t="n"/>
+      <c r="BG52" s="4" t="n"/>
+      <c r="BH52" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI52" s="4" t="n"/>
-      <c r="BJ52" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BK52" s="4" t="n"/>
+      <c r="BJ52" s="4" t="n"/>
+      <c r="BK52" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BL52" s="4" t="n"/>
       <c r="BM52" s="4" t="n"/>
       <c r="BN52" s="4" t="n"/>
@@ -28180,6 +28329,7 @@
       <c r="CH52" s="4" t="n"/>
       <c r="CI52" s="4" t="n"/>
       <c r="CJ52" s="4" t="n"/>
+      <c r="CK52" s="4" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -28272,27 +28422,27 @@
       <c r="AN53" s="4" t="n"/>
       <c r="AO53" s="4" t="n"/>
       <c r="AP53" s="4" t="n"/>
-      <c r="AQ53" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR53" s="4" t="n"/>
-      <c r="AS53" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT53" s="4" t="n"/>
+      <c r="AQ53" s="4" t="n"/>
+      <c r="AR53" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS53" s="4" t="n"/>
+      <c r="AT53" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU53" s="4" t="n"/>
       <c r="AV53" s="4" t="n"/>
       <c r="AW53" s="4" t="n"/>
-      <c r="AX53" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AY53" s="4" t="n"/>
+      <c r="AX53" s="4" t="n"/>
+      <c r="AY53" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ53" s="4" t="n"/>
       <c r="BA53" s="4" t="n"/>
       <c r="BB53" s="4" t="n"/>
@@ -28300,12 +28450,12 @@
       <c r="BD53" s="4" t="n"/>
       <c r="BE53" s="4" t="n"/>
       <c r="BF53" s="4" t="n"/>
-      <c r="BG53" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH53" s="4" t="n"/>
+      <c r="BG53" s="4" t="n"/>
+      <c r="BH53" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI53" s="4" t="n"/>
       <c r="BJ53" s="4" t="n"/>
       <c r="BK53" s="4" t="n"/>
@@ -28329,15 +28479,16 @@
       <c r="CC53" s="4" t="n"/>
       <c r="CD53" s="4" t="n"/>
       <c r="CE53" s="4" t="n"/>
-      <c r="CF53" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CG53" s="4" t="n"/>
+      <c r="CF53" s="4" t="n"/>
+      <c r="CG53" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CH53" s="4" t="n"/>
       <c r="CI53" s="4" t="n"/>
       <c r="CJ53" s="4" t="n"/>
+      <c r="CK53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n"/>
@@ -28426,11 +28577,7 @@
       <c r="AN54" s="4" t="n"/>
       <c r="AO54" s="4" t="n"/>
       <c r="AP54" s="4" t="n"/>
-      <c r="AQ54" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AQ54" s="4" t="n"/>
       <c r="AR54" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -28441,7 +28588,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AT54" s="4" t="n"/>
+      <c r="AT54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU54" s="4" t="n"/>
       <c r="AV54" s="4" t="n"/>
       <c r="AW54" s="4" t="n"/>
@@ -28452,11 +28603,7 @@
       <c r="BB54" s="4" t="n"/>
       <c r="BC54" s="4" t="n"/>
       <c r="BD54" s="4" t="n"/>
-      <c r="BE54" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BE54" s="4" t="n"/>
       <c r="BF54" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -28467,18 +28614,22 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="BH54" s="4" t="n"/>
+      <c r="BH54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI54" s="4" t="n"/>
       <c r="BJ54" s="4" t="n"/>
       <c r="BK54" s="4" t="n"/>
       <c r="BL54" s="4" t="n"/>
       <c r="BM54" s="4" t="n"/>
-      <c r="BN54" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BO54" s="4" t="n"/>
+      <c r="BN54" s="4" t="n"/>
+      <c r="BO54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BP54" s="4" t="n"/>
       <c r="BQ54" s="4" t="n"/>
       <c r="BR54" s="4" t="n"/>
@@ -28495,15 +28646,16 @@
       <c r="CC54" s="4" t="n"/>
       <c r="CD54" s="4" t="n"/>
       <c r="CE54" s="4" t="n"/>
-      <c r="CF54" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CG54" s="4" t="n"/>
+      <c r="CF54" s="4" t="n"/>
+      <c r="CG54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CH54" s="4" t="n"/>
       <c r="CI54" s="4" t="n"/>
-      <c r="CJ54" s="4" t="inlineStr">
+      <c r="CJ54" s="4" t="n"/>
+      <c r="CK54" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -28580,17 +28732,17 @@
       </c>
       <c r="AO55" s="4" t="n"/>
       <c r="AP55" s="4" t="n"/>
-      <c r="AQ55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AQ55" s="4" t="n"/>
       <c r="AR55" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AS55" s="4" t="n"/>
+      <c r="AS55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT55" s="4" t="n"/>
       <c r="AU55" s="4" t="n"/>
       <c r="AV55" s="4" t="n"/>
@@ -28602,26 +28754,26 @@
       <c r="BB55" s="4" t="n"/>
       <c r="BC55" s="4" t="n"/>
       <c r="BD55" s="4" t="n"/>
-      <c r="BE55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BF55" s="4" t="n"/>
+      <c r="BE55" s="4" t="n"/>
+      <c r="BF55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BG55" s="4" t="n"/>
       <c r="BH55" s="4" t="n"/>
       <c r="BI55" s="4" t="n"/>
-      <c r="BJ55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BJ55" s="4" t="n"/>
       <c r="BK55" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BL55" s="4" t="n"/>
+      <c r="BL55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BM55" s="4" t="n"/>
       <c r="BN55" s="4" t="n"/>
       <c r="BO55" s="4" t="n"/>
@@ -28646,6 +28798,7 @@
       <c r="CH55" s="4" t="n"/>
       <c r="CI55" s="4" t="n"/>
       <c r="CJ55" s="4" t="n"/>
+      <c r="CK55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n"/>
@@ -28722,18 +28875,18 @@
       <c r="AN56" s="4" t="n"/>
       <c r="AO56" s="4" t="n"/>
       <c r="AP56" s="4" t="n"/>
-      <c r="AQ56" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR56" s="4" t="n"/>
-      <c r="AS56" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT56" s="4" t="n"/>
+      <c r="AQ56" s="4" t="n"/>
+      <c r="AR56" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS56" s="4" t="n"/>
+      <c r="AT56" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU56" s="4" t="n"/>
       <c r="AV56" s="4" t="n"/>
       <c r="AW56" s="4" t="n"/>
@@ -28746,12 +28899,12 @@
       <c r="BD56" s="4" t="n"/>
       <c r="BE56" s="4" t="n"/>
       <c r="BF56" s="4" t="n"/>
-      <c r="BG56" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH56" s="4" t="n"/>
+      <c r="BG56" s="4" t="n"/>
+      <c r="BH56" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI56" s="4" t="n"/>
       <c r="BJ56" s="4" t="n"/>
       <c r="BK56" s="4" t="n"/>
@@ -28779,7 +28932,8 @@
       <c r="CG56" s="4" t="n"/>
       <c r="CH56" s="4" t="n"/>
       <c r="CI56" s="4" t="n"/>
-      <c r="CJ56" s="4" t="inlineStr">
+      <c r="CJ56" s="4" t="n"/>
+      <c r="CK56" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -28880,31 +29034,31 @@
         </is>
       </c>
       <c r="AP57" s="4" t="n"/>
-      <c r="AQ57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR57" s="4" t="n"/>
-      <c r="AS57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AQ57" s="4" t="n"/>
+      <c r="AR57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS57" s="4" t="n"/>
       <c r="AT57" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AU57" s="4" t="n"/>
+      <c r="AU57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AV57" s="4" t="n"/>
       <c r="AW57" s="4" t="n"/>
-      <c r="AX57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AY57" s="4" t="n"/>
+      <c r="AX57" s="4" t="n"/>
+      <c r="AY57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ57" s="4" t="n"/>
       <c r="BA57" s="4" t="n"/>
       <c r="BB57" s="4" t="n"/>
@@ -28912,12 +29066,12 @@
       <c r="BD57" s="4" t="n"/>
       <c r="BE57" s="4" t="n"/>
       <c r="BF57" s="4" t="n"/>
-      <c r="BG57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH57" s="4" t="n"/>
+      <c r="BG57" s="4" t="n"/>
+      <c r="BH57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI57" s="4" t="n"/>
       <c r="BJ57" s="4" t="n"/>
       <c r="BK57" s="4" t="n"/>
@@ -28941,15 +29095,16 @@
       <c r="CC57" s="4" t="n"/>
       <c r="CD57" s="4" t="n"/>
       <c r="CE57" s="4" t="n"/>
-      <c r="CF57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CG57" s="4" t="n"/>
+      <c r="CF57" s="4" t="n"/>
+      <c r="CG57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CH57" s="4" t="n"/>
       <c r="CI57" s="4" t="n"/>
-      <c r="CJ57" s="4" t="inlineStr">
+      <c r="CJ57" s="4" t="n"/>
+      <c r="CK57" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -29058,18 +29213,18 @@
       <c r="AN58" s="4" t="n"/>
       <c r="AO58" s="4" t="n"/>
       <c r="AP58" s="4" t="n"/>
-      <c r="AQ58" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR58" s="4" t="n"/>
-      <c r="AS58" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT58" s="4" t="n"/>
+      <c r="AQ58" s="4" t="n"/>
+      <c r="AR58" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS58" s="4" t="n"/>
+      <c r="AT58" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU58" s="4" t="n"/>
       <c r="AV58" s="4" t="n"/>
       <c r="AW58" s="4" t="n"/>
@@ -29079,19 +29234,19 @@
       <c r="BA58" s="4" t="n"/>
       <c r="BB58" s="4" t="n"/>
       <c r="BC58" s="4" t="n"/>
-      <c r="BD58" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BE58" s="4" t="n"/>
+      <c r="BD58" s="4" t="n"/>
+      <c r="BE58" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BF58" s="4" t="n"/>
-      <c r="BG58" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH58" s="4" t="n"/>
+      <c r="BG58" s="4" t="n"/>
+      <c r="BH58" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI58" s="4" t="n"/>
       <c r="BJ58" s="4" t="n"/>
       <c r="BK58" s="4" t="n"/>
@@ -29120,6 +29275,7 @@
       <c r="CH58" s="4" t="n"/>
       <c r="CI58" s="4" t="n"/>
       <c r="CJ58" s="4" t="n"/>
+      <c r="CK58" s="4" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n"/>
@@ -29196,17 +29352,17 @@
       </c>
       <c r="AO59" s="4" t="n"/>
       <c r="AP59" s="4" t="n"/>
-      <c r="AQ59" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AQ59" s="4" t="n"/>
       <c r="AR59" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AS59" s="4" t="n"/>
+      <c r="AS59" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT59" s="4" t="n"/>
       <c r="AU59" s="4" t="n"/>
       <c r="AV59" s="4" t="n"/>
@@ -29220,18 +29376,18 @@
       <c r="BD59" s="4" t="n"/>
       <c r="BE59" s="4" t="n"/>
       <c r="BF59" s="4" t="n"/>
-      <c r="BG59" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH59" s="4" t="n"/>
-      <c r="BI59" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BJ59" s="4" t="n"/>
+      <c r="BG59" s="4" t="n"/>
+      <c r="BH59" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI59" s="4" t="n"/>
+      <c r="BJ59" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BK59" s="4" t="n"/>
       <c r="BL59" s="4" t="n"/>
       <c r="BM59" s="4" t="n"/>
@@ -29258,6 +29414,7 @@
       <c r="CH59" s="4" t="n"/>
       <c r="CI59" s="4" t="n"/>
       <c r="CJ59" s="4" t="n"/>
+      <c r="CK59" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n"/>
@@ -29338,18 +29495,18 @@
       <c r="AN60" s="4" t="n"/>
       <c r="AO60" s="4" t="n"/>
       <c r="AP60" s="4" t="n"/>
-      <c r="AQ60" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR60" s="4" t="n"/>
-      <c r="AS60" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT60" s="4" t="n"/>
+      <c r="AQ60" s="4" t="n"/>
+      <c r="AR60" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS60" s="4" t="n"/>
+      <c r="AT60" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU60" s="4" t="n"/>
       <c r="AV60" s="4" t="n"/>
       <c r="AW60" s="4" t="n"/>
@@ -29362,12 +29519,12 @@
       <c r="BD60" s="4" t="n"/>
       <c r="BE60" s="4" t="n"/>
       <c r="BF60" s="4" t="n"/>
-      <c r="BG60" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH60" s="4" t="n"/>
+      <c r="BG60" s="4" t="n"/>
+      <c r="BH60" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI60" s="4" t="n"/>
       <c r="BJ60" s="4" t="n"/>
       <c r="BK60" s="4" t="n"/>
@@ -29395,7 +29552,8 @@
       <c r="CG60" s="4" t="n"/>
       <c r="CH60" s="4" t="n"/>
       <c r="CI60" s="4" t="n"/>
-      <c r="CJ60" s="4" t="inlineStr">
+      <c r="CJ60" s="4" t="n"/>
+      <c r="CK60" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -29484,12 +29642,12 @@
       </c>
       <c r="AO61" s="4" t="n"/>
       <c r="AP61" s="4" t="n"/>
-      <c r="AQ61" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR61" s="4" t="n"/>
+      <c r="AQ61" s="4" t="n"/>
+      <c r="AR61" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS61" s="4" t="n"/>
       <c r="AT61" s="4" t="n"/>
       <c r="AU61" s="4" t="n"/>
@@ -29502,30 +29660,30 @@
       <c r="BB61" s="4" t="n"/>
       <c r="BC61" s="4" t="n"/>
       <c r="BD61" s="4" t="n"/>
-      <c r="BE61" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BF61" s="4" t="n"/>
-      <c r="BG61" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH61" s="4" t="n"/>
-      <c r="BI61" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BJ61" s="4" t="n"/>
-      <c r="BK61" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BL61" s="4" t="n"/>
+      <c r="BE61" s="4" t="n"/>
+      <c r="BF61" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BG61" s="4" t="n"/>
+      <c r="BH61" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI61" s="4" t="n"/>
+      <c r="BJ61" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BK61" s="4" t="n"/>
+      <c r="BL61" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BM61" s="4" t="n"/>
       <c r="BN61" s="4" t="n"/>
       <c r="BO61" s="4" t="n"/>
@@ -29550,6 +29708,7 @@
       <c r="CH61" s="4" t="n"/>
       <c r="CI61" s="4" t="n"/>
       <c r="CJ61" s="4" t="n"/>
+      <c r="CK61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="n"/>
@@ -29638,38 +29797,38 @@
       </c>
       <c r="AO62" s="4" t="n"/>
       <c r="AP62" s="4" t="n"/>
-      <c r="AQ62" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR62" s="4" t="n"/>
+      <c r="AQ62" s="4" t="n"/>
+      <c r="AR62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS62" s="4" t="n"/>
       <c r="AT62" s="4" t="n"/>
       <c r="AU62" s="4" t="n"/>
       <c r="AV62" s="4" t="n"/>
       <c r="AW62" s="4" t="n"/>
-      <c r="AX62" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AY62" s="4" t="n"/>
+      <c r="AX62" s="4" t="n"/>
+      <c r="AY62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ62" s="4" t="n"/>
       <c r="BA62" s="4" t="n"/>
       <c r="BB62" s="4" t="n"/>
       <c r="BC62" s="4" t="n"/>
-      <c r="BD62" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BD62" s="4" t="n"/>
       <c r="BE62" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BF62" s="4" t="n"/>
+      <c r="BF62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BG62" s="4" t="n"/>
       <c r="BH62" s="4" t="n"/>
       <c r="BI62" s="4" t="n"/>
@@ -29700,6 +29859,7 @@
       <c r="CH62" s="4" t="n"/>
       <c r="CI62" s="4" t="n"/>
       <c r="CJ62" s="4" t="n"/>
+      <c r="CK62" s="4" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n"/>
@@ -29792,11 +29952,7 @@
       </c>
       <c r="AO63" s="4" t="n"/>
       <c r="AP63" s="4" t="n"/>
-      <c r="AQ63" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AQ63" s="4" t="n"/>
       <c r="AR63" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -29807,7 +29963,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AT63" s="4" t="n"/>
+      <c r="AT63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU63" s="4" t="n"/>
       <c r="AV63" s="4" t="n"/>
       <c r="AW63" s="4" t="n"/>
@@ -29819,17 +29979,17 @@
       <c r="BC63" s="4" t="n"/>
       <c r="BD63" s="4" t="n"/>
       <c r="BE63" s="4" t="n"/>
-      <c r="BF63" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BF63" s="4" t="n"/>
       <c r="BG63" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BH63" s="4" t="n"/>
+      <c r="BH63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI63" s="4" t="n"/>
       <c r="BJ63" s="4" t="n"/>
       <c r="BK63" s="4" t="n"/>
@@ -29858,6 +30018,7 @@
       <c r="CH63" s="4" t="n"/>
       <c r="CI63" s="4" t="n"/>
       <c r="CJ63" s="4" t="n"/>
+      <c r="CK63" s="4" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n"/>
@@ -29954,11 +30115,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AQ64" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AQ64" s="4" t="n"/>
       <c r="AR64" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -29969,16 +30126,20 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AT64" s="4" t="n"/>
+      <c r="AT64" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU64" s="4" t="n"/>
       <c r="AV64" s="4" t="n"/>
       <c r="AW64" s="4" t="n"/>
-      <c r="AX64" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AY64" s="4" t="n"/>
+      <c r="AX64" s="4" t="n"/>
+      <c r="AY64" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ64" s="4" t="n"/>
       <c r="BA64" s="4" t="n"/>
       <c r="BB64" s="4" t="n"/>
@@ -29986,12 +30147,12 @@
       <c r="BD64" s="4" t="n"/>
       <c r="BE64" s="4" t="n"/>
       <c r="BF64" s="4" t="n"/>
-      <c r="BG64" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH64" s="4" t="n"/>
+      <c r="BG64" s="4" t="n"/>
+      <c r="BH64" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI64" s="4" t="n"/>
       <c r="BJ64" s="4" t="n"/>
       <c r="BK64" s="4" t="n"/>
@@ -30018,12 +30179,13 @@
       <c r="CF64" s="4" t="n"/>
       <c r="CG64" s="4" t="n"/>
       <c r="CH64" s="4" t="n"/>
-      <c r="CI64" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CJ64" s="4" t="n"/>
+      <c r="CI64" s="4" t="n"/>
+      <c r="CJ64" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CK64" s="4" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -30100,48 +30262,48 @@
       <c r="AN65" s="4" t="n"/>
       <c r="AO65" s="4" t="n"/>
       <c r="AP65" s="4" t="n"/>
-      <c r="AQ65" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR65" s="4" t="n"/>
-      <c r="AS65" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT65" s="4" t="n"/>
+      <c r="AQ65" s="4" t="n"/>
+      <c r="AR65" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS65" s="4" t="n"/>
+      <c r="AT65" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU65" s="4" t="n"/>
       <c r="AV65" s="4" t="n"/>
       <c r="AW65" s="4" t="n"/>
-      <c r="AX65" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AX65" s="4" t="n"/>
       <c r="AY65" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="AZ65" s="4" t="n"/>
+      <c r="AZ65" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BA65" s="4" t="n"/>
       <c r="BB65" s="4" t="n"/>
       <c r="BC65" s="4" t="n"/>
-      <c r="BD65" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BE65" s="4" t="n"/>
+      <c r="BD65" s="4" t="n"/>
+      <c r="BE65" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BF65" s="4" t="n"/>
-      <c r="BG65" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH65" s="4" t="n"/>
+      <c r="BG65" s="4" t="n"/>
+      <c r="BH65" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI65" s="4" t="n"/>
       <c r="BJ65" s="4" t="n"/>
       <c r="BK65" s="4" t="n"/>
@@ -30170,6 +30332,7 @@
       <c r="CH65" s="4" t="n"/>
       <c r="CI65" s="4" t="n"/>
       <c r="CJ65" s="4" t="n"/>
+      <c r="CK65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="n"/>
@@ -30262,18 +30425,18 @@
       <c r="AN66" s="4" t="n"/>
       <c r="AO66" s="4" t="n"/>
       <c r="AP66" s="4" t="n"/>
-      <c r="AQ66" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR66" s="4" t="n"/>
-      <c r="AS66" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT66" s="4" t="n"/>
+      <c r="AQ66" s="4" t="n"/>
+      <c r="AR66" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS66" s="4" t="n"/>
+      <c r="AT66" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU66" s="4" t="n"/>
       <c r="AV66" s="4" t="n"/>
       <c r="AW66" s="4" t="n"/>
@@ -30286,12 +30449,12 @@
       <c r="BD66" s="4" t="n"/>
       <c r="BE66" s="4" t="n"/>
       <c r="BF66" s="4" t="n"/>
-      <c r="BG66" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH66" s="4" t="n"/>
+      <c r="BG66" s="4" t="n"/>
+      <c r="BH66" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI66" s="4" t="n"/>
       <c r="BJ66" s="4" t="n"/>
       <c r="BK66" s="4" t="n"/>
@@ -30320,6 +30483,7 @@
       <c r="CH66" s="4" t="n"/>
       <c r="CI66" s="4" t="n"/>
       <c r="CJ66" s="4" t="n"/>
+      <c r="CK66" s="4" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n"/>
@@ -30407,27 +30571,23 @@
       <c r="AU67" s="4" t="n"/>
       <c r="AV67" s="4" t="n"/>
       <c r="AW67" s="4" t="n"/>
-      <c r="AX67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AY67" s="4" t="n"/>
+      <c r="AX67" s="4" t="n"/>
+      <c r="AY67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ67" s="4" t="n"/>
       <c r="BA67" s="4" t="n"/>
       <c r="BB67" s="4" t="n"/>
       <c r="BC67" s="4" t="n"/>
-      <c r="BD67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BE67" s="4" t="n"/>
-      <c r="BF67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BD67" s="4" t="n"/>
+      <c r="BE67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BF67" s="4" t="n"/>
       <c r="BG67" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -30443,39 +30603,43 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="BJ67" s="4" t="n"/>
+      <c r="BJ67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BK67" s="4" t="n"/>
       <c r="BL67" s="4" t="n"/>
       <c r="BM67" s="4" t="n"/>
-      <c r="BN67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BN67" s="4" t="n"/>
       <c r="BO67" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BP67" s="4" t="n"/>
-      <c r="BQ67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BP67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BQ67" s="4" t="n"/>
       <c r="BR67" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BS67" s="4" t="n"/>
+      <c r="BS67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BT67" s="4" t="n"/>
-      <c r="BU67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BV67" s="4" t="n"/>
+      <c r="BU67" s="4" t="n"/>
+      <c r="BV67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BW67" s="4" t="n"/>
       <c r="BX67" s="4" t="n"/>
       <c r="BY67" s="4" t="n"/>
@@ -30490,6 +30654,7 @@
       <c r="CH67" s="4" t="n"/>
       <c r="CI67" s="4" t="n"/>
       <c r="CJ67" s="4" t="n"/>
+      <c r="CK67" s="4" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n"/>
@@ -30566,53 +30731,53 @@
       <c r="AN68" s="4" t="n"/>
       <c r="AO68" s="4" t="n"/>
       <c r="AP68" s="4" t="n"/>
-      <c r="AQ68" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR68" s="4" t="n"/>
-      <c r="AS68" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT68" s="4" t="n"/>
+      <c r="AQ68" s="4" t="n"/>
+      <c r="AR68" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS68" s="4" t="n"/>
+      <c r="AT68" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU68" s="4" t="n"/>
       <c r="AV68" s="4" t="n"/>
       <c r="AW68" s="4" t="n"/>
-      <c r="AX68" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AY68" s="4" t="n"/>
+      <c r="AX68" s="4" t="n"/>
+      <c r="AY68" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ68" s="4" t="n"/>
       <c r="BA68" s="4" t="n"/>
       <c r="BB68" s="4" t="n"/>
       <c r="BC68" s="4" t="n"/>
-      <c r="BD68" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BE68" s="4" t="n"/>
+      <c r="BD68" s="4" t="n"/>
+      <c r="BE68" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BF68" s="4" t="n"/>
-      <c r="BG68" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH68" s="4" t="n"/>
+      <c r="BG68" s="4" t="n"/>
+      <c r="BH68" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI68" s="4" t="n"/>
       <c r="BJ68" s="4" t="n"/>
       <c r="BK68" s="4" t="n"/>
-      <c r="BL68" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BM68" s="4" t="n"/>
+      <c r="BL68" s="4" t="n"/>
+      <c r="BM68" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BN68" s="4" t="n"/>
       <c r="BO68" s="4" t="n"/>
       <c r="BP68" s="4" t="n"/>
@@ -30634,12 +30799,13 @@
       <c r="CF68" s="4" t="n"/>
       <c r="CG68" s="4" t="n"/>
       <c r="CH68" s="4" t="n"/>
-      <c r="CI68" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CJ68" s="4" t="n"/>
+      <c r="CI68" s="4" t="n"/>
+      <c r="CJ68" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="CK68" s="4" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -30736,12 +30902,12 @@
       </c>
       <c r="AO69" s="4" t="n"/>
       <c r="AP69" s="4" t="n"/>
-      <c r="AQ69" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR69" s="4" t="n"/>
+      <c r="AQ69" s="4" t="n"/>
+      <c r="AR69" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS69" s="4" t="n"/>
       <c r="AT69" s="4" t="n"/>
       <c r="AU69" s="4" t="n"/>
@@ -30753,26 +30919,26 @@
       <c r="BA69" s="4" t="n"/>
       <c r="BB69" s="4" t="n"/>
       <c r="BC69" s="4" t="n"/>
-      <c r="BD69" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BE69" s="4" t="n"/>
+      <c r="BD69" s="4" t="n"/>
+      <c r="BE69" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BF69" s="4" t="n"/>
-      <c r="BG69" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH69" s="4" t="n"/>
+      <c r="BG69" s="4" t="n"/>
+      <c r="BH69" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI69" s="4" t="n"/>
-      <c r="BJ69" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BK69" s="4" t="n"/>
+      <c r="BJ69" s="4" t="n"/>
+      <c r="BK69" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BL69" s="4" t="n"/>
       <c r="BM69" s="4" t="n"/>
       <c r="BN69" s="4" t="n"/>
@@ -30792,16 +30958,17 @@
       <c r="CB69" s="4" t="n"/>
       <c r="CC69" s="4" t="n"/>
       <c r="CD69" s="4" t="n"/>
-      <c r="CE69" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CF69" s="4" t="n"/>
+      <c r="CE69" s="4" t="n"/>
+      <c r="CF69" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CG69" s="4" t="n"/>
       <c r="CH69" s="4" t="n"/>
       <c r="CI69" s="4" t="n"/>
       <c r="CJ69" s="4" t="n"/>
+      <c r="CK69" s="4" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="n"/>
@@ -30886,12 +31053,12 @@
       </c>
       <c r="AO70" s="4" t="n"/>
       <c r="AP70" s="4" t="n"/>
-      <c r="AQ70" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR70" s="4" t="n"/>
+      <c r="AQ70" s="4" t="n"/>
+      <c r="AR70" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS70" s="4" t="n"/>
       <c r="AT70" s="4" t="n"/>
       <c r="AU70" s="4" t="n"/>
@@ -30906,18 +31073,18 @@
       <c r="BD70" s="4" t="n"/>
       <c r="BE70" s="4" t="n"/>
       <c r="BF70" s="4" t="n"/>
-      <c r="BG70" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH70" s="4" t="n"/>
-      <c r="BI70" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BJ70" s="4" t="n"/>
+      <c r="BG70" s="4" t="n"/>
+      <c r="BH70" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI70" s="4" t="n"/>
+      <c r="BJ70" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BK70" s="4" t="n"/>
       <c r="BL70" s="4" t="n"/>
       <c r="BM70" s="4" t="n"/>
@@ -30933,12 +31100,12 @@
       <c r="BW70" s="4" t="n"/>
       <c r="BX70" s="4" t="n"/>
       <c r="BY70" s="4" t="n"/>
-      <c r="BZ70" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CA70" s="4" t="n"/>
+      <c r="BZ70" s="4" t="n"/>
+      <c r="CA70" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CB70" s="4" t="n"/>
       <c r="CC70" s="4" t="n"/>
       <c r="CD70" s="4" t="n"/>
@@ -30948,6 +31115,7 @@
       <c r="CH70" s="4" t="n"/>
       <c r="CI70" s="4" t="n"/>
       <c r="CJ70" s="4" t="n"/>
+      <c r="CK70" s="4" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n"/>
@@ -31036,40 +31204,40 @@
       <c r="AN71" s="4" t="n"/>
       <c r="AO71" s="4" t="n"/>
       <c r="AP71" s="4" t="n"/>
-      <c r="AQ71" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR71" s="4" t="n"/>
-      <c r="AS71" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT71" s="4" t="n"/>
+      <c r="AQ71" s="4" t="n"/>
+      <c r="AR71" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS71" s="4" t="n"/>
+      <c r="AT71" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU71" s="4" t="n"/>
       <c r="AV71" s="4" t="n"/>
       <c r="AW71" s="4" t="n"/>
       <c r="AX71" s="4" t="n"/>
-      <c r="AY71" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AZ71" s="4" t="n"/>
+      <c r="AY71" s="4" t="n"/>
+      <c r="AZ71" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BA71" s="4" t="n"/>
       <c r="BB71" s="4" t="n"/>
       <c r="BC71" s="4" t="n"/>
       <c r="BD71" s="4" t="n"/>
       <c r="BE71" s="4" t="n"/>
       <c r="BF71" s="4" t="n"/>
-      <c r="BG71" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH71" s="4" t="n"/>
+      <c r="BG71" s="4" t="n"/>
+      <c r="BH71" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI71" s="4" t="n"/>
       <c r="BJ71" s="4" t="n"/>
       <c r="BK71" s="4" t="n"/>
@@ -31098,6 +31266,7 @@
       <c r="CH71" s="4" t="n"/>
       <c r="CI71" s="4" t="n"/>
       <c r="CJ71" s="4" t="n"/>
+      <c r="CK71" s="4" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n"/>
@@ -31196,50 +31365,54 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AS72" s="4" t="n"/>
+      <c r="AS72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT72" s="4" t="n"/>
       <c r="AU72" s="4" t="n"/>
       <c r="AV72" s="4" t="n"/>
       <c r="AW72" s="4" t="n"/>
-      <c r="AX72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AY72" s="4" t="n"/>
+      <c r="AX72" s="4" t="n"/>
+      <c r="AY72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ72" s="4" t="n"/>
       <c r="BA72" s="4" t="n"/>
       <c r="BB72" s="4" t="n"/>
       <c r="BC72" s="4" t="n"/>
       <c r="BD72" s="4" t="n"/>
-      <c r="BE72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BE72" s="4" t="n"/>
       <c r="BF72" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BG72" s="4" t="n"/>
+      <c r="BG72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BH72" s="4" t="n"/>
-      <c r="BI72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BJ72" s="4" t="n"/>
+      <c r="BI72" s="4" t="n"/>
+      <c r="BJ72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BK72" s="4" t="n"/>
       <c r="BL72" s="4" t="n"/>
       <c r="BM72" s="4" t="n"/>
       <c r="BN72" s="4" t="n"/>
-      <c r="BO72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BP72" s="4" t="n"/>
+      <c r="BO72" s="4" t="n"/>
+      <c r="BP72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BQ72" s="4" t="n"/>
       <c r="BR72" s="4" t="n"/>
       <c r="BS72" s="4" t="n"/>
@@ -31254,16 +31427,17 @@
       <c r="CB72" s="4" t="n"/>
       <c r="CC72" s="4" t="n"/>
       <c r="CD72" s="4" t="n"/>
-      <c r="CE72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CF72" s="4" t="n"/>
+      <c r="CE72" s="4" t="n"/>
+      <c r="CF72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CG72" s="4" t="n"/>
       <c r="CH72" s="4" t="n"/>
       <c r="CI72" s="4" t="n"/>
       <c r="CJ72" s="4" t="n"/>
+      <c r="CK72" s="4" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -31333,12 +31507,12 @@
       <c r="AO73" s="4" t="n"/>
       <c r="AP73" s="4" t="n"/>
       <c r="AQ73" s="4" t="n"/>
-      <c r="AR73" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS73" s="4" t="n"/>
+      <c r="AR73" s="4" t="n"/>
+      <c r="AS73" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT73" s="4" t="n"/>
       <c r="AU73" s="4" t="n"/>
       <c r="AV73" s="4" t="n"/>
@@ -31351,23 +31525,23 @@
       <c r="BC73" s="4" t="n"/>
       <c r="BD73" s="4" t="n"/>
       <c r="BE73" s="4" t="n"/>
-      <c r="BF73" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BF73" s="4" t="n"/>
       <c r="BG73" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BH73" s="4" t="n"/>
-      <c r="BI73" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BJ73" s="4" t="n"/>
+      <c r="BH73" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI73" s="4" t="n"/>
+      <c r="BJ73" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BK73" s="4" t="n"/>
       <c r="BL73" s="4" t="n"/>
       <c r="BM73" s="4" t="n"/>
@@ -31385,12 +31559,12 @@
       <c r="BY73" s="4" t="n"/>
       <c r="BZ73" s="4" t="n"/>
       <c r="CA73" s="4" t="n"/>
-      <c r="CB73" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="CC73" s="4" t="n"/>
+      <c r="CB73" s="4" t="n"/>
+      <c r="CC73" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CD73" s="4" t="n"/>
       <c r="CE73" s="4" t="n"/>
       <c r="CF73" s="4" t="n"/>
@@ -31398,6 +31572,7 @@
       <c r="CH73" s="4" t="n"/>
       <c r="CI73" s="4" t="n"/>
       <c r="CJ73" s="4" t="n"/>
+      <c r="CK73" s="4" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="n"/>
@@ -31478,11 +31653,7 @@
       <c r="AN74" s="4" t="n"/>
       <c r="AO74" s="4" t="n"/>
       <c r="AP74" s="4" t="n"/>
-      <c r="AQ74" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AQ74" s="4" t="n"/>
       <c r="AR74" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -31493,33 +31664,37 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AT74" s="4" t="n"/>
+      <c r="AT74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU74" s="4" t="n"/>
       <c r="AV74" s="4" t="n"/>
       <c r="AW74" s="4" t="n"/>
-      <c r="AX74" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AY74" s="4" t="n"/>
+      <c r="AX74" s="4" t="n"/>
+      <c r="AY74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ74" s="4" t="n"/>
       <c r="BA74" s="4" t="n"/>
       <c r="BB74" s="4" t="n"/>
       <c r="BC74" s="4" t="n"/>
-      <c r="BD74" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BE74" s="4" t="n"/>
+      <c r="BD74" s="4" t="n"/>
+      <c r="BE74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BF74" s="4" t="n"/>
-      <c r="BG74" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH74" s="4" t="n"/>
+      <c r="BG74" s="4" t="n"/>
+      <c r="BH74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI74" s="4" t="n"/>
       <c r="BJ74" s="4" t="n"/>
       <c r="BK74" s="4" t="n"/>
@@ -31547,7 +31722,8 @@
       <c r="CG74" s="4" t="n"/>
       <c r="CH74" s="4" t="n"/>
       <c r="CI74" s="4" t="n"/>
-      <c r="CJ74" s="4" t="inlineStr">
+      <c r="CJ74" s="4" t="n"/>
+      <c r="CK74" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -31640,71 +31816,71 @@
       <c r="AN75" s="4" t="n"/>
       <c r="AO75" s="4" t="n"/>
       <c r="AP75" s="4" t="n"/>
-      <c r="AQ75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR75" s="4" t="n"/>
-      <c r="AS75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT75" s="4" t="n"/>
+      <c r="AQ75" s="4" t="n"/>
+      <c r="AR75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS75" s="4" t="n"/>
+      <c r="AT75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU75" s="4" t="n"/>
       <c r="AV75" s="4" t="n"/>
       <c r="AW75" s="4" t="n"/>
-      <c r="AX75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AY75" s="4" t="n"/>
+      <c r="AX75" s="4" t="n"/>
+      <c r="AY75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AZ75" s="4" t="n"/>
       <c r="BA75" s="4" t="n"/>
       <c r="BB75" s="4" t="n"/>
       <c r="BC75" s="4" t="n"/>
-      <c r="BD75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BE75" s="4" t="n"/>
+      <c r="BD75" s="4" t="n"/>
+      <c r="BE75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BF75" s="4" t="n"/>
-      <c r="BG75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH75" s="4" t="n"/>
-      <c r="BI75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BJ75" s="4" t="n"/>
+      <c r="BG75" s="4" t="n"/>
+      <c r="BH75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI75" s="4" t="n"/>
+      <c r="BJ75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BK75" s="4" t="n"/>
       <c r="BL75" s="4" t="n"/>
       <c r="BM75" s="4" t="n"/>
-      <c r="BN75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BO75" s="4" t="n"/>
+      <c r="BN75" s="4" t="n"/>
+      <c r="BO75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BP75" s="4" t="n"/>
       <c r="BQ75" s="4" t="n"/>
       <c r="BR75" s="4" t="n"/>
       <c r="BS75" s="4" t="n"/>
       <c r="BT75" s="4" t="n"/>
       <c r="BU75" s="4" t="n"/>
-      <c r="BV75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BW75" s="4" t="n"/>
+      <c r="BV75" s="4" t="n"/>
+      <c r="BW75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BX75" s="4" t="n"/>
       <c r="BY75" s="4" t="n"/>
       <c r="BZ75" s="4" t="n"/>
@@ -31718,6 +31894,7 @@
       <c r="CH75" s="4" t="n"/>
       <c r="CI75" s="4" t="n"/>
       <c r="CJ75" s="4" t="n"/>
+      <c r="CK75" s="4" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="n"/>
@@ -31775,12 +31952,12 @@
       <c r="AO76" s="4" t="n"/>
       <c r="AP76" s="4" t="n"/>
       <c r="AQ76" s="4" t="n"/>
-      <c r="AR76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AS76" s="4" t="n"/>
+      <c r="AR76" s="4" t="n"/>
+      <c r="AS76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT76" s="4" t="n"/>
       <c r="AU76" s="4" t="n"/>
       <c r="AV76" s="4" t="n"/>
@@ -31792,17 +31969,17 @@
       <c r="BB76" s="4" t="n"/>
       <c r="BC76" s="4" t="n"/>
       <c r="BD76" s="4" t="n"/>
-      <c r="BE76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BE76" s="4" t="n"/>
       <c r="BF76" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BG76" s="4" t="n"/>
+      <c r="BG76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BH76" s="4" t="n"/>
       <c r="BI76" s="4" t="n"/>
       <c r="BJ76" s="4" t="n"/>
@@ -31810,12 +31987,12 @@
       <c r="BL76" s="4" t="n"/>
       <c r="BM76" s="4" t="n"/>
       <c r="BN76" s="4" t="n"/>
-      <c r="BO76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BP76" s="4" t="n"/>
+      <c r="BO76" s="4" t="n"/>
+      <c r="BP76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BQ76" s="4" t="n"/>
       <c r="BR76" s="4" t="n"/>
       <c r="BS76" s="4" t="n"/>
@@ -31826,11 +32003,7 @@
       <c r="BX76" s="4" t="n"/>
       <c r="BY76" s="4" t="n"/>
       <c r="BZ76" s="4" t="n"/>
-      <c r="CA76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="CA76" s="4" t="n"/>
       <c r="CB76" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -31841,13 +32014,18 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="CD76" s="4" t="n"/>
+      <c r="CD76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="CE76" s="4" t="n"/>
       <c r="CF76" s="4" t="n"/>
       <c r="CG76" s="4" t="n"/>
       <c r="CH76" s="4" t="n"/>
       <c r="CI76" s="4" t="n"/>
       <c r="CJ76" s="4" t="n"/>
+      <c r="CK76" s="4" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -31948,25 +32126,25 @@
       <c r="AN77" s="4" t="n"/>
       <c r="AO77" s="4" t="n"/>
       <c r="AP77" s="4" t="n"/>
-      <c r="AQ77" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR77" s="4" t="n"/>
-      <c r="AS77" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT77" s="4" t="n"/>
+      <c r="AQ77" s="4" t="n"/>
+      <c r="AR77" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS77" s="4" t="n"/>
+      <c r="AT77" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU77" s="4" t="n"/>
-      <c r="AV77" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AW77" s="4" t="n"/>
+      <c r="AV77" s="4" t="n"/>
+      <c r="AW77" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AX77" s="4" t="n"/>
       <c r="AY77" s="4" t="n"/>
       <c r="AZ77" s="4" t="n"/>
@@ -31976,12 +32154,12 @@
       <c r="BD77" s="4" t="n"/>
       <c r="BE77" s="4" t="n"/>
       <c r="BF77" s="4" t="n"/>
-      <c r="BG77" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH77" s="4" t="n"/>
+      <c r="BG77" s="4" t="n"/>
+      <c r="BH77" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI77" s="4" t="n"/>
       <c r="BJ77" s="4" t="n"/>
       <c r="BK77" s="4" t="n"/>
@@ -32010,6 +32188,7 @@
       <c r="CH77" s="4" t="n"/>
       <c r="CI77" s="4" t="n"/>
       <c r="CJ77" s="4" t="n"/>
+      <c r="CK77" s="4" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="n"/>
@@ -32102,18 +32281,18 @@
       <c r="AN78" s="4" t="n"/>
       <c r="AO78" s="4" t="n"/>
       <c r="AP78" s="4" t="n"/>
-      <c r="AQ78" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR78" s="4" t="n"/>
-      <c r="AS78" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT78" s="4" t="n"/>
+      <c r="AQ78" s="4" t="n"/>
+      <c r="AR78" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS78" s="4" t="n"/>
+      <c r="AT78" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU78" s="4" t="n"/>
       <c r="AV78" s="4" t="n"/>
       <c r="AW78" s="4" t="n"/>
@@ -32126,12 +32305,12 @@
       <c r="BD78" s="4" t="n"/>
       <c r="BE78" s="4" t="n"/>
       <c r="BF78" s="4" t="n"/>
-      <c r="BG78" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH78" s="4" t="n"/>
+      <c r="BG78" s="4" t="n"/>
+      <c r="BH78" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI78" s="4" t="n"/>
       <c r="BJ78" s="4" t="n"/>
       <c r="BK78" s="4" t="n"/>
@@ -32160,6 +32339,7 @@
       <c r="CH78" s="4" t="n"/>
       <c r="CI78" s="4" t="n"/>
       <c r="CJ78" s="4" t="n"/>
+      <c r="CK78" s="4" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n"/>
@@ -32248,18 +32428,18 @@
       <c r="AN79" s="4" t="n"/>
       <c r="AO79" s="4" t="n"/>
       <c r="AP79" s="4" t="n"/>
-      <c r="AQ79" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR79" s="4" t="n"/>
-      <c r="AS79" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT79" s="4" t="n"/>
+      <c r="AQ79" s="4" t="n"/>
+      <c r="AR79" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS79" s="4" t="n"/>
+      <c r="AT79" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU79" s="4" t="n"/>
       <c r="AV79" s="4" t="n"/>
       <c r="AW79" s="4" t="n"/>
@@ -32267,21 +32447,21 @@
       <c r="AY79" s="4" t="n"/>
       <c r="AZ79" s="4" t="n"/>
       <c r="BA79" s="4" t="n"/>
-      <c r="BB79" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BC79" s="4" t="n"/>
+      <c r="BB79" s="4" t="n"/>
+      <c r="BC79" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BD79" s="4" t="n"/>
       <c r="BE79" s="4" t="n"/>
       <c r="BF79" s="4" t="n"/>
-      <c r="BG79" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH79" s="4" t="n"/>
+      <c r="BG79" s="4" t="n"/>
+      <c r="BH79" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI79" s="4" t="n"/>
       <c r="BJ79" s="4" t="n"/>
       <c r="BK79" s="4" t="n"/>
@@ -32310,6 +32490,7 @@
       <c r="CH79" s="4" t="n"/>
       <c r="CI79" s="4" t="n"/>
       <c r="CJ79" s="4" t="n"/>
+      <c r="CK79" s="4" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="n"/>
@@ -32394,25 +32575,25 @@
       <c r="AN80" s="4" t="n"/>
       <c r="AO80" s="4" t="n"/>
       <c r="AP80" s="4" t="n"/>
-      <c r="AQ80" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR80" s="4" t="n"/>
-      <c r="AS80" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT80" s="4" t="n"/>
+      <c r="AQ80" s="4" t="n"/>
+      <c r="AR80" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS80" s="4" t="n"/>
+      <c r="AT80" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AU80" s="4" t="n"/>
-      <c r="AV80" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AW80" s="4" t="n"/>
+      <c r="AV80" s="4" t="n"/>
+      <c r="AW80" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AX80" s="4" t="n"/>
       <c r="AY80" s="4" t="n"/>
       <c r="AZ80" s="4" t="n"/>
@@ -32422,12 +32603,12 @@
       <c r="BD80" s="4" t="n"/>
       <c r="BE80" s="4" t="n"/>
       <c r="BF80" s="4" t="n"/>
-      <c r="BG80" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH80" s="4" t="n"/>
+      <c r="BG80" s="4" t="n"/>
+      <c r="BH80" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI80" s="4" t="n"/>
       <c r="BJ80" s="4" t="n"/>
       <c r="BK80" s="4" t="n"/>
@@ -32456,6 +32637,7 @@
       <c r="CH80" s="4" t="n"/>
       <c r="CI80" s="4" t="n"/>
       <c r="CJ80" s="4" t="n"/>
+      <c r="CK80" s="4" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
@@ -32586,6 +32768,7 @@
       <c r="CH81" s="4" t="n"/>
       <c r="CI81" s="4" t="n"/>
       <c r="CJ81" s="4" t="n"/>
+      <c r="CK81" s="4" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="n"/>
@@ -32696,6 +32879,7 @@
       <c r="CH82" s="4" t="n"/>
       <c r="CI82" s="4" t="n"/>
       <c r="CJ82" s="4" t="n"/>
+      <c r="CK82" s="4" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n"/>
@@ -32814,6 +32998,7 @@
       <c r="CH83" s="4" t="n"/>
       <c r="CI83" s="4" t="n"/>
       <c r="CJ83" s="4" t="n"/>
+      <c r="CK83" s="4" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="n"/>
@@ -32828,7 +33013,11 @@
       <c r="F84" s="4" t="n"/>
       <c r="G84" s="4" t="n"/>
       <c r="H84" s="4" t="n"/>
-      <c r="I84" s="4" t="n"/>
+      <c r="I84" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -32935,12 +33124,12 @@
       <c r="BI84" s="4" t="n"/>
       <c r="BJ84" s="4" t="n"/>
       <c r="BK84" s="4" t="n"/>
-      <c r="BL84" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BM84" s="4" t="n"/>
+      <c r="BL84" s="4" t="n"/>
+      <c r="BM84" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BN84" s="4" t="n"/>
       <c r="BO84" s="4" t="n"/>
       <c r="BP84" s="4" t="n"/>
@@ -32964,9 +33153,10 @@
       <c r="CH84" s="4" t="n"/>
       <c r="CI84" s="4" t="n"/>
       <c r="CJ84" s="4" t="n"/>
+      <c r="CK84" s="4" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:CJ84"/>
+  <autoFilter ref="A1:CK84"/>
   <mergeCells count="21">
     <mergeCell ref="A61:A64"/>
     <mergeCell ref="A69:A72"/>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -16412,7 +16412,7 @@
       <c r="U53" s="4" t="n"/>
       <c r="V53" s="4" t="n"/>
       <c r="W53" s="4" t="n">
-        <v>32.6</v>
+        <v>32.7</v>
       </c>
       <c r="X53" s="4" t="n"/>
       <c r="Y53" s="4" t="n"/>
@@ -16430,13 +16430,13 @@
         <v>33.64</v>
       </c>
       <c r="AI53" s="4" t="n">
-        <v>33.7</v>
+        <v>33.49</v>
       </c>
       <c r="AJ53" s="4" t="n">
         <v>33.29</v>
       </c>
       <c r="AK53" s="4" t="n">
-        <v>32.7</v>
+        <v>32.6</v>
       </c>
       <c r="AL53" s="4" t="n"/>
       <c r="AM53" s="4" t="n"/>
@@ -17477,11 +17477,17 @@
           <t>河岸狂飙</t>
         </is>
       </c>
-      <c r="C63" s="4" t="n"/>
-      <c r="D63" s="4" t="n"/>
-      <c r="E63" s="4" t="n"/>
+      <c r="C63" s="4" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="D63" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="E63" s="4" t="n">
+        <v>23.7</v>
+      </c>
       <c r="F63" s="4" t="n">
-        <v>23.09</v>
+        <v>23.05</v>
       </c>
       <c r="G63" s="4" t="n"/>
       <c r="H63" s="4" t="n"/>
@@ -17491,8 +17497,12 @@
       </c>
       <c r="K63" s="4" t="n"/>
       <c r="L63" s="4" t="n"/>
-      <c r="M63" s="4" t="n"/>
-      <c r="N63" s="4" t="n"/>
+      <c r="M63" s="4" t="n">
+        <v>22.99</v>
+      </c>
+      <c r="N63" s="4" t="n">
+        <v>23.08</v>
+      </c>
       <c r="O63" s="4" t="n"/>
       <c r="P63" s="4" t="n"/>
       <c r="Q63" s="4" t="n"/>
@@ -17580,17 +17590,11 @@
           <t>河滨城堡</t>
         </is>
       </c>
-      <c r="C64" s="4" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="D64" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="E64" s="4" t="n">
-        <v>23.7</v>
-      </c>
+      <c r="C64" s="4" t="n"/>
+      <c r="D64" s="4" t="n"/>
+      <c r="E64" s="4" t="n"/>
       <c r="F64" s="4" t="n">
-        <v>23.05</v>
+        <v>33.3</v>
       </c>
       <c r="G64" s="4" t="n"/>
       <c r="H64" s="4" t="n"/>
@@ -17599,15 +17603,15 @@
       <c r="K64" s="4" t="n"/>
       <c r="L64" s="4" t="n"/>
       <c r="M64" s="4" t="n">
-        <v>22.99</v>
-      </c>
-      <c r="N64" s="4" t="n">
-        <v>23.08</v>
-      </c>
+        <v>32.9</v>
+      </c>
+      <c r="N64" s="4" t="n"/>
       <c r="O64" s="4" t="n"/>
       <c r="P64" s="4" t="n"/>
       <c r="Q64" s="4" t="n"/>
-      <c r="R64" s="4" t="n"/>
+      <c r="R64" s="4" t="n">
+        <v>33.55</v>
+      </c>
       <c r="S64" s="4" t="n"/>
       <c r="T64" s="4" t="n"/>
       <c r="U64" s="4" t="n"/>
@@ -17619,9 +17623,7 @@
       <c r="AA64" s="4" t="n"/>
       <c r="AB64" s="4" t="n"/>
       <c r="AC64" s="4" t="n"/>
-      <c r="AD64" s="4" t="n">
-        <v>24.6</v>
-      </c>
+      <c r="AD64" s="4" t="n"/>
       <c r="AE64" s="4" t="n"/>
       <c r="AF64" s="4" t="n"/>
       <c r="AG64" s="4" t="n"/>
@@ -29868,9 +29870,21 @@
           <t>河岸狂飙</t>
         </is>
       </c>
-      <c r="C63" s="4" t="n"/>
-      <c r="D63" s="4" t="n"/>
-      <c r="E63" s="4" t="n"/>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -30027,21 +30041,9 @@
           <t>河滨城堡</t>
         </is>
       </c>
-      <c r="C64" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D64" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="C64" s="4" t="n"/>
+      <c r="D64" s="4" t="n"/>
+      <c r="E64" s="4" t="n"/>
       <c r="F64" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -30062,11 +30064,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N64" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N64" s="4" t="n"/>
       <c r="O64" s="4" t="n"/>
       <c r="P64" s="4" t="n"/>
       <c r="Q64" s="4" t="n"/>
@@ -30090,11 +30088,7 @@
       <c r="AA64" s="4" t="n"/>
       <c r="AB64" s="4" t="n"/>
       <c r="AC64" s="4" t="n"/>
-      <c r="AD64" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AD64" s="4" t="n"/>
       <c r="AE64" s="4" t="n"/>
       <c r="AF64" s="4" t="n"/>
       <c r="AG64" s="4" t="n"/>
@@ -44816,7 +44810,9 @@
       <c r="Q25" s="4" t="n"/>
       <c r="R25" s="4" t="n"/>
       <c r="S25" s="4" t="n"/>
-      <c r="T25" s="4" t="n"/>
+      <c r="T25" s="4" t="n">
+        <v>24.69</v>
+      </c>
       <c r="U25" s="4" t="n"/>
       <c r="V25" s="4" t="n"/>
       <c r="W25" s="4" t="n"/>
@@ -44825,13 +44821,15 @@
       <c r="Z25" s="4" t="n"/>
       <c r="AA25" s="4" t="n"/>
       <c r="AB25" s="4" t="n">
-        <v>34.4</v>
+        <v>24.4</v>
       </c>
       <c r="AC25" s="4" t="n"/>
       <c r="AD25" s="4" t="n"/>
       <c r="AE25" s="4" t="n"/>
       <c r="AF25" s="4" t="n"/>
-      <c r="AG25" s="4" t="n"/>
+      <c r="AG25" s="4" t="n">
+        <v>24.5</v>
+      </c>
       <c r="AH25" s="4" t="n"/>
       <c r="AI25" s="4" t="n"/>
       <c r="AJ25" s="4" t="n"/>
@@ -44848,7 +44846,9 @@
       <c r="AS25" s="4" t="n"/>
       <c r="AT25" s="4" t="n"/>
       <c r="AU25" s="4" t="n"/>
-      <c r="AV25" s="4" t="n"/>
+      <c r="AV25" s="4" t="n">
+        <v>24.8</v>
+      </c>
       <c r="AW25" s="4" t="n"/>
       <c r="AX25" s="4" t="n"/>
       <c r="AY25" s="4" t="n"/>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -8766,12 +8766,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>速尾</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>9x8</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>速尾</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -8863,10 +8863,10 @@
       </c>
       <c r="D2" s="4" t="n"/>
       <c r="E2" s="4" t="n"/>
-      <c r="F2" s="4" t="n">
+      <c r="F2" s="4" t="n"/>
+      <c r="G2" s="4" t="n">
         <v>16.9</v>
       </c>
-      <c r="G2" s="4" t="n"/>
       <c r="H2" s="4" t="n"/>
       <c r="I2" s="4" t="n"/>
       <c r="J2" s="4" t="n"/>
@@ -8933,10 +8933,10 @@
       </c>
       <c r="D4" s="4" t="n"/>
       <c r="E4" s="4" t="n"/>
-      <c r="F4" s="4" t="n">
+      <c r="F4" s="4" t="n"/>
+      <c r="G4" s="4" t="n">
         <v>24.99</v>
       </c>
-      <c r="G4" s="4" t="n"/>
       <c r="H4" s="4" t="n"/>
       <c r="I4" s="4" t="n">
         <v>24.59</v>
@@ -8974,10 +8974,10 @@
       </c>
       <c r="D5" s="4" t="n"/>
       <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n">
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="n">
         <v>22.5</v>
       </c>
-      <c r="G5" s="4" t="n"/>
       <c r="H5" s="4" t="n"/>
       <c r="I5" s="4" t="n"/>
       <c r="J5" s="4" t="n"/>
@@ -9017,10 +9017,10 @@
       <c r="E6" s="4" t="n">
         <v>22.39</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F6" s="4" t="n"/>
+      <c r="G6" s="4" t="n">
         <v>23.58</v>
       </c>
-      <c r="G6" s="4" t="n"/>
       <c r="H6" s="4" t="n">
         <v>22.54</v>
       </c>
@@ -9062,10 +9062,10 @@
       </c>
       <c r="D7" s="4" t="n"/>
       <c r="E7" s="4" t="n"/>
-      <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n">
+      <c r="F7" s="4" t="n">
         <v>18.75</v>
       </c>
+      <c r="G7" s="4" t="n"/>
       <c r="H7" s="4" t="n">
         <v>18.45</v>
       </c>
@@ -9294,10 +9294,10 @@
       </c>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
-      <c r="F13" s="4" t="n">
+      <c r="F13" s="4" t="n"/>
+      <c r="G13" s="4" t="n">
         <v>21.39</v>
       </c>
-      <c r="G13" s="4" t="n"/>
       <c r="H13" s="4" t="n"/>
       <c r="I13" s="4" t="n"/>
       <c r="J13" s="4" t="n"/>
@@ -9364,10 +9364,10 @@
       </c>
       <c r="D15" s="4" t="n"/>
       <c r="E15" s="4" t="n"/>
-      <c r="F15" s="4" t="n">
+      <c r="F15" s="4" t="n"/>
+      <c r="G15" s="4" t="n">
         <v>14.7</v>
       </c>
-      <c r="G15" s="4" t="n"/>
       <c r="H15" s="4" t="n"/>
       <c r="I15" s="4" t="n"/>
       <c r="J15" s="4" t="n"/>
@@ -9539,10 +9539,10 @@
       </c>
       <c r="D20" s="4" t="n"/>
       <c r="E20" s="4" t="n"/>
-      <c r="F20" s="4" t="n">
+      <c r="F20" s="4" t="n"/>
+      <c r="G20" s="4" t="n">
         <v>18.95</v>
       </c>
-      <c r="G20" s="4" t="n"/>
       <c r="H20" s="4" t="n">
         <v>18.69</v>
       </c>
@@ -9663,12 +9663,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>玻璃★3</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>9x8★6</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>玻璃★3</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -9791,10 +9791,10 @@
           <t>跳船</t>
         </is>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n">
         <v>22.75</v>
       </c>
-      <c r="E5" s="4" t="n"/>
       <c r="F5" s="4" t="n"/>
       <c r="G5" s="4" t="n"/>
       <c r="H5" s="4" t="n"/>
@@ -9991,10 +9991,10 @@
           <t>跳图</t>
         </is>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="n">
         <v>21.46</v>
       </c>
-      <c r="E13" s="4" t="n"/>
       <c r="F13" s="4" t="n"/>
       <c r="G13" s="4" t="n"/>
       <c r="H13" s="4" t="n"/>
@@ -10014,10 +10014,10 @@
           <t>跳图</t>
         </is>
       </c>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="n">
+      <c r="D14" s="4" t="n">
         <v>24.8</v>
       </c>
+      <c r="E14" s="4" t="n"/>
       <c r="F14" s="4" t="n"/>
       <c r="G14" s="4" t="n"/>
       <c r="H14" s="4" t="n"/>
@@ -37271,17 +37271,17 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>玻璃</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>速尾</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>9x8</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>玻璃</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>速尾</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -37475,11 +37475,11 @@
       <c r="D2" s="4" t="n"/>
       <c r="E2" s="4" t="n"/>
       <c r="F2" s="4" t="n"/>
-      <c r="G2" s="4" t="n">
+      <c r="G2" s="4" t="n"/>
+      <c r="H2" s="4" t="n"/>
+      <c r="I2" s="4" t="n">
         <v>18.89</v>
       </c>
-      <c r="H2" s="4" t="n"/>
-      <c r="I2" s="4" t="n"/>
       <c r="J2" s="4" t="n"/>
       <c r="K2" s="4" t="n"/>
       <c r="L2" s="4" t="n"/>
@@ -37535,10 +37535,10 @@
       </c>
       <c r="E3" s="4" t="n"/>
       <c r="F3" s="4" t="n"/>
-      <c r="G3" s="4" t="n"/>
-      <c r="H3" s="4" t="n">
+      <c r="G3" s="4" t="n">
         <v>28.42</v>
       </c>
+      <c r="H3" s="4" t="n"/>
       <c r="I3" s="4" t="n"/>
       <c r="J3" s="4" t="n">
         <v>28.45</v>
@@ -37602,10 +37602,10 @@
         <v>30.95</v>
       </c>
       <c r="G4" s="4" t="n"/>
-      <c r="H4" s="4" t="n"/>
-      <c r="I4" s="4" t="n">
+      <c r="H4" s="4" t="n">
         <v>31.69</v>
       </c>
+      <c r="I4" s="4" t="n"/>
       <c r="J4" s="4" t="n">
         <v>30.8</v>
       </c>
@@ -37664,13 +37664,13 @@
       <c r="E5" s="4" t="n"/>
       <c r="F5" s="4" t="n"/>
       <c r="G5" s="4" t="n">
+        <v>17.99</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>18.03</v>
+      </c>
+      <c r="I5" s="4" t="n">
         <v>18.15</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>17.99</v>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>18.03</v>
       </c>
       <c r="J5" s="4" t="n"/>
       <c r="K5" s="4" t="n">
@@ -37737,11 +37737,11 @@
       <c r="D6" s="4" t="n"/>
       <c r="E6" s="4" t="n"/>
       <c r="F6" s="4" t="n"/>
-      <c r="G6" s="4" t="n">
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="4" t="n"/>
+      <c r="I6" s="4" t="n">
         <v>17.95</v>
       </c>
-      <c r="H6" s="4" t="n"/>
-      <c r="I6" s="4" t="n"/>
       <c r="J6" s="4" t="n"/>
       <c r="K6" s="4" t="n"/>
       <c r="L6" s="4" t="n"/>
@@ -37799,10 +37799,10 @@
         <v>24.39</v>
       </c>
       <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n">
+      <c r="G7" s="4" t="n">
         <v>24.69</v>
       </c>
+      <c r="H7" s="4" t="n"/>
       <c r="I7" s="4" t="n"/>
       <c r="J7" s="4" t="n"/>
       <c r="K7" s="4" t="n">
@@ -37861,13 +37861,13 @@
       <c r="F8" s="4" t="n">
         <v>27.73</v>
       </c>
-      <c r="G8" s="4" t="n"/>
+      <c r="G8" s="4" t="n">
+        <v>27.72</v>
+      </c>
       <c r="H8" s="4" t="n">
-        <v>27.72</v>
-      </c>
-      <c r="I8" s="4" t="n">
         <v>28.59</v>
       </c>
+      <c r="I8" s="4" t="n"/>
       <c r="J8" s="4" t="n">
         <v>28.1</v>
       </c>
@@ -37927,10 +37927,10 @@
       </c>
       <c r="E9" s="4" t="n"/>
       <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="n"/>
-      <c r="H9" s="4" t="n">
+      <c r="G9" s="4" t="n">
         <v>20.09</v>
       </c>
+      <c r="H9" s="4" t="n"/>
       <c r="I9" s="4" t="n"/>
       <c r="J9" s="4" t="n"/>
       <c r="K9" s="4" t="n"/>
@@ -37997,12 +37997,12 @@
       <c r="D10" s="4" t="n"/>
       <c r="E10" s="4" t="n"/>
       <c r="F10" s="4" t="n"/>
-      <c r="G10" s="4" t="n">
+      <c r="G10" s="4" t="n"/>
+      <c r="H10" s="4" t="n">
+        <v>23.43</v>
+      </c>
+      <c r="I10" s="4" t="n">
         <v>23.42</v>
-      </c>
-      <c r="H10" s="4" t="n"/>
-      <c r="I10" s="4" t="n">
-        <v>23.43</v>
       </c>
       <c r="J10" s="4" t="n"/>
       <c r="K10" s="4" t="n"/>
@@ -38061,10 +38061,10 @@
       <c r="F11" s="4" t="n">
         <v>35.25</v>
       </c>
-      <c r="G11" s="4" t="n"/>
-      <c r="H11" s="4" t="n">
+      <c r="G11" s="4" t="n">
         <v>35.49</v>
       </c>
+      <c r="H11" s="4" t="n"/>
       <c r="I11" s="4" t="n"/>
       <c r="J11" s="4" t="n"/>
       <c r="K11" s="4" t="n"/>
@@ -38114,10 +38114,10 @@
       <c r="E12" s="4" t="n"/>
       <c r="F12" s="4" t="n"/>
       <c r="G12" s="4" t="n"/>
-      <c r="H12" s="4" t="n"/>
-      <c r="I12" s="4" t="n">
+      <c r="H12" s="4" t="n">
         <v>21.83</v>
       </c>
+      <c r="I12" s="4" t="n"/>
       <c r="J12" s="4" t="n"/>
       <c r="K12" s="4" t="n">
         <v>21.55</v>
@@ -38243,11 +38243,11 @@
         <v>25.29</v>
       </c>
       <c r="F14" s="4" t="n"/>
-      <c r="G14" s="4" t="n">
+      <c r="G14" s="4" t="n"/>
+      <c r="H14" s="4" t="n"/>
+      <c r="I14" s="4" t="n">
         <v>26.19</v>
       </c>
-      <c r="H14" s="4" t="n"/>
-      <c r="I14" s="4" t="n"/>
       <c r="J14" s="4" t="n"/>
       <c r="K14" s="4" t="n"/>
       <c r="L14" s="4" t="n"/>
@@ -38310,13 +38310,13 @@
         <v>28.9</v>
       </c>
       <c r="G15" s="4" t="n">
+        <v>28.82</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>29.49</v>
+      </c>
+      <c r="I15" s="4" t="n">
         <v>29.19</v>
-      </c>
-      <c r="H15" s="4" t="n">
-        <v>28.82</v>
-      </c>
-      <c r="I15" s="4" t="n">
-        <v>29.49</v>
       </c>
       <c r="J15" s="4" t="n"/>
       <c r="K15" s="4" t="n"/>
@@ -38434,13 +38434,13 @@
       </c>
       <c r="F17" s="4" t="n"/>
       <c r="G17" s="4" t="n">
+        <v>29.75</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>30.59</v>
+      </c>
+      <c r="I17" s="4" t="n">
         <v>30.69</v>
-      </c>
-      <c r="H17" s="4" t="n">
-        <v>29.75</v>
-      </c>
-      <c r="I17" s="4" t="n">
-        <v>30.59</v>
       </c>
       <c r="J17" s="4" t="n"/>
       <c r="K17" s="4" t="n"/>
@@ -38496,10 +38496,10 @@
       <c r="E18" s="4" t="n"/>
       <c r="F18" s="4" t="n"/>
       <c r="G18" s="4" t="n"/>
-      <c r="H18" s="4" t="n"/>
-      <c r="I18" s="4" t="n">
+      <c r="H18" s="4" t="n">
         <v>23.72</v>
       </c>
+      <c r="I18" s="4" t="n"/>
       <c r="J18" s="4" t="n">
         <v>23.98</v>
       </c>
@@ -38571,11 +38571,11 @@
       <c r="F19" s="4" t="n">
         <v>32.19</v>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="G19" s="4" t="n"/>
+      <c r="H19" s="4" t="n"/>
+      <c r="I19" s="4" t="n">
         <v>33.05</v>
       </c>
-      <c r="H19" s="4" t="n"/>
-      <c r="I19" s="4" t="n"/>
       <c r="J19" s="4" t="n"/>
       <c r="K19" s="4" t="n"/>
       <c r="L19" s="4" t="n"/>
@@ -38627,11 +38627,11 @@
         <v>22.09</v>
       </c>
       <c r="F20" s="4" t="n"/>
-      <c r="G20" s="4" t="n">
+      <c r="G20" s="4" t="n"/>
+      <c r="H20" s="4" t="n"/>
+      <c r="I20" s="4" t="n">
         <v>22.4</v>
       </c>
-      <c r="H20" s="4" t="n"/>
-      <c r="I20" s="4" t="n"/>
       <c r="J20" s="4" t="n"/>
       <c r="K20" s="4" t="n"/>
       <c r="L20" s="4" t="n"/>
@@ -38928,10 +38928,10 @@
       <c r="E25" s="4" t="n"/>
       <c r="F25" s="4" t="n"/>
       <c r="G25" s="4" t="n"/>
-      <c r="H25" s="4" t="n"/>
-      <c r="I25" s="4" t="n">
+      <c r="H25" s="4" t="n">
         <v>24.35</v>
       </c>
+      <c r="I25" s="4" t="n"/>
       <c r="J25" s="4" t="n"/>
       <c r="K25" s="4" t="n"/>
       <c r="L25" s="4" t="n">
@@ -38992,10 +38992,10 @@
       <c r="E26" s="4" t="n"/>
       <c r="F26" s="4" t="n"/>
       <c r="G26" s="4" t="n"/>
-      <c r="H26" s="4" t="n"/>
-      <c r="I26" s="4" t="n">
+      <c r="H26" s="4" t="n">
         <v>18.89</v>
       </c>
+      <c r="I26" s="4" t="n"/>
       <c r="J26" s="4" t="n"/>
       <c r="K26" s="4" t="n">
         <v>18.6</v>
@@ -39055,10 +39055,10 @@
       <c r="D27" s="4" t="n"/>
       <c r="E27" s="4" t="n"/>
       <c r="F27" s="4" t="n"/>
-      <c r="G27" s="4" t="n"/>
-      <c r="H27" s="4" t="n">
+      <c r="G27" s="4" t="n">
         <v>32.85</v>
       </c>
+      <c r="H27" s="4" t="n"/>
       <c r="I27" s="4" t="n"/>
       <c r="J27" s="4" t="n">
         <v>32.79</v>
@@ -39116,10 +39116,10 @@
       </c>
       <c r="F28" s="4" t="n"/>
       <c r="G28" s="4" t="n"/>
-      <c r="H28" s="4" t="n"/>
-      <c r="I28" s="4" t="n">
+      <c r="H28" s="4" t="n">
         <v>33.09</v>
       </c>
+      <c r="I28" s="4" t="n"/>
       <c r="J28" s="4" t="n"/>
       <c r="K28" s="4" t="n">
         <v>33.05</v>
@@ -39177,10 +39177,10 @@
         <v>17.29</v>
       </c>
       <c r="F29" s="4" t="n"/>
-      <c r="G29" s="4" t="n"/>
-      <c r="H29" s="4" t="n">
+      <c r="G29" s="4" t="n">
         <v>17.89</v>
       </c>
+      <c r="H29" s="4" t="n"/>
       <c r="I29" s="4" t="n"/>
       <c r="J29" s="4" t="n"/>
       <c r="K29" s="4" t="n"/>
@@ -39239,11 +39239,11 @@
       <c r="D30" s="4" t="n"/>
       <c r="E30" s="4" t="n"/>
       <c r="F30" s="4" t="n"/>
-      <c r="G30" s="4" t="n">
+      <c r="G30" s="4" t="n"/>
+      <c r="H30" s="4" t="n"/>
+      <c r="I30" s="4" t="n">
         <v>23.1</v>
       </c>
-      <c r="H30" s="4" t="n"/>
-      <c r="I30" s="4" t="n"/>
       <c r="J30" s="4" t="n"/>
       <c r="K30" s="4" t="n"/>
       <c r="L30" s="4" t="n"/>
@@ -39299,12 +39299,12 @@
       <c r="D31" s="4" t="n"/>
       <c r="E31" s="4" t="n"/>
       <c r="F31" s="4" t="n"/>
-      <c r="G31" s="4" t="n">
+      <c r="G31" s="4" t="n"/>
+      <c r="H31" s="4" t="n">
+        <v>19.35</v>
+      </c>
+      <c r="I31" s="4" t="n">
         <v>18.99</v>
-      </c>
-      <c r="H31" s="4" t="n"/>
-      <c r="I31" s="4" t="n">
-        <v>19.35</v>
       </c>
       <c r="J31" s="4" t="n"/>
       <c r="K31" s="4" t="n"/>
@@ -39369,12 +39369,12 @@
       <c r="F32" s="4" t="n">
         <v>27.8</v>
       </c>
-      <c r="G32" s="4" t="n">
+      <c r="G32" s="4" t="n"/>
+      <c r="H32" s="4" t="n">
+        <v>28.39</v>
+      </c>
+      <c r="I32" s="4" t="n">
         <v>29.06</v>
-      </c>
-      <c r="H32" s="4" t="n"/>
-      <c r="I32" s="4" t="n">
-        <v>28.39</v>
       </c>
       <c r="J32" s="4" t="n"/>
       <c r="K32" s="4" t="n"/>
@@ -39435,11 +39435,11 @@
       <c r="D33" s="4" t="n"/>
       <c r="E33" s="4" t="n"/>
       <c r="F33" s="4" t="n"/>
-      <c r="G33" s="4" t="n">
+      <c r="G33" s="4" t="n"/>
+      <c r="H33" s="4" t="n"/>
+      <c r="I33" s="4" t="n">
         <v>19.89</v>
       </c>
-      <c r="H33" s="4" t="n"/>
-      <c r="I33" s="4" t="n"/>
       <c r="J33" s="4" t="n"/>
       <c r="K33" s="4" t="n"/>
       <c r="L33" s="4" t="n"/>
@@ -39502,10 +39502,10 @@
       </c>
       <c r="F34" s="4" t="n"/>
       <c r="G34" s="4" t="n"/>
-      <c r="H34" s="4" t="n"/>
-      <c r="I34" s="4" t="n">
+      <c r="H34" s="4" t="n">
         <v>35.49</v>
       </c>
+      <c r="I34" s="4" t="n"/>
       <c r="J34" s="4" t="n">
         <v>34.7</v>
       </c>
@@ -39557,12 +39557,12 @@
       <c r="D35" s="4" t="n"/>
       <c r="E35" s="4" t="n"/>
       <c r="F35" s="4" t="n"/>
-      <c r="G35" s="4" t="n">
+      <c r="G35" s="4" t="n"/>
+      <c r="H35" s="4" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="I35" s="4" t="n">
         <v>23.59</v>
-      </c>
-      <c r="H35" s="4" t="n"/>
-      <c r="I35" s="4" t="n">
-        <v>23.6</v>
       </c>
       <c r="J35" s="4" t="n"/>
       <c r="K35" s="4" t="n"/>
@@ -39623,11 +39623,11 @@
       <c r="F36" s="4" t="n">
         <v>34.6</v>
       </c>
-      <c r="G36" s="4" t="n">
+      <c r="G36" s="4" t="n"/>
+      <c r="H36" s="4" t="n"/>
+      <c r="I36" s="4" t="n">
         <v>35.89</v>
       </c>
-      <c r="H36" s="4" t="n"/>
-      <c r="I36" s="4" t="n"/>
       <c r="J36" s="4" t="n"/>
       <c r="K36" s="4" t="n"/>
       <c r="L36" s="4" t="n"/>
@@ -39683,11 +39683,11 @@
         <v>22.45</v>
       </c>
       <c r="F37" s="4" t="n"/>
-      <c r="G37" s="4" t="n">
+      <c r="G37" s="4" t="n"/>
+      <c r="H37" s="4" t="n"/>
+      <c r="I37" s="4" t="n">
         <v>23.05</v>
       </c>
-      <c r="H37" s="4" t="n"/>
-      <c r="I37" s="4" t="n"/>
       <c r="J37" s="4" t="n"/>
       <c r="K37" s="4" t="n"/>
       <c r="L37" s="4" t="n"/>
@@ -39739,12 +39739,12 @@
       <c r="D38" s="4" t="n"/>
       <c r="E38" s="4" t="n"/>
       <c r="F38" s="4" t="n"/>
-      <c r="G38" s="4" t="n">
+      <c r="G38" s="4" t="n"/>
+      <c r="H38" s="4" t="n">
+        <v>20.99</v>
+      </c>
+      <c r="I38" s="4" t="n">
         <v>21.48</v>
-      </c>
-      <c r="H38" s="4" t="n"/>
-      <c r="I38" s="4" t="n">
-        <v>20.99</v>
       </c>
       <c r="J38" s="4" t="n"/>
       <c r="K38" s="4" t="n">
@@ -39808,10 +39808,10 @@
       <c r="E39" s="4" t="n"/>
       <c r="F39" s="4" t="n"/>
       <c r="G39" s="4" t="n"/>
-      <c r="H39" s="4" t="n"/>
-      <c r="I39" s="4" t="n">
+      <c r="H39" s="4" t="n">
         <v>29.75</v>
       </c>
+      <c r="I39" s="4" t="n"/>
       <c r="J39" s="4" t="n"/>
       <c r="K39" s="4" t="n">
         <v>29.95</v>
@@ -39872,12 +39872,12 @@
         <v>33.59</v>
       </c>
       <c r="G40" s="4" t="n">
+        <v>33.99</v>
+      </c>
+      <c r="H40" s="4" t="n"/>
+      <c r="I40" s="4" t="n">
         <v>34.9</v>
       </c>
-      <c r="H40" s="4" t="n">
-        <v>33.99</v>
-      </c>
-      <c r="I40" s="4" t="n"/>
       <c r="J40" s="4" t="n"/>
       <c r="K40" s="4" t="n"/>
       <c r="L40" s="4" t="n"/>
@@ -39937,10 +39937,10 @@
       <c r="F41" s="4" t="n">
         <v>30.39</v>
       </c>
-      <c r="G41" s="4" t="n"/>
-      <c r="H41" s="4" t="n">
+      <c r="G41" s="4" t="n">
         <v>30.29</v>
       </c>
+      <c r="H41" s="4" t="n"/>
       <c r="I41" s="4" t="n"/>
       <c r="J41" s="4" t="n"/>
       <c r="K41" s="4" t="n"/>
@@ -39991,11 +39991,11 @@
       </c>
       <c r="E42" s="4" t="n"/>
       <c r="F42" s="4" t="n"/>
-      <c r="G42" s="4" t="n">
+      <c r="G42" s="4" t="n"/>
+      <c r="H42" s="4" t="n"/>
+      <c r="I42" s="4" t="n">
         <v>22.3</v>
       </c>
-      <c r="H42" s="4" t="n"/>
-      <c r="I42" s="4" t="n"/>
       <c r="J42" s="4" t="n"/>
       <c r="K42" s="4" t="n"/>
       <c r="L42" s="4" t="n">
@@ -40061,10 +40061,10 @@
       <c r="F43" s="4" t="n">
         <v>38.09</v>
       </c>
-      <c r="G43" s="4" t="n"/>
-      <c r="H43" s="4" t="n">
+      <c r="G43" s="4" t="n">
         <v>38.2</v>
       </c>
+      <c r="H43" s="4" t="n"/>
       <c r="I43" s="4" t="n"/>
       <c r="J43" s="4" t="n"/>
       <c r="K43" s="4" t="n"/>
@@ -40113,11 +40113,11 @@
       <c r="D44" s="4" t="n"/>
       <c r="E44" s="4" t="n"/>
       <c r="F44" s="4" t="n"/>
-      <c r="G44" s="4" t="n">
+      <c r="G44" s="4" t="n"/>
+      <c r="H44" s="4" t="n"/>
+      <c r="I44" s="4" t="n">
         <v>22.25</v>
       </c>
-      <c r="H44" s="4" t="n"/>
-      <c r="I44" s="4" t="n"/>
       <c r="J44" s="4" t="n"/>
       <c r="K44" s="4" t="n"/>
       <c r="L44" s="4" t="n">
@@ -40190,10 +40190,10 @@
       </c>
       <c r="F45" s="4" t="n"/>
       <c r="G45" s="4" t="n"/>
-      <c r="H45" s="4" t="n"/>
-      <c r="I45" s="4" t="n">
+      <c r="H45" s="4" t="n">
         <v>40.69</v>
       </c>
+      <c r="I45" s="4" t="n"/>
       <c r="J45" s="4" t="n"/>
       <c r="K45" s="4" t="n"/>
       <c r="L45" s="4" t="n"/>
@@ -40251,10 +40251,10 @@
       <c r="F46" s="4" t="n">
         <v>32.29</v>
       </c>
-      <c r="G46" s="4" t="n"/>
-      <c r="H46" s="4" t="n">
+      <c r="G46" s="4" t="n">
         <v>32.49</v>
       </c>
+      <c r="H46" s="4" t="n"/>
       <c r="I46" s="4" t="n"/>
       <c r="J46" s="4" t="n"/>
       <c r="K46" s="4" t="n"/>
@@ -40477,11 +40477,11 @@
         <v>25.99</v>
       </c>
       <c r="F50" s="4" t="n"/>
-      <c r="G50" s="4" t="n">
+      <c r="G50" s="4" t="n"/>
+      <c r="H50" s="4" t="n"/>
+      <c r="I50" s="4" t="n">
         <v>26.59</v>
       </c>
-      <c r="H50" s="4" t="n"/>
-      <c r="I50" s="4" t="n"/>
       <c r="J50" s="4" t="n"/>
       <c r="K50" s="4" t="n"/>
       <c r="L50" s="4" t="n"/>
@@ -40536,13 +40536,13 @@
       <c r="E51" s="4" t="n"/>
       <c r="F51" s="4" t="n"/>
       <c r="G51" s="4" t="n">
+        <v>24.09</v>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>24.29</v>
+      </c>
+      <c r="I51" s="4" t="n">
         <v>24.39</v>
-      </c>
-      <c r="H51" s="4" t="n">
-        <v>24.09</v>
-      </c>
-      <c r="I51" s="4" t="n">
-        <v>24.29</v>
       </c>
       <c r="J51" s="4" t="n"/>
       <c r="K51" s="4" t="n">
@@ -40605,10 +40605,10 @@
       <c r="F52" s="4" t="n">
         <v>32.3</v>
       </c>
-      <c r="G52" s="4" t="n"/>
-      <c r="H52" s="4" t="n">
+      <c r="G52" s="4" t="n">
         <v>32.05</v>
       </c>
+      <c r="H52" s="4" t="n"/>
       <c r="I52" s="4" t="n"/>
       <c r="J52" s="4" t="n"/>
       <c r="K52" s="4" t="n"/>
@@ -40782,12 +40782,12 @@
       </c>
       <c r="F55" s="4" t="n"/>
       <c r="G55" s="4" t="n">
+        <v>32.85</v>
+      </c>
+      <c r="H55" s="4" t="n"/>
+      <c r="I55" s="4" t="n">
         <v>32.73</v>
       </c>
-      <c r="H55" s="4" t="n">
-        <v>32.85</v>
-      </c>
-      <c r="I55" s="4" t="n"/>
       <c r="J55" s="4" t="n"/>
       <c r="K55" s="4" t="n"/>
       <c r="L55" s="4" t="n"/>
@@ -40845,10 +40845,10 @@
       <c r="F56" s="4" t="n">
         <v>35.6</v>
       </c>
-      <c r="G56" s="4" t="n"/>
-      <c r="H56" s="4" t="n">
+      <c r="G56" s="4" t="n">
         <v>35.95</v>
       </c>
+      <c r="H56" s="4" t="n"/>
       <c r="I56" s="4" t="n"/>
       <c r="J56" s="4" t="n"/>
       <c r="K56" s="4" t="n"/>
@@ -40907,10 +40907,10 @@
         <v>34.55</v>
       </c>
       <c r="F57" s="4" t="n"/>
-      <c r="G57" s="4" t="n"/>
-      <c r="H57" s="4" t="n">
+      <c r="G57" s="4" t="n">
         <v>35.55</v>
       </c>
+      <c r="H57" s="4" t="n"/>
       <c r="I57" s="4" t="n"/>
       <c r="J57" s="4" t="n"/>
       <c r="K57" s="4" t="n"/>
@@ -40967,10 +40967,10 @@
       <c r="F58" s="4" t="n">
         <v>24.43</v>
       </c>
-      <c r="G58" s="4" t="n"/>
-      <c r="H58" s="4" t="n">
+      <c r="G58" s="4" t="n">
         <v>24.59</v>
       </c>
+      <c r="H58" s="4" t="n"/>
       <c r="I58" s="4" t="n"/>
       <c r="J58" s="4" t="n"/>
       <c r="K58" s="4" t="n"/>
@@ -41026,12 +41026,12 @@
       <c r="E59" s="4" t="n"/>
       <c r="F59" s="4" t="n"/>
       <c r="G59" s="4" t="n">
+        <v>21.29</v>
+      </c>
+      <c r="H59" s="4" t="n"/>
+      <c r="I59" s="4" t="n">
         <v>21.19</v>
       </c>
-      <c r="H59" s="4" t="n">
-        <v>21.29</v>
-      </c>
-      <c r="I59" s="4" t="n"/>
       <c r="J59" s="4" t="n"/>
       <c r="K59" s="4" t="n"/>
       <c r="L59" s="4" t="n"/>
@@ -41149,11 +41149,11 @@
       </c>
       <c r="E61" s="4" t="n"/>
       <c r="F61" s="4" t="n"/>
-      <c r="G61" s="4" t="n">
+      <c r="G61" s="4" t="n"/>
+      <c r="H61" s="4" t="n"/>
+      <c r="I61" s="4" t="n">
         <v>21.72</v>
       </c>
-      <c r="H61" s="4" t="n"/>
-      <c r="I61" s="4" t="n"/>
       <c r="J61" s="4" t="n"/>
       <c r="K61" s="4" t="n"/>
       <c r="L61" s="4" t="n">
@@ -41228,13 +41228,13 @@
         <v>29.85</v>
       </c>
       <c r="G62" s="4" t="n">
+        <v>29.99</v>
+      </c>
+      <c r="H62" s="4" t="n">
+        <v>30.89</v>
+      </c>
+      <c r="I62" s="4" t="n">
         <v>31.49</v>
-      </c>
-      <c r="H62" s="4" t="n">
-        <v>29.99</v>
-      </c>
-      <c r="I62" s="4" t="n">
-        <v>30.89</v>
       </c>
       <c r="J62" s="4" t="n"/>
       <c r="K62" s="4" t="n"/>
@@ -41286,12 +41286,12 @@
       <c r="E63" s="4" t="n"/>
       <c r="F63" s="4" t="n"/>
       <c r="G63" s="4" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="H63" s="4" t="n"/>
+      <c r="I63" s="4" t="n">
         <v>24.5</v>
       </c>
-      <c r="H63" s="4" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="I63" s="4" t="n"/>
       <c r="J63" s="4" t="n"/>
       <c r="K63" s="4" t="n"/>
       <c r="L63" s="4" t="n"/>
@@ -41347,10 +41347,10 @@
       <c r="F64" s="4" t="n">
         <v>33.8</v>
       </c>
-      <c r="G64" s="4" t="n"/>
-      <c r="H64" s="4" t="n">
+      <c r="G64" s="4" t="n">
         <v>33.89</v>
       </c>
+      <c r="H64" s="4" t="n"/>
       <c r="I64" s="4" t="n"/>
       <c r="J64" s="4" t="n"/>
       <c r="K64" s="4" t="n"/>
@@ -41410,10 +41410,10 @@
         <v>32.9</v>
       </c>
       <c r="G65" s="4" t="n"/>
-      <c r="H65" s="4" t="n"/>
-      <c r="I65" s="4" t="n">
+      <c r="H65" s="4" t="n">
         <v>33.79</v>
       </c>
+      <c r="I65" s="4" t="n"/>
       <c r="J65" s="4" t="n"/>
       <c r="K65" s="4" t="n"/>
       <c r="L65" s="4" t="n"/>
@@ -41518,10 +41518,10 @@
       <c r="E67" s="4" t="n"/>
       <c r="F67" s="4" t="n"/>
       <c r="G67" s="4" t="n"/>
-      <c r="H67" s="4" t="n"/>
-      <c r="I67" s="4" t="n">
+      <c r="H67" s="4" t="n">
         <v>18.09</v>
       </c>
+      <c r="I67" s="4" t="n"/>
       <c r="J67" s="4" t="n"/>
       <c r="K67" s="4" t="n"/>
       <c r="L67" s="4" t="n"/>
@@ -41581,10 +41581,10 @@
       <c r="D68" s="4" t="n"/>
       <c r="E68" s="4" t="n"/>
       <c r="F68" s="4" t="n"/>
-      <c r="G68" s="4" t="n"/>
-      <c r="H68" s="4" t="n">
+      <c r="G68" s="4" t="n">
         <v>27.5</v>
       </c>
+      <c r="H68" s="4" t="n"/>
       <c r="I68" s="4" t="n"/>
       <c r="J68" s="4" t="n"/>
       <c r="K68" s="4" t="n"/>
@@ -41647,10 +41647,10 @@
       <c r="F69" s="4" t="n">
         <v>32.97</v>
       </c>
-      <c r="G69" s="4" t="n"/>
-      <c r="H69" s="4" t="n">
+      <c r="G69" s="4" t="n">
         <v>33.79</v>
       </c>
+      <c r="H69" s="4" t="n"/>
       <c r="I69" s="4" t="n"/>
       <c r="J69" s="4" t="n"/>
       <c r="K69" s="4" t="n"/>
@@ -41702,10 +41702,10 @@
       <c r="E70" s="4" t="n"/>
       <c r="F70" s="4" t="n"/>
       <c r="G70" s="4" t="n"/>
-      <c r="H70" s="4" t="n"/>
-      <c r="I70" s="4" t="n">
+      <c r="H70" s="4" t="n">
         <v>21.63</v>
       </c>
+      <c r="I70" s="4" t="n"/>
       <c r="J70" s="4" t="n"/>
       <c r="K70" s="4" t="n"/>
       <c r="L70" s="4" t="n">
@@ -41767,10 +41767,10 @@
       <c r="F71" s="4" t="n">
         <v>38.07</v>
       </c>
-      <c r="G71" s="4" t="n"/>
-      <c r="H71" s="4" t="n">
+      <c r="G71" s="4" t="n">
         <v>38.3</v>
       </c>
+      <c r="H71" s="4" t="n"/>
       <c r="I71" s="4" t="n"/>
       <c r="J71" s="4" t="n">
         <v>38.79</v>
@@ -41825,12 +41825,12 @@
         <v>25.6</v>
       </c>
       <c r="F72" s="4" t="n"/>
-      <c r="G72" s="4" t="n">
+      <c r="G72" s="4" t="n"/>
+      <c r="H72" s="4" t="n">
+        <v>25.85</v>
+      </c>
+      <c r="I72" s="4" t="n">
         <v>25.93</v>
-      </c>
-      <c r="H72" s="4" t="n"/>
-      <c r="I72" s="4" t="n">
-        <v>25.85</v>
       </c>
       <c r="J72" s="4" t="n"/>
       <c r="K72" s="4" t="n"/>
@@ -41895,11 +41895,11 @@
       <c r="D73" s="4" t="n"/>
       <c r="E73" s="4" t="n"/>
       <c r="F73" s="4" t="n"/>
-      <c r="G73" s="4" t="n">
+      <c r="G73" s="4" t="n"/>
+      <c r="H73" s="4" t="n"/>
+      <c r="I73" s="4" t="n">
         <v>19.19</v>
       </c>
-      <c r="H73" s="4" t="n"/>
-      <c r="I73" s="4" t="n"/>
       <c r="J73" s="4" t="n"/>
       <c r="K73" s="4" t="n"/>
       <c r="L73" s="4" t="n"/>
@@ -41956,10 +41956,10 @@
       <c r="E74" s="4" t="n"/>
       <c r="F74" s="4" t="n"/>
       <c r="G74" s="4" t="n"/>
-      <c r="H74" s="4" t="n"/>
-      <c r="I74" s="4" t="n">
+      <c r="H74" s="4" t="n">
         <v>33.95</v>
       </c>
+      <c r="I74" s="4" t="n"/>
       <c r="J74" s="4" t="n">
         <v>34.79</v>
       </c>
@@ -42014,10 +42014,10 @@
       <c r="E75" s="4" t="n"/>
       <c r="F75" s="4" t="n"/>
       <c r="G75" s="4" t="n"/>
-      <c r="H75" s="4" t="n"/>
-      <c r="I75" s="4" t="n">
+      <c r="H75" s="4" t="n">
         <v>26.69</v>
       </c>
+      <c r="I75" s="4" t="n"/>
       <c r="J75" s="4" t="n"/>
       <c r="K75" s="4" t="n">
         <v>26.25</v>
@@ -42069,11 +42069,11 @@
       <c r="D76" s="4" t="n"/>
       <c r="E76" s="4" t="n"/>
       <c r="F76" s="4" t="n"/>
-      <c r="G76" s="4" t="n">
+      <c r="G76" s="4" t="n"/>
+      <c r="H76" s="4" t="n"/>
+      <c r="I76" s="4" t="n">
         <v>16.6</v>
       </c>
-      <c r="H76" s="4" t="n"/>
-      <c r="I76" s="4" t="n"/>
       <c r="J76" s="4" t="n"/>
       <c r="K76" s="4" t="n"/>
       <c r="L76" s="4" t="n"/>
@@ -42193,10 +42193,10 @@
       <c r="F78" s="4" t="n">
         <v>31.2</v>
       </c>
-      <c r="G78" s="4" t="n"/>
-      <c r="H78" s="4" t="n">
+      <c r="G78" s="4" t="n">
         <v>31.59</v>
       </c>
+      <c r="H78" s="4" t="n"/>
       <c r="I78" s="4" t="n"/>
       <c r="J78" s="4" t="n">
         <v>31.8</v>
@@ -42371,10 +42371,10 @@
       <c r="F81" s="4" t="n">
         <v>63.6</v>
       </c>
-      <c r="G81" s="4" t="n"/>
-      <c r="H81" s="4" t="n">
+      <c r="G81" s="4" t="n">
         <v>63.99</v>
       </c>
+      <c r="H81" s="4" t="n"/>
       <c r="I81" s="4" t="n"/>
       <c r="J81" s="4" t="n"/>
       <c r="K81" s="4" t="n"/>
@@ -42540,10 +42540,10 @@
         <v>26.59</v>
       </c>
       <c r="G84" s="4" t="n"/>
-      <c r="H84" s="4" t="n"/>
-      <c r="I84" s="4" t="n">
+      <c r="H84" s="4" t="n">
         <v>27.39</v>
       </c>
+      <c r="I84" s="4" t="n"/>
       <c r="J84" s="4" t="n"/>
       <c r="K84" s="4" t="n"/>
       <c r="L84" s="4" t="n"/>
@@ -42750,37 +42750,37 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>玻璃★1</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>玻璃★2</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>玻璃★3</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>速尾★4</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>速尾★5</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>速尾★6</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>9x8★6</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>玻璃★1</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>玻璃★2</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>玻璃★3</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>速尾★4</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>速尾★5</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>速尾★6</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
@@ -43016,15 +43016,15 @@
       <c r="K2" s="4" t="n"/>
       <c r="L2" s="4" t="n"/>
       <c r="M2" s="4" t="n"/>
-      <c r="N2" s="4" t="n">
-        <v>19.1</v>
-      </c>
+      <c r="N2" s="4" t="n"/>
       <c r="O2" s="4" t="n"/>
       <c r="P2" s="4" t="n"/>
       <c r="Q2" s="4" t="n"/>
       <c r="R2" s="4" t="n"/>
       <c r="S2" s="4" t="n"/>
-      <c r="T2" s="4" t="n"/>
+      <c r="T2" s="4" t="n">
+        <v>19.1</v>
+      </c>
       <c r="U2" s="4" t="n"/>
       <c r="V2" s="4" t="n"/>
       <c r="W2" s="4" t="n"/>
@@ -43244,17 +43244,17 @@
       <c r="K5" s="4" t="n"/>
       <c r="L5" s="4" t="n"/>
       <c r="M5" s="4" t="n"/>
-      <c r="N5" s="4" t="n">
-        <v>18.2</v>
-      </c>
+      <c r="N5" s="4" t="n"/>
       <c r="O5" s="4" t="n"/>
       <c r="P5" s="4" t="n"/>
-      <c r="Q5" s="4" t="n"/>
-      <c r="R5" s="4" t="n">
+      <c r="Q5" s="4" t="n">
         <v>18.48</v>
       </c>
+      <c r="R5" s="4" t="n"/>
       <c r="S5" s="4" t="n"/>
-      <c r="T5" s="4" t="n"/>
+      <c r="T5" s="4" t="n">
+        <v>18.2</v>
+      </c>
       <c r="U5" s="4" t="n"/>
       <c r="V5" s="4" t="n"/>
       <c r="W5" s="4" t="n"/>
@@ -43324,15 +43324,15 @@
       <c r="K6" s="4" t="n"/>
       <c r="L6" s="4" t="n"/>
       <c r="M6" s="4" t="n"/>
-      <c r="N6" s="4" t="n">
-        <v>18.05</v>
-      </c>
+      <c r="N6" s="4" t="n"/>
       <c r="O6" s="4" t="n"/>
       <c r="P6" s="4" t="n"/>
       <c r="Q6" s="4" t="n"/>
       <c r="R6" s="4" t="n"/>
       <c r="S6" s="4" t="n"/>
-      <c r="T6" s="4" t="n"/>
+      <c r="T6" s="4" t="n">
+        <v>18.05</v>
+      </c>
       <c r="U6" s="4" t="n"/>
       <c r="V6" s="4" t="n"/>
       <c r="W6" s="4" t="n"/>
@@ -43480,10 +43480,10 @@
         <v>27.75</v>
       </c>
       <c r="M8" s="4" t="n"/>
-      <c r="N8" s="4" t="n"/>
-      <c r="O8" s="4" t="n">
+      <c r="N8" s="4" t="n">
         <v>28.23</v>
       </c>
+      <c r="O8" s="4" t="n"/>
       <c r="P8" s="4" t="n"/>
       <c r="Q8" s="4" t="n"/>
       <c r="R8" s="4" t="n"/>
@@ -43557,10 +43557,10 @@
       <c r="N9" s="4" t="n"/>
       <c r="O9" s="4" t="n"/>
       <c r="P9" s="4" t="n"/>
-      <c r="Q9" s="4" t="n"/>
-      <c r="R9" s="4" t="n">
+      <c r="Q9" s="4" t="n">
         <v>20.52</v>
       </c>
+      <c r="R9" s="4" t="n"/>
       <c r="S9" s="4" t="n"/>
       <c r="T9" s="4" t="n"/>
       <c r="U9" s="4" t="n"/>
@@ -43632,16 +43632,16 @@
       <c r="K10" s="4" t="n"/>
       <c r="L10" s="4" t="n"/>
       <c r="M10" s="4" t="n"/>
-      <c r="N10" s="4" t="n">
-        <v>23.5</v>
-      </c>
+      <c r="N10" s="4" t="n"/>
       <c r="O10" s="4" t="n"/>
       <c r="P10" s="4" t="n"/>
       <c r="Q10" s="4" t="n"/>
       <c r="R10" s="4" t="n"/>
-      <c r="S10" s="4" t="n"/>
+      <c r="S10" s="4" t="n">
+        <v>23.4</v>
+      </c>
       <c r="T10" s="4" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="U10" s="4" t="n"/>
       <c r="V10" s="4" t="n"/>
@@ -43787,10 +43787,10 @@
       <c r="N12" s="4" t="n"/>
       <c r="O12" s="4" t="n"/>
       <c r="P12" s="4" t="n"/>
-      <c r="Q12" s="4" t="n"/>
-      <c r="R12" s="4" t="n">
+      <c r="Q12" s="4" t="n">
         <v>21.99</v>
       </c>
+      <c r="R12" s="4" t="n"/>
       <c r="S12" s="4" t="n"/>
       <c r="T12" s="4" t="n"/>
       <c r="U12" s="4" t="n"/>
@@ -43954,10 +43954,10 @@
       <c r="K14" s="4" t="n"/>
       <c r="L14" s="4" t="n"/>
       <c r="M14" s="4" t="n"/>
-      <c r="N14" s="4" t="n"/>
-      <c r="O14" s="4" t="n">
+      <c r="N14" s="4" t="n">
         <v>26.15</v>
       </c>
+      <c r="O14" s="4" t="n"/>
       <c r="P14" s="4" t="n"/>
       <c r="Q14" s="4" t="n"/>
       <c r="R14" s="4" t="n"/>
@@ -44034,15 +44034,15 @@
       </c>
       <c r="L15" s="4" t="n"/>
       <c r="M15" s="4" t="n"/>
-      <c r="N15" s="4" t="n">
-        <v>29.59</v>
-      </c>
+      <c r="N15" s="4" t="n"/>
       <c r="O15" s="4" t="n"/>
       <c r="P15" s="4" t="n"/>
       <c r="Q15" s="4" t="n"/>
       <c r="R15" s="4" t="n"/>
       <c r="S15" s="4" t="n"/>
-      <c r="T15" s="4" t="n"/>
+      <c r="T15" s="4" t="n">
+        <v>29.59</v>
+      </c>
       <c r="U15" s="4" t="n"/>
       <c r="V15" s="4" t="n"/>
       <c r="W15" s="4" t="n"/>
@@ -44194,10 +44194,10 @@
       <c r="K17" s="4" t="n"/>
       <c r="L17" s="4" t="n"/>
       <c r="M17" s="4" t="n"/>
-      <c r="N17" s="4" t="n"/>
-      <c r="O17" s="4" t="n">
+      <c r="N17" s="4" t="n">
         <v>30.49</v>
       </c>
+      <c r="O17" s="4" t="n"/>
       <c r="P17" s="4" t="n"/>
       <c r="Q17" s="4" t="n"/>
       <c r="R17" s="4" t="n"/>
@@ -44273,10 +44273,10 @@
       <c r="N18" s="4" t="n"/>
       <c r="O18" s="4" t="n"/>
       <c r="P18" s="4" t="n"/>
-      <c r="Q18" s="4" t="n"/>
-      <c r="R18" s="4" t="n">
+      <c r="Q18" s="4" t="n">
         <v>24.59</v>
       </c>
+      <c r="R18" s="4" t="n"/>
       <c r="S18" s="4" t="n"/>
       <c r="T18" s="4" t="n"/>
       <c r="U18" s="4" t="n"/>
@@ -44352,15 +44352,15 @@
       <c r="M19" s="4" t="n">
         <v>32.5</v>
       </c>
-      <c r="N19" s="4" t="n">
-        <v>33.4</v>
-      </c>
+      <c r="N19" s="4" t="n"/>
       <c r="O19" s="4" t="n"/>
       <c r="P19" s="4" t="n"/>
       <c r="Q19" s="4" t="n"/>
       <c r="R19" s="4" t="n"/>
       <c r="S19" s="4" t="n"/>
-      <c r="T19" s="4" t="n"/>
+      <c r="T19" s="4" t="n">
+        <v>33.4</v>
+      </c>
       <c r="U19" s="4" t="n"/>
       <c r="V19" s="4" t="n"/>
       <c r="W19" s="4" t="n"/>
@@ -44426,15 +44426,15 @@
         <v>22.4</v>
       </c>
       <c r="M20" s="4" t="n"/>
-      <c r="N20" s="4" t="n">
-        <v>22.59</v>
-      </c>
+      <c r="N20" s="4" t="n"/>
       <c r="O20" s="4" t="n"/>
       <c r="P20" s="4" t="n"/>
       <c r="Q20" s="4" t="n"/>
       <c r="R20" s="4" t="n"/>
       <c r="S20" s="4" t="n"/>
-      <c r="T20" s="4" t="n"/>
+      <c r="T20" s="4" t="n">
+        <v>22.59</v>
+      </c>
       <c r="U20" s="4" t="n"/>
       <c r="V20" s="4" t="n"/>
       <c r="W20" s="4" t="n"/>
@@ -44729,14 +44729,14 @@
       <c r="N24" s="4" t="n"/>
       <c r="O24" s="4" t="n"/>
       <c r="P24" s="4" t="n"/>
-      <c r="Q24" s="4" t="n"/>
-      <c r="R24" s="4" t="n">
+      <c r="Q24" s="4" t="n">
         <v>23.69</v>
       </c>
-      <c r="S24" s="4" t="n"/>
-      <c r="T24" s="4" t="n">
+      <c r="R24" s="4" t="n"/>
+      <c r="S24" s="4" t="n">
         <v>23.3</v>
       </c>
+      <c r="T24" s="4" t="n"/>
       <c r="U24" s="4" t="n"/>
       <c r="V24" s="4" t="n"/>
       <c r="W24" s="4" t="n"/>
@@ -44809,10 +44809,10 @@
       <c r="P25" s="4" t="n"/>
       <c r="Q25" s="4" t="n"/>
       <c r="R25" s="4" t="n"/>
-      <c r="S25" s="4" t="n"/>
-      <c r="T25" s="4" t="n">
+      <c r="S25" s="4" t="n">
         <v>24.69</v>
       </c>
+      <c r="T25" s="4" t="n"/>
       <c r="U25" s="4" t="n"/>
       <c r="V25" s="4" t="n"/>
       <c r="W25" s="4" t="n"/>
@@ -44891,10 +44891,10 @@
       <c r="P26" s="4" t="n"/>
       <c r="Q26" s="4" t="n"/>
       <c r="R26" s="4" t="n"/>
-      <c r="S26" s="4" t="n"/>
-      <c r="T26" s="4" t="n">
+      <c r="S26" s="4" t="n">
         <v>18.99</v>
       </c>
+      <c r="T26" s="4" t="n"/>
       <c r="U26" s="4" t="n"/>
       <c r="V26" s="4" t="n"/>
       <c r="W26" s="4" t="n"/>
@@ -44966,15 +44966,15 @@
       <c r="K27" s="4" t="n"/>
       <c r="L27" s="4" t="n"/>
       <c r="M27" s="4" t="n"/>
-      <c r="N27" s="4" t="n">
-        <v>35.2</v>
-      </c>
+      <c r="N27" s="4" t="n"/>
       <c r="O27" s="4" t="n"/>
       <c r="P27" s="4" t="n"/>
       <c r="Q27" s="4" t="n"/>
       <c r="R27" s="4" t="n"/>
       <c r="S27" s="4" t="n"/>
-      <c r="T27" s="4" t="n"/>
+      <c r="T27" s="4" t="n">
+        <v>35.2</v>
+      </c>
       <c r="U27" s="4" t="n">
         <v>34.19</v>
       </c>
@@ -45049,10 +45049,10 @@
       <c r="P28" s="4" t="n"/>
       <c r="Q28" s="4" t="n"/>
       <c r="R28" s="4" t="n"/>
-      <c r="S28" s="4" t="n"/>
-      <c r="T28" s="4" t="n">
+      <c r="S28" s="4" t="n">
         <v>33.5</v>
       </c>
+      <c r="T28" s="4" t="n"/>
       <c r="U28" s="4" t="n"/>
       <c r="V28" s="4" t="n"/>
       <c r="W28" s="4" t="n"/>
@@ -45200,15 +45200,15 @@
       <c r="K30" s="4" t="n"/>
       <c r="L30" s="4" t="n"/>
       <c r="M30" s="4" t="n"/>
-      <c r="N30" s="4" t="n">
-        <v>23.19</v>
-      </c>
+      <c r="N30" s="4" t="n"/>
       <c r="O30" s="4" t="n"/>
       <c r="P30" s="4" t="n"/>
       <c r="Q30" s="4" t="n"/>
       <c r="R30" s="4" t="n"/>
       <c r="S30" s="4" t="n"/>
-      <c r="T30" s="4" t="n"/>
+      <c r="T30" s="4" t="n">
+        <v>23.19</v>
+      </c>
       <c r="U30" s="4" t="n"/>
       <c r="V30" s="4" t="n"/>
       <c r="W30" s="4" t="n"/>
@@ -45270,15 +45270,15 @@
       <c r="K31" s="4" t="n"/>
       <c r="L31" s="4" t="n"/>
       <c r="M31" s="4" t="n"/>
-      <c r="N31" s="4" t="n">
-        <v>19.19</v>
-      </c>
+      <c r="N31" s="4" t="n"/>
       <c r="O31" s="4" t="n"/>
       <c r="P31" s="4" t="n"/>
       <c r="Q31" s="4" t="n"/>
       <c r="R31" s="4" t="n"/>
       <c r="S31" s="4" t="n"/>
-      <c r="T31" s="4" t="n"/>
+      <c r="T31" s="4" t="n">
+        <v>19.19</v>
+      </c>
       <c r="U31" s="4" t="n"/>
       <c r="V31" s="4" t="n"/>
       <c r="W31" s="4" t="n"/>
@@ -45348,15 +45348,15 @@
       <c r="K32" s="4" t="n"/>
       <c r="L32" s="4" t="n"/>
       <c r="M32" s="4" t="n"/>
-      <c r="N32" s="4" t="n">
-        <v>29.4</v>
-      </c>
+      <c r="N32" s="4" t="n"/>
       <c r="O32" s="4" t="n"/>
       <c r="P32" s="4" t="n"/>
       <c r="Q32" s="4" t="n"/>
       <c r="R32" s="4" t="n"/>
       <c r="S32" s="4" t="n"/>
-      <c r="T32" s="4" t="n"/>
+      <c r="T32" s="4" t="n">
+        <v>29.4</v>
+      </c>
       <c r="U32" s="4" t="n"/>
       <c r="V32" s="4" t="n"/>
       <c r="W32" s="4" t="n"/>
@@ -45432,15 +45432,15 @@
       <c r="K33" s="4" t="n"/>
       <c r="L33" s="4" t="n"/>
       <c r="M33" s="4" t="n"/>
-      <c r="N33" s="4" t="n">
-        <v>19.99</v>
-      </c>
+      <c r="N33" s="4" t="n"/>
       <c r="O33" s="4" t="n"/>
       <c r="P33" s="4" t="n"/>
       <c r="Q33" s="4" t="n"/>
       <c r="R33" s="4" t="n"/>
       <c r="S33" s="4" t="n"/>
-      <c r="T33" s="4" t="n"/>
+      <c r="T33" s="4" t="n">
+        <v>19.99</v>
+      </c>
       <c r="U33" s="4" t="n"/>
       <c r="V33" s="4" t="n"/>
       <c r="W33" s="4" t="n"/>
@@ -45511,13 +45511,13 @@
       <c r="N34" s="4" t="n"/>
       <c r="O34" s="4" t="n"/>
       <c r="P34" s="4" t="n"/>
-      <c r="Q34" s="4" t="n"/>
+      <c r="Q34" s="4" t="n">
+        <v>35.8</v>
+      </c>
       <c r="R34" s="4" t="n">
-        <v>35.8</v>
-      </c>
-      <c r="S34" s="4" t="n">
         <v>35.6</v>
       </c>
+      <c r="S34" s="4" t="n"/>
       <c r="T34" s="4" t="n"/>
       <c r="U34" s="4" t="n"/>
       <c r="V34" s="4" t="n">
@@ -45584,15 +45584,15 @@
       <c r="K35" s="4" t="n"/>
       <c r="L35" s="4" t="n"/>
       <c r="M35" s="4" t="n"/>
-      <c r="N35" s="4" t="n">
-        <v>23.7</v>
-      </c>
+      <c r="N35" s="4" t="n"/>
       <c r="O35" s="4" t="n"/>
       <c r="P35" s="4" t="n"/>
       <c r="Q35" s="4" t="n"/>
       <c r="R35" s="4" t="n"/>
       <c r="S35" s="4" t="n"/>
-      <c r="T35" s="4" t="n"/>
+      <c r="T35" s="4" t="n">
+        <v>23.7</v>
+      </c>
       <c r="U35" s="4" t="n"/>
       <c r="V35" s="4" t="n"/>
       <c r="W35" s="4" t="n"/>
@@ -45748,15 +45748,15 @@
         <v>22.69</v>
       </c>
       <c r="M37" s="4" t="n"/>
-      <c r="N37" s="4" t="n">
-        <v>23.29</v>
-      </c>
+      <c r="N37" s="4" t="n"/>
       <c r="O37" s="4" t="n"/>
       <c r="P37" s="4" t="n"/>
       <c r="Q37" s="4" t="n"/>
       <c r="R37" s="4" t="n"/>
       <c r="S37" s="4" t="n"/>
-      <c r="T37" s="4" t="n"/>
+      <c r="T37" s="4" t="n">
+        <v>23.29</v>
+      </c>
       <c r="U37" s="4" t="n"/>
       <c r="V37" s="4" t="n"/>
       <c r="W37" s="4" t="n"/>
@@ -45899,10 +45899,10 @@
       <c r="P39" s="4" t="n"/>
       <c r="Q39" s="4" t="n"/>
       <c r="R39" s="4" t="n"/>
-      <c r="S39" s="4" t="n"/>
-      <c r="T39" s="4" t="n">
+      <c r="S39" s="4" t="n">
         <v>29.9</v>
       </c>
+      <c r="T39" s="4" t="n"/>
       <c r="U39" s="4" t="n"/>
       <c r="V39" s="4" t="n"/>
       <c r="W39" s="4" t="n"/>
@@ -45980,15 +45980,15 @@
       <c r="M40" s="4" t="n">
         <v>34.3</v>
       </c>
-      <c r="N40" s="4" t="n">
-        <v>35.2</v>
-      </c>
+      <c r="N40" s="4" t="n"/>
       <c r="O40" s="4" t="n"/>
       <c r="P40" s="4" t="n"/>
       <c r="Q40" s="4" t="n"/>
       <c r="R40" s="4" t="n"/>
       <c r="S40" s="4" t="n"/>
-      <c r="T40" s="4" t="n"/>
+      <c r="T40" s="4" t="n">
+        <v>35.2</v>
+      </c>
       <c r="U40" s="4" t="n"/>
       <c r="V40" s="4" t="n"/>
       <c r="W40" s="4" t="n"/>
@@ -46138,15 +46138,15 @@
       <c r="K42" s="4" t="n"/>
       <c r="L42" s="4" t="n"/>
       <c r="M42" s="4" t="n"/>
-      <c r="N42" s="4" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="N42" s="4" t="n"/>
       <c r="O42" s="4" t="n"/>
       <c r="P42" s="4" t="n"/>
       <c r="Q42" s="4" t="n"/>
       <c r="R42" s="4" t="n"/>
       <c r="S42" s="4" t="n"/>
-      <c r="T42" s="4" t="n"/>
+      <c r="T42" s="4" t="n">
+        <v>22.5</v>
+      </c>
       <c r="U42" s="4" t="n">
         <v>23.3</v>
       </c>
@@ -46288,15 +46288,15 @@
       <c r="K44" s="4" t="n"/>
       <c r="L44" s="4" t="n"/>
       <c r="M44" s="4" t="n"/>
-      <c r="N44" s="4" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="N44" s="4" t="n"/>
       <c r="O44" s="4" t="n"/>
       <c r="P44" s="4" t="n"/>
       <c r="Q44" s="4" t="n"/>
       <c r="R44" s="4" t="n"/>
       <c r="S44" s="4" t="n"/>
-      <c r="T44" s="4" t="n"/>
+      <c r="T44" s="4" t="n">
+        <v>22.5</v>
+      </c>
       <c r="U44" s="4" t="n"/>
       <c r="V44" s="4" t="n"/>
       <c r="W44" s="4" t="n"/>
@@ -46372,10 +46372,10 @@
       <c r="M45" s="4" t="n">
         <v>39.19</v>
       </c>
-      <c r="N45" s="4" t="n"/>
-      <c r="O45" s="4" t="n">
+      <c r="N45" s="4" t="n">
         <v>39.79</v>
       </c>
+      <c r="O45" s="4" t="n"/>
       <c r="P45" s="4" t="n"/>
       <c r="Q45" s="4" t="n"/>
       <c r="R45" s="4" t="n"/>
@@ -46530,16 +46530,16 @@
       <c r="M47" s="4" t="n">
         <v>40.99</v>
       </c>
-      <c r="N47" s="4" t="n"/>
+      <c r="N47" s="4" t="n">
+        <v>41.5</v>
+      </c>
       <c r="O47" s="4" t="n">
-        <v>41.5</v>
+        <v>41.4</v>
       </c>
       <c r="P47" s="4" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="Q47" s="4" t="n">
         <v>41.3</v>
       </c>
+      <c r="Q47" s="4" t="n"/>
       <c r="R47" s="4" t="n"/>
       <c r="S47" s="4" t="n"/>
       <c r="T47" s="4" t="n"/>
@@ -46616,13 +46616,13 @@
       <c r="O48" s="4" t="n"/>
       <c r="P48" s="4" t="n"/>
       <c r="Q48" s="4" t="n"/>
-      <c r="R48" s="4" t="n"/>
+      <c r="R48" s="4" t="n">
+        <v>25.79</v>
+      </c>
       <c r="S48" s="4" t="n">
-        <v>25.79</v>
-      </c>
-      <c r="T48" s="4" t="n">
         <v>25.2</v>
       </c>
+      <c r="T48" s="4" t="n"/>
       <c r="U48" s="4" t="n"/>
       <c r="V48" s="4" t="n"/>
       <c r="W48" s="4" t="n"/>
@@ -46692,15 +46692,15 @@
       </c>
       <c r="L49" s="4" t="n"/>
       <c r="M49" s="4" t="n"/>
-      <c r="N49" s="4" t="n">
-        <v>30.79</v>
-      </c>
+      <c r="N49" s="4" t="n"/>
       <c r="O49" s="4" t="n"/>
       <c r="P49" s="4" t="n"/>
       <c r="Q49" s="4" t="n"/>
       <c r="R49" s="4" t="n"/>
       <c r="S49" s="4" t="n"/>
-      <c r="T49" s="4" t="n"/>
+      <c r="T49" s="4" t="n">
+        <v>30.79</v>
+      </c>
       <c r="U49" s="4" t="n"/>
       <c r="V49" s="4" t="n"/>
       <c r="W49" s="4" t="n"/>
@@ -46764,15 +46764,15 @@
       <c r="K50" s="4" t="n"/>
       <c r="L50" s="4" t="n"/>
       <c r="M50" s="4" t="n"/>
-      <c r="N50" s="4" t="n">
-        <v>26.67</v>
-      </c>
+      <c r="N50" s="4" t="n"/>
       <c r="O50" s="4" t="n"/>
       <c r="P50" s="4" t="n"/>
       <c r="Q50" s="4" t="n"/>
       <c r="R50" s="4" t="n"/>
       <c r="S50" s="4" t="n"/>
-      <c r="T50" s="4" t="n"/>
+      <c r="T50" s="4" t="n">
+        <v>26.67</v>
+      </c>
       <c r="U50" s="4" t="n"/>
       <c r="V50" s="4" t="n"/>
       <c r="W50" s="4" t="n"/>
@@ -46836,15 +46836,15 @@
       <c r="K51" s="4" t="n"/>
       <c r="L51" s="4" t="n"/>
       <c r="M51" s="4" t="n"/>
-      <c r="N51" s="4" t="n">
-        <v>24.5</v>
-      </c>
+      <c r="N51" s="4" t="n"/>
       <c r="O51" s="4" t="n"/>
       <c r="P51" s="4" t="n"/>
       <c r="Q51" s="4" t="n"/>
       <c r="R51" s="4" t="n"/>
       <c r="S51" s="4" t="n"/>
-      <c r="T51" s="4" t="n"/>
+      <c r="T51" s="4" t="n">
+        <v>24.5</v>
+      </c>
       <c r="U51" s="4" t="n"/>
       <c r="V51" s="4" t="n"/>
       <c r="W51" s="4" t="n"/>
@@ -46918,19 +46918,19 @@
       <c r="K52" s="4" t="n"/>
       <c r="L52" s="4" t="n"/>
       <c r="M52" s="4" t="n"/>
-      <c r="N52" s="4" t="n"/>
+      <c r="N52" s="4" t="n">
+        <v>32.6</v>
+      </c>
       <c r="O52" s="4" t="n">
-        <v>32.6</v>
+        <v>32.4</v>
       </c>
       <c r="P52" s="4" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
       <c r="Q52" s="4" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="R52" s="4" t="n">
         <v>34.1</v>
       </c>
+      <c r="R52" s="4" t="n"/>
       <c r="S52" s="4" t="n"/>
       <c r="T52" s="4" t="n"/>
       <c r="U52" s="4" t="n"/>
@@ -47152,15 +47152,15 @@
       <c r="K55" s="4" t="n"/>
       <c r="L55" s="4" t="n"/>
       <c r="M55" s="4" t="n"/>
-      <c r="N55" s="4" t="n">
-        <v>32.99</v>
-      </c>
+      <c r="N55" s="4" t="n"/>
       <c r="O55" s="4" t="n"/>
       <c r="P55" s="4" t="n"/>
       <c r="Q55" s="4" t="n"/>
       <c r="R55" s="4" t="n"/>
       <c r="S55" s="4" t="n"/>
-      <c r="T55" s="4" t="n"/>
+      <c r="T55" s="4" t="n">
+        <v>32.99</v>
+      </c>
       <c r="U55" s="4" t="n"/>
       <c r="V55" s="4" t="n"/>
       <c r="W55" s="4" t="n"/>
@@ -47306,14 +47306,14 @@
         <v>35</v>
       </c>
       <c r="M57" s="4" t="n"/>
-      <c r="N57" s="4" t="n"/>
-      <c r="O57" s="4" t="n">
+      <c r="N57" s="4" t="n">
         <v>36.4</v>
       </c>
-      <c r="P57" s="4" t="n"/>
-      <c r="Q57" s="4" t="n">
+      <c r="O57" s="4" t="n"/>
+      <c r="P57" s="4" t="n">
         <v>36.19</v>
       </c>
+      <c r="Q57" s="4" t="n"/>
       <c r="R57" s="4" t="n"/>
       <c r="S57" s="4" t="n"/>
       <c r="T57" s="4" t="n"/>
@@ -47391,10 +47391,10 @@
       <c r="N58" s="4" t="n"/>
       <c r="O58" s="4" t="n"/>
       <c r="P58" s="4" t="n"/>
-      <c r="Q58" s="4" t="n"/>
-      <c r="R58" s="4" t="n">
+      <c r="Q58" s="4" t="n">
         <v>26.8</v>
       </c>
+      <c r="R58" s="4" t="n"/>
       <c r="S58" s="4" t="n"/>
       <c r="T58" s="4" t="n"/>
       <c r="U58" s="4" t="n"/>
@@ -47464,15 +47464,15 @@
       <c r="K59" s="4" t="n"/>
       <c r="L59" s="4" t="n"/>
       <c r="M59" s="4" t="n"/>
-      <c r="N59" s="4" t="n">
-        <v>21.35</v>
-      </c>
+      <c r="N59" s="4" t="n"/>
       <c r="O59" s="4" t="n"/>
       <c r="P59" s="4" t="n"/>
       <c r="Q59" s="4" t="n"/>
       <c r="R59" s="4" t="n"/>
       <c r="S59" s="4" t="n"/>
-      <c r="T59" s="4" t="n"/>
+      <c r="T59" s="4" t="n">
+        <v>21.35</v>
+      </c>
       <c r="U59" s="4" t="n"/>
       <c r="V59" s="4" t="n"/>
       <c r="W59" s="4" t="n"/>
@@ -47624,15 +47624,15 @@
       <c r="K61" s="4" t="n"/>
       <c r="L61" s="4" t="n"/>
       <c r="M61" s="4" t="n"/>
-      <c r="N61" s="4" t="n">
-        <v>21.89</v>
-      </c>
+      <c r="N61" s="4" t="n"/>
       <c r="O61" s="4" t="n"/>
       <c r="P61" s="4" t="n"/>
       <c r="Q61" s="4" t="n"/>
       <c r="R61" s="4" t="n"/>
       <c r="S61" s="4" t="n"/>
-      <c r="T61" s="4" t="n"/>
+      <c r="T61" s="4" t="n">
+        <v>21.89</v>
+      </c>
       <c r="U61" s="4" t="n"/>
       <c r="V61" s="4" t="n"/>
       <c r="W61" s="4" t="n"/>
@@ -47700,18 +47700,18 @@
       <c r="M62" s="4" t="n">
         <v>31.1</v>
       </c>
-      <c r="N62" s="4" t="n">
-        <v>31.9</v>
-      </c>
+      <c r="N62" s="4" t="n"/>
       <c r="O62" s="4" t="n"/>
       <c r="P62" s="4" t="n"/>
-      <c r="Q62" s="4" t="n"/>
-      <c r="R62" s="4" t="n">
+      <c r="Q62" s="4" t="n">
         <v>32.45</v>
       </c>
-      <c r="S62" s="4" t="n"/>
+      <c r="R62" s="4" t="n"/>
+      <c r="S62" s="4" t="n">
+        <v>31.29</v>
+      </c>
       <c r="T62" s="4" t="n">
-        <v>31.29</v>
+        <v>31.9</v>
       </c>
       <c r="U62" s="4" t="n"/>
       <c r="V62" s="4" t="n"/>
@@ -47783,18 +47783,18 @@
       <c r="L63" s="4" t="n"/>
       <c r="M63" s="4" t="n"/>
       <c r="N63" s="4" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="O63" s="4" t="n">
         <v>24.39</v>
       </c>
-      <c r="P63" s="4" t="n"/>
-      <c r="Q63" s="4" t="n">
+      <c r="O63" s="4" t="n"/>
+      <c r="P63" s="4" t="n">
         <v>23.95</v>
       </c>
+      <c r="Q63" s="4" t="n"/>
       <c r="R63" s="4" t="n"/>
       <c r="S63" s="4" t="n"/>
-      <c r="T63" s="4" t="n"/>
+      <c r="T63" s="4" t="n">
+        <v>24.6</v>
+      </c>
       <c r="U63" s="4" t="n"/>
       <c r="V63" s="4" t="n">
         <v>25.39</v>
@@ -47866,9 +47866,7 @@
         <v>33.6</v>
       </c>
       <c r="M64" s="4" t="n"/>
-      <c r="N64" s="4" t="n">
-        <v>24.6</v>
-      </c>
+      <c r="N64" s="4" t="n"/>
       <c r="O64" s="4" t="n"/>
       <c r="P64" s="4" t="n"/>
       <c r="Q64" s="4" t="n"/>
@@ -48091,14 +48089,14 @@
       <c r="N67" s="4" t="n"/>
       <c r="O67" s="4" t="n"/>
       <c r="P67" s="4" t="n"/>
-      <c r="Q67" s="4" t="n"/>
-      <c r="R67" s="4" t="n">
+      <c r="Q67" s="4" t="n">
         <v>18.9</v>
       </c>
-      <c r="S67" s="4" t="n"/>
-      <c r="T67" s="4" t="n">
+      <c r="R67" s="4" t="n"/>
+      <c r="S67" s="4" t="n">
         <v>18.49</v>
       </c>
+      <c r="T67" s="4" t="n"/>
       <c r="U67" s="4" t="n"/>
       <c r="V67" s="4" t="n"/>
       <c r="W67" s="4" t="n"/>
@@ -48173,10 +48171,10 @@
       <c r="P68" s="4" t="n"/>
       <c r="Q68" s="4" t="n"/>
       <c r="R68" s="4" t="n"/>
-      <c r="S68" s="4" t="n"/>
-      <c r="T68" s="4" t="n">
+      <c r="S68" s="4" t="n">
         <v>28.1</v>
       </c>
+      <c r="T68" s="4" t="n"/>
       <c r="U68" s="4" t="n"/>
       <c r="V68" s="4" t="n"/>
       <c r="W68" s="4" t="n"/>
@@ -48246,15 +48244,15 @@
       <c r="M69" s="4" t="n">
         <v>33.8</v>
       </c>
-      <c r="N69" s="4" t="n">
-        <v>35.36</v>
-      </c>
+      <c r="N69" s="4" t="n"/>
       <c r="O69" s="4" t="n"/>
       <c r="P69" s="4" t="n"/>
       <c r="Q69" s="4" t="n"/>
       <c r="R69" s="4" t="n"/>
       <c r="S69" s="4" t="n"/>
-      <c r="T69" s="4" t="n"/>
+      <c r="T69" s="4" t="n">
+        <v>35.36</v>
+      </c>
       <c r="U69" s="4" t="n"/>
       <c r="V69" s="4" t="n"/>
       <c r="W69" s="4" t="n"/>
@@ -48460,15 +48458,15 @@
       <c r="K72" s="4" t="n"/>
       <c r="L72" s="4" t="n"/>
       <c r="M72" s="4" t="n"/>
-      <c r="N72" s="4" t="n">
-        <v>26.15</v>
-      </c>
+      <c r="N72" s="4" t="n"/>
       <c r="O72" s="4" t="n"/>
       <c r="P72" s="4" t="n"/>
       <c r="Q72" s="4" t="n"/>
       <c r="R72" s="4" t="n"/>
       <c r="S72" s="4" t="n"/>
-      <c r="T72" s="4" t="n"/>
+      <c r="T72" s="4" t="n">
+        <v>26.15</v>
+      </c>
       <c r="U72" s="4" t="n"/>
       <c r="V72" s="4" t="n"/>
       <c r="W72" s="4" t="n"/>
@@ -48540,15 +48538,15 @@
       <c r="K73" s="4" t="n"/>
       <c r="L73" s="4" t="n"/>
       <c r="M73" s="4" t="n"/>
-      <c r="N73" s="4" t="n">
-        <v>19.4</v>
-      </c>
+      <c r="N73" s="4" t="n"/>
       <c r="O73" s="4" t="n"/>
       <c r="P73" s="4" t="n"/>
       <c r="Q73" s="4" t="n"/>
       <c r="R73" s="4" t="n"/>
       <c r="S73" s="4" t="n"/>
-      <c r="T73" s="4" t="n"/>
+      <c r="T73" s="4" t="n">
+        <v>19.4</v>
+      </c>
       <c r="U73" s="4" t="n"/>
       <c r="V73" s="4" t="n"/>
       <c r="W73" s="4" t="n"/>
@@ -48627,10 +48625,10 @@
       <c r="P74" s="4" t="n"/>
       <c r="Q74" s="4" t="n"/>
       <c r="R74" s="4" t="n"/>
-      <c r="S74" s="4" t="n"/>
-      <c r="T74" s="4" t="n">
+      <c r="S74" s="4" t="n">
         <v>34.39</v>
       </c>
+      <c r="T74" s="4" t="n"/>
       <c r="U74" s="4" t="n">
         <v>35.6</v>
       </c>
@@ -48701,10 +48699,10 @@
       <c r="P75" s="4" t="n"/>
       <c r="Q75" s="4" t="n"/>
       <c r="R75" s="4" t="n"/>
-      <c r="S75" s="4" t="n"/>
-      <c r="T75" s="4" t="n">
+      <c r="S75" s="4" t="n">
         <v>27.1</v>
       </c>
+      <c r="T75" s="4" t="n"/>
       <c r="U75" s="4" t="n"/>
       <c r="V75" s="4" t="n"/>
       <c r="W75" s="4" t="n"/>
@@ -48776,15 +48774,15 @@
       <c r="K76" s="4" t="n"/>
       <c r="L76" s="4" t="n"/>
       <c r="M76" s="4" t="n"/>
-      <c r="N76" s="4" t="n">
-        <v>16.99</v>
-      </c>
+      <c r="N76" s="4" t="n"/>
       <c r="O76" s="4" t="n"/>
       <c r="P76" s="4" t="n"/>
       <c r="Q76" s="4" t="n"/>
       <c r="R76" s="4" t="n"/>
       <c r="S76" s="4" t="n"/>
-      <c r="T76" s="4" t="n"/>
+      <c r="T76" s="4" t="n">
+        <v>16.99</v>
+      </c>
       <c r="U76" s="4" t="n"/>
       <c r="V76" s="4" t="n"/>
       <c r="W76" s="4" t="n"/>
@@ -48941,10 +48939,10 @@
         <v>31.6</v>
       </c>
       <c r="N78" s="4" t="n"/>
-      <c r="O78" s="4" t="n"/>
-      <c r="P78" s="4" t="n">
+      <c r="O78" s="4" t="n">
         <v>32.2</v>
       </c>
+      <c r="P78" s="4" t="n"/>
       <c r="Q78" s="4" t="n"/>
       <c r="R78" s="4" t="n"/>
       <c r="S78" s="4" t="n"/>
@@ -49021,10 +49019,10 @@
         <v>23.2</v>
       </c>
       <c r="N79" s="4" t="n"/>
-      <c r="O79" s="4" t="n"/>
-      <c r="P79" s="4" t="n">
+      <c r="O79" s="4" t="n">
         <v>23.3</v>
       </c>
+      <c r="P79" s="4" t="n"/>
       <c r="Q79" s="4" t="n"/>
       <c r="R79" s="4" t="n"/>
       <c r="S79" s="4" t="n"/>
@@ -49102,10 +49100,10 @@
       <c r="M80" s="4" t="n"/>
       <c r="N80" s="4" t="n"/>
       <c r="O80" s="4" t="n"/>
-      <c r="P80" s="4" t="n"/>
-      <c r="Q80" s="4" t="n">
+      <c r="P80" s="4" t="n">
         <v>29.49</v>
       </c>
+      <c r="Q80" s="4" t="n"/>
       <c r="R80" s="4" t="n"/>
       <c r="S80" s="4" t="n"/>
       <c r="T80" s="4" t="n"/>
@@ -49181,10 +49179,10 @@
         <v>63.8</v>
       </c>
       <c r="N81" s="4" t="n"/>
-      <c r="O81" s="4" t="n"/>
-      <c r="P81" s="4" t="n">
+      <c r="O81" s="4" t="n">
         <v>65.39</v>
       </c>
+      <c r="P81" s="4" t="n"/>
       <c r="Q81" s="4" t="n"/>
       <c r="R81" s="4" t="n"/>
       <c r="S81" s="4" t="n"/>
@@ -49261,10 +49259,10 @@
       <c r="N82" s="4" t="n"/>
       <c r="O82" s="4" t="n"/>
       <c r="P82" s="4" t="n"/>
-      <c r="Q82" s="4" t="n"/>
-      <c r="R82" s="4" t="n">
+      <c r="Q82" s="4" t="n">
         <v>57.7</v>
       </c>
+      <c r="R82" s="4" t="n"/>
       <c r="S82" s="4" t="n"/>
       <c r="T82" s="4" t="n"/>
       <c r="U82" s="4" t="n"/>
@@ -49419,10 +49417,10 @@
       <c r="P84" s="4" t="n"/>
       <c r="Q84" s="4" t="n"/>
       <c r="R84" s="4" t="n"/>
-      <c r="S84" s="4" t="n"/>
-      <c r="T84" s="4" t="n">
+      <c r="S84" s="4" t="n">
         <v>27.6</v>
       </c>
+      <c r="T84" s="4" t="n"/>
       <c r="U84" s="4" t="n"/>
       <c r="V84" s="4" t="n"/>
       <c r="W84" s="4" t="n"/>
@@ -49638,37 +49636,37 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>玻璃★1</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>玻璃★2</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>玻璃★3</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>速尾★4</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>速尾★5</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>速尾★6</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>9x8★6</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>玻璃★1</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>玻璃★2</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>玻璃★3</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>速尾★4</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>速尾★5</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>速尾★6</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
@@ -49904,17 +49902,17 @@
       <c r="K2" s="4" t="n"/>
       <c r="L2" s="4" t="n"/>
       <c r="M2" s="4" t="n"/>
-      <c r="N2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N2" s="4" t="n"/>
       <c r="O2" s="4" t="n"/>
       <c r="P2" s="4" t="n"/>
       <c r="Q2" s="4" t="n"/>
       <c r="R2" s="4" t="n"/>
       <c r="S2" s="4" t="n"/>
-      <c r="T2" s="4" t="n"/>
+      <c r="T2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U2" s="4" t="n"/>
       <c r="V2" s="4" t="n"/>
       <c r="W2" s="4" t="n"/>
@@ -50013,12 +50011,12 @@
       <c r="P3" s="4" t="n"/>
       <c r="Q3" s="4" t="n"/>
       <c r="R3" s="4" t="n"/>
-      <c r="S3" s="4" t="n"/>
-      <c r="T3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T3" s="4" t="n"/>
       <c r="U3" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -50133,12 +50131,12 @@
       <c r="P4" s="4" t="n"/>
       <c r="Q4" s="4" t="n"/>
       <c r="R4" s="4" t="n"/>
-      <c r="S4" s="4" t="n"/>
-      <c r="T4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T4" s="4" t="n"/>
       <c r="U4" s="4" t="n"/>
       <c r="V4" s="4" t="n"/>
       <c r="W4" s="4" t="n"/>
@@ -50232,20 +50230,20 @@
       <c r="K5" s="4" t="n"/>
       <c r="L5" s="4" t="n"/>
       <c r="M5" s="4" t="n"/>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N5" s="4" t="n"/>
       <c r="O5" s="4" t="n"/>
       <c r="P5" s="4" t="n"/>
-      <c r="Q5" s="4" t="n"/>
-      <c r="R5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="4" t="n"/>
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R5" s="4" t="n"/>
+      <c r="S5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="T5" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -50340,17 +50338,17 @@
       <c r="K6" s="4" t="n"/>
       <c r="L6" s="4" t="n"/>
       <c r="M6" s="4" t="n"/>
-      <c r="N6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N6" s="4" t="n"/>
       <c r="O6" s="4" t="n"/>
       <c r="P6" s="4" t="n"/>
       <c r="Q6" s="4" t="n"/>
       <c r="R6" s="4" t="n"/>
       <c r="S6" s="4" t="n"/>
-      <c r="T6" s="4" t="n"/>
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U6" s="4" t="n"/>
       <c r="V6" s="4" t="n"/>
       <c r="W6" s="4" t="n"/>
@@ -50444,17 +50442,17 @@
       </c>
       <c r="L7" s="4" t="n"/>
       <c r="M7" s="4" t="n"/>
-      <c r="N7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N7" s="4" t="n"/>
       <c r="O7" s="4" t="n"/>
       <c r="P7" s="4" t="n"/>
       <c r="Q7" s="4" t="n"/>
       <c r="R7" s="4" t="n"/>
       <c r="S7" s="4" t="n"/>
-      <c r="T7" s="4" t="n"/>
+      <c r="T7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U7" s="4" t="n"/>
       <c r="V7" s="4" t="n"/>
       <c r="W7" s="4" t="n"/>
@@ -50576,21 +50574,21 @@
         </is>
       </c>
       <c r="M8" s="4" t="n"/>
-      <c r="N8" s="4" t="n"/>
-      <c r="O8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O8" s="4" t="n"/>
       <c r="P8" s="4" t="n"/>
       <c r="Q8" s="4" t="n"/>
       <c r="R8" s="4" t="n"/>
-      <c r="S8" s="4" t="n"/>
-      <c r="T8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="S8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T8" s="4" t="n"/>
       <c r="U8" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -50680,21 +50678,21 @@
       <c r="K9" s="4" t="n"/>
       <c r="L9" s="4" t="n"/>
       <c r="M9" s="4" t="n"/>
-      <c r="N9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N9" s="4" t="n"/>
       <c r="O9" s="4" t="n"/>
       <c r="P9" s="4" t="n"/>
-      <c r="Q9" s="4" t="n"/>
-      <c r="R9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R9" s="4" t="n"/>
       <c r="S9" s="4" t="n"/>
-      <c r="T9" s="4" t="n"/>
+      <c r="T9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U9" s="4" t="n"/>
       <c r="V9" s="4" t="n"/>
       <c r="W9" s="4" t="n"/>
@@ -50800,16 +50798,16 @@
       <c r="K10" s="4" t="n"/>
       <c r="L10" s="4" t="n"/>
       <c r="M10" s="4" t="n"/>
-      <c r="N10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N10" s="4" t="n"/>
       <c r="O10" s="4" t="n"/>
       <c r="P10" s="4" t="n"/>
       <c r="Q10" s="4" t="n"/>
       <c r="R10" s="4" t="n"/>
-      <c r="S10" s="4" t="n"/>
+      <c r="S10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="T10" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -51016,20 +51014,20 @@
       <c r="K12" s="4" t="n"/>
       <c r="L12" s="4" t="n"/>
       <c r="M12" s="4" t="n"/>
-      <c r="N12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N12" s="4" t="n"/>
       <c r="O12" s="4" t="n"/>
       <c r="P12" s="4" t="n"/>
-      <c r="Q12" s="4" t="n"/>
-      <c r="R12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S12" s="4" t="n"/>
+      <c r="Q12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R12" s="4" t="n"/>
+      <c r="S12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="T12" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -51145,12 +51143,12 @@
       <c r="P13" s="4" t="n"/>
       <c r="Q13" s="4" t="n"/>
       <c r="R13" s="4" t="n"/>
-      <c r="S13" s="4" t="n"/>
-      <c r="T13" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="S13" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T13" s="4" t="n"/>
       <c r="U13" s="4" t="n"/>
       <c r="V13" s="4" t="inlineStr">
         <is>
@@ -51265,16 +51263,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="O14" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O14" s="4" t="n"/>
       <c r="P14" s="4" t="n"/>
       <c r="Q14" s="4" t="n"/>
       <c r="R14" s="4" t="n"/>
       <c r="S14" s="4" t="n"/>
-      <c r="T14" s="4" t="n"/>
+      <c r="T14" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U14" s="4" t="n"/>
       <c r="V14" s="4" t="n"/>
       <c r="W14" s="4" t="n"/>
@@ -51376,16 +51374,16 @@
       </c>
       <c r="L15" s="4" t="n"/>
       <c r="M15" s="4" t="n"/>
-      <c r="N15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N15" s="4" t="n"/>
       <c r="O15" s="4" t="n"/>
       <c r="P15" s="4" t="n"/>
       <c r="Q15" s="4" t="n"/>
       <c r="R15" s="4" t="n"/>
-      <c r="S15" s="4" t="n"/>
+      <c r="S15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="T15" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -51617,16 +51615,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="O17" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O17" s="4" t="n"/>
       <c r="P17" s="4" t="n"/>
       <c r="Q17" s="4" t="n"/>
       <c r="R17" s="4" t="n"/>
       <c r="S17" s="4" t="n"/>
-      <c r="T17" s="4" t="n"/>
+      <c r="T17" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U17" s="4" t="n"/>
       <c r="V17" s="4" t="n"/>
       <c r="W17" s="4" t="n"/>
@@ -51727,18 +51725,18 @@
       <c r="N18" s="4" t="n"/>
       <c r="O18" s="4" t="n"/>
       <c r="P18" s="4" t="n"/>
-      <c r="Q18" s="4" t="n"/>
-      <c r="R18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S18" s="4" t="n"/>
-      <c r="T18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R18" s="4" t="n"/>
+      <c r="S18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T18" s="4" t="n"/>
       <c r="U18" s="4" t="n"/>
       <c r="V18" s="4" t="n"/>
       <c r="W18" s="4" t="n"/>
@@ -51852,16 +51850,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N19" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N19" s="4" t="n"/>
       <c r="O19" s="4" t="n"/>
       <c r="P19" s="4" t="n"/>
       <c r="Q19" s="4" t="n"/>
       <c r="R19" s="4" t="n"/>
-      <c r="S19" s="4" t="n"/>
+      <c r="S19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="T19" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -51960,17 +51958,17 @@
         </is>
       </c>
       <c r="M20" s="4" t="n"/>
-      <c r="N20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N20" s="4" t="n"/>
       <c r="O20" s="4" t="n"/>
       <c r="P20" s="4" t="n"/>
       <c r="Q20" s="4" t="n"/>
       <c r="R20" s="4" t="n"/>
       <c r="S20" s="4" t="n"/>
-      <c r="T20" s="4" t="n"/>
+      <c r="T20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U20" s="4" t="n"/>
       <c r="V20" s="4" t="n"/>
       <c r="W20" s="4" t="n"/>
@@ -52073,12 +52071,12 @@
       <c r="P21" s="4" t="n"/>
       <c r="Q21" s="4" t="n"/>
       <c r="R21" s="4" t="n"/>
-      <c r="S21" s="4" t="n"/>
-      <c r="T21" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="S21" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T21" s="4" t="n"/>
       <c r="U21" s="4" t="n"/>
       <c r="V21" s="4" t="inlineStr">
         <is>
@@ -52285,12 +52283,12 @@
       <c r="P23" s="4" t="n"/>
       <c r="Q23" s="4" t="n"/>
       <c r="R23" s="4" t="n"/>
-      <c r="S23" s="4" t="n"/>
-      <c r="T23" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="S23" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T23" s="4" t="n"/>
       <c r="U23" s="4" t="n"/>
       <c r="V23" s="4" t="inlineStr">
         <is>
@@ -52376,20 +52374,20 @@
       <c r="K24" s="4" t="n"/>
       <c r="L24" s="4" t="n"/>
       <c r="M24" s="4" t="n"/>
-      <c r="N24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N24" s="4" t="n"/>
       <c r="O24" s="4" t="n"/>
       <c r="P24" s="4" t="n"/>
-      <c r="Q24" s="4" t="n"/>
-      <c r="R24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S24" s="4" t="n"/>
+      <c r="Q24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R24" s="4" t="n"/>
+      <c r="S24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="T24" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -52493,12 +52491,12 @@
       <c r="P25" s="4" t="n"/>
       <c r="Q25" s="4" t="n"/>
       <c r="R25" s="4" t="n"/>
-      <c r="S25" s="4" t="n"/>
-      <c r="T25" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="S25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T25" s="4" t="n"/>
       <c r="U25" s="4" t="n"/>
       <c r="V25" s="4" t="n"/>
       <c r="W25" s="4" t="n"/>
@@ -52592,16 +52590,16 @@
       <c r="K26" s="4" t="n"/>
       <c r="L26" s="4" t="n"/>
       <c r="M26" s="4" t="n"/>
-      <c r="N26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N26" s="4" t="n"/>
       <c r="O26" s="4" t="n"/>
       <c r="P26" s="4" t="n"/>
       <c r="Q26" s="4" t="n"/>
       <c r="R26" s="4" t="n"/>
-      <c r="S26" s="4" t="n"/>
+      <c r="S26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="T26" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -52712,17 +52710,17 @@
       <c r="K27" s="4" t="n"/>
       <c r="L27" s="4" t="n"/>
       <c r="M27" s="4" t="n"/>
-      <c r="N27" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N27" s="4" t="n"/>
       <c r="O27" s="4" t="n"/>
       <c r="P27" s="4" t="n"/>
       <c r="Q27" s="4" t="n"/>
       <c r="R27" s="4" t="n"/>
       <c r="S27" s="4" t="n"/>
-      <c r="T27" s="4" t="n"/>
+      <c r="T27" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U27" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -52829,12 +52827,12 @@
       <c r="P28" s="4" t="n"/>
       <c r="Q28" s="4" t="n"/>
       <c r="R28" s="4" t="n"/>
-      <c r="S28" s="4" t="n"/>
-      <c r="T28" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="S28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T28" s="4" t="n"/>
       <c r="U28" s="4" t="n"/>
       <c r="V28" s="4" t="n"/>
       <c r="W28" s="4" t="n"/>
@@ -53032,17 +53030,17 @@
       <c r="K30" s="4" t="n"/>
       <c r="L30" s="4" t="n"/>
       <c r="M30" s="4" t="n"/>
-      <c r="N30" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N30" s="4" t="n"/>
       <c r="O30" s="4" t="n"/>
       <c r="P30" s="4" t="n"/>
       <c r="Q30" s="4" t="n"/>
       <c r="R30" s="4" t="n"/>
       <c r="S30" s="4" t="n"/>
-      <c r="T30" s="4" t="n"/>
+      <c r="T30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U30" s="4" t="n"/>
       <c r="V30" s="4" t="n"/>
       <c r="W30" s="4" t="n"/>
@@ -53136,17 +53134,17 @@
       <c r="K31" s="4" t="n"/>
       <c r="L31" s="4" t="n"/>
       <c r="M31" s="4" t="n"/>
-      <c r="N31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N31" s="4" t="n"/>
       <c r="O31" s="4" t="n"/>
       <c r="P31" s="4" t="n"/>
       <c r="Q31" s="4" t="n"/>
       <c r="R31" s="4" t="n"/>
       <c r="S31" s="4" t="n"/>
-      <c r="T31" s="4" t="n"/>
+      <c r="T31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U31" s="4" t="n"/>
       <c r="V31" s="4" t="n"/>
       <c r="W31" s="4" t="n"/>
@@ -53252,17 +53250,17 @@
       <c r="K32" s="4" t="n"/>
       <c r="L32" s="4" t="n"/>
       <c r="M32" s="4" t="n"/>
-      <c r="N32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N32" s="4" t="n"/>
       <c r="O32" s="4" t="n"/>
       <c r="P32" s="4" t="n"/>
       <c r="Q32" s="4" t="n"/>
       <c r="R32" s="4" t="n"/>
       <c r="S32" s="4" t="n"/>
-      <c r="T32" s="4" t="n"/>
+      <c r="T32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U32" s="4" t="n"/>
       <c r="V32" s="4" t="n"/>
       <c r="W32" s="4" t="n"/>
@@ -53368,17 +53366,17 @@
       <c r="K33" s="4" t="n"/>
       <c r="L33" s="4" t="n"/>
       <c r="M33" s="4" t="n"/>
-      <c r="N33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N33" s="4" t="n"/>
       <c r="O33" s="4" t="n"/>
       <c r="P33" s="4" t="n"/>
       <c r="Q33" s="4" t="n"/>
       <c r="R33" s="4" t="n"/>
       <c r="S33" s="4" t="n"/>
-      <c r="T33" s="4" t="n"/>
+      <c r="T33" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U33" s="4" t="n"/>
       <c r="V33" s="4" t="n"/>
       <c r="W33" s="4" t="n"/>
@@ -53483,7 +53481,11 @@
       <c r="N34" s="4" t="n"/>
       <c r="O34" s="4" t="n"/>
       <c r="P34" s="4" t="n"/>
-      <c r="Q34" s="4" t="n"/>
+      <c r="Q34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="R34" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -53494,11 +53496,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="T34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="T34" s="4" t="n"/>
       <c r="U34" s="4" t="n"/>
       <c r="V34" s="4" t="inlineStr">
         <is>
@@ -53592,17 +53590,17 @@
       <c r="K35" s="4" t="n"/>
       <c r="L35" s="4" t="n"/>
       <c r="M35" s="4" t="n"/>
-      <c r="N35" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N35" s="4" t="n"/>
       <c r="O35" s="4" t="n"/>
       <c r="P35" s="4" t="n"/>
       <c r="Q35" s="4" t="n"/>
       <c r="R35" s="4" t="n"/>
       <c r="S35" s="4" t="n"/>
-      <c r="T35" s="4" t="n"/>
+      <c r="T35" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U35" s="4" t="n"/>
       <c r="V35" s="4" t="n"/>
       <c r="W35" s="4" t="n"/>
@@ -53712,16 +53710,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N36" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N36" s="4" t="n"/>
       <c r="O36" s="4" t="n"/>
       <c r="P36" s="4" t="n"/>
       <c r="Q36" s="4" t="n"/>
       <c r="R36" s="4" t="n"/>
-      <c r="S36" s="4" t="n"/>
+      <c r="S36" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="T36" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -53832,17 +53830,17 @@
         </is>
       </c>
       <c r="M37" s="4" t="n"/>
-      <c r="N37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N37" s="4" t="n"/>
       <c r="O37" s="4" t="n"/>
       <c r="P37" s="4" t="n"/>
       <c r="Q37" s="4" t="n"/>
       <c r="R37" s="4" t="n"/>
       <c r="S37" s="4" t="n"/>
-      <c r="T37" s="4" t="n"/>
+      <c r="T37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U37" s="4" t="n"/>
       <c r="V37" s="4" t="n"/>
       <c r="W37" s="4" t="n"/>
@@ -53936,16 +53934,16 @@
       <c r="K38" s="4" t="n"/>
       <c r="L38" s="4" t="n"/>
       <c r="M38" s="4" t="n"/>
-      <c r="N38" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N38" s="4" t="n"/>
       <c r="O38" s="4" t="n"/>
       <c r="P38" s="4" t="n"/>
       <c r="Q38" s="4" t="n"/>
       <c r="R38" s="4" t="n"/>
-      <c r="S38" s="4" t="n"/>
+      <c r="S38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="T38" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -54057,12 +54055,12 @@
       <c r="P39" s="4" t="n"/>
       <c r="Q39" s="4" t="n"/>
       <c r="R39" s="4" t="n"/>
-      <c r="S39" s="4" t="n"/>
-      <c r="T39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="S39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T39" s="4" t="n"/>
       <c r="U39" s="4" t="n"/>
       <c r="V39" s="4" t="n"/>
       <c r="W39" s="4" t="n"/>
@@ -54192,17 +54190,17 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N40" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N40" s="4" t="n"/>
       <c r="O40" s="4" t="n"/>
       <c r="P40" s="4" t="n"/>
       <c r="Q40" s="4" t="n"/>
       <c r="R40" s="4" t="n"/>
       <c r="S40" s="4" t="n"/>
-      <c r="T40" s="4" t="n"/>
+      <c r="T40" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U40" s="4" t="n"/>
       <c r="V40" s="4" t="n"/>
       <c r="W40" s="4" t="n"/>
@@ -54400,17 +54398,17 @@
       <c r="K42" s="4" t="n"/>
       <c r="L42" s="4" t="n"/>
       <c r="M42" s="4" t="n"/>
-      <c r="N42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N42" s="4" t="n"/>
       <c r="O42" s="4" t="n"/>
       <c r="P42" s="4" t="n"/>
       <c r="Q42" s="4" t="n"/>
       <c r="R42" s="4" t="n"/>
       <c r="S42" s="4" t="n"/>
-      <c r="T42" s="4" t="n"/>
+      <c r="T42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U42" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -54608,17 +54606,17 @@
       <c r="K44" s="4" t="n"/>
       <c r="L44" s="4" t="n"/>
       <c r="M44" s="4" t="n"/>
-      <c r="N44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N44" s="4" t="n"/>
       <c r="O44" s="4" t="n"/>
       <c r="P44" s="4" t="n"/>
       <c r="Q44" s="4" t="n"/>
       <c r="R44" s="4" t="n"/>
       <c r="S44" s="4" t="n"/>
-      <c r="T44" s="4" t="n"/>
+      <c r="T44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U44" s="4" t="n"/>
       <c r="V44" s="4" t="n"/>
       <c r="W44" s="4" t="n"/>
@@ -54733,16 +54731,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="O45" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O45" s="4" t="n"/>
       <c r="P45" s="4" t="n"/>
       <c r="Q45" s="4" t="n"/>
       <c r="R45" s="4" t="n"/>
       <c r="S45" s="4" t="n"/>
-      <c r="T45" s="4" t="n"/>
+      <c r="T45" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U45" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -54856,17 +54854,17 @@
         </is>
       </c>
       <c r="M46" s="4" t="n"/>
-      <c r="N46" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N46" s="4" t="n"/>
       <c r="O46" s="4" t="n"/>
       <c r="P46" s="4" t="n"/>
       <c r="Q46" s="4" t="n"/>
       <c r="R46" s="4" t="n"/>
       <c r="S46" s="4" t="n"/>
-      <c r="T46" s="4" t="n"/>
+      <c r="T46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U46" s="4" t="n"/>
       <c r="V46" s="4" t="n"/>
       <c r="W46" s="4" t="n"/>
@@ -54979,14 +54977,14 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="Q47" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q47" s="4" t="n"/>
       <c r="R47" s="4" t="n"/>
       <c r="S47" s="4" t="n"/>
-      <c r="T47" s="4" t="n"/>
+      <c r="T47" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U47" s="4" t="n"/>
       <c r="V47" s="4" t="n"/>
       <c r="W47" s="4" t="n"/>
@@ -55092,15 +55090,15 @@
       <c r="K48" s="4" t="n"/>
       <c r="L48" s="4" t="n"/>
       <c r="M48" s="4" t="n"/>
-      <c r="N48" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N48" s="4" t="n"/>
       <c r="O48" s="4" t="n"/>
       <c r="P48" s="4" t="n"/>
       <c r="Q48" s="4" t="n"/>
-      <c r="R48" s="4" t="n"/>
+      <c r="R48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="S48" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -55208,17 +55206,17 @@
       </c>
       <c r="L49" s="4" t="n"/>
       <c r="M49" s="4" t="n"/>
-      <c r="N49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N49" s="4" t="n"/>
       <c r="O49" s="4" t="n"/>
       <c r="P49" s="4" t="n"/>
       <c r="Q49" s="4" t="n"/>
       <c r="R49" s="4" t="n"/>
       <c r="S49" s="4" t="n"/>
-      <c r="T49" s="4" t="n"/>
+      <c r="T49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U49" s="4" t="n"/>
       <c r="V49" s="4" t="n"/>
       <c r="W49" s="4" t="n"/>
@@ -55308,17 +55306,17 @@
       <c r="K50" s="4" t="n"/>
       <c r="L50" s="4" t="n"/>
       <c r="M50" s="4" t="n"/>
-      <c r="N50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N50" s="4" t="n"/>
       <c r="O50" s="4" t="n"/>
       <c r="P50" s="4" t="n"/>
       <c r="Q50" s="4" t="n"/>
       <c r="R50" s="4" t="n"/>
       <c r="S50" s="4" t="n"/>
-      <c r="T50" s="4" t="n"/>
+      <c r="T50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U50" s="4" t="n"/>
       <c r="V50" s="4" t="n"/>
       <c r="W50" s="4" t="n"/>
@@ -55412,17 +55410,17 @@
       <c r="K51" s="4" t="n"/>
       <c r="L51" s="4" t="n"/>
       <c r="M51" s="4" t="n"/>
-      <c r="N51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N51" s="4" t="n"/>
       <c r="O51" s="4" t="n"/>
       <c r="P51" s="4" t="n"/>
       <c r="Q51" s="4" t="n"/>
       <c r="R51" s="4" t="n"/>
       <c r="S51" s="4" t="n"/>
-      <c r="T51" s="4" t="n"/>
+      <c r="T51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U51" s="4" t="n"/>
       <c r="V51" s="4" t="n"/>
       <c r="W51" s="4" t="n"/>
@@ -55536,7 +55534,11 @@
       <c r="K52" s="4" t="n"/>
       <c r="L52" s="4" t="n"/>
       <c r="M52" s="4" t="n"/>
-      <c r="N52" s="4" t="n"/>
+      <c r="N52" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="O52" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -55552,11 +55554,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="R52" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="R52" s="4" t="n"/>
       <c r="S52" s="4" t="n"/>
       <c r="T52" s="4" t="n"/>
       <c r="U52" s="4" t="n"/>
@@ -55661,12 +55659,12 @@
       <c r="P53" s="4" t="n"/>
       <c r="Q53" s="4" t="n"/>
       <c r="R53" s="4" t="n"/>
-      <c r="S53" s="4" t="n"/>
-      <c r="T53" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="S53" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T53" s="4" t="n"/>
       <c r="U53" s="4" t="n"/>
       <c r="V53" s="4" t="inlineStr">
         <is>
@@ -55876,17 +55874,17 @@
       <c r="K55" s="4" t="n"/>
       <c r="L55" s="4" t="n"/>
       <c r="M55" s="4" t="n"/>
-      <c r="N55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N55" s="4" t="n"/>
       <c r="O55" s="4" t="n"/>
       <c r="P55" s="4" t="n"/>
       <c r="Q55" s="4" t="n"/>
       <c r="R55" s="4" t="n"/>
       <c r="S55" s="4" t="n"/>
-      <c r="T55" s="4" t="n"/>
+      <c r="T55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U55" s="4" t="n"/>
       <c r="V55" s="4" t="n"/>
       <c r="W55" s="4" t="n"/>
@@ -55988,17 +55986,17 @@
       <c r="K56" s="4" t="n"/>
       <c r="L56" s="4" t="n"/>
       <c r="M56" s="4" t="n"/>
-      <c r="N56" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N56" s="4" t="n"/>
       <c r="O56" s="4" t="n"/>
       <c r="P56" s="4" t="n"/>
       <c r="Q56" s="4" t="n"/>
       <c r="R56" s="4" t="n"/>
       <c r="S56" s="4" t="n"/>
-      <c r="T56" s="4" t="n"/>
+      <c r="T56" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U56" s="4" t="n"/>
       <c r="V56" s="4" t="inlineStr">
         <is>
@@ -56096,25 +56094,25 @@
         </is>
       </c>
       <c r="M57" s="4" t="n"/>
-      <c r="N57" s="4" t="n"/>
-      <c r="O57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P57" s="4" t="n"/>
-      <c r="Q57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="O57" s="4" t="n"/>
+      <c r="P57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q57" s="4" t="n"/>
       <c r="R57" s="4" t="n"/>
-      <c r="S57" s="4" t="n"/>
-      <c r="T57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="S57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T57" s="4" t="n"/>
       <c r="U57" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -56219,12 +56217,12 @@
       <c r="N58" s="4" t="n"/>
       <c r="O58" s="4" t="n"/>
       <c r="P58" s="4" t="n"/>
-      <c r="Q58" s="4" t="n"/>
-      <c r="R58" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q58" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R58" s="4" t="n"/>
       <c r="S58" s="4" t="n"/>
       <c r="T58" s="4" t="n"/>
       <c r="U58" s="4" t="n"/>
@@ -56320,17 +56318,17 @@
       <c r="K59" s="4" t="n"/>
       <c r="L59" s="4" t="n"/>
       <c r="M59" s="4" t="n"/>
-      <c r="N59" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N59" s="4" t="n"/>
       <c r="O59" s="4" t="n"/>
       <c r="P59" s="4" t="n"/>
       <c r="Q59" s="4" t="n"/>
       <c r="R59" s="4" t="n"/>
       <c r="S59" s="4" t="n"/>
-      <c r="T59" s="4" t="n"/>
+      <c r="T59" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U59" s="4" t="n"/>
       <c r="V59" s="4" t="n"/>
       <c r="W59" s="4" t="n"/>
@@ -56540,17 +56538,17 @@
       <c r="K61" s="4" t="n"/>
       <c r="L61" s="4" t="n"/>
       <c r="M61" s="4" t="n"/>
-      <c r="N61" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N61" s="4" t="n"/>
       <c r="O61" s="4" t="n"/>
       <c r="P61" s="4" t="n"/>
       <c r="Q61" s="4" t="n"/>
       <c r="R61" s="4" t="n"/>
       <c r="S61" s="4" t="n"/>
-      <c r="T61" s="4" t="n"/>
+      <c r="T61" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U61" s="4" t="n"/>
       <c r="V61" s="4" t="n"/>
       <c r="W61" s="4" t="n"/>
@@ -56668,20 +56666,20 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N62" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N62" s="4" t="n"/>
       <c r="O62" s="4" t="n"/>
       <c r="P62" s="4" t="n"/>
-      <c r="Q62" s="4" t="n"/>
-      <c r="R62" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S62" s="4" t="n"/>
+      <c r="Q62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R62" s="4" t="n"/>
+      <c r="S62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="T62" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -56793,20 +56791,20 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="O63" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="P63" s="4" t="n"/>
-      <c r="Q63" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O63" s="4" t="n"/>
+      <c r="P63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q63" s="4" t="n"/>
       <c r="R63" s="4" t="n"/>
       <c r="S63" s="4" t="n"/>
-      <c r="T63" s="4" t="n"/>
+      <c r="T63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U63" s="4" t="n"/>
       <c r="V63" s="4" t="inlineStr">
         <is>
@@ -56916,16 +56914,16 @@
         </is>
       </c>
       <c r="M64" s="4" t="n"/>
-      <c r="N64" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N64" s="4" t="n"/>
       <c r="O64" s="4" t="n"/>
       <c r="P64" s="4" t="n"/>
       <c r="Q64" s="4" t="n"/>
       <c r="R64" s="4" t="n"/>
-      <c r="S64" s="4" t="n"/>
+      <c r="S64" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="T64" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -57029,12 +57027,12 @@
       <c r="P65" s="4" t="n"/>
       <c r="Q65" s="4" t="n"/>
       <c r="R65" s="4" t="n"/>
-      <c r="S65" s="4" t="n"/>
-      <c r="T65" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="S65" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T65" s="4" t="n"/>
       <c r="U65" s="4" t="n"/>
       <c r="V65" s="4" t="inlineStr">
         <is>
@@ -57220,20 +57218,20 @@
       <c r="K67" s="4" t="n"/>
       <c r="L67" s="4" t="n"/>
       <c r="M67" s="4" t="n"/>
-      <c r="N67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N67" s="4" t="n"/>
       <c r="O67" s="4" t="n"/>
       <c r="P67" s="4" t="n"/>
-      <c r="Q67" s="4" t="n"/>
-      <c r="R67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S67" s="4" t="n"/>
+      <c r="Q67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R67" s="4" t="n"/>
+      <c r="S67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="T67" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -57361,12 +57359,12 @@
       <c r="P68" s="4" t="n"/>
       <c r="Q68" s="4" t="n"/>
       <c r="R68" s="4" t="n"/>
-      <c r="S68" s="4" t="n"/>
-      <c r="T68" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="S68" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T68" s="4" t="n"/>
       <c r="U68" s="4" t="n"/>
       <c r="V68" s="4" t="n"/>
       <c r="W68" s="4" t="n"/>
@@ -57456,17 +57454,17 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N69" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N69" s="4" t="n"/>
       <c r="O69" s="4" t="n"/>
       <c r="P69" s="4" t="n"/>
       <c r="Q69" s="4" t="n"/>
       <c r="R69" s="4" t="n"/>
       <c r="S69" s="4" t="n"/>
-      <c r="T69" s="4" t="n"/>
+      <c r="T69" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U69" s="4" t="n"/>
       <c r="V69" s="4" t="n"/>
       <c r="W69" s="4" t="n"/>
@@ -57548,17 +57546,17 @@
       <c r="K70" s="4" t="n"/>
       <c r="L70" s="4" t="n"/>
       <c r="M70" s="4" t="n"/>
-      <c r="N70" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N70" s="4" t="n"/>
       <c r="O70" s="4" t="n"/>
       <c r="P70" s="4" t="n"/>
       <c r="Q70" s="4" t="n"/>
       <c r="R70" s="4" t="n"/>
       <c r="S70" s="4" t="n"/>
-      <c r="T70" s="4" t="n"/>
+      <c r="T70" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U70" s="4" t="n"/>
       <c r="V70" s="4" t="n"/>
       <c r="W70" s="4" t="n"/>
@@ -57748,16 +57746,16 @@
       <c r="K72" s="4" t="n"/>
       <c r="L72" s="4" t="n"/>
       <c r="M72" s="4" t="n"/>
-      <c r="N72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N72" s="4" t="n"/>
       <c r="O72" s="4" t="n"/>
       <c r="P72" s="4" t="n"/>
       <c r="Q72" s="4" t="n"/>
       <c r="R72" s="4" t="n"/>
-      <c r="S72" s="4" t="n"/>
+      <c r="S72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="T72" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -57860,17 +57858,17 @@
       <c r="K73" s="4" t="n"/>
       <c r="L73" s="4" t="n"/>
       <c r="M73" s="4" t="n"/>
-      <c r="N73" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N73" s="4" t="n"/>
       <c r="O73" s="4" t="n"/>
       <c r="P73" s="4" t="n"/>
       <c r="Q73" s="4" t="n"/>
       <c r="R73" s="4" t="n"/>
       <c r="S73" s="4" t="n"/>
-      <c r="T73" s="4" t="n"/>
+      <c r="T73" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U73" s="4" t="n"/>
       <c r="V73" s="4" t="n"/>
       <c r="W73" s="4" t="n"/>
@@ -57984,16 +57982,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="N74" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N74" s="4" t="n"/>
       <c r="O74" s="4" t="n"/>
       <c r="P74" s="4" t="n"/>
       <c r="Q74" s="4" t="n"/>
       <c r="R74" s="4" t="n"/>
-      <c r="S74" s="4" t="n"/>
+      <c r="S74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="T74" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -58093,12 +58091,12 @@
       <c r="P75" s="4" t="n"/>
       <c r="Q75" s="4" t="n"/>
       <c r="R75" s="4" t="n"/>
-      <c r="S75" s="4" t="n"/>
-      <c r="T75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="S75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T75" s="4" t="n"/>
       <c r="U75" s="4" t="n"/>
       <c r="V75" s="4" t="n"/>
       <c r="W75" s="4" t="n"/>
@@ -58200,17 +58198,17 @@
       <c r="K76" s="4" t="n"/>
       <c r="L76" s="4" t="n"/>
       <c r="M76" s="4" t="n"/>
-      <c r="N76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="N76" s="4" t="n"/>
       <c r="O76" s="4" t="n"/>
       <c r="P76" s="4" t="n"/>
       <c r="Q76" s="4" t="n"/>
       <c r="R76" s="4" t="n"/>
       <c r="S76" s="4" t="n"/>
-      <c r="T76" s="4" t="n"/>
+      <c r="T76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U76" s="4" t="n"/>
       <c r="V76" s="4" t="n"/>
       <c r="W76" s="4" t="n"/>
@@ -58429,12 +58427,12 @@
         </is>
       </c>
       <c r="N78" s="4" t="n"/>
-      <c r="O78" s="4" t="n"/>
-      <c r="P78" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O78" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P78" s="4" t="n"/>
       <c r="Q78" s="4" t="n"/>
       <c r="R78" s="4" t="n"/>
       <c r="S78" s="4" t="n"/>
@@ -58537,12 +58535,12 @@
         </is>
       </c>
       <c r="N79" s="4" t="n"/>
-      <c r="O79" s="4" t="n"/>
-      <c r="P79" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O79" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P79" s="4" t="n"/>
       <c r="Q79" s="4" t="n"/>
       <c r="R79" s="4" t="n"/>
       <c r="S79" s="4" t="n"/>
@@ -58650,12 +58648,12 @@
       <c r="M80" s="4" t="n"/>
       <c r="N80" s="4" t="n"/>
       <c r="O80" s="4" t="n"/>
-      <c r="P80" s="4" t="n"/>
-      <c r="Q80" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="P80" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q80" s="4" t="n"/>
       <c r="R80" s="4" t="n"/>
       <c r="S80" s="4" t="n"/>
       <c r="T80" s="4" t="n"/>
@@ -58757,12 +58755,12 @@
         </is>
       </c>
       <c r="N81" s="4" t="n"/>
-      <c r="O81" s="4" t="n"/>
-      <c r="P81" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="O81" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="P81" s="4" t="n"/>
       <c r="Q81" s="4" t="n"/>
       <c r="R81" s="4" t="n"/>
       <c r="S81" s="4" t="n"/>
@@ -58851,12 +58849,12 @@
       <c r="N82" s="4" t="n"/>
       <c r="O82" s="4" t="n"/>
       <c r="P82" s="4" t="n"/>
-      <c r="Q82" s="4" t="n"/>
-      <c r="R82" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="Q82" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R82" s="4" t="n"/>
       <c r="S82" s="4" t="n"/>
       <c r="T82" s="4" t="n"/>
       <c r="U82" s="4" t="n"/>
@@ -59037,12 +59035,12 @@
       <c r="P84" s="4" t="n"/>
       <c r="Q84" s="4" t="n"/>
       <c r="R84" s="4" t="n"/>
-      <c r="S84" s="4" t="n"/>
-      <c r="T84" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="S84" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="T84" s="4" t="n"/>
       <c r="U84" s="4" t="n"/>
       <c r="V84" s="4" t="n"/>
       <c r="W84" s="4" t="n"/>
@@ -59168,17 +59166,17 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>玻璃</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>速尾</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>9x8</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>玻璃</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>速尾</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -59244,13 +59242,13 @@
         </is>
       </c>
       <c r="C2" s="4" t="n"/>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D2" s="4" t="n"/>
       <c r="E2" s="4" t="n"/>
-      <c r="F2" s="4" t="n"/>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G2" s="4" t="n"/>
       <c r="H2" s="4" t="inlineStr">
         <is>
@@ -59286,17 +59284,17 @@
         </is>
       </c>
       <c r="C3" s="4" t="n"/>
-      <c r="D3" s="4" t="n"/>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="F3" s="4" t="n"/>
       <c r="G3" s="4" t="n"/>
       <c r="H3" s="4" t="n"/>
       <c r="I3" s="4" t="n"/>
@@ -59317,12 +59315,12 @@
       </c>
       <c r="C4" s="4" t="n"/>
       <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="n"/>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="n"/>
       <c r="G4" s="4" t="n"/>
       <c r="H4" s="4" t="n"/>
       <c r="I4" s="4" t="n"/>
@@ -59342,12 +59340,12 @@
         </is>
       </c>
       <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -59388,13 +59386,13 @@
         </is>
       </c>
       <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D6" s="4" t="n"/>
       <c r="E6" s="4" t="n"/>
-      <c r="F6" s="4" t="n"/>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G6" s="4" t="n"/>
       <c r="H6" s="4" t="inlineStr">
         <is>
@@ -59431,12 +59429,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="n"/>
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -59465,12 +59463,12 @@
       </c>
       <c r="C8" s="4" t="n"/>
       <c r="D8" s="4" t="n"/>
-      <c r="E8" s="4" t="n"/>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="n"/>
       <c r="G8" s="4" t="n"/>
       <c r="H8" s="4" t="n"/>
       <c r="I8" s="4" t="n"/>
@@ -59490,13 +59488,13 @@
         </is>
       </c>
       <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D9" s="4" t="n"/>
       <c r="E9" s="4" t="n"/>
-      <c r="F9" s="4" t="n"/>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -59536,13 +59534,13 @@
         </is>
       </c>
       <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D10" s="4" t="n"/>
       <c r="E10" s="4" t="n"/>
-      <c r="F10" s="4" t="n"/>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -59590,12 +59588,12 @@
         </is>
       </c>
       <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="n"/>
       <c r="F11" s="4" t="n"/>
       <c r="G11" s="4" t="n"/>
       <c r="H11" s="4" t="n"/>
@@ -59616,12 +59614,12 @@
         </is>
       </c>
       <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -59659,12 +59657,12 @@
       </c>
       <c r="C13" s="4" t="n"/>
       <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="n"/>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="n"/>
       <c r="G13" s="4" t="n"/>
       <c r="H13" s="4" t="n"/>
       <c r="I13" s="4" t="n"/>
@@ -59693,12 +59691,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -59726,12 +59724,12 @@
         </is>
       </c>
       <c r="C15" s="4" t="n"/>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="n"/>
+      <c r="D15" s="4" t="n"/>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -59764,12 +59762,12 @@
         </is>
       </c>
       <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n"/>
       <c r="F16" s="4" t="n"/>
       <c r="G16" s="4" t="n"/>
       <c r="H16" s="4" t="n"/>
@@ -59795,12 +59793,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="n"/>
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G17" s="4" t="n"/>
       <c r="H17" s="4" t="inlineStr">
         <is>
@@ -59841,12 +59839,12 @@
       </c>
       <c r="C18" s="4" t="n"/>
       <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="n"/>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="n"/>
       <c r="G18" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -59878,12 +59876,12 @@
         </is>
       </c>
       <c r="C19" s="4" t="n"/>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -59916,13 +59914,13 @@
         </is>
       </c>
       <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D20" s="4" t="n"/>
       <c r="E20" s="4" t="n"/>
-      <c r="F20" s="4" t="n"/>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G20" s="4" t="n"/>
       <c r="H20" s="4" t="inlineStr">
         <is>
@@ -59959,12 +59957,12 @@
       </c>
       <c r="C21" s="4" t="n"/>
       <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="n"/>
       <c r="G21" s="4" t="n"/>
       <c r="H21" s="4" t="n"/>
       <c r="I21" s="4" t="n"/>
@@ -60014,17 +60012,17 @@
         </is>
       </c>
       <c r="C23" s="4" t="n"/>
-      <c r="D23" s="4" t="n"/>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="F23" s="4" t="n"/>
       <c r="G23" s="4" t="n"/>
       <c r="H23" s="4" t="n"/>
       <c r="I23" s="4" t="n"/>
@@ -60044,12 +60042,12 @@
         </is>
       </c>
       <c r="C24" s="4" t="n"/>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -60087,12 +60085,12 @@
       </c>
       <c r="C25" s="4" t="n"/>
       <c r="D25" s="4" t="n"/>
-      <c r="E25" s="4" t="n"/>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="n"/>
       <c r="G25" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -60124,13 +60122,13 @@
         </is>
       </c>
       <c r="C26" s="4" t="n"/>
-      <c r="D26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D26" s="4" t="n"/>
       <c r="E26" s="4" t="n"/>
-      <c r="F26" s="4" t="n"/>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -60197,12 +60195,12 @@
       </c>
       <c r="C28" s="4" t="n"/>
       <c r="D28" s="4" t="n"/>
-      <c r="E28" s="4" t="n"/>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="n"/>
       <c r="G28" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -60234,12 +60232,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D29" s="4" t="n"/>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="n"/>
       <c r="F29" s="4" t="n"/>
       <c r="G29" s="4" t="n"/>
       <c r="H29" s="4" t="n"/>
@@ -60264,13 +60262,13 @@
         </is>
       </c>
       <c r="C30" s="4" t="n"/>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D30" s="4" t="n"/>
       <c r="E30" s="4" t="n"/>
-      <c r="F30" s="4" t="n"/>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G30" s="4" t="n"/>
       <c r="H30" s="4" t="inlineStr">
         <is>
@@ -60306,13 +60304,13 @@
         </is>
       </c>
       <c r="C31" s="4" t="n"/>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D31" s="4" t="n"/>
       <c r="E31" s="4" t="n"/>
-      <c r="F31" s="4" t="n"/>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G31" s="4" t="n"/>
       <c r="H31" s="4" t="n"/>
       <c r="I31" s="4" t="n"/>
@@ -60344,13 +60342,13 @@
         </is>
       </c>
       <c r="C32" s="4" t="n"/>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D32" s="4" t="n"/>
       <c r="E32" s="4" t="n"/>
-      <c r="F32" s="4" t="n"/>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G32" s="4" t="n"/>
       <c r="H32" s="4" t="n"/>
       <c r="I32" s="4" t="n"/>
@@ -60378,13 +60376,13 @@
         </is>
       </c>
       <c r="C33" s="4" t="n"/>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D33" s="4" t="n"/>
       <c r="E33" s="4" t="n"/>
-      <c r="F33" s="4" t="n"/>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G33" s="4" t="n"/>
       <c r="H33" s="4" t="inlineStr">
         <is>
@@ -60421,12 +60419,12 @@
       </c>
       <c r="C34" s="4" t="n"/>
       <c r="D34" s="4" t="n"/>
-      <c r="E34" s="4" t="n"/>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="n"/>
       <c r="G34" s="4" t="n"/>
       <c r="H34" s="4" t="n"/>
       <c r="I34" s="4" t="n"/>
@@ -60446,13 +60444,13 @@
         </is>
       </c>
       <c r="C35" s="4" t="n"/>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D35" s="4" t="n"/>
       <c r="E35" s="4" t="n"/>
-      <c r="F35" s="4" t="n"/>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G35" s="4" t="n"/>
       <c r="H35" s="4" t="inlineStr">
         <is>
@@ -60484,12 +60482,12 @@
         </is>
       </c>
       <c r="C36" s="4" t="n"/>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="n"/>
+      <c r="D36" s="4" t="n"/>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -60522,13 +60520,13 @@
         </is>
       </c>
       <c r="C37" s="4" t="n"/>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D37" s="4" t="n"/>
       <c r="E37" s="4" t="n"/>
-      <c r="F37" s="4" t="n"/>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G37" s="4" t="n"/>
       <c r="H37" s="4" t="n"/>
       <c r="I37" s="4" t="n"/>
@@ -60556,12 +60554,12 @@
         </is>
       </c>
       <c r="C38" s="4" t="n"/>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="n"/>
+      <c r="D38" s="4" t="n"/>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -60599,12 +60597,12 @@
       </c>
       <c r="C39" s="4" t="n"/>
       <c r="D39" s="4" t="n"/>
-      <c r="E39" s="4" t="n"/>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="n"/>
       <c r="G39" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -60640,13 +60638,13 @@
         </is>
       </c>
       <c r="C40" s="4" t="n"/>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D40" s="4" t="n"/>
       <c r="E40" s="4" t="n"/>
-      <c r="F40" s="4" t="n"/>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G40" s="4" t="n"/>
       <c r="H40" s="4" t="n"/>
       <c r="I40" s="4" t="n"/>
@@ -60678,12 +60676,12 @@
         </is>
       </c>
       <c r="C41" s="4" t="n"/>
-      <c r="D41" s="4" t="n"/>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="n"/>
       <c r="F41" s="4" t="n"/>
       <c r="G41" s="4" t="n"/>
       <c r="H41" s="4" t="n"/>
@@ -60704,13 +60702,13 @@
         </is>
       </c>
       <c r="C42" s="4" t="n"/>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D42" s="4" t="n"/>
       <c r="E42" s="4" t="n"/>
-      <c r="F42" s="4" t="n"/>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -60742,12 +60740,12 @@
         </is>
       </c>
       <c r="C43" s="4" t="n"/>
-      <c r="D43" s="4" t="n"/>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="n"/>
       <c r="F43" s="4" t="n"/>
       <c r="G43" s="4" t="n"/>
       <c r="H43" s="4" t="n"/>
@@ -60772,13 +60770,13 @@
         </is>
       </c>
       <c r="C44" s="4" t="n"/>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D44" s="4" t="n"/>
       <c r="E44" s="4" t="n"/>
-      <c r="F44" s="4" t="n"/>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G44" s="4" t="n"/>
       <c r="H44" s="4" t="inlineStr">
         <is>
@@ -60814,12 +60812,12 @@
         </is>
       </c>
       <c r="C45" s="4" t="n"/>
-      <c r="D45" s="4" t="n"/>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="n"/>
       <c r="F45" s="4" t="n"/>
       <c r="G45" s="4" t="n"/>
       <c r="H45" s="4" t="n"/>
@@ -60845,12 +60843,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F46" s="4" t="n"/>
+      <c r="E46" s="4" t="n"/>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G46" s="4" t="n"/>
       <c r="H46" s="4" t="n"/>
       <c r="I46" s="4" t="n"/>
@@ -60883,12 +60881,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="n"/>
+      <c r="E47" s="4" t="n"/>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G47" s="4" t="n"/>
       <c r="H47" s="4" t="n"/>
       <c r="I47" s="4" t="n"/>
@@ -60917,12 +60915,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F48" s="4" t="n"/>
+      <c r="E48" s="4" t="n"/>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G48" s="4" t="n"/>
       <c r="H48" s="4" t="n"/>
       <c r="I48" s="4" t="n"/>
@@ -60946,13 +60944,13 @@
         </is>
       </c>
       <c r="C49" s="4" t="n"/>
-      <c r="D49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D49" s="4" t="n"/>
       <c r="E49" s="4" t="n"/>
-      <c r="F49" s="4" t="n"/>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G49" s="4" t="n"/>
       <c r="H49" s="4" t="inlineStr">
         <is>
@@ -60984,13 +60982,13 @@
         </is>
       </c>
       <c r="C50" s="4" t="n"/>
-      <c r="D50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D50" s="4" t="n"/>
       <c r="E50" s="4" t="n"/>
-      <c r="F50" s="4" t="n"/>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G50" s="4" t="n"/>
       <c r="H50" s="4" t="inlineStr">
         <is>
@@ -61022,13 +61020,13 @@
         </is>
       </c>
       <c r="C51" s="4" t="n"/>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D51" s="4" t="n"/>
       <c r="E51" s="4" t="n"/>
-      <c r="F51" s="4" t="n"/>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -61064,12 +61062,12 @@
         </is>
       </c>
       <c r="C52" s="4" t="n"/>
-      <c r="D52" s="4" t="n"/>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="n"/>
       <c r="F52" s="4" t="n"/>
       <c r="G52" s="4" t="n"/>
       <c r="H52" s="4" t="n"/>
@@ -61099,12 +61097,12 @@
       </c>
       <c r="C53" s="4" t="n"/>
       <c r="D53" s="4" t="n"/>
-      <c r="E53" s="4" t="n"/>
-      <c r="F53" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="n"/>
       <c r="G53" s="4" t="n"/>
       <c r="H53" s="4" t="n"/>
       <c r="I53" s="4" t="n"/>
@@ -61146,13 +61144,13 @@
         </is>
       </c>
       <c r="C55" s="4" t="n"/>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D55" s="4" t="n"/>
       <c r="E55" s="4" t="n"/>
-      <c r="F55" s="4" t="n"/>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G55" s="4" t="n"/>
       <c r="H55" s="4" t="inlineStr">
         <is>
@@ -61184,13 +61182,13 @@
         </is>
       </c>
       <c r="C56" s="4" t="n"/>
-      <c r="D56" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D56" s="4" t="n"/>
       <c r="E56" s="4" t="n"/>
-      <c r="F56" s="4" t="n"/>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G56" s="4" t="n"/>
       <c r="H56" s="4" t="n"/>
       <c r="I56" s="4" t="n"/>
@@ -61214,17 +61212,17 @@
         </is>
       </c>
       <c r="C57" s="4" t="n"/>
-      <c r="D57" s="4" t="n"/>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="F57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="F57" s="4" t="n"/>
       <c r="G57" s="4" t="n"/>
       <c r="H57" s="4" t="n"/>
       <c r="I57" s="4" t="n"/>
@@ -61266,13 +61264,13 @@
         </is>
       </c>
       <c r="C59" s="4" t="n"/>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D59" s="4" t="n"/>
       <c r="E59" s="4" t="n"/>
-      <c r="F59" s="4" t="n"/>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G59" s="4" t="n"/>
       <c r="H59" s="4" t="inlineStr">
         <is>
@@ -61308,12 +61306,12 @@
         </is>
       </c>
       <c r="C60" s="4" t="n"/>
-      <c r="D60" s="4" t="n"/>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="n"/>
       <c r="F60" s="4" t="n"/>
       <c r="G60" s="4" t="n"/>
       <c r="H60" s="4" t="n"/>
@@ -61338,13 +61336,13 @@
         </is>
       </c>
       <c r="C61" s="4" t="n"/>
-      <c r="D61" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D61" s="4" t="n"/>
       <c r="E61" s="4" t="n"/>
-      <c r="F61" s="4" t="n"/>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -61388,12 +61386,12 @@
         </is>
       </c>
       <c r="C62" s="4" t="n"/>
-      <c r="D62" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E62" s="4" t="n"/>
+      <c r="D62" s="4" t="n"/>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -61435,12 +61433,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F63" s="4" t="n"/>
+      <c r="E63" s="4" t="n"/>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G63" s="4" t="n"/>
       <c r="H63" s="4" t="inlineStr">
         <is>
@@ -61469,12 +61467,12 @@
       </c>
       <c r="C64" s="4" t="n"/>
       <c r="D64" s="4" t="n"/>
-      <c r="E64" s="4" t="n"/>
-      <c r="F64" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="n"/>
       <c r="G64" s="4" t="n"/>
       <c r="H64" s="4" t="n"/>
       <c r="I64" s="4" t="n"/>
@@ -61499,12 +61497,12 @@
       </c>
       <c r="C65" s="4" t="n"/>
       <c r="D65" s="4" t="n"/>
-      <c r="E65" s="4" t="n"/>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="n"/>
       <c r="G65" s="4" t="n"/>
       <c r="H65" s="4" t="n"/>
       <c r="I65" s="4" t="n"/>
@@ -61546,12 +61544,12 @@
         </is>
       </c>
       <c r="C67" s="4" t="n"/>
-      <c r="D67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E67" s="4" t="n"/>
+      <c r="D67" s="4" t="n"/>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -61601,12 +61599,12 @@
       </c>
       <c r="C68" s="4" t="n"/>
       <c r="D68" s="4" t="n"/>
-      <c r="E68" s="4" t="n"/>
-      <c r="F68" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="n"/>
       <c r="G68" s="4" t="n"/>
       <c r="H68" s="4" t="n"/>
       <c r="I68" s="4" t="n"/>
@@ -61635,12 +61633,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="n"/>
+      <c r="E69" s="4" t="n"/>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G69" s="4" t="n"/>
       <c r="H69" s="4" t="n"/>
       <c r="I69" s="4" t="n"/>
@@ -61664,13 +61662,13 @@
         </is>
       </c>
       <c r="C70" s="4" t="n"/>
-      <c r="D70" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D70" s="4" t="n"/>
       <c r="E70" s="4" t="n"/>
-      <c r="F70" s="4" t="n"/>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -61706,12 +61704,12 @@
         </is>
       </c>
       <c r="C71" s="4" t="n"/>
-      <c r="D71" s="4" t="n"/>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="n"/>
       <c r="F71" s="4" t="n"/>
       <c r="G71" s="4" t="n"/>
       <c r="H71" s="4" t="n"/>
@@ -61732,12 +61730,12 @@
         </is>
       </c>
       <c r="C72" s="4" t="n"/>
-      <c r="D72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E72" s="4" t="n"/>
+      <c r="D72" s="4" t="n"/>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -61782,13 +61780,13 @@
         </is>
       </c>
       <c r="C73" s="4" t="n"/>
-      <c r="D73" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D73" s="4" t="n"/>
       <c r="E73" s="4" t="n"/>
-      <c r="F73" s="4" t="n"/>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G73" s="4" t="n"/>
       <c r="H73" s="4" t="n"/>
       <c r="I73" s="4" t="n"/>
@@ -61820,12 +61818,12 @@
         </is>
       </c>
       <c r="C74" s="4" t="n"/>
-      <c r="D74" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E74" s="4" t="n"/>
+      <c r="D74" s="4" t="n"/>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -61855,12 +61853,12 @@
       </c>
       <c r="C75" s="4" t="n"/>
       <c r="D75" s="4" t="n"/>
-      <c r="E75" s="4" t="n"/>
-      <c r="F75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="n"/>
       <c r="G75" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -61896,13 +61894,13 @@
         </is>
       </c>
       <c r="C76" s="4" t="n"/>
-      <c r="D76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D76" s="4" t="n"/>
       <c r="E76" s="4" t="n"/>
-      <c r="F76" s="4" t="n"/>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G76" s="4" t="n"/>
       <c r="H76" s="4" t="inlineStr">
         <is>
@@ -61934,12 +61932,12 @@
         </is>
       </c>
       <c r="C77" s="4" t="n"/>
-      <c r="D77" s="4" t="n"/>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="n"/>
       <c r="F77" s="4" t="n"/>
       <c r="G77" s="4" t="n"/>
       <c r="H77" s="4" t="n"/>
@@ -61982,12 +61980,12 @@
         </is>
       </c>
       <c r="C79" s="4" t="n"/>
-      <c r="D79" s="4" t="n"/>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="n"/>
       <c r="F79" s="4" t="n"/>
       <c r="G79" s="4" t="n"/>
       <c r="H79" s="4" t="n"/>
@@ -62008,12 +62006,12 @@
         </is>
       </c>
       <c r="C80" s="4" t="n"/>
-      <c r="D80" s="4" t="n"/>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="n"/>
       <c r="F80" s="4" t="n"/>
       <c r="G80" s="4" t="n"/>
       <c r="H80" s="4" t="n"/>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -37401,17 +37401,17 @@
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
+          <t>大超</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
           <t>小牛</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>统治</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>大超</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
@@ -37769,10 +37769,10 @@
       <c r="AD6" s="4" t="n"/>
       <c r="AE6" s="4" t="n"/>
       <c r="AF6" s="4" t="n"/>
-      <c r="AG6" s="4" t="n">
+      <c r="AG6" s="4" t="n"/>
+      <c r="AH6" s="4" t="n">
         <v>18.6</v>
       </c>
-      <c r="AH6" s="4" t="n"/>
       <c r="AI6" s="4" t="n"/>
       <c r="AJ6" s="4" t="n"/>
       <c r="AK6" s="4" t="n"/>
@@ -38540,10 +38540,10 @@
         <v>23.99</v>
       </c>
       <c r="AG18" s="4" t="n"/>
-      <c r="AH18" s="4" t="n">
+      <c r="AH18" s="4" t="n"/>
+      <c r="AI18" s="4" t="n">
         <v>23.79</v>
       </c>
-      <c r="AI18" s="4" t="n"/>
       <c r="AJ18" s="4" t="n"/>
       <c r="AK18" s="4" t="n"/>
       <c r="AL18" s="4" t="n"/>
@@ -38661,10 +38661,10 @@
       <c r="AD20" s="4" t="n"/>
       <c r="AE20" s="4" t="n"/>
       <c r="AF20" s="4" t="n"/>
-      <c r="AG20" s="4" t="n">
+      <c r="AG20" s="4" t="n"/>
+      <c r="AH20" s="4" t="n">
         <v>23.5</v>
       </c>
-      <c r="AH20" s="4" t="n"/>
       <c r="AI20" s="4" t="n"/>
       <c r="AJ20" s="4" t="n"/>
       <c r="AK20" s="4" t="n"/>
@@ -38786,10 +38786,10 @@
       <c r="AE22" s="4" t="n"/>
       <c r="AF22" s="4" t="n"/>
       <c r="AG22" s="4" t="n"/>
-      <c r="AH22" s="4" t="n">
+      <c r="AH22" s="4" t="n"/>
+      <c r="AI22" s="4" t="n">
         <v>31.75</v>
       </c>
-      <c r="AI22" s="4" t="n"/>
       <c r="AJ22" s="4" t="n"/>
       <c r="AK22" s="4" t="n"/>
       <c r="AL22" s="4" t="n"/>
@@ -39209,11 +39209,11 @@
       <c r="AD29" s="4" t="n"/>
       <c r="AE29" s="4" t="n"/>
       <c r="AF29" s="4" t="n"/>
-      <c r="AG29" s="4" t="n"/>
+      <c r="AG29" s="4" t="n">
+        <v>18.25</v>
+      </c>
       <c r="AH29" s="4" t="n"/>
-      <c r="AI29" s="4" t="n">
-        <v>18.25</v>
-      </c>
+      <c r="AI29" s="4" t="n"/>
       <c r="AJ29" s="4" t="n"/>
       <c r="AK29" s="4" t="n"/>
       <c r="AL29" s="4" t="n"/>
@@ -39781,10 +39781,10 @@
       <c r="AD38" s="4" t="n"/>
       <c r="AE38" s="4" t="n"/>
       <c r="AF38" s="4" t="n"/>
-      <c r="AG38" s="4" t="n">
+      <c r="AG38" s="4" t="n"/>
+      <c r="AH38" s="4" t="n">
         <v>21.87</v>
       </c>
-      <c r="AH38" s="4" t="n"/>
       <c r="AI38" s="4" t="n"/>
       <c r="AJ38" s="4" t="n"/>
       <c r="AK38" s="4" t="n"/>
@@ -40353,12 +40353,18 @@
           <t>直道冲刺</t>
         </is>
       </c>
-      <c r="C48" s="4" t="n"/>
-      <c r="D48" s="4" t="n"/>
+      <c r="C48" s="4" t="n">
+        <v>24.84</v>
+      </c>
+      <c r="D48" s="4" t="n">
+        <v>24.7</v>
+      </c>
       <c r="E48" s="4" t="n"/>
       <c r="F48" s="4" t="n"/>
       <c r="G48" s="4" t="n"/>
-      <c r="H48" s="4" t="n"/>
+      <c r="H48" s="4" t="n">
+        <v>24.97</v>
+      </c>
       <c r="I48" s="4" t="n"/>
       <c r="J48" s="4" t="n"/>
       <c r="K48" s="4" t="n">
@@ -40693,11 +40699,11 @@
       <c r="AD53" s="4" t="n"/>
       <c r="AE53" s="4" t="n"/>
       <c r="AF53" s="4" t="n"/>
-      <c r="AG53" s="4" t="n"/>
+      <c r="AG53" s="4" t="n">
+        <v>33.99</v>
+      </c>
       <c r="AH53" s="4" t="n"/>
-      <c r="AI53" s="4" t="n">
-        <v>33.99</v>
-      </c>
+      <c r="AI53" s="4" t="n"/>
       <c r="AJ53" s="4" t="n"/>
       <c r="AK53" s="4" t="n"/>
       <c r="AL53" s="4" t="n"/>
@@ -40850,7 +40856,9 @@
       </c>
       <c r="H56" s="4" t="n"/>
       <c r="I56" s="4" t="n"/>
-      <c r="J56" s="4" t="n"/>
+      <c r="J56" s="4" t="n">
+        <v>36.89</v>
+      </c>
       <c r="K56" s="4" t="n"/>
       <c r="L56" s="4" t="n"/>
       <c r="M56" s="4" t="n"/>
@@ -40937,11 +40945,11 @@
       <c r="AD57" s="4" t="n"/>
       <c r="AE57" s="4" t="n"/>
       <c r="AF57" s="4" t="n"/>
-      <c r="AG57" s="4" t="n"/>
+      <c r="AG57" s="4" t="n">
+        <v>35.59</v>
+      </c>
       <c r="AH57" s="4" t="n"/>
-      <c r="AI57" s="4" t="n">
-        <v>35.59</v>
-      </c>
+      <c r="AI57" s="4" t="n"/>
       <c r="AJ57" s="4" t="n"/>
       <c r="AK57" s="4" t="n"/>
       <c r="AL57" s="4" t="n"/>
@@ -41377,7 +41385,9 @@
       <c r="AD64" s="4" t="n"/>
       <c r="AE64" s="4" t="n"/>
       <c r="AF64" s="4" t="n"/>
-      <c r="AG64" s="4" t="n"/>
+      <c r="AG64" s="4" t="n">
+        <v>35.45</v>
+      </c>
       <c r="AH64" s="4" t="n"/>
       <c r="AI64" s="4" t="n"/>
       <c r="AJ64" s="4" t="n"/>
@@ -42226,10 +42236,10 @@
       <c r="AE78" s="4" t="n"/>
       <c r="AF78" s="4" t="n"/>
       <c r="AG78" s="4" t="n"/>
-      <c r="AH78" s="4" t="n">
+      <c r="AH78" s="4" t="n"/>
+      <c r="AI78" s="4" t="n">
         <v>32.1</v>
       </c>
-      <c r="AI78" s="4" t="n"/>
       <c r="AJ78" s="4" t="n"/>
       <c r="AK78" s="4" t="n"/>
       <c r="AL78" s="4" t="n"/>
@@ -42940,17 +42950,17 @@
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
+          <t>大超★1</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>大超★3</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
           <t>小牛★6</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>大超★1</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>大超★3</t>
         </is>
       </c>
       <c r="BC1" s="1" t="inlineStr">
@@ -45162,13 +45172,13 @@
       <c r="AW29" s="4" t="n"/>
       <c r="AX29" s="4" t="n"/>
       <c r="AY29" s="4" t="n"/>
-      <c r="AZ29" s="4" t="n"/>
+      <c r="AZ29" s="4" t="n">
+        <v>18.6</v>
+      </c>
       <c r="BA29" s="4" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="BB29" s="4" t="n">
         <v>18.4</v>
       </c>
+      <c r="BB29" s="4" t="n"/>
       <c r="BC29" s="4" t="n"/>
       <c r="BD29" s="4" t="n"/>
       <c r="BE29" s="4" t="n"/>
@@ -45217,7 +45227,9 @@
       <c r="Z30" s="4" t="n"/>
       <c r="AA30" s="4" t="n"/>
       <c r="AB30" s="4" t="n"/>
-      <c r="AC30" s="4" t="n"/>
+      <c r="AC30" s="4" t="n">
+        <v>23.49</v>
+      </c>
       <c r="AD30" s="4" t="n"/>
       <c r="AE30" s="4" t="n"/>
       <c r="AF30" s="4" t="n"/>
@@ -45394,11 +45406,11 @@
       <c r="AW32" s="4" t="n"/>
       <c r="AX32" s="4" t="n"/>
       <c r="AY32" s="4" t="n"/>
-      <c r="AZ32" s="4" t="n">
+      <c r="AZ32" s="4" t="n"/>
+      <c r="BA32" s="4" t="n"/>
+      <c r="BB32" s="4" t="n">
         <v>30.1</v>
       </c>
-      <c r="BA32" s="4" t="n"/>
-      <c r="BB32" s="4" t="n"/>
       <c r="BC32" s="4" t="n">
         <v>29.56</v>
       </c>
@@ -47352,13 +47364,13 @@
       <c r="AW57" s="4" t="n"/>
       <c r="AX57" s="4" t="n"/>
       <c r="AY57" s="4" t="n"/>
-      <c r="AZ57" s="4" t="n"/>
+      <c r="AZ57" s="4" t="n">
+        <v>36.39</v>
+      </c>
       <c r="BA57" s="4" t="n">
-        <v>36.39</v>
-      </c>
-      <c r="BB57" s="4" t="n">
         <v>35.9</v>
       </c>
+      <c r="BB57" s="4" t="n"/>
       <c r="BC57" s="4" t="n"/>
       <c r="BD57" s="4" t="n"/>
       <c r="BE57" s="4" t="n"/>
@@ -49826,17 +49838,17 @@
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
+          <t>大超★1</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>大超★3</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
           <t>小牛★6</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>大超★1</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>大超★3</t>
         </is>
       </c>
       <c r="BC1" s="1" t="inlineStr">
@@ -50396,13 +50408,13 @@
       <c r="AW6" s="4" t="n"/>
       <c r="AX6" s="4" t="n"/>
       <c r="AY6" s="4" t="n"/>
-      <c r="AZ6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AZ6" s="4" t="n"/>
       <c r="BA6" s="4" t="n"/>
-      <c r="BB6" s="4" t="n"/>
+      <c r="BB6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC6" s="4" t="n"/>
       <c r="BD6" s="4" t="n"/>
       <c r="BE6" s="4" t="n"/>
@@ -52988,17 +53000,17 @@
       <c r="AW29" s="4" t="n"/>
       <c r="AX29" s="4" t="n"/>
       <c r="AY29" s="4" t="n"/>
-      <c r="AZ29" s="4" t="n"/>
+      <c r="AZ29" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BA29" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BB29" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BB29" s="4" t="n"/>
       <c r="BC29" s="4" t="n"/>
       <c r="BD29" s="4" t="n"/>
       <c r="BE29" s="4" t="n"/>
@@ -53316,13 +53328,13 @@
       <c r="AW32" s="4" t="n"/>
       <c r="AX32" s="4" t="n"/>
       <c r="AY32" s="4" t="n"/>
-      <c r="AZ32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AZ32" s="4" t="n"/>
       <c r="BA32" s="4" t="n"/>
-      <c r="BB32" s="4" t="n"/>
+      <c r="BB32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC32" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -55836,12 +55848,12 @@
       <c r="AW54" s="4" t="n"/>
       <c r="AX54" s="4" t="n"/>
       <c r="AY54" s="4" t="n"/>
-      <c r="AZ54" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BA54" s="4" t="n"/>
+      <c r="AZ54" s="4" t="n"/>
+      <c r="BA54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BB54" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -56168,17 +56180,17 @@
       <c r="AW57" s="4" t="n"/>
       <c r="AX57" s="4" t="n"/>
       <c r="AY57" s="4" t="n"/>
-      <c r="AZ57" s="4" t="n"/>
+      <c r="AZ57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BA57" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BB57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BB57" s="4" t="n"/>
       <c r="BC57" s="4" t="n"/>
       <c r="BD57" s="4" t="n"/>
       <c r="BE57" s="4" t="n"/>
@@ -57304,13 +57316,13 @@
       <c r="AW67" s="4" t="n"/>
       <c r="AX67" s="4" t="n"/>
       <c r="AY67" s="4" t="n"/>
-      <c r="AZ67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AZ67" s="4" t="n"/>
       <c r="BA67" s="4" t="n"/>
-      <c r="BB67" s="4" t="n"/>
+      <c r="BB67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC67" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -58164,13 +58176,13 @@
       <c r="AW75" s="4" t="n"/>
       <c r="AX75" s="4" t="n"/>
       <c r="AY75" s="4" t="n"/>
-      <c r="AZ75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AZ75" s="4" t="n"/>
       <c r="BA75" s="4" t="n"/>
-      <c r="BB75" s="4" t="n"/>
+      <c r="BB75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BC75" s="4" t="n"/>
       <c r="BD75" s="4" t="n"/>
       <c r="BE75" s="4" t="n"/>
@@ -58705,12 +58717,12 @@
       <c r="AX80" s="4" t="n"/>
       <c r="AY80" s="4" t="n"/>
       <c r="AZ80" s="4" t="n"/>
-      <c r="BA80" s="4" t="n"/>
-      <c r="BB80" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BA80" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BB80" s="4" t="n"/>
       <c r="BC80" s="4" t="n"/>
       <c r="BD80" s="4" t="n"/>
       <c r="BE80" s="4" t="n"/>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -12566,7 +12566,9 @@
       <c r="AB18" s="4" t="n"/>
       <c r="AC18" s="4" t="n"/>
       <c r="AD18" s="4" t="n"/>
-      <c r="AE18" s="4" t="n"/>
+      <c r="AE18" s="4" t="n">
+        <v>23.1</v>
+      </c>
       <c r="AF18" s="4" t="n"/>
       <c r="AG18" s="4" t="n"/>
       <c r="AH18" s="4" t="n"/>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -25,7 +25,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'五区_高手'!$A$1:$CK$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'五区_普通'!$A$1:$CK$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'五区_自动'!$A$1:$U$84</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'四区_理论'!$A$1:$AR$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'四区_理论'!$A$1:$AT$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'四区_高手'!$A$1:$BJ$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'四区_普通'!$A$1:$BJ$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'四区_自动'!$A$1:$P$84</definedName>
@@ -16767,7 +16767,9 @@
       <c r="AO56" s="4" t="n"/>
       <c r="AP56" s="4" t="n"/>
       <c r="AQ56" s="4" t="n"/>
-      <c r="AR56" s="4" t="n"/>
+      <c r="AR56" s="4" t="n">
+        <v>35.89</v>
+      </c>
       <c r="AS56" s="4" t="n"/>
       <c r="AT56" s="4" t="n"/>
       <c r="AU56" s="4" t="n"/>
@@ -37191,7 +37193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR84"/>
+  <dimension ref="A1:AT84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -37238,6 +37240,8 @@
     <col width="7.5" customWidth="1" min="42" max="42"/>
     <col width="7.5" customWidth="1" min="43" max="43"/>
     <col width="7.5" customWidth="1" min="44" max="44"/>
+    <col width="7.5" customWidth="1" min="45" max="45"/>
+    <col width="7.5" customWidth="1" min="46" max="46"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -37418,45 +37422,55 @@
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
+          <t>cs</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
           <t>fe3</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>杰弟</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>六子</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>biome</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>帕梅</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>ts900</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>风扇</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>保时捷919</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>600lt</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>5n</t>
         </is>
@@ -37521,6 +37535,8 @@
       <c r="AP2" s="4" t="n"/>
       <c r="AQ2" s="4" t="n"/>
       <c r="AR2" s="4" t="n"/>
+      <c r="AS2" s="4" t="n"/>
+      <c r="AT2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n"/>
@@ -37585,6 +37601,8 @@
       <c r="AP3" s="4" t="n"/>
       <c r="AQ3" s="4" t="n"/>
       <c r="AR3" s="4" t="n"/>
+      <c r="AS3" s="4" t="n"/>
+      <c r="AT3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n"/>
@@ -37649,6 +37667,8 @@
       <c r="AP4" s="4" t="n"/>
       <c r="AQ4" s="4" t="n"/>
       <c r="AR4" s="4" t="n"/>
+      <c r="AS4" s="4" t="n"/>
+      <c r="AT4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n"/>
@@ -37710,19 +37730,21 @@
       <c r="AG5" s="4" t="n"/>
       <c r="AH5" s="4" t="n"/>
       <c r="AI5" s="4" t="n"/>
-      <c r="AJ5" s="4" t="n">
+      <c r="AJ5" s="4" t="n"/>
+      <c r="AK5" s="4" t="n">
         <v>18.17</v>
       </c>
-      <c r="AK5" s="4" t="n">
+      <c r="AL5" s="4" t="n">
         <v>17.93</v>
       </c>
-      <c r="AL5" s="4" t="n"/>
       <c r="AM5" s="4" t="n"/>
       <c r="AN5" s="4" t="n"/>
       <c r="AO5" s="4" t="n"/>
       <c r="AP5" s="4" t="n"/>
       <c r="AQ5" s="4" t="n"/>
       <c r="AR5" s="4" t="n"/>
+      <c r="AS5" s="4" t="n"/>
+      <c r="AT5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -37785,6 +37807,8 @@
       <c r="AP6" s="4" t="n"/>
       <c r="AQ6" s="4" t="n"/>
       <c r="AR6" s="4" t="n"/>
+      <c r="AS6" s="4" t="n"/>
+      <c r="AT6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
@@ -37843,6 +37867,8 @@
       <c r="AP7" s="4" t="n"/>
       <c r="AQ7" s="4" t="n"/>
       <c r="AR7" s="4" t="n"/>
+      <c r="AS7" s="4" t="n"/>
+      <c r="AT7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
@@ -37913,6 +37939,8 @@
       <c r="AP8" s="4" t="n"/>
       <c r="AQ8" s="4" t="n"/>
       <c r="AR8" s="4" t="n"/>
+      <c r="AS8" s="4" t="n"/>
+      <c r="AT8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n"/>
@@ -37977,12 +38005,14 @@
       <c r="AL9" s="4" t="n"/>
       <c r="AM9" s="4" t="n"/>
       <c r="AN9" s="4" t="n"/>
-      <c r="AO9" s="4" t="n">
+      <c r="AO9" s="4" t="n"/>
+      <c r="AP9" s="4" t="n">
         <v>19.94</v>
       </c>
-      <c r="AP9" s="4" t="n"/>
       <c r="AQ9" s="4" t="n"/>
       <c r="AR9" s="4" t="n"/>
+      <c r="AS9" s="4" t="n"/>
+      <c r="AT9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -38045,6 +38075,8 @@
       <c r="AP10" s="4" t="n"/>
       <c r="AQ10" s="4" t="n"/>
       <c r="AR10" s="4" t="n"/>
+      <c r="AS10" s="4" t="n"/>
+      <c r="AT10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
@@ -38103,6 +38135,8 @@
       <c r="AP11" s="4" t="n"/>
       <c r="AQ11" s="4" t="n"/>
       <c r="AR11" s="4" t="n"/>
+      <c r="AS11" s="4" t="n"/>
+      <c r="AT11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
@@ -38167,6 +38201,8 @@
       <c r="AP12" s="4" t="n"/>
       <c r="AQ12" s="4" t="n"/>
       <c r="AR12" s="4" t="n"/>
+      <c r="AS12" s="4" t="n"/>
+      <c r="AT12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
@@ -38223,6 +38259,8 @@
       <c r="AP13" s="4" t="n"/>
       <c r="AQ13" s="4" t="n"/>
       <c r="AR13" s="4" t="n"/>
+      <c r="AS13" s="4" t="n"/>
+      <c r="AT13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -38239,7 +38277,7 @@
         <v>25.49</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>25.32</v>
+        <v>25.25</v>
       </c>
       <c r="E14" s="4" t="n">
         <v>25.29</v>
@@ -38291,6 +38329,8 @@
       <c r="AP14" s="4" t="n"/>
       <c r="AQ14" s="4" t="n"/>
       <c r="AR14" s="4" t="n"/>
+      <c r="AS14" s="4" t="n"/>
+      <c r="AT14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
@@ -38359,6 +38399,8 @@
       <c r="AP15" s="4" t="n"/>
       <c r="AQ15" s="4" t="n"/>
       <c r="AR15" s="4" t="n"/>
+      <c r="AS15" s="4" t="n"/>
+      <c r="AT15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
@@ -38417,6 +38459,8 @@
       <c r="AP16" s="4" t="n"/>
       <c r="AQ16" s="4" t="n"/>
       <c r="AR16" s="4" t="n"/>
+      <c r="AS16" s="4" t="n"/>
+      <c r="AT16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
@@ -38479,6 +38523,8 @@
       <c r="AP17" s="4" t="n"/>
       <c r="AQ17" s="4" t="n"/>
       <c r="AR17" s="4" t="n"/>
+      <c r="AS17" s="4" t="n"/>
+      <c r="AT17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -38555,6 +38601,8 @@
       <c r="AP18" s="4" t="n"/>
       <c r="AQ18" s="4" t="n"/>
       <c r="AR18" s="4" t="n"/>
+      <c r="AS18" s="4" t="n"/>
+      <c r="AT18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
@@ -38606,7 +38654,9 @@
       <c r="AG19" s="4" t="n"/>
       <c r="AH19" s="4" t="n"/>
       <c r="AI19" s="4" t="n"/>
-      <c r="AJ19" s="4" t="n"/>
+      <c r="AJ19" s="4" t="n">
+        <v>33.5</v>
+      </c>
       <c r="AK19" s="4" t="n"/>
       <c r="AL19" s="4" t="n"/>
       <c r="AM19" s="4" t="n"/>
@@ -38614,7 +38664,11 @@
       <c r="AO19" s="4" t="n"/>
       <c r="AP19" s="4" t="n"/>
       <c r="AQ19" s="4" t="n"/>
-      <c r="AR19" s="4" t="n"/>
+      <c r="AR19" s="4" t="n">
+        <v>33.45</v>
+      </c>
+      <c r="AS19" s="4" t="n"/>
+      <c r="AT19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
@@ -38672,13 +38726,15 @@
       <c r="AK20" s="4" t="n"/>
       <c r="AL20" s="4" t="n"/>
       <c r="AM20" s="4" t="n"/>
-      <c r="AN20" s="4" t="n">
+      <c r="AN20" s="4" t="n"/>
+      <c r="AO20" s="4" t="n">
         <v>23.75</v>
       </c>
-      <c r="AO20" s="4" t="n"/>
       <c r="AP20" s="4" t="n"/>
       <c r="AQ20" s="4" t="n"/>
       <c r="AR20" s="4" t="n"/>
+      <c r="AS20" s="4" t="n"/>
+      <c r="AT20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
@@ -38735,6 +38791,8 @@
       <c r="AP21" s="4" t="n"/>
       <c r="AQ21" s="4" t="n"/>
       <c r="AR21" s="4" t="n"/>
+      <c r="AS21" s="4" t="n"/>
+      <c r="AT21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -38801,6 +38859,8 @@
       <c r="AP22" s="4" t="n"/>
       <c r="AQ22" s="4" t="n"/>
       <c r="AR22" s="4" t="n"/>
+      <c r="AS22" s="4" t="n"/>
+      <c r="AT22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
@@ -38859,6 +38919,8 @@
       <c r="AP23" s="4" t="n"/>
       <c r="AQ23" s="4" t="n"/>
       <c r="AR23" s="4" t="n"/>
+      <c r="AS23" s="4" t="n"/>
+      <c r="AT23" s="4" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
@@ -38917,6 +38979,8 @@
       <c r="AP24" s="4" t="n"/>
       <c r="AQ24" s="4" t="n"/>
       <c r="AR24" s="4" t="n"/>
+      <c r="AS24" s="4" t="n"/>
+      <c r="AT24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
@@ -38977,6 +39041,8 @@
       <c r="AP25" s="4" t="n"/>
       <c r="AQ25" s="4" t="n"/>
       <c r="AR25" s="4" t="n"/>
+      <c r="AS25" s="4" t="n"/>
+      <c r="AT25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -39043,6 +39109,8 @@
       <c r="AP26" s="4" t="n"/>
       <c r="AQ26" s="4" t="n"/>
       <c r="AR26" s="4" t="n"/>
+      <c r="AS26" s="4" t="n"/>
+      <c r="AT26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n"/>
@@ -39052,7 +39120,7 @@
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>32.59</v>
+        <v>32.39</v>
       </c>
       <c r="D27" s="4" t="n"/>
       <c r="E27" s="4" t="n"/>
@@ -39101,6 +39169,8 @@
       <c r="AP27" s="4" t="n"/>
       <c r="AQ27" s="4" t="n"/>
       <c r="AR27" s="4" t="n"/>
+      <c r="AS27" s="4" t="n"/>
+      <c r="AT27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
@@ -39163,6 +39233,8 @@
       <c r="AP28" s="4" t="n"/>
       <c r="AQ28" s="4" t="n"/>
       <c r="AR28" s="4" t="n"/>
+      <c r="AS28" s="4" t="n"/>
+      <c r="AT28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n"/>
@@ -39225,6 +39297,8 @@
       <c r="AP29" s="4" t="n"/>
       <c r="AQ29" s="4" t="n"/>
       <c r="AR29" s="4" t="n"/>
+      <c r="AS29" s="4" t="n"/>
+      <c r="AT29" s="4" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -39280,7 +39354,9 @@
       <c r="AG30" s="4" t="n"/>
       <c r="AH30" s="4" t="n"/>
       <c r="AI30" s="4" t="n"/>
-      <c r="AJ30" s="4" t="n"/>
+      <c r="AJ30" s="4" t="n">
+        <v>23.52</v>
+      </c>
       <c r="AK30" s="4" t="n"/>
       <c r="AL30" s="4" t="n"/>
       <c r="AM30" s="4" t="n"/>
@@ -39289,6 +39365,8 @@
       <c r="AP30" s="4" t="n"/>
       <c r="AQ30" s="4" t="n"/>
       <c r="AR30" s="4" t="n"/>
+      <c r="AS30" s="4" t="n"/>
+      <c r="AT30" s="4" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n"/>
@@ -39353,6 +39431,8 @@
       <c r="AP31" s="4" t="n"/>
       <c r="AQ31" s="4" t="n"/>
       <c r="AR31" s="4" t="n"/>
+      <c r="AS31" s="4" t="n"/>
+      <c r="AT31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n"/>
@@ -39410,10 +39490,10 @@
       <c r="AG32" s="4" t="n"/>
       <c r="AH32" s="4" t="n"/>
       <c r="AI32" s="4" t="n"/>
-      <c r="AJ32" s="4" t="n">
+      <c r="AJ32" s="4" t="n"/>
+      <c r="AK32" s="4" t="n">
         <v>29.05</v>
       </c>
-      <c r="AK32" s="4" t="n"/>
       <c r="AL32" s="4" t="n"/>
       <c r="AM32" s="4" t="n"/>
       <c r="AN32" s="4" t="n"/>
@@ -39421,6 +39501,8 @@
       <c r="AP32" s="4" t="n"/>
       <c r="AQ32" s="4" t="n"/>
       <c r="AR32" s="4" t="n"/>
+      <c r="AS32" s="4" t="n"/>
+      <c r="AT32" s="4" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -39480,13 +39562,15 @@
       <c r="AK33" s="4" t="n"/>
       <c r="AL33" s="4" t="n"/>
       <c r="AM33" s="4" t="n"/>
-      <c r="AN33" s="4" t="n">
+      <c r="AN33" s="4" t="n"/>
+      <c r="AO33" s="4" t="n">
         <v>21.09</v>
       </c>
-      <c r="AO33" s="4" t="n"/>
       <c r="AP33" s="4" t="n"/>
       <c r="AQ33" s="4" t="n"/>
       <c r="AR33" s="4" t="n"/>
+      <c r="AS33" s="4" t="n"/>
+      <c r="AT33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n"/>
@@ -39547,6 +39631,8 @@
       <c r="AP34" s="4" t="n"/>
       <c r="AQ34" s="4" t="n"/>
       <c r="AR34" s="4" t="n"/>
+      <c r="AS34" s="4" t="n"/>
+      <c r="AT34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n"/>
@@ -39607,6 +39693,8 @@
       <c r="AP35" s="4" t="n"/>
       <c r="AQ35" s="4" t="n"/>
       <c r="AR35" s="4" t="n"/>
+      <c r="AS35" s="4" t="n"/>
+      <c r="AT35" s="4" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n"/>
@@ -39665,6 +39753,8 @@
       <c r="AP36" s="4" t="n"/>
       <c r="AQ36" s="4" t="n"/>
       <c r="AR36" s="4" t="n"/>
+      <c r="AS36" s="4" t="n"/>
+      <c r="AT36" s="4" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -39729,6 +39819,8 @@
       <c r="AP37" s="4" t="n"/>
       <c r="AQ37" s="4" t="n"/>
       <c r="AR37" s="4" t="n"/>
+      <c r="AS37" s="4" t="n"/>
+      <c r="AT37" s="4" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n"/>
@@ -39797,6 +39889,8 @@
       <c r="AP38" s="4" t="n"/>
       <c r="AQ38" s="4" t="n"/>
       <c r="AR38" s="4" t="n"/>
+      <c r="AS38" s="4" t="n"/>
+      <c r="AT38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n"/>
@@ -39855,6 +39949,8 @@
       <c r="AP39" s="4" t="n"/>
       <c r="AQ39" s="4" t="n"/>
       <c r="AR39" s="4" t="n"/>
+      <c r="AS39" s="4" t="n"/>
+      <c r="AT39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n"/>
@@ -39917,6 +40013,8 @@
       <c r="AP40" s="4" t="n"/>
       <c r="AQ40" s="4" t="n"/>
       <c r="AR40" s="4" t="n"/>
+      <c r="AS40" s="4" t="n"/>
+      <c r="AT40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -39979,6 +40077,8 @@
       <c r="AP41" s="4" t="n"/>
       <c r="AQ41" s="4" t="n"/>
       <c r="AR41" s="4" t="n"/>
+      <c r="AS41" s="4" t="n"/>
+      <c r="AT41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n"/>
@@ -40043,6 +40143,8 @@
       <c r="AP42" s="4" t="n"/>
       <c r="AQ42" s="4" t="n"/>
       <c r="AR42" s="4" t="n"/>
+      <c r="AS42" s="4" t="n"/>
+      <c r="AT42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n"/>
@@ -40103,6 +40205,8 @@
       <c r="AP43" s="4" t="n"/>
       <c r="AQ43" s="4" t="n"/>
       <c r="AR43" s="4" t="n"/>
+      <c r="AS43" s="4" t="n"/>
+      <c r="AT43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n"/>
@@ -40164,15 +40268,17 @@
       <c r="AI44" s="4" t="n"/>
       <c r="AJ44" s="4" t="n"/>
       <c r="AK44" s="4" t="n"/>
-      <c r="AL44" s="4" t="n">
+      <c r="AL44" s="4" t="n"/>
+      <c r="AM44" s="4" t="n">
         <v>22.65</v>
       </c>
-      <c r="AM44" s="4" t="n"/>
       <c r="AN44" s="4" t="n"/>
       <c r="AO44" s="4" t="n"/>
       <c r="AP44" s="4" t="n"/>
       <c r="AQ44" s="4" t="n"/>
       <c r="AR44" s="4" t="n"/>
+      <c r="AS44" s="4" t="n"/>
+      <c r="AT44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -40233,6 +40339,8 @@
       <c r="AP45" s="4" t="n"/>
       <c r="AQ45" s="4" t="n"/>
       <c r="AR45" s="4" t="n"/>
+      <c r="AS45" s="4" t="n"/>
+      <c r="AT45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n"/>
@@ -40293,6 +40401,8 @@
       <c r="AP46" s="4" t="n"/>
       <c r="AQ46" s="4" t="n"/>
       <c r="AR46" s="4" t="n"/>
+      <c r="AS46" s="4" t="n"/>
+      <c r="AT46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n"/>
@@ -40347,6 +40457,8 @@
       <c r="AP47" s="4" t="n"/>
       <c r="AQ47" s="4" t="n"/>
       <c r="AR47" s="4" t="n"/>
+      <c r="AS47" s="4" t="n"/>
+      <c r="AT47" s="4" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n"/>
@@ -40409,6 +40521,8 @@
       <c r="AP48" s="4" t="n"/>
       <c r="AQ48" s="4" t="n"/>
       <c r="AR48" s="4" t="n"/>
+      <c r="AS48" s="4" t="n"/>
+      <c r="AT48" s="4" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -40471,6 +40585,8 @@
       <c r="AP49" s="4" t="n"/>
       <c r="AQ49" s="4" t="n"/>
       <c r="AR49" s="4" t="n"/>
+      <c r="AS49" s="4" t="n"/>
+      <c r="AT49" s="4" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="n"/>
@@ -40526,11 +40642,13 @@
       <c r="AM50" s="4" t="n"/>
       <c r="AN50" s="4" t="n"/>
       <c r="AO50" s="4" t="n"/>
-      <c r="AP50" s="4" t="n">
+      <c r="AP50" s="4" t="n"/>
+      <c r="AQ50" s="4" t="n">
         <v>26.89</v>
       </c>
-      <c r="AQ50" s="4" t="n"/>
       <c r="AR50" s="4" t="n"/>
+      <c r="AS50" s="4" t="n"/>
+      <c r="AT50" s="4" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n"/>
@@ -40595,6 +40713,8 @@
       <c r="AP51" s="4" t="n"/>
       <c r="AQ51" s="4" t="n"/>
       <c r="AR51" s="4" t="n"/>
+      <c r="AS51" s="4" t="n"/>
+      <c r="AT51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n"/>
@@ -40655,6 +40775,8 @@
       <c r="AP52" s="4" t="n"/>
       <c r="AQ52" s="4" t="n"/>
       <c r="AR52" s="4" t="n"/>
+      <c r="AS52" s="4" t="n"/>
+      <c r="AT52" s="4" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -40715,6 +40837,8 @@
       <c r="AP53" s="4" t="n"/>
       <c r="AQ53" s="4" t="n"/>
       <c r="AR53" s="4" t="n"/>
+      <c r="AS53" s="4" t="n"/>
+      <c r="AT53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n"/>
@@ -40773,6 +40897,8 @@
       <c r="AP54" s="4" t="n"/>
       <c r="AQ54" s="4" t="n"/>
       <c r="AR54" s="4" t="n"/>
+      <c r="AS54" s="4" t="n"/>
+      <c r="AT54" s="4" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n"/>
@@ -40837,6 +40963,8 @@
       <c r="AP55" s="4" t="n"/>
       <c r="AQ55" s="4" t="n"/>
       <c r="AR55" s="4" t="n"/>
+      <c r="AS55" s="4" t="n"/>
+      <c r="AT55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n"/>
@@ -40895,6 +41023,8 @@
       <c r="AP56" s="4" t="n"/>
       <c r="AQ56" s="4" t="n"/>
       <c r="AR56" s="4" t="n"/>
+      <c r="AS56" s="4" t="n"/>
+      <c r="AT56" s="4" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -40961,6 +41091,8 @@
       <c r="AP57" s="4" t="n"/>
       <c r="AQ57" s="4" t="n"/>
       <c r="AR57" s="4" t="n"/>
+      <c r="AS57" s="4" t="n"/>
+      <c r="AT57" s="4" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="n"/>
@@ -41021,6 +41153,8 @@
       <c r="AP58" s="4" t="n"/>
       <c r="AQ58" s="4" t="n"/>
       <c r="AR58" s="4" t="n"/>
+      <c r="AS58" s="4" t="n"/>
+      <c r="AT58" s="4" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n"/>
@@ -41081,6 +41215,8 @@
       <c r="AP59" s="4" t="n"/>
       <c r="AQ59" s="4" t="n"/>
       <c r="AR59" s="4" t="n"/>
+      <c r="AS59" s="4" t="n"/>
+      <c r="AT59" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n"/>
@@ -41137,10 +41273,12 @@
       <c r="AN60" s="4" t="n"/>
       <c r="AO60" s="4" t="n"/>
       <c r="AP60" s="4" t="n"/>
-      <c r="AQ60" s="4" t="n">
+      <c r="AQ60" s="4" t="n"/>
+      <c r="AR60" s="4" t="n"/>
+      <c r="AS60" s="4" t="n">
         <v>38.65</v>
       </c>
-      <c r="AR60" s="4" t="n"/>
+      <c r="AT60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -41205,20 +41343,22 @@
       <c r="AH61" s="4" t="n"/>
       <c r="AI61" s="4" t="n"/>
       <c r="AJ61" s="4" t="n"/>
-      <c r="AK61" s="4" t="n">
+      <c r="AK61" s="4" t="n"/>
+      <c r="AL61" s="4" t="n">
         <v>21.74</v>
       </c>
-      <c r="AL61" s="4" t="n">
+      <c r="AM61" s="4" t="n">
         <v>22.3</v>
       </c>
-      <c r="AM61" s="4" t="n">
+      <c r="AN61" s="4" t="n">
         <v>21.92</v>
       </c>
-      <c r="AN61" s="4" t="n"/>
       <c r="AO61" s="4" t="n"/>
       <c r="AP61" s="4" t="n"/>
       <c r="AQ61" s="4" t="n"/>
       <c r="AR61" s="4" t="n"/>
+      <c r="AS61" s="4" t="n"/>
+      <c r="AT61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="n"/>
@@ -41281,6 +41421,8 @@
       <c r="AP62" s="4" t="n"/>
       <c r="AQ62" s="4" t="n"/>
       <c r="AR62" s="4" t="n"/>
+      <c r="AS62" s="4" t="n"/>
+      <c r="AT62" s="4" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n"/>
@@ -41339,6 +41481,8 @@
       <c r="AP63" s="4" t="n"/>
       <c r="AQ63" s="4" t="n"/>
       <c r="AR63" s="4" t="n"/>
+      <c r="AS63" s="4" t="n"/>
+      <c r="AT63" s="4" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n"/>
@@ -41401,6 +41545,8 @@
       <c r="AP64" s="4" t="n"/>
       <c r="AQ64" s="4" t="n"/>
       <c r="AR64" s="4" t="n"/>
+      <c r="AS64" s="4" t="n"/>
+      <c r="AT64" s="4" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -41461,6 +41607,8 @@
       <c r="AP65" s="4" t="n"/>
       <c r="AQ65" s="4" t="n"/>
       <c r="AR65" s="4" t="n"/>
+      <c r="AS65" s="4" t="n"/>
+      <c r="AT65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="n"/>
@@ -41517,6 +41665,8 @@
       <c r="AP66" s="4" t="n"/>
       <c r="AQ66" s="4" t="n"/>
       <c r="AR66" s="4" t="n"/>
+      <c r="AS66" s="4" t="n"/>
+      <c r="AT66" s="4" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n"/>
@@ -41579,6 +41729,8 @@
       <c r="AP67" s="4" t="n"/>
       <c r="AQ67" s="4" t="n"/>
       <c r="AR67" s="4" t="n"/>
+      <c r="AS67" s="4" t="n"/>
+      <c r="AT67" s="4" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n"/>
@@ -41635,6 +41787,8 @@
       <c r="AP68" s="4" t="n"/>
       <c r="AQ68" s="4" t="n"/>
       <c r="AR68" s="4" t="n"/>
+      <c r="AS68" s="4" t="n"/>
+      <c r="AT68" s="4" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -41701,6 +41855,8 @@
       <c r="AP69" s="4" t="n"/>
       <c r="AQ69" s="4" t="n"/>
       <c r="AR69" s="4" t="n"/>
+      <c r="AS69" s="4" t="n"/>
+      <c r="AT69" s="4" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="n"/>
@@ -41761,6 +41917,8 @@
       <c r="AP70" s="4" t="n"/>
       <c r="AQ70" s="4" t="n"/>
       <c r="AR70" s="4" t="n"/>
+      <c r="AS70" s="4" t="n"/>
+      <c r="AT70" s="4" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n"/>
@@ -41821,6 +41979,8 @@
       <c r="AP71" s="4" t="n"/>
       <c r="AQ71" s="4" t="n"/>
       <c r="AR71" s="4" t="n"/>
+      <c r="AS71" s="4" t="n"/>
+      <c r="AT71" s="4" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n"/>
@@ -41883,14 +42043,16 @@
       <c r="AJ72" s="4" t="n"/>
       <c r="AK72" s="4" t="n"/>
       <c r="AL72" s="4" t="n"/>
-      <c r="AM72" s="4" t="n">
+      <c r="AM72" s="4" t="n"/>
+      <c r="AN72" s="4" t="n">
         <v>26.15</v>
       </c>
-      <c r="AN72" s="4" t="n"/>
       <c r="AO72" s="4" t="n"/>
       <c r="AP72" s="4" t="n"/>
       <c r="AQ72" s="4" t="n"/>
       <c r="AR72" s="4" t="n"/>
+      <c r="AS72" s="4" t="n"/>
+      <c r="AT72" s="4" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -41953,6 +42115,8 @@
       <c r="AP73" s="4" t="n"/>
       <c r="AQ73" s="4" t="n"/>
       <c r="AR73" s="4" t="n"/>
+      <c r="AS73" s="4" t="n"/>
+      <c r="AT73" s="4" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="n"/>
@@ -42011,6 +42175,8 @@
       <c r="AP74" s="4" t="n"/>
       <c r="AQ74" s="4" t="n"/>
       <c r="AR74" s="4" t="n"/>
+      <c r="AS74" s="4" t="n"/>
+      <c r="AT74" s="4" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n"/>
@@ -42069,6 +42235,8 @@
       <c r="AP75" s="4" t="n"/>
       <c r="AQ75" s="4" t="n"/>
       <c r="AR75" s="4" t="n"/>
+      <c r="AS75" s="4" t="n"/>
+      <c r="AT75" s="4" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="n"/>
@@ -42125,6 +42293,8 @@
       <c r="AP76" s="4" t="n"/>
       <c r="AQ76" s="4" t="n"/>
       <c r="AR76" s="4" t="n"/>
+      <c r="AS76" s="4" t="n"/>
+      <c r="AT76" s="4" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -42187,6 +42357,8 @@
       <c r="AP77" s="4" t="n"/>
       <c r="AQ77" s="4" t="n"/>
       <c r="AR77" s="4" t="n"/>
+      <c r="AS77" s="4" t="n"/>
+      <c r="AT77" s="4" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="n"/>
@@ -42251,6 +42423,8 @@
       <c r="AP78" s="4" t="n"/>
       <c r="AQ78" s="4" t="n"/>
       <c r="AR78" s="4" t="n"/>
+      <c r="AS78" s="4" t="n"/>
+      <c r="AT78" s="4" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n"/>
@@ -42309,6 +42483,8 @@
       <c r="AP79" s="4" t="n"/>
       <c r="AQ79" s="4" t="n"/>
       <c r="AR79" s="4" t="n"/>
+      <c r="AS79" s="4" t="n"/>
+      <c r="AT79" s="4" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="n"/>
@@ -42363,6 +42539,8 @@
       <c r="AP80" s="4" t="n"/>
       <c r="AQ80" s="4" t="n"/>
       <c r="AR80" s="4" t="n"/>
+      <c r="AS80" s="4" t="n"/>
+      <c r="AT80" s="4" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
@@ -42423,6 +42601,8 @@
       <c r="AP81" s="4" t="n"/>
       <c r="AQ81" s="4" t="n"/>
       <c r="AR81" s="4" t="n"/>
+      <c r="AS81" s="4" t="n"/>
+      <c r="AT81" s="4" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="n"/>
@@ -42477,6 +42657,8 @@
       <c r="AP82" s="4" t="n"/>
       <c r="AQ82" s="4" t="n"/>
       <c r="AR82" s="4" t="n"/>
+      <c r="AS82" s="4" t="n"/>
+      <c r="AT82" s="4" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n"/>
@@ -42531,6 +42713,8 @@
       <c r="AP83" s="4" t="n"/>
       <c r="AQ83" s="4" t="n"/>
       <c r="AR83" s="4" t="n"/>
+      <c r="AS83" s="4" t="n"/>
+      <c r="AT83" s="4" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="n"/>
@@ -42591,9 +42775,11 @@
       <c r="AP84" s="4" t="n"/>
       <c r="AQ84" s="4" t="n"/>
       <c r="AR84" s="4" t="n"/>
+      <c r="AS84" s="4" t="n"/>
+      <c r="AT84" s="4" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR84"/>
+  <autoFilter ref="A1:AT84"/>
   <mergeCells count="21">
     <mergeCell ref="A61:A64"/>
     <mergeCell ref="A69:A72"/>
@@ -42967,32 +43153,32 @@
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
+          <t>cs★6</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
           <t>fe3★5</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>六子★6</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>英灵殿★6</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>ts900★6</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>风扇★5</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>cs★6</t>
         </is>
       </c>
       <c r="BI1" s="1" t="inlineStr">
@@ -45413,10 +45599,10 @@
       <c r="BB32" s="4" t="n">
         <v>30.1</v>
       </c>
-      <c r="BC32" s="4" t="n">
+      <c r="BC32" s="4" t="n"/>
+      <c r="BD32" s="4" t="n">
         <v>29.56</v>
       </c>
-      <c r="BD32" s="4" t="n"/>
       <c r="BE32" s="4" t="n"/>
       <c r="BF32" s="4" t="n"/>
       <c r="BG32" s="4" t="n"/>
@@ -45647,10 +45833,10 @@
       <c r="BB35" s="4" t="n"/>
       <c r="BC35" s="4" t="n"/>
       <c r="BD35" s="4" t="n"/>
-      <c r="BE35" s="4" t="n">
+      <c r="BE35" s="4" t="n"/>
+      <c r="BF35" s="4" t="n">
         <v>24.9</v>
       </c>
-      <c r="BF35" s="4" t="n"/>
       <c r="BG35" s="4" t="n"/>
       <c r="BH35" s="4" t="n"/>
       <c r="BI35" s="4" t="n"/>
@@ -46751,10 +46937,10 @@
       <c r="BB49" s="4" t="n"/>
       <c r="BC49" s="4" t="n"/>
       <c r="BD49" s="4" t="n"/>
-      <c r="BE49" s="4" t="n">
+      <c r="BE49" s="4" t="n"/>
+      <c r="BF49" s="4" t="n">
         <v>31.69</v>
       </c>
-      <c r="BF49" s="4" t="n"/>
       <c r="BG49" s="4" t="n"/>
       <c r="BH49" s="4" t="n"/>
       <c r="BI49" s="4" t="n"/>
@@ -46897,14 +47083,14 @@
       <c r="AZ51" s="4" t="n"/>
       <c r="BA51" s="4" t="n"/>
       <c r="BB51" s="4" t="n"/>
-      <c r="BC51" s="4" t="n"/>
+      <c r="BC51" s="4" t="n">
+        <v>24.95</v>
+      </c>
       <c r="BD51" s="4" t="n"/>
       <c r="BE51" s="4" t="n"/>
       <c r="BF51" s="4" t="n"/>
       <c r="BG51" s="4" t="n"/>
-      <c r="BH51" s="4" t="n">
-        <v>24.95</v>
-      </c>
+      <c r="BH51" s="4" t="n"/>
       <c r="BI51" s="4" t="n"/>
       <c r="BJ51" s="4" t="n"/>
     </row>
@@ -48519,10 +48705,10 @@
       <c r="AZ72" s="4" t="n"/>
       <c r="BA72" s="4" t="n"/>
       <c r="BB72" s="4" t="n"/>
-      <c r="BC72" s="4" t="n">
+      <c r="BC72" s="4" t="n"/>
+      <c r="BD72" s="4" t="n">
         <v>26.39</v>
       </c>
-      <c r="BD72" s="4" t="n"/>
       <c r="BE72" s="4" t="n"/>
       <c r="BF72" s="4" t="n"/>
       <c r="BG72" s="4" t="n"/>
@@ -49855,32 +50041,32 @@
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
+          <t>cs★6</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
           <t>fe3★5</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>六子★6</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>英灵殿★6</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>ts900★6</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>风扇★5</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>cs★6</t>
         </is>
       </c>
       <c r="BI1" s="1" t="inlineStr">
@@ -50776,12 +50962,12 @@
       <c r="BC9" s="4" t="n"/>
       <c r="BD9" s="4" t="n"/>
       <c r="BE9" s="4" t="n"/>
-      <c r="BF9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BG9" s="4" t="n"/>
+      <c r="BF9" s="4" t="n"/>
+      <c r="BG9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BH9" s="4" t="n"/>
       <c r="BI9" s="4" t="n"/>
       <c r="BJ9" s="4" t="inlineStr">
@@ -50898,12 +51084,12 @@
       <c r="BA10" s="4" t="n"/>
       <c r="BB10" s="4" t="n"/>
       <c r="BC10" s="4" t="n"/>
-      <c r="BD10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BE10" s="4" t="n"/>
+      <c r="BD10" s="4" t="n"/>
+      <c r="BE10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BF10" s="4" t="n"/>
       <c r="BG10" s="4" t="n"/>
       <c r="BH10" s="4" t="n"/>
@@ -51114,12 +51300,12 @@
       <c r="BA12" s="4" t="n"/>
       <c r="BB12" s="4" t="n"/>
       <c r="BC12" s="4" t="n"/>
-      <c r="BD12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BE12" s="4" t="n"/>
+      <c r="BD12" s="4" t="n"/>
+      <c r="BE12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BF12" s="4" t="n"/>
       <c r="BG12" s="4" t="n"/>
       <c r="BH12" s="4" t="n"/>
@@ -51818,12 +52004,12 @@
       <c r="BA18" s="4" t="n"/>
       <c r="BB18" s="4" t="n"/>
       <c r="BC18" s="4" t="n"/>
-      <c r="BD18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BE18" s="4" t="n"/>
+      <c r="BD18" s="4" t="n"/>
+      <c r="BE18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BF18" s="4" t="n"/>
       <c r="BG18" s="4" t="n"/>
       <c r="BH18" s="4" t="n"/>
@@ -53222,12 +53408,12 @@
       <c r="BA31" s="4" t="n"/>
       <c r="BB31" s="4" t="n"/>
       <c r="BC31" s="4" t="n"/>
-      <c r="BD31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BE31" s="4" t="n"/>
+      <c r="BD31" s="4" t="n"/>
+      <c r="BE31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BF31" s="4" t="n"/>
       <c r="BG31" s="4" t="n"/>
       <c r="BH31" s="4" t="n"/>
@@ -53337,18 +53523,18 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="BC32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BD32" s="4" t="n"/>
-      <c r="BE32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BF32" s="4" t="n"/>
+      <c r="BC32" s="4" t="n"/>
+      <c r="BD32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BE32" s="4" t="n"/>
+      <c r="BF32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BG32" s="4" t="n"/>
       <c r="BH32" s="4" t="n"/>
       <c r="BI32" s="4" t="n"/>
@@ -53449,12 +53635,12 @@
       <c r="AZ33" s="4" t="n"/>
       <c r="BA33" s="4" t="n"/>
       <c r="BB33" s="4" t="n"/>
-      <c r="BC33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BD33" s="4" t="n"/>
+      <c r="BC33" s="4" t="n"/>
+      <c r="BD33" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE33" s="4" t="n"/>
       <c r="BF33" s="4" t="n"/>
       <c r="BG33" s="4" t="n"/>
@@ -53673,18 +53859,18 @@
       <c r="AZ35" s="4" t="n"/>
       <c r="BA35" s="4" t="n"/>
       <c r="BB35" s="4" t="n"/>
-      <c r="BC35" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BD35" s="4" t="n"/>
-      <c r="BE35" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BF35" s="4" t="n"/>
+      <c r="BC35" s="4" t="n"/>
+      <c r="BD35" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BE35" s="4" t="n"/>
+      <c r="BF35" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BG35" s="4" t="n"/>
       <c r="BH35" s="4" t="n"/>
       <c r="BI35" s="4" t="n"/>
@@ -53915,12 +54101,12 @@
       <c r="BB37" s="4" t="n"/>
       <c r="BC37" s="4" t="n"/>
       <c r="BD37" s="4" t="n"/>
-      <c r="BE37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BF37" s="4" t="n"/>
+      <c r="BE37" s="4" t="n"/>
+      <c r="BF37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BG37" s="4" t="n"/>
       <c r="BH37" s="4" t="n"/>
       <c r="BI37" s="4" t="n"/>
@@ -54035,12 +54221,12 @@
       <c r="BB38" s="4" t="n"/>
       <c r="BC38" s="4" t="n"/>
       <c r="BD38" s="4" t="n"/>
-      <c r="BE38" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BF38" s="4" t="n"/>
+      <c r="BE38" s="4" t="n"/>
+      <c r="BF38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BG38" s="4" t="n"/>
       <c r="BH38" s="4" t="n"/>
       <c r="BI38" s="4" t="n"/>
@@ -54147,12 +54333,12 @@
       <c r="BB39" s="4" t="n"/>
       <c r="BC39" s="4" t="n"/>
       <c r="BD39" s="4" t="n"/>
-      <c r="BE39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BF39" s="4" t="n"/>
+      <c r="BE39" s="4" t="n"/>
+      <c r="BF39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BG39" s="4" t="n"/>
       <c r="BH39" s="4" t="n"/>
       <c r="BI39" s="4" t="n"/>
@@ -54275,12 +54461,12 @@
       <c r="BB40" s="4" t="n"/>
       <c r="BC40" s="4" t="n"/>
       <c r="BD40" s="4" t="n"/>
-      <c r="BE40" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BF40" s="4" t="n"/>
+      <c r="BE40" s="4" t="n"/>
+      <c r="BF40" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BG40" s="4" t="n"/>
       <c r="BH40" s="4" t="n"/>
       <c r="BI40" s="4" t="n"/>
@@ -54690,12 +54876,12 @@
       <c r="BA44" s="4" t="n"/>
       <c r="BB44" s="4" t="n"/>
       <c r="BC44" s="4" t="n"/>
-      <c r="BD44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BE44" s="4" t="n"/>
+      <c r="BD44" s="4" t="n"/>
+      <c r="BE44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BF44" s="4" t="n"/>
       <c r="BG44" s="4" t="n"/>
       <c r="BH44" s="4" t="n"/>
@@ -55057,12 +55243,12 @@
       <c r="AZ47" s="4" t="n"/>
       <c r="BA47" s="4" t="n"/>
       <c r="BB47" s="4" t="n"/>
-      <c r="BC47" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BD47" s="4" t="n"/>
+      <c r="BC47" s="4" t="n"/>
+      <c r="BD47" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE47" s="4" t="n"/>
       <c r="BF47" s="4" t="n"/>
       <c r="BG47" s="4" t="n"/>
@@ -55287,12 +55473,12 @@
       <c r="BB49" s="4" t="n"/>
       <c r="BC49" s="4" t="n"/>
       <c r="BD49" s="4" t="n"/>
-      <c r="BE49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BF49" s="4" t="n"/>
+      <c r="BE49" s="4" t="n"/>
+      <c r="BF49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BG49" s="4" t="n"/>
       <c r="BH49" s="4" t="n"/>
       <c r="BI49" s="4" t="n"/>
@@ -55385,20 +55571,20 @@
       <c r="AZ50" s="4" t="n"/>
       <c r="BA50" s="4" t="n"/>
       <c r="BB50" s="4" t="n"/>
-      <c r="BC50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BD50" s="4" t="n"/>
+      <c r="BC50" s="4" t="n"/>
+      <c r="BD50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE50" s="4" t="n"/>
       <c r="BF50" s="4" t="n"/>
-      <c r="BG50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH50" s="4" t="n"/>
+      <c r="BG50" s="4" t="n"/>
+      <c r="BH50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI50" s="4" t="n"/>
       <c r="BJ50" s="4" t="inlineStr">
         <is>
@@ -55505,16 +55691,16 @@
       <c r="AZ51" s="4" t="n"/>
       <c r="BA51" s="4" t="n"/>
       <c r="BB51" s="4" t="n"/>
-      <c r="BC51" s="4" t="n"/>
+      <c r="BC51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BD51" s="4" t="n"/>
       <c r="BE51" s="4" t="n"/>
       <c r="BF51" s="4" t="n"/>
       <c r="BG51" s="4" t="n"/>
-      <c r="BH51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH51" s="4" t="n"/>
       <c r="BI51" s="4" t="n"/>
       <c r="BJ51" s="4" t="n"/>
     </row>
@@ -55957,12 +56143,12 @@
       <c r="AZ55" s="4" t="n"/>
       <c r="BA55" s="4" t="n"/>
       <c r="BB55" s="4" t="n"/>
-      <c r="BC55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BD55" s="4" t="n"/>
+      <c r="BC55" s="4" t="n"/>
+      <c r="BD55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE55" s="4" t="n"/>
       <c r="BF55" s="4" t="n"/>
       <c r="BG55" s="4" t="n"/>
@@ -57325,17 +57511,17 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="BC67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BC67" s="4" t="n"/>
       <c r="BD67" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="BE67" s="4" t="n"/>
+      <c r="BE67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BF67" s="4" t="n"/>
       <c r="BG67" s="4" t="n"/>
       <c r="BH67" s="4" t="n"/>
@@ -57635,12 +57821,12 @@
       <c r="BB70" s="4" t="n"/>
       <c r="BC70" s="4" t="n"/>
       <c r="BD70" s="4" t="n"/>
-      <c r="BE70" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BF70" s="4" t="n"/>
+      <c r="BE70" s="4" t="n"/>
+      <c r="BF70" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BG70" s="4" t="n"/>
       <c r="BH70" s="4" t="n"/>
       <c r="BI70" s="4" t="n"/>
@@ -57837,12 +58023,12 @@
       <c r="AZ72" s="4" t="n"/>
       <c r="BA72" s="4" t="n"/>
       <c r="BB72" s="4" t="n"/>
-      <c r="BC72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BD72" s="4" t="n"/>
+      <c r="BC72" s="4" t="n"/>
+      <c r="BD72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE72" s="4" t="n"/>
       <c r="BF72" s="4" t="n"/>
       <c r="BG72" s="4" t="n"/>
@@ -58273,20 +58459,20 @@
       <c r="AZ76" s="4" t="n"/>
       <c r="BA76" s="4" t="n"/>
       <c r="BB76" s="4" t="n"/>
-      <c r="BC76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BD76" s="4" t="n"/>
+      <c r="BC76" s="4" t="n"/>
+      <c r="BD76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BE76" s="4" t="n"/>
       <c r="BF76" s="4" t="n"/>
-      <c r="BG76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BH76" s="4" t="n"/>
+      <c r="BG76" s="4" t="n"/>
+      <c r="BH76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BI76" s="4" t="inlineStr">
         <is>
           <t>✓</t>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -10705,7 +10705,7 @@
       </c>
       <c r="BY1" s="1" t="inlineStr">
         <is>
-          <t>保时捷919★6</t>
+          <t>919★6</t>
         </is>
       </c>
       <c r="BZ1" s="1" t="inlineStr">
@@ -20372,7 +20372,7 @@
       </c>
       <c r="BY1" s="1" t="inlineStr">
         <is>
-          <t>保时捷919★6</t>
+          <t>919★6</t>
         </is>
       </c>
       <c r="BZ1" s="1" t="inlineStr">
@@ -37462,7 +37462,7 @@
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>保时捷919</t>
+          <t>919</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -37362,27 +37362,27 @@
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
+          <t>att</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
           <t>塞纳</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>白龙</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>sf90</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>urs</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>att</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
@@ -37783,10 +37783,10 @@
       <c r="V6" s="4" t="n"/>
       <c r="W6" s="4" t="n"/>
       <c r="X6" s="4" t="n"/>
-      <c r="Y6" s="4" t="n">
+      <c r="Y6" s="4" t="n"/>
+      <c r="Z6" s="4" t="n">
         <v>18.2</v>
       </c>
-      <c r="Z6" s="4" t="n"/>
       <c r="AA6" s="4" t="n"/>
       <c r="AB6" s="4" t="n"/>
       <c r="AC6" s="4" t="n"/>
@@ -38176,15 +38176,15 @@
       <c r="U12" s="4" t="n"/>
       <c r="V12" s="4" t="n"/>
       <c r="W12" s="4" t="n"/>
-      <c r="X12" s="4" t="n"/>
-      <c r="Y12" s="4" t="n">
+      <c r="X12" s="4" t="n">
+        <v>21.85</v>
+      </c>
+      <c r="Y12" s="4" t="n"/>
+      <c r="Z12" s="4" t="n">
         <v>21.87</v>
       </c>
-      <c r="Z12" s="4" t="n"/>
       <c r="AA12" s="4" t="n"/>
-      <c r="AB12" s="4" t="n">
-        <v>21.85</v>
-      </c>
+      <c r="AB12" s="4" t="n"/>
       <c r="AC12" s="4" t="n"/>
       <c r="AD12" s="4" t="n"/>
       <c r="AE12" s="4" t="n"/>
@@ -38376,10 +38376,10 @@
       <c r="U15" s="4" t="n"/>
       <c r="V15" s="4" t="n"/>
       <c r="W15" s="4" t="n"/>
-      <c r="X15" s="4" t="n">
+      <c r="X15" s="4" t="n"/>
+      <c r="Y15" s="4" t="n">
         <v>29.7</v>
       </c>
-      <c r="Y15" s="4" t="n"/>
       <c r="Z15" s="4" t="n"/>
       <c r="AA15" s="4" t="n"/>
       <c r="AB15" s="4" t="n"/>
@@ -39018,13 +39018,13 @@
       <c r="U25" s="4" t="n"/>
       <c r="V25" s="4" t="n"/>
       <c r="W25" s="4" t="n"/>
-      <c r="X25" s="4" t="n"/>
+      <c r="X25" s="4" t="n">
+        <v>24.22</v>
+      </c>
       <c r="Y25" s="4" t="n"/>
       <c r="Z25" s="4" t="n"/>
       <c r="AA25" s="4" t="n"/>
-      <c r="AB25" s="4" t="n">
-        <v>24.22</v>
-      </c>
+      <c r="AB25" s="4" t="n"/>
       <c r="AC25" s="4" t="n"/>
       <c r="AD25" s="4" t="n"/>
       <c r="AE25" s="4" t="n"/>
@@ -39407,10 +39407,10 @@
         <v>19.29</v>
       </c>
       <c r="X31" s="4" t="n"/>
-      <c r="Y31" s="4" t="n">
+      <c r="Y31" s="4" t="n"/>
+      <c r="Z31" s="4" t="n">
         <v>19.15</v>
       </c>
-      <c r="Z31" s="4" t="n"/>
       <c r="AA31" s="4" t="n"/>
       <c r="AB31" s="4" t="n"/>
       <c r="AC31" s="4" t="n"/>
@@ -39479,10 +39479,10 @@
       <c r="X32" s="4" t="n"/>
       <c r="Y32" s="4" t="n"/>
       <c r="Z32" s="4" t="n"/>
-      <c r="AA32" s="4" t="n">
+      <c r="AA32" s="4" t="n"/>
+      <c r="AB32" s="4" t="n">
         <v>28.79</v>
       </c>
-      <c r="AB32" s="4" t="n"/>
       <c r="AC32" s="4" t="n"/>
       <c r="AD32" s="4" t="n"/>
       <c r="AE32" s="4" t="n"/>
@@ -39546,10 +39546,10 @@
       </c>
       <c r="X33" s="4" t="n"/>
       <c r="Y33" s="4" t="n"/>
-      <c r="Z33" s="4" t="n">
+      <c r="Z33" s="4" t="n"/>
+      <c r="AA33" s="4" t="n">
         <v>20.23</v>
       </c>
-      <c r="AA33" s="4" t="n"/>
       <c r="AB33" s="4" t="n"/>
       <c r="AC33" s="4" t="n"/>
       <c r="AD33" s="4" t="n"/>
@@ -39668,14 +39668,14 @@
       <c r="U35" s="4" t="n"/>
       <c r="V35" s="4" t="n"/>
       <c r="W35" s="4" t="n"/>
-      <c r="X35" s="4" t="n">
+      <c r="X35" s="4" t="n"/>
+      <c r="Y35" s="4" t="n">
         <v>23.99</v>
       </c>
-      <c r="Y35" s="4" t="n"/>
-      <c r="Z35" s="4" t="n">
+      <c r="Z35" s="4" t="n"/>
+      <c r="AA35" s="4" t="n">
         <v>23.45</v>
       </c>
-      <c r="AA35" s="4" t="n"/>
       <c r="AB35" s="4" t="n"/>
       <c r="AC35" s="4" t="n"/>
       <c r="AD35" s="4" t="n"/>
@@ -39799,10 +39799,10 @@
       <c r="X37" s="4" t="n"/>
       <c r="Y37" s="4" t="n"/>
       <c r="Z37" s="4" t="n"/>
-      <c r="AA37" s="4" t="n">
+      <c r="AA37" s="4" t="n"/>
+      <c r="AB37" s="4" t="n">
         <v>23.11</v>
       </c>
-      <c r="AB37" s="4" t="n"/>
       <c r="AC37" s="4" t="n"/>
       <c r="AD37" s="4" t="n"/>
       <c r="AE37" s="4" t="n"/>
@@ -39990,10 +39990,10 @@
       <c r="U40" s="4" t="n"/>
       <c r="V40" s="4" t="n"/>
       <c r="W40" s="4" t="n"/>
-      <c r="X40" s="4" t="n">
+      <c r="X40" s="4" t="n"/>
+      <c r="Y40" s="4" t="n">
         <v>35.3</v>
       </c>
-      <c r="Y40" s="4" t="n"/>
       <c r="Z40" s="4" t="n"/>
       <c r="AA40" s="4" t="n"/>
       <c r="AB40" s="4" t="n"/>
@@ -40247,13 +40247,13 @@
       <c r="V44" s="4" t="n"/>
       <c r="W44" s="4" t="n"/>
       <c r="X44" s="4" t="n"/>
-      <c r="Y44" s="4" t="n">
+      <c r="Y44" s="4" t="n"/>
+      <c r="Z44" s="4" t="n">
         <v>22.5</v>
       </c>
-      <c r="Z44" s="4" t="n">
+      <c r="AA44" s="4" t="n">
         <v>22.7</v>
       </c>
-      <c r="AA44" s="4" t="n"/>
       <c r="AB44" s="4" t="n"/>
       <c r="AC44" s="4" t="n"/>
       <c r="AD44" s="4" t="n">
@@ -40437,10 +40437,10 @@
       <c r="X47" s="4" t="n"/>
       <c r="Y47" s="4" t="n"/>
       <c r="Z47" s="4" t="n"/>
-      <c r="AA47" s="4" t="n">
+      <c r="AA47" s="4" t="n"/>
+      <c r="AB47" s="4" t="n">
         <v>42.29</v>
       </c>
-      <c r="AB47" s="4" t="n"/>
       <c r="AC47" s="4" t="n"/>
       <c r="AD47" s="4" t="n"/>
       <c r="AE47" s="4" t="n"/>
@@ -40562,10 +40562,10 @@
       <c r="U49" s="4" t="n"/>
       <c r="V49" s="4" t="n"/>
       <c r="W49" s="4" t="n"/>
-      <c r="X49" s="4" t="n">
+      <c r="X49" s="4" t="n"/>
+      <c r="Y49" s="4" t="n">
         <v>30.82</v>
       </c>
-      <c r="Y49" s="4" t="n"/>
       <c r="Z49" s="4" t="n"/>
       <c r="AA49" s="4" t="n"/>
       <c r="AB49" s="4" t="n"/>
@@ -40690,13 +40690,13 @@
       <c r="U51" s="4" t="n"/>
       <c r="V51" s="4" t="n"/>
       <c r="W51" s="4" t="n"/>
-      <c r="X51" s="4" t="n"/>
+      <c r="X51" s="4" t="n">
+        <v>23.99</v>
+      </c>
       <c r="Y51" s="4" t="n"/>
       <c r="Z51" s="4" t="n"/>
       <c r="AA51" s="4" t="n"/>
-      <c r="AB51" s="4" t="n">
-        <v>23.99</v>
-      </c>
+      <c r="AB51" s="4" t="n"/>
       <c r="AC51" s="4" t="n"/>
       <c r="AD51" s="4" t="n"/>
       <c r="AE51" s="4" t="n"/>
@@ -40752,10 +40752,10 @@
       <c r="U52" s="4" t="n"/>
       <c r="V52" s="4" t="n"/>
       <c r="W52" s="4" t="n"/>
-      <c r="X52" s="4" t="n">
+      <c r="X52" s="4" t="n"/>
+      <c r="Y52" s="4" t="n">
         <v>34.29</v>
       </c>
-      <c r="Y52" s="4" t="n"/>
       <c r="Z52" s="4" t="n"/>
       <c r="AA52" s="4" t="n"/>
       <c r="AB52" s="4" t="n"/>
@@ -40938,10 +40938,10 @@
       <c r="U55" s="4" t="n"/>
       <c r="V55" s="4" t="n"/>
       <c r="W55" s="4" t="n"/>
-      <c r="X55" s="4" t="n">
+      <c r="X55" s="4" t="n"/>
+      <c r="Y55" s="4" t="n">
         <v>33.45</v>
       </c>
-      <c r="Y55" s="4" t="n"/>
       <c r="Z55" s="4" t="n"/>
       <c r="AA55" s="4" t="n"/>
       <c r="AB55" s="4" t="n"/>
@@ -41326,10 +41326,10 @@
       <c r="W61" s="4" t="n"/>
       <c r="X61" s="4" t="n"/>
       <c r="Y61" s="4" t="n"/>
-      <c r="Z61" s="4" t="n">
+      <c r="Z61" s="4" t="n"/>
+      <c r="AA61" s="4" t="n">
         <v>22.15</v>
       </c>
-      <c r="AA61" s="4" t="n"/>
       <c r="AB61" s="4" t="n"/>
       <c r="AC61" s="4" t="n">
         <v>22.4</v>
@@ -41705,10 +41705,10 @@
       <c r="V67" s="4" t="n"/>
       <c r="W67" s="4" t="n"/>
       <c r="X67" s="4" t="n"/>
-      <c r="Y67" s="4" t="n">
+      <c r="Y67" s="4" t="n"/>
+      <c r="Z67" s="4" t="n">
         <v>18.2</v>
       </c>
-      <c r="Z67" s="4" t="n"/>
       <c r="AA67" s="4" t="n"/>
       <c r="AB67" s="4" t="n"/>
       <c r="AC67" s="4" t="n"/>
@@ -41835,10 +41835,10 @@
       <c r="X69" s="4" t="n"/>
       <c r="Y69" s="4" t="n"/>
       <c r="Z69" s="4" t="n"/>
-      <c r="AA69" s="4" t="n">
+      <c r="AA69" s="4" t="n"/>
+      <c r="AB69" s="4" t="n">
         <v>34.49</v>
       </c>
-      <c r="AB69" s="4" t="n"/>
       <c r="AC69" s="4" t="n"/>
       <c r="AD69" s="4" t="n"/>
       <c r="AE69" s="4" t="n"/>
@@ -42024,13 +42024,13 @@
       <c r="W72" s="4" t="n"/>
       <c r="X72" s="4" t="n"/>
       <c r="Y72" s="4" t="n"/>
-      <c r="Z72" s="4" t="n">
+      <c r="Z72" s="4" t="n"/>
+      <c r="AA72" s="4" t="n">
         <v>26.25</v>
       </c>
-      <c r="AA72" s="4" t="n">
+      <c r="AB72" s="4" t="n">
         <v>25.81</v>
       </c>
-      <c r="AB72" s="4" t="n"/>
       <c r="AC72" s="4" t="n"/>
       <c r="AD72" s="4" t="n"/>
       <c r="AE72" s="4" t="n">
@@ -43093,32 +43093,32 @@
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
+          <t>att★2</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>att★6</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
           <t>塞纳★6</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>白龙★6</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>sf90★6</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>urs★6</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>att★2</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>att★6</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
@@ -44024,13 +44024,13 @@
       <c r="AO12" s="4" t="n"/>
       <c r="AP12" s="4" t="n"/>
       <c r="AQ12" s="4" t="n"/>
-      <c r="AR12" s="4" t="n"/>
+      <c r="AR12" s="4" t="n">
+        <v>22.19</v>
+      </c>
       <c r="AS12" s="4" t="n"/>
       <c r="AT12" s="4" t="n"/>
       <c r="AU12" s="4" t="n"/>
-      <c r="AV12" s="4" t="n">
-        <v>22.19</v>
-      </c>
+      <c r="AV12" s="4" t="n"/>
       <c r="AW12" s="4" t="n"/>
       <c r="AX12" s="4" t="n"/>
       <c r="AY12" s="4" t="n"/>
@@ -44265,11 +44265,11 @@
       <c r="AN15" s="4" t="n"/>
       <c r="AO15" s="4" t="n"/>
       <c r="AP15" s="4" t="n"/>
-      <c r="AQ15" s="4" t="n">
+      <c r="AQ15" s="4" t="n"/>
+      <c r="AR15" s="4" t="n"/>
+      <c r="AS15" s="4" t="n">
         <v>29.95</v>
       </c>
-      <c r="AR15" s="4" t="n"/>
-      <c r="AS15" s="4" t="n"/>
       <c r="AT15" s="4" t="n"/>
       <c r="AU15" s="4" t="n"/>
       <c r="AV15" s="4" t="n"/>
@@ -45040,13 +45040,13 @@
       <c r="AO25" s="4" t="n"/>
       <c r="AP25" s="4" t="n"/>
       <c r="AQ25" s="4" t="n"/>
-      <c r="AR25" s="4" t="n"/>
+      <c r="AR25" s="4" t="n">
+        <v>24.8</v>
+      </c>
       <c r="AS25" s="4" t="n"/>
       <c r="AT25" s="4" t="n"/>
       <c r="AU25" s="4" t="n"/>
-      <c r="AV25" s="4" t="n">
-        <v>24.8</v>
-      </c>
+      <c r="AV25" s="4" t="n"/>
       <c r="AW25" s="4" t="n"/>
       <c r="AX25" s="4" t="n"/>
       <c r="AY25" s="4" t="n"/>
@@ -45504,11 +45504,11 @@
       <c r="AO31" s="4" t="n"/>
       <c r="AP31" s="4" t="n"/>
       <c r="AQ31" s="4" t="n"/>
-      <c r="AR31" s="4" t="n">
+      <c r="AR31" s="4" t="n"/>
+      <c r="AS31" s="4" t="n"/>
+      <c r="AT31" s="4" t="n">
         <v>19.2</v>
       </c>
-      <c r="AS31" s="4" t="n"/>
-      <c r="AT31" s="4" t="n"/>
       <c r="AU31" s="4" t="n"/>
       <c r="AV31" s="4" t="n"/>
       <c r="AW31" s="4" t="n"/>
@@ -45585,7 +45585,9 @@
       <c r="AN32" s="4" t="n"/>
       <c r="AO32" s="4" t="n"/>
       <c r="AP32" s="4" t="n"/>
-      <c r="AQ32" s="4" t="n"/>
+      <c r="AQ32" s="4" t="n">
+        <v>30.9</v>
+      </c>
       <c r="AR32" s="4" t="n"/>
       <c r="AS32" s="4" t="n"/>
       <c r="AT32" s="4" t="n"/>
@@ -45743,13 +45745,13 @@
       <c r="AN34" s="4" t="n"/>
       <c r="AO34" s="4" t="n"/>
       <c r="AP34" s="4" t="n"/>
-      <c r="AQ34" s="4" t="n"/>
+      <c r="AQ34" s="4" t="n">
+        <v>35.7</v>
+      </c>
       <c r="AR34" s="4" t="n"/>
       <c r="AS34" s="4" t="n"/>
       <c r="AT34" s="4" t="n"/>
-      <c r="AU34" s="4" t="n">
-        <v>35.7</v>
-      </c>
+      <c r="AU34" s="4" t="n"/>
       <c r="AV34" s="4" t="n"/>
       <c r="AW34" s="4" t="n"/>
       <c r="AX34" s="4" t="n"/>
@@ -45819,11 +45821,11 @@
       <c r="AP35" s="4" t="n"/>
       <c r="AQ35" s="4" t="n"/>
       <c r="AR35" s="4" t="n"/>
-      <c r="AS35" s="4" t="n">
+      <c r="AS35" s="4" t="n"/>
+      <c r="AT35" s="4" t="n"/>
+      <c r="AU35" s="4" t="n">
         <v>23.74</v>
       </c>
-      <c r="AT35" s="4" t="n"/>
-      <c r="AU35" s="4" t="n"/>
       <c r="AV35" s="4" t="n"/>
       <c r="AW35" s="4" t="n"/>
       <c r="AX35" s="4" t="n"/>
@@ -46215,11 +46217,11 @@
       <c r="AN40" s="4" t="n"/>
       <c r="AO40" s="4" t="n"/>
       <c r="AP40" s="4" t="n"/>
-      <c r="AQ40" s="4" t="n">
+      <c r="AQ40" s="4" t="n"/>
+      <c r="AR40" s="4" t="n"/>
+      <c r="AS40" s="4" t="n">
         <v>35.5</v>
       </c>
-      <c r="AR40" s="4" t="n"/>
-      <c r="AS40" s="4" t="n"/>
       <c r="AT40" s="4" t="n"/>
       <c r="AU40" s="4" t="n"/>
       <c r="AV40" s="4" t="n"/>
@@ -46765,13 +46767,13 @@
       <c r="AN47" s="4" t="n"/>
       <c r="AO47" s="4" t="n"/>
       <c r="AP47" s="4" t="n"/>
-      <c r="AQ47" s="4" t="n"/>
+      <c r="AQ47" s="4" t="n">
+        <v>45.1</v>
+      </c>
       <c r="AR47" s="4" t="n"/>
       <c r="AS47" s="4" t="n"/>
       <c r="AT47" s="4" t="n"/>
-      <c r="AU47" s="4" t="n">
-        <v>45.1</v>
-      </c>
+      <c r="AU47" s="4" t="n"/>
       <c r="AV47" s="4" t="n"/>
       <c r="AW47" s="4" t="n"/>
       <c r="AX47" s="4" t="n"/>
@@ -47157,11 +47159,11 @@
       <c r="AN52" s="4" t="n"/>
       <c r="AO52" s="4" t="n"/>
       <c r="AP52" s="4" t="n"/>
-      <c r="AQ52" s="4" t="n">
+      <c r="AQ52" s="4" t="n"/>
+      <c r="AR52" s="4" t="n"/>
+      <c r="AS52" s="4" t="n">
         <v>34.59</v>
       </c>
-      <c r="AR52" s="4" t="n"/>
-      <c r="AS52" s="4" t="n"/>
       <c r="AT52" s="4" t="n"/>
       <c r="AU52" s="4" t="n"/>
       <c r="AV52" s="4" t="n"/>
@@ -48205,7 +48207,9 @@
         <v>35.19</v>
       </c>
       <c r="F66" s="4" t="n"/>
-      <c r="G66" s="4" t="n"/>
+      <c r="G66" s="4" t="n">
+        <v>34.95</v>
+      </c>
       <c r="H66" s="4" t="n"/>
       <c r="I66" s="4" t="n"/>
       <c r="J66" s="4" t="n"/>
@@ -48399,7 +48403,9 @@
       <c r="AN68" s="4" t="n"/>
       <c r="AO68" s="4" t="n"/>
       <c r="AP68" s="4" t="n"/>
-      <c r="AQ68" s="4" t="n"/>
+      <c r="AQ68" s="4" t="n">
+        <v>30.13</v>
+      </c>
       <c r="AR68" s="4" t="n"/>
       <c r="AS68" s="4" t="n"/>
       <c r="AT68" s="4" t="n"/>
@@ -49981,32 +49987,32 @@
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
+          <t>att★2</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>att★6</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
           <t>塞纳★6</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>白龙★6</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>sf90★6</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>urs★6</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>att★2</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>att★6</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
@@ -50152,19 +50158,19 @@
       <c r="AO2" s="4" t="n"/>
       <c r="AP2" s="4" t="n"/>
       <c r="AQ2" s="4" t="n"/>
-      <c r="AR2" s="4" t="n"/>
-      <c r="AS2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AR2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS2" s="4" t="n"/>
       <c r="AT2" s="4" t="n"/>
-      <c r="AU2" s="4" t="n"/>
-      <c r="AV2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AV2" s="4" t="n"/>
       <c r="AW2" s="4" t="n"/>
       <c r="AX2" s="4" t="n"/>
       <c r="AY2" s="4" t="n"/>
@@ -50276,15 +50282,15 @@
         </is>
       </c>
       <c r="AQ3" s="4" t="n"/>
-      <c r="AR3" s="4" t="n"/>
+      <c r="AR3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS3" s="4" t="n"/>
       <c r="AT3" s="4" t="n"/>
       <c r="AU3" s="4" t="n"/>
-      <c r="AV3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV3" s="4" t="n"/>
       <c r="AW3" s="4" t="n"/>
       <c r="AX3" s="4" t="n"/>
       <c r="AY3" s="4" t="n"/>
@@ -50380,15 +50386,15 @@
         </is>
       </c>
       <c r="AQ4" s="4" t="n"/>
-      <c r="AR4" s="4" t="n"/>
+      <c r="AR4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS4" s="4" t="n"/>
       <c r="AT4" s="4" t="n"/>
       <c r="AU4" s="4" t="n"/>
-      <c r="AV4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV4" s="4" t="n"/>
       <c r="AW4" s="4" t="n"/>
       <c r="AX4" s="4" t="n"/>
       <c r="AY4" s="4" t="n"/>
@@ -50488,19 +50494,19 @@
       <c r="AO5" s="4" t="n"/>
       <c r="AP5" s="4" t="n"/>
       <c r="AQ5" s="4" t="n"/>
-      <c r="AR5" s="4" t="n"/>
-      <c r="AS5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AR5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS5" s="4" t="n"/>
       <c r="AT5" s="4" t="n"/>
-      <c r="AU5" s="4" t="n"/>
-      <c r="AV5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AV5" s="4" t="n"/>
       <c r="AW5" s="4" t="n"/>
       <c r="AX5" s="4" t="n"/>
       <c r="AY5" s="4" t="n"/>
@@ -50584,15 +50590,15 @@
       <c r="AO6" s="4" t="n"/>
       <c r="AP6" s="4" t="n"/>
       <c r="AQ6" s="4" t="n"/>
-      <c r="AR6" s="4" t="n"/>
+      <c r="AR6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS6" s="4" t="n"/>
       <c r="AT6" s="4" t="n"/>
       <c r="AU6" s="4" t="n"/>
-      <c r="AV6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV6" s="4" t="n"/>
       <c r="AW6" s="4" t="n"/>
       <c r="AX6" s="4" t="n"/>
       <c r="AY6" s="4" t="n"/>
@@ -50704,15 +50710,15 @@
         </is>
       </c>
       <c r="AQ7" s="4" t="n"/>
-      <c r="AR7" s="4" t="n"/>
+      <c r="AR7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS7" s="4" t="n"/>
       <c r="AT7" s="4" t="n"/>
       <c r="AU7" s="4" t="n"/>
-      <c r="AV7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV7" s="4" t="n"/>
       <c r="AW7" s="4" t="n"/>
       <c r="AX7" s="4" t="n"/>
       <c r="AY7" s="4" t="n"/>
@@ -50836,15 +50842,15 @@
         </is>
       </c>
       <c r="AQ8" s="4" t="n"/>
-      <c r="AR8" s="4" t="n"/>
+      <c r="AR8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS8" s="4" t="n"/>
       <c r="AT8" s="4" t="n"/>
       <c r="AU8" s="4" t="n"/>
-      <c r="AV8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV8" s="4" t="n"/>
       <c r="AW8" s="4" t="n"/>
       <c r="AX8" s="4" t="n"/>
       <c r="AY8" s="4" t="n"/>
@@ -50944,15 +50950,15 @@
       <c r="AO9" s="4" t="n"/>
       <c r="AP9" s="4" t="n"/>
       <c r="AQ9" s="4" t="n"/>
-      <c r="AR9" s="4" t="n"/>
+      <c r="AR9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS9" s="4" t="n"/>
       <c r="AT9" s="4" t="n"/>
       <c r="AU9" s="4" t="n"/>
-      <c r="AV9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV9" s="4" t="n"/>
       <c r="AW9" s="4" t="n"/>
       <c r="AX9" s="4" t="n"/>
       <c r="AY9" s="4" t="n"/>
@@ -51064,19 +51070,19 @@
       <c r="AO10" s="4" t="n"/>
       <c r="AP10" s="4" t="n"/>
       <c r="AQ10" s="4" t="n"/>
-      <c r="AR10" s="4" t="n"/>
-      <c r="AS10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AR10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS10" s="4" t="n"/>
       <c r="AT10" s="4" t="n"/>
-      <c r="AU10" s="4" t="n"/>
-      <c r="AV10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AV10" s="4" t="n"/>
       <c r="AW10" s="4" t="n"/>
       <c r="AX10" s="4" t="n"/>
       <c r="AY10" s="4" t="n"/>
@@ -51172,15 +51178,15 @@
       </c>
       <c r="AP11" s="4" t="n"/>
       <c r="AQ11" s="4" t="n"/>
-      <c r="AR11" s="4" t="n"/>
+      <c r="AR11" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS11" s="4" t="n"/>
       <c r="AT11" s="4" t="n"/>
       <c r="AU11" s="4" t="n"/>
-      <c r="AV11" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV11" s="4" t="n"/>
       <c r="AW11" s="4" t="n"/>
       <c r="AX11" s="4" t="n"/>
       <c r="AY11" s="4" t="n"/>
@@ -51284,15 +51290,15 @@
       <c r="AO12" s="4" t="n"/>
       <c r="AP12" s="4" t="n"/>
       <c r="AQ12" s="4" t="n"/>
-      <c r="AR12" s="4" t="n"/>
+      <c r="AR12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS12" s="4" t="n"/>
       <c r="AT12" s="4" t="n"/>
       <c r="AU12" s="4" t="n"/>
-      <c r="AV12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV12" s="4" t="n"/>
       <c r="AW12" s="4" t="n"/>
       <c r="AX12" s="4" t="n"/>
       <c r="AY12" s="4" t="n"/>
@@ -51392,15 +51398,15 @@
         </is>
       </c>
       <c r="AQ13" s="4" t="n"/>
-      <c r="AR13" s="4" t="n"/>
+      <c r="AR13" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS13" s="4" t="n"/>
       <c r="AT13" s="4" t="n"/>
       <c r="AU13" s="4" t="n"/>
-      <c r="AV13" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV13" s="4" t="n"/>
       <c r="AW13" s="4" t="n"/>
       <c r="AX13" s="4" t="n"/>
       <c r="AY13" s="4" t="n"/>
@@ -51516,15 +51522,15 @@
       <c r="AO14" s="4" t="n"/>
       <c r="AP14" s="4" t="n"/>
       <c r="AQ14" s="4" t="n"/>
-      <c r="AR14" s="4" t="n"/>
+      <c r="AR14" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS14" s="4" t="n"/>
       <c r="AT14" s="4" t="n"/>
       <c r="AU14" s="4" t="n"/>
-      <c r="AV14" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV14" s="4" t="n"/>
       <c r="AW14" s="4" t="n"/>
       <c r="AX14" s="4" t="n"/>
       <c r="AY14" s="4" t="n"/>
@@ -51635,24 +51641,24 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AQ15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR15" s="4" t="n"/>
+      <c r="AQ15" s="4" t="n"/>
+      <c r="AR15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS15" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
       <c r="AT15" s="4" t="n"/>
-      <c r="AU15" s="4" t="n"/>
-      <c r="AV15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AV15" s="4" t="n"/>
       <c r="AW15" s="4" t="n"/>
       <c r="AX15" s="4" t="n"/>
       <c r="AY15" s="4" t="n"/>
@@ -51760,15 +51766,15 @@
       </c>
       <c r="AP16" s="4" t="n"/>
       <c r="AQ16" s="4" t="n"/>
-      <c r="AR16" s="4" t="n"/>
+      <c r="AR16" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS16" s="4" t="n"/>
       <c r="AT16" s="4" t="n"/>
       <c r="AU16" s="4" t="n"/>
-      <c r="AV16" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV16" s="4" t="n"/>
       <c r="AW16" s="4" t="n"/>
       <c r="AX16" s="4" t="n"/>
       <c r="AY16" s="4" t="n"/>
@@ -51872,19 +51878,19 @@
       <c r="AO17" s="4" t="n"/>
       <c r="AP17" s="4" t="n"/>
       <c r="AQ17" s="4" t="n"/>
-      <c r="AR17" s="4" t="n"/>
-      <c r="AS17" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AR17" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS17" s="4" t="n"/>
       <c r="AT17" s="4" t="n"/>
-      <c r="AU17" s="4" t="n"/>
-      <c r="AV17" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU17" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AV17" s="4" t="n"/>
       <c r="AW17" s="4" t="n"/>
       <c r="AX17" s="4" t="n"/>
       <c r="AY17" s="4" t="n"/>
@@ -51988,15 +51994,15 @@
       <c r="AO18" s="4" t="n"/>
       <c r="AP18" s="4" t="n"/>
       <c r="AQ18" s="4" t="n"/>
-      <c r="AR18" s="4" t="n"/>
+      <c r="AR18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS18" s="4" t="n"/>
       <c r="AT18" s="4" t="n"/>
       <c r="AU18" s="4" t="n"/>
-      <c r="AV18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV18" s="4" t="n"/>
       <c r="AW18" s="4" t="n"/>
       <c r="AX18" s="4" t="n"/>
       <c r="AY18" s="4" t="n"/>
@@ -52099,24 +52105,24 @@
       <c r="AN19" s="4" t="n"/>
       <c r="AO19" s="4" t="n"/>
       <c r="AP19" s="4" t="n"/>
-      <c r="AQ19" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR19" s="4" t="n"/>
+      <c r="AQ19" s="4" t="n"/>
+      <c r="AR19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS19" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
       <c r="AT19" s="4" t="n"/>
-      <c r="AU19" s="4" t="n"/>
-      <c r="AV19" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AV19" s="4" t="n"/>
       <c r="AW19" s="4" t="n"/>
       <c r="AX19" s="4" t="n"/>
       <c r="AY19" s="4" t="n"/>
@@ -52203,24 +52209,24 @@
       <c r="AN20" s="4" t="n"/>
       <c r="AO20" s="4" t="n"/>
       <c r="AP20" s="4" t="n"/>
-      <c r="AQ20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR20" s="4" t="n"/>
+      <c r="AQ20" s="4" t="n"/>
+      <c r="AR20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS20" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
       <c r="AT20" s="4" t="n"/>
-      <c r="AU20" s="4" t="n"/>
-      <c r="AV20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AV20" s="4" t="n"/>
       <c r="AW20" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -52320,15 +52326,15 @@
         </is>
       </c>
       <c r="AQ21" s="4" t="n"/>
-      <c r="AR21" s="4" t="n"/>
+      <c r="AR21" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS21" s="4" t="n"/>
       <c r="AT21" s="4" t="n"/>
       <c r="AU21" s="4" t="n"/>
-      <c r="AV21" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV21" s="4" t="n"/>
       <c r="AW21" s="4" t="n"/>
       <c r="AX21" s="4" t="n"/>
       <c r="AY21" s="4" t="n"/>
@@ -52428,15 +52434,15 @@
       <c r="AO22" s="4" t="n"/>
       <c r="AP22" s="4" t="n"/>
       <c r="AQ22" s="4" t="n"/>
-      <c r="AR22" s="4" t="n"/>
+      <c r="AR22" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS22" s="4" t="n"/>
       <c r="AT22" s="4" t="n"/>
       <c r="AU22" s="4" t="n"/>
-      <c r="AV22" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV22" s="4" t="n"/>
       <c r="AW22" s="4" t="n"/>
       <c r="AX22" s="4" t="n"/>
       <c r="AY22" s="4" t="n"/>
@@ -52532,15 +52538,15 @@
       </c>
       <c r="AP23" s="4" t="n"/>
       <c r="AQ23" s="4" t="n"/>
-      <c r="AR23" s="4" t="n"/>
+      <c r="AR23" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS23" s="4" t="n"/>
       <c r="AT23" s="4" t="n"/>
       <c r="AU23" s="4" t="n"/>
-      <c r="AV23" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV23" s="4" t="n"/>
       <c r="AW23" s="4" t="n"/>
       <c r="AX23" s="4" t="n"/>
       <c r="AY23" s="4" t="n"/>
@@ -52644,15 +52650,15 @@
       <c r="AO24" s="4" t="n"/>
       <c r="AP24" s="4" t="n"/>
       <c r="AQ24" s="4" t="n"/>
-      <c r="AR24" s="4" t="n"/>
+      <c r="AR24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS24" s="4" t="n"/>
       <c r="AT24" s="4" t="n"/>
       <c r="AU24" s="4" t="n"/>
-      <c r="AV24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV24" s="4" t="n"/>
       <c r="AW24" s="4" t="n"/>
       <c r="AX24" s="4" t="n"/>
       <c r="AY24" s="4" t="n"/>
@@ -52740,15 +52746,15 @@
       <c r="AO25" s="4" t="n"/>
       <c r="AP25" s="4" t="n"/>
       <c r="AQ25" s="4" t="n"/>
-      <c r="AR25" s="4" t="n"/>
+      <c r="AR25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS25" s="4" t="n"/>
       <c r="AT25" s="4" t="n"/>
       <c r="AU25" s="4" t="n"/>
-      <c r="AV25" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV25" s="4" t="n"/>
       <c r="AW25" s="4" t="n"/>
       <c r="AX25" s="4" t="n"/>
       <c r="AY25" s="4" t="n"/>
@@ -52860,15 +52866,15 @@
       <c r="AO26" s="4" t="n"/>
       <c r="AP26" s="4" t="n"/>
       <c r="AQ26" s="4" t="n"/>
-      <c r="AR26" s="4" t="n"/>
+      <c r="AR26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS26" s="4" t="n"/>
       <c r="AT26" s="4" t="n"/>
       <c r="AU26" s="4" t="n"/>
-      <c r="AV26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV26" s="4" t="n"/>
       <c r="AW26" s="4" t="n"/>
       <c r="AX26" s="4" t="n"/>
       <c r="AY26" s="4" t="inlineStr">
@@ -52972,15 +52978,15 @@
         </is>
       </c>
       <c r="AQ27" s="4" t="n"/>
-      <c r="AR27" s="4" t="n"/>
+      <c r="AR27" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS27" s="4" t="n"/>
       <c r="AT27" s="4" t="n"/>
       <c r="AU27" s="4" t="n"/>
-      <c r="AV27" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV27" s="4" t="n"/>
       <c r="AW27" s="4" t="n"/>
       <c r="AX27" s="4" t="n"/>
       <c r="AY27" s="4" t="n"/>
@@ -53080,15 +53086,15 @@
       <c r="AO28" s="4" t="n"/>
       <c r="AP28" s="4" t="n"/>
       <c r="AQ28" s="4" t="n"/>
-      <c r="AR28" s="4" t="n"/>
+      <c r="AR28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS28" s="4" t="n"/>
       <c r="AT28" s="4" t="n"/>
       <c r="AU28" s="4" t="n"/>
-      <c r="AV28" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV28" s="4" t="n"/>
       <c r="AW28" s="4" t="n"/>
       <c r="AX28" s="4" t="n"/>
       <c r="AY28" s="4" t="n"/>
@@ -53176,15 +53182,15 @@
       </c>
       <c r="AP29" s="4" t="n"/>
       <c r="AQ29" s="4" t="n"/>
-      <c r="AR29" s="4" t="n"/>
+      <c r="AR29" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS29" s="4" t="n"/>
       <c r="AT29" s="4" t="n"/>
       <c r="AU29" s="4" t="n"/>
-      <c r="AV29" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV29" s="4" t="n"/>
       <c r="AW29" s="4" t="n"/>
       <c r="AX29" s="4" t="n"/>
       <c r="AY29" s="4" t="n"/>
@@ -53275,24 +53281,24 @@
       <c r="AN30" s="4" t="n"/>
       <c r="AO30" s="4" t="n"/>
       <c r="AP30" s="4" t="n"/>
-      <c r="AQ30" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR30" s="4" t="n"/>
+      <c r="AQ30" s="4" t="n"/>
+      <c r="AR30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS30" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
       <c r="AT30" s="4" t="n"/>
-      <c r="AU30" s="4" t="n"/>
-      <c r="AV30" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AV30" s="4" t="n"/>
       <c r="AW30" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -53389,18 +53395,18 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="AS31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AT31" s="4" t="n"/>
-      <c r="AU31" s="4" t="n"/>
-      <c r="AV31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AS31" s="4" t="n"/>
+      <c r="AT31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AU31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AV31" s="4" t="n"/>
       <c r="AW31" s="4" t="n"/>
       <c r="AX31" s="4" t="n"/>
       <c r="AY31" s="4" t="n"/>
@@ -53503,16 +53509,20 @@
       <c r="AN32" s="4" t="n"/>
       <c r="AO32" s="4" t="n"/>
       <c r="AP32" s="4" t="n"/>
-      <c r="AQ32" s="4" t="n"/>
-      <c r="AR32" s="4" t="n"/>
+      <c r="AQ32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AR32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS32" s="4" t="n"/>
       <c r="AT32" s="4" t="n"/>
       <c r="AU32" s="4" t="n"/>
-      <c r="AV32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV32" s="4" t="n"/>
       <c r="AW32" s="4" t="n"/>
       <c r="AX32" s="4" t="n"/>
       <c r="AY32" s="4" t="n"/>
@@ -53616,19 +53626,19 @@
       <c r="AO33" s="4" t="n"/>
       <c r="AP33" s="4" t="n"/>
       <c r="AQ33" s="4" t="n"/>
-      <c r="AR33" s="4" t="n"/>
-      <c r="AS33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AR33" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS33" s="4" t="n"/>
       <c r="AT33" s="4" t="n"/>
-      <c r="AU33" s="4" t="n"/>
-      <c r="AV33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU33" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AV33" s="4" t="n"/>
       <c r="AW33" s="4" t="n"/>
       <c r="AX33" s="4" t="n"/>
       <c r="AY33" s="4" t="n"/>
@@ -53739,20 +53749,20 @@
         </is>
       </c>
       <c r="AP34" s="4" t="n"/>
-      <c r="AQ34" s="4" t="n"/>
-      <c r="AR34" s="4" t="n"/>
+      <c r="AQ34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AR34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS34" s="4" t="n"/>
       <c r="AT34" s="4" t="n"/>
-      <c r="AU34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AV34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU34" s="4" t="n"/>
+      <c r="AV34" s="4" t="n"/>
       <c r="AW34" s="4" t="n"/>
       <c r="AX34" s="4" t="n"/>
       <c r="AY34" s="4" t="n"/>
@@ -53835,24 +53845,24 @@
       <c r="AN35" s="4" t="n"/>
       <c r="AO35" s="4" t="n"/>
       <c r="AP35" s="4" t="n"/>
-      <c r="AQ35" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR35" s="4" t="n"/>
+      <c r="AQ35" s="4" t="n"/>
+      <c r="AR35" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS35" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
       <c r="AT35" s="4" t="n"/>
-      <c r="AU35" s="4" t="n"/>
-      <c r="AV35" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU35" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AV35" s="4" t="n"/>
       <c r="AW35" s="4" t="n"/>
       <c r="AX35" s="4" t="n"/>
       <c r="AY35" s="4" t="n"/>
@@ -53964,15 +53974,15 @@
       <c r="AO36" s="4" t="n"/>
       <c r="AP36" s="4" t="n"/>
       <c r="AQ36" s="4" t="n"/>
-      <c r="AR36" s="4" t="n"/>
+      <c r="AR36" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS36" s="4" t="n"/>
       <c r="AT36" s="4" t="n"/>
       <c r="AU36" s="4" t="n"/>
-      <c r="AV36" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV36" s="4" t="n"/>
       <c r="AW36" s="4" t="n"/>
       <c r="AX36" s="4" t="n"/>
       <c r="AY36" s="4" t="n"/>
@@ -54080,19 +54090,19 @@
       <c r="AO37" s="4" t="n"/>
       <c r="AP37" s="4" t="n"/>
       <c r="AQ37" s="4" t="n"/>
-      <c r="AR37" s="4" t="n"/>
-      <c r="AS37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AR37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS37" s="4" t="n"/>
       <c r="AT37" s="4" t="n"/>
-      <c r="AU37" s="4" t="n"/>
-      <c r="AV37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AV37" s="4" t="n"/>
       <c r="AW37" s="4" t="n"/>
       <c r="AX37" s="4" t="n"/>
       <c r="AY37" s="4" t="n"/>
@@ -54204,15 +54214,15 @@
       <c r="AO38" s="4" t="n"/>
       <c r="AP38" s="4" t="n"/>
       <c r="AQ38" s="4" t="n"/>
-      <c r="AR38" s="4" t="n"/>
+      <c r="AR38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS38" s="4" t="n"/>
       <c r="AT38" s="4" t="n"/>
       <c r="AU38" s="4" t="n"/>
-      <c r="AV38" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV38" s="4" t="n"/>
       <c r="AW38" s="4" t="n"/>
       <c r="AX38" s="4" t="n"/>
       <c r="AY38" s="4" t="n"/>
@@ -54316,15 +54326,15 @@
       <c r="AO39" s="4" t="n"/>
       <c r="AP39" s="4" t="n"/>
       <c r="AQ39" s="4" t="n"/>
-      <c r="AR39" s="4" t="n"/>
+      <c r="AR39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS39" s="4" t="n"/>
       <c r="AT39" s="4" t="n"/>
       <c r="AU39" s="4" t="n"/>
-      <c r="AV39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV39" s="4" t="n"/>
       <c r="AW39" s="4" t="n"/>
       <c r="AX39" s="4" t="n"/>
       <c r="AY39" s="4" t="n"/>
@@ -54435,24 +54445,24 @@
       <c r="AN40" s="4" t="n"/>
       <c r="AO40" s="4" t="n"/>
       <c r="AP40" s="4" t="n"/>
-      <c r="AQ40" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR40" s="4" t="n"/>
+      <c r="AQ40" s="4" t="n"/>
+      <c r="AR40" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS40" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
       <c r="AT40" s="4" t="n"/>
-      <c r="AU40" s="4" t="n"/>
-      <c r="AV40" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU40" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AV40" s="4" t="n"/>
       <c r="AW40" s="4" t="n"/>
       <c r="AX40" s="4" t="n"/>
       <c r="AY40" s="4" t="n"/>
@@ -54548,15 +54558,15 @@
       <c r="AO41" s="4" t="n"/>
       <c r="AP41" s="4" t="n"/>
       <c r="AQ41" s="4" t="n"/>
-      <c r="AR41" s="4" t="n"/>
+      <c r="AR41" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS41" s="4" t="n"/>
       <c r="AT41" s="4" t="n"/>
       <c r="AU41" s="4" t="n"/>
-      <c r="AV41" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV41" s="4" t="n"/>
       <c r="AW41" s="4" t="n"/>
       <c r="AX41" s="4" t="n"/>
       <c r="AY41" s="4" t="n"/>
@@ -54660,15 +54670,15 @@
       <c r="AO42" s="4" t="n"/>
       <c r="AP42" s="4" t="n"/>
       <c r="AQ42" s="4" t="n"/>
-      <c r="AR42" s="4" t="n"/>
+      <c r="AR42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS42" s="4" t="n"/>
       <c r="AT42" s="4" t="n"/>
       <c r="AU42" s="4" t="n"/>
-      <c r="AV42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV42" s="4" t="n"/>
       <c r="AW42" s="4" t="n"/>
       <c r="AX42" s="4" t="n"/>
       <c r="AY42" s="4" t="n"/>
@@ -54764,15 +54774,15 @@
       <c r="AO43" s="4" t="n"/>
       <c r="AP43" s="4" t="n"/>
       <c r="AQ43" s="4" t="n"/>
-      <c r="AR43" s="4" t="n"/>
+      <c r="AR43" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS43" s="4" t="n"/>
       <c r="AT43" s="4" t="n"/>
       <c r="AU43" s="4" t="n"/>
-      <c r="AV43" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV43" s="4" t="n"/>
       <c r="AW43" s="4" t="n"/>
       <c r="AX43" s="4" t="n"/>
       <c r="AY43" s="4" t="n"/>
@@ -54855,20 +54865,20 @@
       <c r="AN44" s="4" t="n"/>
       <c r="AO44" s="4" t="n"/>
       <c r="AP44" s="4" t="n"/>
-      <c r="AQ44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR44" s="4" t="n"/>
-      <c r="AS44" s="4" t="n"/>
+      <c r="AQ44" s="4" t="n"/>
+      <c r="AR44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT44" s="4" t="n"/>
       <c r="AU44" s="4" t="n"/>
-      <c r="AV44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV44" s="4" t="n"/>
       <c r="AW44" s="4" t="n"/>
       <c r="AX44" s="4" t="n"/>
       <c r="AY44" s="4" t="n"/>
@@ -54988,15 +54998,15 @@
       </c>
       <c r="AP45" s="4" t="n"/>
       <c r="AQ45" s="4" t="n"/>
-      <c r="AR45" s="4" t="n"/>
+      <c r="AR45" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS45" s="4" t="n"/>
       <c r="AT45" s="4" t="n"/>
       <c r="AU45" s="4" t="n"/>
-      <c r="AV45" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV45" s="4" t="n"/>
       <c r="AW45" s="4" t="n"/>
       <c r="AX45" s="4" t="n"/>
       <c r="AY45" s="4" t="n"/>
@@ -55103,24 +55113,24 @@
         </is>
       </c>
       <c r="AP46" s="4" t="n"/>
-      <c r="AQ46" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR46" s="4" t="n"/>
+      <c r="AQ46" s="4" t="n"/>
+      <c r="AR46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS46" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
       <c r="AT46" s="4" t="n"/>
-      <c r="AU46" s="4" t="n"/>
-      <c r="AV46" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AV46" s="4" t="n"/>
       <c r="AW46" s="4" t="n"/>
       <c r="AX46" s="4" t="n"/>
       <c r="AY46" s="4" t="n"/>
@@ -55223,20 +55233,20 @@
         </is>
       </c>
       <c r="AP47" s="4" t="n"/>
-      <c r="AQ47" s="4" t="n"/>
-      <c r="AR47" s="4" t="n"/>
+      <c r="AQ47" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AR47" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS47" s="4" t="n"/>
       <c r="AT47" s="4" t="n"/>
-      <c r="AU47" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AV47" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU47" s="4" t="n"/>
+      <c r="AV47" s="4" t="n"/>
       <c r="AW47" s="4" t="n"/>
       <c r="AX47" s="4" t="n"/>
       <c r="AY47" s="4" t="n"/>
@@ -55352,13 +55362,13 @@
       </c>
       <c r="AP48" s="4" t="n"/>
       <c r="AQ48" s="4" t="n"/>
-      <c r="AR48" s="4" t="n"/>
+      <c r="AR48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS48" s="4" t="n"/>
-      <c r="AT48" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AT48" s="4" t="n"/>
       <c r="AU48" s="4" t="n"/>
       <c r="AV48" s="4" t="inlineStr">
         <is>
@@ -55447,24 +55457,24 @@
       <c r="AN49" s="4" t="n"/>
       <c r="AO49" s="4" t="n"/>
       <c r="AP49" s="4" t="n"/>
-      <c r="AQ49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR49" s="4" t="n"/>
+      <c r="AQ49" s="4" t="n"/>
+      <c r="AR49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS49" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
       <c r="AT49" s="4" t="n"/>
-      <c r="AU49" s="4" t="n"/>
-      <c r="AV49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AV49" s="4" t="n"/>
       <c r="AW49" s="4" t="n"/>
       <c r="AX49" s="4" t="n"/>
       <c r="AY49" s="4" t="n"/>
@@ -55548,19 +55558,19 @@
       <c r="AO50" s="4" t="n"/>
       <c r="AP50" s="4" t="n"/>
       <c r="AQ50" s="4" t="n"/>
-      <c r="AR50" s="4" t="n"/>
-      <c r="AS50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AR50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS50" s="4" t="n"/>
       <c r="AT50" s="4" t="n"/>
-      <c r="AU50" s="4" t="n"/>
-      <c r="AV50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AV50" s="4" t="n"/>
       <c r="AW50" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -55676,15 +55686,15 @@
       <c r="AO51" s="4" t="n"/>
       <c r="AP51" s="4" t="n"/>
       <c r="AQ51" s="4" t="n"/>
-      <c r="AR51" s="4" t="n"/>
+      <c r="AR51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS51" s="4" t="n"/>
       <c r="AT51" s="4" t="n"/>
       <c r="AU51" s="4" t="n"/>
-      <c r="AV51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV51" s="4" t="n"/>
       <c r="AW51" s="4" t="n"/>
       <c r="AX51" s="4" t="n"/>
       <c r="AY51" s="4" t="n"/>
@@ -55799,20 +55809,20 @@
         </is>
       </c>
       <c r="AP52" s="4" t="n"/>
-      <c r="AQ52" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR52" s="4" t="n"/>
-      <c r="AS52" s="4" t="n"/>
+      <c r="AQ52" s="4" t="n"/>
+      <c r="AR52" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS52" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT52" s="4" t="n"/>
       <c r="AU52" s="4" t="n"/>
-      <c r="AV52" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV52" s="4" t="n"/>
       <c r="AW52" s="4" t="n"/>
       <c r="AX52" s="4" t="n"/>
       <c r="AY52" s="4" t="n"/>
@@ -55912,15 +55922,15 @@
         </is>
       </c>
       <c r="AQ53" s="4" t="n"/>
-      <c r="AR53" s="4" t="n"/>
+      <c r="AR53" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS53" s="4" t="n"/>
       <c r="AT53" s="4" t="n"/>
       <c r="AU53" s="4" t="n"/>
-      <c r="AV53" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV53" s="4" t="n"/>
       <c r="AW53" s="4" t="n"/>
       <c r="AX53" s="4" t="n"/>
       <c r="AY53" s="4" t="n"/>
@@ -56024,15 +56034,15 @@
         </is>
       </c>
       <c r="AQ54" s="4" t="n"/>
-      <c r="AR54" s="4" t="n"/>
+      <c r="AR54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS54" s="4" t="n"/>
       <c r="AT54" s="4" t="n"/>
       <c r="AU54" s="4" t="n"/>
-      <c r="AV54" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV54" s="4" t="n"/>
       <c r="AW54" s="4" t="n"/>
       <c r="AX54" s="4" t="n"/>
       <c r="AY54" s="4" t="n"/>
@@ -56115,24 +56125,24 @@
       <c r="AN55" s="4" t="n"/>
       <c r="AO55" s="4" t="n"/>
       <c r="AP55" s="4" t="n"/>
-      <c r="AQ55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR55" s="4" t="n"/>
+      <c r="AQ55" s="4" t="n"/>
+      <c r="AR55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS55" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
       <c r="AT55" s="4" t="n"/>
-      <c r="AU55" s="4" t="n"/>
-      <c r="AV55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AV55" s="4" t="n"/>
       <c r="AW55" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -56236,15 +56246,15 @@
       </c>
       <c r="AP56" s="4" t="n"/>
       <c r="AQ56" s="4" t="n"/>
-      <c r="AR56" s="4" t="n"/>
+      <c r="AR56" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS56" s="4" t="n"/>
       <c r="AT56" s="4" t="n"/>
       <c r="AU56" s="4" t="n"/>
-      <c r="AV56" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV56" s="4" t="n"/>
       <c r="AW56" s="4" t="n"/>
       <c r="AX56" s="4" t="n"/>
       <c r="AY56" s="4" t="n"/>
@@ -56356,15 +56366,15 @@
         </is>
       </c>
       <c r="AQ57" s="4" t="n"/>
-      <c r="AR57" s="4" t="n"/>
+      <c r="AR57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS57" s="4" t="n"/>
       <c r="AT57" s="4" t="n"/>
       <c r="AU57" s="4" t="n"/>
-      <c r="AV57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV57" s="4" t="n"/>
       <c r="AW57" s="4" t="n"/>
       <c r="AX57" s="4" t="n"/>
       <c r="AY57" s="4" t="n"/>
@@ -56468,15 +56478,15 @@
       </c>
       <c r="AP58" s="4" t="n"/>
       <c r="AQ58" s="4" t="n"/>
-      <c r="AR58" s="4" t="n"/>
+      <c r="AR58" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS58" s="4" t="n"/>
       <c r="AT58" s="4" t="n"/>
       <c r="AU58" s="4" t="n"/>
-      <c r="AV58" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV58" s="4" t="n"/>
       <c r="AW58" s="4" t="n"/>
       <c r="AX58" s="4" t="n"/>
       <c r="AY58" s="4" t="n"/>
@@ -56568,19 +56578,19 @@
       <c r="AO59" s="4" t="n"/>
       <c r="AP59" s="4" t="n"/>
       <c r="AQ59" s="4" t="n"/>
-      <c r="AR59" s="4" t="n"/>
-      <c r="AS59" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AR59" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS59" s="4" t="n"/>
       <c r="AT59" s="4" t="n"/>
-      <c r="AU59" s="4" t="n"/>
-      <c r="AV59" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU59" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AV59" s="4" t="n"/>
       <c r="AW59" s="4" t="n"/>
       <c r="AX59" s="4" t="n"/>
       <c r="AY59" s="4" t="n"/>
@@ -56688,15 +56698,15 @@
       </c>
       <c r="AP60" s="4" t="n"/>
       <c r="AQ60" s="4" t="n"/>
-      <c r="AR60" s="4" t="n"/>
+      <c r="AR60" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS60" s="4" t="n"/>
       <c r="AT60" s="4" t="n"/>
       <c r="AU60" s="4" t="n"/>
-      <c r="AV60" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV60" s="4" t="n"/>
       <c r="AW60" s="4" t="n"/>
       <c r="AX60" s="4" t="n"/>
       <c r="AY60" s="4" t="n"/>
@@ -56795,24 +56805,24 @@
       <c r="AN61" s="4" t="n"/>
       <c r="AO61" s="4" t="n"/>
       <c r="AP61" s="4" t="n"/>
-      <c r="AQ61" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR61" s="4" t="n"/>
+      <c r="AQ61" s="4" t="n"/>
+      <c r="AR61" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS61" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
       <c r="AT61" s="4" t="n"/>
-      <c r="AU61" s="4" t="n"/>
-      <c r="AV61" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU61" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AV61" s="4" t="n"/>
       <c r="AW61" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -56920,19 +56930,19 @@
       <c r="AO62" s="4" t="n"/>
       <c r="AP62" s="4" t="n"/>
       <c r="AQ62" s="4" t="n"/>
-      <c r="AR62" s="4" t="n"/>
-      <c r="AS62" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AR62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS62" s="4" t="n"/>
       <c r="AT62" s="4" t="n"/>
-      <c r="AU62" s="4" t="n"/>
-      <c r="AV62" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AV62" s="4" t="n"/>
       <c r="AW62" s="4" t="n"/>
       <c r="AX62" s="4" t="n"/>
       <c r="AY62" s="4" t="n"/>
@@ -57056,15 +57066,15 @@
       </c>
       <c r="AP63" s="4" t="n"/>
       <c r="AQ63" s="4" t="n"/>
-      <c r="AR63" s="4" t="n"/>
+      <c r="AR63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS63" s="4" t="n"/>
       <c r="AT63" s="4" t="n"/>
       <c r="AU63" s="4" t="n"/>
-      <c r="AV63" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV63" s="4" t="n"/>
       <c r="AW63" s="4" t="n"/>
       <c r="AX63" s="4" t="n"/>
       <c r="AY63" s="4" t="n"/>
@@ -57172,15 +57182,15 @@
         </is>
       </c>
       <c r="AQ64" s="4" t="n"/>
-      <c r="AR64" s="4" t="n"/>
+      <c r="AR64" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS64" s="4" t="n"/>
       <c r="AT64" s="4" t="n"/>
       <c r="AU64" s="4" t="n"/>
-      <c r="AV64" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV64" s="4" t="n"/>
       <c r="AW64" s="4" t="n"/>
       <c r="AX64" s="4" t="n"/>
       <c r="AY64" s="4" t="n"/>
@@ -57272,15 +57282,15 @@
       <c r="AO65" s="4" t="n"/>
       <c r="AP65" s="4" t="n"/>
       <c r="AQ65" s="4" t="n"/>
-      <c r="AR65" s="4" t="n"/>
+      <c r="AR65" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS65" s="4" t="n"/>
       <c r="AT65" s="4" t="n"/>
       <c r="AU65" s="4" t="n"/>
-      <c r="AV65" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV65" s="4" t="n"/>
       <c r="AW65" s="4" t="n"/>
       <c r="AX65" s="4" t="n"/>
       <c r="AY65" s="4" t="n"/>
@@ -57376,15 +57386,15 @@
       </c>
       <c r="AP66" s="4" t="n"/>
       <c r="AQ66" s="4" t="n"/>
-      <c r="AR66" s="4" t="n"/>
+      <c r="AR66" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS66" s="4" t="n"/>
       <c r="AT66" s="4" t="n"/>
       <c r="AU66" s="4" t="n"/>
-      <c r="AV66" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV66" s="4" t="n"/>
       <c r="AW66" s="4" t="n"/>
       <c r="AX66" s="4" t="n"/>
       <c r="AY66" s="4" t="n"/>
@@ -57492,15 +57502,15 @@
       <c r="AO67" s="4" t="n"/>
       <c r="AP67" s="4" t="n"/>
       <c r="AQ67" s="4" t="n"/>
-      <c r="AR67" s="4" t="n"/>
+      <c r="AR67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS67" s="4" t="n"/>
       <c r="AT67" s="4" t="n"/>
       <c r="AU67" s="4" t="n"/>
-      <c r="AV67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV67" s="4" t="n"/>
       <c r="AW67" s="4" t="n"/>
       <c r="AX67" s="4" t="n"/>
       <c r="AY67" s="4" t="n"/>
@@ -57599,16 +57609,20 @@
       <c r="AN68" s="4" t="n"/>
       <c r="AO68" s="4" t="n"/>
       <c r="AP68" s="4" t="n"/>
-      <c r="AQ68" s="4" t="n"/>
-      <c r="AR68" s="4" t="n"/>
+      <c r="AQ68" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AR68" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS68" s="4" t="n"/>
       <c r="AT68" s="4" t="n"/>
       <c r="AU68" s="4" t="n"/>
-      <c r="AV68" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV68" s="4" t="n"/>
       <c r="AW68" s="4" t="n"/>
       <c r="AX68" s="4" t="n"/>
       <c r="AY68" s="4" t="n"/>
@@ -57695,18 +57709,18 @@
       <c r="AN69" s="4" t="n"/>
       <c r="AO69" s="4" t="n"/>
       <c r="AP69" s="4" t="n"/>
-      <c r="AQ69" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="AR69" s="4" t="n"/>
-      <c r="AS69" s="4" t="n"/>
-      <c r="AT69" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AQ69" s="4" t="n"/>
+      <c r="AR69" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS69" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AT69" s="4" t="n"/>
       <c r="AU69" s="4" t="n"/>
       <c r="AV69" s="4" t="inlineStr">
         <is>
@@ -57804,15 +57818,15 @@
       <c r="AO70" s="4" t="n"/>
       <c r="AP70" s="4" t="n"/>
       <c r="AQ70" s="4" t="n"/>
-      <c r="AR70" s="4" t="n"/>
+      <c r="AR70" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS70" s="4" t="n"/>
       <c r="AT70" s="4" t="n"/>
       <c r="AU70" s="4" t="n"/>
-      <c r="AV70" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV70" s="4" t="n"/>
       <c r="AW70" s="4" t="n"/>
       <c r="AX70" s="4" t="n"/>
       <c r="AY70" s="4" t="n"/>
@@ -57904,15 +57918,15 @@
       </c>
       <c r="AP71" s="4" t="n"/>
       <c r="AQ71" s="4" t="n"/>
-      <c r="AR71" s="4" t="n"/>
+      <c r="AR71" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS71" s="4" t="n"/>
       <c r="AT71" s="4" t="n"/>
       <c r="AU71" s="4" t="n"/>
-      <c r="AV71" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV71" s="4" t="n"/>
       <c r="AW71" s="4" t="n"/>
       <c r="AX71" s="4" t="n"/>
       <c r="AY71" s="4" t="n"/>
@@ -58004,13 +58018,13 @@
       <c r="AO72" s="4" t="n"/>
       <c r="AP72" s="4" t="n"/>
       <c r="AQ72" s="4" t="n"/>
-      <c r="AR72" s="4" t="n"/>
+      <c r="AR72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS72" s="4" t="n"/>
-      <c r="AT72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AT72" s="4" t="n"/>
       <c r="AU72" s="4" t="n"/>
       <c r="AV72" s="4" t="inlineStr">
         <is>
@@ -58120,19 +58134,19 @@
       <c r="AO73" s="4" t="n"/>
       <c r="AP73" s="4" t="n"/>
       <c r="AQ73" s="4" t="n"/>
-      <c r="AR73" s="4" t="n"/>
-      <c r="AS73" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AR73" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS73" s="4" t="n"/>
       <c r="AT73" s="4" t="n"/>
-      <c r="AU73" s="4" t="n"/>
-      <c r="AV73" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU73" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AV73" s="4" t="n"/>
       <c r="AW73" s="4" t="n"/>
       <c r="AX73" s="4" t="n"/>
       <c r="AY73" s="4" t="n"/>
@@ -58244,15 +58258,15 @@
       <c r="AO74" s="4" t="n"/>
       <c r="AP74" s="4" t="n"/>
       <c r="AQ74" s="4" t="n"/>
-      <c r="AR74" s="4" t="n"/>
+      <c r="AR74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS74" s="4" t="n"/>
       <c r="AT74" s="4" t="n"/>
       <c r="AU74" s="4" t="n"/>
-      <c r="AV74" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV74" s="4" t="n"/>
       <c r="AW74" s="4" t="n"/>
       <c r="AX74" s="4" t="n"/>
       <c r="AY74" s="4" t="n"/>
@@ -58352,15 +58366,15 @@
       <c r="AO75" s="4" t="n"/>
       <c r="AP75" s="4" t="n"/>
       <c r="AQ75" s="4" t="n"/>
-      <c r="AR75" s="4" t="n"/>
+      <c r="AR75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS75" s="4" t="n"/>
       <c r="AT75" s="4" t="n"/>
       <c r="AU75" s="4" t="n"/>
-      <c r="AV75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV75" s="4" t="n"/>
       <c r="AW75" s="4" t="n"/>
       <c r="AX75" s="4" t="n"/>
       <c r="AY75" s="4" t="n"/>
@@ -58440,19 +58454,19 @@
       <c r="AO76" s="4" t="n"/>
       <c r="AP76" s="4" t="n"/>
       <c r="AQ76" s="4" t="n"/>
-      <c r="AR76" s="4" t="n"/>
-      <c r="AS76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AR76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AS76" s="4" t="n"/>
       <c r="AT76" s="4" t="n"/>
-      <c r="AU76" s="4" t="n"/>
-      <c r="AV76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AU76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="AV76" s="4" t="n"/>
       <c r="AW76" s="4" t="n"/>
       <c r="AX76" s="4" t="n"/>
       <c r="AY76" s="4" t="n"/>
@@ -58572,15 +58586,15 @@
       </c>
       <c r="AP77" s="4" t="n"/>
       <c r="AQ77" s="4" t="n"/>
-      <c r="AR77" s="4" t="n"/>
+      <c r="AR77" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS77" s="4" t="n"/>
       <c r="AT77" s="4" t="n"/>
       <c r="AU77" s="4" t="n"/>
-      <c r="AV77" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV77" s="4" t="n"/>
       <c r="AW77" s="4" t="n"/>
       <c r="AX77" s="4" t="n"/>
       <c r="AY77" s="4" t="n"/>
@@ -58680,15 +58694,15 @@
         </is>
       </c>
       <c r="AQ78" s="4" t="n"/>
-      <c r="AR78" s="4" t="n"/>
+      <c r="AR78" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS78" s="4" t="n"/>
       <c r="AT78" s="4" t="n"/>
       <c r="AU78" s="4" t="n"/>
-      <c r="AV78" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV78" s="4" t="n"/>
       <c r="AW78" s="4" t="n"/>
       <c r="AX78" s="4" t="n"/>
       <c r="AY78" s="4" t="n"/>
@@ -58792,15 +58806,15 @@
         </is>
       </c>
       <c r="AQ79" s="4" t="n"/>
-      <c r="AR79" s="4" t="n"/>
+      <c r="AR79" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS79" s="4" t="n"/>
       <c r="AT79" s="4" t="n"/>
       <c r="AU79" s="4" t="n"/>
-      <c r="AV79" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV79" s="4" t="n"/>
       <c r="AW79" s="4" t="n"/>
       <c r="AX79" s="4" t="n"/>
       <c r="AY79" s="4" t="n"/>
@@ -58892,15 +58906,15 @@
       </c>
       <c r="AP80" s="4" t="n"/>
       <c r="AQ80" s="4" t="n"/>
-      <c r="AR80" s="4" t="n"/>
+      <c r="AR80" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS80" s="4" t="n"/>
       <c r="AT80" s="4" t="n"/>
       <c r="AU80" s="4" t="n"/>
-      <c r="AV80" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV80" s="4" t="n"/>
       <c r="AW80" s="4" t="n"/>
       <c r="AX80" s="4" t="n"/>
       <c r="AY80" s="4" t="n"/>
@@ -58988,15 +59002,15 @@
       <c r="AO81" s="4" t="n"/>
       <c r="AP81" s="4" t="n"/>
       <c r="AQ81" s="4" t="n"/>
-      <c r="AR81" s="4" t="n"/>
+      <c r="AR81" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS81" s="4" t="n"/>
       <c r="AT81" s="4" t="n"/>
       <c r="AU81" s="4" t="n"/>
-      <c r="AV81" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV81" s="4" t="n"/>
       <c r="AW81" s="4" t="n"/>
       <c r="AX81" s="4" t="n"/>
       <c r="AY81" s="4" t="n"/>
@@ -59080,15 +59094,15 @@
       <c r="AO82" s="4" t="n"/>
       <c r="AP82" s="4" t="n"/>
       <c r="AQ82" s="4" t="n"/>
-      <c r="AR82" s="4" t="n"/>
+      <c r="AR82" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS82" s="4" t="n"/>
       <c r="AT82" s="4" t="n"/>
       <c r="AU82" s="4" t="n"/>
-      <c r="AV82" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV82" s="4" t="n"/>
       <c r="AW82" s="4" t="n"/>
       <c r="AX82" s="4" t="n"/>
       <c r="AY82" s="4" t="n"/>
@@ -59168,15 +59182,15 @@
       <c r="AO83" s="4" t="n"/>
       <c r="AP83" s="4" t="n"/>
       <c r="AQ83" s="4" t="n"/>
-      <c r="AR83" s="4" t="n"/>
+      <c r="AR83" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS83" s="4" t="n"/>
       <c r="AT83" s="4" t="n"/>
       <c r="AU83" s="4" t="n"/>
-      <c r="AV83" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV83" s="4" t="n"/>
       <c r="AW83" s="4" t="n"/>
       <c r="AX83" s="4" t="n"/>
       <c r="AY83" s="4" t="n"/>
@@ -59268,15 +59282,15 @@
       <c r="AO84" s="4" t="n"/>
       <c r="AP84" s="4" t="n"/>
       <c r="AQ84" s="4" t="n"/>
-      <c r="AR84" s="4" t="n"/>
+      <c r="AR84" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AS84" s="4" t="n"/>
       <c r="AT84" s="4" t="n"/>
       <c r="AU84" s="4" t="n"/>
-      <c r="AV84" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AV84" s="4" t="n"/>
       <c r="AW84" s="4" t="n"/>
       <c r="AX84" s="4" t="n"/>
       <c r="AY84" s="4" t="n"/>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -7434,7 +7434,7 @@
       <c r="A80" s="6" t="n"/>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>飞跃城市</t>
+          <t>飞越城市</t>
         </is>
       </c>
       <c r="C80" s="4" t="n">
@@ -19317,7 +19317,7 @@
       <c r="A80" s="6" t="n"/>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>飞跃城市</t>
+          <t>飞越城市</t>
         </is>
       </c>
       <c r="C80" s="4" t="n"/>
@@ -32494,7 +32494,7 @@
       <c r="A80" s="6" t="n"/>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>飞跃城市</t>
+          <t>飞越城市</t>
         </is>
       </c>
       <c r="C80" s="4" t="n"/>
@@ -37015,7 +37015,7 @@
       <c r="A80" s="6" t="n"/>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>飞跃城市</t>
+          <t>飞越城市</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
@@ -42490,7 +42490,7 @@
       <c r="A80" s="6" t="n"/>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>飞跃城市</t>
+          <t>飞越城市</t>
         </is>
       </c>
       <c r="C80" s="4" t="n"/>
@@ -49286,7 +49286,7 @@
       <c r="A80" s="6" t="n"/>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>飞跃城市</t>
+          <t>飞越城市</t>
         </is>
       </c>
       <c r="C80" s="4" t="n"/>
@@ -58834,7 +58834,7 @@
       <c r="A80" s="6" t="n"/>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>飞跃城市</t>
+          <t>飞越城市</t>
         </is>
       </c>
       <c r="C80" s="4" t="n"/>
@@ -62216,7 +62216,7 @@
       <c r="A80" s="6" t="n"/>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>飞跃城市</t>
+          <t>飞越城市</t>
         </is>
       </c>
       <c r="C80" s="4" t="n"/>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -25,7 +25,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'五区_高手'!$A$1:$CK$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'五区_普通'!$A$1:$CK$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'五区_自动'!$A$1:$U$84</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'四区_理论'!$A$1:$AT$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'四区_理论'!$A$1:$AU$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'四区_高手'!$A$1:$BJ$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'四区_普通'!$A$1:$BJ$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'四区_自动'!$A$1:$P$84</definedName>
@@ -37193,7 +37193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT84"/>
+  <dimension ref="A1:AU84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -37242,6 +37242,7 @@
     <col width="7.5" customWidth="1" min="44" max="44"/>
     <col width="7.5" customWidth="1" min="45" max="45"/>
     <col width="7.5" customWidth="1" min="46" max="46"/>
+    <col width="7.5" customWidth="1" min="47" max="47"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -37457,20 +37458,25 @@
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
+          <t>dose</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
           <t>风扇</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>919</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>600lt</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>5n</t>
         </is>
@@ -37537,6 +37543,7 @@
       <c r="AR2" s="4" t="n"/>
       <c r="AS2" s="4" t="n"/>
       <c r="AT2" s="4" t="n"/>
+      <c r="AU2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n"/>
@@ -37603,6 +37610,7 @@
       <c r="AR3" s="4" t="n"/>
       <c r="AS3" s="4" t="n"/>
       <c r="AT3" s="4" t="n"/>
+      <c r="AU3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n"/>
@@ -37669,6 +37677,7 @@
       <c r="AR4" s="4" t="n"/>
       <c r="AS4" s="4" t="n"/>
       <c r="AT4" s="4" t="n"/>
+      <c r="AU4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n"/>
@@ -37745,6 +37754,7 @@
       <c r="AR5" s="4" t="n"/>
       <c r="AS5" s="4" t="n"/>
       <c r="AT5" s="4" t="n"/>
+      <c r="AU5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -37809,6 +37819,7 @@
       <c r="AR6" s="4" t="n"/>
       <c r="AS6" s="4" t="n"/>
       <c r="AT6" s="4" t="n"/>
+      <c r="AU6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
@@ -37869,6 +37880,7 @@
       <c r="AR7" s="4" t="n"/>
       <c r="AS7" s="4" t="n"/>
       <c r="AT7" s="4" t="n"/>
+      <c r="AU7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
@@ -37941,6 +37953,7 @@
       <c r="AR8" s="4" t="n"/>
       <c r="AS8" s="4" t="n"/>
       <c r="AT8" s="4" t="n"/>
+      <c r="AU8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n"/>
@@ -38013,6 +38026,7 @@
       <c r="AR9" s="4" t="n"/>
       <c r="AS9" s="4" t="n"/>
       <c r="AT9" s="4" t="n"/>
+      <c r="AU9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -38077,6 +38091,7 @@
       <c r="AR10" s="4" t="n"/>
       <c r="AS10" s="4" t="n"/>
       <c r="AT10" s="4" t="n"/>
+      <c r="AU10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
@@ -38137,6 +38152,7 @@
       <c r="AR11" s="4" t="n"/>
       <c r="AS11" s="4" t="n"/>
       <c r="AT11" s="4" t="n"/>
+      <c r="AU11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
@@ -38203,6 +38219,7 @@
       <c r="AR12" s="4" t="n"/>
       <c r="AS12" s="4" t="n"/>
       <c r="AT12" s="4" t="n"/>
+      <c r="AU12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
@@ -38261,6 +38278,7 @@
       <c r="AR13" s="4" t="n"/>
       <c r="AS13" s="4" t="n"/>
       <c r="AT13" s="4" t="n"/>
+      <c r="AU13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -38331,6 +38349,7 @@
       <c r="AR14" s="4" t="n"/>
       <c r="AS14" s="4" t="n"/>
       <c r="AT14" s="4" t="n"/>
+      <c r="AU14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
@@ -38401,6 +38420,7 @@
       <c r="AR15" s="4" t="n"/>
       <c r="AS15" s="4" t="n"/>
       <c r="AT15" s="4" t="n"/>
+      <c r="AU15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
@@ -38461,6 +38481,7 @@
       <c r="AR16" s="4" t="n"/>
       <c r="AS16" s="4" t="n"/>
       <c r="AT16" s="4" t="n"/>
+      <c r="AU16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
@@ -38525,6 +38546,7 @@
       <c r="AR17" s="4" t="n"/>
       <c r="AS17" s="4" t="n"/>
       <c r="AT17" s="4" t="n"/>
+      <c r="AU17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -38603,6 +38625,7 @@
       <c r="AR18" s="4" t="n"/>
       <c r="AS18" s="4" t="n"/>
       <c r="AT18" s="4" t="n"/>
+      <c r="AU18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
@@ -38664,11 +38687,12 @@
       <c r="AO19" s="4" t="n"/>
       <c r="AP19" s="4" t="n"/>
       <c r="AQ19" s="4" t="n"/>
-      <c r="AR19" s="4" t="n">
+      <c r="AR19" s="4" t="n"/>
+      <c r="AS19" s="4" t="n">
         <v>33.45</v>
       </c>
-      <c r="AS19" s="4" t="n"/>
       <c r="AT19" s="4" t="n"/>
+      <c r="AU19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
@@ -38735,6 +38759,7 @@
       <c r="AR20" s="4" t="n"/>
       <c r="AS20" s="4" t="n"/>
       <c r="AT20" s="4" t="n"/>
+      <c r="AU20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
@@ -38793,6 +38818,7 @@
       <c r="AR21" s="4" t="n"/>
       <c r="AS21" s="4" t="n"/>
       <c r="AT21" s="4" t="n"/>
+      <c r="AU21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -38861,6 +38887,7 @@
       <c r="AR22" s="4" t="n"/>
       <c r="AS22" s="4" t="n"/>
       <c r="AT22" s="4" t="n"/>
+      <c r="AU22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
@@ -38921,6 +38948,7 @@
       <c r="AR23" s="4" t="n"/>
       <c r="AS23" s="4" t="n"/>
       <c r="AT23" s="4" t="n"/>
+      <c r="AU23" s="4" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
@@ -38981,6 +39009,7 @@
       <c r="AR24" s="4" t="n"/>
       <c r="AS24" s="4" t="n"/>
       <c r="AT24" s="4" t="n"/>
+      <c r="AU24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
@@ -39043,6 +39072,7 @@
       <c r="AR25" s="4" t="n"/>
       <c r="AS25" s="4" t="n"/>
       <c r="AT25" s="4" t="n"/>
+      <c r="AU25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -39111,6 +39141,7 @@
       <c r="AR26" s="4" t="n"/>
       <c r="AS26" s="4" t="n"/>
       <c r="AT26" s="4" t="n"/>
+      <c r="AU26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n"/>
@@ -39171,6 +39202,7 @@
       <c r="AR27" s="4" t="n"/>
       <c r="AS27" s="4" t="n"/>
       <c r="AT27" s="4" t="n"/>
+      <c r="AU27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
@@ -39235,6 +39267,7 @@
       <c r="AR28" s="4" t="n"/>
       <c r="AS28" s="4" t="n"/>
       <c r="AT28" s="4" t="n"/>
+      <c r="AU28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n"/>
@@ -39299,6 +39332,7 @@
       <c r="AR29" s="4" t="n"/>
       <c r="AS29" s="4" t="n"/>
       <c r="AT29" s="4" t="n"/>
+      <c r="AU29" s="4" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -39367,6 +39401,7 @@
       <c r="AR30" s="4" t="n"/>
       <c r="AS30" s="4" t="n"/>
       <c r="AT30" s="4" t="n"/>
+      <c r="AU30" s="4" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n"/>
@@ -39433,6 +39468,7 @@
       <c r="AR31" s="4" t="n"/>
       <c r="AS31" s="4" t="n"/>
       <c r="AT31" s="4" t="n"/>
+      <c r="AU31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n"/>
@@ -39503,6 +39539,7 @@
       <c r="AR32" s="4" t="n"/>
       <c r="AS32" s="4" t="n"/>
       <c r="AT32" s="4" t="n"/>
+      <c r="AU32" s="4" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -39571,6 +39608,7 @@
       <c r="AR33" s="4" t="n"/>
       <c r="AS33" s="4" t="n"/>
       <c r="AT33" s="4" t="n"/>
+      <c r="AU33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n"/>
@@ -39584,7 +39622,7 @@
       </c>
       <c r="D34" s="4" t="n"/>
       <c r="E34" s="4" t="n">
-        <v>33.95</v>
+        <v>33.58</v>
       </c>
       <c r="F34" s="4" t="n"/>
       <c r="G34" s="4" t="n"/>
@@ -39633,6 +39671,7 @@
       <c r="AR34" s="4" t="n"/>
       <c r="AS34" s="4" t="n"/>
       <c r="AT34" s="4" t="n"/>
+      <c r="AU34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n"/>
@@ -39695,6 +39734,7 @@
       <c r="AR35" s="4" t="n"/>
       <c r="AS35" s="4" t="n"/>
       <c r="AT35" s="4" t="n"/>
+      <c r="AU35" s="4" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n"/>
@@ -39755,6 +39795,7 @@
       <c r="AR36" s="4" t="n"/>
       <c r="AS36" s="4" t="n"/>
       <c r="AT36" s="4" t="n"/>
+      <c r="AU36" s="4" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -39821,6 +39862,7 @@
       <c r="AR37" s="4" t="n"/>
       <c r="AS37" s="4" t="n"/>
       <c r="AT37" s="4" t="n"/>
+      <c r="AU37" s="4" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n"/>
@@ -39891,6 +39933,7 @@
       <c r="AR38" s="4" t="n"/>
       <c r="AS38" s="4" t="n"/>
       <c r="AT38" s="4" t="n"/>
+      <c r="AU38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n"/>
@@ -39951,6 +39994,7 @@
       <c r="AR39" s="4" t="n"/>
       <c r="AS39" s="4" t="n"/>
       <c r="AT39" s="4" t="n"/>
+      <c r="AU39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n"/>
@@ -40015,6 +40059,7 @@
       <c r="AR40" s="4" t="n"/>
       <c r="AS40" s="4" t="n"/>
       <c r="AT40" s="4" t="n"/>
+      <c r="AU40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -40079,6 +40124,7 @@
       <c r="AR41" s="4" t="n"/>
       <c r="AS41" s="4" t="n"/>
       <c r="AT41" s="4" t="n"/>
+      <c r="AU41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n"/>
@@ -40141,10 +40187,13 @@
       <c r="AN42" s="4" t="n"/>
       <c r="AO42" s="4" t="n"/>
       <c r="AP42" s="4" t="n"/>
-      <c r="AQ42" s="4" t="n"/>
+      <c r="AQ42" s="4" t="n">
+        <v>22.63</v>
+      </c>
       <c r="AR42" s="4" t="n"/>
       <c r="AS42" s="4" t="n"/>
       <c r="AT42" s="4" t="n"/>
+      <c r="AU42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n"/>
@@ -40207,6 +40256,7 @@
       <c r="AR43" s="4" t="n"/>
       <c r="AS43" s="4" t="n"/>
       <c r="AT43" s="4" t="n"/>
+      <c r="AU43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n"/>
@@ -40279,6 +40329,7 @@
       <c r="AR44" s="4" t="n"/>
       <c r="AS44" s="4" t="n"/>
       <c r="AT44" s="4" t="n"/>
+      <c r="AU44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -40341,6 +40392,7 @@
       <c r="AR45" s="4" t="n"/>
       <c r="AS45" s="4" t="n"/>
       <c r="AT45" s="4" t="n"/>
+      <c r="AU45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n"/>
@@ -40403,6 +40455,7 @@
       <c r="AR46" s="4" t="n"/>
       <c r="AS46" s="4" t="n"/>
       <c r="AT46" s="4" t="n"/>
+      <c r="AU46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n"/>
@@ -40459,6 +40512,7 @@
       <c r="AR47" s="4" t="n"/>
       <c r="AS47" s="4" t="n"/>
       <c r="AT47" s="4" t="n"/>
+      <c r="AU47" s="4" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n"/>
@@ -40523,6 +40577,7 @@
       <c r="AR48" s="4" t="n"/>
       <c r="AS48" s="4" t="n"/>
       <c r="AT48" s="4" t="n"/>
+      <c r="AU48" s="4" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -40587,6 +40642,7 @@
       <c r="AR49" s="4" t="n"/>
       <c r="AS49" s="4" t="n"/>
       <c r="AT49" s="4" t="n"/>
+      <c r="AU49" s="4" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="n"/>
@@ -40643,12 +40699,13 @@
       <c r="AN50" s="4" t="n"/>
       <c r="AO50" s="4" t="n"/>
       <c r="AP50" s="4" t="n"/>
-      <c r="AQ50" s="4" t="n">
+      <c r="AQ50" s="4" t="n"/>
+      <c r="AR50" s="4" t="n">
         <v>26.89</v>
       </c>
-      <c r="AR50" s="4" t="n"/>
       <c r="AS50" s="4" t="n"/>
       <c r="AT50" s="4" t="n"/>
+      <c r="AU50" s="4" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n"/>
@@ -40715,6 +40772,7 @@
       <c r="AR51" s="4" t="n"/>
       <c r="AS51" s="4" t="n"/>
       <c r="AT51" s="4" t="n"/>
+      <c r="AU51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n"/>
@@ -40777,6 +40835,7 @@
       <c r="AR52" s="4" t="n"/>
       <c r="AS52" s="4" t="n"/>
       <c r="AT52" s="4" t="n"/>
+      <c r="AU52" s="4" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -40839,6 +40898,7 @@
       <c r="AR53" s="4" t="n"/>
       <c r="AS53" s="4" t="n"/>
       <c r="AT53" s="4" t="n"/>
+      <c r="AU53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n"/>
@@ -40899,6 +40959,7 @@
       <c r="AR54" s="4" t="n"/>
       <c r="AS54" s="4" t="n"/>
       <c r="AT54" s="4" t="n"/>
+      <c r="AU54" s="4" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n"/>
@@ -40965,6 +41026,7 @@
       <c r="AR55" s="4" t="n"/>
       <c r="AS55" s="4" t="n"/>
       <c r="AT55" s="4" t="n"/>
+      <c r="AU55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n"/>
@@ -41025,6 +41087,7 @@
       <c r="AR56" s="4" t="n"/>
       <c r="AS56" s="4" t="n"/>
       <c r="AT56" s="4" t="n"/>
+      <c r="AU56" s="4" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -41093,6 +41156,7 @@
       <c r="AR57" s="4" t="n"/>
       <c r="AS57" s="4" t="n"/>
       <c r="AT57" s="4" t="n"/>
+      <c r="AU57" s="4" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="n"/>
@@ -41155,6 +41219,7 @@
       <c r="AR58" s="4" t="n"/>
       <c r="AS58" s="4" t="n"/>
       <c r="AT58" s="4" t="n"/>
+      <c r="AU58" s="4" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n"/>
@@ -41217,6 +41282,7 @@
       <c r="AR59" s="4" t="n"/>
       <c r="AS59" s="4" t="n"/>
       <c r="AT59" s="4" t="n"/>
+      <c r="AU59" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n"/>
@@ -41275,10 +41341,11 @@
       <c r="AP60" s="4" t="n"/>
       <c r="AQ60" s="4" t="n"/>
       <c r="AR60" s="4" t="n"/>
-      <c r="AS60" s="4" t="n">
+      <c r="AS60" s="4" t="n"/>
+      <c r="AT60" s="4" t="n">
         <v>38.65</v>
       </c>
-      <c r="AT60" s="4" t="n"/>
+      <c r="AU60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -41359,6 +41426,7 @@
       <c r="AR61" s="4" t="n"/>
       <c r="AS61" s="4" t="n"/>
       <c r="AT61" s="4" t="n"/>
+      <c r="AU61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="n"/>
@@ -41423,6 +41491,7 @@
       <c r="AR62" s="4" t="n"/>
       <c r="AS62" s="4" t="n"/>
       <c r="AT62" s="4" t="n"/>
+      <c r="AU62" s="4" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n"/>
@@ -41483,6 +41552,7 @@
       <c r="AR63" s="4" t="n"/>
       <c r="AS63" s="4" t="n"/>
       <c r="AT63" s="4" t="n"/>
+      <c r="AU63" s="4" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n"/>
@@ -41547,6 +41617,7 @@
       <c r="AR64" s="4" t="n"/>
       <c r="AS64" s="4" t="n"/>
       <c r="AT64" s="4" t="n"/>
+      <c r="AU64" s="4" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -41609,6 +41680,7 @@
       <c r="AR65" s="4" t="n"/>
       <c r="AS65" s="4" t="n"/>
       <c r="AT65" s="4" t="n"/>
+      <c r="AU65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="n"/>
@@ -41667,6 +41739,7 @@
       <c r="AR66" s="4" t="n"/>
       <c r="AS66" s="4" t="n"/>
       <c r="AT66" s="4" t="n"/>
+      <c r="AU66" s="4" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n"/>
@@ -41731,6 +41804,7 @@
       <c r="AR67" s="4" t="n"/>
       <c r="AS67" s="4" t="n"/>
       <c r="AT67" s="4" t="n"/>
+      <c r="AU67" s="4" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n"/>
@@ -41789,6 +41863,7 @@
       <c r="AR68" s="4" t="n"/>
       <c r="AS68" s="4" t="n"/>
       <c r="AT68" s="4" t="n"/>
+      <c r="AU68" s="4" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -41857,6 +41932,7 @@
       <c r="AR69" s="4" t="n"/>
       <c r="AS69" s="4" t="n"/>
       <c r="AT69" s="4" t="n"/>
+      <c r="AU69" s="4" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="n"/>
@@ -41919,6 +41995,7 @@
       <c r="AR70" s="4" t="n"/>
       <c r="AS70" s="4" t="n"/>
       <c r="AT70" s="4" t="n"/>
+      <c r="AU70" s="4" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n"/>
@@ -41981,6 +42058,7 @@
       <c r="AR71" s="4" t="n"/>
       <c r="AS71" s="4" t="n"/>
       <c r="AT71" s="4" t="n"/>
+      <c r="AU71" s="4" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n"/>
@@ -42053,6 +42131,7 @@
       <c r="AR72" s="4" t="n"/>
       <c r="AS72" s="4" t="n"/>
       <c r="AT72" s="4" t="n"/>
+      <c r="AU72" s="4" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -42117,6 +42196,7 @@
       <c r="AR73" s="4" t="n"/>
       <c r="AS73" s="4" t="n"/>
       <c r="AT73" s="4" t="n"/>
+      <c r="AU73" s="4" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="n"/>
@@ -42177,6 +42257,7 @@
       <c r="AR74" s="4" t="n"/>
       <c r="AS74" s="4" t="n"/>
       <c r="AT74" s="4" t="n"/>
+      <c r="AU74" s="4" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n"/>
@@ -42237,6 +42318,7 @@
       <c r="AR75" s="4" t="n"/>
       <c r="AS75" s="4" t="n"/>
       <c r="AT75" s="4" t="n"/>
+      <c r="AU75" s="4" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="n"/>
@@ -42295,6 +42377,7 @@
       <c r="AR76" s="4" t="n"/>
       <c r="AS76" s="4" t="n"/>
       <c r="AT76" s="4" t="n"/>
+      <c r="AU76" s="4" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -42359,6 +42442,7 @@
       <c r="AR77" s="4" t="n"/>
       <c r="AS77" s="4" t="n"/>
       <c r="AT77" s="4" t="n"/>
+      <c r="AU77" s="4" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="n"/>
@@ -42425,6 +42509,7 @@
       <c r="AR78" s="4" t="n"/>
       <c r="AS78" s="4" t="n"/>
       <c r="AT78" s="4" t="n"/>
+      <c r="AU78" s="4" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n"/>
@@ -42485,6 +42570,7 @@
       <c r="AR79" s="4" t="n"/>
       <c r="AS79" s="4" t="n"/>
       <c r="AT79" s="4" t="n"/>
+      <c r="AU79" s="4" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="n"/>
@@ -42541,6 +42627,7 @@
       <c r="AR80" s="4" t="n"/>
       <c r="AS80" s="4" t="n"/>
       <c r="AT80" s="4" t="n"/>
+      <c r="AU80" s="4" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
@@ -42603,6 +42690,7 @@
       <c r="AR81" s="4" t="n"/>
       <c r="AS81" s="4" t="n"/>
       <c r="AT81" s="4" t="n"/>
+      <c r="AU81" s="4" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="n"/>
@@ -42659,6 +42747,7 @@
       <c r="AR82" s="4" t="n"/>
       <c r="AS82" s="4" t="n"/>
       <c r="AT82" s="4" t="n"/>
+      <c r="AU82" s="4" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n"/>
@@ -42715,6 +42804,7 @@
       <c r="AR83" s="4" t="n"/>
       <c r="AS83" s="4" t="n"/>
       <c r="AT83" s="4" t="n"/>
+      <c r="AU83" s="4" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="n"/>
@@ -42777,9 +42867,10 @@
       <c r="AR84" s="4" t="n"/>
       <c r="AS84" s="4" t="n"/>
       <c r="AT84" s="4" t="n"/>
+      <c r="AU84" s="4" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AT84"/>
+  <autoFilter ref="A1:AU84"/>
   <mergeCells count="21">
     <mergeCell ref="A61:A64"/>
     <mergeCell ref="A69:A72"/>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -26,8 +26,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'五区_普通'!$A$1:$CK$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'五区_自动'!$A$1:$U$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'四区_理论'!$A$1:$AU$84</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'四区_高手'!$A$1:$BJ$84</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'四区_普通'!$A$1:$BJ$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'四区_高手'!$A$1:$BL$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'四区_普通'!$A$1:$BL$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'四区_自动'!$A$1:$P$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'五区_理论_特殊跑法'!$A$1:$AO$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'五区_高手_特殊跑法'!$A$1:$T$21</definedName>
@@ -42904,7 +42904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BJ84"/>
+  <dimension ref="A1:BL84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -42969,6 +42969,8 @@
     <col width="7.5" customWidth="1" min="60" max="60"/>
     <col width="7.5" customWidth="1" min="61" max="61"/>
     <col width="7.5" customWidth="1" min="62" max="62"/>
+    <col width="7.5" customWidth="1" min="63" max="63"/>
+    <col width="7.5" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -43269,15 +43271,25 @@
       </c>
       <c r="BH1" s="1" t="inlineStr">
         <is>
+          <t>dose★3</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>dose★4</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
           <t>风扇★5</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>600lt★5</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>5n★4</t>
         </is>
@@ -43360,6 +43372,8 @@
       <c r="BH2" s="4" t="n"/>
       <c r="BI2" s="4" t="n"/>
       <c r="BJ2" s="4" t="n"/>
+      <c r="BK2" s="4" t="n"/>
+      <c r="BL2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n"/>
@@ -43436,6 +43450,8 @@
       <c r="BH3" s="4" t="n"/>
       <c r="BI3" s="4" t="n"/>
       <c r="BJ3" s="4" t="n"/>
+      <c r="BK3" s="4" t="n"/>
+      <c r="BL3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n"/>
@@ -43510,6 +43526,8 @@
       <c r="BH4" s="4" t="n"/>
       <c r="BI4" s="4" t="n"/>
       <c r="BJ4" s="4" t="n"/>
+      <c r="BK4" s="4" t="n"/>
+      <c r="BL4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n"/>
@@ -43590,6 +43608,8 @@
       <c r="BH5" s="4" t="n"/>
       <c r="BI5" s="4" t="n"/>
       <c r="BJ5" s="4" t="n"/>
+      <c r="BK5" s="4" t="n"/>
+      <c r="BL5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -43664,6 +43684,8 @@
       <c r="BH6" s="4" t="n"/>
       <c r="BI6" s="4" t="n"/>
       <c r="BJ6" s="4" t="n"/>
+      <c r="BK6" s="4" t="n"/>
+      <c r="BL6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
@@ -43736,6 +43758,8 @@
       <c r="BH7" s="4" t="n"/>
       <c r="BI7" s="4" t="n"/>
       <c r="BJ7" s="4" t="n"/>
+      <c r="BK7" s="4" t="n"/>
+      <c r="BL7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
@@ -43824,6 +43848,8 @@
       <c r="BH8" s="4" t="n"/>
       <c r="BI8" s="4" t="n"/>
       <c r="BJ8" s="4" t="n"/>
+      <c r="BK8" s="4" t="n"/>
+      <c r="BL8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n"/>
@@ -43898,6 +43924,8 @@
       <c r="BH9" s="4" t="n"/>
       <c r="BI9" s="4" t="n"/>
       <c r="BJ9" s="4" t="n"/>
+      <c r="BK9" s="4" t="n"/>
+      <c r="BL9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -43978,6 +44006,8 @@
       <c r="BH10" s="4" t="n"/>
       <c r="BI10" s="4" t="n"/>
       <c r="BJ10" s="4" t="n"/>
+      <c r="BK10" s="4" t="n"/>
+      <c r="BL10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
@@ -44054,6 +44084,8 @@
       <c r="BH11" s="4" t="n"/>
       <c r="BI11" s="4" t="n"/>
       <c r="BJ11" s="4" t="n"/>
+      <c r="BK11" s="4" t="n"/>
+      <c r="BL11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
@@ -44136,6 +44168,8 @@
       <c r="BH12" s="4" t="n"/>
       <c r="BI12" s="4" t="n"/>
       <c r="BJ12" s="4" t="n"/>
+      <c r="BK12" s="4" t="n"/>
+      <c r="BL12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
@@ -44210,6 +44244,8 @@
       <c r="BH13" s="4" t="n"/>
       <c r="BI13" s="4" t="n"/>
       <c r="BJ13" s="4" t="n"/>
+      <c r="BK13" s="4" t="n"/>
+      <c r="BL13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -44296,6 +44332,8 @@
       <c r="BH14" s="4" t="n"/>
       <c r="BI14" s="4" t="n"/>
       <c r="BJ14" s="4" t="n"/>
+      <c r="BK14" s="4" t="n"/>
+      <c r="BL14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
@@ -44378,6 +44416,8 @@
       <c r="BH15" s="4" t="n"/>
       <c r="BI15" s="4" t="n"/>
       <c r="BJ15" s="4" t="n"/>
+      <c r="BK15" s="4" t="n"/>
+      <c r="BL15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
@@ -44462,6 +44502,8 @@
       <c r="BH16" s="4" t="n"/>
       <c r="BI16" s="4" t="n"/>
       <c r="BJ16" s="4" t="n"/>
+      <c r="BK16" s="4" t="n"/>
+      <c r="BL16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
@@ -44536,6 +44578,8 @@
       <c r="BH17" s="4" t="n"/>
       <c r="BI17" s="4" t="n"/>
       <c r="BJ17" s="4" t="n"/>
+      <c r="BK17" s="4" t="n"/>
+      <c r="BL17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -44614,6 +44658,8 @@
       <c r="BH18" s="4" t="n"/>
       <c r="BI18" s="4" t="n"/>
       <c r="BJ18" s="4" t="n"/>
+      <c r="BK18" s="4" t="n"/>
+      <c r="BL18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
@@ -44692,6 +44738,8 @@
       <c r="BH19" s="4" t="n"/>
       <c r="BI19" s="4" t="n"/>
       <c r="BJ19" s="4" t="n"/>
+      <c r="BK19" s="4" t="n"/>
+      <c r="BL19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
@@ -44768,6 +44816,8 @@
       <c r="BH20" s="4" t="n"/>
       <c r="BI20" s="4" t="n"/>
       <c r="BJ20" s="4" t="n"/>
+      <c r="BK20" s="4" t="n"/>
+      <c r="BL20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
@@ -44840,6 +44890,8 @@
       <c r="BH21" s="4" t="n"/>
       <c r="BI21" s="4" t="n"/>
       <c r="BJ21" s="4" t="n"/>
+      <c r="BK21" s="4" t="n"/>
+      <c r="BL21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -44918,6 +44970,8 @@
       <c r="BH22" s="4" t="n"/>
       <c r="BI22" s="4" t="n"/>
       <c r="BJ22" s="4" t="n"/>
+      <c r="BK22" s="4" t="n"/>
+      <c r="BL22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
@@ -44996,6 +45050,8 @@
       <c r="BH23" s="4" t="n"/>
       <c r="BI23" s="4" t="n"/>
       <c r="BJ23" s="4" t="n"/>
+      <c r="BK23" s="4" t="n"/>
+      <c r="BL23" s="4" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
@@ -45074,6 +45130,8 @@
       <c r="BH24" s="4" t="n"/>
       <c r="BI24" s="4" t="n"/>
       <c r="BJ24" s="4" t="n"/>
+      <c r="BK24" s="4" t="n"/>
+      <c r="BL24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
@@ -45152,6 +45210,8 @@
       <c r="BH25" s="4" t="n"/>
       <c r="BI25" s="4" t="n"/>
       <c r="BJ25" s="4" t="n"/>
+      <c r="BK25" s="4" t="n"/>
+      <c r="BL25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -45234,6 +45294,8 @@
       <c r="BH26" s="4" t="n"/>
       <c r="BI26" s="4" t="n"/>
       <c r="BJ26" s="4" t="n"/>
+      <c r="BK26" s="4" t="n"/>
+      <c r="BL26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n"/>
@@ -45310,6 +45372,8 @@
       <c r="BH27" s="4" t="n"/>
       <c r="BI27" s="4" t="n"/>
       <c r="BJ27" s="4" t="n"/>
+      <c r="BK27" s="4" t="n"/>
+      <c r="BL27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
@@ -45390,6 +45454,8 @@
       <c r="BH28" s="4" t="n"/>
       <c r="BI28" s="4" t="n"/>
       <c r="BJ28" s="4" t="n"/>
+      <c r="BK28" s="4" t="n"/>
+      <c r="BL28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n"/>
@@ -45466,6 +45532,8 @@
       <c r="BH29" s="4" t="n"/>
       <c r="BI29" s="4" t="n"/>
       <c r="BJ29" s="4" t="n"/>
+      <c r="BK29" s="4" t="n"/>
+      <c r="BL29" s="4" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -45542,6 +45610,8 @@
       <c r="BH30" s="4" t="n"/>
       <c r="BI30" s="4" t="n"/>
       <c r="BJ30" s="4" t="n"/>
+      <c r="BK30" s="4" t="n"/>
+      <c r="BL30" s="4" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n"/>
@@ -45616,6 +45686,8 @@
       <c r="BH31" s="4" t="n"/>
       <c r="BI31" s="4" t="n"/>
       <c r="BJ31" s="4" t="n"/>
+      <c r="BK31" s="4" t="n"/>
+      <c r="BL31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n"/>
@@ -45702,6 +45774,8 @@
       <c r="BH32" s="4" t="n"/>
       <c r="BI32" s="4" t="n"/>
       <c r="BJ32" s="4" t="n"/>
+      <c r="BK32" s="4" t="n"/>
+      <c r="BL32" s="4" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -45780,6 +45854,8 @@
       <c r="BH33" s="4" t="n"/>
       <c r="BI33" s="4" t="n"/>
       <c r="BJ33" s="4" t="n"/>
+      <c r="BK33" s="4" t="n"/>
+      <c r="BL33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n"/>
@@ -45858,6 +45934,8 @@
       <c r="BH34" s="4" t="n"/>
       <c r="BI34" s="4" t="n"/>
       <c r="BJ34" s="4" t="n"/>
+      <c r="BK34" s="4" t="n"/>
+      <c r="BL34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n"/>
@@ -45934,6 +46012,8 @@
       <c r="BH35" s="4" t="n"/>
       <c r="BI35" s="4" t="n"/>
       <c r="BJ35" s="4" t="n"/>
+      <c r="BK35" s="4" t="n"/>
+      <c r="BL35" s="4" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n"/>
@@ -46008,6 +46088,8 @@
       <c r="BH36" s="4" t="n"/>
       <c r="BI36" s="4" t="n"/>
       <c r="BJ36" s="4" t="n"/>
+      <c r="BK36" s="4" t="n"/>
+      <c r="BL36" s="4" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -46094,6 +46176,8 @@
       <c r="BH37" s="4" t="n"/>
       <c r="BI37" s="4" t="n"/>
       <c r="BJ37" s="4" t="n"/>
+      <c r="BK37" s="4" t="n"/>
+      <c r="BL37" s="4" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n"/>
@@ -46168,6 +46252,8 @@
       <c r="BH38" s="4" t="n"/>
       <c r="BI38" s="4" t="n"/>
       <c r="BJ38" s="4" t="n"/>
+      <c r="BK38" s="4" t="n"/>
+      <c r="BL38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n"/>
@@ -46242,6 +46328,8 @@
       <c r="BH39" s="4" t="n"/>
       <c r="BI39" s="4" t="n"/>
       <c r="BJ39" s="4" t="n"/>
+      <c r="BK39" s="4" t="n"/>
+      <c r="BL39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n"/>
@@ -46330,6 +46418,8 @@
       <c r="BH40" s="4" t="n"/>
       <c r="BI40" s="4" t="n"/>
       <c r="BJ40" s="4" t="n"/>
+      <c r="BK40" s="4" t="n"/>
+      <c r="BL40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -46408,6 +46498,8 @@
       <c r="BH41" s="4" t="n"/>
       <c r="BI41" s="4" t="n"/>
       <c r="BJ41" s="4" t="n"/>
+      <c r="BK41" s="4" t="n"/>
+      <c r="BL41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n"/>
@@ -46488,6 +46580,8 @@
       <c r="BH42" s="4" t="n"/>
       <c r="BI42" s="4" t="n"/>
       <c r="BJ42" s="4" t="n"/>
+      <c r="BK42" s="4" t="n"/>
+      <c r="BL42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n"/>
@@ -46562,6 +46656,8 @@
       <c r="BH43" s="4" t="n"/>
       <c r="BI43" s="4" t="n"/>
       <c r="BJ43" s="4" t="n"/>
+      <c r="BK43" s="4" t="n"/>
+      <c r="BL43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n"/>
@@ -46634,6 +46730,8 @@
       <c r="BH44" s="4" t="n"/>
       <c r="BI44" s="4" t="n"/>
       <c r="BJ44" s="4" t="n"/>
+      <c r="BK44" s="4" t="n"/>
+      <c r="BL44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -46724,6 +46822,8 @@
       <c r="BH45" s="4" t="n"/>
       <c r="BI45" s="4" t="n"/>
       <c r="BJ45" s="4" t="n"/>
+      <c r="BK45" s="4" t="n"/>
+      <c r="BL45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n"/>
@@ -46802,6 +46902,8 @@
       <c r="BH46" s="4" t="n"/>
       <c r="BI46" s="4" t="n"/>
       <c r="BJ46" s="4" t="n"/>
+      <c r="BK46" s="4" t="n"/>
+      <c r="BL46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n"/>
@@ -46880,6 +46982,8 @@
       <c r="BH47" s="4" t="n"/>
       <c r="BI47" s="4" t="n"/>
       <c r="BJ47" s="4" t="n"/>
+      <c r="BK47" s="4" t="n"/>
+      <c r="BL47" s="4" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n"/>
@@ -46960,6 +47064,8 @@
       <c r="BH48" s="4" t="n"/>
       <c r="BI48" s="4" t="n"/>
       <c r="BJ48" s="4" t="n"/>
+      <c r="BK48" s="4" t="n"/>
+      <c r="BL48" s="4" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -47038,6 +47144,8 @@
       <c r="BH49" s="4" t="n"/>
       <c r="BI49" s="4" t="n"/>
       <c r="BJ49" s="4" t="n"/>
+      <c r="BK49" s="4" t="n"/>
+      <c r="BL49" s="4" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="n"/>
@@ -47110,6 +47218,8 @@
       <c r="BH50" s="4" t="n"/>
       <c r="BI50" s="4" t="n"/>
       <c r="BJ50" s="4" t="n"/>
+      <c r="BK50" s="4" t="n"/>
+      <c r="BL50" s="4" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n"/>
@@ -47186,6 +47296,8 @@
       <c r="BH51" s="4" t="n"/>
       <c r="BI51" s="4" t="n"/>
       <c r="BJ51" s="4" t="n"/>
+      <c r="BK51" s="4" t="n"/>
+      <c r="BL51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n"/>
@@ -47272,6 +47384,8 @@
       <c r="BH52" s="4" t="n"/>
       <c r="BI52" s="4" t="n"/>
       <c r="BJ52" s="4" t="n"/>
+      <c r="BK52" s="4" t="n"/>
+      <c r="BL52" s="4" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -47352,6 +47466,8 @@
       <c r="BH53" s="4" t="n"/>
       <c r="BI53" s="4" t="n"/>
       <c r="BJ53" s="4" t="n"/>
+      <c r="BK53" s="4" t="n"/>
+      <c r="BL53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n"/>
@@ -47426,6 +47542,8 @@
       <c r="BH54" s="4" t="n"/>
       <c r="BI54" s="4" t="n"/>
       <c r="BJ54" s="4" t="n"/>
+      <c r="BK54" s="4" t="n"/>
+      <c r="BL54" s="4" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n"/>
@@ -47498,6 +47616,8 @@
       <c r="BH55" s="4" t="n"/>
       <c r="BI55" s="4" t="n"/>
       <c r="BJ55" s="4" t="n"/>
+      <c r="BK55" s="4" t="n"/>
+      <c r="BL55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n"/>
@@ -47572,6 +47692,8 @@
       <c r="BH56" s="4" t="n"/>
       <c r="BI56" s="4" t="n"/>
       <c r="BJ56" s="4" t="n"/>
+      <c r="BK56" s="4" t="n"/>
+      <c r="BL56" s="4" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -47660,6 +47782,8 @@
       <c r="BH57" s="4" t="n"/>
       <c r="BI57" s="4" t="n"/>
       <c r="BJ57" s="4" t="n"/>
+      <c r="BK57" s="4" t="n"/>
+      <c r="BL57" s="4" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="n"/>
@@ -47734,6 +47858,8 @@
       <c r="BH58" s="4" t="n"/>
       <c r="BI58" s="4" t="n"/>
       <c r="BJ58" s="4" t="n"/>
+      <c r="BK58" s="4" t="n"/>
+      <c r="BL58" s="4" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n"/>
@@ -47810,6 +47936,8 @@
       <c r="BH59" s="4" t="n"/>
       <c r="BI59" s="4" t="n"/>
       <c r="BJ59" s="4" t="n"/>
+      <c r="BK59" s="4" t="n"/>
+      <c r="BL59" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n"/>
@@ -47892,6 +48020,8 @@
       <c r="BH60" s="4" t="n"/>
       <c r="BI60" s="4" t="n"/>
       <c r="BJ60" s="4" t="n"/>
+      <c r="BK60" s="4" t="n"/>
+      <c r="BL60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -47968,6 +48098,8 @@
       <c r="BH61" s="4" t="n"/>
       <c r="BI61" s="4" t="n"/>
       <c r="BJ61" s="4" t="n"/>
+      <c r="BK61" s="4" t="n"/>
+      <c r="BL61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="n"/>
@@ -48048,6 +48180,8 @@
       <c r="BH62" s="4" t="n"/>
       <c r="BI62" s="4" t="n"/>
       <c r="BJ62" s="4" t="n"/>
+      <c r="BK62" s="4" t="n"/>
+      <c r="BL62" s="4" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n"/>
@@ -48134,6 +48268,8 @@
       <c r="BH63" s="4" t="n"/>
       <c r="BI63" s="4" t="n"/>
       <c r="BJ63" s="4" t="n"/>
+      <c r="BK63" s="4" t="n"/>
+      <c r="BL63" s="4" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n"/>
@@ -48210,6 +48346,8 @@
       <c r="BH64" s="4" t="n"/>
       <c r="BI64" s="4" t="n"/>
       <c r="BJ64" s="4" t="n"/>
+      <c r="BK64" s="4" t="n"/>
+      <c r="BL64" s="4" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -48284,6 +48422,8 @@
       <c r="BH65" s="4" t="n"/>
       <c r="BI65" s="4" t="n"/>
       <c r="BJ65" s="4" t="n"/>
+      <c r="BK65" s="4" t="n"/>
+      <c r="BL65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="n"/>
@@ -48362,6 +48502,8 @@
       <c r="BH66" s="4" t="n"/>
       <c r="BI66" s="4" t="n"/>
       <c r="BJ66" s="4" t="n"/>
+      <c r="BK66" s="4" t="n"/>
+      <c r="BL66" s="4" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n"/>
@@ -48438,6 +48580,8 @@
       <c r="BH67" s="4" t="n"/>
       <c r="BI67" s="4" t="n"/>
       <c r="BJ67" s="4" t="n"/>
+      <c r="BK67" s="4" t="n"/>
+      <c r="BL67" s="4" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n"/>
@@ -48516,6 +48660,8 @@
       <c r="BH68" s="4" t="n"/>
       <c r="BI68" s="4" t="n"/>
       <c r="BJ68" s="4" t="n"/>
+      <c r="BK68" s="4" t="n"/>
+      <c r="BL68" s="4" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -48592,6 +48738,8 @@
       <c r="BH69" s="4" t="n"/>
       <c r="BI69" s="4" t="n"/>
       <c r="BJ69" s="4" t="n"/>
+      <c r="BK69" s="4" t="n"/>
+      <c r="BL69" s="4" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="n"/>
@@ -48664,6 +48812,8 @@
       <c r="BH70" s="4" t="n"/>
       <c r="BI70" s="4" t="n"/>
       <c r="BJ70" s="4" t="n"/>
+      <c r="BK70" s="4" t="n"/>
+      <c r="BL70" s="4" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n"/>
@@ -48736,6 +48886,8 @@
       <c r="BH71" s="4" t="n"/>
       <c r="BI71" s="4" t="n"/>
       <c r="BJ71" s="4" t="n"/>
+      <c r="BK71" s="4" t="n"/>
+      <c r="BL71" s="4" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n"/>
@@ -48812,6 +48964,8 @@
       <c r="BH72" s="4" t="n"/>
       <c r="BI72" s="4" t="n"/>
       <c r="BJ72" s="4" t="n"/>
+      <c r="BK72" s="4" t="n"/>
+      <c r="BL72" s="4" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -48892,6 +49046,8 @@
       <c r="BH73" s="4" t="n"/>
       <c r="BI73" s="4" t="n"/>
       <c r="BJ73" s="4" t="n"/>
+      <c r="BK73" s="4" t="n"/>
+      <c r="BL73" s="4" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="n"/>
@@ -48972,6 +49128,8 @@
       <c r="BH74" s="4" t="n"/>
       <c r="BI74" s="4" t="n"/>
       <c r="BJ74" s="4" t="n"/>
+      <c r="BK74" s="4" t="n"/>
+      <c r="BL74" s="4" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n"/>
@@ -49052,6 +49210,8 @@
       <c r="BH75" s="4" t="n"/>
       <c r="BI75" s="4" t="n"/>
       <c r="BJ75" s="4" t="n"/>
+      <c r="BK75" s="4" t="n"/>
+      <c r="BL75" s="4" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="n"/>
@@ -49126,6 +49286,8 @@
       <c r="BH76" s="4" t="n"/>
       <c r="BI76" s="4" t="n"/>
       <c r="BJ76" s="4" t="n"/>
+      <c r="BK76" s="4" t="n"/>
+      <c r="BL76" s="4" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -49210,6 +49372,8 @@
       <c r="BH77" s="4" t="n"/>
       <c r="BI77" s="4" t="n"/>
       <c r="BJ77" s="4" t="n"/>
+      <c r="BK77" s="4" t="n"/>
+      <c r="BL77" s="4" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="n"/>
@@ -49290,6 +49454,8 @@
       <c r="BH78" s="4" t="n"/>
       <c r="BI78" s="4" t="n"/>
       <c r="BJ78" s="4" t="n"/>
+      <c r="BK78" s="4" t="n"/>
+      <c r="BL78" s="4" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n"/>
@@ -49372,6 +49538,8 @@
       <c r="BH79" s="4" t="n"/>
       <c r="BI79" s="4" t="n"/>
       <c r="BJ79" s="4" t="n"/>
+      <c r="BK79" s="4" t="n"/>
+      <c r="BL79" s="4" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="n"/>
@@ -49446,6 +49614,8 @@
       <c r="BH80" s="4" t="n"/>
       <c r="BI80" s="4" t="n"/>
       <c r="BJ80" s="4" t="n"/>
+      <c r="BK80" s="4" t="n"/>
+      <c r="BL80" s="4" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
@@ -49526,6 +49696,8 @@
       <c r="BH81" s="4" t="n"/>
       <c r="BI81" s="4" t="n"/>
       <c r="BJ81" s="4" t="n"/>
+      <c r="BK81" s="4" t="n"/>
+      <c r="BL81" s="4" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="n"/>
@@ -49604,6 +49776,8 @@
       <c r="BH82" s="4" t="n"/>
       <c r="BI82" s="4" t="n"/>
       <c r="BJ82" s="4" t="n"/>
+      <c r="BK82" s="4" t="n"/>
+      <c r="BL82" s="4" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n"/>
@@ -49680,6 +49854,8 @@
       <c r="BH83" s="4" t="n"/>
       <c r="BI83" s="4" t="n"/>
       <c r="BJ83" s="4" t="n"/>
+      <c r="BK83" s="4" t="n"/>
+      <c r="BL83" s="4" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="n"/>
@@ -49762,9 +49938,11 @@
       <c r="BH84" s="4" t="n"/>
       <c r="BI84" s="4" t="n"/>
       <c r="BJ84" s="4" t="n"/>
+      <c r="BK84" s="4" t="n"/>
+      <c r="BL84" s="4" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BJ84"/>
+  <autoFilter ref="A1:BL84"/>
   <mergeCells count="21">
     <mergeCell ref="A61:A64"/>
     <mergeCell ref="A69:A72"/>
@@ -49798,7 +49976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BJ84"/>
+  <dimension ref="A1:BL84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -49863,6 +50041,8 @@
     <col width="7.5" customWidth="1" min="60" max="60"/>
     <col width="7.5" customWidth="1" min="61" max="61"/>
     <col width="7.5" customWidth="1" min="62" max="62"/>
+    <col width="7.5" customWidth="1" min="63" max="63"/>
+    <col width="7.5" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -50163,15 +50343,25 @@
       </c>
       <c r="BH1" s="1" t="inlineStr">
         <is>
+          <t>dose★3</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>dose★4</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
           <t>风扇★5</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>600lt★5</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>5n★4</t>
         </is>
@@ -50273,9 +50463,19 @@
       <c r="BE2" s="4" t="n"/>
       <c r="BF2" s="4" t="n"/>
       <c r="BG2" s="4" t="n"/>
-      <c r="BH2" s="4" t="n"/>
-      <c r="BI2" s="4" t="n"/>
-      <c r="BJ2" s="4" t="inlineStr">
+      <c r="BH2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI2" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BJ2" s="4" t="n"/>
+      <c r="BK2" s="4" t="n"/>
+      <c r="BL2" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -50393,9 +50593,19 @@
       <c r="BE3" s="4" t="n"/>
       <c r="BF3" s="4" t="n"/>
       <c r="BG3" s="4" t="n"/>
-      <c r="BH3" s="4" t="n"/>
-      <c r="BI3" s="4" t="n"/>
+      <c r="BH3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI3" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ3" s="4" t="n"/>
+      <c r="BK3" s="4" t="n"/>
+      <c r="BL3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n"/>
@@ -50497,9 +50707,19 @@
       <c r="BE4" s="4" t="n"/>
       <c r="BF4" s="4" t="n"/>
       <c r="BG4" s="4" t="n"/>
-      <c r="BH4" s="4" t="n"/>
-      <c r="BI4" s="4" t="n"/>
+      <c r="BH4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI4" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ4" s="4" t="n"/>
+      <c r="BK4" s="4" t="n"/>
+      <c r="BL4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n"/>
@@ -50609,9 +50829,19 @@
       <c r="BE5" s="4" t="n"/>
       <c r="BF5" s="4" t="n"/>
       <c r="BG5" s="4" t="n"/>
-      <c r="BH5" s="4" t="n"/>
-      <c r="BI5" s="4" t="n"/>
+      <c r="BH5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI5" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ5" s="4" t="n"/>
+      <c r="BK5" s="4" t="n"/>
+      <c r="BL5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -50705,9 +50935,19 @@
       <c r="BE6" s="4" t="n"/>
       <c r="BF6" s="4" t="n"/>
       <c r="BG6" s="4" t="n"/>
-      <c r="BH6" s="4" t="n"/>
-      <c r="BI6" s="4" t="n"/>
-      <c r="BJ6" s="4" t="inlineStr">
+      <c r="BH6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI6" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BJ6" s="4" t="n"/>
+      <c r="BK6" s="4" t="n"/>
+      <c r="BL6" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -50821,9 +51061,19 @@
       <c r="BE7" s="4" t="n"/>
       <c r="BF7" s="4" t="n"/>
       <c r="BG7" s="4" t="n"/>
-      <c r="BH7" s="4" t="n"/>
-      <c r="BI7" s="4" t="n"/>
+      <c r="BH7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ7" s="4" t="n"/>
+      <c r="BK7" s="4" t="n"/>
+      <c r="BL7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
@@ -50953,9 +51203,19 @@
       <c r="BE8" s="4" t="n"/>
       <c r="BF8" s="4" t="n"/>
       <c r="BG8" s="4" t="n"/>
-      <c r="BH8" s="4" t="n"/>
-      <c r="BI8" s="4" t="n"/>
+      <c r="BH8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI8" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ8" s="4" t="n"/>
+      <c r="BK8" s="4" t="n"/>
+      <c r="BL8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n"/>
@@ -51065,9 +51325,19 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="BH9" s="4" t="n"/>
-      <c r="BI9" s="4" t="n"/>
-      <c r="BJ9" s="4" t="inlineStr">
+      <c r="BH9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI9" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BJ9" s="4" t="n"/>
+      <c r="BK9" s="4" t="n"/>
+      <c r="BL9" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -51189,9 +51459,19 @@
       </c>
       <c r="BF10" s="4" t="n"/>
       <c r="BG10" s="4" t="n"/>
-      <c r="BH10" s="4" t="n"/>
-      <c r="BI10" s="4" t="n"/>
+      <c r="BH10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI10" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ10" s="4" t="n"/>
+      <c r="BK10" s="4" t="n"/>
+      <c r="BL10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
@@ -51289,9 +51569,19 @@
       <c r="BE11" s="4" t="n"/>
       <c r="BF11" s="4" t="n"/>
       <c r="BG11" s="4" t="n"/>
-      <c r="BH11" s="4" t="n"/>
-      <c r="BI11" s="4" t="n"/>
+      <c r="BH11" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI11" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ11" s="4" t="n"/>
+      <c r="BK11" s="4" t="n"/>
+      <c r="BL11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
@@ -51405,9 +51695,19 @@
       </c>
       <c r="BF12" s="4" t="n"/>
       <c r="BG12" s="4" t="n"/>
-      <c r="BH12" s="4" t="n"/>
-      <c r="BI12" s="4" t="n"/>
+      <c r="BH12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI12" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ12" s="4" t="n"/>
+      <c r="BK12" s="4" t="n"/>
+      <c r="BL12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
@@ -51509,9 +51809,19 @@
       <c r="BE13" s="4" t="n"/>
       <c r="BF13" s="4" t="n"/>
       <c r="BG13" s="4" t="n"/>
-      <c r="BH13" s="4" t="n"/>
-      <c r="BI13" s="4" t="n"/>
+      <c r="BH13" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI13" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ13" s="4" t="n"/>
+      <c r="BK13" s="4" t="n"/>
+      <c r="BL13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -51633,9 +51943,19 @@
       <c r="BE14" s="4" t="n"/>
       <c r="BF14" s="4" t="n"/>
       <c r="BG14" s="4" t="n"/>
-      <c r="BH14" s="4" t="n"/>
-      <c r="BI14" s="4" t="n"/>
+      <c r="BH14" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI14" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ14" s="4" t="n"/>
+      <c r="BK14" s="4" t="n"/>
+      <c r="BL14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
@@ -51761,9 +52081,19 @@
       <c r="BE15" s="4" t="n"/>
       <c r="BF15" s="4" t="n"/>
       <c r="BG15" s="4" t="n"/>
-      <c r="BH15" s="4" t="n"/>
-      <c r="BI15" s="4" t="n"/>
+      <c r="BH15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI15" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ15" s="4" t="n"/>
+      <c r="BK15" s="4" t="n"/>
+      <c r="BL15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
@@ -51877,9 +52207,19 @@
       <c r="BE16" s="4" t="n"/>
       <c r="BF16" s="4" t="n"/>
       <c r="BG16" s="4" t="n"/>
-      <c r="BH16" s="4" t="n"/>
-      <c r="BI16" s="4" t="n"/>
+      <c r="BH16" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI16" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ16" s="4" t="n"/>
+      <c r="BK16" s="4" t="n"/>
+      <c r="BL16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
@@ -51993,9 +52333,19 @@
       <c r="BE17" s="4" t="n"/>
       <c r="BF17" s="4" t="n"/>
       <c r="BG17" s="4" t="n"/>
-      <c r="BH17" s="4" t="n"/>
-      <c r="BI17" s="4" t="n"/>
+      <c r="BH17" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI17" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ17" s="4" t="n"/>
+      <c r="BK17" s="4" t="n"/>
+      <c r="BL17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -52109,9 +52459,19 @@
       </c>
       <c r="BF18" s="4" t="n"/>
       <c r="BG18" s="4" t="n"/>
-      <c r="BH18" s="4" t="n"/>
-      <c r="BI18" s="4" t="n"/>
+      <c r="BH18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI18" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ18" s="4" t="n"/>
+      <c r="BK18" s="4" t="n"/>
+      <c r="BL18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
@@ -52225,9 +52585,19 @@
       <c r="BE19" s="4" t="n"/>
       <c r="BF19" s="4" t="n"/>
       <c r="BG19" s="4" t="n"/>
-      <c r="BH19" s="4" t="n"/>
-      <c r="BI19" s="4" t="n"/>
+      <c r="BH19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI19" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ19" s="4" t="n"/>
+      <c r="BK19" s="4" t="n"/>
+      <c r="BL19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
@@ -52333,9 +52703,19 @@
       <c r="BE20" s="4" t="n"/>
       <c r="BF20" s="4" t="n"/>
       <c r="BG20" s="4" t="n"/>
-      <c r="BH20" s="4" t="n"/>
-      <c r="BI20" s="4" t="n"/>
-      <c r="BJ20" s="4" t="inlineStr">
+      <c r="BH20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BJ20" s="4" t="n"/>
+      <c r="BK20" s="4" t="n"/>
+      <c r="BL20" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -52437,9 +52817,19 @@
       <c r="BE21" s="4" t="n"/>
       <c r="BF21" s="4" t="n"/>
       <c r="BG21" s="4" t="n"/>
-      <c r="BH21" s="4" t="n"/>
-      <c r="BI21" s="4" t="n"/>
+      <c r="BH21" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI21" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ21" s="4" t="n"/>
+      <c r="BK21" s="4" t="n"/>
+      <c r="BL21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -52545,9 +52935,19 @@
       <c r="BE22" s="4" t="n"/>
       <c r="BF22" s="4" t="n"/>
       <c r="BG22" s="4" t="n"/>
-      <c r="BH22" s="4" t="n"/>
-      <c r="BI22" s="4" t="n"/>
+      <c r="BH22" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI22" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ22" s="4" t="n"/>
+      <c r="BK22" s="4" t="n"/>
+      <c r="BL22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
@@ -52649,9 +53049,19 @@
       <c r="BE23" s="4" t="n"/>
       <c r="BF23" s="4" t="n"/>
       <c r="BG23" s="4" t="n"/>
-      <c r="BH23" s="4" t="n"/>
-      <c r="BI23" s="4" t="n"/>
+      <c r="BH23" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI23" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ23" s="4" t="n"/>
+      <c r="BK23" s="4" t="n"/>
+      <c r="BL23" s="4" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
@@ -52761,9 +53171,19 @@
       <c r="BE24" s="4" t="n"/>
       <c r="BF24" s="4" t="n"/>
       <c r="BG24" s="4" t="n"/>
-      <c r="BH24" s="4" t="n"/>
-      <c r="BI24" s="4" t="n"/>
+      <c r="BH24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI24" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ24" s="4" t="n"/>
+      <c r="BK24" s="4" t="n"/>
+      <c r="BL24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
@@ -52857,9 +53277,19 @@
       <c r="BE25" s="4" t="n"/>
       <c r="BF25" s="4" t="n"/>
       <c r="BG25" s="4" t="n"/>
-      <c r="BH25" s="4" t="n"/>
-      <c r="BI25" s="4" t="n"/>
-      <c r="BJ25" s="4" t="inlineStr">
+      <c r="BH25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI25" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BJ25" s="4" t="n"/>
+      <c r="BK25" s="4" t="n"/>
+      <c r="BL25" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -52981,9 +53411,19 @@
       <c r="BE26" s="4" t="n"/>
       <c r="BF26" s="4" t="n"/>
       <c r="BG26" s="4" t="n"/>
-      <c r="BH26" s="4" t="n"/>
-      <c r="BI26" s="4" t="n"/>
+      <c r="BH26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI26" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ26" s="4" t="n"/>
+      <c r="BK26" s="4" t="n"/>
+      <c r="BL26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n"/>
@@ -53089,9 +53529,19 @@
       <c r="BE27" s="4" t="n"/>
       <c r="BF27" s="4" t="n"/>
       <c r="BG27" s="4" t="n"/>
-      <c r="BH27" s="4" t="n"/>
-      <c r="BI27" s="4" t="n"/>
+      <c r="BH27" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI27" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ27" s="4" t="n"/>
+      <c r="BK27" s="4" t="n"/>
+      <c r="BL27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
@@ -53197,9 +53647,19 @@
       <c r="BE28" s="4" t="n"/>
       <c r="BF28" s="4" t="n"/>
       <c r="BG28" s="4" t="n"/>
-      <c r="BH28" s="4" t="n"/>
-      <c r="BI28" s="4" t="n"/>
+      <c r="BH28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI28" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ28" s="4" t="n"/>
+      <c r="BK28" s="4" t="n"/>
+      <c r="BL28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n"/>
@@ -53301,9 +53761,19 @@
       <c r="BE29" s="4" t="n"/>
       <c r="BF29" s="4" t="n"/>
       <c r="BG29" s="4" t="n"/>
-      <c r="BH29" s="4" t="n"/>
-      <c r="BI29" s="4" t="n"/>
+      <c r="BH29" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI29" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ29" s="4" t="n"/>
+      <c r="BK29" s="4" t="n"/>
+      <c r="BL29" s="4" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -53405,9 +53875,19 @@
       <c r="BE30" s="4" t="n"/>
       <c r="BF30" s="4" t="n"/>
       <c r="BG30" s="4" t="n"/>
-      <c r="BH30" s="4" t="n"/>
-      <c r="BI30" s="4" t="n"/>
-      <c r="BJ30" s="4" t="inlineStr">
+      <c r="BH30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BJ30" s="4" t="n"/>
+      <c r="BK30" s="4" t="n"/>
+      <c r="BL30" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -53513,9 +53993,19 @@
       </c>
       <c r="BF31" s="4" t="n"/>
       <c r="BG31" s="4" t="n"/>
-      <c r="BH31" s="4" t="n"/>
-      <c r="BI31" s="4" t="n"/>
-      <c r="BJ31" s="4" t="inlineStr">
+      <c r="BH31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI31" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BJ31" s="4" t="n"/>
+      <c r="BK31" s="4" t="n"/>
+      <c r="BL31" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -53637,9 +54127,19 @@
         </is>
       </c>
       <c r="BG32" s="4" t="n"/>
-      <c r="BH32" s="4" t="n"/>
-      <c r="BI32" s="4" t="n"/>
-      <c r="BJ32" s="4" t="inlineStr">
+      <c r="BH32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI32" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BJ32" s="4" t="n"/>
+      <c r="BK32" s="4" t="n"/>
+      <c r="BL32" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -53745,9 +54245,19 @@
       <c r="BE33" s="4" t="n"/>
       <c r="BF33" s="4" t="n"/>
       <c r="BG33" s="4" t="n"/>
-      <c r="BH33" s="4" t="n"/>
-      <c r="BI33" s="4" t="n"/>
-      <c r="BJ33" s="4" t="inlineStr">
+      <c r="BH33" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI33" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BJ33" s="4" t="n"/>
+      <c r="BK33" s="4" t="n"/>
+      <c r="BL33" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -53865,9 +54375,19 @@
       <c r="BE34" s="4" t="n"/>
       <c r="BF34" s="4" t="n"/>
       <c r="BG34" s="4" t="n"/>
-      <c r="BH34" s="4" t="n"/>
-      <c r="BI34" s="4" t="n"/>
-      <c r="BJ34" s="4" t="inlineStr">
+      <c r="BH34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BJ34" s="4" t="n"/>
+      <c r="BK34" s="4" t="n"/>
+      <c r="BL34" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -53973,9 +54493,19 @@
         </is>
       </c>
       <c r="BG35" s="4" t="n"/>
-      <c r="BH35" s="4" t="n"/>
-      <c r="BI35" s="4" t="n"/>
-      <c r="BJ35" s="4" t="inlineStr">
+      <c r="BH35" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI35" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BJ35" s="4" t="n"/>
+      <c r="BK35" s="4" t="n"/>
+      <c r="BL35" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -54085,9 +54615,19 @@
       <c r="BE36" s="4" t="n"/>
       <c r="BF36" s="4" t="n"/>
       <c r="BG36" s="4" t="n"/>
-      <c r="BH36" s="4" t="n"/>
-      <c r="BI36" s="4" t="n"/>
+      <c r="BH36" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI36" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ36" s="4" t="n"/>
+      <c r="BK36" s="4" t="n"/>
+      <c r="BL36" s="4" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -54209,9 +54749,19 @@
         </is>
       </c>
       <c r="BG37" s="4" t="n"/>
-      <c r="BH37" s="4" t="n"/>
-      <c r="BI37" s="4" t="n"/>
-      <c r="BJ37" s="4" t="inlineStr">
+      <c r="BH37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI37" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BJ37" s="4" t="n"/>
+      <c r="BK37" s="4" t="n"/>
+      <c r="BL37" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -54329,9 +54879,19 @@
         </is>
       </c>
       <c r="BG38" s="4" t="n"/>
-      <c r="BH38" s="4" t="n"/>
-      <c r="BI38" s="4" t="n"/>
+      <c r="BH38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI38" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ38" s="4" t="n"/>
+      <c r="BK38" s="4" t="n"/>
+      <c r="BL38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n"/>
@@ -54441,9 +55001,19 @@
         </is>
       </c>
       <c r="BG39" s="4" t="n"/>
-      <c r="BH39" s="4" t="n"/>
-      <c r="BI39" s="4" t="n"/>
+      <c r="BH39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI39" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ39" s="4" t="n"/>
+      <c r="BK39" s="4" t="n"/>
+      <c r="BL39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n"/>
@@ -54569,9 +55139,19 @@
         </is>
       </c>
       <c r="BG40" s="4" t="n"/>
-      <c r="BH40" s="4" t="n"/>
-      <c r="BI40" s="4" t="n"/>
+      <c r="BH40" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI40" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ40" s="4" t="n"/>
+      <c r="BK40" s="4" t="n"/>
+      <c r="BL40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -54669,9 +55249,19 @@
       <c r="BE41" s="4" t="n"/>
       <c r="BF41" s="4" t="n"/>
       <c r="BG41" s="4" t="n"/>
-      <c r="BH41" s="4" t="n"/>
-      <c r="BI41" s="4" t="n"/>
+      <c r="BH41" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI41" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ41" s="4" t="n"/>
+      <c r="BK41" s="4" t="n"/>
+      <c r="BL41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n"/>
@@ -54781,9 +55371,19 @@
       <c r="BE42" s="4" t="n"/>
       <c r="BF42" s="4" t="n"/>
       <c r="BG42" s="4" t="n"/>
-      <c r="BH42" s="4" t="n"/>
-      <c r="BI42" s="4" t="n"/>
+      <c r="BH42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI42" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ42" s="4" t="n"/>
+      <c r="BK42" s="4" t="n"/>
+      <c r="BL42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n"/>
@@ -54885,9 +55485,19 @@
       <c r="BE43" s="4" t="n"/>
       <c r="BF43" s="4" t="n"/>
       <c r="BG43" s="4" t="n"/>
-      <c r="BH43" s="4" t="n"/>
-      <c r="BI43" s="4" t="n"/>
+      <c r="BH43" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI43" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ43" s="4" t="n"/>
+      <c r="BK43" s="4" t="n"/>
+      <c r="BL43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n"/>
@@ -54985,9 +55595,19 @@
       </c>
       <c r="BF44" s="4" t="n"/>
       <c r="BG44" s="4" t="n"/>
-      <c r="BH44" s="4" t="n"/>
-      <c r="BI44" s="4" t="n"/>
+      <c r="BH44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI44" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ44" s="4" t="n"/>
+      <c r="BK44" s="4" t="n"/>
+      <c r="BL44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -55109,9 +55729,19 @@
       <c r="BE45" s="4" t="n"/>
       <c r="BF45" s="4" t="n"/>
       <c r="BG45" s="4" t="n"/>
-      <c r="BH45" s="4" t="n"/>
-      <c r="BI45" s="4" t="n"/>
+      <c r="BH45" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI45" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ45" s="4" t="n"/>
+      <c r="BK45" s="4" t="n"/>
+      <c r="BL45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n"/>
@@ -55233,9 +55863,19 @@
       <c r="BE46" s="4" t="n"/>
       <c r="BF46" s="4" t="n"/>
       <c r="BG46" s="4" t="n"/>
-      <c r="BH46" s="4" t="n"/>
-      <c r="BI46" s="4" t="n"/>
+      <c r="BH46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI46" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ46" s="4" t="n"/>
+      <c r="BK46" s="4" t="n"/>
+      <c r="BL46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n"/>
@@ -55353,9 +55993,19 @@
       <c r="BE47" s="4" t="n"/>
       <c r="BF47" s="4" t="n"/>
       <c r="BG47" s="4" t="n"/>
-      <c r="BH47" s="4" t="n"/>
-      <c r="BI47" s="4" t="n"/>
+      <c r="BH47" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI47" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ47" s="4" t="n"/>
+      <c r="BK47" s="4" t="n"/>
+      <c r="BL47" s="4" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n"/>
@@ -55477,9 +56127,19 @@
       <c r="BE48" s="4" t="n"/>
       <c r="BF48" s="4" t="n"/>
       <c r="BG48" s="4" t="n"/>
-      <c r="BH48" s="4" t="n"/>
-      <c r="BI48" s="4" t="n"/>
+      <c r="BH48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI48" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ48" s="4" t="n"/>
+      <c r="BK48" s="4" t="n"/>
+      <c r="BL48" s="4" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -55581,9 +56241,19 @@
         </is>
       </c>
       <c r="BG49" s="4" t="n"/>
-      <c r="BH49" s="4" t="n"/>
-      <c r="BI49" s="4" t="n"/>
-      <c r="BJ49" s="4" t="inlineStr">
+      <c r="BH49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI49" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BJ49" s="4" t="n"/>
+      <c r="BK49" s="4" t="n"/>
+      <c r="BL49" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -55686,8 +56356,18 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="BI50" s="4" t="n"/>
+      <c r="BI50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ50" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BK50" s="4" t="n"/>
+      <c r="BL50" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -55801,9 +56481,19 @@
       <c r="BE51" s="4" t="n"/>
       <c r="BF51" s="4" t="n"/>
       <c r="BG51" s="4" t="n"/>
-      <c r="BH51" s="4" t="n"/>
-      <c r="BI51" s="4" t="n"/>
+      <c r="BH51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI51" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ51" s="4" t="n"/>
+      <c r="BK51" s="4" t="n"/>
+      <c r="BL51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n"/>
@@ -55925,9 +56615,19 @@
       <c r="BE52" s="4" t="n"/>
       <c r="BF52" s="4" t="n"/>
       <c r="BG52" s="4" t="n"/>
-      <c r="BH52" s="4" t="n"/>
-      <c r="BI52" s="4" t="n"/>
+      <c r="BH52" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI52" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ52" s="4" t="n"/>
+      <c r="BK52" s="4" t="n"/>
+      <c r="BL52" s="4" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -56033,9 +56733,19 @@
       <c r="BE53" s="4" t="n"/>
       <c r="BF53" s="4" t="n"/>
       <c r="BG53" s="4" t="n"/>
-      <c r="BH53" s="4" t="n"/>
-      <c r="BI53" s="4" t="n"/>
+      <c r="BH53" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI53" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ53" s="4" t="n"/>
+      <c r="BK53" s="4" t="n"/>
+      <c r="BL53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n"/>
@@ -56153,9 +56863,19 @@
       <c r="BE54" s="4" t="n"/>
       <c r="BF54" s="4" t="n"/>
       <c r="BG54" s="4" t="n"/>
-      <c r="BH54" s="4" t="n"/>
-      <c r="BI54" s="4" t="n"/>
+      <c r="BH54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI54" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ54" s="4" t="n"/>
+      <c r="BK54" s="4" t="n"/>
+      <c r="BL54" s="4" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n"/>
@@ -56253,9 +56973,19 @@
       <c r="BE55" s="4" t="n"/>
       <c r="BF55" s="4" t="n"/>
       <c r="BG55" s="4" t="n"/>
-      <c r="BH55" s="4" t="n"/>
-      <c r="BI55" s="4" t="n"/>
-      <c r="BJ55" s="4" t="inlineStr">
+      <c r="BH55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI55" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BJ55" s="4" t="n"/>
+      <c r="BK55" s="4" t="n"/>
+      <c r="BL55" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -56357,9 +57087,19 @@
       <c r="BE56" s="4" t="n"/>
       <c r="BF56" s="4" t="n"/>
       <c r="BG56" s="4" t="n"/>
-      <c r="BH56" s="4" t="n"/>
-      <c r="BI56" s="4" t="n"/>
+      <c r="BH56" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI56" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ56" s="4" t="n"/>
+      <c r="BK56" s="4" t="n"/>
+      <c r="BL56" s="4" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -56485,9 +57225,19 @@
       <c r="BE57" s="4" t="n"/>
       <c r="BF57" s="4" t="n"/>
       <c r="BG57" s="4" t="n"/>
-      <c r="BH57" s="4" t="n"/>
-      <c r="BI57" s="4" t="n"/>
+      <c r="BH57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ57" s="4" t="n"/>
+      <c r="BK57" s="4" t="n"/>
+      <c r="BL57" s="4" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="n"/>
@@ -56589,9 +57339,19 @@
       <c r="BE58" s="4" t="n"/>
       <c r="BF58" s="4" t="n"/>
       <c r="BG58" s="4" t="n"/>
-      <c r="BH58" s="4" t="n"/>
-      <c r="BI58" s="4" t="n"/>
+      <c r="BH58" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI58" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ58" s="4" t="n"/>
+      <c r="BK58" s="4" t="n"/>
+      <c r="BL58" s="4" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n"/>
@@ -56693,9 +57453,19 @@
       <c r="BE59" s="4" t="n"/>
       <c r="BF59" s="4" t="n"/>
       <c r="BG59" s="4" t="n"/>
-      <c r="BH59" s="4" t="n"/>
-      <c r="BI59" s="4" t="n"/>
+      <c r="BH59" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI59" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ59" s="4" t="n"/>
+      <c r="BK59" s="4" t="n"/>
+      <c r="BL59" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n"/>
@@ -56809,9 +57579,19 @@
       <c r="BE60" s="4" t="n"/>
       <c r="BF60" s="4" t="n"/>
       <c r="BG60" s="4" t="n"/>
-      <c r="BH60" s="4" t="n"/>
-      <c r="BI60" s="4" t="n"/>
+      <c r="BH60" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI60" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ60" s="4" t="n"/>
+      <c r="BK60" s="4" t="n"/>
+      <c r="BL60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -56933,9 +57713,19 @@
       <c r="BE61" s="4" t="n"/>
       <c r="BF61" s="4" t="n"/>
       <c r="BG61" s="4" t="n"/>
-      <c r="BH61" s="4" t="n"/>
-      <c r="BI61" s="4" t="n"/>
+      <c r="BH61" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI61" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ61" s="4" t="n"/>
+      <c r="BK61" s="4" t="n"/>
+      <c r="BL61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="n"/>
@@ -57045,9 +57835,19 @@
       <c r="BE62" s="4" t="n"/>
       <c r="BF62" s="4" t="n"/>
       <c r="BG62" s="4" t="n"/>
-      <c r="BH62" s="4" t="n"/>
-      <c r="BI62" s="4" t="n"/>
-      <c r="BJ62" s="4" t="inlineStr">
+      <c r="BH62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI62" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BJ62" s="4" t="n"/>
+      <c r="BK62" s="4" t="n"/>
+      <c r="BL62" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -57177,9 +57977,19 @@
       <c r="BE63" s="4" t="n"/>
       <c r="BF63" s="4" t="n"/>
       <c r="BG63" s="4" t="n"/>
-      <c r="BH63" s="4" t="n"/>
-      <c r="BI63" s="4" t="n"/>
+      <c r="BH63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI63" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ63" s="4" t="n"/>
+      <c r="BK63" s="4" t="n"/>
+      <c r="BL63" s="4" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n"/>
@@ -57293,9 +58103,19 @@
       <c r="BE64" s="4" t="n"/>
       <c r="BF64" s="4" t="n"/>
       <c r="BG64" s="4" t="n"/>
-      <c r="BH64" s="4" t="n"/>
-      <c r="BI64" s="4" t="n"/>
+      <c r="BH64" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI64" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ64" s="4" t="n"/>
+      <c r="BK64" s="4" t="n"/>
+      <c r="BL64" s="4" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -57393,9 +58213,19 @@
       <c r="BE65" s="4" t="n"/>
       <c r="BF65" s="4" t="n"/>
       <c r="BG65" s="4" t="n"/>
-      <c r="BH65" s="4" t="n"/>
-      <c r="BI65" s="4" t="n"/>
+      <c r="BH65" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI65" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ65" s="4" t="n"/>
+      <c r="BK65" s="4" t="n"/>
+      <c r="BL65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="n"/>
@@ -57497,9 +58327,19 @@
       <c r="BE66" s="4" t="n"/>
       <c r="BF66" s="4" t="n"/>
       <c r="BG66" s="4" t="n"/>
-      <c r="BH66" s="4" t="n"/>
-      <c r="BI66" s="4" t="n"/>
+      <c r="BH66" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI66" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ66" s="4" t="n"/>
+      <c r="BK66" s="4" t="n"/>
+      <c r="BL66" s="4" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n"/>
@@ -57625,9 +58465,19 @@
       </c>
       <c r="BF67" s="4" t="n"/>
       <c r="BG67" s="4" t="n"/>
-      <c r="BH67" s="4" t="n"/>
-      <c r="BI67" s="4" t="n"/>
+      <c r="BH67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI67" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ67" s="4" t="n"/>
+      <c r="BK67" s="4" t="n"/>
+      <c r="BL67" s="4" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n"/>
@@ -57725,9 +58575,19 @@
       <c r="BE68" s="4" t="n"/>
       <c r="BF68" s="4" t="n"/>
       <c r="BG68" s="4" t="n"/>
-      <c r="BH68" s="4" t="n"/>
-      <c r="BI68" s="4" t="n"/>
+      <c r="BH68" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI68" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ68" s="4" t="n"/>
+      <c r="BK68" s="4" t="n"/>
+      <c r="BL68" s="4" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -57829,9 +58689,19 @@
       <c r="BE69" s="4" t="n"/>
       <c r="BF69" s="4" t="n"/>
       <c r="BG69" s="4" t="n"/>
-      <c r="BH69" s="4" t="n"/>
-      <c r="BI69" s="4" t="n"/>
+      <c r="BH69" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI69" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ69" s="4" t="n"/>
+      <c r="BK69" s="4" t="n"/>
+      <c r="BL69" s="4" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="n"/>
@@ -57933,9 +58803,19 @@
         </is>
       </c>
       <c r="BG70" s="4" t="n"/>
-      <c r="BH70" s="4" t="n"/>
-      <c r="BI70" s="4" t="n"/>
+      <c r="BH70" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI70" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ70" s="4" t="n"/>
+      <c r="BK70" s="4" t="n"/>
+      <c r="BL70" s="4" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n"/>
@@ -58029,9 +58909,19 @@
       <c r="BE71" s="4" t="n"/>
       <c r="BF71" s="4" t="n"/>
       <c r="BG71" s="4" t="n"/>
-      <c r="BH71" s="4" t="n"/>
-      <c r="BI71" s="4" t="n"/>
+      <c r="BH71" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI71" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ71" s="4" t="n"/>
+      <c r="BK71" s="4" t="n"/>
+      <c r="BL71" s="4" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n"/>
@@ -58137,9 +59027,19 @@
       <c r="BE72" s="4" t="n"/>
       <c r="BF72" s="4" t="n"/>
       <c r="BG72" s="4" t="n"/>
-      <c r="BH72" s="4" t="n"/>
-      <c r="BI72" s="4" t="n"/>
+      <c r="BH72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI72" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ72" s="4" t="n"/>
+      <c r="BK72" s="4" t="n"/>
+      <c r="BL72" s="4" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -58249,9 +59149,19 @@
       <c r="BE73" s="4" t="n"/>
       <c r="BF73" s="4" t="n"/>
       <c r="BG73" s="4" t="n"/>
-      <c r="BH73" s="4" t="n"/>
-      <c r="BI73" s="4" t="n"/>
-      <c r="BJ73" s="4" t="inlineStr">
+      <c r="BH73" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI73" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BJ73" s="4" t="n"/>
+      <c r="BK73" s="4" t="n"/>
+      <c r="BL73" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -58369,9 +59279,19 @@
       <c r="BE74" s="4" t="n"/>
       <c r="BF74" s="4" t="n"/>
       <c r="BG74" s="4" t="n"/>
-      <c r="BH74" s="4" t="n"/>
-      <c r="BI74" s="4" t="n"/>
+      <c r="BH74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI74" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ74" s="4" t="n"/>
+      <c r="BK74" s="4" t="n"/>
+      <c r="BL74" s="4" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n"/>
@@ -58481,9 +59401,19 @@
       <c r="BE75" s="4" t="n"/>
       <c r="BF75" s="4" t="n"/>
       <c r="BG75" s="4" t="n"/>
-      <c r="BH75" s="4" t="n"/>
-      <c r="BI75" s="4" t="n"/>
+      <c r="BH75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI75" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ75" s="4" t="n"/>
+      <c r="BK75" s="4" t="n"/>
+      <c r="BL75" s="4" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="n"/>
@@ -58588,6 +59518,16 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="BK76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BL76" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -58697,9 +59637,19 @@
       <c r="BE77" s="4" t="n"/>
       <c r="BF77" s="4" t="n"/>
       <c r="BG77" s="4" t="n"/>
-      <c r="BH77" s="4" t="n"/>
-      <c r="BI77" s="4" t="n"/>
+      <c r="BH77" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI77" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ77" s="4" t="n"/>
+      <c r="BK77" s="4" t="n"/>
+      <c r="BL77" s="4" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="n"/>
@@ -58805,9 +59755,19 @@
       <c r="BE78" s="4" t="n"/>
       <c r="BF78" s="4" t="n"/>
       <c r="BG78" s="4" t="n"/>
-      <c r="BH78" s="4" t="n"/>
-      <c r="BI78" s="4" t="n"/>
+      <c r="BH78" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI78" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ78" s="4" t="n"/>
+      <c r="BK78" s="4" t="n"/>
+      <c r="BL78" s="4" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n"/>
@@ -58917,9 +59877,19 @@
       <c r="BE79" s="4" t="n"/>
       <c r="BF79" s="4" t="n"/>
       <c r="BG79" s="4" t="n"/>
-      <c r="BH79" s="4" t="n"/>
-      <c r="BI79" s="4" t="n"/>
+      <c r="BH79" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI79" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ79" s="4" t="n"/>
+      <c r="BK79" s="4" t="n"/>
+      <c r="BL79" s="4" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="n"/>
@@ -59021,9 +59991,19 @@
       <c r="BE80" s="4" t="n"/>
       <c r="BF80" s="4" t="n"/>
       <c r="BG80" s="4" t="n"/>
-      <c r="BH80" s="4" t="n"/>
-      <c r="BI80" s="4" t="n"/>
+      <c r="BH80" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI80" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ80" s="4" t="n"/>
+      <c r="BK80" s="4" t="n"/>
+      <c r="BL80" s="4" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
@@ -59113,9 +60093,19 @@
       <c r="BE81" s="4" t="n"/>
       <c r="BF81" s="4" t="n"/>
       <c r="BG81" s="4" t="n"/>
-      <c r="BH81" s="4" t="n"/>
-      <c r="BI81" s="4" t="n"/>
+      <c r="BH81" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI81" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ81" s="4" t="n"/>
+      <c r="BK81" s="4" t="n"/>
+      <c r="BL81" s="4" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="n"/>
@@ -59205,9 +60195,19 @@
       <c r="BE82" s="4" t="n"/>
       <c r="BF82" s="4" t="n"/>
       <c r="BG82" s="4" t="n"/>
-      <c r="BH82" s="4" t="n"/>
-      <c r="BI82" s="4" t="n"/>
+      <c r="BH82" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI82" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ82" s="4" t="n"/>
+      <c r="BK82" s="4" t="n"/>
+      <c r="BL82" s="4" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n"/>
@@ -59293,9 +60293,19 @@
       <c r="BE83" s="4" t="n"/>
       <c r="BF83" s="4" t="n"/>
       <c r="BG83" s="4" t="n"/>
-      <c r="BH83" s="4" t="n"/>
-      <c r="BI83" s="4" t="n"/>
+      <c r="BH83" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI83" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ83" s="4" t="n"/>
+      <c r="BK83" s="4" t="n"/>
+      <c r="BL83" s="4" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="n"/>
@@ -59393,12 +60403,22 @@
       <c r="BE84" s="4" t="n"/>
       <c r="BF84" s="4" t="n"/>
       <c r="BG84" s="4" t="n"/>
-      <c r="BH84" s="4" t="n"/>
-      <c r="BI84" s="4" t="n"/>
+      <c r="BH84" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="BI84" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="BJ84" s="4" t="n"/>
+      <c r="BK84" s="4" t="n"/>
+      <c r="BL84" s="4" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BJ84"/>
+  <autoFilter ref="A1:BL84"/>
   <mergeCells count="21">
     <mergeCell ref="A61:A64"/>
     <mergeCell ref="A69:A72"/>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -26,8 +26,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'五区_普通'!$A$1:$CK$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'五区_自动'!$A$1:$U$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'四区_理论'!$A$1:$AU$84</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'四区_高手'!$A$1:$BL$84</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'四区_普通'!$A$1:$BL$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'四区_高手'!$A$1:$BJ$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'四区_普通'!$A$1:$BJ$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'四区_自动'!$A$1:$P$84</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'五区_理论_特殊跑法'!$A$1:$AO$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'五区_高手_特殊跑法'!$A$1:$T$21</definedName>
@@ -42904,7 +42904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL84"/>
+  <dimension ref="A1:BJ84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -42969,8 +42969,6 @@
     <col width="7.5" customWidth="1" min="60" max="60"/>
     <col width="7.5" customWidth="1" min="61" max="61"/>
     <col width="7.5" customWidth="1" min="62" max="62"/>
-    <col width="7.5" customWidth="1" min="63" max="63"/>
-    <col width="7.5" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -43271,25 +43269,15 @@
       </c>
       <c r="BH1" s="1" t="inlineStr">
         <is>
-          <t>dose★3</t>
+          <t>风扇★5</t>
         </is>
       </c>
       <c r="BI1" s="1" t="inlineStr">
         <is>
-          <t>dose★4</t>
+          <t>600lt★5</t>
         </is>
       </c>
       <c r="BJ1" s="1" t="inlineStr">
-        <is>
-          <t>风扇★5</t>
-        </is>
-      </c>
-      <c r="BK1" s="1" t="inlineStr">
-        <is>
-          <t>600lt★5</t>
-        </is>
-      </c>
-      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>5n★4</t>
         </is>
@@ -43372,8 +43360,6 @@
       <c r="BH2" s="4" t="n"/>
       <c r="BI2" s="4" t="n"/>
       <c r="BJ2" s="4" t="n"/>
-      <c r="BK2" s="4" t="n"/>
-      <c r="BL2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n"/>
@@ -43450,8 +43436,6 @@
       <c r="BH3" s="4" t="n"/>
       <c r="BI3" s="4" t="n"/>
       <c r="BJ3" s="4" t="n"/>
-      <c r="BK3" s="4" t="n"/>
-      <c r="BL3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n"/>
@@ -43526,8 +43510,6 @@
       <c r="BH4" s="4" t="n"/>
       <c r="BI4" s="4" t="n"/>
       <c r="BJ4" s="4" t="n"/>
-      <c r="BK4" s="4" t="n"/>
-      <c r="BL4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n"/>
@@ -43608,8 +43590,6 @@
       <c r="BH5" s="4" t="n"/>
       <c r="BI5" s="4" t="n"/>
       <c r="BJ5" s="4" t="n"/>
-      <c r="BK5" s="4" t="n"/>
-      <c r="BL5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -43684,8 +43664,6 @@
       <c r="BH6" s="4" t="n"/>
       <c r="BI6" s="4" t="n"/>
       <c r="BJ6" s="4" t="n"/>
-      <c r="BK6" s="4" t="n"/>
-      <c r="BL6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
@@ -43758,8 +43736,6 @@
       <c r="BH7" s="4" t="n"/>
       <c r="BI7" s="4" t="n"/>
       <c r="BJ7" s="4" t="n"/>
-      <c r="BK7" s="4" t="n"/>
-      <c r="BL7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
@@ -43848,8 +43824,6 @@
       <c r="BH8" s="4" t="n"/>
       <c r="BI8" s="4" t="n"/>
       <c r="BJ8" s="4" t="n"/>
-      <c r="BK8" s="4" t="n"/>
-      <c r="BL8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n"/>
@@ -43924,8 +43898,6 @@
       <c r="BH9" s="4" t="n"/>
       <c r="BI9" s="4" t="n"/>
       <c r="BJ9" s="4" t="n"/>
-      <c r="BK9" s="4" t="n"/>
-      <c r="BL9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -44006,8 +43978,6 @@
       <c r="BH10" s="4" t="n"/>
       <c r="BI10" s="4" t="n"/>
       <c r="BJ10" s="4" t="n"/>
-      <c r="BK10" s="4" t="n"/>
-      <c r="BL10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
@@ -44084,8 +44054,6 @@
       <c r="BH11" s="4" t="n"/>
       <c r="BI11" s="4" t="n"/>
       <c r="BJ11" s="4" t="n"/>
-      <c r="BK11" s="4" t="n"/>
-      <c r="BL11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
@@ -44168,8 +44136,6 @@
       <c r="BH12" s="4" t="n"/>
       <c r="BI12" s="4" t="n"/>
       <c r="BJ12" s="4" t="n"/>
-      <c r="BK12" s="4" t="n"/>
-      <c r="BL12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
@@ -44244,8 +44210,6 @@
       <c r="BH13" s="4" t="n"/>
       <c r="BI13" s="4" t="n"/>
       <c r="BJ13" s="4" t="n"/>
-      <c r="BK13" s="4" t="n"/>
-      <c r="BL13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -44332,8 +44296,6 @@
       <c r="BH14" s="4" t="n"/>
       <c r="BI14" s="4" t="n"/>
       <c r="BJ14" s="4" t="n"/>
-      <c r="BK14" s="4" t="n"/>
-      <c r="BL14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
@@ -44416,8 +44378,6 @@
       <c r="BH15" s="4" t="n"/>
       <c r="BI15" s="4" t="n"/>
       <c r="BJ15" s="4" t="n"/>
-      <c r="BK15" s="4" t="n"/>
-      <c r="BL15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
@@ -44502,8 +44462,6 @@
       <c r="BH16" s="4" t="n"/>
       <c r="BI16" s="4" t="n"/>
       <c r="BJ16" s="4" t="n"/>
-      <c r="BK16" s="4" t="n"/>
-      <c r="BL16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
@@ -44578,8 +44536,6 @@
       <c r="BH17" s="4" t="n"/>
       <c r="BI17" s="4" t="n"/>
       <c r="BJ17" s="4" t="n"/>
-      <c r="BK17" s="4" t="n"/>
-      <c r="BL17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -44658,8 +44614,6 @@
       <c r="BH18" s="4" t="n"/>
       <c r="BI18" s="4" t="n"/>
       <c r="BJ18" s="4" t="n"/>
-      <c r="BK18" s="4" t="n"/>
-      <c r="BL18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
@@ -44738,8 +44692,6 @@
       <c r="BH19" s="4" t="n"/>
       <c r="BI19" s="4" t="n"/>
       <c r="BJ19" s="4" t="n"/>
-      <c r="BK19" s="4" t="n"/>
-      <c r="BL19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
@@ -44816,8 +44768,6 @@
       <c r="BH20" s="4" t="n"/>
       <c r="BI20" s="4" t="n"/>
       <c r="BJ20" s="4" t="n"/>
-      <c r="BK20" s="4" t="n"/>
-      <c r="BL20" s="4" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
@@ -44890,8 +44840,6 @@
       <c r="BH21" s="4" t="n"/>
       <c r="BI21" s="4" t="n"/>
       <c r="BJ21" s="4" t="n"/>
-      <c r="BK21" s="4" t="n"/>
-      <c r="BL21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -44970,8 +44918,6 @@
       <c r="BH22" s="4" t="n"/>
       <c r="BI22" s="4" t="n"/>
       <c r="BJ22" s="4" t="n"/>
-      <c r="BK22" s="4" t="n"/>
-      <c r="BL22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
@@ -45050,8 +44996,6 @@
       <c r="BH23" s="4" t="n"/>
       <c r="BI23" s="4" t="n"/>
       <c r="BJ23" s="4" t="n"/>
-      <c r="BK23" s="4" t="n"/>
-      <c r="BL23" s="4" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
@@ -45130,8 +45074,6 @@
       <c r="BH24" s="4" t="n"/>
       <c r="BI24" s="4" t="n"/>
       <c r="BJ24" s="4" t="n"/>
-      <c r="BK24" s="4" t="n"/>
-      <c r="BL24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
@@ -45210,8 +45152,6 @@
       <c r="BH25" s="4" t="n"/>
       <c r="BI25" s="4" t="n"/>
       <c r="BJ25" s="4" t="n"/>
-      <c r="BK25" s="4" t="n"/>
-      <c r="BL25" s="4" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -45294,8 +45234,6 @@
       <c r="BH26" s="4" t="n"/>
       <c r="BI26" s="4" t="n"/>
       <c r="BJ26" s="4" t="n"/>
-      <c r="BK26" s="4" t="n"/>
-      <c r="BL26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n"/>
@@ -45372,8 +45310,6 @@
       <c r="BH27" s="4" t="n"/>
       <c r="BI27" s="4" t="n"/>
       <c r="BJ27" s="4" t="n"/>
-      <c r="BK27" s="4" t="n"/>
-      <c r="BL27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
@@ -45454,8 +45390,6 @@
       <c r="BH28" s="4" t="n"/>
       <c r="BI28" s="4" t="n"/>
       <c r="BJ28" s="4" t="n"/>
-      <c r="BK28" s="4" t="n"/>
-      <c r="BL28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n"/>
@@ -45532,8 +45466,6 @@
       <c r="BH29" s="4" t="n"/>
       <c r="BI29" s="4" t="n"/>
       <c r="BJ29" s="4" t="n"/>
-      <c r="BK29" s="4" t="n"/>
-      <c r="BL29" s="4" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -45610,8 +45542,6 @@
       <c r="BH30" s="4" t="n"/>
       <c r="BI30" s="4" t="n"/>
       <c r="BJ30" s="4" t="n"/>
-      <c r="BK30" s="4" t="n"/>
-      <c r="BL30" s="4" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n"/>
@@ -45686,8 +45616,6 @@
       <c r="BH31" s="4" t="n"/>
       <c r="BI31" s="4" t="n"/>
       <c r="BJ31" s="4" t="n"/>
-      <c r="BK31" s="4" t="n"/>
-      <c r="BL31" s="4" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6" t="n"/>
@@ -45774,8 +45702,6 @@
       <c r="BH32" s="4" t="n"/>
       <c r="BI32" s="4" t="n"/>
       <c r="BJ32" s="4" t="n"/>
-      <c r="BK32" s="4" t="n"/>
-      <c r="BL32" s="4" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -45854,8 +45780,6 @@
       <c r="BH33" s="4" t="n"/>
       <c r="BI33" s="4" t="n"/>
       <c r="BJ33" s="4" t="n"/>
-      <c r="BK33" s="4" t="n"/>
-      <c r="BL33" s="4" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="n"/>
@@ -45934,8 +45858,6 @@
       <c r="BH34" s="4" t="n"/>
       <c r="BI34" s="4" t="n"/>
       <c r="BJ34" s="4" t="n"/>
-      <c r="BK34" s="4" t="n"/>
-      <c r="BL34" s="4" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n"/>
@@ -46012,8 +45934,6 @@
       <c r="BH35" s="4" t="n"/>
       <c r="BI35" s="4" t="n"/>
       <c r="BJ35" s="4" t="n"/>
-      <c r="BK35" s="4" t="n"/>
-      <c r="BL35" s="4" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n"/>
@@ -46088,8 +46008,6 @@
       <c r="BH36" s="4" t="n"/>
       <c r="BI36" s="4" t="n"/>
       <c r="BJ36" s="4" t="n"/>
-      <c r="BK36" s="4" t="n"/>
-      <c r="BL36" s="4" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -46176,8 +46094,6 @@
       <c r="BH37" s="4" t="n"/>
       <c r="BI37" s="4" t="n"/>
       <c r="BJ37" s="4" t="n"/>
-      <c r="BK37" s="4" t="n"/>
-      <c r="BL37" s="4" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n"/>
@@ -46252,8 +46168,6 @@
       <c r="BH38" s="4" t="n"/>
       <c r="BI38" s="4" t="n"/>
       <c r="BJ38" s="4" t="n"/>
-      <c r="BK38" s="4" t="n"/>
-      <c r="BL38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n"/>
@@ -46328,8 +46242,6 @@
       <c r="BH39" s="4" t="n"/>
       <c r="BI39" s="4" t="n"/>
       <c r="BJ39" s="4" t="n"/>
-      <c r="BK39" s="4" t="n"/>
-      <c r="BL39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n"/>
@@ -46418,8 +46330,6 @@
       <c r="BH40" s="4" t="n"/>
       <c r="BI40" s="4" t="n"/>
       <c r="BJ40" s="4" t="n"/>
-      <c r="BK40" s="4" t="n"/>
-      <c r="BL40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -46498,8 +46408,6 @@
       <c r="BH41" s="4" t="n"/>
       <c r="BI41" s="4" t="n"/>
       <c r="BJ41" s="4" t="n"/>
-      <c r="BK41" s="4" t="n"/>
-      <c r="BL41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n"/>
@@ -46580,8 +46488,6 @@
       <c r="BH42" s="4" t="n"/>
       <c r="BI42" s="4" t="n"/>
       <c r="BJ42" s="4" t="n"/>
-      <c r="BK42" s="4" t="n"/>
-      <c r="BL42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n"/>
@@ -46656,8 +46562,6 @@
       <c r="BH43" s="4" t="n"/>
       <c r="BI43" s="4" t="n"/>
       <c r="BJ43" s="4" t="n"/>
-      <c r="BK43" s="4" t="n"/>
-      <c r="BL43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n"/>
@@ -46730,8 +46634,6 @@
       <c r="BH44" s="4" t="n"/>
       <c r="BI44" s="4" t="n"/>
       <c r="BJ44" s="4" t="n"/>
-      <c r="BK44" s="4" t="n"/>
-      <c r="BL44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -46822,8 +46724,6 @@
       <c r="BH45" s="4" t="n"/>
       <c r="BI45" s="4" t="n"/>
       <c r="BJ45" s="4" t="n"/>
-      <c r="BK45" s="4" t="n"/>
-      <c r="BL45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n"/>
@@ -46902,8 +46802,6 @@
       <c r="BH46" s="4" t="n"/>
       <c r="BI46" s="4" t="n"/>
       <c r="BJ46" s="4" t="n"/>
-      <c r="BK46" s="4" t="n"/>
-      <c r="BL46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n"/>
@@ -46982,8 +46880,6 @@
       <c r="BH47" s="4" t="n"/>
       <c r="BI47" s="4" t="n"/>
       <c r="BJ47" s="4" t="n"/>
-      <c r="BK47" s="4" t="n"/>
-      <c r="BL47" s="4" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n"/>
@@ -47064,8 +46960,6 @@
       <c r="BH48" s="4" t="n"/>
       <c r="BI48" s="4" t="n"/>
       <c r="BJ48" s="4" t="n"/>
-      <c r="BK48" s="4" t="n"/>
-      <c r="BL48" s="4" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -47144,8 +47038,6 @@
       <c r="BH49" s="4" t="n"/>
       <c r="BI49" s="4" t="n"/>
       <c r="BJ49" s="4" t="n"/>
-      <c r="BK49" s="4" t="n"/>
-      <c r="BL49" s="4" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="5" t="n"/>
@@ -47218,8 +47110,6 @@
       <c r="BH50" s="4" t="n"/>
       <c r="BI50" s="4" t="n"/>
       <c r="BJ50" s="4" t="n"/>
-      <c r="BK50" s="4" t="n"/>
-      <c r="BL50" s="4" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n"/>
@@ -47296,8 +47186,6 @@
       <c r="BH51" s="4" t="n"/>
       <c r="BI51" s="4" t="n"/>
       <c r="BJ51" s="4" t="n"/>
-      <c r="BK51" s="4" t="n"/>
-      <c r="BL51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n"/>
@@ -47384,8 +47272,6 @@
       <c r="BH52" s="4" t="n"/>
       <c r="BI52" s="4" t="n"/>
       <c r="BJ52" s="4" t="n"/>
-      <c r="BK52" s="4" t="n"/>
-      <c r="BL52" s="4" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -47466,8 +47352,6 @@
       <c r="BH53" s="4" t="n"/>
       <c r="BI53" s="4" t="n"/>
       <c r="BJ53" s="4" t="n"/>
-      <c r="BK53" s="4" t="n"/>
-      <c r="BL53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n"/>
@@ -47542,8 +47426,6 @@
       <c r="BH54" s="4" t="n"/>
       <c r="BI54" s="4" t="n"/>
       <c r="BJ54" s="4" t="n"/>
-      <c r="BK54" s="4" t="n"/>
-      <c r="BL54" s="4" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n"/>
@@ -47616,8 +47498,6 @@
       <c r="BH55" s="4" t="n"/>
       <c r="BI55" s="4" t="n"/>
       <c r="BJ55" s="4" t="n"/>
-      <c r="BK55" s="4" t="n"/>
-      <c r="BL55" s="4" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n"/>
@@ -47692,8 +47572,6 @@
       <c r="BH56" s="4" t="n"/>
       <c r="BI56" s="4" t="n"/>
       <c r="BJ56" s="4" t="n"/>
-      <c r="BK56" s="4" t="n"/>
-      <c r="BL56" s="4" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -47782,8 +47660,6 @@
       <c r="BH57" s="4" t="n"/>
       <c r="BI57" s="4" t="n"/>
       <c r="BJ57" s="4" t="n"/>
-      <c r="BK57" s="4" t="n"/>
-      <c r="BL57" s="4" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="n"/>
@@ -47858,8 +47734,6 @@
       <c r="BH58" s="4" t="n"/>
       <c r="BI58" s="4" t="n"/>
       <c r="BJ58" s="4" t="n"/>
-      <c r="BK58" s="4" t="n"/>
-      <c r="BL58" s="4" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n"/>
@@ -47936,8 +47810,6 @@
       <c r="BH59" s="4" t="n"/>
       <c r="BI59" s="4" t="n"/>
       <c r="BJ59" s="4" t="n"/>
-      <c r="BK59" s="4" t="n"/>
-      <c r="BL59" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n"/>
@@ -48020,8 +47892,6 @@
       <c r="BH60" s="4" t="n"/>
       <c r="BI60" s="4" t="n"/>
       <c r="BJ60" s="4" t="n"/>
-      <c r="BK60" s="4" t="n"/>
-      <c r="BL60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -48098,8 +47968,6 @@
       <c r="BH61" s="4" t="n"/>
       <c r="BI61" s="4" t="n"/>
       <c r="BJ61" s="4" t="n"/>
-      <c r="BK61" s="4" t="n"/>
-      <c r="BL61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="n"/>
@@ -48180,8 +48048,6 @@
       <c r="BH62" s="4" t="n"/>
       <c r="BI62" s="4" t="n"/>
       <c r="BJ62" s="4" t="n"/>
-      <c r="BK62" s="4" t="n"/>
-      <c r="BL62" s="4" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n"/>
@@ -48268,8 +48134,6 @@
       <c r="BH63" s="4" t="n"/>
       <c r="BI63" s="4" t="n"/>
       <c r="BJ63" s="4" t="n"/>
-      <c r="BK63" s="4" t="n"/>
-      <c r="BL63" s="4" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n"/>
@@ -48346,8 +48210,6 @@
       <c r="BH64" s="4" t="n"/>
       <c r="BI64" s="4" t="n"/>
       <c r="BJ64" s="4" t="n"/>
-      <c r="BK64" s="4" t="n"/>
-      <c r="BL64" s="4" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -48422,8 +48284,6 @@
       <c r="BH65" s="4" t="n"/>
       <c r="BI65" s="4" t="n"/>
       <c r="BJ65" s="4" t="n"/>
-      <c r="BK65" s="4" t="n"/>
-      <c r="BL65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="n"/>
@@ -48502,8 +48362,6 @@
       <c r="BH66" s="4" t="n"/>
       <c r="BI66" s="4" t="n"/>
       <c r="BJ66" s="4" t="n"/>
-      <c r="BK66" s="4" t="n"/>
-      <c r="BL66" s="4" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n"/>
@@ -48580,8 +48438,6 @@
       <c r="BH67" s="4" t="n"/>
       <c r="BI67" s="4" t="n"/>
       <c r="BJ67" s="4" t="n"/>
-      <c r="BK67" s="4" t="n"/>
-      <c r="BL67" s="4" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n"/>
@@ -48660,8 +48516,6 @@
       <c r="BH68" s="4" t="n"/>
       <c r="BI68" s="4" t="n"/>
       <c r="BJ68" s="4" t="n"/>
-      <c r="BK68" s="4" t="n"/>
-      <c r="BL68" s="4" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -48738,8 +48592,6 @@
       <c r="BH69" s="4" t="n"/>
       <c r="BI69" s="4" t="n"/>
       <c r="BJ69" s="4" t="n"/>
-      <c r="BK69" s="4" t="n"/>
-      <c r="BL69" s="4" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="n"/>
@@ -48812,8 +48664,6 @@
       <c r="BH70" s="4" t="n"/>
       <c r="BI70" s="4" t="n"/>
       <c r="BJ70" s="4" t="n"/>
-      <c r="BK70" s="4" t="n"/>
-      <c r="BL70" s="4" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n"/>
@@ -48886,8 +48736,6 @@
       <c r="BH71" s="4" t="n"/>
       <c r="BI71" s="4" t="n"/>
       <c r="BJ71" s="4" t="n"/>
-      <c r="BK71" s="4" t="n"/>
-      <c r="BL71" s="4" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n"/>
@@ -48964,8 +48812,6 @@
       <c r="BH72" s="4" t="n"/>
       <c r="BI72" s="4" t="n"/>
       <c r="BJ72" s="4" t="n"/>
-      <c r="BK72" s="4" t="n"/>
-      <c r="BL72" s="4" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -49046,8 +48892,6 @@
       <c r="BH73" s="4" t="n"/>
       <c r="BI73" s="4" t="n"/>
       <c r="BJ73" s="4" t="n"/>
-      <c r="BK73" s="4" t="n"/>
-      <c r="BL73" s="4" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="5" t="n"/>
@@ -49128,8 +48972,6 @@
       <c r="BH74" s="4" t="n"/>
       <c r="BI74" s="4" t="n"/>
       <c r="BJ74" s="4" t="n"/>
-      <c r="BK74" s="4" t="n"/>
-      <c r="BL74" s="4" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n"/>
@@ -49210,8 +49052,6 @@
       <c r="BH75" s="4" t="n"/>
       <c r="BI75" s="4" t="n"/>
       <c r="BJ75" s="4" t="n"/>
-      <c r="BK75" s="4" t="n"/>
-      <c r="BL75" s="4" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="n"/>
@@ -49286,8 +49126,6 @@
       <c r="BH76" s="4" t="n"/>
       <c r="BI76" s="4" t="n"/>
       <c r="BJ76" s="4" t="n"/>
-      <c r="BK76" s="4" t="n"/>
-      <c r="BL76" s="4" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -49372,8 +49210,6 @@
       <c r="BH77" s="4" t="n"/>
       <c r="BI77" s="4" t="n"/>
       <c r="BJ77" s="4" t="n"/>
-      <c r="BK77" s="4" t="n"/>
-      <c r="BL77" s="4" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="n"/>
@@ -49454,8 +49290,6 @@
       <c r="BH78" s="4" t="n"/>
       <c r="BI78" s="4" t="n"/>
       <c r="BJ78" s="4" t="n"/>
-      <c r="BK78" s="4" t="n"/>
-      <c r="BL78" s="4" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n"/>
@@ -49538,8 +49372,6 @@
       <c r="BH79" s="4" t="n"/>
       <c r="BI79" s="4" t="n"/>
       <c r="BJ79" s="4" t="n"/>
-      <c r="BK79" s="4" t="n"/>
-      <c r="BL79" s="4" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="n"/>
@@ -49614,8 +49446,6 @@
       <c r="BH80" s="4" t="n"/>
       <c r="BI80" s="4" t="n"/>
       <c r="BJ80" s="4" t="n"/>
-      <c r="BK80" s="4" t="n"/>
-      <c r="BL80" s="4" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
@@ -49696,8 +49526,6 @@
       <c r="BH81" s="4" t="n"/>
       <c r="BI81" s="4" t="n"/>
       <c r="BJ81" s="4" t="n"/>
-      <c r="BK81" s="4" t="n"/>
-      <c r="BL81" s="4" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="n"/>
@@ -49776,8 +49604,6 @@
       <c r="BH82" s="4" t="n"/>
       <c r="BI82" s="4" t="n"/>
       <c r="BJ82" s="4" t="n"/>
-      <c r="BK82" s="4" t="n"/>
-      <c r="BL82" s="4" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n"/>
@@ -49854,8 +49680,6 @@
       <c r="BH83" s="4" t="n"/>
       <c r="BI83" s="4" t="n"/>
       <c r="BJ83" s="4" t="n"/>
-      <c r="BK83" s="4" t="n"/>
-      <c r="BL83" s="4" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="n"/>
@@ -49938,11 +49762,9 @@
       <c r="BH84" s="4" t="n"/>
       <c r="BI84" s="4" t="n"/>
       <c r="BJ84" s="4" t="n"/>
-      <c r="BK84" s="4" t="n"/>
-      <c r="BL84" s="4" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BL84"/>
+  <autoFilter ref="A1:BJ84"/>
   <mergeCells count="21">
     <mergeCell ref="A61:A64"/>
     <mergeCell ref="A69:A72"/>
@@ -49976,7 +49798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL84"/>
+  <dimension ref="A1:BJ84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -50041,8 +49863,6 @@
     <col width="7.5" customWidth="1" min="60" max="60"/>
     <col width="7.5" customWidth="1" min="61" max="61"/>
     <col width="7.5" customWidth="1" min="62" max="62"/>
-    <col width="7.5" customWidth="1" min="63" max="63"/>
-    <col width="7.5" customWidth="1" min="64" max="64"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -50343,25 +50163,15 @@
       </c>
       <c r="BH1" s="1" t="inlineStr">
         <is>
-          <t>dose★3</t>
+          <t>风扇★5</t>
         </is>
       </c>
       <c r="BI1" s="1" t="inlineStr">
         <is>
-          <t>dose★4</t>
+          <t>600lt★5</t>
         </is>
       </c>
       <c r="BJ1" s="1" t="inlineStr">
-        <is>
-          <t>风扇★5</t>
-        </is>
-      </c>
-      <c r="BK1" s="1" t="inlineStr">
-        <is>
-          <t>600lt★5</t>
-        </is>
-      </c>
-      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>5n★4</t>
         </is>
@@ -50463,19 +50273,9 @@
       <c r="BE2" s="4" t="n"/>
       <c r="BF2" s="4" t="n"/>
       <c r="BG2" s="4" t="n"/>
-      <c r="BH2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI2" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BJ2" s="4" t="n"/>
-      <c r="BK2" s="4" t="n"/>
-      <c r="BL2" s="4" t="inlineStr">
+      <c r="BH2" s="4" t="n"/>
+      <c r="BI2" s="4" t="n"/>
+      <c r="BJ2" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -50593,19 +50393,9 @@
       <c r="BE3" s="4" t="n"/>
       <c r="BF3" s="4" t="n"/>
       <c r="BG3" s="4" t="n"/>
-      <c r="BH3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI3" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH3" s="4" t="n"/>
+      <c r="BI3" s="4" t="n"/>
       <c r="BJ3" s="4" t="n"/>
-      <c r="BK3" s="4" t="n"/>
-      <c r="BL3" s="4" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="n"/>
@@ -50707,19 +50497,9 @@
       <c r="BE4" s="4" t="n"/>
       <c r="BF4" s="4" t="n"/>
       <c r="BG4" s="4" t="n"/>
-      <c r="BH4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI4" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH4" s="4" t="n"/>
+      <c r="BI4" s="4" t="n"/>
       <c r="BJ4" s="4" t="n"/>
-      <c r="BK4" s="4" t="n"/>
-      <c r="BL4" s="4" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="n"/>
@@ -50829,19 +50609,9 @@
       <c r="BE5" s="4" t="n"/>
       <c r="BF5" s="4" t="n"/>
       <c r="BG5" s="4" t="n"/>
-      <c r="BH5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI5" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH5" s="4" t="n"/>
+      <c r="BI5" s="4" t="n"/>
       <c r="BJ5" s="4" t="n"/>
-      <c r="BK5" s="4" t="n"/>
-      <c r="BL5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -50935,19 +50705,9 @@
       <c r="BE6" s="4" t="n"/>
       <c r="BF6" s="4" t="n"/>
       <c r="BG6" s="4" t="n"/>
-      <c r="BH6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI6" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BJ6" s="4" t="n"/>
-      <c r="BK6" s="4" t="n"/>
-      <c r="BL6" s="4" t="inlineStr">
+      <c r="BH6" s="4" t="n"/>
+      <c r="BI6" s="4" t="n"/>
+      <c r="BJ6" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -51061,19 +50821,9 @@
       <c r="BE7" s="4" t="n"/>
       <c r="BF7" s="4" t="n"/>
       <c r="BG7" s="4" t="n"/>
-      <c r="BH7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI7" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH7" s="4" t="n"/>
+      <c r="BI7" s="4" t="n"/>
       <c r="BJ7" s="4" t="n"/>
-      <c r="BK7" s="4" t="n"/>
-      <c r="BL7" s="4" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
@@ -51203,19 +50953,9 @@
       <c r="BE8" s="4" t="n"/>
       <c r="BF8" s="4" t="n"/>
       <c r="BG8" s="4" t="n"/>
-      <c r="BH8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI8" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH8" s="4" t="n"/>
+      <c r="BI8" s="4" t="n"/>
       <c r="BJ8" s="4" t="n"/>
-      <c r="BK8" s="4" t="n"/>
-      <c r="BL8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n"/>
@@ -51325,19 +51065,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="BH9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI9" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BJ9" s="4" t="n"/>
-      <c r="BK9" s="4" t="n"/>
-      <c r="BL9" s="4" t="inlineStr">
+      <c r="BH9" s="4" t="n"/>
+      <c r="BI9" s="4" t="n"/>
+      <c r="BJ9" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -51459,19 +51189,9 @@
       </c>
       <c r="BF10" s="4" t="n"/>
       <c r="BG10" s="4" t="n"/>
-      <c r="BH10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI10" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH10" s="4" t="n"/>
+      <c r="BI10" s="4" t="n"/>
       <c r="BJ10" s="4" t="n"/>
-      <c r="BK10" s="4" t="n"/>
-      <c r="BL10" s="4" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
@@ -51569,19 +51289,9 @@
       <c r="BE11" s="4" t="n"/>
       <c r="BF11" s="4" t="n"/>
       <c r="BG11" s="4" t="n"/>
-      <c r="BH11" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI11" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH11" s="4" t="n"/>
+      <c r="BI11" s="4" t="n"/>
       <c r="BJ11" s="4" t="n"/>
-      <c r="BK11" s="4" t="n"/>
-      <c r="BL11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
@@ -51695,19 +51405,9 @@
       </c>
       <c r="BF12" s="4" t="n"/>
       <c r="BG12" s="4" t="n"/>
-      <c r="BH12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI12" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH12" s="4" t="n"/>
+      <c r="BI12" s="4" t="n"/>
       <c r="BJ12" s="4" t="n"/>
-      <c r="BK12" s="4" t="n"/>
-      <c r="BL12" s="4" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
@@ -51809,19 +51509,9 @@
       <c r="BE13" s="4" t="n"/>
       <c r="BF13" s="4" t="n"/>
       <c r="BG13" s="4" t="n"/>
-      <c r="BH13" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI13" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH13" s="4" t="n"/>
+      <c r="BI13" s="4" t="n"/>
       <c r="BJ13" s="4" t="n"/>
-      <c r="BK13" s="4" t="n"/>
-      <c r="BL13" s="4" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -51943,19 +51633,9 @@
       <c r="BE14" s="4" t="n"/>
       <c r="BF14" s="4" t="n"/>
       <c r="BG14" s="4" t="n"/>
-      <c r="BH14" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI14" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH14" s="4" t="n"/>
+      <c r="BI14" s="4" t="n"/>
       <c r="BJ14" s="4" t="n"/>
-      <c r="BK14" s="4" t="n"/>
-      <c r="BL14" s="4" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
@@ -52081,19 +51761,9 @@
       <c r="BE15" s="4" t="n"/>
       <c r="BF15" s="4" t="n"/>
       <c r="BG15" s="4" t="n"/>
-      <c r="BH15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI15" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH15" s="4" t="n"/>
+      <c r="BI15" s="4" t="n"/>
       <c r="BJ15" s="4" t="n"/>
-      <c r="BK15" s="4" t="n"/>
-      <c r="BL15" s="4" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="n"/>
@@ -52207,19 +51877,9 @@
       <c r="BE16" s="4" t="n"/>
       <c r="BF16" s="4" t="n"/>
       <c r="BG16" s="4" t="n"/>
-      <c r="BH16" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI16" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH16" s="4" t="n"/>
+      <c r="BI16" s="4" t="n"/>
       <c r="BJ16" s="4" t="n"/>
-      <c r="BK16" s="4" t="n"/>
-      <c r="BL16" s="4" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
@@ -52333,19 +51993,9 @@
       <c r="BE17" s="4" t="n"/>
       <c r="BF17" s="4" t="n"/>
       <c r="BG17" s="4" t="n"/>
-      <c r="BH17" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI17" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH17" s="4" t="n"/>
+      <c r="BI17" s="4" t="n"/>
       <c r="BJ17" s="4" t="n"/>
-      <c r="BK17" s="4" t="n"/>
-      <c r="BL17" s="4" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -52459,19 +52109,9 @@
       </c>
       <c r="BF18" s="4" t="n"/>
       <c r="BG18" s="4" t="n"/>
-      <c r="BH18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI18" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH18" s="4" t="n"/>
+      <c r="BI18" s="4" t="n"/>
       <c r="BJ18" s="4" t="n"/>
-      <c r="BK18" s="4" t="n"/>
-      <c r="BL18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n"/>
@@ -52585,19 +52225,9 @@
       <c r="BE19" s="4" t="n"/>
       <c r="BF19" s="4" t="n"/>
       <c r="BG19" s="4" t="n"/>
-      <c r="BH19" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI19" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH19" s="4" t="n"/>
+      <c r="BI19" s="4" t="n"/>
       <c r="BJ19" s="4" t="n"/>
-      <c r="BK19" s="4" t="n"/>
-      <c r="BL19" s="4" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="n"/>
@@ -52703,19 +52333,9 @@
       <c r="BE20" s="4" t="n"/>
       <c r="BF20" s="4" t="n"/>
       <c r="BG20" s="4" t="n"/>
-      <c r="BH20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI20" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BJ20" s="4" t="n"/>
-      <c r="BK20" s="4" t="n"/>
-      <c r="BL20" s="4" t="inlineStr">
+      <c r="BH20" s="4" t="n"/>
+      <c r="BI20" s="4" t="n"/>
+      <c r="BJ20" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -52817,19 +52437,9 @@
       <c r="BE21" s="4" t="n"/>
       <c r="BF21" s="4" t="n"/>
       <c r="BG21" s="4" t="n"/>
-      <c r="BH21" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI21" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH21" s="4" t="n"/>
+      <c r="BI21" s="4" t="n"/>
       <c r="BJ21" s="4" t="n"/>
-      <c r="BK21" s="4" t="n"/>
-      <c r="BL21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -52935,19 +52545,9 @@
       <c r="BE22" s="4" t="n"/>
       <c r="BF22" s="4" t="n"/>
       <c r="BG22" s="4" t="n"/>
-      <c r="BH22" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI22" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH22" s="4" t="n"/>
+      <c r="BI22" s="4" t="n"/>
       <c r="BJ22" s="4" t="n"/>
-      <c r="BK22" s="4" t="n"/>
-      <c r="BL22" s="4" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n"/>
@@ -53049,19 +52649,9 @@
       <c r="BE23" s="4" t="n"/>
       <c r="BF23" s="4" t="n"/>
       <c r="BG23" s="4" t="n"/>
-      <c r="BH23" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI23" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH23" s="4" t="n"/>
+      <c r="BI23" s="4" t="n"/>
       <c r="BJ23" s="4" t="n"/>
-      <c r="BK23" s="4" t="n"/>
-      <c r="BL23" s="4" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="n"/>
@@ -53171,19 +52761,9 @@
       <c r="BE24" s="4" t="n"/>
       <c r="BF24" s="4" t="n"/>
       <c r="BG24" s="4" t="n"/>
-      <c r="BH24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI24" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH24" s="4" t="n"/>
+      <c r="BI24" s="4" t="n"/>
       <c r="BJ24" s="4" t="n"/>
-      <c r="BK24" s="4" t="n"/>
-      <c r="BL24" s="4" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
@@ -53277,19 +52857,9 @@
       <c r="BE25" s="4" t="n"/>
       <c r="BF25" s="4" t="n"/>
       <c r="BG25" s="4" t="n"/>
-      <c r="BH25" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI25" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BJ25" s="4" t="n"/>
-      <c r="BK25" s="4" t="n"/>
-      <c r="BL25" s="4" t="inlineStr">
+      <c r="BH25" s="4" t="n"/>
+      <c r="BI25" s="4" t="n"/>
+      <c r="BJ25" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -53411,19 +52981,9 @@
       <c r="BE26" s="4" t="n"/>
       <c r="BF26" s="4" t="n"/>
       <c r="BG26" s="4" t="n"/>
-      <c r="BH26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI26" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH26" s="4" t="n"/>
+      <c r="BI26" s="4" t="n"/>
       <c r="BJ26" s="4" t="n"/>
-      <c r="BK26" s="4" t="n"/>
-      <c r="BL26" s="4" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n"/>
@@ -53529,19 +53089,9 @@
       <c r="BE27" s="4" t="n"/>
       <c r="BF27" s="4" t="n"/>
       <c r="BG27" s="4" t="n"/>
-      <c r="BH27" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI27" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH27" s="4" t="n"/>
+      <c r="BI27" s="4" t="n"/>
       <c r="BJ27" s="4" t="n"/>
-      <c r="BK27" s="4" t="n"/>
-      <c r="BL27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n"/>
@@ -53647,19 +53197,9 @@
       <c r="BE28" s="4" t="n"/>
       <c r="BF28" s="4" t="n"/>
       <c r="BG28" s="4" t="n"/>
-      <c r="BH28" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI28" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH28" s="4" t="n"/>
+      <c r="BI28" s="4" t="n"/>
       <c r="BJ28" s="4" t="n"/>
-      <c r="BK28" s="4" t="n"/>
-      <c r="BL28" s="4" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n"/>
@@ -53761,19 +53301,9 @@
       <c r="BE29" s="4" t="n"/>
       <c r="BF29" s="4" t="n"/>
       <c r="BG29" s="4" t="n"/>
-      <c r="BH29" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI29" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH29" s="4" t="n"/>
+      <c r="BI29" s="4" t="n"/>
       <c r="BJ29" s="4" t="n"/>
-      <c r="BK29" s="4" t="n"/>
-      <c r="BL29" s="4" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -53875,19 +53405,9 @@
       <c r="BE30" s="4" t="n"/>
       <c r="BF30" s="4" t="n"/>
       <c r="BG30" s="4" t="n"/>
-      <c r="BH30" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI30" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BJ30" s="4" t="n"/>
-      <c r="BK30" s="4" t="n"/>
-      <c r="BL30" s="4" t="inlineStr">
+      <c r="BH30" s="4" t="n"/>
+      <c r="BI30" s="4" t="n"/>
+      <c r="BJ30" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -53993,19 +53513,9 @@
       </c>
       <c r="BF31" s="4" t="n"/>
       <c r="BG31" s="4" t="n"/>
-      <c r="BH31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI31" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BJ31" s="4" t="n"/>
-      <c r="BK31" s="4" t="n"/>
-      <c r="BL31" s="4" t="inlineStr">
+      <c r="BH31" s="4" t="n"/>
+      <c r="BI31" s="4" t="n"/>
+      <c r="BJ31" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -54127,19 +53637,9 @@
         </is>
       </c>
       <c r="BG32" s="4" t="n"/>
-      <c r="BH32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI32" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BJ32" s="4" t="n"/>
-      <c r="BK32" s="4" t="n"/>
-      <c r="BL32" s="4" t="inlineStr">
+      <c r="BH32" s="4" t="n"/>
+      <c r="BI32" s="4" t="n"/>
+      <c r="BJ32" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -54245,19 +53745,9 @@
       <c r="BE33" s="4" t="n"/>
       <c r="BF33" s="4" t="n"/>
       <c r="BG33" s="4" t="n"/>
-      <c r="BH33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI33" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BJ33" s="4" t="n"/>
-      <c r="BK33" s="4" t="n"/>
-      <c r="BL33" s="4" t="inlineStr">
+      <c r="BH33" s="4" t="n"/>
+      <c r="BI33" s="4" t="n"/>
+      <c r="BJ33" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -54375,19 +53865,9 @@
       <c r="BE34" s="4" t="n"/>
       <c r="BF34" s="4" t="n"/>
       <c r="BG34" s="4" t="n"/>
-      <c r="BH34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BJ34" s="4" t="n"/>
-      <c r="BK34" s="4" t="n"/>
-      <c r="BL34" s="4" t="inlineStr">
+      <c r="BH34" s="4" t="n"/>
+      <c r="BI34" s="4" t="n"/>
+      <c r="BJ34" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -54493,19 +53973,9 @@
         </is>
       </c>
       <c r="BG35" s="4" t="n"/>
-      <c r="BH35" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI35" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BJ35" s="4" t="n"/>
-      <c r="BK35" s="4" t="n"/>
-      <c r="BL35" s="4" t="inlineStr">
+      <c r="BH35" s="4" t="n"/>
+      <c r="BI35" s="4" t="n"/>
+      <c r="BJ35" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -54615,19 +54085,9 @@
       <c r="BE36" s="4" t="n"/>
       <c r="BF36" s="4" t="n"/>
       <c r="BG36" s="4" t="n"/>
-      <c r="BH36" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI36" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH36" s="4" t="n"/>
+      <c r="BI36" s="4" t="n"/>
       <c r="BJ36" s="4" t="n"/>
-      <c r="BK36" s="4" t="n"/>
-      <c r="BL36" s="4" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -54749,19 +54209,9 @@
         </is>
       </c>
       <c r="BG37" s="4" t="n"/>
-      <c r="BH37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI37" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BJ37" s="4" t="n"/>
-      <c r="BK37" s="4" t="n"/>
-      <c r="BL37" s="4" t="inlineStr">
+      <c r="BH37" s="4" t="n"/>
+      <c r="BI37" s="4" t="n"/>
+      <c r="BJ37" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -54879,19 +54329,9 @@
         </is>
       </c>
       <c r="BG38" s="4" t="n"/>
-      <c r="BH38" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI38" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH38" s="4" t="n"/>
+      <c r="BI38" s="4" t="n"/>
       <c r="BJ38" s="4" t="n"/>
-      <c r="BK38" s="4" t="n"/>
-      <c r="BL38" s="4" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n"/>
@@ -55001,19 +54441,9 @@
         </is>
       </c>
       <c r="BG39" s="4" t="n"/>
-      <c r="BH39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI39" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH39" s="4" t="n"/>
+      <c r="BI39" s="4" t="n"/>
       <c r="BJ39" s="4" t="n"/>
-      <c r="BK39" s="4" t="n"/>
-      <c r="BL39" s="4" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n"/>
@@ -55139,19 +54569,9 @@
         </is>
       </c>
       <c r="BG40" s="4" t="n"/>
-      <c r="BH40" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI40" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH40" s="4" t="n"/>
+      <c r="BI40" s="4" t="n"/>
       <c r="BJ40" s="4" t="n"/>
-      <c r="BK40" s="4" t="n"/>
-      <c r="BL40" s="4" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -55249,19 +54669,9 @@
       <c r="BE41" s="4" t="n"/>
       <c r="BF41" s="4" t="n"/>
       <c r="BG41" s="4" t="n"/>
-      <c r="BH41" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI41" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH41" s="4" t="n"/>
+      <c r="BI41" s="4" t="n"/>
       <c r="BJ41" s="4" t="n"/>
-      <c r="BK41" s="4" t="n"/>
-      <c r="BL41" s="4" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="n"/>
@@ -55371,19 +54781,9 @@
       <c r="BE42" s="4" t="n"/>
       <c r="BF42" s="4" t="n"/>
       <c r="BG42" s="4" t="n"/>
-      <c r="BH42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI42" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH42" s="4" t="n"/>
+      <c r="BI42" s="4" t="n"/>
       <c r="BJ42" s="4" t="n"/>
-      <c r="BK42" s="4" t="n"/>
-      <c r="BL42" s="4" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n"/>
@@ -55485,19 +54885,9 @@
       <c r="BE43" s="4" t="n"/>
       <c r="BF43" s="4" t="n"/>
       <c r="BG43" s="4" t="n"/>
-      <c r="BH43" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI43" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH43" s="4" t="n"/>
+      <c r="BI43" s="4" t="n"/>
       <c r="BJ43" s="4" t="n"/>
-      <c r="BK43" s="4" t="n"/>
-      <c r="BL43" s="4" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n"/>
@@ -55595,19 +54985,9 @@
       </c>
       <c r="BF44" s="4" t="n"/>
       <c r="BG44" s="4" t="n"/>
-      <c r="BH44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI44" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH44" s="4" t="n"/>
+      <c r="BI44" s="4" t="n"/>
       <c r="BJ44" s="4" t="n"/>
-      <c r="BK44" s="4" t="n"/>
-      <c r="BL44" s="4" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -55729,19 +55109,9 @@
       <c r="BE45" s="4" t="n"/>
       <c r="BF45" s="4" t="n"/>
       <c r="BG45" s="4" t="n"/>
-      <c r="BH45" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI45" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH45" s="4" t="n"/>
+      <c r="BI45" s="4" t="n"/>
       <c r="BJ45" s="4" t="n"/>
-      <c r="BK45" s="4" t="n"/>
-      <c r="BL45" s="4" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n"/>
@@ -55863,19 +55233,9 @@
       <c r="BE46" s="4" t="n"/>
       <c r="BF46" s="4" t="n"/>
       <c r="BG46" s="4" t="n"/>
-      <c r="BH46" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI46" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH46" s="4" t="n"/>
+      <c r="BI46" s="4" t="n"/>
       <c r="BJ46" s="4" t="n"/>
-      <c r="BK46" s="4" t="n"/>
-      <c r="BL46" s="4" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="5" t="n"/>
@@ -55993,19 +55353,9 @@
       <c r="BE47" s="4" t="n"/>
       <c r="BF47" s="4" t="n"/>
       <c r="BG47" s="4" t="n"/>
-      <c r="BH47" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI47" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH47" s="4" t="n"/>
+      <c r="BI47" s="4" t="n"/>
       <c r="BJ47" s="4" t="n"/>
-      <c r="BK47" s="4" t="n"/>
-      <c r="BL47" s="4" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n"/>
@@ -56127,19 +55477,9 @@
       <c r="BE48" s="4" t="n"/>
       <c r="BF48" s="4" t="n"/>
       <c r="BG48" s="4" t="n"/>
-      <c r="BH48" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI48" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH48" s="4" t="n"/>
+      <c r="BI48" s="4" t="n"/>
       <c r="BJ48" s="4" t="n"/>
-      <c r="BK48" s="4" t="n"/>
-      <c r="BL48" s="4" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -56241,19 +55581,9 @@
         </is>
       </c>
       <c r="BG49" s="4" t="n"/>
-      <c r="BH49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI49" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BJ49" s="4" t="n"/>
-      <c r="BK49" s="4" t="n"/>
-      <c r="BL49" s="4" t="inlineStr">
+      <c r="BH49" s="4" t="n"/>
+      <c r="BI49" s="4" t="n"/>
+      <c r="BJ49" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -56356,18 +55686,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="BI50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BI50" s="4" t="n"/>
       <c r="BJ50" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BK50" s="4" t="n"/>
-      <c r="BL50" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -56481,19 +55801,9 @@
       <c r="BE51" s="4" t="n"/>
       <c r="BF51" s="4" t="n"/>
       <c r="BG51" s="4" t="n"/>
-      <c r="BH51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI51" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH51" s="4" t="n"/>
+      <c r="BI51" s="4" t="n"/>
       <c r="BJ51" s="4" t="n"/>
-      <c r="BK51" s="4" t="n"/>
-      <c r="BL51" s="4" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n"/>
@@ -56615,19 +55925,9 @@
       <c r="BE52" s="4" t="n"/>
       <c r="BF52" s="4" t="n"/>
       <c r="BG52" s="4" t="n"/>
-      <c r="BH52" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI52" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH52" s="4" t="n"/>
+      <c r="BI52" s="4" t="n"/>
       <c r="BJ52" s="4" t="n"/>
-      <c r="BK52" s="4" t="n"/>
-      <c r="BL52" s="4" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -56733,19 +56033,9 @@
       <c r="BE53" s="4" t="n"/>
       <c r="BF53" s="4" t="n"/>
       <c r="BG53" s="4" t="n"/>
-      <c r="BH53" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI53" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH53" s="4" t="n"/>
+      <c r="BI53" s="4" t="n"/>
       <c r="BJ53" s="4" t="n"/>
-      <c r="BK53" s="4" t="n"/>
-      <c r="BL53" s="4" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n"/>
@@ -56863,19 +56153,9 @@
       <c r="BE54" s="4" t="n"/>
       <c r="BF54" s="4" t="n"/>
       <c r="BG54" s="4" t="n"/>
-      <c r="BH54" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI54" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH54" s="4" t="n"/>
+      <c r="BI54" s="4" t="n"/>
       <c r="BJ54" s="4" t="n"/>
-      <c r="BK54" s="4" t="n"/>
-      <c r="BL54" s="4" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="5" t="n"/>
@@ -56973,19 +56253,9 @@
       <c r="BE55" s="4" t="n"/>
       <c r="BF55" s="4" t="n"/>
       <c r="BG55" s="4" t="n"/>
-      <c r="BH55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI55" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BJ55" s="4" t="n"/>
-      <c r="BK55" s="4" t="n"/>
-      <c r="BL55" s="4" t="inlineStr">
+      <c r="BH55" s="4" t="n"/>
+      <c r="BI55" s="4" t="n"/>
+      <c r="BJ55" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -57087,19 +56357,9 @@
       <c r="BE56" s="4" t="n"/>
       <c r="BF56" s="4" t="n"/>
       <c r="BG56" s="4" t="n"/>
-      <c r="BH56" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI56" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH56" s="4" t="n"/>
+      <c r="BI56" s="4" t="n"/>
       <c r="BJ56" s="4" t="n"/>
-      <c r="BK56" s="4" t="n"/>
-      <c r="BL56" s="4" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -57225,19 +56485,9 @@
       <c r="BE57" s="4" t="n"/>
       <c r="BF57" s="4" t="n"/>
       <c r="BG57" s="4" t="n"/>
-      <c r="BH57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI57" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH57" s="4" t="n"/>
+      <c r="BI57" s="4" t="n"/>
       <c r="BJ57" s="4" t="n"/>
-      <c r="BK57" s="4" t="n"/>
-      <c r="BL57" s="4" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="n"/>
@@ -57339,19 +56589,9 @@
       <c r="BE58" s="4" t="n"/>
       <c r="BF58" s="4" t="n"/>
       <c r="BG58" s="4" t="n"/>
-      <c r="BH58" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI58" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH58" s="4" t="n"/>
+      <c r="BI58" s="4" t="n"/>
       <c r="BJ58" s="4" t="n"/>
-      <c r="BK58" s="4" t="n"/>
-      <c r="BL58" s="4" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="5" t="n"/>
@@ -57453,19 +56693,9 @@
       <c r="BE59" s="4" t="n"/>
       <c r="BF59" s="4" t="n"/>
       <c r="BG59" s="4" t="n"/>
-      <c r="BH59" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI59" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH59" s="4" t="n"/>
+      <c r="BI59" s="4" t="n"/>
       <c r="BJ59" s="4" t="n"/>
-      <c r="BK59" s="4" t="n"/>
-      <c r="BL59" s="4" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n"/>
@@ -57579,19 +56809,9 @@
       <c r="BE60" s="4" t="n"/>
       <c r="BF60" s="4" t="n"/>
       <c r="BG60" s="4" t="n"/>
-      <c r="BH60" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI60" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH60" s="4" t="n"/>
+      <c r="BI60" s="4" t="n"/>
       <c r="BJ60" s="4" t="n"/>
-      <c r="BK60" s="4" t="n"/>
-      <c r="BL60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -57713,19 +56933,9 @@
       <c r="BE61" s="4" t="n"/>
       <c r="BF61" s="4" t="n"/>
       <c r="BG61" s="4" t="n"/>
-      <c r="BH61" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI61" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH61" s="4" t="n"/>
+      <c r="BI61" s="4" t="n"/>
       <c r="BJ61" s="4" t="n"/>
-      <c r="BK61" s="4" t="n"/>
-      <c r="BL61" s="4" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="n"/>
@@ -57835,19 +57045,9 @@
       <c r="BE62" s="4" t="n"/>
       <c r="BF62" s="4" t="n"/>
       <c r="BG62" s="4" t="n"/>
-      <c r="BH62" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI62" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BJ62" s="4" t="n"/>
-      <c r="BK62" s="4" t="n"/>
-      <c r="BL62" s="4" t="inlineStr">
+      <c r="BH62" s="4" t="n"/>
+      <c r="BI62" s="4" t="n"/>
+      <c r="BJ62" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -57977,19 +57177,9 @@
       <c r="BE63" s="4" t="n"/>
       <c r="BF63" s="4" t="n"/>
       <c r="BG63" s="4" t="n"/>
-      <c r="BH63" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI63" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH63" s="4" t="n"/>
+      <c r="BI63" s="4" t="n"/>
       <c r="BJ63" s="4" t="n"/>
-      <c r="BK63" s="4" t="n"/>
-      <c r="BL63" s="4" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n"/>
@@ -58103,19 +57293,9 @@
       <c r="BE64" s="4" t="n"/>
       <c r="BF64" s="4" t="n"/>
       <c r="BG64" s="4" t="n"/>
-      <c r="BH64" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI64" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH64" s="4" t="n"/>
+      <c r="BI64" s="4" t="n"/>
       <c r="BJ64" s="4" t="n"/>
-      <c r="BK64" s="4" t="n"/>
-      <c r="BL64" s="4" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -58213,19 +57393,9 @@
       <c r="BE65" s="4" t="n"/>
       <c r="BF65" s="4" t="n"/>
       <c r="BG65" s="4" t="n"/>
-      <c r="BH65" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI65" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH65" s="4" t="n"/>
+      <c r="BI65" s="4" t="n"/>
       <c r="BJ65" s="4" t="n"/>
-      <c r="BK65" s="4" t="n"/>
-      <c r="BL65" s="4" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="5" t="n"/>
@@ -58327,19 +57497,9 @@
       <c r="BE66" s="4" t="n"/>
       <c r="BF66" s="4" t="n"/>
       <c r="BG66" s="4" t="n"/>
-      <c r="BH66" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI66" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH66" s="4" t="n"/>
+      <c r="BI66" s="4" t="n"/>
       <c r="BJ66" s="4" t="n"/>
-      <c r="BK66" s="4" t="n"/>
-      <c r="BL66" s="4" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n"/>
@@ -58465,19 +57625,9 @@
       </c>
       <c r="BF67" s="4" t="n"/>
       <c r="BG67" s="4" t="n"/>
-      <c r="BH67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI67" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH67" s="4" t="n"/>
+      <c r="BI67" s="4" t="n"/>
       <c r="BJ67" s="4" t="n"/>
-      <c r="BK67" s="4" t="n"/>
-      <c r="BL67" s="4" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n"/>
@@ -58575,19 +57725,9 @@
       <c r="BE68" s="4" t="n"/>
       <c r="BF68" s="4" t="n"/>
       <c r="BG68" s="4" t="n"/>
-      <c r="BH68" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI68" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH68" s="4" t="n"/>
+      <c r="BI68" s="4" t="n"/>
       <c r="BJ68" s="4" t="n"/>
-      <c r="BK68" s="4" t="n"/>
-      <c r="BL68" s="4" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -58689,19 +57829,9 @@
       <c r="BE69" s="4" t="n"/>
       <c r="BF69" s="4" t="n"/>
       <c r="BG69" s="4" t="n"/>
-      <c r="BH69" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI69" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH69" s="4" t="n"/>
+      <c r="BI69" s="4" t="n"/>
       <c r="BJ69" s="4" t="n"/>
-      <c r="BK69" s="4" t="n"/>
-      <c r="BL69" s="4" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="5" t="n"/>
@@ -58803,19 +57933,9 @@
         </is>
       </c>
       <c r="BG70" s="4" t="n"/>
-      <c r="BH70" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI70" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH70" s="4" t="n"/>
+      <c r="BI70" s="4" t="n"/>
       <c r="BJ70" s="4" t="n"/>
-      <c r="BK70" s="4" t="n"/>
-      <c r="BL70" s="4" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n"/>
@@ -58909,19 +58029,9 @@
       <c r="BE71" s="4" t="n"/>
       <c r="BF71" s="4" t="n"/>
       <c r="BG71" s="4" t="n"/>
-      <c r="BH71" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI71" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH71" s="4" t="n"/>
+      <c r="BI71" s="4" t="n"/>
       <c r="BJ71" s="4" t="n"/>
-      <c r="BK71" s="4" t="n"/>
-      <c r="BL71" s="4" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="6" t="n"/>
@@ -59027,19 +58137,9 @@
       <c r="BE72" s="4" t="n"/>
       <c r="BF72" s="4" t="n"/>
       <c r="BG72" s="4" t="n"/>
-      <c r="BH72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI72" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH72" s="4" t="n"/>
+      <c r="BI72" s="4" t="n"/>
       <c r="BJ72" s="4" t="n"/>
-      <c r="BK72" s="4" t="n"/>
-      <c r="BL72" s="4" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -59149,19 +58249,9 @@
       <c r="BE73" s="4" t="n"/>
       <c r="BF73" s="4" t="n"/>
       <c r="BG73" s="4" t="n"/>
-      <c r="BH73" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI73" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BJ73" s="4" t="n"/>
-      <c r="BK73" s="4" t="n"/>
-      <c r="BL73" s="4" t="inlineStr">
+      <c r="BH73" s="4" t="n"/>
+      <c r="BI73" s="4" t="n"/>
+      <c r="BJ73" s="4" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
@@ -59279,19 +58369,9 @@
       <c r="BE74" s="4" t="n"/>
       <c r="BF74" s="4" t="n"/>
       <c r="BG74" s="4" t="n"/>
-      <c r="BH74" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI74" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH74" s="4" t="n"/>
+      <c r="BI74" s="4" t="n"/>
       <c r="BJ74" s="4" t="n"/>
-      <c r="BK74" s="4" t="n"/>
-      <c r="BL74" s="4" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n"/>
@@ -59401,19 +58481,9 @@
       <c r="BE75" s="4" t="n"/>
       <c r="BF75" s="4" t="n"/>
       <c r="BG75" s="4" t="n"/>
-      <c r="BH75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI75" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH75" s="4" t="n"/>
+      <c r="BI75" s="4" t="n"/>
       <c r="BJ75" s="4" t="n"/>
-      <c r="BK75" s="4" t="n"/>
-      <c r="BL75" s="4" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="n"/>
@@ -59518,16 +58588,6 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="BK76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BL76" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -59637,19 +58697,9 @@
       <c r="BE77" s="4" t="n"/>
       <c r="BF77" s="4" t="n"/>
       <c r="BG77" s="4" t="n"/>
-      <c r="BH77" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI77" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH77" s="4" t="n"/>
+      <c r="BI77" s="4" t="n"/>
       <c r="BJ77" s="4" t="n"/>
-      <c r="BK77" s="4" t="n"/>
-      <c r="BL77" s="4" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="5" t="n"/>
@@ -59755,19 +58805,9 @@
       <c r="BE78" s="4" t="n"/>
       <c r="BF78" s="4" t="n"/>
       <c r="BG78" s="4" t="n"/>
-      <c r="BH78" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI78" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH78" s="4" t="n"/>
+      <c r="BI78" s="4" t="n"/>
       <c r="BJ78" s="4" t="n"/>
-      <c r="BK78" s="4" t="n"/>
-      <c r="BL78" s="4" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n"/>
@@ -59877,19 +58917,9 @@
       <c r="BE79" s="4" t="n"/>
       <c r="BF79" s="4" t="n"/>
       <c r="BG79" s="4" t="n"/>
-      <c r="BH79" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI79" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH79" s="4" t="n"/>
+      <c r="BI79" s="4" t="n"/>
       <c r="BJ79" s="4" t="n"/>
-      <c r="BK79" s="4" t="n"/>
-      <c r="BL79" s="4" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="6" t="n"/>
@@ -59991,19 +59021,9 @@
       <c r="BE80" s="4" t="n"/>
       <c r="BF80" s="4" t="n"/>
       <c r="BG80" s="4" t="n"/>
-      <c r="BH80" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI80" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH80" s="4" t="n"/>
+      <c r="BI80" s="4" t="n"/>
       <c r="BJ80" s="4" t="n"/>
-      <c r="BK80" s="4" t="n"/>
-      <c r="BL80" s="4" t="n"/>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
@@ -60093,19 +59113,9 @@
       <c r="BE81" s="4" t="n"/>
       <c r="BF81" s="4" t="n"/>
       <c r="BG81" s="4" t="n"/>
-      <c r="BH81" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI81" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH81" s="4" t="n"/>
+      <c r="BI81" s="4" t="n"/>
       <c r="BJ81" s="4" t="n"/>
-      <c r="BK81" s="4" t="n"/>
-      <c r="BL81" s="4" t="n"/>
     </row>
     <row r="82">
       <c r="A82" s="5" t="n"/>
@@ -60195,19 +59205,9 @@
       <c r="BE82" s="4" t="n"/>
       <c r="BF82" s="4" t="n"/>
       <c r="BG82" s="4" t="n"/>
-      <c r="BH82" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI82" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH82" s="4" t="n"/>
+      <c r="BI82" s="4" t="n"/>
       <c r="BJ82" s="4" t="n"/>
-      <c r="BK82" s="4" t="n"/>
-      <c r="BL82" s="4" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n"/>
@@ -60293,19 +59293,9 @@
       <c r="BE83" s="4" t="n"/>
       <c r="BF83" s="4" t="n"/>
       <c r="BG83" s="4" t="n"/>
-      <c r="BH83" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI83" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH83" s="4" t="n"/>
+      <c r="BI83" s="4" t="n"/>
       <c r="BJ83" s="4" t="n"/>
-      <c r="BK83" s="4" t="n"/>
-      <c r="BL83" s="4" t="n"/>
     </row>
     <row r="84">
       <c r="A84" s="6" t="n"/>
@@ -60403,22 +59393,12 @@
       <c r="BE84" s="4" t="n"/>
       <c r="BF84" s="4" t="n"/>
       <c r="BG84" s="4" t="n"/>
-      <c r="BH84" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="BI84" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="BH84" s="4" t="n"/>
+      <c r="BI84" s="4" t="n"/>
       <c r="BJ84" s="4" t="n"/>
-      <c r="BK84" s="4" t="n"/>
-      <c r="BL84" s="4" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:BL84"/>
+  <autoFilter ref="A1:BJ84"/>
   <mergeCells count="21">
     <mergeCell ref="A61:A64"/>
     <mergeCell ref="A69:A72"/>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -13262,7 +13262,9 @@
       <c r="AP30" s="4" t="n"/>
       <c r="AQ30" s="4" t="n"/>
       <c r="AR30" s="4" t="n"/>
-      <c r="AS30" s="4" t="n"/>
+      <c r="AS30" s="4" t="n">
+        <v>23.49</v>
+      </c>
       <c r="AT30" s="4" t="n"/>
       <c r="AU30" s="4" t="n"/>
       <c r="AV30" s="4" t="n"/>
@@ -21603,7 +21605,11 @@
       <c r="AP30" s="4" t="n"/>
       <c r="AQ30" s="4" t="n"/>
       <c r="AR30" s="4" t="n"/>
-      <c r="AS30" s="4" t="n"/>
+      <c r="AS30" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AT30" s="4" t="n"/>
       <c r="AU30" s="4" t="n"/>
       <c r="AV30" s="4" t="n"/>

--- a/gauntlet_data.xlsx
+++ b/gauntlet_data.xlsx
@@ -5896,11 +5896,11 @@
         <v>20.9</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>20.8</v>
+        <v>20.76</v>
       </c>
       <c r="L61" s="4" t="n"/>
       <c r="M61" s="4" t="n">
-        <v>21</v>
+        <v>20.97</v>
       </c>
       <c r="N61" s="4" t="n">
         <v>21.2</v>
@@ -6985,16 +6985,16 @@
       </c>
       <c r="C74" s="4" t="n"/>
       <c r="D74" s="4" t="n">
-        <v>32.05</v>
+        <v>31.95</v>
       </c>
       <c r="E74" s="4" t="n">
-        <v>31.95</v>
+        <v>31.9</v>
       </c>
       <c r="F74" s="4" t="n">
         <v>32.9</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>31.99</v>
+        <v>31.78</v>
       </c>
       <c r="H74" s="4" t="n">
         <v>32.6</v>
@@ -7005,7 +7005,7 @@
       <c r="J74" s="4" t="n"/>
       <c r="K74" s="4" t="n"/>
       <c r="L74" s="4" t="n">
-        <v>31.89</v>
+        <v>31.85</v>
       </c>
       <c r="M74" s="4" t="n"/>
       <c r="N74" s="4" t="n"/>
@@ -8804,14 +8804,14 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>fp1</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>万达</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>fp1</t>
-        </is>
-      </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
           <t>21c</t>
@@ -8824,12 +8824,12 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>法拉第</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>火山</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>法拉第</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
@@ -8959,10 +8959,10 @@
       <c r="I4" s="4" t="n">
         <v>24.59</v>
       </c>
-      <c r="J4" s="4" t="n"/>
-      <c r="K4" s="4" t="n">
+      <c r="J4" s="4" t="n">
         <v>24.59</v>
       </c>
+      <c r="K4" s="4" t="n"/>
       <c r="L4" s="4" t="n"/>
       <c r="M4" s="4" t="n"/>
       <c r="N4" s="4" t="n"/>
@@ -9094,10 +9094,10 @@
         <v>18.19</v>
       </c>
       <c r="M7" s="4" t="n"/>
-      <c r="N7" s="4" t="n"/>
-      <c r="O7" s="4" t="n">
+      <c r="N7" s="4" t="n">
         <v>18.39</v>
       </c>
+      <c r="O7" s="4" t="n"/>
       <c r="P7" s="4" t="n">
         <v>18.7</v>
       </c>
@@ -9244,10 +9244,10 @@
         <v>29.45</v>
       </c>
       <c r="M11" s="4" t="n"/>
-      <c r="N11" s="4" t="n">
+      <c r="N11" s="4" t="n"/>
+      <c r="O11" s="4" t="n">
         <v>30.59</v>
       </c>
-      <c r="O11" s="4" t="n"/>
       <c r="P11" s="4" t="n"/>
       <c r="Q11" s="4" t="n"/>
       <c r="R11" s="4" t="n"/>
@@ -9452,10 +9452,10 @@
       <c r="G17" s="4" t="n"/>
       <c r="H17" s="4" t="n"/>
       <c r="I17" s="4" t="n"/>
-      <c r="J17" s="4" t="n">
+      <c r="J17" s="4" t="n"/>
+      <c r="K17" s="4" t="n">
         <v>26.7</v>
       </c>
-      <c r="K17" s="4" t="n"/>
       <c r="L17" s="4" t="n"/>
       <c r="M17" s="4" t="n">
         <v>27.5</v>
@@ -9565,10 +9565,10 @@
         <v>18.69</v>
       </c>
       <c r="I20" s="4" t="n"/>
-      <c r="J20" s="4" t="n">
+      <c r="J20" s="4" t="n"/>
+      <c r="K20" s="4" t="n">
         <v>19.15</v>
       </c>
-      <c r="K20" s="4" t="n"/>
       <c r="L20" s="4" t="n"/>
       <c r="M20" s="4" t="n">
         <v>19</v>
@@ -9681,14 +9681,14 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>9x8★6</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>玻璃★3</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>9x8★6</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>c2★6</t>
@@ -9696,12 +9696,12 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>fp1★6</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>万达★6</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>fp1★6</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -9785,10 +9785,10 @@
       <c r="D4" s="4" t="n"/>
       <c r="E4" s="4" t="n"/>
       <c r="F4" s="4" t="n"/>
-      <c r="G4" s="4" t="n"/>
-      <c r="H4" s="4" t="n">
+      <c r="G4" s="4" t="n">
         <v>24.79</v>
       </c>
+      <c r="H4" s="4" t="n"/>
       <c r="I4" s="4" t="n"/>
       <c r="J4" s="4" t="n"/>
       <c r="K4" s="4" t="n"/>
@@ -9809,10 +9809,10 @@
           <t>跳船</t>
         </is>
       </c>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n">
+      <c r="D5" s="4" t="n">
         <v>22.75</v>
       </c>
+      <c r="E5" s="4" t="n"/>
       <c r="F5" s="4" t="n"/>
       <c r="G5" s="4" t="n"/>
       <c r="H5" s="4" t="n"/>
@@ -10009,10 +10009,10 @@
           <t>跳图</t>
         </is>
       </c>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="n">
+      <c r="D13" s="4" t="n">
         <v>21.46</v>
       </c>
+      <c r="E13" s="4" t="n"/>
       <c r="F13" s="4" t="n"/>
       <c r="G13" s="4" t="n"/>
       <c r="H13" s="4" t="n"/>
@@ -10032,10 +10032,10 @@
           <t>跳图</t>
         </is>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n">
         <v>24.8</v>
       </c>
-      <c r="E14" s="4" t="n"/>
       <c r="F14" s="4" t="n"/>
       <c r="G14" s="4" t="n"/>
       <c r="H14" s="4" t="n"/>
@@ -10108,10 +10108,10 @@
       <c r="D17" s="4" t="n"/>
       <c r="E17" s="4" t="n"/>
       <c r="F17" s="4" t="n"/>
-      <c r="G17" s="4" t="n">
+      <c r="G17" s="4" t="n"/>
+      <c r="H17" s="4" t="n">
         <v>26.9</v>
       </c>
-      <c r="H17" s="4" t="n"/>
       <c r="I17" s="4" t="n">
         <v>27.8</v>
       </c>
@@ -11153,7 +11153,9 @@
       </c>
       <c r="I7" s="4" t="n"/>
       <c r="J7" s="4" t="n"/>
-      <c r="K7" s="4" t="n"/>
+      <c r="K7" s="4" t="n">
+        <v>24.09</v>
+      </c>
       <c r="L7" s="4" t="n"/>
       <c r="M7" s="4" t="n"/>
       <c r="N7" s="4" t="n"/>
@@ -11706,7 +11708,9 @@
       <c r="C13" s="4" t="n"/>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
-      <c r="F13" s="4" t="n"/>
+      <c r="F13" s="4" t="n">
+        <v>42.52</v>
+      </c>
       <c r="G13" s="4" t="n"/>
       <c r="H13" s="4" t="n"/>
       <c r="I13" s="4" t="n"/>
@@ -11739,7 +11743,9 @@
       <c r="Z13" s="4" t="n"/>
       <c r="AA13" s="4" t="n"/>
       <c r="AB13" s="4" t="n"/>
-      <c r="AC13" s="4" t="n"/>
+      <c r="AC13" s="4" t="n">
+        <v>43.2</v>
+      </c>
       <c r="AD13" s="4" t="n"/>
       <c r="AE13" s="4" t="n"/>
       <c r="AF13" s="4" t="n"/>
@@ -11751,7 +11757,9 @@
       <c r="AL13" s="4" t="n"/>
       <c r="AM13" s="4" t="n"/>
       <c r="AN13" s="4" t="n"/>
-      <c r="AO13" s="4" t="n"/>
+      <c r="AO13" s="4" t="n">
+        <v>42.34</v>
+      </c>
       <c r="AP13" s="4" t="n"/>
       <c r="AQ13" s="4" t="n"/>
       <c r="AR13" s="4" t="n"/>
@@ -12367,8 +12375,12 @@
       <c r="I20" s="4" t="n"/>
       <c r="J20" s="4" t="n"/>
       <c r="K20" s="4" t="n"/>
-      <c r="L20" s="4" t="n"/>
-      <c r="M20" s="4" t="n"/>
+      <c r="L20" s="4" t="n">
+        <v>22.59</v>
+      </c>
+      <c r="M20" s="4" t="n">
+        <v>22.29</v>
+      </c>
       <c r="N20" s="4" t="n">
         <v>21.89</v>
       </c>
@@ -13689,12 +13701,16 @@
       <c r="Q34" s="4" t="n"/>
       <c r="R34" s="4" t="n"/>
       <c r="S34" s="4" t="n"/>
-      <c r="T34" s="4" t="n"/>
+      <c r="T34" s="4" t="n">
+        <v>34.45</v>
+      </c>
       <c r="U34" s="4" t="n"/>
       <c r="V34" s="4" t="n"/>
       <c r="W34" s="4" t="n"/>
       <c r="X34" s="4" t="n"/>
-      <c r="Y34" s="4" t="n"/>
+      <c r="Y34" s="4" t="n">
+        <v>34.55</v>
+      </c>
       <c r="Z34" s="4" t="n"/>
       <c r="AA34" s="4" t="n"/>
       <c r="AB34" s="4" t="n"/>
@@ -13703,13 +13719,13 @@
       </c>
       <c r="AD34" s="4" t="n"/>
       <c r="AE34" s="4" t="n"/>
-      <c r="AF34" s="4" t="n">
-        <v>34.39</v>
-      </c>
+      <c r="AF34" s="4" t="n"/>
       <c r="AG34" s="4" t="n"/>
       <c r="AH34" s="4" t="n"/>
       <c r="AI34" s="4" t="n"/>
-      <c r="AJ34" s="4" t="n"/>
+      <c r="AJ34" s="4" t="n">
+        <v>34.39</v>
+      </c>
       <c r="AK34" s="4" t="n">
         <v>33.92</v>
       </c>
@@ -15788,9 +15804,11 @@
         <v>34.5</v>
       </c>
       <c r="I57" s="4" t="n"/>
-      <c r="J57" s="4" t="n"/>
+      <c r="J57" s="4" t="n">
+        <v>34.79</v>
+      </c>
       <c r="K57" s="4" t="n">
-        <v>34.6</v>
+        <v>34.49</v>
       </c>
       <c r="L57" s="4" t="n">
         <v>35.2</v>
@@ -19320,7 +19338,11 @@
       </c>
       <c r="I7" s="4" t="n"/>
       <c r="J7" s="4" t="n"/>
-      <c r="K7" s="4" t="n"/>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="L7" s="4" t="n"/>
       <c r="M7" s="4" t="n"/>
       <c r="N7" s="4" t="n"/>
@@ -19973,7 +19995,11 @@
       <c r="C13" s="4" t="n"/>
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
-      <c r="F13" s="4" t="n"/>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G13" s="4" t="n"/>
       <c r="H13" s="4" t="n"/>
       <c r="I13" s="4" t="n"/>
@@ -20016,7 +20042,11 @@
       <c r="Z13" s="4" t="n"/>
       <c r="AA13" s="4" t="n"/>
       <c r="AB13" s="4" t="n"/>
-      <c r="AC13" s="4" t="n"/>
+      <c r="AC13" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AD13" s="4" t="n"/>
       <c r="AE13" s="4" t="n"/>
       <c r="AF13" s="4" t="n"/>
@@ -20028,7 +20058,11 @@
       <c r="AL13" s="4" t="n"/>
       <c r="AM13" s="4" t="n"/>
       <c r="AN13" s="4" t="n"/>
-      <c r="AO13" s="4" t="n"/>
+      <c r="AO13" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AP13" s="4" t="n"/>
       <c r="AQ13" s="4" t="n"/>
       <c r="AR13" s="4" t="n"/>
@@ -20742,8 +20776,16 @@
       <c r="I20" s="4" t="n"/>
       <c r="J20" s="4" t="n"/>
       <c r="K20" s="4" t="n"/>
-      <c r="L20" s="4" t="n"/>
-      <c r="M20" s="4" t="n"/>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -22288,12 +22330,20 @@
       <c r="Q34" s="4" t="n"/>
       <c r="R34" s="4" t="n"/>
       <c r="S34" s="4" t="n"/>
-      <c r="T34" s="4" t="n"/>
+      <c r="T34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="U34" s="4" t="n"/>
       <c r="V34" s="4" t="n"/>
       <c r="W34" s="4" t="n"/>
       <c r="X34" s="4" t="n"/>
-      <c r="Y34" s="4" t="n"/>
+      <c r="Y34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="Z34" s="4" t="n"/>
       <c r="AA34" s="4" t="n"/>
       <c r="AB34" s="4" t="n"/>
@@ -22304,15 +22354,15 @@
       </c>
       <c r="AD34" s="4" t="n"/>
       <c r="AE34" s="4" t="n"/>
-      <c r="AF34" s="4" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="AF34" s="4" t="n"/>
       <c r="AG34" s="4" t="n"/>
       <c r="AH34" s="4" t="n"/>
       <c r="AI34" s="4" t="n"/>
-      <c r="AJ34" s="4" t="n"/>
+      <c r="AJ34" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="AK34" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -24745,7 +24795,11 @@
         </is>
       </c>
       <c r="I57" s="4" t="n"/>
-      <c r="J57" s="4" t="n"/>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
           <t>✓</t>
@@ -31771,19 +31825,19 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>9x8</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>速尾</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>玻璃</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>9x8</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>速尾</t>
-        </is>
-      </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>ssc</t>
@@ -31801,19 +31855,19 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>fp1</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>狼崽</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>万达</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>狼崽</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>fp1</t>
-        </is>
-      </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
           <t>21c</t>
@@ -31826,12 +31880,12 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>法拉第</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
           <t>火山</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>法拉第</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
@@ -31985,10 +32039,10 @@
       <c r="D2" s="4" t="n"/>
       <c r="E2" s="4" t="n"/>
       <c r="F2" s="4" t="n"/>
-      <c r="G2" s="4" t="n"/>
-      <c r="H2" s="4" t="n">
+      <c r="G2" s="4" t="n">
         <v>18.89</v>
       </c>
+      <c r="H2" s="4" t="n"/>
       <c r="I2" s="4" t="n"/>
       <c r="J2" s="4" t="n"/>
       <c r="K2" s="4" t="n"/>
@@ -32047,11 +32101,11 @@
       </c>
       <c r="E3" s="4" t="n"/>
       <c r="F3" s="4" t="n"/>
-      <c r="G3" s="4" t="n">
+      <c r="G3" s="4" t="n"/>
+      <c r="H3" s="4" t="n"/>
+      <c r="I3" s="4" t="n">
         <v>28.42</v>
       </c>
-      <c r="H3" s="4" t="n"/>
-      <c r="I3" s="4" t="n"/>
       <c r="J3" s="4" t="n">
         <v>28.45</v>
       </c>
@@ -32116,10 +32170,10 @@
         <v>30.95</v>
       </c>
       <c r="G4" s="4" t="n"/>
-      <c r="H4" s="4" t="n"/>
-      <c r="I4" s="4" t="n">
+      <c r="H4" s="4" t="n">
         <v>31.69</v>
       </c>
+      <c r="I4" s="4" t="n"/>
       <c r="J4" s="4" t="n">
         <v>30.8</v>
       </c>
@@ -32180,13 +32234,13 @@
       <c r="E5" s="4" t="n"/>
       <c r="F5" s="4" t="n"/>
       <c r="G5" s="4" t="n">
+        <v>18.15</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>18.03</v>
+      </c>
+      <c r="I5" s="4" t="n">
         <v>17.99</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>18.15</v>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>18.03</v>
       </c>
       <c r="J5" s="4" t="n"/>
       <c r="K5" s="4" t="n">
@@ -32202,10 +32256,10 @@
       <c r="Q5" s="4" t="n">
         <v>18.39</v>
       </c>
-      <c r="R5" s="4" t="n">
+      <c r="R5" s="4" t="n"/>
+      <c r="S5" s="4" t="n">
         <v>18.46</v>
       </c>
-      <c r="S5" s="4" t="n"/>
       <c r="T5" s="4" t="n"/>
       <c r="U5" s="4" t="n"/>
       <c r="V5" s="4" t="n"/>
@@ -32255,10 +32309,10 @@
       <c r="D6" s="4" t="n"/>
       <c r="E6" s="4" t="n"/>
       <c r="F6" s="4" t="n"/>
-      <c r="G6" s="4" t="n"/>
-      <c r="H6" s="4" t="n">
+      <c r="G6" s="4" t="n">
         <v>17.95</v>
       </c>
+      <c r="H6" s="4" t="n"/>
       <c r="I6" s="4" t="n"/>
       <c r="J6" s="4" t="n"/>
       <c r="K6" s="4" t="n"/>
@@ -32319,11 +32373,11 @@
         <v>24.39</v>
       </c>
       <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n">
+      <c r="G7" s="4" t="n"/>
+      <c r="H7" s="4" t="n"/>
+      <c r="I7" s="4" t="n">
         <v>24.69</v>
       </c>
-      <c r="H7" s="4" t="n"/>
-      <c r="I7" s="4" t="n"/>
       <c r="J7" s="4" t="n"/>
       <c r="K7" s="4" t="n">
         <v>24.99</v>
@@ -32383,12 +32437,12 @@
       <c r="F8" s="4" t="n">
         <v>27.73</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G8" s="4" t="n"/>
+      <c r="H8" s="4" t="n">
+        <v>28.59</v>
+      </c>
+      <c r="I8" s="4" t="n">
         <v>27.72</v>
-      </c>
-      <c r="H8" s="4" t="n"/>
-      <c r="I8" s="4" t="n">
-        <v>28.59</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>28.1</v>
@@ -32451,21 +32505,21 @@
       </c>
       <c r="E9" s="4" t="n"/>
       <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="n">
+      <c r="G9" s="4" t="n"/>
+      <c r="H9" s="4" t="n"/>
+      <c r="I9" s="4" t="n">
         <v>20.09</v>
       </c>
-      <c r="H9" s="4" t="n"/>
-      <c r="I9" s="4" t="n"/>
       <c r="J9" s="4" t="n"/>
       <c r="K9" s="4" t="n"/>
       <c r="L9" s="4" t="n">
         <v>19.55</v>
       </c>
-      <c r="M9" s="4" t="n"/>
+      <c r="M9" s="4" t="n">
+        <v>19.85</v>
+      </c>
       <c r="N9" s="4" t="n"/>
-      <c r="O9" s="4" t="n">
-        <v>19.85</v>
-      </c>
+      <c r="O9" s="4" t="n"/>
       <c r="P9" s="4" t="n">
         <v>19.47</v>
       </c>
@@ -32473,10 +32527,10 @@
         <v>20.19</v>
       </c>
       <c r="R9" s="4" t="n">
+        <v>19.69</v>
+      </c>
+      <c r="S9" s="4" t="n">
         <v>20.39</v>
-      </c>
-      <c r="S9" s="4" t="n">
-        <v>19.69</v>
       </c>
       <c r="T9" s="4" t="n"/>
       <c r="U9" s="4" t="n"/>
@@ -32523,13 +32577,13 @@
       <c r="D10" s="4" t="n"/>
       <c r="E10" s="4" t="n"/>
       <c r="F10" s="4" t="n"/>
-      <c r="G10" s="4" t="n"/>
+      <c r="G10" s="4" t="n">
+        <v>23.42</v>
+      </c>
       <c r="H10" s="4" t="n">
-        <v>23.42</v>
-      </c>
-      <c r="I10" s="4" t="n">
         <v>23.43</v>
       </c>
+      <c r="I10" s="4" t="n"/>
       <c r="J10" s="4" t="n"/>
       <c r="K10" s="4" t="n"/>
       <c r="L10" s="4" t="n"/>
@@ -32540,10 +32594,10 @@
         <v>23.11</v>
       </c>
       <c r="Q10" s="4" t="n"/>
-      <c r="R10" s="4" t="n"/>
-      <c r="S10" s="4" t="n">
+      <c r="R10" s="4" t="n">
         <v>23.29</v>
       </c>
+      <c r="S10" s="4" t="n"/>
       <c r="T10" s="4" t="n"/>
       <c r="U10" s="4" t="n"/>
       <c r="V10" s="4" t="n"/>
@@ -32589,11 +32643,11 @@
       <c r="F11" s="4" t="n">
         <v>35.25</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="G11" s="4" t="n"/>
+      <c r="H11" s="4" t="n"/>
+      <c r="I11" s="4" t="n">
         <v>35.49</v>
       </c>
-      <c r="H11" s="4" t="n"/>
-      <c r="I11" s="4" t="n"/>
       <c r="J11" s="4" t="n"/>
       <c r="K11" s="4" t="n"/>
       <c r="L11" s="4" t="n"/>
@@ -32644,10 +32698,10 @@
       <c r="E12" s="4" t="n"/>
       <c r="F12" s="4" t="n"/>
       <c r="G12" s="4" t="n"/>
-      <c r="H12" s="4" t="n"/>
-      <c r="I12" s="4" t="n">
+      <c r="H12" s="4" t="n">
         <v>21.83</v>
       </c>
+      <c r="I12" s="4" t="n"/>
       <c r="J12" s="4" t="n"/>
       <c r="K12" s="4" t="n">
         <v>21.55</v>
@@ -32662,10 +32716,10 @@
         <v>21.39</v>
       </c>
       <c r="Q12" s="4" t="n"/>
-      <c r="R12" s="4" t="n"/>
-      <c r="S12" s="4" t="n">
+      <c r="R12" s="4" t="n">
         <v>21.81</v>
       </c>
+      <c r="S12" s="4" t="n"/>
       <c r="T12" s="4" t="n"/>
       <c r="U12" s="4" t="n"/>
       <c r="V12" s="4" t="n"/>
@@ -32777,10 +32831,10 @@
         <v>25.29</v>
       </c>
       <c r="F14" s="4" t="n"/>
-      <c r="G14" s="4" t="n"/>
-      <c r="H14" s="4" t="n">
+      <c r="G14" s="4" t="n">
         <v>26.19</v>
       </c>
+      <c r="H14" s="4" t="n"/>
       <c r="I14" s="4" t="n"/>
       <c r="J14" s="4" t="n"/>
       <c r="K14" s="4" t="n"/>
@@ -32790,10 +32844,10 @@
       <c r="O14" s="4" t="n"/>
       <c r="P14" s="4" t="n"/>
       <c r="Q14" s="4" t="n"/>
-      <c r="R14" s="4" t="n">
+      <c r="R14" s="4" t="n"/>
+      <c r="S14" s="4" t="n">
         <v>26.6</v>
       </c>
-      <c r="S14" s="4" t="n"/>
       <c r="T14" s="4" t="n"/>
       <c r="U14" s="4" t="n"/>
       <c r="V14" s="4" t="n">
@@ -32846,13 +32900,13 @@
         <v>28.9</v>
       </c>
       <c r="G15" s="4" t="n">
+        <v>29.19</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>29.49</v>
+      </c>
+      <c r="I15" s="4" t="n">
         <v>28.82</v>
-      </c>
-      <c r="H15" s="4" t="n">
-        <v>29.19</v>
-      </c>
-      <c r="I15" s="4" t="n">
-        <v>29.49</v>
       </c>
       <c r="J15" s="4" t="n"/>
       <c r="K15" s="4" t="n"/>
@@ -32974,13 +33028,13 @@
       </c>
       <c r="F17" s="4" t="n"/>
       <c r="G17" s="4" t="n">
+        <v>30.69</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>30.59</v>
+      </c>
+      <c r="I17" s="4" t="n">
         <v>29.75</v>
-      </c>
-      <c r="H17" s="4" t="n">
-        <v>30.69</v>
-      </c>
-      <c r="I17" s="4" t="n">
-        <v>30.59</v>
       </c>
       <c r="J17" s="4" t="n"/>
       <c r="K17" s="4" t="n"/>
@@ -33038,10 +33092,10 @@
       <c r="E18" s="4" t="n"/>
       <c r="F18" s="4" t="n"/>
       <c r="G18" s="4" t="n"/>
-      <c r="H18" s="4" t="n"/>
-      <c r="I18" s="4" t="n">
+      <c r="H18" s="4" t="n">
         <v>23.72</v>
       </c>
+      <c r="I18" s="4" t="n"/>
       <c r="J18" s="4" t="n">
         <v>23.98</v>
       </c>
@@ -33059,10 +33113,10 @@
       <c r="P18" s="4" t="n"/>
       <c r="Q18" s="4" t="n"/>
       <c r="R18" s="4" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="S18" s="4" t="n">
         <v>24.49</v>
-      </c>
-      <c r="S18" s="4" t="n">
-        <v>23.75</v>
       </c>
       <c r="T18" s="4" t="n"/>
       <c r="U18" s="4" t="n">
@@ -33115,19 +33169,19 @@
       <c r="F19" s="4" t="n">
         <v>32.19</v>
       </c>
-      <c r="G19" s="4" t="n"/>
-      <c r="H19" s="4" t="n">
+      <c r="G19" s="4" t="n">
         <v>33.05</v>
       </c>
+      <c r="H19" s="4" t="n"/>
       <c r="I19" s="4" t="n"/>
       <c r="J19" s="4" t="n"/>
       <c r="K19" s="4" t="n"/>
       <c r="L19" s="4" t="n"/>
-      <c r="M19" s="4" t="n"/>
+      <c r="M19" s="4" t="n">
+        <v>33.07</v>
+      </c>
       <c r="N19" s="4" t="n"/>
-      <c r="O19" s="4" t="n">
-        <v>33.07</v>
-      </c>
+      <c r="O19" s="4" t="n"/>
       <c r="P19" s="4" t="n"/>
       <c r="Q19" s="4" t="n"/>
       <c r="R19" s="4" t="n"/>
@@ -33177,19 +33231,19 @@
         <v>22.09</v>
       </c>
       <c r="F20" s="4" t="n"/>
-      <c r="G20" s="4" t="n"/>
-      <c r="H20" s="4" t="n">
+      <c r="G20" s="4" t="n">
         <v>22.4</v>
       </c>
+      <c r="H20" s="4" t="n"/>
       <c r="I20" s="4" t="n"/>
       <c r="J20" s="4" t="n"/>
       <c r="K20" s="4" t="n"/>
       <c r="L20" s="4" t="n"/>
-      <c r="M20" s="4" t="n">
+      <c r="M20" s="4" t="n"/>
+      <c r="N20" s="4" t="n"/>
+      <c r="O20" s="4" t="n">
         <v>22.59</v>
       </c>
-      <c r="N20" s="4" t="n"/>
-      <c r="O20" s="4" t="n"/>
       <c r="P20" s="4" t="n"/>
       <c r="Q20" s="4" t="n"/>
       <c r="R20" s="4" t="n"/>
@@ -33322,10 +33376,10 @@
       <c r="O22" s="4" t="n"/>
       <c r="P22" s="4" t="n"/>
       <c r="Q22" s="4" t="n"/>
-      <c r="R22" s="4" t="n"/>
-      <c r="S22" s="4" t="n">
+      <c r="R22" s="4" t="n">
         <v>31.89</v>
       </c>
+      <c r="S22" s="4" t="n"/>
       <c r="T22" s="4" t="n"/>
       <c r="U22" s="4" t="n"/>
       <c r="V22" s="4" t="n"/>
@@ -33444,10 +33498,10 @@
         <v>22.69</v>
       </c>
       <c r="Q24" s="4" t="n"/>
-      <c r="R24" s="4" t="n"/>
-      <c r="S24" s="4" t="n">
+      <c r="R24" s="4" t="n">
         <v>22.89</v>
       </c>
+      <c r="S24" s="4" t="n"/>
       <c r="T24" s="4" t="n"/>
       <c r="U24" s="4" t="n"/>
       <c r="V24" s="4" t="n"/>
@@ -33488,10 +33542,10 @@
       <c r="E25" s="4" t="n"/>
       <c r="F25" s="4" t="n"/>
       <c r="G25" s="4" t="n"/>
-      <c r="H25" s="4" t="n"/>
-      <c r="I25" s="4" t="n">
+      <c r="H25" s="4" t="n">
         <v>24.35</v>
       </c>
+      <c r="I25" s="4" t="n"/>
       <c r="J25" s="4" t="n"/>
       <c r="K25" s="4" t="n"/>
       <c r="L25" s="4" t="n">
@@ -33504,10 +33558,10 @@
         <v>24.13</v>
       </c>
       <c r="Q25" s="4" t="n"/>
-      <c r="R25" s="4" t="n">
+      <c r="R25" s="4" t="n"/>
+      <c r="S25" s="4" t="n">
         <v>24.89</v>
       </c>
-      <c r="S25" s="4" t="n"/>
       <c r="T25" s="4" t="n"/>
       <c r="U25" s="4" t="n"/>
       <c r="V25" s="4" t="n"/>
@@ -33554,10 +33608,10 @@
       <c r="E26" s="4" t="n"/>
       <c r="F26" s="4" t="n"/>
       <c r="G26" s="4" t="n"/>
-      <c r="H26" s="4" t="n"/>
-      <c r="I26" s="4" t="n">
+      <c r="H26" s="4" t="n">
         <v>18.89</v>
       </c>
+      <c r="I26" s="4" t="n"/>
       <c r="J26" s="4" t="n"/>
       <c r="K26" s="4" t="n">
         <v>18.6</v>
@@ -33572,10 +33626,10 @@
         <v>18.59</v>
       </c>
       <c r="Q26" s="4" t="n"/>
-      <c r="R26" s="4" t="n"/>
-      <c r="S26" s="4" t="n">
+      <c r="R26" s="4" t="n">
         <v>18.69</v>
       </c>
+      <c r="S26" s="4" t="n"/>
       <c r="T26" s="4" t="n"/>
       <c r="U26" s="4" t="n"/>
       <c r="V26" s="4" t="n"/>
@@ -33619,11 +33673,11 @@
       <c r="D27" s="4" t="n"/>
       <c r="E27" s="4" t="n"/>
       <c r="F27" s="4" t="n"/>
-      <c r="G27" s="4" t="n">
+      <c r="G27" s="4" t="n"/>
+      <c r="H27" s="4" t="n"/>
+      <c r="I27" s="4" t="n">
         <v>32.85</v>
       </c>
-      <c r="H27" s="4" t="n"/>
-      <c r="I27" s="4" t="n"/>
       <c r="J27" s="4" t="n">
         <v>32.79</v>
       </c>
@@ -33682,10 +33736,10 @@
       </c>
       <c r="F28" s="4" t="n"/>
       <c r="G28" s="4" t="n"/>
-      <c r="H28" s="4" t="n"/>
-      <c r="I28" s="4" t="n">
+      <c r="H28" s="4" t="n">
         <v>33.09</v>
       </c>
+      <c r="I28" s="4" t="n"/>
       <c r="J28" s="4" t="n"/>
       <c r="K28" s="4" t="n">
         <v>33.05</v>
@@ -33745,11 +33799,11 @@
         <v>17.29</v>
       </c>
       <c r="F29" s="4" t="n"/>
-      <c r="G29" s="4" t="n">
+      <c r="G29" s="4" t="n"/>
+      <c r="H29" s="4" t="n"/>
+      <c r="I29" s="4" t="n">
         <v>17.89</v>
       </c>
-      <c r="H29" s="4" t="n"/>
-      <c r="I29" s="4" t="n"/>
       <c r="J29" s="4" t="n"/>
       <c r="K29" s="4" t="n"/>
       <c r="L29" s="4" t="n"/>
@@ -33809,19 +33863,19 @@
       <c r="D30" s="4" t="n"/>
       <c r="E30" s="4" t="n"/>
       <c r="F30" s="4" t="n"/>
-      <c r="G30" s="4" t="n"/>
-      <c r="H30" s="4" t="n">
+      <c r="G30" s="4" t="n">
         <v>23.1</v>
       </c>
+      <c r="H30" s="4" t="n"/>
       <c r="I30" s="4" t="n"/>
       <c r="J30" s="4" t="n"/>
       <c r="K30" s="4" t="n"/>
       <c r="L30" s="4" t="n"/>
-      <c r="M30" s="4" t="n">
+      <c r="M30" s="4" t="n"/>
+      <c r="N30" s="4" t="n"/>
+      <c r="O30" s="4" t="n">
         <v>23.29</v>
       </c>
-      <c r="N30" s="4" t="n"/>
-      <c r="O30" s="4" t="n"/>
       <c r="P30" s="4" t="n"/>
       <c r="Q30" s="4" t="n">
         <v>23.39</v>
@@ -33873,13 +33927,13 @@
       <c r="D31" s="4" t="n"/>
       <c r="E31" s="4" t="n"/>
       <c r="F31" s="4" t="n"/>
-      <c r="G31" s="4" t="n"/>
+      <c r="G31" s="4" t="n">
+        <v>18.99</v>
+      </c>
       <c r="H31" s="4" t="n">
-        <v>18.99</v>
-      </c>
-      <c r="I31" s="4" t="n">
         <v>19.35</v>
       </c>
+      <c r="I31" s="4" t="n"/>
       <c r="J31" s="4" t="n"/>
       <c r="K31" s="4" t="n"/>
       <c r="L31" s="4" t="n"/>
@@ -33945,13 +33999,13 @@
       <c r="F32" s="4" t="n">
         <v>27.8</v>
       </c>
-      <c r="G32" s="4" t="n"/>
+      <c r="G32" s="4" t="n">
+        <v>29.06</v>
+      </c>
       <c r="H32" s="4" t="n">
-        <v>29.06</v>
-      </c>
-      <c r="I32" s="4" t="n">
         <v>28.39</v>
       </c>
+      <c r="I32" s="4" t="n"/>
       <c r="J32" s="4" t="n"/>
       <c r="K32" s="4" t="n"/>
       <c r="L32" s="4" t="n"/>
@@ -34013,19 +34067,19 @@
       <c r="D33" s="4" t="n"/>
       <c r="E33" s="4" t="n"/>
       <c r="F33" s="4" t="n"/>
-      <c r="G33" s="4" t="n"/>
-      <c r="H33" s="4" t="n">
+      <c r="G33" s="4" t="n">
         <v>19.89</v>
       </c>
+      <c r="H33" s="4" t="n"/>
       <c r="I33" s="4" t="n"/>
       <c r="J33" s="4" t="n"/>
       <c r="K33" s="4" t="n"/>
       <c r="L33" s="4" t="n"/>
-      <c r="M33" s="4" t="n">
+      <c r="M33" s="4" t="n"/>
+      <c r="N33" s="4" t="n"/>
+      <c r="O33" s="4" t="n">
         <v>20.21</v>
       </c>
-      <c r="N33" s="4" t="n"/>
-      <c r="O33" s="4" t="n"/>
       <c r="P33" s="4" t="n"/>
       <c r="Q33" s="4" t="n">
         <v>20.49</v>
@@ -34082,10 +34136,10 @@
       </c>
       <c r="F34" s="4" t="n"/>
       <c r="G34" s="4" t="n"/>
-      <c r="H34" s="4" t="n"/>
-      <c r="I34" s="4" t="n">
+      <c r="H34" s="4" t="n">
         <v>35.49</v>
       </c>
+      <c r="I34" s="4" t="n"/>
       <c r="J34" s="4" t="n">
         <v>34.7</v>
       </c>
@@ -34139,21 +34193,21 @@
       <c r="D35" s="4" t="n"/>
       <c r="E35" s="4" t="n"/>
       <c r="F35" s="4" t="n"/>
-      <c r="G35" s="4" t="n"/>
+      <c r="G35" s="4" t="n">
+        <v>23.59</v>
+      </c>
       <c r="H35" s="4" t="n">
-        <v>23.59</v>
-      </c>
-      <c r="I35" s="4" t="n">
         <v>23.6</v>
       </c>
+      <c r="I35" s="4" t="n"/>
       <c r="J35" s="4" t="n"/>
       <c r="K35" s="4" t="n"/>
       <c r="L35" s="4" t="n"/>
-      <c r="M35" s="4" t="n">
+      <c r="M35" s="4" t="n"/>
+      <c r="N35" s="4" t="n"/>
+      <c r="O35" s="4" t="n">
         <v>23.69</v>
       </c>
-      <c r="N35" s="4" t="n"/>
-      <c r="O35" s="4" t="n"/>
       <c r="P35" s="4" t="n"/>
       <c r="Q35" s="4" t="n"/>
       <c r="R35" s="4" t="n"/>
@@ -34207,10 +34261,10 @@
       <c r="F36" s="4" t="n">
         <v>34.6</v>
       </c>
-      <c r="G36" s="4" t="n"/>
-      <c r="H36" s="4" t="n">
+      <c r="G36" s="4" t="n">
         <v>35.89</v>
       </c>
+      <c r="H36" s="4" t="n"/>
       <c r="I36" s="4" t="n"/>
       <c r="J36" s="4" t="n"/>
       <c r="K36" s="4" t="n"/>
@@ -34269,10 +34323,10 @@
         <v>22.45</v>
       </c>
       <c r="F37" s="4" t="n"/>
-      <c r="G37" s="4" t="n"/>
-      <c r="H37" s="4" t="n">
+      <c r="G37" s="4" t="n">
         <v>23.05</v>
       </c>
+      <c r="H37" s="4" t="n"/>
       <c r="I37" s="4" t="n"/>
       <c r="J37" s="4" t="n"/>
       <c r="K37" s="4" t="n"/>
@@ -34327,13 +34381,13 @@
       <c r="D38" s="4" t="n"/>
       <c r="E38" s="4" t="n"/>
       <c r="F38" s="4" t="n"/>
-      <c r="G38" s="4" t="n"/>
+      <c r="G38" s="4" t="n">
+        <v>21.48</v>
+      </c>
       <c r="H38" s="4" t="n">
-        <v>21.48</v>
-      </c>
-      <c r="I38" s="4" t="n">
         <v>20.99</v>
       </c>
+      <c r="I38" s="4" t="n"/>
       <c r="J38" s="4" t="n"/>
       <c r="K38" s="4" t="n">
         <v>21.09</v>
@@ -34349,10 +34403,10 @@
       </c>
       <c r="Q38" s="4" t="n"/>
       <c r="R38" s="4" t="n">
+        <v>21.19</v>
+      </c>
+      <c r="S38" s="4" t="n">
         <v>21.79</v>
-      </c>
-      <c r="S38" s="4" t="n">
-        <v>21.19</v>
       </c>
       <c r="T38" s="4" t="n"/>
       <c r="U38" s="4" t="n">
@@ -34398,10 +34452,10 @@
       <c r="E39" s="4" t="n"/>
       <c r="F39" s="4" t="n"/>
       <c r="G39" s="4" t="n"/>
-      <c r="H39" s="4" t="n"/>
-      <c r="I39" s="4" t="n">
+      <c r="H39" s="4" t="n">
         <v>29.75</v>
       </c>
+      <c r="I39" s="4" t="n"/>
       <c r="J39" s="4" t="n"/>
       <c r="K39" s="4" t="n">
         <v>29.95</v>
@@ -34464,12 +34518,12 @@
         <v>33.59</v>
       </c>
       <c r="G40" s="4" t="n">
+        <v>34.9</v>
+      </c>
+      <c r="H40" s="4" t="n"/>
+      <c r="I40" s="4" t="n">
         <v>33.99</v>
       </c>
-      <c r="H40" s="4" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="I40" s="4" t="n"/>
       <c r="J40" s="4" t="n"/>
       <c r="K40" s="4" t="n"/>
       <c r="L40" s="4" t="n"/>
@@ -34531,11 +34585,11 @@
       <c r="F41" s="4" t="n">
         <v>30.39</v>
       </c>
-      <c r="G41" s="4" t="n">
+      <c r="G41" s="4" t="n"/>
+      <c r="H41" s="4" t="n"/>
+      <c r="I41" s="4" t="n">
         <v>30.29</v>
       </c>
-      <c r="H41" s="4" t="n"/>
-      <c r="I41" s="4" t="n"/>
       <c r="J41" s="4" t="n"/>
       <c r="K41" s="4" t="n"/>
       <c r="L41" s="4" t="n"/>
@@ -34587,23 +34641,23 @@
       </c>
       <c r="E42" s="4" t="n"/>
       <c r="F42" s="4" t="n"/>
-      <c r="G42" s="4" t="n"/>
-      <c r="H42" s="4" t="n">
+      <c r="G42" s="4" t="n">
         <v>22.3</v>
       </c>
+      <c r="H42" s="4" t="n"/>
       <c r="I42" s="4" t="n"/>
       <c r="J42" s="4" t="n"/>
       <c r="K42" s="4" t="n"/>
       <c r="L42" s="4" t="n">
         <v>22.05</v>
       </c>
-      <c r="M42" s="4" t="n"/>
+      <c r="M42" s="4" t="n">
+        <v>22.79</v>
+      </c>
       <c r="N42" s="4" t="n">
         <v>22.89</v>
       </c>
-      <c r="O42" s="4" t="n">
-        <v>22.79</v>
-      </c>
+      <c r="O42" s="4" t="n"/>
       <c r="P42" s="4" t="n">
         <v>21.95</v>
       </c>
@@ -34661,11 +34715,11 @@
       <c r="F43" s="4" t="n">
         <v>38.09</v>
       </c>
-      <c r="G43" s="4" t="n">
+      <c r="G43" s="4" t="n"/>
+      <c r="H43" s="4" t="n"/>
+      <c r="I43" s="4" t="n">
         <v>38.2</v>
       </c>
-      <c r="H43" s="4" t="n"/>
-      <c r="I43" s="4" t="n"/>
       <c r="J43" s="4" t="n"/>
       <c r="K43" s="4" t="n"/>
       <c r="L43" s="4" t="n"/>
@@ -34715,10 +34769,10 @@
       <c r="D44" s="4" t="n"/>
       <c r="E44" s="4" t="n"/>
       <c r="F44" s="4" t="n"/>
-      <c r="G44" s="4" t="n"/>
-      <c r="H44" s="4" t="n">
+      <c r="G44" s="4" t="n">
         <v>22.25</v>
       </c>
+      <c r="H44" s="4" t="n"/>
       <c r="I44" s="4" t="n"/>
       <c r="J44" s="4" t="n"/>
       <c r="K44" s="4" t="n"/>
@@ -34794,10 +34848,10 @@
       </c>
       <c r="F45" s="4" t="n"/>
       <c r="G45" s="4" t="n"/>
-      <c r="H45" s="4" t="n"/>
-      <c r="I45" s="4" t="n">
+      <c r="H45" s="4" t="n">
         <v>40.69</v>
       </c>
+      <c r="I45" s="4" t="n"/>
       <c r="J45" s="4" t="n"/>
       <c r="K45" s="4" t="n"/>
       <c r="L45" s="4" t="n"/>
@@ -34857,11 +34911,11 @@
       <c r="F46" s="4" t="n">
         <v>32.29</v>
       </c>
-      <c r="G46" s="4" t="n">
+      <c r="G46" s="4" t="n"/>
+      <c r="H46" s="4" t="n"/>
+      <c r="I46" s="4" t="n">
         <v>32.49</v>
       </c>
-      <c r="H46" s="4" t="n"/>
-      <c r="I46" s="4" t="n"/>
       <c r="J46" s="4" t="n"/>
       <c r="K46" s="4" t="n"/>
       <c r="L46" s="4" t="n"/>
@@ -34972,10 +35026,10 @@
       <c r="E48" s="4" t="n"/>
       <c r="F48" s="4" t="n"/>
       <c r="G48" s="4" t="n"/>
-      <c r="H48" s="4" t="n"/>
-      <c r="I48" s="4" t="n">
+      <c r="H48" s="4" t="n">
         <v>24.97</v>
       </c>
+      <c r="I48" s="4" t="n"/>
       <c r="J48" s="4" t="n"/>
       <c r="K48" s="4" t="n">
         <v>24.79</v>
@@ -35045,11 +35099,11 @@
       <c r="J49" s="4" t="n"/>
       <c r="K49" s="4" t="n"/>
       <c r="L49" s="4" t="n"/>
-      <c r="M49" s="4" t="n">
+      <c r="M49" s="4" t="n"/>
+      <c r="N49" s="4" t="n"/>
+      <c r="O49" s="4" t="n">
         <v>30.99</v>
       </c>
-      <c r="N49" s="4" t="n"/>
-      <c r="O49" s="4" t="n"/>
       <c r="P49" s="4" t="n"/>
       <c r="Q49" s="4" t="n"/>
       <c r="R49" s="4" t="n"/>
@@ -35097,19 +35151,19 @@
         <v>25.99</v>
       </c>
       <c r="F50" s="4" t="n"/>
-      <c r="G50" s="4" t="n"/>
-      <c r="H50" s="4" t="n">
+      <c r="G50" s="4" t="n">
         <v>26.59</v>
       </c>
+      <c r="H50" s="4" t="n"/>
       <c r="I50" s="4" t="n"/>
       <c r="J50" s="4" t="n"/>
       <c r="K50" s="4" t="n"/>
       <c r="L50" s="4" t="n"/>
-      <c r="M50" s="4" t="n">
+      <c r="M50" s="4" t="n"/>
+      <c r="N50" s="4" t="n"/>
+      <c r="O50" s="4" t="n">
         <v>26.75</v>
       </c>
-      <c r="N50" s="4" t="n"/>
-      <c r="O50" s="4" t="n"/>
       <c r="P50" s="4" t="n"/>
       <c r="Q50" s="4" t="n"/>
       <c r="R50" s="4" t="n"/>
@@ -35158,13 +35212,13 @@
       <c r="E51" s="4" t="n"/>
       <c r="F51" s="4" t="n"/>
       <c r="G51" s="4" t="n">
+        <v>24.39</v>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>24.29</v>
+      </c>
+      <c r="I51" s="4" t="n">
         <v>24.09</v>
-      </c>
-      <c r="H51" s="4" t="n">
-        <v>24.39</v>
-      </c>
-      <c r="I51" s="4" t="n">
-        <v>24.29</v>
       </c>
       <c r="J51" s="4" t="n"/>
       <c r="K51" s="4" t="n">
@@ -35229,11 +35283,11 @@
       <c r="F52" s="4" t="n">
         <v>32.3</v>
       </c>
-      <c r="G52" s="4" t="n">
+      <c r="G52" s="4" t="n"/>
+      <c r="H52" s="4" t="n"/>
+      <c r="I52" s="4" t="n">
         <v>32.05</v>
       </c>
-      <c r="H52" s="4" t="n"/>
-      <c r="I52" s="4" t="n"/>
       <c r="J52" s="4" t="n"/>
       <c r="K52" s="4" t="n"/>
       <c r="L52" s="4" t="n"/>
@@ -35412,20 +35466,20 @@
       </c>
       <c r="F55" s="4" t="n"/>
       <c r="G55" s="4" t="n">
+        <v>32.73</v>
+      </c>
+      <c r="H55" s="4" t="n"/>
+      <c r="I55" s="4" t="n">
         <v>32.85</v>
       </c>
-      <c r="H55" s="4" t="n">
-        <v>32.73</v>
-      </c>
-      <c r="I55" s="4" t="n"/>
       <c r="J55" s="4" t="n"/>
       <c r="K55" s="4" t="n"/>
       <c r="L55" s="4" t="n"/>
-      <c r="M55" s="4" t="n">
+      <c r="M55" s="4" t="n"/>
+      <c r="N55" s="4" t="n"/>
+      <c r="O55" s="4" t="n">
         <v>33.3</v>
       </c>
-      <c r="N55" s="4" t="n"/>
-      <c r="O55" s="4" t="n"/>
       <c r="P55" s="4" t="n"/>
       <c r="Q55" s="4" t="n"/>
       <c r="R55" s="4" t="n"/>
@@ -35477,11 +35531,11 @@
       <c r="F56" s="4" t="n">
         <v>35.6</v>
       </c>
-      <c r="G56" s="4" t="n">
+      <c r="G56" s="4" t="n"/>
+      <c r="H56" s="4" t="n"/>
+      <c r="I56" s="4" t="n">
         <v>35.95</v>
       </c>
-      <c r="H56" s="4" t="n"/>
-      <c r="I56" s="4" t="n"/>
       <c r="J56" s="4" t="n">
         <v>36.89</v>
       </c>
@@ -35543,11 +35597,11 @@
         <v>34.55</v>
       </c>
       <c r="F57" s="4" t="n"/>
-      <c r="G57" s="4" t="n">
+      <c r="G57" s="4" t="n"/>
+      <c r="H57" s="4" t="n"/>
+      <c r="I57" s="4" t="n">
         <v>35.55</v>
       </c>
-      <c r="H57" s="4" t="n"/>
-      <c r="I57" s="4" t="n"/>
       <c r="J57" s="4" t="n"/>
       <c r="K57" s="4" t="n"/>
       <c r="L57" s="4" t="n"/>
@@ -35605,11 +35659,11 @@
       <c r="F58" s="4" t="n">
         <v>24.43</v>
       </c>
-      <c r="G58" s="4" t="n">
+      <c r="G58" s="4" t="n"/>
+      <c r="H58" s="4" t="n"/>
+      <c r="I58" s="4" t="n">
         <v>24.59</v>
       </c>
-      <c r="H58" s="4" t="n"/>
-      <c r="I58" s="4" t="n"/>
       <c r="J58" s="4" t="n"/>
       <c r="K58" s="4" t="n"/>
       <c r="L58" s="4" t="n"/>
@@ -35666,26 +35720,26 @@
       <c r="E59" s="4" t="n"/>
       <c r="F59" s="4" t="n"/>
       <c r="G59" s="4" t="n">
+        <v>21.19</v>
+      </c>
+      <c r="H59" s="4" t="n"/>
+      <c r="I59" s="4" t="n">
         <v>21.29</v>
       </c>
-      <c r="H59" s="4" t="n">
-        <v>21.19</v>
-      </c>
-      <c r="I59" s="4" t="n"/>
       <c r="J59" s="4" t="n"/>
       <c r="K59" s="4" t="n"/>
       <c r="L59" s="4" t="n"/>
-      <c r="M59" s="4" t="n"/>
+      <c r="M59" s="4" t="n">
+        <v>21.22</v>
+      </c>
       <c r="N59" s="4" t="n"/>
-      <c r="O59" s="4" t="n">
-        <v>21.22</v>
-      </c>
+      <c r="O59" s="4" t="n"/>
       <c r="P59" s="4" t="n"/>
       <c r="Q59" s="4" t="n"/>
-      <c r="R59" s="4" t="n">
+      <c r="R59" s="4" t="n"/>
+      <c r="S59" s="4" t="n">
         <v>22.13</v>
       </c>
-      <c r="S59" s="4" t="n"/>
       <c r="T59" s="4" t="n"/>
       <c r="U59" s="4" t="n"/>
       <c r="V59" s="4" t="n"/>
@@ -35793,29 +35847,29 @@
       </c>
       <c r="E61" s="4" t="n"/>
       <c r="F61" s="4" t="n"/>
-      <c r="G61" s="4" t="n"/>
-      <c r="H61" s="4" t="n">
+      <c r="G61" s="4" t="n">
         <v>21.72</v>
       </c>
+      <c r="H61" s="4" t="n"/>
       <c r="I61" s="4" t="n"/>
       <c r="J61" s="4" t="n"/>
       <c r="K61" s="4" t="n"/>
       <c r="L61" s="4" t="n">
         <v>21.75</v>
       </c>
-      <c r="M61" s="4" t="n"/>
+      <c r="M61" s="4" t="n">
+        <v>21.75</v>
+      </c>
       <c r="N61" s="4" t="n"/>
-      <c r="O61" s="4" t="n">
-        <v>21.75</v>
-      </c>
+      <c r="O61" s="4" t="n"/>
       <c r="P61" s="4" t="n">
         <v>21.82</v>
       </c>
       <c r="Q61" s="4" t="n"/>
-      <c r="R61" s="4" t="n">
+      <c r="R61" s="4" t="n"/>
+      <c r="S61" s="4" t="n">
         <v>22.5</v>
       </c>
-      <c r="S61" s="4" t="n"/>
       <c r="T61" s="4" t="n"/>
       <c r="U61" s="4" t="n"/>
       <c r="V61" s="4" t="n"/>
@@ -35874,13 +35928,13 @@
         <v>29.85</v>
       </c>
       <c r="G62" s="4" t="n">
+        <v>31.49</v>
+      </c>
+      <c r="H62" s="4" t="n">
+        <v>30.89</v>
+      </c>
+      <c r="I62" s="4" t="n">
         <v>29.99</v>
-      </c>
-      <c r="H62" s="4" t="n">
-        <v>31.49</v>
-      </c>
-      <c r="I62" s="4" t="n">
-        <v>30.89</v>
       </c>
       <c r="J62" s="4" t="n"/>
       <c r="K62" s="4" t="n"/>
@@ -35934,12 +35988,12 @@
       <c r="E63" s="4" t="n"/>
       <c r="F63" s="4" t="n"/>
       <c r="G63" s="4" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="H63" s="4" t="n"/>
+      <c r="I63" s="4" t="n">
         <v>23.8</v>
       </c>
-      <c r="H63" s="4" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="I63" s="4" t="n"/>
       <c r="J63" s="4" t="n"/>
       <c r="K63" s="4" t="n"/>
       <c r="L63" s="4" t="n"/>
@@ -35997,11 +36051,11 @@
       <c r="F64" s="4" t="n">
         <v>33.8</v>
       </c>
-      <c r="G64" s="4" t="n">
+      <c r="G64" s="4" t="n"/>
+      <c r="H64" s="4" t="n"/>
+      <c r="I64" s="4" t="n">
         <v>33.89</v>
       </c>
-      <c r="H64" s="4" t="n"/>
-      <c r="I64" s="4" t="n"/>
       <c r="J64" s="4" t="n"/>
       <c r="K64" s="4" t="n"/>
       <c r="L64" s="4" t="n"/>
@@ -36064,10 +36118,10 @@
         <v>32.9</v>
       </c>
       <c r="G65" s="4" t="n"/>
-      <c r="H65" s="4" t="n"/>
-      <c r="I65" s="4" t="n">
+      <c r="H65" s="4" t="n">
         <v>33.79</v>
       </c>
+      <c r="I65" s="4" t="n"/>
       <c r="J65" s="4" t="n"/>
       <c r="K65" s="4" t="n"/>
       <c r="L65" s="4" t="n"/>
@@ -36176,10 +36230,10 @@
       <c r="E67" s="4" t="n"/>
       <c r="F67" s="4" t="n"/>
       <c r="G67" s="4" t="n"/>
-      <c r="H67" s="4" t="n"/>
-      <c r="I67" s="4" t="n">
+      <c r="H67" s="4" t="n">
         <v>18.09</v>
       </c>
+      <c r="I67" s="4" t="n"/>
       <c r="J67" s="4" t="n"/>
       <c r="K67" s="4" t="n"/>
       <c r="L67" s="4" t="n"/>
@@ -36190,10 +36244,10 @@
         <v>17.95</v>
       </c>
       <c r="Q67" s="4" t="n"/>
-      <c r="R67" s="4" t="n"/>
-      <c r="S67" s="4" t="n">
+      <c r="R67" s="4" t="n">
         <v>18.13</v>
       </c>
+      <c r="S67" s="4" t="n"/>
       <c r="T67" s="4" t="n"/>
       <c r="U67" s="4" t="n">
         <v>18.55</v>
@@ -36241,11 +36295,11 @@
       <c r="D68" s="4" t="n"/>
       <c r="E68" s="4" t="n"/>
       <c r="F68" s="4" t="n"/>
-      <c r="G68" s="4" t="n">
+      <c r="G68" s="4" t="n"/>
+      <c r="H68" s="4" t="n"/>
+      <c r="I68" s="4" t="n">
         <v>27.5</v>
       </c>
-      <c r="H68" s="4" t="n"/>
-      <c r="I68" s="4" t="n"/>
       <c r="J68" s="4" t="n"/>
       <c r="K68" s="4" t="n"/>
       <c r="L68" s="4" t="n"/>
@@ -36309,11 +36363,11 @@
       <c r="F69" s="4" t="n">
         <v>32.97</v>
       </c>
-      <c r="G69" s="4" t="n">
+      <c r="G69" s="4" t="n"/>
+      <c r="H69" s="4" t="n"/>
+      <c r="I69" s="4" t="n">
         <v>33.79</v>
       </c>
-      <c r="H69" s="4" t="n"/>
-      <c r="I69" s="4" t="n"/>
       <c r="J69" s="4" t="n"/>
       <c r="K69" s="4" t="n"/>
       <c r="L69" s="4" t="n"/>
@@ -36366,10 +36420,10 @@
       <c r="E70" s="4" t="n"/>
       <c r="F70" s="4" t="n"/>
       <c r="G70" s="4" t="n"/>
-      <c r="H70" s="4" t="n"/>
-      <c r="I70" s="4" t="n">
+      <c r="H70" s="4" t="n">
         <v>21.63</v>
       </c>
+      <c r="I70" s="4" t="n"/>
       <c r="J70" s="4" t="n"/>
       <c r="K70" s="4" t="n"/>
       <c r="L70" s="4" t="n">
@@ -36382,10 +36436,10 @@
         <v>20.99</v>
       </c>
       <c r="Q70" s="4" t="n"/>
-      <c r="R70" s="4" t="n">
+      <c r="R70" s="4" t="n"/>
+      <c r="S70" s="4" t="n">
         <v>22.03</v>
       </c>
-      <c r="S70" s="4" t="n"/>
       <c r="T70" s="4" t="n"/>
       <c r="U70" s="4" t="n"/>
       <c r="V70" s="4" t="n"/>
@@ -36433,11 +36487,11 @@
       <c r="F71" s="4" t="n">
         <v>38.07</v>
       </c>
-      <c r="G71" s="4" t="n">
+      <c r="G71" s="4" t="n"/>
+      <c r="H71" s="4" t="n"/>
+      <c r="I71" s="4" t="n">
         <v>38.3</v>
       </c>
-      <c r="H71" s="4" t="n"/>
-      <c r="I71" s="4" t="n"/>
       <c r="J71" s="4" t="n">
         <v>38.79</v>
       </c>
@@ -36493,23 +36547,23 @@
         <v>25.6</v>
       </c>
       <c r="F72" s="4" t="n"/>
-      <c r="G72" s="4" t="n"/>
+      <c r="G72" s="4" t="n">
+        <v>25.93</v>
+      </c>
       <c r="H72" s="4" t="n">
-        <v>25.93</v>
-      </c>
-      <c r="I72" s="4" t="n">
         <v>25.85</v>
       </c>
+      <c r="I72" s="4" t="n"/>
       <c r="J72" s="4" t="n"/>
       <c r="K72" s="4" t="n"/>
       <c r="L72" s="4" t="n">
         <v>25.79</v>
       </c>
-      <c r="M72" s="4" t="n">
+      <c r="M72" s="4" t="n"/>
+      <c r="N72" s="4" t="n"/>
+      <c r="O72" s="4" t="n">
         <v>26.1</v>
       </c>
-      <c r="N72" s="4" t="n"/>
-      <c r="O72" s="4" t="n"/>
       <c r="P72" s="4" t="n"/>
       <c r="Q72" s="4" t="n"/>
       <c r="R72" s="4" t="n"/>
@@ -36565,19 +36619,19 @@
       <c r="D73" s="4" t="n"/>
       <c r="E73" s="4" t="n"/>
       <c r="F73" s="4" t="n"/>
-      <c r="G73" s="4" t="n"/>
-      <c r="H73" s="4" t="n">
+      <c r="G73" s="4" t="n">
         <v>19.19</v>
       </c>
+      <c r="H73" s="4" t="n"/>
       <c r="I73" s="4" t="n"/>
       <c r="J73" s="4" t="n"/>
       <c r="K73" s="4" t="n"/>
       <c r="L73" s="4" t="n"/>
-      <c r="M73" s="4" t="n">
+      <c r="M73" s="4" t="n"/>
+      <c r="N73" s="4" t="n"/>
+      <c r="O73" s="4" t="n">
         <v>19.4</v>
       </c>
-      <c r="N73" s="4" t="n"/>
-      <c r="O73" s="4" t="n"/>
       <c r="P73" s="4" t="n"/>
       <c r="Q73" s="4" t="n">
         <v>19.39</v>
@@ -36628,20 +36682,20 @@
       <c r="E74" s="4" t="n"/>
       <c r="F74" s="4" t="n"/>
       <c r="G74" s="4" t="n"/>
-      <c r="H74" s="4" t="n"/>
-      <c r="I74" s="4" t="n">
+      <c r="H74" s="4" t="n">
         <v>33.95</v>
       </c>
+      <c r="I74" s="4" t="n"/>
       <c r="J74" s="4" t="n">
         <v>34.79</v>
       </c>
       <c r="K74" s="4" t="n"/>
       <c r="L74" s="4" t="n"/>
-      <c r="M74" s="4" t="n">
+      <c r="M74" s="4" t="n"/>
+      <c r="N74" s="4" t="n"/>
+      <c r="O74" s="4" t="n">
         <v>35.2</v>
       </c>
-      <c r="N74" s="4" t="n"/>
-      <c r="O74" s="4" t="n"/>
       <c r="P74" s="4" t="n"/>
       <c r="Q74" s="4" t="n"/>
       <c r="R74" s="4" t="n"/>
@@ -36688,10 +36742,10 @@
       <c r="E75" s="4" t="n"/>
       <c r="F75" s="4" t="n"/>
       <c r="G75" s="4" t="n"/>
-      <c r="H75" s="4" t="n"/>
-      <c r="I75" s="4" t="n">
+      <c r="H75" s="4" t="n">
         <v>26.69</v>
       </c>
+      <c r="I75" s="4" t="n"/>
       <c r="J75" s="4" t="n"/>
       <c r="K75" s="4" t="n">
         <v>26.25</v>
@@ -36702,10 +36756,10 @@
       <c r="O75" s="4" t="n"/>
       <c r="P75" s="4" t="n"/>
       <c r="Q75" s="4" t="n"/>
-      <c r="R75" s="4" t="n"/>
-      <c r="S75" s="4" t="n">
+      <c r="R75" s="4" t="n">
         <v>27.49</v>
       </c>
+      <c r="S75" s="4" t="n"/>
       <c r="T75" s="4" t="n"/>
       <c r="U75" s="4" t="n"/>
       <c r="V75" s="4" t="n"/>
@@ -36745,19 +36799,19 @@
       <c r="D76" s="4" t="n"/>
       <c r="E76" s="4" t="n"/>
       <c r="F76" s="4" t="n"/>
-      <c r="G76" s="4" t="n"/>
-      <c r="H76" s="4" t="n">
+      <c r="G76" s="4" t="n">
         <v>16.6</v>
       </c>
+      <c r="H76" s="4" t="n"/>
       <c r="I76" s="4" t="n"/>
       <c r="J76" s="4" t="n"/>
       <c r="K76" s="4" t="n"/>
       <c r="L76" s="4" t="n"/>
-      <c r="M76" s="4" t="n">
+      <c r="M76" s="4" t="n"/>
+      <c r="N76" s="4" t="n"/>
+      <c r="O76" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="N76" s="4" t="n"/>
-      <c r="O76" s="4" t="n"/>
       <c r="P76" s="4" t="n"/>
       <c r="Q76" s="4" t="n">
         <v>17.09</v>
@@ -36873,11 +36927,11 @@
       <c r="F78" s="4" t="n">
         <v>31.2</v>
       </c>
-      <c r="G78" s="4" t="n">
+      <c r="G78" s="4" t="n"/>
+      <c r="H78" s="4" t="n"/>
+      <c r="I78" s="4" t="n">
         <v>31.59</v>
       </c>
-      <c r="H78" s="4" t="n"/>
-      <c r="I78" s="4" t="n"/>
       <c r="J78" s="4" t="n">
         <v>31.8</v>
       </c>
@@ -37057,11 +37111,11 @@
       <c r="F81" s="4" t="n">
         <v>63.6</v>
       </c>
-      <c r="G81" s="4" t="n">
+      <c r="G81" s="4" t="n"/>
+      <c r="H81" s="4" t="n"/>
+      <c r="I81" s="4" t="n">
         <v>63.99</v>
       </c>
-      <c r="H81" s="4" t="n"/>
-      <c r="I81" s="4" t="n"/>
       <c r="J81" s="4" t="n"/>
       <c r="K81" s="4" t="n"/>
       <c r="L81" s="4" t="n"/>
@@ -37232,10 +37286,10 @@
         <v>26.59</v>
       </c>
       <c r="G84" s="4" t="n"/>
-      <c r="H84" s="4" t="n"/>
-      <c r="I84" s="4" t="n">
+      <c r="H84" s="4" t="n">
         <v>27.39</v>
       </c>
+      <c r="I84" s="4" t="n"/>
       <c r="J84" s="4" t="n"/>
       <c r="K84" s="4" t="n"/>
       <c r="L84" s="4" t="n"/>
@@ -37437,39 +37491,39 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>9x8★6</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>速尾★4</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>速尾★5</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>速尾★6</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>玻璃★1</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>玻璃★2</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>玻璃★3</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>9x8★6</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>速尾★4</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>速尾★5</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>速尾★6</t>
-        </is>
-      </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
           <t>ssc★1</t>
@@ -37522,24 +37576,24 @@
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
+          <t>fp1★5</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>fp1★6</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>狼崽★5</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
           <t>万达★6</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>狼崽★5</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>fp1★5</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>fp1★6</t>
-        </is>
-      </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>21c★2</t>
@@ -37562,12 +37616,12 @@
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
+          <t>法拉第★6</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
           <t>火山★5</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>法拉第★6</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
@@ -37668,12 +37722,12 @@
       <c r="K2" s="4" t="n"/>
       <c r="L2" s="4" t="n"/>
       <c r="M2" s="4" t="n"/>
-      <c r="N2" s="4" t="n"/>
+      <c r="N2" s="4" t="n">
+        <v>19.1</v>
+      </c>
       <c r="O2" s="4" t="n"/>
       <c r="P2" s="4" t="n"/>
-      <c r="Q2" s="4" t="n">
-        <v>19.1</v>
-      </c>
+      <c r="Q2" s="4" t="n"/>
       <c r="R2" s="4" t="n"/>
       <c r="S2" s="4" t="n"/>
       <c r="T2" s="4" t="n"/>
@@ -37687,12 +37741,12 @@
       <c r="AB2" s="4" t="n"/>
       <c r="AC2" s="4" t="n"/>
       <c r="AD2" s="4" t="n"/>
-      <c r="AE2" s="4" t="n">
-        <v>19.2</v>
-      </c>
+      <c r="AE2" s="4" t="n"/>
       <c r="AF2" s="4" t="n"/>
       <c r="AG2" s="4" t="n"/>
-      <c r="AH2" s="4" t="n"/>
+      <c r="AH2" s="4" t="n">
+        <v>19.2</v>
+      </c>
       <c r="AI2" s="4" t="n"/>
       <c r="AJ2" s="4" t="n"/>
       <c r="AK2" s="4" t="n"/>
@@ -37875,21 +37929,21 @@
       <c r="K5" s="4" t="n"/>
       <c r="L5" s="4" t="n"/>
       <c r="M5" s="4" t="n"/>
-      <c r="N5" s="4" t="n"/>
-      <c r="O5" s="4" t="n"/>
-      <c r="P5" s="4" t="n"/>
+      <c r="N5" s="4" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="O5" s="4" t="n">
+        <v>18.48</v>
+      </c>
+      <c r="P5" s="4" t="n">
+        <v>18.3</v>
+      </c>
       <c r="Q5" s="4" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="R5" s="4" t="n">
-        <v>18.48</v>
-      </c>
-      <c r="S5" s="4" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="T5" s="4" t="n">
         <v>18.15</v>
       </c>
+      <c r="R5" s="4" t="n"/>
+      <c r="S5" s="4" t="n"/>
+      <c r="T5" s="4" t="n"/>
       <c r="U5" s="4" t="n"/>
       <c r="V5" s="4" t="n"/>
       <c r="W5" s="4" t="n"/>
@@ -37952,12 +38006,12 @@
       <c r="K6" s="4" t="n"/>
       <c r="L6" s="4" t="n"/>
       <c r="M6" s="4" t="n"/>
-      <c r="N6" s="4" t="n"/>
+      <c r="N6" s="4" t="n">
+        <v>18.05</v>
+      </c>
       <c r="O6" s="4" t="n"/>
       <c r="P6" s="4" t="n"/>
-      <c r="Q6" s="4" t="n">
-        <v>18.05</v>
-      </c>
+      <c r="Q6" s="4" t="n"/>
       <c r="R6" s="4" t="n"/>
       <c r="S6" s="4" t="n"/>
       <c r="T6" s="4" t="n"/>
@@ -38094,13 +38148,13 @@
         <v>27.75</v>
       </c>
       <c r="M8" s="4" t="n"/>
-      <c r="N8" s="4" t="n">
-        <v>28.23</v>
-      </c>
+      <c r="N8" s="4" t="n"/>
       <c r="O8" s="4" t="n"/>
       <c r="P8" s="4" t="n"/>
       <c r="Q8" s="4" t="n"/>
-      <c r="R8" s="4" t="n"/>
+      <c r="R8" s="4" t="n">
+        <v>28.23</v>
+      </c>
       <c r="S8" s="4" t="n"/>
       <c r="T8" s="4" t="n"/>
       <c r="U8" s="4" t="n">
@@ -38163,15 +38217,15 @@
       <c r="K9" s="4" t="n"/>
       <c r="L9" s="4" t="n"/>
       <c r="M9" s="4" t="n"/>
-      <c r="N9" s="4" t="n"/>
-      <c r="O9" s="4" t="n"/>
+      <c r="N9" s="4" t="n">
+        <v>20.19</v>
+      </c>
+      <c r="O9" s="4" t="n">
+        <v>20.52</v>
+      </c>
       <c r="P9" s="4" t="n"/>
-      <c r="Q9" s="4" t="n">
-        <v>20.19</v>
-      </c>
-      <c r="R9" s="4" t="n">
-        <v>20.52</v>
-      </c>
+      <c r="Q9" s="4" t="n"/>
+      <c r="R9" s="4" t="n"/>
       <c r="S9" s="4" t="n"/>
       <c r="T9" s="4" t="n"/>
       <c r="U9" s="4" t="n"/>
@@ -38187,11 +38241,11 @@
         <v>19.78</v>
       </c>
       <c r="AE9" s="4" t="n"/>
-      <c r="AF9" s="4" t="n"/>
+      <c r="AF9" s="4" t="n">
+        <v>19.89</v>
+      </c>
       <c r="AG9" s="4" t="n"/>
-      <c r="AH9" s="4" t="n">
-        <v>19.89</v>
-      </c>
+      <c r="AH9" s="4" t="n"/>
       <c r="AI9" s="4" t="n"/>
       <c r="AJ9" s="4" t="n"/>
       <c r="AK9" s="4" t="n">
@@ -38200,10 +38254,10 @@
       <c r="AL9" s="4" t="n">
         <v>20.29</v>
       </c>
-      <c r="AM9" s="4" t="n">
+      <c r="AM9" s="4" t="n"/>
+      <c r="AN9" s="4" t="n">
         <v>20.49</v>
       </c>
-      <c r="AN9" s="4" t="n"/>
       <c r="AO9" s="4" t="n"/>
       <c r="AP9" s="4" t="n"/>
       <c r="AQ9" s="4" t="n"/>
@@ -38242,17 +38296,17 @@
       <c r="K10" s="4" t="n"/>
       <c r="L10" s="4" t="n"/>
       <c r="M10" s="4" t="n"/>
-      <c r="N10" s="4" t="n"/>
+      <c r="N10" s="4" t="n">
+        <v>23.5</v>
+      </c>
       <c r="O10" s="4" t="n"/>
       <c r="P10" s="4" t="n"/>
       <c r="Q10" s="4" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="R10" s="4" t="n"/>
       <c r="S10" s="4" t="n"/>
-      <c r="T10" s="4" t="n">
-        <v>23.4</v>
-      </c>
+      <c r="T10" s="4" t="n"/>
       <c r="U10" s="4" t="n"/>
       <c r="V10" s="4" t="n"/>
       <c r="W10" s="4" t="n"/>
@@ -38333,10 +38387,10 @@
       <c r="AC11" s="4" t="n"/>
       <c r="AD11" s="4" t="n"/>
       <c r="AE11" s="4" t="n"/>
-      <c r="AF11" s="4" t="n">
+      <c r="AF11" s="4" t="n"/>
+      <c r="AG11" s="4" t="n">
         <v>37.99</v>
       </c>
-      <c r="AG11" s="4" t="n"/>
       <c r="AH11" s="4" t="n"/>
       <c r="AI11" s="4" t="n"/>
       <c r="AJ11" s="4" t="n"/>
@@ -38383,12 +38437,12 @@
       <c r="N12" s="4" t="n"/>
       <c r="O12" s="4" t="n"/>
       <c r="P12" s="4" t="n"/>
-      <c r="Q12" s="4" t="n"/>
+      <c r="Q12" s="4" t="n">
+        <v>21.99</v>
+      </c>
       <c r="R12" s="4" t="n"/>
       <c r="S12" s="4" t="n"/>
-      <c r="T12" s="4" t="n">
-        <v>21.99</v>
-      </c>
+      <c r="T12" s="4" t="n"/>
       <c r="U12" s="4" t="n"/>
       <c r="V12" s="4" t="n"/>
       <c r="W12" s="4" t="n"/>
@@ -38415,10 +38469,10 @@
         <v>21.69</v>
       </c>
       <c r="AL12" s="4" t="n"/>
-      <c r="AM12" s="4" t="n"/>
-      <c r="AN12" s="4" t="n">
+      <c r="AM12" s="4" t="n">
         <v>22.1</v>
       </c>
+      <c r="AN12" s="4" t="n"/>
       <c r="AO12" s="4" t="n"/>
       <c r="AP12" s="4" t="n"/>
       <c r="AQ12" s="4" t="n"/>
@@ -38453,7 +38507,9 @@
       <c r="G13" s="4" t="n">
         <v>41.8</v>
       </c>
-      <c r="H13" s="4" t="n"/>
+      <c r="H13" s="4" t="n">
+        <v>42.34</v>
+      </c>
       <c r="I13" s="4" t="n"/>
       <c r="J13" s="4" t="n"/>
       <c r="K13" s="4" t="n"/>
@@ -38536,13 +38592,13 @@
       <c r="K14" s="4" t="n"/>
       <c r="L14" s="4" t="n"/>
       <c r="M14" s="4" t="n"/>
-      <c r="N14" s="4" t="n">
-        <v>26.15</v>
-      </c>
+      <c r="N14" s="4" t="n"/>
       <c r="O14" s="4" t="n"/>
       <c r="P14" s="4" t="n"/>
       <c r="Q14" s="4" t="n"/>
-      <c r="R14" s="4" t="n"/>
+      <c r="R14" s="4" t="n">
+        <v>26.15</v>
+      </c>
       <c r="S14" s="4" t="n"/>
       <c r="T14" s="4" t="n"/>
       <c r="U14" s="4" t="n"/>
@@ -38555,11 +38611,11 @@
       <c r="AB14" s="4" t="n"/>
       <c r="AC14" s="4" t="n"/>
       <c r="AD14" s="4" t="n"/>
-      <c r="AE14" s="4" t="n"/>
+      <c r="AE14" s="4" t="n">
+        <v>26.72</v>
+      </c>
       <c r="AF14" s="4" t="n"/>
-      <c r="AG14" s="4" t="n">
-        <v>26.69</v>
-      </c>
+      <c r="AG14" s="4" t="n"/>
       <c r="AH14" s="4" t="n"/>
       <c r="AI14" s="4" t="n"/>
       <c r="AJ14" s="4" t="n"/>
@@ -38613,12 +38669,12 @@
       </c>
       <c r="L15" s="4" t="n"/>
       <c r="M15" s="4" t="n"/>
-      <c r="N15" s="4" t="n"/>
+      <c r="N15" s="4" t="n">
+        <v>29.59</v>
+      </c>
       <c r="O15" s="4" t="n"/>
       <c r="P15" s="4" t="n"/>
-      <c r="Q15" s="4" t="n">
-        <v>29.59</v>
-      </c>
+      <c r="Q15" s="4" t="n"/>
       <c r="R15" s="4" t="n"/>
       <c r="S15" s="4" t="n"/>
       <c r="T15" s="4" t="n"/>
@@ -38633,10 +38689,10 @@
       <c r="AC15" s="4" t="n"/>
       <c r="AD15" s="4" t="n"/>
       <c r="AE15" s="4" t="n"/>
-      <c r="AF15" s="4" t="n">
+      <c r="AF15" s="4" t="n"/>
+      <c r="AG15" s="4" t="n">
         <v>30.4</v>
       </c>
-      <c r="AG15" s="4" t="n"/>
       <c r="AH15" s="4" t="n"/>
       <c r="AI15" s="4" t="n"/>
       <c r="AJ15" s="4" t="n"/>
@@ -38724,7 +38780,9 @@
       <c r="AM16" s="4" t="n"/>
       <c r="AN16" s="4" t="n"/>
       <c r="AO16" s="4" t="n"/>
-      <c r="AP16" s="4" t="n"/>
+      <c r="AP16" s="4" t="n">
+        <v>40.95</v>
+      </c>
       <c r="AQ16" s="4" t="n"/>
       <c r="AR16" s="4" t="n"/>
       <c r="AS16" s="4" t="n"/>
@@ -38761,13 +38819,13 @@
       </c>
       <c r="L17" s="4" t="n"/>
       <c r="M17" s="4" t="n"/>
-      <c r="N17" s="4" t="n">
-        <v>30.49</v>
-      </c>
+      <c r="N17" s="4" t="n"/>
       <c r="O17" s="4" t="n"/>
       <c r="P17" s="4" t="n"/>
       <c r="Q17" s="4" t="n"/>
-      <c r="R17" s="4" t="n"/>
+      <c r="R17" s="4" t="n">
+        <v>30.49</v>
+      </c>
       <c r="S17" s="4" t="n"/>
       <c r="T17" s="4" t="n"/>
       <c r="U17" s="4" t="n"/>
@@ -38780,11 +38838,11 @@
       <c r="AB17" s="4" t="n"/>
       <c r="AC17" s="4" t="n"/>
       <c r="AD17" s="4" t="n"/>
-      <c r="AE17" s="4" t="n"/>
+      <c r="AE17" s="4" t="n">
+        <v>31.49</v>
+      </c>
       <c r="AF17" s="4" t="n"/>
-      <c r="AG17" s="4" t="n">
-        <v>31.49</v>
-      </c>
+      <c r="AG17" s="4" t="n"/>
       <c r="AH17" s="4" t="n"/>
       <c r="AI17" s="4" t="n"/>
       <c r="AJ17" s="4" t="n"/>
@@ -38831,16 +38889,16 @@
       <c r="L18" s="4" t="n"/>
       <c r="M18" s="4" t="n"/>
       <c r="N18" s="4" t="n"/>
-      <c r="O18" s="4" t="n"/>
+      <c r="O18" s="4" t="n">
+        <v>24.59</v>
+      </c>
       <c r="P18" s="4" t="n"/>
-      <c r="Q18" s="4" t="n"/>
-      <c r="R18" s="4" t="n">
-        <v>24.59</v>
-      </c>
+      <c r="Q18" s="4" t="n">
+        <v>23.99</v>
+      </c>
+      <c r="R18" s="4" t="n"/>
       <c r="S18" s="4" t="n"/>
-      <c r="T18" s="4" t="n">
-        <v>23.99</v>
-      </c>
+      <c r="T18" s="4" t="n"/>
       <c r="U18" s="4" t="n"/>
       <c r="V18" s="4" t="n"/>
       <c r="W18" s="4" t="n"/>
@@ -38858,10 +38916,10 @@
       <c r="AC18" s="4" t="n"/>
       <c r="AD18" s="4" t="n"/>
       <c r="AE18" s="4" t="n"/>
-      <c r="AF18" s="4" t="n">
+      <c r="AF18" s="4" t="n"/>
+      <c r="AG18" s="4" t="n">
         <v>24.79</v>
       </c>
-      <c r="AG18" s="4" t="n"/>
       <c r="AH18" s="4" t="n"/>
       <c r="AI18" s="4" t="n"/>
       <c r="AJ18" s="4" t="n"/>
@@ -38913,12 +38971,12 @@
       <c r="M19" s="4" t="n">
         <v>32.5</v>
       </c>
-      <c r="N19" s="4" t="n"/>
+      <c r="N19" s="4" t="n">
+        <v>33.4</v>
+      </c>
       <c r="O19" s="4" t="n"/>
       <c r="P19" s="4" t="n"/>
-      <c r="Q19" s="4" t="n">
-        <v>33.4</v>
-      </c>
+      <c r="Q19" s="4" t="n"/>
       <c r="R19" s="4" t="n"/>
       <c r="S19" s="4" t="n"/>
       <c r="T19" s="4" t="n"/>
@@ -38980,12 +39038,12 @@
         <v>22.4</v>
       </c>
       <c r="M20" s="4" t="n"/>
-      <c r="N20" s="4" t="n"/>
+      <c r="N20" s="4" t="n">
+        <v>22.59</v>
+      </c>
       <c r="O20" s="4" t="n"/>
       <c r="P20" s="4" t="n"/>
-      <c r="Q20" s="4" t="n">
-        <v>22.59</v>
-      </c>
+      <c r="Q20" s="4" t="n"/>
       <c r="R20" s="4" t="n"/>
       <c r="S20" s="4" t="n"/>
       <c r="T20" s="4" t="n"/>
@@ -38999,12 +39057,12 @@
       <c r="AB20" s="4" t="n"/>
       <c r="AC20" s="4" t="n"/>
       <c r="AD20" s="4" t="n"/>
-      <c r="AE20" s="4" t="n">
-        <v>22.8</v>
-      </c>
+      <c r="AE20" s="4" t="n"/>
       <c r="AF20" s="4" t="n"/>
       <c r="AG20" s="4" t="n"/>
-      <c r="AH20" s="4" t="n"/>
+      <c r="AH20" s="4" t="n">
+        <v>22.8</v>
+      </c>
       <c r="AI20" s="4" t="n"/>
       <c r="AJ20" s="4" t="n"/>
       <c r="AK20" s="4" t="n"/>
@@ -39207,10 +39265,10 @@
       <c r="AC23" s="4" t="n"/>
       <c r="AD23" s="4" t="n"/>
       <c r="AE23" s="4" t="n"/>
-      <c r="AF23" s="4" t="n">
+      <c r="AF23" s="4" t="n"/>
+      <c r="AG23" s="4" t="n">
         <v>32.3</v>
       </c>
-      <c r="AG23" s="4" t="n"/>
       <c r="AH23" s="4" t="n"/>
       <c r="AI23" s="4" t="n"/>
       <c r="AJ23" s="4" t="n"/>
@@ -39253,16 +39311,16 @@
       <c r="L24" s="4" t="n"/>
       <c r="M24" s="4" t="n"/>
       <c r="N24" s="4" t="n"/>
-      <c r="O24" s="4" t="n"/>
+      <c r="O24" s="4" t="n">
+        <v>23.69</v>
+      </c>
       <c r="P24" s="4" t="n"/>
-      <c r="Q24" s="4" t="n"/>
-      <c r="R24" s="4" t="n">
-        <v>23.69</v>
-      </c>
+      <c r="Q24" s="4" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="R24" s="4" t="n"/>
       <c r="S24" s="4" t="n"/>
-      <c r="T24" s="4" t="n">
-        <v>23.3</v>
-      </c>
+      <c r="T24" s="4" t="n"/>
       <c r="U24" s="4" t="n"/>
       <c r="V24" s="4" t="n"/>
       <c r="W24" s="4" t="n"/>
@@ -39279,18 +39337,22 @@
       <c r="AD24" s="4" t="n">
         <v>22.85</v>
       </c>
-      <c r="AE24" s="4" t="n"/>
+      <c r="AE24" s="4" t="n">
+        <v>23.63</v>
+      </c>
       <c r="AF24" s="4" t="n"/>
-      <c r="AG24" s="4" t="n"/>
+      <c r="AG24" s="4" t="n">
+        <v>23.79</v>
+      </c>
       <c r="AH24" s="4" t="n"/>
       <c r="AI24" s="4" t="n"/>
       <c r="AJ24" s="4" t="n"/>
       <c r="AK24" s="4" t="n"/>
       <c r="AL24" s="4" t="n"/>
-      <c r="AM24" s="4" t="n"/>
-      <c r="AN24" s="4" t="n">
+      <c r="AM24" s="4" t="n">
         <v>23.03</v>
       </c>
+      <c r="AN24" s="4" t="n"/>
       <c r="AO24" s="4" t="n"/>
       <c r="AP24" s="4" t="n"/>
       <c r="AQ24" s="4" t="n"/>
@@ -39326,14 +39388,16 @@
       <c r="L25" s="4" t="n"/>
       <c r="M25" s="4" t="n"/>
       <c r="N25" s="4" t="n"/>
-      <c r="O25" s="4" t="n"/>
+      <c r="O25" s="4" t="n">
+        <v>24.83</v>
+      </c>
       <c r="P25" s="4" t="n"/>
-      <c r="Q25" s="4" t="n"/>
+      <c r="Q25" s="4" t="n">
+        <v>24.69</v>
+      </c>
       <c r="R25" s="4" t="n"/>
       <c r="S25" s="4" t="n"/>
-      <c r="T25" s="4" t="n">
-        <v>24.69</v>
-      </c>
+      <c r="T25" s="4" t="n"/>
       <c r="U25" s="4" t="n"/>
       <c r="V25" s="4" t="n"/>
       <c r="W25" s="4" t="n"/>
@@ -39357,9 +39421,11 @@
       </c>
       <c r="AL25" s="4" t="n"/>
       <c r="AM25" s="4" t="n">
+        <v>24.89</v>
+      </c>
+      <c r="AN25" s="4" t="n">
         <v>25.5</v>
       </c>
-      <c r="AN25" s="4" t="n"/>
       <c r="AO25" s="4" t="n"/>
       <c r="AP25" s="4" t="n"/>
       <c r="AQ25" s="4" t="n"/>
@@ -39405,12 +39471,12 @@
       <c r="N26" s="4" t="n"/>
       <c r="O26" s="4" t="n"/>
       <c r="P26" s="4" t="n"/>
-      <c r="Q26" s="4" t="n"/>
+      <c r="Q26" s="4" t="n">
+        <v>18.99</v>
+      </c>
       <c r="R26" s="4" t="n"/>
       <c r="S26" s="4" t="n"/>
-      <c r="T26" s="4" t="n">
-        <v>18.99</v>
-      </c>
+      <c r="T26" s="4" t="n"/>
       <c r="U26" s="4" t="n"/>
       <c r="V26" s="4" t="n"/>
       <c r="W26" s="4" t="n"/>
@@ -39426,10 +39492,10 @@
         <v>18.95</v>
       </c>
       <c r="AE26" s="4" t="n"/>
-      <c r="AF26" s="4" t="n">
+      <c r="AF26" s="4" t="n"/>
+      <c r="AG26" s="4" t="n">
         <v>19.5</v>
       </c>
-      <c r="AG26" s="4" t="n"/>
       <c r="AH26" s="4" t="n"/>
       <c r="AI26" s="4" t="n"/>
       <c r="AJ26" s="4" t="n">
@@ -39477,12 +39543,12 @@
       <c r="K27" s="4" t="n"/>
       <c r="L27" s="4" t="n"/>
       <c r="M27" s="4" t="n"/>
-      <c r="N27" s="4" t="n"/>
+      <c r="N27" s="4" t="n">
+        <v>35.2</v>
+      </c>
       <c r="O27" s="4" t="n"/>
       <c r="P27" s="4" t="n"/>
-      <c r="Q27" s="4" t="n">
-        <v>35.2</v>
-      </c>
+      <c r="Q27" s="4" t="n"/>
       <c r="R27" s="4" t="n"/>
       <c r="S27" s="4" t="n"/>
       <c r="T27" s="4" t="n"/>
@@ -39551,12 +39617,12 @@
       <c r="N28" s="4" t="n"/>
       <c r="O28" s="4" t="n"/>
       <c r="P28" s="4" t="n"/>
-      <c r="Q28" s="4" t="n"/>
+      <c r="Q28" s="4" t="n">
+        <v>33.5</v>
+      </c>
       <c r="R28" s="4" t="n"/>
       <c r="S28" s="4" t="n"/>
-      <c r="T28" s="4" t="n">
-        <v>33.5</v>
-      </c>
+      <c r="T28" s="4" t="n"/>
       <c r="U28" s="4" t="n"/>
       <c r="V28" s="4" t="n"/>
       <c r="W28" s="4" t="n"/>
@@ -39690,12 +39756,12 @@
       <c r="K30" s="4" t="n"/>
       <c r="L30" s="4" t="n"/>
       <c r="M30" s="4" t="n"/>
-      <c r="N30" s="4" t="n"/>
+      <c r="N30" s="4" t="n">
+        <v>23.19</v>
+      </c>
       <c r="O30" s="4" t="n"/>
       <c r="P30" s="4" t="n"/>
-      <c r="Q30" s="4" t="n">
-        <v>23.19</v>
-      </c>
+      <c r="Q30" s="4" t="n"/>
       <c r="R30" s="4" t="n"/>
       <c r="S30" s="4" t="n"/>
       <c r="T30" s="4" t="n"/>
@@ -39709,12 +39775,12 @@
       <c r="AB30" s="4" t="n"/>
       <c r="AC30" s="4" t="n"/>
       <c r="AD30" s="4" t="n"/>
-      <c r="AE30" s="4" t="n">
-        <v>23.49</v>
-      </c>
+      <c r="AE30" s="4" t="n"/>
       <c r="AF30" s="4" t="n"/>
       <c r="AG30" s="4" t="n"/>
-      <c r="AH30" s="4" t="n"/>
+      <c r="AH30" s="4" t="n">
+        <v>23.49</v>
+      </c>
       <c r="AI30" s="4" t="n"/>
       <c r="AJ30" s="4" t="n"/>
       <c r="AK30" s="4" t="n"/>
@@ -39757,12 +39823,12 @@
       <c r="K31" s="4" t="n"/>
       <c r="L31" s="4" t="n"/>
       <c r="M31" s="4" t="n"/>
-      <c r="N31" s="4" t="n"/>
+      <c r="N31" s="4" t="n">
+        <v>19.19</v>
+      </c>
       <c r="O31" s="4" t="n"/>
       <c r="P31" s="4" t="n"/>
-      <c r="Q31" s="4" t="n">
-        <v>19.19</v>
-      </c>
+      <c r="Q31" s="4" t="n"/>
       <c r="R31" s="4" t="n"/>
       <c r="S31" s="4" t="n"/>
       <c r="T31" s="4" t="n"/>
@@ -39776,12 +39842,12 @@
       <c r="AB31" s="4" t="n"/>
       <c r="AC31" s="4" t="n"/>
       <c r="AD31" s="4" t="n"/>
-      <c r="AE31" s="4" t="n">
-        <v>19.45</v>
-      </c>
+      <c r="AE31" s="4" t="n"/>
       <c r="AF31" s="4" t="n"/>
       <c r="AG31" s="4" t="n"/>
-      <c r="AH31" s="4" t="n"/>
+      <c r="AH31" s="4" t="n">
+        <v>19.45</v>
+      </c>
       <c r="AI31" s="4" t="n"/>
       <c r="AJ31" s="4" t="n"/>
       <c r="AK31" s="4" t="n"/>
@@ -39828,12 +39894,12 @@
       <c r="K32" s="4" t="n"/>
       <c r="L32" s="4" t="n"/>
       <c r="M32" s="4" t="n"/>
-      <c r="N32" s="4" t="n"/>
+      <c r="N32" s="4" t="n">
+        <v>29.4</v>
+      </c>
       <c r="O32" s="4" t="n"/>
       <c r="P32" s="4" t="n"/>
-      <c r="Q32" s="4" t="n">
-        <v>29.4</v>
-      </c>
+      <c r="Q32" s="4" t="n"/>
       <c r="R32" s="4" t="n"/>
       <c r="S32" s="4" t="n"/>
       <c r="T32" s="4" t="n"/>
@@ -39847,22 +39913,22 @@
       <c r="AB32" s="4" t="n"/>
       <c r="AC32" s="4" t="n"/>
       <c r="AD32" s="4" t="n"/>
-      <c r="AE32" s="4" t="n"/>
-      <c r="AF32" s="4" t="n">
+      <c r="AE32" s="4" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="AF32" s="4" t="n"/>
+      <c r="AG32" s="4" t="n">
         <v>29.3</v>
-      </c>
-      <c r="AG32" s="4" t="n">
-        <v>29.8</v>
       </c>
       <c r="AH32" s="4" t="n"/>
       <c r="AI32" s="4" t="n"/>
       <c r="AJ32" s="4" t="n"/>
       <c r="AK32" s="4" t="n"/>
       <c r="AL32" s="4" t="n"/>
-      <c r="AM32" s="4" t="n">
+      <c r="AM32" s="4" t="n"/>
+      <c r="AN32" s="4" t="n">
         <v>29.6</v>
       </c>
-      <c r="AN32" s="4" t="n"/>
       <c r="AO32" s="4" t="n"/>
       <c r="AP32" s="4" t="n"/>
       <c r="AQ32" s="4" t="n"/>
@@ -39907,12 +39973,12 @@
       <c r="K33" s="4" t="n"/>
       <c r="L33" s="4" t="n"/>
       <c r="M33" s="4" t="n"/>
-      <c r="N33" s="4" t="n"/>
+      <c r="N33" s="4" t="n">
+        <v>19.99</v>
+      </c>
       <c r="O33" s="4" t="n"/>
       <c r="P33" s="4" t="n"/>
-      <c r="Q33" s="4" t="n">
-        <v>19.99</v>
-      </c>
+      <c r="Q33" s="4" t="n"/>
       <c r="R33" s="4" t="n"/>
       <c r="S33" s="4" t="n"/>
       <c r="T33" s="4" t="n"/>
@@ -39926,12 +39992,12 @@
       <c r="AB33" s="4" t="n"/>
       <c r="AC33" s="4" t="n"/>
       <c r="AD33" s="4" t="n"/>
-      <c r="AE33" s="4" t="n">
-        <v>20.4</v>
-      </c>
+      <c r="AE33" s="4" t="n"/>
       <c r="AF33" s="4" t="n"/>
       <c r="AG33" s="4" t="n"/>
-      <c r="AH33" s="4" t="n"/>
+      <c r="AH33" s="4" t="n">
+        <v>20.4</v>
+      </c>
       <c r="AI33" s="4" t="n"/>
       <c r="AJ33" s="4" t="n"/>
       <c r="AK33" s="4" t="n"/>
@@ -39977,15 +40043,15 @@
       <c r="L34" s="4" t="n"/>
       <c r="M34" s="4" t="n"/>
       <c r="N34" s="4" t="n"/>
-      <c r="O34" s="4" t="n"/>
-      <c r="P34" s="4" t="n"/>
+      <c r="O34" s="4" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="P34" s="4" t="n">
+        <v>35.6</v>
+      </c>
       <c r="Q34" s="4" t="n"/>
-      <c r="R34" s="4" t="n">
-        <v>35.8</v>
-      </c>
-      <c r="S34" s="4" t="n">
-        <v>35.6</v>
-      </c>
+      <c r="R34" s="4" t="n"/>
+      <c r="S34" s="4" t="n"/>
       <c r="T34" s="4" t="n"/>
       <c r="U34" s="4" t="n"/>
       <c r="V34" s="4" t="n">
@@ -40045,12 +40111,12 @@
       <c r="K35" s="4" t="n"/>
       <c r="L35" s="4" t="n"/>
       <c r="M35" s="4" t="n"/>
-      <c r="N35" s="4" t="n"/>
+      <c r="N35" s="4" t="n">
+        <v>23.7</v>
+      </c>
       <c r="O35" s="4" t="n"/>
       <c r="P35" s="4" t="n"/>
-      <c r="Q35" s="4" t="n">
-        <v>23.7</v>
-      </c>
+      <c r="Q35" s="4" t="n"/>
       <c r="R35" s="4" t="n"/>
       <c r="S35" s="4" t="n"/>
       <c r="T35" s="4" t="n"/>
@@ -40195,12 +40261,12 @@
         <v>22.69</v>
       </c>
       <c r="M37" s="4" t="n"/>
-      <c r="N37" s="4" t="n"/>
+      <c r="N37" s="4" t="n">
+        <v>23.29</v>
+      </c>
       <c r="O37" s="4" t="n"/>
       <c r="P37" s="4" t="n"/>
-      <c r="Q37" s="4" t="n">
-        <v>23.29</v>
-      </c>
+      <c r="Q37" s="4" t="n"/>
       <c r="R37" s="4" t="n"/>
       <c r="S37" s="4" t="n"/>
       <c r="T37" s="4" t="n"/>
@@ -40214,11 +40280,11 @@
       <c r="AB37" s="4" t="n"/>
       <c r="AC37" s="4" t="n"/>
       <c r="AD37" s="4" t="n"/>
-      <c r="AE37" s="4" t="n"/>
+      <c r="AE37" s="4" t="n">
+        <v>23.67</v>
+      </c>
       <c r="AF37" s="4" t="n"/>
-      <c r="AG37" s="4" t="n">
-        <v>23.67</v>
-      </c>
+      <c r="AG37" s="4" t="n"/>
       <c r="AH37" s="4" t="n"/>
       <c r="AI37" s="4" t="n"/>
       <c r="AJ37" s="4" t="n"/>
@@ -40265,12 +40331,12 @@
       <c r="N38" s="4" t="n"/>
       <c r="O38" s="4" t="n"/>
       <c r="P38" s="4" t="n"/>
-      <c r="Q38" s="4" t="n"/>
+      <c r="Q38" s="4" t="n">
+        <v>21.29</v>
+      </c>
       <c r="R38" s="4" t="n"/>
       <c r="S38" s="4" t="n"/>
-      <c r="T38" s="4" t="n">
-        <v>21.29</v>
-      </c>
+      <c r="T38" s="4" t="n"/>
       <c r="U38" s="4" t="n"/>
       <c r="V38" s="4" t="n"/>
       <c r="W38" s="4" t="n"/>
@@ -40285,11 +40351,11 @@
       <c r="AD38" s="4" t="n">
         <v>20.89</v>
       </c>
-      <c r="AE38" s="4" t="n"/>
+      <c r="AE38" s="4" t="n">
+        <v>21.59</v>
+      </c>
       <c r="AF38" s="4" t="n"/>
-      <c r="AG38" s="4" t="n">
-        <v>21.59</v>
-      </c>
+      <c r="AG38" s="4" t="n"/>
       <c r="AH38" s="4" t="n"/>
       <c r="AI38" s="4" t="n"/>
       <c r="AJ38" s="4" t="n">
@@ -40297,10 +40363,10 @@
       </c>
       <c r="AK38" s="4" t="n"/>
       <c r="AL38" s="4" t="n"/>
-      <c r="AM38" s="4" t="n">
+      <c r="AM38" s="4" t="n"/>
+      <c r="AN38" s="4" t="n">
         <v>21.99</v>
       </c>
-      <c r="AN38" s="4" t="n"/>
       <c r="AO38" s="4" t="n">
         <v>22.49</v>
       </c>
@@ -40339,13 +40405,15 @@
       <c r="M39" s="4" t="n"/>
       <c r="N39" s="4" t="n"/>
       <c r="O39" s="4" t="n"/>
-      <c r="P39" s="4" t="n"/>
-      <c r="Q39" s="4" t="n"/>
+      <c r="P39" s="4" t="n">
+        <v>30.35</v>
+      </c>
+      <c r="Q39" s="4" t="n">
+        <v>29.9</v>
+      </c>
       <c r="R39" s="4" t="n"/>
       <c r="S39" s="4" t="n"/>
-      <c r="T39" s="4" t="n">
-        <v>29.9</v>
-      </c>
+      <c r="T39" s="4" t="n"/>
       <c r="U39" s="4" t="n"/>
       <c r="V39" s="4" t="n"/>
       <c r="W39" s="4" t="n"/>
@@ -40358,11 +40426,11 @@
       <c r="AB39" s="4" t="n"/>
       <c r="AC39" s="4" t="n"/>
       <c r="AD39" s="4" t="n"/>
-      <c r="AE39" s="4" t="n"/>
+      <c r="AE39" s="4" t="n">
+        <v>30.89</v>
+      </c>
       <c r="AF39" s="4" t="n"/>
-      <c r="AG39" s="4" t="n">
-        <v>30.89</v>
-      </c>
+      <c r="AG39" s="4" t="n"/>
       <c r="AH39" s="4" t="n"/>
       <c r="AI39" s="4" t="n"/>
       <c r="AJ39" s="4" t="n"/>
@@ -40416,12 +40484,12 @@
       <c r="M40" s="4" t="n">
         <v>34.3</v>
       </c>
-      <c r="N40" s="4" t="n"/>
+      <c r="N40" s="4" t="n">
+        <v>35.2</v>
+      </c>
       <c r="O40" s="4" t="n"/>
       <c r="P40" s="4" t="n"/>
-      <c r="Q40" s="4" t="n">
-        <v>35.2</v>
-      </c>
+      <c r="Q40" s="4" t="n"/>
       <c r="R40" s="4" t="n"/>
       <c r="S40" s="4" t="n"/>
       <c r="T40" s="4" t="n"/>
@@ -40436,13 +40504,13 @@
       <c r="AC40" s="4" t="n"/>
       <c r="AD40" s="4" t="n"/>
       <c r="AE40" s="4" t="n">
+        <v>35.86</v>
+      </c>
+      <c r="AF40" s="4" t="n"/>
+      <c r="AG40" s="4" t="n"/>
+      <c r="AH40" s="4" t="n">
         <v>35.4</v>
       </c>
-      <c r="AF40" s="4" t="n"/>
-      <c r="AG40" s="4" t="n">
-        <v>35.86</v>
-      </c>
-      <c r="AH40" s="4" t="n"/>
       <c r="AI40" s="4" t="n"/>
       <c r="AJ40" s="4" t="n"/>
       <c r="AK40" s="4" t="n"/>
@@ -40560,12 +40628,12 @@
       <c r="K42" s="4" t="n"/>
       <c r="L42" s="4" t="n"/>
       <c r="M42" s="4" t="n"/>
-      <c r="N42" s="4" t="n"/>
+      <c r="N42" s="4" t="n">
+        <v>22.5</v>
+      </c>
       <c r="O42" s="4" t="n"/>
       <c r="P42" s="4" t="n"/>
-      <c r="Q42" s="4" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="Q42" s="4" t="n"/>
       <c r="R42" s="4" t="n"/>
       <c r="S42" s="4" t="n"/>
       <c r="T42" s="4" t="n"/>
@@ -40584,10 +40652,10 @@
         <v>22.3</v>
       </c>
       <c r="AE42" s="4" t="n"/>
-      <c r="AF42" s="4" t="n">
+      <c r="AF42" s="4" t="n"/>
+      <c r="AG42" s="4" t="n">
         <v>22.8</v>
       </c>
-      <c r="AG42" s="4" t="n"/>
       <c r="AH42" s="4" t="n"/>
       <c r="AI42" s="4" t="n"/>
       <c r="AJ42" s="4" t="n"/>
@@ -40652,7 +40720,9 @@
       <c r="AB43" s="4" t="n"/>
       <c r="AC43" s="4" t="n"/>
       <c r="AD43" s="4" t="n"/>
-      <c r="AE43" s="4" t="n"/>
+      <c r="AE43" s="4" t="n">
+        <v>40.67</v>
+      </c>
       <c r="AF43" s="4" t="n"/>
       <c r="AG43" s="4" t="n"/>
       <c r="AH43" s="4" t="n"/>
@@ -40696,12 +40766,12 @@
       <c r="K44" s="4" t="n"/>
       <c r="L44" s="4" t="n"/>
       <c r="M44" s="4" t="n"/>
-      <c r="N44" s="4" t="n"/>
+      <c r="N44" s="4" t="n">
+        <v>22.5</v>
+      </c>
       <c r="O44" s="4" t="n"/>
       <c r="P44" s="4" t="n"/>
-      <c r="Q44" s="4" t="n">
-        <v>22.5</v>
-      </c>
+      <c r="Q44" s="4" t="n"/>
       <c r="R44" s="4" t="n"/>
       <c r="S44" s="4" t="n"/>
       <c r="T44" s="4" t="n"/>
@@ -40715,12 +40785,12 @@
       <c r="AB44" s="4" t="n"/>
       <c r="AC44" s="4" t="n"/>
       <c r="AD44" s="4" t="n"/>
-      <c r="AE44" s="4" t="n">
-        <v>22.6</v>
-      </c>
+      <c r="AE44" s="4" t="n"/>
       <c r="AF44" s="4" t="n"/>
       <c r="AG44" s="4" t="n"/>
-      <c r="AH44" s="4" t="n"/>
+      <c r="AH44" s="4" t="n">
+        <v>22.6</v>
+      </c>
       <c r="AI44" s="4" t="n"/>
       <c r="AJ44" s="4" t="n"/>
       <c r="AK44" s="4" t="n"/>
@@ -40773,13 +40843,13 @@
       <c r="M45" s="4" t="n">
         <v>39.19</v>
       </c>
-      <c r="N45" s="4" t="n">
-        <v>39.79</v>
-      </c>
+      <c r="N45" s="4" t="n"/>
       <c r="O45" s="4" t="n"/>
       <c r="P45" s="4" t="n"/>
       <c r="Q45" s="4" t="n"/>
-      <c r="R45" s="4" t="n"/>
+      <c r="R45" s="4" t="n">
+        <v>39.79</v>
+      </c>
       <c r="S45" s="4" t="n"/>
       <c r="T45" s="4" t="n"/>
       <c r="U45" s="4" t="n">
@@ -40918,18 +40988,20 @@
         <v>40.99</v>
       </c>
       <c r="N47" s="4" t="n">
+        <v>42.99</v>
+      </c>
+      <c r="O47" s="4" t="n"/>
+      <c r="P47" s="4" t="n"/>
+      <c r="Q47" s="4" t="n"/>
+      <c r="R47" s="4" t="n">
         <v>41.5</v>
       </c>
-      <c r="O47" s="4" t="n">
+      <c r="S47" s="4" t="n">
         <v>41.4</v>
       </c>
-      <c r="P47" s="4" t="n">
+      <c r="T47" s="4" t="n">
         <v>41.3</v>
       </c>
-      <c r="Q47" s="4" t="n"/>
-      <c r="R47" s="4" t="n"/>
-      <c r="S47" s="4" t="n"/>
-      <c r="T47" s="4" t="n"/>
       <c r="U47" s="4" t="n"/>
       <c r="V47" s="4" t="n"/>
       <c r="W47" s="4" t="n"/>
@@ -40994,15 +41066,15 @@
       <c r="M48" s="4" t="n"/>
       <c r="N48" s="4" t="n"/>
       <c r="O48" s="4" t="n"/>
-      <c r="P48" s="4" t="n"/>
-      <c r="Q48" s="4" t="n"/>
+      <c r="P48" s="4" t="n">
+        <v>25.79</v>
+      </c>
+      <c r="Q48" s="4" t="n">
+        <v>25.2</v>
+      </c>
       <c r="R48" s="4" t="n"/>
-      <c r="S48" s="4" t="n">
-        <v>25.79</v>
-      </c>
-      <c r="T48" s="4" t="n">
-        <v>25.2</v>
-      </c>
+      <c r="S48" s="4" t="n"/>
+      <c r="T48" s="4" t="n"/>
       <c r="U48" s="4" t="n"/>
       <c r="V48" s="4" t="n"/>
       <c r="W48" s="4" t="n"/>
@@ -41014,10 +41086,10 @@
       <c r="AC48" s="4" t="n"/>
       <c r="AD48" s="4" t="n"/>
       <c r="AE48" s="4" t="n"/>
-      <c r="AF48" s="4" t="n">
+      <c r="AF48" s="4" t="n"/>
+      <c r="AG48" s="4" t="n">
         <v>25.8</v>
       </c>
-      <c r="AG48" s="4" t="n"/>
       <c r="AH48" s="4" t="n"/>
       <c r="AI48" s="4" t="n"/>
       <c r="AJ48" s="4" t="n"/>
@@ -41065,12 +41137,12 @@
       </c>
       <c r="L49" s="4" t="n"/>
       <c r="M49" s="4" t="n"/>
-      <c r="N49" s="4" t="n"/>
+      <c r="N49" s="4" t="n">
+        <v>30.79</v>
+      </c>
       <c r="O49" s="4" t="n"/>
       <c r="P49" s="4" t="n"/>
-      <c r="Q49" s="4" t="n">
-        <v>30.79</v>
-      </c>
+      <c r="Q49" s="4" t="n"/>
       <c r="R49" s="4" t="n"/>
       <c r="S49" s="4" t="n"/>
       <c r="T49" s="4" t="n"/>
@@ -41130,12 +41202,12 @@
       <c r="K50" s="4" t="n"/>
       <c r="L50" s="4" t="n"/>
       <c r="M50" s="4" t="n"/>
-      <c r="N50" s="4" t="n"/>
+      <c r="N50" s="4" t="n">
+        <v>26.67</v>
+      </c>
       <c r="O50" s="4" t="n"/>
       <c r="P50" s="4" t="n"/>
-      <c r="Q50" s="4" t="n">
-        <v>26.67</v>
-      </c>
+      <c r="Q50" s="4" t="n"/>
       <c r="R50" s="4" t="n"/>
       <c r="S50" s="4" t="n"/>
       <c r="T50" s="4" t="n"/>
@@ -41149,12 +41221,12 @@
       <c r="AB50" s="4" t="n"/>
       <c r="AC50" s="4" t="n"/>
       <c r="AD50" s="4" t="n"/>
-      <c r="AE50" s="4" t="n">
-        <v>27.09</v>
-      </c>
+      <c r="AE50" s="4" t="n"/>
       <c r="AF50" s="4" t="n"/>
       <c r="AG50" s="4" t="n"/>
-      <c r="AH50" s="4" t="n"/>
+      <c r="AH50" s="4" t="n">
+        <v>27.09</v>
+      </c>
       <c r="AI50" s="4" t="n"/>
       <c r="AJ50" s="4" t="n"/>
       <c r="AK50" s="4" t="n"/>
@@ -41195,12 +41267,12 @@
       <c r="K51" s="4" t="n"/>
       <c r="L51" s="4" t="n"/>
       <c r="M51" s="4" t="n"/>
-      <c r="N51" s="4" t="n"/>
+      <c r="N51" s="4" t="n">
+        <v>24.5</v>
+      </c>
       <c r="O51" s="4" t="n"/>
       <c r="P51" s="4" t="n"/>
-      <c r="Q51" s="4" t="n">
-        <v>24.5</v>
-      </c>
+      <c r="Q51" s="4" t="n"/>
       <c r="R51" s="4" t="n"/>
       <c r="S51" s="4" t="n"/>
       <c r="T51" s="4" t="n"/>
@@ -41272,21 +41344,21 @@
       <c r="K52" s="4" t="n"/>
       <c r="L52" s="4" t="n"/>
       <c r="M52" s="4" t="n"/>
-      <c r="N52" s="4" t="n">
-        <v>32.6</v>
-      </c>
+      <c r="N52" s="4" t="n"/>
       <c r="O52" s="4" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="P52" s="4" t="n">
-        <v>32.3</v>
-      </c>
+        <v>34.1</v>
+      </c>
+      <c r="P52" s="4" t="n"/>
       <c r="Q52" s="4" t="n"/>
       <c r="R52" s="4" t="n">
-        <v>34.1</v>
-      </c>
-      <c r="S52" s="4" t="n"/>
-      <c r="T52" s="4" t="n"/>
+        <v>32.6</v>
+      </c>
+      <c r="S52" s="4" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="T52" s="4" t="n">
+        <v>32.3</v>
+      </c>
       <c r="U52" s="4" t="n"/>
       <c r="V52" s="4" t="n"/>
       <c r="W52" s="4" t="n"/>
@@ -41491,12 +41563,12 @@
       <c r="K55" s="4" t="n"/>
       <c r="L55" s="4" t="n"/>
       <c r="M55" s="4" t="n"/>
-      <c r="N55" s="4" t="n"/>
+      <c r="N55" s="4" t="n">
+        <v>32.99</v>
+      </c>
       <c r="O55" s="4" t="n"/>
       <c r="P55" s="4" t="n"/>
-      <c r="Q55" s="4" t="n">
-        <v>32.99</v>
-      </c>
+      <c r="Q55" s="4" t="n"/>
       <c r="R55" s="4" t="n"/>
       <c r="S55" s="4" t="n"/>
       <c r="T55" s="4" t="n"/>
@@ -41510,12 +41582,12 @@
       <c r="AB55" s="4" t="n"/>
       <c r="AC55" s="4" t="n"/>
       <c r="AD55" s="4" t="n"/>
-      <c r="AE55" s="4" t="n">
-        <v>33.29</v>
-      </c>
+      <c r="AE55" s="4" t="n"/>
       <c r="AF55" s="4" t="n"/>
       <c r="AG55" s="4" t="n"/>
-      <c r="AH55" s="4" t="n"/>
+      <c r="AH55" s="4" t="n">
+        <v>33.29</v>
+      </c>
       <c r="AI55" s="4" t="n"/>
       <c r="AJ55" s="4" t="n"/>
       <c r="AK55" s="4" t="n"/>
@@ -41637,17 +41709,17 @@
         <v>35</v>
       </c>
       <c r="M57" s="4" t="n"/>
-      <c r="N57" s="4" t="n">
+      <c r="N57" s="4" t="n"/>
+      <c r="O57" s="4" t="n"/>
+      <c r="P57" s="4" t="n"/>
+      <c r="Q57" s="4" t="n"/>
+      <c r="R57" s="4" t="n">
         <v>36.4</v>
       </c>
-      <c r="O57" s="4" t="n"/>
-      <c r="P57" s="4" t="n">
+      <c r="S57" s="4" t="n"/>
+      <c r="T57" s="4" t="n">
         <v>36.19</v>
       </c>
-      <c r="Q57" s="4" t="n"/>
-      <c r="R57" s="4" t="n"/>
-      <c r="S57" s="4" t="n"/>
-      <c r="T57" s="4" t="n"/>
       <c r="U57" s="4" t="n">
         <v>37.29</v>
       </c>
@@ -41713,12 +41785,12 @@
       <c r="L58" s="4" t="n"/>
       <c r="M58" s="4" t="n"/>
       <c r="N58" s="4" t="n"/>
-      <c r="O58" s="4" t="n"/>
+      <c r="O58" s="4" t="n">
+        <v>26.8</v>
+      </c>
       <c r="P58" s="4" t="n"/>
       <c r="Q58" s="4" t="n"/>
-      <c r="R58" s="4" t="n">
-        <v>26.8</v>
-      </c>
+      <c r="R58" s="4" t="n"/>
       <c r="S58" s="4" t="n"/>
       <c r="T58" s="4" t="n"/>
       <c r="U58" s="4" t="n"/>
@@ -41781,12 +41853,12 @@
       <c r="K59" s="4" t="n"/>
       <c r="L59" s="4" t="n"/>
       <c r="M59" s="4" t="n"/>
-      <c r="N59" s="4" t="n"/>
+      <c r="N59" s="4" t="n">
+        <v>21.35</v>
+      </c>
       <c r="O59" s="4" t="n"/>
       <c r="P59" s="4" t="n"/>
-      <c r="Q59" s="4" t="n">
-        <v>21.35</v>
-      </c>
+      <c r="Q59" s="4" t="n"/>
       <c r="R59" s="4" t="n"/>
       <c r="S59" s="4" t="n"/>
       <c r="T59" s="4" t="n"/>
@@ -41801,11 +41873,11 @@
       <c r="AC59" s="4" t="n"/>
       <c r="AD59" s="4" t="n"/>
       <c r="AE59" s="4" t="n"/>
-      <c r="AF59" s="4" t="n"/>
+      <c r="AF59" s="4" t="n">
+        <v>21.45</v>
+      </c>
       <c r="AG59" s="4" t="n"/>
-      <c r="AH59" s="4" t="n">
-        <v>21.45</v>
-      </c>
+      <c r="AH59" s="4" t="n"/>
       <c r="AI59" s="4" t="n"/>
       <c r="AJ59" s="4" t="n"/>
       <c r="AK59" s="4" t="n"/>
@@ -41927,12 +41999,12 @@
       <c r="K61" s="4" t="n"/>
       <c r="L61" s="4" t="n"/>
       <c r="M61" s="4" t="n"/>
-      <c r="N61" s="4" t="n"/>
+      <c r="N61" s="4" t="n">
+        <v>21.89</v>
+      </c>
       <c r="O61" s="4" t="n"/>
       <c r="P61" s="4" t="n"/>
-      <c r="Q61" s="4" t="n">
-        <v>21.89</v>
-      </c>
+      <c r="Q61" s="4" t="n"/>
       <c r="R61" s="4" t="n"/>
       <c r="S61" s="4" t="n"/>
       <c r="T61" s="4" t="n"/>
@@ -41998,19 +42070,19 @@
       <c r="M62" s="4" t="n">
         <v>31.1</v>
       </c>
-      <c r="N62" s="4" t="n"/>
-      <c r="O62" s="4" t="n"/>
+      <c r="N62" s="4" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="O62" s="4" t="n">
+        <v>32.09</v>
+      </c>
       <c r="P62" s="4" t="n"/>
       <c r="Q62" s="4" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="R62" s="4" t="n">
-        <v>32.45</v>
-      </c>
+        <v>31.29</v>
+      </c>